--- a/assets/data/bcv/excel/ove_bcv_pib_sector_institucional_anual.xlsx
+++ b/assets/data/bcv/excel/ove_bcv_pib_sector_institucional_anual.xlsx
@@ -736,7 +736,7 @@
       </c>
       <c r="S7" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T22:27:02Z</t>
+          <t>2026-09-13T22:31:32Z</t>
         </is>
       </c>
     </row>
@@ -821,7 +821,7 @@
       </c>
       <c r="S8" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T22:27:02Z</t>
+          <t>2026-09-13T22:31:32Z</t>
         </is>
       </c>
     </row>
@@ -906,7 +906,7 @@
       </c>
       <c r="S9" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T22:27:02Z</t>
+          <t>2026-09-13T22:31:32Z</t>
         </is>
       </c>
     </row>
@@ -991,7 +991,7 @@
       </c>
       <c r="S10" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T22:27:02Z</t>
+          <t>2026-09-13T22:31:32Z</t>
         </is>
       </c>
     </row>
@@ -1076,7 +1076,7 @@
       </c>
       <c r="S11" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T22:27:02Z</t>
+          <t>2026-09-13T22:31:32Z</t>
         </is>
       </c>
     </row>
@@ -1161,7 +1161,7 @@
       </c>
       <c r="S12" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T22:27:02Z</t>
+          <t>2026-09-13T22:31:32Z</t>
         </is>
       </c>
     </row>
@@ -1246,7 +1246,7 @@
       </c>
       <c r="S13" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T22:27:02Z</t>
+          <t>2026-09-13T22:31:32Z</t>
         </is>
       </c>
     </row>
@@ -1331,7 +1331,7 @@
       </c>
       <c r="S14" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T22:27:02Z</t>
+          <t>2026-09-13T22:31:32Z</t>
         </is>
       </c>
     </row>
@@ -1416,7 +1416,7 @@
       </c>
       <c r="S15" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T22:27:02Z</t>
+          <t>2026-09-13T22:31:32Z</t>
         </is>
       </c>
     </row>
@@ -1501,7 +1501,7 @@
       </c>
       <c r="S16" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T22:27:02Z</t>
+          <t>2026-09-13T22:31:32Z</t>
         </is>
       </c>
     </row>
@@ -1586,7 +1586,7 @@
       </c>
       <c r="S17" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T22:27:02Z</t>
+          <t>2026-09-13T22:31:32Z</t>
         </is>
       </c>
     </row>
@@ -1671,7 +1671,7 @@
       </c>
       <c r="S18" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T22:27:02Z</t>
+          <t>2026-09-13T22:31:32Z</t>
         </is>
       </c>
     </row>
@@ -1756,7 +1756,7 @@
       </c>
       <c r="S19" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T22:27:02Z</t>
+          <t>2026-09-13T22:31:32Z</t>
         </is>
       </c>
     </row>
@@ -1841,7 +1841,7 @@
       </c>
       <c r="S20" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T22:27:02Z</t>
+          <t>2026-09-13T22:31:32Z</t>
         </is>
       </c>
     </row>
@@ -1926,7 +1926,7 @@
       </c>
       <c r="S21" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T22:27:02Z</t>
+          <t>2026-09-13T22:31:32Z</t>
         </is>
       </c>
     </row>
@@ -2011,7 +2011,7 @@
       </c>
       <c r="S22" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T22:27:02Z</t>
+          <t>2026-09-13T22:31:32Z</t>
         </is>
       </c>
     </row>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="S23" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T22:27:02Z</t>
+          <t>2026-09-13T22:31:32Z</t>
         </is>
       </c>
     </row>
@@ -2181,7 +2181,7 @@
       </c>
       <c r="S24" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T22:27:02Z</t>
+          <t>2026-09-13T22:31:32Z</t>
         </is>
       </c>
     </row>
@@ -2266,7 +2266,7 @@
       </c>
       <c r="S25" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T22:27:02Z</t>
+          <t>2026-09-13T22:31:32Z</t>
         </is>
       </c>
     </row>
@@ -2351,7 +2351,7 @@
       </c>
       <c r="S26" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T22:27:02Z</t>
+          <t>2026-09-13T22:31:32Z</t>
         </is>
       </c>
     </row>
@@ -2436,7 +2436,7 @@
       </c>
       <c r="S27" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T22:27:02Z</t>
+          <t>2026-09-13T22:31:32Z</t>
         </is>
       </c>
     </row>
@@ -2525,7 +2525,7 @@
       </c>
       <c r="S28" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T22:27:02Z</t>
+          <t>2026-09-13T22:31:32Z</t>
         </is>
       </c>
     </row>
@@ -2614,7 +2614,7 @@
       </c>
       <c r="S29" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T22:27:02Z</t>
+          <t>2026-09-13T22:31:32Z</t>
         </is>
       </c>
     </row>
@@ -2699,7 +2699,7 @@
       </c>
       <c r="S30" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T22:27:02Z</t>
+          <t>2026-09-13T22:31:32Z</t>
         </is>
       </c>
     </row>
@@ -2788,7 +2788,7 @@
       </c>
       <c r="S31" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T22:27:02Z</t>
+          <t>2026-09-13T22:31:32Z</t>
         </is>
       </c>
     </row>
@@ -2877,7 +2877,7 @@
       </c>
       <c r="S32" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T22:27:02Z</t>
+          <t>2026-09-13T22:31:32Z</t>
         </is>
       </c>
     </row>
@@ -2962,7 +2962,7 @@
       </c>
       <c r="S33" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T22:27:02Z</t>
+          <t>2026-09-13T22:31:32Z</t>
         </is>
       </c>
     </row>
@@ -3051,7 +3051,7 @@
       </c>
       <c r="S34" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T22:27:02Z</t>
+          <t>2026-09-13T22:31:32Z</t>
         </is>
       </c>
     </row>
@@ -3140,7 +3140,7 @@
       </c>
       <c r="S35" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T22:27:02Z</t>
+          <t>2026-09-13T22:31:32Z</t>
         </is>
       </c>
     </row>
@@ -3225,7 +3225,7 @@
       </c>
       <c r="S36" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T22:27:02Z</t>
+          <t>2026-09-13T22:31:32Z</t>
         </is>
       </c>
     </row>
@@ -3314,7 +3314,7 @@
       </c>
       <c r="S37" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T22:27:02Z</t>
+          <t>2026-09-13T22:31:32Z</t>
         </is>
       </c>
     </row>
@@ -3403,7 +3403,7 @@
       </c>
       <c r="S38" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T22:27:02Z</t>
+          <t>2026-09-13T22:31:32Z</t>
         </is>
       </c>
     </row>
@@ -3488,7 +3488,7 @@
       </c>
       <c r="S39" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T22:27:02Z</t>
+          <t>2026-09-13T22:31:32Z</t>
         </is>
       </c>
     </row>
@@ -3577,7 +3577,7 @@
       </c>
       <c r="S40" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T22:27:02Z</t>
+          <t>2026-09-13T22:31:32Z</t>
         </is>
       </c>
     </row>
@@ -3666,7 +3666,7 @@
       </c>
       <c r="S41" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T22:27:02Z</t>
+          <t>2026-09-13T22:31:32Z</t>
         </is>
       </c>
     </row>
@@ -3751,7 +3751,7 @@
       </c>
       <c r="S42" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T22:27:02Z</t>
+          <t>2026-09-13T22:31:32Z</t>
         </is>
       </c>
     </row>
@@ -3840,7 +3840,7 @@
       </c>
       <c r="S43" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T22:27:02Z</t>
+          <t>2026-09-13T22:31:32Z</t>
         </is>
       </c>
     </row>
@@ -3929,7 +3929,7 @@
       </c>
       <c r="S44" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T22:27:02Z</t>
+          <t>2026-09-13T22:31:32Z</t>
         </is>
       </c>
     </row>
@@ -4014,7 +4014,7 @@
       </c>
       <c r="S45" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T22:27:02Z</t>
+          <t>2026-09-13T22:31:32Z</t>
         </is>
       </c>
     </row>
@@ -4103,7 +4103,7 @@
       </c>
       <c r="S46" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T22:27:02Z</t>
+          <t>2026-09-13T22:31:32Z</t>
         </is>
       </c>
     </row>
@@ -4192,7 +4192,7 @@
       </c>
       <c r="S47" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T22:27:02Z</t>
+          <t>2026-09-13T22:31:32Z</t>
         </is>
       </c>
     </row>
@@ -4277,7 +4277,7 @@
       </c>
       <c r="S48" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T22:27:02Z</t>
+          <t>2026-09-13T22:31:32Z</t>
         </is>
       </c>
     </row>
@@ -4366,7 +4366,7 @@
       </c>
       <c r="S49" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T22:27:02Z</t>
+          <t>2026-09-13T22:31:32Z</t>
         </is>
       </c>
     </row>
@@ -4455,7 +4455,7 @@
       </c>
       <c r="S50" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T22:27:02Z</t>
+          <t>2026-09-13T22:31:32Z</t>
         </is>
       </c>
     </row>
@@ -4540,7 +4540,7 @@
       </c>
       <c r="S51" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T22:27:02Z</t>
+          <t>2026-09-13T22:31:32Z</t>
         </is>
       </c>
     </row>
@@ -4629,7 +4629,7 @@
       </c>
       <c r="S52" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T22:27:02Z</t>
+          <t>2026-09-13T22:31:32Z</t>
         </is>
       </c>
     </row>
@@ -4718,7 +4718,7 @@
       </c>
       <c r="S53" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T22:27:02Z</t>
+          <t>2026-09-13T22:31:32Z</t>
         </is>
       </c>
     </row>
@@ -4803,7 +4803,7 @@
       </c>
       <c r="S54" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T22:27:02Z</t>
+          <t>2026-09-13T22:31:32Z</t>
         </is>
       </c>
     </row>
@@ -4892,7 +4892,7 @@
       </c>
       <c r="S55" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T22:27:02Z</t>
+          <t>2026-09-13T22:31:32Z</t>
         </is>
       </c>
     </row>
@@ -4981,7 +4981,7 @@
       </c>
       <c r="S56" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T22:27:02Z</t>
+          <t>2026-09-13T22:31:32Z</t>
         </is>
       </c>
     </row>
@@ -5070,7 +5070,7 @@
       </c>
       <c r="S57" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T22:27:02Z</t>
+          <t>2026-09-13T22:31:32Z</t>
         </is>
       </c>
     </row>
@@ -5159,7 +5159,7 @@
       </c>
       <c r="S58" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T22:27:02Z</t>
+          <t>2026-09-13T22:31:32Z</t>
         </is>
       </c>
     </row>
@@ -5248,7 +5248,7 @@
       </c>
       <c r="S59" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T22:27:02Z</t>
+          <t>2026-09-13T22:31:32Z</t>
         </is>
       </c>
     </row>
@@ -5337,7 +5337,7 @@
       </c>
       <c r="S60" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T22:27:02Z</t>
+          <t>2026-09-13T22:31:32Z</t>
         </is>
       </c>
     </row>
@@ -5426,7 +5426,7 @@
       </c>
       <c r="S61" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T22:27:02Z</t>
+          <t>2026-09-13T22:31:32Z</t>
         </is>
       </c>
     </row>
@@ -5515,7 +5515,7 @@
       </c>
       <c r="S62" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T22:27:02Z</t>
+          <t>2026-09-13T22:31:32Z</t>
         </is>
       </c>
     </row>
@@ -5604,7 +5604,7 @@
       </c>
       <c r="S63" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T22:27:02Z</t>
+          <t>2026-09-13T22:31:32Z</t>
         </is>
       </c>
     </row>
@@ -5693,7 +5693,7 @@
       </c>
       <c r="S64" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T22:27:02Z</t>
+          <t>2026-09-13T22:31:32Z</t>
         </is>
       </c>
     </row>
@@ -5782,7 +5782,7 @@
       </c>
       <c r="S65" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T22:27:02Z</t>
+          <t>2026-09-13T22:31:32Z</t>
         </is>
       </c>
     </row>
@@ -5871,7 +5871,7 @@
       </c>
       <c r="S66" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T22:27:02Z</t>
+          <t>2026-09-13T22:31:32Z</t>
         </is>
       </c>
     </row>
@@ -5960,7 +5960,7 @@
       </c>
       <c r="S67" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T22:27:02Z</t>
+          <t>2026-09-13T22:31:32Z</t>
         </is>
       </c>
     </row>
@@ -6045,7 +6045,7 @@
       </c>
       <c r="S68" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T22:27:02Z</t>
+          <t>2026-09-13T22:31:32Z</t>
         </is>
       </c>
     </row>
@@ -6130,7 +6130,7 @@
       </c>
       <c r="S69" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T22:27:02Z</t>
+          <t>2026-09-13T22:31:32Z</t>
         </is>
       </c>
     </row>
@@ -6215,7 +6215,7 @@
       </c>
       <c r="S70" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T22:27:02Z</t>
+          <t>2026-09-13T22:31:32Z</t>
         </is>
       </c>
     </row>
@@ -6300,7 +6300,7 @@
       </c>
       <c r="S71" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T22:27:02Z</t>
+          <t>2026-09-13T22:31:32Z</t>
         </is>
       </c>
     </row>
@@ -6385,7 +6385,7 @@
       </c>
       <c r="S72" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T22:27:02Z</t>
+          <t>2026-09-13T22:31:32Z</t>
         </is>
       </c>
     </row>
@@ -6470,7 +6470,7 @@
       </c>
       <c r="S73" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T22:27:02Z</t>
+          <t>2026-09-13T22:31:32Z</t>
         </is>
       </c>
     </row>
@@ -6555,7 +6555,7 @@
       </c>
       <c r="S74" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T22:27:02Z</t>
+          <t>2026-09-13T22:31:32Z</t>
         </is>
       </c>
     </row>
@@ -6640,7 +6640,7 @@
       </c>
       <c r="S75" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T22:27:02Z</t>
+          <t>2026-09-13T22:31:32Z</t>
         </is>
       </c>
     </row>
@@ -6725,7 +6725,7 @@
       </c>
       <c r="S76" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T22:27:02Z</t>
+          <t>2026-09-13T22:31:32Z</t>
         </is>
       </c>
     </row>
@@ -6810,7 +6810,7 @@
       </c>
       <c r="S77" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T22:27:02Z</t>
+          <t>2026-09-13T22:31:32Z</t>
         </is>
       </c>
     </row>
@@ -6895,7 +6895,7 @@
       </c>
       <c r="S78" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T22:27:02Z</t>
+          <t>2026-09-13T22:31:32Z</t>
         </is>
       </c>
     </row>
@@ -6980,7 +6980,7 @@
       </c>
       <c r="S79" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T22:27:02Z</t>
+          <t>2026-09-13T22:31:32Z</t>
         </is>
       </c>
     </row>
@@ -7065,7 +7065,7 @@
       </c>
       <c r="S80" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T22:27:02Z</t>
+          <t>2026-09-13T22:31:32Z</t>
         </is>
       </c>
     </row>
@@ -7150,7 +7150,7 @@
       </c>
       <c r="S81" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T22:27:02Z</t>
+          <t>2026-09-13T22:31:32Z</t>
         </is>
       </c>
     </row>
@@ -7235,7 +7235,7 @@
       </c>
       <c r="S82" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T22:27:02Z</t>
+          <t>2026-09-13T22:31:32Z</t>
         </is>
       </c>
     </row>
@@ -7320,7 +7320,7 @@
       </c>
       <c r="S83" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T22:27:02Z</t>
+          <t>2026-09-13T22:31:32Z</t>
         </is>
       </c>
     </row>
@@ -7405,7 +7405,7 @@
       </c>
       <c r="S84" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T22:27:02Z</t>
+          <t>2026-09-13T22:31:32Z</t>
         </is>
       </c>
     </row>
@@ -7490,7 +7490,7 @@
       </c>
       <c r="S85" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T22:27:02Z</t>
+          <t>2026-09-13T22:31:32Z</t>
         </is>
       </c>
     </row>
@@ -7575,7 +7575,7 @@
       </c>
       <c r="S86" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T22:27:02Z</t>
+          <t>2026-09-13T22:31:32Z</t>
         </is>
       </c>
     </row>
@@ -7660,7 +7660,7 @@
       </c>
       <c r="S87" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T22:27:02Z</t>
+          <t>2026-09-13T22:31:32Z</t>
         </is>
       </c>
     </row>
@@ -7745,7 +7745,7 @@
       </c>
       <c r="S88" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T22:27:02Z</t>
+          <t>2026-09-13T22:31:32Z</t>
         </is>
       </c>
     </row>
@@ -7834,7 +7834,7 @@
       </c>
       <c r="S89" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T22:27:02Z</t>
+          <t>2026-09-13T22:31:32Z</t>
         </is>
       </c>
     </row>
@@ -7923,7 +7923,7 @@
       </c>
       <c r="S90" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T22:27:02Z</t>
+          <t>2026-09-13T22:31:32Z</t>
         </is>
       </c>
     </row>
@@ -8008,7 +8008,7 @@
       </c>
       <c r="S91" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T22:27:02Z</t>
+          <t>2026-09-13T22:31:32Z</t>
         </is>
       </c>
     </row>
@@ -8097,7 +8097,7 @@
       </c>
       <c r="S92" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T22:27:02Z</t>
+          <t>2026-09-13T22:31:32Z</t>
         </is>
       </c>
     </row>
@@ -8186,7 +8186,7 @@
       </c>
       <c r="S93" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T22:27:02Z</t>
+          <t>2026-09-13T22:31:32Z</t>
         </is>
       </c>
     </row>
@@ -8271,7 +8271,7 @@
       </c>
       <c r="S94" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T22:27:02Z</t>
+          <t>2026-09-13T22:31:32Z</t>
         </is>
       </c>
     </row>
@@ -8360,7 +8360,7 @@
       </c>
       <c r="S95" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T22:27:02Z</t>
+          <t>2026-09-13T22:31:32Z</t>
         </is>
       </c>
     </row>
@@ -8449,7 +8449,7 @@
       </c>
       <c r="S96" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T22:27:02Z</t>
+          <t>2026-09-13T22:31:32Z</t>
         </is>
       </c>
     </row>
@@ -8534,7 +8534,7 @@
       </c>
       <c r="S97" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T22:27:02Z</t>
+          <t>2026-09-13T22:31:32Z</t>
         </is>
       </c>
     </row>
@@ -8623,7 +8623,7 @@
       </c>
       <c r="S98" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T22:27:02Z</t>
+          <t>2026-09-13T22:31:32Z</t>
         </is>
       </c>
     </row>
@@ -8712,7 +8712,7 @@
       </c>
       <c r="S99" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T22:27:02Z</t>
+          <t>2026-09-13T22:31:32Z</t>
         </is>
       </c>
     </row>
@@ -8797,7 +8797,7 @@
       </c>
       <c r="S100" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T22:27:02Z</t>
+          <t>2026-09-13T22:31:32Z</t>
         </is>
       </c>
     </row>
@@ -8886,7 +8886,7 @@
       </c>
       <c r="S101" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T22:27:02Z</t>
+          <t>2026-09-13T22:31:32Z</t>
         </is>
       </c>
     </row>
@@ -8975,7 +8975,7 @@
       </c>
       <c r="S102" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T22:27:02Z</t>
+          <t>2026-09-13T22:31:32Z</t>
         </is>
       </c>
     </row>
@@ -9060,7 +9060,7 @@
       </c>
       <c r="S103" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T22:27:02Z</t>
+          <t>2026-09-13T22:31:32Z</t>
         </is>
       </c>
     </row>
@@ -9149,7 +9149,7 @@
       </c>
       <c r="S104" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T22:27:02Z</t>
+          <t>2026-09-13T22:31:32Z</t>
         </is>
       </c>
     </row>
@@ -9238,7 +9238,7 @@
       </c>
       <c r="S105" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T22:27:02Z</t>
+          <t>2026-09-13T22:31:32Z</t>
         </is>
       </c>
     </row>
@@ -9323,7 +9323,7 @@
       </c>
       <c r="S106" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T22:27:02Z</t>
+          <t>2026-09-13T22:31:32Z</t>
         </is>
       </c>
     </row>
@@ -9412,7 +9412,7 @@
       </c>
       <c r="S107" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T22:27:02Z</t>
+          <t>2026-09-13T22:31:32Z</t>
         </is>
       </c>
     </row>
@@ -9501,7 +9501,7 @@
       </c>
       <c r="S108" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T22:27:02Z</t>
+          <t>2026-09-13T22:31:32Z</t>
         </is>
       </c>
     </row>
@@ -9586,7 +9586,7 @@
       </c>
       <c r="S109" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T22:27:02Z</t>
+          <t>2026-09-13T22:31:32Z</t>
         </is>
       </c>
     </row>
@@ -9675,7 +9675,7 @@
       </c>
       <c r="S110" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T22:27:02Z</t>
+          <t>2026-09-13T22:31:32Z</t>
         </is>
       </c>
     </row>
@@ -9764,7 +9764,7 @@
       </c>
       <c r="S111" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T22:27:02Z</t>
+          <t>2026-09-13T22:31:32Z</t>
         </is>
       </c>
     </row>
@@ -9849,7 +9849,7 @@
       </c>
       <c r="S112" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T22:27:02Z</t>
+          <t>2026-09-13T22:31:32Z</t>
         </is>
       </c>
     </row>
@@ -9938,7 +9938,7 @@
       </c>
       <c r="S113" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T22:27:02Z</t>
+          <t>2026-09-13T22:31:32Z</t>
         </is>
       </c>
     </row>
@@ -10027,7 +10027,7 @@
       </c>
       <c r="S114" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T22:27:02Z</t>
+          <t>2026-09-13T22:31:32Z</t>
         </is>
       </c>
     </row>
@@ -10112,7 +10112,7 @@
       </c>
       <c r="S115" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T22:27:02Z</t>
+          <t>2026-09-13T22:31:32Z</t>
         </is>
       </c>
     </row>
@@ -10201,7 +10201,7 @@
       </c>
       <c r="S116" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T22:27:02Z</t>
+          <t>2026-09-13T22:31:32Z</t>
         </is>
       </c>
     </row>
@@ -10290,7 +10290,7 @@
       </c>
       <c r="S117" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T22:27:02Z</t>
+          <t>2026-09-13T22:31:32Z</t>
         </is>
       </c>
     </row>
@@ -10379,7 +10379,7 @@
       </c>
       <c r="S118" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T22:27:02Z</t>
+          <t>2026-09-13T22:31:32Z</t>
         </is>
       </c>
     </row>
@@ -10468,7 +10468,7 @@
       </c>
       <c r="S119" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T22:27:02Z</t>
+          <t>2026-09-13T22:31:32Z</t>
         </is>
       </c>
     </row>
@@ -10557,7 +10557,7 @@
       </c>
       <c r="S120" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T22:27:02Z</t>
+          <t>2026-09-13T22:31:32Z</t>
         </is>
       </c>
     </row>
@@ -10646,7 +10646,7 @@
       </c>
       <c r="S121" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T22:27:02Z</t>
+          <t>2026-09-13T22:31:32Z</t>
         </is>
       </c>
     </row>
@@ -10735,7 +10735,7 @@
       </c>
       <c r="S122" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T22:27:02Z</t>
+          <t>2026-09-13T22:31:32Z</t>
         </is>
       </c>
     </row>
@@ -10824,7 +10824,7 @@
       </c>
       <c r="S123" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T22:27:02Z</t>
+          <t>2026-09-13T22:31:32Z</t>
         </is>
       </c>
     </row>
@@ -10913,7 +10913,7 @@
       </c>
       <c r="S124" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T22:27:02Z</t>
+          <t>2026-09-13T22:31:32Z</t>
         </is>
       </c>
     </row>
@@ -11002,7 +11002,7 @@
       </c>
       <c r="S125" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T22:27:02Z</t>
+          <t>2026-09-13T22:31:32Z</t>
         </is>
       </c>
     </row>
@@ -11091,7 +11091,7 @@
       </c>
       <c r="S126" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T22:27:02Z</t>
+          <t>2026-09-13T22:31:32Z</t>
         </is>
       </c>
     </row>
@@ -11180,7 +11180,7 @@
       </c>
       <c r="S127" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T22:27:02Z</t>
+          <t>2026-09-13T22:31:32Z</t>
         </is>
       </c>
     </row>
@@ -11269,7 +11269,7 @@
       </c>
       <c r="S128" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T22:27:02Z</t>
+          <t>2026-09-13T22:31:32Z</t>
         </is>
       </c>
     </row>
@@ -11354,7 +11354,7 @@
       </c>
       <c r="S129" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T22:27:02Z</t>
+          <t>2026-09-13T22:31:32Z</t>
         </is>
       </c>
     </row>
@@ -11439,7 +11439,7 @@
       </c>
       <c r="S130" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T22:27:02Z</t>
+          <t>2026-09-13T22:31:32Z</t>
         </is>
       </c>
     </row>
@@ -11524,7 +11524,7 @@
       </c>
       <c r="S131" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T22:27:02Z</t>
+          <t>2026-09-13T22:31:32Z</t>
         </is>
       </c>
     </row>
@@ -11609,7 +11609,7 @@
       </c>
       <c r="S132" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T22:27:02Z</t>
+          <t>2026-09-13T22:31:32Z</t>
         </is>
       </c>
     </row>
@@ -11694,7 +11694,7 @@
       </c>
       <c r="S133" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T22:27:02Z</t>
+          <t>2026-09-13T22:31:32Z</t>
         </is>
       </c>
     </row>
@@ -11779,7 +11779,7 @@
       </c>
       <c r="S134" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T22:27:02Z</t>
+          <t>2026-09-13T22:31:32Z</t>
         </is>
       </c>
     </row>
@@ -11864,7 +11864,7 @@
       </c>
       <c r="S135" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T22:27:02Z</t>
+          <t>2026-09-13T22:31:32Z</t>
         </is>
       </c>
     </row>
@@ -11949,7 +11949,7 @@
       </c>
       <c r="S136" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T22:27:02Z</t>
+          <t>2026-09-13T22:31:32Z</t>
         </is>
       </c>
     </row>
@@ -12034,7 +12034,7 @@
       </c>
       <c r="S137" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T22:27:02Z</t>
+          <t>2026-09-13T22:31:32Z</t>
         </is>
       </c>
     </row>
@@ -12119,7 +12119,7 @@
       </c>
       <c r="S138" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T22:27:02Z</t>
+          <t>2026-09-13T22:31:32Z</t>
         </is>
       </c>
     </row>
@@ -12204,7 +12204,7 @@
       </c>
       <c r="S139" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T22:27:02Z</t>
+          <t>2026-09-13T22:31:32Z</t>
         </is>
       </c>
     </row>
@@ -12289,7 +12289,7 @@
       </c>
       <c r="S140" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T22:27:02Z</t>
+          <t>2026-09-13T22:31:32Z</t>
         </is>
       </c>
     </row>
@@ -12374,7 +12374,7 @@
       </c>
       <c r="S141" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T22:27:02Z</t>
+          <t>2026-09-13T22:31:32Z</t>
         </is>
       </c>
     </row>
@@ -12459,7 +12459,7 @@
       </c>
       <c r="S142" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T22:27:02Z</t>
+          <t>2026-09-13T22:31:32Z</t>
         </is>
       </c>
     </row>
@@ -12544,7 +12544,7 @@
       </c>
       <c r="S143" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T22:27:02Z</t>
+          <t>2026-09-13T22:31:32Z</t>
         </is>
       </c>
     </row>
@@ -12629,7 +12629,7 @@
       </c>
       <c r="S144" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T22:27:02Z</t>
+          <t>2026-09-13T22:31:32Z</t>
         </is>
       </c>
     </row>
@@ -12714,7 +12714,7 @@
       </c>
       <c r="S145" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T22:27:02Z</t>
+          <t>2026-09-13T22:31:32Z</t>
         </is>
       </c>
     </row>
@@ -12799,7 +12799,7 @@
       </c>
       <c r="S146" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T22:27:02Z</t>
+          <t>2026-09-13T22:31:32Z</t>
         </is>
       </c>
     </row>
@@ -12884,7 +12884,7 @@
       </c>
       <c r="S147" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T22:27:02Z</t>
+          <t>2026-09-13T22:31:32Z</t>
         </is>
       </c>
     </row>
@@ -12969,7 +12969,7 @@
       </c>
       <c r="S148" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T22:27:02Z</t>
+          <t>2026-09-13T22:31:32Z</t>
         </is>
       </c>
     </row>
@@ -13054,7 +13054,7 @@
       </c>
       <c r="S149" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T22:27:02Z</t>
+          <t>2026-09-13T22:31:32Z</t>
         </is>
       </c>
     </row>
@@ -13143,7 +13143,7 @@
       </c>
       <c r="S150" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T22:27:02Z</t>
+          <t>2026-09-13T22:31:32Z</t>
         </is>
       </c>
     </row>
@@ -13232,7 +13232,7 @@
       </c>
       <c r="S151" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T22:27:02Z</t>
+          <t>2026-09-13T22:31:32Z</t>
         </is>
       </c>
     </row>
@@ -13317,7 +13317,7 @@
       </c>
       <c r="S152" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T22:27:02Z</t>
+          <t>2026-09-13T22:31:32Z</t>
         </is>
       </c>
     </row>
@@ -13406,7 +13406,7 @@
       </c>
       <c r="S153" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T22:27:02Z</t>
+          <t>2026-09-13T22:31:32Z</t>
         </is>
       </c>
     </row>
@@ -13495,7 +13495,7 @@
       </c>
       <c r="S154" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T22:27:02Z</t>
+          <t>2026-09-13T22:31:32Z</t>
         </is>
       </c>
     </row>
@@ -13580,7 +13580,7 @@
       </c>
       <c r="S155" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T22:27:02Z</t>
+          <t>2026-09-13T22:31:32Z</t>
         </is>
       </c>
     </row>
@@ -13669,7 +13669,7 @@
       </c>
       <c r="S156" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T22:27:02Z</t>
+          <t>2026-09-13T22:31:32Z</t>
         </is>
       </c>
     </row>
@@ -13758,7 +13758,7 @@
       </c>
       <c r="S157" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T22:27:02Z</t>
+          <t>2026-09-13T22:31:32Z</t>
         </is>
       </c>
     </row>
@@ -13843,7 +13843,7 @@
       </c>
       <c r="S158" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T22:27:02Z</t>
+          <t>2026-09-13T22:31:32Z</t>
         </is>
       </c>
     </row>
@@ -13932,7 +13932,7 @@
       </c>
       <c r="S159" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T22:27:02Z</t>
+          <t>2026-09-13T22:31:32Z</t>
         </is>
       </c>
     </row>
@@ -14021,7 +14021,7 @@
       </c>
       <c r="S160" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T22:27:02Z</t>
+          <t>2026-09-13T22:31:32Z</t>
         </is>
       </c>
     </row>
@@ -14106,7 +14106,7 @@
       </c>
       <c r="S161" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T22:27:02Z</t>
+          <t>2026-09-13T22:31:32Z</t>
         </is>
       </c>
     </row>
@@ -14195,7 +14195,7 @@
       </c>
       <c r="S162" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T22:27:02Z</t>
+          <t>2026-09-13T22:31:32Z</t>
         </is>
       </c>
     </row>
@@ -14284,7 +14284,7 @@
       </c>
       <c r="S163" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T22:27:02Z</t>
+          <t>2026-09-13T22:31:32Z</t>
         </is>
       </c>
     </row>
@@ -14369,7 +14369,7 @@
       </c>
       <c r="S164" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T22:27:02Z</t>
+          <t>2026-09-13T22:31:32Z</t>
         </is>
       </c>
     </row>
@@ -14458,7 +14458,7 @@
       </c>
       <c r="S165" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T22:27:02Z</t>
+          <t>2026-09-13T22:31:32Z</t>
         </is>
       </c>
     </row>
@@ -14547,7 +14547,7 @@
       </c>
       <c r="S166" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T22:27:02Z</t>
+          <t>2026-09-13T22:31:32Z</t>
         </is>
       </c>
     </row>
@@ -14632,7 +14632,7 @@
       </c>
       <c r="S167" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T22:27:02Z</t>
+          <t>2026-09-13T22:31:32Z</t>
         </is>
       </c>
     </row>
@@ -14721,7 +14721,7 @@
       </c>
       <c r="S168" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T22:27:02Z</t>
+          <t>2026-09-13T22:31:32Z</t>
         </is>
       </c>
     </row>
@@ -14810,7 +14810,7 @@
       </c>
       <c r="S169" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T22:27:02Z</t>
+          <t>2026-09-13T22:31:32Z</t>
         </is>
       </c>
     </row>
@@ -14895,7 +14895,7 @@
       </c>
       <c r="S170" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T22:27:02Z</t>
+          <t>2026-09-13T22:31:32Z</t>
         </is>
       </c>
     </row>
@@ -14984,7 +14984,7 @@
       </c>
       <c r="S171" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T22:27:02Z</t>
+          <t>2026-09-13T22:31:32Z</t>
         </is>
       </c>
     </row>
@@ -15073,7 +15073,7 @@
       </c>
       <c r="S172" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T22:27:02Z</t>
+          <t>2026-09-13T22:31:32Z</t>
         </is>
       </c>
     </row>
@@ -15158,7 +15158,7 @@
       </c>
       <c r="S173" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T22:27:02Z</t>
+          <t>2026-09-13T22:31:32Z</t>
         </is>
       </c>
     </row>
@@ -15247,7 +15247,7 @@
       </c>
       <c r="S174" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T22:27:02Z</t>
+          <t>2026-09-13T22:31:32Z</t>
         </is>
       </c>
     </row>
@@ -15336,7 +15336,7 @@
       </c>
       <c r="S175" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T22:27:02Z</t>
+          <t>2026-09-13T22:31:32Z</t>
         </is>
       </c>
     </row>
@@ -15421,7 +15421,7 @@
       </c>
       <c r="S176" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T22:27:02Z</t>
+          <t>2026-09-13T22:31:32Z</t>
         </is>
       </c>
     </row>
@@ -15510,7 +15510,7 @@
       </c>
       <c r="S177" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T22:27:02Z</t>
+          <t>2026-09-13T22:31:32Z</t>
         </is>
       </c>
     </row>
@@ -15599,7 +15599,7 @@
       </c>
       <c r="S178" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T22:27:02Z</t>
+          <t>2026-09-13T22:31:32Z</t>
         </is>
       </c>
     </row>
@@ -15688,7 +15688,7 @@
       </c>
       <c r="S179" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T22:27:02Z</t>
+          <t>2026-09-13T22:31:32Z</t>
         </is>
       </c>
     </row>
@@ -15777,7 +15777,7 @@
       </c>
       <c r="S180" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T22:27:02Z</t>
+          <t>2026-09-13T22:31:32Z</t>
         </is>
       </c>
     </row>
@@ -15866,7 +15866,7 @@
       </c>
       <c r="S181" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T22:27:02Z</t>
+          <t>2026-09-13T22:31:32Z</t>
         </is>
       </c>
     </row>
@@ -15955,7 +15955,7 @@
       </c>
       <c r="S182" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T22:27:02Z</t>
+          <t>2026-09-13T22:31:32Z</t>
         </is>
       </c>
     </row>
@@ -16044,7 +16044,7 @@
       </c>
       <c r="S183" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T22:27:02Z</t>
+          <t>2026-09-13T22:31:32Z</t>
         </is>
       </c>
     </row>
@@ -16133,7 +16133,7 @@
       </c>
       <c r="S184" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T22:27:02Z</t>
+          <t>2026-09-13T22:31:32Z</t>
         </is>
       </c>
     </row>
@@ -16222,7 +16222,7 @@
       </c>
       <c r="S185" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T22:27:02Z</t>
+          <t>2026-09-13T22:31:32Z</t>
         </is>
       </c>
     </row>
@@ -16311,7 +16311,7 @@
       </c>
       <c r="S186" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T22:27:02Z</t>
+          <t>2026-09-13T22:31:32Z</t>
         </is>
       </c>
     </row>
@@ -16400,7 +16400,7 @@
       </c>
       <c r="S187" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T22:27:02Z</t>
+          <t>2026-09-13T22:31:32Z</t>
         </is>
       </c>
     </row>
@@ -16489,7 +16489,7 @@
       </c>
       <c r="S188" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T22:27:02Z</t>
+          <t>2026-09-13T22:31:32Z</t>
         </is>
       </c>
     </row>
@@ -16578,7 +16578,7 @@
       </c>
       <c r="S189" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T22:27:02Z</t>
+          <t>2026-09-13T22:31:32Z</t>
         </is>
       </c>
     </row>
@@ -16663,7 +16663,7 @@
       </c>
       <c r="S190" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T22:27:02Z</t>
+          <t>2026-09-13T22:31:32Z</t>
         </is>
       </c>
     </row>
@@ -16748,7 +16748,7 @@
       </c>
       <c r="S191" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T22:27:02Z</t>
+          <t>2026-09-13T22:31:32Z</t>
         </is>
       </c>
     </row>
@@ -16833,7 +16833,7 @@
       </c>
       <c r="S192" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T22:27:02Z</t>
+          <t>2026-09-13T22:31:32Z</t>
         </is>
       </c>
     </row>
@@ -16918,7 +16918,7 @@
       </c>
       <c r="S193" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T22:27:02Z</t>
+          <t>2026-09-13T22:31:32Z</t>
         </is>
       </c>
     </row>
@@ -17003,7 +17003,7 @@
       </c>
       <c r="S194" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T22:27:02Z</t>
+          <t>2026-09-13T22:31:32Z</t>
         </is>
       </c>
     </row>
@@ -17088,7 +17088,7 @@
       </c>
       <c r="S195" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T22:27:02Z</t>
+          <t>2026-09-13T22:31:32Z</t>
         </is>
       </c>
     </row>
@@ -17173,7 +17173,7 @@
       </c>
       <c r="S196" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T22:27:02Z</t>
+          <t>2026-09-13T22:31:32Z</t>
         </is>
       </c>
     </row>
@@ -17258,7 +17258,7 @@
       </c>
       <c r="S197" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T22:27:02Z</t>
+          <t>2026-09-13T22:31:32Z</t>
         </is>
       </c>
     </row>
@@ -17343,7 +17343,7 @@
       </c>
       <c r="S198" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T22:27:02Z</t>
+          <t>2026-09-13T22:31:32Z</t>
         </is>
       </c>
     </row>
@@ -17428,7 +17428,7 @@
       </c>
       <c r="S199" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T22:27:02Z</t>
+          <t>2026-09-13T22:31:32Z</t>
         </is>
       </c>
     </row>
@@ -17513,7 +17513,7 @@
       </c>
       <c r="S200" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T22:27:02Z</t>
+          <t>2026-09-13T22:31:32Z</t>
         </is>
       </c>
     </row>
@@ -17598,7 +17598,7 @@
       </c>
       <c r="S201" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T22:27:02Z</t>
+          <t>2026-09-13T22:31:32Z</t>
         </is>
       </c>
     </row>
@@ -17683,7 +17683,7 @@
       </c>
       <c r="S202" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T22:27:02Z</t>
+          <t>2026-09-13T22:31:32Z</t>
         </is>
       </c>
     </row>
@@ -17768,7 +17768,7 @@
       </c>
       <c r="S203" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T22:27:02Z</t>
+          <t>2026-09-13T22:31:32Z</t>
         </is>
       </c>
     </row>
@@ -17853,7 +17853,7 @@
       </c>
       <c r="S204" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T22:27:02Z</t>
+          <t>2026-09-13T22:31:32Z</t>
         </is>
       </c>
     </row>
@@ -17938,7 +17938,7 @@
       </c>
       <c r="S205" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T22:27:02Z</t>
+          <t>2026-09-13T22:31:32Z</t>
         </is>
       </c>
     </row>
@@ -18023,7 +18023,7 @@
       </c>
       <c r="S206" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T22:27:02Z</t>
+          <t>2026-09-13T22:31:32Z</t>
         </is>
       </c>
     </row>
@@ -18108,7 +18108,7 @@
       </c>
       <c r="S207" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T22:27:02Z</t>
+          <t>2026-09-13T22:31:32Z</t>
         </is>
       </c>
     </row>
@@ -18193,7 +18193,7 @@
       </c>
       <c r="S208" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T22:27:02Z</t>
+          <t>2026-09-13T22:31:32Z</t>
         </is>
       </c>
     </row>
@@ -18278,7 +18278,7 @@
       </c>
       <c r="S209" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T22:27:02Z</t>
+          <t>2026-09-13T22:31:32Z</t>
         </is>
       </c>
     </row>
@@ -18363,7 +18363,7 @@
       </c>
       <c r="S210" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T22:27:02Z</t>
+          <t>2026-09-13T22:31:32Z</t>
         </is>
       </c>
     </row>
@@ -18452,7 +18452,7 @@
       </c>
       <c r="S211" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T22:27:02Z</t>
+          <t>2026-09-13T22:31:32Z</t>
         </is>
       </c>
     </row>
@@ -18541,7 +18541,7 @@
       </c>
       <c r="S212" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T22:27:02Z</t>
+          <t>2026-09-13T22:31:32Z</t>
         </is>
       </c>
     </row>
@@ -18626,7 +18626,7 @@
       </c>
       <c r="S213" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T22:27:02Z</t>
+          <t>2026-09-13T22:31:32Z</t>
         </is>
       </c>
     </row>
@@ -18715,7 +18715,7 @@
       </c>
       <c r="S214" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T22:27:02Z</t>
+          <t>2026-09-13T22:31:32Z</t>
         </is>
       </c>
     </row>
@@ -18804,7 +18804,7 @@
       </c>
       <c r="S215" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T22:27:02Z</t>
+          <t>2026-09-13T22:31:32Z</t>
         </is>
       </c>
     </row>
@@ -18889,7 +18889,7 @@
       </c>
       <c r="S216" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T22:27:02Z</t>
+          <t>2026-09-13T22:31:32Z</t>
         </is>
       </c>
     </row>
@@ -18978,7 +18978,7 @@
       </c>
       <c r="S217" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T22:27:02Z</t>
+          <t>2026-09-13T22:31:32Z</t>
         </is>
       </c>
     </row>
@@ -19067,7 +19067,7 @@
       </c>
       <c r="S218" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T22:27:02Z</t>
+          <t>2026-09-13T22:31:32Z</t>
         </is>
       </c>
     </row>
@@ -19152,7 +19152,7 @@
       </c>
       <c r="S219" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T22:27:02Z</t>
+          <t>2026-09-13T22:31:32Z</t>
         </is>
       </c>
     </row>
@@ -19241,7 +19241,7 @@
       </c>
       <c r="S220" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T22:27:02Z</t>
+          <t>2026-09-13T22:31:32Z</t>
         </is>
       </c>
     </row>
@@ -19330,7 +19330,7 @@
       </c>
       <c r="S221" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T22:27:02Z</t>
+          <t>2026-09-13T22:31:32Z</t>
         </is>
       </c>
     </row>
@@ -19415,7 +19415,7 @@
       </c>
       <c r="S222" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T22:27:02Z</t>
+          <t>2026-09-13T22:31:32Z</t>
         </is>
       </c>
     </row>
@@ -19504,7 +19504,7 @@
       </c>
       <c r="S223" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T22:27:02Z</t>
+          <t>2026-09-13T22:31:32Z</t>
         </is>
       </c>
     </row>
@@ -19593,7 +19593,7 @@
       </c>
       <c r="S224" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T22:27:02Z</t>
+          <t>2026-09-13T22:31:32Z</t>
         </is>
       </c>
     </row>
@@ -19678,7 +19678,7 @@
       </c>
       <c r="S225" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T22:27:02Z</t>
+          <t>2026-09-13T22:31:32Z</t>
         </is>
       </c>
     </row>
@@ -19767,7 +19767,7 @@
       </c>
       <c r="S226" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T22:27:02Z</t>
+          <t>2026-09-13T22:31:32Z</t>
         </is>
       </c>
     </row>
@@ -19856,7 +19856,7 @@
       </c>
       <c r="S227" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T22:27:02Z</t>
+          <t>2026-09-13T22:31:32Z</t>
         </is>
       </c>
     </row>
@@ -19941,7 +19941,7 @@
       </c>
       <c r="S228" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T22:27:02Z</t>
+          <t>2026-09-13T22:31:32Z</t>
         </is>
       </c>
     </row>
@@ -20030,7 +20030,7 @@
       </c>
       <c r="S229" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T22:27:02Z</t>
+          <t>2026-09-13T22:31:32Z</t>
         </is>
       </c>
     </row>
@@ -20119,7 +20119,7 @@
       </c>
       <c r="S230" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T22:27:02Z</t>
+          <t>2026-09-13T22:31:32Z</t>
         </is>
       </c>
     </row>
@@ -20204,7 +20204,7 @@
       </c>
       <c r="S231" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T22:27:02Z</t>
+          <t>2026-09-13T22:31:32Z</t>
         </is>
       </c>
     </row>
@@ -20293,7 +20293,7 @@
       </c>
       <c r="S232" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T22:27:02Z</t>
+          <t>2026-09-13T22:31:32Z</t>
         </is>
       </c>
     </row>
@@ -20382,7 +20382,7 @@
       </c>
       <c r="S233" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T22:27:02Z</t>
+          <t>2026-09-13T22:31:32Z</t>
         </is>
       </c>
     </row>
@@ -20467,7 +20467,7 @@
       </c>
       <c r="S234" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T22:27:02Z</t>
+          <t>2026-09-13T22:31:32Z</t>
         </is>
       </c>
     </row>
@@ -20556,7 +20556,7 @@
       </c>
       <c r="S235" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T22:27:02Z</t>
+          <t>2026-09-13T22:31:32Z</t>
         </is>
       </c>
     </row>
@@ -20645,7 +20645,7 @@
       </c>
       <c r="S236" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T22:27:02Z</t>
+          <t>2026-09-13T22:31:32Z</t>
         </is>
       </c>
     </row>
@@ -20730,7 +20730,7 @@
       </c>
       <c r="S237" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T22:27:02Z</t>
+          <t>2026-09-13T22:31:32Z</t>
         </is>
       </c>
     </row>
@@ -20819,7 +20819,7 @@
       </c>
       <c r="S238" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T22:27:02Z</t>
+          <t>2026-09-13T22:31:32Z</t>
         </is>
       </c>
     </row>
@@ -20908,7 +20908,7 @@
       </c>
       <c r="S239" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T22:27:02Z</t>
+          <t>2026-09-13T22:31:32Z</t>
         </is>
       </c>
     </row>
@@ -20997,7 +20997,7 @@
       </c>
       <c r="S240" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T22:27:02Z</t>
+          <t>2026-09-13T22:31:32Z</t>
         </is>
       </c>
     </row>
@@ -21086,7 +21086,7 @@
       </c>
       <c r="S241" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T22:27:02Z</t>
+          <t>2026-09-13T22:31:32Z</t>
         </is>
       </c>
     </row>
@@ -21175,7 +21175,7 @@
       </c>
       <c r="S242" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T22:27:02Z</t>
+          <t>2026-09-13T22:31:32Z</t>
         </is>
       </c>
     </row>
@@ -21264,7 +21264,7 @@
       </c>
       <c r="S243" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T22:27:02Z</t>
+          <t>2026-09-13T22:31:32Z</t>
         </is>
       </c>
     </row>
@@ -21353,7 +21353,7 @@
       </c>
       <c r="S244" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T22:27:02Z</t>
+          <t>2026-09-13T22:31:32Z</t>
         </is>
       </c>
     </row>
@@ -21442,7 +21442,7 @@
       </c>
       <c r="S245" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T22:27:02Z</t>
+          <t>2026-09-13T22:31:32Z</t>
         </is>
       </c>
     </row>
@@ -21531,7 +21531,7 @@
       </c>
       <c r="S246" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T22:27:02Z</t>
+          <t>2026-09-13T22:31:32Z</t>
         </is>
       </c>
     </row>
@@ -21620,7 +21620,7 @@
       </c>
       <c r="S247" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T22:27:02Z</t>
+          <t>2026-09-13T22:31:32Z</t>
         </is>
       </c>
     </row>
@@ -21709,7 +21709,7 @@
       </c>
       <c r="S248" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T22:27:02Z</t>
+          <t>2026-09-13T22:31:32Z</t>
         </is>
       </c>
     </row>
@@ -21798,7 +21798,7 @@
       </c>
       <c r="S249" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T22:27:02Z</t>
+          <t>2026-09-13T22:31:32Z</t>
         </is>
       </c>
     </row>
@@ -21887,7 +21887,7 @@
       </c>
       <c r="S250" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T22:27:02Z</t>
+          <t>2026-09-13T22:31:32Z</t>
         </is>
       </c>
     </row>
@@ -22019,7 +22019,7 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T22:27:02Z</t>
+          <t>2026-09-13T22:31:32Z</t>
         </is>
       </c>
     </row>
@@ -22099,7 +22099,7 @@
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>{"dataset_id": "bcv_pib_sector_institucional_anual", "title": "Producto interno bruto por sector institucional anual", "table": "Variaciones porcentuales", "source_file": "5_2_1_si_anual.xlsx", "base": "2007", "price_type": "Precios constantes", "measure": "Variación porcentual interanual", "frequency": "Anual", "period": "2025", "year": 2025, "quarter": null, "classification": "Sector institucional", "component": "Impuestos netos sobre los productos", "value": 10.600260421283764, "unit": "Porcentaje", "status": "Preliminar", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/cuentas_macroeconomicas/5_2_1_si_anual.xlsx", "fetched_at": "2026-09-12T22:27:02Z"}</t>
+          <t>{"dataset_id": "bcv_pib_sector_institucional_anual", "title": "Producto interno bruto por sector institucional anual", "table": "Variaciones porcentuales", "source_file": "5_2_1_si_anual.xlsx", "base": "2007", "price_type": "Precios constantes", "measure": "Variación porcentual interanual", "frequency": "Anual", "period": "2025", "year": 2025, "quarter": null, "classification": "Sector institucional", "component": "Impuestos netos sobre los productos", "value": 10.600260421283764, "unit": "Porcentaje", "status": "Preliminar", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/cuentas_macroeconomicas/5_2_1_si_anual.xlsx", "fetched_at": "2026-09-13T22:31:32Z"}</t>
         </is>
       </c>
     </row>

--- a/assets/data/bcv/excel/ove_bcv_pib_sector_institucional_anual.xlsx
+++ b/assets/data/bcv/excel/ove_bcv_pib_sector_institucional_anual.xlsx
@@ -736,7 +736,7 @@
       </c>
       <c r="S7" s="4" t="inlineStr">
         <is>
-          <t>2026-09-13T22:31:32Z</t>
+          <t>2026-09-14T23:16:43Z</t>
         </is>
       </c>
     </row>
@@ -821,7 +821,7 @@
       </c>
       <c r="S8" s="4" t="inlineStr">
         <is>
-          <t>2026-09-13T22:31:32Z</t>
+          <t>2026-09-14T23:16:43Z</t>
         </is>
       </c>
     </row>
@@ -906,7 +906,7 @@
       </c>
       <c r="S9" s="4" t="inlineStr">
         <is>
-          <t>2026-09-13T22:31:32Z</t>
+          <t>2026-09-14T23:16:43Z</t>
         </is>
       </c>
     </row>
@@ -991,7 +991,7 @@
       </c>
       <c r="S10" s="4" t="inlineStr">
         <is>
-          <t>2026-09-13T22:31:32Z</t>
+          <t>2026-09-14T23:16:43Z</t>
         </is>
       </c>
     </row>
@@ -1076,7 +1076,7 @@
       </c>
       <c r="S11" s="4" t="inlineStr">
         <is>
-          <t>2026-09-13T22:31:32Z</t>
+          <t>2026-09-14T23:16:43Z</t>
         </is>
       </c>
     </row>
@@ -1161,7 +1161,7 @@
       </c>
       <c r="S12" s="4" t="inlineStr">
         <is>
-          <t>2026-09-13T22:31:32Z</t>
+          <t>2026-09-14T23:16:43Z</t>
         </is>
       </c>
     </row>
@@ -1246,7 +1246,7 @@
       </c>
       <c r="S13" s="4" t="inlineStr">
         <is>
-          <t>2026-09-13T22:31:32Z</t>
+          <t>2026-09-14T23:16:43Z</t>
         </is>
       </c>
     </row>
@@ -1331,7 +1331,7 @@
       </c>
       <c r="S14" s="4" t="inlineStr">
         <is>
-          <t>2026-09-13T22:31:32Z</t>
+          <t>2026-09-14T23:16:43Z</t>
         </is>
       </c>
     </row>
@@ -1416,7 +1416,7 @@
       </c>
       <c r="S15" s="4" t="inlineStr">
         <is>
-          <t>2026-09-13T22:31:32Z</t>
+          <t>2026-09-14T23:16:43Z</t>
         </is>
       </c>
     </row>
@@ -1501,7 +1501,7 @@
       </c>
       <c r="S16" s="4" t="inlineStr">
         <is>
-          <t>2026-09-13T22:31:32Z</t>
+          <t>2026-09-14T23:16:43Z</t>
         </is>
       </c>
     </row>
@@ -1586,7 +1586,7 @@
       </c>
       <c r="S17" s="4" t="inlineStr">
         <is>
-          <t>2026-09-13T22:31:32Z</t>
+          <t>2026-09-14T23:16:43Z</t>
         </is>
       </c>
     </row>
@@ -1671,7 +1671,7 @@
       </c>
       <c r="S18" s="4" t="inlineStr">
         <is>
-          <t>2026-09-13T22:31:32Z</t>
+          <t>2026-09-14T23:16:43Z</t>
         </is>
       </c>
     </row>
@@ -1756,7 +1756,7 @@
       </c>
       <c r="S19" s="4" t="inlineStr">
         <is>
-          <t>2026-09-13T22:31:32Z</t>
+          <t>2026-09-14T23:16:43Z</t>
         </is>
       </c>
     </row>
@@ -1841,7 +1841,7 @@
       </c>
       <c r="S20" s="4" t="inlineStr">
         <is>
-          <t>2026-09-13T22:31:32Z</t>
+          <t>2026-09-14T23:16:43Z</t>
         </is>
       </c>
     </row>
@@ -1926,7 +1926,7 @@
       </c>
       <c r="S21" s="4" t="inlineStr">
         <is>
-          <t>2026-09-13T22:31:32Z</t>
+          <t>2026-09-14T23:16:43Z</t>
         </is>
       </c>
     </row>
@@ -2011,7 +2011,7 @@
       </c>
       <c r="S22" s="4" t="inlineStr">
         <is>
-          <t>2026-09-13T22:31:32Z</t>
+          <t>2026-09-14T23:16:43Z</t>
         </is>
       </c>
     </row>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="S23" s="4" t="inlineStr">
         <is>
-          <t>2026-09-13T22:31:32Z</t>
+          <t>2026-09-14T23:16:43Z</t>
         </is>
       </c>
     </row>
@@ -2181,7 +2181,7 @@
       </c>
       <c r="S24" s="4" t="inlineStr">
         <is>
-          <t>2026-09-13T22:31:32Z</t>
+          <t>2026-09-14T23:16:43Z</t>
         </is>
       </c>
     </row>
@@ -2266,7 +2266,7 @@
       </c>
       <c r="S25" s="4" t="inlineStr">
         <is>
-          <t>2026-09-13T22:31:32Z</t>
+          <t>2026-09-14T23:16:43Z</t>
         </is>
       </c>
     </row>
@@ -2351,7 +2351,7 @@
       </c>
       <c r="S26" s="4" t="inlineStr">
         <is>
-          <t>2026-09-13T22:31:32Z</t>
+          <t>2026-09-14T23:16:43Z</t>
         </is>
       </c>
     </row>
@@ -2436,7 +2436,7 @@
       </c>
       <c r="S27" s="4" t="inlineStr">
         <is>
-          <t>2026-09-13T22:31:32Z</t>
+          <t>2026-09-14T23:16:43Z</t>
         </is>
       </c>
     </row>
@@ -2525,7 +2525,7 @@
       </c>
       <c r="S28" s="4" t="inlineStr">
         <is>
-          <t>2026-09-13T22:31:32Z</t>
+          <t>2026-09-14T23:16:43Z</t>
         </is>
       </c>
     </row>
@@ -2614,7 +2614,7 @@
       </c>
       <c r="S29" s="4" t="inlineStr">
         <is>
-          <t>2026-09-13T22:31:32Z</t>
+          <t>2026-09-14T23:16:43Z</t>
         </is>
       </c>
     </row>
@@ -2699,7 +2699,7 @@
       </c>
       <c r="S30" s="4" t="inlineStr">
         <is>
-          <t>2026-09-13T22:31:32Z</t>
+          <t>2026-09-14T23:16:43Z</t>
         </is>
       </c>
     </row>
@@ -2788,7 +2788,7 @@
       </c>
       <c r="S31" s="4" t="inlineStr">
         <is>
-          <t>2026-09-13T22:31:32Z</t>
+          <t>2026-09-14T23:16:43Z</t>
         </is>
       </c>
     </row>
@@ -2877,7 +2877,7 @@
       </c>
       <c r="S32" s="4" t="inlineStr">
         <is>
-          <t>2026-09-13T22:31:32Z</t>
+          <t>2026-09-14T23:16:43Z</t>
         </is>
       </c>
     </row>
@@ -2962,7 +2962,7 @@
       </c>
       <c r="S33" s="4" t="inlineStr">
         <is>
-          <t>2026-09-13T22:31:32Z</t>
+          <t>2026-09-14T23:16:43Z</t>
         </is>
       </c>
     </row>
@@ -3051,7 +3051,7 @@
       </c>
       <c r="S34" s="4" t="inlineStr">
         <is>
-          <t>2026-09-13T22:31:32Z</t>
+          <t>2026-09-14T23:16:43Z</t>
         </is>
       </c>
     </row>
@@ -3140,7 +3140,7 @@
       </c>
       <c r="S35" s="4" t="inlineStr">
         <is>
-          <t>2026-09-13T22:31:32Z</t>
+          <t>2026-09-14T23:16:43Z</t>
         </is>
       </c>
     </row>
@@ -3225,7 +3225,7 @@
       </c>
       <c r="S36" s="4" t="inlineStr">
         <is>
-          <t>2026-09-13T22:31:32Z</t>
+          <t>2026-09-14T23:16:43Z</t>
         </is>
       </c>
     </row>
@@ -3314,7 +3314,7 @@
       </c>
       <c r="S37" s="4" t="inlineStr">
         <is>
-          <t>2026-09-13T22:31:32Z</t>
+          <t>2026-09-14T23:16:43Z</t>
         </is>
       </c>
     </row>
@@ -3403,7 +3403,7 @@
       </c>
       <c r="S38" s="4" t="inlineStr">
         <is>
-          <t>2026-09-13T22:31:32Z</t>
+          <t>2026-09-14T23:16:43Z</t>
         </is>
       </c>
     </row>
@@ -3488,7 +3488,7 @@
       </c>
       <c r="S39" s="4" t="inlineStr">
         <is>
-          <t>2026-09-13T22:31:32Z</t>
+          <t>2026-09-14T23:16:43Z</t>
         </is>
       </c>
     </row>
@@ -3577,7 +3577,7 @@
       </c>
       <c r="S40" s="4" t="inlineStr">
         <is>
-          <t>2026-09-13T22:31:32Z</t>
+          <t>2026-09-14T23:16:43Z</t>
         </is>
       </c>
     </row>
@@ -3666,7 +3666,7 @@
       </c>
       <c r="S41" s="4" t="inlineStr">
         <is>
-          <t>2026-09-13T22:31:32Z</t>
+          <t>2026-09-14T23:16:43Z</t>
         </is>
       </c>
     </row>
@@ -3751,7 +3751,7 @@
       </c>
       <c r="S42" s="4" t="inlineStr">
         <is>
-          <t>2026-09-13T22:31:32Z</t>
+          <t>2026-09-14T23:16:43Z</t>
         </is>
       </c>
     </row>
@@ -3840,7 +3840,7 @@
       </c>
       <c r="S43" s="4" t="inlineStr">
         <is>
-          <t>2026-09-13T22:31:32Z</t>
+          <t>2026-09-14T23:16:43Z</t>
         </is>
       </c>
     </row>
@@ -3929,7 +3929,7 @@
       </c>
       <c r="S44" s="4" t="inlineStr">
         <is>
-          <t>2026-09-13T22:31:32Z</t>
+          <t>2026-09-14T23:16:43Z</t>
         </is>
       </c>
     </row>
@@ -4014,7 +4014,7 @@
       </c>
       <c r="S45" s="4" t="inlineStr">
         <is>
-          <t>2026-09-13T22:31:32Z</t>
+          <t>2026-09-14T23:16:43Z</t>
         </is>
       </c>
     </row>
@@ -4103,7 +4103,7 @@
       </c>
       <c r="S46" s="4" t="inlineStr">
         <is>
-          <t>2026-09-13T22:31:32Z</t>
+          <t>2026-09-14T23:16:43Z</t>
         </is>
       </c>
     </row>
@@ -4192,7 +4192,7 @@
       </c>
       <c r="S47" s="4" t="inlineStr">
         <is>
-          <t>2026-09-13T22:31:32Z</t>
+          <t>2026-09-14T23:16:43Z</t>
         </is>
       </c>
     </row>
@@ -4277,7 +4277,7 @@
       </c>
       <c r="S48" s="4" t="inlineStr">
         <is>
-          <t>2026-09-13T22:31:32Z</t>
+          <t>2026-09-14T23:16:43Z</t>
         </is>
       </c>
     </row>
@@ -4366,7 +4366,7 @@
       </c>
       <c r="S49" s="4" t="inlineStr">
         <is>
-          <t>2026-09-13T22:31:32Z</t>
+          <t>2026-09-14T23:16:43Z</t>
         </is>
       </c>
     </row>
@@ -4455,7 +4455,7 @@
       </c>
       <c r="S50" s="4" t="inlineStr">
         <is>
-          <t>2026-09-13T22:31:32Z</t>
+          <t>2026-09-14T23:16:43Z</t>
         </is>
       </c>
     </row>
@@ -4540,7 +4540,7 @@
       </c>
       <c r="S51" s="4" t="inlineStr">
         <is>
-          <t>2026-09-13T22:31:32Z</t>
+          <t>2026-09-14T23:16:43Z</t>
         </is>
       </c>
     </row>
@@ -4629,7 +4629,7 @@
       </c>
       <c r="S52" s="4" t="inlineStr">
         <is>
-          <t>2026-09-13T22:31:32Z</t>
+          <t>2026-09-14T23:16:43Z</t>
         </is>
       </c>
     </row>
@@ -4718,7 +4718,7 @@
       </c>
       <c r="S53" s="4" t="inlineStr">
         <is>
-          <t>2026-09-13T22:31:32Z</t>
+          <t>2026-09-14T23:16:43Z</t>
         </is>
       </c>
     </row>
@@ -4803,7 +4803,7 @@
       </c>
       <c r="S54" s="4" t="inlineStr">
         <is>
-          <t>2026-09-13T22:31:32Z</t>
+          <t>2026-09-14T23:16:43Z</t>
         </is>
       </c>
     </row>
@@ -4892,7 +4892,7 @@
       </c>
       <c r="S55" s="4" t="inlineStr">
         <is>
-          <t>2026-09-13T22:31:32Z</t>
+          <t>2026-09-14T23:16:43Z</t>
         </is>
       </c>
     </row>
@@ -4981,7 +4981,7 @@
       </c>
       <c r="S56" s="4" t="inlineStr">
         <is>
-          <t>2026-09-13T22:31:32Z</t>
+          <t>2026-09-14T23:16:43Z</t>
         </is>
       </c>
     </row>
@@ -5070,7 +5070,7 @@
       </c>
       <c r="S57" s="4" t="inlineStr">
         <is>
-          <t>2026-09-13T22:31:32Z</t>
+          <t>2026-09-14T23:16:43Z</t>
         </is>
       </c>
     </row>
@@ -5159,7 +5159,7 @@
       </c>
       <c r="S58" s="4" t="inlineStr">
         <is>
-          <t>2026-09-13T22:31:32Z</t>
+          <t>2026-09-14T23:16:43Z</t>
         </is>
       </c>
     </row>
@@ -5248,7 +5248,7 @@
       </c>
       <c r="S59" s="4" t="inlineStr">
         <is>
-          <t>2026-09-13T22:31:32Z</t>
+          <t>2026-09-14T23:16:43Z</t>
         </is>
       </c>
     </row>
@@ -5337,7 +5337,7 @@
       </c>
       <c r="S60" s="4" t="inlineStr">
         <is>
-          <t>2026-09-13T22:31:32Z</t>
+          <t>2026-09-14T23:16:43Z</t>
         </is>
       </c>
     </row>
@@ -5426,7 +5426,7 @@
       </c>
       <c r="S61" s="4" t="inlineStr">
         <is>
-          <t>2026-09-13T22:31:32Z</t>
+          <t>2026-09-14T23:16:43Z</t>
         </is>
       </c>
     </row>
@@ -5515,7 +5515,7 @@
       </c>
       <c r="S62" s="4" t="inlineStr">
         <is>
-          <t>2026-09-13T22:31:32Z</t>
+          <t>2026-09-14T23:16:43Z</t>
         </is>
       </c>
     </row>
@@ -5604,7 +5604,7 @@
       </c>
       <c r="S63" s="4" t="inlineStr">
         <is>
-          <t>2026-09-13T22:31:32Z</t>
+          <t>2026-09-14T23:16:43Z</t>
         </is>
       </c>
     </row>
@@ -5693,7 +5693,7 @@
       </c>
       <c r="S64" s="4" t="inlineStr">
         <is>
-          <t>2026-09-13T22:31:32Z</t>
+          <t>2026-09-14T23:16:43Z</t>
         </is>
       </c>
     </row>
@@ -5782,7 +5782,7 @@
       </c>
       <c r="S65" s="4" t="inlineStr">
         <is>
-          <t>2026-09-13T22:31:32Z</t>
+          <t>2026-09-14T23:16:43Z</t>
         </is>
       </c>
     </row>
@@ -5871,7 +5871,7 @@
       </c>
       <c r="S66" s="4" t="inlineStr">
         <is>
-          <t>2026-09-13T22:31:32Z</t>
+          <t>2026-09-14T23:16:43Z</t>
         </is>
       </c>
     </row>
@@ -5960,7 +5960,7 @@
       </c>
       <c r="S67" s="4" t="inlineStr">
         <is>
-          <t>2026-09-13T22:31:32Z</t>
+          <t>2026-09-14T23:16:43Z</t>
         </is>
       </c>
     </row>
@@ -6045,7 +6045,7 @@
       </c>
       <c r="S68" s="4" t="inlineStr">
         <is>
-          <t>2026-09-13T22:31:32Z</t>
+          <t>2026-09-14T23:16:43Z</t>
         </is>
       </c>
     </row>
@@ -6130,7 +6130,7 @@
       </c>
       <c r="S69" s="4" t="inlineStr">
         <is>
-          <t>2026-09-13T22:31:32Z</t>
+          <t>2026-09-14T23:16:43Z</t>
         </is>
       </c>
     </row>
@@ -6215,7 +6215,7 @@
       </c>
       <c r="S70" s="4" t="inlineStr">
         <is>
-          <t>2026-09-13T22:31:32Z</t>
+          <t>2026-09-14T23:16:43Z</t>
         </is>
       </c>
     </row>
@@ -6300,7 +6300,7 @@
       </c>
       <c r="S71" s="4" t="inlineStr">
         <is>
-          <t>2026-09-13T22:31:32Z</t>
+          <t>2026-09-14T23:16:43Z</t>
         </is>
       </c>
     </row>
@@ -6385,7 +6385,7 @@
       </c>
       <c r="S72" s="4" t="inlineStr">
         <is>
-          <t>2026-09-13T22:31:32Z</t>
+          <t>2026-09-14T23:16:43Z</t>
         </is>
       </c>
     </row>
@@ -6470,7 +6470,7 @@
       </c>
       <c r="S73" s="4" t="inlineStr">
         <is>
-          <t>2026-09-13T22:31:32Z</t>
+          <t>2026-09-14T23:16:43Z</t>
         </is>
       </c>
     </row>
@@ -6555,7 +6555,7 @@
       </c>
       <c r="S74" s="4" t="inlineStr">
         <is>
-          <t>2026-09-13T22:31:32Z</t>
+          <t>2026-09-14T23:16:43Z</t>
         </is>
       </c>
     </row>
@@ -6640,7 +6640,7 @@
       </c>
       <c r="S75" s="4" t="inlineStr">
         <is>
-          <t>2026-09-13T22:31:32Z</t>
+          <t>2026-09-14T23:16:43Z</t>
         </is>
       </c>
     </row>
@@ -6725,7 +6725,7 @@
       </c>
       <c r="S76" s="4" t="inlineStr">
         <is>
-          <t>2026-09-13T22:31:32Z</t>
+          <t>2026-09-14T23:16:43Z</t>
         </is>
       </c>
     </row>
@@ -6810,7 +6810,7 @@
       </c>
       <c r="S77" s="4" t="inlineStr">
         <is>
-          <t>2026-09-13T22:31:32Z</t>
+          <t>2026-09-14T23:16:43Z</t>
         </is>
       </c>
     </row>
@@ -6895,7 +6895,7 @@
       </c>
       <c r="S78" s="4" t="inlineStr">
         <is>
-          <t>2026-09-13T22:31:32Z</t>
+          <t>2026-09-14T23:16:43Z</t>
         </is>
       </c>
     </row>
@@ -6980,7 +6980,7 @@
       </c>
       <c r="S79" s="4" t="inlineStr">
         <is>
-          <t>2026-09-13T22:31:32Z</t>
+          <t>2026-09-14T23:16:43Z</t>
         </is>
       </c>
     </row>
@@ -7065,7 +7065,7 @@
       </c>
       <c r="S80" s="4" t="inlineStr">
         <is>
-          <t>2026-09-13T22:31:32Z</t>
+          <t>2026-09-14T23:16:43Z</t>
         </is>
       </c>
     </row>
@@ -7150,7 +7150,7 @@
       </c>
       <c r="S81" s="4" t="inlineStr">
         <is>
-          <t>2026-09-13T22:31:32Z</t>
+          <t>2026-09-14T23:16:43Z</t>
         </is>
       </c>
     </row>
@@ -7235,7 +7235,7 @@
       </c>
       <c r="S82" s="4" t="inlineStr">
         <is>
-          <t>2026-09-13T22:31:32Z</t>
+          <t>2026-09-14T23:16:43Z</t>
         </is>
       </c>
     </row>
@@ -7320,7 +7320,7 @@
       </c>
       <c r="S83" s="4" t="inlineStr">
         <is>
-          <t>2026-09-13T22:31:32Z</t>
+          <t>2026-09-14T23:16:43Z</t>
         </is>
       </c>
     </row>
@@ -7405,7 +7405,7 @@
       </c>
       <c r="S84" s="4" t="inlineStr">
         <is>
-          <t>2026-09-13T22:31:32Z</t>
+          <t>2026-09-14T23:16:43Z</t>
         </is>
       </c>
     </row>
@@ -7490,7 +7490,7 @@
       </c>
       <c r="S85" s="4" t="inlineStr">
         <is>
-          <t>2026-09-13T22:31:32Z</t>
+          <t>2026-09-14T23:16:43Z</t>
         </is>
       </c>
     </row>
@@ -7575,7 +7575,7 @@
       </c>
       <c r="S86" s="4" t="inlineStr">
         <is>
-          <t>2026-09-13T22:31:32Z</t>
+          <t>2026-09-14T23:16:43Z</t>
         </is>
       </c>
     </row>
@@ -7660,7 +7660,7 @@
       </c>
       <c r="S87" s="4" t="inlineStr">
         <is>
-          <t>2026-09-13T22:31:32Z</t>
+          <t>2026-09-14T23:16:43Z</t>
         </is>
       </c>
     </row>
@@ -7745,7 +7745,7 @@
       </c>
       <c r="S88" s="4" t="inlineStr">
         <is>
-          <t>2026-09-13T22:31:32Z</t>
+          <t>2026-09-14T23:16:43Z</t>
         </is>
       </c>
     </row>
@@ -7834,7 +7834,7 @@
       </c>
       <c r="S89" s="4" t="inlineStr">
         <is>
-          <t>2026-09-13T22:31:32Z</t>
+          <t>2026-09-14T23:16:43Z</t>
         </is>
       </c>
     </row>
@@ -7923,7 +7923,7 @@
       </c>
       <c r="S90" s="4" t="inlineStr">
         <is>
-          <t>2026-09-13T22:31:32Z</t>
+          <t>2026-09-14T23:16:43Z</t>
         </is>
       </c>
     </row>
@@ -8008,7 +8008,7 @@
       </c>
       <c r="S91" s="4" t="inlineStr">
         <is>
-          <t>2026-09-13T22:31:32Z</t>
+          <t>2026-09-14T23:16:43Z</t>
         </is>
       </c>
     </row>
@@ -8097,7 +8097,7 @@
       </c>
       <c r="S92" s="4" t="inlineStr">
         <is>
-          <t>2026-09-13T22:31:32Z</t>
+          <t>2026-09-14T23:16:43Z</t>
         </is>
       </c>
     </row>
@@ -8186,7 +8186,7 @@
       </c>
       <c r="S93" s="4" t="inlineStr">
         <is>
-          <t>2026-09-13T22:31:32Z</t>
+          <t>2026-09-14T23:16:43Z</t>
         </is>
       </c>
     </row>
@@ -8271,7 +8271,7 @@
       </c>
       <c r="S94" s="4" t="inlineStr">
         <is>
-          <t>2026-09-13T22:31:32Z</t>
+          <t>2026-09-14T23:16:43Z</t>
         </is>
       </c>
     </row>
@@ -8360,7 +8360,7 @@
       </c>
       <c r="S95" s="4" t="inlineStr">
         <is>
-          <t>2026-09-13T22:31:32Z</t>
+          <t>2026-09-14T23:16:43Z</t>
         </is>
       </c>
     </row>
@@ -8449,7 +8449,7 @@
       </c>
       <c r="S96" s="4" t="inlineStr">
         <is>
-          <t>2026-09-13T22:31:32Z</t>
+          <t>2026-09-14T23:16:43Z</t>
         </is>
       </c>
     </row>
@@ -8534,7 +8534,7 @@
       </c>
       <c r="S97" s="4" t="inlineStr">
         <is>
-          <t>2026-09-13T22:31:32Z</t>
+          <t>2026-09-14T23:16:43Z</t>
         </is>
       </c>
     </row>
@@ -8623,7 +8623,7 @@
       </c>
       <c r="S98" s="4" t="inlineStr">
         <is>
-          <t>2026-09-13T22:31:32Z</t>
+          <t>2026-09-14T23:16:43Z</t>
         </is>
       </c>
     </row>
@@ -8712,7 +8712,7 @@
       </c>
       <c r="S99" s="4" t="inlineStr">
         <is>
-          <t>2026-09-13T22:31:32Z</t>
+          <t>2026-09-14T23:16:43Z</t>
         </is>
       </c>
     </row>
@@ -8797,7 +8797,7 @@
       </c>
       <c r="S100" s="4" t="inlineStr">
         <is>
-          <t>2026-09-13T22:31:32Z</t>
+          <t>2026-09-14T23:16:43Z</t>
         </is>
       </c>
     </row>
@@ -8886,7 +8886,7 @@
       </c>
       <c r="S101" s="4" t="inlineStr">
         <is>
-          <t>2026-09-13T22:31:32Z</t>
+          <t>2026-09-14T23:16:43Z</t>
         </is>
       </c>
     </row>
@@ -8975,7 +8975,7 @@
       </c>
       <c r="S102" s="4" t="inlineStr">
         <is>
-          <t>2026-09-13T22:31:32Z</t>
+          <t>2026-09-14T23:16:43Z</t>
         </is>
       </c>
     </row>
@@ -9060,7 +9060,7 @@
       </c>
       <c r="S103" s="4" t="inlineStr">
         <is>
-          <t>2026-09-13T22:31:32Z</t>
+          <t>2026-09-14T23:16:43Z</t>
         </is>
       </c>
     </row>
@@ -9149,7 +9149,7 @@
       </c>
       <c r="S104" s="4" t="inlineStr">
         <is>
-          <t>2026-09-13T22:31:32Z</t>
+          <t>2026-09-14T23:16:43Z</t>
         </is>
       </c>
     </row>
@@ -9238,7 +9238,7 @@
       </c>
       <c r="S105" s="4" t="inlineStr">
         <is>
-          <t>2026-09-13T22:31:32Z</t>
+          <t>2026-09-14T23:16:43Z</t>
         </is>
       </c>
     </row>
@@ -9323,7 +9323,7 @@
       </c>
       <c r="S106" s="4" t="inlineStr">
         <is>
-          <t>2026-09-13T22:31:32Z</t>
+          <t>2026-09-14T23:16:43Z</t>
         </is>
       </c>
     </row>
@@ -9412,7 +9412,7 @@
       </c>
       <c r="S107" s="4" t="inlineStr">
         <is>
-          <t>2026-09-13T22:31:32Z</t>
+          <t>2026-09-14T23:16:43Z</t>
         </is>
       </c>
     </row>
@@ -9501,7 +9501,7 @@
       </c>
       <c r="S108" s="4" t="inlineStr">
         <is>
-          <t>2026-09-13T22:31:32Z</t>
+          <t>2026-09-14T23:16:43Z</t>
         </is>
       </c>
     </row>
@@ -9586,7 +9586,7 @@
       </c>
       <c r="S109" s="4" t="inlineStr">
         <is>
-          <t>2026-09-13T22:31:32Z</t>
+          <t>2026-09-14T23:16:43Z</t>
         </is>
       </c>
     </row>
@@ -9675,7 +9675,7 @@
       </c>
       <c r="S110" s="4" t="inlineStr">
         <is>
-          <t>2026-09-13T22:31:32Z</t>
+          <t>2026-09-14T23:16:43Z</t>
         </is>
       </c>
     </row>
@@ -9764,7 +9764,7 @@
       </c>
       <c r="S111" s="4" t="inlineStr">
         <is>
-          <t>2026-09-13T22:31:32Z</t>
+          <t>2026-09-14T23:16:43Z</t>
         </is>
       </c>
     </row>
@@ -9849,7 +9849,7 @@
       </c>
       <c r="S112" s="4" t="inlineStr">
         <is>
-          <t>2026-09-13T22:31:32Z</t>
+          <t>2026-09-14T23:16:43Z</t>
         </is>
       </c>
     </row>
@@ -9938,7 +9938,7 @@
       </c>
       <c r="S113" s="4" t="inlineStr">
         <is>
-          <t>2026-09-13T22:31:32Z</t>
+          <t>2026-09-14T23:16:43Z</t>
         </is>
       </c>
     </row>
@@ -10027,7 +10027,7 @@
       </c>
       <c r="S114" s="4" t="inlineStr">
         <is>
-          <t>2026-09-13T22:31:32Z</t>
+          <t>2026-09-14T23:16:43Z</t>
         </is>
       </c>
     </row>
@@ -10112,7 +10112,7 @@
       </c>
       <c r="S115" s="4" t="inlineStr">
         <is>
-          <t>2026-09-13T22:31:32Z</t>
+          <t>2026-09-14T23:16:43Z</t>
         </is>
       </c>
     </row>
@@ -10201,7 +10201,7 @@
       </c>
       <c r="S116" s="4" t="inlineStr">
         <is>
-          <t>2026-09-13T22:31:32Z</t>
+          <t>2026-09-14T23:16:43Z</t>
         </is>
       </c>
     </row>
@@ -10290,7 +10290,7 @@
       </c>
       <c r="S117" s="4" t="inlineStr">
         <is>
-          <t>2026-09-13T22:31:32Z</t>
+          <t>2026-09-14T23:16:43Z</t>
         </is>
       </c>
     </row>
@@ -10379,7 +10379,7 @@
       </c>
       <c r="S118" s="4" t="inlineStr">
         <is>
-          <t>2026-09-13T22:31:32Z</t>
+          <t>2026-09-14T23:16:43Z</t>
         </is>
       </c>
     </row>
@@ -10468,7 +10468,7 @@
       </c>
       <c r="S119" s="4" t="inlineStr">
         <is>
-          <t>2026-09-13T22:31:32Z</t>
+          <t>2026-09-14T23:16:43Z</t>
         </is>
       </c>
     </row>
@@ -10557,7 +10557,7 @@
       </c>
       <c r="S120" s="4" t="inlineStr">
         <is>
-          <t>2026-09-13T22:31:32Z</t>
+          <t>2026-09-14T23:16:43Z</t>
         </is>
       </c>
     </row>
@@ -10646,7 +10646,7 @@
       </c>
       <c r="S121" s="4" t="inlineStr">
         <is>
-          <t>2026-09-13T22:31:32Z</t>
+          <t>2026-09-14T23:16:43Z</t>
         </is>
       </c>
     </row>
@@ -10735,7 +10735,7 @@
       </c>
       <c r="S122" s="4" t="inlineStr">
         <is>
-          <t>2026-09-13T22:31:32Z</t>
+          <t>2026-09-14T23:16:43Z</t>
         </is>
       </c>
     </row>
@@ -10824,7 +10824,7 @@
       </c>
       <c r="S123" s="4" t="inlineStr">
         <is>
-          <t>2026-09-13T22:31:32Z</t>
+          <t>2026-09-14T23:16:43Z</t>
         </is>
       </c>
     </row>
@@ -10913,7 +10913,7 @@
       </c>
       <c r="S124" s="4" t="inlineStr">
         <is>
-          <t>2026-09-13T22:31:32Z</t>
+          <t>2026-09-14T23:16:43Z</t>
         </is>
       </c>
     </row>
@@ -11002,7 +11002,7 @@
       </c>
       <c r="S125" s="4" t="inlineStr">
         <is>
-          <t>2026-09-13T22:31:32Z</t>
+          <t>2026-09-14T23:16:43Z</t>
         </is>
       </c>
     </row>
@@ -11091,7 +11091,7 @@
       </c>
       <c r="S126" s="4" t="inlineStr">
         <is>
-          <t>2026-09-13T22:31:32Z</t>
+          <t>2026-09-14T23:16:43Z</t>
         </is>
       </c>
     </row>
@@ -11180,7 +11180,7 @@
       </c>
       <c r="S127" s="4" t="inlineStr">
         <is>
-          <t>2026-09-13T22:31:32Z</t>
+          <t>2026-09-14T23:16:43Z</t>
         </is>
       </c>
     </row>
@@ -11269,7 +11269,7 @@
       </c>
       <c r="S128" s="4" t="inlineStr">
         <is>
-          <t>2026-09-13T22:31:32Z</t>
+          <t>2026-09-14T23:16:43Z</t>
         </is>
       </c>
     </row>
@@ -11354,7 +11354,7 @@
       </c>
       <c r="S129" s="4" t="inlineStr">
         <is>
-          <t>2026-09-13T22:31:32Z</t>
+          <t>2026-09-14T23:16:43Z</t>
         </is>
       </c>
     </row>
@@ -11439,7 +11439,7 @@
       </c>
       <c r="S130" s="4" t="inlineStr">
         <is>
-          <t>2026-09-13T22:31:32Z</t>
+          <t>2026-09-14T23:16:43Z</t>
         </is>
       </c>
     </row>
@@ -11524,7 +11524,7 @@
       </c>
       <c r="S131" s="4" t="inlineStr">
         <is>
-          <t>2026-09-13T22:31:32Z</t>
+          <t>2026-09-14T23:16:43Z</t>
         </is>
       </c>
     </row>
@@ -11609,7 +11609,7 @@
       </c>
       <c r="S132" s="4" t="inlineStr">
         <is>
-          <t>2026-09-13T22:31:32Z</t>
+          <t>2026-09-14T23:16:43Z</t>
         </is>
       </c>
     </row>
@@ -11694,7 +11694,7 @@
       </c>
       <c r="S133" s="4" t="inlineStr">
         <is>
-          <t>2026-09-13T22:31:32Z</t>
+          <t>2026-09-14T23:16:43Z</t>
         </is>
       </c>
     </row>
@@ -11779,7 +11779,7 @@
       </c>
       <c r="S134" s="4" t="inlineStr">
         <is>
-          <t>2026-09-13T22:31:32Z</t>
+          <t>2026-09-14T23:16:43Z</t>
         </is>
       </c>
     </row>
@@ -11864,7 +11864,7 @@
       </c>
       <c r="S135" s="4" t="inlineStr">
         <is>
-          <t>2026-09-13T22:31:32Z</t>
+          <t>2026-09-14T23:16:43Z</t>
         </is>
       </c>
     </row>
@@ -11949,7 +11949,7 @@
       </c>
       <c r="S136" s="4" t="inlineStr">
         <is>
-          <t>2026-09-13T22:31:32Z</t>
+          <t>2026-09-14T23:16:43Z</t>
         </is>
       </c>
     </row>
@@ -12034,7 +12034,7 @@
       </c>
       <c r="S137" s="4" t="inlineStr">
         <is>
-          <t>2026-09-13T22:31:32Z</t>
+          <t>2026-09-14T23:16:43Z</t>
         </is>
       </c>
     </row>
@@ -12119,7 +12119,7 @@
       </c>
       <c r="S138" s="4" t="inlineStr">
         <is>
-          <t>2026-09-13T22:31:32Z</t>
+          <t>2026-09-14T23:16:43Z</t>
         </is>
       </c>
     </row>
@@ -12204,7 +12204,7 @@
       </c>
       <c r="S139" s="4" t="inlineStr">
         <is>
-          <t>2026-09-13T22:31:32Z</t>
+          <t>2026-09-14T23:16:43Z</t>
         </is>
       </c>
     </row>
@@ -12289,7 +12289,7 @@
       </c>
       <c r="S140" s="4" t="inlineStr">
         <is>
-          <t>2026-09-13T22:31:32Z</t>
+          <t>2026-09-14T23:16:43Z</t>
         </is>
       </c>
     </row>
@@ -12374,7 +12374,7 @@
       </c>
       <c r="S141" s="4" t="inlineStr">
         <is>
-          <t>2026-09-13T22:31:32Z</t>
+          <t>2026-09-14T23:16:43Z</t>
         </is>
       </c>
     </row>
@@ -12459,7 +12459,7 @@
       </c>
       <c r="S142" s="4" t="inlineStr">
         <is>
-          <t>2026-09-13T22:31:32Z</t>
+          <t>2026-09-14T23:16:43Z</t>
         </is>
       </c>
     </row>
@@ -12544,7 +12544,7 @@
       </c>
       <c r="S143" s="4" t="inlineStr">
         <is>
-          <t>2026-09-13T22:31:32Z</t>
+          <t>2026-09-14T23:16:43Z</t>
         </is>
       </c>
     </row>
@@ -12629,7 +12629,7 @@
       </c>
       <c r="S144" s="4" t="inlineStr">
         <is>
-          <t>2026-09-13T22:31:32Z</t>
+          <t>2026-09-14T23:16:43Z</t>
         </is>
       </c>
     </row>
@@ -12714,7 +12714,7 @@
       </c>
       <c r="S145" s="4" t="inlineStr">
         <is>
-          <t>2026-09-13T22:31:32Z</t>
+          <t>2026-09-14T23:16:43Z</t>
         </is>
       </c>
     </row>
@@ -12799,7 +12799,7 @@
       </c>
       <c r="S146" s="4" t="inlineStr">
         <is>
-          <t>2026-09-13T22:31:32Z</t>
+          <t>2026-09-14T23:16:43Z</t>
         </is>
       </c>
     </row>
@@ -12884,7 +12884,7 @@
       </c>
       <c r="S147" s="4" t="inlineStr">
         <is>
-          <t>2026-09-13T22:31:32Z</t>
+          <t>2026-09-14T23:16:43Z</t>
         </is>
       </c>
     </row>
@@ -12969,7 +12969,7 @@
       </c>
       <c r="S148" s="4" t="inlineStr">
         <is>
-          <t>2026-09-13T22:31:32Z</t>
+          <t>2026-09-14T23:16:43Z</t>
         </is>
       </c>
     </row>
@@ -13054,7 +13054,7 @@
       </c>
       <c r="S149" s="4" t="inlineStr">
         <is>
-          <t>2026-09-13T22:31:32Z</t>
+          <t>2026-09-14T23:16:43Z</t>
         </is>
       </c>
     </row>
@@ -13143,7 +13143,7 @@
       </c>
       <c r="S150" s="4" t="inlineStr">
         <is>
-          <t>2026-09-13T22:31:32Z</t>
+          <t>2026-09-14T23:16:43Z</t>
         </is>
       </c>
     </row>
@@ -13232,7 +13232,7 @@
       </c>
       <c r="S151" s="4" t="inlineStr">
         <is>
-          <t>2026-09-13T22:31:32Z</t>
+          <t>2026-09-14T23:16:43Z</t>
         </is>
       </c>
     </row>
@@ -13317,7 +13317,7 @@
       </c>
       <c r="S152" s="4" t="inlineStr">
         <is>
-          <t>2026-09-13T22:31:32Z</t>
+          <t>2026-09-14T23:16:43Z</t>
         </is>
       </c>
     </row>
@@ -13406,7 +13406,7 @@
       </c>
       <c r="S153" s="4" t="inlineStr">
         <is>
-          <t>2026-09-13T22:31:32Z</t>
+          <t>2026-09-14T23:16:43Z</t>
         </is>
       </c>
     </row>
@@ -13495,7 +13495,7 @@
       </c>
       <c r="S154" s="4" t="inlineStr">
         <is>
-          <t>2026-09-13T22:31:32Z</t>
+          <t>2026-09-14T23:16:43Z</t>
         </is>
       </c>
     </row>
@@ -13580,7 +13580,7 @@
       </c>
       <c r="S155" s="4" t="inlineStr">
         <is>
-          <t>2026-09-13T22:31:32Z</t>
+          <t>2026-09-14T23:16:43Z</t>
         </is>
       </c>
     </row>
@@ -13669,7 +13669,7 @@
       </c>
       <c r="S156" s="4" t="inlineStr">
         <is>
-          <t>2026-09-13T22:31:32Z</t>
+          <t>2026-09-14T23:16:43Z</t>
         </is>
       </c>
     </row>
@@ -13758,7 +13758,7 @@
       </c>
       <c r="S157" s="4" t="inlineStr">
         <is>
-          <t>2026-09-13T22:31:32Z</t>
+          <t>2026-09-14T23:16:43Z</t>
         </is>
       </c>
     </row>
@@ -13843,7 +13843,7 @@
       </c>
       <c r="S158" s="4" t="inlineStr">
         <is>
-          <t>2026-09-13T22:31:32Z</t>
+          <t>2026-09-14T23:16:43Z</t>
         </is>
       </c>
     </row>
@@ -13932,7 +13932,7 @@
       </c>
       <c r="S159" s="4" t="inlineStr">
         <is>
-          <t>2026-09-13T22:31:32Z</t>
+          <t>2026-09-14T23:16:43Z</t>
         </is>
       </c>
     </row>
@@ -14021,7 +14021,7 @@
       </c>
       <c r="S160" s="4" t="inlineStr">
         <is>
-          <t>2026-09-13T22:31:32Z</t>
+          <t>2026-09-14T23:16:43Z</t>
         </is>
       </c>
     </row>
@@ -14106,7 +14106,7 @@
       </c>
       <c r="S161" s="4" t="inlineStr">
         <is>
-          <t>2026-09-13T22:31:32Z</t>
+          <t>2026-09-14T23:16:43Z</t>
         </is>
       </c>
     </row>
@@ -14195,7 +14195,7 @@
       </c>
       <c r="S162" s="4" t="inlineStr">
         <is>
-          <t>2026-09-13T22:31:32Z</t>
+          <t>2026-09-14T23:16:43Z</t>
         </is>
       </c>
     </row>
@@ -14284,7 +14284,7 @@
       </c>
       <c r="S163" s="4" t="inlineStr">
         <is>
-          <t>2026-09-13T22:31:32Z</t>
+          <t>2026-09-14T23:16:43Z</t>
         </is>
       </c>
     </row>
@@ -14369,7 +14369,7 @@
       </c>
       <c r="S164" s="4" t="inlineStr">
         <is>
-          <t>2026-09-13T22:31:32Z</t>
+          <t>2026-09-14T23:16:43Z</t>
         </is>
       </c>
     </row>
@@ -14458,7 +14458,7 @@
       </c>
       <c r="S165" s="4" t="inlineStr">
         <is>
-          <t>2026-09-13T22:31:32Z</t>
+          <t>2026-09-14T23:16:43Z</t>
         </is>
       </c>
     </row>
@@ -14547,7 +14547,7 @@
       </c>
       <c r="S166" s="4" t="inlineStr">
         <is>
-          <t>2026-09-13T22:31:32Z</t>
+          <t>2026-09-14T23:16:43Z</t>
         </is>
       </c>
     </row>
@@ -14632,7 +14632,7 @@
       </c>
       <c r="S167" s="4" t="inlineStr">
         <is>
-          <t>2026-09-13T22:31:32Z</t>
+          <t>2026-09-14T23:16:43Z</t>
         </is>
       </c>
     </row>
@@ -14721,7 +14721,7 @@
       </c>
       <c r="S168" s="4" t="inlineStr">
         <is>
-          <t>2026-09-13T22:31:32Z</t>
+          <t>2026-09-14T23:16:43Z</t>
         </is>
       </c>
     </row>
@@ -14810,7 +14810,7 @@
       </c>
       <c r="S169" s="4" t="inlineStr">
         <is>
-          <t>2026-09-13T22:31:32Z</t>
+          <t>2026-09-14T23:16:43Z</t>
         </is>
       </c>
     </row>
@@ -14895,7 +14895,7 @@
       </c>
       <c r="S170" s="4" t="inlineStr">
         <is>
-          <t>2026-09-13T22:31:32Z</t>
+          <t>2026-09-14T23:16:43Z</t>
         </is>
       </c>
     </row>
@@ -14984,7 +14984,7 @@
       </c>
       <c r="S171" s="4" t="inlineStr">
         <is>
-          <t>2026-09-13T22:31:32Z</t>
+          <t>2026-09-14T23:16:43Z</t>
         </is>
       </c>
     </row>
@@ -15073,7 +15073,7 @@
       </c>
       <c r="S172" s="4" t="inlineStr">
         <is>
-          <t>2026-09-13T22:31:32Z</t>
+          <t>2026-09-14T23:16:43Z</t>
         </is>
       </c>
     </row>
@@ -15158,7 +15158,7 @@
       </c>
       <c r="S173" s="4" t="inlineStr">
         <is>
-          <t>2026-09-13T22:31:32Z</t>
+          <t>2026-09-14T23:16:43Z</t>
         </is>
       </c>
     </row>
@@ -15247,7 +15247,7 @@
       </c>
       <c r="S174" s="4" t="inlineStr">
         <is>
-          <t>2026-09-13T22:31:32Z</t>
+          <t>2026-09-14T23:16:43Z</t>
         </is>
       </c>
     </row>
@@ -15336,7 +15336,7 @@
       </c>
       <c r="S175" s="4" t="inlineStr">
         <is>
-          <t>2026-09-13T22:31:32Z</t>
+          <t>2026-09-14T23:16:43Z</t>
         </is>
       </c>
     </row>
@@ -15421,7 +15421,7 @@
       </c>
       <c r="S176" s="4" t="inlineStr">
         <is>
-          <t>2026-09-13T22:31:32Z</t>
+          <t>2026-09-14T23:16:43Z</t>
         </is>
       </c>
     </row>
@@ -15510,7 +15510,7 @@
       </c>
       <c r="S177" s="4" t="inlineStr">
         <is>
-          <t>2026-09-13T22:31:32Z</t>
+          <t>2026-09-14T23:16:43Z</t>
         </is>
       </c>
     </row>
@@ -15599,7 +15599,7 @@
       </c>
       <c r="S178" s="4" t="inlineStr">
         <is>
-          <t>2026-09-13T22:31:32Z</t>
+          <t>2026-09-14T23:16:43Z</t>
         </is>
       </c>
     </row>
@@ -15688,7 +15688,7 @@
       </c>
       <c r="S179" s="4" t="inlineStr">
         <is>
-          <t>2026-09-13T22:31:32Z</t>
+          <t>2026-09-14T23:16:43Z</t>
         </is>
       </c>
     </row>
@@ -15777,7 +15777,7 @@
       </c>
       <c r="S180" s="4" t="inlineStr">
         <is>
-          <t>2026-09-13T22:31:32Z</t>
+          <t>2026-09-14T23:16:43Z</t>
         </is>
       </c>
     </row>
@@ -15866,7 +15866,7 @@
       </c>
       <c r="S181" s="4" t="inlineStr">
         <is>
-          <t>2026-09-13T22:31:32Z</t>
+          <t>2026-09-14T23:16:43Z</t>
         </is>
       </c>
     </row>
@@ -15955,7 +15955,7 @@
       </c>
       <c r="S182" s="4" t="inlineStr">
         <is>
-          <t>2026-09-13T22:31:32Z</t>
+          <t>2026-09-14T23:16:43Z</t>
         </is>
       </c>
     </row>
@@ -16044,7 +16044,7 @@
       </c>
       <c r="S183" s="4" t="inlineStr">
         <is>
-          <t>2026-09-13T22:31:32Z</t>
+          <t>2026-09-14T23:16:43Z</t>
         </is>
       </c>
     </row>
@@ -16133,7 +16133,7 @@
       </c>
       <c r="S184" s="4" t="inlineStr">
         <is>
-          <t>2026-09-13T22:31:32Z</t>
+          <t>2026-09-14T23:16:43Z</t>
         </is>
       </c>
     </row>
@@ -16222,7 +16222,7 @@
       </c>
       <c r="S185" s="4" t="inlineStr">
         <is>
-          <t>2026-09-13T22:31:32Z</t>
+          <t>2026-09-14T23:16:43Z</t>
         </is>
       </c>
     </row>
@@ -16311,7 +16311,7 @@
       </c>
       <c r="S186" s="4" t="inlineStr">
         <is>
-          <t>2026-09-13T22:31:32Z</t>
+          <t>2026-09-14T23:16:43Z</t>
         </is>
       </c>
     </row>
@@ -16400,7 +16400,7 @@
       </c>
       <c r="S187" s="4" t="inlineStr">
         <is>
-          <t>2026-09-13T22:31:32Z</t>
+          <t>2026-09-14T23:16:43Z</t>
         </is>
       </c>
     </row>
@@ -16489,7 +16489,7 @@
       </c>
       <c r="S188" s="4" t="inlineStr">
         <is>
-          <t>2026-09-13T22:31:32Z</t>
+          <t>2026-09-14T23:16:43Z</t>
         </is>
       </c>
     </row>
@@ -16578,7 +16578,7 @@
       </c>
       <c r="S189" s="4" t="inlineStr">
         <is>
-          <t>2026-09-13T22:31:32Z</t>
+          <t>2026-09-14T23:16:43Z</t>
         </is>
       </c>
     </row>
@@ -16663,7 +16663,7 @@
       </c>
       <c r="S190" s="4" t="inlineStr">
         <is>
-          <t>2026-09-13T22:31:32Z</t>
+          <t>2026-09-14T23:16:43Z</t>
         </is>
       </c>
     </row>
@@ -16748,7 +16748,7 @@
       </c>
       <c r="S191" s="4" t="inlineStr">
         <is>
-          <t>2026-09-13T22:31:32Z</t>
+          <t>2026-09-14T23:16:43Z</t>
         </is>
       </c>
     </row>
@@ -16833,7 +16833,7 @@
       </c>
       <c r="S192" s="4" t="inlineStr">
         <is>
-          <t>2026-09-13T22:31:32Z</t>
+          <t>2026-09-14T23:16:43Z</t>
         </is>
       </c>
     </row>
@@ -16918,7 +16918,7 @@
       </c>
       <c r="S193" s="4" t="inlineStr">
         <is>
-          <t>2026-09-13T22:31:32Z</t>
+          <t>2026-09-14T23:16:43Z</t>
         </is>
       </c>
     </row>
@@ -17003,7 +17003,7 @@
       </c>
       <c r="S194" s="4" t="inlineStr">
         <is>
-          <t>2026-09-13T22:31:32Z</t>
+          <t>2026-09-14T23:16:43Z</t>
         </is>
       </c>
     </row>
@@ -17088,7 +17088,7 @@
       </c>
       <c r="S195" s="4" t="inlineStr">
         <is>
-          <t>2026-09-13T22:31:32Z</t>
+          <t>2026-09-14T23:16:43Z</t>
         </is>
       </c>
     </row>
@@ -17173,7 +17173,7 @@
       </c>
       <c r="S196" s="4" t="inlineStr">
         <is>
-          <t>2026-09-13T22:31:32Z</t>
+          <t>2026-09-14T23:16:43Z</t>
         </is>
       </c>
     </row>
@@ -17258,7 +17258,7 @@
       </c>
       <c r="S197" s="4" t="inlineStr">
         <is>
-          <t>2026-09-13T22:31:32Z</t>
+          <t>2026-09-14T23:16:43Z</t>
         </is>
       </c>
     </row>
@@ -17343,7 +17343,7 @@
       </c>
       <c r="S198" s="4" t="inlineStr">
         <is>
-          <t>2026-09-13T22:31:32Z</t>
+          <t>2026-09-14T23:16:43Z</t>
         </is>
       </c>
     </row>
@@ -17428,7 +17428,7 @@
       </c>
       <c r="S199" s="4" t="inlineStr">
         <is>
-          <t>2026-09-13T22:31:32Z</t>
+          <t>2026-09-14T23:16:43Z</t>
         </is>
       </c>
     </row>
@@ -17513,7 +17513,7 @@
       </c>
       <c r="S200" s="4" t="inlineStr">
         <is>
-          <t>2026-09-13T22:31:32Z</t>
+          <t>2026-09-14T23:16:43Z</t>
         </is>
       </c>
     </row>
@@ -17598,7 +17598,7 @@
       </c>
       <c r="S201" s="4" t="inlineStr">
         <is>
-          <t>2026-09-13T22:31:32Z</t>
+          <t>2026-09-14T23:16:43Z</t>
         </is>
       </c>
     </row>
@@ -17683,7 +17683,7 @@
       </c>
       <c r="S202" s="4" t="inlineStr">
         <is>
-          <t>2026-09-13T22:31:32Z</t>
+          <t>2026-09-14T23:16:43Z</t>
         </is>
       </c>
     </row>
@@ -17768,7 +17768,7 @@
       </c>
       <c r="S203" s="4" t="inlineStr">
         <is>
-          <t>2026-09-13T22:31:32Z</t>
+          <t>2026-09-14T23:16:43Z</t>
         </is>
       </c>
     </row>
@@ -17853,7 +17853,7 @@
       </c>
       <c r="S204" s="4" t="inlineStr">
         <is>
-          <t>2026-09-13T22:31:32Z</t>
+          <t>2026-09-14T23:16:43Z</t>
         </is>
       </c>
     </row>
@@ -17938,7 +17938,7 @@
       </c>
       <c r="S205" s="4" t="inlineStr">
         <is>
-          <t>2026-09-13T22:31:32Z</t>
+          <t>2026-09-14T23:16:43Z</t>
         </is>
       </c>
     </row>
@@ -18023,7 +18023,7 @@
       </c>
       <c r="S206" s="4" t="inlineStr">
         <is>
-          <t>2026-09-13T22:31:32Z</t>
+          <t>2026-09-14T23:16:43Z</t>
         </is>
       </c>
     </row>
@@ -18108,7 +18108,7 @@
       </c>
       <c r="S207" s="4" t="inlineStr">
         <is>
-          <t>2026-09-13T22:31:32Z</t>
+          <t>2026-09-14T23:16:43Z</t>
         </is>
       </c>
     </row>
@@ -18193,7 +18193,7 @@
       </c>
       <c r="S208" s="4" t="inlineStr">
         <is>
-          <t>2026-09-13T22:31:32Z</t>
+          <t>2026-09-14T23:16:43Z</t>
         </is>
       </c>
     </row>
@@ -18278,7 +18278,7 @@
       </c>
       <c r="S209" s="4" t="inlineStr">
         <is>
-          <t>2026-09-13T22:31:32Z</t>
+          <t>2026-09-14T23:16:43Z</t>
         </is>
       </c>
     </row>
@@ -18363,7 +18363,7 @@
       </c>
       <c r="S210" s="4" t="inlineStr">
         <is>
-          <t>2026-09-13T22:31:32Z</t>
+          <t>2026-09-14T23:16:43Z</t>
         </is>
       </c>
     </row>
@@ -18452,7 +18452,7 @@
       </c>
       <c r="S211" s="4" t="inlineStr">
         <is>
-          <t>2026-09-13T22:31:32Z</t>
+          <t>2026-09-14T23:16:43Z</t>
         </is>
       </c>
     </row>
@@ -18541,7 +18541,7 @@
       </c>
       <c r="S212" s="4" t="inlineStr">
         <is>
-          <t>2026-09-13T22:31:32Z</t>
+          <t>2026-09-14T23:16:43Z</t>
         </is>
       </c>
     </row>
@@ -18626,7 +18626,7 @@
       </c>
       <c r="S213" s="4" t="inlineStr">
         <is>
-          <t>2026-09-13T22:31:32Z</t>
+          <t>2026-09-14T23:16:43Z</t>
         </is>
       </c>
     </row>
@@ -18715,7 +18715,7 @@
       </c>
       <c r="S214" s="4" t="inlineStr">
         <is>
-          <t>2026-09-13T22:31:32Z</t>
+          <t>2026-09-14T23:16:43Z</t>
         </is>
       </c>
     </row>
@@ -18804,7 +18804,7 @@
       </c>
       <c r="S215" s="4" t="inlineStr">
         <is>
-          <t>2026-09-13T22:31:32Z</t>
+          <t>2026-09-14T23:16:43Z</t>
         </is>
       </c>
     </row>
@@ -18889,7 +18889,7 @@
       </c>
       <c r="S216" s="4" t="inlineStr">
         <is>
-          <t>2026-09-13T22:31:32Z</t>
+          <t>2026-09-14T23:16:43Z</t>
         </is>
       </c>
     </row>
@@ -18978,7 +18978,7 @@
       </c>
       <c r="S217" s="4" t="inlineStr">
         <is>
-          <t>2026-09-13T22:31:32Z</t>
+          <t>2026-09-14T23:16:43Z</t>
         </is>
       </c>
     </row>
@@ -19067,7 +19067,7 @@
       </c>
       <c r="S218" s="4" t="inlineStr">
         <is>
-          <t>2026-09-13T22:31:32Z</t>
+          <t>2026-09-14T23:16:43Z</t>
         </is>
       </c>
     </row>
@@ -19152,7 +19152,7 @@
       </c>
       <c r="S219" s="4" t="inlineStr">
         <is>
-          <t>2026-09-13T22:31:32Z</t>
+          <t>2026-09-14T23:16:43Z</t>
         </is>
       </c>
     </row>
@@ -19241,7 +19241,7 @@
       </c>
       <c r="S220" s="4" t="inlineStr">
         <is>
-          <t>2026-09-13T22:31:32Z</t>
+          <t>2026-09-14T23:16:43Z</t>
         </is>
       </c>
     </row>
@@ -19330,7 +19330,7 @@
       </c>
       <c r="S221" s="4" t="inlineStr">
         <is>
-          <t>2026-09-13T22:31:32Z</t>
+          <t>2026-09-14T23:16:43Z</t>
         </is>
       </c>
     </row>
@@ -19415,7 +19415,7 @@
       </c>
       <c r="S222" s="4" t="inlineStr">
         <is>
-          <t>2026-09-13T22:31:32Z</t>
+          <t>2026-09-14T23:16:43Z</t>
         </is>
       </c>
     </row>
@@ -19504,7 +19504,7 @@
       </c>
       <c r="S223" s="4" t="inlineStr">
         <is>
-          <t>2026-09-13T22:31:32Z</t>
+          <t>2026-09-14T23:16:43Z</t>
         </is>
       </c>
     </row>
@@ -19593,7 +19593,7 @@
       </c>
       <c r="S224" s="4" t="inlineStr">
         <is>
-          <t>2026-09-13T22:31:32Z</t>
+          <t>2026-09-14T23:16:43Z</t>
         </is>
       </c>
     </row>
@@ -19678,7 +19678,7 @@
       </c>
       <c r="S225" s="4" t="inlineStr">
         <is>
-          <t>2026-09-13T22:31:32Z</t>
+          <t>2026-09-14T23:16:43Z</t>
         </is>
       </c>
     </row>
@@ -19767,7 +19767,7 @@
       </c>
       <c r="S226" s="4" t="inlineStr">
         <is>
-          <t>2026-09-13T22:31:32Z</t>
+          <t>2026-09-14T23:16:43Z</t>
         </is>
       </c>
     </row>
@@ -19856,7 +19856,7 @@
       </c>
       <c r="S227" s="4" t="inlineStr">
         <is>
-          <t>2026-09-13T22:31:32Z</t>
+          <t>2026-09-14T23:16:43Z</t>
         </is>
       </c>
     </row>
@@ -19941,7 +19941,7 @@
       </c>
       <c r="S228" s="4" t="inlineStr">
         <is>
-          <t>2026-09-13T22:31:32Z</t>
+          <t>2026-09-14T23:16:43Z</t>
         </is>
       </c>
     </row>
@@ -20030,7 +20030,7 @@
       </c>
       <c r="S229" s="4" t="inlineStr">
         <is>
-          <t>2026-09-13T22:31:32Z</t>
+          <t>2026-09-14T23:16:43Z</t>
         </is>
       </c>
     </row>
@@ -20119,7 +20119,7 @@
       </c>
       <c r="S230" s="4" t="inlineStr">
         <is>
-          <t>2026-09-13T22:31:32Z</t>
+          <t>2026-09-14T23:16:43Z</t>
         </is>
       </c>
     </row>
@@ -20204,7 +20204,7 @@
       </c>
       <c r="S231" s="4" t="inlineStr">
         <is>
-          <t>2026-09-13T22:31:32Z</t>
+          <t>2026-09-14T23:16:43Z</t>
         </is>
       </c>
     </row>
@@ -20293,7 +20293,7 @@
       </c>
       <c r="S232" s="4" t="inlineStr">
         <is>
-          <t>2026-09-13T22:31:32Z</t>
+          <t>2026-09-14T23:16:43Z</t>
         </is>
       </c>
     </row>
@@ -20382,7 +20382,7 @@
       </c>
       <c r="S233" s="4" t="inlineStr">
         <is>
-          <t>2026-09-13T22:31:32Z</t>
+          <t>2026-09-14T23:16:43Z</t>
         </is>
       </c>
     </row>
@@ -20467,7 +20467,7 @@
       </c>
       <c r="S234" s="4" t="inlineStr">
         <is>
-          <t>2026-09-13T22:31:32Z</t>
+          <t>2026-09-14T23:16:43Z</t>
         </is>
       </c>
     </row>
@@ -20556,7 +20556,7 @@
       </c>
       <c r="S235" s="4" t="inlineStr">
         <is>
-          <t>2026-09-13T22:31:32Z</t>
+          <t>2026-09-14T23:16:43Z</t>
         </is>
       </c>
     </row>
@@ -20645,7 +20645,7 @@
       </c>
       <c r="S236" s="4" t="inlineStr">
         <is>
-          <t>2026-09-13T22:31:32Z</t>
+          <t>2026-09-14T23:16:43Z</t>
         </is>
       </c>
     </row>
@@ -20730,7 +20730,7 @@
       </c>
       <c r="S237" s="4" t="inlineStr">
         <is>
-          <t>2026-09-13T22:31:32Z</t>
+          <t>2026-09-14T23:16:43Z</t>
         </is>
       </c>
     </row>
@@ -20819,7 +20819,7 @@
       </c>
       <c r="S238" s="4" t="inlineStr">
         <is>
-          <t>2026-09-13T22:31:32Z</t>
+          <t>2026-09-14T23:16:43Z</t>
         </is>
       </c>
     </row>
@@ -20908,7 +20908,7 @@
       </c>
       <c r="S239" s="4" t="inlineStr">
         <is>
-          <t>2026-09-13T22:31:32Z</t>
+          <t>2026-09-14T23:16:43Z</t>
         </is>
       </c>
     </row>
@@ -20997,7 +20997,7 @@
       </c>
       <c r="S240" s="4" t="inlineStr">
         <is>
-          <t>2026-09-13T22:31:32Z</t>
+          <t>2026-09-14T23:16:43Z</t>
         </is>
       </c>
     </row>
@@ -21086,7 +21086,7 @@
       </c>
       <c r="S241" s="4" t="inlineStr">
         <is>
-          <t>2026-09-13T22:31:32Z</t>
+          <t>2026-09-14T23:16:43Z</t>
         </is>
       </c>
     </row>
@@ -21175,7 +21175,7 @@
       </c>
       <c r="S242" s="4" t="inlineStr">
         <is>
-          <t>2026-09-13T22:31:32Z</t>
+          <t>2026-09-14T23:16:43Z</t>
         </is>
       </c>
     </row>
@@ -21264,7 +21264,7 @@
       </c>
       <c r="S243" s="4" t="inlineStr">
         <is>
-          <t>2026-09-13T22:31:32Z</t>
+          <t>2026-09-14T23:16:43Z</t>
         </is>
       </c>
     </row>
@@ -21353,7 +21353,7 @@
       </c>
       <c r="S244" s="4" t="inlineStr">
         <is>
-          <t>2026-09-13T22:31:32Z</t>
+          <t>2026-09-14T23:16:43Z</t>
         </is>
       </c>
     </row>
@@ -21442,7 +21442,7 @@
       </c>
       <c r="S245" s="4" t="inlineStr">
         <is>
-          <t>2026-09-13T22:31:32Z</t>
+          <t>2026-09-14T23:16:43Z</t>
         </is>
       </c>
     </row>
@@ -21531,7 +21531,7 @@
       </c>
       <c r="S246" s="4" t="inlineStr">
         <is>
-          <t>2026-09-13T22:31:32Z</t>
+          <t>2026-09-14T23:16:43Z</t>
         </is>
       </c>
     </row>
@@ -21620,7 +21620,7 @@
       </c>
       <c r="S247" s="4" t="inlineStr">
         <is>
-          <t>2026-09-13T22:31:32Z</t>
+          <t>2026-09-14T23:16:43Z</t>
         </is>
       </c>
     </row>
@@ -21709,7 +21709,7 @@
       </c>
       <c r="S248" s="4" t="inlineStr">
         <is>
-          <t>2026-09-13T22:31:32Z</t>
+          <t>2026-09-14T23:16:43Z</t>
         </is>
       </c>
     </row>
@@ -21798,7 +21798,7 @@
       </c>
       <c r="S249" s="4" t="inlineStr">
         <is>
-          <t>2026-09-13T22:31:32Z</t>
+          <t>2026-09-14T23:16:43Z</t>
         </is>
       </c>
     </row>
@@ -21887,7 +21887,7 @@
       </c>
       <c r="S250" s="4" t="inlineStr">
         <is>
-          <t>2026-09-13T22:31:32Z</t>
+          <t>2026-09-14T23:16:43Z</t>
         </is>
       </c>
     </row>
@@ -22019,7 +22019,7 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>2026-09-13T22:31:32Z</t>
+          <t>2026-09-14T23:16:43Z</t>
         </is>
       </c>
     </row>
@@ -22099,7 +22099,7 @@
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>{"dataset_id": "bcv_pib_sector_institucional_anual", "title": "Producto interno bruto por sector institucional anual", "table": "Variaciones porcentuales", "source_file": "5_2_1_si_anual.xlsx", "base": "2007", "price_type": "Precios constantes", "measure": "Variación porcentual interanual", "frequency": "Anual", "period": "2025", "year": 2025, "quarter": null, "classification": "Sector institucional", "component": "Impuestos netos sobre los productos", "value": 10.600260421283764, "unit": "Porcentaje", "status": "Preliminar", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/cuentas_macroeconomicas/5_2_1_si_anual.xlsx", "fetched_at": "2026-09-13T22:31:32Z"}</t>
+          <t>{"dataset_id": "bcv_pib_sector_institucional_anual", "title": "Producto interno bruto por sector institucional anual", "table": "Variaciones porcentuales", "source_file": "5_2_1_si_anual.xlsx", "base": "2007", "price_type": "Precios constantes", "measure": "Variación porcentual interanual", "frequency": "Anual", "period": "2025", "year": 2025, "quarter": null, "classification": "Sector institucional", "component": "Impuestos netos sobre los productos", "value": 10.600260421283764, "unit": "Porcentaje", "status": "Preliminar", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/cuentas_macroeconomicas/5_2_1_si_anual.xlsx", "fetched_at": "2026-09-14T23:16:43Z"}</t>
         </is>
       </c>
     </row>

--- a/assets/data/bcv/excel/ove_bcv_pib_sector_institucional_anual.xlsx
+++ b/assets/data/bcv/excel/ove_bcv_pib_sector_institucional_anual.xlsx
@@ -736,7 +736,7 @@
       </c>
       <c r="S7" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14T23:16:43Z</t>
+          <t>2026-09-15T23:01:39Z</t>
         </is>
       </c>
     </row>
@@ -821,7 +821,7 @@
       </c>
       <c r="S8" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14T23:16:43Z</t>
+          <t>2026-09-15T23:01:39Z</t>
         </is>
       </c>
     </row>
@@ -906,7 +906,7 @@
       </c>
       <c r="S9" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14T23:16:43Z</t>
+          <t>2026-09-15T23:01:39Z</t>
         </is>
       </c>
     </row>
@@ -991,7 +991,7 @@
       </c>
       <c r="S10" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14T23:16:43Z</t>
+          <t>2026-09-15T23:01:39Z</t>
         </is>
       </c>
     </row>
@@ -1076,7 +1076,7 @@
       </c>
       <c r="S11" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14T23:16:43Z</t>
+          <t>2026-09-15T23:01:39Z</t>
         </is>
       </c>
     </row>
@@ -1161,7 +1161,7 @@
       </c>
       <c r="S12" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14T23:16:43Z</t>
+          <t>2026-09-15T23:01:39Z</t>
         </is>
       </c>
     </row>
@@ -1246,7 +1246,7 @@
       </c>
       <c r="S13" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14T23:16:43Z</t>
+          <t>2026-09-15T23:01:39Z</t>
         </is>
       </c>
     </row>
@@ -1331,7 +1331,7 @@
       </c>
       <c r="S14" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14T23:16:43Z</t>
+          <t>2026-09-15T23:01:39Z</t>
         </is>
       </c>
     </row>
@@ -1416,7 +1416,7 @@
       </c>
       <c r="S15" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14T23:16:43Z</t>
+          <t>2026-09-15T23:01:39Z</t>
         </is>
       </c>
     </row>
@@ -1501,7 +1501,7 @@
       </c>
       <c r="S16" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14T23:16:43Z</t>
+          <t>2026-09-15T23:01:39Z</t>
         </is>
       </c>
     </row>
@@ -1586,7 +1586,7 @@
       </c>
       <c r="S17" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14T23:16:43Z</t>
+          <t>2026-09-15T23:01:39Z</t>
         </is>
       </c>
     </row>
@@ -1671,7 +1671,7 @@
       </c>
       <c r="S18" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14T23:16:43Z</t>
+          <t>2026-09-15T23:01:39Z</t>
         </is>
       </c>
     </row>
@@ -1756,7 +1756,7 @@
       </c>
       <c r="S19" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14T23:16:43Z</t>
+          <t>2026-09-15T23:01:39Z</t>
         </is>
       </c>
     </row>
@@ -1841,7 +1841,7 @@
       </c>
       <c r="S20" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14T23:16:43Z</t>
+          <t>2026-09-15T23:01:39Z</t>
         </is>
       </c>
     </row>
@@ -1926,7 +1926,7 @@
       </c>
       <c r="S21" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14T23:16:43Z</t>
+          <t>2026-09-15T23:01:39Z</t>
         </is>
       </c>
     </row>
@@ -2011,7 +2011,7 @@
       </c>
       <c r="S22" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14T23:16:43Z</t>
+          <t>2026-09-15T23:01:39Z</t>
         </is>
       </c>
     </row>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="S23" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14T23:16:43Z</t>
+          <t>2026-09-15T23:01:39Z</t>
         </is>
       </c>
     </row>
@@ -2181,7 +2181,7 @@
       </c>
       <c r="S24" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14T23:16:43Z</t>
+          <t>2026-09-15T23:01:39Z</t>
         </is>
       </c>
     </row>
@@ -2266,7 +2266,7 @@
       </c>
       <c r="S25" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14T23:16:43Z</t>
+          <t>2026-09-15T23:01:39Z</t>
         </is>
       </c>
     </row>
@@ -2351,7 +2351,7 @@
       </c>
       <c r="S26" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14T23:16:43Z</t>
+          <t>2026-09-15T23:01:39Z</t>
         </is>
       </c>
     </row>
@@ -2436,7 +2436,7 @@
       </c>
       <c r="S27" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14T23:16:43Z</t>
+          <t>2026-09-15T23:01:39Z</t>
         </is>
       </c>
     </row>
@@ -2525,7 +2525,7 @@
       </c>
       <c r="S28" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14T23:16:43Z</t>
+          <t>2026-09-15T23:01:39Z</t>
         </is>
       </c>
     </row>
@@ -2614,7 +2614,7 @@
       </c>
       <c r="S29" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14T23:16:43Z</t>
+          <t>2026-09-15T23:01:39Z</t>
         </is>
       </c>
     </row>
@@ -2699,7 +2699,7 @@
       </c>
       <c r="S30" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14T23:16:43Z</t>
+          <t>2026-09-15T23:01:39Z</t>
         </is>
       </c>
     </row>
@@ -2788,7 +2788,7 @@
       </c>
       <c r="S31" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14T23:16:43Z</t>
+          <t>2026-09-15T23:01:39Z</t>
         </is>
       </c>
     </row>
@@ -2877,7 +2877,7 @@
       </c>
       <c r="S32" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14T23:16:43Z</t>
+          <t>2026-09-15T23:01:39Z</t>
         </is>
       </c>
     </row>
@@ -2962,7 +2962,7 @@
       </c>
       <c r="S33" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14T23:16:43Z</t>
+          <t>2026-09-15T23:01:39Z</t>
         </is>
       </c>
     </row>
@@ -3051,7 +3051,7 @@
       </c>
       <c r="S34" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14T23:16:43Z</t>
+          <t>2026-09-15T23:01:39Z</t>
         </is>
       </c>
     </row>
@@ -3140,7 +3140,7 @@
       </c>
       <c r="S35" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14T23:16:43Z</t>
+          <t>2026-09-15T23:01:39Z</t>
         </is>
       </c>
     </row>
@@ -3225,7 +3225,7 @@
       </c>
       <c r="S36" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14T23:16:43Z</t>
+          <t>2026-09-15T23:01:39Z</t>
         </is>
       </c>
     </row>
@@ -3314,7 +3314,7 @@
       </c>
       <c r="S37" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14T23:16:43Z</t>
+          <t>2026-09-15T23:01:39Z</t>
         </is>
       </c>
     </row>
@@ -3403,7 +3403,7 @@
       </c>
       <c r="S38" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14T23:16:43Z</t>
+          <t>2026-09-15T23:01:39Z</t>
         </is>
       </c>
     </row>
@@ -3488,7 +3488,7 @@
       </c>
       <c r="S39" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14T23:16:43Z</t>
+          <t>2026-09-15T23:01:39Z</t>
         </is>
       </c>
     </row>
@@ -3577,7 +3577,7 @@
       </c>
       <c r="S40" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14T23:16:43Z</t>
+          <t>2026-09-15T23:01:39Z</t>
         </is>
       </c>
     </row>
@@ -3666,7 +3666,7 @@
       </c>
       <c r="S41" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14T23:16:43Z</t>
+          <t>2026-09-15T23:01:39Z</t>
         </is>
       </c>
     </row>
@@ -3751,7 +3751,7 @@
       </c>
       <c r="S42" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14T23:16:43Z</t>
+          <t>2026-09-15T23:01:39Z</t>
         </is>
       </c>
     </row>
@@ -3840,7 +3840,7 @@
       </c>
       <c r="S43" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14T23:16:43Z</t>
+          <t>2026-09-15T23:01:39Z</t>
         </is>
       </c>
     </row>
@@ -3929,7 +3929,7 @@
       </c>
       <c r="S44" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14T23:16:43Z</t>
+          <t>2026-09-15T23:01:39Z</t>
         </is>
       </c>
     </row>
@@ -4014,7 +4014,7 @@
       </c>
       <c r="S45" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14T23:16:43Z</t>
+          <t>2026-09-15T23:01:39Z</t>
         </is>
       </c>
     </row>
@@ -4103,7 +4103,7 @@
       </c>
       <c r="S46" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14T23:16:43Z</t>
+          <t>2026-09-15T23:01:39Z</t>
         </is>
       </c>
     </row>
@@ -4192,7 +4192,7 @@
       </c>
       <c r="S47" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14T23:16:43Z</t>
+          <t>2026-09-15T23:01:39Z</t>
         </is>
       </c>
     </row>
@@ -4277,7 +4277,7 @@
       </c>
       <c r="S48" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14T23:16:43Z</t>
+          <t>2026-09-15T23:01:39Z</t>
         </is>
       </c>
     </row>
@@ -4366,7 +4366,7 @@
       </c>
       <c r="S49" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14T23:16:43Z</t>
+          <t>2026-09-15T23:01:39Z</t>
         </is>
       </c>
     </row>
@@ -4455,7 +4455,7 @@
       </c>
       <c r="S50" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14T23:16:43Z</t>
+          <t>2026-09-15T23:01:39Z</t>
         </is>
       </c>
     </row>
@@ -4540,7 +4540,7 @@
       </c>
       <c r="S51" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14T23:16:43Z</t>
+          <t>2026-09-15T23:01:39Z</t>
         </is>
       </c>
     </row>
@@ -4629,7 +4629,7 @@
       </c>
       <c r="S52" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14T23:16:43Z</t>
+          <t>2026-09-15T23:01:39Z</t>
         </is>
       </c>
     </row>
@@ -4718,7 +4718,7 @@
       </c>
       <c r="S53" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14T23:16:43Z</t>
+          <t>2026-09-15T23:01:39Z</t>
         </is>
       </c>
     </row>
@@ -4803,7 +4803,7 @@
       </c>
       <c r="S54" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14T23:16:43Z</t>
+          <t>2026-09-15T23:01:39Z</t>
         </is>
       </c>
     </row>
@@ -4892,7 +4892,7 @@
       </c>
       <c r="S55" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14T23:16:43Z</t>
+          <t>2026-09-15T23:01:39Z</t>
         </is>
       </c>
     </row>
@@ -4981,7 +4981,7 @@
       </c>
       <c r="S56" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14T23:16:43Z</t>
+          <t>2026-09-15T23:01:39Z</t>
         </is>
       </c>
     </row>
@@ -5070,7 +5070,7 @@
       </c>
       <c r="S57" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14T23:16:43Z</t>
+          <t>2026-09-15T23:01:39Z</t>
         </is>
       </c>
     </row>
@@ -5159,7 +5159,7 @@
       </c>
       <c r="S58" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14T23:16:43Z</t>
+          <t>2026-09-15T23:01:39Z</t>
         </is>
       </c>
     </row>
@@ -5248,7 +5248,7 @@
       </c>
       <c r="S59" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14T23:16:43Z</t>
+          <t>2026-09-15T23:01:39Z</t>
         </is>
       </c>
     </row>
@@ -5337,7 +5337,7 @@
       </c>
       <c r="S60" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14T23:16:43Z</t>
+          <t>2026-09-15T23:01:39Z</t>
         </is>
       </c>
     </row>
@@ -5426,7 +5426,7 @@
       </c>
       <c r="S61" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14T23:16:43Z</t>
+          <t>2026-09-15T23:01:39Z</t>
         </is>
       </c>
     </row>
@@ -5515,7 +5515,7 @@
       </c>
       <c r="S62" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14T23:16:43Z</t>
+          <t>2026-09-15T23:01:39Z</t>
         </is>
       </c>
     </row>
@@ -5604,7 +5604,7 @@
       </c>
       <c r="S63" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14T23:16:43Z</t>
+          <t>2026-09-15T23:01:39Z</t>
         </is>
       </c>
     </row>
@@ -5693,7 +5693,7 @@
       </c>
       <c r="S64" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14T23:16:43Z</t>
+          <t>2026-09-15T23:01:39Z</t>
         </is>
       </c>
     </row>
@@ -5782,7 +5782,7 @@
       </c>
       <c r="S65" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14T23:16:43Z</t>
+          <t>2026-09-15T23:01:39Z</t>
         </is>
       </c>
     </row>
@@ -5871,7 +5871,7 @@
       </c>
       <c r="S66" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14T23:16:43Z</t>
+          <t>2026-09-15T23:01:39Z</t>
         </is>
       </c>
     </row>
@@ -5960,7 +5960,7 @@
       </c>
       <c r="S67" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14T23:16:43Z</t>
+          <t>2026-09-15T23:01:39Z</t>
         </is>
       </c>
     </row>
@@ -6045,7 +6045,7 @@
       </c>
       <c r="S68" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14T23:16:43Z</t>
+          <t>2026-09-15T23:01:39Z</t>
         </is>
       </c>
     </row>
@@ -6130,7 +6130,7 @@
       </c>
       <c r="S69" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14T23:16:43Z</t>
+          <t>2026-09-15T23:01:39Z</t>
         </is>
       </c>
     </row>
@@ -6215,7 +6215,7 @@
       </c>
       <c r="S70" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14T23:16:43Z</t>
+          <t>2026-09-15T23:01:39Z</t>
         </is>
       </c>
     </row>
@@ -6300,7 +6300,7 @@
       </c>
       <c r="S71" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14T23:16:43Z</t>
+          <t>2026-09-15T23:01:39Z</t>
         </is>
       </c>
     </row>
@@ -6385,7 +6385,7 @@
       </c>
       <c r="S72" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14T23:16:43Z</t>
+          <t>2026-09-15T23:01:39Z</t>
         </is>
       </c>
     </row>
@@ -6470,7 +6470,7 @@
       </c>
       <c r="S73" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14T23:16:43Z</t>
+          <t>2026-09-15T23:01:39Z</t>
         </is>
       </c>
     </row>
@@ -6555,7 +6555,7 @@
       </c>
       <c r="S74" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14T23:16:43Z</t>
+          <t>2026-09-15T23:01:39Z</t>
         </is>
       </c>
     </row>
@@ -6640,7 +6640,7 @@
       </c>
       <c r="S75" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14T23:16:43Z</t>
+          <t>2026-09-15T23:01:39Z</t>
         </is>
       </c>
     </row>
@@ -6725,7 +6725,7 @@
       </c>
       <c r="S76" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14T23:16:43Z</t>
+          <t>2026-09-15T23:01:39Z</t>
         </is>
       </c>
     </row>
@@ -6810,7 +6810,7 @@
       </c>
       <c r="S77" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14T23:16:43Z</t>
+          <t>2026-09-15T23:01:39Z</t>
         </is>
       </c>
     </row>
@@ -6895,7 +6895,7 @@
       </c>
       <c r="S78" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14T23:16:43Z</t>
+          <t>2026-09-15T23:01:39Z</t>
         </is>
       </c>
     </row>
@@ -6980,7 +6980,7 @@
       </c>
       <c r="S79" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14T23:16:43Z</t>
+          <t>2026-09-15T23:01:39Z</t>
         </is>
       </c>
     </row>
@@ -7065,7 +7065,7 @@
       </c>
       <c r="S80" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14T23:16:43Z</t>
+          <t>2026-09-15T23:01:39Z</t>
         </is>
       </c>
     </row>
@@ -7150,7 +7150,7 @@
       </c>
       <c r="S81" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14T23:16:43Z</t>
+          <t>2026-09-15T23:01:39Z</t>
         </is>
       </c>
     </row>
@@ -7235,7 +7235,7 @@
       </c>
       <c r="S82" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14T23:16:43Z</t>
+          <t>2026-09-15T23:01:39Z</t>
         </is>
       </c>
     </row>
@@ -7320,7 +7320,7 @@
       </c>
       <c r="S83" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14T23:16:43Z</t>
+          <t>2026-09-15T23:01:39Z</t>
         </is>
       </c>
     </row>
@@ -7405,7 +7405,7 @@
       </c>
       <c r="S84" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14T23:16:43Z</t>
+          <t>2026-09-15T23:01:39Z</t>
         </is>
       </c>
     </row>
@@ -7490,7 +7490,7 @@
       </c>
       <c r="S85" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14T23:16:43Z</t>
+          <t>2026-09-15T23:01:39Z</t>
         </is>
       </c>
     </row>
@@ -7575,7 +7575,7 @@
       </c>
       <c r="S86" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14T23:16:43Z</t>
+          <t>2026-09-15T23:01:39Z</t>
         </is>
       </c>
     </row>
@@ -7660,7 +7660,7 @@
       </c>
       <c r="S87" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14T23:16:43Z</t>
+          <t>2026-09-15T23:01:39Z</t>
         </is>
       </c>
     </row>
@@ -7745,7 +7745,7 @@
       </c>
       <c r="S88" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14T23:16:43Z</t>
+          <t>2026-09-15T23:01:39Z</t>
         </is>
       </c>
     </row>
@@ -7834,7 +7834,7 @@
       </c>
       <c r="S89" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14T23:16:43Z</t>
+          <t>2026-09-15T23:01:39Z</t>
         </is>
       </c>
     </row>
@@ -7923,7 +7923,7 @@
       </c>
       <c r="S90" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14T23:16:43Z</t>
+          <t>2026-09-15T23:01:39Z</t>
         </is>
       </c>
     </row>
@@ -8008,7 +8008,7 @@
       </c>
       <c r="S91" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14T23:16:43Z</t>
+          <t>2026-09-15T23:01:39Z</t>
         </is>
       </c>
     </row>
@@ -8097,7 +8097,7 @@
       </c>
       <c r="S92" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14T23:16:43Z</t>
+          <t>2026-09-15T23:01:39Z</t>
         </is>
       </c>
     </row>
@@ -8186,7 +8186,7 @@
       </c>
       <c r="S93" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14T23:16:43Z</t>
+          <t>2026-09-15T23:01:39Z</t>
         </is>
       </c>
     </row>
@@ -8271,7 +8271,7 @@
       </c>
       <c r="S94" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14T23:16:43Z</t>
+          <t>2026-09-15T23:01:39Z</t>
         </is>
       </c>
     </row>
@@ -8360,7 +8360,7 @@
       </c>
       <c r="S95" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14T23:16:43Z</t>
+          <t>2026-09-15T23:01:39Z</t>
         </is>
       </c>
     </row>
@@ -8449,7 +8449,7 @@
       </c>
       <c r="S96" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14T23:16:43Z</t>
+          <t>2026-09-15T23:01:39Z</t>
         </is>
       </c>
     </row>
@@ -8534,7 +8534,7 @@
       </c>
       <c r="S97" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14T23:16:43Z</t>
+          <t>2026-09-15T23:01:39Z</t>
         </is>
       </c>
     </row>
@@ -8623,7 +8623,7 @@
       </c>
       <c r="S98" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14T23:16:43Z</t>
+          <t>2026-09-15T23:01:39Z</t>
         </is>
       </c>
     </row>
@@ -8712,7 +8712,7 @@
       </c>
       <c r="S99" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14T23:16:43Z</t>
+          <t>2026-09-15T23:01:39Z</t>
         </is>
       </c>
     </row>
@@ -8797,7 +8797,7 @@
       </c>
       <c r="S100" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14T23:16:43Z</t>
+          <t>2026-09-15T23:01:39Z</t>
         </is>
       </c>
     </row>
@@ -8886,7 +8886,7 @@
       </c>
       <c r="S101" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14T23:16:43Z</t>
+          <t>2026-09-15T23:01:39Z</t>
         </is>
       </c>
     </row>
@@ -8975,7 +8975,7 @@
       </c>
       <c r="S102" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14T23:16:43Z</t>
+          <t>2026-09-15T23:01:39Z</t>
         </is>
       </c>
     </row>
@@ -9060,7 +9060,7 @@
       </c>
       <c r="S103" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14T23:16:43Z</t>
+          <t>2026-09-15T23:01:39Z</t>
         </is>
       </c>
     </row>
@@ -9149,7 +9149,7 @@
       </c>
       <c r="S104" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14T23:16:43Z</t>
+          <t>2026-09-15T23:01:39Z</t>
         </is>
       </c>
     </row>
@@ -9238,7 +9238,7 @@
       </c>
       <c r="S105" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14T23:16:43Z</t>
+          <t>2026-09-15T23:01:39Z</t>
         </is>
       </c>
     </row>
@@ -9323,7 +9323,7 @@
       </c>
       <c r="S106" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14T23:16:43Z</t>
+          <t>2026-09-15T23:01:39Z</t>
         </is>
       </c>
     </row>
@@ -9412,7 +9412,7 @@
       </c>
       <c r="S107" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14T23:16:43Z</t>
+          <t>2026-09-15T23:01:39Z</t>
         </is>
       </c>
     </row>
@@ -9501,7 +9501,7 @@
       </c>
       <c r="S108" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14T23:16:43Z</t>
+          <t>2026-09-15T23:01:39Z</t>
         </is>
       </c>
     </row>
@@ -9586,7 +9586,7 @@
       </c>
       <c r="S109" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14T23:16:43Z</t>
+          <t>2026-09-15T23:01:39Z</t>
         </is>
       </c>
     </row>
@@ -9675,7 +9675,7 @@
       </c>
       <c r="S110" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14T23:16:43Z</t>
+          <t>2026-09-15T23:01:39Z</t>
         </is>
       </c>
     </row>
@@ -9764,7 +9764,7 @@
       </c>
       <c r="S111" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14T23:16:43Z</t>
+          <t>2026-09-15T23:01:39Z</t>
         </is>
       </c>
     </row>
@@ -9849,7 +9849,7 @@
       </c>
       <c r="S112" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14T23:16:43Z</t>
+          <t>2026-09-15T23:01:39Z</t>
         </is>
       </c>
     </row>
@@ -9938,7 +9938,7 @@
       </c>
       <c r="S113" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14T23:16:43Z</t>
+          <t>2026-09-15T23:01:39Z</t>
         </is>
       </c>
     </row>
@@ -10027,7 +10027,7 @@
       </c>
       <c r="S114" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14T23:16:43Z</t>
+          <t>2026-09-15T23:01:39Z</t>
         </is>
       </c>
     </row>
@@ -10112,7 +10112,7 @@
       </c>
       <c r="S115" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14T23:16:43Z</t>
+          <t>2026-09-15T23:01:39Z</t>
         </is>
       </c>
     </row>
@@ -10201,7 +10201,7 @@
       </c>
       <c r="S116" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14T23:16:43Z</t>
+          <t>2026-09-15T23:01:39Z</t>
         </is>
       </c>
     </row>
@@ -10290,7 +10290,7 @@
       </c>
       <c r="S117" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14T23:16:43Z</t>
+          <t>2026-09-15T23:01:39Z</t>
         </is>
       </c>
     </row>
@@ -10379,7 +10379,7 @@
       </c>
       <c r="S118" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14T23:16:43Z</t>
+          <t>2026-09-15T23:01:39Z</t>
         </is>
       </c>
     </row>
@@ -10468,7 +10468,7 @@
       </c>
       <c r="S119" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14T23:16:43Z</t>
+          <t>2026-09-15T23:01:39Z</t>
         </is>
       </c>
     </row>
@@ -10557,7 +10557,7 @@
       </c>
       <c r="S120" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14T23:16:43Z</t>
+          <t>2026-09-15T23:01:39Z</t>
         </is>
       </c>
     </row>
@@ -10646,7 +10646,7 @@
       </c>
       <c r="S121" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14T23:16:43Z</t>
+          <t>2026-09-15T23:01:39Z</t>
         </is>
       </c>
     </row>
@@ -10735,7 +10735,7 @@
       </c>
       <c r="S122" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14T23:16:43Z</t>
+          <t>2026-09-15T23:01:39Z</t>
         </is>
       </c>
     </row>
@@ -10824,7 +10824,7 @@
       </c>
       <c r="S123" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14T23:16:43Z</t>
+          <t>2026-09-15T23:01:39Z</t>
         </is>
       </c>
     </row>
@@ -10913,7 +10913,7 @@
       </c>
       <c r="S124" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14T23:16:43Z</t>
+          <t>2026-09-15T23:01:39Z</t>
         </is>
       </c>
     </row>
@@ -11002,7 +11002,7 @@
       </c>
       <c r="S125" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14T23:16:43Z</t>
+          <t>2026-09-15T23:01:39Z</t>
         </is>
       </c>
     </row>
@@ -11091,7 +11091,7 @@
       </c>
       <c r="S126" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14T23:16:43Z</t>
+          <t>2026-09-15T23:01:39Z</t>
         </is>
       </c>
     </row>
@@ -11180,7 +11180,7 @@
       </c>
       <c r="S127" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14T23:16:43Z</t>
+          <t>2026-09-15T23:01:39Z</t>
         </is>
       </c>
     </row>
@@ -11269,7 +11269,7 @@
       </c>
       <c r="S128" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14T23:16:43Z</t>
+          <t>2026-09-15T23:01:39Z</t>
         </is>
       </c>
     </row>
@@ -11354,7 +11354,7 @@
       </c>
       <c r="S129" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14T23:16:43Z</t>
+          <t>2026-09-15T23:01:39Z</t>
         </is>
       </c>
     </row>
@@ -11439,7 +11439,7 @@
       </c>
       <c r="S130" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14T23:16:43Z</t>
+          <t>2026-09-15T23:01:39Z</t>
         </is>
       </c>
     </row>
@@ -11524,7 +11524,7 @@
       </c>
       <c r="S131" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14T23:16:43Z</t>
+          <t>2026-09-15T23:01:39Z</t>
         </is>
       </c>
     </row>
@@ -11609,7 +11609,7 @@
       </c>
       <c r="S132" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14T23:16:43Z</t>
+          <t>2026-09-15T23:01:39Z</t>
         </is>
       </c>
     </row>
@@ -11694,7 +11694,7 @@
       </c>
       <c r="S133" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14T23:16:43Z</t>
+          <t>2026-09-15T23:01:39Z</t>
         </is>
       </c>
     </row>
@@ -11779,7 +11779,7 @@
       </c>
       <c r="S134" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14T23:16:43Z</t>
+          <t>2026-09-15T23:01:39Z</t>
         </is>
       </c>
     </row>
@@ -11864,7 +11864,7 @@
       </c>
       <c r="S135" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14T23:16:43Z</t>
+          <t>2026-09-15T23:01:39Z</t>
         </is>
       </c>
     </row>
@@ -11949,7 +11949,7 @@
       </c>
       <c r="S136" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14T23:16:43Z</t>
+          <t>2026-09-15T23:01:39Z</t>
         </is>
       </c>
     </row>
@@ -12034,7 +12034,7 @@
       </c>
       <c r="S137" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14T23:16:43Z</t>
+          <t>2026-09-15T23:01:39Z</t>
         </is>
       </c>
     </row>
@@ -12119,7 +12119,7 @@
       </c>
       <c r="S138" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14T23:16:43Z</t>
+          <t>2026-09-15T23:01:39Z</t>
         </is>
       </c>
     </row>
@@ -12204,7 +12204,7 @@
       </c>
       <c r="S139" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14T23:16:43Z</t>
+          <t>2026-09-15T23:01:39Z</t>
         </is>
       </c>
     </row>
@@ -12289,7 +12289,7 @@
       </c>
       <c r="S140" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14T23:16:43Z</t>
+          <t>2026-09-15T23:01:39Z</t>
         </is>
       </c>
     </row>
@@ -12374,7 +12374,7 @@
       </c>
       <c r="S141" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14T23:16:43Z</t>
+          <t>2026-09-15T23:01:39Z</t>
         </is>
       </c>
     </row>
@@ -12459,7 +12459,7 @@
       </c>
       <c r="S142" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14T23:16:43Z</t>
+          <t>2026-09-15T23:01:39Z</t>
         </is>
       </c>
     </row>
@@ -12544,7 +12544,7 @@
       </c>
       <c r="S143" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14T23:16:43Z</t>
+          <t>2026-09-15T23:01:39Z</t>
         </is>
       </c>
     </row>
@@ -12629,7 +12629,7 @@
       </c>
       <c r="S144" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14T23:16:43Z</t>
+          <t>2026-09-15T23:01:39Z</t>
         </is>
       </c>
     </row>
@@ -12714,7 +12714,7 @@
       </c>
       <c r="S145" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14T23:16:43Z</t>
+          <t>2026-09-15T23:01:39Z</t>
         </is>
       </c>
     </row>
@@ -12799,7 +12799,7 @@
       </c>
       <c r="S146" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14T23:16:43Z</t>
+          <t>2026-09-15T23:01:39Z</t>
         </is>
       </c>
     </row>
@@ -12884,7 +12884,7 @@
       </c>
       <c r="S147" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14T23:16:43Z</t>
+          <t>2026-09-15T23:01:39Z</t>
         </is>
       </c>
     </row>
@@ -12969,7 +12969,7 @@
       </c>
       <c r="S148" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14T23:16:43Z</t>
+          <t>2026-09-15T23:01:39Z</t>
         </is>
       </c>
     </row>
@@ -13054,7 +13054,7 @@
       </c>
       <c r="S149" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14T23:16:43Z</t>
+          <t>2026-09-15T23:01:39Z</t>
         </is>
       </c>
     </row>
@@ -13143,7 +13143,7 @@
       </c>
       <c r="S150" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14T23:16:43Z</t>
+          <t>2026-09-15T23:01:39Z</t>
         </is>
       </c>
     </row>
@@ -13232,7 +13232,7 @@
       </c>
       <c r="S151" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14T23:16:43Z</t>
+          <t>2026-09-15T23:01:39Z</t>
         </is>
       </c>
     </row>
@@ -13317,7 +13317,7 @@
       </c>
       <c r="S152" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14T23:16:43Z</t>
+          <t>2026-09-15T23:01:39Z</t>
         </is>
       </c>
     </row>
@@ -13406,7 +13406,7 @@
       </c>
       <c r="S153" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14T23:16:43Z</t>
+          <t>2026-09-15T23:01:39Z</t>
         </is>
       </c>
     </row>
@@ -13495,7 +13495,7 @@
       </c>
       <c r="S154" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14T23:16:43Z</t>
+          <t>2026-09-15T23:01:39Z</t>
         </is>
       </c>
     </row>
@@ -13580,7 +13580,7 @@
       </c>
       <c r="S155" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14T23:16:43Z</t>
+          <t>2026-09-15T23:01:39Z</t>
         </is>
       </c>
     </row>
@@ -13669,7 +13669,7 @@
       </c>
       <c r="S156" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14T23:16:43Z</t>
+          <t>2026-09-15T23:01:39Z</t>
         </is>
       </c>
     </row>
@@ -13758,7 +13758,7 @@
       </c>
       <c r="S157" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14T23:16:43Z</t>
+          <t>2026-09-15T23:01:39Z</t>
         </is>
       </c>
     </row>
@@ -13843,7 +13843,7 @@
       </c>
       <c r="S158" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14T23:16:43Z</t>
+          <t>2026-09-15T23:01:39Z</t>
         </is>
       </c>
     </row>
@@ -13932,7 +13932,7 @@
       </c>
       <c r="S159" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14T23:16:43Z</t>
+          <t>2026-09-15T23:01:39Z</t>
         </is>
       </c>
     </row>
@@ -14021,7 +14021,7 @@
       </c>
       <c r="S160" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14T23:16:43Z</t>
+          <t>2026-09-15T23:01:39Z</t>
         </is>
       </c>
     </row>
@@ -14106,7 +14106,7 @@
       </c>
       <c r="S161" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14T23:16:43Z</t>
+          <t>2026-09-15T23:01:39Z</t>
         </is>
       </c>
     </row>
@@ -14195,7 +14195,7 @@
       </c>
       <c r="S162" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14T23:16:43Z</t>
+          <t>2026-09-15T23:01:39Z</t>
         </is>
       </c>
     </row>
@@ -14284,7 +14284,7 @@
       </c>
       <c r="S163" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14T23:16:43Z</t>
+          <t>2026-09-15T23:01:39Z</t>
         </is>
       </c>
     </row>
@@ -14369,7 +14369,7 @@
       </c>
       <c r="S164" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14T23:16:43Z</t>
+          <t>2026-09-15T23:01:39Z</t>
         </is>
       </c>
     </row>
@@ -14458,7 +14458,7 @@
       </c>
       <c r="S165" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14T23:16:43Z</t>
+          <t>2026-09-15T23:01:39Z</t>
         </is>
       </c>
     </row>
@@ -14547,7 +14547,7 @@
       </c>
       <c r="S166" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14T23:16:43Z</t>
+          <t>2026-09-15T23:01:39Z</t>
         </is>
       </c>
     </row>
@@ -14632,7 +14632,7 @@
       </c>
       <c r="S167" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14T23:16:43Z</t>
+          <t>2026-09-15T23:01:39Z</t>
         </is>
       </c>
     </row>
@@ -14721,7 +14721,7 @@
       </c>
       <c r="S168" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14T23:16:43Z</t>
+          <t>2026-09-15T23:01:39Z</t>
         </is>
       </c>
     </row>
@@ -14810,7 +14810,7 @@
       </c>
       <c r="S169" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14T23:16:43Z</t>
+          <t>2026-09-15T23:01:39Z</t>
         </is>
       </c>
     </row>
@@ -14895,7 +14895,7 @@
       </c>
       <c r="S170" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14T23:16:43Z</t>
+          <t>2026-09-15T23:01:39Z</t>
         </is>
       </c>
     </row>
@@ -14984,7 +14984,7 @@
       </c>
       <c r="S171" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14T23:16:43Z</t>
+          <t>2026-09-15T23:01:39Z</t>
         </is>
       </c>
     </row>
@@ -15073,7 +15073,7 @@
       </c>
       <c r="S172" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14T23:16:43Z</t>
+          <t>2026-09-15T23:01:39Z</t>
         </is>
       </c>
     </row>
@@ -15158,7 +15158,7 @@
       </c>
       <c r="S173" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14T23:16:43Z</t>
+          <t>2026-09-15T23:01:39Z</t>
         </is>
       </c>
     </row>
@@ -15247,7 +15247,7 @@
       </c>
       <c r="S174" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14T23:16:43Z</t>
+          <t>2026-09-15T23:01:39Z</t>
         </is>
       </c>
     </row>
@@ -15336,7 +15336,7 @@
       </c>
       <c r="S175" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14T23:16:43Z</t>
+          <t>2026-09-15T23:01:39Z</t>
         </is>
       </c>
     </row>
@@ -15421,7 +15421,7 @@
       </c>
       <c r="S176" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14T23:16:43Z</t>
+          <t>2026-09-15T23:01:39Z</t>
         </is>
       </c>
     </row>
@@ -15510,7 +15510,7 @@
       </c>
       <c r="S177" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14T23:16:43Z</t>
+          <t>2026-09-15T23:01:39Z</t>
         </is>
       </c>
     </row>
@@ -15599,7 +15599,7 @@
       </c>
       <c r="S178" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14T23:16:43Z</t>
+          <t>2026-09-15T23:01:39Z</t>
         </is>
       </c>
     </row>
@@ -15688,7 +15688,7 @@
       </c>
       <c r="S179" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14T23:16:43Z</t>
+          <t>2026-09-15T23:01:39Z</t>
         </is>
       </c>
     </row>
@@ -15777,7 +15777,7 @@
       </c>
       <c r="S180" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14T23:16:43Z</t>
+          <t>2026-09-15T23:01:39Z</t>
         </is>
       </c>
     </row>
@@ -15866,7 +15866,7 @@
       </c>
       <c r="S181" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14T23:16:43Z</t>
+          <t>2026-09-15T23:01:39Z</t>
         </is>
       </c>
     </row>
@@ -15955,7 +15955,7 @@
       </c>
       <c r="S182" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14T23:16:43Z</t>
+          <t>2026-09-15T23:01:39Z</t>
         </is>
       </c>
     </row>
@@ -16044,7 +16044,7 @@
       </c>
       <c r="S183" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14T23:16:43Z</t>
+          <t>2026-09-15T23:01:39Z</t>
         </is>
       </c>
     </row>
@@ -16133,7 +16133,7 @@
       </c>
       <c r="S184" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14T23:16:43Z</t>
+          <t>2026-09-15T23:01:39Z</t>
         </is>
       </c>
     </row>
@@ -16222,7 +16222,7 @@
       </c>
       <c r="S185" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14T23:16:43Z</t>
+          <t>2026-09-15T23:01:39Z</t>
         </is>
       </c>
     </row>
@@ -16311,7 +16311,7 @@
       </c>
       <c r="S186" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14T23:16:43Z</t>
+          <t>2026-09-15T23:01:39Z</t>
         </is>
       </c>
     </row>
@@ -16400,7 +16400,7 @@
       </c>
       <c r="S187" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14T23:16:43Z</t>
+          <t>2026-09-15T23:01:39Z</t>
         </is>
       </c>
     </row>
@@ -16489,7 +16489,7 @@
       </c>
       <c r="S188" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14T23:16:43Z</t>
+          <t>2026-09-15T23:01:39Z</t>
         </is>
       </c>
     </row>
@@ -16578,7 +16578,7 @@
       </c>
       <c r="S189" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14T23:16:43Z</t>
+          <t>2026-09-15T23:01:39Z</t>
         </is>
       </c>
     </row>
@@ -16663,7 +16663,7 @@
       </c>
       <c r="S190" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14T23:16:43Z</t>
+          <t>2026-09-15T23:01:39Z</t>
         </is>
       </c>
     </row>
@@ -16748,7 +16748,7 @@
       </c>
       <c r="S191" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14T23:16:43Z</t>
+          <t>2026-09-15T23:01:39Z</t>
         </is>
       </c>
     </row>
@@ -16833,7 +16833,7 @@
       </c>
       <c r="S192" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14T23:16:43Z</t>
+          <t>2026-09-15T23:01:39Z</t>
         </is>
       </c>
     </row>
@@ -16918,7 +16918,7 @@
       </c>
       <c r="S193" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14T23:16:43Z</t>
+          <t>2026-09-15T23:01:39Z</t>
         </is>
       </c>
     </row>
@@ -17003,7 +17003,7 @@
       </c>
       <c r="S194" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14T23:16:43Z</t>
+          <t>2026-09-15T23:01:39Z</t>
         </is>
       </c>
     </row>
@@ -17088,7 +17088,7 @@
       </c>
       <c r="S195" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14T23:16:43Z</t>
+          <t>2026-09-15T23:01:39Z</t>
         </is>
       </c>
     </row>
@@ -17173,7 +17173,7 @@
       </c>
       <c r="S196" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14T23:16:43Z</t>
+          <t>2026-09-15T23:01:39Z</t>
         </is>
       </c>
     </row>
@@ -17258,7 +17258,7 @@
       </c>
       <c r="S197" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14T23:16:43Z</t>
+          <t>2026-09-15T23:01:39Z</t>
         </is>
       </c>
     </row>
@@ -17343,7 +17343,7 @@
       </c>
       <c r="S198" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14T23:16:43Z</t>
+          <t>2026-09-15T23:01:39Z</t>
         </is>
       </c>
     </row>
@@ -17428,7 +17428,7 @@
       </c>
       <c r="S199" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14T23:16:43Z</t>
+          <t>2026-09-15T23:01:39Z</t>
         </is>
       </c>
     </row>
@@ -17513,7 +17513,7 @@
       </c>
       <c r="S200" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14T23:16:43Z</t>
+          <t>2026-09-15T23:01:39Z</t>
         </is>
       </c>
     </row>
@@ -17598,7 +17598,7 @@
       </c>
       <c r="S201" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14T23:16:43Z</t>
+          <t>2026-09-15T23:01:39Z</t>
         </is>
       </c>
     </row>
@@ -17683,7 +17683,7 @@
       </c>
       <c r="S202" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14T23:16:43Z</t>
+          <t>2026-09-15T23:01:39Z</t>
         </is>
       </c>
     </row>
@@ -17768,7 +17768,7 @@
       </c>
       <c r="S203" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14T23:16:43Z</t>
+          <t>2026-09-15T23:01:39Z</t>
         </is>
       </c>
     </row>
@@ -17853,7 +17853,7 @@
       </c>
       <c r="S204" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14T23:16:43Z</t>
+          <t>2026-09-15T23:01:39Z</t>
         </is>
       </c>
     </row>
@@ -17938,7 +17938,7 @@
       </c>
       <c r="S205" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14T23:16:43Z</t>
+          <t>2026-09-15T23:01:39Z</t>
         </is>
       </c>
     </row>
@@ -18023,7 +18023,7 @@
       </c>
       <c r="S206" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14T23:16:43Z</t>
+          <t>2026-09-15T23:01:39Z</t>
         </is>
       </c>
     </row>
@@ -18108,7 +18108,7 @@
       </c>
       <c r="S207" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14T23:16:43Z</t>
+          <t>2026-09-15T23:01:39Z</t>
         </is>
       </c>
     </row>
@@ -18193,7 +18193,7 @@
       </c>
       <c r="S208" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14T23:16:43Z</t>
+          <t>2026-09-15T23:01:39Z</t>
         </is>
       </c>
     </row>
@@ -18278,7 +18278,7 @@
       </c>
       <c r="S209" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14T23:16:43Z</t>
+          <t>2026-09-15T23:01:39Z</t>
         </is>
       </c>
     </row>
@@ -18363,7 +18363,7 @@
       </c>
       <c r="S210" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14T23:16:43Z</t>
+          <t>2026-09-15T23:01:39Z</t>
         </is>
       </c>
     </row>
@@ -18452,7 +18452,7 @@
       </c>
       <c r="S211" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14T23:16:43Z</t>
+          <t>2026-09-15T23:01:39Z</t>
         </is>
       </c>
     </row>
@@ -18541,7 +18541,7 @@
       </c>
       <c r="S212" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14T23:16:43Z</t>
+          <t>2026-09-15T23:01:39Z</t>
         </is>
       </c>
     </row>
@@ -18626,7 +18626,7 @@
       </c>
       <c r="S213" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14T23:16:43Z</t>
+          <t>2026-09-15T23:01:39Z</t>
         </is>
       </c>
     </row>
@@ -18715,7 +18715,7 @@
       </c>
       <c r="S214" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14T23:16:43Z</t>
+          <t>2026-09-15T23:01:39Z</t>
         </is>
       </c>
     </row>
@@ -18804,7 +18804,7 @@
       </c>
       <c r="S215" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14T23:16:43Z</t>
+          <t>2026-09-15T23:01:39Z</t>
         </is>
       </c>
     </row>
@@ -18889,7 +18889,7 @@
       </c>
       <c r="S216" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14T23:16:43Z</t>
+          <t>2026-09-15T23:01:39Z</t>
         </is>
       </c>
     </row>
@@ -18978,7 +18978,7 @@
       </c>
       <c r="S217" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14T23:16:43Z</t>
+          <t>2026-09-15T23:01:39Z</t>
         </is>
       </c>
     </row>
@@ -19067,7 +19067,7 @@
       </c>
       <c r="S218" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14T23:16:43Z</t>
+          <t>2026-09-15T23:01:39Z</t>
         </is>
       </c>
     </row>
@@ -19152,7 +19152,7 @@
       </c>
       <c r="S219" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14T23:16:43Z</t>
+          <t>2026-09-15T23:01:39Z</t>
         </is>
       </c>
     </row>
@@ -19241,7 +19241,7 @@
       </c>
       <c r="S220" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14T23:16:43Z</t>
+          <t>2026-09-15T23:01:39Z</t>
         </is>
       </c>
     </row>
@@ -19330,7 +19330,7 @@
       </c>
       <c r="S221" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14T23:16:43Z</t>
+          <t>2026-09-15T23:01:39Z</t>
         </is>
       </c>
     </row>
@@ -19415,7 +19415,7 @@
       </c>
       <c r="S222" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14T23:16:43Z</t>
+          <t>2026-09-15T23:01:39Z</t>
         </is>
       </c>
     </row>
@@ -19504,7 +19504,7 @@
       </c>
       <c r="S223" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14T23:16:43Z</t>
+          <t>2026-09-15T23:01:39Z</t>
         </is>
       </c>
     </row>
@@ -19593,7 +19593,7 @@
       </c>
       <c r="S224" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14T23:16:43Z</t>
+          <t>2026-09-15T23:01:39Z</t>
         </is>
       </c>
     </row>
@@ -19678,7 +19678,7 @@
       </c>
       <c r="S225" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14T23:16:43Z</t>
+          <t>2026-09-15T23:01:39Z</t>
         </is>
       </c>
     </row>
@@ -19767,7 +19767,7 @@
       </c>
       <c r="S226" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14T23:16:43Z</t>
+          <t>2026-09-15T23:01:39Z</t>
         </is>
       </c>
     </row>
@@ -19856,7 +19856,7 @@
       </c>
       <c r="S227" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14T23:16:43Z</t>
+          <t>2026-09-15T23:01:39Z</t>
         </is>
       </c>
     </row>
@@ -19941,7 +19941,7 @@
       </c>
       <c r="S228" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14T23:16:43Z</t>
+          <t>2026-09-15T23:01:39Z</t>
         </is>
       </c>
     </row>
@@ -20030,7 +20030,7 @@
       </c>
       <c r="S229" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14T23:16:43Z</t>
+          <t>2026-09-15T23:01:39Z</t>
         </is>
       </c>
     </row>
@@ -20119,7 +20119,7 @@
       </c>
       <c r="S230" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14T23:16:43Z</t>
+          <t>2026-09-15T23:01:39Z</t>
         </is>
       </c>
     </row>
@@ -20204,7 +20204,7 @@
       </c>
       <c r="S231" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14T23:16:43Z</t>
+          <t>2026-09-15T23:01:39Z</t>
         </is>
       </c>
     </row>
@@ -20293,7 +20293,7 @@
       </c>
       <c r="S232" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14T23:16:43Z</t>
+          <t>2026-09-15T23:01:39Z</t>
         </is>
       </c>
     </row>
@@ -20382,7 +20382,7 @@
       </c>
       <c r="S233" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14T23:16:43Z</t>
+          <t>2026-09-15T23:01:39Z</t>
         </is>
       </c>
     </row>
@@ -20467,7 +20467,7 @@
       </c>
       <c r="S234" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14T23:16:43Z</t>
+          <t>2026-09-15T23:01:39Z</t>
         </is>
       </c>
     </row>
@@ -20556,7 +20556,7 @@
       </c>
       <c r="S235" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14T23:16:43Z</t>
+          <t>2026-09-15T23:01:39Z</t>
         </is>
       </c>
     </row>
@@ -20645,7 +20645,7 @@
       </c>
       <c r="S236" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14T23:16:43Z</t>
+          <t>2026-09-15T23:01:39Z</t>
         </is>
       </c>
     </row>
@@ -20730,7 +20730,7 @@
       </c>
       <c r="S237" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14T23:16:43Z</t>
+          <t>2026-09-15T23:01:39Z</t>
         </is>
       </c>
     </row>
@@ -20819,7 +20819,7 @@
       </c>
       <c r="S238" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14T23:16:43Z</t>
+          <t>2026-09-15T23:01:39Z</t>
         </is>
       </c>
     </row>
@@ -20908,7 +20908,7 @@
       </c>
       <c r="S239" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14T23:16:43Z</t>
+          <t>2026-09-15T23:01:39Z</t>
         </is>
       </c>
     </row>
@@ -20997,7 +20997,7 @@
       </c>
       <c r="S240" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14T23:16:43Z</t>
+          <t>2026-09-15T23:01:39Z</t>
         </is>
       </c>
     </row>
@@ -21086,7 +21086,7 @@
       </c>
       <c r="S241" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14T23:16:43Z</t>
+          <t>2026-09-15T23:01:39Z</t>
         </is>
       </c>
     </row>
@@ -21175,7 +21175,7 @@
       </c>
       <c r="S242" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14T23:16:43Z</t>
+          <t>2026-09-15T23:01:39Z</t>
         </is>
       </c>
     </row>
@@ -21264,7 +21264,7 @@
       </c>
       <c r="S243" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14T23:16:43Z</t>
+          <t>2026-09-15T23:01:39Z</t>
         </is>
       </c>
     </row>
@@ -21353,7 +21353,7 @@
       </c>
       <c r="S244" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14T23:16:43Z</t>
+          <t>2026-09-15T23:01:39Z</t>
         </is>
       </c>
     </row>
@@ -21442,7 +21442,7 @@
       </c>
       <c r="S245" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14T23:16:43Z</t>
+          <t>2026-09-15T23:01:39Z</t>
         </is>
       </c>
     </row>
@@ -21531,7 +21531,7 @@
       </c>
       <c r="S246" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14T23:16:43Z</t>
+          <t>2026-09-15T23:01:39Z</t>
         </is>
       </c>
     </row>
@@ -21620,7 +21620,7 @@
       </c>
       <c r="S247" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14T23:16:43Z</t>
+          <t>2026-09-15T23:01:39Z</t>
         </is>
       </c>
     </row>
@@ -21709,7 +21709,7 @@
       </c>
       <c r="S248" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14T23:16:43Z</t>
+          <t>2026-09-15T23:01:39Z</t>
         </is>
       </c>
     </row>
@@ -21798,7 +21798,7 @@
       </c>
       <c r="S249" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14T23:16:43Z</t>
+          <t>2026-09-15T23:01:39Z</t>
         </is>
       </c>
     </row>
@@ -21887,7 +21887,7 @@
       </c>
       <c r="S250" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14T23:16:43Z</t>
+          <t>2026-09-15T23:01:39Z</t>
         </is>
       </c>
     </row>
@@ -22019,7 +22019,7 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14T23:16:43Z</t>
+          <t>2026-09-15T23:01:39Z</t>
         </is>
       </c>
     </row>
@@ -22099,7 +22099,7 @@
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>{"dataset_id": "bcv_pib_sector_institucional_anual", "title": "Producto interno bruto por sector institucional anual", "table": "Variaciones porcentuales", "source_file": "5_2_1_si_anual.xlsx", "base": "2007", "price_type": "Precios constantes", "measure": "Variación porcentual interanual", "frequency": "Anual", "period": "2025", "year": 2025, "quarter": null, "classification": "Sector institucional", "component": "Impuestos netos sobre los productos", "value": 10.600260421283764, "unit": "Porcentaje", "status": "Preliminar", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/cuentas_macroeconomicas/5_2_1_si_anual.xlsx", "fetched_at": "2026-09-14T23:16:43Z"}</t>
+          <t>{"dataset_id": "bcv_pib_sector_institucional_anual", "title": "Producto interno bruto por sector institucional anual", "table": "Variaciones porcentuales", "source_file": "5_2_1_si_anual.xlsx", "base": "2007", "price_type": "Precios constantes", "measure": "Variación porcentual interanual", "frequency": "Anual", "period": "2025", "year": 2025, "quarter": null, "classification": "Sector institucional", "component": "Impuestos netos sobre los productos", "value": 10.600260421283764, "unit": "Porcentaje", "status": "Preliminar", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/cuentas_macroeconomicas/5_2_1_si_anual.xlsx", "fetched_at": "2026-09-15T23:01:39Z"}</t>
         </is>
       </c>
     </row>

--- a/assets/data/bcv/excel/ove_bcv_pib_sector_institucional_anual.xlsx
+++ b/assets/data/bcv/excel/ove_bcv_pib_sector_institucional_anual.xlsx
@@ -736,7 +736,7 @@
       </c>
       <c r="S7" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15T23:01:39Z</t>
+          <t>2026-09-16T23:07:48Z</t>
         </is>
       </c>
     </row>
@@ -821,7 +821,7 @@
       </c>
       <c r="S8" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15T23:01:39Z</t>
+          <t>2026-09-16T23:07:48Z</t>
         </is>
       </c>
     </row>
@@ -906,7 +906,7 @@
       </c>
       <c r="S9" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15T23:01:39Z</t>
+          <t>2026-09-16T23:07:48Z</t>
         </is>
       </c>
     </row>
@@ -991,7 +991,7 @@
       </c>
       <c r="S10" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15T23:01:39Z</t>
+          <t>2026-09-16T23:07:48Z</t>
         </is>
       </c>
     </row>
@@ -1076,7 +1076,7 @@
       </c>
       <c r="S11" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15T23:01:39Z</t>
+          <t>2026-09-16T23:07:48Z</t>
         </is>
       </c>
     </row>
@@ -1161,7 +1161,7 @@
       </c>
       <c r="S12" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15T23:01:39Z</t>
+          <t>2026-09-16T23:07:48Z</t>
         </is>
       </c>
     </row>
@@ -1246,7 +1246,7 @@
       </c>
       <c r="S13" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15T23:01:39Z</t>
+          <t>2026-09-16T23:07:48Z</t>
         </is>
       </c>
     </row>
@@ -1331,7 +1331,7 @@
       </c>
       <c r="S14" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15T23:01:39Z</t>
+          <t>2026-09-16T23:07:48Z</t>
         </is>
       </c>
     </row>
@@ -1416,7 +1416,7 @@
       </c>
       <c r="S15" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15T23:01:39Z</t>
+          <t>2026-09-16T23:07:48Z</t>
         </is>
       </c>
     </row>
@@ -1501,7 +1501,7 @@
       </c>
       <c r="S16" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15T23:01:39Z</t>
+          <t>2026-09-16T23:07:48Z</t>
         </is>
       </c>
     </row>
@@ -1586,7 +1586,7 @@
       </c>
       <c r="S17" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15T23:01:39Z</t>
+          <t>2026-09-16T23:07:48Z</t>
         </is>
       </c>
     </row>
@@ -1671,7 +1671,7 @@
       </c>
       <c r="S18" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15T23:01:39Z</t>
+          <t>2026-09-16T23:07:48Z</t>
         </is>
       </c>
     </row>
@@ -1756,7 +1756,7 @@
       </c>
       <c r="S19" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15T23:01:39Z</t>
+          <t>2026-09-16T23:07:48Z</t>
         </is>
       </c>
     </row>
@@ -1841,7 +1841,7 @@
       </c>
       <c r="S20" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15T23:01:39Z</t>
+          <t>2026-09-16T23:07:48Z</t>
         </is>
       </c>
     </row>
@@ -1926,7 +1926,7 @@
       </c>
       <c r="S21" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15T23:01:39Z</t>
+          <t>2026-09-16T23:07:48Z</t>
         </is>
       </c>
     </row>
@@ -2011,7 +2011,7 @@
       </c>
       <c r="S22" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15T23:01:39Z</t>
+          <t>2026-09-16T23:07:48Z</t>
         </is>
       </c>
     </row>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="S23" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15T23:01:39Z</t>
+          <t>2026-09-16T23:07:48Z</t>
         </is>
       </c>
     </row>
@@ -2181,7 +2181,7 @@
       </c>
       <c r="S24" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15T23:01:39Z</t>
+          <t>2026-09-16T23:07:48Z</t>
         </is>
       </c>
     </row>
@@ -2266,7 +2266,7 @@
       </c>
       <c r="S25" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15T23:01:39Z</t>
+          <t>2026-09-16T23:07:48Z</t>
         </is>
       </c>
     </row>
@@ -2351,7 +2351,7 @@
       </c>
       <c r="S26" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15T23:01:39Z</t>
+          <t>2026-09-16T23:07:48Z</t>
         </is>
       </c>
     </row>
@@ -2436,7 +2436,7 @@
       </c>
       <c r="S27" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15T23:01:39Z</t>
+          <t>2026-09-16T23:07:48Z</t>
         </is>
       </c>
     </row>
@@ -2525,7 +2525,7 @@
       </c>
       <c r="S28" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15T23:01:39Z</t>
+          <t>2026-09-16T23:07:48Z</t>
         </is>
       </c>
     </row>
@@ -2614,7 +2614,7 @@
       </c>
       <c r="S29" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15T23:01:39Z</t>
+          <t>2026-09-16T23:07:48Z</t>
         </is>
       </c>
     </row>
@@ -2699,7 +2699,7 @@
       </c>
       <c r="S30" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15T23:01:39Z</t>
+          <t>2026-09-16T23:07:48Z</t>
         </is>
       </c>
     </row>
@@ -2788,7 +2788,7 @@
       </c>
       <c r="S31" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15T23:01:39Z</t>
+          <t>2026-09-16T23:07:48Z</t>
         </is>
       </c>
     </row>
@@ -2877,7 +2877,7 @@
       </c>
       <c r="S32" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15T23:01:39Z</t>
+          <t>2026-09-16T23:07:48Z</t>
         </is>
       </c>
     </row>
@@ -2962,7 +2962,7 @@
       </c>
       <c r="S33" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15T23:01:39Z</t>
+          <t>2026-09-16T23:07:48Z</t>
         </is>
       </c>
     </row>
@@ -3051,7 +3051,7 @@
       </c>
       <c r="S34" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15T23:01:39Z</t>
+          <t>2026-09-16T23:07:48Z</t>
         </is>
       </c>
     </row>
@@ -3140,7 +3140,7 @@
       </c>
       <c r="S35" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15T23:01:39Z</t>
+          <t>2026-09-16T23:07:48Z</t>
         </is>
       </c>
     </row>
@@ -3225,7 +3225,7 @@
       </c>
       <c r="S36" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15T23:01:39Z</t>
+          <t>2026-09-16T23:07:48Z</t>
         </is>
       </c>
     </row>
@@ -3314,7 +3314,7 @@
       </c>
       <c r="S37" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15T23:01:39Z</t>
+          <t>2026-09-16T23:07:48Z</t>
         </is>
       </c>
     </row>
@@ -3403,7 +3403,7 @@
       </c>
       <c r="S38" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15T23:01:39Z</t>
+          <t>2026-09-16T23:07:48Z</t>
         </is>
       </c>
     </row>
@@ -3488,7 +3488,7 @@
       </c>
       <c r="S39" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15T23:01:39Z</t>
+          <t>2026-09-16T23:07:48Z</t>
         </is>
       </c>
     </row>
@@ -3577,7 +3577,7 @@
       </c>
       <c r="S40" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15T23:01:39Z</t>
+          <t>2026-09-16T23:07:48Z</t>
         </is>
       </c>
     </row>
@@ -3666,7 +3666,7 @@
       </c>
       <c r="S41" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15T23:01:39Z</t>
+          <t>2026-09-16T23:07:48Z</t>
         </is>
       </c>
     </row>
@@ -3751,7 +3751,7 @@
       </c>
       <c r="S42" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15T23:01:39Z</t>
+          <t>2026-09-16T23:07:48Z</t>
         </is>
       </c>
     </row>
@@ -3840,7 +3840,7 @@
       </c>
       <c r="S43" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15T23:01:39Z</t>
+          <t>2026-09-16T23:07:48Z</t>
         </is>
       </c>
     </row>
@@ -3929,7 +3929,7 @@
       </c>
       <c r="S44" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15T23:01:39Z</t>
+          <t>2026-09-16T23:07:48Z</t>
         </is>
       </c>
     </row>
@@ -4014,7 +4014,7 @@
       </c>
       <c r="S45" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15T23:01:39Z</t>
+          <t>2026-09-16T23:07:48Z</t>
         </is>
       </c>
     </row>
@@ -4103,7 +4103,7 @@
       </c>
       <c r="S46" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15T23:01:39Z</t>
+          <t>2026-09-16T23:07:48Z</t>
         </is>
       </c>
     </row>
@@ -4192,7 +4192,7 @@
       </c>
       <c r="S47" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15T23:01:39Z</t>
+          <t>2026-09-16T23:07:48Z</t>
         </is>
       </c>
     </row>
@@ -4277,7 +4277,7 @@
       </c>
       <c r="S48" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15T23:01:39Z</t>
+          <t>2026-09-16T23:07:48Z</t>
         </is>
       </c>
     </row>
@@ -4366,7 +4366,7 @@
       </c>
       <c r="S49" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15T23:01:39Z</t>
+          <t>2026-09-16T23:07:48Z</t>
         </is>
       </c>
     </row>
@@ -4455,7 +4455,7 @@
       </c>
       <c r="S50" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15T23:01:39Z</t>
+          <t>2026-09-16T23:07:48Z</t>
         </is>
       </c>
     </row>
@@ -4540,7 +4540,7 @@
       </c>
       <c r="S51" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15T23:01:39Z</t>
+          <t>2026-09-16T23:07:48Z</t>
         </is>
       </c>
     </row>
@@ -4629,7 +4629,7 @@
       </c>
       <c r="S52" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15T23:01:39Z</t>
+          <t>2026-09-16T23:07:48Z</t>
         </is>
       </c>
     </row>
@@ -4718,7 +4718,7 @@
       </c>
       <c r="S53" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15T23:01:39Z</t>
+          <t>2026-09-16T23:07:48Z</t>
         </is>
       </c>
     </row>
@@ -4803,7 +4803,7 @@
       </c>
       <c r="S54" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15T23:01:39Z</t>
+          <t>2026-09-16T23:07:48Z</t>
         </is>
       </c>
     </row>
@@ -4892,7 +4892,7 @@
       </c>
       <c r="S55" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15T23:01:39Z</t>
+          <t>2026-09-16T23:07:48Z</t>
         </is>
       </c>
     </row>
@@ -4981,7 +4981,7 @@
       </c>
       <c r="S56" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15T23:01:39Z</t>
+          <t>2026-09-16T23:07:48Z</t>
         </is>
       </c>
     </row>
@@ -5070,7 +5070,7 @@
       </c>
       <c r="S57" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15T23:01:39Z</t>
+          <t>2026-09-16T23:07:48Z</t>
         </is>
       </c>
     </row>
@@ -5159,7 +5159,7 @@
       </c>
       <c r="S58" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15T23:01:39Z</t>
+          <t>2026-09-16T23:07:48Z</t>
         </is>
       </c>
     </row>
@@ -5248,7 +5248,7 @@
       </c>
       <c r="S59" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15T23:01:39Z</t>
+          <t>2026-09-16T23:07:48Z</t>
         </is>
       </c>
     </row>
@@ -5337,7 +5337,7 @@
       </c>
       <c r="S60" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15T23:01:39Z</t>
+          <t>2026-09-16T23:07:48Z</t>
         </is>
       </c>
     </row>
@@ -5426,7 +5426,7 @@
       </c>
       <c r="S61" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15T23:01:39Z</t>
+          <t>2026-09-16T23:07:48Z</t>
         </is>
       </c>
     </row>
@@ -5515,7 +5515,7 @@
       </c>
       <c r="S62" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15T23:01:39Z</t>
+          <t>2026-09-16T23:07:48Z</t>
         </is>
       </c>
     </row>
@@ -5604,7 +5604,7 @@
       </c>
       <c r="S63" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15T23:01:39Z</t>
+          <t>2026-09-16T23:07:48Z</t>
         </is>
       </c>
     </row>
@@ -5693,7 +5693,7 @@
       </c>
       <c r="S64" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15T23:01:39Z</t>
+          <t>2026-09-16T23:07:48Z</t>
         </is>
       </c>
     </row>
@@ -5782,7 +5782,7 @@
       </c>
       <c r="S65" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15T23:01:39Z</t>
+          <t>2026-09-16T23:07:48Z</t>
         </is>
       </c>
     </row>
@@ -5871,7 +5871,7 @@
       </c>
       <c r="S66" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15T23:01:39Z</t>
+          <t>2026-09-16T23:07:48Z</t>
         </is>
       </c>
     </row>
@@ -5960,7 +5960,7 @@
       </c>
       <c r="S67" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15T23:01:39Z</t>
+          <t>2026-09-16T23:07:48Z</t>
         </is>
       </c>
     </row>
@@ -6045,7 +6045,7 @@
       </c>
       <c r="S68" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15T23:01:39Z</t>
+          <t>2026-09-16T23:07:48Z</t>
         </is>
       </c>
     </row>
@@ -6130,7 +6130,7 @@
       </c>
       <c r="S69" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15T23:01:39Z</t>
+          <t>2026-09-16T23:07:48Z</t>
         </is>
       </c>
     </row>
@@ -6215,7 +6215,7 @@
       </c>
       <c r="S70" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15T23:01:39Z</t>
+          <t>2026-09-16T23:07:48Z</t>
         </is>
       </c>
     </row>
@@ -6300,7 +6300,7 @@
       </c>
       <c r="S71" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15T23:01:39Z</t>
+          <t>2026-09-16T23:07:48Z</t>
         </is>
       </c>
     </row>
@@ -6385,7 +6385,7 @@
       </c>
       <c r="S72" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15T23:01:39Z</t>
+          <t>2026-09-16T23:07:48Z</t>
         </is>
       </c>
     </row>
@@ -6470,7 +6470,7 @@
       </c>
       <c r="S73" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15T23:01:39Z</t>
+          <t>2026-09-16T23:07:48Z</t>
         </is>
       </c>
     </row>
@@ -6555,7 +6555,7 @@
       </c>
       <c r="S74" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15T23:01:39Z</t>
+          <t>2026-09-16T23:07:48Z</t>
         </is>
       </c>
     </row>
@@ -6640,7 +6640,7 @@
       </c>
       <c r="S75" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15T23:01:39Z</t>
+          <t>2026-09-16T23:07:48Z</t>
         </is>
       </c>
     </row>
@@ -6725,7 +6725,7 @@
       </c>
       <c r="S76" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15T23:01:39Z</t>
+          <t>2026-09-16T23:07:48Z</t>
         </is>
       </c>
     </row>
@@ -6810,7 +6810,7 @@
       </c>
       <c r="S77" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15T23:01:39Z</t>
+          <t>2026-09-16T23:07:48Z</t>
         </is>
       </c>
     </row>
@@ -6895,7 +6895,7 @@
       </c>
       <c r="S78" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15T23:01:39Z</t>
+          <t>2026-09-16T23:07:48Z</t>
         </is>
       </c>
     </row>
@@ -6980,7 +6980,7 @@
       </c>
       <c r="S79" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15T23:01:39Z</t>
+          <t>2026-09-16T23:07:48Z</t>
         </is>
       </c>
     </row>
@@ -7065,7 +7065,7 @@
       </c>
       <c r="S80" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15T23:01:39Z</t>
+          <t>2026-09-16T23:07:48Z</t>
         </is>
       </c>
     </row>
@@ -7150,7 +7150,7 @@
       </c>
       <c r="S81" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15T23:01:39Z</t>
+          <t>2026-09-16T23:07:48Z</t>
         </is>
       </c>
     </row>
@@ -7235,7 +7235,7 @@
       </c>
       <c r="S82" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15T23:01:39Z</t>
+          <t>2026-09-16T23:07:48Z</t>
         </is>
       </c>
     </row>
@@ -7320,7 +7320,7 @@
       </c>
       <c r="S83" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15T23:01:39Z</t>
+          <t>2026-09-16T23:07:48Z</t>
         </is>
       </c>
     </row>
@@ -7405,7 +7405,7 @@
       </c>
       <c r="S84" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15T23:01:39Z</t>
+          <t>2026-09-16T23:07:48Z</t>
         </is>
       </c>
     </row>
@@ -7490,7 +7490,7 @@
       </c>
       <c r="S85" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15T23:01:39Z</t>
+          <t>2026-09-16T23:07:48Z</t>
         </is>
       </c>
     </row>
@@ -7575,7 +7575,7 @@
       </c>
       <c r="S86" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15T23:01:39Z</t>
+          <t>2026-09-16T23:07:48Z</t>
         </is>
       </c>
     </row>
@@ -7660,7 +7660,7 @@
       </c>
       <c r="S87" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15T23:01:39Z</t>
+          <t>2026-09-16T23:07:48Z</t>
         </is>
       </c>
     </row>
@@ -7745,7 +7745,7 @@
       </c>
       <c r="S88" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15T23:01:39Z</t>
+          <t>2026-09-16T23:07:48Z</t>
         </is>
       </c>
     </row>
@@ -7834,7 +7834,7 @@
       </c>
       <c r="S89" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15T23:01:39Z</t>
+          <t>2026-09-16T23:07:48Z</t>
         </is>
       </c>
     </row>
@@ -7923,7 +7923,7 @@
       </c>
       <c r="S90" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15T23:01:39Z</t>
+          <t>2026-09-16T23:07:48Z</t>
         </is>
       </c>
     </row>
@@ -8008,7 +8008,7 @@
       </c>
       <c r="S91" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15T23:01:39Z</t>
+          <t>2026-09-16T23:07:48Z</t>
         </is>
       </c>
     </row>
@@ -8097,7 +8097,7 @@
       </c>
       <c r="S92" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15T23:01:39Z</t>
+          <t>2026-09-16T23:07:48Z</t>
         </is>
       </c>
     </row>
@@ -8186,7 +8186,7 @@
       </c>
       <c r="S93" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15T23:01:39Z</t>
+          <t>2026-09-16T23:07:48Z</t>
         </is>
       </c>
     </row>
@@ -8271,7 +8271,7 @@
       </c>
       <c r="S94" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15T23:01:39Z</t>
+          <t>2026-09-16T23:07:48Z</t>
         </is>
       </c>
     </row>
@@ -8360,7 +8360,7 @@
       </c>
       <c r="S95" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15T23:01:39Z</t>
+          <t>2026-09-16T23:07:48Z</t>
         </is>
       </c>
     </row>
@@ -8449,7 +8449,7 @@
       </c>
       <c r="S96" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15T23:01:39Z</t>
+          <t>2026-09-16T23:07:48Z</t>
         </is>
       </c>
     </row>
@@ -8534,7 +8534,7 @@
       </c>
       <c r="S97" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15T23:01:39Z</t>
+          <t>2026-09-16T23:07:48Z</t>
         </is>
       </c>
     </row>
@@ -8623,7 +8623,7 @@
       </c>
       <c r="S98" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15T23:01:39Z</t>
+          <t>2026-09-16T23:07:48Z</t>
         </is>
       </c>
     </row>
@@ -8712,7 +8712,7 @@
       </c>
       <c r="S99" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15T23:01:39Z</t>
+          <t>2026-09-16T23:07:48Z</t>
         </is>
       </c>
     </row>
@@ -8797,7 +8797,7 @@
       </c>
       <c r="S100" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15T23:01:39Z</t>
+          <t>2026-09-16T23:07:48Z</t>
         </is>
       </c>
     </row>
@@ -8886,7 +8886,7 @@
       </c>
       <c r="S101" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15T23:01:39Z</t>
+          <t>2026-09-16T23:07:48Z</t>
         </is>
       </c>
     </row>
@@ -8975,7 +8975,7 @@
       </c>
       <c r="S102" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15T23:01:39Z</t>
+          <t>2026-09-16T23:07:48Z</t>
         </is>
       </c>
     </row>
@@ -9060,7 +9060,7 @@
       </c>
       <c r="S103" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15T23:01:39Z</t>
+          <t>2026-09-16T23:07:48Z</t>
         </is>
       </c>
     </row>
@@ -9149,7 +9149,7 @@
       </c>
       <c r="S104" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15T23:01:39Z</t>
+          <t>2026-09-16T23:07:48Z</t>
         </is>
       </c>
     </row>
@@ -9238,7 +9238,7 @@
       </c>
       <c r="S105" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15T23:01:39Z</t>
+          <t>2026-09-16T23:07:48Z</t>
         </is>
       </c>
     </row>
@@ -9323,7 +9323,7 @@
       </c>
       <c r="S106" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15T23:01:39Z</t>
+          <t>2026-09-16T23:07:48Z</t>
         </is>
       </c>
     </row>
@@ -9412,7 +9412,7 @@
       </c>
       <c r="S107" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15T23:01:39Z</t>
+          <t>2026-09-16T23:07:48Z</t>
         </is>
       </c>
     </row>
@@ -9501,7 +9501,7 @@
       </c>
       <c r="S108" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15T23:01:39Z</t>
+          <t>2026-09-16T23:07:48Z</t>
         </is>
       </c>
     </row>
@@ -9586,7 +9586,7 @@
       </c>
       <c r="S109" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15T23:01:39Z</t>
+          <t>2026-09-16T23:07:48Z</t>
         </is>
       </c>
     </row>
@@ -9675,7 +9675,7 @@
       </c>
       <c r="S110" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15T23:01:39Z</t>
+          <t>2026-09-16T23:07:48Z</t>
         </is>
       </c>
     </row>
@@ -9764,7 +9764,7 @@
       </c>
       <c r="S111" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15T23:01:39Z</t>
+          <t>2026-09-16T23:07:48Z</t>
         </is>
       </c>
     </row>
@@ -9849,7 +9849,7 @@
       </c>
       <c r="S112" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15T23:01:39Z</t>
+          <t>2026-09-16T23:07:48Z</t>
         </is>
       </c>
     </row>
@@ -9938,7 +9938,7 @@
       </c>
       <c r="S113" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15T23:01:39Z</t>
+          <t>2026-09-16T23:07:48Z</t>
         </is>
       </c>
     </row>
@@ -10027,7 +10027,7 @@
       </c>
       <c r="S114" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15T23:01:39Z</t>
+          <t>2026-09-16T23:07:48Z</t>
         </is>
       </c>
     </row>
@@ -10112,7 +10112,7 @@
       </c>
       <c r="S115" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15T23:01:39Z</t>
+          <t>2026-09-16T23:07:48Z</t>
         </is>
       </c>
     </row>
@@ -10201,7 +10201,7 @@
       </c>
       <c r="S116" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15T23:01:39Z</t>
+          <t>2026-09-16T23:07:48Z</t>
         </is>
       </c>
     </row>
@@ -10290,7 +10290,7 @@
       </c>
       <c r="S117" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15T23:01:39Z</t>
+          <t>2026-09-16T23:07:48Z</t>
         </is>
       </c>
     </row>
@@ -10379,7 +10379,7 @@
       </c>
       <c r="S118" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15T23:01:39Z</t>
+          <t>2026-09-16T23:07:48Z</t>
         </is>
       </c>
     </row>
@@ -10468,7 +10468,7 @@
       </c>
       <c r="S119" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15T23:01:39Z</t>
+          <t>2026-09-16T23:07:48Z</t>
         </is>
       </c>
     </row>
@@ -10557,7 +10557,7 @@
       </c>
       <c r="S120" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15T23:01:39Z</t>
+          <t>2026-09-16T23:07:48Z</t>
         </is>
       </c>
     </row>
@@ -10646,7 +10646,7 @@
       </c>
       <c r="S121" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15T23:01:39Z</t>
+          <t>2026-09-16T23:07:48Z</t>
         </is>
       </c>
     </row>
@@ -10735,7 +10735,7 @@
       </c>
       <c r="S122" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15T23:01:39Z</t>
+          <t>2026-09-16T23:07:48Z</t>
         </is>
       </c>
     </row>
@@ -10824,7 +10824,7 @@
       </c>
       <c r="S123" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15T23:01:39Z</t>
+          <t>2026-09-16T23:07:48Z</t>
         </is>
       </c>
     </row>
@@ -10913,7 +10913,7 @@
       </c>
       <c r="S124" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15T23:01:39Z</t>
+          <t>2026-09-16T23:07:48Z</t>
         </is>
       </c>
     </row>
@@ -11002,7 +11002,7 @@
       </c>
       <c r="S125" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15T23:01:39Z</t>
+          <t>2026-09-16T23:07:48Z</t>
         </is>
       </c>
     </row>
@@ -11091,7 +11091,7 @@
       </c>
       <c r="S126" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15T23:01:39Z</t>
+          <t>2026-09-16T23:07:48Z</t>
         </is>
       </c>
     </row>
@@ -11180,7 +11180,7 @@
       </c>
       <c r="S127" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15T23:01:39Z</t>
+          <t>2026-09-16T23:07:48Z</t>
         </is>
       </c>
     </row>
@@ -11269,7 +11269,7 @@
       </c>
       <c r="S128" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15T23:01:39Z</t>
+          <t>2026-09-16T23:07:48Z</t>
         </is>
       </c>
     </row>
@@ -11354,7 +11354,7 @@
       </c>
       <c r="S129" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15T23:01:39Z</t>
+          <t>2026-09-16T23:07:48Z</t>
         </is>
       </c>
     </row>
@@ -11439,7 +11439,7 @@
       </c>
       <c r="S130" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15T23:01:39Z</t>
+          <t>2026-09-16T23:07:48Z</t>
         </is>
       </c>
     </row>
@@ -11524,7 +11524,7 @@
       </c>
       <c r="S131" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15T23:01:39Z</t>
+          <t>2026-09-16T23:07:48Z</t>
         </is>
       </c>
     </row>
@@ -11609,7 +11609,7 @@
       </c>
       <c r="S132" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15T23:01:39Z</t>
+          <t>2026-09-16T23:07:48Z</t>
         </is>
       </c>
     </row>
@@ -11694,7 +11694,7 @@
       </c>
       <c r="S133" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15T23:01:39Z</t>
+          <t>2026-09-16T23:07:48Z</t>
         </is>
       </c>
     </row>
@@ -11779,7 +11779,7 @@
       </c>
       <c r="S134" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15T23:01:39Z</t>
+          <t>2026-09-16T23:07:48Z</t>
         </is>
       </c>
     </row>
@@ -11864,7 +11864,7 @@
       </c>
       <c r="S135" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15T23:01:39Z</t>
+          <t>2026-09-16T23:07:48Z</t>
         </is>
       </c>
     </row>
@@ -11949,7 +11949,7 @@
       </c>
       <c r="S136" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15T23:01:39Z</t>
+          <t>2026-09-16T23:07:48Z</t>
         </is>
       </c>
     </row>
@@ -12034,7 +12034,7 @@
       </c>
       <c r="S137" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15T23:01:39Z</t>
+          <t>2026-09-16T23:07:48Z</t>
         </is>
       </c>
     </row>
@@ -12119,7 +12119,7 @@
       </c>
       <c r="S138" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15T23:01:39Z</t>
+          <t>2026-09-16T23:07:48Z</t>
         </is>
       </c>
     </row>
@@ -12204,7 +12204,7 @@
       </c>
       <c r="S139" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15T23:01:39Z</t>
+          <t>2026-09-16T23:07:48Z</t>
         </is>
       </c>
     </row>
@@ -12289,7 +12289,7 @@
       </c>
       <c r="S140" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15T23:01:39Z</t>
+          <t>2026-09-16T23:07:48Z</t>
         </is>
       </c>
     </row>
@@ -12374,7 +12374,7 @@
       </c>
       <c r="S141" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15T23:01:39Z</t>
+          <t>2026-09-16T23:07:48Z</t>
         </is>
       </c>
     </row>
@@ -12459,7 +12459,7 @@
       </c>
       <c r="S142" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15T23:01:39Z</t>
+          <t>2026-09-16T23:07:48Z</t>
         </is>
       </c>
     </row>
@@ -12544,7 +12544,7 @@
       </c>
       <c r="S143" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15T23:01:39Z</t>
+          <t>2026-09-16T23:07:48Z</t>
         </is>
       </c>
     </row>
@@ -12629,7 +12629,7 @@
       </c>
       <c r="S144" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15T23:01:39Z</t>
+          <t>2026-09-16T23:07:48Z</t>
         </is>
       </c>
     </row>
@@ -12714,7 +12714,7 @@
       </c>
       <c r="S145" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15T23:01:39Z</t>
+          <t>2026-09-16T23:07:48Z</t>
         </is>
       </c>
     </row>
@@ -12799,7 +12799,7 @@
       </c>
       <c r="S146" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15T23:01:39Z</t>
+          <t>2026-09-16T23:07:48Z</t>
         </is>
       </c>
     </row>
@@ -12884,7 +12884,7 @@
       </c>
       <c r="S147" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15T23:01:39Z</t>
+          <t>2026-09-16T23:07:48Z</t>
         </is>
       </c>
     </row>
@@ -12969,7 +12969,7 @@
       </c>
       <c r="S148" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15T23:01:39Z</t>
+          <t>2026-09-16T23:07:48Z</t>
         </is>
       </c>
     </row>
@@ -13054,7 +13054,7 @@
       </c>
       <c r="S149" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15T23:01:39Z</t>
+          <t>2026-09-16T23:07:48Z</t>
         </is>
       </c>
     </row>
@@ -13143,7 +13143,7 @@
       </c>
       <c r="S150" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15T23:01:39Z</t>
+          <t>2026-09-16T23:07:48Z</t>
         </is>
       </c>
     </row>
@@ -13232,7 +13232,7 @@
       </c>
       <c r="S151" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15T23:01:39Z</t>
+          <t>2026-09-16T23:07:48Z</t>
         </is>
       </c>
     </row>
@@ -13317,7 +13317,7 @@
       </c>
       <c r="S152" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15T23:01:39Z</t>
+          <t>2026-09-16T23:07:48Z</t>
         </is>
       </c>
     </row>
@@ -13406,7 +13406,7 @@
       </c>
       <c r="S153" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15T23:01:39Z</t>
+          <t>2026-09-16T23:07:48Z</t>
         </is>
       </c>
     </row>
@@ -13495,7 +13495,7 @@
       </c>
       <c r="S154" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15T23:01:39Z</t>
+          <t>2026-09-16T23:07:48Z</t>
         </is>
       </c>
     </row>
@@ -13580,7 +13580,7 @@
       </c>
       <c r="S155" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15T23:01:39Z</t>
+          <t>2026-09-16T23:07:48Z</t>
         </is>
       </c>
     </row>
@@ -13669,7 +13669,7 @@
       </c>
       <c r="S156" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15T23:01:39Z</t>
+          <t>2026-09-16T23:07:48Z</t>
         </is>
       </c>
     </row>
@@ -13758,7 +13758,7 @@
       </c>
       <c r="S157" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15T23:01:39Z</t>
+          <t>2026-09-16T23:07:48Z</t>
         </is>
       </c>
     </row>
@@ -13843,7 +13843,7 @@
       </c>
       <c r="S158" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15T23:01:39Z</t>
+          <t>2026-09-16T23:07:48Z</t>
         </is>
       </c>
     </row>
@@ -13932,7 +13932,7 @@
       </c>
       <c r="S159" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15T23:01:39Z</t>
+          <t>2026-09-16T23:07:48Z</t>
         </is>
       </c>
     </row>
@@ -14021,7 +14021,7 @@
       </c>
       <c r="S160" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15T23:01:39Z</t>
+          <t>2026-09-16T23:07:48Z</t>
         </is>
       </c>
     </row>
@@ -14106,7 +14106,7 @@
       </c>
       <c r="S161" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15T23:01:39Z</t>
+          <t>2026-09-16T23:07:48Z</t>
         </is>
       </c>
     </row>
@@ -14195,7 +14195,7 @@
       </c>
       <c r="S162" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15T23:01:39Z</t>
+          <t>2026-09-16T23:07:48Z</t>
         </is>
       </c>
     </row>
@@ -14284,7 +14284,7 @@
       </c>
       <c r="S163" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15T23:01:39Z</t>
+          <t>2026-09-16T23:07:48Z</t>
         </is>
       </c>
     </row>
@@ -14369,7 +14369,7 @@
       </c>
       <c r="S164" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15T23:01:39Z</t>
+          <t>2026-09-16T23:07:48Z</t>
         </is>
       </c>
     </row>
@@ -14458,7 +14458,7 @@
       </c>
       <c r="S165" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15T23:01:39Z</t>
+          <t>2026-09-16T23:07:48Z</t>
         </is>
       </c>
     </row>
@@ -14547,7 +14547,7 @@
       </c>
       <c r="S166" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15T23:01:39Z</t>
+          <t>2026-09-16T23:07:48Z</t>
         </is>
       </c>
     </row>
@@ -14632,7 +14632,7 @@
       </c>
       <c r="S167" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15T23:01:39Z</t>
+          <t>2026-09-16T23:07:48Z</t>
         </is>
       </c>
     </row>
@@ -14721,7 +14721,7 @@
       </c>
       <c r="S168" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15T23:01:39Z</t>
+          <t>2026-09-16T23:07:48Z</t>
         </is>
       </c>
     </row>
@@ -14810,7 +14810,7 @@
       </c>
       <c r="S169" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15T23:01:39Z</t>
+          <t>2026-09-16T23:07:48Z</t>
         </is>
       </c>
     </row>
@@ -14895,7 +14895,7 @@
       </c>
       <c r="S170" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15T23:01:39Z</t>
+          <t>2026-09-16T23:07:48Z</t>
         </is>
       </c>
     </row>
@@ -14984,7 +14984,7 @@
       </c>
       <c r="S171" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15T23:01:39Z</t>
+          <t>2026-09-16T23:07:48Z</t>
         </is>
       </c>
     </row>
@@ -15073,7 +15073,7 @@
       </c>
       <c r="S172" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15T23:01:39Z</t>
+          <t>2026-09-16T23:07:48Z</t>
         </is>
       </c>
     </row>
@@ -15158,7 +15158,7 @@
       </c>
       <c r="S173" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15T23:01:39Z</t>
+          <t>2026-09-16T23:07:48Z</t>
         </is>
       </c>
     </row>
@@ -15247,7 +15247,7 @@
       </c>
       <c r="S174" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15T23:01:39Z</t>
+          <t>2026-09-16T23:07:48Z</t>
         </is>
       </c>
     </row>
@@ -15336,7 +15336,7 @@
       </c>
       <c r="S175" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15T23:01:39Z</t>
+          <t>2026-09-16T23:07:48Z</t>
         </is>
       </c>
     </row>
@@ -15421,7 +15421,7 @@
       </c>
       <c r="S176" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15T23:01:39Z</t>
+          <t>2026-09-16T23:07:48Z</t>
         </is>
       </c>
     </row>
@@ -15510,7 +15510,7 @@
       </c>
       <c r="S177" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15T23:01:39Z</t>
+          <t>2026-09-16T23:07:48Z</t>
         </is>
       </c>
     </row>
@@ -15599,7 +15599,7 @@
       </c>
       <c r="S178" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15T23:01:39Z</t>
+          <t>2026-09-16T23:07:48Z</t>
         </is>
       </c>
     </row>
@@ -15688,7 +15688,7 @@
       </c>
       <c r="S179" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15T23:01:39Z</t>
+          <t>2026-09-16T23:07:48Z</t>
         </is>
       </c>
     </row>
@@ -15777,7 +15777,7 @@
       </c>
       <c r="S180" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15T23:01:39Z</t>
+          <t>2026-09-16T23:07:48Z</t>
         </is>
       </c>
     </row>
@@ -15866,7 +15866,7 @@
       </c>
       <c r="S181" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15T23:01:39Z</t>
+          <t>2026-09-16T23:07:48Z</t>
         </is>
       </c>
     </row>
@@ -15955,7 +15955,7 @@
       </c>
       <c r="S182" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15T23:01:39Z</t>
+          <t>2026-09-16T23:07:48Z</t>
         </is>
       </c>
     </row>
@@ -16044,7 +16044,7 @@
       </c>
       <c r="S183" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15T23:01:39Z</t>
+          <t>2026-09-16T23:07:48Z</t>
         </is>
       </c>
     </row>
@@ -16133,7 +16133,7 @@
       </c>
       <c r="S184" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15T23:01:39Z</t>
+          <t>2026-09-16T23:07:48Z</t>
         </is>
       </c>
     </row>
@@ -16222,7 +16222,7 @@
       </c>
       <c r="S185" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15T23:01:39Z</t>
+          <t>2026-09-16T23:07:48Z</t>
         </is>
       </c>
     </row>
@@ -16311,7 +16311,7 @@
       </c>
       <c r="S186" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15T23:01:39Z</t>
+          <t>2026-09-16T23:07:48Z</t>
         </is>
       </c>
     </row>
@@ -16400,7 +16400,7 @@
       </c>
       <c r="S187" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15T23:01:39Z</t>
+          <t>2026-09-16T23:07:48Z</t>
         </is>
       </c>
     </row>
@@ -16489,7 +16489,7 @@
       </c>
       <c r="S188" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15T23:01:39Z</t>
+          <t>2026-09-16T23:07:48Z</t>
         </is>
       </c>
     </row>
@@ -16578,7 +16578,7 @@
       </c>
       <c r="S189" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15T23:01:39Z</t>
+          <t>2026-09-16T23:07:48Z</t>
         </is>
       </c>
     </row>
@@ -16663,7 +16663,7 @@
       </c>
       <c r="S190" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15T23:01:39Z</t>
+          <t>2026-09-16T23:07:48Z</t>
         </is>
       </c>
     </row>
@@ -16748,7 +16748,7 @@
       </c>
       <c r="S191" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15T23:01:39Z</t>
+          <t>2026-09-16T23:07:48Z</t>
         </is>
       </c>
     </row>
@@ -16833,7 +16833,7 @@
       </c>
       <c r="S192" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15T23:01:39Z</t>
+          <t>2026-09-16T23:07:48Z</t>
         </is>
       </c>
     </row>
@@ -16918,7 +16918,7 @@
       </c>
       <c r="S193" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15T23:01:39Z</t>
+          <t>2026-09-16T23:07:48Z</t>
         </is>
       </c>
     </row>
@@ -17003,7 +17003,7 @@
       </c>
       <c r="S194" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15T23:01:39Z</t>
+          <t>2026-09-16T23:07:48Z</t>
         </is>
       </c>
     </row>
@@ -17088,7 +17088,7 @@
       </c>
       <c r="S195" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15T23:01:39Z</t>
+          <t>2026-09-16T23:07:48Z</t>
         </is>
       </c>
     </row>
@@ -17173,7 +17173,7 @@
       </c>
       <c r="S196" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15T23:01:39Z</t>
+          <t>2026-09-16T23:07:48Z</t>
         </is>
       </c>
     </row>
@@ -17258,7 +17258,7 @@
       </c>
       <c r="S197" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15T23:01:39Z</t>
+          <t>2026-09-16T23:07:48Z</t>
         </is>
       </c>
     </row>
@@ -17343,7 +17343,7 @@
       </c>
       <c r="S198" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15T23:01:39Z</t>
+          <t>2026-09-16T23:07:48Z</t>
         </is>
       </c>
     </row>
@@ -17428,7 +17428,7 @@
       </c>
       <c r="S199" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15T23:01:39Z</t>
+          <t>2026-09-16T23:07:48Z</t>
         </is>
       </c>
     </row>
@@ -17513,7 +17513,7 @@
       </c>
       <c r="S200" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15T23:01:39Z</t>
+          <t>2026-09-16T23:07:48Z</t>
         </is>
       </c>
     </row>
@@ -17598,7 +17598,7 @@
       </c>
       <c r="S201" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15T23:01:39Z</t>
+          <t>2026-09-16T23:07:48Z</t>
         </is>
       </c>
     </row>
@@ -17683,7 +17683,7 @@
       </c>
       <c r="S202" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15T23:01:39Z</t>
+          <t>2026-09-16T23:07:48Z</t>
         </is>
       </c>
     </row>
@@ -17768,7 +17768,7 @@
       </c>
       <c r="S203" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15T23:01:39Z</t>
+          <t>2026-09-16T23:07:48Z</t>
         </is>
       </c>
     </row>
@@ -17853,7 +17853,7 @@
       </c>
       <c r="S204" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15T23:01:39Z</t>
+          <t>2026-09-16T23:07:48Z</t>
         </is>
       </c>
     </row>
@@ -17938,7 +17938,7 @@
       </c>
       <c r="S205" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15T23:01:39Z</t>
+          <t>2026-09-16T23:07:48Z</t>
         </is>
       </c>
     </row>
@@ -18023,7 +18023,7 @@
       </c>
       <c r="S206" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15T23:01:39Z</t>
+          <t>2026-09-16T23:07:48Z</t>
         </is>
       </c>
     </row>
@@ -18108,7 +18108,7 @@
       </c>
       <c r="S207" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15T23:01:39Z</t>
+          <t>2026-09-16T23:07:48Z</t>
         </is>
       </c>
     </row>
@@ -18193,7 +18193,7 @@
       </c>
       <c r="S208" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15T23:01:39Z</t>
+          <t>2026-09-16T23:07:48Z</t>
         </is>
       </c>
     </row>
@@ -18278,7 +18278,7 @@
       </c>
       <c r="S209" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15T23:01:39Z</t>
+          <t>2026-09-16T23:07:48Z</t>
         </is>
       </c>
     </row>
@@ -18363,7 +18363,7 @@
       </c>
       <c r="S210" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15T23:01:39Z</t>
+          <t>2026-09-16T23:07:48Z</t>
         </is>
       </c>
     </row>
@@ -18452,7 +18452,7 @@
       </c>
       <c r="S211" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15T23:01:39Z</t>
+          <t>2026-09-16T23:07:48Z</t>
         </is>
       </c>
     </row>
@@ -18541,7 +18541,7 @@
       </c>
       <c r="S212" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15T23:01:39Z</t>
+          <t>2026-09-16T23:07:48Z</t>
         </is>
       </c>
     </row>
@@ -18626,7 +18626,7 @@
       </c>
       <c r="S213" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15T23:01:39Z</t>
+          <t>2026-09-16T23:07:48Z</t>
         </is>
       </c>
     </row>
@@ -18715,7 +18715,7 @@
       </c>
       <c r="S214" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15T23:01:39Z</t>
+          <t>2026-09-16T23:07:48Z</t>
         </is>
       </c>
     </row>
@@ -18804,7 +18804,7 @@
       </c>
       <c r="S215" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15T23:01:39Z</t>
+          <t>2026-09-16T23:07:48Z</t>
         </is>
       </c>
     </row>
@@ -18889,7 +18889,7 @@
       </c>
       <c r="S216" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15T23:01:39Z</t>
+          <t>2026-09-16T23:07:48Z</t>
         </is>
       </c>
     </row>
@@ -18978,7 +18978,7 @@
       </c>
       <c r="S217" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15T23:01:39Z</t>
+          <t>2026-09-16T23:07:48Z</t>
         </is>
       </c>
     </row>
@@ -19067,7 +19067,7 @@
       </c>
       <c r="S218" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15T23:01:39Z</t>
+          <t>2026-09-16T23:07:48Z</t>
         </is>
       </c>
     </row>
@@ -19152,7 +19152,7 @@
       </c>
       <c r="S219" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15T23:01:39Z</t>
+          <t>2026-09-16T23:07:48Z</t>
         </is>
       </c>
     </row>
@@ -19241,7 +19241,7 @@
       </c>
       <c r="S220" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15T23:01:39Z</t>
+          <t>2026-09-16T23:07:48Z</t>
         </is>
       </c>
     </row>
@@ -19330,7 +19330,7 @@
       </c>
       <c r="S221" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15T23:01:39Z</t>
+          <t>2026-09-16T23:07:48Z</t>
         </is>
       </c>
     </row>
@@ -19415,7 +19415,7 @@
       </c>
       <c r="S222" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15T23:01:39Z</t>
+          <t>2026-09-16T23:07:48Z</t>
         </is>
       </c>
     </row>
@@ -19504,7 +19504,7 @@
       </c>
       <c r="S223" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15T23:01:39Z</t>
+          <t>2026-09-16T23:07:48Z</t>
         </is>
       </c>
     </row>
@@ -19593,7 +19593,7 @@
       </c>
       <c r="S224" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15T23:01:39Z</t>
+          <t>2026-09-16T23:07:48Z</t>
         </is>
       </c>
     </row>
@@ -19678,7 +19678,7 @@
       </c>
       <c r="S225" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15T23:01:39Z</t>
+          <t>2026-09-16T23:07:48Z</t>
         </is>
       </c>
     </row>
@@ -19767,7 +19767,7 @@
       </c>
       <c r="S226" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15T23:01:39Z</t>
+          <t>2026-09-16T23:07:48Z</t>
         </is>
       </c>
     </row>
@@ -19856,7 +19856,7 @@
       </c>
       <c r="S227" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15T23:01:39Z</t>
+          <t>2026-09-16T23:07:48Z</t>
         </is>
       </c>
     </row>
@@ -19941,7 +19941,7 @@
       </c>
       <c r="S228" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15T23:01:39Z</t>
+          <t>2026-09-16T23:07:48Z</t>
         </is>
       </c>
     </row>
@@ -20030,7 +20030,7 @@
       </c>
       <c r="S229" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15T23:01:39Z</t>
+          <t>2026-09-16T23:07:48Z</t>
         </is>
       </c>
     </row>
@@ -20119,7 +20119,7 @@
       </c>
       <c r="S230" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15T23:01:39Z</t>
+          <t>2026-09-16T23:07:48Z</t>
         </is>
       </c>
     </row>
@@ -20204,7 +20204,7 @@
       </c>
       <c r="S231" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15T23:01:39Z</t>
+          <t>2026-09-16T23:07:48Z</t>
         </is>
       </c>
     </row>
@@ -20293,7 +20293,7 @@
       </c>
       <c r="S232" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15T23:01:39Z</t>
+          <t>2026-09-16T23:07:48Z</t>
         </is>
       </c>
     </row>
@@ -20382,7 +20382,7 @@
       </c>
       <c r="S233" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15T23:01:39Z</t>
+          <t>2026-09-16T23:07:48Z</t>
         </is>
       </c>
     </row>
@@ -20467,7 +20467,7 @@
       </c>
       <c r="S234" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15T23:01:39Z</t>
+          <t>2026-09-16T23:07:48Z</t>
         </is>
       </c>
     </row>
@@ -20556,7 +20556,7 @@
       </c>
       <c r="S235" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15T23:01:39Z</t>
+          <t>2026-09-16T23:07:48Z</t>
         </is>
       </c>
     </row>
@@ -20645,7 +20645,7 @@
       </c>
       <c r="S236" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15T23:01:39Z</t>
+          <t>2026-09-16T23:07:48Z</t>
         </is>
       </c>
     </row>
@@ -20730,7 +20730,7 @@
       </c>
       <c r="S237" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15T23:01:39Z</t>
+          <t>2026-09-16T23:07:48Z</t>
         </is>
       </c>
     </row>
@@ -20819,7 +20819,7 @@
       </c>
       <c r="S238" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15T23:01:39Z</t>
+          <t>2026-09-16T23:07:48Z</t>
         </is>
       </c>
     </row>
@@ -20908,7 +20908,7 @@
       </c>
       <c r="S239" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15T23:01:39Z</t>
+          <t>2026-09-16T23:07:48Z</t>
         </is>
       </c>
     </row>
@@ -20997,7 +20997,7 @@
       </c>
       <c r="S240" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15T23:01:39Z</t>
+          <t>2026-09-16T23:07:48Z</t>
         </is>
       </c>
     </row>
@@ -21086,7 +21086,7 @@
       </c>
       <c r="S241" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15T23:01:39Z</t>
+          <t>2026-09-16T23:07:48Z</t>
         </is>
       </c>
     </row>
@@ -21175,7 +21175,7 @@
       </c>
       <c r="S242" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15T23:01:39Z</t>
+          <t>2026-09-16T23:07:48Z</t>
         </is>
       </c>
     </row>
@@ -21264,7 +21264,7 @@
       </c>
       <c r="S243" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15T23:01:39Z</t>
+          <t>2026-09-16T23:07:48Z</t>
         </is>
       </c>
     </row>
@@ -21353,7 +21353,7 @@
       </c>
       <c r="S244" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15T23:01:39Z</t>
+          <t>2026-09-16T23:07:48Z</t>
         </is>
       </c>
     </row>
@@ -21442,7 +21442,7 @@
       </c>
       <c r="S245" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15T23:01:39Z</t>
+          <t>2026-09-16T23:07:48Z</t>
         </is>
       </c>
     </row>
@@ -21531,7 +21531,7 @@
       </c>
       <c r="S246" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15T23:01:39Z</t>
+          <t>2026-09-16T23:07:48Z</t>
         </is>
       </c>
     </row>
@@ -21620,7 +21620,7 @@
       </c>
       <c r="S247" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15T23:01:39Z</t>
+          <t>2026-09-16T23:07:48Z</t>
         </is>
       </c>
     </row>
@@ -21709,7 +21709,7 @@
       </c>
       <c r="S248" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15T23:01:39Z</t>
+          <t>2026-09-16T23:07:48Z</t>
         </is>
       </c>
     </row>
@@ -21798,7 +21798,7 @@
       </c>
       <c r="S249" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15T23:01:39Z</t>
+          <t>2026-09-16T23:07:48Z</t>
         </is>
       </c>
     </row>
@@ -21887,7 +21887,7 @@
       </c>
       <c r="S250" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15T23:01:39Z</t>
+          <t>2026-09-16T23:07:48Z</t>
         </is>
       </c>
     </row>
@@ -22019,7 +22019,7 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15T23:01:39Z</t>
+          <t>2026-09-16T23:07:48Z</t>
         </is>
       </c>
     </row>
@@ -22099,7 +22099,7 @@
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>{"dataset_id": "bcv_pib_sector_institucional_anual", "title": "Producto interno bruto por sector institucional anual", "table": "Variaciones porcentuales", "source_file": "5_2_1_si_anual.xlsx", "base": "2007", "price_type": "Precios constantes", "measure": "Variación porcentual interanual", "frequency": "Anual", "period": "2025", "year": 2025, "quarter": null, "classification": "Sector institucional", "component": "Impuestos netos sobre los productos", "value": 10.600260421283764, "unit": "Porcentaje", "status": "Preliminar", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/cuentas_macroeconomicas/5_2_1_si_anual.xlsx", "fetched_at": "2026-09-15T23:01:39Z"}</t>
+          <t>{"dataset_id": "bcv_pib_sector_institucional_anual", "title": "Producto interno bruto por sector institucional anual", "table": "Variaciones porcentuales", "source_file": "5_2_1_si_anual.xlsx", "base": "2007", "price_type": "Precios constantes", "measure": "Variación porcentual interanual", "frequency": "Anual", "period": "2025", "year": 2025, "quarter": null, "classification": "Sector institucional", "component": "Impuestos netos sobre los productos", "value": 10.600260421283764, "unit": "Porcentaje", "status": "Preliminar", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/cuentas_macroeconomicas/5_2_1_si_anual.xlsx", "fetched_at": "2026-09-16T23:07:48Z"}</t>
         </is>
       </c>
     </row>

--- a/assets/data/bcv/excel/ove_bcv_pib_sector_institucional_anual.xlsx
+++ b/assets/data/bcv/excel/ove_bcv_pib_sector_institucional_anual.xlsx
@@ -736,7 +736,7 @@
       </c>
       <c r="S7" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T23:07:48Z</t>
+          <t>2026-09-17T17:37:55Z</t>
         </is>
       </c>
     </row>
@@ -821,7 +821,7 @@
       </c>
       <c r="S8" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T23:07:48Z</t>
+          <t>2026-09-17T17:37:55Z</t>
         </is>
       </c>
     </row>
@@ -906,7 +906,7 @@
       </c>
       <c r="S9" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T23:07:48Z</t>
+          <t>2026-09-17T17:37:55Z</t>
         </is>
       </c>
     </row>
@@ -991,7 +991,7 @@
       </c>
       <c r="S10" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T23:07:48Z</t>
+          <t>2026-09-17T17:37:55Z</t>
         </is>
       </c>
     </row>
@@ -1076,7 +1076,7 @@
       </c>
       <c r="S11" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T23:07:48Z</t>
+          <t>2026-09-17T17:37:55Z</t>
         </is>
       </c>
     </row>
@@ -1161,7 +1161,7 @@
       </c>
       <c r="S12" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T23:07:48Z</t>
+          <t>2026-09-17T17:37:55Z</t>
         </is>
       </c>
     </row>
@@ -1246,7 +1246,7 @@
       </c>
       <c r="S13" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T23:07:48Z</t>
+          <t>2026-09-17T17:37:55Z</t>
         </is>
       </c>
     </row>
@@ -1331,7 +1331,7 @@
       </c>
       <c r="S14" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T23:07:48Z</t>
+          <t>2026-09-17T17:37:55Z</t>
         </is>
       </c>
     </row>
@@ -1416,7 +1416,7 @@
       </c>
       <c r="S15" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T23:07:48Z</t>
+          <t>2026-09-17T17:37:55Z</t>
         </is>
       </c>
     </row>
@@ -1501,7 +1501,7 @@
       </c>
       <c r="S16" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T23:07:48Z</t>
+          <t>2026-09-17T17:37:55Z</t>
         </is>
       </c>
     </row>
@@ -1586,7 +1586,7 @@
       </c>
       <c r="S17" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T23:07:48Z</t>
+          <t>2026-09-17T17:37:55Z</t>
         </is>
       </c>
     </row>
@@ -1671,7 +1671,7 @@
       </c>
       <c r="S18" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T23:07:48Z</t>
+          <t>2026-09-17T17:37:55Z</t>
         </is>
       </c>
     </row>
@@ -1756,7 +1756,7 @@
       </c>
       <c r="S19" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T23:07:48Z</t>
+          <t>2026-09-17T17:37:55Z</t>
         </is>
       </c>
     </row>
@@ -1841,7 +1841,7 @@
       </c>
       <c r="S20" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T23:07:48Z</t>
+          <t>2026-09-17T17:37:55Z</t>
         </is>
       </c>
     </row>
@@ -1926,7 +1926,7 @@
       </c>
       <c r="S21" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T23:07:48Z</t>
+          <t>2026-09-17T17:37:55Z</t>
         </is>
       </c>
     </row>
@@ -2011,7 +2011,7 @@
       </c>
       <c r="S22" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T23:07:48Z</t>
+          <t>2026-09-17T17:37:55Z</t>
         </is>
       </c>
     </row>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="S23" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T23:07:48Z</t>
+          <t>2026-09-17T17:37:55Z</t>
         </is>
       </c>
     </row>
@@ -2181,7 +2181,7 @@
       </c>
       <c r="S24" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T23:07:48Z</t>
+          <t>2026-09-17T17:37:55Z</t>
         </is>
       </c>
     </row>
@@ -2266,7 +2266,7 @@
       </c>
       <c r="S25" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T23:07:48Z</t>
+          <t>2026-09-17T17:37:55Z</t>
         </is>
       </c>
     </row>
@@ -2351,7 +2351,7 @@
       </c>
       <c r="S26" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T23:07:48Z</t>
+          <t>2026-09-17T17:37:55Z</t>
         </is>
       </c>
     </row>
@@ -2436,7 +2436,7 @@
       </c>
       <c r="S27" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T23:07:48Z</t>
+          <t>2026-09-17T17:37:55Z</t>
         </is>
       </c>
     </row>
@@ -2525,7 +2525,7 @@
       </c>
       <c r="S28" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T23:07:48Z</t>
+          <t>2026-09-17T17:37:55Z</t>
         </is>
       </c>
     </row>
@@ -2614,7 +2614,7 @@
       </c>
       <c r="S29" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T23:07:48Z</t>
+          <t>2026-09-17T17:37:55Z</t>
         </is>
       </c>
     </row>
@@ -2699,7 +2699,7 @@
       </c>
       <c r="S30" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T23:07:48Z</t>
+          <t>2026-09-17T17:37:55Z</t>
         </is>
       </c>
     </row>
@@ -2788,7 +2788,7 @@
       </c>
       <c r="S31" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T23:07:48Z</t>
+          <t>2026-09-17T17:37:55Z</t>
         </is>
       </c>
     </row>
@@ -2877,7 +2877,7 @@
       </c>
       <c r="S32" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T23:07:48Z</t>
+          <t>2026-09-17T17:37:55Z</t>
         </is>
       </c>
     </row>
@@ -2962,7 +2962,7 @@
       </c>
       <c r="S33" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T23:07:48Z</t>
+          <t>2026-09-17T17:37:55Z</t>
         </is>
       </c>
     </row>
@@ -3051,7 +3051,7 @@
       </c>
       <c r="S34" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T23:07:48Z</t>
+          <t>2026-09-17T17:37:55Z</t>
         </is>
       </c>
     </row>
@@ -3140,7 +3140,7 @@
       </c>
       <c r="S35" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T23:07:48Z</t>
+          <t>2026-09-17T17:37:55Z</t>
         </is>
       </c>
     </row>
@@ -3225,7 +3225,7 @@
       </c>
       <c r="S36" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T23:07:48Z</t>
+          <t>2026-09-17T17:37:55Z</t>
         </is>
       </c>
     </row>
@@ -3314,7 +3314,7 @@
       </c>
       <c r="S37" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T23:07:48Z</t>
+          <t>2026-09-17T17:37:55Z</t>
         </is>
       </c>
     </row>
@@ -3403,7 +3403,7 @@
       </c>
       <c r="S38" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T23:07:48Z</t>
+          <t>2026-09-17T17:37:55Z</t>
         </is>
       </c>
     </row>
@@ -3488,7 +3488,7 @@
       </c>
       <c r="S39" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T23:07:48Z</t>
+          <t>2026-09-17T17:37:55Z</t>
         </is>
       </c>
     </row>
@@ -3577,7 +3577,7 @@
       </c>
       <c r="S40" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T23:07:48Z</t>
+          <t>2026-09-17T17:37:55Z</t>
         </is>
       </c>
     </row>
@@ -3666,7 +3666,7 @@
       </c>
       <c r="S41" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T23:07:48Z</t>
+          <t>2026-09-17T17:37:55Z</t>
         </is>
       </c>
     </row>
@@ -3751,7 +3751,7 @@
       </c>
       <c r="S42" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T23:07:48Z</t>
+          <t>2026-09-17T17:37:55Z</t>
         </is>
       </c>
     </row>
@@ -3840,7 +3840,7 @@
       </c>
       <c r="S43" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T23:07:48Z</t>
+          <t>2026-09-17T17:37:55Z</t>
         </is>
       </c>
     </row>
@@ -3929,7 +3929,7 @@
       </c>
       <c r="S44" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T23:07:48Z</t>
+          <t>2026-09-17T17:37:55Z</t>
         </is>
       </c>
     </row>
@@ -4014,7 +4014,7 @@
       </c>
       <c r="S45" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T23:07:48Z</t>
+          <t>2026-09-17T17:37:55Z</t>
         </is>
       </c>
     </row>
@@ -4103,7 +4103,7 @@
       </c>
       <c r="S46" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T23:07:48Z</t>
+          <t>2026-09-17T17:37:55Z</t>
         </is>
       </c>
     </row>
@@ -4192,7 +4192,7 @@
       </c>
       <c r="S47" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T23:07:48Z</t>
+          <t>2026-09-17T17:37:55Z</t>
         </is>
       </c>
     </row>
@@ -4277,7 +4277,7 @@
       </c>
       <c r="S48" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T23:07:48Z</t>
+          <t>2026-09-17T17:37:55Z</t>
         </is>
       </c>
     </row>
@@ -4366,7 +4366,7 @@
       </c>
       <c r="S49" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T23:07:48Z</t>
+          <t>2026-09-17T17:37:55Z</t>
         </is>
       </c>
     </row>
@@ -4455,7 +4455,7 @@
       </c>
       <c r="S50" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T23:07:48Z</t>
+          <t>2026-09-17T17:37:55Z</t>
         </is>
       </c>
     </row>
@@ -4540,7 +4540,7 @@
       </c>
       <c r="S51" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T23:07:48Z</t>
+          <t>2026-09-17T17:37:55Z</t>
         </is>
       </c>
     </row>
@@ -4629,7 +4629,7 @@
       </c>
       <c r="S52" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T23:07:48Z</t>
+          <t>2026-09-17T17:37:55Z</t>
         </is>
       </c>
     </row>
@@ -4718,7 +4718,7 @@
       </c>
       <c r="S53" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T23:07:48Z</t>
+          <t>2026-09-17T17:37:55Z</t>
         </is>
       </c>
     </row>
@@ -4803,7 +4803,7 @@
       </c>
       <c r="S54" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T23:07:48Z</t>
+          <t>2026-09-17T17:37:55Z</t>
         </is>
       </c>
     </row>
@@ -4892,7 +4892,7 @@
       </c>
       <c r="S55" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T23:07:48Z</t>
+          <t>2026-09-17T17:37:55Z</t>
         </is>
       </c>
     </row>
@@ -4981,7 +4981,7 @@
       </c>
       <c r="S56" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T23:07:48Z</t>
+          <t>2026-09-17T17:37:55Z</t>
         </is>
       </c>
     </row>
@@ -5070,7 +5070,7 @@
       </c>
       <c r="S57" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T23:07:48Z</t>
+          <t>2026-09-17T17:37:55Z</t>
         </is>
       </c>
     </row>
@@ -5159,7 +5159,7 @@
       </c>
       <c r="S58" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T23:07:48Z</t>
+          <t>2026-09-17T17:37:55Z</t>
         </is>
       </c>
     </row>
@@ -5248,7 +5248,7 @@
       </c>
       <c r="S59" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T23:07:48Z</t>
+          <t>2026-09-17T17:37:55Z</t>
         </is>
       </c>
     </row>
@@ -5337,7 +5337,7 @@
       </c>
       <c r="S60" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T23:07:48Z</t>
+          <t>2026-09-17T17:37:55Z</t>
         </is>
       </c>
     </row>
@@ -5426,7 +5426,7 @@
       </c>
       <c r="S61" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T23:07:48Z</t>
+          <t>2026-09-17T17:37:55Z</t>
         </is>
       </c>
     </row>
@@ -5515,7 +5515,7 @@
       </c>
       <c r="S62" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T23:07:48Z</t>
+          <t>2026-09-17T17:37:55Z</t>
         </is>
       </c>
     </row>
@@ -5604,7 +5604,7 @@
       </c>
       <c r="S63" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T23:07:48Z</t>
+          <t>2026-09-17T17:37:55Z</t>
         </is>
       </c>
     </row>
@@ -5693,7 +5693,7 @@
       </c>
       <c r="S64" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T23:07:48Z</t>
+          <t>2026-09-17T17:37:55Z</t>
         </is>
       </c>
     </row>
@@ -5782,7 +5782,7 @@
       </c>
       <c r="S65" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T23:07:48Z</t>
+          <t>2026-09-17T17:37:55Z</t>
         </is>
       </c>
     </row>
@@ -5871,7 +5871,7 @@
       </c>
       <c r="S66" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T23:07:48Z</t>
+          <t>2026-09-17T17:37:55Z</t>
         </is>
       </c>
     </row>
@@ -5960,7 +5960,7 @@
       </c>
       <c r="S67" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T23:07:48Z</t>
+          <t>2026-09-17T17:37:55Z</t>
         </is>
       </c>
     </row>
@@ -6045,7 +6045,7 @@
       </c>
       <c r="S68" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T23:07:48Z</t>
+          <t>2026-09-17T17:37:55Z</t>
         </is>
       </c>
     </row>
@@ -6130,7 +6130,7 @@
       </c>
       <c r="S69" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T23:07:48Z</t>
+          <t>2026-09-17T17:37:55Z</t>
         </is>
       </c>
     </row>
@@ -6215,7 +6215,7 @@
       </c>
       <c r="S70" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T23:07:48Z</t>
+          <t>2026-09-17T17:37:55Z</t>
         </is>
       </c>
     </row>
@@ -6300,7 +6300,7 @@
       </c>
       <c r="S71" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T23:07:48Z</t>
+          <t>2026-09-17T17:37:55Z</t>
         </is>
       </c>
     </row>
@@ -6385,7 +6385,7 @@
       </c>
       <c r="S72" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T23:07:48Z</t>
+          <t>2026-09-17T17:37:55Z</t>
         </is>
       </c>
     </row>
@@ -6470,7 +6470,7 @@
       </c>
       <c r="S73" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T23:07:48Z</t>
+          <t>2026-09-17T17:37:55Z</t>
         </is>
       </c>
     </row>
@@ -6555,7 +6555,7 @@
       </c>
       <c r="S74" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T23:07:48Z</t>
+          <t>2026-09-17T17:37:55Z</t>
         </is>
       </c>
     </row>
@@ -6640,7 +6640,7 @@
       </c>
       <c r="S75" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T23:07:48Z</t>
+          <t>2026-09-17T17:37:55Z</t>
         </is>
       </c>
     </row>
@@ -6725,7 +6725,7 @@
       </c>
       <c r="S76" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T23:07:48Z</t>
+          <t>2026-09-17T17:37:55Z</t>
         </is>
       </c>
     </row>
@@ -6810,7 +6810,7 @@
       </c>
       <c r="S77" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T23:07:48Z</t>
+          <t>2026-09-17T17:37:55Z</t>
         </is>
       </c>
     </row>
@@ -6895,7 +6895,7 @@
       </c>
       <c r="S78" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T23:07:48Z</t>
+          <t>2026-09-17T17:37:55Z</t>
         </is>
       </c>
     </row>
@@ -6980,7 +6980,7 @@
       </c>
       <c r="S79" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T23:07:48Z</t>
+          <t>2026-09-17T17:37:55Z</t>
         </is>
       </c>
     </row>
@@ -7065,7 +7065,7 @@
       </c>
       <c r="S80" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T23:07:48Z</t>
+          <t>2026-09-17T17:37:55Z</t>
         </is>
       </c>
     </row>
@@ -7150,7 +7150,7 @@
       </c>
       <c r="S81" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T23:07:48Z</t>
+          <t>2026-09-17T17:37:55Z</t>
         </is>
       </c>
     </row>
@@ -7235,7 +7235,7 @@
       </c>
       <c r="S82" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T23:07:48Z</t>
+          <t>2026-09-17T17:37:55Z</t>
         </is>
       </c>
     </row>
@@ -7320,7 +7320,7 @@
       </c>
       <c r="S83" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T23:07:48Z</t>
+          <t>2026-09-17T17:37:55Z</t>
         </is>
       </c>
     </row>
@@ -7405,7 +7405,7 @@
       </c>
       <c r="S84" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T23:07:48Z</t>
+          <t>2026-09-17T17:37:55Z</t>
         </is>
       </c>
     </row>
@@ -7490,7 +7490,7 @@
       </c>
       <c r="S85" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T23:07:48Z</t>
+          <t>2026-09-17T17:37:55Z</t>
         </is>
       </c>
     </row>
@@ -7575,7 +7575,7 @@
       </c>
       <c r="S86" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T23:07:48Z</t>
+          <t>2026-09-17T17:37:55Z</t>
         </is>
       </c>
     </row>
@@ -7660,7 +7660,7 @@
       </c>
       <c r="S87" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T23:07:48Z</t>
+          <t>2026-09-17T17:37:55Z</t>
         </is>
       </c>
     </row>
@@ -7745,7 +7745,7 @@
       </c>
       <c r="S88" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T23:07:48Z</t>
+          <t>2026-09-17T17:37:55Z</t>
         </is>
       </c>
     </row>
@@ -7834,7 +7834,7 @@
       </c>
       <c r="S89" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T23:07:48Z</t>
+          <t>2026-09-17T17:37:55Z</t>
         </is>
       </c>
     </row>
@@ -7923,7 +7923,7 @@
       </c>
       <c r="S90" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T23:07:48Z</t>
+          <t>2026-09-17T17:37:55Z</t>
         </is>
       </c>
     </row>
@@ -8008,7 +8008,7 @@
       </c>
       <c r="S91" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T23:07:48Z</t>
+          <t>2026-09-17T17:37:55Z</t>
         </is>
       </c>
     </row>
@@ -8097,7 +8097,7 @@
       </c>
       <c r="S92" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T23:07:48Z</t>
+          <t>2026-09-17T17:37:55Z</t>
         </is>
       </c>
     </row>
@@ -8186,7 +8186,7 @@
       </c>
       <c r="S93" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T23:07:48Z</t>
+          <t>2026-09-17T17:37:55Z</t>
         </is>
       </c>
     </row>
@@ -8271,7 +8271,7 @@
       </c>
       <c r="S94" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T23:07:48Z</t>
+          <t>2026-09-17T17:37:55Z</t>
         </is>
       </c>
     </row>
@@ -8360,7 +8360,7 @@
       </c>
       <c r="S95" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T23:07:48Z</t>
+          <t>2026-09-17T17:37:55Z</t>
         </is>
       </c>
     </row>
@@ -8449,7 +8449,7 @@
       </c>
       <c r="S96" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T23:07:48Z</t>
+          <t>2026-09-17T17:37:55Z</t>
         </is>
       </c>
     </row>
@@ -8534,7 +8534,7 @@
       </c>
       <c r="S97" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T23:07:48Z</t>
+          <t>2026-09-17T17:37:55Z</t>
         </is>
       </c>
     </row>
@@ -8623,7 +8623,7 @@
       </c>
       <c r="S98" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T23:07:48Z</t>
+          <t>2026-09-17T17:37:55Z</t>
         </is>
       </c>
     </row>
@@ -8712,7 +8712,7 @@
       </c>
       <c r="S99" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T23:07:48Z</t>
+          <t>2026-09-17T17:37:55Z</t>
         </is>
       </c>
     </row>
@@ -8797,7 +8797,7 @@
       </c>
       <c r="S100" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T23:07:48Z</t>
+          <t>2026-09-17T17:37:55Z</t>
         </is>
       </c>
     </row>
@@ -8886,7 +8886,7 @@
       </c>
       <c r="S101" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T23:07:48Z</t>
+          <t>2026-09-17T17:37:55Z</t>
         </is>
       </c>
     </row>
@@ -8975,7 +8975,7 @@
       </c>
       <c r="S102" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T23:07:48Z</t>
+          <t>2026-09-17T17:37:55Z</t>
         </is>
       </c>
     </row>
@@ -9060,7 +9060,7 @@
       </c>
       <c r="S103" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T23:07:48Z</t>
+          <t>2026-09-17T17:37:55Z</t>
         </is>
       </c>
     </row>
@@ -9149,7 +9149,7 @@
       </c>
       <c r="S104" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T23:07:48Z</t>
+          <t>2026-09-17T17:37:55Z</t>
         </is>
       </c>
     </row>
@@ -9238,7 +9238,7 @@
       </c>
       <c r="S105" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T23:07:48Z</t>
+          <t>2026-09-17T17:37:55Z</t>
         </is>
       </c>
     </row>
@@ -9323,7 +9323,7 @@
       </c>
       <c r="S106" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T23:07:48Z</t>
+          <t>2026-09-17T17:37:55Z</t>
         </is>
       </c>
     </row>
@@ -9412,7 +9412,7 @@
       </c>
       <c r="S107" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T23:07:48Z</t>
+          <t>2026-09-17T17:37:55Z</t>
         </is>
       </c>
     </row>
@@ -9501,7 +9501,7 @@
       </c>
       <c r="S108" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T23:07:48Z</t>
+          <t>2026-09-17T17:37:55Z</t>
         </is>
       </c>
     </row>
@@ -9586,7 +9586,7 @@
       </c>
       <c r="S109" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T23:07:48Z</t>
+          <t>2026-09-17T17:37:55Z</t>
         </is>
       </c>
     </row>
@@ -9675,7 +9675,7 @@
       </c>
       <c r="S110" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T23:07:48Z</t>
+          <t>2026-09-17T17:37:55Z</t>
         </is>
       </c>
     </row>
@@ -9764,7 +9764,7 @@
       </c>
       <c r="S111" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T23:07:48Z</t>
+          <t>2026-09-17T17:37:55Z</t>
         </is>
       </c>
     </row>
@@ -9849,7 +9849,7 @@
       </c>
       <c r="S112" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T23:07:48Z</t>
+          <t>2026-09-17T17:37:55Z</t>
         </is>
       </c>
     </row>
@@ -9938,7 +9938,7 @@
       </c>
       <c r="S113" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T23:07:48Z</t>
+          <t>2026-09-17T17:37:55Z</t>
         </is>
       </c>
     </row>
@@ -10027,7 +10027,7 @@
       </c>
       <c r="S114" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T23:07:48Z</t>
+          <t>2026-09-17T17:37:55Z</t>
         </is>
       </c>
     </row>
@@ -10112,7 +10112,7 @@
       </c>
       <c r="S115" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T23:07:48Z</t>
+          <t>2026-09-17T17:37:55Z</t>
         </is>
       </c>
     </row>
@@ -10201,7 +10201,7 @@
       </c>
       <c r="S116" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T23:07:48Z</t>
+          <t>2026-09-17T17:37:55Z</t>
         </is>
       </c>
     </row>
@@ -10290,7 +10290,7 @@
       </c>
       <c r="S117" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T23:07:48Z</t>
+          <t>2026-09-17T17:37:55Z</t>
         </is>
       </c>
     </row>
@@ -10379,7 +10379,7 @@
       </c>
       <c r="S118" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T23:07:48Z</t>
+          <t>2026-09-17T17:37:55Z</t>
         </is>
       </c>
     </row>
@@ -10468,7 +10468,7 @@
       </c>
       <c r="S119" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T23:07:48Z</t>
+          <t>2026-09-17T17:37:55Z</t>
         </is>
       </c>
     </row>
@@ -10557,7 +10557,7 @@
       </c>
       <c r="S120" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T23:07:48Z</t>
+          <t>2026-09-17T17:37:55Z</t>
         </is>
       </c>
     </row>
@@ -10646,7 +10646,7 @@
       </c>
       <c r="S121" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T23:07:48Z</t>
+          <t>2026-09-17T17:37:55Z</t>
         </is>
       </c>
     </row>
@@ -10735,7 +10735,7 @@
       </c>
       <c r="S122" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T23:07:48Z</t>
+          <t>2026-09-17T17:37:55Z</t>
         </is>
       </c>
     </row>
@@ -10824,7 +10824,7 @@
       </c>
       <c r="S123" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T23:07:48Z</t>
+          <t>2026-09-17T17:37:55Z</t>
         </is>
       </c>
     </row>
@@ -10913,7 +10913,7 @@
       </c>
       <c r="S124" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T23:07:48Z</t>
+          <t>2026-09-17T17:37:55Z</t>
         </is>
       </c>
     </row>
@@ -11002,7 +11002,7 @@
       </c>
       <c r="S125" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T23:07:48Z</t>
+          <t>2026-09-17T17:37:55Z</t>
         </is>
       </c>
     </row>
@@ -11091,7 +11091,7 @@
       </c>
       <c r="S126" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T23:07:48Z</t>
+          <t>2026-09-17T17:37:55Z</t>
         </is>
       </c>
     </row>
@@ -11180,7 +11180,7 @@
       </c>
       <c r="S127" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T23:07:48Z</t>
+          <t>2026-09-17T17:37:55Z</t>
         </is>
       </c>
     </row>
@@ -11269,7 +11269,7 @@
       </c>
       <c r="S128" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T23:07:48Z</t>
+          <t>2026-09-17T17:37:55Z</t>
         </is>
       </c>
     </row>
@@ -11354,7 +11354,7 @@
       </c>
       <c r="S129" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T23:07:48Z</t>
+          <t>2026-09-17T17:37:55Z</t>
         </is>
       </c>
     </row>
@@ -11439,7 +11439,7 @@
       </c>
       <c r="S130" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T23:07:48Z</t>
+          <t>2026-09-17T17:37:55Z</t>
         </is>
       </c>
     </row>
@@ -11524,7 +11524,7 @@
       </c>
       <c r="S131" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T23:07:48Z</t>
+          <t>2026-09-17T17:37:55Z</t>
         </is>
       </c>
     </row>
@@ -11609,7 +11609,7 @@
       </c>
       <c r="S132" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T23:07:48Z</t>
+          <t>2026-09-17T17:37:55Z</t>
         </is>
       </c>
     </row>
@@ -11694,7 +11694,7 @@
       </c>
       <c r="S133" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T23:07:48Z</t>
+          <t>2026-09-17T17:37:55Z</t>
         </is>
       </c>
     </row>
@@ -11779,7 +11779,7 @@
       </c>
       <c r="S134" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T23:07:48Z</t>
+          <t>2026-09-17T17:37:55Z</t>
         </is>
       </c>
     </row>
@@ -11864,7 +11864,7 @@
       </c>
       <c r="S135" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T23:07:48Z</t>
+          <t>2026-09-17T17:37:55Z</t>
         </is>
       </c>
     </row>
@@ -11949,7 +11949,7 @@
       </c>
       <c r="S136" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T23:07:48Z</t>
+          <t>2026-09-17T17:37:55Z</t>
         </is>
       </c>
     </row>
@@ -12034,7 +12034,7 @@
       </c>
       <c r="S137" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T23:07:48Z</t>
+          <t>2026-09-17T17:37:55Z</t>
         </is>
       </c>
     </row>
@@ -12119,7 +12119,7 @@
       </c>
       <c r="S138" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T23:07:48Z</t>
+          <t>2026-09-17T17:37:55Z</t>
         </is>
       </c>
     </row>
@@ -12204,7 +12204,7 @@
       </c>
       <c r="S139" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T23:07:48Z</t>
+          <t>2026-09-17T17:37:55Z</t>
         </is>
       </c>
     </row>
@@ -12289,7 +12289,7 @@
       </c>
       <c r="S140" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T23:07:48Z</t>
+          <t>2026-09-17T17:37:55Z</t>
         </is>
       </c>
     </row>
@@ -12374,7 +12374,7 @@
       </c>
       <c r="S141" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T23:07:48Z</t>
+          <t>2026-09-17T17:37:55Z</t>
         </is>
       </c>
     </row>
@@ -12459,7 +12459,7 @@
       </c>
       <c r="S142" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T23:07:48Z</t>
+          <t>2026-09-17T17:37:55Z</t>
         </is>
       </c>
     </row>
@@ -12544,7 +12544,7 @@
       </c>
       <c r="S143" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T23:07:48Z</t>
+          <t>2026-09-17T17:37:55Z</t>
         </is>
       </c>
     </row>
@@ -12629,7 +12629,7 @@
       </c>
       <c r="S144" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T23:07:48Z</t>
+          <t>2026-09-17T17:37:55Z</t>
         </is>
       </c>
     </row>
@@ -12714,7 +12714,7 @@
       </c>
       <c r="S145" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T23:07:48Z</t>
+          <t>2026-09-17T17:37:55Z</t>
         </is>
       </c>
     </row>
@@ -12799,7 +12799,7 @@
       </c>
       <c r="S146" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T23:07:48Z</t>
+          <t>2026-09-17T17:37:55Z</t>
         </is>
       </c>
     </row>
@@ -12884,7 +12884,7 @@
       </c>
       <c r="S147" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T23:07:48Z</t>
+          <t>2026-09-17T17:37:55Z</t>
         </is>
       </c>
     </row>
@@ -12969,7 +12969,7 @@
       </c>
       <c r="S148" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T23:07:48Z</t>
+          <t>2026-09-17T17:37:55Z</t>
         </is>
       </c>
     </row>
@@ -13054,7 +13054,7 @@
       </c>
       <c r="S149" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T23:07:48Z</t>
+          <t>2026-09-17T17:37:55Z</t>
         </is>
       </c>
     </row>
@@ -13143,7 +13143,7 @@
       </c>
       <c r="S150" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T23:07:48Z</t>
+          <t>2026-09-17T17:37:55Z</t>
         </is>
       </c>
     </row>
@@ -13232,7 +13232,7 @@
       </c>
       <c r="S151" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T23:07:48Z</t>
+          <t>2026-09-17T17:37:55Z</t>
         </is>
       </c>
     </row>
@@ -13317,7 +13317,7 @@
       </c>
       <c r="S152" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T23:07:48Z</t>
+          <t>2026-09-17T17:37:55Z</t>
         </is>
       </c>
     </row>
@@ -13406,7 +13406,7 @@
       </c>
       <c r="S153" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T23:07:48Z</t>
+          <t>2026-09-17T17:37:55Z</t>
         </is>
       </c>
     </row>
@@ -13495,7 +13495,7 @@
       </c>
       <c r="S154" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T23:07:48Z</t>
+          <t>2026-09-17T17:37:55Z</t>
         </is>
       </c>
     </row>
@@ -13580,7 +13580,7 @@
       </c>
       <c r="S155" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T23:07:48Z</t>
+          <t>2026-09-17T17:37:55Z</t>
         </is>
       </c>
     </row>
@@ -13669,7 +13669,7 @@
       </c>
       <c r="S156" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T23:07:48Z</t>
+          <t>2026-09-17T17:37:55Z</t>
         </is>
       </c>
     </row>
@@ -13758,7 +13758,7 @@
       </c>
       <c r="S157" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T23:07:48Z</t>
+          <t>2026-09-17T17:37:55Z</t>
         </is>
       </c>
     </row>
@@ -13843,7 +13843,7 @@
       </c>
       <c r="S158" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T23:07:48Z</t>
+          <t>2026-09-17T17:37:55Z</t>
         </is>
       </c>
     </row>
@@ -13932,7 +13932,7 @@
       </c>
       <c r="S159" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T23:07:48Z</t>
+          <t>2026-09-17T17:37:55Z</t>
         </is>
       </c>
     </row>
@@ -14021,7 +14021,7 @@
       </c>
       <c r="S160" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T23:07:48Z</t>
+          <t>2026-09-17T17:37:55Z</t>
         </is>
       </c>
     </row>
@@ -14106,7 +14106,7 @@
       </c>
       <c r="S161" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T23:07:48Z</t>
+          <t>2026-09-17T17:37:55Z</t>
         </is>
       </c>
     </row>
@@ -14195,7 +14195,7 @@
       </c>
       <c r="S162" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T23:07:48Z</t>
+          <t>2026-09-17T17:37:55Z</t>
         </is>
       </c>
     </row>
@@ -14284,7 +14284,7 @@
       </c>
       <c r="S163" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T23:07:48Z</t>
+          <t>2026-09-17T17:37:55Z</t>
         </is>
       </c>
     </row>
@@ -14369,7 +14369,7 @@
       </c>
       <c r="S164" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T23:07:48Z</t>
+          <t>2026-09-17T17:37:55Z</t>
         </is>
       </c>
     </row>
@@ -14458,7 +14458,7 @@
       </c>
       <c r="S165" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T23:07:48Z</t>
+          <t>2026-09-17T17:37:55Z</t>
         </is>
       </c>
     </row>
@@ -14547,7 +14547,7 @@
       </c>
       <c r="S166" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T23:07:48Z</t>
+          <t>2026-09-17T17:37:55Z</t>
         </is>
       </c>
     </row>
@@ -14632,7 +14632,7 @@
       </c>
       <c r="S167" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T23:07:48Z</t>
+          <t>2026-09-17T17:37:55Z</t>
         </is>
       </c>
     </row>
@@ -14721,7 +14721,7 @@
       </c>
       <c r="S168" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T23:07:48Z</t>
+          <t>2026-09-17T17:37:55Z</t>
         </is>
       </c>
     </row>
@@ -14810,7 +14810,7 @@
       </c>
       <c r="S169" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T23:07:48Z</t>
+          <t>2026-09-17T17:37:55Z</t>
         </is>
       </c>
     </row>
@@ -14895,7 +14895,7 @@
       </c>
       <c r="S170" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T23:07:48Z</t>
+          <t>2026-09-17T17:37:55Z</t>
         </is>
       </c>
     </row>
@@ -14984,7 +14984,7 @@
       </c>
       <c r="S171" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T23:07:48Z</t>
+          <t>2026-09-17T17:37:55Z</t>
         </is>
       </c>
     </row>
@@ -15073,7 +15073,7 @@
       </c>
       <c r="S172" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T23:07:48Z</t>
+          <t>2026-09-17T17:37:55Z</t>
         </is>
       </c>
     </row>
@@ -15158,7 +15158,7 @@
       </c>
       <c r="S173" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T23:07:48Z</t>
+          <t>2026-09-17T17:37:55Z</t>
         </is>
       </c>
     </row>
@@ -15247,7 +15247,7 @@
       </c>
       <c r="S174" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T23:07:48Z</t>
+          <t>2026-09-17T17:37:55Z</t>
         </is>
       </c>
     </row>
@@ -15336,7 +15336,7 @@
       </c>
       <c r="S175" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T23:07:48Z</t>
+          <t>2026-09-17T17:37:55Z</t>
         </is>
       </c>
     </row>
@@ -15421,7 +15421,7 @@
       </c>
       <c r="S176" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T23:07:48Z</t>
+          <t>2026-09-17T17:37:55Z</t>
         </is>
       </c>
     </row>
@@ -15510,7 +15510,7 @@
       </c>
       <c r="S177" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T23:07:48Z</t>
+          <t>2026-09-17T17:37:55Z</t>
         </is>
       </c>
     </row>
@@ -15599,7 +15599,7 @@
       </c>
       <c r="S178" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T23:07:48Z</t>
+          <t>2026-09-17T17:37:55Z</t>
         </is>
       </c>
     </row>
@@ -15688,7 +15688,7 @@
       </c>
       <c r="S179" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T23:07:48Z</t>
+          <t>2026-09-17T17:37:55Z</t>
         </is>
       </c>
     </row>
@@ -15777,7 +15777,7 @@
       </c>
       <c r="S180" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T23:07:48Z</t>
+          <t>2026-09-17T17:37:55Z</t>
         </is>
       </c>
     </row>
@@ -15866,7 +15866,7 @@
       </c>
       <c r="S181" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T23:07:48Z</t>
+          <t>2026-09-17T17:37:55Z</t>
         </is>
       </c>
     </row>
@@ -15955,7 +15955,7 @@
       </c>
       <c r="S182" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T23:07:48Z</t>
+          <t>2026-09-17T17:37:55Z</t>
         </is>
       </c>
     </row>
@@ -16044,7 +16044,7 @@
       </c>
       <c r="S183" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T23:07:48Z</t>
+          <t>2026-09-17T17:37:55Z</t>
         </is>
       </c>
     </row>
@@ -16133,7 +16133,7 @@
       </c>
       <c r="S184" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T23:07:48Z</t>
+          <t>2026-09-17T17:37:55Z</t>
         </is>
       </c>
     </row>
@@ -16222,7 +16222,7 @@
       </c>
       <c r="S185" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T23:07:48Z</t>
+          <t>2026-09-17T17:37:55Z</t>
         </is>
       </c>
     </row>
@@ -16311,7 +16311,7 @@
       </c>
       <c r="S186" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T23:07:48Z</t>
+          <t>2026-09-17T17:37:55Z</t>
         </is>
       </c>
     </row>
@@ -16400,7 +16400,7 @@
       </c>
       <c r="S187" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T23:07:48Z</t>
+          <t>2026-09-17T17:37:55Z</t>
         </is>
       </c>
     </row>
@@ -16489,7 +16489,7 @@
       </c>
       <c r="S188" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T23:07:48Z</t>
+          <t>2026-09-17T17:37:55Z</t>
         </is>
       </c>
     </row>
@@ -16578,7 +16578,7 @@
       </c>
       <c r="S189" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T23:07:48Z</t>
+          <t>2026-09-17T17:37:55Z</t>
         </is>
       </c>
     </row>
@@ -16663,7 +16663,7 @@
       </c>
       <c r="S190" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T23:07:48Z</t>
+          <t>2026-09-17T17:37:55Z</t>
         </is>
       </c>
     </row>
@@ -16748,7 +16748,7 @@
       </c>
       <c r="S191" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T23:07:48Z</t>
+          <t>2026-09-17T17:37:55Z</t>
         </is>
       </c>
     </row>
@@ -16833,7 +16833,7 @@
       </c>
       <c r="S192" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T23:07:48Z</t>
+          <t>2026-09-17T17:37:55Z</t>
         </is>
       </c>
     </row>
@@ -16918,7 +16918,7 @@
       </c>
       <c r="S193" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T23:07:48Z</t>
+          <t>2026-09-17T17:37:55Z</t>
         </is>
       </c>
     </row>
@@ -17003,7 +17003,7 @@
       </c>
       <c r="S194" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T23:07:48Z</t>
+          <t>2026-09-17T17:37:55Z</t>
         </is>
       </c>
     </row>
@@ -17088,7 +17088,7 @@
       </c>
       <c r="S195" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T23:07:48Z</t>
+          <t>2026-09-17T17:37:55Z</t>
         </is>
       </c>
     </row>
@@ -17173,7 +17173,7 @@
       </c>
       <c r="S196" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T23:07:48Z</t>
+          <t>2026-09-17T17:37:55Z</t>
         </is>
       </c>
     </row>
@@ -17258,7 +17258,7 @@
       </c>
       <c r="S197" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T23:07:48Z</t>
+          <t>2026-09-17T17:37:55Z</t>
         </is>
       </c>
     </row>
@@ -17343,7 +17343,7 @@
       </c>
       <c r="S198" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T23:07:48Z</t>
+          <t>2026-09-17T17:37:55Z</t>
         </is>
       </c>
     </row>
@@ -17428,7 +17428,7 @@
       </c>
       <c r="S199" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T23:07:48Z</t>
+          <t>2026-09-17T17:37:55Z</t>
         </is>
       </c>
     </row>
@@ -17513,7 +17513,7 @@
       </c>
       <c r="S200" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T23:07:48Z</t>
+          <t>2026-09-17T17:37:55Z</t>
         </is>
       </c>
     </row>
@@ -17598,7 +17598,7 @@
       </c>
       <c r="S201" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T23:07:48Z</t>
+          <t>2026-09-17T17:37:55Z</t>
         </is>
       </c>
     </row>
@@ -17683,7 +17683,7 @@
       </c>
       <c r="S202" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T23:07:48Z</t>
+          <t>2026-09-17T17:37:55Z</t>
         </is>
       </c>
     </row>
@@ -17768,7 +17768,7 @@
       </c>
       <c r="S203" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T23:07:48Z</t>
+          <t>2026-09-17T17:37:55Z</t>
         </is>
       </c>
     </row>
@@ -17853,7 +17853,7 @@
       </c>
       <c r="S204" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T23:07:48Z</t>
+          <t>2026-09-17T17:37:55Z</t>
         </is>
       </c>
     </row>
@@ -17938,7 +17938,7 @@
       </c>
       <c r="S205" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T23:07:48Z</t>
+          <t>2026-09-17T17:37:55Z</t>
         </is>
       </c>
     </row>
@@ -18023,7 +18023,7 @@
       </c>
       <c r="S206" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T23:07:48Z</t>
+          <t>2026-09-17T17:37:55Z</t>
         </is>
       </c>
     </row>
@@ -18108,7 +18108,7 @@
       </c>
       <c r="S207" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T23:07:48Z</t>
+          <t>2026-09-17T17:37:55Z</t>
         </is>
       </c>
     </row>
@@ -18193,7 +18193,7 @@
       </c>
       <c r="S208" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T23:07:48Z</t>
+          <t>2026-09-17T17:37:55Z</t>
         </is>
       </c>
     </row>
@@ -18278,7 +18278,7 @@
       </c>
       <c r="S209" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T23:07:48Z</t>
+          <t>2026-09-17T17:37:55Z</t>
         </is>
       </c>
     </row>
@@ -18363,7 +18363,7 @@
       </c>
       <c r="S210" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T23:07:48Z</t>
+          <t>2026-09-17T17:37:55Z</t>
         </is>
       </c>
     </row>
@@ -18452,7 +18452,7 @@
       </c>
       <c r="S211" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T23:07:48Z</t>
+          <t>2026-09-17T17:37:55Z</t>
         </is>
       </c>
     </row>
@@ -18541,7 +18541,7 @@
       </c>
       <c r="S212" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T23:07:48Z</t>
+          <t>2026-09-17T17:37:55Z</t>
         </is>
       </c>
     </row>
@@ -18626,7 +18626,7 @@
       </c>
       <c r="S213" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T23:07:48Z</t>
+          <t>2026-09-17T17:37:55Z</t>
         </is>
       </c>
     </row>
@@ -18715,7 +18715,7 @@
       </c>
       <c r="S214" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T23:07:48Z</t>
+          <t>2026-09-17T17:37:55Z</t>
         </is>
       </c>
     </row>
@@ -18804,7 +18804,7 @@
       </c>
       <c r="S215" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T23:07:48Z</t>
+          <t>2026-09-17T17:37:55Z</t>
         </is>
       </c>
     </row>
@@ -18889,7 +18889,7 @@
       </c>
       <c r="S216" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T23:07:48Z</t>
+          <t>2026-09-17T17:37:55Z</t>
         </is>
       </c>
     </row>
@@ -18978,7 +18978,7 @@
       </c>
       <c r="S217" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T23:07:48Z</t>
+          <t>2026-09-17T17:37:55Z</t>
         </is>
       </c>
     </row>
@@ -19067,7 +19067,7 @@
       </c>
       <c r="S218" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T23:07:48Z</t>
+          <t>2026-09-17T17:37:55Z</t>
         </is>
       </c>
     </row>
@@ -19152,7 +19152,7 @@
       </c>
       <c r="S219" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T23:07:48Z</t>
+          <t>2026-09-17T17:37:55Z</t>
         </is>
       </c>
     </row>
@@ -19241,7 +19241,7 @@
       </c>
       <c r="S220" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T23:07:48Z</t>
+          <t>2026-09-17T17:37:55Z</t>
         </is>
       </c>
     </row>
@@ -19330,7 +19330,7 @@
       </c>
       <c r="S221" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T23:07:48Z</t>
+          <t>2026-09-17T17:37:55Z</t>
         </is>
       </c>
     </row>
@@ -19415,7 +19415,7 @@
       </c>
       <c r="S222" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T23:07:48Z</t>
+          <t>2026-09-17T17:37:55Z</t>
         </is>
       </c>
     </row>
@@ -19504,7 +19504,7 @@
       </c>
       <c r="S223" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T23:07:48Z</t>
+          <t>2026-09-17T17:37:55Z</t>
         </is>
       </c>
     </row>
@@ -19593,7 +19593,7 @@
       </c>
       <c r="S224" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T23:07:48Z</t>
+          <t>2026-09-17T17:37:55Z</t>
         </is>
       </c>
     </row>
@@ -19678,7 +19678,7 @@
       </c>
       <c r="S225" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T23:07:48Z</t>
+          <t>2026-09-17T17:37:55Z</t>
         </is>
       </c>
     </row>
@@ -19767,7 +19767,7 @@
       </c>
       <c r="S226" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T23:07:48Z</t>
+          <t>2026-09-17T17:37:55Z</t>
         </is>
       </c>
     </row>
@@ -19856,7 +19856,7 @@
       </c>
       <c r="S227" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T23:07:48Z</t>
+          <t>2026-09-17T17:37:55Z</t>
         </is>
       </c>
     </row>
@@ -19941,7 +19941,7 @@
       </c>
       <c r="S228" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T23:07:48Z</t>
+          <t>2026-09-17T17:37:55Z</t>
         </is>
       </c>
     </row>
@@ -20030,7 +20030,7 @@
       </c>
       <c r="S229" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T23:07:48Z</t>
+          <t>2026-09-17T17:37:55Z</t>
         </is>
       </c>
     </row>
@@ -20119,7 +20119,7 @@
       </c>
       <c r="S230" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T23:07:48Z</t>
+          <t>2026-09-17T17:37:55Z</t>
         </is>
       </c>
     </row>
@@ -20204,7 +20204,7 @@
       </c>
       <c r="S231" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T23:07:48Z</t>
+          <t>2026-09-17T17:37:55Z</t>
         </is>
       </c>
     </row>
@@ -20293,7 +20293,7 @@
       </c>
       <c r="S232" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T23:07:48Z</t>
+          <t>2026-09-17T17:37:55Z</t>
         </is>
       </c>
     </row>
@@ -20382,7 +20382,7 @@
       </c>
       <c r="S233" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T23:07:48Z</t>
+          <t>2026-09-17T17:37:55Z</t>
         </is>
       </c>
     </row>
@@ -20467,7 +20467,7 @@
       </c>
       <c r="S234" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T23:07:48Z</t>
+          <t>2026-09-17T17:37:55Z</t>
         </is>
       </c>
     </row>
@@ -20556,7 +20556,7 @@
       </c>
       <c r="S235" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T23:07:48Z</t>
+          <t>2026-09-17T17:37:55Z</t>
         </is>
       </c>
     </row>
@@ -20645,7 +20645,7 @@
       </c>
       <c r="S236" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T23:07:48Z</t>
+          <t>2026-09-17T17:37:55Z</t>
         </is>
       </c>
     </row>
@@ -20730,7 +20730,7 @@
       </c>
       <c r="S237" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T23:07:48Z</t>
+          <t>2026-09-17T17:37:55Z</t>
         </is>
       </c>
     </row>
@@ -20819,7 +20819,7 @@
       </c>
       <c r="S238" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T23:07:48Z</t>
+          <t>2026-09-17T17:37:55Z</t>
         </is>
       </c>
     </row>
@@ -20908,7 +20908,7 @@
       </c>
       <c r="S239" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T23:07:48Z</t>
+          <t>2026-09-17T17:37:55Z</t>
         </is>
       </c>
     </row>
@@ -20997,7 +20997,7 @@
       </c>
       <c r="S240" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T23:07:48Z</t>
+          <t>2026-09-17T17:37:55Z</t>
         </is>
       </c>
     </row>
@@ -21086,7 +21086,7 @@
       </c>
       <c r="S241" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T23:07:48Z</t>
+          <t>2026-09-17T17:37:55Z</t>
         </is>
       </c>
     </row>
@@ -21175,7 +21175,7 @@
       </c>
       <c r="S242" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T23:07:48Z</t>
+          <t>2026-09-17T17:37:55Z</t>
         </is>
       </c>
     </row>
@@ -21264,7 +21264,7 @@
       </c>
       <c r="S243" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T23:07:48Z</t>
+          <t>2026-09-17T17:37:55Z</t>
         </is>
       </c>
     </row>
@@ -21353,7 +21353,7 @@
       </c>
       <c r="S244" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T23:07:48Z</t>
+          <t>2026-09-17T17:37:55Z</t>
         </is>
       </c>
     </row>
@@ -21442,7 +21442,7 @@
       </c>
       <c r="S245" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T23:07:48Z</t>
+          <t>2026-09-17T17:37:55Z</t>
         </is>
       </c>
     </row>
@@ -21531,7 +21531,7 @@
       </c>
       <c r="S246" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T23:07:48Z</t>
+          <t>2026-09-17T17:37:55Z</t>
         </is>
       </c>
     </row>
@@ -21620,7 +21620,7 @@
       </c>
       <c r="S247" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T23:07:48Z</t>
+          <t>2026-09-17T17:37:55Z</t>
         </is>
       </c>
     </row>
@@ -21709,7 +21709,7 @@
       </c>
       <c r="S248" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T23:07:48Z</t>
+          <t>2026-09-17T17:37:55Z</t>
         </is>
       </c>
     </row>
@@ -21798,7 +21798,7 @@
       </c>
       <c r="S249" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T23:07:48Z</t>
+          <t>2026-09-17T17:37:55Z</t>
         </is>
       </c>
     </row>
@@ -21887,7 +21887,7 @@
       </c>
       <c r="S250" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T23:07:48Z</t>
+          <t>2026-09-17T17:37:55Z</t>
         </is>
       </c>
     </row>
@@ -22019,7 +22019,7 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T23:07:48Z</t>
+          <t>2026-09-17T17:37:55Z</t>
         </is>
       </c>
     </row>
@@ -22099,7 +22099,7 @@
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>{"dataset_id": "bcv_pib_sector_institucional_anual", "title": "Producto interno bruto por sector institucional anual", "table": "Variaciones porcentuales", "source_file": "5_2_1_si_anual.xlsx", "base": "2007", "price_type": "Precios constantes", "measure": "Variación porcentual interanual", "frequency": "Anual", "period": "2025", "year": 2025, "quarter": null, "classification": "Sector institucional", "component": "Impuestos netos sobre los productos", "value": 10.600260421283764, "unit": "Porcentaje", "status": "Preliminar", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/cuentas_macroeconomicas/5_2_1_si_anual.xlsx", "fetched_at": "2026-09-16T23:07:48Z"}</t>
+          <t>{"dataset_id": "bcv_pib_sector_institucional_anual", "title": "Producto interno bruto por sector institucional anual", "table": "Variaciones porcentuales", "source_file": "5_2_1_si_anual.xlsx", "base": "2007", "price_type": "Precios constantes", "measure": "Variación porcentual interanual", "frequency": "Anual", "period": "2025", "year": 2025, "quarter": null, "classification": "Sector institucional", "component": "Impuestos netos sobre los productos", "value": 10.600260421283764, "unit": "Porcentaje", "status": "Preliminar", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/cuentas_macroeconomicas/5_2_1_si_anual.xlsx", "fetched_at": "2026-09-17T17:37:55Z"}</t>
         </is>
       </c>
     </row>

--- a/assets/data/bcv/excel/ove_bcv_pib_sector_institucional_anual.xlsx
+++ b/assets/data/bcv/excel/ove_bcv_pib_sector_institucional_anual.xlsx
@@ -736,7 +736,7 @@
       </c>
       <c r="S7" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T17:37:55Z</t>
+          <t>2026-09-17T22:58:10Z</t>
         </is>
       </c>
     </row>
@@ -821,7 +821,7 @@
       </c>
       <c r="S8" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T17:37:55Z</t>
+          <t>2026-09-17T22:58:10Z</t>
         </is>
       </c>
     </row>
@@ -906,7 +906,7 @@
       </c>
       <c r="S9" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T17:37:55Z</t>
+          <t>2026-09-17T22:58:10Z</t>
         </is>
       </c>
     </row>
@@ -991,7 +991,7 @@
       </c>
       <c r="S10" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T17:37:55Z</t>
+          <t>2026-09-17T22:58:10Z</t>
         </is>
       </c>
     </row>
@@ -1076,7 +1076,7 @@
       </c>
       <c r="S11" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T17:37:55Z</t>
+          <t>2026-09-17T22:58:10Z</t>
         </is>
       </c>
     </row>
@@ -1161,7 +1161,7 @@
       </c>
       <c r="S12" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T17:37:55Z</t>
+          <t>2026-09-17T22:58:10Z</t>
         </is>
       </c>
     </row>
@@ -1246,7 +1246,7 @@
       </c>
       <c r="S13" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T17:37:55Z</t>
+          <t>2026-09-17T22:58:10Z</t>
         </is>
       </c>
     </row>
@@ -1331,7 +1331,7 @@
       </c>
       <c r="S14" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T17:37:55Z</t>
+          <t>2026-09-17T22:58:10Z</t>
         </is>
       </c>
     </row>
@@ -1416,7 +1416,7 @@
       </c>
       <c r="S15" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T17:37:55Z</t>
+          <t>2026-09-17T22:58:10Z</t>
         </is>
       </c>
     </row>
@@ -1501,7 +1501,7 @@
       </c>
       <c r="S16" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T17:37:55Z</t>
+          <t>2026-09-17T22:58:10Z</t>
         </is>
       </c>
     </row>
@@ -1586,7 +1586,7 @@
       </c>
       <c r="S17" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T17:37:55Z</t>
+          <t>2026-09-17T22:58:10Z</t>
         </is>
       </c>
     </row>
@@ -1671,7 +1671,7 @@
       </c>
       <c r="S18" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T17:37:55Z</t>
+          <t>2026-09-17T22:58:10Z</t>
         </is>
       </c>
     </row>
@@ -1756,7 +1756,7 @@
       </c>
       <c r="S19" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T17:37:55Z</t>
+          <t>2026-09-17T22:58:10Z</t>
         </is>
       </c>
     </row>
@@ -1841,7 +1841,7 @@
       </c>
       <c r="S20" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T17:37:55Z</t>
+          <t>2026-09-17T22:58:10Z</t>
         </is>
       </c>
     </row>
@@ -1926,7 +1926,7 @@
       </c>
       <c r="S21" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T17:37:55Z</t>
+          <t>2026-09-17T22:58:10Z</t>
         </is>
       </c>
     </row>
@@ -2011,7 +2011,7 @@
       </c>
       <c r="S22" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T17:37:55Z</t>
+          <t>2026-09-17T22:58:10Z</t>
         </is>
       </c>
     </row>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="S23" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T17:37:55Z</t>
+          <t>2026-09-17T22:58:10Z</t>
         </is>
       </c>
     </row>
@@ -2181,7 +2181,7 @@
       </c>
       <c r="S24" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T17:37:55Z</t>
+          <t>2026-09-17T22:58:10Z</t>
         </is>
       </c>
     </row>
@@ -2266,7 +2266,7 @@
       </c>
       <c r="S25" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T17:37:55Z</t>
+          <t>2026-09-17T22:58:10Z</t>
         </is>
       </c>
     </row>
@@ -2351,7 +2351,7 @@
       </c>
       <c r="S26" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T17:37:55Z</t>
+          <t>2026-09-17T22:58:10Z</t>
         </is>
       </c>
     </row>
@@ -2436,7 +2436,7 @@
       </c>
       <c r="S27" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T17:37:55Z</t>
+          <t>2026-09-17T22:58:10Z</t>
         </is>
       </c>
     </row>
@@ -2525,7 +2525,7 @@
       </c>
       <c r="S28" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T17:37:55Z</t>
+          <t>2026-09-17T22:58:10Z</t>
         </is>
       </c>
     </row>
@@ -2614,7 +2614,7 @@
       </c>
       <c r="S29" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T17:37:55Z</t>
+          <t>2026-09-17T22:58:10Z</t>
         </is>
       </c>
     </row>
@@ -2699,7 +2699,7 @@
       </c>
       <c r="S30" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T17:37:55Z</t>
+          <t>2026-09-17T22:58:10Z</t>
         </is>
       </c>
     </row>
@@ -2788,7 +2788,7 @@
       </c>
       <c r="S31" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T17:37:55Z</t>
+          <t>2026-09-17T22:58:10Z</t>
         </is>
       </c>
     </row>
@@ -2877,7 +2877,7 @@
       </c>
       <c r="S32" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T17:37:55Z</t>
+          <t>2026-09-17T22:58:10Z</t>
         </is>
       </c>
     </row>
@@ -2962,7 +2962,7 @@
       </c>
       <c r="S33" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T17:37:55Z</t>
+          <t>2026-09-17T22:58:10Z</t>
         </is>
       </c>
     </row>
@@ -3051,7 +3051,7 @@
       </c>
       <c r="S34" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T17:37:55Z</t>
+          <t>2026-09-17T22:58:10Z</t>
         </is>
       </c>
     </row>
@@ -3140,7 +3140,7 @@
       </c>
       <c r="S35" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T17:37:55Z</t>
+          <t>2026-09-17T22:58:10Z</t>
         </is>
       </c>
     </row>
@@ -3225,7 +3225,7 @@
       </c>
       <c r="S36" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T17:37:55Z</t>
+          <t>2026-09-17T22:58:10Z</t>
         </is>
       </c>
     </row>
@@ -3314,7 +3314,7 @@
       </c>
       <c r="S37" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T17:37:55Z</t>
+          <t>2026-09-17T22:58:10Z</t>
         </is>
       </c>
     </row>
@@ -3403,7 +3403,7 @@
       </c>
       <c r="S38" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T17:37:55Z</t>
+          <t>2026-09-17T22:58:10Z</t>
         </is>
       </c>
     </row>
@@ -3488,7 +3488,7 @@
       </c>
       <c r="S39" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T17:37:55Z</t>
+          <t>2026-09-17T22:58:10Z</t>
         </is>
       </c>
     </row>
@@ -3577,7 +3577,7 @@
       </c>
       <c r="S40" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T17:37:55Z</t>
+          <t>2026-09-17T22:58:10Z</t>
         </is>
       </c>
     </row>
@@ -3666,7 +3666,7 @@
       </c>
       <c r="S41" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T17:37:55Z</t>
+          <t>2026-09-17T22:58:10Z</t>
         </is>
       </c>
     </row>
@@ -3751,7 +3751,7 @@
       </c>
       <c r="S42" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T17:37:55Z</t>
+          <t>2026-09-17T22:58:10Z</t>
         </is>
       </c>
     </row>
@@ -3840,7 +3840,7 @@
       </c>
       <c r="S43" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T17:37:55Z</t>
+          <t>2026-09-17T22:58:10Z</t>
         </is>
       </c>
     </row>
@@ -3929,7 +3929,7 @@
       </c>
       <c r="S44" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T17:37:55Z</t>
+          <t>2026-09-17T22:58:10Z</t>
         </is>
       </c>
     </row>
@@ -4014,7 +4014,7 @@
       </c>
       <c r="S45" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T17:37:55Z</t>
+          <t>2026-09-17T22:58:10Z</t>
         </is>
       </c>
     </row>
@@ -4103,7 +4103,7 @@
       </c>
       <c r="S46" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T17:37:55Z</t>
+          <t>2026-09-17T22:58:10Z</t>
         </is>
       </c>
     </row>
@@ -4192,7 +4192,7 @@
       </c>
       <c r="S47" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T17:37:55Z</t>
+          <t>2026-09-17T22:58:10Z</t>
         </is>
       </c>
     </row>
@@ -4277,7 +4277,7 @@
       </c>
       <c r="S48" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T17:37:55Z</t>
+          <t>2026-09-17T22:58:10Z</t>
         </is>
       </c>
     </row>
@@ -4366,7 +4366,7 @@
       </c>
       <c r="S49" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T17:37:55Z</t>
+          <t>2026-09-17T22:58:10Z</t>
         </is>
       </c>
     </row>
@@ -4455,7 +4455,7 @@
       </c>
       <c r="S50" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T17:37:55Z</t>
+          <t>2026-09-17T22:58:10Z</t>
         </is>
       </c>
     </row>
@@ -4540,7 +4540,7 @@
       </c>
       <c r="S51" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T17:37:55Z</t>
+          <t>2026-09-17T22:58:10Z</t>
         </is>
       </c>
     </row>
@@ -4629,7 +4629,7 @@
       </c>
       <c r="S52" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T17:37:55Z</t>
+          <t>2026-09-17T22:58:10Z</t>
         </is>
       </c>
     </row>
@@ -4718,7 +4718,7 @@
       </c>
       <c r="S53" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T17:37:55Z</t>
+          <t>2026-09-17T22:58:10Z</t>
         </is>
       </c>
     </row>
@@ -4803,7 +4803,7 @@
       </c>
       <c r="S54" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T17:37:55Z</t>
+          <t>2026-09-17T22:58:10Z</t>
         </is>
       </c>
     </row>
@@ -4892,7 +4892,7 @@
       </c>
       <c r="S55" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T17:37:55Z</t>
+          <t>2026-09-17T22:58:10Z</t>
         </is>
       </c>
     </row>
@@ -4981,7 +4981,7 @@
       </c>
       <c r="S56" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T17:37:55Z</t>
+          <t>2026-09-17T22:58:10Z</t>
         </is>
       </c>
     </row>
@@ -5070,7 +5070,7 @@
       </c>
       <c r="S57" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T17:37:55Z</t>
+          <t>2026-09-17T22:58:10Z</t>
         </is>
       </c>
     </row>
@@ -5159,7 +5159,7 @@
       </c>
       <c r="S58" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T17:37:55Z</t>
+          <t>2026-09-17T22:58:10Z</t>
         </is>
       </c>
     </row>
@@ -5248,7 +5248,7 @@
       </c>
       <c r="S59" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T17:37:55Z</t>
+          <t>2026-09-17T22:58:10Z</t>
         </is>
       </c>
     </row>
@@ -5337,7 +5337,7 @@
       </c>
       <c r="S60" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T17:37:55Z</t>
+          <t>2026-09-17T22:58:10Z</t>
         </is>
       </c>
     </row>
@@ -5426,7 +5426,7 @@
       </c>
       <c r="S61" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T17:37:55Z</t>
+          <t>2026-09-17T22:58:10Z</t>
         </is>
       </c>
     </row>
@@ -5515,7 +5515,7 @@
       </c>
       <c r="S62" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T17:37:55Z</t>
+          <t>2026-09-17T22:58:10Z</t>
         </is>
       </c>
     </row>
@@ -5604,7 +5604,7 @@
       </c>
       <c r="S63" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T17:37:55Z</t>
+          <t>2026-09-17T22:58:10Z</t>
         </is>
       </c>
     </row>
@@ -5693,7 +5693,7 @@
       </c>
       <c r="S64" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T17:37:55Z</t>
+          <t>2026-09-17T22:58:10Z</t>
         </is>
       </c>
     </row>
@@ -5782,7 +5782,7 @@
       </c>
       <c r="S65" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T17:37:55Z</t>
+          <t>2026-09-17T22:58:10Z</t>
         </is>
       </c>
     </row>
@@ -5871,7 +5871,7 @@
       </c>
       <c r="S66" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T17:37:55Z</t>
+          <t>2026-09-17T22:58:10Z</t>
         </is>
       </c>
     </row>
@@ -5960,7 +5960,7 @@
       </c>
       <c r="S67" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T17:37:55Z</t>
+          <t>2026-09-17T22:58:10Z</t>
         </is>
       </c>
     </row>
@@ -6045,7 +6045,7 @@
       </c>
       <c r="S68" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T17:37:55Z</t>
+          <t>2026-09-17T22:58:10Z</t>
         </is>
       </c>
     </row>
@@ -6130,7 +6130,7 @@
       </c>
       <c r="S69" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T17:37:55Z</t>
+          <t>2026-09-17T22:58:10Z</t>
         </is>
       </c>
     </row>
@@ -6215,7 +6215,7 @@
       </c>
       <c r="S70" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T17:37:55Z</t>
+          <t>2026-09-17T22:58:10Z</t>
         </is>
       </c>
     </row>
@@ -6300,7 +6300,7 @@
       </c>
       <c r="S71" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T17:37:55Z</t>
+          <t>2026-09-17T22:58:10Z</t>
         </is>
       </c>
     </row>
@@ -6385,7 +6385,7 @@
       </c>
       <c r="S72" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T17:37:55Z</t>
+          <t>2026-09-17T22:58:10Z</t>
         </is>
       </c>
     </row>
@@ -6470,7 +6470,7 @@
       </c>
       <c r="S73" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T17:37:55Z</t>
+          <t>2026-09-17T22:58:10Z</t>
         </is>
       </c>
     </row>
@@ -6555,7 +6555,7 @@
       </c>
       <c r="S74" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T17:37:55Z</t>
+          <t>2026-09-17T22:58:10Z</t>
         </is>
       </c>
     </row>
@@ -6640,7 +6640,7 @@
       </c>
       <c r="S75" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T17:37:55Z</t>
+          <t>2026-09-17T22:58:10Z</t>
         </is>
       </c>
     </row>
@@ -6725,7 +6725,7 @@
       </c>
       <c r="S76" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T17:37:55Z</t>
+          <t>2026-09-17T22:58:10Z</t>
         </is>
       </c>
     </row>
@@ -6810,7 +6810,7 @@
       </c>
       <c r="S77" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T17:37:55Z</t>
+          <t>2026-09-17T22:58:10Z</t>
         </is>
       </c>
     </row>
@@ -6895,7 +6895,7 @@
       </c>
       <c r="S78" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T17:37:55Z</t>
+          <t>2026-09-17T22:58:10Z</t>
         </is>
       </c>
     </row>
@@ -6980,7 +6980,7 @@
       </c>
       <c r="S79" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T17:37:55Z</t>
+          <t>2026-09-17T22:58:10Z</t>
         </is>
       </c>
     </row>
@@ -7065,7 +7065,7 @@
       </c>
       <c r="S80" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T17:37:55Z</t>
+          <t>2026-09-17T22:58:10Z</t>
         </is>
       </c>
     </row>
@@ -7150,7 +7150,7 @@
       </c>
       <c r="S81" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T17:37:55Z</t>
+          <t>2026-09-17T22:58:10Z</t>
         </is>
       </c>
     </row>
@@ -7235,7 +7235,7 @@
       </c>
       <c r="S82" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T17:37:55Z</t>
+          <t>2026-09-17T22:58:10Z</t>
         </is>
       </c>
     </row>
@@ -7320,7 +7320,7 @@
       </c>
       <c r="S83" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T17:37:55Z</t>
+          <t>2026-09-17T22:58:10Z</t>
         </is>
       </c>
     </row>
@@ -7405,7 +7405,7 @@
       </c>
       <c r="S84" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T17:37:55Z</t>
+          <t>2026-09-17T22:58:10Z</t>
         </is>
       </c>
     </row>
@@ -7490,7 +7490,7 @@
       </c>
       <c r="S85" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T17:37:55Z</t>
+          <t>2026-09-17T22:58:10Z</t>
         </is>
       </c>
     </row>
@@ -7575,7 +7575,7 @@
       </c>
       <c r="S86" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T17:37:55Z</t>
+          <t>2026-09-17T22:58:10Z</t>
         </is>
       </c>
     </row>
@@ -7660,7 +7660,7 @@
       </c>
       <c r="S87" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T17:37:55Z</t>
+          <t>2026-09-17T22:58:10Z</t>
         </is>
       </c>
     </row>
@@ -7745,7 +7745,7 @@
       </c>
       <c r="S88" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T17:37:55Z</t>
+          <t>2026-09-17T22:58:10Z</t>
         </is>
       </c>
     </row>
@@ -7834,7 +7834,7 @@
       </c>
       <c r="S89" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T17:37:55Z</t>
+          <t>2026-09-17T22:58:10Z</t>
         </is>
       </c>
     </row>
@@ -7923,7 +7923,7 @@
       </c>
       <c r="S90" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T17:37:55Z</t>
+          <t>2026-09-17T22:58:10Z</t>
         </is>
       </c>
     </row>
@@ -8008,7 +8008,7 @@
       </c>
       <c r="S91" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T17:37:55Z</t>
+          <t>2026-09-17T22:58:10Z</t>
         </is>
       </c>
     </row>
@@ -8097,7 +8097,7 @@
       </c>
       <c r="S92" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T17:37:55Z</t>
+          <t>2026-09-17T22:58:10Z</t>
         </is>
       </c>
     </row>
@@ -8186,7 +8186,7 @@
       </c>
       <c r="S93" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T17:37:55Z</t>
+          <t>2026-09-17T22:58:10Z</t>
         </is>
       </c>
     </row>
@@ -8271,7 +8271,7 @@
       </c>
       <c r="S94" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T17:37:55Z</t>
+          <t>2026-09-17T22:58:10Z</t>
         </is>
       </c>
     </row>
@@ -8360,7 +8360,7 @@
       </c>
       <c r="S95" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T17:37:55Z</t>
+          <t>2026-09-17T22:58:10Z</t>
         </is>
       </c>
     </row>
@@ -8449,7 +8449,7 @@
       </c>
       <c r="S96" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T17:37:55Z</t>
+          <t>2026-09-17T22:58:10Z</t>
         </is>
       </c>
     </row>
@@ -8534,7 +8534,7 @@
       </c>
       <c r="S97" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T17:37:55Z</t>
+          <t>2026-09-17T22:58:10Z</t>
         </is>
       </c>
     </row>
@@ -8623,7 +8623,7 @@
       </c>
       <c r="S98" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T17:37:55Z</t>
+          <t>2026-09-17T22:58:10Z</t>
         </is>
       </c>
     </row>
@@ -8712,7 +8712,7 @@
       </c>
       <c r="S99" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T17:37:55Z</t>
+          <t>2026-09-17T22:58:10Z</t>
         </is>
       </c>
     </row>
@@ -8797,7 +8797,7 @@
       </c>
       <c r="S100" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T17:37:55Z</t>
+          <t>2026-09-17T22:58:10Z</t>
         </is>
       </c>
     </row>
@@ -8886,7 +8886,7 @@
       </c>
       <c r="S101" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T17:37:55Z</t>
+          <t>2026-09-17T22:58:10Z</t>
         </is>
       </c>
     </row>
@@ -8975,7 +8975,7 @@
       </c>
       <c r="S102" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T17:37:55Z</t>
+          <t>2026-09-17T22:58:10Z</t>
         </is>
       </c>
     </row>
@@ -9060,7 +9060,7 @@
       </c>
       <c r="S103" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T17:37:55Z</t>
+          <t>2026-09-17T22:58:10Z</t>
         </is>
       </c>
     </row>
@@ -9149,7 +9149,7 @@
       </c>
       <c r="S104" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T17:37:55Z</t>
+          <t>2026-09-17T22:58:10Z</t>
         </is>
       </c>
     </row>
@@ -9238,7 +9238,7 @@
       </c>
       <c r="S105" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T17:37:55Z</t>
+          <t>2026-09-17T22:58:10Z</t>
         </is>
       </c>
     </row>
@@ -9323,7 +9323,7 @@
       </c>
       <c r="S106" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T17:37:55Z</t>
+          <t>2026-09-17T22:58:10Z</t>
         </is>
       </c>
     </row>
@@ -9412,7 +9412,7 @@
       </c>
       <c r="S107" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T17:37:55Z</t>
+          <t>2026-09-17T22:58:10Z</t>
         </is>
       </c>
     </row>
@@ -9501,7 +9501,7 @@
       </c>
       <c r="S108" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T17:37:55Z</t>
+          <t>2026-09-17T22:58:10Z</t>
         </is>
       </c>
     </row>
@@ -9586,7 +9586,7 @@
       </c>
       <c r="S109" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T17:37:55Z</t>
+          <t>2026-09-17T22:58:10Z</t>
         </is>
       </c>
     </row>
@@ -9675,7 +9675,7 @@
       </c>
       <c r="S110" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T17:37:55Z</t>
+          <t>2026-09-17T22:58:10Z</t>
         </is>
       </c>
     </row>
@@ -9764,7 +9764,7 @@
       </c>
       <c r="S111" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T17:37:55Z</t>
+          <t>2026-09-17T22:58:10Z</t>
         </is>
       </c>
     </row>
@@ -9849,7 +9849,7 @@
       </c>
       <c r="S112" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T17:37:55Z</t>
+          <t>2026-09-17T22:58:10Z</t>
         </is>
       </c>
     </row>
@@ -9938,7 +9938,7 @@
       </c>
       <c r="S113" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T17:37:55Z</t>
+          <t>2026-09-17T22:58:10Z</t>
         </is>
       </c>
     </row>
@@ -10027,7 +10027,7 @@
       </c>
       <c r="S114" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T17:37:55Z</t>
+          <t>2026-09-17T22:58:10Z</t>
         </is>
       </c>
     </row>
@@ -10112,7 +10112,7 @@
       </c>
       <c r="S115" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T17:37:55Z</t>
+          <t>2026-09-17T22:58:10Z</t>
         </is>
       </c>
     </row>
@@ -10201,7 +10201,7 @@
       </c>
       <c r="S116" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T17:37:55Z</t>
+          <t>2026-09-17T22:58:10Z</t>
         </is>
       </c>
     </row>
@@ -10290,7 +10290,7 @@
       </c>
       <c r="S117" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T17:37:55Z</t>
+          <t>2026-09-17T22:58:10Z</t>
         </is>
       </c>
     </row>
@@ -10379,7 +10379,7 @@
       </c>
       <c r="S118" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T17:37:55Z</t>
+          <t>2026-09-17T22:58:10Z</t>
         </is>
       </c>
     </row>
@@ -10468,7 +10468,7 @@
       </c>
       <c r="S119" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T17:37:55Z</t>
+          <t>2026-09-17T22:58:10Z</t>
         </is>
       </c>
     </row>
@@ -10557,7 +10557,7 @@
       </c>
       <c r="S120" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T17:37:55Z</t>
+          <t>2026-09-17T22:58:10Z</t>
         </is>
       </c>
     </row>
@@ -10646,7 +10646,7 @@
       </c>
       <c r="S121" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T17:37:55Z</t>
+          <t>2026-09-17T22:58:10Z</t>
         </is>
       </c>
     </row>
@@ -10735,7 +10735,7 @@
       </c>
       <c r="S122" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T17:37:55Z</t>
+          <t>2026-09-17T22:58:10Z</t>
         </is>
       </c>
     </row>
@@ -10824,7 +10824,7 @@
       </c>
       <c r="S123" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T17:37:55Z</t>
+          <t>2026-09-17T22:58:10Z</t>
         </is>
       </c>
     </row>
@@ -10913,7 +10913,7 @@
       </c>
       <c r="S124" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T17:37:55Z</t>
+          <t>2026-09-17T22:58:10Z</t>
         </is>
       </c>
     </row>
@@ -11002,7 +11002,7 @@
       </c>
       <c r="S125" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T17:37:55Z</t>
+          <t>2026-09-17T22:58:10Z</t>
         </is>
       </c>
     </row>
@@ -11091,7 +11091,7 @@
       </c>
       <c r="S126" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T17:37:55Z</t>
+          <t>2026-09-17T22:58:10Z</t>
         </is>
       </c>
     </row>
@@ -11180,7 +11180,7 @@
       </c>
       <c r="S127" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T17:37:55Z</t>
+          <t>2026-09-17T22:58:10Z</t>
         </is>
       </c>
     </row>
@@ -11269,7 +11269,7 @@
       </c>
       <c r="S128" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T17:37:55Z</t>
+          <t>2026-09-17T22:58:10Z</t>
         </is>
       </c>
     </row>
@@ -11354,7 +11354,7 @@
       </c>
       <c r="S129" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T17:37:55Z</t>
+          <t>2026-09-17T22:58:10Z</t>
         </is>
       </c>
     </row>
@@ -11439,7 +11439,7 @@
       </c>
       <c r="S130" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T17:37:55Z</t>
+          <t>2026-09-17T22:58:10Z</t>
         </is>
       </c>
     </row>
@@ -11524,7 +11524,7 @@
       </c>
       <c r="S131" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T17:37:55Z</t>
+          <t>2026-09-17T22:58:10Z</t>
         </is>
       </c>
     </row>
@@ -11609,7 +11609,7 @@
       </c>
       <c r="S132" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T17:37:55Z</t>
+          <t>2026-09-17T22:58:10Z</t>
         </is>
       </c>
     </row>
@@ -11694,7 +11694,7 @@
       </c>
       <c r="S133" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T17:37:55Z</t>
+          <t>2026-09-17T22:58:10Z</t>
         </is>
       </c>
     </row>
@@ -11779,7 +11779,7 @@
       </c>
       <c r="S134" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T17:37:55Z</t>
+          <t>2026-09-17T22:58:10Z</t>
         </is>
       </c>
     </row>
@@ -11864,7 +11864,7 @@
       </c>
       <c r="S135" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T17:37:55Z</t>
+          <t>2026-09-17T22:58:10Z</t>
         </is>
       </c>
     </row>
@@ -11949,7 +11949,7 @@
       </c>
       <c r="S136" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T17:37:55Z</t>
+          <t>2026-09-17T22:58:10Z</t>
         </is>
       </c>
     </row>
@@ -12034,7 +12034,7 @@
       </c>
       <c r="S137" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T17:37:55Z</t>
+          <t>2026-09-17T22:58:10Z</t>
         </is>
       </c>
     </row>
@@ -12119,7 +12119,7 @@
       </c>
       <c r="S138" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T17:37:55Z</t>
+          <t>2026-09-17T22:58:10Z</t>
         </is>
       </c>
     </row>
@@ -12204,7 +12204,7 @@
       </c>
       <c r="S139" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T17:37:55Z</t>
+          <t>2026-09-17T22:58:10Z</t>
         </is>
       </c>
     </row>
@@ -12289,7 +12289,7 @@
       </c>
       <c r="S140" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T17:37:55Z</t>
+          <t>2026-09-17T22:58:10Z</t>
         </is>
       </c>
     </row>
@@ -12374,7 +12374,7 @@
       </c>
       <c r="S141" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T17:37:55Z</t>
+          <t>2026-09-17T22:58:10Z</t>
         </is>
       </c>
     </row>
@@ -12459,7 +12459,7 @@
       </c>
       <c r="S142" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T17:37:55Z</t>
+          <t>2026-09-17T22:58:10Z</t>
         </is>
       </c>
     </row>
@@ -12544,7 +12544,7 @@
       </c>
       <c r="S143" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T17:37:55Z</t>
+          <t>2026-09-17T22:58:10Z</t>
         </is>
       </c>
     </row>
@@ -12629,7 +12629,7 @@
       </c>
       <c r="S144" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T17:37:55Z</t>
+          <t>2026-09-17T22:58:10Z</t>
         </is>
       </c>
     </row>
@@ -12714,7 +12714,7 @@
       </c>
       <c r="S145" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T17:37:55Z</t>
+          <t>2026-09-17T22:58:10Z</t>
         </is>
       </c>
     </row>
@@ -12799,7 +12799,7 @@
       </c>
       <c r="S146" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T17:37:55Z</t>
+          <t>2026-09-17T22:58:10Z</t>
         </is>
       </c>
     </row>
@@ -12884,7 +12884,7 @@
       </c>
       <c r="S147" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T17:37:55Z</t>
+          <t>2026-09-17T22:58:10Z</t>
         </is>
       </c>
     </row>
@@ -12969,7 +12969,7 @@
       </c>
       <c r="S148" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T17:37:55Z</t>
+          <t>2026-09-17T22:58:10Z</t>
         </is>
       </c>
     </row>
@@ -13054,7 +13054,7 @@
       </c>
       <c r="S149" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T17:37:55Z</t>
+          <t>2026-09-17T22:58:10Z</t>
         </is>
       </c>
     </row>
@@ -13143,7 +13143,7 @@
       </c>
       <c r="S150" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T17:37:55Z</t>
+          <t>2026-09-17T22:58:10Z</t>
         </is>
       </c>
     </row>
@@ -13232,7 +13232,7 @@
       </c>
       <c r="S151" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T17:37:55Z</t>
+          <t>2026-09-17T22:58:10Z</t>
         </is>
       </c>
     </row>
@@ -13317,7 +13317,7 @@
       </c>
       <c r="S152" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T17:37:55Z</t>
+          <t>2026-09-17T22:58:10Z</t>
         </is>
       </c>
     </row>
@@ -13406,7 +13406,7 @@
       </c>
       <c r="S153" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T17:37:55Z</t>
+          <t>2026-09-17T22:58:10Z</t>
         </is>
       </c>
     </row>
@@ -13495,7 +13495,7 @@
       </c>
       <c r="S154" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T17:37:55Z</t>
+          <t>2026-09-17T22:58:10Z</t>
         </is>
       </c>
     </row>
@@ -13580,7 +13580,7 @@
       </c>
       <c r="S155" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T17:37:55Z</t>
+          <t>2026-09-17T22:58:10Z</t>
         </is>
       </c>
     </row>
@@ -13669,7 +13669,7 @@
       </c>
       <c r="S156" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T17:37:55Z</t>
+          <t>2026-09-17T22:58:10Z</t>
         </is>
       </c>
     </row>
@@ -13758,7 +13758,7 @@
       </c>
       <c r="S157" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T17:37:55Z</t>
+          <t>2026-09-17T22:58:10Z</t>
         </is>
       </c>
     </row>
@@ -13843,7 +13843,7 @@
       </c>
       <c r="S158" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T17:37:55Z</t>
+          <t>2026-09-17T22:58:10Z</t>
         </is>
       </c>
     </row>
@@ -13932,7 +13932,7 @@
       </c>
       <c r="S159" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T17:37:55Z</t>
+          <t>2026-09-17T22:58:10Z</t>
         </is>
       </c>
     </row>
@@ -14021,7 +14021,7 @@
       </c>
       <c r="S160" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T17:37:55Z</t>
+          <t>2026-09-17T22:58:10Z</t>
         </is>
       </c>
     </row>
@@ -14106,7 +14106,7 @@
       </c>
       <c r="S161" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T17:37:55Z</t>
+          <t>2026-09-17T22:58:10Z</t>
         </is>
       </c>
     </row>
@@ -14195,7 +14195,7 @@
       </c>
       <c r="S162" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T17:37:55Z</t>
+          <t>2026-09-17T22:58:10Z</t>
         </is>
       </c>
     </row>
@@ -14284,7 +14284,7 @@
       </c>
       <c r="S163" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T17:37:55Z</t>
+          <t>2026-09-17T22:58:10Z</t>
         </is>
       </c>
     </row>
@@ -14369,7 +14369,7 @@
       </c>
       <c r="S164" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T17:37:55Z</t>
+          <t>2026-09-17T22:58:10Z</t>
         </is>
       </c>
     </row>
@@ -14458,7 +14458,7 @@
       </c>
       <c r="S165" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T17:37:55Z</t>
+          <t>2026-09-17T22:58:10Z</t>
         </is>
       </c>
     </row>
@@ -14547,7 +14547,7 @@
       </c>
       <c r="S166" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T17:37:55Z</t>
+          <t>2026-09-17T22:58:10Z</t>
         </is>
       </c>
     </row>
@@ -14632,7 +14632,7 @@
       </c>
       <c r="S167" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T17:37:55Z</t>
+          <t>2026-09-17T22:58:10Z</t>
         </is>
       </c>
     </row>
@@ -14721,7 +14721,7 @@
       </c>
       <c r="S168" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T17:37:55Z</t>
+          <t>2026-09-17T22:58:10Z</t>
         </is>
       </c>
     </row>
@@ -14810,7 +14810,7 @@
       </c>
       <c r="S169" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T17:37:55Z</t>
+          <t>2026-09-17T22:58:10Z</t>
         </is>
       </c>
     </row>
@@ -14895,7 +14895,7 @@
       </c>
       <c r="S170" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T17:37:55Z</t>
+          <t>2026-09-17T22:58:10Z</t>
         </is>
       </c>
     </row>
@@ -14984,7 +14984,7 @@
       </c>
       <c r="S171" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T17:37:55Z</t>
+          <t>2026-09-17T22:58:10Z</t>
         </is>
       </c>
     </row>
@@ -15073,7 +15073,7 @@
       </c>
       <c r="S172" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T17:37:55Z</t>
+          <t>2026-09-17T22:58:10Z</t>
         </is>
       </c>
     </row>
@@ -15158,7 +15158,7 @@
       </c>
       <c r="S173" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T17:37:55Z</t>
+          <t>2026-09-17T22:58:10Z</t>
         </is>
       </c>
     </row>
@@ -15247,7 +15247,7 @@
       </c>
       <c r="S174" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T17:37:55Z</t>
+          <t>2026-09-17T22:58:10Z</t>
         </is>
       </c>
     </row>
@@ -15336,7 +15336,7 @@
       </c>
       <c r="S175" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T17:37:55Z</t>
+          <t>2026-09-17T22:58:10Z</t>
         </is>
       </c>
     </row>
@@ -15421,7 +15421,7 @@
       </c>
       <c r="S176" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T17:37:55Z</t>
+          <t>2026-09-17T22:58:10Z</t>
         </is>
       </c>
     </row>
@@ -15510,7 +15510,7 @@
       </c>
       <c r="S177" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T17:37:55Z</t>
+          <t>2026-09-17T22:58:10Z</t>
         </is>
       </c>
     </row>
@@ -15599,7 +15599,7 @@
       </c>
       <c r="S178" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T17:37:55Z</t>
+          <t>2026-09-17T22:58:10Z</t>
         </is>
       </c>
     </row>
@@ -15688,7 +15688,7 @@
       </c>
       <c r="S179" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T17:37:55Z</t>
+          <t>2026-09-17T22:58:10Z</t>
         </is>
       </c>
     </row>
@@ -15777,7 +15777,7 @@
       </c>
       <c r="S180" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T17:37:55Z</t>
+          <t>2026-09-17T22:58:10Z</t>
         </is>
       </c>
     </row>
@@ -15866,7 +15866,7 @@
       </c>
       <c r="S181" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T17:37:55Z</t>
+          <t>2026-09-17T22:58:10Z</t>
         </is>
       </c>
     </row>
@@ -15955,7 +15955,7 @@
       </c>
       <c r="S182" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T17:37:55Z</t>
+          <t>2026-09-17T22:58:10Z</t>
         </is>
       </c>
     </row>
@@ -16044,7 +16044,7 @@
       </c>
       <c r="S183" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T17:37:55Z</t>
+          <t>2026-09-17T22:58:10Z</t>
         </is>
       </c>
     </row>
@@ -16133,7 +16133,7 @@
       </c>
       <c r="S184" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T17:37:55Z</t>
+          <t>2026-09-17T22:58:10Z</t>
         </is>
       </c>
     </row>
@@ -16222,7 +16222,7 @@
       </c>
       <c r="S185" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T17:37:55Z</t>
+          <t>2026-09-17T22:58:10Z</t>
         </is>
       </c>
     </row>
@@ -16311,7 +16311,7 @@
       </c>
       <c r="S186" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T17:37:55Z</t>
+          <t>2026-09-17T22:58:10Z</t>
         </is>
       </c>
     </row>
@@ -16400,7 +16400,7 @@
       </c>
       <c r="S187" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T17:37:55Z</t>
+          <t>2026-09-17T22:58:10Z</t>
         </is>
       </c>
     </row>
@@ -16489,7 +16489,7 @@
       </c>
       <c r="S188" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T17:37:55Z</t>
+          <t>2026-09-17T22:58:10Z</t>
         </is>
       </c>
     </row>
@@ -16578,7 +16578,7 @@
       </c>
       <c r="S189" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T17:37:55Z</t>
+          <t>2026-09-17T22:58:10Z</t>
         </is>
       </c>
     </row>
@@ -16663,7 +16663,7 @@
       </c>
       <c r="S190" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T17:37:55Z</t>
+          <t>2026-09-17T22:58:10Z</t>
         </is>
       </c>
     </row>
@@ -16748,7 +16748,7 @@
       </c>
       <c r="S191" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T17:37:55Z</t>
+          <t>2026-09-17T22:58:10Z</t>
         </is>
       </c>
     </row>
@@ -16833,7 +16833,7 @@
       </c>
       <c r="S192" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T17:37:55Z</t>
+          <t>2026-09-17T22:58:10Z</t>
         </is>
       </c>
     </row>
@@ -16918,7 +16918,7 @@
       </c>
       <c r="S193" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T17:37:55Z</t>
+          <t>2026-09-17T22:58:10Z</t>
         </is>
       </c>
     </row>
@@ -17003,7 +17003,7 @@
       </c>
       <c r="S194" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T17:37:55Z</t>
+          <t>2026-09-17T22:58:10Z</t>
         </is>
       </c>
     </row>
@@ -17088,7 +17088,7 @@
       </c>
       <c r="S195" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T17:37:55Z</t>
+          <t>2026-09-17T22:58:10Z</t>
         </is>
       </c>
     </row>
@@ -17173,7 +17173,7 @@
       </c>
       <c r="S196" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T17:37:55Z</t>
+          <t>2026-09-17T22:58:10Z</t>
         </is>
       </c>
     </row>
@@ -17258,7 +17258,7 @@
       </c>
       <c r="S197" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T17:37:55Z</t>
+          <t>2026-09-17T22:58:10Z</t>
         </is>
       </c>
     </row>
@@ -17343,7 +17343,7 @@
       </c>
       <c r="S198" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T17:37:55Z</t>
+          <t>2026-09-17T22:58:10Z</t>
         </is>
       </c>
     </row>
@@ -17428,7 +17428,7 @@
       </c>
       <c r="S199" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T17:37:55Z</t>
+          <t>2026-09-17T22:58:10Z</t>
         </is>
       </c>
     </row>
@@ -17513,7 +17513,7 @@
       </c>
       <c r="S200" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T17:37:55Z</t>
+          <t>2026-09-17T22:58:10Z</t>
         </is>
       </c>
     </row>
@@ -17598,7 +17598,7 @@
       </c>
       <c r="S201" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T17:37:55Z</t>
+          <t>2026-09-17T22:58:10Z</t>
         </is>
       </c>
     </row>
@@ -17683,7 +17683,7 @@
       </c>
       <c r="S202" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T17:37:55Z</t>
+          <t>2026-09-17T22:58:10Z</t>
         </is>
       </c>
     </row>
@@ -17768,7 +17768,7 @@
       </c>
       <c r="S203" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T17:37:55Z</t>
+          <t>2026-09-17T22:58:10Z</t>
         </is>
       </c>
     </row>
@@ -17853,7 +17853,7 @@
       </c>
       <c r="S204" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T17:37:55Z</t>
+          <t>2026-09-17T22:58:10Z</t>
         </is>
       </c>
     </row>
@@ -17938,7 +17938,7 @@
       </c>
       <c r="S205" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T17:37:55Z</t>
+          <t>2026-09-17T22:58:10Z</t>
         </is>
       </c>
     </row>
@@ -18023,7 +18023,7 @@
       </c>
       <c r="S206" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T17:37:55Z</t>
+          <t>2026-09-17T22:58:10Z</t>
         </is>
       </c>
     </row>
@@ -18108,7 +18108,7 @@
       </c>
       <c r="S207" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T17:37:55Z</t>
+          <t>2026-09-17T22:58:10Z</t>
         </is>
       </c>
     </row>
@@ -18193,7 +18193,7 @@
       </c>
       <c r="S208" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T17:37:55Z</t>
+          <t>2026-09-17T22:58:10Z</t>
         </is>
       </c>
     </row>
@@ -18278,7 +18278,7 @@
       </c>
       <c r="S209" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T17:37:55Z</t>
+          <t>2026-09-17T22:58:10Z</t>
         </is>
       </c>
     </row>
@@ -18363,7 +18363,7 @@
       </c>
       <c r="S210" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T17:37:55Z</t>
+          <t>2026-09-17T22:58:10Z</t>
         </is>
       </c>
     </row>
@@ -18452,7 +18452,7 @@
       </c>
       <c r="S211" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T17:37:55Z</t>
+          <t>2026-09-17T22:58:10Z</t>
         </is>
       </c>
     </row>
@@ -18541,7 +18541,7 @@
       </c>
       <c r="S212" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T17:37:55Z</t>
+          <t>2026-09-17T22:58:10Z</t>
         </is>
       </c>
     </row>
@@ -18626,7 +18626,7 @@
       </c>
       <c r="S213" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T17:37:55Z</t>
+          <t>2026-09-17T22:58:10Z</t>
         </is>
       </c>
     </row>
@@ -18715,7 +18715,7 @@
       </c>
       <c r="S214" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T17:37:55Z</t>
+          <t>2026-09-17T22:58:10Z</t>
         </is>
       </c>
     </row>
@@ -18804,7 +18804,7 @@
       </c>
       <c r="S215" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T17:37:55Z</t>
+          <t>2026-09-17T22:58:10Z</t>
         </is>
       </c>
     </row>
@@ -18889,7 +18889,7 @@
       </c>
       <c r="S216" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T17:37:55Z</t>
+          <t>2026-09-17T22:58:10Z</t>
         </is>
       </c>
     </row>
@@ -18978,7 +18978,7 @@
       </c>
       <c r="S217" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T17:37:55Z</t>
+          <t>2026-09-17T22:58:10Z</t>
         </is>
       </c>
     </row>
@@ -19067,7 +19067,7 @@
       </c>
       <c r="S218" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T17:37:55Z</t>
+          <t>2026-09-17T22:58:10Z</t>
         </is>
       </c>
     </row>
@@ -19152,7 +19152,7 @@
       </c>
       <c r="S219" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T17:37:55Z</t>
+          <t>2026-09-17T22:58:10Z</t>
         </is>
       </c>
     </row>
@@ -19241,7 +19241,7 @@
       </c>
       <c r="S220" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T17:37:55Z</t>
+          <t>2026-09-17T22:58:10Z</t>
         </is>
       </c>
     </row>
@@ -19330,7 +19330,7 @@
       </c>
       <c r="S221" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T17:37:55Z</t>
+          <t>2026-09-17T22:58:10Z</t>
         </is>
       </c>
     </row>
@@ -19415,7 +19415,7 @@
       </c>
       <c r="S222" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T17:37:55Z</t>
+          <t>2026-09-17T22:58:10Z</t>
         </is>
       </c>
     </row>
@@ -19504,7 +19504,7 @@
       </c>
       <c r="S223" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T17:37:55Z</t>
+          <t>2026-09-17T22:58:10Z</t>
         </is>
       </c>
     </row>
@@ -19593,7 +19593,7 @@
       </c>
       <c r="S224" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T17:37:55Z</t>
+          <t>2026-09-17T22:58:10Z</t>
         </is>
       </c>
     </row>
@@ -19678,7 +19678,7 @@
       </c>
       <c r="S225" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T17:37:55Z</t>
+          <t>2026-09-17T22:58:10Z</t>
         </is>
       </c>
     </row>
@@ -19767,7 +19767,7 @@
       </c>
       <c r="S226" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T17:37:55Z</t>
+          <t>2026-09-17T22:58:10Z</t>
         </is>
       </c>
     </row>
@@ -19856,7 +19856,7 @@
       </c>
       <c r="S227" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T17:37:55Z</t>
+          <t>2026-09-17T22:58:10Z</t>
         </is>
       </c>
     </row>
@@ -19941,7 +19941,7 @@
       </c>
       <c r="S228" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T17:37:55Z</t>
+          <t>2026-09-17T22:58:10Z</t>
         </is>
       </c>
     </row>
@@ -20030,7 +20030,7 @@
       </c>
       <c r="S229" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T17:37:55Z</t>
+          <t>2026-09-17T22:58:10Z</t>
         </is>
       </c>
     </row>
@@ -20119,7 +20119,7 @@
       </c>
       <c r="S230" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T17:37:55Z</t>
+          <t>2026-09-17T22:58:10Z</t>
         </is>
       </c>
     </row>
@@ -20204,7 +20204,7 @@
       </c>
       <c r="S231" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T17:37:55Z</t>
+          <t>2026-09-17T22:58:10Z</t>
         </is>
       </c>
     </row>
@@ -20293,7 +20293,7 @@
       </c>
       <c r="S232" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T17:37:55Z</t>
+          <t>2026-09-17T22:58:10Z</t>
         </is>
       </c>
     </row>
@@ -20382,7 +20382,7 @@
       </c>
       <c r="S233" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T17:37:55Z</t>
+          <t>2026-09-17T22:58:10Z</t>
         </is>
       </c>
     </row>
@@ -20467,7 +20467,7 @@
       </c>
       <c r="S234" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T17:37:55Z</t>
+          <t>2026-09-17T22:58:10Z</t>
         </is>
       </c>
     </row>
@@ -20556,7 +20556,7 @@
       </c>
       <c r="S235" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T17:37:55Z</t>
+          <t>2026-09-17T22:58:10Z</t>
         </is>
       </c>
     </row>
@@ -20645,7 +20645,7 @@
       </c>
       <c r="S236" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T17:37:55Z</t>
+          <t>2026-09-17T22:58:10Z</t>
         </is>
       </c>
     </row>
@@ -20730,7 +20730,7 @@
       </c>
       <c r="S237" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T17:37:55Z</t>
+          <t>2026-09-17T22:58:10Z</t>
         </is>
       </c>
     </row>
@@ -20819,7 +20819,7 @@
       </c>
       <c r="S238" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T17:37:55Z</t>
+          <t>2026-09-17T22:58:10Z</t>
         </is>
       </c>
     </row>
@@ -20908,7 +20908,7 @@
       </c>
       <c r="S239" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T17:37:55Z</t>
+          <t>2026-09-17T22:58:10Z</t>
         </is>
       </c>
     </row>
@@ -20997,7 +20997,7 @@
       </c>
       <c r="S240" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T17:37:55Z</t>
+          <t>2026-09-17T22:58:10Z</t>
         </is>
       </c>
     </row>
@@ -21086,7 +21086,7 @@
       </c>
       <c r="S241" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T17:37:55Z</t>
+          <t>2026-09-17T22:58:10Z</t>
         </is>
       </c>
     </row>
@@ -21175,7 +21175,7 @@
       </c>
       <c r="S242" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T17:37:55Z</t>
+          <t>2026-09-17T22:58:10Z</t>
         </is>
       </c>
     </row>
@@ -21264,7 +21264,7 @@
       </c>
       <c r="S243" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T17:37:55Z</t>
+          <t>2026-09-17T22:58:10Z</t>
         </is>
       </c>
     </row>
@@ -21353,7 +21353,7 @@
       </c>
       <c r="S244" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T17:37:55Z</t>
+          <t>2026-09-17T22:58:10Z</t>
         </is>
       </c>
     </row>
@@ -21442,7 +21442,7 @@
       </c>
       <c r="S245" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T17:37:55Z</t>
+          <t>2026-09-17T22:58:10Z</t>
         </is>
       </c>
     </row>
@@ -21531,7 +21531,7 @@
       </c>
       <c r="S246" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T17:37:55Z</t>
+          <t>2026-09-17T22:58:10Z</t>
         </is>
       </c>
     </row>
@@ -21620,7 +21620,7 @@
       </c>
       <c r="S247" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T17:37:55Z</t>
+          <t>2026-09-17T22:58:10Z</t>
         </is>
       </c>
     </row>
@@ -21709,7 +21709,7 @@
       </c>
       <c r="S248" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T17:37:55Z</t>
+          <t>2026-09-17T22:58:10Z</t>
         </is>
       </c>
     </row>
@@ -21798,7 +21798,7 @@
       </c>
       <c r="S249" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T17:37:55Z</t>
+          <t>2026-09-17T22:58:10Z</t>
         </is>
       </c>
     </row>
@@ -21887,7 +21887,7 @@
       </c>
       <c r="S250" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T17:37:55Z</t>
+          <t>2026-09-17T22:58:10Z</t>
         </is>
       </c>
     </row>
@@ -22019,7 +22019,7 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T17:37:55Z</t>
+          <t>2026-09-17T22:58:10Z</t>
         </is>
       </c>
     </row>
@@ -22099,7 +22099,7 @@
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>{"dataset_id": "bcv_pib_sector_institucional_anual", "title": "Producto interno bruto por sector institucional anual", "table": "Variaciones porcentuales", "source_file": "5_2_1_si_anual.xlsx", "base": "2007", "price_type": "Precios constantes", "measure": "Variación porcentual interanual", "frequency": "Anual", "period": "2025", "year": 2025, "quarter": null, "classification": "Sector institucional", "component": "Impuestos netos sobre los productos", "value": 10.600260421283764, "unit": "Porcentaje", "status": "Preliminar", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/cuentas_macroeconomicas/5_2_1_si_anual.xlsx", "fetched_at": "2026-09-17T17:37:55Z"}</t>
+          <t>{"dataset_id": "bcv_pib_sector_institucional_anual", "title": "Producto interno bruto por sector institucional anual", "table": "Variaciones porcentuales", "source_file": "5_2_1_si_anual.xlsx", "base": "2007", "price_type": "Precios constantes", "measure": "Variación porcentual interanual", "frequency": "Anual", "period": "2025", "year": 2025, "quarter": null, "classification": "Sector institucional", "component": "Impuestos netos sobre los productos", "value": 10.600260421283764, "unit": "Porcentaje", "status": "Preliminar", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/cuentas_macroeconomicas/5_2_1_si_anual.xlsx", "fetched_at": "2026-09-17T22:58:10Z"}</t>
         </is>
       </c>
     </row>

--- a/assets/data/bcv/excel/ove_bcv_pib_sector_institucional_anual.xlsx
+++ b/assets/data/bcv/excel/ove_bcv_pib_sector_institucional_anual.xlsx
@@ -736,7 +736,7 @@
       </c>
       <c r="S7" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T22:58:10Z</t>
+          <t>2026-09-18T22:43:53Z</t>
         </is>
       </c>
     </row>
@@ -821,7 +821,7 @@
       </c>
       <c r="S8" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T22:58:10Z</t>
+          <t>2026-09-18T22:43:53Z</t>
         </is>
       </c>
     </row>
@@ -906,7 +906,7 @@
       </c>
       <c r="S9" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T22:58:10Z</t>
+          <t>2026-09-18T22:43:53Z</t>
         </is>
       </c>
     </row>
@@ -991,7 +991,7 @@
       </c>
       <c r="S10" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T22:58:10Z</t>
+          <t>2026-09-18T22:43:53Z</t>
         </is>
       </c>
     </row>
@@ -1076,7 +1076,7 @@
       </c>
       <c r="S11" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T22:58:10Z</t>
+          <t>2026-09-18T22:43:53Z</t>
         </is>
       </c>
     </row>
@@ -1161,7 +1161,7 @@
       </c>
       <c r="S12" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T22:58:10Z</t>
+          <t>2026-09-18T22:43:53Z</t>
         </is>
       </c>
     </row>
@@ -1246,7 +1246,7 @@
       </c>
       <c r="S13" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T22:58:10Z</t>
+          <t>2026-09-18T22:43:53Z</t>
         </is>
       </c>
     </row>
@@ -1331,7 +1331,7 @@
       </c>
       <c r="S14" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T22:58:10Z</t>
+          <t>2026-09-18T22:43:53Z</t>
         </is>
       </c>
     </row>
@@ -1416,7 +1416,7 @@
       </c>
       <c r="S15" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T22:58:10Z</t>
+          <t>2026-09-18T22:43:53Z</t>
         </is>
       </c>
     </row>
@@ -1501,7 +1501,7 @@
       </c>
       <c r="S16" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T22:58:10Z</t>
+          <t>2026-09-18T22:43:53Z</t>
         </is>
       </c>
     </row>
@@ -1586,7 +1586,7 @@
       </c>
       <c r="S17" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T22:58:10Z</t>
+          <t>2026-09-18T22:43:53Z</t>
         </is>
       </c>
     </row>
@@ -1671,7 +1671,7 @@
       </c>
       <c r="S18" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T22:58:10Z</t>
+          <t>2026-09-18T22:43:53Z</t>
         </is>
       </c>
     </row>
@@ -1756,7 +1756,7 @@
       </c>
       <c r="S19" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T22:58:10Z</t>
+          <t>2026-09-18T22:43:53Z</t>
         </is>
       </c>
     </row>
@@ -1841,7 +1841,7 @@
       </c>
       <c r="S20" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T22:58:10Z</t>
+          <t>2026-09-18T22:43:53Z</t>
         </is>
       </c>
     </row>
@@ -1926,7 +1926,7 @@
       </c>
       <c r="S21" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T22:58:10Z</t>
+          <t>2026-09-18T22:43:53Z</t>
         </is>
       </c>
     </row>
@@ -2011,7 +2011,7 @@
       </c>
       <c r="S22" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T22:58:10Z</t>
+          <t>2026-09-18T22:43:53Z</t>
         </is>
       </c>
     </row>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="S23" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T22:58:10Z</t>
+          <t>2026-09-18T22:43:53Z</t>
         </is>
       </c>
     </row>
@@ -2181,7 +2181,7 @@
       </c>
       <c r="S24" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T22:58:10Z</t>
+          <t>2026-09-18T22:43:53Z</t>
         </is>
       </c>
     </row>
@@ -2266,7 +2266,7 @@
       </c>
       <c r="S25" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T22:58:10Z</t>
+          <t>2026-09-18T22:43:53Z</t>
         </is>
       </c>
     </row>
@@ -2351,7 +2351,7 @@
       </c>
       <c r="S26" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T22:58:10Z</t>
+          <t>2026-09-18T22:43:53Z</t>
         </is>
       </c>
     </row>
@@ -2436,7 +2436,7 @@
       </c>
       <c r="S27" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T22:58:10Z</t>
+          <t>2026-09-18T22:43:53Z</t>
         </is>
       </c>
     </row>
@@ -2525,7 +2525,7 @@
       </c>
       <c r="S28" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T22:58:10Z</t>
+          <t>2026-09-18T22:43:53Z</t>
         </is>
       </c>
     </row>
@@ -2614,7 +2614,7 @@
       </c>
       <c r="S29" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T22:58:10Z</t>
+          <t>2026-09-18T22:43:53Z</t>
         </is>
       </c>
     </row>
@@ -2699,7 +2699,7 @@
       </c>
       <c r="S30" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T22:58:10Z</t>
+          <t>2026-09-18T22:43:53Z</t>
         </is>
       </c>
     </row>
@@ -2788,7 +2788,7 @@
       </c>
       <c r="S31" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T22:58:10Z</t>
+          <t>2026-09-18T22:43:53Z</t>
         </is>
       </c>
     </row>
@@ -2877,7 +2877,7 @@
       </c>
       <c r="S32" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T22:58:10Z</t>
+          <t>2026-09-18T22:43:53Z</t>
         </is>
       </c>
     </row>
@@ -2962,7 +2962,7 @@
       </c>
       <c r="S33" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T22:58:10Z</t>
+          <t>2026-09-18T22:43:53Z</t>
         </is>
       </c>
     </row>
@@ -3051,7 +3051,7 @@
       </c>
       <c r="S34" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T22:58:10Z</t>
+          <t>2026-09-18T22:43:53Z</t>
         </is>
       </c>
     </row>
@@ -3140,7 +3140,7 @@
       </c>
       <c r="S35" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T22:58:10Z</t>
+          <t>2026-09-18T22:43:53Z</t>
         </is>
       </c>
     </row>
@@ -3225,7 +3225,7 @@
       </c>
       <c r="S36" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T22:58:10Z</t>
+          <t>2026-09-18T22:43:53Z</t>
         </is>
       </c>
     </row>
@@ -3314,7 +3314,7 @@
       </c>
       <c r="S37" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T22:58:10Z</t>
+          <t>2026-09-18T22:43:53Z</t>
         </is>
       </c>
     </row>
@@ -3403,7 +3403,7 @@
       </c>
       <c r="S38" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T22:58:10Z</t>
+          <t>2026-09-18T22:43:53Z</t>
         </is>
       </c>
     </row>
@@ -3488,7 +3488,7 @@
       </c>
       <c r="S39" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T22:58:10Z</t>
+          <t>2026-09-18T22:43:53Z</t>
         </is>
       </c>
     </row>
@@ -3577,7 +3577,7 @@
       </c>
       <c r="S40" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T22:58:10Z</t>
+          <t>2026-09-18T22:43:53Z</t>
         </is>
       </c>
     </row>
@@ -3666,7 +3666,7 @@
       </c>
       <c r="S41" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T22:58:10Z</t>
+          <t>2026-09-18T22:43:53Z</t>
         </is>
       </c>
     </row>
@@ -3751,7 +3751,7 @@
       </c>
       <c r="S42" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T22:58:10Z</t>
+          <t>2026-09-18T22:43:53Z</t>
         </is>
       </c>
     </row>
@@ -3840,7 +3840,7 @@
       </c>
       <c r="S43" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T22:58:10Z</t>
+          <t>2026-09-18T22:43:53Z</t>
         </is>
       </c>
     </row>
@@ -3929,7 +3929,7 @@
       </c>
       <c r="S44" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T22:58:10Z</t>
+          <t>2026-09-18T22:43:53Z</t>
         </is>
       </c>
     </row>
@@ -4014,7 +4014,7 @@
       </c>
       <c r="S45" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T22:58:10Z</t>
+          <t>2026-09-18T22:43:53Z</t>
         </is>
       </c>
     </row>
@@ -4103,7 +4103,7 @@
       </c>
       <c r="S46" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T22:58:10Z</t>
+          <t>2026-09-18T22:43:53Z</t>
         </is>
       </c>
     </row>
@@ -4192,7 +4192,7 @@
       </c>
       <c r="S47" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T22:58:10Z</t>
+          <t>2026-09-18T22:43:53Z</t>
         </is>
       </c>
     </row>
@@ -4277,7 +4277,7 @@
       </c>
       <c r="S48" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T22:58:10Z</t>
+          <t>2026-09-18T22:43:53Z</t>
         </is>
       </c>
     </row>
@@ -4366,7 +4366,7 @@
       </c>
       <c r="S49" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T22:58:10Z</t>
+          <t>2026-09-18T22:43:53Z</t>
         </is>
       </c>
     </row>
@@ -4455,7 +4455,7 @@
       </c>
       <c r="S50" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T22:58:10Z</t>
+          <t>2026-09-18T22:43:53Z</t>
         </is>
       </c>
     </row>
@@ -4540,7 +4540,7 @@
       </c>
       <c r="S51" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T22:58:10Z</t>
+          <t>2026-09-18T22:43:53Z</t>
         </is>
       </c>
     </row>
@@ -4629,7 +4629,7 @@
       </c>
       <c r="S52" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T22:58:10Z</t>
+          <t>2026-09-18T22:43:53Z</t>
         </is>
       </c>
     </row>
@@ -4718,7 +4718,7 @@
       </c>
       <c r="S53" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T22:58:10Z</t>
+          <t>2026-09-18T22:43:53Z</t>
         </is>
       </c>
     </row>
@@ -4803,7 +4803,7 @@
       </c>
       <c r="S54" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T22:58:10Z</t>
+          <t>2026-09-18T22:43:53Z</t>
         </is>
       </c>
     </row>
@@ -4892,7 +4892,7 @@
       </c>
       <c r="S55" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T22:58:10Z</t>
+          <t>2026-09-18T22:43:53Z</t>
         </is>
       </c>
     </row>
@@ -4981,7 +4981,7 @@
       </c>
       <c r="S56" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T22:58:10Z</t>
+          <t>2026-09-18T22:43:53Z</t>
         </is>
       </c>
     </row>
@@ -5070,7 +5070,7 @@
       </c>
       <c r="S57" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T22:58:10Z</t>
+          <t>2026-09-18T22:43:53Z</t>
         </is>
       </c>
     </row>
@@ -5159,7 +5159,7 @@
       </c>
       <c r="S58" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T22:58:10Z</t>
+          <t>2026-09-18T22:43:53Z</t>
         </is>
       </c>
     </row>
@@ -5248,7 +5248,7 @@
       </c>
       <c r="S59" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T22:58:10Z</t>
+          <t>2026-09-18T22:43:53Z</t>
         </is>
       </c>
     </row>
@@ -5337,7 +5337,7 @@
       </c>
       <c r="S60" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T22:58:10Z</t>
+          <t>2026-09-18T22:43:53Z</t>
         </is>
       </c>
     </row>
@@ -5426,7 +5426,7 @@
       </c>
       <c r="S61" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T22:58:10Z</t>
+          <t>2026-09-18T22:43:53Z</t>
         </is>
       </c>
     </row>
@@ -5515,7 +5515,7 @@
       </c>
       <c r="S62" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T22:58:10Z</t>
+          <t>2026-09-18T22:43:53Z</t>
         </is>
       </c>
     </row>
@@ -5604,7 +5604,7 @@
       </c>
       <c r="S63" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T22:58:10Z</t>
+          <t>2026-09-18T22:43:53Z</t>
         </is>
       </c>
     </row>
@@ -5693,7 +5693,7 @@
       </c>
       <c r="S64" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T22:58:10Z</t>
+          <t>2026-09-18T22:43:53Z</t>
         </is>
       </c>
     </row>
@@ -5782,7 +5782,7 @@
       </c>
       <c r="S65" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T22:58:10Z</t>
+          <t>2026-09-18T22:43:53Z</t>
         </is>
       </c>
     </row>
@@ -5871,7 +5871,7 @@
       </c>
       <c r="S66" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T22:58:10Z</t>
+          <t>2026-09-18T22:43:53Z</t>
         </is>
       </c>
     </row>
@@ -5960,7 +5960,7 @@
       </c>
       <c r="S67" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T22:58:10Z</t>
+          <t>2026-09-18T22:43:53Z</t>
         </is>
       </c>
     </row>
@@ -6045,7 +6045,7 @@
       </c>
       <c r="S68" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T22:58:10Z</t>
+          <t>2026-09-18T22:43:53Z</t>
         </is>
       </c>
     </row>
@@ -6130,7 +6130,7 @@
       </c>
       <c r="S69" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T22:58:10Z</t>
+          <t>2026-09-18T22:43:53Z</t>
         </is>
       </c>
     </row>
@@ -6215,7 +6215,7 @@
       </c>
       <c r="S70" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T22:58:10Z</t>
+          <t>2026-09-18T22:43:53Z</t>
         </is>
       </c>
     </row>
@@ -6300,7 +6300,7 @@
       </c>
       <c r="S71" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T22:58:10Z</t>
+          <t>2026-09-18T22:43:53Z</t>
         </is>
       </c>
     </row>
@@ -6385,7 +6385,7 @@
       </c>
       <c r="S72" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T22:58:10Z</t>
+          <t>2026-09-18T22:43:53Z</t>
         </is>
       </c>
     </row>
@@ -6470,7 +6470,7 @@
       </c>
       <c r="S73" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T22:58:10Z</t>
+          <t>2026-09-18T22:43:53Z</t>
         </is>
       </c>
     </row>
@@ -6555,7 +6555,7 @@
       </c>
       <c r="S74" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T22:58:10Z</t>
+          <t>2026-09-18T22:43:53Z</t>
         </is>
       </c>
     </row>
@@ -6640,7 +6640,7 @@
       </c>
       <c r="S75" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T22:58:10Z</t>
+          <t>2026-09-18T22:43:53Z</t>
         </is>
       </c>
     </row>
@@ -6725,7 +6725,7 @@
       </c>
       <c r="S76" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T22:58:10Z</t>
+          <t>2026-09-18T22:43:53Z</t>
         </is>
       </c>
     </row>
@@ -6810,7 +6810,7 @@
       </c>
       <c r="S77" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T22:58:10Z</t>
+          <t>2026-09-18T22:43:53Z</t>
         </is>
       </c>
     </row>
@@ -6895,7 +6895,7 @@
       </c>
       <c r="S78" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T22:58:10Z</t>
+          <t>2026-09-18T22:43:53Z</t>
         </is>
       </c>
     </row>
@@ -6980,7 +6980,7 @@
       </c>
       <c r="S79" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T22:58:10Z</t>
+          <t>2026-09-18T22:43:53Z</t>
         </is>
       </c>
     </row>
@@ -7065,7 +7065,7 @@
       </c>
       <c r="S80" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T22:58:10Z</t>
+          <t>2026-09-18T22:43:53Z</t>
         </is>
       </c>
     </row>
@@ -7150,7 +7150,7 @@
       </c>
       <c r="S81" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T22:58:10Z</t>
+          <t>2026-09-18T22:43:53Z</t>
         </is>
       </c>
     </row>
@@ -7235,7 +7235,7 @@
       </c>
       <c r="S82" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T22:58:10Z</t>
+          <t>2026-09-18T22:43:53Z</t>
         </is>
       </c>
     </row>
@@ -7320,7 +7320,7 @@
       </c>
       <c r="S83" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T22:58:10Z</t>
+          <t>2026-09-18T22:43:53Z</t>
         </is>
       </c>
     </row>
@@ -7405,7 +7405,7 @@
       </c>
       <c r="S84" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T22:58:10Z</t>
+          <t>2026-09-18T22:43:53Z</t>
         </is>
       </c>
     </row>
@@ -7490,7 +7490,7 @@
       </c>
       <c r="S85" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T22:58:10Z</t>
+          <t>2026-09-18T22:43:53Z</t>
         </is>
       </c>
     </row>
@@ -7575,7 +7575,7 @@
       </c>
       <c r="S86" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T22:58:10Z</t>
+          <t>2026-09-18T22:43:53Z</t>
         </is>
       </c>
     </row>
@@ -7660,7 +7660,7 @@
       </c>
       <c r="S87" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T22:58:10Z</t>
+          <t>2026-09-18T22:43:53Z</t>
         </is>
       </c>
     </row>
@@ -7745,7 +7745,7 @@
       </c>
       <c r="S88" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T22:58:10Z</t>
+          <t>2026-09-18T22:43:53Z</t>
         </is>
       </c>
     </row>
@@ -7834,7 +7834,7 @@
       </c>
       <c r="S89" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T22:58:10Z</t>
+          <t>2026-09-18T22:43:53Z</t>
         </is>
       </c>
     </row>
@@ -7923,7 +7923,7 @@
       </c>
       <c r="S90" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T22:58:10Z</t>
+          <t>2026-09-18T22:43:53Z</t>
         </is>
       </c>
     </row>
@@ -8008,7 +8008,7 @@
       </c>
       <c r="S91" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T22:58:10Z</t>
+          <t>2026-09-18T22:43:53Z</t>
         </is>
       </c>
     </row>
@@ -8097,7 +8097,7 @@
       </c>
       <c r="S92" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T22:58:10Z</t>
+          <t>2026-09-18T22:43:53Z</t>
         </is>
       </c>
     </row>
@@ -8186,7 +8186,7 @@
       </c>
       <c r="S93" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T22:58:10Z</t>
+          <t>2026-09-18T22:43:53Z</t>
         </is>
       </c>
     </row>
@@ -8271,7 +8271,7 @@
       </c>
       <c r="S94" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T22:58:10Z</t>
+          <t>2026-09-18T22:43:53Z</t>
         </is>
       </c>
     </row>
@@ -8360,7 +8360,7 @@
       </c>
       <c r="S95" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T22:58:10Z</t>
+          <t>2026-09-18T22:43:53Z</t>
         </is>
       </c>
     </row>
@@ -8449,7 +8449,7 @@
       </c>
       <c r="S96" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T22:58:10Z</t>
+          <t>2026-09-18T22:43:53Z</t>
         </is>
       </c>
     </row>
@@ -8534,7 +8534,7 @@
       </c>
       <c r="S97" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T22:58:10Z</t>
+          <t>2026-09-18T22:43:53Z</t>
         </is>
       </c>
     </row>
@@ -8623,7 +8623,7 @@
       </c>
       <c r="S98" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T22:58:10Z</t>
+          <t>2026-09-18T22:43:53Z</t>
         </is>
       </c>
     </row>
@@ -8712,7 +8712,7 @@
       </c>
       <c r="S99" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T22:58:10Z</t>
+          <t>2026-09-18T22:43:53Z</t>
         </is>
       </c>
     </row>
@@ -8797,7 +8797,7 @@
       </c>
       <c r="S100" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T22:58:10Z</t>
+          <t>2026-09-18T22:43:53Z</t>
         </is>
       </c>
     </row>
@@ -8886,7 +8886,7 @@
       </c>
       <c r="S101" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T22:58:10Z</t>
+          <t>2026-09-18T22:43:53Z</t>
         </is>
       </c>
     </row>
@@ -8975,7 +8975,7 @@
       </c>
       <c r="S102" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T22:58:10Z</t>
+          <t>2026-09-18T22:43:53Z</t>
         </is>
       </c>
     </row>
@@ -9060,7 +9060,7 @@
       </c>
       <c r="S103" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T22:58:10Z</t>
+          <t>2026-09-18T22:43:53Z</t>
         </is>
       </c>
     </row>
@@ -9149,7 +9149,7 @@
       </c>
       <c r="S104" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T22:58:10Z</t>
+          <t>2026-09-18T22:43:53Z</t>
         </is>
       </c>
     </row>
@@ -9238,7 +9238,7 @@
       </c>
       <c r="S105" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T22:58:10Z</t>
+          <t>2026-09-18T22:43:53Z</t>
         </is>
       </c>
     </row>
@@ -9323,7 +9323,7 @@
       </c>
       <c r="S106" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T22:58:10Z</t>
+          <t>2026-09-18T22:43:53Z</t>
         </is>
       </c>
     </row>
@@ -9412,7 +9412,7 @@
       </c>
       <c r="S107" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T22:58:10Z</t>
+          <t>2026-09-18T22:43:53Z</t>
         </is>
       </c>
     </row>
@@ -9501,7 +9501,7 @@
       </c>
       <c r="S108" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T22:58:10Z</t>
+          <t>2026-09-18T22:43:53Z</t>
         </is>
       </c>
     </row>
@@ -9586,7 +9586,7 @@
       </c>
       <c r="S109" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T22:58:10Z</t>
+          <t>2026-09-18T22:43:53Z</t>
         </is>
       </c>
     </row>
@@ -9675,7 +9675,7 @@
       </c>
       <c r="S110" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T22:58:10Z</t>
+          <t>2026-09-18T22:43:53Z</t>
         </is>
       </c>
     </row>
@@ -9764,7 +9764,7 @@
       </c>
       <c r="S111" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T22:58:10Z</t>
+          <t>2026-09-18T22:43:53Z</t>
         </is>
       </c>
     </row>
@@ -9849,7 +9849,7 @@
       </c>
       <c r="S112" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T22:58:10Z</t>
+          <t>2026-09-18T22:43:53Z</t>
         </is>
       </c>
     </row>
@@ -9938,7 +9938,7 @@
       </c>
       <c r="S113" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T22:58:10Z</t>
+          <t>2026-09-18T22:43:53Z</t>
         </is>
       </c>
     </row>
@@ -10027,7 +10027,7 @@
       </c>
       <c r="S114" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T22:58:10Z</t>
+          <t>2026-09-18T22:43:53Z</t>
         </is>
       </c>
     </row>
@@ -10112,7 +10112,7 @@
       </c>
       <c r="S115" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T22:58:10Z</t>
+          <t>2026-09-18T22:43:53Z</t>
         </is>
       </c>
     </row>
@@ -10201,7 +10201,7 @@
       </c>
       <c r="S116" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T22:58:10Z</t>
+          <t>2026-09-18T22:43:53Z</t>
         </is>
       </c>
     </row>
@@ -10290,7 +10290,7 @@
       </c>
       <c r="S117" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T22:58:10Z</t>
+          <t>2026-09-18T22:43:53Z</t>
         </is>
       </c>
     </row>
@@ -10379,7 +10379,7 @@
       </c>
       <c r="S118" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T22:58:10Z</t>
+          <t>2026-09-18T22:43:53Z</t>
         </is>
       </c>
     </row>
@@ -10468,7 +10468,7 @@
       </c>
       <c r="S119" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T22:58:10Z</t>
+          <t>2026-09-18T22:43:53Z</t>
         </is>
       </c>
     </row>
@@ -10557,7 +10557,7 @@
       </c>
       <c r="S120" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T22:58:10Z</t>
+          <t>2026-09-18T22:43:53Z</t>
         </is>
       </c>
     </row>
@@ -10646,7 +10646,7 @@
       </c>
       <c r="S121" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T22:58:10Z</t>
+          <t>2026-09-18T22:43:53Z</t>
         </is>
       </c>
     </row>
@@ -10735,7 +10735,7 @@
       </c>
       <c r="S122" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T22:58:10Z</t>
+          <t>2026-09-18T22:43:53Z</t>
         </is>
       </c>
     </row>
@@ -10824,7 +10824,7 @@
       </c>
       <c r="S123" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T22:58:10Z</t>
+          <t>2026-09-18T22:43:53Z</t>
         </is>
       </c>
     </row>
@@ -10913,7 +10913,7 @@
       </c>
       <c r="S124" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T22:58:10Z</t>
+          <t>2026-09-18T22:43:53Z</t>
         </is>
       </c>
     </row>
@@ -11002,7 +11002,7 @@
       </c>
       <c r="S125" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T22:58:10Z</t>
+          <t>2026-09-18T22:43:53Z</t>
         </is>
       </c>
     </row>
@@ -11091,7 +11091,7 @@
       </c>
       <c r="S126" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T22:58:10Z</t>
+          <t>2026-09-18T22:43:53Z</t>
         </is>
       </c>
     </row>
@@ -11180,7 +11180,7 @@
       </c>
       <c r="S127" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T22:58:10Z</t>
+          <t>2026-09-18T22:43:53Z</t>
         </is>
       </c>
     </row>
@@ -11269,7 +11269,7 @@
       </c>
       <c r="S128" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T22:58:10Z</t>
+          <t>2026-09-18T22:43:53Z</t>
         </is>
       </c>
     </row>
@@ -11354,7 +11354,7 @@
       </c>
       <c r="S129" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T22:58:10Z</t>
+          <t>2026-09-18T22:43:53Z</t>
         </is>
       </c>
     </row>
@@ -11439,7 +11439,7 @@
       </c>
       <c r="S130" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T22:58:10Z</t>
+          <t>2026-09-18T22:43:53Z</t>
         </is>
       </c>
     </row>
@@ -11524,7 +11524,7 @@
       </c>
       <c r="S131" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T22:58:10Z</t>
+          <t>2026-09-18T22:43:53Z</t>
         </is>
       </c>
     </row>
@@ -11609,7 +11609,7 @@
       </c>
       <c r="S132" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T22:58:10Z</t>
+          <t>2026-09-18T22:43:53Z</t>
         </is>
       </c>
     </row>
@@ -11694,7 +11694,7 @@
       </c>
       <c r="S133" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T22:58:10Z</t>
+          <t>2026-09-18T22:43:53Z</t>
         </is>
       </c>
     </row>
@@ -11779,7 +11779,7 @@
       </c>
       <c r="S134" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T22:58:10Z</t>
+          <t>2026-09-18T22:43:53Z</t>
         </is>
       </c>
     </row>
@@ -11864,7 +11864,7 @@
       </c>
       <c r="S135" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T22:58:10Z</t>
+          <t>2026-09-18T22:43:53Z</t>
         </is>
       </c>
     </row>
@@ -11949,7 +11949,7 @@
       </c>
       <c r="S136" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T22:58:10Z</t>
+          <t>2026-09-18T22:43:53Z</t>
         </is>
       </c>
     </row>
@@ -12034,7 +12034,7 @@
       </c>
       <c r="S137" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T22:58:10Z</t>
+          <t>2026-09-18T22:43:53Z</t>
         </is>
       </c>
     </row>
@@ -12119,7 +12119,7 @@
       </c>
       <c r="S138" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T22:58:10Z</t>
+          <t>2026-09-18T22:43:53Z</t>
         </is>
       </c>
     </row>
@@ -12204,7 +12204,7 @@
       </c>
       <c r="S139" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T22:58:10Z</t>
+          <t>2026-09-18T22:43:53Z</t>
         </is>
       </c>
     </row>
@@ -12289,7 +12289,7 @@
       </c>
       <c r="S140" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T22:58:10Z</t>
+          <t>2026-09-18T22:43:53Z</t>
         </is>
       </c>
     </row>
@@ -12374,7 +12374,7 @@
       </c>
       <c r="S141" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T22:58:10Z</t>
+          <t>2026-09-18T22:43:53Z</t>
         </is>
       </c>
     </row>
@@ -12459,7 +12459,7 @@
       </c>
       <c r="S142" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T22:58:10Z</t>
+          <t>2026-09-18T22:43:53Z</t>
         </is>
       </c>
     </row>
@@ -12544,7 +12544,7 @@
       </c>
       <c r="S143" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T22:58:10Z</t>
+          <t>2026-09-18T22:43:53Z</t>
         </is>
       </c>
     </row>
@@ -12629,7 +12629,7 @@
       </c>
       <c r="S144" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T22:58:10Z</t>
+          <t>2026-09-18T22:43:53Z</t>
         </is>
       </c>
     </row>
@@ -12714,7 +12714,7 @@
       </c>
       <c r="S145" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T22:58:10Z</t>
+          <t>2026-09-18T22:43:53Z</t>
         </is>
       </c>
     </row>
@@ -12799,7 +12799,7 @@
       </c>
       <c r="S146" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T22:58:10Z</t>
+          <t>2026-09-18T22:43:53Z</t>
         </is>
       </c>
     </row>
@@ -12884,7 +12884,7 @@
       </c>
       <c r="S147" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T22:58:10Z</t>
+          <t>2026-09-18T22:43:53Z</t>
         </is>
       </c>
     </row>
@@ -12969,7 +12969,7 @@
       </c>
       <c r="S148" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T22:58:10Z</t>
+          <t>2026-09-18T22:43:53Z</t>
         </is>
       </c>
     </row>
@@ -13054,7 +13054,7 @@
       </c>
       <c r="S149" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T22:58:10Z</t>
+          <t>2026-09-18T22:43:53Z</t>
         </is>
       </c>
     </row>
@@ -13143,7 +13143,7 @@
       </c>
       <c r="S150" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T22:58:10Z</t>
+          <t>2026-09-18T22:43:53Z</t>
         </is>
       </c>
     </row>
@@ -13232,7 +13232,7 @@
       </c>
       <c r="S151" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T22:58:10Z</t>
+          <t>2026-09-18T22:43:53Z</t>
         </is>
       </c>
     </row>
@@ -13317,7 +13317,7 @@
       </c>
       <c r="S152" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T22:58:10Z</t>
+          <t>2026-09-18T22:43:53Z</t>
         </is>
       </c>
     </row>
@@ -13406,7 +13406,7 @@
       </c>
       <c r="S153" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T22:58:10Z</t>
+          <t>2026-09-18T22:43:53Z</t>
         </is>
       </c>
     </row>
@@ -13495,7 +13495,7 @@
       </c>
       <c r="S154" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T22:58:10Z</t>
+          <t>2026-09-18T22:43:53Z</t>
         </is>
       </c>
     </row>
@@ -13580,7 +13580,7 @@
       </c>
       <c r="S155" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T22:58:10Z</t>
+          <t>2026-09-18T22:43:53Z</t>
         </is>
       </c>
     </row>
@@ -13669,7 +13669,7 @@
       </c>
       <c r="S156" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T22:58:10Z</t>
+          <t>2026-09-18T22:43:53Z</t>
         </is>
       </c>
     </row>
@@ -13758,7 +13758,7 @@
       </c>
       <c r="S157" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T22:58:10Z</t>
+          <t>2026-09-18T22:43:53Z</t>
         </is>
       </c>
     </row>
@@ -13843,7 +13843,7 @@
       </c>
       <c r="S158" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T22:58:10Z</t>
+          <t>2026-09-18T22:43:53Z</t>
         </is>
       </c>
     </row>
@@ -13932,7 +13932,7 @@
       </c>
       <c r="S159" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T22:58:10Z</t>
+          <t>2026-09-18T22:43:53Z</t>
         </is>
       </c>
     </row>
@@ -14021,7 +14021,7 @@
       </c>
       <c r="S160" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T22:58:10Z</t>
+          <t>2026-09-18T22:43:53Z</t>
         </is>
       </c>
     </row>
@@ -14106,7 +14106,7 @@
       </c>
       <c r="S161" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T22:58:10Z</t>
+          <t>2026-09-18T22:43:53Z</t>
         </is>
       </c>
     </row>
@@ -14195,7 +14195,7 @@
       </c>
       <c r="S162" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T22:58:10Z</t>
+          <t>2026-09-18T22:43:53Z</t>
         </is>
       </c>
     </row>
@@ -14284,7 +14284,7 @@
       </c>
       <c r="S163" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T22:58:10Z</t>
+          <t>2026-09-18T22:43:53Z</t>
         </is>
       </c>
     </row>
@@ -14369,7 +14369,7 @@
       </c>
       <c r="S164" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T22:58:10Z</t>
+          <t>2026-09-18T22:43:53Z</t>
         </is>
       </c>
     </row>
@@ -14458,7 +14458,7 @@
       </c>
       <c r="S165" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T22:58:10Z</t>
+          <t>2026-09-18T22:43:53Z</t>
         </is>
       </c>
     </row>
@@ -14547,7 +14547,7 @@
       </c>
       <c r="S166" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T22:58:10Z</t>
+          <t>2026-09-18T22:43:53Z</t>
         </is>
       </c>
     </row>
@@ -14632,7 +14632,7 @@
       </c>
       <c r="S167" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T22:58:10Z</t>
+          <t>2026-09-18T22:43:53Z</t>
         </is>
       </c>
     </row>
@@ -14721,7 +14721,7 @@
       </c>
       <c r="S168" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T22:58:10Z</t>
+          <t>2026-09-18T22:43:53Z</t>
         </is>
       </c>
     </row>
@@ -14810,7 +14810,7 @@
       </c>
       <c r="S169" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T22:58:10Z</t>
+          <t>2026-09-18T22:43:53Z</t>
         </is>
       </c>
     </row>
@@ -14895,7 +14895,7 @@
       </c>
       <c r="S170" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T22:58:10Z</t>
+          <t>2026-09-18T22:43:53Z</t>
         </is>
       </c>
     </row>
@@ -14984,7 +14984,7 @@
       </c>
       <c r="S171" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T22:58:10Z</t>
+          <t>2026-09-18T22:43:53Z</t>
         </is>
       </c>
     </row>
@@ -15073,7 +15073,7 @@
       </c>
       <c r="S172" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T22:58:10Z</t>
+          <t>2026-09-18T22:43:53Z</t>
         </is>
       </c>
     </row>
@@ -15158,7 +15158,7 @@
       </c>
       <c r="S173" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T22:58:10Z</t>
+          <t>2026-09-18T22:43:53Z</t>
         </is>
       </c>
     </row>
@@ -15247,7 +15247,7 @@
       </c>
       <c r="S174" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T22:58:10Z</t>
+          <t>2026-09-18T22:43:53Z</t>
         </is>
       </c>
     </row>
@@ -15336,7 +15336,7 @@
       </c>
       <c r="S175" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T22:58:10Z</t>
+          <t>2026-09-18T22:43:53Z</t>
         </is>
       </c>
     </row>
@@ -15421,7 +15421,7 @@
       </c>
       <c r="S176" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T22:58:10Z</t>
+          <t>2026-09-18T22:43:53Z</t>
         </is>
       </c>
     </row>
@@ -15510,7 +15510,7 @@
       </c>
       <c r="S177" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T22:58:10Z</t>
+          <t>2026-09-18T22:43:53Z</t>
         </is>
       </c>
     </row>
@@ -15599,7 +15599,7 @@
       </c>
       <c r="S178" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T22:58:10Z</t>
+          <t>2026-09-18T22:43:53Z</t>
         </is>
       </c>
     </row>
@@ -15688,7 +15688,7 @@
       </c>
       <c r="S179" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T22:58:10Z</t>
+          <t>2026-09-18T22:43:53Z</t>
         </is>
       </c>
     </row>
@@ -15777,7 +15777,7 @@
       </c>
       <c r="S180" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T22:58:10Z</t>
+          <t>2026-09-18T22:43:53Z</t>
         </is>
       </c>
     </row>
@@ -15866,7 +15866,7 @@
       </c>
       <c r="S181" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T22:58:10Z</t>
+          <t>2026-09-18T22:43:53Z</t>
         </is>
       </c>
     </row>
@@ -15955,7 +15955,7 @@
       </c>
       <c r="S182" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T22:58:10Z</t>
+          <t>2026-09-18T22:43:53Z</t>
         </is>
       </c>
     </row>
@@ -16044,7 +16044,7 @@
       </c>
       <c r="S183" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T22:58:10Z</t>
+          <t>2026-09-18T22:43:53Z</t>
         </is>
       </c>
     </row>
@@ -16133,7 +16133,7 @@
       </c>
       <c r="S184" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T22:58:10Z</t>
+          <t>2026-09-18T22:43:53Z</t>
         </is>
       </c>
     </row>
@@ -16222,7 +16222,7 @@
       </c>
       <c r="S185" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T22:58:10Z</t>
+          <t>2026-09-18T22:43:53Z</t>
         </is>
       </c>
     </row>
@@ -16311,7 +16311,7 @@
       </c>
       <c r="S186" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T22:58:10Z</t>
+          <t>2026-09-18T22:43:53Z</t>
         </is>
       </c>
     </row>
@@ -16400,7 +16400,7 @@
       </c>
       <c r="S187" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T22:58:10Z</t>
+          <t>2026-09-18T22:43:53Z</t>
         </is>
       </c>
     </row>
@@ -16489,7 +16489,7 @@
       </c>
       <c r="S188" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T22:58:10Z</t>
+          <t>2026-09-18T22:43:53Z</t>
         </is>
       </c>
     </row>
@@ -16578,7 +16578,7 @@
       </c>
       <c r="S189" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T22:58:10Z</t>
+          <t>2026-09-18T22:43:53Z</t>
         </is>
       </c>
     </row>
@@ -16663,7 +16663,7 @@
       </c>
       <c r="S190" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T22:58:10Z</t>
+          <t>2026-09-18T22:43:53Z</t>
         </is>
       </c>
     </row>
@@ -16748,7 +16748,7 @@
       </c>
       <c r="S191" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T22:58:10Z</t>
+          <t>2026-09-18T22:43:53Z</t>
         </is>
       </c>
     </row>
@@ -16833,7 +16833,7 @@
       </c>
       <c r="S192" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T22:58:10Z</t>
+          <t>2026-09-18T22:43:53Z</t>
         </is>
       </c>
     </row>
@@ -16918,7 +16918,7 @@
       </c>
       <c r="S193" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T22:58:10Z</t>
+          <t>2026-09-18T22:43:53Z</t>
         </is>
       </c>
     </row>
@@ -17003,7 +17003,7 @@
       </c>
       <c r="S194" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T22:58:10Z</t>
+          <t>2026-09-18T22:43:53Z</t>
         </is>
       </c>
     </row>
@@ -17088,7 +17088,7 @@
       </c>
       <c r="S195" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T22:58:10Z</t>
+          <t>2026-09-18T22:43:53Z</t>
         </is>
       </c>
     </row>
@@ -17173,7 +17173,7 @@
       </c>
       <c r="S196" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T22:58:10Z</t>
+          <t>2026-09-18T22:43:53Z</t>
         </is>
       </c>
     </row>
@@ -17258,7 +17258,7 @@
       </c>
       <c r="S197" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T22:58:10Z</t>
+          <t>2026-09-18T22:43:53Z</t>
         </is>
       </c>
     </row>
@@ -17343,7 +17343,7 @@
       </c>
       <c r="S198" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T22:58:10Z</t>
+          <t>2026-09-18T22:43:53Z</t>
         </is>
       </c>
     </row>
@@ -17428,7 +17428,7 @@
       </c>
       <c r="S199" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T22:58:10Z</t>
+          <t>2026-09-18T22:43:53Z</t>
         </is>
       </c>
     </row>
@@ -17513,7 +17513,7 @@
       </c>
       <c r="S200" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T22:58:10Z</t>
+          <t>2026-09-18T22:43:53Z</t>
         </is>
       </c>
     </row>
@@ -17598,7 +17598,7 @@
       </c>
       <c r="S201" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T22:58:10Z</t>
+          <t>2026-09-18T22:43:53Z</t>
         </is>
       </c>
     </row>
@@ -17683,7 +17683,7 @@
       </c>
       <c r="S202" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T22:58:10Z</t>
+          <t>2026-09-18T22:43:53Z</t>
         </is>
       </c>
     </row>
@@ -17768,7 +17768,7 @@
       </c>
       <c r="S203" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T22:58:10Z</t>
+          <t>2026-09-18T22:43:53Z</t>
         </is>
       </c>
     </row>
@@ -17853,7 +17853,7 @@
       </c>
       <c r="S204" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T22:58:10Z</t>
+          <t>2026-09-18T22:43:53Z</t>
         </is>
       </c>
     </row>
@@ -17938,7 +17938,7 @@
       </c>
       <c r="S205" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T22:58:10Z</t>
+          <t>2026-09-18T22:43:53Z</t>
         </is>
       </c>
     </row>
@@ -18023,7 +18023,7 @@
       </c>
       <c r="S206" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T22:58:10Z</t>
+          <t>2026-09-18T22:43:53Z</t>
         </is>
       </c>
     </row>
@@ -18108,7 +18108,7 @@
       </c>
       <c r="S207" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T22:58:10Z</t>
+          <t>2026-09-18T22:43:53Z</t>
         </is>
       </c>
     </row>
@@ -18193,7 +18193,7 @@
       </c>
       <c r="S208" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T22:58:10Z</t>
+          <t>2026-09-18T22:43:53Z</t>
         </is>
       </c>
     </row>
@@ -18278,7 +18278,7 @@
       </c>
       <c r="S209" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T22:58:10Z</t>
+          <t>2026-09-18T22:43:53Z</t>
         </is>
       </c>
     </row>
@@ -18363,7 +18363,7 @@
       </c>
       <c r="S210" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T22:58:10Z</t>
+          <t>2026-09-18T22:43:53Z</t>
         </is>
       </c>
     </row>
@@ -18452,7 +18452,7 @@
       </c>
       <c r="S211" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T22:58:10Z</t>
+          <t>2026-09-18T22:43:53Z</t>
         </is>
       </c>
     </row>
@@ -18541,7 +18541,7 @@
       </c>
       <c r="S212" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T22:58:10Z</t>
+          <t>2026-09-18T22:43:53Z</t>
         </is>
       </c>
     </row>
@@ -18626,7 +18626,7 @@
       </c>
       <c r="S213" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T22:58:10Z</t>
+          <t>2026-09-18T22:43:53Z</t>
         </is>
       </c>
     </row>
@@ -18715,7 +18715,7 @@
       </c>
       <c r="S214" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T22:58:10Z</t>
+          <t>2026-09-18T22:43:53Z</t>
         </is>
       </c>
     </row>
@@ -18804,7 +18804,7 @@
       </c>
       <c r="S215" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T22:58:10Z</t>
+          <t>2026-09-18T22:43:53Z</t>
         </is>
       </c>
     </row>
@@ -18889,7 +18889,7 @@
       </c>
       <c r="S216" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T22:58:10Z</t>
+          <t>2026-09-18T22:43:53Z</t>
         </is>
       </c>
     </row>
@@ -18978,7 +18978,7 @@
       </c>
       <c r="S217" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T22:58:10Z</t>
+          <t>2026-09-18T22:43:53Z</t>
         </is>
       </c>
     </row>
@@ -19067,7 +19067,7 @@
       </c>
       <c r="S218" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T22:58:10Z</t>
+          <t>2026-09-18T22:43:53Z</t>
         </is>
       </c>
     </row>
@@ -19152,7 +19152,7 @@
       </c>
       <c r="S219" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T22:58:10Z</t>
+          <t>2026-09-18T22:43:53Z</t>
         </is>
       </c>
     </row>
@@ -19241,7 +19241,7 @@
       </c>
       <c r="S220" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T22:58:10Z</t>
+          <t>2026-09-18T22:43:53Z</t>
         </is>
       </c>
     </row>
@@ -19330,7 +19330,7 @@
       </c>
       <c r="S221" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T22:58:10Z</t>
+          <t>2026-09-18T22:43:53Z</t>
         </is>
       </c>
     </row>
@@ -19415,7 +19415,7 @@
       </c>
       <c r="S222" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T22:58:10Z</t>
+          <t>2026-09-18T22:43:53Z</t>
         </is>
       </c>
     </row>
@@ -19504,7 +19504,7 @@
       </c>
       <c r="S223" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T22:58:10Z</t>
+          <t>2026-09-18T22:43:53Z</t>
         </is>
       </c>
     </row>
@@ -19593,7 +19593,7 @@
       </c>
       <c r="S224" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T22:58:10Z</t>
+          <t>2026-09-18T22:43:53Z</t>
         </is>
       </c>
     </row>
@@ -19678,7 +19678,7 @@
       </c>
       <c r="S225" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T22:58:10Z</t>
+          <t>2026-09-18T22:43:53Z</t>
         </is>
       </c>
     </row>
@@ -19767,7 +19767,7 @@
       </c>
       <c r="S226" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T22:58:10Z</t>
+          <t>2026-09-18T22:43:53Z</t>
         </is>
       </c>
     </row>
@@ -19856,7 +19856,7 @@
       </c>
       <c r="S227" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T22:58:10Z</t>
+          <t>2026-09-18T22:43:53Z</t>
         </is>
       </c>
     </row>
@@ -19941,7 +19941,7 @@
       </c>
       <c r="S228" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T22:58:10Z</t>
+          <t>2026-09-18T22:43:53Z</t>
         </is>
       </c>
     </row>
@@ -20030,7 +20030,7 @@
       </c>
       <c r="S229" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T22:58:10Z</t>
+          <t>2026-09-18T22:43:53Z</t>
         </is>
       </c>
     </row>
@@ -20119,7 +20119,7 @@
       </c>
       <c r="S230" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T22:58:10Z</t>
+          <t>2026-09-18T22:43:53Z</t>
         </is>
       </c>
     </row>
@@ -20204,7 +20204,7 @@
       </c>
       <c r="S231" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T22:58:10Z</t>
+          <t>2026-09-18T22:43:53Z</t>
         </is>
       </c>
     </row>
@@ -20293,7 +20293,7 @@
       </c>
       <c r="S232" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T22:58:10Z</t>
+          <t>2026-09-18T22:43:53Z</t>
         </is>
       </c>
     </row>
@@ -20382,7 +20382,7 @@
       </c>
       <c r="S233" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T22:58:10Z</t>
+          <t>2026-09-18T22:43:53Z</t>
         </is>
       </c>
     </row>
@@ -20467,7 +20467,7 @@
       </c>
       <c r="S234" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T22:58:10Z</t>
+          <t>2026-09-18T22:43:53Z</t>
         </is>
       </c>
     </row>
@@ -20556,7 +20556,7 @@
       </c>
       <c r="S235" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T22:58:10Z</t>
+          <t>2026-09-18T22:43:53Z</t>
         </is>
       </c>
     </row>
@@ -20645,7 +20645,7 @@
       </c>
       <c r="S236" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T22:58:10Z</t>
+          <t>2026-09-18T22:43:53Z</t>
         </is>
       </c>
     </row>
@@ -20730,7 +20730,7 @@
       </c>
       <c r="S237" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T22:58:10Z</t>
+          <t>2026-09-18T22:43:53Z</t>
         </is>
       </c>
     </row>
@@ -20819,7 +20819,7 @@
       </c>
       <c r="S238" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T22:58:10Z</t>
+          <t>2026-09-18T22:43:53Z</t>
         </is>
       </c>
     </row>
@@ -20908,7 +20908,7 @@
       </c>
       <c r="S239" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T22:58:10Z</t>
+          <t>2026-09-18T22:43:53Z</t>
         </is>
       </c>
     </row>
@@ -20997,7 +20997,7 @@
       </c>
       <c r="S240" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T22:58:10Z</t>
+          <t>2026-09-18T22:43:53Z</t>
         </is>
       </c>
     </row>
@@ -21086,7 +21086,7 @@
       </c>
       <c r="S241" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T22:58:10Z</t>
+          <t>2026-09-18T22:43:53Z</t>
         </is>
       </c>
     </row>
@@ -21175,7 +21175,7 @@
       </c>
       <c r="S242" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T22:58:10Z</t>
+          <t>2026-09-18T22:43:53Z</t>
         </is>
       </c>
     </row>
@@ -21264,7 +21264,7 @@
       </c>
       <c r="S243" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T22:58:10Z</t>
+          <t>2026-09-18T22:43:53Z</t>
         </is>
       </c>
     </row>
@@ -21353,7 +21353,7 @@
       </c>
       <c r="S244" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T22:58:10Z</t>
+          <t>2026-09-18T22:43:53Z</t>
         </is>
       </c>
     </row>
@@ -21442,7 +21442,7 @@
       </c>
       <c r="S245" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T22:58:10Z</t>
+          <t>2026-09-18T22:43:53Z</t>
         </is>
       </c>
     </row>
@@ -21531,7 +21531,7 @@
       </c>
       <c r="S246" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T22:58:10Z</t>
+          <t>2026-09-18T22:43:53Z</t>
         </is>
       </c>
     </row>
@@ -21620,7 +21620,7 @@
       </c>
       <c r="S247" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T22:58:10Z</t>
+          <t>2026-09-18T22:43:53Z</t>
         </is>
       </c>
     </row>
@@ -21709,7 +21709,7 @@
       </c>
       <c r="S248" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T22:58:10Z</t>
+          <t>2026-09-18T22:43:53Z</t>
         </is>
       </c>
     </row>
@@ -21798,7 +21798,7 @@
       </c>
       <c r="S249" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T22:58:10Z</t>
+          <t>2026-09-18T22:43:53Z</t>
         </is>
       </c>
     </row>
@@ -21887,7 +21887,7 @@
       </c>
       <c r="S250" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T22:58:10Z</t>
+          <t>2026-09-18T22:43:53Z</t>
         </is>
       </c>
     </row>
@@ -22019,7 +22019,7 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T22:58:10Z</t>
+          <t>2026-09-18T22:43:53Z</t>
         </is>
       </c>
     </row>
@@ -22099,7 +22099,7 @@
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>{"dataset_id": "bcv_pib_sector_institucional_anual", "title": "Producto interno bruto por sector institucional anual", "table": "Variaciones porcentuales", "source_file": "5_2_1_si_anual.xlsx", "base": "2007", "price_type": "Precios constantes", "measure": "Variación porcentual interanual", "frequency": "Anual", "period": "2025", "year": 2025, "quarter": null, "classification": "Sector institucional", "component": "Impuestos netos sobre los productos", "value": 10.600260421283764, "unit": "Porcentaje", "status": "Preliminar", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/cuentas_macroeconomicas/5_2_1_si_anual.xlsx", "fetched_at": "2026-09-17T22:58:10Z"}</t>
+          <t>{"dataset_id": "bcv_pib_sector_institucional_anual", "title": "Producto interno bruto por sector institucional anual", "table": "Variaciones porcentuales", "source_file": "5_2_1_si_anual.xlsx", "base": "2007", "price_type": "Precios constantes", "measure": "Variación porcentual interanual", "frequency": "Anual", "period": "2025", "year": 2025, "quarter": null, "classification": "Sector institucional", "component": "Impuestos netos sobre los productos", "value": 10.600260421283764, "unit": "Porcentaje", "status": "Preliminar", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/cuentas_macroeconomicas/5_2_1_si_anual.xlsx", "fetched_at": "2026-09-18T22:43:53Z"}</t>
         </is>
       </c>
     </row>

--- a/assets/data/bcv/excel/ove_bcv_pib_sector_institucional_anual.xlsx
+++ b/assets/data/bcv/excel/ove_bcv_pib_sector_institucional_anual.xlsx
@@ -736,7 +736,7 @@
       </c>
       <c r="S7" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18T22:43:53Z</t>
+          <t>2026-09-19T22:23:12Z</t>
         </is>
       </c>
     </row>
@@ -821,7 +821,7 @@
       </c>
       <c r="S8" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18T22:43:53Z</t>
+          <t>2026-09-19T22:23:12Z</t>
         </is>
       </c>
     </row>
@@ -906,7 +906,7 @@
       </c>
       <c r="S9" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18T22:43:53Z</t>
+          <t>2026-09-19T22:23:12Z</t>
         </is>
       </c>
     </row>
@@ -991,7 +991,7 @@
       </c>
       <c r="S10" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18T22:43:53Z</t>
+          <t>2026-09-19T22:23:12Z</t>
         </is>
       </c>
     </row>
@@ -1076,7 +1076,7 @@
       </c>
       <c r="S11" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18T22:43:53Z</t>
+          <t>2026-09-19T22:23:12Z</t>
         </is>
       </c>
     </row>
@@ -1161,7 +1161,7 @@
       </c>
       <c r="S12" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18T22:43:53Z</t>
+          <t>2026-09-19T22:23:12Z</t>
         </is>
       </c>
     </row>
@@ -1246,7 +1246,7 @@
       </c>
       <c r="S13" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18T22:43:53Z</t>
+          <t>2026-09-19T22:23:12Z</t>
         </is>
       </c>
     </row>
@@ -1331,7 +1331,7 @@
       </c>
       <c r="S14" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18T22:43:53Z</t>
+          <t>2026-09-19T22:23:12Z</t>
         </is>
       </c>
     </row>
@@ -1416,7 +1416,7 @@
       </c>
       <c r="S15" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18T22:43:53Z</t>
+          <t>2026-09-19T22:23:12Z</t>
         </is>
       </c>
     </row>
@@ -1501,7 +1501,7 @@
       </c>
       <c r="S16" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18T22:43:53Z</t>
+          <t>2026-09-19T22:23:12Z</t>
         </is>
       </c>
     </row>
@@ -1586,7 +1586,7 @@
       </c>
       <c r="S17" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18T22:43:53Z</t>
+          <t>2026-09-19T22:23:12Z</t>
         </is>
       </c>
     </row>
@@ -1671,7 +1671,7 @@
       </c>
       <c r="S18" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18T22:43:53Z</t>
+          <t>2026-09-19T22:23:12Z</t>
         </is>
       </c>
     </row>
@@ -1756,7 +1756,7 @@
       </c>
       <c r="S19" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18T22:43:53Z</t>
+          <t>2026-09-19T22:23:12Z</t>
         </is>
       </c>
     </row>
@@ -1841,7 +1841,7 @@
       </c>
       <c r="S20" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18T22:43:53Z</t>
+          <t>2026-09-19T22:23:12Z</t>
         </is>
       </c>
     </row>
@@ -1926,7 +1926,7 @@
       </c>
       <c r="S21" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18T22:43:53Z</t>
+          <t>2026-09-19T22:23:12Z</t>
         </is>
       </c>
     </row>
@@ -2011,7 +2011,7 @@
       </c>
       <c r="S22" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18T22:43:53Z</t>
+          <t>2026-09-19T22:23:12Z</t>
         </is>
       </c>
     </row>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="S23" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18T22:43:53Z</t>
+          <t>2026-09-19T22:23:12Z</t>
         </is>
       </c>
     </row>
@@ -2181,7 +2181,7 @@
       </c>
       <c r="S24" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18T22:43:53Z</t>
+          <t>2026-09-19T22:23:12Z</t>
         </is>
       </c>
     </row>
@@ -2266,7 +2266,7 @@
       </c>
       <c r="S25" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18T22:43:53Z</t>
+          <t>2026-09-19T22:23:12Z</t>
         </is>
       </c>
     </row>
@@ -2351,7 +2351,7 @@
       </c>
       <c r="S26" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18T22:43:53Z</t>
+          <t>2026-09-19T22:23:12Z</t>
         </is>
       </c>
     </row>
@@ -2436,7 +2436,7 @@
       </c>
       <c r="S27" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18T22:43:53Z</t>
+          <t>2026-09-19T22:23:12Z</t>
         </is>
       </c>
     </row>
@@ -2525,7 +2525,7 @@
       </c>
       <c r="S28" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18T22:43:53Z</t>
+          <t>2026-09-19T22:23:12Z</t>
         </is>
       </c>
     </row>
@@ -2614,7 +2614,7 @@
       </c>
       <c r="S29" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18T22:43:53Z</t>
+          <t>2026-09-19T22:23:12Z</t>
         </is>
       </c>
     </row>
@@ -2699,7 +2699,7 @@
       </c>
       <c r="S30" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18T22:43:53Z</t>
+          <t>2026-09-19T22:23:12Z</t>
         </is>
       </c>
     </row>
@@ -2788,7 +2788,7 @@
       </c>
       <c r="S31" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18T22:43:53Z</t>
+          <t>2026-09-19T22:23:12Z</t>
         </is>
       </c>
     </row>
@@ -2877,7 +2877,7 @@
       </c>
       <c r="S32" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18T22:43:53Z</t>
+          <t>2026-09-19T22:23:12Z</t>
         </is>
       </c>
     </row>
@@ -2962,7 +2962,7 @@
       </c>
       <c r="S33" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18T22:43:53Z</t>
+          <t>2026-09-19T22:23:12Z</t>
         </is>
       </c>
     </row>
@@ -3051,7 +3051,7 @@
       </c>
       <c r="S34" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18T22:43:53Z</t>
+          <t>2026-09-19T22:23:12Z</t>
         </is>
       </c>
     </row>
@@ -3140,7 +3140,7 @@
       </c>
       <c r="S35" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18T22:43:53Z</t>
+          <t>2026-09-19T22:23:12Z</t>
         </is>
       </c>
     </row>
@@ -3225,7 +3225,7 @@
       </c>
       <c r="S36" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18T22:43:53Z</t>
+          <t>2026-09-19T22:23:12Z</t>
         </is>
       </c>
     </row>
@@ -3314,7 +3314,7 @@
       </c>
       <c r="S37" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18T22:43:53Z</t>
+          <t>2026-09-19T22:23:12Z</t>
         </is>
       </c>
     </row>
@@ -3403,7 +3403,7 @@
       </c>
       <c r="S38" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18T22:43:53Z</t>
+          <t>2026-09-19T22:23:12Z</t>
         </is>
       </c>
     </row>
@@ -3488,7 +3488,7 @@
       </c>
       <c r="S39" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18T22:43:53Z</t>
+          <t>2026-09-19T22:23:12Z</t>
         </is>
       </c>
     </row>
@@ -3577,7 +3577,7 @@
       </c>
       <c r="S40" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18T22:43:53Z</t>
+          <t>2026-09-19T22:23:12Z</t>
         </is>
       </c>
     </row>
@@ -3666,7 +3666,7 @@
       </c>
       <c r="S41" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18T22:43:53Z</t>
+          <t>2026-09-19T22:23:12Z</t>
         </is>
       </c>
     </row>
@@ -3751,7 +3751,7 @@
       </c>
       <c r="S42" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18T22:43:53Z</t>
+          <t>2026-09-19T22:23:12Z</t>
         </is>
       </c>
     </row>
@@ -3840,7 +3840,7 @@
       </c>
       <c r="S43" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18T22:43:53Z</t>
+          <t>2026-09-19T22:23:12Z</t>
         </is>
       </c>
     </row>
@@ -3929,7 +3929,7 @@
       </c>
       <c r="S44" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18T22:43:53Z</t>
+          <t>2026-09-19T22:23:12Z</t>
         </is>
       </c>
     </row>
@@ -4014,7 +4014,7 @@
       </c>
       <c r="S45" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18T22:43:53Z</t>
+          <t>2026-09-19T22:23:12Z</t>
         </is>
       </c>
     </row>
@@ -4103,7 +4103,7 @@
       </c>
       <c r="S46" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18T22:43:53Z</t>
+          <t>2026-09-19T22:23:12Z</t>
         </is>
       </c>
     </row>
@@ -4192,7 +4192,7 @@
       </c>
       <c r="S47" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18T22:43:53Z</t>
+          <t>2026-09-19T22:23:12Z</t>
         </is>
       </c>
     </row>
@@ -4277,7 +4277,7 @@
       </c>
       <c r="S48" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18T22:43:53Z</t>
+          <t>2026-09-19T22:23:12Z</t>
         </is>
       </c>
     </row>
@@ -4366,7 +4366,7 @@
       </c>
       <c r="S49" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18T22:43:53Z</t>
+          <t>2026-09-19T22:23:12Z</t>
         </is>
       </c>
     </row>
@@ -4455,7 +4455,7 @@
       </c>
       <c r="S50" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18T22:43:53Z</t>
+          <t>2026-09-19T22:23:12Z</t>
         </is>
       </c>
     </row>
@@ -4540,7 +4540,7 @@
       </c>
       <c r="S51" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18T22:43:53Z</t>
+          <t>2026-09-19T22:23:12Z</t>
         </is>
       </c>
     </row>
@@ -4629,7 +4629,7 @@
       </c>
       <c r="S52" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18T22:43:53Z</t>
+          <t>2026-09-19T22:23:12Z</t>
         </is>
       </c>
     </row>
@@ -4718,7 +4718,7 @@
       </c>
       <c r="S53" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18T22:43:53Z</t>
+          <t>2026-09-19T22:23:12Z</t>
         </is>
       </c>
     </row>
@@ -4803,7 +4803,7 @@
       </c>
       <c r="S54" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18T22:43:53Z</t>
+          <t>2026-09-19T22:23:12Z</t>
         </is>
       </c>
     </row>
@@ -4892,7 +4892,7 @@
       </c>
       <c r="S55" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18T22:43:53Z</t>
+          <t>2026-09-19T22:23:12Z</t>
         </is>
       </c>
     </row>
@@ -4981,7 +4981,7 @@
       </c>
       <c r="S56" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18T22:43:53Z</t>
+          <t>2026-09-19T22:23:12Z</t>
         </is>
       </c>
     </row>
@@ -5070,7 +5070,7 @@
       </c>
       <c r="S57" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18T22:43:53Z</t>
+          <t>2026-09-19T22:23:12Z</t>
         </is>
       </c>
     </row>
@@ -5159,7 +5159,7 @@
       </c>
       <c r="S58" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18T22:43:53Z</t>
+          <t>2026-09-19T22:23:12Z</t>
         </is>
       </c>
     </row>
@@ -5248,7 +5248,7 @@
       </c>
       <c r="S59" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18T22:43:53Z</t>
+          <t>2026-09-19T22:23:12Z</t>
         </is>
       </c>
     </row>
@@ -5337,7 +5337,7 @@
       </c>
       <c r="S60" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18T22:43:53Z</t>
+          <t>2026-09-19T22:23:12Z</t>
         </is>
       </c>
     </row>
@@ -5426,7 +5426,7 @@
       </c>
       <c r="S61" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18T22:43:53Z</t>
+          <t>2026-09-19T22:23:12Z</t>
         </is>
       </c>
     </row>
@@ -5515,7 +5515,7 @@
       </c>
       <c r="S62" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18T22:43:53Z</t>
+          <t>2026-09-19T22:23:12Z</t>
         </is>
       </c>
     </row>
@@ -5604,7 +5604,7 @@
       </c>
       <c r="S63" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18T22:43:53Z</t>
+          <t>2026-09-19T22:23:12Z</t>
         </is>
       </c>
     </row>
@@ -5693,7 +5693,7 @@
       </c>
       <c r="S64" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18T22:43:53Z</t>
+          <t>2026-09-19T22:23:12Z</t>
         </is>
       </c>
     </row>
@@ -5782,7 +5782,7 @@
       </c>
       <c r="S65" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18T22:43:53Z</t>
+          <t>2026-09-19T22:23:12Z</t>
         </is>
       </c>
     </row>
@@ -5871,7 +5871,7 @@
       </c>
       <c r="S66" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18T22:43:53Z</t>
+          <t>2026-09-19T22:23:12Z</t>
         </is>
       </c>
     </row>
@@ -5960,7 +5960,7 @@
       </c>
       <c r="S67" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18T22:43:53Z</t>
+          <t>2026-09-19T22:23:12Z</t>
         </is>
       </c>
     </row>
@@ -6045,7 +6045,7 @@
       </c>
       <c r="S68" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18T22:43:53Z</t>
+          <t>2026-09-19T22:23:12Z</t>
         </is>
       </c>
     </row>
@@ -6130,7 +6130,7 @@
       </c>
       <c r="S69" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18T22:43:53Z</t>
+          <t>2026-09-19T22:23:12Z</t>
         </is>
       </c>
     </row>
@@ -6215,7 +6215,7 @@
       </c>
       <c r="S70" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18T22:43:53Z</t>
+          <t>2026-09-19T22:23:12Z</t>
         </is>
       </c>
     </row>
@@ -6300,7 +6300,7 @@
       </c>
       <c r="S71" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18T22:43:53Z</t>
+          <t>2026-09-19T22:23:12Z</t>
         </is>
       </c>
     </row>
@@ -6385,7 +6385,7 @@
       </c>
       <c r="S72" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18T22:43:53Z</t>
+          <t>2026-09-19T22:23:12Z</t>
         </is>
       </c>
     </row>
@@ -6470,7 +6470,7 @@
       </c>
       <c r="S73" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18T22:43:53Z</t>
+          <t>2026-09-19T22:23:12Z</t>
         </is>
       </c>
     </row>
@@ -6555,7 +6555,7 @@
       </c>
       <c r="S74" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18T22:43:53Z</t>
+          <t>2026-09-19T22:23:12Z</t>
         </is>
       </c>
     </row>
@@ -6640,7 +6640,7 @@
       </c>
       <c r="S75" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18T22:43:53Z</t>
+          <t>2026-09-19T22:23:12Z</t>
         </is>
       </c>
     </row>
@@ -6725,7 +6725,7 @@
       </c>
       <c r="S76" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18T22:43:53Z</t>
+          <t>2026-09-19T22:23:12Z</t>
         </is>
       </c>
     </row>
@@ -6810,7 +6810,7 @@
       </c>
       <c r="S77" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18T22:43:53Z</t>
+          <t>2026-09-19T22:23:12Z</t>
         </is>
       </c>
     </row>
@@ -6895,7 +6895,7 @@
       </c>
       <c r="S78" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18T22:43:53Z</t>
+          <t>2026-09-19T22:23:12Z</t>
         </is>
       </c>
     </row>
@@ -6980,7 +6980,7 @@
       </c>
       <c r="S79" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18T22:43:53Z</t>
+          <t>2026-09-19T22:23:12Z</t>
         </is>
       </c>
     </row>
@@ -7065,7 +7065,7 @@
       </c>
       <c r="S80" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18T22:43:53Z</t>
+          <t>2026-09-19T22:23:12Z</t>
         </is>
       </c>
     </row>
@@ -7150,7 +7150,7 @@
       </c>
       <c r="S81" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18T22:43:53Z</t>
+          <t>2026-09-19T22:23:12Z</t>
         </is>
       </c>
     </row>
@@ -7235,7 +7235,7 @@
       </c>
       <c r="S82" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18T22:43:53Z</t>
+          <t>2026-09-19T22:23:12Z</t>
         </is>
       </c>
     </row>
@@ -7320,7 +7320,7 @@
       </c>
       <c r="S83" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18T22:43:53Z</t>
+          <t>2026-09-19T22:23:12Z</t>
         </is>
       </c>
     </row>
@@ -7405,7 +7405,7 @@
       </c>
       <c r="S84" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18T22:43:53Z</t>
+          <t>2026-09-19T22:23:12Z</t>
         </is>
       </c>
     </row>
@@ -7490,7 +7490,7 @@
       </c>
       <c r="S85" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18T22:43:53Z</t>
+          <t>2026-09-19T22:23:12Z</t>
         </is>
       </c>
     </row>
@@ -7575,7 +7575,7 @@
       </c>
       <c r="S86" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18T22:43:53Z</t>
+          <t>2026-09-19T22:23:12Z</t>
         </is>
       </c>
     </row>
@@ -7660,7 +7660,7 @@
       </c>
       <c r="S87" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18T22:43:53Z</t>
+          <t>2026-09-19T22:23:12Z</t>
         </is>
       </c>
     </row>
@@ -7745,7 +7745,7 @@
       </c>
       <c r="S88" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18T22:43:53Z</t>
+          <t>2026-09-19T22:23:12Z</t>
         </is>
       </c>
     </row>
@@ -7834,7 +7834,7 @@
       </c>
       <c r="S89" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18T22:43:53Z</t>
+          <t>2026-09-19T22:23:12Z</t>
         </is>
       </c>
     </row>
@@ -7923,7 +7923,7 @@
       </c>
       <c r="S90" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18T22:43:53Z</t>
+          <t>2026-09-19T22:23:12Z</t>
         </is>
       </c>
     </row>
@@ -8008,7 +8008,7 @@
       </c>
       <c r="S91" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18T22:43:53Z</t>
+          <t>2026-09-19T22:23:12Z</t>
         </is>
       </c>
     </row>
@@ -8097,7 +8097,7 @@
       </c>
       <c r="S92" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18T22:43:53Z</t>
+          <t>2026-09-19T22:23:12Z</t>
         </is>
       </c>
     </row>
@@ -8186,7 +8186,7 @@
       </c>
       <c r="S93" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18T22:43:53Z</t>
+          <t>2026-09-19T22:23:12Z</t>
         </is>
       </c>
     </row>
@@ -8271,7 +8271,7 @@
       </c>
       <c r="S94" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18T22:43:53Z</t>
+          <t>2026-09-19T22:23:12Z</t>
         </is>
       </c>
     </row>
@@ -8360,7 +8360,7 @@
       </c>
       <c r="S95" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18T22:43:53Z</t>
+          <t>2026-09-19T22:23:12Z</t>
         </is>
       </c>
     </row>
@@ -8449,7 +8449,7 @@
       </c>
       <c r="S96" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18T22:43:53Z</t>
+          <t>2026-09-19T22:23:12Z</t>
         </is>
       </c>
     </row>
@@ -8534,7 +8534,7 @@
       </c>
       <c r="S97" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18T22:43:53Z</t>
+          <t>2026-09-19T22:23:12Z</t>
         </is>
       </c>
     </row>
@@ -8623,7 +8623,7 @@
       </c>
       <c r="S98" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18T22:43:53Z</t>
+          <t>2026-09-19T22:23:12Z</t>
         </is>
       </c>
     </row>
@@ -8712,7 +8712,7 @@
       </c>
       <c r="S99" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18T22:43:53Z</t>
+          <t>2026-09-19T22:23:12Z</t>
         </is>
       </c>
     </row>
@@ -8797,7 +8797,7 @@
       </c>
       <c r="S100" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18T22:43:53Z</t>
+          <t>2026-09-19T22:23:12Z</t>
         </is>
       </c>
     </row>
@@ -8886,7 +8886,7 @@
       </c>
       <c r="S101" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18T22:43:53Z</t>
+          <t>2026-09-19T22:23:12Z</t>
         </is>
       </c>
     </row>
@@ -8975,7 +8975,7 @@
       </c>
       <c r="S102" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18T22:43:53Z</t>
+          <t>2026-09-19T22:23:12Z</t>
         </is>
       </c>
     </row>
@@ -9060,7 +9060,7 @@
       </c>
       <c r="S103" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18T22:43:53Z</t>
+          <t>2026-09-19T22:23:12Z</t>
         </is>
       </c>
     </row>
@@ -9149,7 +9149,7 @@
       </c>
       <c r="S104" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18T22:43:53Z</t>
+          <t>2026-09-19T22:23:12Z</t>
         </is>
       </c>
     </row>
@@ -9238,7 +9238,7 @@
       </c>
       <c r="S105" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18T22:43:53Z</t>
+          <t>2026-09-19T22:23:12Z</t>
         </is>
       </c>
     </row>
@@ -9323,7 +9323,7 @@
       </c>
       <c r="S106" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18T22:43:53Z</t>
+          <t>2026-09-19T22:23:12Z</t>
         </is>
       </c>
     </row>
@@ -9412,7 +9412,7 @@
       </c>
       <c r="S107" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18T22:43:53Z</t>
+          <t>2026-09-19T22:23:12Z</t>
         </is>
       </c>
     </row>
@@ -9501,7 +9501,7 @@
       </c>
       <c r="S108" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18T22:43:53Z</t>
+          <t>2026-09-19T22:23:12Z</t>
         </is>
       </c>
     </row>
@@ -9586,7 +9586,7 @@
       </c>
       <c r="S109" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18T22:43:53Z</t>
+          <t>2026-09-19T22:23:12Z</t>
         </is>
       </c>
     </row>
@@ -9675,7 +9675,7 @@
       </c>
       <c r="S110" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18T22:43:53Z</t>
+          <t>2026-09-19T22:23:12Z</t>
         </is>
       </c>
     </row>
@@ -9764,7 +9764,7 @@
       </c>
       <c r="S111" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18T22:43:53Z</t>
+          <t>2026-09-19T22:23:12Z</t>
         </is>
       </c>
     </row>
@@ -9849,7 +9849,7 @@
       </c>
       <c r="S112" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18T22:43:53Z</t>
+          <t>2026-09-19T22:23:12Z</t>
         </is>
       </c>
     </row>
@@ -9938,7 +9938,7 @@
       </c>
       <c r="S113" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18T22:43:53Z</t>
+          <t>2026-09-19T22:23:12Z</t>
         </is>
       </c>
     </row>
@@ -10027,7 +10027,7 @@
       </c>
       <c r="S114" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18T22:43:53Z</t>
+          <t>2026-09-19T22:23:12Z</t>
         </is>
       </c>
     </row>
@@ -10112,7 +10112,7 @@
       </c>
       <c r="S115" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18T22:43:53Z</t>
+          <t>2026-09-19T22:23:12Z</t>
         </is>
       </c>
     </row>
@@ -10201,7 +10201,7 @@
       </c>
       <c r="S116" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18T22:43:53Z</t>
+          <t>2026-09-19T22:23:12Z</t>
         </is>
       </c>
     </row>
@@ -10290,7 +10290,7 @@
       </c>
       <c r="S117" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18T22:43:53Z</t>
+          <t>2026-09-19T22:23:12Z</t>
         </is>
       </c>
     </row>
@@ -10379,7 +10379,7 @@
       </c>
       <c r="S118" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18T22:43:53Z</t>
+          <t>2026-09-19T22:23:12Z</t>
         </is>
       </c>
     </row>
@@ -10468,7 +10468,7 @@
       </c>
       <c r="S119" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18T22:43:53Z</t>
+          <t>2026-09-19T22:23:12Z</t>
         </is>
       </c>
     </row>
@@ -10557,7 +10557,7 @@
       </c>
       <c r="S120" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18T22:43:53Z</t>
+          <t>2026-09-19T22:23:12Z</t>
         </is>
       </c>
     </row>
@@ -10646,7 +10646,7 @@
       </c>
       <c r="S121" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18T22:43:53Z</t>
+          <t>2026-09-19T22:23:12Z</t>
         </is>
       </c>
     </row>
@@ -10735,7 +10735,7 @@
       </c>
       <c r="S122" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18T22:43:53Z</t>
+          <t>2026-09-19T22:23:12Z</t>
         </is>
       </c>
     </row>
@@ -10824,7 +10824,7 @@
       </c>
       <c r="S123" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18T22:43:53Z</t>
+          <t>2026-09-19T22:23:12Z</t>
         </is>
       </c>
     </row>
@@ -10913,7 +10913,7 @@
       </c>
       <c r="S124" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18T22:43:53Z</t>
+          <t>2026-09-19T22:23:12Z</t>
         </is>
       </c>
     </row>
@@ -11002,7 +11002,7 @@
       </c>
       <c r="S125" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18T22:43:53Z</t>
+          <t>2026-09-19T22:23:12Z</t>
         </is>
       </c>
     </row>
@@ -11091,7 +11091,7 @@
       </c>
       <c r="S126" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18T22:43:53Z</t>
+          <t>2026-09-19T22:23:12Z</t>
         </is>
       </c>
     </row>
@@ -11180,7 +11180,7 @@
       </c>
       <c r="S127" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18T22:43:53Z</t>
+          <t>2026-09-19T22:23:12Z</t>
         </is>
       </c>
     </row>
@@ -11269,7 +11269,7 @@
       </c>
       <c r="S128" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18T22:43:53Z</t>
+          <t>2026-09-19T22:23:12Z</t>
         </is>
       </c>
     </row>
@@ -11354,7 +11354,7 @@
       </c>
       <c r="S129" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18T22:43:53Z</t>
+          <t>2026-09-19T22:23:12Z</t>
         </is>
       </c>
     </row>
@@ -11439,7 +11439,7 @@
       </c>
       <c r="S130" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18T22:43:53Z</t>
+          <t>2026-09-19T22:23:12Z</t>
         </is>
       </c>
     </row>
@@ -11524,7 +11524,7 @@
       </c>
       <c r="S131" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18T22:43:53Z</t>
+          <t>2026-09-19T22:23:12Z</t>
         </is>
       </c>
     </row>
@@ -11609,7 +11609,7 @@
       </c>
       <c r="S132" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18T22:43:53Z</t>
+          <t>2026-09-19T22:23:12Z</t>
         </is>
       </c>
     </row>
@@ -11694,7 +11694,7 @@
       </c>
       <c r="S133" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18T22:43:53Z</t>
+          <t>2026-09-19T22:23:12Z</t>
         </is>
       </c>
     </row>
@@ -11779,7 +11779,7 @@
       </c>
       <c r="S134" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18T22:43:53Z</t>
+          <t>2026-09-19T22:23:12Z</t>
         </is>
       </c>
     </row>
@@ -11864,7 +11864,7 @@
       </c>
       <c r="S135" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18T22:43:53Z</t>
+          <t>2026-09-19T22:23:12Z</t>
         </is>
       </c>
     </row>
@@ -11949,7 +11949,7 @@
       </c>
       <c r="S136" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18T22:43:53Z</t>
+          <t>2026-09-19T22:23:12Z</t>
         </is>
       </c>
     </row>
@@ -12034,7 +12034,7 @@
       </c>
       <c r="S137" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18T22:43:53Z</t>
+          <t>2026-09-19T22:23:12Z</t>
         </is>
       </c>
     </row>
@@ -12119,7 +12119,7 @@
       </c>
       <c r="S138" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18T22:43:53Z</t>
+          <t>2026-09-19T22:23:12Z</t>
         </is>
       </c>
     </row>
@@ -12204,7 +12204,7 @@
       </c>
       <c r="S139" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18T22:43:53Z</t>
+          <t>2026-09-19T22:23:12Z</t>
         </is>
       </c>
     </row>
@@ -12289,7 +12289,7 @@
       </c>
       <c r="S140" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18T22:43:53Z</t>
+          <t>2026-09-19T22:23:12Z</t>
         </is>
       </c>
     </row>
@@ -12374,7 +12374,7 @@
       </c>
       <c r="S141" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18T22:43:53Z</t>
+          <t>2026-09-19T22:23:12Z</t>
         </is>
       </c>
     </row>
@@ -12459,7 +12459,7 @@
       </c>
       <c r="S142" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18T22:43:53Z</t>
+          <t>2026-09-19T22:23:12Z</t>
         </is>
       </c>
     </row>
@@ -12544,7 +12544,7 @@
       </c>
       <c r="S143" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18T22:43:53Z</t>
+          <t>2026-09-19T22:23:12Z</t>
         </is>
       </c>
     </row>
@@ -12629,7 +12629,7 @@
       </c>
       <c r="S144" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18T22:43:53Z</t>
+          <t>2026-09-19T22:23:12Z</t>
         </is>
       </c>
     </row>
@@ -12714,7 +12714,7 @@
       </c>
       <c r="S145" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18T22:43:53Z</t>
+          <t>2026-09-19T22:23:12Z</t>
         </is>
       </c>
     </row>
@@ -12799,7 +12799,7 @@
       </c>
       <c r="S146" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18T22:43:53Z</t>
+          <t>2026-09-19T22:23:12Z</t>
         </is>
       </c>
     </row>
@@ -12884,7 +12884,7 @@
       </c>
       <c r="S147" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18T22:43:53Z</t>
+          <t>2026-09-19T22:23:12Z</t>
         </is>
       </c>
     </row>
@@ -12969,7 +12969,7 @@
       </c>
       <c r="S148" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18T22:43:53Z</t>
+          <t>2026-09-19T22:23:12Z</t>
         </is>
       </c>
     </row>
@@ -13054,7 +13054,7 @@
       </c>
       <c r="S149" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18T22:43:53Z</t>
+          <t>2026-09-19T22:23:12Z</t>
         </is>
       </c>
     </row>
@@ -13143,7 +13143,7 @@
       </c>
       <c r="S150" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18T22:43:53Z</t>
+          <t>2026-09-19T22:23:12Z</t>
         </is>
       </c>
     </row>
@@ -13232,7 +13232,7 @@
       </c>
       <c r="S151" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18T22:43:53Z</t>
+          <t>2026-09-19T22:23:12Z</t>
         </is>
       </c>
     </row>
@@ -13317,7 +13317,7 @@
       </c>
       <c r="S152" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18T22:43:53Z</t>
+          <t>2026-09-19T22:23:12Z</t>
         </is>
       </c>
     </row>
@@ -13406,7 +13406,7 @@
       </c>
       <c r="S153" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18T22:43:53Z</t>
+          <t>2026-09-19T22:23:12Z</t>
         </is>
       </c>
     </row>
@@ -13495,7 +13495,7 @@
       </c>
       <c r="S154" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18T22:43:53Z</t>
+          <t>2026-09-19T22:23:12Z</t>
         </is>
       </c>
     </row>
@@ -13580,7 +13580,7 @@
       </c>
       <c r="S155" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18T22:43:53Z</t>
+          <t>2026-09-19T22:23:12Z</t>
         </is>
       </c>
     </row>
@@ -13669,7 +13669,7 @@
       </c>
       <c r="S156" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18T22:43:53Z</t>
+          <t>2026-09-19T22:23:12Z</t>
         </is>
       </c>
     </row>
@@ -13758,7 +13758,7 @@
       </c>
       <c r="S157" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18T22:43:53Z</t>
+          <t>2026-09-19T22:23:12Z</t>
         </is>
       </c>
     </row>
@@ -13843,7 +13843,7 @@
       </c>
       <c r="S158" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18T22:43:53Z</t>
+          <t>2026-09-19T22:23:12Z</t>
         </is>
       </c>
     </row>
@@ -13932,7 +13932,7 @@
       </c>
       <c r="S159" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18T22:43:53Z</t>
+          <t>2026-09-19T22:23:12Z</t>
         </is>
       </c>
     </row>
@@ -14021,7 +14021,7 @@
       </c>
       <c r="S160" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18T22:43:53Z</t>
+          <t>2026-09-19T22:23:12Z</t>
         </is>
       </c>
     </row>
@@ -14106,7 +14106,7 @@
       </c>
       <c r="S161" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18T22:43:53Z</t>
+          <t>2026-09-19T22:23:12Z</t>
         </is>
       </c>
     </row>
@@ -14195,7 +14195,7 @@
       </c>
       <c r="S162" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18T22:43:53Z</t>
+          <t>2026-09-19T22:23:12Z</t>
         </is>
       </c>
     </row>
@@ -14284,7 +14284,7 @@
       </c>
       <c r="S163" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18T22:43:53Z</t>
+          <t>2026-09-19T22:23:12Z</t>
         </is>
       </c>
     </row>
@@ -14369,7 +14369,7 @@
       </c>
       <c r="S164" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18T22:43:53Z</t>
+          <t>2026-09-19T22:23:12Z</t>
         </is>
       </c>
     </row>
@@ -14458,7 +14458,7 @@
       </c>
       <c r="S165" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18T22:43:53Z</t>
+          <t>2026-09-19T22:23:12Z</t>
         </is>
       </c>
     </row>
@@ -14547,7 +14547,7 @@
       </c>
       <c r="S166" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18T22:43:53Z</t>
+          <t>2026-09-19T22:23:12Z</t>
         </is>
       </c>
     </row>
@@ -14632,7 +14632,7 @@
       </c>
       <c r="S167" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18T22:43:53Z</t>
+          <t>2026-09-19T22:23:12Z</t>
         </is>
       </c>
     </row>
@@ -14721,7 +14721,7 @@
       </c>
       <c r="S168" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18T22:43:53Z</t>
+          <t>2026-09-19T22:23:12Z</t>
         </is>
       </c>
     </row>
@@ -14810,7 +14810,7 @@
       </c>
       <c r="S169" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18T22:43:53Z</t>
+          <t>2026-09-19T22:23:12Z</t>
         </is>
       </c>
     </row>
@@ -14895,7 +14895,7 @@
       </c>
       <c r="S170" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18T22:43:53Z</t>
+          <t>2026-09-19T22:23:12Z</t>
         </is>
       </c>
     </row>
@@ -14984,7 +14984,7 @@
       </c>
       <c r="S171" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18T22:43:53Z</t>
+          <t>2026-09-19T22:23:12Z</t>
         </is>
       </c>
     </row>
@@ -15073,7 +15073,7 @@
       </c>
       <c r="S172" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18T22:43:53Z</t>
+          <t>2026-09-19T22:23:12Z</t>
         </is>
       </c>
     </row>
@@ -15158,7 +15158,7 @@
       </c>
       <c r="S173" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18T22:43:53Z</t>
+          <t>2026-09-19T22:23:12Z</t>
         </is>
       </c>
     </row>
@@ -15247,7 +15247,7 @@
       </c>
       <c r="S174" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18T22:43:53Z</t>
+          <t>2026-09-19T22:23:12Z</t>
         </is>
       </c>
     </row>
@@ -15336,7 +15336,7 @@
       </c>
       <c r="S175" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18T22:43:53Z</t>
+          <t>2026-09-19T22:23:12Z</t>
         </is>
       </c>
     </row>
@@ -15421,7 +15421,7 @@
       </c>
       <c r="S176" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18T22:43:53Z</t>
+          <t>2026-09-19T22:23:12Z</t>
         </is>
       </c>
     </row>
@@ -15510,7 +15510,7 @@
       </c>
       <c r="S177" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18T22:43:53Z</t>
+          <t>2026-09-19T22:23:12Z</t>
         </is>
       </c>
     </row>
@@ -15599,7 +15599,7 @@
       </c>
       <c r="S178" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18T22:43:53Z</t>
+          <t>2026-09-19T22:23:12Z</t>
         </is>
       </c>
     </row>
@@ -15688,7 +15688,7 @@
       </c>
       <c r="S179" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18T22:43:53Z</t>
+          <t>2026-09-19T22:23:12Z</t>
         </is>
       </c>
     </row>
@@ -15777,7 +15777,7 @@
       </c>
       <c r="S180" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18T22:43:53Z</t>
+          <t>2026-09-19T22:23:12Z</t>
         </is>
       </c>
     </row>
@@ -15866,7 +15866,7 @@
       </c>
       <c r="S181" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18T22:43:53Z</t>
+          <t>2026-09-19T22:23:12Z</t>
         </is>
       </c>
     </row>
@@ -15955,7 +15955,7 @@
       </c>
       <c r="S182" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18T22:43:53Z</t>
+          <t>2026-09-19T22:23:12Z</t>
         </is>
       </c>
     </row>
@@ -16044,7 +16044,7 @@
       </c>
       <c r="S183" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18T22:43:53Z</t>
+          <t>2026-09-19T22:23:12Z</t>
         </is>
       </c>
     </row>
@@ -16133,7 +16133,7 @@
       </c>
       <c r="S184" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18T22:43:53Z</t>
+          <t>2026-09-19T22:23:12Z</t>
         </is>
       </c>
     </row>
@@ -16222,7 +16222,7 @@
       </c>
       <c r="S185" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18T22:43:53Z</t>
+          <t>2026-09-19T22:23:12Z</t>
         </is>
       </c>
     </row>
@@ -16311,7 +16311,7 @@
       </c>
       <c r="S186" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18T22:43:53Z</t>
+          <t>2026-09-19T22:23:12Z</t>
         </is>
       </c>
     </row>
@@ -16400,7 +16400,7 @@
       </c>
       <c r="S187" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18T22:43:53Z</t>
+          <t>2026-09-19T22:23:12Z</t>
         </is>
       </c>
     </row>
@@ -16489,7 +16489,7 @@
       </c>
       <c r="S188" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18T22:43:53Z</t>
+          <t>2026-09-19T22:23:12Z</t>
         </is>
       </c>
     </row>
@@ -16578,7 +16578,7 @@
       </c>
       <c r="S189" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18T22:43:53Z</t>
+          <t>2026-09-19T22:23:12Z</t>
         </is>
       </c>
     </row>
@@ -16663,7 +16663,7 @@
       </c>
       <c r="S190" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18T22:43:53Z</t>
+          <t>2026-09-19T22:23:12Z</t>
         </is>
       </c>
     </row>
@@ -16748,7 +16748,7 @@
       </c>
       <c r="S191" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18T22:43:53Z</t>
+          <t>2026-09-19T22:23:12Z</t>
         </is>
       </c>
     </row>
@@ -16833,7 +16833,7 @@
       </c>
       <c r="S192" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18T22:43:53Z</t>
+          <t>2026-09-19T22:23:12Z</t>
         </is>
       </c>
     </row>
@@ -16918,7 +16918,7 @@
       </c>
       <c r="S193" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18T22:43:53Z</t>
+          <t>2026-09-19T22:23:12Z</t>
         </is>
       </c>
     </row>
@@ -17003,7 +17003,7 @@
       </c>
       <c r="S194" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18T22:43:53Z</t>
+          <t>2026-09-19T22:23:12Z</t>
         </is>
       </c>
     </row>
@@ -17088,7 +17088,7 @@
       </c>
       <c r="S195" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18T22:43:53Z</t>
+          <t>2026-09-19T22:23:12Z</t>
         </is>
       </c>
     </row>
@@ -17173,7 +17173,7 @@
       </c>
       <c r="S196" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18T22:43:53Z</t>
+          <t>2026-09-19T22:23:12Z</t>
         </is>
       </c>
     </row>
@@ -17258,7 +17258,7 @@
       </c>
       <c r="S197" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18T22:43:53Z</t>
+          <t>2026-09-19T22:23:12Z</t>
         </is>
       </c>
     </row>
@@ -17343,7 +17343,7 @@
       </c>
       <c r="S198" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18T22:43:53Z</t>
+          <t>2026-09-19T22:23:12Z</t>
         </is>
       </c>
     </row>
@@ -17428,7 +17428,7 @@
       </c>
       <c r="S199" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18T22:43:53Z</t>
+          <t>2026-09-19T22:23:12Z</t>
         </is>
       </c>
     </row>
@@ -17513,7 +17513,7 @@
       </c>
       <c r="S200" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18T22:43:53Z</t>
+          <t>2026-09-19T22:23:12Z</t>
         </is>
       </c>
     </row>
@@ -17598,7 +17598,7 @@
       </c>
       <c r="S201" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18T22:43:53Z</t>
+          <t>2026-09-19T22:23:12Z</t>
         </is>
       </c>
     </row>
@@ -17683,7 +17683,7 @@
       </c>
       <c r="S202" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18T22:43:53Z</t>
+          <t>2026-09-19T22:23:12Z</t>
         </is>
       </c>
     </row>
@@ -17768,7 +17768,7 @@
       </c>
       <c r="S203" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18T22:43:53Z</t>
+          <t>2026-09-19T22:23:12Z</t>
         </is>
       </c>
     </row>
@@ -17853,7 +17853,7 @@
       </c>
       <c r="S204" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18T22:43:53Z</t>
+          <t>2026-09-19T22:23:12Z</t>
         </is>
       </c>
     </row>
@@ -17938,7 +17938,7 @@
       </c>
       <c r="S205" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18T22:43:53Z</t>
+          <t>2026-09-19T22:23:12Z</t>
         </is>
       </c>
     </row>
@@ -18023,7 +18023,7 @@
       </c>
       <c r="S206" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18T22:43:53Z</t>
+          <t>2026-09-19T22:23:12Z</t>
         </is>
       </c>
     </row>
@@ -18108,7 +18108,7 @@
       </c>
       <c r="S207" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18T22:43:53Z</t>
+          <t>2026-09-19T22:23:12Z</t>
         </is>
       </c>
     </row>
@@ -18193,7 +18193,7 @@
       </c>
       <c r="S208" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18T22:43:53Z</t>
+          <t>2026-09-19T22:23:12Z</t>
         </is>
       </c>
     </row>
@@ -18278,7 +18278,7 @@
       </c>
       <c r="S209" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18T22:43:53Z</t>
+          <t>2026-09-19T22:23:12Z</t>
         </is>
       </c>
     </row>
@@ -18363,7 +18363,7 @@
       </c>
       <c r="S210" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18T22:43:53Z</t>
+          <t>2026-09-19T22:23:12Z</t>
         </is>
       </c>
     </row>
@@ -18452,7 +18452,7 @@
       </c>
       <c r="S211" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18T22:43:53Z</t>
+          <t>2026-09-19T22:23:12Z</t>
         </is>
       </c>
     </row>
@@ -18541,7 +18541,7 @@
       </c>
       <c r="S212" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18T22:43:53Z</t>
+          <t>2026-09-19T22:23:12Z</t>
         </is>
       </c>
     </row>
@@ -18626,7 +18626,7 @@
       </c>
       <c r="S213" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18T22:43:53Z</t>
+          <t>2026-09-19T22:23:12Z</t>
         </is>
       </c>
     </row>
@@ -18715,7 +18715,7 @@
       </c>
       <c r="S214" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18T22:43:53Z</t>
+          <t>2026-09-19T22:23:12Z</t>
         </is>
       </c>
     </row>
@@ -18804,7 +18804,7 @@
       </c>
       <c r="S215" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18T22:43:53Z</t>
+          <t>2026-09-19T22:23:12Z</t>
         </is>
       </c>
     </row>
@@ -18889,7 +18889,7 @@
       </c>
       <c r="S216" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18T22:43:53Z</t>
+          <t>2026-09-19T22:23:12Z</t>
         </is>
       </c>
     </row>
@@ -18978,7 +18978,7 @@
       </c>
       <c r="S217" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18T22:43:53Z</t>
+          <t>2026-09-19T22:23:12Z</t>
         </is>
       </c>
     </row>
@@ -19067,7 +19067,7 @@
       </c>
       <c r="S218" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18T22:43:53Z</t>
+          <t>2026-09-19T22:23:12Z</t>
         </is>
       </c>
     </row>
@@ -19152,7 +19152,7 @@
       </c>
       <c r="S219" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18T22:43:53Z</t>
+          <t>2026-09-19T22:23:12Z</t>
         </is>
       </c>
     </row>
@@ -19241,7 +19241,7 @@
       </c>
       <c r="S220" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18T22:43:53Z</t>
+          <t>2026-09-19T22:23:12Z</t>
         </is>
       </c>
     </row>
@@ -19330,7 +19330,7 @@
       </c>
       <c r="S221" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18T22:43:53Z</t>
+          <t>2026-09-19T22:23:12Z</t>
         </is>
       </c>
     </row>
@@ -19415,7 +19415,7 @@
       </c>
       <c r="S222" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18T22:43:53Z</t>
+          <t>2026-09-19T22:23:12Z</t>
         </is>
       </c>
     </row>
@@ -19504,7 +19504,7 @@
       </c>
       <c r="S223" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18T22:43:53Z</t>
+          <t>2026-09-19T22:23:12Z</t>
         </is>
       </c>
     </row>
@@ -19593,7 +19593,7 @@
       </c>
       <c r="S224" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18T22:43:53Z</t>
+          <t>2026-09-19T22:23:12Z</t>
         </is>
       </c>
     </row>
@@ -19678,7 +19678,7 @@
       </c>
       <c r="S225" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18T22:43:53Z</t>
+          <t>2026-09-19T22:23:12Z</t>
         </is>
       </c>
     </row>
@@ -19767,7 +19767,7 @@
       </c>
       <c r="S226" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18T22:43:53Z</t>
+          <t>2026-09-19T22:23:12Z</t>
         </is>
       </c>
     </row>
@@ -19856,7 +19856,7 @@
       </c>
       <c r="S227" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18T22:43:53Z</t>
+          <t>2026-09-19T22:23:12Z</t>
         </is>
       </c>
     </row>
@@ -19941,7 +19941,7 @@
       </c>
       <c r="S228" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18T22:43:53Z</t>
+          <t>2026-09-19T22:23:12Z</t>
         </is>
       </c>
     </row>
@@ -20030,7 +20030,7 @@
       </c>
       <c r="S229" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18T22:43:53Z</t>
+          <t>2026-09-19T22:23:12Z</t>
         </is>
       </c>
     </row>
@@ -20119,7 +20119,7 @@
       </c>
       <c r="S230" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18T22:43:53Z</t>
+          <t>2026-09-19T22:23:12Z</t>
         </is>
       </c>
     </row>
@@ -20204,7 +20204,7 @@
       </c>
       <c r="S231" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18T22:43:53Z</t>
+          <t>2026-09-19T22:23:12Z</t>
         </is>
       </c>
     </row>
@@ -20293,7 +20293,7 @@
       </c>
       <c r="S232" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18T22:43:53Z</t>
+          <t>2026-09-19T22:23:12Z</t>
         </is>
       </c>
     </row>
@@ -20382,7 +20382,7 @@
       </c>
       <c r="S233" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18T22:43:53Z</t>
+          <t>2026-09-19T22:23:12Z</t>
         </is>
       </c>
     </row>
@@ -20467,7 +20467,7 @@
       </c>
       <c r="S234" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18T22:43:53Z</t>
+          <t>2026-09-19T22:23:12Z</t>
         </is>
       </c>
     </row>
@@ -20556,7 +20556,7 @@
       </c>
       <c r="S235" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18T22:43:53Z</t>
+          <t>2026-09-19T22:23:12Z</t>
         </is>
       </c>
     </row>
@@ -20645,7 +20645,7 @@
       </c>
       <c r="S236" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18T22:43:53Z</t>
+          <t>2026-09-19T22:23:12Z</t>
         </is>
       </c>
     </row>
@@ -20730,7 +20730,7 @@
       </c>
       <c r="S237" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18T22:43:53Z</t>
+          <t>2026-09-19T22:23:12Z</t>
         </is>
       </c>
     </row>
@@ -20819,7 +20819,7 @@
       </c>
       <c r="S238" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18T22:43:53Z</t>
+          <t>2026-09-19T22:23:12Z</t>
         </is>
       </c>
     </row>
@@ -20908,7 +20908,7 @@
       </c>
       <c r="S239" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18T22:43:53Z</t>
+          <t>2026-09-19T22:23:12Z</t>
         </is>
       </c>
     </row>
@@ -20997,7 +20997,7 @@
       </c>
       <c r="S240" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18T22:43:53Z</t>
+          <t>2026-09-19T22:23:12Z</t>
         </is>
       </c>
     </row>
@@ -21086,7 +21086,7 @@
       </c>
       <c r="S241" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18T22:43:53Z</t>
+          <t>2026-09-19T22:23:12Z</t>
         </is>
       </c>
     </row>
@@ -21175,7 +21175,7 @@
       </c>
       <c r="S242" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18T22:43:53Z</t>
+          <t>2026-09-19T22:23:12Z</t>
         </is>
       </c>
     </row>
@@ -21264,7 +21264,7 @@
       </c>
       <c r="S243" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18T22:43:53Z</t>
+          <t>2026-09-19T22:23:12Z</t>
         </is>
       </c>
     </row>
@@ -21353,7 +21353,7 @@
       </c>
       <c r="S244" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18T22:43:53Z</t>
+          <t>2026-09-19T22:23:12Z</t>
         </is>
       </c>
     </row>
@@ -21442,7 +21442,7 @@
       </c>
       <c r="S245" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18T22:43:53Z</t>
+          <t>2026-09-19T22:23:12Z</t>
         </is>
       </c>
     </row>
@@ -21531,7 +21531,7 @@
       </c>
       <c r="S246" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18T22:43:53Z</t>
+          <t>2026-09-19T22:23:12Z</t>
         </is>
       </c>
     </row>
@@ -21620,7 +21620,7 @@
       </c>
       <c r="S247" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18T22:43:53Z</t>
+          <t>2026-09-19T22:23:12Z</t>
         </is>
       </c>
     </row>
@@ -21709,7 +21709,7 @@
       </c>
       <c r="S248" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18T22:43:53Z</t>
+          <t>2026-09-19T22:23:12Z</t>
         </is>
       </c>
     </row>
@@ -21798,7 +21798,7 @@
       </c>
       <c r="S249" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18T22:43:53Z</t>
+          <t>2026-09-19T22:23:12Z</t>
         </is>
       </c>
     </row>
@@ -21887,7 +21887,7 @@
       </c>
       <c r="S250" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18T22:43:53Z</t>
+          <t>2026-09-19T22:23:12Z</t>
         </is>
       </c>
     </row>
@@ -22019,7 +22019,7 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18T22:43:53Z</t>
+          <t>2026-09-19T22:23:12Z</t>
         </is>
       </c>
     </row>
@@ -22099,7 +22099,7 @@
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>{"dataset_id": "bcv_pib_sector_institucional_anual", "title": "Producto interno bruto por sector institucional anual", "table": "Variaciones porcentuales", "source_file": "5_2_1_si_anual.xlsx", "base": "2007", "price_type": "Precios constantes", "measure": "Variación porcentual interanual", "frequency": "Anual", "period": "2025", "year": 2025, "quarter": null, "classification": "Sector institucional", "component": "Impuestos netos sobre los productos", "value": 10.600260421283764, "unit": "Porcentaje", "status": "Preliminar", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/cuentas_macroeconomicas/5_2_1_si_anual.xlsx", "fetched_at": "2026-09-18T22:43:53Z"}</t>
+          <t>{"dataset_id": "bcv_pib_sector_institucional_anual", "title": "Producto interno bruto por sector institucional anual", "table": "Variaciones porcentuales", "source_file": "5_2_1_si_anual.xlsx", "base": "2007", "price_type": "Precios constantes", "measure": "Variación porcentual interanual", "frequency": "Anual", "period": "2025", "year": 2025, "quarter": null, "classification": "Sector institucional", "component": "Impuestos netos sobre los productos", "value": 10.600260421283764, "unit": "Porcentaje", "status": "Preliminar", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/cuentas_macroeconomicas/5_2_1_si_anual.xlsx", "fetched_at": "2026-09-19T22:23:12Z"}</t>
         </is>
       </c>
     </row>

--- a/assets/data/bcv/excel/ove_bcv_pib_sector_institucional_anual.xlsx
+++ b/assets/data/bcv/excel/ove_bcv_pib_sector_institucional_anual.xlsx
@@ -736,7 +736,7 @@
       </c>
       <c r="S7" s="4" t="inlineStr">
         <is>
-          <t>2026-09-19T22:23:12Z</t>
+          <t>2026-09-20T22:35:41Z</t>
         </is>
       </c>
     </row>
@@ -821,7 +821,7 @@
       </c>
       <c r="S8" s="4" t="inlineStr">
         <is>
-          <t>2026-09-19T22:23:12Z</t>
+          <t>2026-09-20T22:35:41Z</t>
         </is>
       </c>
     </row>
@@ -906,7 +906,7 @@
       </c>
       <c r="S9" s="4" t="inlineStr">
         <is>
-          <t>2026-09-19T22:23:12Z</t>
+          <t>2026-09-20T22:35:41Z</t>
         </is>
       </c>
     </row>
@@ -991,7 +991,7 @@
       </c>
       <c r="S10" s="4" t="inlineStr">
         <is>
-          <t>2026-09-19T22:23:12Z</t>
+          <t>2026-09-20T22:35:41Z</t>
         </is>
       </c>
     </row>
@@ -1076,7 +1076,7 @@
       </c>
       <c r="S11" s="4" t="inlineStr">
         <is>
-          <t>2026-09-19T22:23:12Z</t>
+          <t>2026-09-20T22:35:41Z</t>
         </is>
       </c>
     </row>
@@ -1161,7 +1161,7 @@
       </c>
       <c r="S12" s="4" t="inlineStr">
         <is>
-          <t>2026-09-19T22:23:12Z</t>
+          <t>2026-09-20T22:35:41Z</t>
         </is>
       </c>
     </row>
@@ -1246,7 +1246,7 @@
       </c>
       <c r="S13" s="4" t="inlineStr">
         <is>
-          <t>2026-09-19T22:23:12Z</t>
+          <t>2026-09-20T22:35:41Z</t>
         </is>
       </c>
     </row>
@@ -1331,7 +1331,7 @@
       </c>
       <c r="S14" s="4" t="inlineStr">
         <is>
-          <t>2026-09-19T22:23:12Z</t>
+          <t>2026-09-20T22:35:41Z</t>
         </is>
       </c>
     </row>
@@ -1416,7 +1416,7 @@
       </c>
       <c r="S15" s="4" t="inlineStr">
         <is>
-          <t>2026-09-19T22:23:12Z</t>
+          <t>2026-09-20T22:35:41Z</t>
         </is>
       </c>
     </row>
@@ -1501,7 +1501,7 @@
       </c>
       <c r="S16" s="4" t="inlineStr">
         <is>
-          <t>2026-09-19T22:23:12Z</t>
+          <t>2026-09-20T22:35:41Z</t>
         </is>
       </c>
     </row>
@@ -1586,7 +1586,7 @@
       </c>
       <c r="S17" s="4" t="inlineStr">
         <is>
-          <t>2026-09-19T22:23:12Z</t>
+          <t>2026-09-20T22:35:41Z</t>
         </is>
       </c>
     </row>
@@ -1671,7 +1671,7 @@
       </c>
       <c r="S18" s="4" t="inlineStr">
         <is>
-          <t>2026-09-19T22:23:12Z</t>
+          <t>2026-09-20T22:35:41Z</t>
         </is>
       </c>
     </row>
@@ -1756,7 +1756,7 @@
       </c>
       <c r="S19" s="4" t="inlineStr">
         <is>
-          <t>2026-09-19T22:23:12Z</t>
+          <t>2026-09-20T22:35:41Z</t>
         </is>
       </c>
     </row>
@@ -1841,7 +1841,7 @@
       </c>
       <c r="S20" s="4" t="inlineStr">
         <is>
-          <t>2026-09-19T22:23:12Z</t>
+          <t>2026-09-20T22:35:41Z</t>
         </is>
       </c>
     </row>
@@ -1926,7 +1926,7 @@
       </c>
       <c r="S21" s="4" t="inlineStr">
         <is>
-          <t>2026-09-19T22:23:12Z</t>
+          <t>2026-09-20T22:35:41Z</t>
         </is>
       </c>
     </row>
@@ -2011,7 +2011,7 @@
       </c>
       <c r="S22" s="4" t="inlineStr">
         <is>
-          <t>2026-09-19T22:23:12Z</t>
+          <t>2026-09-20T22:35:41Z</t>
         </is>
       </c>
     </row>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="S23" s="4" t="inlineStr">
         <is>
-          <t>2026-09-19T22:23:12Z</t>
+          <t>2026-09-20T22:35:41Z</t>
         </is>
       </c>
     </row>
@@ -2181,7 +2181,7 @@
       </c>
       <c r="S24" s="4" t="inlineStr">
         <is>
-          <t>2026-09-19T22:23:12Z</t>
+          <t>2026-09-20T22:35:41Z</t>
         </is>
       </c>
     </row>
@@ -2266,7 +2266,7 @@
       </c>
       <c r="S25" s="4" t="inlineStr">
         <is>
-          <t>2026-09-19T22:23:12Z</t>
+          <t>2026-09-20T22:35:41Z</t>
         </is>
       </c>
     </row>
@@ -2351,7 +2351,7 @@
       </c>
       <c r="S26" s="4" t="inlineStr">
         <is>
-          <t>2026-09-19T22:23:12Z</t>
+          <t>2026-09-20T22:35:41Z</t>
         </is>
       </c>
     </row>
@@ -2436,7 +2436,7 @@
       </c>
       <c r="S27" s="4" t="inlineStr">
         <is>
-          <t>2026-09-19T22:23:12Z</t>
+          <t>2026-09-20T22:35:41Z</t>
         </is>
       </c>
     </row>
@@ -2525,7 +2525,7 @@
       </c>
       <c r="S28" s="4" t="inlineStr">
         <is>
-          <t>2026-09-19T22:23:12Z</t>
+          <t>2026-09-20T22:35:41Z</t>
         </is>
       </c>
     </row>
@@ -2614,7 +2614,7 @@
       </c>
       <c r="S29" s="4" t="inlineStr">
         <is>
-          <t>2026-09-19T22:23:12Z</t>
+          <t>2026-09-20T22:35:41Z</t>
         </is>
       </c>
     </row>
@@ -2699,7 +2699,7 @@
       </c>
       <c r="S30" s="4" t="inlineStr">
         <is>
-          <t>2026-09-19T22:23:12Z</t>
+          <t>2026-09-20T22:35:41Z</t>
         </is>
       </c>
     </row>
@@ -2788,7 +2788,7 @@
       </c>
       <c r="S31" s="4" t="inlineStr">
         <is>
-          <t>2026-09-19T22:23:12Z</t>
+          <t>2026-09-20T22:35:41Z</t>
         </is>
       </c>
     </row>
@@ -2877,7 +2877,7 @@
       </c>
       <c r="S32" s="4" t="inlineStr">
         <is>
-          <t>2026-09-19T22:23:12Z</t>
+          <t>2026-09-20T22:35:41Z</t>
         </is>
       </c>
     </row>
@@ -2962,7 +2962,7 @@
       </c>
       <c r="S33" s="4" t="inlineStr">
         <is>
-          <t>2026-09-19T22:23:12Z</t>
+          <t>2026-09-20T22:35:41Z</t>
         </is>
       </c>
     </row>
@@ -3051,7 +3051,7 @@
       </c>
       <c r="S34" s="4" t="inlineStr">
         <is>
-          <t>2026-09-19T22:23:12Z</t>
+          <t>2026-09-20T22:35:41Z</t>
         </is>
       </c>
     </row>
@@ -3140,7 +3140,7 @@
       </c>
       <c r="S35" s="4" t="inlineStr">
         <is>
-          <t>2026-09-19T22:23:12Z</t>
+          <t>2026-09-20T22:35:41Z</t>
         </is>
       </c>
     </row>
@@ -3225,7 +3225,7 @@
       </c>
       <c r="S36" s="4" t="inlineStr">
         <is>
-          <t>2026-09-19T22:23:12Z</t>
+          <t>2026-09-20T22:35:41Z</t>
         </is>
       </c>
     </row>
@@ -3314,7 +3314,7 @@
       </c>
       <c r="S37" s="4" t="inlineStr">
         <is>
-          <t>2026-09-19T22:23:12Z</t>
+          <t>2026-09-20T22:35:41Z</t>
         </is>
       </c>
     </row>
@@ -3403,7 +3403,7 @@
       </c>
       <c r="S38" s="4" t="inlineStr">
         <is>
-          <t>2026-09-19T22:23:12Z</t>
+          <t>2026-09-20T22:35:41Z</t>
         </is>
       </c>
     </row>
@@ -3488,7 +3488,7 @@
       </c>
       <c r="S39" s="4" t="inlineStr">
         <is>
-          <t>2026-09-19T22:23:12Z</t>
+          <t>2026-09-20T22:35:41Z</t>
         </is>
       </c>
     </row>
@@ -3577,7 +3577,7 @@
       </c>
       <c r="S40" s="4" t="inlineStr">
         <is>
-          <t>2026-09-19T22:23:12Z</t>
+          <t>2026-09-20T22:35:41Z</t>
         </is>
       </c>
     </row>
@@ -3666,7 +3666,7 @@
       </c>
       <c r="S41" s="4" t="inlineStr">
         <is>
-          <t>2026-09-19T22:23:12Z</t>
+          <t>2026-09-20T22:35:41Z</t>
         </is>
       </c>
     </row>
@@ -3751,7 +3751,7 @@
       </c>
       <c r="S42" s="4" t="inlineStr">
         <is>
-          <t>2026-09-19T22:23:12Z</t>
+          <t>2026-09-20T22:35:41Z</t>
         </is>
       </c>
     </row>
@@ -3840,7 +3840,7 @@
       </c>
       <c r="S43" s="4" t="inlineStr">
         <is>
-          <t>2026-09-19T22:23:12Z</t>
+          <t>2026-09-20T22:35:41Z</t>
         </is>
       </c>
     </row>
@@ -3929,7 +3929,7 @@
       </c>
       <c r="S44" s="4" t="inlineStr">
         <is>
-          <t>2026-09-19T22:23:12Z</t>
+          <t>2026-09-20T22:35:41Z</t>
         </is>
       </c>
     </row>
@@ -4014,7 +4014,7 @@
       </c>
       <c r="S45" s="4" t="inlineStr">
         <is>
-          <t>2026-09-19T22:23:12Z</t>
+          <t>2026-09-20T22:35:41Z</t>
         </is>
       </c>
     </row>
@@ -4103,7 +4103,7 @@
       </c>
       <c r="S46" s="4" t="inlineStr">
         <is>
-          <t>2026-09-19T22:23:12Z</t>
+          <t>2026-09-20T22:35:41Z</t>
         </is>
       </c>
     </row>
@@ -4192,7 +4192,7 @@
       </c>
       <c r="S47" s="4" t="inlineStr">
         <is>
-          <t>2026-09-19T22:23:12Z</t>
+          <t>2026-09-20T22:35:41Z</t>
         </is>
       </c>
     </row>
@@ -4277,7 +4277,7 @@
       </c>
       <c r="S48" s="4" t="inlineStr">
         <is>
-          <t>2026-09-19T22:23:12Z</t>
+          <t>2026-09-20T22:35:41Z</t>
         </is>
       </c>
     </row>
@@ -4366,7 +4366,7 @@
       </c>
       <c r="S49" s="4" t="inlineStr">
         <is>
-          <t>2026-09-19T22:23:12Z</t>
+          <t>2026-09-20T22:35:41Z</t>
         </is>
       </c>
     </row>
@@ -4455,7 +4455,7 @@
       </c>
       <c r="S50" s="4" t="inlineStr">
         <is>
-          <t>2026-09-19T22:23:12Z</t>
+          <t>2026-09-20T22:35:41Z</t>
         </is>
       </c>
     </row>
@@ -4540,7 +4540,7 @@
       </c>
       <c r="S51" s="4" t="inlineStr">
         <is>
-          <t>2026-09-19T22:23:12Z</t>
+          <t>2026-09-20T22:35:41Z</t>
         </is>
       </c>
     </row>
@@ -4629,7 +4629,7 @@
       </c>
       <c r="S52" s="4" t="inlineStr">
         <is>
-          <t>2026-09-19T22:23:12Z</t>
+          <t>2026-09-20T22:35:41Z</t>
         </is>
       </c>
     </row>
@@ -4718,7 +4718,7 @@
       </c>
       <c r="S53" s="4" t="inlineStr">
         <is>
-          <t>2026-09-19T22:23:12Z</t>
+          <t>2026-09-20T22:35:41Z</t>
         </is>
       </c>
     </row>
@@ -4803,7 +4803,7 @@
       </c>
       <c r="S54" s="4" t="inlineStr">
         <is>
-          <t>2026-09-19T22:23:12Z</t>
+          <t>2026-09-20T22:35:41Z</t>
         </is>
       </c>
     </row>
@@ -4892,7 +4892,7 @@
       </c>
       <c r="S55" s="4" t="inlineStr">
         <is>
-          <t>2026-09-19T22:23:12Z</t>
+          <t>2026-09-20T22:35:41Z</t>
         </is>
       </c>
     </row>
@@ -4981,7 +4981,7 @@
       </c>
       <c r="S56" s="4" t="inlineStr">
         <is>
-          <t>2026-09-19T22:23:12Z</t>
+          <t>2026-09-20T22:35:41Z</t>
         </is>
       </c>
     </row>
@@ -5070,7 +5070,7 @@
       </c>
       <c r="S57" s="4" t="inlineStr">
         <is>
-          <t>2026-09-19T22:23:12Z</t>
+          <t>2026-09-20T22:35:41Z</t>
         </is>
       </c>
     </row>
@@ -5159,7 +5159,7 @@
       </c>
       <c r="S58" s="4" t="inlineStr">
         <is>
-          <t>2026-09-19T22:23:12Z</t>
+          <t>2026-09-20T22:35:41Z</t>
         </is>
       </c>
     </row>
@@ -5248,7 +5248,7 @@
       </c>
       <c r="S59" s="4" t="inlineStr">
         <is>
-          <t>2026-09-19T22:23:12Z</t>
+          <t>2026-09-20T22:35:41Z</t>
         </is>
       </c>
     </row>
@@ -5337,7 +5337,7 @@
       </c>
       <c r="S60" s="4" t="inlineStr">
         <is>
-          <t>2026-09-19T22:23:12Z</t>
+          <t>2026-09-20T22:35:41Z</t>
         </is>
       </c>
     </row>
@@ -5426,7 +5426,7 @@
       </c>
       <c r="S61" s="4" t="inlineStr">
         <is>
-          <t>2026-09-19T22:23:12Z</t>
+          <t>2026-09-20T22:35:41Z</t>
         </is>
       </c>
     </row>
@@ -5515,7 +5515,7 @@
       </c>
       <c r="S62" s="4" t="inlineStr">
         <is>
-          <t>2026-09-19T22:23:12Z</t>
+          <t>2026-09-20T22:35:41Z</t>
         </is>
       </c>
     </row>
@@ -5604,7 +5604,7 @@
       </c>
       <c r="S63" s="4" t="inlineStr">
         <is>
-          <t>2026-09-19T22:23:12Z</t>
+          <t>2026-09-20T22:35:41Z</t>
         </is>
       </c>
     </row>
@@ -5693,7 +5693,7 @@
       </c>
       <c r="S64" s="4" t="inlineStr">
         <is>
-          <t>2026-09-19T22:23:12Z</t>
+          <t>2026-09-20T22:35:41Z</t>
         </is>
       </c>
     </row>
@@ -5782,7 +5782,7 @@
       </c>
       <c r="S65" s="4" t="inlineStr">
         <is>
-          <t>2026-09-19T22:23:12Z</t>
+          <t>2026-09-20T22:35:41Z</t>
         </is>
       </c>
     </row>
@@ -5871,7 +5871,7 @@
       </c>
       <c r="S66" s="4" t="inlineStr">
         <is>
-          <t>2026-09-19T22:23:12Z</t>
+          <t>2026-09-20T22:35:41Z</t>
         </is>
       </c>
     </row>
@@ -5960,7 +5960,7 @@
       </c>
       <c r="S67" s="4" t="inlineStr">
         <is>
-          <t>2026-09-19T22:23:12Z</t>
+          <t>2026-09-20T22:35:41Z</t>
         </is>
       </c>
     </row>
@@ -6045,7 +6045,7 @@
       </c>
       <c r="S68" s="4" t="inlineStr">
         <is>
-          <t>2026-09-19T22:23:12Z</t>
+          <t>2026-09-20T22:35:41Z</t>
         </is>
       </c>
     </row>
@@ -6130,7 +6130,7 @@
       </c>
       <c r="S69" s="4" t="inlineStr">
         <is>
-          <t>2026-09-19T22:23:12Z</t>
+          <t>2026-09-20T22:35:41Z</t>
         </is>
       </c>
     </row>
@@ -6215,7 +6215,7 @@
       </c>
       <c r="S70" s="4" t="inlineStr">
         <is>
-          <t>2026-09-19T22:23:12Z</t>
+          <t>2026-09-20T22:35:41Z</t>
         </is>
       </c>
     </row>
@@ -6300,7 +6300,7 @@
       </c>
       <c r="S71" s="4" t="inlineStr">
         <is>
-          <t>2026-09-19T22:23:12Z</t>
+          <t>2026-09-20T22:35:41Z</t>
         </is>
       </c>
     </row>
@@ -6385,7 +6385,7 @@
       </c>
       <c r="S72" s="4" t="inlineStr">
         <is>
-          <t>2026-09-19T22:23:12Z</t>
+          <t>2026-09-20T22:35:41Z</t>
         </is>
       </c>
     </row>
@@ -6470,7 +6470,7 @@
       </c>
       <c r="S73" s="4" t="inlineStr">
         <is>
-          <t>2026-09-19T22:23:12Z</t>
+          <t>2026-09-20T22:35:41Z</t>
         </is>
       </c>
     </row>
@@ -6555,7 +6555,7 @@
       </c>
       <c r="S74" s="4" t="inlineStr">
         <is>
-          <t>2026-09-19T22:23:12Z</t>
+          <t>2026-09-20T22:35:41Z</t>
         </is>
       </c>
     </row>
@@ -6640,7 +6640,7 @@
       </c>
       <c r="S75" s="4" t="inlineStr">
         <is>
-          <t>2026-09-19T22:23:12Z</t>
+          <t>2026-09-20T22:35:41Z</t>
         </is>
       </c>
     </row>
@@ -6725,7 +6725,7 @@
       </c>
       <c r="S76" s="4" t="inlineStr">
         <is>
-          <t>2026-09-19T22:23:12Z</t>
+          <t>2026-09-20T22:35:41Z</t>
         </is>
       </c>
     </row>
@@ -6810,7 +6810,7 @@
       </c>
       <c r="S77" s="4" t="inlineStr">
         <is>
-          <t>2026-09-19T22:23:12Z</t>
+          <t>2026-09-20T22:35:41Z</t>
         </is>
       </c>
     </row>
@@ -6895,7 +6895,7 @@
       </c>
       <c r="S78" s="4" t="inlineStr">
         <is>
-          <t>2026-09-19T22:23:12Z</t>
+          <t>2026-09-20T22:35:41Z</t>
         </is>
       </c>
     </row>
@@ -6980,7 +6980,7 @@
       </c>
       <c r="S79" s="4" t="inlineStr">
         <is>
-          <t>2026-09-19T22:23:12Z</t>
+          <t>2026-09-20T22:35:41Z</t>
         </is>
       </c>
     </row>
@@ -7065,7 +7065,7 @@
       </c>
       <c r="S80" s="4" t="inlineStr">
         <is>
-          <t>2026-09-19T22:23:12Z</t>
+          <t>2026-09-20T22:35:41Z</t>
         </is>
       </c>
     </row>
@@ -7150,7 +7150,7 @@
       </c>
       <c r="S81" s="4" t="inlineStr">
         <is>
-          <t>2026-09-19T22:23:12Z</t>
+          <t>2026-09-20T22:35:41Z</t>
         </is>
       </c>
     </row>
@@ -7235,7 +7235,7 @@
       </c>
       <c r="S82" s="4" t="inlineStr">
         <is>
-          <t>2026-09-19T22:23:12Z</t>
+          <t>2026-09-20T22:35:41Z</t>
         </is>
       </c>
     </row>
@@ -7320,7 +7320,7 @@
       </c>
       <c r="S83" s="4" t="inlineStr">
         <is>
-          <t>2026-09-19T22:23:12Z</t>
+          <t>2026-09-20T22:35:41Z</t>
         </is>
       </c>
     </row>
@@ -7405,7 +7405,7 @@
       </c>
       <c r="S84" s="4" t="inlineStr">
         <is>
-          <t>2026-09-19T22:23:12Z</t>
+          <t>2026-09-20T22:35:41Z</t>
         </is>
       </c>
     </row>
@@ -7490,7 +7490,7 @@
       </c>
       <c r="S85" s="4" t="inlineStr">
         <is>
-          <t>2026-09-19T22:23:12Z</t>
+          <t>2026-09-20T22:35:41Z</t>
         </is>
       </c>
     </row>
@@ -7575,7 +7575,7 @@
       </c>
       <c r="S86" s="4" t="inlineStr">
         <is>
-          <t>2026-09-19T22:23:12Z</t>
+          <t>2026-09-20T22:35:41Z</t>
         </is>
       </c>
     </row>
@@ -7660,7 +7660,7 @@
       </c>
       <c r="S87" s="4" t="inlineStr">
         <is>
-          <t>2026-09-19T22:23:12Z</t>
+          <t>2026-09-20T22:35:41Z</t>
         </is>
       </c>
     </row>
@@ -7745,7 +7745,7 @@
       </c>
       <c r="S88" s="4" t="inlineStr">
         <is>
-          <t>2026-09-19T22:23:12Z</t>
+          <t>2026-09-20T22:35:41Z</t>
         </is>
       </c>
     </row>
@@ -7834,7 +7834,7 @@
       </c>
       <c r="S89" s="4" t="inlineStr">
         <is>
-          <t>2026-09-19T22:23:12Z</t>
+          <t>2026-09-20T22:35:41Z</t>
         </is>
       </c>
     </row>
@@ -7923,7 +7923,7 @@
       </c>
       <c r="S90" s="4" t="inlineStr">
         <is>
-          <t>2026-09-19T22:23:12Z</t>
+          <t>2026-09-20T22:35:41Z</t>
         </is>
       </c>
     </row>
@@ -8008,7 +8008,7 @@
       </c>
       <c r="S91" s="4" t="inlineStr">
         <is>
-          <t>2026-09-19T22:23:12Z</t>
+          <t>2026-09-20T22:35:41Z</t>
         </is>
       </c>
     </row>
@@ -8097,7 +8097,7 @@
       </c>
       <c r="S92" s="4" t="inlineStr">
         <is>
-          <t>2026-09-19T22:23:12Z</t>
+          <t>2026-09-20T22:35:41Z</t>
         </is>
       </c>
     </row>
@@ -8186,7 +8186,7 @@
       </c>
       <c r="S93" s="4" t="inlineStr">
         <is>
-          <t>2026-09-19T22:23:12Z</t>
+          <t>2026-09-20T22:35:41Z</t>
         </is>
       </c>
     </row>
@@ -8271,7 +8271,7 @@
       </c>
       <c r="S94" s="4" t="inlineStr">
         <is>
-          <t>2026-09-19T22:23:12Z</t>
+          <t>2026-09-20T22:35:41Z</t>
         </is>
       </c>
     </row>
@@ -8360,7 +8360,7 @@
       </c>
       <c r="S95" s="4" t="inlineStr">
         <is>
-          <t>2026-09-19T22:23:12Z</t>
+          <t>2026-09-20T22:35:41Z</t>
         </is>
       </c>
     </row>
@@ -8449,7 +8449,7 @@
       </c>
       <c r="S96" s="4" t="inlineStr">
         <is>
-          <t>2026-09-19T22:23:12Z</t>
+          <t>2026-09-20T22:35:41Z</t>
         </is>
       </c>
     </row>
@@ -8534,7 +8534,7 @@
       </c>
       <c r="S97" s="4" t="inlineStr">
         <is>
-          <t>2026-09-19T22:23:12Z</t>
+          <t>2026-09-20T22:35:41Z</t>
         </is>
       </c>
     </row>
@@ -8623,7 +8623,7 @@
       </c>
       <c r="S98" s="4" t="inlineStr">
         <is>
-          <t>2026-09-19T22:23:12Z</t>
+          <t>2026-09-20T22:35:41Z</t>
         </is>
       </c>
     </row>
@@ -8712,7 +8712,7 @@
       </c>
       <c r="S99" s="4" t="inlineStr">
         <is>
-          <t>2026-09-19T22:23:12Z</t>
+          <t>2026-09-20T22:35:41Z</t>
         </is>
       </c>
     </row>
@@ -8797,7 +8797,7 @@
       </c>
       <c r="S100" s="4" t="inlineStr">
         <is>
-          <t>2026-09-19T22:23:12Z</t>
+          <t>2026-09-20T22:35:41Z</t>
         </is>
       </c>
     </row>
@@ -8886,7 +8886,7 @@
       </c>
       <c r="S101" s="4" t="inlineStr">
         <is>
-          <t>2026-09-19T22:23:12Z</t>
+          <t>2026-09-20T22:35:41Z</t>
         </is>
       </c>
     </row>
@@ -8975,7 +8975,7 @@
       </c>
       <c r="S102" s="4" t="inlineStr">
         <is>
-          <t>2026-09-19T22:23:12Z</t>
+          <t>2026-09-20T22:35:41Z</t>
         </is>
       </c>
     </row>
@@ -9060,7 +9060,7 @@
       </c>
       <c r="S103" s="4" t="inlineStr">
         <is>
-          <t>2026-09-19T22:23:12Z</t>
+          <t>2026-09-20T22:35:41Z</t>
         </is>
       </c>
     </row>
@@ -9149,7 +9149,7 @@
       </c>
       <c r="S104" s="4" t="inlineStr">
         <is>
-          <t>2026-09-19T22:23:12Z</t>
+          <t>2026-09-20T22:35:41Z</t>
         </is>
       </c>
     </row>
@@ -9238,7 +9238,7 @@
       </c>
       <c r="S105" s="4" t="inlineStr">
         <is>
-          <t>2026-09-19T22:23:12Z</t>
+          <t>2026-09-20T22:35:41Z</t>
         </is>
       </c>
     </row>
@@ -9323,7 +9323,7 @@
       </c>
       <c r="S106" s="4" t="inlineStr">
         <is>
-          <t>2026-09-19T22:23:12Z</t>
+          <t>2026-09-20T22:35:41Z</t>
         </is>
       </c>
     </row>
@@ -9412,7 +9412,7 @@
       </c>
       <c r="S107" s="4" t="inlineStr">
         <is>
-          <t>2026-09-19T22:23:12Z</t>
+          <t>2026-09-20T22:35:41Z</t>
         </is>
       </c>
     </row>
@@ -9501,7 +9501,7 @@
       </c>
       <c r="S108" s="4" t="inlineStr">
         <is>
-          <t>2026-09-19T22:23:12Z</t>
+          <t>2026-09-20T22:35:41Z</t>
         </is>
       </c>
     </row>
@@ -9586,7 +9586,7 @@
       </c>
       <c r="S109" s="4" t="inlineStr">
         <is>
-          <t>2026-09-19T22:23:12Z</t>
+          <t>2026-09-20T22:35:41Z</t>
         </is>
       </c>
     </row>
@@ -9675,7 +9675,7 @@
       </c>
       <c r="S110" s="4" t="inlineStr">
         <is>
-          <t>2026-09-19T22:23:12Z</t>
+          <t>2026-09-20T22:35:41Z</t>
         </is>
       </c>
     </row>
@@ -9764,7 +9764,7 @@
       </c>
       <c r="S111" s="4" t="inlineStr">
         <is>
-          <t>2026-09-19T22:23:12Z</t>
+          <t>2026-09-20T22:35:41Z</t>
         </is>
       </c>
     </row>
@@ -9849,7 +9849,7 @@
       </c>
       <c r="S112" s="4" t="inlineStr">
         <is>
-          <t>2026-09-19T22:23:12Z</t>
+          <t>2026-09-20T22:35:41Z</t>
         </is>
       </c>
     </row>
@@ -9938,7 +9938,7 @@
       </c>
       <c r="S113" s="4" t="inlineStr">
         <is>
-          <t>2026-09-19T22:23:12Z</t>
+          <t>2026-09-20T22:35:41Z</t>
         </is>
       </c>
     </row>
@@ -10027,7 +10027,7 @@
       </c>
       <c r="S114" s="4" t="inlineStr">
         <is>
-          <t>2026-09-19T22:23:12Z</t>
+          <t>2026-09-20T22:35:41Z</t>
         </is>
       </c>
     </row>
@@ -10112,7 +10112,7 @@
       </c>
       <c r="S115" s="4" t="inlineStr">
         <is>
-          <t>2026-09-19T22:23:12Z</t>
+          <t>2026-09-20T22:35:41Z</t>
         </is>
       </c>
     </row>
@@ -10201,7 +10201,7 @@
       </c>
       <c r="S116" s="4" t="inlineStr">
         <is>
-          <t>2026-09-19T22:23:12Z</t>
+          <t>2026-09-20T22:35:41Z</t>
         </is>
       </c>
     </row>
@@ -10290,7 +10290,7 @@
       </c>
       <c r="S117" s="4" t="inlineStr">
         <is>
-          <t>2026-09-19T22:23:12Z</t>
+          <t>2026-09-20T22:35:41Z</t>
         </is>
       </c>
     </row>
@@ -10379,7 +10379,7 @@
       </c>
       <c r="S118" s="4" t="inlineStr">
         <is>
-          <t>2026-09-19T22:23:12Z</t>
+          <t>2026-09-20T22:35:41Z</t>
         </is>
       </c>
     </row>
@@ -10468,7 +10468,7 @@
       </c>
       <c r="S119" s="4" t="inlineStr">
         <is>
-          <t>2026-09-19T22:23:12Z</t>
+          <t>2026-09-20T22:35:41Z</t>
         </is>
       </c>
     </row>
@@ -10557,7 +10557,7 @@
       </c>
       <c r="S120" s="4" t="inlineStr">
         <is>
-          <t>2026-09-19T22:23:12Z</t>
+          <t>2026-09-20T22:35:41Z</t>
         </is>
       </c>
     </row>
@@ -10646,7 +10646,7 @@
       </c>
       <c r="S121" s="4" t="inlineStr">
         <is>
-          <t>2026-09-19T22:23:12Z</t>
+          <t>2026-09-20T22:35:41Z</t>
         </is>
       </c>
     </row>
@@ -10735,7 +10735,7 @@
       </c>
       <c r="S122" s="4" t="inlineStr">
         <is>
-          <t>2026-09-19T22:23:12Z</t>
+          <t>2026-09-20T22:35:41Z</t>
         </is>
       </c>
     </row>
@@ -10824,7 +10824,7 @@
       </c>
       <c r="S123" s="4" t="inlineStr">
         <is>
-          <t>2026-09-19T22:23:12Z</t>
+          <t>2026-09-20T22:35:41Z</t>
         </is>
       </c>
     </row>
@@ -10913,7 +10913,7 @@
       </c>
       <c r="S124" s="4" t="inlineStr">
         <is>
-          <t>2026-09-19T22:23:12Z</t>
+          <t>2026-09-20T22:35:41Z</t>
         </is>
       </c>
     </row>
@@ -11002,7 +11002,7 @@
       </c>
       <c r="S125" s="4" t="inlineStr">
         <is>
-          <t>2026-09-19T22:23:12Z</t>
+          <t>2026-09-20T22:35:41Z</t>
         </is>
       </c>
     </row>
@@ -11091,7 +11091,7 @@
       </c>
       <c r="S126" s="4" t="inlineStr">
         <is>
-          <t>2026-09-19T22:23:12Z</t>
+          <t>2026-09-20T22:35:41Z</t>
         </is>
       </c>
     </row>
@@ -11180,7 +11180,7 @@
       </c>
       <c r="S127" s="4" t="inlineStr">
         <is>
-          <t>2026-09-19T22:23:12Z</t>
+          <t>2026-09-20T22:35:41Z</t>
         </is>
       </c>
     </row>
@@ -11269,7 +11269,7 @@
       </c>
       <c r="S128" s="4" t="inlineStr">
         <is>
-          <t>2026-09-19T22:23:12Z</t>
+          <t>2026-09-20T22:35:41Z</t>
         </is>
       </c>
     </row>
@@ -11354,7 +11354,7 @@
       </c>
       <c r="S129" s="4" t="inlineStr">
         <is>
-          <t>2026-09-19T22:23:12Z</t>
+          <t>2026-09-20T22:35:41Z</t>
         </is>
       </c>
     </row>
@@ -11439,7 +11439,7 @@
       </c>
       <c r="S130" s="4" t="inlineStr">
         <is>
-          <t>2026-09-19T22:23:12Z</t>
+          <t>2026-09-20T22:35:41Z</t>
         </is>
       </c>
     </row>
@@ -11524,7 +11524,7 @@
       </c>
       <c r="S131" s="4" t="inlineStr">
         <is>
-          <t>2026-09-19T22:23:12Z</t>
+          <t>2026-09-20T22:35:41Z</t>
         </is>
       </c>
     </row>
@@ -11609,7 +11609,7 @@
       </c>
       <c r="S132" s="4" t="inlineStr">
         <is>
-          <t>2026-09-19T22:23:12Z</t>
+          <t>2026-09-20T22:35:41Z</t>
         </is>
       </c>
     </row>
@@ -11694,7 +11694,7 @@
       </c>
       <c r="S133" s="4" t="inlineStr">
         <is>
-          <t>2026-09-19T22:23:12Z</t>
+          <t>2026-09-20T22:35:41Z</t>
         </is>
       </c>
     </row>
@@ -11779,7 +11779,7 @@
       </c>
       <c r="S134" s="4" t="inlineStr">
         <is>
-          <t>2026-09-19T22:23:12Z</t>
+          <t>2026-09-20T22:35:41Z</t>
         </is>
       </c>
     </row>
@@ -11864,7 +11864,7 @@
       </c>
       <c r="S135" s="4" t="inlineStr">
         <is>
-          <t>2026-09-19T22:23:12Z</t>
+          <t>2026-09-20T22:35:41Z</t>
         </is>
       </c>
     </row>
@@ -11949,7 +11949,7 @@
       </c>
       <c r="S136" s="4" t="inlineStr">
         <is>
-          <t>2026-09-19T22:23:12Z</t>
+          <t>2026-09-20T22:35:41Z</t>
         </is>
       </c>
     </row>
@@ -12034,7 +12034,7 @@
       </c>
       <c r="S137" s="4" t="inlineStr">
         <is>
-          <t>2026-09-19T22:23:12Z</t>
+          <t>2026-09-20T22:35:41Z</t>
         </is>
       </c>
     </row>
@@ -12119,7 +12119,7 @@
       </c>
       <c r="S138" s="4" t="inlineStr">
         <is>
-          <t>2026-09-19T22:23:12Z</t>
+          <t>2026-09-20T22:35:41Z</t>
         </is>
       </c>
     </row>
@@ -12204,7 +12204,7 @@
       </c>
       <c r="S139" s="4" t="inlineStr">
         <is>
-          <t>2026-09-19T22:23:12Z</t>
+          <t>2026-09-20T22:35:41Z</t>
         </is>
       </c>
     </row>
@@ -12289,7 +12289,7 @@
       </c>
       <c r="S140" s="4" t="inlineStr">
         <is>
-          <t>2026-09-19T22:23:12Z</t>
+          <t>2026-09-20T22:35:41Z</t>
         </is>
       </c>
     </row>
@@ -12374,7 +12374,7 @@
       </c>
       <c r="S141" s="4" t="inlineStr">
         <is>
-          <t>2026-09-19T22:23:12Z</t>
+          <t>2026-09-20T22:35:41Z</t>
         </is>
       </c>
     </row>
@@ -12459,7 +12459,7 @@
       </c>
       <c r="S142" s="4" t="inlineStr">
         <is>
-          <t>2026-09-19T22:23:12Z</t>
+          <t>2026-09-20T22:35:41Z</t>
         </is>
       </c>
     </row>
@@ -12544,7 +12544,7 @@
       </c>
       <c r="S143" s="4" t="inlineStr">
         <is>
-          <t>2026-09-19T22:23:12Z</t>
+          <t>2026-09-20T22:35:41Z</t>
         </is>
       </c>
     </row>
@@ -12629,7 +12629,7 @@
       </c>
       <c r="S144" s="4" t="inlineStr">
         <is>
-          <t>2026-09-19T22:23:12Z</t>
+          <t>2026-09-20T22:35:41Z</t>
         </is>
       </c>
     </row>
@@ -12714,7 +12714,7 @@
       </c>
       <c r="S145" s="4" t="inlineStr">
         <is>
-          <t>2026-09-19T22:23:12Z</t>
+          <t>2026-09-20T22:35:41Z</t>
         </is>
       </c>
     </row>
@@ -12799,7 +12799,7 @@
       </c>
       <c r="S146" s="4" t="inlineStr">
         <is>
-          <t>2026-09-19T22:23:12Z</t>
+          <t>2026-09-20T22:35:41Z</t>
         </is>
       </c>
     </row>
@@ -12884,7 +12884,7 @@
       </c>
       <c r="S147" s="4" t="inlineStr">
         <is>
-          <t>2026-09-19T22:23:12Z</t>
+          <t>2026-09-20T22:35:41Z</t>
         </is>
       </c>
     </row>
@@ -12969,7 +12969,7 @@
       </c>
       <c r="S148" s="4" t="inlineStr">
         <is>
-          <t>2026-09-19T22:23:12Z</t>
+          <t>2026-09-20T22:35:41Z</t>
         </is>
       </c>
     </row>
@@ -13054,7 +13054,7 @@
       </c>
       <c r="S149" s="4" t="inlineStr">
         <is>
-          <t>2026-09-19T22:23:12Z</t>
+          <t>2026-09-20T22:35:41Z</t>
         </is>
       </c>
     </row>
@@ -13143,7 +13143,7 @@
       </c>
       <c r="S150" s="4" t="inlineStr">
         <is>
-          <t>2026-09-19T22:23:12Z</t>
+          <t>2026-09-20T22:35:41Z</t>
         </is>
       </c>
     </row>
@@ -13232,7 +13232,7 @@
       </c>
       <c r="S151" s="4" t="inlineStr">
         <is>
-          <t>2026-09-19T22:23:12Z</t>
+          <t>2026-09-20T22:35:41Z</t>
         </is>
       </c>
     </row>
@@ -13317,7 +13317,7 @@
       </c>
       <c r="S152" s="4" t="inlineStr">
         <is>
-          <t>2026-09-19T22:23:12Z</t>
+          <t>2026-09-20T22:35:41Z</t>
         </is>
       </c>
     </row>
@@ -13406,7 +13406,7 @@
       </c>
       <c r="S153" s="4" t="inlineStr">
         <is>
-          <t>2026-09-19T22:23:12Z</t>
+          <t>2026-09-20T22:35:41Z</t>
         </is>
       </c>
     </row>
@@ -13495,7 +13495,7 @@
       </c>
       <c r="S154" s="4" t="inlineStr">
         <is>
-          <t>2026-09-19T22:23:12Z</t>
+          <t>2026-09-20T22:35:41Z</t>
         </is>
       </c>
     </row>
@@ -13580,7 +13580,7 @@
       </c>
       <c r="S155" s="4" t="inlineStr">
         <is>
-          <t>2026-09-19T22:23:12Z</t>
+          <t>2026-09-20T22:35:41Z</t>
         </is>
       </c>
     </row>
@@ -13669,7 +13669,7 @@
       </c>
       <c r="S156" s="4" t="inlineStr">
         <is>
-          <t>2026-09-19T22:23:12Z</t>
+          <t>2026-09-20T22:35:41Z</t>
         </is>
       </c>
     </row>
@@ -13758,7 +13758,7 @@
       </c>
       <c r="S157" s="4" t="inlineStr">
         <is>
-          <t>2026-09-19T22:23:12Z</t>
+          <t>2026-09-20T22:35:41Z</t>
         </is>
       </c>
     </row>
@@ -13843,7 +13843,7 @@
       </c>
       <c r="S158" s="4" t="inlineStr">
         <is>
-          <t>2026-09-19T22:23:12Z</t>
+          <t>2026-09-20T22:35:41Z</t>
         </is>
       </c>
     </row>
@@ -13932,7 +13932,7 @@
       </c>
       <c r="S159" s="4" t="inlineStr">
         <is>
-          <t>2026-09-19T22:23:12Z</t>
+          <t>2026-09-20T22:35:41Z</t>
         </is>
       </c>
     </row>
@@ -14021,7 +14021,7 @@
       </c>
       <c r="S160" s="4" t="inlineStr">
         <is>
-          <t>2026-09-19T22:23:12Z</t>
+          <t>2026-09-20T22:35:41Z</t>
         </is>
       </c>
     </row>
@@ -14106,7 +14106,7 @@
       </c>
       <c r="S161" s="4" t="inlineStr">
         <is>
-          <t>2026-09-19T22:23:12Z</t>
+          <t>2026-09-20T22:35:41Z</t>
         </is>
       </c>
     </row>
@@ -14195,7 +14195,7 @@
       </c>
       <c r="S162" s="4" t="inlineStr">
         <is>
-          <t>2026-09-19T22:23:12Z</t>
+          <t>2026-09-20T22:35:41Z</t>
         </is>
       </c>
     </row>
@@ -14284,7 +14284,7 @@
       </c>
       <c r="S163" s="4" t="inlineStr">
         <is>
-          <t>2026-09-19T22:23:12Z</t>
+          <t>2026-09-20T22:35:41Z</t>
         </is>
       </c>
     </row>
@@ -14369,7 +14369,7 @@
       </c>
       <c r="S164" s="4" t="inlineStr">
         <is>
-          <t>2026-09-19T22:23:12Z</t>
+          <t>2026-09-20T22:35:41Z</t>
         </is>
       </c>
     </row>
@@ -14458,7 +14458,7 @@
       </c>
       <c r="S165" s="4" t="inlineStr">
         <is>
-          <t>2026-09-19T22:23:12Z</t>
+          <t>2026-09-20T22:35:41Z</t>
         </is>
       </c>
     </row>
@@ -14547,7 +14547,7 @@
       </c>
       <c r="S166" s="4" t="inlineStr">
         <is>
-          <t>2026-09-19T22:23:12Z</t>
+          <t>2026-09-20T22:35:41Z</t>
         </is>
       </c>
     </row>
@@ -14632,7 +14632,7 @@
       </c>
       <c r="S167" s="4" t="inlineStr">
         <is>
-          <t>2026-09-19T22:23:12Z</t>
+          <t>2026-09-20T22:35:41Z</t>
         </is>
       </c>
     </row>
@@ -14721,7 +14721,7 @@
       </c>
       <c r="S168" s="4" t="inlineStr">
         <is>
-          <t>2026-09-19T22:23:12Z</t>
+          <t>2026-09-20T22:35:41Z</t>
         </is>
       </c>
     </row>
@@ -14810,7 +14810,7 @@
       </c>
       <c r="S169" s="4" t="inlineStr">
         <is>
-          <t>2026-09-19T22:23:12Z</t>
+          <t>2026-09-20T22:35:41Z</t>
         </is>
       </c>
     </row>
@@ -14895,7 +14895,7 @@
       </c>
       <c r="S170" s="4" t="inlineStr">
         <is>
-          <t>2026-09-19T22:23:12Z</t>
+          <t>2026-09-20T22:35:41Z</t>
         </is>
       </c>
     </row>
@@ -14984,7 +14984,7 @@
       </c>
       <c r="S171" s="4" t="inlineStr">
         <is>
-          <t>2026-09-19T22:23:12Z</t>
+          <t>2026-09-20T22:35:41Z</t>
         </is>
       </c>
     </row>
@@ -15073,7 +15073,7 @@
       </c>
       <c r="S172" s="4" t="inlineStr">
         <is>
-          <t>2026-09-19T22:23:12Z</t>
+          <t>2026-09-20T22:35:41Z</t>
         </is>
       </c>
     </row>
@@ -15158,7 +15158,7 @@
       </c>
       <c r="S173" s="4" t="inlineStr">
         <is>
-          <t>2026-09-19T22:23:12Z</t>
+          <t>2026-09-20T22:35:41Z</t>
         </is>
       </c>
     </row>
@@ -15247,7 +15247,7 @@
       </c>
       <c r="S174" s="4" t="inlineStr">
         <is>
-          <t>2026-09-19T22:23:12Z</t>
+          <t>2026-09-20T22:35:41Z</t>
         </is>
       </c>
     </row>
@@ -15336,7 +15336,7 @@
       </c>
       <c r="S175" s="4" t="inlineStr">
         <is>
-          <t>2026-09-19T22:23:12Z</t>
+          <t>2026-09-20T22:35:41Z</t>
         </is>
       </c>
     </row>
@@ -15421,7 +15421,7 @@
       </c>
       <c r="S176" s="4" t="inlineStr">
         <is>
-          <t>2026-09-19T22:23:12Z</t>
+          <t>2026-09-20T22:35:41Z</t>
         </is>
       </c>
     </row>
@@ -15510,7 +15510,7 @@
       </c>
       <c r="S177" s="4" t="inlineStr">
         <is>
-          <t>2026-09-19T22:23:12Z</t>
+          <t>2026-09-20T22:35:41Z</t>
         </is>
       </c>
     </row>
@@ -15599,7 +15599,7 @@
       </c>
       <c r="S178" s="4" t="inlineStr">
         <is>
-          <t>2026-09-19T22:23:12Z</t>
+          <t>2026-09-20T22:35:41Z</t>
         </is>
       </c>
     </row>
@@ -15688,7 +15688,7 @@
       </c>
       <c r="S179" s="4" t="inlineStr">
         <is>
-          <t>2026-09-19T22:23:12Z</t>
+          <t>2026-09-20T22:35:41Z</t>
         </is>
       </c>
     </row>
@@ -15777,7 +15777,7 @@
       </c>
       <c r="S180" s="4" t="inlineStr">
         <is>
-          <t>2026-09-19T22:23:12Z</t>
+          <t>2026-09-20T22:35:41Z</t>
         </is>
       </c>
     </row>
@@ -15866,7 +15866,7 @@
       </c>
       <c r="S181" s="4" t="inlineStr">
         <is>
-          <t>2026-09-19T22:23:12Z</t>
+          <t>2026-09-20T22:35:41Z</t>
         </is>
       </c>
     </row>
@@ -15955,7 +15955,7 @@
       </c>
       <c r="S182" s="4" t="inlineStr">
         <is>
-          <t>2026-09-19T22:23:12Z</t>
+          <t>2026-09-20T22:35:41Z</t>
         </is>
       </c>
     </row>
@@ -16044,7 +16044,7 @@
       </c>
       <c r="S183" s="4" t="inlineStr">
         <is>
-          <t>2026-09-19T22:23:12Z</t>
+          <t>2026-09-20T22:35:41Z</t>
         </is>
       </c>
     </row>
@@ -16133,7 +16133,7 @@
       </c>
       <c r="S184" s="4" t="inlineStr">
         <is>
-          <t>2026-09-19T22:23:12Z</t>
+          <t>2026-09-20T22:35:41Z</t>
         </is>
       </c>
     </row>
@@ -16222,7 +16222,7 @@
       </c>
       <c r="S185" s="4" t="inlineStr">
         <is>
-          <t>2026-09-19T22:23:12Z</t>
+          <t>2026-09-20T22:35:41Z</t>
         </is>
       </c>
     </row>
@@ -16311,7 +16311,7 @@
       </c>
       <c r="S186" s="4" t="inlineStr">
         <is>
-          <t>2026-09-19T22:23:12Z</t>
+          <t>2026-09-20T22:35:41Z</t>
         </is>
       </c>
     </row>
@@ -16400,7 +16400,7 @@
       </c>
       <c r="S187" s="4" t="inlineStr">
         <is>
-          <t>2026-09-19T22:23:12Z</t>
+          <t>2026-09-20T22:35:41Z</t>
         </is>
       </c>
     </row>
@@ -16489,7 +16489,7 @@
       </c>
       <c r="S188" s="4" t="inlineStr">
         <is>
-          <t>2026-09-19T22:23:12Z</t>
+          <t>2026-09-20T22:35:41Z</t>
         </is>
       </c>
     </row>
@@ -16578,7 +16578,7 @@
       </c>
       <c r="S189" s="4" t="inlineStr">
         <is>
-          <t>2026-09-19T22:23:12Z</t>
+          <t>2026-09-20T22:35:41Z</t>
         </is>
       </c>
     </row>
@@ -16663,7 +16663,7 @@
       </c>
       <c r="S190" s="4" t="inlineStr">
         <is>
-          <t>2026-09-19T22:23:12Z</t>
+          <t>2026-09-20T22:35:41Z</t>
         </is>
       </c>
     </row>
@@ -16748,7 +16748,7 @@
       </c>
       <c r="S191" s="4" t="inlineStr">
         <is>
-          <t>2026-09-19T22:23:12Z</t>
+          <t>2026-09-20T22:35:41Z</t>
         </is>
       </c>
     </row>
@@ -16833,7 +16833,7 @@
       </c>
       <c r="S192" s="4" t="inlineStr">
         <is>
-          <t>2026-09-19T22:23:12Z</t>
+          <t>2026-09-20T22:35:41Z</t>
         </is>
       </c>
     </row>
@@ -16918,7 +16918,7 @@
       </c>
       <c r="S193" s="4" t="inlineStr">
         <is>
-          <t>2026-09-19T22:23:12Z</t>
+          <t>2026-09-20T22:35:41Z</t>
         </is>
       </c>
     </row>
@@ -17003,7 +17003,7 @@
       </c>
       <c r="S194" s="4" t="inlineStr">
         <is>
-          <t>2026-09-19T22:23:12Z</t>
+          <t>2026-09-20T22:35:41Z</t>
         </is>
       </c>
     </row>
@@ -17088,7 +17088,7 @@
       </c>
       <c r="S195" s="4" t="inlineStr">
         <is>
-          <t>2026-09-19T22:23:12Z</t>
+          <t>2026-09-20T22:35:41Z</t>
         </is>
       </c>
     </row>
@@ -17173,7 +17173,7 @@
       </c>
       <c r="S196" s="4" t="inlineStr">
         <is>
-          <t>2026-09-19T22:23:12Z</t>
+          <t>2026-09-20T22:35:41Z</t>
         </is>
       </c>
     </row>
@@ -17258,7 +17258,7 @@
       </c>
       <c r="S197" s="4" t="inlineStr">
         <is>
-          <t>2026-09-19T22:23:12Z</t>
+          <t>2026-09-20T22:35:41Z</t>
         </is>
       </c>
     </row>
@@ -17343,7 +17343,7 @@
       </c>
       <c r="S198" s="4" t="inlineStr">
         <is>
-          <t>2026-09-19T22:23:12Z</t>
+          <t>2026-09-20T22:35:41Z</t>
         </is>
       </c>
     </row>
@@ -17428,7 +17428,7 @@
       </c>
       <c r="S199" s="4" t="inlineStr">
         <is>
-          <t>2026-09-19T22:23:12Z</t>
+          <t>2026-09-20T22:35:41Z</t>
         </is>
       </c>
     </row>
@@ -17513,7 +17513,7 @@
       </c>
       <c r="S200" s="4" t="inlineStr">
         <is>
-          <t>2026-09-19T22:23:12Z</t>
+          <t>2026-09-20T22:35:41Z</t>
         </is>
       </c>
     </row>
@@ -17598,7 +17598,7 @@
       </c>
       <c r="S201" s="4" t="inlineStr">
         <is>
-          <t>2026-09-19T22:23:12Z</t>
+          <t>2026-09-20T22:35:41Z</t>
         </is>
       </c>
     </row>
@@ -17683,7 +17683,7 @@
       </c>
       <c r="S202" s="4" t="inlineStr">
         <is>
-          <t>2026-09-19T22:23:12Z</t>
+          <t>2026-09-20T22:35:41Z</t>
         </is>
       </c>
     </row>
@@ -17768,7 +17768,7 @@
       </c>
       <c r="S203" s="4" t="inlineStr">
         <is>
-          <t>2026-09-19T22:23:12Z</t>
+          <t>2026-09-20T22:35:41Z</t>
         </is>
       </c>
     </row>
@@ -17853,7 +17853,7 @@
       </c>
       <c r="S204" s="4" t="inlineStr">
         <is>
-          <t>2026-09-19T22:23:12Z</t>
+          <t>2026-09-20T22:35:41Z</t>
         </is>
       </c>
     </row>
@@ -17938,7 +17938,7 @@
       </c>
       <c r="S205" s="4" t="inlineStr">
         <is>
-          <t>2026-09-19T22:23:12Z</t>
+          <t>2026-09-20T22:35:41Z</t>
         </is>
       </c>
     </row>
@@ -18023,7 +18023,7 @@
       </c>
       <c r="S206" s="4" t="inlineStr">
         <is>
-          <t>2026-09-19T22:23:12Z</t>
+          <t>2026-09-20T22:35:41Z</t>
         </is>
       </c>
     </row>
@@ -18108,7 +18108,7 @@
       </c>
       <c r="S207" s="4" t="inlineStr">
         <is>
-          <t>2026-09-19T22:23:12Z</t>
+          <t>2026-09-20T22:35:41Z</t>
         </is>
       </c>
     </row>
@@ -18193,7 +18193,7 @@
       </c>
       <c r="S208" s="4" t="inlineStr">
         <is>
-          <t>2026-09-19T22:23:12Z</t>
+          <t>2026-09-20T22:35:41Z</t>
         </is>
       </c>
     </row>
@@ -18278,7 +18278,7 @@
       </c>
       <c r="S209" s="4" t="inlineStr">
         <is>
-          <t>2026-09-19T22:23:12Z</t>
+          <t>2026-09-20T22:35:41Z</t>
         </is>
       </c>
     </row>
@@ -18363,7 +18363,7 @@
       </c>
       <c r="S210" s="4" t="inlineStr">
         <is>
-          <t>2026-09-19T22:23:12Z</t>
+          <t>2026-09-20T22:35:41Z</t>
         </is>
       </c>
     </row>
@@ -18452,7 +18452,7 @@
       </c>
       <c r="S211" s="4" t="inlineStr">
         <is>
-          <t>2026-09-19T22:23:12Z</t>
+          <t>2026-09-20T22:35:41Z</t>
         </is>
       </c>
     </row>
@@ -18541,7 +18541,7 @@
       </c>
       <c r="S212" s="4" t="inlineStr">
         <is>
-          <t>2026-09-19T22:23:12Z</t>
+          <t>2026-09-20T22:35:41Z</t>
         </is>
       </c>
     </row>
@@ -18626,7 +18626,7 @@
       </c>
       <c r="S213" s="4" t="inlineStr">
         <is>
-          <t>2026-09-19T22:23:12Z</t>
+          <t>2026-09-20T22:35:41Z</t>
         </is>
       </c>
     </row>
@@ -18715,7 +18715,7 @@
       </c>
       <c r="S214" s="4" t="inlineStr">
         <is>
-          <t>2026-09-19T22:23:12Z</t>
+          <t>2026-09-20T22:35:41Z</t>
         </is>
       </c>
     </row>
@@ -18804,7 +18804,7 @@
       </c>
       <c r="S215" s="4" t="inlineStr">
         <is>
-          <t>2026-09-19T22:23:12Z</t>
+          <t>2026-09-20T22:35:41Z</t>
         </is>
       </c>
     </row>
@@ -18889,7 +18889,7 @@
       </c>
       <c r="S216" s="4" t="inlineStr">
         <is>
-          <t>2026-09-19T22:23:12Z</t>
+          <t>2026-09-20T22:35:41Z</t>
         </is>
       </c>
     </row>
@@ -18978,7 +18978,7 @@
       </c>
       <c r="S217" s="4" t="inlineStr">
         <is>
-          <t>2026-09-19T22:23:12Z</t>
+          <t>2026-09-20T22:35:41Z</t>
         </is>
       </c>
     </row>
@@ -19067,7 +19067,7 @@
       </c>
       <c r="S218" s="4" t="inlineStr">
         <is>
-          <t>2026-09-19T22:23:12Z</t>
+          <t>2026-09-20T22:35:41Z</t>
         </is>
       </c>
     </row>
@@ -19152,7 +19152,7 @@
       </c>
       <c r="S219" s="4" t="inlineStr">
         <is>
-          <t>2026-09-19T22:23:12Z</t>
+          <t>2026-09-20T22:35:41Z</t>
         </is>
       </c>
     </row>
@@ -19241,7 +19241,7 @@
       </c>
       <c r="S220" s="4" t="inlineStr">
         <is>
-          <t>2026-09-19T22:23:12Z</t>
+          <t>2026-09-20T22:35:41Z</t>
         </is>
       </c>
     </row>
@@ -19330,7 +19330,7 @@
       </c>
       <c r="S221" s="4" t="inlineStr">
         <is>
-          <t>2026-09-19T22:23:12Z</t>
+          <t>2026-09-20T22:35:41Z</t>
         </is>
       </c>
     </row>
@@ -19415,7 +19415,7 @@
       </c>
       <c r="S222" s="4" t="inlineStr">
         <is>
-          <t>2026-09-19T22:23:12Z</t>
+          <t>2026-09-20T22:35:41Z</t>
         </is>
       </c>
     </row>
@@ -19504,7 +19504,7 @@
       </c>
       <c r="S223" s="4" t="inlineStr">
         <is>
-          <t>2026-09-19T22:23:12Z</t>
+          <t>2026-09-20T22:35:41Z</t>
         </is>
       </c>
     </row>
@@ -19593,7 +19593,7 @@
       </c>
       <c r="S224" s="4" t="inlineStr">
         <is>
-          <t>2026-09-19T22:23:12Z</t>
+          <t>2026-09-20T22:35:41Z</t>
         </is>
       </c>
     </row>
@@ -19678,7 +19678,7 @@
       </c>
       <c r="S225" s="4" t="inlineStr">
         <is>
-          <t>2026-09-19T22:23:12Z</t>
+          <t>2026-09-20T22:35:41Z</t>
         </is>
       </c>
     </row>
@@ -19767,7 +19767,7 @@
       </c>
       <c r="S226" s="4" t="inlineStr">
         <is>
-          <t>2026-09-19T22:23:12Z</t>
+          <t>2026-09-20T22:35:41Z</t>
         </is>
       </c>
     </row>
@@ -19856,7 +19856,7 @@
       </c>
       <c r="S227" s="4" t="inlineStr">
         <is>
-          <t>2026-09-19T22:23:12Z</t>
+          <t>2026-09-20T22:35:41Z</t>
         </is>
       </c>
     </row>
@@ -19941,7 +19941,7 @@
       </c>
       <c r="S228" s="4" t="inlineStr">
         <is>
-          <t>2026-09-19T22:23:12Z</t>
+          <t>2026-09-20T22:35:41Z</t>
         </is>
       </c>
     </row>
@@ -20030,7 +20030,7 @@
       </c>
       <c r="S229" s="4" t="inlineStr">
         <is>
-          <t>2026-09-19T22:23:12Z</t>
+          <t>2026-09-20T22:35:41Z</t>
         </is>
       </c>
     </row>
@@ -20119,7 +20119,7 @@
       </c>
       <c r="S230" s="4" t="inlineStr">
         <is>
-          <t>2026-09-19T22:23:12Z</t>
+          <t>2026-09-20T22:35:41Z</t>
         </is>
       </c>
     </row>
@@ -20204,7 +20204,7 @@
       </c>
       <c r="S231" s="4" t="inlineStr">
         <is>
-          <t>2026-09-19T22:23:12Z</t>
+          <t>2026-09-20T22:35:41Z</t>
         </is>
       </c>
     </row>
@@ -20293,7 +20293,7 @@
       </c>
       <c r="S232" s="4" t="inlineStr">
         <is>
-          <t>2026-09-19T22:23:12Z</t>
+          <t>2026-09-20T22:35:41Z</t>
         </is>
       </c>
     </row>
@@ -20382,7 +20382,7 @@
       </c>
       <c r="S233" s="4" t="inlineStr">
         <is>
-          <t>2026-09-19T22:23:12Z</t>
+          <t>2026-09-20T22:35:41Z</t>
         </is>
       </c>
     </row>
@@ -20467,7 +20467,7 @@
       </c>
       <c r="S234" s="4" t="inlineStr">
         <is>
-          <t>2026-09-19T22:23:12Z</t>
+          <t>2026-09-20T22:35:41Z</t>
         </is>
       </c>
     </row>
@@ -20556,7 +20556,7 @@
       </c>
       <c r="S235" s="4" t="inlineStr">
         <is>
-          <t>2026-09-19T22:23:12Z</t>
+          <t>2026-09-20T22:35:41Z</t>
         </is>
       </c>
     </row>
@@ -20645,7 +20645,7 @@
       </c>
       <c r="S236" s="4" t="inlineStr">
         <is>
-          <t>2026-09-19T22:23:12Z</t>
+          <t>2026-09-20T22:35:41Z</t>
         </is>
       </c>
     </row>
@@ -20730,7 +20730,7 @@
       </c>
       <c r="S237" s="4" t="inlineStr">
         <is>
-          <t>2026-09-19T22:23:12Z</t>
+          <t>2026-09-20T22:35:41Z</t>
         </is>
       </c>
     </row>
@@ -20819,7 +20819,7 @@
       </c>
       <c r="S238" s="4" t="inlineStr">
         <is>
-          <t>2026-09-19T22:23:12Z</t>
+          <t>2026-09-20T22:35:41Z</t>
         </is>
       </c>
     </row>
@@ -20908,7 +20908,7 @@
       </c>
       <c r="S239" s="4" t="inlineStr">
         <is>
-          <t>2026-09-19T22:23:12Z</t>
+          <t>2026-09-20T22:35:41Z</t>
         </is>
       </c>
     </row>
@@ -20997,7 +20997,7 @@
       </c>
       <c r="S240" s="4" t="inlineStr">
         <is>
-          <t>2026-09-19T22:23:12Z</t>
+          <t>2026-09-20T22:35:41Z</t>
         </is>
       </c>
     </row>
@@ -21086,7 +21086,7 @@
       </c>
       <c r="S241" s="4" t="inlineStr">
         <is>
-          <t>2026-09-19T22:23:12Z</t>
+          <t>2026-09-20T22:35:41Z</t>
         </is>
       </c>
     </row>
@@ -21175,7 +21175,7 @@
       </c>
       <c r="S242" s="4" t="inlineStr">
         <is>
-          <t>2026-09-19T22:23:12Z</t>
+          <t>2026-09-20T22:35:41Z</t>
         </is>
       </c>
     </row>
@@ -21264,7 +21264,7 @@
       </c>
       <c r="S243" s="4" t="inlineStr">
         <is>
-          <t>2026-09-19T22:23:12Z</t>
+          <t>2026-09-20T22:35:41Z</t>
         </is>
       </c>
     </row>
@@ -21353,7 +21353,7 @@
       </c>
       <c r="S244" s="4" t="inlineStr">
         <is>
-          <t>2026-09-19T22:23:12Z</t>
+          <t>2026-09-20T22:35:41Z</t>
         </is>
       </c>
     </row>
@@ -21442,7 +21442,7 @@
       </c>
       <c r="S245" s="4" t="inlineStr">
         <is>
-          <t>2026-09-19T22:23:12Z</t>
+          <t>2026-09-20T22:35:41Z</t>
         </is>
       </c>
     </row>
@@ -21531,7 +21531,7 @@
       </c>
       <c r="S246" s="4" t="inlineStr">
         <is>
-          <t>2026-09-19T22:23:12Z</t>
+          <t>2026-09-20T22:35:41Z</t>
         </is>
       </c>
     </row>
@@ -21620,7 +21620,7 @@
       </c>
       <c r="S247" s="4" t="inlineStr">
         <is>
-          <t>2026-09-19T22:23:12Z</t>
+          <t>2026-09-20T22:35:41Z</t>
         </is>
       </c>
     </row>
@@ -21709,7 +21709,7 @@
       </c>
       <c r="S248" s="4" t="inlineStr">
         <is>
-          <t>2026-09-19T22:23:12Z</t>
+          <t>2026-09-20T22:35:41Z</t>
         </is>
       </c>
     </row>
@@ -21798,7 +21798,7 @@
       </c>
       <c r="S249" s="4" t="inlineStr">
         <is>
-          <t>2026-09-19T22:23:12Z</t>
+          <t>2026-09-20T22:35:41Z</t>
         </is>
       </c>
     </row>
@@ -21887,7 +21887,7 @@
       </c>
       <c r="S250" s="4" t="inlineStr">
         <is>
-          <t>2026-09-19T22:23:12Z</t>
+          <t>2026-09-20T22:35:41Z</t>
         </is>
       </c>
     </row>
@@ -22019,7 +22019,7 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>2026-09-19T22:23:12Z</t>
+          <t>2026-09-20T22:35:41Z</t>
         </is>
       </c>
     </row>
@@ -22099,7 +22099,7 @@
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>{"dataset_id": "bcv_pib_sector_institucional_anual", "title": "Producto interno bruto por sector institucional anual", "table": "Variaciones porcentuales", "source_file": "5_2_1_si_anual.xlsx", "base": "2007", "price_type": "Precios constantes", "measure": "Variación porcentual interanual", "frequency": "Anual", "period": "2025", "year": 2025, "quarter": null, "classification": "Sector institucional", "component": "Impuestos netos sobre los productos", "value": 10.600260421283764, "unit": "Porcentaje", "status": "Preliminar", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/cuentas_macroeconomicas/5_2_1_si_anual.xlsx", "fetched_at": "2026-09-19T22:23:12Z"}</t>
+          <t>{"dataset_id": "bcv_pib_sector_institucional_anual", "title": "Producto interno bruto por sector institucional anual", "table": "Variaciones porcentuales", "source_file": "5_2_1_si_anual.xlsx", "base": "2007", "price_type": "Precios constantes", "measure": "Variación porcentual interanual", "frequency": "Anual", "period": "2025", "year": 2025, "quarter": null, "classification": "Sector institucional", "component": "Impuestos netos sobre los productos", "value": 10.600260421283764, "unit": "Porcentaje", "status": "Preliminar", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/cuentas_macroeconomicas/5_2_1_si_anual.xlsx", "fetched_at": "2026-09-20T22:35:41Z"}</t>
         </is>
       </c>
     </row>

--- a/assets/data/bcv/excel/ove_bcv_pib_sector_institucional_anual.xlsx
+++ b/assets/data/bcv/excel/ove_bcv_pib_sector_institucional_anual.xlsx
@@ -736,7 +736,7 @@
       </c>
       <c r="S7" s="4" t="inlineStr">
         <is>
-          <t>2026-09-20T22:35:41Z</t>
+          <t>2026-09-21T23:27:49Z</t>
         </is>
       </c>
     </row>
@@ -821,7 +821,7 @@
       </c>
       <c r="S8" s="4" t="inlineStr">
         <is>
-          <t>2026-09-20T22:35:41Z</t>
+          <t>2026-09-21T23:27:49Z</t>
         </is>
       </c>
     </row>
@@ -906,7 +906,7 @@
       </c>
       <c r="S9" s="4" t="inlineStr">
         <is>
-          <t>2026-09-20T22:35:41Z</t>
+          <t>2026-09-21T23:27:49Z</t>
         </is>
       </c>
     </row>
@@ -991,7 +991,7 @@
       </c>
       <c r="S10" s="4" t="inlineStr">
         <is>
-          <t>2026-09-20T22:35:41Z</t>
+          <t>2026-09-21T23:27:49Z</t>
         </is>
       </c>
     </row>
@@ -1076,7 +1076,7 @@
       </c>
       <c r="S11" s="4" t="inlineStr">
         <is>
-          <t>2026-09-20T22:35:41Z</t>
+          <t>2026-09-21T23:27:49Z</t>
         </is>
       </c>
     </row>
@@ -1161,7 +1161,7 @@
       </c>
       <c r="S12" s="4" t="inlineStr">
         <is>
-          <t>2026-09-20T22:35:41Z</t>
+          <t>2026-09-21T23:27:49Z</t>
         </is>
       </c>
     </row>
@@ -1246,7 +1246,7 @@
       </c>
       <c r="S13" s="4" t="inlineStr">
         <is>
-          <t>2026-09-20T22:35:41Z</t>
+          <t>2026-09-21T23:27:49Z</t>
         </is>
       </c>
     </row>
@@ -1331,7 +1331,7 @@
       </c>
       <c r="S14" s="4" t="inlineStr">
         <is>
-          <t>2026-09-20T22:35:41Z</t>
+          <t>2026-09-21T23:27:49Z</t>
         </is>
       </c>
     </row>
@@ -1416,7 +1416,7 @@
       </c>
       <c r="S15" s="4" t="inlineStr">
         <is>
-          <t>2026-09-20T22:35:41Z</t>
+          <t>2026-09-21T23:27:49Z</t>
         </is>
       </c>
     </row>
@@ -1501,7 +1501,7 @@
       </c>
       <c r="S16" s="4" t="inlineStr">
         <is>
-          <t>2026-09-20T22:35:41Z</t>
+          <t>2026-09-21T23:27:49Z</t>
         </is>
       </c>
     </row>
@@ -1586,7 +1586,7 @@
       </c>
       <c r="S17" s="4" t="inlineStr">
         <is>
-          <t>2026-09-20T22:35:41Z</t>
+          <t>2026-09-21T23:27:49Z</t>
         </is>
       </c>
     </row>
@@ -1671,7 +1671,7 @@
       </c>
       <c r="S18" s="4" t="inlineStr">
         <is>
-          <t>2026-09-20T22:35:41Z</t>
+          <t>2026-09-21T23:27:49Z</t>
         </is>
       </c>
     </row>
@@ -1756,7 +1756,7 @@
       </c>
       <c r="S19" s="4" t="inlineStr">
         <is>
-          <t>2026-09-20T22:35:41Z</t>
+          <t>2026-09-21T23:27:49Z</t>
         </is>
       </c>
     </row>
@@ -1841,7 +1841,7 @@
       </c>
       <c r="S20" s="4" t="inlineStr">
         <is>
-          <t>2026-09-20T22:35:41Z</t>
+          <t>2026-09-21T23:27:49Z</t>
         </is>
       </c>
     </row>
@@ -1926,7 +1926,7 @@
       </c>
       <c r="S21" s="4" t="inlineStr">
         <is>
-          <t>2026-09-20T22:35:41Z</t>
+          <t>2026-09-21T23:27:49Z</t>
         </is>
       </c>
     </row>
@@ -2011,7 +2011,7 @@
       </c>
       <c r="S22" s="4" t="inlineStr">
         <is>
-          <t>2026-09-20T22:35:41Z</t>
+          <t>2026-09-21T23:27:49Z</t>
         </is>
       </c>
     </row>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="S23" s="4" t="inlineStr">
         <is>
-          <t>2026-09-20T22:35:41Z</t>
+          <t>2026-09-21T23:27:49Z</t>
         </is>
       </c>
     </row>
@@ -2181,7 +2181,7 @@
       </c>
       <c r="S24" s="4" t="inlineStr">
         <is>
-          <t>2026-09-20T22:35:41Z</t>
+          <t>2026-09-21T23:27:49Z</t>
         </is>
       </c>
     </row>
@@ -2266,7 +2266,7 @@
       </c>
       <c r="S25" s="4" t="inlineStr">
         <is>
-          <t>2026-09-20T22:35:41Z</t>
+          <t>2026-09-21T23:27:49Z</t>
         </is>
       </c>
     </row>
@@ -2351,7 +2351,7 @@
       </c>
       <c r="S26" s="4" t="inlineStr">
         <is>
-          <t>2026-09-20T22:35:41Z</t>
+          <t>2026-09-21T23:27:49Z</t>
         </is>
       </c>
     </row>
@@ -2436,7 +2436,7 @@
       </c>
       <c r="S27" s="4" t="inlineStr">
         <is>
-          <t>2026-09-20T22:35:41Z</t>
+          <t>2026-09-21T23:27:49Z</t>
         </is>
       </c>
     </row>
@@ -2525,7 +2525,7 @@
       </c>
       <c r="S28" s="4" t="inlineStr">
         <is>
-          <t>2026-09-20T22:35:41Z</t>
+          <t>2026-09-21T23:27:49Z</t>
         </is>
       </c>
     </row>
@@ -2614,7 +2614,7 @@
       </c>
       <c r="S29" s="4" t="inlineStr">
         <is>
-          <t>2026-09-20T22:35:41Z</t>
+          <t>2026-09-21T23:27:49Z</t>
         </is>
       </c>
     </row>
@@ -2699,7 +2699,7 @@
       </c>
       <c r="S30" s="4" t="inlineStr">
         <is>
-          <t>2026-09-20T22:35:41Z</t>
+          <t>2026-09-21T23:27:49Z</t>
         </is>
       </c>
     </row>
@@ -2788,7 +2788,7 @@
       </c>
       <c r="S31" s="4" t="inlineStr">
         <is>
-          <t>2026-09-20T22:35:41Z</t>
+          <t>2026-09-21T23:27:49Z</t>
         </is>
       </c>
     </row>
@@ -2877,7 +2877,7 @@
       </c>
       <c r="S32" s="4" t="inlineStr">
         <is>
-          <t>2026-09-20T22:35:41Z</t>
+          <t>2026-09-21T23:27:49Z</t>
         </is>
       </c>
     </row>
@@ -2962,7 +2962,7 @@
       </c>
       <c r="S33" s="4" t="inlineStr">
         <is>
-          <t>2026-09-20T22:35:41Z</t>
+          <t>2026-09-21T23:27:49Z</t>
         </is>
       </c>
     </row>
@@ -3051,7 +3051,7 @@
       </c>
       <c r="S34" s="4" t="inlineStr">
         <is>
-          <t>2026-09-20T22:35:41Z</t>
+          <t>2026-09-21T23:27:49Z</t>
         </is>
       </c>
     </row>
@@ -3140,7 +3140,7 @@
       </c>
       <c r="S35" s="4" t="inlineStr">
         <is>
-          <t>2026-09-20T22:35:41Z</t>
+          <t>2026-09-21T23:27:49Z</t>
         </is>
       </c>
     </row>
@@ -3225,7 +3225,7 @@
       </c>
       <c r="S36" s="4" t="inlineStr">
         <is>
-          <t>2026-09-20T22:35:41Z</t>
+          <t>2026-09-21T23:27:49Z</t>
         </is>
       </c>
     </row>
@@ -3314,7 +3314,7 @@
       </c>
       <c r="S37" s="4" t="inlineStr">
         <is>
-          <t>2026-09-20T22:35:41Z</t>
+          <t>2026-09-21T23:27:49Z</t>
         </is>
       </c>
     </row>
@@ -3403,7 +3403,7 @@
       </c>
       <c r="S38" s="4" t="inlineStr">
         <is>
-          <t>2026-09-20T22:35:41Z</t>
+          <t>2026-09-21T23:27:49Z</t>
         </is>
       </c>
     </row>
@@ -3488,7 +3488,7 @@
       </c>
       <c r="S39" s="4" t="inlineStr">
         <is>
-          <t>2026-09-20T22:35:41Z</t>
+          <t>2026-09-21T23:27:49Z</t>
         </is>
       </c>
     </row>
@@ -3577,7 +3577,7 @@
       </c>
       <c r="S40" s="4" t="inlineStr">
         <is>
-          <t>2026-09-20T22:35:41Z</t>
+          <t>2026-09-21T23:27:49Z</t>
         </is>
       </c>
     </row>
@@ -3666,7 +3666,7 @@
       </c>
       <c r="S41" s="4" t="inlineStr">
         <is>
-          <t>2026-09-20T22:35:41Z</t>
+          <t>2026-09-21T23:27:49Z</t>
         </is>
       </c>
     </row>
@@ -3751,7 +3751,7 @@
       </c>
       <c r="S42" s="4" t="inlineStr">
         <is>
-          <t>2026-09-20T22:35:41Z</t>
+          <t>2026-09-21T23:27:49Z</t>
         </is>
       </c>
     </row>
@@ -3840,7 +3840,7 @@
       </c>
       <c r="S43" s="4" t="inlineStr">
         <is>
-          <t>2026-09-20T22:35:41Z</t>
+          <t>2026-09-21T23:27:49Z</t>
         </is>
       </c>
     </row>
@@ -3929,7 +3929,7 @@
       </c>
       <c r="S44" s="4" t="inlineStr">
         <is>
-          <t>2026-09-20T22:35:41Z</t>
+          <t>2026-09-21T23:27:49Z</t>
         </is>
       </c>
     </row>
@@ -4014,7 +4014,7 @@
       </c>
       <c r="S45" s="4" t="inlineStr">
         <is>
-          <t>2026-09-20T22:35:41Z</t>
+          <t>2026-09-21T23:27:49Z</t>
         </is>
       </c>
     </row>
@@ -4103,7 +4103,7 @@
       </c>
       <c r="S46" s="4" t="inlineStr">
         <is>
-          <t>2026-09-20T22:35:41Z</t>
+          <t>2026-09-21T23:27:49Z</t>
         </is>
       </c>
     </row>
@@ -4192,7 +4192,7 @@
       </c>
       <c r="S47" s="4" t="inlineStr">
         <is>
-          <t>2026-09-20T22:35:41Z</t>
+          <t>2026-09-21T23:27:49Z</t>
         </is>
       </c>
     </row>
@@ -4277,7 +4277,7 @@
       </c>
       <c r="S48" s="4" t="inlineStr">
         <is>
-          <t>2026-09-20T22:35:41Z</t>
+          <t>2026-09-21T23:27:49Z</t>
         </is>
       </c>
     </row>
@@ -4366,7 +4366,7 @@
       </c>
       <c r="S49" s="4" t="inlineStr">
         <is>
-          <t>2026-09-20T22:35:41Z</t>
+          <t>2026-09-21T23:27:49Z</t>
         </is>
       </c>
     </row>
@@ -4455,7 +4455,7 @@
       </c>
       <c r="S50" s="4" t="inlineStr">
         <is>
-          <t>2026-09-20T22:35:41Z</t>
+          <t>2026-09-21T23:27:49Z</t>
         </is>
       </c>
     </row>
@@ -4540,7 +4540,7 @@
       </c>
       <c r="S51" s="4" t="inlineStr">
         <is>
-          <t>2026-09-20T22:35:41Z</t>
+          <t>2026-09-21T23:27:49Z</t>
         </is>
       </c>
     </row>
@@ -4629,7 +4629,7 @@
       </c>
       <c r="S52" s="4" t="inlineStr">
         <is>
-          <t>2026-09-20T22:35:41Z</t>
+          <t>2026-09-21T23:27:49Z</t>
         </is>
       </c>
     </row>
@@ -4718,7 +4718,7 @@
       </c>
       <c r="S53" s="4" t="inlineStr">
         <is>
-          <t>2026-09-20T22:35:41Z</t>
+          <t>2026-09-21T23:27:49Z</t>
         </is>
       </c>
     </row>
@@ -4803,7 +4803,7 @@
       </c>
       <c r="S54" s="4" t="inlineStr">
         <is>
-          <t>2026-09-20T22:35:41Z</t>
+          <t>2026-09-21T23:27:49Z</t>
         </is>
       </c>
     </row>
@@ -4892,7 +4892,7 @@
       </c>
       <c r="S55" s="4" t="inlineStr">
         <is>
-          <t>2026-09-20T22:35:41Z</t>
+          <t>2026-09-21T23:27:49Z</t>
         </is>
       </c>
     </row>
@@ -4981,7 +4981,7 @@
       </c>
       <c r="S56" s="4" t="inlineStr">
         <is>
-          <t>2026-09-20T22:35:41Z</t>
+          <t>2026-09-21T23:27:49Z</t>
         </is>
       </c>
     </row>
@@ -5070,7 +5070,7 @@
       </c>
       <c r="S57" s="4" t="inlineStr">
         <is>
-          <t>2026-09-20T22:35:41Z</t>
+          <t>2026-09-21T23:27:49Z</t>
         </is>
       </c>
     </row>
@@ -5159,7 +5159,7 @@
       </c>
       <c r="S58" s="4" t="inlineStr">
         <is>
-          <t>2026-09-20T22:35:41Z</t>
+          <t>2026-09-21T23:27:49Z</t>
         </is>
       </c>
     </row>
@@ -5248,7 +5248,7 @@
       </c>
       <c r="S59" s="4" t="inlineStr">
         <is>
-          <t>2026-09-20T22:35:41Z</t>
+          <t>2026-09-21T23:27:49Z</t>
         </is>
       </c>
     </row>
@@ -5337,7 +5337,7 @@
       </c>
       <c r="S60" s="4" t="inlineStr">
         <is>
-          <t>2026-09-20T22:35:41Z</t>
+          <t>2026-09-21T23:27:49Z</t>
         </is>
       </c>
     </row>
@@ -5426,7 +5426,7 @@
       </c>
       <c r="S61" s="4" t="inlineStr">
         <is>
-          <t>2026-09-20T22:35:41Z</t>
+          <t>2026-09-21T23:27:49Z</t>
         </is>
       </c>
     </row>
@@ -5515,7 +5515,7 @@
       </c>
       <c r="S62" s="4" t="inlineStr">
         <is>
-          <t>2026-09-20T22:35:41Z</t>
+          <t>2026-09-21T23:27:49Z</t>
         </is>
       </c>
     </row>
@@ -5604,7 +5604,7 @@
       </c>
       <c r="S63" s="4" t="inlineStr">
         <is>
-          <t>2026-09-20T22:35:41Z</t>
+          <t>2026-09-21T23:27:49Z</t>
         </is>
       </c>
     </row>
@@ -5693,7 +5693,7 @@
       </c>
       <c r="S64" s="4" t="inlineStr">
         <is>
-          <t>2026-09-20T22:35:41Z</t>
+          <t>2026-09-21T23:27:49Z</t>
         </is>
       </c>
     </row>
@@ -5782,7 +5782,7 @@
       </c>
       <c r="S65" s="4" t="inlineStr">
         <is>
-          <t>2026-09-20T22:35:41Z</t>
+          <t>2026-09-21T23:27:49Z</t>
         </is>
       </c>
     </row>
@@ -5871,7 +5871,7 @@
       </c>
       <c r="S66" s="4" t="inlineStr">
         <is>
-          <t>2026-09-20T22:35:41Z</t>
+          <t>2026-09-21T23:27:49Z</t>
         </is>
       </c>
     </row>
@@ -5960,7 +5960,7 @@
       </c>
       <c r="S67" s="4" t="inlineStr">
         <is>
-          <t>2026-09-20T22:35:41Z</t>
+          <t>2026-09-21T23:27:49Z</t>
         </is>
       </c>
     </row>
@@ -6045,7 +6045,7 @@
       </c>
       <c r="S68" s="4" t="inlineStr">
         <is>
-          <t>2026-09-20T22:35:41Z</t>
+          <t>2026-09-21T23:27:49Z</t>
         </is>
       </c>
     </row>
@@ -6130,7 +6130,7 @@
       </c>
       <c r="S69" s="4" t="inlineStr">
         <is>
-          <t>2026-09-20T22:35:41Z</t>
+          <t>2026-09-21T23:27:49Z</t>
         </is>
       </c>
     </row>
@@ -6215,7 +6215,7 @@
       </c>
       <c r="S70" s="4" t="inlineStr">
         <is>
-          <t>2026-09-20T22:35:41Z</t>
+          <t>2026-09-21T23:27:49Z</t>
         </is>
       </c>
     </row>
@@ -6300,7 +6300,7 @@
       </c>
       <c r="S71" s="4" t="inlineStr">
         <is>
-          <t>2026-09-20T22:35:41Z</t>
+          <t>2026-09-21T23:27:49Z</t>
         </is>
       </c>
     </row>
@@ -6385,7 +6385,7 @@
       </c>
       <c r="S72" s="4" t="inlineStr">
         <is>
-          <t>2026-09-20T22:35:41Z</t>
+          <t>2026-09-21T23:27:49Z</t>
         </is>
       </c>
     </row>
@@ -6470,7 +6470,7 @@
       </c>
       <c r="S73" s="4" t="inlineStr">
         <is>
-          <t>2026-09-20T22:35:41Z</t>
+          <t>2026-09-21T23:27:49Z</t>
         </is>
       </c>
     </row>
@@ -6555,7 +6555,7 @@
       </c>
       <c r="S74" s="4" t="inlineStr">
         <is>
-          <t>2026-09-20T22:35:41Z</t>
+          <t>2026-09-21T23:27:49Z</t>
         </is>
       </c>
     </row>
@@ -6640,7 +6640,7 @@
       </c>
       <c r="S75" s="4" t="inlineStr">
         <is>
-          <t>2026-09-20T22:35:41Z</t>
+          <t>2026-09-21T23:27:49Z</t>
         </is>
       </c>
     </row>
@@ -6725,7 +6725,7 @@
       </c>
       <c r="S76" s="4" t="inlineStr">
         <is>
-          <t>2026-09-20T22:35:41Z</t>
+          <t>2026-09-21T23:27:49Z</t>
         </is>
       </c>
     </row>
@@ -6810,7 +6810,7 @@
       </c>
       <c r="S77" s="4" t="inlineStr">
         <is>
-          <t>2026-09-20T22:35:41Z</t>
+          <t>2026-09-21T23:27:49Z</t>
         </is>
       </c>
     </row>
@@ -6895,7 +6895,7 @@
       </c>
       <c r="S78" s="4" t="inlineStr">
         <is>
-          <t>2026-09-20T22:35:41Z</t>
+          <t>2026-09-21T23:27:49Z</t>
         </is>
       </c>
     </row>
@@ -6980,7 +6980,7 @@
       </c>
       <c r="S79" s="4" t="inlineStr">
         <is>
-          <t>2026-09-20T22:35:41Z</t>
+          <t>2026-09-21T23:27:49Z</t>
         </is>
       </c>
     </row>
@@ -7065,7 +7065,7 @@
       </c>
       <c r="S80" s="4" t="inlineStr">
         <is>
-          <t>2026-09-20T22:35:41Z</t>
+          <t>2026-09-21T23:27:49Z</t>
         </is>
       </c>
     </row>
@@ -7150,7 +7150,7 @@
       </c>
       <c r="S81" s="4" t="inlineStr">
         <is>
-          <t>2026-09-20T22:35:41Z</t>
+          <t>2026-09-21T23:27:49Z</t>
         </is>
       </c>
     </row>
@@ -7235,7 +7235,7 @@
       </c>
       <c r="S82" s="4" t="inlineStr">
         <is>
-          <t>2026-09-20T22:35:41Z</t>
+          <t>2026-09-21T23:27:49Z</t>
         </is>
       </c>
     </row>
@@ -7320,7 +7320,7 @@
       </c>
       <c r="S83" s="4" t="inlineStr">
         <is>
-          <t>2026-09-20T22:35:41Z</t>
+          <t>2026-09-21T23:27:49Z</t>
         </is>
       </c>
     </row>
@@ -7405,7 +7405,7 @@
       </c>
       <c r="S84" s="4" t="inlineStr">
         <is>
-          <t>2026-09-20T22:35:41Z</t>
+          <t>2026-09-21T23:27:49Z</t>
         </is>
       </c>
     </row>
@@ -7490,7 +7490,7 @@
       </c>
       <c r="S85" s="4" t="inlineStr">
         <is>
-          <t>2026-09-20T22:35:41Z</t>
+          <t>2026-09-21T23:27:49Z</t>
         </is>
       </c>
     </row>
@@ -7575,7 +7575,7 @@
       </c>
       <c r="S86" s="4" t="inlineStr">
         <is>
-          <t>2026-09-20T22:35:41Z</t>
+          <t>2026-09-21T23:27:49Z</t>
         </is>
       </c>
     </row>
@@ -7660,7 +7660,7 @@
       </c>
       <c r="S87" s="4" t="inlineStr">
         <is>
-          <t>2026-09-20T22:35:41Z</t>
+          <t>2026-09-21T23:27:49Z</t>
         </is>
       </c>
     </row>
@@ -7745,7 +7745,7 @@
       </c>
       <c r="S88" s="4" t="inlineStr">
         <is>
-          <t>2026-09-20T22:35:41Z</t>
+          <t>2026-09-21T23:27:49Z</t>
         </is>
       </c>
     </row>
@@ -7834,7 +7834,7 @@
       </c>
       <c r="S89" s="4" t="inlineStr">
         <is>
-          <t>2026-09-20T22:35:41Z</t>
+          <t>2026-09-21T23:27:49Z</t>
         </is>
       </c>
     </row>
@@ -7923,7 +7923,7 @@
       </c>
       <c r="S90" s="4" t="inlineStr">
         <is>
-          <t>2026-09-20T22:35:41Z</t>
+          <t>2026-09-21T23:27:49Z</t>
         </is>
       </c>
     </row>
@@ -8008,7 +8008,7 @@
       </c>
       <c r="S91" s="4" t="inlineStr">
         <is>
-          <t>2026-09-20T22:35:41Z</t>
+          <t>2026-09-21T23:27:49Z</t>
         </is>
       </c>
     </row>
@@ -8097,7 +8097,7 @@
       </c>
       <c r="S92" s="4" t="inlineStr">
         <is>
-          <t>2026-09-20T22:35:41Z</t>
+          <t>2026-09-21T23:27:49Z</t>
         </is>
       </c>
     </row>
@@ -8186,7 +8186,7 @@
       </c>
       <c r="S93" s="4" t="inlineStr">
         <is>
-          <t>2026-09-20T22:35:41Z</t>
+          <t>2026-09-21T23:27:49Z</t>
         </is>
       </c>
     </row>
@@ -8271,7 +8271,7 @@
       </c>
       <c r="S94" s="4" t="inlineStr">
         <is>
-          <t>2026-09-20T22:35:41Z</t>
+          <t>2026-09-21T23:27:49Z</t>
         </is>
       </c>
     </row>
@@ -8360,7 +8360,7 @@
       </c>
       <c r="S95" s="4" t="inlineStr">
         <is>
-          <t>2026-09-20T22:35:41Z</t>
+          <t>2026-09-21T23:27:49Z</t>
         </is>
       </c>
     </row>
@@ -8449,7 +8449,7 @@
       </c>
       <c r="S96" s="4" t="inlineStr">
         <is>
-          <t>2026-09-20T22:35:41Z</t>
+          <t>2026-09-21T23:27:49Z</t>
         </is>
       </c>
     </row>
@@ -8534,7 +8534,7 @@
       </c>
       <c r="S97" s="4" t="inlineStr">
         <is>
-          <t>2026-09-20T22:35:41Z</t>
+          <t>2026-09-21T23:27:49Z</t>
         </is>
       </c>
     </row>
@@ -8623,7 +8623,7 @@
       </c>
       <c r="S98" s="4" t="inlineStr">
         <is>
-          <t>2026-09-20T22:35:41Z</t>
+          <t>2026-09-21T23:27:49Z</t>
         </is>
       </c>
     </row>
@@ -8712,7 +8712,7 @@
       </c>
       <c r="S99" s="4" t="inlineStr">
         <is>
-          <t>2026-09-20T22:35:41Z</t>
+          <t>2026-09-21T23:27:49Z</t>
         </is>
       </c>
     </row>
@@ -8797,7 +8797,7 @@
       </c>
       <c r="S100" s="4" t="inlineStr">
         <is>
-          <t>2026-09-20T22:35:41Z</t>
+          <t>2026-09-21T23:27:49Z</t>
         </is>
       </c>
     </row>
@@ -8886,7 +8886,7 @@
       </c>
       <c r="S101" s="4" t="inlineStr">
         <is>
-          <t>2026-09-20T22:35:41Z</t>
+          <t>2026-09-21T23:27:49Z</t>
         </is>
       </c>
     </row>
@@ -8975,7 +8975,7 @@
       </c>
       <c r="S102" s="4" t="inlineStr">
         <is>
-          <t>2026-09-20T22:35:41Z</t>
+          <t>2026-09-21T23:27:49Z</t>
         </is>
       </c>
     </row>
@@ -9060,7 +9060,7 @@
       </c>
       <c r="S103" s="4" t="inlineStr">
         <is>
-          <t>2026-09-20T22:35:41Z</t>
+          <t>2026-09-21T23:27:49Z</t>
         </is>
       </c>
     </row>
@@ -9149,7 +9149,7 @@
       </c>
       <c r="S104" s="4" t="inlineStr">
         <is>
-          <t>2026-09-20T22:35:41Z</t>
+          <t>2026-09-21T23:27:49Z</t>
         </is>
       </c>
     </row>
@@ -9238,7 +9238,7 @@
       </c>
       <c r="S105" s="4" t="inlineStr">
         <is>
-          <t>2026-09-20T22:35:41Z</t>
+          <t>2026-09-21T23:27:49Z</t>
         </is>
       </c>
     </row>
@@ -9323,7 +9323,7 @@
       </c>
       <c r="S106" s="4" t="inlineStr">
         <is>
-          <t>2026-09-20T22:35:41Z</t>
+          <t>2026-09-21T23:27:49Z</t>
         </is>
       </c>
     </row>
@@ -9412,7 +9412,7 @@
       </c>
       <c r="S107" s="4" t="inlineStr">
         <is>
-          <t>2026-09-20T22:35:41Z</t>
+          <t>2026-09-21T23:27:49Z</t>
         </is>
       </c>
     </row>
@@ -9501,7 +9501,7 @@
       </c>
       <c r="S108" s="4" t="inlineStr">
         <is>
-          <t>2026-09-20T22:35:41Z</t>
+          <t>2026-09-21T23:27:49Z</t>
         </is>
       </c>
     </row>
@@ -9586,7 +9586,7 @@
       </c>
       <c r="S109" s="4" t="inlineStr">
         <is>
-          <t>2026-09-20T22:35:41Z</t>
+          <t>2026-09-21T23:27:49Z</t>
         </is>
       </c>
     </row>
@@ -9675,7 +9675,7 @@
       </c>
       <c r="S110" s="4" t="inlineStr">
         <is>
-          <t>2026-09-20T22:35:41Z</t>
+          <t>2026-09-21T23:27:49Z</t>
         </is>
       </c>
     </row>
@@ -9764,7 +9764,7 @@
       </c>
       <c r="S111" s="4" t="inlineStr">
         <is>
-          <t>2026-09-20T22:35:41Z</t>
+          <t>2026-09-21T23:27:49Z</t>
         </is>
       </c>
     </row>
@@ -9849,7 +9849,7 @@
       </c>
       <c r="S112" s="4" t="inlineStr">
         <is>
-          <t>2026-09-20T22:35:41Z</t>
+          <t>2026-09-21T23:27:49Z</t>
         </is>
       </c>
     </row>
@@ -9938,7 +9938,7 @@
       </c>
       <c r="S113" s="4" t="inlineStr">
         <is>
-          <t>2026-09-20T22:35:41Z</t>
+          <t>2026-09-21T23:27:49Z</t>
         </is>
       </c>
     </row>
@@ -10027,7 +10027,7 @@
       </c>
       <c r="S114" s="4" t="inlineStr">
         <is>
-          <t>2026-09-20T22:35:41Z</t>
+          <t>2026-09-21T23:27:49Z</t>
         </is>
       </c>
     </row>
@@ -10112,7 +10112,7 @@
       </c>
       <c r="S115" s="4" t="inlineStr">
         <is>
-          <t>2026-09-20T22:35:41Z</t>
+          <t>2026-09-21T23:27:49Z</t>
         </is>
       </c>
     </row>
@@ -10201,7 +10201,7 @@
       </c>
       <c r="S116" s="4" t="inlineStr">
         <is>
-          <t>2026-09-20T22:35:41Z</t>
+          <t>2026-09-21T23:27:49Z</t>
         </is>
       </c>
     </row>
@@ -10290,7 +10290,7 @@
       </c>
       <c r="S117" s="4" t="inlineStr">
         <is>
-          <t>2026-09-20T22:35:41Z</t>
+          <t>2026-09-21T23:27:49Z</t>
         </is>
       </c>
     </row>
@@ -10379,7 +10379,7 @@
       </c>
       <c r="S118" s="4" t="inlineStr">
         <is>
-          <t>2026-09-20T22:35:41Z</t>
+          <t>2026-09-21T23:27:49Z</t>
         </is>
       </c>
     </row>
@@ -10468,7 +10468,7 @@
       </c>
       <c r="S119" s="4" t="inlineStr">
         <is>
-          <t>2026-09-20T22:35:41Z</t>
+          <t>2026-09-21T23:27:49Z</t>
         </is>
       </c>
     </row>
@@ -10557,7 +10557,7 @@
       </c>
       <c r="S120" s="4" t="inlineStr">
         <is>
-          <t>2026-09-20T22:35:41Z</t>
+          <t>2026-09-21T23:27:49Z</t>
         </is>
       </c>
     </row>
@@ -10646,7 +10646,7 @@
       </c>
       <c r="S121" s="4" t="inlineStr">
         <is>
-          <t>2026-09-20T22:35:41Z</t>
+          <t>2026-09-21T23:27:49Z</t>
         </is>
       </c>
     </row>
@@ -10735,7 +10735,7 @@
       </c>
       <c r="S122" s="4" t="inlineStr">
         <is>
-          <t>2026-09-20T22:35:41Z</t>
+          <t>2026-09-21T23:27:49Z</t>
         </is>
       </c>
     </row>
@@ -10824,7 +10824,7 @@
       </c>
       <c r="S123" s="4" t="inlineStr">
         <is>
-          <t>2026-09-20T22:35:41Z</t>
+          <t>2026-09-21T23:27:49Z</t>
         </is>
       </c>
     </row>
@@ -10913,7 +10913,7 @@
       </c>
       <c r="S124" s="4" t="inlineStr">
         <is>
-          <t>2026-09-20T22:35:41Z</t>
+          <t>2026-09-21T23:27:49Z</t>
         </is>
       </c>
     </row>
@@ -11002,7 +11002,7 @@
       </c>
       <c r="S125" s="4" t="inlineStr">
         <is>
-          <t>2026-09-20T22:35:41Z</t>
+          <t>2026-09-21T23:27:49Z</t>
         </is>
       </c>
     </row>
@@ -11091,7 +11091,7 @@
       </c>
       <c r="S126" s="4" t="inlineStr">
         <is>
-          <t>2026-09-20T22:35:41Z</t>
+          <t>2026-09-21T23:27:49Z</t>
         </is>
       </c>
     </row>
@@ -11180,7 +11180,7 @@
       </c>
       <c r="S127" s="4" t="inlineStr">
         <is>
-          <t>2026-09-20T22:35:41Z</t>
+          <t>2026-09-21T23:27:49Z</t>
         </is>
       </c>
     </row>
@@ -11269,7 +11269,7 @@
       </c>
       <c r="S128" s="4" t="inlineStr">
         <is>
-          <t>2026-09-20T22:35:41Z</t>
+          <t>2026-09-21T23:27:49Z</t>
         </is>
       </c>
     </row>
@@ -11354,7 +11354,7 @@
       </c>
       <c r="S129" s="4" t="inlineStr">
         <is>
-          <t>2026-09-20T22:35:41Z</t>
+          <t>2026-09-21T23:27:49Z</t>
         </is>
       </c>
     </row>
@@ -11439,7 +11439,7 @@
       </c>
       <c r="S130" s="4" t="inlineStr">
         <is>
-          <t>2026-09-20T22:35:41Z</t>
+          <t>2026-09-21T23:27:49Z</t>
         </is>
       </c>
     </row>
@@ -11524,7 +11524,7 @@
       </c>
       <c r="S131" s="4" t="inlineStr">
         <is>
-          <t>2026-09-20T22:35:41Z</t>
+          <t>2026-09-21T23:27:49Z</t>
         </is>
       </c>
     </row>
@@ -11609,7 +11609,7 @@
       </c>
       <c r="S132" s="4" t="inlineStr">
         <is>
-          <t>2026-09-20T22:35:41Z</t>
+          <t>2026-09-21T23:27:49Z</t>
         </is>
       </c>
     </row>
@@ -11694,7 +11694,7 @@
       </c>
       <c r="S133" s="4" t="inlineStr">
         <is>
-          <t>2026-09-20T22:35:41Z</t>
+          <t>2026-09-21T23:27:49Z</t>
         </is>
       </c>
     </row>
@@ -11779,7 +11779,7 @@
       </c>
       <c r="S134" s="4" t="inlineStr">
         <is>
-          <t>2026-09-20T22:35:41Z</t>
+          <t>2026-09-21T23:27:49Z</t>
         </is>
       </c>
     </row>
@@ -11864,7 +11864,7 @@
       </c>
       <c r="S135" s="4" t="inlineStr">
         <is>
-          <t>2026-09-20T22:35:41Z</t>
+          <t>2026-09-21T23:27:49Z</t>
         </is>
       </c>
     </row>
@@ -11949,7 +11949,7 @@
       </c>
       <c r="S136" s="4" t="inlineStr">
         <is>
-          <t>2026-09-20T22:35:41Z</t>
+          <t>2026-09-21T23:27:49Z</t>
         </is>
       </c>
     </row>
@@ -12034,7 +12034,7 @@
       </c>
       <c r="S137" s="4" t="inlineStr">
         <is>
-          <t>2026-09-20T22:35:41Z</t>
+          <t>2026-09-21T23:27:49Z</t>
         </is>
       </c>
     </row>
@@ -12119,7 +12119,7 @@
       </c>
       <c r="S138" s="4" t="inlineStr">
         <is>
-          <t>2026-09-20T22:35:41Z</t>
+          <t>2026-09-21T23:27:49Z</t>
         </is>
       </c>
     </row>
@@ -12204,7 +12204,7 @@
       </c>
       <c r="S139" s="4" t="inlineStr">
         <is>
-          <t>2026-09-20T22:35:41Z</t>
+          <t>2026-09-21T23:27:49Z</t>
         </is>
       </c>
     </row>
@@ -12289,7 +12289,7 @@
       </c>
       <c r="S140" s="4" t="inlineStr">
         <is>
-          <t>2026-09-20T22:35:41Z</t>
+          <t>2026-09-21T23:27:49Z</t>
         </is>
       </c>
     </row>
@@ -12374,7 +12374,7 @@
       </c>
       <c r="S141" s="4" t="inlineStr">
         <is>
-          <t>2026-09-20T22:35:41Z</t>
+          <t>2026-09-21T23:27:49Z</t>
         </is>
       </c>
     </row>
@@ -12459,7 +12459,7 @@
       </c>
       <c r="S142" s="4" t="inlineStr">
         <is>
-          <t>2026-09-20T22:35:41Z</t>
+          <t>2026-09-21T23:27:49Z</t>
         </is>
       </c>
     </row>
@@ -12544,7 +12544,7 @@
       </c>
       <c r="S143" s="4" t="inlineStr">
         <is>
-          <t>2026-09-20T22:35:41Z</t>
+          <t>2026-09-21T23:27:49Z</t>
         </is>
       </c>
     </row>
@@ -12629,7 +12629,7 @@
       </c>
       <c r="S144" s="4" t="inlineStr">
         <is>
-          <t>2026-09-20T22:35:41Z</t>
+          <t>2026-09-21T23:27:49Z</t>
         </is>
       </c>
     </row>
@@ -12714,7 +12714,7 @@
       </c>
       <c r="S145" s="4" t="inlineStr">
         <is>
-          <t>2026-09-20T22:35:41Z</t>
+          <t>2026-09-21T23:27:49Z</t>
         </is>
       </c>
     </row>
@@ -12799,7 +12799,7 @@
       </c>
       <c r="S146" s="4" t="inlineStr">
         <is>
-          <t>2026-09-20T22:35:41Z</t>
+          <t>2026-09-21T23:27:49Z</t>
         </is>
       </c>
     </row>
@@ -12884,7 +12884,7 @@
       </c>
       <c r="S147" s="4" t="inlineStr">
         <is>
-          <t>2026-09-20T22:35:41Z</t>
+          <t>2026-09-21T23:27:49Z</t>
         </is>
       </c>
     </row>
@@ -12969,7 +12969,7 @@
       </c>
       <c r="S148" s="4" t="inlineStr">
         <is>
-          <t>2026-09-20T22:35:41Z</t>
+          <t>2026-09-21T23:27:49Z</t>
         </is>
       </c>
     </row>
@@ -13054,7 +13054,7 @@
       </c>
       <c r="S149" s="4" t="inlineStr">
         <is>
-          <t>2026-09-20T22:35:41Z</t>
+          <t>2026-09-21T23:27:49Z</t>
         </is>
       </c>
     </row>
@@ -13143,7 +13143,7 @@
       </c>
       <c r="S150" s="4" t="inlineStr">
         <is>
-          <t>2026-09-20T22:35:41Z</t>
+          <t>2026-09-21T23:27:49Z</t>
         </is>
       </c>
     </row>
@@ -13232,7 +13232,7 @@
       </c>
       <c r="S151" s="4" t="inlineStr">
         <is>
-          <t>2026-09-20T22:35:41Z</t>
+          <t>2026-09-21T23:27:49Z</t>
         </is>
       </c>
     </row>
@@ -13317,7 +13317,7 @@
       </c>
       <c r="S152" s="4" t="inlineStr">
         <is>
-          <t>2026-09-20T22:35:41Z</t>
+          <t>2026-09-21T23:27:49Z</t>
         </is>
       </c>
     </row>
@@ -13406,7 +13406,7 @@
       </c>
       <c r="S153" s="4" t="inlineStr">
         <is>
-          <t>2026-09-20T22:35:41Z</t>
+          <t>2026-09-21T23:27:49Z</t>
         </is>
       </c>
     </row>
@@ -13495,7 +13495,7 @@
       </c>
       <c r="S154" s="4" t="inlineStr">
         <is>
-          <t>2026-09-20T22:35:41Z</t>
+          <t>2026-09-21T23:27:49Z</t>
         </is>
       </c>
     </row>
@@ -13580,7 +13580,7 @@
       </c>
       <c r="S155" s="4" t="inlineStr">
         <is>
-          <t>2026-09-20T22:35:41Z</t>
+          <t>2026-09-21T23:27:49Z</t>
         </is>
       </c>
     </row>
@@ -13669,7 +13669,7 @@
       </c>
       <c r="S156" s="4" t="inlineStr">
         <is>
-          <t>2026-09-20T22:35:41Z</t>
+          <t>2026-09-21T23:27:49Z</t>
         </is>
       </c>
     </row>
@@ -13758,7 +13758,7 @@
       </c>
       <c r="S157" s="4" t="inlineStr">
         <is>
-          <t>2026-09-20T22:35:41Z</t>
+          <t>2026-09-21T23:27:49Z</t>
         </is>
       </c>
     </row>
@@ -13843,7 +13843,7 @@
       </c>
       <c r="S158" s="4" t="inlineStr">
         <is>
-          <t>2026-09-20T22:35:41Z</t>
+          <t>2026-09-21T23:27:49Z</t>
         </is>
       </c>
     </row>
@@ -13932,7 +13932,7 @@
       </c>
       <c r="S159" s="4" t="inlineStr">
         <is>
-          <t>2026-09-20T22:35:41Z</t>
+          <t>2026-09-21T23:27:49Z</t>
         </is>
       </c>
     </row>
@@ -14021,7 +14021,7 @@
       </c>
       <c r="S160" s="4" t="inlineStr">
         <is>
-          <t>2026-09-20T22:35:41Z</t>
+          <t>2026-09-21T23:27:49Z</t>
         </is>
       </c>
     </row>
@@ -14106,7 +14106,7 @@
       </c>
       <c r="S161" s="4" t="inlineStr">
         <is>
-          <t>2026-09-20T22:35:41Z</t>
+          <t>2026-09-21T23:27:49Z</t>
         </is>
       </c>
     </row>
@@ -14195,7 +14195,7 @@
       </c>
       <c r="S162" s="4" t="inlineStr">
         <is>
-          <t>2026-09-20T22:35:41Z</t>
+          <t>2026-09-21T23:27:49Z</t>
         </is>
       </c>
     </row>
@@ -14284,7 +14284,7 @@
       </c>
       <c r="S163" s="4" t="inlineStr">
         <is>
-          <t>2026-09-20T22:35:41Z</t>
+          <t>2026-09-21T23:27:49Z</t>
         </is>
       </c>
     </row>
@@ -14369,7 +14369,7 @@
       </c>
       <c r="S164" s="4" t="inlineStr">
         <is>
-          <t>2026-09-20T22:35:41Z</t>
+          <t>2026-09-21T23:27:49Z</t>
         </is>
       </c>
     </row>
@@ -14458,7 +14458,7 @@
       </c>
       <c r="S165" s="4" t="inlineStr">
         <is>
-          <t>2026-09-20T22:35:41Z</t>
+          <t>2026-09-21T23:27:49Z</t>
         </is>
       </c>
     </row>
@@ -14547,7 +14547,7 @@
       </c>
       <c r="S166" s="4" t="inlineStr">
         <is>
-          <t>2026-09-20T22:35:41Z</t>
+          <t>2026-09-21T23:27:49Z</t>
         </is>
       </c>
     </row>
@@ -14632,7 +14632,7 @@
       </c>
       <c r="S167" s="4" t="inlineStr">
         <is>
-          <t>2026-09-20T22:35:41Z</t>
+          <t>2026-09-21T23:27:49Z</t>
         </is>
       </c>
     </row>
@@ -14721,7 +14721,7 @@
       </c>
       <c r="S168" s="4" t="inlineStr">
         <is>
-          <t>2026-09-20T22:35:41Z</t>
+          <t>2026-09-21T23:27:49Z</t>
         </is>
       </c>
     </row>
@@ -14810,7 +14810,7 @@
       </c>
       <c r="S169" s="4" t="inlineStr">
         <is>
-          <t>2026-09-20T22:35:41Z</t>
+          <t>2026-09-21T23:27:49Z</t>
         </is>
       </c>
     </row>
@@ -14895,7 +14895,7 @@
       </c>
       <c r="S170" s="4" t="inlineStr">
         <is>
-          <t>2026-09-20T22:35:41Z</t>
+          <t>2026-09-21T23:27:49Z</t>
         </is>
       </c>
     </row>
@@ -14984,7 +14984,7 @@
       </c>
       <c r="S171" s="4" t="inlineStr">
         <is>
-          <t>2026-09-20T22:35:41Z</t>
+          <t>2026-09-21T23:27:49Z</t>
         </is>
       </c>
     </row>
@@ -15073,7 +15073,7 @@
       </c>
       <c r="S172" s="4" t="inlineStr">
         <is>
-          <t>2026-09-20T22:35:41Z</t>
+          <t>2026-09-21T23:27:49Z</t>
         </is>
       </c>
     </row>
@@ -15158,7 +15158,7 @@
       </c>
       <c r="S173" s="4" t="inlineStr">
         <is>
-          <t>2026-09-20T22:35:41Z</t>
+          <t>2026-09-21T23:27:49Z</t>
         </is>
       </c>
     </row>
@@ -15247,7 +15247,7 @@
       </c>
       <c r="S174" s="4" t="inlineStr">
         <is>
-          <t>2026-09-20T22:35:41Z</t>
+          <t>2026-09-21T23:27:49Z</t>
         </is>
       </c>
     </row>
@@ -15336,7 +15336,7 @@
       </c>
       <c r="S175" s="4" t="inlineStr">
         <is>
-          <t>2026-09-20T22:35:41Z</t>
+          <t>2026-09-21T23:27:49Z</t>
         </is>
       </c>
     </row>
@@ -15421,7 +15421,7 @@
       </c>
       <c r="S176" s="4" t="inlineStr">
         <is>
-          <t>2026-09-20T22:35:41Z</t>
+          <t>2026-09-21T23:27:49Z</t>
         </is>
       </c>
     </row>
@@ -15510,7 +15510,7 @@
       </c>
       <c r="S177" s="4" t="inlineStr">
         <is>
-          <t>2026-09-20T22:35:41Z</t>
+          <t>2026-09-21T23:27:49Z</t>
         </is>
       </c>
     </row>
@@ -15599,7 +15599,7 @@
       </c>
       <c r="S178" s="4" t="inlineStr">
         <is>
-          <t>2026-09-20T22:35:41Z</t>
+          <t>2026-09-21T23:27:49Z</t>
         </is>
       </c>
     </row>
@@ -15688,7 +15688,7 @@
       </c>
       <c r="S179" s="4" t="inlineStr">
         <is>
-          <t>2026-09-20T22:35:41Z</t>
+          <t>2026-09-21T23:27:49Z</t>
         </is>
       </c>
     </row>
@@ -15777,7 +15777,7 @@
       </c>
       <c r="S180" s="4" t="inlineStr">
         <is>
-          <t>2026-09-20T22:35:41Z</t>
+          <t>2026-09-21T23:27:49Z</t>
         </is>
       </c>
     </row>
@@ -15866,7 +15866,7 @@
       </c>
       <c r="S181" s="4" t="inlineStr">
         <is>
-          <t>2026-09-20T22:35:41Z</t>
+          <t>2026-09-21T23:27:49Z</t>
         </is>
       </c>
     </row>
@@ -15955,7 +15955,7 @@
       </c>
       <c r="S182" s="4" t="inlineStr">
         <is>
-          <t>2026-09-20T22:35:41Z</t>
+          <t>2026-09-21T23:27:49Z</t>
         </is>
       </c>
     </row>
@@ -16044,7 +16044,7 @@
       </c>
       <c r="S183" s="4" t="inlineStr">
         <is>
-          <t>2026-09-20T22:35:41Z</t>
+          <t>2026-09-21T23:27:49Z</t>
         </is>
       </c>
     </row>
@@ -16133,7 +16133,7 @@
       </c>
       <c r="S184" s="4" t="inlineStr">
         <is>
-          <t>2026-09-20T22:35:41Z</t>
+          <t>2026-09-21T23:27:49Z</t>
         </is>
       </c>
     </row>
@@ -16222,7 +16222,7 @@
       </c>
       <c r="S185" s="4" t="inlineStr">
         <is>
-          <t>2026-09-20T22:35:41Z</t>
+          <t>2026-09-21T23:27:49Z</t>
         </is>
       </c>
     </row>
@@ -16311,7 +16311,7 @@
       </c>
       <c r="S186" s="4" t="inlineStr">
         <is>
-          <t>2026-09-20T22:35:41Z</t>
+          <t>2026-09-21T23:27:49Z</t>
         </is>
       </c>
     </row>
@@ -16400,7 +16400,7 @@
       </c>
       <c r="S187" s="4" t="inlineStr">
         <is>
-          <t>2026-09-20T22:35:41Z</t>
+          <t>2026-09-21T23:27:49Z</t>
         </is>
       </c>
     </row>
@@ -16489,7 +16489,7 @@
       </c>
       <c r="S188" s="4" t="inlineStr">
         <is>
-          <t>2026-09-20T22:35:41Z</t>
+          <t>2026-09-21T23:27:49Z</t>
         </is>
       </c>
     </row>
@@ -16578,7 +16578,7 @@
       </c>
       <c r="S189" s="4" t="inlineStr">
         <is>
-          <t>2026-09-20T22:35:41Z</t>
+          <t>2026-09-21T23:27:49Z</t>
         </is>
       </c>
     </row>
@@ -16663,7 +16663,7 @@
       </c>
       <c r="S190" s="4" t="inlineStr">
         <is>
-          <t>2026-09-20T22:35:41Z</t>
+          <t>2026-09-21T23:27:49Z</t>
         </is>
       </c>
     </row>
@@ -16748,7 +16748,7 @@
       </c>
       <c r="S191" s="4" t="inlineStr">
         <is>
-          <t>2026-09-20T22:35:41Z</t>
+          <t>2026-09-21T23:27:49Z</t>
         </is>
       </c>
     </row>
@@ -16833,7 +16833,7 @@
       </c>
       <c r="S192" s="4" t="inlineStr">
         <is>
-          <t>2026-09-20T22:35:41Z</t>
+          <t>2026-09-21T23:27:49Z</t>
         </is>
       </c>
     </row>
@@ -16918,7 +16918,7 @@
       </c>
       <c r="S193" s="4" t="inlineStr">
         <is>
-          <t>2026-09-20T22:35:41Z</t>
+          <t>2026-09-21T23:27:49Z</t>
         </is>
       </c>
     </row>
@@ -17003,7 +17003,7 @@
       </c>
       <c r="S194" s="4" t="inlineStr">
         <is>
-          <t>2026-09-20T22:35:41Z</t>
+          <t>2026-09-21T23:27:49Z</t>
         </is>
       </c>
     </row>
@@ -17088,7 +17088,7 @@
       </c>
       <c r="S195" s="4" t="inlineStr">
         <is>
-          <t>2026-09-20T22:35:41Z</t>
+          <t>2026-09-21T23:27:49Z</t>
         </is>
       </c>
     </row>
@@ -17173,7 +17173,7 @@
       </c>
       <c r="S196" s="4" t="inlineStr">
         <is>
-          <t>2026-09-20T22:35:41Z</t>
+          <t>2026-09-21T23:27:49Z</t>
         </is>
       </c>
     </row>
@@ -17258,7 +17258,7 @@
       </c>
       <c r="S197" s="4" t="inlineStr">
         <is>
-          <t>2026-09-20T22:35:41Z</t>
+          <t>2026-09-21T23:27:49Z</t>
         </is>
       </c>
     </row>
@@ -17343,7 +17343,7 @@
       </c>
       <c r="S198" s="4" t="inlineStr">
         <is>
-          <t>2026-09-20T22:35:41Z</t>
+          <t>2026-09-21T23:27:49Z</t>
         </is>
       </c>
     </row>
@@ -17428,7 +17428,7 @@
       </c>
       <c r="S199" s="4" t="inlineStr">
         <is>
-          <t>2026-09-20T22:35:41Z</t>
+          <t>2026-09-21T23:27:49Z</t>
         </is>
       </c>
     </row>
@@ -17513,7 +17513,7 @@
       </c>
       <c r="S200" s="4" t="inlineStr">
         <is>
-          <t>2026-09-20T22:35:41Z</t>
+          <t>2026-09-21T23:27:49Z</t>
         </is>
       </c>
     </row>
@@ -17598,7 +17598,7 @@
       </c>
       <c r="S201" s="4" t="inlineStr">
         <is>
-          <t>2026-09-20T22:35:41Z</t>
+          <t>2026-09-21T23:27:49Z</t>
         </is>
       </c>
     </row>
@@ -17683,7 +17683,7 @@
       </c>
       <c r="S202" s="4" t="inlineStr">
         <is>
-          <t>2026-09-20T22:35:41Z</t>
+          <t>2026-09-21T23:27:49Z</t>
         </is>
       </c>
     </row>
@@ -17768,7 +17768,7 @@
       </c>
       <c r="S203" s="4" t="inlineStr">
         <is>
-          <t>2026-09-20T22:35:41Z</t>
+          <t>2026-09-21T23:27:49Z</t>
         </is>
       </c>
     </row>
@@ -17853,7 +17853,7 @@
       </c>
       <c r="S204" s="4" t="inlineStr">
         <is>
-          <t>2026-09-20T22:35:41Z</t>
+          <t>2026-09-21T23:27:49Z</t>
         </is>
       </c>
     </row>
@@ -17938,7 +17938,7 @@
       </c>
       <c r="S205" s="4" t="inlineStr">
         <is>
-          <t>2026-09-20T22:35:41Z</t>
+          <t>2026-09-21T23:27:49Z</t>
         </is>
       </c>
     </row>
@@ -18023,7 +18023,7 @@
       </c>
       <c r="S206" s="4" t="inlineStr">
         <is>
-          <t>2026-09-20T22:35:41Z</t>
+          <t>2026-09-21T23:27:49Z</t>
         </is>
       </c>
     </row>
@@ -18108,7 +18108,7 @@
       </c>
       <c r="S207" s="4" t="inlineStr">
         <is>
-          <t>2026-09-20T22:35:41Z</t>
+          <t>2026-09-21T23:27:49Z</t>
         </is>
       </c>
     </row>
@@ -18193,7 +18193,7 @@
       </c>
       <c r="S208" s="4" t="inlineStr">
         <is>
-          <t>2026-09-20T22:35:41Z</t>
+          <t>2026-09-21T23:27:49Z</t>
         </is>
       </c>
     </row>
@@ -18278,7 +18278,7 @@
       </c>
       <c r="S209" s="4" t="inlineStr">
         <is>
-          <t>2026-09-20T22:35:41Z</t>
+          <t>2026-09-21T23:27:49Z</t>
         </is>
       </c>
     </row>
@@ -18363,7 +18363,7 @@
       </c>
       <c r="S210" s="4" t="inlineStr">
         <is>
-          <t>2026-09-20T22:35:41Z</t>
+          <t>2026-09-21T23:27:49Z</t>
         </is>
       </c>
     </row>
@@ -18452,7 +18452,7 @@
       </c>
       <c r="S211" s="4" t="inlineStr">
         <is>
-          <t>2026-09-20T22:35:41Z</t>
+          <t>2026-09-21T23:27:49Z</t>
         </is>
       </c>
     </row>
@@ -18541,7 +18541,7 @@
       </c>
       <c r="S212" s="4" t="inlineStr">
         <is>
-          <t>2026-09-20T22:35:41Z</t>
+          <t>2026-09-21T23:27:49Z</t>
         </is>
       </c>
     </row>
@@ -18626,7 +18626,7 @@
       </c>
       <c r="S213" s="4" t="inlineStr">
         <is>
-          <t>2026-09-20T22:35:41Z</t>
+          <t>2026-09-21T23:27:49Z</t>
         </is>
       </c>
     </row>
@@ -18715,7 +18715,7 @@
       </c>
       <c r="S214" s="4" t="inlineStr">
         <is>
-          <t>2026-09-20T22:35:41Z</t>
+          <t>2026-09-21T23:27:49Z</t>
         </is>
       </c>
     </row>
@@ -18804,7 +18804,7 @@
       </c>
       <c r="S215" s="4" t="inlineStr">
         <is>
-          <t>2026-09-20T22:35:41Z</t>
+          <t>2026-09-21T23:27:49Z</t>
         </is>
       </c>
     </row>
@@ -18889,7 +18889,7 @@
       </c>
       <c r="S216" s="4" t="inlineStr">
         <is>
-          <t>2026-09-20T22:35:41Z</t>
+          <t>2026-09-21T23:27:49Z</t>
         </is>
       </c>
     </row>
@@ -18978,7 +18978,7 @@
       </c>
       <c r="S217" s="4" t="inlineStr">
         <is>
-          <t>2026-09-20T22:35:41Z</t>
+          <t>2026-09-21T23:27:49Z</t>
         </is>
       </c>
     </row>
@@ -19067,7 +19067,7 @@
       </c>
       <c r="S218" s="4" t="inlineStr">
         <is>
-          <t>2026-09-20T22:35:41Z</t>
+          <t>2026-09-21T23:27:49Z</t>
         </is>
       </c>
     </row>
@@ -19152,7 +19152,7 @@
       </c>
       <c r="S219" s="4" t="inlineStr">
         <is>
-          <t>2026-09-20T22:35:41Z</t>
+          <t>2026-09-21T23:27:49Z</t>
         </is>
       </c>
     </row>
@@ -19241,7 +19241,7 @@
       </c>
       <c r="S220" s="4" t="inlineStr">
         <is>
-          <t>2026-09-20T22:35:41Z</t>
+          <t>2026-09-21T23:27:49Z</t>
         </is>
       </c>
     </row>
@@ -19330,7 +19330,7 @@
       </c>
       <c r="S221" s="4" t="inlineStr">
         <is>
-          <t>2026-09-20T22:35:41Z</t>
+          <t>2026-09-21T23:27:49Z</t>
         </is>
       </c>
     </row>
@@ -19415,7 +19415,7 @@
       </c>
       <c r="S222" s="4" t="inlineStr">
         <is>
-          <t>2026-09-20T22:35:41Z</t>
+          <t>2026-09-21T23:27:49Z</t>
         </is>
       </c>
     </row>
@@ -19504,7 +19504,7 @@
       </c>
       <c r="S223" s="4" t="inlineStr">
         <is>
-          <t>2026-09-20T22:35:41Z</t>
+          <t>2026-09-21T23:27:49Z</t>
         </is>
       </c>
     </row>
@@ -19593,7 +19593,7 @@
       </c>
       <c r="S224" s="4" t="inlineStr">
         <is>
-          <t>2026-09-20T22:35:41Z</t>
+          <t>2026-09-21T23:27:49Z</t>
         </is>
       </c>
     </row>
@@ -19678,7 +19678,7 @@
       </c>
       <c r="S225" s="4" t="inlineStr">
         <is>
-          <t>2026-09-20T22:35:41Z</t>
+          <t>2026-09-21T23:27:49Z</t>
         </is>
       </c>
     </row>
@@ -19767,7 +19767,7 @@
       </c>
       <c r="S226" s="4" t="inlineStr">
         <is>
-          <t>2026-09-20T22:35:41Z</t>
+          <t>2026-09-21T23:27:49Z</t>
         </is>
       </c>
     </row>
@@ -19856,7 +19856,7 @@
       </c>
       <c r="S227" s="4" t="inlineStr">
         <is>
-          <t>2026-09-20T22:35:41Z</t>
+          <t>2026-09-21T23:27:49Z</t>
         </is>
       </c>
     </row>
@@ -19941,7 +19941,7 @@
       </c>
       <c r="S228" s="4" t="inlineStr">
         <is>
-          <t>2026-09-20T22:35:41Z</t>
+          <t>2026-09-21T23:27:49Z</t>
         </is>
       </c>
     </row>
@@ -20030,7 +20030,7 @@
       </c>
       <c r="S229" s="4" t="inlineStr">
         <is>
-          <t>2026-09-20T22:35:41Z</t>
+          <t>2026-09-21T23:27:49Z</t>
         </is>
       </c>
     </row>
@@ -20119,7 +20119,7 @@
       </c>
       <c r="S230" s="4" t="inlineStr">
         <is>
-          <t>2026-09-20T22:35:41Z</t>
+          <t>2026-09-21T23:27:49Z</t>
         </is>
       </c>
     </row>
@@ -20204,7 +20204,7 @@
       </c>
       <c r="S231" s="4" t="inlineStr">
         <is>
-          <t>2026-09-20T22:35:41Z</t>
+          <t>2026-09-21T23:27:49Z</t>
         </is>
       </c>
     </row>
@@ -20293,7 +20293,7 @@
       </c>
       <c r="S232" s="4" t="inlineStr">
         <is>
-          <t>2026-09-20T22:35:41Z</t>
+          <t>2026-09-21T23:27:49Z</t>
         </is>
       </c>
     </row>
@@ -20382,7 +20382,7 @@
       </c>
       <c r="S233" s="4" t="inlineStr">
         <is>
-          <t>2026-09-20T22:35:41Z</t>
+          <t>2026-09-21T23:27:49Z</t>
         </is>
       </c>
     </row>
@@ -20467,7 +20467,7 @@
       </c>
       <c r="S234" s="4" t="inlineStr">
         <is>
-          <t>2026-09-20T22:35:41Z</t>
+          <t>2026-09-21T23:27:49Z</t>
         </is>
       </c>
     </row>
@@ -20556,7 +20556,7 @@
       </c>
       <c r="S235" s="4" t="inlineStr">
         <is>
-          <t>2026-09-20T22:35:41Z</t>
+          <t>2026-09-21T23:27:49Z</t>
         </is>
       </c>
     </row>
@@ -20645,7 +20645,7 @@
       </c>
       <c r="S236" s="4" t="inlineStr">
         <is>
-          <t>2026-09-20T22:35:41Z</t>
+          <t>2026-09-21T23:27:49Z</t>
         </is>
       </c>
     </row>
@@ -20730,7 +20730,7 @@
       </c>
       <c r="S237" s="4" t="inlineStr">
         <is>
-          <t>2026-09-20T22:35:41Z</t>
+          <t>2026-09-21T23:27:49Z</t>
         </is>
       </c>
     </row>
@@ -20819,7 +20819,7 @@
       </c>
       <c r="S238" s="4" t="inlineStr">
         <is>
-          <t>2026-09-20T22:35:41Z</t>
+          <t>2026-09-21T23:27:49Z</t>
         </is>
       </c>
     </row>
@@ -20908,7 +20908,7 @@
       </c>
       <c r="S239" s="4" t="inlineStr">
         <is>
-          <t>2026-09-20T22:35:41Z</t>
+          <t>2026-09-21T23:27:49Z</t>
         </is>
       </c>
     </row>
@@ -20997,7 +20997,7 @@
       </c>
       <c r="S240" s="4" t="inlineStr">
         <is>
-          <t>2026-09-20T22:35:41Z</t>
+          <t>2026-09-21T23:27:49Z</t>
         </is>
       </c>
     </row>
@@ -21086,7 +21086,7 @@
       </c>
       <c r="S241" s="4" t="inlineStr">
         <is>
-          <t>2026-09-20T22:35:41Z</t>
+          <t>2026-09-21T23:27:49Z</t>
         </is>
       </c>
     </row>
@@ -21175,7 +21175,7 @@
       </c>
       <c r="S242" s="4" t="inlineStr">
         <is>
-          <t>2026-09-20T22:35:41Z</t>
+          <t>2026-09-21T23:27:49Z</t>
         </is>
       </c>
     </row>
@@ -21264,7 +21264,7 @@
       </c>
       <c r="S243" s="4" t="inlineStr">
         <is>
-          <t>2026-09-20T22:35:41Z</t>
+          <t>2026-09-21T23:27:49Z</t>
         </is>
       </c>
     </row>
@@ -21353,7 +21353,7 @@
       </c>
       <c r="S244" s="4" t="inlineStr">
         <is>
-          <t>2026-09-20T22:35:41Z</t>
+          <t>2026-09-21T23:27:49Z</t>
         </is>
       </c>
     </row>
@@ -21442,7 +21442,7 @@
       </c>
       <c r="S245" s="4" t="inlineStr">
         <is>
-          <t>2026-09-20T22:35:41Z</t>
+          <t>2026-09-21T23:27:49Z</t>
         </is>
       </c>
     </row>
@@ -21531,7 +21531,7 @@
       </c>
       <c r="S246" s="4" t="inlineStr">
         <is>
-          <t>2026-09-20T22:35:41Z</t>
+          <t>2026-09-21T23:27:49Z</t>
         </is>
       </c>
     </row>
@@ -21620,7 +21620,7 @@
       </c>
       <c r="S247" s="4" t="inlineStr">
         <is>
-          <t>2026-09-20T22:35:41Z</t>
+          <t>2026-09-21T23:27:49Z</t>
         </is>
       </c>
     </row>
@@ -21709,7 +21709,7 @@
       </c>
       <c r="S248" s="4" t="inlineStr">
         <is>
-          <t>2026-09-20T22:35:41Z</t>
+          <t>2026-09-21T23:27:49Z</t>
         </is>
       </c>
     </row>
@@ -21798,7 +21798,7 @@
       </c>
       <c r="S249" s="4" t="inlineStr">
         <is>
-          <t>2026-09-20T22:35:41Z</t>
+          <t>2026-09-21T23:27:49Z</t>
         </is>
       </c>
     </row>
@@ -21887,7 +21887,7 @@
       </c>
       <c r="S250" s="4" t="inlineStr">
         <is>
-          <t>2026-09-20T22:35:41Z</t>
+          <t>2026-09-21T23:27:49Z</t>
         </is>
       </c>
     </row>
@@ -22019,7 +22019,7 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>2026-09-20T22:35:41Z</t>
+          <t>2026-09-21T23:27:49Z</t>
         </is>
       </c>
     </row>
@@ -22099,7 +22099,7 @@
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>{"dataset_id": "bcv_pib_sector_institucional_anual", "title": "Producto interno bruto por sector institucional anual", "table": "Variaciones porcentuales", "source_file": "5_2_1_si_anual.xlsx", "base": "2007", "price_type": "Precios constantes", "measure": "Variación porcentual interanual", "frequency": "Anual", "period": "2025", "year": 2025, "quarter": null, "classification": "Sector institucional", "component": "Impuestos netos sobre los productos", "value": 10.600260421283764, "unit": "Porcentaje", "status": "Preliminar", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/cuentas_macroeconomicas/5_2_1_si_anual.xlsx", "fetched_at": "2026-09-20T22:35:41Z"}</t>
+          <t>{"dataset_id": "bcv_pib_sector_institucional_anual", "title": "Producto interno bruto por sector institucional anual", "table": "Variaciones porcentuales", "source_file": "5_2_1_si_anual.xlsx", "base": "2007", "price_type": "Precios constantes", "measure": "Variación porcentual interanual", "frequency": "Anual", "period": "2025", "year": 2025, "quarter": null, "classification": "Sector institucional", "component": "Impuestos netos sobre los productos", "value": 10.600260421283764, "unit": "Porcentaje", "status": "Preliminar", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/cuentas_macroeconomicas/5_2_1_si_anual.xlsx", "fetched_at": "2026-09-21T23:27:49Z"}</t>
         </is>
       </c>
     </row>

--- a/assets/data/bcv/excel/ove_bcv_pib_sector_institucional_anual.xlsx
+++ b/assets/data/bcv/excel/ove_bcv_pib_sector_institucional_anual.xlsx
@@ -736,7 +736,7 @@
       </c>
       <c r="S7" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21T23:27:49Z</t>
+          <t>2026-09-22T17:38:14Z</t>
         </is>
       </c>
     </row>
@@ -821,7 +821,7 @@
       </c>
       <c r="S8" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21T23:27:49Z</t>
+          <t>2026-09-22T17:38:14Z</t>
         </is>
       </c>
     </row>
@@ -906,7 +906,7 @@
       </c>
       <c r="S9" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21T23:27:49Z</t>
+          <t>2026-09-22T17:38:14Z</t>
         </is>
       </c>
     </row>
@@ -991,7 +991,7 @@
       </c>
       <c r="S10" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21T23:27:49Z</t>
+          <t>2026-09-22T17:38:14Z</t>
         </is>
       </c>
     </row>
@@ -1076,7 +1076,7 @@
       </c>
       <c r="S11" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21T23:27:49Z</t>
+          <t>2026-09-22T17:38:14Z</t>
         </is>
       </c>
     </row>
@@ -1161,7 +1161,7 @@
       </c>
       <c r="S12" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21T23:27:49Z</t>
+          <t>2026-09-22T17:38:14Z</t>
         </is>
       </c>
     </row>
@@ -1246,7 +1246,7 @@
       </c>
       <c r="S13" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21T23:27:49Z</t>
+          <t>2026-09-22T17:38:14Z</t>
         </is>
       </c>
     </row>
@@ -1331,7 +1331,7 @@
       </c>
       <c r="S14" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21T23:27:49Z</t>
+          <t>2026-09-22T17:38:14Z</t>
         </is>
       </c>
     </row>
@@ -1416,7 +1416,7 @@
       </c>
       <c r="S15" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21T23:27:49Z</t>
+          <t>2026-09-22T17:38:14Z</t>
         </is>
       </c>
     </row>
@@ -1501,7 +1501,7 @@
       </c>
       <c r="S16" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21T23:27:49Z</t>
+          <t>2026-09-22T17:38:14Z</t>
         </is>
       </c>
     </row>
@@ -1586,7 +1586,7 @@
       </c>
       <c r="S17" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21T23:27:49Z</t>
+          <t>2026-09-22T17:38:14Z</t>
         </is>
       </c>
     </row>
@@ -1671,7 +1671,7 @@
       </c>
       <c r="S18" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21T23:27:49Z</t>
+          <t>2026-09-22T17:38:14Z</t>
         </is>
       </c>
     </row>
@@ -1756,7 +1756,7 @@
       </c>
       <c r="S19" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21T23:27:49Z</t>
+          <t>2026-09-22T17:38:14Z</t>
         </is>
       </c>
     </row>
@@ -1841,7 +1841,7 @@
       </c>
       <c r="S20" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21T23:27:49Z</t>
+          <t>2026-09-22T17:38:14Z</t>
         </is>
       </c>
     </row>
@@ -1926,7 +1926,7 @@
       </c>
       <c r="S21" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21T23:27:49Z</t>
+          <t>2026-09-22T17:38:14Z</t>
         </is>
       </c>
     </row>
@@ -2011,7 +2011,7 @@
       </c>
       <c r="S22" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21T23:27:49Z</t>
+          <t>2026-09-22T17:38:14Z</t>
         </is>
       </c>
     </row>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="S23" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21T23:27:49Z</t>
+          <t>2026-09-22T17:38:14Z</t>
         </is>
       </c>
     </row>
@@ -2181,7 +2181,7 @@
       </c>
       <c r="S24" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21T23:27:49Z</t>
+          <t>2026-09-22T17:38:14Z</t>
         </is>
       </c>
     </row>
@@ -2266,7 +2266,7 @@
       </c>
       <c r="S25" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21T23:27:49Z</t>
+          <t>2026-09-22T17:38:14Z</t>
         </is>
       </c>
     </row>
@@ -2351,7 +2351,7 @@
       </c>
       <c r="S26" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21T23:27:49Z</t>
+          <t>2026-09-22T17:38:14Z</t>
         </is>
       </c>
     </row>
@@ -2436,7 +2436,7 @@
       </c>
       <c r="S27" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21T23:27:49Z</t>
+          <t>2026-09-22T17:38:14Z</t>
         </is>
       </c>
     </row>
@@ -2525,7 +2525,7 @@
       </c>
       <c r="S28" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21T23:27:49Z</t>
+          <t>2026-09-22T17:38:14Z</t>
         </is>
       </c>
     </row>
@@ -2614,7 +2614,7 @@
       </c>
       <c r="S29" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21T23:27:49Z</t>
+          <t>2026-09-22T17:38:14Z</t>
         </is>
       </c>
     </row>
@@ -2699,7 +2699,7 @@
       </c>
       <c r="S30" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21T23:27:49Z</t>
+          <t>2026-09-22T17:38:14Z</t>
         </is>
       </c>
     </row>
@@ -2788,7 +2788,7 @@
       </c>
       <c r="S31" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21T23:27:49Z</t>
+          <t>2026-09-22T17:38:14Z</t>
         </is>
       </c>
     </row>
@@ -2877,7 +2877,7 @@
       </c>
       <c r="S32" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21T23:27:49Z</t>
+          <t>2026-09-22T17:38:14Z</t>
         </is>
       </c>
     </row>
@@ -2962,7 +2962,7 @@
       </c>
       <c r="S33" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21T23:27:49Z</t>
+          <t>2026-09-22T17:38:14Z</t>
         </is>
       </c>
     </row>
@@ -3051,7 +3051,7 @@
       </c>
       <c r="S34" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21T23:27:49Z</t>
+          <t>2026-09-22T17:38:14Z</t>
         </is>
       </c>
     </row>
@@ -3140,7 +3140,7 @@
       </c>
       <c r="S35" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21T23:27:49Z</t>
+          <t>2026-09-22T17:38:14Z</t>
         </is>
       </c>
     </row>
@@ -3225,7 +3225,7 @@
       </c>
       <c r="S36" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21T23:27:49Z</t>
+          <t>2026-09-22T17:38:14Z</t>
         </is>
       </c>
     </row>
@@ -3314,7 +3314,7 @@
       </c>
       <c r="S37" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21T23:27:49Z</t>
+          <t>2026-09-22T17:38:14Z</t>
         </is>
       </c>
     </row>
@@ -3403,7 +3403,7 @@
       </c>
       <c r="S38" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21T23:27:49Z</t>
+          <t>2026-09-22T17:38:14Z</t>
         </is>
       </c>
     </row>
@@ -3488,7 +3488,7 @@
       </c>
       <c r="S39" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21T23:27:49Z</t>
+          <t>2026-09-22T17:38:14Z</t>
         </is>
       </c>
     </row>
@@ -3577,7 +3577,7 @@
       </c>
       <c r="S40" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21T23:27:49Z</t>
+          <t>2026-09-22T17:38:14Z</t>
         </is>
       </c>
     </row>
@@ -3666,7 +3666,7 @@
       </c>
       <c r="S41" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21T23:27:49Z</t>
+          <t>2026-09-22T17:38:14Z</t>
         </is>
       </c>
     </row>
@@ -3751,7 +3751,7 @@
       </c>
       <c r="S42" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21T23:27:49Z</t>
+          <t>2026-09-22T17:38:14Z</t>
         </is>
       </c>
     </row>
@@ -3840,7 +3840,7 @@
       </c>
       <c r="S43" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21T23:27:49Z</t>
+          <t>2026-09-22T17:38:14Z</t>
         </is>
       </c>
     </row>
@@ -3929,7 +3929,7 @@
       </c>
       <c r="S44" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21T23:27:49Z</t>
+          <t>2026-09-22T17:38:14Z</t>
         </is>
       </c>
     </row>
@@ -4014,7 +4014,7 @@
       </c>
       <c r="S45" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21T23:27:49Z</t>
+          <t>2026-09-22T17:38:14Z</t>
         </is>
       </c>
     </row>
@@ -4103,7 +4103,7 @@
       </c>
       <c r="S46" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21T23:27:49Z</t>
+          <t>2026-09-22T17:38:14Z</t>
         </is>
       </c>
     </row>
@@ -4192,7 +4192,7 @@
       </c>
       <c r="S47" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21T23:27:49Z</t>
+          <t>2026-09-22T17:38:14Z</t>
         </is>
       </c>
     </row>
@@ -4277,7 +4277,7 @@
       </c>
       <c r="S48" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21T23:27:49Z</t>
+          <t>2026-09-22T17:38:14Z</t>
         </is>
       </c>
     </row>
@@ -4366,7 +4366,7 @@
       </c>
       <c r="S49" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21T23:27:49Z</t>
+          <t>2026-09-22T17:38:14Z</t>
         </is>
       </c>
     </row>
@@ -4455,7 +4455,7 @@
       </c>
       <c r="S50" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21T23:27:49Z</t>
+          <t>2026-09-22T17:38:14Z</t>
         </is>
       </c>
     </row>
@@ -4540,7 +4540,7 @@
       </c>
       <c r="S51" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21T23:27:49Z</t>
+          <t>2026-09-22T17:38:14Z</t>
         </is>
       </c>
     </row>
@@ -4629,7 +4629,7 @@
       </c>
       <c r="S52" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21T23:27:49Z</t>
+          <t>2026-09-22T17:38:14Z</t>
         </is>
       </c>
     </row>
@@ -4718,7 +4718,7 @@
       </c>
       <c r="S53" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21T23:27:49Z</t>
+          <t>2026-09-22T17:38:14Z</t>
         </is>
       </c>
     </row>
@@ -4803,7 +4803,7 @@
       </c>
       <c r="S54" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21T23:27:49Z</t>
+          <t>2026-09-22T17:38:14Z</t>
         </is>
       </c>
     </row>
@@ -4892,7 +4892,7 @@
       </c>
       <c r="S55" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21T23:27:49Z</t>
+          <t>2026-09-22T17:38:14Z</t>
         </is>
       </c>
     </row>
@@ -4981,7 +4981,7 @@
       </c>
       <c r="S56" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21T23:27:49Z</t>
+          <t>2026-09-22T17:38:14Z</t>
         </is>
       </c>
     </row>
@@ -5070,7 +5070,7 @@
       </c>
       <c r="S57" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21T23:27:49Z</t>
+          <t>2026-09-22T17:38:14Z</t>
         </is>
       </c>
     </row>
@@ -5159,7 +5159,7 @@
       </c>
       <c r="S58" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21T23:27:49Z</t>
+          <t>2026-09-22T17:38:14Z</t>
         </is>
       </c>
     </row>
@@ -5248,7 +5248,7 @@
       </c>
       <c r="S59" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21T23:27:49Z</t>
+          <t>2026-09-22T17:38:14Z</t>
         </is>
       </c>
     </row>
@@ -5337,7 +5337,7 @@
       </c>
       <c r="S60" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21T23:27:49Z</t>
+          <t>2026-09-22T17:38:14Z</t>
         </is>
       </c>
     </row>
@@ -5426,7 +5426,7 @@
       </c>
       <c r="S61" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21T23:27:49Z</t>
+          <t>2026-09-22T17:38:14Z</t>
         </is>
       </c>
     </row>
@@ -5515,7 +5515,7 @@
       </c>
       <c r="S62" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21T23:27:49Z</t>
+          <t>2026-09-22T17:38:14Z</t>
         </is>
       </c>
     </row>
@@ -5604,7 +5604,7 @@
       </c>
       <c r="S63" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21T23:27:49Z</t>
+          <t>2026-09-22T17:38:14Z</t>
         </is>
       </c>
     </row>
@@ -5693,7 +5693,7 @@
       </c>
       <c r="S64" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21T23:27:49Z</t>
+          <t>2026-09-22T17:38:14Z</t>
         </is>
       </c>
     </row>
@@ -5782,7 +5782,7 @@
       </c>
       <c r="S65" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21T23:27:49Z</t>
+          <t>2026-09-22T17:38:14Z</t>
         </is>
       </c>
     </row>
@@ -5871,7 +5871,7 @@
       </c>
       <c r="S66" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21T23:27:49Z</t>
+          <t>2026-09-22T17:38:14Z</t>
         </is>
       </c>
     </row>
@@ -5960,7 +5960,7 @@
       </c>
       <c r="S67" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21T23:27:49Z</t>
+          <t>2026-09-22T17:38:14Z</t>
         </is>
       </c>
     </row>
@@ -6045,7 +6045,7 @@
       </c>
       <c r="S68" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21T23:27:49Z</t>
+          <t>2026-09-22T17:38:14Z</t>
         </is>
       </c>
     </row>
@@ -6130,7 +6130,7 @@
       </c>
       <c r="S69" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21T23:27:49Z</t>
+          <t>2026-09-22T17:38:14Z</t>
         </is>
       </c>
     </row>
@@ -6215,7 +6215,7 @@
       </c>
       <c r="S70" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21T23:27:49Z</t>
+          <t>2026-09-22T17:38:14Z</t>
         </is>
       </c>
     </row>
@@ -6300,7 +6300,7 @@
       </c>
       <c r="S71" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21T23:27:49Z</t>
+          <t>2026-09-22T17:38:14Z</t>
         </is>
       </c>
     </row>
@@ -6385,7 +6385,7 @@
       </c>
       <c r="S72" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21T23:27:49Z</t>
+          <t>2026-09-22T17:38:14Z</t>
         </is>
       </c>
     </row>
@@ -6470,7 +6470,7 @@
       </c>
       <c r="S73" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21T23:27:49Z</t>
+          <t>2026-09-22T17:38:14Z</t>
         </is>
       </c>
     </row>
@@ -6555,7 +6555,7 @@
       </c>
       <c r="S74" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21T23:27:49Z</t>
+          <t>2026-09-22T17:38:14Z</t>
         </is>
       </c>
     </row>
@@ -6640,7 +6640,7 @@
       </c>
       <c r="S75" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21T23:27:49Z</t>
+          <t>2026-09-22T17:38:14Z</t>
         </is>
       </c>
     </row>
@@ -6725,7 +6725,7 @@
       </c>
       <c r="S76" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21T23:27:49Z</t>
+          <t>2026-09-22T17:38:14Z</t>
         </is>
       </c>
     </row>
@@ -6810,7 +6810,7 @@
       </c>
       <c r="S77" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21T23:27:49Z</t>
+          <t>2026-09-22T17:38:14Z</t>
         </is>
       </c>
     </row>
@@ -6895,7 +6895,7 @@
       </c>
       <c r="S78" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21T23:27:49Z</t>
+          <t>2026-09-22T17:38:14Z</t>
         </is>
       </c>
     </row>
@@ -6980,7 +6980,7 @@
       </c>
       <c r="S79" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21T23:27:49Z</t>
+          <t>2026-09-22T17:38:14Z</t>
         </is>
       </c>
     </row>
@@ -7065,7 +7065,7 @@
       </c>
       <c r="S80" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21T23:27:49Z</t>
+          <t>2026-09-22T17:38:14Z</t>
         </is>
       </c>
     </row>
@@ -7150,7 +7150,7 @@
       </c>
       <c r="S81" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21T23:27:49Z</t>
+          <t>2026-09-22T17:38:14Z</t>
         </is>
       </c>
     </row>
@@ -7235,7 +7235,7 @@
       </c>
       <c r="S82" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21T23:27:49Z</t>
+          <t>2026-09-22T17:38:14Z</t>
         </is>
       </c>
     </row>
@@ -7320,7 +7320,7 @@
       </c>
       <c r="S83" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21T23:27:49Z</t>
+          <t>2026-09-22T17:38:14Z</t>
         </is>
       </c>
     </row>
@@ -7405,7 +7405,7 @@
       </c>
       <c r="S84" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21T23:27:49Z</t>
+          <t>2026-09-22T17:38:14Z</t>
         </is>
       </c>
     </row>
@@ -7490,7 +7490,7 @@
       </c>
       <c r="S85" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21T23:27:49Z</t>
+          <t>2026-09-22T17:38:14Z</t>
         </is>
       </c>
     </row>
@@ -7575,7 +7575,7 @@
       </c>
       <c r="S86" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21T23:27:49Z</t>
+          <t>2026-09-22T17:38:14Z</t>
         </is>
       </c>
     </row>
@@ -7660,7 +7660,7 @@
       </c>
       <c r="S87" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21T23:27:49Z</t>
+          <t>2026-09-22T17:38:14Z</t>
         </is>
       </c>
     </row>
@@ -7745,7 +7745,7 @@
       </c>
       <c r="S88" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21T23:27:49Z</t>
+          <t>2026-09-22T17:38:14Z</t>
         </is>
       </c>
     </row>
@@ -7834,7 +7834,7 @@
       </c>
       <c r="S89" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21T23:27:49Z</t>
+          <t>2026-09-22T17:38:14Z</t>
         </is>
       </c>
     </row>
@@ -7923,7 +7923,7 @@
       </c>
       <c r="S90" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21T23:27:49Z</t>
+          <t>2026-09-22T17:38:14Z</t>
         </is>
       </c>
     </row>
@@ -8008,7 +8008,7 @@
       </c>
       <c r="S91" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21T23:27:49Z</t>
+          <t>2026-09-22T17:38:14Z</t>
         </is>
       </c>
     </row>
@@ -8097,7 +8097,7 @@
       </c>
       <c r="S92" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21T23:27:49Z</t>
+          <t>2026-09-22T17:38:14Z</t>
         </is>
       </c>
     </row>
@@ -8186,7 +8186,7 @@
       </c>
       <c r="S93" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21T23:27:49Z</t>
+          <t>2026-09-22T17:38:14Z</t>
         </is>
       </c>
     </row>
@@ -8271,7 +8271,7 @@
       </c>
       <c r="S94" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21T23:27:49Z</t>
+          <t>2026-09-22T17:38:14Z</t>
         </is>
       </c>
     </row>
@@ -8360,7 +8360,7 @@
       </c>
       <c r="S95" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21T23:27:49Z</t>
+          <t>2026-09-22T17:38:14Z</t>
         </is>
       </c>
     </row>
@@ -8449,7 +8449,7 @@
       </c>
       <c r="S96" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21T23:27:49Z</t>
+          <t>2026-09-22T17:38:14Z</t>
         </is>
       </c>
     </row>
@@ -8534,7 +8534,7 @@
       </c>
       <c r="S97" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21T23:27:49Z</t>
+          <t>2026-09-22T17:38:14Z</t>
         </is>
       </c>
     </row>
@@ -8623,7 +8623,7 @@
       </c>
       <c r="S98" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21T23:27:49Z</t>
+          <t>2026-09-22T17:38:14Z</t>
         </is>
       </c>
     </row>
@@ -8712,7 +8712,7 @@
       </c>
       <c r="S99" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21T23:27:49Z</t>
+          <t>2026-09-22T17:38:14Z</t>
         </is>
       </c>
     </row>
@@ -8797,7 +8797,7 @@
       </c>
       <c r="S100" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21T23:27:49Z</t>
+          <t>2026-09-22T17:38:14Z</t>
         </is>
       </c>
     </row>
@@ -8886,7 +8886,7 @@
       </c>
       <c r="S101" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21T23:27:49Z</t>
+          <t>2026-09-22T17:38:14Z</t>
         </is>
       </c>
     </row>
@@ -8975,7 +8975,7 @@
       </c>
       <c r="S102" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21T23:27:49Z</t>
+          <t>2026-09-22T17:38:14Z</t>
         </is>
       </c>
     </row>
@@ -9060,7 +9060,7 @@
       </c>
       <c r="S103" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21T23:27:49Z</t>
+          <t>2026-09-22T17:38:14Z</t>
         </is>
       </c>
     </row>
@@ -9149,7 +9149,7 @@
       </c>
       <c r="S104" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21T23:27:49Z</t>
+          <t>2026-09-22T17:38:14Z</t>
         </is>
       </c>
     </row>
@@ -9238,7 +9238,7 @@
       </c>
       <c r="S105" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21T23:27:49Z</t>
+          <t>2026-09-22T17:38:14Z</t>
         </is>
       </c>
     </row>
@@ -9323,7 +9323,7 @@
       </c>
       <c r="S106" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21T23:27:49Z</t>
+          <t>2026-09-22T17:38:14Z</t>
         </is>
       </c>
     </row>
@@ -9412,7 +9412,7 @@
       </c>
       <c r="S107" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21T23:27:49Z</t>
+          <t>2026-09-22T17:38:14Z</t>
         </is>
       </c>
     </row>
@@ -9501,7 +9501,7 @@
       </c>
       <c r="S108" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21T23:27:49Z</t>
+          <t>2026-09-22T17:38:14Z</t>
         </is>
       </c>
     </row>
@@ -9586,7 +9586,7 @@
       </c>
       <c r="S109" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21T23:27:49Z</t>
+          <t>2026-09-22T17:38:14Z</t>
         </is>
       </c>
     </row>
@@ -9675,7 +9675,7 @@
       </c>
       <c r="S110" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21T23:27:49Z</t>
+          <t>2026-09-22T17:38:14Z</t>
         </is>
       </c>
     </row>
@@ -9764,7 +9764,7 @@
       </c>
       <c r="S111" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21T23:27:49Z</t>
+          <t>2026-09-22T17:38:14Z</t>
         </is>
       </c>
     </row>
@@ -9849,7 +9849,7 @@
       </c>
       <c r="S112" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21T23:27:49Z</t>
+          <t>2026-09-22T17:38:14Z</t>
         </is>
       </c>
     </row>
@@ -9938,7 +9938,7 @@
       </c>
       <c r="S113" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21T23:27:49Z</t>
+          <t>2026-09-22T17:38:14Z</t>
         </is>
       </c>
     </row>
@@ -10027,7 +10027,7 @@
       </c>
       <c r="S114" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21T23:27:49Z</t>
+          <t>2026-09-22T17:38:14Z</t>
         </is>
       </c>
     </row>
@@ -10112,7 +10112,7 @@
       </c>
       <c r="S115" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21T23:27:49Z</t>
+          <t>2026-09-22T17:38:14Z</t>
         </is>
       </c>
     </row>
@@ -10201,7 +10201,7 @@
       </c>
       <c r="S116" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21T23:27:49Z</t>
+          <t>2026-09-22T17:38:14Z</t>
         </is>
       </c>
     </row>
@@ -10290,7 +10290,7 @@
       </c>
       <c r="S117" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21T23:27:49Z</t>
+          <t>2026-09-22T17:38:14Z</t>
         </is>
       </c>
     </row>
@@ -10379,7 +10379,7 @@
       </c>
       <c r="S118" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21T23:27:49Z</t>
+          <t>2026-09-22T17:38:14Z</t>
         </is>
       </c>
     </row>
@@ -10468,7 +10468,7 @@
       </c>
       <c r="S119" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21T23:27:49Z</t>
+          <t>2026-09-22T17:38:14Z</t>
         </is>
       </c>
     </row>
@@ -10557,7 +10557,7 @@
       </c>
       <c r="S120" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21T23:27:49Z</t>
+          <t>2026-09-22T17:38:14Z</t>
         </is>
       </c>
     </row>
@@ -10646,7 +10646,7 @@
       </c>
       <c r="S121" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21T23:27:49Z</t>
+          <t>2026-09-22T17:38:14Z</t>
         </is>
       </c>
     </row>
@@ -10735,7 +10735,7 @@
       </c>
       <c r="S122" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21T23:27:49Z</t>
+          <t>2026-09-22T17:38:14Z</t>
         </is>
       </c>
     </row>
@@ -10824,7 +10824,7 @@
       </c>
       <c r="S123" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21T23:27:49Z</t>
+          <t>2026-09-22T17:38:14Z</t>
         </is>
       </c>
     </row>
@@ -10913,7 +10913,7 @@
       </c>
       <c r="S124" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21T23:27:49Z</t>
+          <t>2026-09-22T17:38:14Z</t>
         </is>
       </c>
     </row>
@@ -11002,7 +11002,7 @@
       </c>
       <c r="S125" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21T23:27:49Z</t>
+          <t>2026-09-22T17:38:14Z</t>
         </is>
       </c>
     </row>
@@ -11091,7 +11091,7 @@
       </c>
       <c r="S126" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21T23:27:49Z</t>
+          <t>2026-09-22T17:38:14Z</t>
         </is>
       </c>
     </row>
@@ -11180,7 +11180,7 @@
       </c>
       <c r="S127" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21T23:27:49Z</t>
+          <t>2026-09-22T17:38:14Z</t>
         </is>
       </c>
     </row>
@@ -11269,7 +11269,7 @@
       </c>
       <c r="S128" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21T23:27:49Z</t>
+          <t>2026-09-22T17:38:14Z</t>
         </is>
       </c>
     </row>
@@ -11354,7 +11354,7 @@
       </c>
       <c r="S129" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21T23:27:49Z</t>
+          <t>2026-09-22T17:38:14Z</t>
         </is>
       </c>
     </row>
@@ -11439,7 +11439,7 @@
       </c>
       <c r="S130" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21T23:27:49Z</t>
+          <t>2026-09-22T17:38:14Z</t>
         </is>
       </c>
     </row>
@@ -11524,7 +11524,7 @@
       </c>
       <c r="S131" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21T23:27:49Z</t>
+          <t>2026-09-22T17:38:14Z</t>
         </is>
       </c>
     </row>
@@ -11609,7 +11609,7 @@
       </c>
       <c r="S132" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21T23:27:49Z</t>
+          <t>2026-09-22T17:38:14Z</t>
         </is>
       </c>
     </row>
@@ -11694,7 +11694,7 @@
       </c>
       <c r="S133" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21T23:27:49Z</t>
+          <t>2026-09-22T17:38:14Z</t>
         </is>
       </c>
     </row>
@@ -11779,7 +11779,7 @@
       </c>
       <c r="S134" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21T23:27:49Z</t>
+          <t>2026-09-22T17:38:14Z</t>
         </is>
       </c>
     </row>
@@ -11864,7 +11864,7 @@
       </c>
       <c r="S135" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21T23:27:49Z</t>
+          <t>2026-09-22T17:38:14Z</t>
         </is>
       </c>
     </row>
@@ -11949,7 +11949,7 @@
       </c>
       <c r="S136" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21T23:27:49Z</t>
+          <t>2026-09-22T17:38:14Z</t>
         </is>
       </c>
     </row>
@@ -12034,7 +12034,7 @@
       </c>
       <c r="S137" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21T23:27:49Z</t>
+          <t>2026-09-22T17:38:14Z</t>
         </is>
       </c>
     </row>
@@ -12119,7 +12119,7 @@
       </c>
       <c r="S138" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21T23:27:49Z</t>
+          <t>2026-09-22T17:38:14Z</t>
         </is>
       </c>
     </row>
@@ -12204,7 +12204,7 @@
       </c>
       <c r="S139" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21T23:27:49Z</t>
+          <t>2026-09-22T17:38:14Z</t>
         </is>
       </c>
     </row>
@@ -12289,7 +12289,7 @@
       </c>
       <c r="S140" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21T23:27:49Z</t>
+          <t>2026-09-22T17:38:14Z</t>
         </is>
       </c>
     </row>
@@ -12374,7 +12374,7 @@
       </c>
       <c r="S141" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21T23:27:49Z</t>
+          <t>2026-09-22T17:38:14Z</t>
         </is>
       </c>
     </row>
@@ -12459,7 +12459,7 @@
       </c>
       <c r="S142" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21T23:27:49Z</t>
+          <t>2026-09-22T17:38:14Z</t>
         </is>
       </c>
     </row>
@@ -12544,7 +12544,7 @@
       </c>
       <c r="S143" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21T23:27:49Z</t>
+          <t>2026-09-22T17:38:14Z</t>
         </is>
       </c>
     </row>
@@ -12629,7 +12629,7 @@
       </c>
       <c r="S144" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21T23:27:49Z</t>
+          <t>2026-09-22T17:38:14Z</t>
         </is>
       </c>
     </row>
@@ -12714,7 +12714,7 @@
       </c>
       <c r="S145" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21T23:27:49Z</t>
+          <t>2026-09-22T17:38:14Z</t>
         </is>
       </c>
     </row>
@@ -12799,7 +12799,7 @@
       </c>
       <c r="S146" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21T23:27:49Z</t>
+          <t>2026-09-22T17:38:14Z</t>
         </is>
       </c>
     </row>
@@ -12884,7 +12884,7 @@
       </c>
       <c r="S147" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21T23:27:49Z</t>
+          <t>2026-09-22T17:38:14Z</t>
         </is>
       </c>
     </row>
@@ -12969,7 +12969,7 @@
       </c>
       <c r="S148" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21T23:27:49Z</t>
+          <t>2026-09-22T17:38:14Z</t>
         </is>
       </c>
     </row>
@@ -13054,7 +13054,7 @@
       </c>
       <c r="S149" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21T23:27:49Z</t>
+          <t>2026-09-22T17:38:14Z</t>
         </is>
       </c>
     </row>
@@ -13143,7 +13143,7 @@
       </c>
       <c r="S150" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21T23:27:49Z</t>
+          <t>2026-09-22T17:38:14Z</t>
         </is>
       </c>
     </row>
@@ -13232,7 +13232,7 @@
       </c>
       <c r="S151" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21T23:27:49Z</t>
+          <t>2026-09-22T17:38:14Z</t>
         </is>
       </c>
     </row>
@@ -13317,7 +13317,7 @@
       </c>
       <c r="S152" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21T23:27:49Z</t>
+          <t>2026-09-22T17:38:14Z</t>
         </is>
       </c>
     </row>
@@ -13406,7 +13406,7 @@
       </c>
       <c r="S153" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21T23:27:49Z</t>
+          <t>2026-09-22T17:38:14Z</t>
         </is>
       </c>
     </row>
@@ -13495,7 +13495,7 @@
       </c>
       <c r="S154" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21T23:27:49Z</t>
+          <t>2026-09-22T17:38:14Z</t>
         </is>
       </c>
     </row>
@@ -13580,7 +13580,7 @@
       </c>
       <c r="S155" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21T23:27:49Z</t>
+          <t>2026-09-22T17:38:14Z</t>
         </is>
       </c>
     </row>
@@ -13669,7 +13669,7 @@
       </c>
       <c r="S156" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21T23:27:49Z</t>
+          <t>2026-09-22T17:38:14Z</t>
         </is>
       </c>
     </row>
@@ -13758,7 +13758,7 @@
       </c>
       <c r="S157" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21T23:27:49Z</t>
+          <t>2026-09-22T17:38:14Z</t>
         </is>
       </c>
     </row>
@@ -13843,7 +13843,7 @@
       </c>
       <c r="S158" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21T23:27:49Z</t>
+          <t>2026-09-22T17:38:14Z</t>
         </is>
       </c>
     </row>
@@ -13932,7 +13932,7 @@
       </c>
       <c r="S159" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21T23:27:49Z</t>
+          <t>2026-09-22T17:38:14Z</t>
         </is>
       </c>
     </row>
@@ -14021,7 +14021,7 @@
       </c>
       <c r="S160" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21T23:27:49Z</t>
+          <t>2026-09-22T17:38:14Z</t>
         </is>
       </c>
     </row>
@@ -14106,7 +14106,7 @@
       </c>
       <c r="S161" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21T23:27:49Z</t>
+          <t>2026-09-22T17:38:14Z</t>
         </is>
       </c>
     </row>
@@ -14195,7 +14195,7 @@
       </c>
       <c r="S162" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21T23:27:49Z</t>
+          <t>2026-09-22T17:38:14Z</t>
         </is>
       </c>
     </row>
@@ -14284,7 +14284,7 @@
       </c>
       <c r="S163" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21T23:27:49Z</t>
+          <t>2026-09-22T17:38:14Z</t>
         </is>
       </c>
     </row>
@@ -14369,7 +14369,7 @@
       </c>
       <c r="S164" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21T23:27:49Z</t>
+          <t>2026-09-22T17:38:14Z</t>
         </is>
       </c>
     </row>
@@ -14458,7 +14458,7 @@
       </c>
       <c r="S165" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21T23:27:49Z</t>
+          <t>2026-09-22T17:38:14Z</t>
         </is>
       </c>
     </row>
@@ -14547,7 +14547,7 @@
       </c>
       <c r="S166" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21T23:27:49Z</t>
+          <t>2026-09-22T17:38:14Z</t>
         </is>
       </c>
     </row>
@@ -14632,7 +14632,7 @@
       </c>
       <c r="S167" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21T23:27:49Z</t>
+          <t>2026-09-22T17:38:14Z</t>
         </is>
       </c>
     </row>
@@ -14721,7 +14721,7 @@
       </c>
       <c r="S168" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21T23:27:49Z</t>
+          <t>2026-09-22T17:38:14Z</t>
         </is>
       </c>
     </row>
@@ -14810,7 +14810,7 @@
       </c>
       <c r="S169" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21T23:27:49Z</t>
+          <t>2026-09-22T17:38:14Z</t>
         </is>
       </c>
     </row>
@@ -14895,7 +14895,7 @@
       </c>
       <c r="S170" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21T23:27:49Z</t>
+          <t>2026-09-22T17:38:14Z</t>
         </is>
       </c>
     </row>
@@ -14984,7 +14984,7 @@
       </c>
       <c r="S171" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21T23:27:49Z</t>
+          <t>2026-09-22T17:38:14Z</t>
         </is>
       </c>
     </row>
@@ -15073,7 +15073,7 @@
       </c>
       <c r="S172" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21T23:27:49Z</t>
+          <t>2026-09-22T17:38:14Z</t>
         </is>
       </c>
     </row>
@@ -15158,7 +15158,7 @@
       </c>
       <c r="S173" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21T23:27:49Z</t>
+          <t>2026-09-22T17:38:14Z</t>
         </is>
       </c>
     </row>
@@ -15247,7 +15247,7 @@
       </c>
       <c r="S174" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21T23:27:49Z</t>
+          <t>2026-09-22T17:38:14Z</t>
         </is>
       </c>
     </row>
@@ -15336,7 +15336,7 @@
       </c>
       <c r="S175" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21T23:27:49Z</t>
+          <t>2026-09-22T17:38:14Z</t>
         </is>
       </c>
     </row>
@@ -15421,7 +15421,7 @@
       </c>
       <c r="S176" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21T23:27:49Z</t>
+          <t>2026-09-22T17:38:14Z</t>
         </is>
       </c>
     </row>
@@ -15510,7 +15510,7 @@
       </c>
       <c r="S177" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21T23:27:49Z</t>
+          <t>2026-09-22T17:38:14Z</t>
         </is>
       </c>
     </row>
@@ -15599,7 +15599,7 @@
       </c>
       <c r="S178" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21T23:27:49Z</t>
+          <t>2026-09-22T17:38:14Z</t>
         </is>
       </c>
     </row>
@@ -15688,7 +15688,7 @@
       </c>
       <c r="S179" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21T23:27:49Z</t>
+          <t>2026-09-22T17:38:14Z</t>
         </is>
       </c>
     </row>
@@ -15777,7 +15777,7 @@
       </c>
       <c r="S180" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21T23:27:49Z</t>
+          <t>2026-09-22T17:38:14Z</t>
         </is>
       </c>
     </row>
@@ -15866,7 +15866,7 @@
       </c>
       <c r="S181" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21T23:27:49Z</t>
+          <t>2026-09-22T17:38:14Z</t>
         </is>
       </c>
     </row>
@@ -15955,7 +15955,7 @@
       </c>
       <c r="S182" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21T23:27:49Z</t>
+          <t>2026-09-22T17:38:14Z</t>
         </is>
       </c>
     </row>
@@ -16044,7 +16044,7 @@
       </c>
       <c r="S183" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21T23:27:49Z</t>
+          <t>2026-09-22T17:38:14Z</t>
         </is>
       </c>
     </row>
@@ -16133,7 +16133,7 @@
       </c>
       <c r="S184" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21T23:27:49Z</t>
+          <t>2026-09-22T17:38:14Z</t>
         </is>
       </c>
     </row>
@@ -16222,7 +16222,7 @@
       </c>
       <c r="S185" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21T23:27:49Z</t>
+          <t>2026-09-22T17:38:14Z</t>
         </is>
       </c>
     </row>
@@ -16311,7 +16311,7 @@
       </c>
       <c r="S186" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21T23:27:49Z</t>
+          <t>2026-09-22T17:38:14Z</t>
         </is>
       </c>
     </row>
@@ -16400,7 +16400,7 @@
       </c>
       <c r="S187" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21T23:27:49Z</t>
+          <t>2026-09-22T17:38:14Z</t>
         </is>
       </c>
     </row>
@@ -16489,7 +16489,7 @@
       </c>
       <c r="S188" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21T23:27:49Z</t>
+          <t>2026-09-22T17:38:14Z</t>
         </is>
       </c>
     </row>
@@ -16578,7 +16578,7 @@
       </c>
       <c r="S189" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21T23:27:49Z</t>
+          <t>2026-09-22T17:38:14Z</t>
         </is>
       </c>
     </row>
@@ -16663,7 +16663,7 @@
       </c>
       <c r="S190" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21T23:27:49Z</t>
+          <t>2026-09-22T17:38:14Z</t>
         </is>
       </c>
     </row>
@@ -16748,7 +16748,7 @@
       </c>
       <c r="S191" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21T23:27:49Z</t>
+          <t>2026-09-22T17:38:14Z</t>
         </is>
       </c>
     </row>
@@ -16833,7 +16833,7 @@
       </c>
       <c r="S192" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21T23:27:49Z</t>
+          <t>2026-09-22T17:38:14Z</t>
         </is>
       </c>
     </row>
@@ -16918,7 +16918,7 @@
       </c>
       <c r="S193" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21T23:27:49Z</t>
+          <t>2026-09-22T17:38:14Z</t>
         </is>
       </c>
     </row>
@@ -17003,7 +17003,7 @@
       </c>
       <c r="S194" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21T23:27:49Z</t>
+          <t>2026-09-22T17:38:14Z</t>
         </is>
       </c>
     </row>
@@ -17088,7 +17088,7 @@
       </c>
       <c r="S195" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21T23:27:49Z</t>
+          <t>2026-09-22T17:38:14Z</t>
         </is>
       </c>
     </row>
@@ -17173,7 +17173,7 @@
       </c>
       <c r="S196" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21T23:27:49Z</t>
+          <t>2026-09-22T17:38:14Z</t>
         </is>
       </c>
     </row>
@@ -17258,7 +17258,7 @@
       </c>
       <c r="S197" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21T23:27:49Z</t>
+          <t>2026-09-22T17:38:14Z</t>
         </is>
       </c>
     </row>
@@ -17343,7 +17343,7 @@
       </c>
       <c r="S198" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21T23:27:49Z</t>
+          <t>2026-09-22T17:38:14Z</t>
         </is>
       </c>
     </row>
@@ -17428,7 +17428,7 @@
       </c>
       <c r="S199" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21T23:27:49Z</t>
+          <t>2026-09-22T17:38:14Z</t>
         </is>
       </c>
     </row>
@@ -17513,7 +17513,7 @@
       </c>
       <c r="S200" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21T23:27:49Z</t>
+          <t>2026-09-22T17:38:14Z</t>
         </is>
       </c>
     </row>
@@ -17598,7 +17598,7 @@
       </c>
       <c r="S201" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21T23:27:49Z</t>
+          <t>2026-09-22T17:38:14Z</t>
         </is>
       </c>
     </row>
@@ -17683,7 +17683,7 @@
       </c>
       <c r="S202" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21T23:27:49Z</t>
+          <t>2026-09-22T17:38:14Z</t>
         </is>
       </c>
     </row>
@@ -17768,7 +17768,7 @@
       </c>
       <c r="S203" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21T23:27:49Z</t>
+          <t>2026-09-22T17:38:14Z</t>
         </is>
       </c>
     </row>
@@ -17853,7 +17853,7 @@
       </c>
       <c r="S204" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21T23:27:49Z</t>
+          <t>2026-09-22T17:38:14Z</t>
         </is>
       </c>
     </row>
@@ -17938,7 +17938,7 @@
       </c>
       <c r="S205" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21T23:27:49Z</t>
+          <t>2026-09-22T17:38:14Z</t>
         </is>
       </c>
     </row>
@@ -18023,7 +18023,7 @@
       </c>
       <c r="S206" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21T23:27:49Z</t>
+          <t>2026-09-22T17:38:14Z</t>
         </is>
       </c>
     </row>
@@ -18108,7 +18108,7 @@
       </c>
       <c r="S207" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21T23:27:49Z</t>
+          <t>2026-09-22T17:38:14Z</t>
         </is>
       </c>
     </row>
@@ -18193,7 +18193,7 @@
       </c>
       <c r="S208" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21T23:27:49Z</t>
+          <t>2026-09-22T17:38:14Z</t>
         </is>
       </c>
     </row>
@@ -18278,7 +18278,7 @@
       </c>
       <c r="S209" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21T23:27:49Z</t>
+          <t>2026-09-22T17:38:14Z</t>
         </is>
       </c>
     </row>
@@ -18363,7 +18363,7 @@
       </c>
       <c r="S210" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21T23:27:49Z</t>
+          <t>2026-09-22T17:38:14Z</t>
         </is>
       </c>
     </row>
@@ -18452,7 +18452,7 @@
       </c>
       <c r="S211" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21T23:27:49Z</t>
+          <t>2026-09-22T17:38:14Z</t>
         </is>
       </c>
     </row>
@@ -18541,7 +18541,7 @@
       </c>
       <c r="S212" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21T23:27:49Z</t>
+          <t>2026-09-22T17:38:14Z</t>
         </is>
       </c>
     </row>
@@ -18626,7 +18626,7 @@
       </c>
       <c r="S213" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21T23:27:49Z</t>
+          <t>2026-09-22T17:38:14Z</t>
         </is>
       </c>
     </row>
@@ -18715,7 +18715,7 @@
       </c>
       <c r="S214" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21T23:27:49Z</t>
+          <t>2026-09-22T17:38:14Z</t>
         </is>
       </c>
     </row>
@@ -18804,7 +18804,7 @@
       </c>
       <c r="S215" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21T23:27:49Z</t>
+          <t>2026-09-22T17:38:14Z</t>
         </is>
       </c>
     </row>
@@ -18889,7 +18889,7 @@
       </c>
       <c r="S216" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21T23:27:49Z</t>
+          <t>2026-09-22T17:38:14Z</t>
         </is>
       </c>
     </row>
@@ -18978,7 +18978,7 @@
       </c>
       <c r="S217" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21T23:27:49Z</t>
+          <t>2026-09-22T17:38:14Z</t>
         </is>
       </c>
     </row>
@@ -19067,7 +19067,7 @@
       </c>
       <c r="S218" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21T23:27:49Z</t>
+          <t>2026-09-22T17:38:14Z</t>
         </is>
       </c>
     </row>
@@ -19152,7 +19152,7 @@
       </c>
       <c r="S219" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21T23:27:49Z</t>
+          <t>2026-09-22T17:38:14Z</t>
         </is>
       </c>
     </row>
@@ -19241,7 +19241,7 @@
       </c>
       <c r="S220" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21T23:27:49Z</t>
+          <t>2026-09-22T17:38:14Z</t>
         </is>
       </c>
     </row>
@@ -19330,7 +19330,7 @@
       </c>
       <c r="S221" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21T23:27:49Z</t>
+          <t>2026-09-22T17:38:14Z</t>
         </is>
       </c>
     </row>
@@ -19415,7 +19415,7 @@
       </c>
       <c r="S222" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21T23:27:49Z</t>
+          <t>2026-09-22T17:38:14Z</t>
         </is>
       </c>
     </row>
@@ -19504,7 +19504,7 @@
       </c>
       <c r="S223" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21T23:27:49Z</t>
+          <t>2026-09-22T17:38:14Z</t>
         </is>
       </c>
     </row>
@@ -19593,7 +19593,7 @@
       </c>
       <c r="S224" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21T23:27:49Z</t>
+          <t>2026-09-22T17:38:14Z</t>
         </is>
       </c>
     </row>
@@ -19678,7 +19678,7 @@
       </c>
       <c r="S225" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21T23:27:49Z</t>
+          <t>2026-09-22T17:38:14Z</t>
         </is>
       </c>
     </row>
@@ -19767,7 +19767,7 @@
       </c>
       <c r="S226" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21T23:27:49Z</t>
+          <t>2026-09-22T17:38:14Z</t>
         </is>
       </c>
     </row>
@@ -19856,7 +19856,7 @@
       </c>
       <c r="S227" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21T23:27:49Z</t>
+          <t>2026-09-22T17:38:14Z</t>
         </is>
       </c>
     </row>
@@ -19941,7 +19941,7 @@
       </c>
       <c r="S228" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21T23:27:49Z</t>
+          <t>2026-09-22T17:38:14Z</t>
         </is>
       </c>
     </row>
@@ -20030,7 +20030,7 @@
       </c>
       <c r="S229" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21T23:27:49Z</t>
+          <t>2026-09-22T17:38:14Z</t>
         </is>
       </c>
     </row>
@@ -20119,7 +20119,7 @@
       </c>
       <c r="S230" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21T23:27:49Z</t>
+          <t>2026-09-22T17:38:14Z</t>
         </is>
       </c>
     </row>
@@ -20204,7 +20204,7 @@
       </c>
       <c r="S231" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21T23:27:49Z</t>
+          <t>2026-09-22T17:38:14Z</t>
         </is>
       </c>
     </row>
@@ -20293,7 +20293,7 @@
       </c>
       <c r="S232" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21T23:27:49Z</t>
+          <t>2026-09-22T17:38:14Z</t>
         </is>
       </c>
     </row>
@@ -20382,7 +20382,7 @@
       </c>
       <c r="S233" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21T23:27:49Z</t>
+          <t>2026-09-22T17:38:14Z</t>
         </is>
       </c>
     </row>
@@ -20467,7 +20467,7 @@
       </c>
       <c r="S234" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21T23:27:49Z</t>
+          <t>2026-09-22T17:38:14Z</t>
         </is>
       </c>
     </row>
@@ -20556,7 +20556,7 @@
       </c>
       <c r="S235" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21T23:27:49Z</t>
+          <t>2026-09-22T17:38:14Z</t>
         </is>
       </c>
     </row>
@@ -20645,7 +20645,7 @@
       </c>
       <c r="S236" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21T23:27:49Z</t>
+          <t>2026-09-22T17:38:14Z</t>
         </is>
       </c>
     </row>
@@ -20730,7 +20730,7 @@
       </c>
       <c r="S237" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21T23:27:49Z</t>
+          <t>2026-09-22T17:38:14Z</t>
         </is>
       </c>
     </row>
@@ -20819,7 +20819,7 @@
       </c>
       <c r="S238" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21T23:27:49Z</t>
+          <t>2026-09-22T17:38:14Z</t>
         </is>
       </c>
     </row>
@@ -20908,7 +20908,7 @@
       </c>
       <c r="S239" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21T23:27:49Z</t>
+          <t>2026-09-22T17:38:14Z</t>
         </is>
       </c>
     </row>
@@ -20997,7 +20997,7 @@
       </c>
       <c r="S240" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21T23:27:49Z</t>
+          <t>2026-09-22T17:38:14Z</t>
         </is>
       </c>
     </row>
@@ -21086,7 +21086,7 @@
       </c>
       <c r="S241" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21T23:27:49Z</t>
+          <t>2026-09-22T17:38:14Z</t>
         </is>
       </c>
     </row>
@@ -21175,7 +21175,7 @@
       </c>
       <c r="S242" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21T23:27:49Z</t>
+          <t>2026-09-22T17:38:14Z</t>
         </is>
       </c>
     </row>
@@ -21264,7 +21264,7 @@
       </c>
       <c r="S243" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21T23:27:49Z</t>
+          <t>2026-09-22T17:38:14Z</t>
         </is>
       </c>
     </row>
@@ -21353,7 +21353,7 @@
       </c>
       <c r="S244" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21T23:27:49Z</t>
+          <t>2026-09-22T17:38:14Z</t>
         </is>
       </c>
     </row>
@@ -21442,7 +21442,7 @@
       </c>
       <c r="S245" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21T23:27:49Z</t>
+          <t>2026-09-22T17:38:14Z</t>
         </is>
       </c>
     </row>
@@ -21531,7 +21531,7 @@
       </c>
       <c r="S246" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21T23:27:49Z</t>
+          <t>2026-09-22T17:38:14Z</t>
         </is>
       </c>
     </row>
@@ -21620,7 +21620,7 @@
       </c>
       <c r="S247" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21T23:27:49Z</t>
+          <t>2026-09-22T17:38:14Z</t>
         </is>
       </c>
     </row>
@@ -21709,7 +21709,7 @@
       </c>
       <c r="S248" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21T23:27:49Z</t>
+          <t>2026-09-22T17:38:14Z</t>
         </is>
       </c>
     </row>
@@ -21798,7 +21798,7 @@
       </c>
       <c r="S249" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21T23:27:49Z</t>
+          <t>2026-09-22T17:38:14Z</t>
         </is>
       </c>
     </row>
@@ -21887,7 +21887,7 @@
       </c>
       <c r="S250" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21T23:27:49Z</t>
+          <t>2026-09-22T17:38:14Z</t>
         </is>
       </c>
     </row>
@@ -22019,7 +22019,7 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21T23:27:49Z</t>
+          <t>2026-09-22T17:38:14Z</t>
         </is>
       </c>
     </row>
@@ -22099,7 +22099,7 @@
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>{"dataset_id": "bcv_pib_sector_institucional_anual", "title": "Producto interno bruto por sector institucional anual", "table": "Variaciones porcentuales", "source_file": "5_2_1_si_anual.xlsx", "base": "2007", "price_type": "Precios constantes", "measure": "Variación porcentual interanual", "frequency": "Anual", "period": "2025", "year": 2025, "quarter": null, "classification": "Sector institucional", "component": "Impuestos netos sobre los productos", "value": 10.600260421283764, "unit": "Porcentaje", "status": "Preliminar", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/cuentas_macroeconomicas/5_2_1_si_anual.xlsx", "fetched_at": "2026-09-21T23:27:49Z"}</t>
+          <t>{"dataset_id": "bcv_pib_sector_institucional_anual", "title": "Producto interno bruto por sector institucional anual", "table": "Variaciones porcentuales", "source_file": "5_2_1_si_anual.xlsx", "base": "2007", "price_type": "Precios constantes", "measure": "Variación porcentual interanual", "frequency": "Anual", "period": "2025", "year": 2025, "quarter": null, "classification": "Sector institucional", "component": "Impuestos netos sobre los productos", "value": 10.600260421283764, "unit": "Porcentaje", "status": "Preliminar", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/cuentas_macroeconomicas/5_2_1_si_anual.xlsx", "fetched_at": "2026-09-22T17:38:14Z"}</t>
         </is>
       </c>
     </row>

--- a/assets/data/bcv/excel/ove_bcv_pib_sector_institucional_anual.xlsx
+++ b/assets/data/bcv/excel/ove_bcv_pib_sector_institucional_anual.xlsx
@@ -736,7 +736,7 @@
       </c>
       <c r="S7" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T17:38:14Z</t>
+          <t>2026-09-22T23:08:03Z</t>
         </is>
       </c>
     </row>
@@ -821,7 +821,7 @@
       </c>
       <c r="S8" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T17:38:14Z</t>
+          <t>2026-09-22T23:08:03Z</t>
         </is>
       </c>
     </row>
@@ -906,7 +906,7 @@
       </c>
       <c r="S9" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T17:38:14Z</t>
+          <t>2026-09-22T23:08:03Z</t>
         </is>
       </c>
     </row>
@@ -991,7 +991,7 @@
       </c>
       <c r="S10" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T17:38:14Z</t>
+          <t>2026-09-22T23:08:03Z</t>
         </is>
       </c>
     </row>
@@ -1076,7 +1076,7 @@
       </c>
       <c r="S11" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T17:38:14Z</t>
+          <t>2026-09-22T23:08:03Z</t>
         </is>
       </c>
     </row>
@@ -1161,7 +1161,7 @@
       </c>
       <c r="S12" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T17:38:14Z</t>
+          <t>2026-09-22T23:08:03Z</t>
         </is>
       </c>
     </row>
@@ -1246,7 +1246,7 @@
       </c>
       <c r="S13" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T17:38:14Z</t>
+          <t>2026-09-22T23:08:03Z</t>
         </is>
       </c>
     </row>
@@ -1331,7 +1331,7 @@
       </c>
       <c r="S14" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T17:38:14Z</t>
+          <t>2026-09-22T23:08:03Z</t>
         </is>
       </c>
     </row>
@@ -1416,7 +1416,7 @@
       </c>
       <c r="S15" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T17:38:14Z</t>
+          <t>2026-09-22T23:08:03Z</t>
         </is>
       </c>
     </row>
@@ -1501,7 +1501,7 @@
       </c>
       <c r="S16" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T17:38:14Z</t>
+          <t>2026-09-22T23:08:03Z</t>
         </is>
       </c>
     </row>
@@ -1586,7 +1586,7 @@
       </c>
       <c r="S17" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T17:38:14Z</t>
+          <t>2026-09-22T23:08:03Z</t>
         </is>
       </c>
     </row>
@@ -1671,7 +1671,7 @@
       </c>
       <c r="S18" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T17:38:14Z</t>
+          <t>2026-09-22T23:08:03Z</t>
         </is>
       </c>
     </row>
@@ -1756,7 +1756,7 @@
       </c>
       <c r="S19" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T17:38:14Z</t>
+          <t>2026-09-22T23:08:03Z</t>
         </is>
       </c>
     </row>
@@ -1841,7 +1841,7 @@
       </c>
       <c r="S20" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T17:38:14Z</t>
+          <t>2026-09-22T23:08:03Z</t>
         </is>
       </c>
     </row>
@@ -1926,7 +1926,7 @@
       </c>
       <c r="S21" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T17:38:14Z</t>
+          <t>2026-09-22T23:08:03Z</t>
         </is>
       </c>
     </row>
@@ -2011,7 +2011,7 @@
       </c>
       <c r="S22" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T17:38:14Z</t>
+          <t>2026-09-22T23:08:03Z</t>
         </is>
       </c>
     </row>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="S23" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T17:38:14Z</t>
+          <t>2026-09-22T23:08:03Z</t>
         </is>
       </c>
     </row>
@@ -2181,7 +2181,7 @@
       </c>
       <c r="S24" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T17:38:14Z</t>
+          <t>2026-09-22T23:08:03Z</t>
         </is>
       </c>
     </row>
@@ -2266,7 +2266,7 @@
       </c>
       <c r="S25" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T17:38:14Z</t>
+          <t>2026-09-22T23:08:03Z</t>
         </is>
       </c>
     </row>
@@ -2351,7 +2351,7 @@
       </c>
       <c r="S26" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T17:38:14Z</t>
+          <t>2026-09-22T23:08:03Z</t>
         </is>
       </c>
     </row>
@@ -2436,7 +2436,7 @@
       </c>
       <c r="S27" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T17:38:14Z</t>
+          <t>2026-09-22T23:08:03Z</t>
         </is>
       </c>
     </row>
@@ -2525,7 +2525,7 @@
       </c>
       <c r="S28" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T17:38:14Z</t>
+          <t>2026-09-22T23:08:03Z</t>
         </is>
       </c>
     </row>
@@ -2614,7 +2614,7 @@
       </c>
       <c r="S29" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T17:38:14Z</t>
+          <t>2026-09-22T23:08:03Z</t>
         </is>
       </c>
     </row>
@@ -2699,7 +2699,7 @@
       </c>
       <c r="S30" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T17:38:14Z</t>
+          <t>2026-09-22T23:08:03Z</t>
         </is>
       </c>
     </row>
@@ -2788,7 +2788,7 @@
       </c>
       <c r="S31" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T17:38:14Z</t>
+          <t>2026-09-22T23:08:03Z</t>
         </is>
       </c>
     </row>
@@ -2877,7 +2877,7 @@
       </c>
       <c r="S32" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T17:38:14Z</t>
+          <t>2026-09-22T23:08:03Z</t>
         </is>
       </c>
     </row>
@@ -2962,7 +2962,7 @@
       </c>
       <c r="S33" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T17:38:14Z</t>
+          <t>2026-09-22T23:08:03Z</t>
         </is>
       </c>
     </row>
@@ -3051,7 +3051,7 @@
       </c>
       <c r="S34" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T17:38:14Z</t>
+          <t>2026-09-22T23:08:03Z</t>
         </is>
       </c>
     </row>
@@ -3140,7 +3140,7 @@
       </c>
       <c r="S35" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T17:38:14Z</t>
+          <t>2026-09-22T23:08:03Z</t>
         </is>
       </c>
     </row>
@@ -3225,7 +3225,7 @@
       </c>
       <c r="S36" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T17:38:14Z</t>
+          <t>2026-09-22T23:08:03Z</t>
         </is>
       </c>
     </row>
@@ -3314,7 +3314,7 @@
       </c>
       <c r="S37" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T17:38:14Z</t>
+          <t>2026-09-22T23:08:03Z</t>
         </is>
       </c>
     </row>
@@ -3403,7 +3403,7 @@
       </c>
       <c r="S38" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T17:38:14Z</t>
+          <t>2026-09-22T23:08:03Z</t>
         </is>
       </c>
     </row>
@@ -3488,7 +3488,7 @@
       </c>
       <c r="S39" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T17:38:14Z</t>
+          <t>2026-09-22T23:08:03Z</t>
         </is>
       </c>
     </row>
@@ -3577,7 +3577,7 @@
       </c>
       <c r="S40" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T17:38:14Z</t>
+          <t>2026-09-22T23:08:03Z</t>
         </is>
       </c>
     </row>
@@ -3666,7 +3666,7 @@
       </c>
       <c r="S41" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T17:38:14Z</t>
+          <t>2026-09-22T23:08:03Z</t>
         </is>
       </c>
     </row>
@@ -3751,7 +3751,7 @@
       </c>
       <c r="S42" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T17:38:14Z</t>
+          <t>2026-09-22T23:08:03Z</t>
         </is>
       </c>
     </row>
@@ -3840,7 +3840,7 @@
       </c>
       <c r="S43" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T17:38:14Z</t>
+          <t>2026-09-22T23:08:03Z</t>
         </is>
       </c>
     </row>
@@ -3929,7 +3929,7 @@
       </c>
       <c r="S44" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T17:38:14Z</t>
+          <t>2026-09-22T23:08:03Z</t>
         </is>
       </c>
     </row>
@@ -4014,7 +4014,7 @@
       </c>
       <c r="S45" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T17:38:14Z</t>
+          <t>2026-09-22T23:08:03Z</t>
         </is>
       </c>
     </row>
@@ -4103,7 +4103,7 @@
       </c>
       <c r="S46" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T17:38:14Z</t>
+          <t>2026-09-22T23:08:03Z</t>
         </is>
       </c>
     </row>
@@ -4192,7 +4192,7 @@
       </c>
       <c r="S47" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T17:38:14Z</t>
+          <t>2026-09-22T23:08:03Z</t>
         </is>
       </c>
     </row>
@@ -4277,7 +4277,7 @@
       </c>
       <c r="S48" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T17:38:14Z</t>
+          <t>2026-09-22T23:08:03Z</t>
         </is>
       </c>
     </row>
@@ -4366,7 +4366,7 @@
       </c>
       <c r="S49" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T17:38:14Z</t>
+          <t>2026-09-22T23:08:03Z</t>
         </is>
       </c>
     </row>
@@ -4455,7 +4455,7 @@
       </c>
       <c r="S50" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T17:38:14Z</t>
+          <t>2026-09-22T23:08:03Z</t>
         </is>
       </c>
     </row>
@@ -4540,7 +4540,7 @@
       </c>
       <c r="S51" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T17:38:14Z</t>
+          <t>2026-09-22T23:08:03Z</t>
         </is>
       </c>
     </row>
@@ -4629,7 +4629,7 @@
       </c>
       <c r="S52" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T17:38:14Z</t>
+          <t>2026-09-22T23:08:03Z</t>
         </is>
       </c>
     </row>
@@ -4718,7 +4718,7 @@
       </c>
       <c r="S53" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T17:38:14Z</t>
+          <t>2026-09-22T23:08:03Z</t>
         </is>
       </c>
     </row>
@@ -4803,7 +4803,7 @@
       </c>
       <c r="S54" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T17:38:14Z</t>
+          <t>2026-09-22T23:08:03Z</t>
         </is>
       </c>
     </row>
@@ -4892,7 +4892,7 @@
       </c>
       <c r="S55" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T17:38:14Z</t>
+          <t>2026-09-22T23:08:03Z</t>
         </is>
       </c>
     </row>
@@ -4981,7 +4981,7 @@
       </c>
       <c r="S56" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T17:38:14Z</t>
+          <t>2026-09-22T23:08:03Z</t>
         </is>
       </c>
     </row>
@@ -5070,7 +5070,7 @@
       </c>
       <c r="S57" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T17:38:14Z</t>
+          <t>2026-09-22T23:08:03Z</t>
         </is>
       </c>
     </row>
@@ -5159,7 +5159,7 @@
       </c>
       <c r="S58" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T17:38:14Z</t>
+          <t>2026-09-22T23:08:03Z</t>
         </is>
       </c>
     </row>
@@ -5248,7 +5248,7 @@
       </c>
       <c r="S59" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T17:38:14Z</t>
+          <t>2026-09-22T23:08:03Z</t>
         </is>
       </c>
     </row>
@@ -5337,7 +5337,7 @@
       </c>
       <c r="S60" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T17:38:14Z</t>
+          <t>2026-09-22T23:08:03Z</t>
         </is>
       </c>
     </row>
@@ -5426,7 +5426,7 @@
       </c>
       <c r="S61" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T17:38:14Z</t>
+          <t>2026-09-22T23:08:03Z</t>
         </is>
       </c>
     </row>
@@ -5515,7 +5515,7 @@
       </c>
       <c r="S62" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T17:38:14Z</t>
+          <t>2026-09-22T23:08:03Z</t>
         </is>
       </c>
     </row>
@@ -5604,7 +5604,7 @@
       </c>
       <c r="S63" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T17:38:14Z</t>
+          <t>2026-09-22T23:08:03Z</t>
         </is>
       </c>
     </row>
@@ -5693,7 +5693,7 @@
       </c>
       <c r="S64" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T17:38:14Z</t>
+          <t>2026-09-22T23:08:03Z</t>
         </is>
       </c>
     </row>
@@ -5782,7 +5782,7 @@
       </c>
       <c r="S65" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T17:38:14Z</t>
+          <t>2026-09-22T23:08:03Z</t>
         </is>
       </c>
     </row>
@@ -5871,7 +5871,7 @@
       </c>
       <c r="S66" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T17:38:14Z</t>
+          <t>2026-09-22T23:08:03Z</t>
         </is>
       </c>
     </row>
@@ -5960,7 +5960,7 @@
       </c>
       <c r="S67" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T17:38:14Z</t>
+          <t>2026-09-22T23:08:03Z</t>
         </is>
       </c>
     </row>
@@ -6045,7 +6045,7 @@
       </c>
       <c r="S68" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T17:38:14Z</t>
+          <t>2026-09-22T23:08:03Z</t>
         </is>
       </c>
     </row>
@@ -6130,7 +6130,7 @@
       </c>
       <c r="S69" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T17:38:14Z</t>
+          <t>2026-09-22T23:08:03Z</t>
         </is>
       </c>
     </row>
@@ -6215,7 +6215,7 @@
       </c>
       <c r="S70" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T17:38:14Z</t>
+          <t>2026-09-22T23:08:03Z</t>
         </is>
       </c>
     </row>
@@ -6300,7 +6300,7 @@
       </c>
       <c r="S71" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T17:38:14Z</t>
+          <t>2026-09-22T23:08:03Z</t>
         </is>
       </c>
     </row>
@@ -6385,7 +6385,7 @@
       </c>
       <c r="S72" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T17:38:14Z</t>
+          <t>2026-09-22T23:08:03Z</t>
         </is>
       </c>
     </row>
@@ -6470,7 +6470,7 @@
       </c>
       <c r="S73" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T17:38:14Z</t>
+          <t>2026-09-22T23:08:03Z</t>
         </is>
       </c>
     </row>
@@ -6555,7 +6555,7 @@
       </c>
       <c r="S74" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T17:38:14Z</t>
+          <t>2026-09-22T23:08:03Z</t>
         </is>
       </c>
     </row>
@@ -6640,7 +6640,7 @@
       </c>
       <c r="S75" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T17:38:14Z</t>
+          <t>2026-09-22T23:08:03Z</t>
         </is>
       </c>
     </row>
@@ -6725,7 +6725,7 @@
       </c>
       <c r="S76" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T17:38:14Z</t>
+          <t>2026-09-22T23:08:03Z</t>
         </is>
       </c>
     </row>
@@ -6810,7 +6810,7 @@
       </c>
       <c r="S77" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T17:38:14Z</t>
+          <t>2026-09-22T23:08:03Z</t>
         </is>
       </c>
     </row>
@@ -6895,7 +6895,7 @@
       </c>
       <c r="S78" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T17:38:14Z</t>
+          <t>2026-09-22T23:08:03Z</t>
         </is>
       </c>
     </row>
@@ -6980,7 +6980,7 @@
       </c>
       <c r="S79" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T17:38:14Z</t>
+          <t>2026-09-22T23:08:03Z</t>
         </is>
       </c>
     </row>
@@ -7065,7 +7065,7 @@
       </c>
       <c r="S80" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T17:38:14Z</t>
+          <t>2026-09-22T23:08:03Z</t>
         </is>
       </c>
     </row>
@@ -7150,7 +7150,7 @@
       </c>
       <c r="S81" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T17:38:14Z</t>
+          <t>2026-09-22T23:08:03Z</t>
         </is>
       </c>
     </row>
@@ -7235,7 +7235,7 @@
       </c>
       <c r="S82" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T17:38:14Z</t>
+          <t>2026-09-22T23:08:03Z</t>
         </is>
       </c>
     </row>
@@ -7320,7 +7320,7 @@
       </c>
       <c r="S83" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T17:38:14Z</t>
+          <t>2026-09-22T23:08:03Z</t>
         </is>
       </c>
     </row>
@@ -7405,7 +7405,7 @@
       </c>
       <c r="S84" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T17:38:14Z</t>
+          <t>2026-09-22T23:08:03Z</t>
         </is>
       </c>
     </row>
@@ -7490,7 +7490,7 @@
       </c>
       <c r="S85" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T17:38:14Z</t>
+          <t>2026-09-22T23:08:03Z</t>
         </is>
       </c>
     </row>
@@ -7575,7 +7575,7 @@
       </c>
       <c r="S86" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T17:38:14Z</t>
+          <t>2026-09-22T23:08:03Z</t>
         </is>
       </c>
     </row>
@@ -7660,7 +7660,7 @@
       </c>
       <c r="S87" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T17:38:14Z</t>
+          <t>2026-09-22T23:08:03Z</t>
         </is>
       </c>
     </row>
@@ -7745,7 +7745,7 @@
       </c>
       <c r="S88" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T17:38:14Z</t>
+          <t>2026-09-22T23:08:03Z</t>
         </is>
       </c>
     </row>
@@ -7834,7 +7834,7 @@
       </c>
       <c r="S89" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T17:38:14Z</t>
+          <t>2026-09-22T23:08:03Z</t>
         </is>
       </c>
     </row>
@@ -7923,7 +7923,7 @@
       </c>
       <c r="S90" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T17:38:14Z</t>
+          <t>2026-09-22T23:08:03Z</t>
         </is>
       </c>
     </row>
@@ -8008,7 +8008,7 @@
       </c>
       <c r="S91" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T17:38:14Z</t>
+          <t>2026-09-22T23:08:03Z</t>
         </is>
       </c>
     </row>
@@ -8097,7 +8097,7 @@
       </c>
       <c r="S92" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T17:38:14Z</t>
+          <t>2026-09-22T23:08:03Z</t>
         </is>
       </c>
     </row>
@@ -8186,7 +8186,7 @@
       </c>
       <c r="S93" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T17:38:14Z</t>
+          <t>2026-09-22T23:08:03Z</t>
         </is>
       </c>
     </row>
@@ -8271,7 +8271,7 @@
       </c>
       <c r="S94" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T17:38:14Z</t>
+          <t>2026-09-22T23:08:03Z</t>
         </is>
       </c>
     </row>
@@ -8360,7 +8360,7 @@
       </c>
       <c r="S95" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T17:38:14Z</t>
+          <t>2026-09-22T23:08:03Z</t>
         </is>
       </c>
     </row>
@@ -8449,7 +8449,7 @@
       </c>
       <c r="S96" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T17:38:14Z</t>
+          <t>2026-09-22T23:08:03Z</t>
         </is>
       </c>
     </row>
@@ -8534,7 +8534,7 @@
       </c>
       <c r="S97" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T17:38:14Z</t>
+          <t>2026-09-22T23:08:03Z</t>
         </is>
       </c>
     </row>
@@ -8623,7 +8623,7 @@
       </c>
       <c r="S98" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T17:38:14Z</t>
+          <t>2026-09-22T23:08:03Z</t>
         </is>
       </c>
     </row>
@@ -8712,7 +8712,7 @@
       </c>
       <c r="S99" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T17:38:14Z</t>
+          <t>2026-09-22T23:08:03Z</t>
         </is>
       </c>
     </row>
@@ -8797,7 +8797,7 @@
       </c>
       <c r="S100" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T17:38:14Z</t>
+          <t>2026-09-22T23:08:03Z</t>
         </is>
       </c>
     </row>
@@ -8886,7 +8886,7 @@
       </c>
       <c r="S101" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T17:38:14Z</t>
+          <t>2026-09-22T23:08:03Z</t>
         </is>
       </c>
     </row>
@@ -8975,7 +8975,7 @@
       </c>
       <c r="S102" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T17:38:14Z</t>
+          <t>2026-09-22T23:08:03Z</t>
         </is>
       </c>
     </row>
@@ -9060,7 +9060,7 @@
       </c>
       <c r="S103" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T17:38:14Z</t>
+          <t>2026-09-22T23:08:03Z</t>
         </is>
       </c>
     </row>
@@ -9149,7 +9149,7 @@
       </c>
       <c r="S104" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T17:38:14Z</t>
+          <t>2026-09-22T23:08:03Z</t>
         </is>
       </c>
     </row>
@@ -9238,7 +9238,7 @@
       </c>
       <c r="S105" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T17:38:14Z</t>
+          <t>2026-09-22T23:08:03Z</t>
         </is>
       </c>
     </row>
@@ -9323,7 +9323,7 @@
       </c>
       <c r="S106" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T17:38:14Z</t>
+          <t>2026-09-22T23:08:03Z</t>
         </is>
       </c>
     </row>
@@ -9412,7 +9412,7 @@
       </c>
       <c r="S107" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T17:38:14Z</t>
+          <t>2026-09-22T23:08:03Z</t>
         </is>
       </c>
     </row>
@@ -9501,7 +9501,7 @@
       </c>
       <c r="S108" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T17:38:14Z</t>
+          <t>2026-09-22T23:08:03Z</t>
         </is>
       </c>
     </row>
@@ -9586,7 +9586,7 @@
       </c>
       <c r="S109" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T17:38:14Z</t>
+          <t>2026-09-22T23:08:03Z</t>
         </is>
       </c>
     </row>
@@ -9675,7 +9675,7 @@
       </c>
       <c r="S110" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T17:38:14Z</t>
+          <t>2026-09-22T23:08:03Z</t>
         </is>
       </c>
     </row>
@@ -9764,7 +9764,7 @@
       </c>
       <c r="S111" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T17:38:14Z</t>
+          <t>2026-09-22T23:08:03Z</t>
         </is>
       </c>
     </row>
@@ -9849,7 +9849,7 @@
       </c>
       <c r="S112" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T17:38:14Z</t>
+          <t>2026-09-22T23:08:03Z</t>
         </is>
       </c>
     </row>
@@ -9938,7 +9938,7 @@
       </c>
       <c r="S113" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T17:38:14Z</t>
+          <t>2026-09-22T23:08:03Z</t>
         </is>
       </c>
     </row>
@@ -10027,7 +10027,7 @@
       </c>
       <c r="S114" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T17:38:14Z</t>
+          <t>2026-09-22T23:08:03Z</t>
         </is>
       </c>
     </row>
@@ -10112,7 +10112,7 @@
       </c>
       <c r="S115" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T17:38:14Z</t>
+          <t>2026-09-22T23:08:03Z</t>
         </is>
       </c>
     </row>
@@ -10201,7 +10201,7 @@
       </c>
       <c r="S116" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T17:38:14Z</t>
+          <t>2026-09-22T23:08:03Z</t>
         </is>
       </c>
     </row>
@@ -10290,7 +10290,7 @@
       </c>
       <c r="S117" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T17:38:14Z</t>
+          <t>2026-09-22T23:08:03Z</t>
         </is>
       </c>
     </row>
@@ -10379,7 +10379,7 @@
       </c>
       <c r="S118" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T17:38:14Z</t>
+          <t>2026-09-22T23:08:03Z</t>
         </is>
       </c>
     </row>
@@ -10468,7 +10468,7 @@
       </c>
       <c r="S119" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T17:38:14Z</t>
+          <t>2026-09-22T23:08:03Z</t>
         </is>
       </c>
     </row>
@@ -10557,7 +10557,7 @@
       </c>
       <c r="S120" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T17:38:14Z</t>
+          <t>2026-09-22T23:08:03Z</t>
         </is>
       </c>
     </row>
@@ -10646,7 +10646,7 @@
       </c>
       <c r="S121" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T17:38:14Z</t>
+          <t>2026-09-22T23:08:03Z</t>
         </is>
       </c>
     </row>
@@ -10735,7 +10735,7 @@
       </c>
       <c r="S122" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T17:38:14Z</t>
+          <t>2026-09-22T23:08:03Z</t>
         </is>
       </c>
     </row>
@@ -10824,7 +10824,7 @@
       </c>
       <c r="S123" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T17:38:14Z</t>
+          <t>2026-09-22T23:08:03Z</t>
         </is>
       </c>
     </row>
@@ -10913,7 +10913,7 @@
       </c>
       <c r="S124" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T17:38:14Z</t>
+          <t>2026-09-22T23:08:03Z</t>
         </is>
       </c>
     </row>
@@ -11002,7 +11002,7 @@
       </c>
       <c r="S125" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T17:38:14Z</t>
+          <t>2026-09-22T23:08:03Z</t>
         </is>
       </c>
     </row>
@@ -11091,7 +11091,7 @@
       </c>
       <c r="S126" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T17:38:14Z</t>
+          <t>2026-09-22T23:08:03Z</t>
         </is>
       </c>
     </row>
@@ -11180,7 +11180,7 @@
       </c>
       <c r="S127" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T17:38:14Z</t>
+          <t>2026-09-22T23:08:03Z</t>
         </is>
       </c>
     </row>
@@ -11269,7 +11269,7 @@
       </c>
       <c r="S128" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T17:38:14Z</t>
+          <t>2026-09-22T23:08:03Z</t>
         </is>
       </c>
     </row>
@@ -11354,7 +11354,7 @@
       </c>
       <c r="S129" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T17:38:14Z</t>
+          <t>2026-09-22T23:08:03Z</t>
         </is>
       </c>
     </row>
@@ -11439,7 +11439,7 @@
       </c>
       <c r="S130" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T17:38:14Z</t>
+          <t>2026-09-22T23:08:03Z</t>
         </is>
       </c>
     </row>
@@ -11524,7 +11524,7 @@
       </c>
       <c r="S131" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T17:38:14Z</t>
+          <t>2026-09-22T23:08:03Z</t>
         </is>
       </c>
     </row>
@@ -11609,7 +11609,7 @@
       </c>
       <c r="S132" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T17:38:14Z</t>
+          <t>2026-09-22T23:08:03Z</t>
         </is>
       </c>
     </row>
@@ -11694,7 +11694,7 @@
       </c>
       <c r="S133" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T17:38:14Z</t>
+          <t>2026-09-22T23:08:03Z</t>
         </is>
       </c>
     </row>
@@ -11779,7 +11779,7 @@
       </c>
       <c r="S134" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T17:38:14Z</t>
+          <t>2026-09-22T23:08:03Z</t>
         </is>
       </c>
     </row>
@@ -11864,7 +11864,7 @@
       </c>
       <c r="S135" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T17:38:14Z</t>
+          <t>2026-09-22T23:08:03Z</t>
         </is>
       </c>
     </row>
@@ -11949,7 +11949,7 @@
       </c>
       <c r="S136" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T17:38:14Z</t>
+          <t>2026-09-22T23:08:03Z</t>
         </is>
       </c>
     </row>
@@ -12034,7 +12034,7 @@
       </c>
       <c r="S137" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T17:38:14Z</t>
+          <t>2026-09-22T23:08:03Z</t>
         </is>
       </c>
     </row>
@@ -12119,7 +12119,7 @@
       </c>
       <c r="S138" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T17:38:14Z</t>
+          <t>2026-09-22T23:08:03Z</t>
         </is>
       </c>
     </row>
@@ -12204,7 +12204,7 @@
       </c>
       <c r="S139" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T17:38:14Z</t>
+          <t>2026-09-22T23:08:03Z</t>
         </is>
       </c>
     </row>
@@ -12289,7 +12289,7 @@
       </c>
       <c r="S140" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T17:38:14Z</t>
+          <t>2026-09-22T23:08:03Z</t>
         </is>
       </c>
     </row>
@@ -12374,7 +12374,7 @@
       </c>
       <c r="S141" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T17:38:14Z</t>
+          <t>2026-09-22T23:08:03Z</t>
         </is>
       </c>
     </row>
@@ -12459,7 +12459,7 @@
       </c>
       <c r="S142" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T17:38:14Z</t>
+          <t>2026-09-22T23:08:03Z</t>
         </is>
       </c>
     </row>
@@ -12544,7 +12544,7 @@
       </c>
       <c r="S143" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T17:38:14Z</t>
+          <t>2026-09-22T23:08:03Z</t>
         </is>
       </c>
     </row>
@@ -12629,7 +12629,7 @@
       </c>
       <c r="S144" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T17:38:14Z</t>
+          <t>2026-09-22T23:08:03Z</t>
         </is>
       </c>
     </row>
@@ -12714,7 +12714,7 @@
       </c>
       <c r="S145" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T17:38:14Z</t>
+          <t>2026-09-22T23:08:03Z</t>
         </is>
       </c>
     </row>
@@ -12799,7 +12799,7 @@
       </c>
       <c r="S146" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T17:38:14Z</t>
+          <t>2026-09-22T23:08:03Z</t>
         </is>
       </c>
     </row>
@@ -12884,7 +12884,7 @@
       </c>
       <c r="S147" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T17:38:14Z</t>
+          <t>2026-09-22T23:08:03Z</t>
         </is>
       </c>
     </row>
@@ -12969,7 +12969,7 @@
       </c>
       <c r="S148" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T17:38:14Z</t>
+          <t>2026-09-22T23:08:03Z</t>
         </is>
       </c>
     </row>
@@ -13054,7 +13054,7 @@
       </c>
       <c r="S149" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T17:38:14Z</t>
+          <t>2026-09-22T23:08:03Z</t>
         </is>
       </c>
     </row>
@@ -13143,7 +13143,7 @@
       </c>
       <c r="S150" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T17:38:14Z</t>
+          <t>2026-09-22T23:08:03Z</t>
         </is>
       </c>
     </row>
@@ -13232,7 +13232,7 @@
       </c>
       <c r="S151" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T17:38:14Z</t>
+          <t>2026-09-22T23:08:03Z</t>
         </is>
       </c>
     </row>
@@ -13317,7 +13317,7 @@
       </c>
       <c r="S152" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T17:38:14Z</t>
+          <t>2026-09-22T23:08:03Z</t>
         </is>
       </c>
     </row>
@@ -13406,7 +13406,7 @@
       </c>
       <c r="S153" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T17:38:14Z</t>
+          <t>2026-09-22T23:08:03Z</t>
         </is>
       </c>
     </row>
@@ -13495,7 +13495,7 @@
       </c>
       <c r="S154" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T17:38:14Z</t>
+          <t>2026-09-22T23:08:03Z</t>
         </is>
       </c>
     </row>
@@ -13580,7 +13580,7 @@
       </c>
       <c r="S155" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T17:38:14Z</t>
+          <t>2026-09-22T23:08:03Z</t>
         </is>
       </c>
     </row>
@@ -13669,7 +13669,7 @@
       </c>
       <c r="S156" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T17:38:14Z</t>
+          <t>2026-09-22T23:08:03Z</t>
         </is>
       </c>
     </row>
@@ -13758,7 +13758,7 @@
       </c>
       <c r="S157" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T17:38:14Z</t>
+          <t>2026-09-22T23:08:03Z</t>
         </is>
       </c>
     </row>
@@ -13843,7 +13843,7 @@
       </c>
       <c r="S158" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T17:38:14Z</t>
+          <t>2026-09-22T23:08:03Z</t>
         </is>
       </c>
     </row>
@@ -13932,7 +13932,7 @@
       </c>
       <c r="S159" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T17:38:14Z</t>
+          <t>2026-09-22T23:08:03Z</t>
         </is>
       </c>
     </row>
@@ -14021,7 +14021,7 @@
       </c>
       <c r="S160" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T17:38:14Z</t>
+          <t>2026-09-22T23:08:03Z</t>
         </is>
       </c>
     </row>
@@ -14106,7 +14106,7 @@
       </c>
       <c r="S161" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T17:38:14Z</t>
+          <t>2026-09-22T23:08:03Z</t>
         </is>
       </c>
     </row>
@@ -14195,7 +14195,7 @@
       </c>
       <c r="S162" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T17:38:14Z</t>
+          <t>2026-09-22T23:08:03Z</t>
         </is>
       </c>
     </row>
@@ -14284,7 +14284,7 @@
       </c>
       <c r="S163" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T17:38:14Z</t>
+          <t>2026-09-22T23:08:03Z</t>
         </is>
       </c>
     </row>
@@ -14369,7 +14369,7 @@
       </c>
       <c r="S164" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T17:38:14Z</t>
+          <t>2026-09-22T23:08:03Z</t>
         </is>
       </c>
     </row>
@@ -14458,7 +14458,7 @@
       </c>
       <c r="S165" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T17:38:14Z</t>
+          <t>2026-09-22T23:08:03Z</t>
         </is>
       </c>
     </row>
@@ -14547,7 +14547,7 @@
       </c>
       <c r="S166" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T17:38:14Z</t>
+          <t>2026-09-22T23:08:03Z</t>
         </is>
       </c>
     </row>
@@ -14632,7 +14632,7 @@
       </c>
       <c r="S167" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T17:38:14Z</t>
+          <t>2026-09-22T23:08:03Z</t>
         </is>
       </c>
     </row>
@@ -14721,7 +14721,7 @@
       </c>
       <c r="S168" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T17:38:14Z</t>
+          <t>2026-09-22T23:08:03Z</t>
         </is>
       </c>
     </row>
@@ -14810,7 +14810,7 @@
       </c>
       <c r="S169" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T17:38:14Z</t>
+          <t>2026-09-22T23:08:03Z</t>
         </is>
       </c>
     </row>
@@ -14895,7 +14895,7 @@
       </c>
       <c r="S170" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T17:38:14Z</t>
+          <t>2026-09-22T23:08:03Z</t>
         </is>
       </c>
     </row>
@@ -14984,7 +14984,7 @@
       </c>
       <c r="S171" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T17:38:14Z</t>
+          <t>2026-09-22T23:08:03Z</t>
         </is>
       </c>
     </row>
@@ -15073,7 +15073,7 @@
       </c>
       <c r="S172" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T17:38:14Z</t>
+          <t>2026-09-22T23:08:03Z</t>
         </is>
       </c>
     </row>
@@ -15158,7 +15158,7 @@
       </c>
       <c r="S173" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T17:38:14Z</t>
+          <t>2026-09-22T23:08:03Z</t>
         </is>
       </c>
     </row>
@@ -15247,7 +15247,7 @@
       </c>
       <c r="S174" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T17:38:14Z</t>
+          <t>2026-09-22T23:08:03Z</t>
         </is>
       </c>
     </row>
@@ -15336,7 +15336,7 @@
       </c>
       <c r="S175" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T17:38:14Z</t>
+          <t>2026-09-22T23:08:03Z</t>
         </is>
       </c>
     </row>
@@ -15421,7 +15421,7 @@
       </c>
       <c r="S176" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T17:38:14Z</t>
+          <t>2026-09-22T23:08:03Z</t>
         </is>
       </c>
     </row>
@@ -15510,7 +15510,7 @@
       </c>
       <c r="S177" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T17:38:14Z</t>
+          <t>2026-09-22T23:08:03Z</t>
         </is>
       </c>
     </row>
@@ -15599,7 +15599,7 @@
       </c>
       <c r="S178" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T17:38:14Z</t>
+          <t>2026-09-22T23:08:03Z</t>
         </is>
       </c>
     </row>
@@ -15688,7 +15688,7 @@
       </c>
       <c r="S179" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T17:38:14Z</t>
+          <t>2026-09-22T23:08:03Z</t>
         </is>
       </c>
     </row>
@@ -15777,7 +15777,7 @@
       </c>
       <c r="S180" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T17:38:14Z</t>
+          <t>2026-09-22T23:08:03Z</t>
         </is>
       </c>
     </row>
@@ -15866,7 +15866,7 @@
       </c>
       <c r="S181" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T17:38:14Z</t>
+          <t>2026-09-22T23:08:03Z</t>
         </is>
       </c>
     </row>
@@ -15955,7 +15955,7 @@
       </c>
       <c r="S182" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T17:38:14Z</t>
+          <t>2026-09-22T23:08:03Z</t>
         </is>
       </c>
     </row>
@@ -16044,7 +16044,7 @@
       </c>
       <c r="S183" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T17:38:14Z</t>
+          <t>2026-09-22T23:08:03Z</t>
         </is>
       </c>
     </row>
@@ -16133,7 +16133,7 @@
       </c>
       <c r="S184" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T17:38:14Z</t>
+          <t>2026-09-22T23:08:03Z</t>
         </is>
       </c>
     </row>
@@ -16222,7 +16222,7 @@
       </c>
       <c r="S185" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T17:38:14Z</t>
+          <t>2026-09-22T23:08:03Z</t>
         </is>
       </c>
     </row>
@@ -16311,7 +16311,7 @@
       </c>
       <c r="S186" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T17:38:14Z</t>
+          <t>2026-09-22T23:08:03Z</t>
         </is>
       </c>
     </row>
@@ -16400,7 +16400,7 @@
       </c>
       <c r="S187" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T17:38:14Z</t>
+          <t>2026-09-22T23:08:03Z</t>
         </is>
       </c>
     </row>
@@ -16489,7 +16489,7 @@
       </c>
       <c r="S188" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T17:38:14Z</t>
+          <t>2026-09-22T23:08:03Z</t>
         </is>
       </c>
     </row>
@@ -16578,7 +16578,7 @@
       </c>
       <c r="S189" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T17:38:14Z</t>
+          <t>2026-09-22T23:08:03Z</t>
         </is>
       </c>
     </row>
@@ -16663,7 +16663,7 @@
       </c>
       <c r="S190" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T17:38:14Z</t>
+          <t>2026-09-22T23:08:03Z</t>
         </is>
       </c>
     </row>
@@ -16748,7 +16748,7 @@
       </c>
       <c r="S191" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T17:38:14Z</t>
+          <t>2026-09-22T23:08:03Z</t>
         </is>
       </c>
     </row>
@@ -16833,7 +16833,7 @@
       </c>
       <c r="S192" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T17:38:14Z</t>
+          <t>2026-09-22T23:08:03Z</t>
         </is>
       </c>
     </row>
@@ -16918,7 +16918,7 @@
       </c>
       <c r="S193" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T17:38:14Z</t>
+          <t>2026-09-22T23:08:03Z</t>
         </is>
       </c>
     </row>
@@ -17003,7 +17003,7 @@
       </c>
       <c r="S194" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T17:38:14Z</t>
+          <t>2026-09-22T23:08:03Z</t>
         </is>
       </c>
     </row>
@@ -17088,7 +17088,7 @@
       </c>
       <c r="S195" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T17:38:14Z</t>
+          <t>2026-09-22T23:08:03Z</t>
         </is>
       </c>
     </row>
@@ -17173,7 +17173,7 @@
       </c>
       <c r="S196" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T17:38:14Z</t>
+          <t>2026-09-22T23:08:03Z</t>
         </is>
       </c>
     </row>
@@ -17258,7 +17258,7 @@
       </c>
       <c r="S197" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T17:38:14Z</t>
+          <t>2026-09-22T23:08:03Z</t>
         </is>
       </c>
     </row>
@@ -17343,7 +17343,7 @@
       </c>
       <c r="S198" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T17:38:14Z</t>
+          <t>2026-09-22T23:08:03Z</t>
         </is>
       </c>
     </row>
@@ -17428,7 +17428,7 @@
       </c>
       <c r="S199" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T17:38:14Z</t>
+          <t>2026-09-22T23:08:03Z</t>
         </is>
       </c>
     </row>
@@ -17513,7 +17513,7 @@
       </c>
       <c r="S200" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T17:38:14Z</t>
+          <t>2026-09-22T23:08:03Z</t>
         </is>
       </c>
     </row>
@@ -17598,7 +17598,7 @@
       </c>
       <c r="S201" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T17:38:14Z</t>
+          <t>2026-09-22T23:08:03Z</t>
         </is>
       </c>
     </row>
@@ -17683,7 +17683,7 @@
       </c>
       <c r="S202" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T17:38:14Z</t>
+          <t>2026-09-22T23:08:03Z</t>
         </is>
       </c>
     </row>
@@ -17768,7 +17768,7 @@
       </c>
       <c r="S203" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T17:38:14Z</t>
+          <t>2026-09-22T23:08:03Z</t>
         </is>
       </c>
     </row>
@@ -17853,7 +17853,7 @@
       </c>
       <c r="S204" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T17:38:14Z</t>
+          <t>2026-09-22T23:08:03Z</t>
         </is>
       </c>
     </row>
@@ -17938,7 +17938,7 @@
       </c>
       <c r="S205" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T17:38:14Z</t>
+          <t>2026-09-22T23:08:03Z</t>
         </is>
       </c>
     </row>
@@ -18023,7 +18023,7 @@
       </c>
       <c r="S206" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T17:38:14Z</t>
+          <t>2026-09-22T23:08:03Z</t>
         </is>
       </c>
     </row>
@@ -18108,7 +18108,7 @@
       </c>
       <c r="S207" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T17:38:14Z</t>
+          <t>2026-09-22T23:08:03Z</t>
         </is>
       </c>
     </row>
@@ -18193,7 +18193,7 @@
       </c>
       <c r="S208" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T17:38:14Z</t>
+          <t>2026-09-22T23:08:03Z</t>
         </is>
       </c>
     </row>
@@ -18278,7 +18278,7 @@
       </c>
       <c r="S209" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T17:38:14Z</t>
+          <t>2026-09-22T23:08:03Z</t>
         </is>
       </c>
     </row>
@@ -18363,7 +18363,7 @@
       </c>
       <c r="S210" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T17:38:14Z</t>
+          <t>2026-09-22T23:08:03Z</t>
         </is>
       </c>
     </row>
@@ -18452,7 +18452,7 @@
       </c>
       <c r="S211" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T17:38:14Z</t>
+          <t>2026-09-22T23:08:03Z</t>
         </is>
       </c>
     </row>
@@ -18541,7 +18541,7 @@
       </c>
       <c r="S212" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T17:38:14Z</t>
+          <t>2026-09-22T23:08:03Z</t>
         </is>
       </c>
     </row>
@@ -18626,7 +18626,7 @@
       </c>
       <c r="S213" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T17:38:14Z</t>
+          <t>2026-09-22T23:08:03Z</t>
         </is>
       </c>
     </row>
@@ -18715,7 +18715,7 @@
       </c>
       <c r="S214" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T17:38:14Z</t>
+          <t>2026-09-22T23:08:03Z</t>
         </is>
       </c>
     </row>
@@ -18804,7 +18804,7 @@
       </c>
       <c r="S215" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T17:38:14Z</t>
+          <t>2026-09-22T23:08:03Z</t>
         </is>
       </c>
     </row>
@@ -18889,7 +18889,7 @@
       </c>
       <c r="S216" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T17:38:14Z</t>
+          <t>2026-09-22T23:08:03Z</t>
         </is>
       </c>
     </row>
@@ -18978,7 +18978,7 @@
       </c>
       <c r="S217" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T17:38:14Z</t>
+          <t>2026-09-22T23:08:03Z</t>
         </is>
       </c>
     </row>
@@ -19067,7 +19067,7 @@
       </c>
       <c r="S218" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T17:38:14Z</t>
+          <t>2026-09-22T23:08:03Z</t>
         </is>
       </c>
     </row>
@@ -19152,7 +19152,7 @@
       </c>
       <c r="S219" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T17:38:14Z</t>
+          <t>2026-09-22T23:08:03Z</t>
         </is>
       </c>
     </row>
@@ -19241,7 +19241,7 @@
       </c>
       <c r="S220" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T17:38:14Z</t>
+          <t>2026-09-22T23:08:03Z</t>
         </is>
       </c>
     </row>
@@ -19330,7 +19330,7 @@
       </c>
       <c r="S221" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T17:38:14Z</t>
+          <t>2026-09-22T23:08:03Z</t>
         </is>
       </c>
     </row>
@@ -19415,7 +19415,7 @@
       </c>
       <c r="S222" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T17:38:14Z</t>
+          <t>2026-09-22T23:08:03Z</t>
         </is>
       </c>
     </row>
@@ -19504,7 +19504,7 @@
       </c>
       <c r="S223" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T17:38:14Z</t>
+          <t>2026-09-22T23:08:03Z</t>
         </is>
       </c>
     </row>
@@ -19593,7 +19593,7 @@
       </c>
       <c r="S224" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T17:38:14Z</t>
+          <t>2026-09-22T23:08:03Z</t>
         </is>
       </c>
     </row>
@@ -19678,7 +19678,7 @@
       </c>
       <c r="S225" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T17:38:14Z</t>
+          <t>2026-09-22T23:08:03Z</t>
         </is>
       </c>
     </row>
@@ -19767,7 +19767,7 @@
       </c>
       <c r="S226" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T17:38:14Z</t>
+          <t>2026-09-22T23:08:03Z</t>
         </is>
       </c>
     </row>
@@ -19856,7 +19856,7 @@
       </c>
       <c r="S227" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T17:38:14Z</t>
+          <t>2026-09-22T23:08:03Z</t>
         </is>
       </c>
     </row>
@@ -19941,7 +19941,7 @@
       </c>
       <c r="S228" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T17:38:14Z</t>
+          <t>2026-09-22T23:08:03Z</t>
         </is>
       </c>
     </row>
@@ -20030,7 +20030,7 @@
       </c>
       <c r="S229" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T17:38:14Z</t>
+          <t>2026-09-22T23:08:03Z</t>
         </is>
       </c>
     </row>
@@ -20119,7 +20119,7 @@
       </c>
       <c r="S230" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T17:38:14Z</t>
+          <t>2026-09-22T23:08:03Z</t>
         </is>
       </c>
     </row>
@@ -20204,7 +20204,7 @@
       </c>
       <c r="S231" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T17:38:14Z</t>
+          <t>2026-09-22T23:08:03Z</t>
         </is>
       </c>
     </row>
@@ -20293,7 +20293,7 @@
       </c>
       <c r="S232" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T17:38:14Z</t>
+          <t>2026-09-22T23:08:03Z</t>
         </is>
       </c>
     </row>
@@ -20382,7 +20382,7 @@
       </c>
       <c r="S233" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T17:38:14Z</t>
+          <t>2026-09-22T23:08:03Z</t>
         </is>
       </c>
     </row>
@@ -20467,7 +20467,7 @@
       </c>
       <c r="S234" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T17:38:14Z</t>
+          <t>2026-09-22T23:08:03Z</t>
         </is>
       </c>
     </row>
@@ -20556,7 +20556,7 @@
       </c>
       <c r="S235" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T17:38:14Z</t>
+          <t>2026-09-22T23:08:03Z</t>
         </is>
       </c>
     </row>
@@ -20645,7 +20645,7 @@
       </c>
       <c r="S236" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T17:38:14Z</t>
+          <t>2026-09-22T23:08:03Z</t>
         </is>
       </c>
     </row>
@@ -20730,7 +20730,7 @@
       </c>
       <c r="S237" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T17:38:14Z</t>
+          <t>2026-09-22T23:08:03Z</t>
         </is>
       </c>
     </row>
@@ -20819,7 +20819,7 @@
       </c>
       <c r="S238" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T17:38:14Z</t>
+          <t>2026-09-22T23:08:03Z</t>
         </is>
       </c>
     </row>
@@ -20908,7 +20908,7 @@
       </c>
       <c r="S239" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T17:38:14Z</t>
+          <t>2026-09-22T23:08:03Z</t>
         </is>
       </c>
     </row>
@@ -20997,7 +20997,7 @@
       </c>
       <c r="S240" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T17:38:14Z</t>
+          <t>2026-09-22T23:08:03Z</t>
         </is>
       </c>
     </row>
@@ -21086,7 +21086,7 @@
       </c>
       <c r="S241" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T17:38:14Z</t>
+          <t>2026-09-22T23:08:03Z</t>
         </is>
       </c>
     </row>
@@ -21175,7 +21175,7 @@
       </c>
       <c r="S242" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T17:38:14Z</t>
+          <t>2026-09-22T23:08:03Z</t>
         </is>
       </c>
     </row>
@@ -21264,7 +21264,7 @@
       </c>
       <c r="S243" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T17:38:14Z</t>
+          <t>2026-09-22T23:08:03Z</t>
         </is>
       </c>
     </row>
@@ -21353,7 +21353,7 @@
       </c>
       <c r="S244" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T17:38:14Z</t>
+          <t>2026-09-22T23:08:03Z</t>
         </is>
       </c>
     </row>
@@ -21442,7 +21442,7 @@
       </c>
       <c r="S245" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T17:38:14Z</t>
+          <t>2026-09-22T23:08:03Z</t>
         </is>
       </c>
     </row>
@@ -21531,7 +21531,7 @@
       </c>
       <c r="S246" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T17:38:14Z</t>
+          <t>2026-09-22T23:08:03Z</t>
         </is>
       </c>
     </row>
@@ -21620,7 +21620,7 @@
       </c>
       <c r="S247" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T17:38:14Z</t>
+          <t>2026-09-22T23:08:03Z</t>
         </is>
       </c>
     </row>
@@ -21709,7 +21709,7 @@
       </c>
       <c r="S248" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T17:38:14Z</t>
+          <t>2026-09-22T23:08:03Z</t>
         </is>
       </c>
     </row>
@@ -21798,7 +21798,7 @@
       </c>
       <c r="S249" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T17:38:14Z</t>
+          <t>2026-09-22T23:08:03Z</t>
         </is>
       </c>
     </row>
@@ -21887,7 +21887,7 @@
       </c>
       <c r="S250" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T17:38:14Z</t>
+          <t>2026-09-22T23:08:03Z</t>
         </is>
       </c>
     </row>
@@ -22019,7 +22019,7 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T17:38:14Z</t>
+          <t>2026-09-22T23:08:03Z</t>
         </is>
       </c>
     </row>
@@ -22099,7 +22099,7 @@
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>{"dataset_id": "bcv_pib_sector_institucional_anual", "title": "Producto interno bruto por sector institucional anual", "table": "Variaciones porcentuales", "source_file": "5_2_1_si_anual.xlsx", "base": "2007", "price_type": "Precios constantes", "measure": "Variación porcentual interanual", "frequency": "Anual", "period": "2025", "year": 2025, "quarter": null, "classification": "Sector institucional", "component": "Impuestos netos sobre los productos", "value": 10.600260421283764, "unit": "Porcentaje", "status": "Preliminar", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/cuentas_macroeconomicas/5_2_1_si_anual.xlsx", "fetched_at": "2026-09-22T17:38:14Z"}</t>
+          <t>{"dataset_id": "bcv_pib_sector_institucional_anual", "title": "Producto interno bruto por sector institucional anual", "table": "Variaciones porcentuales", "source_file": "5_2_1_si_anual.xlsx", "base": "2007", "price_type": "Precios constantes", "measure": "Variación porcentual interanual", "frequency": "Anual", "period": "2025", "year": 2025, "quarter": null, "classification": "Sector institucional", "component": "Impuestos netos sobre los productos", "value": 10.600260421283764, "unit": "Porcentaje", "status": "Preliminar", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/cuentas_macroeconomicas/5_2_1_si_anual.xlsx", "fetched_at": "2026-09-22T23:08:03Z"}</t>
         </is>
       </c>
     </row>

--- a/assets/data/bcv/excel/ove_bcv_pib_sector_institucional_anual.xlsx
+++ b/assets/data/bcv/excel/ove_bcv_pib_sector_institucional_anual.xlsx
@@ -736,7 +736,7 @@
       </c>
       <c r="S7" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T23:08:03Z</t>
+          <t>2026-09-23T23:02:38Z</t>
         </is>
       </c>
     </row>
@@ -821,7 +821,7 @@
       </c>
       <c r="S8" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T23:08:03Z</t>
+          <t>2026-09-23T23:02:38Z</t>
         </is>
       </c>
     </row>
@@ -906,7 +906,7 @@
       </c>
       <c r="S9" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T23:08:03Z</t>
+          <t>2026-09-23T23:02:38Z</t>
         </is>
       </c>
     </row>
@@ -991,7 +991,7 @@
       </c>
       <c r="S10" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T23:08:03Z</t>
+          <t>2026-09-23T23:02:38Z</t>
         </is>
       </c>
     </row>
@@ -1076,7 +1076,7 @@
       </c>
       <c r="S11" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T23:08:03Z</t>
+          <t>2026-09-23T23:02:38Z</t>
         </is>
       </c>
     </row>
@@ -1161,7 +1161,7 @@
       </c>
       <c r="S12" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T23:08:03Z</t>
+          <t>2026-09-23T23:02:38Z</t>
         </is>
       </c>
     </row>
@@ -1246,7 +1246,7 @@
       </c>
       <c r="S13" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T23:08:03Z</t>
+          <t>2026-09-23T23:02:38Z</t>
         </is>
       </c>
     </row>
@@ -1331,7 +1331,7 @@
       </c>
       <c r="S14" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T23:08:03Z</t>
+          <t>2026-09-23T23:02:38Z</t>
         </is>
       </c>
     </row>
@@ -1416,7 +1416,7 @@
       </c>
       <c r="S15" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T23:08:03Z</t>
+          <t>2026-09-23T23:02:38Z</t>
         </is>
       </c>
     </row>
@@ -1501,7 +1501,7 @@
       </c>
       <c r="S16" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T23:08:03Z</t>
+          <t>2026-09-23T23:02:38Z</t>
         </is>
       </c>
     </row>
@@ -1586,7 +1586,7 @@
       </c>
       <c r="S17" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T23:08:03Z</t>
+          <t>2026-09-23T23:02:38Z</t>
         </is>
       </c>
     </row>
@@ -1671,7 +1671,7 @@
       </c>
       <c r="S18" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T23:08:03Z</t>
+          <t>2026-09-23T23:02:38Z</t>
         </is>
       </c>
     </row>
@@ -1756,7 +1756,7 @@
       </c>
       <c r="S19" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T23:08:03Z</t>
+          <t>2026-09-23T23:02:38Z</t>
         </is>
       </c>
     </row>
@@ -1841,7 +1841,7 @@
       </c>
       <c r="S20" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T23:08:03Z</t>
+          <t>2026-09-23T23:02:38Z</t>
         </is>
       </c>
     </row>
@@ -1926,7 +1926,7 @@
       </c>
       <c r="S21" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T23:08:03Z</t>
+          <t>2026-09-23T23:02:38Z</t>
         </is>
       </c>
     </row>
@@ -2011,7 +2011,7 @@
       </c>
       <c r="S22" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T23:08:03Z</t>
+          <t>2026-09-23T23:02:38Z</t>
         </is>
       </c>
     </row>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="S23" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T23:08:03Z</t>
+          <t>2026-09-23T23:02:38Z</t>
         </is>
       </c>
     </row>
@@ -2181,7 +2181,7 @@
       </c>
       <c r="S24" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T23:08:03Z</t>
+          <t>2026-09-23T23:02:38Z</t>
         </is>
       </c>
     </row>
@@ -2266,7 +2266,7 @@
       </c>
       <c r="S25" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T23:08:03Z</t>
+          <t>2026-09-23T23:02:38Z</t>
         </is>
       </c>
     </row>
@@ -2351,7 +2351,7 @@
       </c>
       <c r="S26" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T23:08:03Z</t>
+          <t>2026-09-23T23:02:38Z</t>
         </is>
       </c>
     </row>
@@ -2436,7 +2436,7 @@
       </c>
       <c r="S27" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T23:08:03Z</t>
+          <t>2026-09-23T23:02:38Z</t>
         </is>
       </c>
     </row>
@@ -2525,7 +2525,7 @@
       </c>
       <c r="S28" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T23:08:03Z</t>
+          <t>2026-09-23T23:02:38Z</t>
         </is>
       </c>
     </row>
@@ -2614,7 +2614,7 @@
       </c>
       <c r="S29" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T23:08:03Z</t>
+          <t>2026-09-23T23:02:38Z</t>
         </is>
       </c>
     </row>
@@ -2699,7 +2699,7 @@
       </c>
       <c r="S30" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T23:08:03Z</t>
+          <t>2026-09-23T23:02:38Z</t>
         </is>
       </c>
     </row>
@@ -2788,7 +2788,7 @@
       </c>
       <c r="S31" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T23:08:03Z</t>
+          <t>2026-09-23T23:02:38Z</t>
         </is>
       </c>
     </row>
@@ -2877,7 +2877,7 @@
       </c>
       <c r="S32" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T23:08:03Z</t>
+          <t>2026-09-23T23:02:38Z</t>
         </is>
       </c>
     </row>
@@ -2962,7 +2962,7 @@
       </c>
       <c r="S33" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T23:08:03Z</t>
+          <t>2026-09-23T23:02:38Z</t>
         </is>
       </c>
     </row>
@@ -3051,7 +3051,7 @@
       </c>
       <c r="S34" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T23:08:03Z</t>
+          <t>2026-09-23T23:02:38Z</t>
         </is>
       </c>
     </row>
@@ -3140,7 +3140,7 @@
       </c>
       <c r="S35" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T23:08:03Z</t>
+          <t>2026-09-23T23:02:38Z</t>
         </is>
       </c>
     </row>
@@ -3225,7 +3225,7 @@
       </c>
       <c r="S36" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T23:08:03Z</t>
+          <t>2026-09-23T23:02:38Z</t>
         </is>
       </c>
     </row>
@@ -3314,7 +3314,7 @@
       </c>
       <c r="S37" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T23:08:03Z</t>
+          <t>2026-09-23T23:02:38Z</t>
         </is>
       </c>
     </row>
@@ -3403,7 +3403,7 @@
       </c>
       <c r="S38" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T23:08:03Z</t>
+          <t>2026-09-23T23:02:38Z</t>
         </is>
       </c>
     </row>
@@ -3488,7 +3488,7 @@
       </c>
       <c r="S39" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T23:08:03Z</t>
+          <t>2026-09-23T23:02:38Z</t>
         </is>
       </c>
     </row>
@@ -3577,7 +3577,7 @@
       </c>
       <c r="S40" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T23:08:03Z</t>
+          <t>2026-09-23T23:02:38Z</t>
         </is>
       </c>
     </row>
@@ -3666,7 +3666,7 @@
       </c>
       <c r="S41" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T23:08:03Z</t>
+          <t>2026-09-23T23:02:38Z</t>
         </is>
       </c>
     </row>
@@ -3751,7 +3751,7 @@
       </c>
       <c r="S42" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T23:08:03Z</t>
+          <t>2026-09-23T23:02:38Z</t>
         </is>
       </c>
     </row>
@@ -3840,7 +3840,7 @@
       </c>
       <c r="S43" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T23:08:03Z</t>
+          <t>2026-09-23T23:02:38Z</t>
         </is>
       </c>
     </row>
@@ -3929,7 +3929,7 @@
       </c>
       <c r="S44" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T23:08:03Z</t>
+          <t>2026-09-23T23:02:38Z</t>
         </is>
       </c>
     </row>
@@ -4014,7 +4014,7 @@
       </c>
       <c r="S45" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T23:08:03Z</t>
+          <t>2026-09-23T23:02:38Z</t>
         </is>
       </c>
     </row>
@@ -4103,7 +4103,7 @@
       </c>
       <c r="S46" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T23:08:03Z</t>
+          <t>2026-09-23T23:02:38Z</t>
         </is>
       </c>
     </row>
@@ -4192,7 +4192,7 @@
       </c>
       <c r="S47" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T23:08:03Z</t>
+          <t>2026-09-23T23:02:38Z</t>
         </is>
       </c>
     </row>
@@ -4277,7 +4277,7 @@
       </c>
       <c r="S48" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T23:08:03Z</t>
+          <t>2026-09-23T23:02:38Z</t>
         </is>
       </c>
     </row>
@@ -4366,7 +4366,7 @@
       </c>
       <c r="S49" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T23:08:03Z</t>
+          <t>2026-09-23T23:02:38Z</t>
         </is>
       </c>
     </row>
@@ -4455,7 +4455,7 @@
       </c>
       <c r="S50" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T23:08:03Z</t>
+          <t>2026-09-23T23:02:38Z</t>
         </is>
       </c>
     </row>
@@ -4540,7 +4540,7 @@
       </c>
       <c r="S51" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T23:08:03Z</t>
+          <t>2026-09-23T23:02:38Z</t>
         </is>
       </c>
     </row>
@@ -4629,7 +4629,7 @@
       </c>
       <c r="S52" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T23:08:03Z</t>
+          <t>2026-09-23T23:02:38Z</t>
         </is>
       </c>
     </row>
@@ -4718,7 +4718,7 @@
       </c>
       <c r="S53" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T23:08:03Z</t>
+          <t>2026-09-23T23:02:38Z</t>
         </is>
       </c>
     </row>
@@ -4803,7 +4803,7 @@
       </c>
       <c r="S54" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T23:08:03Z</t>
+          <t>2026-09-23T23:02:38Z</t>
         </is>
       </c>
     </row>
@@ -4892,7 +4892,7 @@
       </c>
       <c r="S55" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T23:08:03Z</t>
+          <t>2026-09-23T23:02:38Z</t>
         </is>
       </c>
     </row>
@@ -4981,7 +4981,7 @@
       </c>
       <c r="S56" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T23:08:03Z</t>
+          <t>2026-09-23T23:02:38Z</t>
         </is>
       </c>
     </row>
@@ -5070,7 +5070,7 @@
       </c>
       <c r="S57" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T23:08:03Z</t>
+          <t>2026-09-23T23:02:38Z</t>
         </is>
       </c>
     </row>
@@ -5159,7 +5159,7 @@
       </c>
       <c r="S58" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T23:08:03Z</t>
+          <t>2026-09-23T23:02:38Z</t>
         </is>
       </c>
     </row>
@@ -5248,7 +5248,7 @@
       </c>
       <c r="S59" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T23:08:03Z</t>
+          <t>2026-09-23T23:02:38Z</t>
         </is>
       </c>
     </row>
@@ -5337,7 +5337,7 @@
       </c>
       <c r="S60" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T23:08:03Z</t>
+          <t>2026-09-23T23:02:38Z</t>
         </is>
       </c>
     </row>
@@ -5426,7 +5426,7 @@
       </c>
       <c r="S61" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T23:08:03Z</t>
+          <t>2026-09-23T23:02:38Z</t>
         </is>
       </c>
     </row>
@@ -5515,7 +5515,7 @@
       </c>
       <c r="S62" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T23:08:03Z</t>
+          <t>2026-09-23T23:02:38Z</t>
         </is>
       </c>
     </row>
@@ -5604,7 +5604,7 @@
       </c>
       <c r="S63" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T23:08:03Z</t>
+          <t>2026-09-23T23:02:38Z</t>
         </is>
       </c>
     </row>
@@ -5693,7 +5693,7 @@
       </c>
       <c r="S64" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T23:08:03Z</t>
+          <t>2026-09-23T23:02:38Z</t>
         </is>
       </c>
     </row>
@@ -5782,7 +5782,7 @@
       </c>
       <c r="S65" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T23:08:03Z</t>
+          <t>2026-09-23T23:02:38Z</t>
         </is>
       </c>
     </row>
@@ -5871,7 +5871,7 @@
       </c>
       <c r="S66" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T23:08:03Z</t>
+          <t>2026-09-23T23:02:38Z</t>
         </is>
       </c>
     </row>
@@ -5960,7 +5960,7 @@
       </c>
       <c r="S67" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T23:08:03Z</t>
+          <t>2026-09-23T23:02:38Z</t>
         </is>
       </c>
     </row>
@@ -6045,7 +6045,7 @@
       </c>
       <c r="S68" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T23:08:03Z</t>
+          <t>2026-09-23T23:02:38Z</t>
         </is>
       </c>
     </row>
@@ -6130,7 +6130,7 @@
       </c>
       <c r="S69" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T23:08:03Z</t>
+          <t>2026-09-23T23:02:38Z</t>
         </is>
       </c>
     </row>
@@ -6215,7 +6215,7 @@
       </c>
       <c r="S70" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T23:08:03Z</t>
+          <t>2026-09-23T23:02:38Z</t>
         </is>
       </c>
     </row>
@@ -6300,7 +6300,7 @@
       </c>
       <c r="S71" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T23:08:03Z</t>
+          <t>2026-09-23T23:02:38Z</t>
         </is>
       </c>
     </row>
@@ -6385,7 +6385,7 @@
       </c>
       <c r="S72" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T23:08:03Z</t>
+          <t>2026-09-23T23:02:38Z</t>
         </is>
       </c>
     </row>
@@ -6470,7 +6470,7 @@
       </c>
       <c r="S73" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T23:08:03Z</t>
+          <t>2026-09-23T23:02:38Z</t>
         </is>
       </c>
     </row>
@@ -6555,7 +6555,7 @@
       </c>
       <c r="S74" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T23:08:03Z</t>
+          <t>2026-09-23T23:02:38Z</t>
         </is>
       </c>
     </row>
@@ -6640,7 +6640,7 @@
       </c>
       <c r="S75" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T23:08:03Z</t>
+          <t>2026-09-23T23:02:38Z</t>
         </is>
       </c>
     </row>
@@ -6725,7 +6725,7 @@
       </c>
       <c r="S76" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T23:08:03Z</t>
+          <t>2026-09-23T23:02:38Z</t>
         </is>
       </c>
     </row>
@@ -6810,7 +6810,7 @@
       </c>
       <c r="S77" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T23:08:03Z</t>
+          <t>2026-09-23T23:02:38Z</t>
         </is>
       </c>
     </row>
@@ -6895,7 +6895,7 @@
       </c>
       <c r="S78" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T23:08:03Z</t>
+          <t>2026-09-23T23:02:38Z</t>
         </is>
       </c>
     </row>
@@ -6980,7 +6980,7 @@
       </c>
       <c r="S79" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T23:08:03Z</t>
+          <t>2026-09-23T23:02:38Z</t>
         </is>
       </c>
     </row>
@@ -7065,7 +7065,7 @@
       </c>
       <c r="S80" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T23:08:03Z</t>
+          <t>2026-09-23T23:02:38Z</t>
         </is>
       </c>
     </row>
@@ -7150,7 +7150,7 @@
       </c>
       <c r="S81" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T23:08:03Z</t>
+          <t>2026-09-23T23:02:38Z</t>
         </is>
       </c>
     </row>
@@ -7235,7 +7235,7 @@
       </c>
       <c r="S82" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T23:08:03Z</t>
+          <t>2026-09-23T23:02:38Z</t>
         </is>
       </c>
     </row>
@@ -7320,7 +7320,7 @@
       </c>
       <c r="S83" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T23:08:03Z</t>
+          <t>2026-09-23T23:02:38Z</t>
         </is>
       </c>
     </row>
@@ -7405,7 +7405,7 @@
       </c>
       <c r="S84" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T23:08:03Z</t>
+          <t>2026-09-23T23:02:38Z</t>
         </is>
       </c>
     </row>
@@ -7490,7 +7490,7 @@
       </c>
       <c r="S85" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T23:08:03Z</t>
+          <t>2026-09-23T23:02:38Z</t>
         </is>
       </c>
     </row>
@@ -7575,7 +7575,7 @@
       </c>
       <c r="S86" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T23:08:03Z</t>
+          <t>2026-09-23T23:02:38Z</t>
         </is>
       </c>
     </row>
@@ -7660,7 +7660,7 @@
       </c>
       <c r="S87" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T23:08:03Z</t>
+          <t>2026-09-23T23:02:38Z</t>
         </is>
       </c>
     </row>
@@ -7745,7 +7745,7 @@
       </c>
       <c r="S88" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T23:08:03Z</t>
+          <t>2026-09-23T23:02:38Z</t>
         </is>
       </c>
     </row>
@@ -7834,7 +7834,7 @@
       </c>
       <c r="S89" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T23:08:03Z</t>
+          <t>2026-09-23T23:02:38Z</t>
         </is>
       </c>
     </row>
@@ -7923,7 +7923,7 @@
       </c>
       <c r="S90" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T23:08:03Z</t>
+          <t>2026-09-23T23:02:38Z</t>
         </is>
       </c>
     </row>
@@ -8008,7 +8008,7 @@
       </c>
       <c r="S91" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T23:08:03Z</t>
+          <t>2026-09-23T23:02:38Z</t>
         </is>
       </c>
     </row>
@@ -8097,7 +8097,7 @@
       </c>
       <c r="S92" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T23:08:03Z</t>
+          <t>2026-09-23T23:02:38Z</t>
         </is>
       </c>
     </row>
@@ -8186,7 +8186,7 @@
       </c>
       <c r="S93" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T23:08:03Z</t>
+          <t>2026-09-23T23:02:38Z</t>
         </is>
       </c>
     </row>
@@ -8271,7 +8271,7 @@
       </c>
       <c r="S94" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T23:08:03Z</t>
+          <t>2026-09-23T23:02:38Z</t>
         </is>
       </c>
     </row>
@@ -8360,7 +8360,7 @@
       </c>
       <c r="S95" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T23:08:03Z</t>
+          <t>2026-09-23T23:02:38Z</t>
         </is>
       </c>
     </row>
@@ -8449,7 +8449,7 @@
       </c>
       <c r="S96" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T23:08:03Z</t>
+          <t>2026-09-23T23:02:38Z</t>
         </is>
       </c>
     </row>
@@ -8534,7 +8534,7 @@
       </c>
       <c r="S97" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T23:08:03Z</t>
+          <t>2026-09-23T23:02:38Z</t>
         </is>
       </c>
     </row>
@@ -8623,7 +8623,7 @@
       </c>
       <c r="S98" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T23:08:03Z</t>
+          <t>2026-09-23T23:02:38Z</t>
         </is>
       </c>
     </row>
@@ -8712,7 +8712,7 @@
       </c>
       <c r="S99" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T23:08:03Z</t>
+          <t>2026-09-23T23:02:38Z</t>
         </is>
       </c>
     </row>
@@ -8797,7 +8797,7 @@
       </c>
       <c r="S100" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T23:08:03Z</t>
+          <t>2026-09-23T23:02:38Z</t>
         </is>
       </c>
     </row>
@@ -8886,7 +8886,7 @@
       </c>
       <c r="S101" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T23:08:03Z</t>
+          <t>2026-09-23T23:02:38Z</t>
         </is>
       </c>
     </row>
@@ -8975,7 +8975,7 @@
       </c>
       <c r="S102" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T23:08:03Z</t>
+          <t>2026-09-23T23:02:38Z</t>
         </is>
       </c>
     </row>
@@ -9060,7 +9060,7 @@
       </c>
       <c r="S103" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T23:08:03Z</t>
+          <t>2026-09-23T23:02:38Z</t>
         </is>
       </c>
     </row>
@@ -9149,7 +9149,7 @@
       </c>
       <c r="S104" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T23:08:03Z</t>
+          <t>2026-09-23T23:02:38Z</t>
         </is>
       </c>
     </row>
@@ -9238,7 +9238,7 @@
       </c>
       <c r="S105" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T23:08:03Z</t>
+          <t>2026-09-23T23:02:38Z</t>
         </is>
       </c>
     </row>
@@ -9323,7 +9323,7 @@
       </c>
       <c r="S106" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T23:08:03Z</t>
+          <t>2026-09-23T23:02:38Z</t>
         </is>
       </c>
     </row>
@@ -9412,7 +9412,7 @@
       </c>
       <c r="S107" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T23:08:03Z</t>
+          <t>2026-09-23T23:02:38Z</t>
         </is>
       </c>
     </row>
@@ -9501,7 +9501,7 @@
       </c>
       <c r="S108" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T23:08:03Z</t>
+          <t>2026-09-23T23:02:38Z</t>
         </is>
       </c>
     </row>
@@ -9586,7 +9586,7 @@
       </c>
       <c r="S109" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T23:08:03Z</t>
+          <t>2026-09-23T23:02:38Z</t>
         </is>
       </c>
     </row>
@@ -9675,7 +9675,7 @@
       </c>
       <c r="S110" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T23:08:03Z</t>
+          <t>2026-09-23T23:02:38Z</t>
         </is>
       </c>
     </row>
@@ -9764,7 +9764,7 @@
       </c>
       <c r="S111" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T23:08:03Z</t>
+          <t>2026-09-23T23:02:38Z</t>
         </is>
       </c>
     </row>
@@ -9849,7 +9849,7 @@
       </c>
       <c r="S112" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T23:08:03Z</t>
+          <t>2026-09-23T23:02:38Z</t>
         </is>
       </c>
     </row>
@@ -9938,7 +9938,7 @@
       </c>
       <c r="S113" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T23:08:03Z</t>
+          <t>2026-09-23T23:02:38Z</t>
         </is>
       </c>
     </row>
@@ -10027,7 +10027,7 @@
       </c>
       <c r="S114" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T23:08:03Z</t>
+          <t>2026-09-23T23:02:38Z</t>
         </is>
       </c>
     </row>
@@ -10112,7 +10112,7 @@
       </c>
       <c r="S115" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T23:08:03Z</t>
+          <t>2026-09-23T23:02:38Z</t>
         </is>
       </c>
     </row>
@@ -10201,7 +10201,7 @@
       </c>
       <c r="S116" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T23:08:03Z</t>
+          <t>2026-09-23T23:02:38Z</t>
         </is>
       </c>
     </row>
@@ -10290,7 +10290,7 @@
       </c>
       <c r="S117" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T23:08:03Z</t>
+          <t>2026-09-23T23:02:38Z</t>
         </is>
       </c>
     </row>
@@ -10379,7 +10379,7 @@
       </c>
       <c r="S118" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T23:08:03Z</t>
+          <t>2026-09-23T23:02:38Z</t>
         </is>
       </c>
     </row>
@@ -10468,7 +10468,7 @@
       </c>
       <c r="S119" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T23:08:03Z</t>
+          <t>2026-09-23T23:02:38Z</t>
         </is>
       </c>
     </row>
@@ -10557,7 +10557,7 @@
       </c>
       <c r="S120" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T23:08:03Z</t>
+          <t>2026-09-23T23:02:38Z</t>
         </is>
       </c>
     </row>
@@ -10646,7 +10646,7 @@
       </c>
       <c r="S121" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T23:08:03Z</t>
+          <t>2026-09-23T23:02:38Z</t>
         </is>
       </c>
     </row>
@@ -10735,7 +10735,7 @@
       </c>
       <c r="S122" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T23:08:03Z</t>
+          <t>2026-09-23T23:02:38Z</t>
         </is>
       </c>
     </row>
@@ -10824,7 +10824,7 @@
       </c>
       <c r="S123" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T23:08:03Z</t>
+          <t>2026-09-23T23:02:38Z</t>
         </is>
       </c>
     </row>
@@ -10913,7 +10913,7 @@
       </c>
       <c r="S124" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T23:08:03Z</t>
+          <t>2026-09-23T23:02:38Z</t>
         </is>
       </c>
     </row>
@@ -11002,7 +11002,7 @@
       </c>
       <c r="S125" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T23:08:03Z</t>
+          <t>2026-09-23T23:02:38Z</t>
         </is>
       </c>
     </row>
@@ -11091,7 +11091,7 @@
       </c>
       <c r="S126" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T23:08:03Z</t>
+          <t>2026-09-23T23:02:38Z</t>
         </is>
       </c>
     </row>
@@ -11180,7 +11180,7 @@
       </c>
       <c r="S127" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T23:08:03Z</t>
+          <t>2026-09-23T23:02:38Z</t>
         </is>
       </c>
     </row>
@@ -11269,7 +11269,7 @@
       </c>
       <c r="S128" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T23:08:03Z</t>
+          <t>2026-09-23T23:02:38Z</t>
         </is>
       </c>
     </row>
@@ -11354,7 +11354,7 @@
       </c>
       <c r="S129" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T23:08:03Z</t>
+          <t>2026-09-23T23:02:38Z</t>
         </is>
       </c>
     </row>
@@ -11439,7 +11439,7 @@
       </c>
       <c r="S130" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T23:08:03Z</t>
+          <t>2026-09-23T23:02:38Z</t>
         </is>
       </c>
     </row>
@@ -11524,7 +11524,7 @@
       </c>
       <c r="S131" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T23:08:03Z</t>
+          <t>2026-09-23T23:02:38Z</t>
         </is>
       </c>
     </row>
@@ -11609,7 +11609,7 @@
       </c>
       <c r="S132" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T23:08:03Z</t>
+          <t>2026-09-23T23:02:38Z</t>
         </is>
       </c>
     </row>
@@ -11694,7 +11694,7 @@
       </c>
       <c r="S133" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T23:08:03Z</t>
+          <t>2026-09-23T23:02:38Z</t>
         </is>
       </c>
     </row>
@@ -11779,7 +11779,7 @@
       </c>
       <c r="S134" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T23:08:03Z</t>
+          <t>2026-09-23T23:02:38Z</t>
         </is>
       </c>
     </row>
@@ -11864,7 +11864,7 @@
       </c>
       <c r="S135" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T23:08:03Z</t>
+          <t>2026-09-23T23:02:38Z</t>
         </is>
       </c>
     </row>
@@ -11949,7 +11949,7 @@
       </c>
       <c r="S136" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T23:08:03Z</t>
+          <t>2026-09-23T23:02:38Z</t>
         </is>
       </c>
     </row>
@@ -12034,7 +12034,7 @@
       </c>
       <c r="S137" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T23:08:03Z</t>
+          <t>2026-09-23T23:02:38Z</t>
         </is>
       </c>
     </row>
@@ -12119,7 +12119,7 @@
       </c>
       <c r="S138" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T23:08:03Z</t>
+          <t>2026-09-23T23:02:38Z</t>
         </is>
       </c>
     </row>
@@ -12204,7 +12204,7 @@
       </c>
       <c r="S139" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T23:08:03Z</t>
+          <t>2026-09-23T23:02:38Z</t>
         </is>
       </c>
     </row>
@@ -12289,7 +12289,7 @@
       </c>
       <c r="S140" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T23:08:03Z</t>
+          <t>2026-09-23T23:02:38Z</t>
         </is>
       </c>
     </row>
@@ -12374,7 +12374,7 @@
       </c>
       <c r="S141" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T23:08:03Z</t>
+          <t>2026-09-23T23:02:38Z</t>
         </is>
       </c>
     </row>
@@ -12459,7 +12459,7 @@
       </c>
       <c r="S142" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T23:08:03Z</t>
+          <t>2026-09-23T23:02:38Z</t>
         </is>
       </c>
     </row>
@@ -12544,7 +12544,7 @@
       </c>
       <c r="S143" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T23:08:03Z</t>
+          <t>2026-09-23T23:02:38Z</t>
         </is>
       </c>
     </row>
@@ -12629,7 +12629,7 @@
       </c>
       <c r="S144" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T23:08:03Z</t>
+          <t>2026-09-23T23:02:38Z</t>
         </is>
       </c>
     </row>
@@ -12714,7 +12714,7 @@
       </c>
       <c r="S145" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T23:08:03Z</t>
+          <t>2026-09-23T23:02:38Z</t>
         </is>
       </c>
     </row>
@@ -12799,7 +12799,7 @@
       </c>
       <c r="S146" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T23:08:03Z</t>
+          <t>2026-09-23T23:02:38Z</t>
         </is>
       </c>
     </row>
@@ -12884,7 +12884,7 @@
       </c>
       <c r="S147" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T23:08:03Z</t>
+          <t>2026-09-23T23:02:38Z</t>
         </is>
       </c>
     </row>
@@ -12969,7 +12969,7 @@
       </c>
       <c r="S148" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T23:08:03Z</t>
+          <t>2026-09-23T23:02:38Z</t>
         </is>
       </c>
     </row>
@@ -13054,7 +13054,7 @@
       </c>
       <c r="S149" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T23:08:03Z</t>
+          <t>2026-09-23T23:02:38Z</t>
         </is>
       </c>
     </row>
@@ -13143,7 +13143,7 @@
       </c>
       <c r="S150" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T23:08:03Z</t>
+          <t>2026-09-23T23:02:38Z</t>
         </is>
       </c>
     </row>
@@ -13232,7 +13232,7 @@
       </c>
       <c r="S151" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T23:08:03Z</t>
+          <t>2026-09-23T23:02:38Z</t>
         </is>
       </c>
     </row>
@@ -13317,7 +13317,7 @@
       </c>
       <c r="S152" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T23:08:03Z</t>
+          <t>2026-09-23T23:02:38Z</t>
         </is>
       </c>
     </row>
@@ -13406,7 +13406,7 @@
       </c>
       <c r="S153" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T23:08:03Z</t>
+          <t>2026-09-23T23:02:38Z</t>
         </is>
       </c>
     </row>
@@ -13495,7 +13495,7 @@
       </c>
       <c r="S154" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T23:08:03Z</t>
+          <t>2026-09-23T23:02:38Z</t>
         </is>
       </c>
     </row>
@@ -13580,7 +13580,7 @@
       </c>
       <c r="S155" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T23:08:03Z</t>
+          <t>2026-09-23T23:02:38Z</t>
         </is>
       </c>
     </row>
@@ -13669,7 +13669,7 @@
       </c>
       <c r="S156" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T23:08:03Z</t>
+          <t>2026-09-23T23:02:38Z</t>
         </is>
       </c>
     </row>
@@ -13758,7 +13758,7 @@
       </c>
       <c r="S157" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T23:08:03Z</t>
+          <t>2026-09-23T23:02:38Z</t>
         </is>
       </c>
     </row>
@@ -13843,7 +13843,7 @@
       </c>
       <c r="S158" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T23:08:03Z</t>
+          <t>2026-09-23T23:02:38Z</t>
         </is>
       </c>
     </row>
@@ -13932,7 +13932,7 @@
       </c>
       <c r="S159" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T23:08:03Z</t>
+          <t>2026-09-23T23:02:38Z</t>
         </is>
       </c>
     </row>
@@ -14021,7 +14021,7 @@
       </c>
       <c r="S160" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T23:08:03Z</t>
+          <t>2026-09-23T23:02:38Z</t>
         </is>
       </c>
     </row>
@@ -14106,7 +14106,7 @@
       </c>
       <c r="S161" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T23:08:03Z</t>
+          <t>2026-09-23T23:02:38Z</t>
         </is>
       </c>
     </row>
@@ -14195,7 +14195,7 @@
       </c>
       <c r="S162" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T23:08:03Z</t>
+          <t>2026-09-23T23:02:38Z</t>
         </is>
       </c>
     </row>
@@ -14284,7 +14284,7 @@
       </c>
       <c r="S163" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T23:08:03Z</t>
+          <t>2026-09-23T23:02:38Z</t>
         </is>
       </c>
     </row>
@@ -14369,7 +14369,7 @@
       </c>
       <c r="S164" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T23:08:03Z</t>
+          <t>2026-09-23T23:02:38Z</t>
         </is>
       </c>
     </row>
@@ -14458,7 +14458,7 @@
       </c>
       <c r="S165" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T23:08:03Z</t>
+          <t>2026-09-23T23:02:38Z</t>
         </is>
       </c>
     </row>
@@ -14547,7 +14547,7 @@
       </c>
       <c r="S166" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T23:08:03Z</t>
+          <t>2026-09-23T23:02:38Z</t>
         </is>
       </c>
     </row>
@@ -14632,7 +14632,7 @@
       </c>
       <c r="S167" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T23:08:03Z</t>
+          <t>2026-09-23T23:02:38Z</t>
         </is>
       </c>
     </row>
@@ -14721,7 +14721,7 @@
       </c>
       <c r="S168" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T23:08:03Z</t>
+          <t>2026-09-23T23:02:38Z</t>
         </is>
       </c>
     </row>
@@ -14810,7 +14810,7 @@
       </c>
       <c r="S169" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T23:08:03Z</t>
+          <t>2026-09-23T23:02:38Z</t>
         </is>
       </c>
     </row>
@@ -14895,7 +14895,7 @@
       </c>
       <c r="S170" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T23:08:03Z</t>
+          <t>2026-09-23T23:02:38Z</t>
         </is>
       </c>
     </row>
@@ -14984,7 +14984,7 @@
       </c>
       <c r="S171" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T23:08:03Z</t>
+          <t>2026-09-23T23:02:38Z</t>
         </is>
       </c>
     </row>
@@ -15073,7 +15073,7 @@
       </c>
       <c r="S172" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T23:08:03Z</t>
+          <t>2026-09-23T23:02:38Z</t>
         </is>
       </c>
     </row>
@@ -15158,7 +15158,7 @@
       </c>
       <c r="S173" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T23:08:03Z</t>
+          <t>2026-09-23T23:02:38Z</t>
         </is>
       </c>
     </row>
@@ -15247,7 +15247,7 @@
       </c>
       <c r="S174" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T23:08:03Z</t>
+          <t>2026-09-23T23:02:38Z</t>
         </is>
       </c>
     </row>
@@ -15336,7 +15336,7 @@
       </c>
       <c r="S175" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T23:08:03Z</t>
+          <t>2026-09-23T23:02:38Z</t>
         </is>
       </c>
     </row>
@@ -15421,7 +15421,7 @@
       </c>
       <c r="S176" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T23:08:03Z</t>
+          <t>2026-09-23T23:02:38Z</t>
         </is>
       </c>
     </row>
@@ -15510,7 +15510,7 @@
       </c>
       <c r="S177" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T23:08:03Z</t>
+          <t>2026-09-23T23:02:38Z</t>
         </is>
       </c>
     </row>
@@ -15599,7 +15599,7 @@
       </c>
       <c r="S178" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T23:08:03Z</t>
+          <t>2026-09-23T23:02:38Z</t>
         </is>
       </c>
     </row>
@@ -15688,7 +15688,7 @@
       </c>
       <c r="S179" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T23:08:03Z</t>
+          <t>2026-09-23T23:02:38Z</t>
         </is>
       </c>
     </row>
@@ -15777,7 +15777,7 @@
       </c>
       <c r="S180" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T23:08:03Z</t>
+          <t>2026-09-23T23:02:38Z</t>
         </is>
       </c>
     </row>
@@ -15866,7 +15866,7 @@
       </c>
       <c r="S181" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T23:08:03Z</t>
+          <t>2026-09-23T23:02:38Z</t>
         </is>
       </c>
     </row>
@@ -15955,7 +15955,7 @@
       </c>
       <c r="S182" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T23:08:03Z</t>
+          <t>2026-09-23T23:02:38Z</t>
         </is>
       </c>
     </row>
@@ -16044,7 +16044,7 @@
       </c>
       <c r="S183" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T23:08:03Z</t>
+          <t>2026-09-23T23:02:38Z</t>
         </is>
       </c>
     </row>
@@ -16133,7 +16133,7 @@
       </c>
       <c r="S184" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T23:08:03Z</t>
+          <t>2026-09-23T23:02:38Z</t>
         </is>
       </c>
     </row>
@@ -16222,7 +16222,7 @@
       </c>
       <c r="S185" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T23:08:03Z</t>
+          <t>2026-09-23T23:02:38Z</t>
         </is>
       </c>
     </row>
@@ -16311,7 +16311,7 @@
       </c>
       <c r="S186" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T23:08:03Z</t>
+          <t>2026-09-23T23:02:38Z</t>
         </is>
       </c>
     </row>
@@ -16400,7 +16400,7 @@
       </c>
       <c r="S187" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T23:08:03Z</t>
+          <t>2026-09-23T23:02:38Z</t>
         </is>
       </c>
     </row>
@@ -16489,7 +16489,7 @@
       </c>
       <c r="S188" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T23:08:03Z</t>
+          <t>2026-09-23T23:02:38Z</t>
         </is>
       </c>
     </row>
@@ -16578,7 +16578,7 @@
       </c>
       <c r="S189" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T23:08:03Z</t>
+          <t>2026-09-23T23:02:38Z</t>
         </is>
       </c>
     </row>
@@ -16663,7 +16663,7 @@
       </c>
       <c r="S190" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T23:08:03Z</t>
+          <t>2026-09-23T23:02:38Z</t>
         </is>
       </c>
     </row>
@@ -16748,7 +16748,7 @@
       </c>
       <c r="S191" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T23:08:03Z</t>
+          <t>2026-09-23T23:02:38Z</t>
         </is>
       </c>
     </row>
@@ -16833,7 +16833,7 @@
       </c>
       <c r="S192" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T23:08:03Z</t>
+          <t>2026-09-23T23:02:38Z</t>
         </is>
       </c>
     </row>
@@ -16918,7 +16918,7 @@
       </c>
       <c r="S193" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T23:08:03Z</t>
+          <t>2026-09-23T23:02:38Z</t>
         </is>
       </c>
     </row>
@@ -17003,7 +17003,7 @@
       </c>
       <c r="S194" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T23:08:03Z</t>
+          <t>2026-09-23T23:02:38Z</t>
         </is>
       </c>
     </row>
@@ -17088,7 +17088,7 @@
       </c>
       <c r="S195" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T23:08:03Z</t>
+          <t>2026-09-23T23:02:38Z</t>
         </is>
       </c>
     </row>
@@ -17173,7 +17173,7 @@
       </c>
       <c r="S196" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T23:08:03Z</t>
+          <t>2026-09-23T23:02:38Z</t>
         </is>
       </c>
     </row>
@@ -17258,7 +17258,7 @@
       </c>
       <c r="S197" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T23:08:03Z</t>
+          <t>2026-09-23T23:02:38Z</t>
         </is>
       </c>
     </row>
@@ -17343,7 +17343,7 @@
       </c>
       <c r="S198" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T23:08:03Z</t>
+          <t>2026-09-23T23:02:38Z</t>
         </is>
       </c>
     </row>
@@ -17428,7 +17428,7 @@
       </c>
       <c r="S199" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T23:08:03Z</t>
+          <t>2026-09-23T23:02:38Z</t>
         </is>
       </c>
     </row>
@@ -17513,7 +17513,7 @@
       </c>
       <c r="S200" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T23:08:03Z</t>
+          <t>2026-09-23T23:02:38Z</t>
         </is>
       </c>
     </row>
@@ -17598,7 +17598,7 @@
       </c>
       <c r="S201" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T23:08:03Z</t>
+          <t>2026-09-23T23:02:38Z</t>
         </is>
       </c>
     </row>
@@ -17683,7 +17683,7 @@
       </c>
       <c r="S202" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T23:08:03Z</t>
+          <t>2026-09-23T23:02:38Z</t>
         </is>
       </c>
     </row>
@@ -17768,7 +17768,7 @@
       </c>
       <c r="S203" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T23:08:03Z</t>
+          <t>2026-09-23T23:02:38Z</t>
         </is>
       </c>
     </row>
@@ -17853,7 +17853,7 @@
       </c>
       <c r="S204" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T23:08:03Z</t>
+          <t>2026-09-23T23:02:38Z</t>
         </is>
       </c>
     </row>
@@ -17938,7 +17938,7 @@
       </c>
       <c r="S205" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T23:08:03Z</t>
+          <t>2026-09-23T23:02:38Z</t>
         </is>
       </c>
     </row>
@@ -18023,7 +18023,7 @@
       </c>
       <c r="S206" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T23:08:03Z</t>
+          <t>2026-09-23T23:02:38Z</t>
         </is>
       </c>
     </row>
@@ -18108,7 +18108,7 @@
       </c>
       <c r="S207" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T23:08:03Z</t>
+          <t>2026-09-23T23:02:38Z</t>
         </is>
       </c>
     </row>
@@ -18193,7 +18193,7 @@
       </c>
       <c r="S208" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T23:08:03Z</t>
+          <t>2026-09-23T23:02:38Z</t>
         </is>
       </c>
     </row>
@@ -18278,7 +18278,7 @@
       </c>
       <c r="S209" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T23:08:03Z</t>
+          <t>2026-09-23T23:02:38Z</t>
         </is>
       </c>
     </row>
@@ -18363,7 +18363,7 @@
       </c>
       <c r="S210" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T23:08:03Z</t>
+          <t>2026-09-23T23:02:38Z</t>
         </is>
       </c>
     </row>
@@ -18452,7 +18452,7 @@
       </c>
       <c r="S211" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T23:08:03Z</t>
+          <t>2026-09-23T23:02:38Z</t>
         </is>
       </c>
     </row>
@@ -18541,7 +18541,7 @@
       </c>
       <c r="S212" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T23:08:03Z</t>
+          <t>2026-09-23T23:02:38Z</t>
         </is>
       </c>
     </row>
@@ -18626,7 +18626,7 @@
       </c>
       <c r="S213" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T23:08:03Z</t>
+          <t>2026-09-23T23:02:38Z</t>
         </is>
       </c>
     </row>
@@ -18715,7 +18715,7 @@
       </c>
       <c r="S214" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T23:08:03Z</t>
+          <t>2026-09-23T23:02:38Z</t>
         </is>
       </c>
     </row>
@@ -18804,7 +18804,7 @@
       </c>
       <c r="S215" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T23:08:03Z</t>
+          <t>2026-09-23T23:02:38Z</t>
         </is>
       </c>
     </row>
@@ -18889,7 +18889,7 @@
       </c>
       <c r="S216" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T23:08:03Z</t>
+          <t>2026-09-23T23:02:38Z</t>
         </is>
       </c>
     </row>
@@ -18978,7 +18978,7 @@
       </c>
       <c r="S217" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T23:08:03Z</t>
+          <t>2026-09-23T23:02:38Z</t>
         </is>
       </c>
     </row>
@@ -19067,7 +19067,7 @@
       </c>
       <c r="S218" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T23:08:03Z</t>
+          <t>2026-09-23T23:02:38Z</t>
         </is>
       </c>
     </row>
@@ -19152,7 +19152,7 @@
       </c>
       <c r="S219" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T23:08:03Z</t>
+          <t>2026-09-23T23:02:38Z</t>
         </is>
       </c>
     </row>
@@ -19241,7 +19241,7 @@
       </c>
       <c r="S220" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T23:08:03Z</t>
+          <t>2026-09-23T23:02:38Z</t>
         </is>
       </c>
     </row>
@@ -19330,7 +19330,7 @@
       </c>
       <c r="S221" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T23:08:03Z</t>
+          <t>2026-09-23T23:02:38Z</t>
         </is>
       </c>
     </row>
@@ -19415,7 +19415,7 @@
       </c>
       <c r="S222" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T23:08:03Z</t>
+          <t>2026-09-23T23:02:38Z</t>
         </is>
       </c>
     </row>
@@ -19504,7 +19504,7 @@
       </c>
       <c r="S223" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T23:08:03Z</t>
+          <t>2026-09-23T23:02:38Z</t>
         </is>
       </c>
     </row>
@@ -19593,7 +19593,7 @@
       </c>
       <c r="S224" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T23:08:03Z</t>
+          <t>2026-09-23T23:02:38Z</t>
         </is>
       </c>
     </row>
@@ -19678,7 +19678,7 @@
       </c>
       <c r="S225" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T23:08:03Z</t>
+          <t>2026-09-23T23:02:38Z</t>
         </is>
       </c>
     </row>
@@ -19767,7 +19767,7 @@
       </c>
       <c r="S226" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T23:08:03Z</t>
+          <t>2026-09-23T23:02:38Z</t>
         </is>
       </c>
     </row>
@@ -19856,7 +19856,7 @@
       </c>
       <c r="S227" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T23:08:03Z</t>
+          <t>2026-09-23T23:02:38Z</t>
         </is>
       </c>
     </row>
@@ -19941,7 +19941,7 @@
       </c>
       <c r="S228" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T23:08:03Z</t>
+          <t>2026-09-23T23:02:38Z</t>
         </is>
       </c>
     </row>
@@ -20030,7 +20030,7 @@
       </c>
       <c r="S229" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T23:08:03Z</t>
+          <t>2026-09-23T23:02:38Z</t>
         </is>
       </c>
     </row>
@@ -20119,7 +20119,7 @@
       </c>
       <c r="S230" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T23:08:03Z</t>
+          <t>2026-09-23T23:02:38Z</t>
         </is>
       </c>
     </row>
@@ -20204,7 +20204,7 @@
       </c>
       <c r="S231" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T23:08:03Z</t>
+          <t>2026-09-23T23:02:38Z</t>
         </is>
       </c>
     </row>
@@ -20293,7 +20293,7 @@
       </c>
       <c r="S232" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T23:08:03Z</t>
+          <t>2026-09-23T23:02:38Z</t>
         </is>
       </c>
     </row>
@@ -20382,7 +20382,7 @@
       </c>
       <c r="S233" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T23:08:03Z</t>
+          <t>2026-09-23T23:02:38Z</t>
         </is>
       </c>
     </row>
@@ -20467,7 +20467,7 @@
       </c>
       <c r="S234" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T23:08:03Z</t>
+          <t>2026-09-23T23:02:38Z</t>
         </is>
       </c>
     </row>
@@ -20556,7 +20556,7 @@
       </c>
       <c r="S235" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T23:08:03Z</t>
+          <t>2026-09-23T23:02:38Z</t>
         </is>
       </c>
     </row>
@@ -20645,7 +20645,7 @@
       </c>
       <c r="S236" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T23:08:03Z</t>
+          <t>2026-09-23T23:02:38Z</t>
         </is>
       </c>
     </row>
@@ -20730,7 +20730,7 @@
       </c>
       <c r="S237" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T23:08:03Z</t>
+          <t>2026-09-23T23:02:38Z</t>
         </is>
       </c>
     </row>
@@ -20819,7 +20819,7 @@
       </c>
       <c r="S238" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T23:08:03Z</t>
+          <t>2026-09-23T23:02:38Z</t>
         </is>
       </c>
     </row>
@@ -20908,7 +20908,7 @@
       </c>
       <c r="S239" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T23:08:03Z</t>
+          <t>2026-09-23T23:02:38Z</t>
         </is>
       </c>
     </row>
@@ -20997,7 +20997,7 @@
       </c>
       <c r="S240" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T23:08:03Z</t>
+          <t>2026-09-23T23:02:38Z</t>
         </is>
       </c>
     </row>
@@ -21086,7 +21086,7 @@
       </c>
       <c r="S241" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T23:08:03Z</t>
+          <t>2026-09-23T23:02:38Z</t>
         </is>
       </c>
     </row>
@@ -21175,7 +21175,7 @@
       </c>
       <c r="S242" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T23:08:03Z</t>
+          <t>2026-09-23T23:02:38Z</t>
         </is>
       </c>
     </row>
@@ -21264,7 +21264,7 @@
       </c>
       <c r="S243" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T23:08:03Z</t>
+          <t>2026-09-23T23:02:38Z</t>
         </is>
       </c>
     </row>
@@ -21353,7 +21353,7 @@
       </c>
       <c r="S244" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T23:08:03Z</t>
+          <t>2026-09-23T23:02:38Z</t>
         </is>
       </c>
     </row>
@@ -21442,7 +21442,7 @@
       </c>
       <c r="S245" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T23:08:03Z</t>
+          <t>2026-09-23T23:02:38Z</t>
         </is>
       </c>
     </row>
@@ -21531,7 +21531,7 @@
       </c>
       <c r="S246" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T23:08:03Z</t>
+          <t>2026-09-23T23:02:38Z</t>
         </is>
       </c>
     </row>
@@ -21620,7 +21620,7 @@
       </c>
       <c r="S247" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T23:08:03Z</t>
+          <t>2026-09-23T23:02:38Z</t>
         </is>
       </c>
     </row>
@@ -21709,7 +21709,7 @@
       </c>
       <c r="S248" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T23:08:03Z</t>
+          <t>2026-09-23T23:02:38Z</t>
         </is>
       </c>
     </row>
@@ -21798,7 +21798,7 @@
       </c>
       <c r="S249" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T23:08:03Z</t>
+          <t>2026-09-23T23:02:38Z</t>
         </is>
       </c>
     </row>
@@ -21887,7 +21887,7 @@
       </c>
       <c r="S250" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T23:08:03Z</t>
+          <t>2026-09-23T23:02:38Z</t>
         </is>
       </c>
     </row>
@@ -22019,7 +22019,7 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T23:08:03Z</t>
+          <t>2026-09-23T23:02:38Z</t>
         </is>
       </c>
     </row>
@@ -22099,7 +22099,7 @@
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>{"dataset_id": "bcv_pib_sector_institucional_anual", "title": "Producto interno bruto por sector institucional anual", "table": "Variaciones porcentuales", "source_file": "5_2_1_si_anual.xlsx", "base": "2007", "price_type": "Precios constantes", "measure": "Variación porcentual interanual", "frequency": "Anual", "period": "2025", "year": 2025, "quarter": null, "classification": "Sector institucional", "component": "Impuestos netos sobre los productos", "value": 10.600260421283764, "unit": "Porcentaje", "status": "Preliminar", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/cuentas_macroeconomicas/5_2_1_si_anual.xlsx", "fetched_at": "2026-09-22T23:08:03Z"}</t>
+          <t>{"dataset_id": "bcv_pib_sector_institucional_anual", "title": "Producto interno bruto por sector institucional anual", "table": "Variaciones porcentuales", "source_file": "5_2_1_si_anual.xlsx", "base": "2007", "price_type": "Precios constantes", "measure": "Variación porcentual interanual", "frequency": "Anual", "period": "2025", "year": 2025, "quarter": null, "classification": "Sector institucional", "component": "Impuestos netos sobre los productos", "value": 10.600260421283764, "unit": "Porcentaje", "status": "Preliminar", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/cuentas_macroeconomicas/5_2_1_si_anual.xlsx", "fetched_at": "2026-09-23T23:02:38Z"}</t>
         </is>
       </c>
     </row>

--- a/assets/data/bcv/excel/ove_bcv_pib_sector_institucional_anual.xlsx
+++ b/assets/data/bcv/excel/ove_bcv_pib_sector_institucional_anual.xlsx
@@ -736,7 +736,7 @@
       </c>
       <c r="S7" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23T23:02:38Z</t>
+          <t>2026-09-24T23:17:58Z</t>
         </is>
       </c>
     </row>
@@ -821,7 +821,7 @@
       </c>
       <c r="S8" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23T23:02:38Z</t>
+          <t>2026-09-24T23:17:58Z</t>
         </is>
       </c>
     </row>
@@ -906,7 +906,7 @@
       </c>
       <c r="S9" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23T23:02:38Z</t>
+          <t>2026-09-24T23:17:58Z</t>
         </is>
       </c>
     </row>
@@ -991,7 +991,7 @@
       </c>
       <c r="S10" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23T23:02:38Z</t>
+          <t>2026-09-24T23:17:58Z</t>
         </is>
       </c>
     </row>
@@ -1076,7 +1076,7 @@
       </c>
       <c r="S11" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23T23:02:38Z</t>
+          <t>2026-09-24T23:17:58Z</t>
         </is>
       </c>
     </row>
@@ -1161,7 +1161,7 @@
       </c>
       <c r="S12" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23T23:02:38Z</t>
+          <t>2026-09-24T23:17:58Z</t>
         </is>
       </c>
     </row>
@@ -1246,7 +1246,7 @@
       </c>
       <c r="S13" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23T23:02:38Z</t>
+          <t>2026-09-24T23:17:58Z</t>
         </is>
       </c>
     </row>
@@ -1331,7 +1331,7 @@
       </c>
       <c r="S14" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23T23:02:38Z</t>
+          <t>2026-09-24T23:17:58Z</t>
         </is>
       </c>
     </row>
@@ -1416,7 +1416,7 @@
       </c>
       <c r="S15" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23T23:02:38Z</t>
+          <t>2026-09-24T23:17:58Z</t>
         </is>
       </c>
     </row>
@@ -1501,7 +1501,7 @@
       </c>
       <c r="S16" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23T23:02:38Z</t>
+          <t>2026-09-24T23:17:58Z</t>
         </is>
       </c>
     </row>
@@ -1586,7 +1586,7 @@
       </c>
       <c r="S17" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23T23:02:38Z</t>
+          <t>2026-09-24T23:17:58Z</t>
         </is>
       </c>
     </row>
@@ -1671,7 +1671,7 @@
       </c>
       <c r="S18" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23T23:02:38Z</t>
+          <t>2026-09-24T23:17:58Z</t>
         </is>
       </c>
     </row>
@@ -1756,7 +1756,7 @@
       </c>
       <c r="S19" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23T23:02:38Z</t>
+          <t>2026-09-24T23:17:58Z</t>
         </is>
       </c>
     </row>
@@ -1841,7 +1841,7 @@
       </c>
       <c r="S20" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23T23:02:38Z</t>
+          <t>2026-09-24T23:17:58Z</t>
         </is>
       </c>
     </row>
@@ -1926,7 +1926,7 @@
       </c>
       <c r="S21" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23T23:02:38Z</t>
+          <t>2026-09-24T23:17:58Z</t>
         </is>
       </c>
     </row>
@@ -2011,7 +2011,7 @@
       </c>
       <c r="S22" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23T23:02:38Z</t>
+          <t>2026-09-24T23:17:58Z</t>
         </is>
       </c>
     </row>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="S23" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23T23:02:38Z</t>
+          <t>2026-09-24T23:17:58Z</t>
         </is>
       </c>
     </row>
@@ -2181,7 +2181,7 @@
       </c>
       <c r="S24" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23T23:02:38Z</t>
+          <t>2026-09-24T23:17:58Z</t>
         </is>
       </c>
     </row>
@@ -2266,7 +2266,7 @@
       </c>
       <c r="S25" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23T23:02:38Z</t>
+          <t>2026-09-24T23:17:58Z</t>
         </is>
       </c>
     </row>
@@ -2351,7 +2351,7 @@
       </c>
       <c r="S26" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23T23:02:38Z</t>
+          <t>2026-09-24T23:17:58Z</t>
         </is>
       </c>
     </row>
@@ -2436,7 +2436,7 @@
       </c>
       <c r="S27" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23T23:02:38Z</t>
+          <t>2026-09-24T23:17:58Z</t>
         </is>
       </c>
     </row>
@@ -2525,7 +2525,7 @@
       </c>
       <c r="S28" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23T23:02:38Z</t>
+          <t>2026-09-24T23:17:58Z</t>
         </is>
       </c>
     </row>
@@ -2614,7 +2614,7 @@
       </c>
       <c r="S29" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23T23:02:38Z</t>
+          <t>2026-09-24T23:17:58Z</t>
         </is>
       </c>
     </row>
@@ -2699,7 +2699,7 @@
       </c>
       <c r="S30" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23T23:02:38Z</t>
+          <t>2026-09-24T23:17:58Z</t>
         </is>
       </c>
     </row>
@@ -2788,7 +2788,7 @@
       </c>
       <c r="S31" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23T23:02:38Z</t>
+          <t>2026-09-24T23:17:58Z</t>
         </is>
       </c>
     </row>
@@ -2877,7 +2877,7 @@
       </c>
       <c r="S32" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23T23:02:38Z</t>
+          <t>2026-09-24T23:17:58Z</t>
         </is>
       </c>
     </row>
@@ -2962,7 +2962,7 @@
       </c>
       <c r="S33" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23T23:02:38Z</t>
+          <t>2026-09-24T23:17:58Z</t>
         </is>
       </c>
     </row>
@@ -3051,7 +3051,7 @@
       </c>
       <c r="S34" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23T23:02:38Z</t>
+          <t>2026-09-24T23:17:58Z</t>
         </is>
       </c>
     </row>
@@ -3140,7 +3140,7 @@
       </c>
       <c r="S35" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23T23:02:38Z</t>
+          <t>2026-09-24T23:17:58Z</t>
         </is>
       </c>
     </row>
@@ -3225,7 +3225,7 @@
       </c>
       <c r="S36" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23T23:02:38Z</t>
+          <t>2026-09-24T23:17:58Z</t>
         </is>
       </c>
     </row>
@@ -3314,7 +3314,7 @@
       </c>
       <c r="S37" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23T23:02:38Z</t>
+          <t>2026-09-24T23:17:58Z</t>
         </is>
       </c>
     </row>
@@ -3403,7 +3403,7 @@
       </c>
       <c r="S38" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23T23:02:38Z</t>
+          <t>2026-09-24T23:17:58Z</t>
         </is>
       </c>
     </row>
@@ -3488,7 +3488,7 @@
       </c>
       <c r="S39" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23T23:02:38Z</t>
+          <t>2026-09-24T23:17:58Z</t>
         </is>
       </c>
     </row>
@@ -3577,7 +3577,7 @@
       </c>
       <c r="S40" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23T23:02:38Z</t>
+          <t>2026-09-24T23:17:58Z</t>
         </is>
       </c>
     </row>
@@ -3666,7 +3666,7 @@
       </c>
       <c r="S41" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23T23:02:38Z</t>
+          <t>2026-09-24T23:17:58Z</t>
         </is>
       </c>
     </row>
@@ -3751,7 +3751,7 @@
       </c>
       <c r="S42" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23T23:02:38Z</t>
+          <t>2026-09-24T23:17:58Z</t>
         </is>
       </c>
     </row>
@@ -3840,7 +3840,7 @@
       </c>
       <c r="S43" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23T23:02:38Z</t>
+          <t>2026-09-24T23:17:58Z</t>
         </is>
       </c>
     </row>
@@ -3929,7 +3929,7 @@
       </c>
       <c r="S44" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23T23:02:38Z</t>
+          <t>2026-09-24T23:17:58Z</t>
         </is>
       </c>
     </row>
@@ -4014,7 +4014,7 @@
       </c>
       <c r="S45" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23T23:02:38Z</t>
+          <t>2026-09-24T23:17:58Z</t>
         </is>
       </c>
     </row>
@@ -4103,7 +4103,7 @@
       </c>
       <c r="S46" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23T23:02:38Z</t>
+          <t>2026-09-24T23:17:58Z</t>
         </is>
       </c>
     </row>
@@ -4192,7 +4192,7 @@
       </c>
       <c r="S47" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23T23:02:38Z</t>
+          <t>2026-09-24T23:17:58Z</t>
         </is>
       </c>
     </row>
@@ -4277,7 +4277,7 @@
       </c>
       <c r="S48" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23T23:02:38Z</t>
+          <t>2026-09-24T23:17:58Z</t>
         </is>
       </c>
     </row>
@@ -4366,7 +4366,7 @@
       </c>
       <c r="S49" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23T23:02:38Z</t>
+          <t>2026-09-24T23:17:58Z</t>
         </is>
       </c>
     </row>
@@ -4455,7 +4455,7 @@
       </c>
       <c r="S50" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23T23:02:38Z</t>
+          <t>2026-09-24T23:17:58Z</t>
         </is>
       </c>
     </row>
@@ -4540,7 +4540,7 @@
       </c>
       <c r="S51" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23T23:02:38Z</t>
+          <t>2026-09-24T23:17:58Z</t>
         </is>
       </c>
     </row>
@@ -4629,7 +4629,7 @@
       </c>
       <c r="S52" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23T23:02:38Z</t>
+          <t>2026-09-24T23:17:58Z</t>
         </is>
       </c>
     </row>
@@ -4718,7 +4718,7 @@
       </c>
       <c r="S53" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23T23:02:38Z</t>
+          <t>2026-09-24T23:17:58Z</t>
         </is>
       </c>
     </row>
@@ -4803,7 +4803,7 @@
       </c>
       <c r="S54" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23T23:02:38Z</t>
+          <t>2026-09-24T23:17:58Z</t>
         </is>
       </c>
     </row>
@@ -4892,7 +4892,7 @@
       </c>
       <c r="S55" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23T23:02:38Z</t>
+          <t>2026-09-24T23:17:58Z</t>
         </is>
       </c>
     </row>
@@ -4981,7 +4981,7 @@
       </c>
       <c r="S56" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23T23:02:38Z</t>
+          <t>2026-09-24T23:17:58Z</t>
         </is>
       </c>
     </row>
@@ -5070,7 +5070,7 @@
       </c>
       <c r="S57" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23T23:02:38Z</t>
+          <t>2026-09-24T23:17:58Z</t>
         </is>
       </c>
     </row>
@@ -5159,7 +5159,7 @@
       </c>
       <c r="S58" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23T23:02:38Z</t>
+          <t>2026-09-24T23:17:58Z</t>
         </is>
       </c>
     </row>
@@ -5248,7 +5248,7 @@
       </c>
       <c r="S59" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23T23:02:38Z</t>
+          <t>2026-09-24T23:17:58Z</t>
         </is>
       </c>
     </row>
@@ -5337,7 +5337,7 @@
       </c>
       <c r="S60" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23T23:02:38Z</t>
+          <t>2026-09-24T23:17:58Z</t>
         </is>
       </c>
     </row>
@@ -5426,7 +5426,7 @@
       </c>
       <c r="S61" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23T23:02:38Z</t>
+          <t>2026-09-24T23:17:58Z</t>
         </is>
       </c>
     </row>
@@ -5515,7 +5515,7 @@
       </c>
       <c r="S62" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23T23:02:38Z</t>
+          <t>2026-09-24T23:17:58Z</t>
         </is>
       </c>
     </row>
@@ -5604,7 +5604,7 @@
       </c>
       <c r="S63" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23T23:02:38Z</t>
+          <t>2026-09-24T23:17:58Z</t>
         </is>
       </c>
     </row>
@@ -5693,7 +5693,7 @@
       </c>
       <c r="S64" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23T23:02:38Z</t>
+          <t>2026-09-24T23:17:58Z</t>
         </is>
       </c>
     </row>
@@ -5782,7 +5782,7 @@
       </c>
       <c r="S65" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23T23:02:38Z</t>
+          <t>2026-09-24T23:17:58Z</t>
         </is>
       </c>
     </row>
@@ -5871,7 +5871,7 @@
       </c>
       <c r="S66" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23T23:02:38Z</t>
+          <t>2026-09-24T23:17:58Z</t>
         </is>
       </c>
     </row>
@@ -5960,7 +5960,7 @@
       </c>
       <c r="S67" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23T23:02:38Z</t>
+          <t>2026-09-24T23:17:58Z</t>
         </is>
       </c>
     </row>
@@ -6045,7 +6045,7 @@
       </c>
       <c r="S68" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23T23:02:38Z</t>
+          <t>2026-09-24T23:17:58Z</t>
         </is>
       </c>
     </row>
@@ -6130,7 +6130,7 @@
       </c>
       <c r="S69" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23T23:02:38Z</t>
+          <t>2026-09-24T23:17:58Z</t>
         </is>
       </c>
     </row>
@@ -6215,7 +6215,7 @@
       </c>
       <c r="S70" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23T23:02:38Z</t>
+          <t>2026-09-24T23:17:58Z</t>
         </is>
       </c>
     </row>
@@ -6300,7 +6300,7 @@
       </c>
       <c r="S71" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23T23:02:38Z</t>
+          <t>2026-09-24T23:17:58Z</t>
         </is>
       </c>
     </row>
@@ -6385,7 +6385,7 @@
       </c>
       <c r="S72" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23T23:02:38Z</t>
+          <t>2026-09-24T23:17:58Z</t>
         </is>
       </c>
     </row>
@@ -6470,7 +6470,7 @@
       </c>
       <c r="S73" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23T23:02:38Z</t>
+          <t>2026-09-24T23:17:58Z</t>
         </is>
       </c>
     </row>
@@ -6555,7 +6555,7 @@
       </c>
       <c r="S74" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23T23:02:38Z</t>
+          <t>2026-09-24T23:17:58Z</t>
         </is>
       </c>
     </row>
@@ -6640,7 +6640,7 @@
       </c>
       <c r="S75" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23T23:02:38Z</t>
+          <t>2026-09-24T23:17:58Z</t>
         </is>
       </c>
     </row>
@@ -6725,7 +6725,7 @@
       </c>
       <c r="S76" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23T23:02:38Z</t>
+          <t>2026-09-24T23:17:58Z</t>
         </is>
       </c>
     </row>
@@ -6810,7 +6810,7 @@
       </c>
       <c r="S77" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23T23:02:38Z</t>
+          <t>2026-09-24T23:17:58Z</t>
         </is>
       </c>
     </row>
@@ -6895,7 +6895,7 @@
       </c>
       <c r="S78" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23T23:02:38Z</t>
+          <t>2026-09-24T23:17:58Z</t>
         </is>
       </c>
     </row>
@@ -6980,7 +6980,7 @@
       </c>
       <c r="S79" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23T23:02:38Z</t>
+          <t>2026-09-24T23:17:58Z</t>
         </is>
       </c>
     </row>
@@ -7065,7 +7065,7 @@
       </c>
       <c r="S80" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23T23:02:38Z</t>
+          <t>2026-09-24T23:17:58Z</t>
         </is>
       </c>
     </row>
@@ -7150,7 +7150,7 @@
       </c>
       <c r="S81" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23T23:02:38Z</t>
+          <t>2026-09-24T23:17:58Z</t>
         </is>
       </c>
     </row>
@@ -7235,7 +7235,7 @@
       </c>
       <c r="S82" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23T23:02:38Z</t>
+          <t>2026-09-24T23:17:58Z</t>
         </is>
       </c>
     </row>
@@ -7320,7 +7320,7 @@
       </c>
       <c r="S83" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23T23:02:38Z</t>
+          <t>2026-09-24T23:17:58Z</t>
         </is>
       </c>
     </row>
@@ -7405,7 +7405,7 @@
       </c>
       <c r="S84" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23T23:02:38Z</t>
+          <t>2026-09-24T23:17:58Z</t>
         </is>
       </c>
     </row>
@@ -7490,7 +7490,7 @@
       </c>
       <c r="S85" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23T23:02:38Z</t>
+          <t>2026-09-24T23:17:58Z</t>
         </is>
       </c>
     </row>
@@ -7575,7 +7575,7 @@
       </c>
       <c r="S86" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23T23:02:38Z</t>
+          <t>2026-09-24T23:17:58Z</t>
         </is>
       </c>
     </row>
@@ -7660,7 +7660,7 @@
       </c>
       <c r="S87" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23T23:02:38Z</t>
+          <t>2026-09-24T23:17:58Z</t>
         </is>
       </c>
     </row>
@@ -7745,7 +7745,7 @@
       </c>
       <c r="S88" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23T23:02:38Z</t>
+          <t>2026-09-24T23:17:58Z</t>
         </is>
       </c>
     </row>
@@ -7834,7 +7834,7 @@
       </c>
       <c r="S89" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23T23:02:38Z</t>
+          <t>2026-09-24T23:17:58Z</t>
         </is>
       </c>
     </row>
@@ -7923,7 +7923,7 @@
       </c>
       <c r="S90" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23T23:02:38Z</t>
+          <t>2026-09-24T23:17:58Z</t>
         </is>
       </c>
     </row>
@@ -8008,7 +8008,7 @@
       </c>
       <c r="S91" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23T23:02:38Z</t>
+          <t>2026-09-24T23:17:58Z</t>
         </is>
       </c>
     </row>
@@ -8097,7 +8097,7 @@
       </c>
       <c r="S92" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23T23:02:38Z</t>
+          <t>2026-09-24T23:17:58Z</t>
         </is>
       </c>
     </row>
@@ -8186,7 +8186,7 @@
       </c>
       <c r="S93" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23T23:02:38Z</t>
+          <t>2026-09-24T23:17:58Z</t>
         </is>
       </c>
     </row>
@@ -8271,7 +8271,7 @@
       </c>
       <c r="S94" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23T23:02:38Z</t>
+          <t>2026-09-24T23:17:58Z</t>
         </is>
       </c>
     </row>
@@ -8360,7 +8360,7 @@
       </c>
       <c r="S95" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23T23:02:38Z</t>
+          <t>2026-09-24T23:17:58Z</t>
         </is>
       </c>
     </row>
@@ -8449,7 +8449,7 @@
       </c>
       <c r="S96" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23T23:02:38Z</t>
+          <t>2026-09-24T23:17:58Z</t>
         </is>
       </c>
     </row>
@@ -8534,7 +8534,7 @@
       </c>
       <c r="S97" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23T23:02:38Z</t>
+          <t>2026-09-24T23:17:58Z</t>
         </is>
       </c>
     </row>
@@ -8623,7 +8623,7 @@
       </c>
       <c r="S98" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23T23:02:38Z</t>
+          <t>2026-09-24T23:17:58Z</t>
         </is>
       </c>
     </row>
@@ -8712,7 +8712,7 @@
       </c>
       <c r="S99" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23T23:02:38Z</t>
+          <t>2026-09-24T23:17:58Z</t>
         </is>
       </c>
     </row>
@@ -8797,7 +8797,7 @@
       </c>
       <c r="S100" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23T23:02:38Z</t>
+          <t>2026-09-24T23:17:58Z</t>
         </is>
       </c>
     </row>
@@ -8886,7 +8886,7 @@
       </c>
       <c r="S101" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23T23:02:38Z</t>
+          <t>2026-09-24T23:17:58Z</t>
         </is>
       </c>
     </row>
@@ -8975,7 +8975,7 @@
       </c>
       <c r="S102" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23T23:02:38Z</t>
+          <t>2026-09-24T23:17:58Z</t>
         </is>
       </c>
     </row>
@@ -9060,7 +9060,7 @@
       </c>
       <c r="S103" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23T23:02:38Z</t>
+          <t>2026-09-24T23:17:58Z</t>
         </is>
       </c>
     </row>
@@ -9149,7 +9149,7 @@
       </c>
       <c r="S104" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23T23:02:38Z</t>
+          <t>2026-09-24T23:17:58Z</t>
         </is>
       </c>
     </row>
@@ -9238,7 +9238,7 @@
       </c>
       <c r="S105" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23T23:02:38Z</t>
+          <t>2026-09-24T23:17:58Z</t>
         </is>
       </c>
     </row>
@@ -9323,7 +9323,7 @@
       </c>
       <c r="S106" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23T23:02:38Z</t>
+          <t>2026-09-24T23:17:58Z</t>
         </is>
       </c>
     </row>
@@ -9412,7 +9412,7 @@
       </c>
       <c r="S107" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23T23:02:38Z</t>
+          <t>2026-09-24T23:17:58Z</t>
         </is>
       </c>
     </row>
@@ -9501,7 +9501,7 @@
       </c>
       <c r="S108" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23T23:02:38Z</t>
+          <t>2026-09-24T23:17:58Z</t>
         </is>
       </c>
     </row>
@@ -9586,7 +9586,7 @@
       </c>
       <c r="S109" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23T23:02:38Z</t>
+          <t>2026-09-24T23:17:58Z</t>
         </is>
       </c>
     </row>
@@ -9675,7 +9675,7 @@
       </c>
       <c r="S110" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23T23:02:38Z</t>
+          <t>2026-09-24T23:17:58Z</t>
         </is>
       </c>
     </row>
@@ -9764,7 +9764,7 @@
       </c>
       <c r="S111" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23T23:02:38Z</t>
+          <t>2026-09-24T23:17:58Z</t>
         </is>
       </c>
     </row>
@@ -9849,7 +9849,7 @@
       </c>
       <c r="S112" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23T23:02:38Z</t>
+          <t>2026-09-24T23:17:58Z</t>
         </is>
       </c>
     </row>
@@ -9938,7 +9938,7 @@
       </c>
       <c r="S113" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23T23:02:38Z</t>
+          <t>2026-09-24T23:17:58Z</t>
         </is>
       </c>
     </row>
@@ -10027,7 +10027,7 @@
       </c>
       <c r="S114" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23T23:02:38Z</t>
+          <t>2026-09-24T23:17:58Z</t>
         </is>
       </c>
     </row>
@@ -10112,7 +10112,7 @@
       </c>
       <c r="S115" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23T23:02:38Z</t>
+          <t>2026-09-24T23:17:58Z</t>
         </is>
       </c>
     </row>
@@ -10201,7 +10201,7 @@
       </c>
       <c r="S116" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23T23:02:38Z</t>
+          <t>2026-09-24T23:17:58Z</t>
         </is>
       </c>
     </row>
@@ -10290,7 +10290,7 @@
       </c>
       <c r="S117" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23T23:02:38Z</t>
+          <t>2026-09-24T23:17:58Z</t>
         </is>
       </c>
     </row>
@@ -10379,7 +10379,7 @@
       </c>
       <c r="S118" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23T23:02:38Z</t>
+          <t>2026-09-24T23:17:58Z</t>
         </is>
       </c>
     </row>
@@ -10468,7 +10468,7 @@
       </c>
       <c r="S119" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23T23:02:38Z</t>
+          <t>2026-09-24T23:17:58Z</t>
         </is>
       </c>
     </row>
@@ -10557,7 +10557,7 @@
       </c>
       <c r="S120" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23T23:02:38Z</t>
+          <t>2026-09-24T23:17:58Z</t>
         </is>
       </c>
     </row>
@@ -10646,7 +10646,7 @@
       </c>
       <c r="S121" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23T23:02:38Z</t>
+          <t>2026-09-24T23:17:58Z</t>
         </is>
       </c>
     </row>
@@ -10735,7 +10735,7 @@
       </c>
       <c r="S122" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23T23:02:38Z</t>
+          <t>2026-09-24T23:17:58Z</t>
         </is>
       </c>
     </row>
@@ -10824,7 +10824,7 @@
       </c>
       <c r="S123" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23T23:02:38Z</t>
+          <t>2026-09-24T23:17:58Z</t>
         </is>
       </c>
     </row>
@@ -10913,7 +10913,7 @@
       </c>
       <c r="S124" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23T23:02:38Z</t>
+          <t>2026-09-24T23:17:58Z</t>
         </is>
       </c>
     </row>
@@ -11002,7 +11002,7 @@
       </c>
       <c r="S125" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23T23:02:38Z</t>
+          <t>2026-09-24T23:17:58Z</t>
         </is>
       </c>
     </row>
@@ -11091,7 +11091,7 @@
       </c>
       <c r="S126" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23T23:02:38Z</t>
+          <t>2026-09-24T23:17:58Z</t>
         </is>
       </c>
     </row>
@@ -11180,7 +11180,7 @@
       </c>
       <c r="S127" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23T23:02:38Z</t>
+          <t>2026-09-24T23:17:58Z</t>
         </is>
       </c>
     </row>
@@ -11269,7 +11269,7 @@
       </c>
       <c r="S128" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23T23:02:38Z</t>
+          <t>2026-09-24T23:17:58Z</t>
         </is>
       </c>
     </row>
@@ -11354,7 +11354,7 @@
       </c>
       <c r="S129" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23T23:02:38Z</t>
+          <t>2026-09-24T23:17:58Z</t>
         </is>
       </c>
     </row>
@@ -11439,7 +11439,7 @@
       </c>
       <c r="S130" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23T23:02:38Z</t>
+          <t>2026-09-24T23:17:58Z</t>
         </is>
       </c>
     </row>
@@ -11524,7 +11524,7 @@
       </c>
       <c r="S131" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23T23:02:38Z</t>
+          <t>2026-09-24T23:17:58Z</t>
         </is>
       </c>
     </row>
@@ -11609,7 +11609,7 @@
       </c>
       <c r="S132" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23T23:02:38Z</t>
+          <t>2026-09-24T23:17:58Z</t>
         </is>
       </c>
     </row>
@@ -11694,7 +11694,7 @@
       </c>
       <c r="S133" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23T23:02:38Z</t>
+          <t>2026-09-24T23:17:58Z</t>
         </is>
       </c>
     </row>
@@ -11779,7 +11779,7 @@
       </c>
       <c r="S134" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23T23:02:38Z</t>
+          <t>2026-09-24T23:17:58Z</t>
         </is>
       </c>
     </row>
@@ -11864,7 +11864,7 @@
       </c>
       <c r="S135" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23T23:02:38Z</t>
+          <t>2026-09-24T23:17:58Z</t>
         </is>
       </c>
     </row>
@@ -11949,7 +11949,7 @@
       </c>
       <c r="S136" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23T23:02:38Z</t>
+          <t>2026-09-24T23:17:58Z</t>
         </is>
       </c>
     </row>
@@ -12034,7 +12034,7 @@
       </c>
       <c r="S137" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23T23:02:38Z</t>
+          <t>2026-09-24T23:17:58Z</t>
         </is>
       </c>
     </row>
@@ -12119,7 +12119,7 @@
       </c>
       <c r="S138" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23T23:02:38Z</t>
+          <t>2026-09-24T23:17:58Z</t>
         </is>
       </c>
     </row>
@@ -12204,7 +12204,7 @@
       </c>
       <c r="S139" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23T23:02:38Z</t>
+          <t>2026-09-24T23:17:58Z</t>
         </is>
       </c>
     </row>
@@ -12289,7 +12289,7 @@
       </c>
       <c r="S140" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23T23:02:38Z</t>
+          <t>2026-09-24T23:17:58Z</t>
         </is>
       </c>
     </row>
@@ -12374,7 +12374,7 @@
       </c>
       <c r="S141" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23T23:02:38Z</t>
+          <t>2026-09-24T23:17:58Z</t>
         </is>
       </c>
     </row>
@@ -12459,7 +12459,7 @@
       </c>
       <c r="S142" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23T23:02:38Z</t>
+          <t>2026-09-24T23:17:58Z</t>
         </is>
       </c>
     </row>
@@ -12544,7 +12544,7 @@
       </c>
       <c r="S143" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23T23:02:38Z</t>
+          <t>2026-09-24T23:17:58Z</t>
         </is>
       </c>
     </row>
@@ -12629,7 +12629,7 @@
       </c>
       <c r="S144" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23T23:02:38Z</t>
+          <t>2026-09-24T23:17:58Z</t>
         </is>
       </c>
     </row>
@@ -12714,7 +12714,7 @@
       </c>
       <c r="S145" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23T23:02:38Z</t>
+          <t>2026-09-24T23:17:58Z</t>
         </is>
       </c>
     </row>
@@ -12799,7 +12799,7 @@
       </c>
       <c r="S146" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23T23:02:38Z</t>
+          <t>2026-09-24T23:17:58Z</t>
         </is>
       </c>
     </row>
@@ -12884,7 +12884,7 @@
       </c>
       <c r="S147" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23T23:02:38Z</t>
+          <t>2026-09-24T23:17:58Z</t>
         </is>
       </c>
     </row>
@@ -12969,7 +12969,7 @@
       </c>
       <c r="S148" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23T23:02:38Z</t>
+          <t>2026-09-24T23:17:58Z</t>
         </is>
       </c>
     </row>
@@ -13054,7 +13054,7 @@
       </c>
       <c r="S149" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23T23:02:38Z</t>
+          <t>2026-09-24T23:17:58Z</t>
         </is>
       </c>
     </row>
@@ -13143,7 +13143,7 @@
       </c>
       <c r="S150" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23T23:02:38Z</t>
+          <t>2026-09-24T23:17:58Z</t>
         </is>
       </c>
     </row>
@@ -13232,7 +13232,7 @@
       </c>
       <c r="S151" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23T23:02:38Z</t>
+          <t>2026-09-24T23:17:58Z</t>
         </is>
       </c>
     </row>
@@ -13317,7 +13317,7 @@
       </c>
       <c r="S152" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23T23:02:38Z</t>
+          <t>2026-09-24T23:17:58Z</t>
         </is>
       </c>
     </row>
@@ -13406,7 +13406,7 @@
       </c>
       <c r="S153" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23T23:02:38Z</t>
+          <t>2026-09-24T23:17:58Z</t>
         </is>
       </c>
     </row>
@@ -13495,7 +13495,7 @@
       </c>
       <c r="S154" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23T23:02:38Z</t>
+          <t>2026-09-24T23:17:58Z</t>
         </is>
       </c>
     </row>
@@ -13580,7 +13580,7 @@
       </c>
       <c r="S155" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23T23:02:38Z</t>
+          <t>2026-09-24T23:17:58Z</t>
         </is>
       </c>
     </row>
@@ -13669,7 +13669,7 @@
       </c>
       <c r="S156" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23T23:02:38Z</t>
+          <t>2026-09-24T23:17:58Z</t>
         </is>
       </c>
     </row>
@@ -13758,7 +13758,7 @@
       </c>
       <c r="S157" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23T23:02:38Z</t>
+          <t>2026-09-24T23:17:58Z</t>
         </is>
       </c>
     </row>
@@ -13843,7 +13843,7 @@
       </c>
       <c r="S158" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23T23:02:38Z</t>
+          <t>2026-09-24T23:17:58Z</t>
         </is>
       </c>
     </row>
@@ -13932,7 +13932,7 @@
       </c>
       <c r="S159" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23T23:02:38Z</t>
+          <t>2026-09-24T23:17:58Z</t>
         </is>
       </c>
     </row>
@@ -14021,7 +14021,7 @@
       </c>
       <c r="S160" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23T23:02:38Z</t>
+          <t>2026-09-24T23:17:58Z</t>
         </is>
       </c>
     </row>
@@ -14106,7 +14106,7 @@
       </c>
       <c r="S161" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23T23:02:38Z</t>
+          <t>2026-09-24T23:17:58Z</t>
         </is>
       </c>
     </row>
@@ -14195,7 +14195,7 @@
       </c>
       <c r="S162" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23T23:02:38Z</t>
+          <t>2026-09-24T23:17:58Z</t>
         </is>
       </c>
     </row>
@@ -14284,7 +14284,7 @@
       </c>
       <c r="S163" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23T23:02:38Z</t>
+          <t>2026-09-24T23:17:58Z</t>
         </is>
       </c>
     </row>
@@ -14369,7 +14369,7 @@
       </c>
       <c r="S164" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23T23:02:38Z</t>
+          <t>2026-09-24T23:17:58Z</t>
         </is>
       </c>
     </row>
@@ -14458,7 +14458,7 @@
       </c>
       <c r="S165" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23T23:02:38Z</t>
+          <t>2026-09-24T23:17:58Z</t>
         </is>
       </c>
     </row>
@@ -14547,7 +14547,7 @@
       </c>
       <c r="S166" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23T23:02:38Z</t>
+          <t>2026-09-24T23:17:58Z</t>
         </is>
       </c>
     </row>
@@ -14632,7 +14632,7 @@
       </c>
       <c r="S167" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23T23:02:38Z</t>
+          <t>2026-09-24T23:17:58Z</t>
         </is>
       </c>
     </row>
@@ -14721,7 +14721,7 @@
       </c>
       <c r="S168" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23T23:02:38Z</t>
+          <t>2026-09-24T23:17:58Z</t>
         </is>
       </c>
     </row>
@@ -14810,7 +14810,7 @@
       </c>
       <c r="S169" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23T23:02:38Z</t>
+          <t>2026-09-24T23:17:58Z</t>
         </is>
       </c>
     </row>
@@ -14895,7 +14895,7 @@
       </c>
       <c r="S170" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23T23:02:38Z</t>
+          <t>2026-09-24T23:17:58Z</t>
         </is>
       </c>
     </row>
@@ -14984,7 +14984,7 @@
       </c>
       <c r="S171" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23T23:02:38Z</t>
+          <t>2026-09-24T23:17:58Z</t>
         </is>
       </c>
     </row>
@@ -15073,7 +15073,7 @@
       </c>
       <c r="S172" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23T23:02:38Z</t>
+          <t>2026-09-24T23:17:58Z</t>
         </is>
       </c>
     </row>
@@ -15158,7 +15158,7 @@
       </c>
       <c r="S173" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23T23:02:38Z</t>
+          <t>2026-09-24T23:17:58Z</t>
         </is>
       </c>
     </row>
@@ -15247,7 +15247,7 @@
       </c>
       <c r="S174" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23T23:02:38Z</t>
+          <t>2026-09-24T23:17:58Z</t>
         </is>
       </c>
     </row>
@@ -15336,7 +15336,7 @@
       </c>
       <c r="S175" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23T23:02:38Z</t>
+          <t>2026-09-24T23:17:58Z</t>
         </is>
       </c>
     </row>
@@ -15421,7 +15421,7 @@
       </c>
       <c r="S176" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23T23:02:38Z</t>
+          <t>2026-09-24T23:17:58Z</t>
         </is>
       </c>
     </row>
@@ -15510,7 +15510,7 @@
       </c>
       <c r="S177" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23T23:02:38Z</t>
+          <t>2026-09-24T23:17:58Z</t>
         </is>
       </c>
     </row>
@@ -15599,7 +15599,7 @@
       </c>
       <c r="S178" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23T23:02:38Z</t>
+          <t>2026-09-24T23:17:58Z</t>
         </is>
       </c>
     </row>
@@ -15688,7 +15688,7 @@
       </c>
       <c r="S179" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23T23:02:38Z</t>
+          <t>2026-09-24T23:17:58Z</t>
         </is>
       </c>
     </row>
@@ -15777,7 +15777,7 @@
       </c>
       <c r="S180" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23T23:02:38Z</t>
+          <t>2026-09-24T23:17:58Z</t>
         </is>
       </c>
     </row>
@@ -15866,7 +15866,7 @@
       </c>
       <c r="S181" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23T23:02:38Z</t>
+          <t>2026-09-24T23:17:58Z</t>
         </is>
       </c>
     </row>
@@ -15955,7 +15955,7 @@
       </c>
       <c r="S182" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23T23:02:38Z</t>
+          <t>2026-09-24T23:17:58Z</t>
         </is>
       </c>
     </row>
@@ -16044,7 +16044,7 @@
       </c>
       <c r="S183" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23T23:02:38Z</t>
+          <t>2026-09-24T23:17:58Z</t>
         </is>
       </c>
     </row>
@@ -16133,7 +16133,7 @@
       </c>
       <c r="S184" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23T23:02:38Z</t>
+          <t>2026-09-24T23:17:58Z</t>
         </is>
       </c>
     </row>
@@ -16222,7 +16222,7 @@
       </c>
       <c r="S185" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23T23:02:38Z</t>
+          <t>2026-09-24T23:17:58Z</t>
         </is>
       </c>
     </row>
@@ -16311,7 +16311,7 @@
       </c>
       <c r="S186" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23T23:02:38Z</t>
+          <t>2026-09-24T23:17:58Z</t>
         </is>
       </c>
     </row>
@@ -16400,7 +16400,7 @@
       </c>
       <c r="S187" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23T23:02:38Z</t>
+          <t>2026-09-24T23:17:58Z</t>
         </is>
       </c>
     </row>
@@ -16489,7 +16489,7 @@
       </c>
       <c r="S188" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23T23:02:38Z</t>
+          <t>2026-09-24T23:17:58Z</t>
         </is>
       </c>
     </row>
@@ -16578,7 +16578,7 @@
       </c>
       <c r="S189" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23T23:02:38Z</t>
+          <t>2026-09-24T23:17:58Z</t>
         </is>
       </c>
     </row>
@@ -16663,7 +16663,7 @@
       </c>
       <c r="S190" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23T23:02:38Z</t>
+          <t>2026-09-24T23:17:58Z</t>
         </is>
       </c>
     </row>
@@ -16748,7 +16748,7 @@
       </c>
       <c r="S191" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23T23:02:38Z</t>
+          <t>2026-09-24T23:17:58Z</t>
         </is>
       </c>
     </row>
@@ -16833,7 +16833,7 @@
       </c>
       <c r="S192" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23T23:02:38Z</t>
+          <t>2026-09-24T23:17:58Z</t>
         </is>
       </c>
     </row>
@@ -16918,7 +16918,7 @@
       </c>
       <c r="S193" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23T23:02:38Z</t>
+          <t>2026-09-24T23:17:58Z</t>
         </is>
       </c>
     </row>
@@ -17003,7 +17003,7 @@
       </c>
       <c r="S194" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23T23:02:38Z</t>
+          <t>2026-09-24T23:17:58Z</t>
         </is>
       </c>
     </row>
@@ -17088,7 +17088,7 @@
       </c>
       <c r="S195" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23T23:02:38Z</t>
+          <t>2026-09-24T23:17:58Z</t>
         </is>
       </c>
     </row>
@@ -17173,7 +17173,7 @@
       </c>
       <c r="S196" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23T23:02:38Z</t>
+          <t>2026-09-24T23:17:58Z</t>
         </is>
       </c>
     </row>
@@ -17258,7 +17258,7 @@
       </c>
       <c r="S197" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23T23:02:38Z</t>
+          <t>2026-09-24T23:17:58Z</t>
         </is>
       </c>
     </row>
@@ -17343,7 +17343,7 @@
       </c>
       <c r="S198" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23T23:02:38Z</t>
+          <t>2026-09-24T23:17:58Z</t>
         </is>
       </c>
     </row>
@@ -17428,7 +17428,7 @@
       </c>
       <c r="S199" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23T23:02:38Z</t>
+          <t>2026-09-24T23:17:58Z</t>
         </is>
       </c>
     </row>
@@ -17513,7 +17513,7 @@
       </c>
       <c r="S200" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23T23:02:38Z</t>
+          <t>2026-09-24T23:17:58Z</t>
         </is>
       </c>
     </row>
@@ -17598,7 +17598,7 @@
       </c>
       <c r="S201" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23T23:02:38Z</t>
+          <t>2026-09-24T23:17:58Z</t>
         </is>
       </c>
     </row>
@@ -17683,7 +17683,7 @@
       </c>
       <c r="S202" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23T23:02:38Z</t>
+          <t>2026-09-24T23:17:58Z</t>
         </is>
       </c>
     </row>
@@ -17768,7 +17768,7 @@
       </c>
       <c r="S203" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23T23:02:38Z</t>
+          <t>2026-09-24T23:17:58Z</t>
         </is>
       </c>
     </row>
@@ -17853,7 +17853,7 @@
       </c>
       <c r="S204" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23T23:02:38Z</t>
+          <t>2026-09-24T23:17:58Z</t>
         </is>
       </c>
     </row>
@@ -17938,7 +17938,7 @@
       </c>
       <c r="S205" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23T23:02:38Z</t>
+          <t>2026-09-24T23:17:58Z</t>
         </is>
       </c>
     </row>
@@ -18023,7 +18023,7 @@
       </c>
       <c r="S206" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23T23:02:38Z</t>
+          <t>2026-09-24T23:17:58Z</t>
         </is>
       </c>
     </row>
@@ -18108,7 +18108,7 @@
       </c>
       <c r="S207" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23T23:02:38Z</t>
+          <t>2026-09-24T23:17:58Z</t>
         </is>
       </c>
     </row>
@@ -18193,7 +18193,7 @@
       </c>
       <c r="S208" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23T23:02:38Z</t>
+          <t>2026-09-24T23:17:58Z</t>
         </is>
       </c>
     </row>
@@ -18278,7 +18278,7 @@
       </c>
       <c r="S209" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23T23:02:38Z</t>
+          <t>2026-09-24T23:17:58Z</t>
         </is>
       </c>
     </row>
@@ -18363,7 +18363,7 @@
       </c>
       <c r="S210" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23T23:02:38Z</t>
+          <t>2026-09-24T23:17:58Z</t>
         </is>
       </c>
     </row>
@@ -18452,7 +18452,7 @@
       </c>
       <c r="S211" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23T23:02:38Z</t>
+          <t>2026-09-24T23:17:58Z</t>
         </is>
       </c>
     </row>
@@ -18541,7 +18541,7 @@
       </c>
       <c r="S212" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23T23:02:38Z</t>
+          <t>2026-09-24T23:17:58Z</t>
         </is>
       </c>
     </row>
@@ -18626,7 +18626,7 @@
       </c>
       <c r="S213" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23T23:02:38Z</t>
+          <t>2026-09-24T23:17:58Z</t>
         </is>
       </c>
     </row>
@@ -18715,7 +18715,7 @@
       </c>
       <c r="S214" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23T23:02:38Z</t>
+          <t>2026-09-24T23:17:58Z</t>
         </is>
       </c>
     </row>
@@ -18804,7 +18804,7 @@
       </c>
       <c r="S215" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23T23:02:38Z</t>
+          <t>2026-09-24T23:17:58Z</t>
         </is>
       </c>
     </row>
@@ -18889,7 +18889,7 @@
       </c>
       <c r="S216" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23T23:02:38Z</t>
+          <t>2026-09-24T23:17:58Z</t>
         </is>
       </c>
     </row>
@@ -18978,7 +18978,7 @@
       </c>
       <c r="S217" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23T23:02:38Z</t>
+          <t>2026-09-24T23:17:58Z</t>
         </is>
       </c>
     </row>
@@ -19067,7 +19067,7 @@
       </c>
       <c r="S218" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23T23:02:38Z</t>
+          <t>2026-09-24T23:17:58Z</t>
         </is>
       </c>
     </row>
@@ -19152,7 +19152,7 @@
       </c>
       <c r="S219" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23T23:02:38Z</t>
+          <t>2026-09-24T23:17:58Z</t>
         </is>
       </c>
     </row>
@@ -19241,7 +19241,7 @@
       </c>
       <c r="S220" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23T23:02:38Z</t>
+          <t>2026-09-24T23:17:58Z</t>
         </is>
       </c>
     </row>
@@ -19330,7 +19330,7 @@
       </c>
       <c r="S221" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23T23:02:38Z</t>
+          <t>2026-09-24T23:17:58Z</t>
         </is>
       </c>
     </row>
@@ -19415,7 +19415,7 @@
       </c>
       <c r="S222" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23T23:02:38Z</t>
+          <t>2026-09-24T23:17:58Z</t>
         </is>
       </c>
     </row>
@@ -19504,7 +19504,7 @@
       </c>
       <c r="S223" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23T23:02:38Z</t>
+          <t>2026-09-24T23:17:58Z</t>
         </is>
       </c>
     </row>
@@ -19593,7 +19593,7 @@
       </c>
       <c r="S224" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23T23:02:38Z</t>
+          <t>2026-09-24T23:17:58Z</t>
         </is>
       </c>
     </row>
@@ -19678,7 +19678,7 @@
       </c>
       <c r="S225" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23T23:02:38Z</t>
+          <t>2026-09-24T23:17:58Z</t>
         </is>
       </c>
     </row>
@@ -19767,7 +19767,7 @@
       </c>
       <c r="S226" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23T23:02:38Z</t>
+          <t>2026-09-24T23:17:58Z</t>
         </is>
       </c>
     </row>
@@ -19856,7 +19856,7 @@
       </c>
       <c r="S227" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23T23:02:38Z</t>
+          <t>2026-09-24T23:17:58Z</t>
         </is>
       </c>
     </row>
@@ -19941,7 +19941,7 @@
       </c>
       <c r="S228" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23T23:02:38Z</t>
+          <t>2026-09-24T23:17:58Z</t>
         </is>
       </c>
     </row>
@@ -20030,7 +20030,7 @@
       </c>
       <c r="S229" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23T23:02:38Z</t>
+          <t>2026-09-24T23:17:58Z</t>
         </is>
       </c>
     </row>
@@ -20119,7 +20119,7 @@
       </c>
       <c r="S230" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23T23:02:38Z</t>
+          <t>2026-09-24T23:17:58Z</t>
         </is>
       </c>
     </row>
@@ -20204,7 +20204,7 @@
       </c>
       <c r="S231" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23T23:02:38Z</t>
+          <t>2026-09-24T23:17:58Z</t>
         </is>
       </c>
     </row>
@@ -20293,7 +20293,7 @@
       </c>
       <c r="S232" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23T23:02:38Z</t>
+          <t>2026-09-24T23:17:58Z</t>
         </is>
       </c>
     </row>
@@ -20382,7 +20382,7 @@
       </c>
       <c r="S233" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23T23:02:38Z</t>
+          <t>2026-09-24T23:17:58Z</t>
         </is>
       </c>
     </row>
@@ -20467,7 +20467,7 @@
       </c>
       <c r="S234" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23T23:02:38Z</t>
+          <t>2026-09-24T23:17:58Z</t>
         </is>
       </c>
     </row>
@@ -20556,7 +20556,7 @@
       </c>
       <c r="S235" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23T23:02:38Z</t>
+          <t>2026-09-24T23:17:58Z</t>
         </is>
       </c>
     </row>
@@ -20645,7 +20645,7 @@
       </c>
       <c r="S236" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23T23:02:38Z</t>
+          <t>2026-09-24T23:17:58Z</t>
         </is>
       </c>
     </row>
@@ -20730,7 +20730,7 @@
       </c>
       <c r="S237" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23T23:02:38Z</t>
+          <t>2026-09-24T23:17:58Z</t>
         </is>
       </c>
     </row>
@@ -20819,7 +20819,7 @@
       </c>
       <c r="S238" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23T23:02:38Z</t>
+          <t>2026-09-24T23:17:58Z</t>
         </is>
       </c>
     </row>
@@ -20908,7 +20908,7 @@
       </c>
       <c r="S239" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23T23:02:38Z</t>
+          <t>2026-09-24T23:17:58Z</t>
         </is>
       </c>
     </row>
@@ -20997,7 +20997,7 @@
       </c>
       <c r="S240" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23T23:02:38Z</t>
+          <t>2026-09-24T23:17:58Z</t>
         </is>
       </c>
     </row>
@@ -21086,7 +21086,7 @@
       </c>
       <c r="S241" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23T23:02:38Z</t>
+          <t>2026-09-24T23:17:58Z</t>
         </is>
       </c>
     </row>
@@ -21175,7 +21175,7 @@
       </c>
       <c r="S242" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23T23:02:38Z</t>
+          <t>2026-09-24T23:17:58Z</t>
         </is>
       </c>
     </row>
@@ -21264,7 +21264,7 @@
       </c>
       <c r="S243" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23T23:02:38Z</t>
+          <t>2026-09-24T23:17:58Z</t>
         </is>
       </c>
     </row>
@@ -21353,7 +21353,7 @@
       </c>
       <c r="S244" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23T23:02:38Z</t>
+          <t>2026-09-24T23:17:58Z</t>
         </is>
       </c>
     </row>
@@ -21442,7 +21442,7 @@
       </c>
       <c r="S245" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23T23:02:38Z</t>
+          <t>2026-09-24T23:17:58Z</t>
         </is>
       </c>
     </row>
@@ -21531,7 +21531,7 @@
       </c>
       <c r="S246" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23T23:02:38Z</t>
+          <t>2026-09-24T23:17:58Z</t>
         </is>
       </c>
     </row>
@@ -21620,7 +21620,7 @@
       </c>
       <c r="S247" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23T23:02:38Z</t>
+          <t>2026-09-24T23:17:58Z</t>
         </is>
       </c>
     </row>
@@ -21709,7 +21709,7 @@
       </c>
       <c r="S248" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23T23:02:38Z</t>
+          <t>2026-09-24T23:17:58Z</t>
         </is>
       </c>
     </row>
@@ -21798,7 +21798,7 @@
       </c>
       <c r="S249" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23T23:02:38Z</t>
+          <t>2026-09-24T23:17:58Z</t>
         </is>
       </c>
     </row>
@@ -21887,7 +21887,7 @@
       </c>
       <c r="S250" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23T23:02:38Z</t>
+          <t>2026-09-24T23:17:58Z</t>
         </is>
       </c>
     </row>
@@ -22019,7 +22019,7 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23T23:02:38Z</t>
+          <t>2026-09-24T23:17:58Z</t>
         </is>
       </c>
     </row>
@@ -22099,7 +22099,7 @@
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>{"dataset_id": "bcv_pib_sector_institucional_anual", "title": "Producto interno bruto por sector institucional anual", "table": "Variaciones porcentuales", "source_file": "5_2_1_si_anual.xlsx", "base": "2007", "price_type": "Precios constantes", "measure": "Variación porcentual interanual", "frequency": "Anual", "period": "2025", "year": 2025, "quarter": null, "classification": "Sector institucional", "component": "Impuestos netos sobre los productos", "value": 10.600260421283764, "unit": "Porcentaje", "status": "Preliminar", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/cuentas_macroeconomicas/5_2_1_si_anual.xlsx", "fetched_at": "2026-09-23T23:02:38Z"}</t>
+          <t>{"dataset_id": "bcv_pib_sector_institucional_anual", "title": "Producto interno bruto por sector institucional anual", "table": "Variaciones porcentuales", "source_file": "5_2_1_si_anual.xlsx", "base": "2007", "price_type": "Precios constantes", "measure": "Variación porcentual interanual", "frequency": "Anual", "period": "2025", "year": 2025, "quarter": null, "classification": "Sector institucional", "component": "Impuestos netos sobre los productos", "value": 10.600260421283764, "unit": "Porcentaje", "status": "Preliminar", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/cuentas_macroeconomicas/5_2_1_si_anual.xlsx", "fetched_at": "2026-09-24T23:17:58Z"}</t>
         </is>
       </c>
     </row>

--- a/assets/data/bcv/excel/ove_bcv_pib_sector_institucional_anual.xlsx
+++ b/assets/data/bcv/excel/ove_bcv_pib_sector_institucional_anual.xlsx
@@ -736,7 +736,7 @@
       </c>
       <c r="S7" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T23:17:58Z</t>
+          <t>2026-09-25T23:23:39Z</t>
         </is>
       </c>
     </row>
@@ -821,7 +821,7 @@
       </c>
       <c r="S8" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T23:17:58Z</t>
+          <t>2026-09-25T23:23:39Z</t>
         </is>
       </c>
     </row>
@@ -906,7 +906,7 @@
       </c>
       <c r="S9" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T23:17:58Z</t>
+          <t>2026-09-25T23:23:39Z</t>
         </is>
       </c>
     </row>
@@ -991,7 +991,7 @@
       </c>
       <c r="S10" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T23:17:58Z</t>
+          <t>2026-09-25T23:23:39Z</t>
         </is>
       </c>
     </row>
@@ -1076,7 +1076,7 @@
       </c>
       <c r="S11" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T23:17:58Z</t>
+          <t>2026-09-25T23:23:39Z</t>
         </is>
       </c>
     </row>
@@ -1161,7 +1161,7 @@
       </c>
       <c r="S12" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T23:17:58Z</t>
+          <t>2026-09-25T23:23:39Z</t>
         </is>
       </c>
     </row>
@@ -1246,7 +1246,7 @@
       </c>
       <c r="S13" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T23:17:58Z</t>
+          <t>2026-09-25T23:23:39Z</t>
         </is>
       </c>
     </row>
@@ -1331,7 +1331,7 @@
       </c>
       <c r="S14" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T23:17:58Z</t>
+          <t>2026-09-25T23:23:39Z</t>
         </is>
       </c>
     </row>
@@ -1416,7 +1416,7 @@
       </c>
       <c r="S15" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T23:17:58Z</t>
+          <t>2026-09-25T23:23:39Z</t>
         </is>
       </c>
     </row>
@@ -1501,7 +1501,7 @@
       </c>
       <c r="S16" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T23:17:58Z</t>
+          <t>2026-09-25T23:23:39Z</t>
         </is>
       </c>
     </row>
@@ -1586,7 +1586,7 @@
       </c>
       <c r="S17" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T23:17:58Z</t>
+          <t>2026-09-25T23:23:39Z</t>
         </is>
       </c>
     </row>
@@ -1671,7 +1671,7 @@
       </c>
       <c r="S18" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T23:17:58Z</t>
+          <t>2026-09-25T23:23:39Z</t>
         </is>
       </c>
     </row>
@@ -1756,7 +1756,7 @@
       </c>
       <c r="S19" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T23:17:58Z</t>
+          <t>2026-09-25T23:23:39Z</t>
         </is>
       </c>
     </row>
@@ -1841,7 +1841,7 @@
       </c>
       <c r="S20" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T23:17:58Z</t>
+          <t>2026-09-25T23:23:39Z</t>
         </is>
       </c>
     </row>
@@ -1926,7 +1926,7 @@
       </c>
       <c r="S21" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T23:17:58Z</t>
+          <t>2026-09-25T23:23:39Z</t>
         </is>
       </c>
     </row>
@@ -2011,7 +2011,7 @@
       </c>
       <c r="S22" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T23:17:58Z</t>
+          <t>2026-09-25T23:23:39Z</t>
         </is>
       </c>
     </row>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="S23" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T23:17:58Z</t>
+          <t>2026-09-25T23:23:39Z</t>
         </is>
       </c>
     </row>
@@ -2181,7 +2181,7 @@
       </c>
       <c r="S24" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T23:17:58Z</t>
+          <t>2026-09-25T23:23:39Z</t>
         </is>
       </c>
     </row>
@@ -2266,7 +2266,7 @@
       </c>
       <c r="S25" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T23:17:58Z</t>
+          <t>2026-09-25T23:23:39Z</t>
         </is>
       </c>
     </row>
@@ -2351,7 +2351,7 @@
       </c>
       <c r="S26" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T23:17:58Z</t>
+          <t>2026-09-25T23:23:39Z</t>
         </is>
       </c>
     </row>
@@ -2436,7 +2436,7 @@
       </c>
       <c r="S27" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T23:17:58Z</t>
+          <t>2026-09-25T23:23:39Z</t>
         </is>
       </c>
     </row>
@@ -2525,7 +2525,7 @@
       </c>
       <c r="S28" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T23:17:58Z</t>
+          <t>2026-09-25T23:23:39Z</t>
         </is>
       </c>
     </row>
@@ -2614,7 +2614,7 @@
       </c>
       <c r="S29" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T23:17:58Z</t>
+          <t>2026-09-25T23:23:39Z</t>
         </is>
       </c>
     </row>
@@ -2699,7 +2699,7 @@
       </c>
       <c r="S30" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T23:17:58Z</t>
+          <t>2026-09-25T23:23:39Z</t>
         </is>
       </c>
     </row>
@@ -2788,7 +2788,7 @@
       </c>
       <c r="S31" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T23:17:58Z</t>
+          <t>2026-09-25T23:23:39Z</t>
         </is>
       </c>
     </row>
@@ -2877,7 +2877,7 @@
       </c>
       <c r="S32" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T23:17:58Z</t>
+          <t>2026-09-25T23:23:39Z</t>
         </is>
       </c>
     </row>
@@ -2962,7 +2962,7 @@
       </c>
       <c r="S33" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T23:17:58Z</t>
+          <t>2026-09-25T23:23:39Z</t>
         </is>
       </c>
     </row>
@@ -3051,7 +3051,7 @@
       </c>
       <c r="S34" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T23:17:58Z</t>
+          <t>2026-09-25T23:23:39Z</t>
         </is>
       </c>
     </row>
@@ -3140,7 +3140,7 @@
       </c>
       <c r="S35" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T23:17:58Z</t>
+          <t>2026-09-25T23:23:39Z</t>
         </is>
       </c>
     </row>
@@ -3225,7 +3225,7 @@
       </c>
       <c r="S36" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T23:17:58Z</t>
+          <t>2026-09-25T23:23:39Z</t>
         </is>
       </c>
     </row>
@@ -3314,7 +3314,7 @@
       </c>
       <c r="S37" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T23:17:58Z</t>
+          <t>2026-09-25T23:23:39Z</t>
         </is>
       </c>
     </row>
@@ -3403,7 +3403,7 @@
       </c>
       <c r="S38" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T23:17:58Z</t>
+          <t>2026-09-25T23:23:39Z</t>
         </is>
       </c>
     </row>
@@ -3488,7 +3488,7 @@
       </c>
       <c r="S39" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T23:17:58Z</t>
+          <t>2026-09-25T23:23:39Z</t>
         </is>
       </c>
     </row>
@@ -3577,7 +3577,7 @@
       </c>
       <c r="S40" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T23:17:58Z</t>
+          <t>2026-09-25T23:23:39Z</t>
         </is>
       </c>
     </row>
@@ -3666,7 +3666,7 @@
       </c>
       <c r="S41" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T23:17:58Z</t>
+          <t>2026-09-25T23:23:39Z</t>
         </is>
       </c>
     </row>
@@ -3751,7 +3751,7 @@
       </c>
       <c r="S42" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T23:17:58Z</t>
+          <t>2026-09-25T23:23:39Z</t>
         </is>
       </c>
     </row>
@@ -3840,7 +3840,7 @@
       </c>
       <c r="S43" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T23:17:58Z</t>
+          <t>2026-09-25T23:23:39Z</t>
         </is>
       </c>
     </row>
@@ -3929,7 +3929,7 @@
       </c>
       <c r="S44" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T23:17:58Z</t>
+          <t>2026-09-25T23:23:39Z</t>
         </is>
       </c>
     </row>
@@ -4014,7 +4014,7 @@
       </c>
       <c r="S45" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T23:17:58Z</t>
+          <t>2026-09-25T23:23:39Z</t>
         </is>
       </c>
     </row>
@@ -4103,7 +4103,7 @@
       </c>
       <c r="S46" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T23:17:58Z</t>
+          <t>2026-09-25T23:23:39Z</t>
         </is>
       </c>
     </row>
@@ -4192,7 +4192,7 @@
       </c>
       <c r="S47" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T23:17:58Z</t>
+          <t>2026-09-25T23:23:39Z</t>
         </is>
       </c>
     </row>
@@ -4277,7 +4277,7 @@
       </c>
       <c r="S48" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T23:17:58Z</t>
+          <t>2026-09-25T23:23:39Z</t>
         </is>
       </c>
     </row>
@@ -4366,7 +4366,7 @@
       </c>
       <c r="S49" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T23:17:58Z</t>
+          <t>2026-09-25T23:23:39Z</t>
         </is>
       </c>
     </row>
@@ -4455,7 +4455,7 @@
       </c>
       <c r="S50" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T23:17:58Z</t>
+          <t>2026-09-25T23:23:39Z</t>
         </is>
       </c>
     </row>
@@ -4540,7 +4540,7 @@
       </c>
       <c r="S51" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T23:17:58Z</t>
+          <t>2026-09-25T23:23:39Z</t>
         </is>
       </c>
     </row>
@@ -4629,7 +4629,7 @@
       </c>
       <c r="S52" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T23:17:58Z</t>
+          <t>2026-09-25T23:23:39Z</t>
         </is>
       </c>
     </row>
@@ -4718,7 +4718,7 @@
       </c>
       <c r="S53" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T23:17:58Z</t>
+          <t>2026-09-25T23:23:39Z</t>
         </is>
       </c>
     </row>
@@ -4803,7 +4803,7 @@
       </c>
       <c r="S54" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T23:17:58Z</t>
+          <t>2026-09-25T23:23:39Z</t>
         </is>
       </c>
     </row>
@@ -4892,7 +4892,7 @@
       </c>
       <c r="S55" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T23:17:58Z</t>
+          <t>2026-09-25T23:23:39Z</t>
         </is>
       </c>
     </row>
@@ -4981,7 +4981,7 @@
       </c>
       <c r="S56" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T23:17:58Z</t>
+          <t>2026-09-25T23:23:39Z</t>
         </is>
       </c>
     </row>
@@ -5070,7 +5070,7 @@
       </c>
       <c r="S57" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T23:17:58Z</t>
+          <t>2026-09-25T23:23:39Z</t>
         </is>
       </c>
     </row>
@@ -5159,7 +5159,7 @@
       </c>
       <c r="S58" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T23:17:58Z</t>
+          <t>2026-09-25T23:23:39Z</t>
         </is>
       </c>
     </row>
@@ -5248,7 +5248,7 @@
       </c>
       <c r="S59" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T23:17:58Z</t>
+          <t>2026-09-25T23:23:39Z</t>
         </is>
       </c>
     </row>
@@ -5337,7 +5337,7 @@
       </c>
       <c r="S60" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T23:17:58Z</t>
+          <t>2026-09-25T23:23:39Z</t>
         </is>
       </c>
     </row>
@@ -5426,7 +5426,7 @@
       </c>
       <c r="S61" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T23:17:58Z</t>
+          <t>2026-09-25T23:23:39Z</t>
         </is>
       </c>
     </row>
@@ -5515,7 +5515,7 @@
       </c>
       <c r="S62" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T23:17:58Z</t>
+          <t>2026-09-25T23:23:39Z</t>
         </is>
       </c>
     </row>
@@ -5604,7 +5604,7 @@
       </c>
       <c r="S63" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T23:17:58Z</t>
+          <t>2026-09-25T23:23:39Z</t>
         </is>
       </c>
     </row>
@@ -5693,7 +5693,7 @@
       </c>
       <c r="S64" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T23:17:58Z</t>
+          <t>2026-09-25T23:23:39Z</t>
         </is>
       </c>
     </row>
@@ -5782,7 +5782,7 @@
       </c>
       <c r="S65" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T23:17:58Z</t>
+          <t>2026-09-25T23:23:39Z</t>
         </is>
       </c>
     </row>
@@ -5871,7 +5871,7 @@
       </c>
       <c r="S66" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T23:17:58Z</t>
+          <t>2026-09-25T23:23:39Z</t>
         </is>
       </c>
     </row>
@@ -5960,7 +5960,7 @@
       </c>
       <c r="S67" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T23:17:58Z</t>
+          <t>2026-09-25T23:23:39Z</t>
         </is>
       </c>
     </row>
@@ -6045,7 +6045,7 @@
       </c>
       <c r="S68" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T23:17:58Z</t>
+          <t>2026-09-25T23:23:39Z</t>
         </is>
       </c>
     </row>
@@ -6130,7 +6130,7 @@
       </c>
       <c r="S69" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T23:17:58Z</t>
+          <t>2026-09-25T23:23:39Z</t>
         </is>
       </c>
     </row>
@@ -6215,7 +6215,7 @@
       </c>
       <c r="S70" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T23:17:58Z</t>
+          <t>2026-09-25T23:23:39Z</t>
         </is>
       </c>
     </row>
@@ -6300,7 +6300,7 @@
       </c>
       <c r="S71" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T23:17:58Z</t>
+          <t>2026-09-25T23:23:39Z</t>
         </is>
       </c>
     </row>
@@ -6385,7 +6385,7 @@
       </c>
       <c r="S72" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T23:17:58Z</t>
+          <t>2026-09-25T23:23:39Z</t>
         </is>
       </c>
     </row>
@@ -6470,7 +6470,7 @@
       </c>
       <c r="S73" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T23:17:58Z</t>
+          <t>2026-09-25T23:23:39Z</t>
         </is>
       </c>
     </row>
@@ -6555,7 +6555,7 @@
       </c>
       <c r="S74" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T23:17:58Z</t>
+          <t>2026-09-25T23:23:39Z</t>
         </is>
       </c>
     </row>
@@ -6640,7 +6640,7 @@
       </c>
       <c r="S75" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T23:17:58Z</t>
+          <t>2026-09-25T23:23:39Z</t>
         </is>
       </c>
     </row>
@@ -6725,7 +6725,7 @@
       </c>
       <c r="S76" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T23:17:58Z</t>
+          <t>2026-09-25T23:23:39Z</t>
         </is>
       </c>
     </row>
@@ -6810,7 +6810,7 @@
       </c>
       <c r="S77" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T23:17:58Z</t>
+          <t>2026-09-25T23:23:39Z</t>
         </is>
       </c>
     </row>
@@ -6895,7 +6895,7 @@
       </c>
       <c r="S78" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T23:17:58Z</t>
+          <t>2026-09-25T23:23:39Z</t>
         </is>
       </c>
     </row>
@@ -6980,7 +6980,7 @@
       </c>
       <c r="S79" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T23:17:58Z</t>
+          <t>2026-09-25T23:23:39Z</t>
         </is>
       </c>
     </row>
@@ -7065,7 +7065,7 @@
       </c>
       <c r="S80" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T23:17:58Z</t>
+          <t>2026-09-25T23:23:39Z</t>
         </is>
       </c>
     </row>
@@ -7150,7 +7150,7 @@
       </c>
       <c r="S81" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T23:17:58Z</t>
+          <t>2026-09-25T23:23:39Z</t>
         </is>
       </c>
     </row>
@@ -7235,7 +7235,7 @@
       </c>
       <c r="S82" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T23:17:58Z</t>
+          <t>2026-09-25T23:23:39Z</t>
         </is>
       </c>
     </row>
@@ -7320,7 +7320,7 @@
       </c>
       <c r="S83" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T23:17:58Z</t>
+          <t>2026-09-25T23:23:39Z</t>
         </is>
       </c>
     </row>
@@ -7405,7 +7405,7 @@
       </c>
       <c r="S84" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T23:17:58Z</t>
+          <t>2026-09-25T23:23:39Z</t>
         </is>
       </c>
     </row>
@@ -7490,7 +7490,7 @@
       </c>
       <c r="S85" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T23:17:58Z</t>
+          <t>2026-09-25T23:23:39Z</t>
         </is>
       </c>
     </row>
@@ -7575,7 +7575,7 @@
       </c>
       <c r="S86" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T23:17:58Z</t>
+          <t>2026-09-25T23:23:39Z</t>
         </is>
       </c>
     </row>
@@ -7660,7 +7660,7 @@
       </c>
       <c r="S87" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T23:17:58Z</t>
+          <t>2026-09-25T23:23:39Z</t>
         </is>
       </c>
     </row>
@@ -7745,7 +7745,7 @@
       </c>
       <c r="S88" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T23:17:58Z</t>
+          <t>2026-09-25T23:23:39Z</t>
         </is>
       </c>
     </row>
@@ -7834,7 +7834,7 @@
       </c>
       <c r="S89" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T23:17:58Z</t>
+          <t>2026-09-25T23:23:39Z</t>
         </is>
       </c>
     </row>
@@ -7923,7 +7923,7 @@
       </c>
       <c r="S90" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T23:17:58Z</t>
+          <t>2026-09-25T23:23:39Z</t>
         </is>
       </c>
     </row>
@@ -8008,7 +8008,7 @@
       </c>
       <c r="S91" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T23:17:58Z</t>
+          <t>2026-09-25T23:23:39Z</t>
         </is>
       </c>
     </row>
@@ -8097,7 +8097,7 @@
       </c>
       <c r="S92" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T23:17:58Z</t>
+          <t>2026-09-25T23:23:39Z</t>
         </is>
       </c>
     </row>
@@ -8186,7 +8186,7 @@
       </c>
       <c r="S93" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T23:17:58Z</t>
+          <t>2026-09-25T23:23:39Z</t>
         </is>
       </c>
     </row>
@@ -8271,7 +8271,7 @@
       </c>
       <c r="S94" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T23:17:58Z</t>
+          <t>2026-09-25T23:23:39Z</t>
         </is>
       </c>
     </row>
@@ -8360,7 +8360,7 @@
       </c>
       <c r="S95" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T23:17:58Z</t>
+          <t>2026-09-25T23:23:39Z</t>
         </is>
       </c>
     </row>
@@ -8449,7 +8449,7 @@
       </c>
       <c r="S96" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T23:17:58Z</t>
+          <t>2026-09-25T23:23:39Z</t>
         </is>
       </c>
     </row>
@@ -8534,7 +8534,7 @@
       </c>
       <c r="S97" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T23:17:58Z</t>
+          <t>2026-09-25T23:23:39Z</t>
         </is>
       </c>
     </row>
@@ -8623,7 +8623,7 @@
       </c>
       <c r="S98" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T23:17:58Z</t>
+          <t>2026-09-25T23:23:39Z</t>
         </is>
       </c>
     </row>
@@ -8712,7 +8712,7 @@
       </c>
       <c r="S99" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T23:17:58Z</t>
+          <t>2026-09-25T23:23:39Z</t>
         </is>
       </c>
     </row>
@@ -8797,7 +8797,7 @@
       </c>
       <c r="S100" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T23:17:58Z</t>
+          <t>2026-09-25T23:23:39Z</t>
         </is>
       </c>
     </row>
@@ -8886,7 +8886,7 @@
       </c>
       <c r="S101" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T23:17:58Z</t>
+          <t>2026-09-25T23:23:39Z</t>
         </is>
       </c>
     </row>
@@ -8975,7 +8975,7 @@
       </c>
       <c r="S102" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T23:17:58Z</t>
+          <t>2026-09-25T23:23:39Z</t>
         </is>
       </c>
     </row>
@@ -9060,7 +9060,7 @@
       </c>
       <c r="S103" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T23:17:58Z</t>
+          <t>2026-09-25T23:23:39Z</t>
         </is>
       </c>
     </row>
@@ -9149,7 +9149,7 @@
       </c>
       <c r="S104" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T23:17:58Z</t>
+          <t>2026-09-25T23:23:39Z</t>
         </is>
       </c>
     </row>
@@ -9238,7 +9238,7 @@
       </c>
       <c r="S105" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T23:17:58Z</t>
+          <t>2026-09-25T23:23:39Z</t>
         </is>
       </c>
     </row>
@@ -9323,7 +9323,7 @@
       </c>
       <c r="S106" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T23:17:58Z</t>
+          <t>2026-09-25T23:23:39Z</t>
         </is>
       </c>
     </row>
@@ -9412,7 +9412,7 @@
       </c>
       <c r="S107" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T23:17:58Z</t>
+          <t>2026-09-25T23:23:39Z</t>
         </is>
       </c>
     </row>
@@ -9501,7 +9501,7 @@
       </c>
       <c r="S108" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T23:17:58Z</t>
+          <t>2026-09-25T23:23:39Z</t>
         </is>
       </c>
     </row>
@@ -9586,7 +9586,7 @@
       </c>
       <c r="S109" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T23:17:58Z</t>
+          <t>2026-09-25T23:23:39Z</t>
         </is>
       </c>
     </row>
@@ -9675,7 +9675,7 @@
       </c>
       <c r="S110" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T23:17:58Z</t>
+          <t>2026-09-25T23:23:39Z</t>
         </is>
       </c>
     </row>
@@ -9764,7 +9764,7 @@
       </c>
       <c r="S111" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T23:17:58Z</t>
+          <t>2026-09-25T23:23:39Z</t>
         </is>
       </c>
     </row>
@@ -9849,7 +9849,7 @@
       </c>
       <c r="S112" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T23:17:58Z</t>
+          <t>2026-09-25T23:23:39Z</t>
         </is>
       </c>
     </row>
@@ -9938,7 +9938,7 @@
       </c>
       <c r="S113" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T23:17:58Z</t>
+          <t>2026-09-25T23:23:39Z</t>
         </is>
       </c>
     </row>
@@ -10027,7 +10027,7 @@
       </c>
       <c r="S114" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T23:17:58Z</t>
+          <t>2026-09-25T23:23:39Z</t>
         </is>
       </c>
     </row>
@@ -10112,7 +10112,7 @@
       </c>
       <c r="S115" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T23:17:58Z</t>
+          <t>2026-09-25T23:23:39Z</t>
         </is>
       </c>
     </row>
@@ -10201,7 +10201,7 @@
       </c>
       <c r="S116" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T23:17:58Z</t>
+          <t>2026-09-25T23:23:39Z</t>
         </is>
       </c>
     </row>
@@ -10290,7 +10290,7 @@
       </c>
       <c r="S117" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T23:17:58Z</t>
+          <t>2026-09-25T23:23:39Z</t>
         </is>
       </c>
     </row>
@@ -10379,7 +10379,7 @@
       </c>
       <c r="S118" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T23:17:58Z</t>
+          <t>2026-09-25T23:23:39Z</t>
         </is>
       </c>
     </row>
@@ -10468,7 +10468,7 @@
       </c>
       <c r="S119" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T23:17:58Z</t>
+          <t>2026-09-25T23:23:39Z</t>
         </is>
       </c>
     </row>
@@ -10557,7 +10557,7 @@
       </c>
       <c r="S120" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T23:17:58Z</t>
+          <t>2026-09-25T23:23:39Z</t>
         </is>
       </c>
     </row>
@@ -10646,7 +10646,7 @@
       </c>
       <c r="S121" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T23:17:58Z</t>
+          <t>2026-09-25T23:23:39Z</t>
         </is>
       </c>
     </row>
@@ -10735,7 +10735,7 @@
       </c>
       <c r="S122" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T23:17:58Z</t>
+          <t>2026-09-25T23:23:39Z</t>
         </is>
       </c>
     </row>
@@ -10824,7 +10824,7 @@
       </c>
       <c r="S123" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T23:17:58Z</t>
+          <t>2026-09-25T23:23:39Z</t>
         </is>
       </c>
     </row>
@@ -10913,7 +10913,7 @@
       </c>
       <c r="S124" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T23:17:58Z</t>
+          <t>2026-09-25T23:23:39Z</t>
         </is>
       </c>
     </row>
@@ -11002,7 +11002,7 @@
       </c>
       <c r="S125" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T23:17:58Z</t>
+          <t>2026-09-25T23:23:39Z</t>
         </is>
       </c>
     </row>
@@ -11091,7 +11091,7 @@
       </c>
       <c r="S126" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T23:17:58Z</t>
+          <t>2026-09-25T23:23:39Z</t>
         </is>
       </c>
     </row>
@@ -11180,7 +11180,7 @@
       </c>
       <c r="S127" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T23:17:58Z</t>
+          <t>2026-09-25T23:23:39Z</t>
         </is>
       </c>
     </row>
@@ -11269,7 +11269,7 @@
       </c>
       <c r="S128" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T23:17:58Z</t>
+          <t>2026-09-25T23:23:39Z</t>
         </is>
       </c>
     </row>
@@ -11354,7 +11354,7 @@
       </c>
       <c r="S129" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T23:17:58Z</t>
+          <t>2026-09-25T23:23:39Z</t>
         </is>
       </c>
     </row>
@@ -11439,7 +11439,7 @@
       </c>
       <c r="S130" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T23:17:58Z</t>
+          <t>2026-09-25T23:23:39Z</t>
         </is>
       </c>
     </row>
@@ -11524,7 +11524,7 @@
       </c>
       <c r="S131" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T23:17:58Z</t>
+          <t>2026-09-25T23:23:39Z</t>
         </is>
       </c>
     </row>
@@ -11609,7 +11609,7 @@
       </c>
       <c r="S132" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T23:17:58Z</t>
+          <t>2026-09-25T23:23:39Z</t>
         </is>
       </c>
     </row>
@@ -11694,7 +11694,7 @@
       </c>
       <c r="S133" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T23:17:58Z</t>
+          <t>2026-09-25T23:23:39Z</t>
         </is>
       </c>
     </row>
@@ -11779,7 +11779,7 @@
       </c>
       <c r="S134" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T23:17:58Z</t>
+          <t>2026-09-25T23:23:39Z</t>
         </is>
       </c>
     </row>
@@ -11864,7 +11864,7 @@
       </c>
       <c r="S135" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T23:17:58Z</t>
+          <t>2026-09-25T23:23:39Z</t>
         </is>
       </c>
     </row>
@@ -11949,7 +11949,7 @@
       </c>
       <c r="S136" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T23:17:58Z</t>
+          <t>2026-09-25T23:23:39Z</t>
         </is>
       </c>
     </row>
@@ -12034,7 +12034,7 @@
       </c>
       <c r="S137" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T23:17:58Z</t>
+          <t>2026-09-25T23:23:39Z</t>
         </is>
       </c>
     </row>
@@ -12119,7 +12119,7 @@
       </c>
       <c r="S138" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T23:17:58Z</t>
+          <t>2026-09-25T23:23:39Z</t>
         </is>
       </c>
     </row>
@@ -12204,7 +12204,7 @@
       </c>
       <c r="S139" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T23:17:58Z</t>
+          <t>2026-09-25T23:23:39Z</t>
         </is>
       </c>
     </row>
@@ -12289,7 +12289,7 @@
       </c>
       <c r="S140" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T23:17:58Z</t>
+          <t>2026-09-25T23:23:39Z</t>
         </is>
       </c>
     </row>
@@ -12374,7 +12374,7 @@
       </c>
       <c r="S141" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T23:17:58Z</t>
+          <t>2026-09-25T23:23:39Z</t>
         </is>
       </c>
     </row>
@@ -12459,7 +12459,7 @@
       </c>
       <c r="S142" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T23:17:58Z</t>
+          <t>2026-09-25T23:23:39Z</t>
         </is>
       </c>
     </row>
@@ -12544,7 +12544,7 @@
       </c>
       <c r="S143" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T23:17:58Z</t>
+          <t>2026-09-25T23:23:39Z</t>
         </is>
       </c>
     </row>
@@ -12629,7 +12629,7 @@
       </c>
       <c r="S144" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T23:17:58Z</t>
+          <t>2026-09-25T23:23:39Z</t>
         </is>
       </c>
     </row>
@@ -12714,7 +12714,7 @@
       </c>
       <c r="S145" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T23:17:58Z</t>
+          <t>2026-09-25T23:23:39Z</t>
         </is>
       </c>
     </row>
@@ -12799,7 +12799,7 @@
       </c>
       <c r="S146" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T23:17:58Z</t>
+          <t>2026-09-25T23:23:39Z</t>
         </is>
       </c>
     </row>
@@ -12884,7 +12884,7 @@
       </c>
       <c r="S147" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T23:17:58Z</t>
+          <t>2026-09-25T23:23:39Z</t>
         </is>
       </c>
     </row>
@@ -12969,7 +12969,7 @@
       </c>
       <c r="S148" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T23:17:58Z</t>
+          <t>2026-09-25T23:23:39Z</t>
         </is>
       </c>
     </row>
@@ -13054,7 +13054,7 @@
       </c>
       <c r="S149" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T23:17:58Z</t>
+          <t>2026-09-25T23:23:39Z</t>
         </is>
       </c>
     </row>
@@ -13143,7 +13143,7 @@
       </c>
       <c r="S150" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T23:17:58Z</t>
+          <t>2026-09-25T23:23:39Z</t>
         </is>
       </c>
     </row>
@@ -13232,7 +13232,7 @@
       </c>
       <c r="S151" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T23:17:58Z</t>
+          <t>2026-09-25T23:23:39Z</t>
         </is>
       </c>
     </row>
@@ -13317,7 +13317,7 @@
       </c>
       <c r="S152" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T23:17:58Z</t>
+          <t>2026-09-25T23:23:39Z</t>
         </is>
       </c>
     </row>
@@ -13406,7 +13406,7 @@
       </c>
       <c r="S153" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T23:17:58Z</t>
+          <t>2026-09-25T23:23:39Z</t>
         </is>
       </c>
     </row>
@@ -13495,7 +13495,7 @@
       </c>
       <c r="S154" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T23:17:58Z</t>
+          <t>2026-09-25T23:23:39Z</t>
         </is>
       </c>
     </row>
@@ -13580,7 +13580,7 @@
       </c>
       <c r="S155" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T23:17:58Z</t>
+          <t>2026-09-25T23:23:39Z</t>
         </is>
       </c>
     </row>
@@ -13669,7 +13669,7 @@
       </c>
       <c r="S156" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T23:17:58Z</t>
+          <t>2026-09-25T23:23:39Z</t>
         </is>
       </c>
     </row>
@@ -13758,7 +13758,7 @@
       </c>
       <c r="S157" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T23:17:58Z</t>
+          <t>2026-09-25T23:23:39Z</t>
         </is>
       </c>
     </row>
@@ -13843,7 +13843,7 @@
       </c>
       <c r="S158" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T23:17:58Z</t>
+          <t>2026-09-25T23:23:39Z</t>
         </is>
       </c>
     </row>
@@ -13932,7 +13932,7 @@
       </c>
       <c r="S159" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T23:17:58Z</t>
+          <t>2026-09-25T23:23:39Z</t>
         </is>
       </c>
     </row>
@@ -14021,7 +14021,7 @@
       </c>
       <c r="S160" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T23:17:58Z</t>
+          <t>2026-09-25T23:23:39Z</t>
         </is>
       </c>
     </row>
@@ -14106,7 +14106,7 @@
       </c>
       <c r="S161" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T23:17:58Z</t>
+          <t>2026-09-25T23:23:39Z</t>
         </is>
       </c>
     </row>
@@ -14195,7 +14195,7 @@
       </c>
       <c r="S162" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T23:17:58Z</t>
+          <t>2026-09-25T23:23:39Z</t>
         </is>
       </c>
     </row>
@@ -14284,7 +14284,7 @@
       </c>
       <c r="S163" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T23:17:58Z</t>
+          <t>2026-09-25T23:23:39Z</t>
         </is>
       </c>
     </row>
@@ -14369,7 +14369,7 @@
       </c>
       <c r="S164" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T23:17:58Z</t>
+          <t>2026-09-25T23:23:39Z</t>
         </is>
       </c>
     </row>
@@ -14458,7 +14458,7 @@
       </c>
       <c r="S165" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T23:17:58Z</t>
+          <t>2026-09-25T23:23:39Z</t>
         </is>
       </c>
     </row>
@@ -14547,7 +14547,7 @@
       </c>
       <c r="S166" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T23:17:58Z</t>
+          <t>2026-09-25T23:23:39Z</t>
         </is>
       </c>
     </row>
@@ -14632,7 +14632,7 @@
       </c>
       <c r="S167" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T23:17:58Z</t>
+          <t>2026-09-25T23:23:39Z</t>
         </is>
       </c>
     </row>
@@ -14721,7 +14721,7 @@
       </c>
       <c r="S168" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T23:17:58Z</t>
+          <t>2026-09-25T23:23:39Z</t>
         </is>
       </c>
     </row>
@@ -14810,7 +14810,7 @@
       </c>
       <c r="S169" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T23:17:58Z</t>
+          <t>2026-09-25T23:23:39Z</t>
         </is>
       </c>
     </row>
@@ -14895,7 +14895,7 @@
       </c>
       <c r="S170" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T23:17:58Z</t>
+          <t>2026-09-25T23:23:39Z</t>
         </is>
       </c>
     </row>
@@ -14984,7 +14984,7 @@
       </c>
       <c r="S171" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T23:17:58Z</t>
+          <t>2026-09-25T23:23:39Z</t>
         </is>
       </c>
     </row>
@@ -15073,7 +15073,7 @@
       </c>
       <c r="S172" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T23:17:58Z</t>
+          <t>2026-09-25T23:23:39Z</t>
         </is>
       </c>
     </row>
@@ -15158,7 +15158,7 @@
       </c>
       <c r="S173" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T23:17:58Z</t>
+          <t>2026-09-25T23:23:39Z</t>
         </is>
       </c>
     </row>
@@ -15247,7 +15247,7 @@
       </c>
       <c r="S174" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T23:17:58Z</t>
+          <t>2026-09-25T23:23:39Z</t>
         </is>
       </c>
     </row>
@@ -15336,7 +15336,7 @@
       </c>
       <c r="S175" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T23:17:58Z</t>
+          <t>2026-09-25T23:23:39Z</t>
         </is>
       </c>
     </row>
@@ -15421,7 +15421,7 @@
       </c>
       <c r="S176" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T23:17:58Z</t>
+          <t>2026-09-25T23:23:39Z</t>
         </is>
       </c>
     </row>
@@ -15510,7 +15510,7 @@
       </c>
       <c r="S177" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T23:17:58Z</t>
+          <t>2026-09-25T23:23:39Z</t>
         </is>
       </c>
     </row>
@@ -15599,7 +15599,7 @@
       </c>
       <c r="S178" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T23:17:58Z</t>
+          <t>2026-09-25T23:23:39Z</t>
         </is>
       </c>
     </row>
@@ -15688,7 +15688,7 @@
       </c>
       <c r="S179" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T23:17:58Z</t>
+          <t>2026-09-25T23:23:39Z</t>
         </is>
       </c>
     </row>
@@ -15777,7 +15777,7 @@
       </c>
       <c r="S180" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T23:17:58Z</t>
+          <t>2026-09-25T23:23:39Z</t>
         </is>
       </c>
     </row>
@@ -15866,7 +15866,7 @@
       </c>
       <c r="S181" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T23:17:58Z</t>
+          <t>2026-09-25T23:23:39Z</t>
         </is>
       </c>
     </row>
@@ -15955,7 +15955,7 @@
       </c>
       <c r="S182" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T23:17:58Z</t>
+          <t>2026-09-25T23:23:39Z</t>
         </is>
       </c>
     </row>
@@ -16044,7 +16044,7 @@
       </c>
       <c r="S183" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T23:17:58Z</t>
+          <t>2026-09-25T23:23:39Z</t>
         </is>
       </c>
     </row>
@@ -16133,7 +16133,7 @@
       </c>
       <c r="S184" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T23:17:58Z</t>
+          <t>2026-09-25T23:23:39Z</t>
         </is>
       </c>
     </row>
@@ -16222,7 +16222,7 @@
       </c>
       <c r="S185" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T23:17:58Z</t>
+          <t>2026-09-25T23:23:39Z</t>
         </is>
       </c>
     </row>
@@ -16311,7 +16311,7 @@
       </c>
       <c r="S186" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T23:17:58Z</t>
+          <t>2026-09-25T23:23:39Z</t>
         </is>
       </c>
     </row>
@@ -16400,7 +16400,7 @@
       </c>
       <c r="S187" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T23:17:58Z</t>
+          <t>2026-09-25T23:23:39Z</t>
         </is>
       </c>
     </row>
@@ -16489,7 +16489,7 @@
       </c>
       <c r="S188" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T23:17:58Z</t>
+          <t>2026-09-25T23:23:39Z</t>
         </is>
       </c>
     </row>
@@ -16578,7 +16578,7 @@
       </c>
       <c r="S189" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T23:17:58Z</t>
+          <t>2026-09-25T23:23:39Z</t>
         </is>
       </c>
     </row>
@@ -16663,7 +16663,7 @@
       </c>
       <c r="S190" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T23:17:58Z</t>
+          <t>2026-09-25T23:23:39Z</t>
         </is>
       </c>
     </row>
@@ -16748,7 +16748,7 @@
       </c>
       <c r="S191" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T23:17:58Z</t>
+          <t>2026-09-25T23:23:39Z</t>
         </is>
       </c>
     </row>
@@ -16833,7 +16833,7 @@
       </c>
       <c r="S192" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T23:17:58Z</t>
+          <t>2026-09-25T23:23:39Z</t>
         </is>
       </c>
     </row>
@@ -16918,7 +16918,7 @@
       </c>
       <c r="S193" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T23:17:58Z</t>
+          <t>2026-09-25T23:23:39Z</t>
         </is>
       </c>
     </row>
@@ -17003,7 +17003,7 @@
       </c>
       <c r="S194" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T23:17:58Z</t>
+          <t>2026-09-25T23:23:39Z</t>
         </is>
       </c>
     </row>
@@ -17088,7 +17088,7 @@
       </c>
       <c r="S195" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T23:17:58Z</t>
+          <t>2026-09-25T23:23:39Z</t>
         </is>
       </c>
     </row>
@@ -17173,7 +17173,7 @@
       </c>
       <c r="S196" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T23:17:58Z</t>
+          <t>2026-09-25T23:23:39Z</t>
         </is>
       </c>
     </row>
@@ -17258,7 +17258,7 @@
       </c>
       <c r="S197" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T23:17:58Z</t>
+          <t>2026-09-25T23:23:39Z</t>
         </is>
       </c>
     </row>
@@ -17343,7 +17343,7 @@
       </c>
       <c r="S198" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T23:17:58Z</t>
+          <t>2026-09-25T23:23:39Z</t>
         </is>
       </c>
     </row>
@@ -17428,7 +17428,7 @@
       </c>
       <c r="S199" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T23:17:58Z</t>
+          <t>2026-09-25T23:23:39Z</t>
         </is>
       </c>
     </row>
@@ -17513,7 +17513,7 @@
       </c>
       <c r="S200" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T23:17:58Z</t>
+          <t>2026-09-25T23:23:39Z</t>
         </is>
       </c>
     </row>
@@ -17598,7 +17598,7 @@
       </c>
       <c r="S201" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T23:17:58Z</t>
+          <t>2026-09-25T23:23:39Z</t>
         </is>
       </c>
     </row>
@@ -17683,7 +17683,7 @@
       </c>
       <c r="S202" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T23:17:58Z</t>
+          <t>2026-09-25T23:23:39Z</t>
         </is>
       </c>
     </row>
@@ -17768,7 +17768,7 @@
       </c>
       <c r="S203" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T23:17:58Z</t>
+          <t>2026-09-25T23:23:39Z</t>
         </is>
       </c>
     </row>
@@ -17853,7 +17853,7 @@
       </c>
       <c r="S204" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T23:17:58Z</t>
+          <t>2026-09-25T23:23:39Z</t>
         </is>
       </c>
     </row>
@@ -17938,7 +17938,7 @@
       </c>
       <c r="S205" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T23:17:58Z</t>
+          <t>2026-09-25T23:23:39Z</t>
         </is>
       </c>
     </row>
@@ -18023,7 +18023,7 @@
       </c>
       <c r="S206" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T23:17:58Z</t>
+          <t>2026-09-25T23:23:39Z</t>
         </is>
       </c>
     </row>
@@ -18108,7 +18108,7 @@
       </c>
       <c r="S207" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T23:17:58Z</t>
+          <t>2026-09-25T23:23:39Z</t>
         </is>
       </c>
     </row>
@@ -18193,7 +18193,7 @@
       </c>
       <c r="S208" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T23:17:58Z</t>
+          <t>2026-09-25T23:23:39Z</t>
         </is>
       </c>
     </row>
@@ -18278,7 +18278,7 @@
       </c>
       <c r="S209" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T23:17:58Z</t>
+          <t>2026-09-25T23:23:39Z</t>
         </is>
       </c>
     </row>
@@ -18363,7 +18363,7 @@
       </c>
       <c r="S210" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T23:17:58Z</t>
+          <t>2026-09-25T23:23:39Z</t>
         </is>
       </c>
     </row>
@@ -18452,7 +18452,7 @@
       </c>
       <c r="S211" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T23:17:58Z</t>
+          <t>2026-09-25T23:23:39Z</t>
         </is>
       </c>
     </row>
@@ -18541,7 +18541,7 @@
       </c>
       <c r="S212" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T23:17:58Z</t>
+          <t>2026-09-25T23:23:39Z</t>
         </is>
       </c>
     </row>
@@ -18626,7 +18626,7 @@
       </c>
       <c r="S213" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T23:17:58Z</t>
+          <t>2026-09-25T23:23:39Z</t>
         </is>
       </c>
     </row>
@@ -18715,7 +18715,7 @@
       </c>
       <c r="S214" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T23:17:58Z</t>
+          <t>2026-09-25T23:23:39Z</t>
         </is>
       </c>
     </row>
@@ -18804,7 +18804,7 @@
       </c>
       <c r="S215" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T23:17:58Z</t>
+          <t>2026-09-25T23:23:39Z</t>
         </is>
       </c>
     </row>
@@ -18889,7 +18889,7 @@
       </c>
       <c r="S216" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T23:17:58Z</t>
+          <t>2026-09-25T23:23:39Z</t>
         </is>
       </c>
     </row>
@@ -18978,7 +18978,7 @@
       </c>
       <c r="S217" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T23:17:58Z</t>
+          <t>2026-09-25T23:23:39Z</t>
         </is>
       </c>
     </row>
@@ -19067,7 +19067,7 @@
       </c>
       <c r="S218" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T23:17:58Z</t>
+          <t>2026-09-25T23:23:39Z</t>
         </is>
       </c>
     </row>
@@ -19152,7 +19152,7 @@
       </c>
       <c r="S219" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T23:17:58Z</t>
+          <t>2026-09-25T23:23:39Z</t>
         </is>
       </c>
     </row>
@@ -19241,7 +19241,7 @@
       </c>
       <c r="S220" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T23:17:58Z</t>
+          <t>2026-09-25T23:23:39Z</t>
         </is>
       </c>
     </row>
@@ -19330,7 +19330,7 @@
       </c>
       <c r="S221" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T23:17:58Z</t>
+          <t>2026-09-25T23:23:39Z</t>
         </is>
       </c>
     </row>
@@ -19415,7 +19415,7 @@
       </c>
       <c r="S222" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T23:17:58Z</t>
+          <t>2026-09-25T23:23:39Z</t>
         </is>
       </c>
     </row>
@@ -19504,7 +19504,7 @@
       </c>
       <c r="S223" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T23:17:58Z</t>
+          <t>2026-09-25T23:23:39Z</t>
         </is>
       </c>
     </row>
@@ -19593,7 +19593,7 @@
       </c>
       <c r="S224" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T23:17:58Z</t>
+          <t>2026-09-25T23:23:39Z</t>
         </is>
       </c>
     </row>
@@ -19678,7 +19678,7 @@
       </c>
       <c r="S225" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T23:17:58Z</t>
+          <t>2026-09-25T23:23:39Z</t>
         </is>
       </c>
     </row>
@@ -19767,7 +19767,7 @@
       </c>
       <c r="S226" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T23:17:58Z</t>
+          <t>2026-09-25T23:23:39Z</t>
         </is>
       </c>
     </row>
@@ -19856,7 +19856,7 @@
       </c>
       <c r="S227" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T23:17:58Z</t>
+          <t>2026-09-25T23:23:39Z</t>
         </is>
       </c>
     </row>
@@ -19941,7 +19941,7 @@
       </c>
       <c r="S228" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T23:17:58Z</t>
+          <t>2026-09-25T23:23:39Z</t>
         </is>
       </c>
     </row>
@@ -20030,7 +20030,7 @@
       </c>
       <c r="S229" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T23:17:58Z</t>
+          <t>2026-09-25T23:23:39Z</t>
         </is>
       </c>
     </row>
@@ -20119,7 +20119,7 @@
       </c>
       <c r="S230" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T23:17:58Z</t>
+          <t>2026-09-25T23:23:39Z</t>
         </is>
       </c>
     </row>
@@ -20204,7 +20204,7 @@
       </c>
       <c r="S231" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T23:17:58Z</t>
+          <t>2026-09-25T23:23:39Z</t>
         </is>
       </c>
     </row>
@@ -20293,7 +20293,7 @@
       </c>
       <c r="S232" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T23:17:58Z</t>
+          <t>2026-09-25T23:23:39Z</t>
         </is>
       </c>
     </row>
@@ -20382,7 +20382,7 @@
       </c>
       <c r="S233" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T23:17:58Z</t>
+          <t>2026-09-25T23:23:39Z</t>
         </is>
       </c>
     </row>
@@ -20467,7 +20467,7 @@
       </c>
       <c r="S234" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T23:17:58Z</t>
+          <t>2026-09-25T23:23:39Z</t>
         </is>
       </c>
     </row>
@@ -20556,7 +20556,7 @@
       </c>
       <c r="S235" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T23:17:58Z</t>
+          <t>2026-09-25T23:23:39Z</t>
         </is>
       </c>
     </row>
@@ -20645,7 +20645,7 @@
       </c>
       <c r="S236" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T23:17:58Z</t>
+          <t>2026-09-25T23:23:39Z</t>
         </is>
       </c>
     </row>
@@ -20730,7 +20730,7 @@
       </c>
       <c r="S237" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T23:17:58Z</t>
+          <t>2026-09-25T23:23:39Z</t>
         </is>
       </c>
     </row>
@@ -20819,7 +20819,7 @@
       </c>
       <c r="S238" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T23:17:58Z</t>
+          <t>2026-09-25T23:23:39Z</t>
         </is>
       </c>
     </row>
@@ -20908,7 +20908,7 @@
       </c>
       <c r="S239" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T23:17:58Z</t>
+          <t>2026-09-25T23:23:39Z</t>
         </is>
       </c>
     </row>
@@ -20997,7 +20997,7 @@
       </c>
       <c r="S240" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T23:17:58Z</t>
+          <t>2026-09-25T23:23:39Z</t>
         </is>
       </c>
     </row>
@@ -21086,7 +21086,7 @@
       </c>
       <c r="S241" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T23:17:58Z</t>
+          <t>2026-09-25T23:23:39Z</t>
         </is>
       </c>
     </row>
@@ -21175,7 +21175,7 @@
       </c>
       <c r="S242" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T23:17:58Z</t>
+          <t>2026-09-25T23:23:39Z</t>
         </is>
       </c>
     </row>
@@ -21264,7 +21264,7 @@
       </c>
       <c r="S243" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T23:17:58Z</t>
+          <t>2026-09-25T23:23:39Z</t>
         </is>
       </c>
     </row>
@@ -21353,7 +21353,7 @@
       </c>
       <c r="S244" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T23:17:58Z</t>
+          <t>2026-09-25T23:23:39Z</t>
         </is>
       </c>
     </row>
@@ -21442,7 +21442,7 @@
       </c>
       <c r="S245" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T23:17:58Z</t>
+          <t>2026-09-25T23:23:39Z</t>
         </is>
       </c>
     </row>
@@ -21531,7 +21531,7 @@
       </c>
       <c r="S246" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T23:17:58Z</t>
+          <t>2026-09-25T23:23:39Z</t>
         </is>
       </c>
     </row>
@@ -21620,7 +21620,7 @@
       </c>
       <c r="S247" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T23:17:58Z</t>
+          <t>2026-09-25T23:23:39Z</t>
         </is>
       </c>
     </row>
@@ -21709,7 +21709,7 @@
       </c>
       <c r="S248" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T23:17:58Z</t>
+          <t>2026-09-25T23:23:39Z</t>
         </is>
       </c>
     </row>
@@ -21798,7 +21798,7 @@
       </c>
       <c r="S249" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T23:17:58Z</t>
+          <t>2026-09-25T23:23:39Z</t>
         </is>
       </c>
     </row>
@@ -21887,7 +21887,7 @@
       </c>
       <c r="S250" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T23:17:58Z</t>
+          <t>2026-09-25T23:23:39Z</t>
         </is>
       </c>
     </row>
@@ -22019,7 +22019,7 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T23:17:58Z</t>
+          <t>2026-09-25T23:23:39Z</t>
         </is>
       </c>
     </row>
@@ -22099,7 +22099,7 @@
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>{"dataset_id": "bcv_pib_sector_institucional_anual", "title": "Producto interno bruto por sector institucional anual", "table": "Variaciones porcentuales", "source_file": "5_2_1_si_anual.xlsx", "base": "2007", "price_type": "Precios constantes", "measure": "Variación porcentual interanual", "frequency": "Anual", "period": "2025", "year": 2025, "quarter": null, "classification": "Sector institucional", "component": "Impuestos netos sobre los productos", "value": 10.600260421283764, "unit": "Porcentaje", "status": "Preliminar", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/cuentas_macroeconomicas/5_2_1_si_anual.xlsx", "fetched_at": "2026-09-24T23:17:58Z"}</t>
+          <t>{"dataset_id": "bcv_pib_sector_institucional_anual", "title": "Producto interno bruto por sector institucional anual", "table": "Variaciones porcentuales", "source_file": "5_2_1_si_anual.xlsx", "base": "2007", "price_type": "Precios constantes", "measure": "Variación porcentual interanual", "frequency": "Anual", "period": "2025", "year": 2025, "quarter": null, "classification": "Sector institucional", "component": "Impuestos netos sobre los productos", "value": 10.600260421283764, "unit": "Porcentaje", "status": "Preliminar", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/cuentas_macroeconomicas/5_2_1_si_anual.xlsx", "fetched_at": "2026-09-25T23:23:39Z"}</t>
         </is>
       </c>
     </row>

--- a/assets/data/bcv/excel/ove_bcv_pib_sector_institucional_anual.xlsx
+++ b/assets/data/bcv/excel/ove_bcv_pib_sector_institucional_anual.xlsx
@@ -736,7 +736,7 @@
       </c>
       <c r="S7" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25T23:23:39Z</t>
+          <t>2026-09-26T23:03:46Z</t>
         </is>
       </c>
     </row>
@@ -821,7 +821,7 @@
       </c>
       <c r="S8" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25T23:23:39Z</t>
+          <t>2026-09-26T23:03:46Z</t>
         </is>
       </c>
     </row>
@@ -906,7 +906,7 @@
       </c>
       <c r="S9" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25T23:23:39Z</t>
+          <t>2026-09-26T23:03:46Z</t>
         </is>
       </c>
     </row>
@@ -991,7 +991,7 @@
       </c>
       <c r="S10" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25T23:23:39Z</t>
+          <t>2026-09-26T23:03:46Z</t>
         </is>
       </c>
     </row>
@@ -1076,7 +1076,7 @@
       </c>
       <c r="S11" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25T23:23:39Z</t>
+          <t>2026-09-26T23:03:46Z</t>
         </is>
       </c>
     </row>
@@ -1161,7 +1161,7 @@
       </c>
       <c r="S12" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25T23:23:39Z</t>
+          <t>2026-09-26T23:03:46Z</t>
         </is>
       </c>
     </row>
@@ -1246,7 +1246,7 @@
       </c>
       <c r="S13" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25T23:23:39Z</t>
+          <t>2026-09-26T23:03:46Z</t>
         </is>
       </c>
     </row>
@@ -1331,7 +1331,7 @@
       </c>
       <c r="S14" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25T23:23:39Z</t>
+          <t>2026-09-26T23:03:46Z</t>
         </is>
       </c>
     </row>
@@ -1416,7 +1416,7 @@
       </c>
       <c r="S15" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25T23:23:39Z</t>
+          <t>2026-09-26T23:03:46Z</t>
         </is>
       </c>
     </row>
@@ -1501,7 +1501,7 @@
       </c>
       <c r="S16" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25T23:23:39Z</t>
+          <t>2026-09-26T23:03:46Z</t>
         </is>
       </c>
     </row>
@@ -1586,7 +1586,7 @@
       </c>
       <c r="S17" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25T23:23:39Z</t>
+          <t>2026-09-26T23:03:46Z</t>
         </is>
       </c>
     </row>
@@ -1671,7 +1671,7 @@
       </c>
       <c r="S18" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25T23:23:39Z</t>
+          <t>2026-09-26T23:03:46Z</t>
         </is>
       </c>
     </row>
@@ -1756,7 +1756,7 @@
       </c>
       <c r="S19" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25T23:23:39Z</t>
+          <t>2026-09-26T23:03:46Z</t>
         </is>
       </c>
     </row>
@@ -1841,7 +1841,7 @@
       </c>
       <c r="S20" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25T23:23:39Z</t>
+          <t>2026-09-26T23:03:46Z</t>
         </is>
       </c>
     </row>
@@ -1926,7 +1926,7 @@
       </c>
       <c r="S21" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25T23:23:39Z</t>
+          <t>2026-09-26T23:03:46Z</t>
         </is>
       </c>
     </row>
@@ -2011,7 +2011,7 @@
       </c>
       <c r="S22" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25T23:23:39Z</t>
+          <t>2026-09-26T23:03:46Z</t>
         </is>
       </c>
     </row>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="S23" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25T23:23:39Z</t>
+          <t>2026-09-26T23:03:46Z</t>
         </is>
       </c>
     </row>
@@ -2181,7 +2181,7 @@
       </c>
       <c r="S24" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25T23:23:39Z</t>
+          <t>2026-09-26T23:03:46Z</t>
         </is>
       </c>
     </row>
@@ -2266,7 +2266,7 @@
       </c>
       <c r="S25" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25T23:23:39Z</t>
+          <t>2026-09-26T23:03:46Z</t>
         </is>
       </c>
     </row>
@@ -2351,7 +2351,7 @@
       </c>
       <c r="S26" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25T23:23:39Z</t>
+          <t>2026-09-26T23:03:46Z</t>
         </is>
       </c>
     </row>
@@ -2436,7 +2436,7 @@
       </c>
       <c r="S27" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25T23:23:39Z</t>
+          <t>2026-09-26T23:03:46Z</t>
         </is>
       </c>
     </row>
@@ -2525,7 +2525,7 @@
       </c>
       <c r="S28" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25T23:23:39Z</t>
+          <t>2026-09-26T23:03:46Z</t>
         </is>
       </c>
     </row>
@@ -2614,7 +2614,7 @@
       </c>
       <c r="S29" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25T23:23:39Z</t>
+          <t>2026-09-26T23:03:46Z</t>
         </is>
       </c>
     </row>
@@ -2699,7 +2699,7 @@
       </c>
       <c r="S30" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25T23:23:39Z</t>
+          <t>2026-09-26T23:03:46Z</t>
         </is>
       </c>
     </row>
@@ -2788,7 +2788,7 @@
       </c>
       <c r="S31" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25T23:23:39Z</t>
+          <t>2026-09-26T23:03:46Z</t>
         </is>
       </c>
     </row>
@@ -2877,7 +2877,7 @@
       </c>
       <c r="S32" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25T23:23:39Z</t>
+          <t>2026-09-26T23:03:46Z</t>
         </is>
       </c>
     </row>
@@ -2962,7 +2962,7 @@
       </c>
       <c r="S33" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25T23:23:39Z</t>
+          <t>2026-09-26T23:03:46Z</t>
         </is>
       </c>
     </row>
@@ -3051,7 +3051,7 @@
       </c>
       <c r="S34" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25T23:23:39Z</t>
+          <t>2026-09-26T23:03:46Z</t>
         </is>
       </c>
     </row>
@@ -3140,7 +3140,7 @@
       </c>
       <c r="S35" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25T23:23:39Z</t>
+          <t>2026-09-26T23:03:46Z</t>
         </is>
       </c>
     </row>
@@ -3225,7 +3225,7 @@
       </c>
       <c r="S36" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25T23:23:39Z</t>
+          <t>2026-09-26T23:03:46Z</t>
         </is>
       </c>
     </row>
@@ -3314,7 +3314,7 @@
       </c>
       <c r="S37" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25T23:23:39Z</t>
+          <t>2026-09-26T23:03:46Z</t>
         </is>
       </c>
     </row>
@@ -3403,7 +3403,7 @@
       </c>
       <c r="S38" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25T23:23:39Z</t>
+          <t>2026-09-26T23:03:46Z</t>
         </is>
       </c>
     </row>
@@ -3488,7 +3488,7 @@
       </c>
       <c r="S39" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25T23:23:39Z</t>
+          <t>2026-09-26T23:03:46Z</t>
         </is>
       </c>
     </row>
@@ -3577,7 +3577,7 @@
       </c>
       <c r="S40" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25T23:23:39Z</t>
+          <t>2026-09-26T23:03:46Z</t>
         </is>
       </c>
     </row>
@@ -3666,7 +3666,7 @@
       </c>
       <c r="S41" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25T23:23:39Z</t>
+          <t>2026-09-26T23:03:46Z</t>
         </is>
       </c>
     </row>
@@ -3751,7 +3751,7 @@
       </c>
       <c r="S42" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25T23:23:39Z</t>
+          <t>2026-09-26T23:03:46Z</t>
         </is>
       </c>
     </row>
@@ -3840,7 +3840,7 @@
       </c>
       <c r="S43" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25T23:23:39Z</t>
+          <t>2026-09-26T23:03:46Z</t>
         </is>
       </c>
     </row>
@@ -3929,7 +3929,7 @@
       </c>
       <c r="S44" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25T23:23:39Z</t>
+          <t>2026-09-26T23:03:46Z</t>
         </is>
       </c>
     </row>
@@ -4014,7 +4014,7 @@
       </c>
       <c r="S45" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25T23:23:39Z</t>
+          <t>2026-09-26T23:03:46Z</t>
         </is>
       </c>
     </row>
@@ -4103,7 +4103,7 @@
       </c>
       <c r="S46" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25T23:23:39Z</t>
+          <t>2026-09-26T23:03:46Z</t>
         </is>
       </c>
     </row>
@@ -4192,7 +4192,7 @@
       </c>
       <c r="S47" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25T23:23:39Z</t>
+          <t>2026-09-26T23:03:46Z</t>
         </is>
       </c>
     </row>
@@ -4277,7 +4277,7 @@
       </c>
       <c r="S48" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25T23:23:39Z</t>
+          <t>2026-09-26T23:03:46Z</t>
         </is>
       </c>
     </row>
@@ -4366,7 +4366,7 @@
       </c>
       <c r="S49" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25T23:23:39Z</t>
+          <t>2026-09-26T23:03:46Z</t>
         </is>
       </c>
     </row>
@@ -4455,7 +4455,7 @@
       </c>
       <c r="S50" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25T23:23:39Z</t>
+          <t>2026-09-26T23:03:46Z</t>
         </is>
       </c>
     </row>
@@ -4540,7 +4540,7 @@
       </c>
       <c r="S51" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25T23:23:39Z</t>
+          <t>2026-09-26T23:03:46Z</t>
         </is>
       </c>
     </row>
@@ -4629,7 +4629,7 @@
       </c>
       <c r="S52" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25T23:23:39Z</t>
+          <t>2026-09-26T23:03:46Z</t>
         </is>
       </c>
     </row>
@@ -4718,7 +4718,7 @@
       </c>
       <c r="S53" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25T23:23:39Z</t>
+          <t>2026-09-26T23:03:46Z</t>
         </is>
       </c>
     </row>
@@ -4803,7 +4803,7 @@
       </c>
       <c r="S54" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25T23:23:39Z</t>
+          <t>2026-09-26T23:03:46Z</t>
         </is>
       </c>
     </row>
@@ -4892,7 +4892,7 @@
       </c>
       <c r="S55" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25T23:23:39Z</t>
+          <t>2026-09-26T23:03:46Z</t>
         </is>
       </c>
     </row>
@@ -4981,7 +4981,7 @@
       </c>
       <c r="S56" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25T23:23:39Z</t>
+          <t>2026-09-26T23:03:46Z</t>
         </is>
       </c>
     </row>
@@ -5070,7 +5070,7 @@
       </c>
       <c r="S57" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25T23:23:39Z</t>
+          <t>2026-09-26T23:03:46Z</t>
         </is>
       </c>
     </row>
@@ -5159,7 +5159,7 @@
       </c>
       <c r="S58" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25T23:23:39Z</t>
+          <t>2026-09-26T23:03:46Z</t>
         </is>
       </c>
     </row>
@@ -5248,7 +5248,7 @@
       </c>
       <c r="S59" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25T23:23:39Z</t>
+          <t>2026-09-26T23:03:46Z</t>
         </is>
       </c>
     </row>
@@ -5337,7 +5337,7 @@
       </c>
       <c r="S60" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25T23:23:39Z</t>
+          <t>2026-09-26T23:03:46Z</t>
         </is>
       </c>
     </row>
@@ -5426,7 +5426,7 @@
       </c>
       <c r="S61" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25T23:23:39Z</t>
+          <t>2026-09-26T23:03:46Z</t>
         </is>
       </c>
     </row>
@@ -5515,7 +5515,7 @@
       </c>
       <c r="S62" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25T23:23:39Z</t>
+          <t>2026-09-26T23:03:46Z</t>
         </is>
       </c>
     </row>
@@ -5604,7 +5604,7 @@
       </c>
       <c r="S63" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25T23:23:39Z</t>
+          <t>2026-09-26T23:03:46Z</t>
         </is>
       </c>
     </row>
@@ -5693,7 +5693,7 @@
       </c>
       <c r="S64" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25T23:23:39Z</t>
+          <t>2026-09-26T23:03:46Z</t>
         </is>
       </c>
     </row>
@@ -5782,7 +5782,7 @@
       </c>
       <c r="S65" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25T23:23:39Z</t>
+          <t>2026-09-26T23:03:46Z</t>
         </is>
       </c>
     </row>
@@ -5871,7 +5871,7 @@
       </c>
       <c r="S66" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25T23:23:39Z</t>
+          <t>2026-09-26T23:03:46Z</t>
         </is>
       </c>
     </row>
@@ -5960,7 +5960,7 @@
       </c>
       <c r="S67" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25T23:23:39Z</t>
+          <t>2026-09-26T23:03:46Z</t>
         </is>
       </c>
     </row>
@@ -6045,7 +6045,7 @@
       </c>
       <c r="S68" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25T23:23:39Z</t>
+          <t>2026-09-26T23:03:46Z</t>
         </is>
       </c>
     </row>
@@ -6130,7 +6130,7 @@
       </c>
       <c r="S69" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25T23:23:39Z</t>
+          <t>2026-09-26T23:03:46Z</t>
         </is>
       </c>
     </row>
@@ -6215,7 +6215,7 @@
       </c>
       <c r="S70" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25T23:23:39Z</t>
+          <t>2026-09-26T23:03:46Z</t>
         </is>
       </c>
     </row>
@@ -6300,7 +6300,7 @@
       </c>
       <c r="S71" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25T23:23:39Z</t>
+          <t>2026-09-26T23:03:46Z</t>
         </is>
       </c>
     </row>
@@ -6385,7 +6385,7 @@
       </c>
       <c r="S72" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25T23:23:39Z</t>
+          <t>2026-09-26T23:03:46Z</t>
         </is>
       </c>
     </row>
@@ -6470,7 +6470,7 @@
       </c>
       <c r="S73" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25T23:23:39Z</t>
+          <t>2026-09-26T23:03:46Z</t>
         </is>
       </c>
     </row>
@@ -6555,7 +6555,7 @@
       </c>
       <c r="S74" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25T23:23:39Z</t>
+          <t>2026-09-26T23:03:46Z</t>
         </is>
       </c>
     </row>
@@ -6640,7 +6640,7 @@
       </c>
       <c r="S75" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25T23:23:39Z</t>
+          <t>2026-09-26T23:03:46Z</t>
         </is>
       </c>
     </row>
@@ -6725,7 +6725,7 @@
       </c>
       <c r="S76" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25T23:23:39Z</t>
+          <t>2026-09-26T23:03:46Z</t>
         </is>
       </c>
     </row>
@@ -6810,7 +6810,7 @@
       </c>
       <c r="S77" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25T23:23:39Z</t>
+          <t>2026-09-26T23:03:46Z</t>
         </is>
       </c>
     </row>
@@ -6895,7 +6895,7 @@
       </c>
       <c r="S78" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25T23:23:39Z</t>
+          <t>2026-09-26T23:03:46Z</t>
         </is>
       </c>
     </row>
@@ -6980,7 +6980,7 @@
       </c>
       <c r="S79" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25T23:23:39Z</t>
+          <t>2026-09-26T23:03:46Z</t>
         </is>
       </c>
     </row>
@@ -7065,7 +7065,7 @@
       </c>
       <c r="S80" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25T23:23:39Z</t>
+          <t>2026-09-26T23:03:46Z</t>
         </is>
       </c>
     </row>
@@ -7150,7 +7150,7 @@
       </c>
       <c r="S81" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25T23:23:39Z</t>
+          <t>2026-09-26T23:03:46Z</t>
         </is>
       </c>
     </row>
@@ -7235,7 +7235,7 @@
       </c>
       <c r="S82" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25T23:23:39Z</t>
+          <t>2026-09-26T23:03:46Z</t>
         </is>
       </c>
     </row>
@@ -7320,7 +7320,7 @@
       </c>
       <c r="S83" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25T23:23:39Z</t>
+          <t>2026-09-26T23:03:46Z</t>
         </is>
       </c>
     </row>
@@ -7405,7 +7405,7 @@
       </c>
       <c r="S84" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25T23:23:39Z</t>
+          <t>2026-09-26T23:03:46Z</t>
         </is>
       </c>
     </row>
@@ -7490,7 +7490,7 @@
       </c>
       <c r="S85" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25T23:23:39Z</t>
+          <t>2026-09-26T23:03:46Z</t>
         </is>
       </c>
     </row>
@@ -7575,7 +7575,7 @@
       </c>
       <c r="S86" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25T23:23:39Z</t>
+          <t>2026-09-26T23:03:46Z</t>
         </is>
       </c>
     </row>
@@ -7660,7 +7660,7 @@
       </c>
       <c r="S87" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25T23:23:39Z</t>
+          <t>2026-09-26T23:03:46Z</t>
         </is>
       </c>
     </row>
@@ -7745,7 +7745,7 @@
       </c>
       <c r="S88" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25T23:23:39Z</t>
+          <t>2026-09-26T23:03:46Z</t>
         </is>
       </c>
     </row>
@@ -7834,7 +7834,7 @@
       </c>
       <c r="S89" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25T23:23:39Z</t>
+          <t>2026-09-26T23:03:46Z</t>
         </is>
       </c>
     </row>
@@ -7923,7 +7923,7 @@
       </c>
       <c r="S90" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25T23:23:39Z</t>
+          <t>2026-09-26T23:03:46Z</t>
         </is>
       </c>
     </row>
@@ -8008,7 +8008,7 @@
       </c>
       <c r="S91" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25T23:23:39Z</t>
+          <t>2026-09-26T23:03:46Z</t>
         </is>
       </c>
     </row>
@@ -8097,7 +8097,7 @@
       </c>
       <c r="S92" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25T23:23:39Z</t>
+          <t>2026-09-26T23:03:46Z</t>
         </is>
       </c>
     </row>
@@ -8186,7 +8186,7 @@
       </c>
       <c r="S93" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25T23:23:39Z</t>
+          <t>2026-09-26T23:03:46Z</t>
         </is>
       </c>
     </row>
@@ -8271,7 +8271,7 @@
       </c>
       <c r="S94" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25T23:23:39Z</t>
+          <t>2026-09-26T23:03:46Z</t>
         </is>
       </c>
     </row>
@@ -8360,7 +8360,7 @@
       </c>
       <c r="S95" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25T23:23:39Z</t>
+          <t>2026-09-26T23:03:46Z</t>
         </is>
       </c>
     </row>
@@ -8449,7 +8449,7 @@
       </c>
       <c r="S96" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25T23:23:39Z</t>
+          <t>2026-09-26T23:03:46Z</t>
         </is>
       </c>
     </row>
@@ -8534,7 +8534,7 @@
       </c>
       <c r="S97" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25T23:23:39Z</t>
+          <t>2026-09-26T23:03:46Z</t>
         </is>
       </c>
     </row>
@@ -8623,7 +8623,7 @@
       </c>
       <c r="S98" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25T23:23:39Z</t>
+          <t>2026-09-26T23:03:46Z</t>
         </is>
       </c>
     </row>
@@ -8712,7 +8712,7 @@
       </c>
       <c r="S99" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25T23:23:39Z</t>
+          <t>2026-09-26T23:03:46Z</t>
         </is>
       </c>
     </row>
@@ -8797,7 +8797,7 @@
       </c>
       <c r="S100" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25T23:23:39Z</t>
+          <t>2026-09-26T23:03:46Z</t>
         </is>
       </c>
     </row>
@@ -8886,7 +8886,7 @@
       </c>
       <c r="S101" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25T23:23:39Z</t>
+          <t>2026-09-26T23:03:46Z</t>
         </is>
       </c>
     </row>
@@ -8975,7 +8975,7 @@
       </c>
       <c r="S102" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25T23:23:39Z</t>
+          <t>2026-09-26T23:03:46Z</t>
         </is>
       </c>
     </row>
@@ -9060,7 +9060,7 @@
       </c>
       <c r="S103" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25T23:23:39Z</t>
+          <t>2026-09-26T23:03:46Z</t>
         </is>
       </c>
     </row>
@@ -9149,7 +9149,7 @@
       </c>
       <c r="S104" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25T23:23:39Z</t>
+          <t>2026-09-26T23:03:46Z</t>
         </is>
       </c>
     </row>
@@ -9238,7 +9238,7 @@
       </c>
       <c r="S105" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25T23:23:39Z</t>
+          <t>2026-09-26T23:03:46Z</t>
         </is>
       </c>
     </row>
@@ -9323,7 +9323,7 @@
       </c>
       <c r="S106" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25T23:23:39Z</t>
+          <t>2026-09-26T23:03:46Z</t>
         </is>
       </c>
     </row>
@@ -9412,7 +9412,7 @@
       </c>
       <c r="S107" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25T23:23:39Z</t>
+          <t>2026-09-26T23:03:46Z</t>
         </is>
       </c>
     </row>
@@ -9501,7 +9501,7 @@
       </c>
       <c r="S108" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25T23:23:39Z</t>
+          <t>2026-09-26T23:03:46Z</t>
         </is>
       </c>
     </row>
@@ -9586,7 +9586,7 @@
       </c>
       <c r="S109" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25T23:23:39Z</t>
+          <t>2026-09-26T23:03:46Z</t>
         </is>
       </c>
     </row>
@@ -9675,7 +9675,7 @@
       </c>
       <c r="S110" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25T23:23:39Z</t>
+          <t>2026-09-26T23:03:46Z</t>
         </is>
       </c>
     </row>
@@ -9764,7 +9764,7 @@
       </c>
       <c r="S111" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25T23:23:39Z</t>
+          <t>2026-09-26T23:03:46Z</t>
         </is>
       </c>
     </row>
@@ -9849,7 +9849,7 @@
       </c>
       <c r="S112" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25T23:23:39Z</t>
+          <t>2026-09-26T23:03:46Z</t>
         </is>
       </c>
     </row>
@@ -9938,7 +9938,7 @@
       </c>
       <c r="S113" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25T23:23:39Z</t>
+          <t>2026-09-26T23:03:46Z</t>
         </is>
       </c>
     </row>
@@ -10027,7 +10027,7 @@
       </c>
       <c r="S114" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25T23:23:39Z</t>
+          <t>2026-09-26T23:03:46Z</t>
         </is>
       </c>
     </row>
@@ -10112,7 +10112,7 @@
       </c>
       <c r="S115" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25T23:23:39Z</t>
+          <t>2026-09-26T23:03:46Z</t>
         </is>
       </c>
     </row>
@@ -10201,7 +10201,7 @@
       </c>
       <c r="S116" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25T23:23:39Z</t>
+          <t>2026-09-26T23:03:46Z</t>
         </is>
       </c>
     </row>
@@ -10290,7 +10290,7 @@
       </c>
       <c r="S117" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25T23:23:39Z</t>
+          <t>2026-09-26T23:03:46Z</t>
         </is>
       </c>
     </row>
@@ -10379,7 +10379,7 @@
       </c>
       <c r="S118" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25T23:23:39Z</t>
+          <t>2026-09-26T23:03:46Z</t>
         </is>
       </c>
     </row>
@@ -10468,7 +10468,7 @@
       </c>
       <c r="S119" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25T23:23:39Z</t>
+          <t>2026-09-26T23:03:46Z</t>
         </is>
       </c>
     </row>
@@ -10557,7 +10557,7 @@
       </c>
       <c r="S120" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25T23:23:39Z</t>
+          <t>2026-09-26T23:03:46Z</t>
         </is>
       </c>
     </row>
@@ -10646,7 +10646,7 @@
       </c>
       <c r="S121" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25T23:23:39Z</t>
+          <t>2026-09-26T23:03:46Z</t>
         </is>
       </c>
     </row>
@@ -10735,7 +10735,7 @@
       </c>
       <c r="S122" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25T23:23:39Z</t>
+          <t>2026-09-26T23:03:46Z</t>
         </is>
       </c>
     </row>
@@ -10824,7 +10824,7 @@
       </c>
       <c r="S123" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25T23:23:39Z</t>
+          <t>2026-09-26T23:03:46Z</t>
         </is>
       </c>
     </row>
@@ -10913,7 +10913,7 @@
       </c>
       <c r="S124" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25T23:23:39Z</t>
+          <t>2026-09-26T23:03:46Z</t>
         </is>
       </c>
     </row>
@@ -11002,7 +11002,7 @@
       </c>
       <c r="S125" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25T23:23:39Z</t>
+          <t>2026-09-26T23:03:46Z</t>
         </is>
       </c>
     </row>
@@ -11091,7 +11091,7 @@
       </c>
       <c r="S126" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25T23:23:39Z</t>
+          <t>2026-09-26T23:03:46Z</t>
         </is>
       </c>
     </row>
@@ -11180,7 +11180,7 @@
       </c>
       <c r="S127" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25T23:23:39Z</t>
+          <t>2026-09-26T23:03:46Z</t>
         </is>
       </c>
     </row>
@@ -11269,7 +11269,7 @@
       </c>
       <c r="S128" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25T23:23:39Z</t>
+          <t>2026-09-26T23:03:46Z</t>
         </is>
       </c>
     </row>
@@ -11354,7 +11354,7 @@
       </c>
       <c r="S129" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25T23:23:39Z</t>
+          <t>2026-09-26T23:03:46Z</t>
         </is>
       </c>
     </row>
@@ -11439,7 +11439,7 @@
       </c>
       <c r="S130" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25T23:23:39Z</t>
+          <t>2026-09-26T23:03:46Z</t>
         </is>
       </c>
     </row>
@@ -11524,7 +11524,7 @@
       </c>
       <c r="S131" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25T23:23:39Z</t>
+          <t>2026-09-26T23:03:46Z</t>
         </is>
       </c>
     </row>
@@ -11609,7 +11609,7 @@
       </c>
       <c r="S132" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25T23:23:39Z</t>
+          <t>2026-09-26T23:03:46Z</t>
         </is>
       </c>
     </row>
@@ -11694,7 +11694,7 @@
       </c>
       <c r="S133" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25T23:23:39Z</t>
+          <t>2026-09-26T23:03:46Z</t>
         </is>
       </c>
     </row>
@@ -11779,7 +11779,7 @@
       </c>
       <c r="S134" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25T23:23:39Z</t>
+          <t>2026-09-26T23:03:46Z</t>
         </is>
       </c>
     </row>
@@ -11864,7 +11864,7 @@
       </c>
       <c r="S135" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25T23:23:39Z</t>
+          <t>2026-09-26T23:03:46Z</t>
         </is>
       </c>
     </row>
@@ -11949,7 +11949,7 @@
       </c>
       <c r="S136" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25T23:23:39Z</t>
+          <t>2026-09-26T23:03:46Z</t>
         </is>
       </c>
     </row>
@@ -12034,7 +12034,7 @@
       </c>
       <c r="S137" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25T23:23:39Z</t>
+          <t>2026-09-26T23:03:46Z</t>
         </is>
       </c>
     </row>
@@ -12119,7 +12119,7 @@
       </c>
       <c r="S138" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25T23:23:39Z</t>
+          <t>2026-09-26T23:03:46Z</t>
         </is>
       </c>
     </row>
@@ -12204,7 +12204,7 @@
       </c>
       <c r="S139" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25T23:23:39Z</t>
+          <t>2026-09-26T23:03:46Z</t>
         </is>
       </c>
     </row>
@@ -12289,7 +12289,7 @@
       </c>
       <c r="S140" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25T23:23:39Z</t>
+          <t>2026-09-26T23:03:46Z</t>
         </is>
       </c>
     </row>
@@ -12374,7 +12374,7 @@
       </c>
       <c r="S141" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25T23:23:39Z</t>
+          <t>2026-09-26T23:03:46Z</t>
         </is>
       </c>
     </row>
@@ -12459,7 +12459,7 @@
       </c>
       <c r="S142" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25T23:23:39Z</t>
+          <t>2026-09-26T23:03:46Z</t>
         </is>
       </c>
     </row>
@@ -12544,7 +12544,7 @@
       </c>
       <c r="S143" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25T23:23:39Z</t>
+          <t>2026-09-26T23:03:46Z</t>
         </is>
       </c>
     </row>
@@ -12629,7 +12629,7 @@
       </c>
       <c r="S144" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25T23:23:39Z</t>
+          <t>2026-09-26T23:03:46Z</t>
         </is>
       </c>
     </row>
@@ -12714,7 +12714,7 @@
       </c>
       <c r="S145" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25T23:23:39Z</t>
+          <t>2026-09-26T23:03:46Z</t>
         </is>
       </c>
     </row>
@@ -12799,7 +12799,7 @@
       </c>
       <c r="S146" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25T23:23:39Z</t>
+          <t>2026-09-26T23:03:46Z</t>
         </is>
       </c>
     </row>
@@ -12884,7 +12884,7 @@
       </c>
       <c r="S147" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25T23:23:39Z</t>
+          <t>2026-09-26T23:03:46Z</t>
         </is>
       </c>
     </row>
@@ -12969,7 +12969,7 @@
       </c>
       <c r="S148" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25T23:23:39Z</t>
+          <t>2026-09-26T23:03:46Z</t>
         </is>
       </c>
     </row>
@@ -13054,7 +13054,7 @@
       </c>
       <c r="S149" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25T23:23:39Z</t>
+          <t>2026-09-26T23:03:46Z</t>
         </is>
       </c>
     </row>
@@ -13143,7 +13143,7 @@
       </c>
       <c r="S150" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25T23:23:39Z</t>
+          <t>2026-09-26T23:03:46Z</t>
         </is>
       </c>
     </row>
@@ -13232,7 +13232,7 @@
       </c>
       <c r="S151" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25T23:23:39Z</t>
+          <t>2026-09-26T23:03:46Z</t>
         </is>
       </c>
     </row>
@@ -13317,7 +13317,7 @@
       </c>
       <c r="S152" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25T23:23:39Z</t>
+          <t>2026-09-26T23:03:46Z</t>
         </is>
       </c>
     </row>
@@ -13406,7 +13406,7 @@
       </c>
       <c r="S153" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25T23:23:39Z</t>
+          <t>2026-09-26T23:03:46Z</t>
         </is>
       </c>
     </row>
@@ -13495,7 +13495,7 @@
       </c>
       <c r="S154" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25T23:23:39Z</t>
+          <t>2026-09-26T23:03:46Z</t>
         </is>
       </c>
     </row>
@@ -13580,7 +13580,7 @@
       </c>
       <c r="S155" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25T23:23:39Z</t>
+          <t>2026-09-26T23:03:46Z</t>
         </is>
       </c>
     </row>
@@ -13669,7 +13669,7 @@
       </c>
       <c r="S156" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25T23:23:39Z</t>
+          <t>2026-09-26T23:03:46Z</t>
         </is>
       </c>
     </row>
@@ -13758,7 +13758,7 @@
       </c>
       <c r="S157" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25T23:23:39Z</t>
+          <t>2026-09-26T23:03:46Z</t>
         </is>
       </c>
     </row>
@@ -13843,7 +13843,7 @@
       </c>
       <c r="S158" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25T23:23:39Z</t>
+          <t>2026-09-26T23:03:46Z</t>
         </is>
       </c>
     </row>
@@ -13932,7 +13932,7 @@
       </c>
       <c r="S159" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25T23:23:39Z</t>
+          <t>2026-09-26T23:03:46Z</t>
         </is>
       </c>
     </row>
@@ -14021,7 +14021,7 @@
       </c>
       <c r="S160" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25T23:23:39Z</t>
+          <t>2026-09-26T23:03:46Z</t>
         </is>
       </c>
     </row>
@@ -14106,7 +14106,7 @@
       </c>
       <c r="S161" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25T23:23:39Z</t>
+          <t>2026-09-26T23:03:46Z</t>
         </is>
       </c>
     </row>
@@ -14195,7 +14195,7 @@
       </c>
       <c r="S162" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25T23:23:39Z</t>
+          <t>2026-09-26T23:03:46Z</t>
         </is>
       </c>
     </row>
@@ -14284,7 +14284,7 @@
       </c>
       <c r="S163" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25T23:23:39Z</t>
+          <t>2026-09-26T23:03:46Z</t>
         </is>
       </c>
     </row>
@@ -14369,7 +14369,7 @@
       </c>
       <c r="S164" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25T23:23:39Z</t>
+          <t>2026-09-26T23:03:46Z</t>
         </is>
       </c>
     </row>
@@ -14458,7 +14458,7 @@
       </c>
       <c r="S165" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25T23:23:39Z</t>
+          <t>2026-09-26T23:03:46Z</t>
         </is>
       </c>
     </row>
@@ -14547,7 +14547,7 @@
       </c>
       <c r="S166" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25T23:23:39Z</t>
+          <t>2026-09-26T23:03:46Z</t>
         </is>
       </c>
     </row>
@@ -14632,7 +14632,7 @@
       </c>
       <c r="S167" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25T23:23:39Z</t>
+          <t>2026-09-26T23:03:46Z</t>
         </is>
       </c>
     </row>
@@ -14721,7 +14721,7 @@
       </c>
       <c r="S168" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25T23:23:39Z</t>
+          <t>2026-09-26T23:03:46Z</t>
         </is>
       </c>
     </row>
@@ -14810,7 +14810,7 @@
       </c>
       <c r="S169" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25T23:23:39Z</t>
+          <t>2026-09-26T23:03:46Z</t>
         </is>
       </c>
     </row>
@@ -14895,7 +14895,7 @@
       </c>
       <c r="S170" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25T23:23:39Z</t>
+          <t>2026-09-26T23:03:46Z</t>
         </is>
       </c>
     </row>
@@ -14984,7 +14984,7 @@
       </c>
       <c r="S171" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25T23:23:39Z</t>
+          <t>2026-09-26T23:03:46Z</t>
         </is>
       </c>
     </row>
@@ -15073,7 +15073,7 @@
       </c>
       <c r="S172" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25T23:23:39Z</t>
+          <t>2026-09-26T23:03:46Z</t>
         </is>
       </c>
     </row>
@@ -15158,7 +15158,7 @@
       </c>
       <c r="S173" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25T23:23:39Z</t>
+          <t>2026-09-26T23:03:46Z</t>
         </is>
       </c>
     </row>
@@ -15247,7 +15247,7 @@
       </c>
       <c r="S174" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25T23:23:39Z</t>
+          <t>2026-09-26T23:03:46Z</t>
         </is>
       </c>
     </row>
@@ -15336,7 +15336,7 @@
       </c>
       <c r="S175" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25T23:23:39Z</t>
+          <t>2026-09-26T23:03:46Z</t>
         </is>
       </c>
     </row>
@@ -15421,7 +15421,7 @@
       </c>
       <c r="S176" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25T23:23:39Z</t>
+          <t>2026-09-26T23:03:46Z</t>
         </is>
       </c>
     </row>
@@ -15510,7 +15510,7 @@
       </c>
       <c r="S177" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25T23:23:39Z</t>
+          <t>2026-09-26T23:03:46Z</t>
         </is>
       </c>
     </row>
@@ -15599,7 +15599,7 @@
       </c>
       <c r="S178" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25T23:23:39Z</t>
+          <t>2026-09-26T23:03:46Z</t>
         </is>
       </c>
     </row>
@@ -15688,7 +15688,7 @@
       </c>
       <c r="S179" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25T23:23:39Z</t>
+          <t>2026-09-26T23:03:46Z</t>
         </is>
       </c>
     </row>
@@ -15777,7 +15777,7 @@
       </c>
       <c r="S180" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25T23:23:39Z</t>
+          <t>2026-09-26T23:03:46Z</t>
         </is>
       </c>
     </row>
@@ -15866,7 +15866,7 @@
       </c>
       <c r="S181" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25T23:23:39Z</t>
+          <t>2026-09-26T23:03:46Z</t>
         </is>
       </c>
     </row>
@@ -15955,7 +15955,7 @@
       </c>
       <c r="S182" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25T23:23:39Z</t>
+          <t>2026-09-26T23:03:46Z</t>
         </is>
       </c>
     </row>
@@ -16044,7 +16044,7 @@
       </c>
       <c r="S183" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25T23:23:39Z</t>
+          <t>2026-09-26T23:03:46Z</t>
         </is>
       </c>
     </row>
@@ -16133,7 +16133,7 @@
       </c>
       <c r="S184" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25T23:23:39Z</t>
+          <t>2026-09-26T23:03:46Z</t>
         </is>
       </c>
     </row>
@@ -16222,7 +16222,7 @@
       </c>
       <c r="S185" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25T23:23:39Z</t>
+          <t>2026-09-26T23:03:46Z</t>
         </is>
       </c>
     </row>
@@ -16311,7 +16311,7 @@
       </c>
       <c r="S186" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25T23:23:39Z</t>
+          <t>2026-09-26T23:03:46Z</t>
         </is>
       </c>
     </row>
@@ -16400,7 +16400,7 @@
       </c>
       <c r="S187" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25T23:23:39Z</t>
+          <t>2026-09-26T23:03:46Z</t>
         </is>
       </c>
     </row>
@@ -16489,7 +16489,7 @@
       </c>
       <c r="S188" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25T23:23:39Z</t>
+          <t>2026-09-26T23:03:46Z</t>
         </is>
       </c>
     </row>
@@ -16578,7 +16578,7 @@
       </c>
       <c r="S189" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25T23:23:39Z</t>
+          <t>2026-09-26T23:03:46Z</t>
         </is>
       </c>
     </row>
@@ -16663,7 +16663,7 @@
       </c>
       <c r="S190" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25T23:23:39Z</t>
+          <t>2026-09-26T23:03:46Z</t>
         </is>
       </c>
     </row>
@@ -16748,7 +16748,7 @@
       </c>
       <c r="S191" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25T23:23:39Z</t>
+          <t>2026-09-26T23:03:46Z</t>
         </is>
       </c>
     </row>
@@ -16833,7 +16833,7 @@
       </c>
       <c r="S192" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25T23:23:39Z</t>
+          <t>2026-09-26T23:03:46Z</t>
         </is>
       </c>
     </row>
@@ -16918,7 +16918,7 @@
       </c>
       <c r="S193" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25T23:23:39Z</t>
+          <t>2026-09-26T23:03:46Z</t>
         </is>
       </c>
     </row>
@@ -17003,7 +17003,7 @@
       </c>
       <c r="S194" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25T23:23:39Z</t>
+          <t>2026-09-26T23:03:46Z</t>
         </is>
       </c>
     </row>
@@ -17088,7 +17088,7 @@
       </c>
       <c r="S195" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25T23:23:39Z</t>
+          <t>2026-09-26T23:03:46Z</t>
         </is>
       </c>
     </row>
@@ -17173,7 +17173,7 @@
       </c>
       <c r="S196" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25T23:23:39Z</t>
+          <t>2026-09-26T23:03:46Z</t>
         </is>
       </c>
     </row>
@@ -17258,7 +17258,7 @@
       </c>
       <c r="S197" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25T23:23:39Z</t>
+          <t>2026-09-26T23:03:46Z</t>
         </is>
       </c>
     </row>
@@ -17343,7 +17343,7 @@
       </c>
       <c r="S198" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25T23:23:39Z</t>
+          <t>2026-09-26T23:03:46Z</t>
         </is>
       </c>
     </row>
@@ -17428,7 +17428,7 @@
       </c>
       <c r="S199" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25T23:23:39Z</t>
+          <t>2026-09-26T23:03:46Z</t>
         </is>
       </c>
     </row>
@@ -17513,7 +17513,7 @@
       </c>
       <c r="S200" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25T23:23:39Z</t>
+          <t>2026-09-26T23:03:46Z</t>
         </is>
       </c>
     </row>
@@ -17598,7 +17598,7 @@
       </c>
       <c r="S201" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25T23:23:39Z</t>
+          <t>2026-09-26T23:03:46Z</t>
         </is>
       </c>
     </row>
@@ -17683,7 +17683,7 @@
       </c>
       <c r="S202" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25T23:23:39Z</t>
+          <t>2026-09-26T23:03:46Z</t>
         </is>
       </c>
     </row>
@@ -17768,7 +17768,7 @@
       </c>
       <c r="S203" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25T23:23:39Z</t>
+          <t>2026-09-26T23:03:46Z</t>
         </is>
       </c>
     </row>
@@ -17853,7 +17853,7 @@
       </c>
       <c r="S204" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25T23:23:39Z</t>
+          <t>2026-09-26T23:03:46Z</t>
         </is>
       </c>
     </row>
@@ -17938,7 +17938,7 @@
       </c>
       <c r="S205" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25T23:23:39Z</t>
+          <t>2026-09-26T23:03:46Z</t>
         </is>
       </c>
     </row>
@@ -18023,7 +18023,7 @@
       </c>
       <c r="S206" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25T23:23:39Z</t>
+          <t>2026-09-26T23:03:46Z</t>
         </is>
       </c>
     </row>
@@ -18108,7 +18108,7 @@
       </c>
       <c r="S207" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25T23:23:39Z</t>
+          <t>2026-09-26T23:03:46Z</t>
         </is>
       </c>
     </row>
@@ -18193,7 +18193,7 @@
       </c>
       <c r="S208" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25T23:23:39Z</t>
+          <t>2026-09-26T23:03:46Z</t>
         </is>
       </c>
     </row>
@@ -18278,7 +18278,7 @@
       </c>
       <c r="S209" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25T23:23:39Z</t>
+          <t>2026-09-26T23:03:46Z</t>
         </is>
       </c>
     </row>
@@ -18363,7 +18363,7 @@
       </c>
       <c r="S210" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25T23:23:39Z</t>
+          <t>2026-09-26T23:03:46Z</t>
         </is>
       </c>
     </row>
@@ -18452,7 +18452,7 @@
       </c>
       <c r="S211" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25T23:23:39Z</t>
+          <t>2026-09-26T23:03:46Z</t>
         </is>
       </c>
     </row>
@@ -18541,7 +18541,7 @@
       </c>
       <c r="S212" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25T23:23:39Z</t>
+          <t>2026-09-26T23:03:46Z</t>
         </is>
       </c>
     </row>
@@ -18626,7 +18626,7 @@
       </c>
       <c r="S213" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25T23:23:39Z</t>
+          <t>2026-09-26T23:03:46Z</t>
         </is>
       </c>
     </row>
@@ -18715,7 +18715,7 @@
       </c>
       <c r="S214" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25T23:23:39Z</t>
+          <t>2026-09-26T23:03:46Z</t>
         </is>
       </c>
     </row>
@@ -18804,7 +18804,7 @@
       </c>
       <c r="S215" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25T23:23:39Z</t>
+          <t>2026-09-26T23:03:46Z</t>
         </is>
       </c>
     </row>
@@ -18889,7 +18889,7 @@
       </c>
       <c r="S216" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25T23:23:39Z</t>
+          <t>2026-09-26T23:03:46Z</t>
         </is>
       </c>
     </row>
@@ -18978,7 +18978,7 @@
       </c>
       <c r="S217" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25T23:23:39Z</t>
+          <t>2026-09-26T23:03:46Z</t>
         </is>
       </c>
     </row>
@@ -19067,7 +19067,7 @@
       </c>
       <c r="S218" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25T23:23:39Z</t>
+          <t>2026-09-26T23:03:46Z</t>
         </is>
       </c>
     </row>
@@ -19152,7 +19152,7 @@
       </c>
       <c r="S219" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25T23:23:39Z</t>
+          <t>2026-09-26T23:03:46Z</t>
         </is>
       </c>
     </row>
@@ -19241,7 +19241,7 @@
       </c>
       <c r="S220" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25T23:23:39Z</t>
+          <t>2026-09-26T23:03:46Z</t>
         </is>
       </c>
     </row>
@@ -19330,7 +19330,7 @@
       </c>
       <c r="S221" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25T23:23:39Z</t>
+          <t>2026-09-26T23:03:46Z</t>
         </is>
       </c>
     </row>
@@ -19415,7 +19415,7 @@
       </c>
       <c r="S222" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25T23:23:39Z</t>
+          <t>2026-09-26T23:03:46Z</t>
         </is>
       </c>
     </row>
@@ -19504,7 +19504,7 @@
       </c>
       <c r="S223" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25T23:23:39Z</t>
+          <t>2026-09-26T23:03:46Z</t>
         </is>
       </c>
     </row>
@@ -19593,7 +19593,7 @@
       </c>
       <c r="S224" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25T23:23:39Z</t>
+          <t>2026-09-26T23:03:46Z</t>
         </is>
       </c>
     </row>
@@ -19678,7 +19678,7 @@
       </c>
       <c r="S225" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25T23:23:39Z</t>
+          <t>2026-09-26T23:03:46Z</t>
         </is>
       </c>
     </row>
@@ -19767,7 +19767,7 @@
       </c>
       <c r="S226" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25T23:23:39Z</t>
+          <t>2026-09-26T23:03:46Z</t>
         </is>
       </c>
     </row>
@@ -19856,7 +19856,7 @@
       </c>
       <c r="S227" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25T23:23:39Z</t>
+          <t>2026-09-26T23:03:46Z</t>
         </is>
       </c>
     </row>
@@ -19941,7 +19941,7 @@
       </c>
       <c r="S228" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25T23:23:39Z</t>
+          <t>2026-09-26T23:03:46Z</t>
         </is>
       </c>
     </row>
@@ -20030,7 +20030,7 @@
       </c>
       <c r="S229" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25T23:23:39Z</t>
+          <t>2026-09-26T23:03:46Z</t>
         </is>
       </c>
     </row>
@@ -20119,7 +20119,7 @@
       </c>
       <c r="S230" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25T23:23:39Z</t>
+          <t>2026-09-26T23:03:46Z</t>
         </is>
       </c>
     </row>
@@ -20204,7 +20204,7 @@
       </c>
       <c r="S231" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25T23:23:39Z</t>
+          <t>2026-09-26T23:03:46Z</t>
         </is>
       </c>
     </row>
@@ -20293,7 +20293,7 @@
       </c>
       <c r="S232" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25T23:23:39Z</t>
+          <t>2026-09-26T23:03:46Z</t>
         </is>
       </c>
     </row>
@@ -20382,7 +20382,7 @@
       </c>
       <c r="S233" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25T23:23:39Z</t>
+          <t>2026-09-26T23:03:46Z</t>
         </is>
       </c>
     </row>
@@ -20467,7 +20467,7 @@
       </c>
       <c r="S234" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25T23:23:39Z</t>
+          <t>2026-09-26T23:03:46Z</t>
         </is>
       </c>
     </row>
@@ -20556,7 +20556,7 @@
       </c>
       <c r="S235" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25T23:23:39Z</t>
+          <t>2026-09-26T23:03:46Z</t>
         </is>
       </c>
     </row>
@@ -20645,7 +20645,7 @@
       </c>
       <c r="S236" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25T23:23:39Z</t>
+          <t>2026-09-26T23:03:46Z</t>
         </is>
       </c>
     </row>
@@ -20730,7 +20730,7 @@
       </c>
       <c r="S237" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25T23:23:39Z</t>
+          <t>2026-09-26T23:03:46Z</t>
         </is>
       </c>
     </row>
@@ -20819,7 +20819,7 @@
       </c>
       <c r="S238" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25T23:23:39Z</t>
+          <t>2026-09-26T23:03:46Z</t>
         </is>
       </c>
     </row>
@@ -20908,7 +20908,7 @@
       </c>
       <c r="S239" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25T23:23:39Z</t>
+          <t>2026-09-26T23:03:46Z</t>
         </is>
       </c>
     </row>
@@ -20997,7 +20997,7 @@
       </c>
       <c r="S240" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25T23:23:39Z</t>
+          <t>2026-09-26T23:03:46Z</t>
         </is>
       </c>
     </row>
@@ -21086,7 +21086,7 @@
       </c>
       <c r="S241" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25T23:23:39Z</t>
+          <t>2026-09-26T23:03:46Z</t>
         </is>
       </c>
     </row>
@@ -21175,7 +21175,7 @@
       </c>
       <c r="S242" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25T23:23:39Z</t>
+          <t>2026-09-26T23:03:46Z</t>
         </is>
       </c>
     </row>
@@ -21264,7 +21264,7 @@
       </c>
       <c r="S243" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25T23:23:39Z</t>
+          <t>2026-09-26T23:03:46Z</t>
         </is>
       </c>
     </row>
@@ -21353,7 +21353,7 @@
       </c>
       <c r="S244" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25T23:23:39Z</t>
+          <t>2026-09-26T23:03:46Z</t>
         </is>
       </c>
     </row>
@@ -21442,7 +21442,7 @@
       </c>
       <c r="S245" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25T23:23:39Z</t>
+          <t>2026-09-26T23:03:46Z</t>
         </is>
       </c>
     </row>
@@ -21531,7 +21531,7 @@
       </c>
       <c r="S246" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25T23:23:39Z</t>
+          <t>2026-09-26T23:03:46Z</t>
         </is>
       </c>
     </row>
@@ -21620,7 +21620,7 @@
       </c>
       <c r="S247" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25T23:23:39Z</t>
+          <t>2026-09-26T23:03:46Z</t>
         </is>
       </c>
     </row>
@@ -21709,7 +21709,7 @@
       </c>
       <c r="S248" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25T23:23:39Z</t>
+          <t>2026-09-26T23:03:46Z</t>
         </is>
       </c>
     </row>
@@ -21798,7 +21798,7 @@
       </c>
       <c r="S249" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25T23:23:39Z</t>
+          <t>2026-09-26T23:03:46Z</t>
         </is>
       </c>
     </row>
@@ -21887,7 +21887,7 @@
       </c>
       <c r="S250" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25T23:23:39Z</t>
+          <t>2026-09-26T23:03:46Z</t>
         </is>
       </c>
     </row>
@@ -22019,7 +22019,7 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25T23:23:39Z</t>
+          <t>2026-09-26T23:03:46Z</t>
         </is>
       </c>
     </row>
@@ -22099,7 +22099,7 @@
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>{"dataset_id": "bcv_pib_sector_institucional_anual", "title": "Producto interno bruto por sector institucional anual", "table": "Variaciones porcentuales", "source_file": "5_2_1_si_anual.xlsx", "base": "2007", "price_type": "Precios constantes", "measure": "Variación porcentual interanual", "frequency": "Anual", "period": "2025", "year": 2025, "quarter": null, "classification": "Sector institucional", "component": "Impuestos netos sobre los productos", "value": 10.600260421283764, "unit": "Porcentaje", "status": "Preliminar", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/cuentas_macroeconomicas/5_2_1_si_anual.xlsx", "fetched_at": "2026-09-25T23:23:39Z"}</t>
+          <t>{"dataset_id": "bcv_pib_sector_institucional_anual", "title": "Producto interno bruto por sector institucional anual", "table": "Variaciones porcentuales", "source_file": "5_2_1_si_anual.xlsx", "base": "2007", "price_type": "Precios constantes", "measure": "Variación porcentual interanual", "frequency": "Anual", "period": "2025", "year": 2025, "quarter": null, "classification": "Sector institucional", "component": "Impuestos netos sobre los productos", "value": 10.600260421283764, "unit": "Porcentaje", "status": "Preliminar", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/cuentas_macroeconomicas/5_2_1_si_anual.xlsx", "fetched_at": "2026-09-26T23:03:46Z"}</t>
         </is>
       </c>
     </row>

--- a/assets/data/bcv/excel/ove_bcv_pib_sector_institucional_anual.xlsx
+++ b/assets/data/bcv/excel/ove_bcv_pib_sector_institucional_anual.xlsx
@@ -736,7 +736,7 @@
       </c>
       <c r="S7" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26T23:03:46Z</t>
+          <t>2026-09-27T23:13:02Z</t>
         </is>
       </c>
     </row>
@@ -821,7 +821,7 @@
       </c>
       <c r="S8" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26T23:03:46Z</t>
+          <t>2026-09-27T23:13:02Z</t>
         </is>
       </c>
     </row>
@@ -906,7 +906,7 @@
       </c>
       <c r="S9" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26T23:03:46Z</t>
+          <t>2026-09-27T23:13:02Z</t>
         </is>
       </c>
     </row>
@@ -991,7 +991,7 @@
       </c>
       <c r="S10" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26T23:03:46Z</t>
+          <t>2026-09-27T23:13:02Z</t>
         </is>
       </c>
     </row>
@@ -1076,7 +1076,7 @@
       </c>
       <c r="S11" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26T23:03:46Z</t>
+          <t>2026-09-27T23:13:02Z</t>
         </is>
       </c>
     </row>
@@ -1161,7 +1161,7 @@
       </c>
       <c r="S12" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26T23:03:46Z</t>
+          <t>2026-09-27T23:13:02Z</t>
         </is>
       </c>
     </row>
@@ -1246,7 +1246,7 @@
       </c>
       <c r="S13" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26T23:03:46Z</t>
+          <t>2026-09-27T23:13:02Z</t>
         </is>
       </c>
     </row>
@@ -1331,7 +1331,7 @@
       </c>
       <c r="S14" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26T23:03:46Z</t>
+          <t>2026-09-27T23:13:02Z</t>
         </is>
       </c>
     </row>
@@ -1416,7 +1416,7 @@
       </c>
       <c r="S15" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26T23:03:46Z</t>
+          <t>2026-09-27T23:13:02Z</t>
         </is>
       </c>
     </row>
@@ -1501,7 +1501,7 @@
       </c>
       <c r="S16" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26T23:03:46Z</t>
+          <t>2026-09-27T23:13:02Z</t>
         </is>
       </c>
     </row>
@@ -1586,7 +1586,7 @@
       </c>
       <c r="S17" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26T23:03:46Z</t>
+          <t>2026-09-27T23:13:02Z</t>
         </is>
       </c>
     </row>
@@ -1671,7 +1671,7 @@
       </c>
       <c r="S18" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26T23:03:46Z</t>
+          <t>2026-09-27T23:13:02Z</t>
         </is>
       </c>
     </row>
@@ -1756,7 +1756,7 @@
       </c>
       <c r="S19" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26T23:03:46Z</t>
+          <t>2026-09-27T23:13:02Z</t>
         </is>
       </c>
     </row>
@@ -1841,7 +1841,7 @@
       </c>
       <c r="S20" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26T23:03:46Z</t>
+          <t>2026-09-27T23:13:02Z</t>
         </is>
       </c>
     </row>
@@ -1926,7 +1926,7 @@
       </c>
       <c r="S21" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26T23:03:46Z</t>
+          <t>2026-09-27T23:13:02Z</t>
         </is>
       </c>
     </row>
@@ -2011,7 +2011,7 @@
       </c>
       <c r="S22" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26T23:03:46Z</t>
+          <t>2026-09-27T23:13:02Z</t>
         </is>
       </c>
     </row>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="S23" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26T23:03:46Z</t>
+          <t>2026-09-27T23:13:02Z</t>
         </is>
       </c>
     </row>
@@ -2181,7 +2181,7 @@
       </c>
       <c r="S24" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26T23:03:46Z</t>
+          <t>2026-09-27T23:13:02Z</t>
         </is>
       </c>
     </row>
@@ -2266,7 +2266,7 @@
       </c>
       <c r="S25" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26T23:03:46Z</t>
+          <t>2026-09-27T23:13:02Z</t>
         </is>
       </c>
     </row>
@@ -2351,7 +2351,7 @@
       </c>
       <c r="S26" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26T23:03:46Z</t>
+          <t>2026-09-27T23:13:02Z</t>
         </is>
       </c>
     </row>
@@ -2436,7 +2436,7 @@
       </c>
       <c r="S27" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26T23:03:46Z</t>
+          <t>2026-09-27T23:13:02Z</t>
         </is>
       </c>
     </row>
@@ -2525,7 +2525,7 @@
       </c>
       <c r="S28" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26T23:03:46Z</t>
+          <t>2026-09-27T23:13:02Z</t>
         </is>
       </c>
     </row>
@@ -2614,7 +2614,7 @@
       </c>
       <c r="S29" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26T23:03:46Z</t>
+          <t>2026-09-27T23:13:02Z</t>
         </is>
       </c>
     </row>
@@ -2699,7 +2699,7 @@
       </c>
       <c r="S30" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26T23:03:46Z</t>
+          <t>2026-09-27T23:13:02Z</t>
         </is>
       </c>
     </row>
@@ -2788,7 +2788,7 @@
       </c>
       <c r="S31" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26T23:03:46Z</t>
+          <t>2026-09-27T23:13:02Z</t>
         </is>
       </c>
     </row>
@@ -2877,7 +2877,7 @@
       </c>
       <c r="S32" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26T23:03:46Z</t>
+          <t>2026-09-27T23:13:02Z</t>
         </is>
       </c>
     </row>
@@ -2962,7 +2962,7 @@
       </c>
       <c r="S33" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26T23:03:46Z</t>
+          <t>2026-09-27T23:13:02Z</t>
         </is>
       </c>
     </row>
@@ -3051,7 +3051,7 @@
       </c>
       <c r="S34" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26T23:03:46Z</t>
+          <t>2026-09-27T23:13:02Z</t>
         </is>
       </c>
     </row>
@@ -3140,7 +3140,7 @@
       </c>
       <c r="S35" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26T23:03:46Z</t>
+          <t>2026-09-27T23:13:02Z</t>
         </is>
       </c>
     </row>
@@ -3225,7 +3225,7 @@
       </c>
       <c r="S36" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26T23:03:46Z</t>
+          <t>2026-09-27T23:13:02Z</t>
         </is>
       </c>
     </row>
@@ -3314,7 +3314,7 @@
       </c>
       <c r="S37" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26T23:03:46Z</t>
+          <t>2026-09-27T23:13:02Z</t>
         </is>
       </c>
     </row>
@@ -3403,7 +3403,7 @@
       </c>
       <c r="S38" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26T23:03:46Z</t>
+          <t>2026-09-27T23:13:02Z</t>
         </is>
       </c>
     </row>
@@ -3488,7 +3488,7 @@
       </c>
       <c r="S39" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26T23:03:46Z</t>
+          <t>2026-09-27T23:13:02Z</t>
         </is>
       </c>
     </row>
@@ -3577,7 +3577,7 @@
       </c>
       <c r="S40" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26T23:03:46Z</t>
+          <t>2026-09-27T23:13:02Z</t>
         </is>
       </c>
     </row>
@@ -3666,7 +3666,7 @@
       </c>
       <c r="S41" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26T23:03:46Z</t>
+          <t>2026-09-27T23:13:02Z</t>
         </is>
       </c>
     </row>
@@ -3751,7 +3751,7 @@
       </c>
       <c r="S42" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26T23:03:46Z</t>
+          <t>2026-09-27T23:13:02Z</t>
         </is>
       </c>
     </row>
@@ -3840,7 +3840,7 @@
       </c>
       <c r="S43" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26T23:03:46Z</t>
+          <t>2026-09-27T23:13:02Z</t>
         </is>
       </c>
     </row>
@@ -3929,7 +3929,7 @@
       </c>
       <c r="S44" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26T23:03:46Z</t>
+          <t>2026-09-27T23:13:02Z</t>
         </is>
       </c>
     </row>
@@ -4014,7 +4014,7 @@
       </c>
       <c r="S45" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26T23:03:46Z</t>
+          <t>2026-09-27T23:13:02Z</t>
         </is>
       </c>
     </row>
@@ -4103,7 +4103,7 @@
       </c>
       <c r="S46" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26T23:03:46Z</t>
+          <t>2026-09-27T23:13:02Z</t>
         </is>
       </c>
     </row>
@@ -4192,7 +4192,7 @@
       </c>
       <c r="S47" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26T23:03:46Z</t>
+          <t>2026-09-27T23:13:02Z</t>
         </is>
       </c>
     </row>
@@ -4277,7 +4277,7 @@
       </c>
       <c r="S48" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26T23:03:46Z</t>
+          <t>2026-09-27T23:13:02Z</t>
         </is>
       </c>
     </row>
@@ -4366,7 +4366,7 @@
       </c>
       <c r="S49" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26T23:03:46Z</t>
+          <t>2026-09-27T23:13:02Z</t>
         </is>
       </c>
     </row>
@@ -4455,7 +4455,7 @@
       </c>
       <c r="S50" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26T23:03:46Z</t>
+          <t>2026-09-27T23:13:02Z</t>
         </is>
       </c>
     </row>
@@ -4540,7 +4540,7 @@
       </c>
       <c r="S51" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26T23:03:46Z</t>
+          <t>2026-09-27T23:13:02Z</t>
         </is>
       </c>
     </row>
@@ -4629,7 +4629,7 @@
       </c>
       <c r="S52" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26T23:03:46Z</t>
+          <t>2026-09-27T23:13:02Z</t>
         </is>
       </c>
     </row>
@@ -4718,7 +4718,7 @@
       </c>
       <c r="S53" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26T23:03:46Z</t>
+          <t>2026-09-27T23:13:02Z</t>
         </is>
       </c>
     </row>
@@ -4803,7 +4803,7 @@
       </c>
       <c r="S54" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26T23:03:46Z</t>
+          <t>2026-09-27T23:13:02Z</t>
         </is>
       </c>
     </row>
@@ -4892,7 +4892,7 @@
       </c>
       <c r="S55" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26T23:03:46Z</t>
+          <t>2026-09-27T23:13:02Z</t>
         </is>
       </c>
     </row>
@@ -4981,7 +4981,7 @@
       </c>
       <c r="S56" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26T23:03:46Z</t>
+          <t>2026-09-27T23:13:02Z</t>
         </is>
       </c>
     </row>
@@ -5070,7 +5070,7 @@
       </c>
       <c r="S57" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26T23:03:46Z</t>
+          <t>2026-09-27T23:13:02Z</t>
         </is>
       </c>
     </row>
@@ -5159,7 +5159,7 @@
       </c>
       <c r="S58" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26T23:03:46Z</t>
+          <t>2026-09-27T23:13:02Z</t>
         </is>
       </c>
     </row>
@@ -5248,7 +5248,7 @@
       </c>
       <c r="S59" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26T23:03:46Z</t>
+          <t>2026-09-27T23:13:02Z</t>
         </is>
       </c>
     </row>
@@ -5337,7 +5337,7 @@
       </c>
       <c r="S60" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26T23:03:46Z</t>
+          <t>2026-09-27T23:13:02Z</t>
         </is>
       </c>
     </row>
@@ -5426,7 +5426,7 @@
       </c>
       <c r="S61" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26T23:03:46Z</t>
+          <t>2026-09-27T23:13:02Z</t>
         </is>
       </c>
     </row>
@@ -5515,7 +5515,7 @@
       </c>
       <c r="S62" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26T23:03:46Z</t>
+          <t>2026-09-27T23:13:02Z</t>
         </is>
       </c>
     </row>
@@ -5604,7 +5604,7 @@
       </c>
       <c r="S63" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26T23:03:46Z</t>
+          <t>2026-09-27T23:13:02Z</t>
         </is>
       </c>
     </row>
@@ -5693,7 +5693,7 @@
       </c>
       <c r="S64" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26T23:03:46Z</t>
+          <t>2026-09-27T23:13:02Z</t>
         </is>
       </c>
     </row>
@@ -5782,7 +5782,7 @@
       </c>
       <c r="S65" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26T23:03:46Z</t>
+          <t>2026-09-27T23:13:02Z</t>
         </is>
       </c>
     </row>
@@ -5871,7 +5871,7 @@
       </c>
       <c r="S66" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26T23:03:46Z</t>
+          <t>2026-09-27T23:13:02Z</t>
         </is>
       </c>
     </row>
@@ -5960,7 +5960,7 @@
       </c>
       <c r="S67" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26T23:03:46Z</t>
+          <t>2026-09-27T23:13:02Z</t>
         </is>
       </c>
     </row>
@@ -6045,7 +6045,7 @@
       </c>
       <c r="S68" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26T23:03:46Z</t>
+          <t>2026-09-27T23:13:02Z</t>
         </is>
       </c>
     </row>
@@ -6130,7 +6130,7 @@
       </c>
       <c r="S69" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26T23:03:46Z</t>
+          <t>2026-09-27T23:13:02Z</t>
         </is>
       </c>
     </row>
@@ -6215,7 +6215,7 @@
       </c>
       <c r="S70" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26T23:03:46Z</t>
+          <t>2026-09-27T23:13:02Z</t>
         </is>
       </c>
     </row>
@@ -6300,7 +6300,7 @@
       </c>
       <c r="S71" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26T23:03:46Z</t>
+          <t>2026-09-27T23:13:02Z</t>
         </is>
       </c>
     </row>
@@ -6385,7 +6385,7 @@
       </c>
       <c r="S72" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26T23:03:46Z</t>
+          <t>2026-09-27T23:13:02Z</t>
         </is>
       </c>
     </row>
@@ -6470,7 +6470,7 @@
       </c>
       <c r="S73" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26T23:03:46Z</t>
+          <t>2026-09-27T23:13:02Z</t>
         </is>
       </c>
     </row>
@@ -6555,7 +6555,7 @@
       </c>
       <c r="S74" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26T23:03:46Z</t>
+          <t>2026-09-27T23:13:02Z</t>
         </is>
       </c>
     </row>
@@ -6640,7 +6640,7 @@
       </c>
       <c r="S75" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26T23:03:46Z</t>
+          <t>2026-09-27T23:13:02Z</t>
         </is>
       </c>
     </row>
@@ -6725,7 +6725,7 @@
       </c>
       <c r="S76" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26T23:03:46Z</t>
+          <t>2026-09-27T23:13:02Z</t>
         </is>
       </c>
     </row>
@@ -6810,7 +6810,7 @@
       </c>
       <c r="S77" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26T23:03:46Z</t>
+          <t>2026-09-27T23:13:02Z</t>
         </is>
       </c>
     </row>
@@ -6895,7 +6895,7 @@
       </c>
       <c r="S78" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26T23:03:46Z</t>
+          <t>2026-09-27T23:13:02Z</t>
         </is>
       </c>
     </row>
@@ -6980,7 +6980,7 @@
       </c>
       <c r="S79" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26T23:03:46Z</t>
+          <t>2026-09-27T23:13:02Z</t>
         </is>
       </c>
     </row>
@@ -7065,7 +7065,7 @@
       </c>
       <c r="S80" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26T23:03:46Z</t>
+          <t>2026-09-27T23:13:02Z</t>
         </is>
       </c>
     </row>
@@ -7150,7 +7150,7 @@
       </c>
       <c r="S81" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26T23:03:46Z</t>
+          <t>2026-09-27T23:13:02Z</t>
         </is>
       </c>
     </row>
@@ -7235,7 +7235,7 @@
       </c>
       <c r="S82" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26T23:03:46Z</t>
+          <t>2026-09-27T23:13:02Z</t>
         </is>
       </c>
     </row>
@@ -7320,7 +7320,7 @@
       </c>
       <c r="S83" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26T23:03:46Z</t>
+          <t>2026-09-27T23:13:02Z</t>
         </is>
       </c>
     </row>
@@ -7405,7 +7405,7 @@
       </c>
       <c r="S84" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26T23:03:46Z</t>
+          <t>2026-09-27T23:13:02Z</t>
         </is>
       </c>
     </row>
@@ -7490,7 +7490,7 @@
       </c>
       <c r="S85" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26T23:03:46Z</t>
+          <t>2026-09-27T23:13:02Z</t>
         </is>
       </c>
     </row>
@@ -7575,7 +7575,7 @@
       </c>
       <c r="S86" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26T23:03:46Z</t>
+          <t>2026-09-27T23:13:02Z</t>
         </is>
       </c>
     </row>
@@ -7660,7 +7660,7 @@
       </c>
       <c r="S87" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26T23:03:46Z</t>
+          <t>2026-09-27T23:13:02Z</t>
         </is>
       </c>
     </row>
@@ -7745,7 +7745,7 @@
       </c>
       <c r="S88" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26T23:03:46Z</t>
+          <t>2026-09-27T23:13:02Z</t>
         </is>
       </c>
     </row>
@@ -7834,7 +7834,7 @@
       </c>
       <c r="S89" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26T23:03:46Z</t>
+          <t>2026-09-27T23:13:02Z</t>
         </is>
       </c>
     </row>
@@ -7923,7 +7923,7 @@
       </c>
       <c r="S90" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26T23:03:46Z</t>
+          <t>2026-09-27T23:13:02Z</t>
         </is>
       </c>
     </row>
@@ -8008,7 +8008,7 @@
       </c>
       <c r="S91" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26T23:03:46Z</t>
+          <t>2026-09-27T23:13:02Z</t>
         </is>
       </c>
     </row>
@@ -8097,7 +8097,7 @@
       </c>
       <c r="S92" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26T23:03:46Z</t>
+          <t>2026-09-27T23:13:02Z</t>
         </is>
       </c>
     </row>
@@ -8186,7 +8186,7 @@
       </c>
       <c r="S93" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26T23:03:46Z</t>
+          <t>2026-09-27T23:13:02Z</t>
         </is>
       </c>
     </row>
@@ -8271,7 +8271,7 @@
       </c>
       <c r="S94" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26T23:03:46Z</t>
+          <t>2026-09-27T23:13:02Z</t>
         </is>
       </c>
     </row>
@@ -8360,7 +8360,7 @@
       </c>
       <c r="S95" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26T23:03:46Z</t>
+          <t>2026-09-27T23:13:02Z</t>
         </is>
       </c>
     </row>
@@ -8449,7 +8449,7 @@
       </c>
       <c r="S96" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26T23:03:46Z</t>
+          <t>2026-09-27T23:13:02Z</t>
         </is>
       </c>
     </row>
@@ -8534,7 +8534,7 @@
       </c>
       <c r="S97" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26T23:03:46Z</t>
+          <t>2026-09-27T23:13:02Z</t>
         </is>
       </c>
     </row>
@@ -8623,7 +8623,7 @@
       </c>
       <c r="S98" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26T23:03:46Z</t>
+          <t>2026-09-27T23:13:02Z</t>
         </is>
       </c>
     </row>
@@ -8712,7 +8712,7 @@
       </c>
       <c r="S99" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26T23:03:46Z</t>
+          <t>2026-09-27T23:13:02Z</t>
         </is>
       </c>
     </row>
@@ -8797,7 +8797,7 @@
       </c>
       <c r="S100" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26T23:03:46Z</t>
+          <t>2026-09-27T23:13:02Z</t>
         </is>
       </c>
     </row>
@@ -8886,7 +8886,7 @@
       </c>
       <c r="S101" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26T23:03:46Z</t>
+          <t>2026-09-27T23:13:02Z</t>
         </is>
       </c>
     </row>
@@ -8975,7 +8975,7 @@
       </c>
       <c r="S102" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26T23:03:46Z</t>
+          <t>2026-09-27T23:13:02Z</t>
         </is>
       </c>
     </row>
@@ -9060,7 +9060,7 @@
       </c>
       <c r="S103" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26T23:03:46Z</t>
+          <t>2026-09-27T23:13:02Z</t>
         </is>
       </c>
     </row>
@@ -9149,7 +9149,7 @@
       </c>
       <c r="S104" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26T23:03:46Z</t>
+          <t>2026-09-27T23:13:02Z</t>
         </is>
       </c>
     </row>
@@ -9238,7 +9238,7 @@
       </c>
       <c r="S105" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26T23:03:46Z</t>
+          <t>2026-09-27T23:13:02Z</t>
         </is>
       </c>
     </row>
@@ -9323,7 +9323,7 @@
       </c>
       <c r="S106" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26T23:03:46Z</t>
+          <t>2026-09-27T23:13:02Z</t>
         </is>
       </c>
     </row>
@@ -9412,7 +9412,7 @@
       </c>
       <c r="S107" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26T23:03:46Z</t>
+          <t>2026-09-27T23:13:02Z</t>
         </is>
       </c>
     </row>
@@ -9501,7 +9501,7 @@
       </c>
       <c r="S108" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26T23:03:46Z</t>
+          <t>2026-09-27T23:13:02Z</t>
         </is>
       </c>
     </row>
@@ -9586,7 +9586,7 @@
       </c>
       <c r="S109" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26T23:03:46Z</t>
+          <t>2026-09-27T23:13:02Z</t>
         </is>
       </c>
     </row>
@@ -9675,7 +9675,7 @@
       </c>
       <c r="S110" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26T23:03:46Z</t>
+          <t>2026-09-27T23:13:02Z</t>
         </is>
       </c>
     </row>
@@ -9764,7 +9764,7 @@
       </c>
       <c r="S111" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26T23:03:46Z</t>
+          <t>2026-09-27T23:13:02Z</t>
         </is>
       </c>
     </row>
@@ -9849,7 +9849,7 @@
       </c>
       <c r="S112" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26T23:03:46Z</t>
+          <t>2026-09-27T23:13:02Z</t>
         </is>
       </c>
     </row>
@@ -9938,7 +9938,7 @@
       </c>
       <c r="S113" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26T23:03:46Z</t>
+          <t>2026-09-27T23:13:02Z</t>
         </is>
       </c>
     </row>
@@ -10027,7 +10027,7 @@
       </c>
       <c r="S114" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26T23:03:46Z</t>
+          <t>2026-09-27T23:13:02Z</t>
         </is>
       </c>
     </row>
@@ -10112,7 +10112,7 @@
       </c>
       <c r="S115" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26T23:03:46Z</t>
+          <t>2026-09-27T23:13:02Z</t>
         </is>
       </c>
     </row>
@@ -10201,7 +10201,7 @@
       </c>
       <c r="S116" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26T23:03:46Z</t>
+          <t>2026-09-27T23:13:02Z</t>
         </is>
       </c>
     </row>
@@ -10290,7 +10290,7 @@
       </c>
       <c r="S117" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26T23:03:46Z</t>
+          <t>2026-09-27T23:13:02Z</t>
         </is>
       </c>
     </row>
@@ -10379,7 +10379,7 @@
       </c>
       <c r="S118" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26T23:03:46Z</t>
+          <t>2026-09-27T23:13:02Z</t>
         </is>
       </c>
     </row>
@@ -10468,7 +10468,7 @@
       </c>
       <c r="S119" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26T23:03:46Z</t>
+          <t>2026-09-27T23:13:02Z</t>
         </is>
       </c>
     </row>
@@ -10557,7 +10557,7 @@
       </c>
       <c r="S120" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26T23:03:46Z</t>
+          <t>2026-09-27T23:13:02Z</t>
         </is>
       </c>
     </row>
@@ -10646,7 +10646,7 @@
       </c>
       <c r="S121" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26T23:03:46Z</t>
+          <t>2026-09-27T23:13:02Z</t>
         </is>
       </c>
     </row>
@@ -10735,7 +10735,7 @@
       </c>
       <c r="S122" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26T23:03:46Z</t>
+          <t>2026-09-27T23:13:02Z</t>
         </is>
       </c>
     </row>
@@ -10824,7 +10824,7 @@
       </c>
       <c r="S123" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26T23:03:46Z</t>
+          <t>2026-09-27T23:13:02Z</t>
         </is>
       </c>
     </row>
@@ -10913,7 +10913,7 @@
       </c>
       <c r="S124" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26T23:03:46Z</t>
+          <t>2026-09-27T23:13:02Z</t>
         </is>
       </c>
     </row>
@@ -11002,7 +11002,7 @@
       </c>
       <c r="S125" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26T23:03:46Z</t>
+          <t>2026-09-27T23:13:02Z</t>
         </is>
       </c>
     </row>
@@ -11091,7 +11091,7 @@
       </c>
       <c r="S126" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26T23:03:46Z</t>
+          <t>2026-09-27T23:13:02Z</t>
         </is>
       </c>
     </row>
@@ -11180,7 +11180,7 @@
       </c>
       <c r="S127" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26T23:03:46Z</t>
+          <t>2026-09-27T23:13:02Z</t>
         </is>
       </c>
     </row>
@@ -11269,7 +11269,7 @@
       </c>
       <c r="S128" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26T23:03:46Z</t>
+          <t>2026-09-27T23:13:02Z</t>
         </is>
       </c>
     </row>
@@ -11354,7 +11354,7 @@
       </c>
       <c r="S129" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26T23:03:46Z</t>
+          <t>2026-09-27T23:13:02Z</t>
         </is>
       </c>
     </row>
@@ -11439,7 +11439,7 @@
       </c>
       <c r="S130" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26T23:03:46Z</t>
+          <t>2026-09-27T23:13:02Z</t>
         </is>
       </c>
     </row>
@@ -11524,7 +11524,7 @@
       </c>
       <c r="S131" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26T23:03:46Z</t>
+          <t>2026-09-27T23:13:02Z</t>
         </is>
       </c>
     </row>
@@ -11609,7 +11609,7 @@
       </c>
       <c r="S132" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26T23:03:46Z</t>
+          <t>2026-09-27T23:13:02Z</t>
         </is>
       </c>
     </row>
@@ -11694,7 +11694,7 @@
       </c>
       <c r="S133" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26T23:03:46Z</t>
+          <t>2026-09-27T23:13:02Z</t>
         </is>
       </c>
     </row>
@@ -11779,7 +11779,7 @@
       </c>
       <c r="S134" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26T23:03:46Z</t>
+          <t>2026-09-27T23:13:02Z</t>
         </is>
       </c>
     </row>
@@ -11864,7 +11864,7 @@
       </c>
       <c r="S135" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26T23:03:46Z</t>
+          <t>2026-09-27T23:13:02Z</t>
         </is>
       </c>
     </row>
@@ -11949,7 +11949,7 @@
       </c>
       <c r="S136" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26T23:03:46Z</t>
+          <t>2026-09-27T23:13:02Z</t>
         </is>
       </c>
     </row>
@@ -12034,7 +12034,7 @@
       </c>
       <c r="S137" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26T23:03:46Z</t>
+          <t>2026-09-27T23:13:02Z</t>
         </is>
       </c>
     </row>
@@ -12119,7 +12119,7 @@
       </c>
       <c r="S138" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26T23:03:46Z</t>
+          <t>2026-09-27T23:13:02Z</t>
         </is>
       </c>
     </row>
@@ -12204,7 +12204,7 @@
       </c>
       <c r="S139" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26T23:03:46Z</t>
+          <t>2026-09-27T23:13:02Z</t>
         </is>
       </c>
     </row>
@@ -12289,7 +12289,7 @@
       </c>
       <c r="S140" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26T23:03:46Z</t>
+          <t>2026-09-27T23:13:02Z</t>
         </is>
       </c>
     </row>
@@ -12374,7 +12374,7 @@
       </c>
       <c r="S141" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26T23:03:46Z</t>
+          <t>2026-09-27T23:13:02Z</t>
         </is>
       </c>
     </row>
@@ -12459,7 +12459,7 @@
       </c>
       <c r="S142" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26T23:03:46Z</t>
+          <t>2026-09-27T23:13:02Z</t>
         </is>
       </c>
     </row>
@@ -12544,7 +12544,7 @@
       </c>
       <c r="S143" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26T23:03:46Z</t>
+          <t>2026-09-27T23:13:02Z</t>
         </is>
       </c>
     </row>
@@ -12629,7 +12629,7 @@
       </c>
       <c r="S144" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26T23:03:46Z</t>
+          <t>2026-09-27T23:13:02Z</t>
         </is>
       </c>
     </row>
@@ -12714,7 +12714,7 @@
       </c>
       <c r="S145" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26T23:03:46Z</t>
+          <t>2026-09-27T23:13:02Z</t>
         </is>
       </c>
     </row>
@@ -12799,7 +12799,7 @@
       </c>
       <c r="S146" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26T23:03:46Z</t>
+          <t>2026-09-27T23:13:02Z</t>
         </is>
       </c>
     </row>
@@ -12884,7 +12884,7 @@
       </c>
       <c r="S147" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26T23:03:46Z</t>
+          <t>2026-09-27T23:13:02Z</t>
         </is>
       </c>
     </row>
@@ -12969,7 +12969,7 @@
       </c>
       <c r="S148" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26T23:03:46Z</t>
+          <t>2026-09-27T23:13:02Z</t>
         </is>
       </c>
     </row>
@@ -13054,7 +13054,7 @@
       </c>
       <c r="S149" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26T23:03:46Z</t>
+          <t>2026-09-27T23:13:02Z</t>
         </is>
       </c>
     </row>
@@ -13143,7 +13143,7 @@
       </c>
       <c r="S150" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26T23:03:46Z</t>
+          <t>2026-09-27T23:13:02Z</t>
         </is>
       </c>
     </row>
@@ -13232,7 +13232,7 @@
       </c>
       <c r="S151" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26T23:03:46Z</t>
+          <t>2026-09-27T23:13:02Z</t>
         </is>
       </c>
     </row>
@@ -13317,7 +13317,7 @@
       </c>
       <c r="S152" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26T23:03:46Z</t>
+          <t>2026-09-27T23:13:02Z</t>
         </is>
       </c>
     </row>
@@ -13406,7 +13406,7 @@
       </c>
       <c r="S153" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26T23:03:46Z</t>
+          <t>2026-09-27T23:13:02Z</t>
         </is>
       </c>
     </row>
@@ -13495,7 +13495,7 @@
       </c>
       <c r="S154" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26T23:03:46Z</t>
+          <t>2026-09-27T23:13:02Z</t>
         </is>
       </c>
     </row>
@@ -13580,7 +13580,7 @@
       </c>
       <c r="S155" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26T23:03:46Z</t>
+          <t>2026-09-27T23:13:02Z</t>
         </is>
       </c>
     </row>
@@ -13669,7 +13669,7 @@
       </c>
       <c r="S156" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26T23:03:46Z</t>
+          <t>2026-09-27T23:13:02Z</t>
         </is>
       </c>
     </row>
@@ -13758,7 +13758,7 @@
       </c>
       <c r="S157" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26T23:03:46Z</t>
+          <t>2026-09-27T23:13:02Z</t>
         </is>
       </c>
     </row>
@@ -13843,7 +13843,7 @@
       </c>
       <c r="S158" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26T23:03:46Z</t>
+          <t>2026-09-27T23:13:02Z</t>
         </is>
       </c>
     </row>
@@ -13932,7 +13932,7 @@
       </c>
       <c r="S159" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26T23:03:46Z</t>
+          <t>2026-09-27T23:13:02Z</t>
         </is>
       </c>
     </row>
@@ -14021,7 +14021,7 @@
       </c>
       <c r="S160" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26T23:03:46Z</t>
+          <t>2026-09-27T23:13:02Z</t>
         </is>
       </c>
     </row>
@@ -14106,7 +14106,7 @@
       </c>
       <c r="S161" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26T23:03:46Z</t>
+          <t>2026-09-27T23:13:02Z</t>
         </is>
       </c>
     </row>
@@ -14195,7 +14195,7 @@
       </c>
       <c r="S162" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26T23:03:46Z</t>
+          <t>2026-09-27T23:13:02Z</t>
         </is>
       </c>
     </row>
@@ -14284,7 +14284,7 @@
       </c>
       <c r="S163" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26T23:03:46Z</t>
+          <t>2026-09-27T23:13:02Z</t>
         </is>
       </c>
     </row>
@@ -14369,7 +14369,7 @@
       </c>
       <c r="S164" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26T23:03:46Z</t>
+          <t>2026-09-27T23:13:02Z</t>
         </is>
       </c>
     </row>
@@ -14458,7 +14458,7 @@
       </c>
       <c r="S165" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26T23:03:46Z</t>
+          <t>2026-09-27T23:13:02Z</t>
         </is>
       </c>
     </row>
@@ -14547,7 +14547,7 @@
       </c>
       <c r="S166" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26T23:03:46Z</t>
+          <t>2026-09-27T23:13:02Z</t>
         </is>
       </c>
     </row>
@@ -14632,7 +14632,7 @@
       </c>
       <c r="S167" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26T23:03:46Z</t>
+          <t>2026-09-27T23:13:02Z</t>
         </is>
       </c>
     </row>
@@ -14721,7 +14721,7 @@
       </c>
       <c r="S168" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26T23:03:46Z</t>
+          <t>2026-09-27T23:13:02Z</t>
         </is>
       </c>
     </row>
@@ -14810,7 +14810,7 @@
       </c>
       <c r="S169" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26T23:03:46Z</t>
+          <t>2026-09-27T23:13:02Z</t>
         </is>
       </c>
     </row>
@@ -14895,7 +14895,7 @@
       </c>
       <c r="S170" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26T23:03:46Z</t>
+          <t>2026-09-27T23:13:02Z</t>
         </is>
       </c>
     </row>
@@ -14984,7 +14984,7 @@
       </c>
       <c r="S171" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26T23:03:46Z</t>
+          <t>2026-09-27T23:13:02Z</t>
         </is>
       </c>
     </row>
@@ -15073,7 +15073,7 @@
       </c>
       <c r="S172" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26T23:03:46Z</t>
+          <t>2026-09-27T23:13:02Z</t>
         </is>
       </c>
     </row>
@@ -15158,7 +15158,7 @@
       </c>
       <c r="S173" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26T23:03:46Z</t>
+          <t>2026-09-27T23:13:02Z</t>
         </is>
       </c>
     </row>
@@ -15247,7 +15247,7 @@
       </c>
       <c r="S174" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26T23:03:46Z</t>
+          <t>2026-09-27T23:13:02Z</t>
         </is>
       </c>
     </row>
@@ -15336,7 +15336,7 @@
       </c>
       <c r="S175" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26T23:03:46Z</t>
+          <t>2026-09-27T23:13:02Z</t>
         </is>
       </c>
     </row>
@@ -15421,7 +15421,7 @@
       </c>
       <c r="S176" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26T23:03:46Z</t>
+          <t>2026-09-27T23:13:02Z</t>
         </is>
       </c>
     </row>
@@ -15510,7 +15510,7 @@
       </c>
       <c r="S177" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26T23:03:46Z</t>
+          <t>2026-09-27T23:13:02Z</t>
         </is>
       </c>
     </row>
@@ -15599,7 +15599,7 @@
       </c>
       <c r="S178" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26T23:03:46Z</t>
+          <t>2026-09-27T23:13:02Z</t>
         </is>
       </c>
     </row>
@@ -15688,7 +15688,7 @@
       </c>
       <c r="S179" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26T23:03:46Z</t>
+          <t>2026-09-27T23:13:02Z</t>
         </is>
       </c>
     </row>
@@ -15777,7 +15777,7 @@
       </c>
       <c r="S180" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26T23:03:46Z</t>
+          <t>2026-09-27T23:13:02Z</t>
         </is>
       </c>
     </row>
@@ -15866,7 +15866,7 @@
       </c>
       <c r="S181" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26T23:03:46Z</t>
+          <t>2026-09-27T23:13:02Z</t>
         </is>
       </c>
     </row>
@@ -15955,7 +15955,7 @@
       </c>
       <c r="S182" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26T23:03:46Z</t>
+          <t>2026-09-27T23:13:02Z</t>
         </is>
       </c>
     </row>
@@ -16044,7 +16044,7 @@
       </c>
       <c r="S183" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26T23:03:46Z</t>
+          <t>2026-09-27T23:13:02Z</t>
         </is>
       </c>
     </row>
@@ -16133,7 +16133,7 @@
       </c>
       <c r="S184" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26T23:03:46Z</t>
+          <t>2026-09-27T23:13:02Z</t>
         </is>
       </c>
     </row>
@@ -16222,7 +16222,7 @@
       </c>
       <c r="S185" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26T23:03:46Z</t>
+          <t>2026-09-27T23:13:02Z</t>
         </is>
       </c>
     </row>
@@ -16311,7 +16311,7 @@
       </c>
       <c r="S186" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26T23:03:46Z</t>
+          <t>2026-09-27T23:13:02Z</t>
         </is>
       </c>
     </row>
@@ -16400,7 +16400,7 @@
       </c>
       <c r="S187" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26T23:03:46Z</t>
+          <t>2026-09-27T23:13:02Z</t>
         </is>
       </c>
     </row>
@@ -16489,7 +16489,7 @@
       </c>
       <c r="S188" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26T23:03:46Z</t>
+          <t>2026-09-27T23:13:02Z</t>
         </is>
       </c>
     </row>
@@ -16578,7 +16578,7 @@
       </c>
       <c r="S189" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26T23:03:46Z</t>
+          <t>2026-09-27T23:13:02Z</t>
         </is>
       </c>
     </row>
@@ -16663,7 +16663,7 @@
       </c>
       <c r="S190" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26T23:03:46Z</t>
+          <t>2026-09-27T23:13:02Z</t>
         </is>
       </c>
     </row>
@@ -16748,7 +16748,7 @@
       </c>
       <c r="S191" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26T23:03:46Z</t>
+          <t>2026-09-27T23:13:02Z</t>
         </is>
       </c>
     </row>
@@ -16833,7 +16833,7 @@
       </c>
       <c r="S192" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26T23:03:46Z</t>
+          <t>2026-09-27T23:13:02Z</t>
         </is>
       </c>
     </row>
@@ -16918,7 +16918,7 @@
       </c>
       <c r="S193" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26T23:03:46Z</t>
+          <t>2026-09-27T23:13:02Z</t>
         </is>
       </c>
     </row>
@@ -17003,7 +17003,7 @@
       </c>
       <c r="S194" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26T23:03:46Z</t>
+          <t>2026-09-27T23:13:02Z</t>
         </is>
       </c>
     </row>
@@ -17088,7 +17088,7 @@
       </c>
       <c r="S195" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26T23:03:46Z</t>
+          <t>2026-09-27T23:13:02Z</t>
         </is>
       </c>
     </row>
@@ -17173,7 +17173,7 @@
       </c>
       <c r="S196" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26T23:03:46Z</t>
+          <t>2026-09-27T23:13:02Z</t>
         </is>
       </c>
     </row>
@@ -17258,7 +17258,7 @@
       </c>
       <c r="S197" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26T23:03:46Z</t>
+          <t>2026-09-27T23:13:02Z</t>
         </is>
       </c>
     </row>
@@ -17343,7 +17343,7 @@
       </c>
       <c r="S198" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26T23:03:46Z</t>
+          <t>2026-09-27T23:13:02Z</t>
         </is>
       </c>
     </row>
@@ -17428,7 +17428,7 @@
       </c>
       <c r="S199" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26T23:03:46Z</t>
+          <t>2026-09-27T23:13:02Z</t>
         </is>
       </c>
     </row>
@@ -17513,7 +17513,7 @@
       </c>
       <c r="S200" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26T23:03:46Z</t>
+          <t>2026-09-27T23:13:02Z</t>
         </is>
       </c>
     </row>
@@ -17598,7 +17598,7 @@
       </c>
       <c r="S201" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26T23:03:46Z</t>
+          <t>2026-09-27T23:13:02Z</t>
         </is>
       </c>
     </row>
@@ -17683,7 +17683,7 @@
       </c>
       <c r="S202" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26T23:03:46Z</t>
+          <t>2026-09-27T23:13:02Z</t>
         </is>
       </c>
     </row>
@@ -17768,7 +17768,7 @@
       </c>
       <c r="S203" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26T23:03:46Z</t>
+          <t>2026-09-27T23:13:02Z</t>
         </is>
       </c>
     </row>
@@ -17853,7 +17853,7 @@
       </c>
       <c r="S204" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26T23:03:46Z</t>
+          <t>2026-09-27T23:13:02Z</t>
         </is>
       </c>
     </row>
@@ -17938,7 +17938,7 @@
       </c>
       <c r="S205" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26T23:03:46Z</t>
+          <t>2026-09-27T23:13:02Z</t>
         </is>
       </c>
     </row>
@@ -18023,7 +18023,7 @@
       </c>
       <c r="S206" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26T23:03:46Z</t>
+          <t>2026-09-27T23:13:02Z</t>
         </is>
       </c>
     </row>
@@ -18108,7 +18108,7 @@
       </c>
       <c r="S207" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26T23:03:46Z</t>
+          <t>2026-09-27T23:13:02Z</t>
         </is>
       </c>
     </row>
@@ -18193,7 +18193,7 @@
       </c>
       <c r="S208" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26T23:03:46Z</t>
+          <t>2026-09-27T23:13:02Z</t>
         </is>
       </c>
     </row>
@@ -18278,7 +18278,7 @@
       </c>
       <c r="S209" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26T23:03:46Z</t>
+          <t>2026-09-27T23:13:02Z</t>
         </is>
       </c>
     </row>
@@ -18363,7 +18363,7 @@
       </c>
       <c r="S210" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26T23:03:46Z</t>
+          <t>2026-09-27T23:13:02Z</t>
         </is>
       </c>
     </row>
@@ -18452,7 +18452,7 @@
       </c>
       <c r="S211" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26T23:03:46Z</t>
+          <t>2026-09-27T23:13:02Z</t>
         </is>
       </c>
     </row>
@@ -18541,7 +18541,7 @@
       </c>
       <c r="S212" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26T23:03:46Z</t>
+          <t>2026-09-27T23:13:02Z</t>
         </is>
       </c>
     </row>
@@ -18626,7 +18626,7 @@
       </c>
       <c r="S213" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26T23:03:46Z</t>
+          <t>2026-09-27T23:13:02Z</t>
         </is>
       </c>
     </row>
@@ -18715,7 +18715,7 @@
       </c>
       <c r="S214" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26T23:03:46Z</t>
+          <t>2026-09-27T23:13:02Z</t>
         </is>
       </c>
     </row>
@@ -18804,7 +18804,7 @@
       </c>
       <c r="S215" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26T23:03:46Z</t>
+          <t>2026-09-27T23:13:02Z</t>
         </is>
       </c>
     </row>
@@ -18889,7 +18889,7 @@
       </c>
       <c r="S216" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26T23:03:46Z</t>
+          <t>2026-09-27T23:13:02Z</t>
         </is>
       </c>
     </row>
@@ -18978,7 +18978,7 @@
       </c>
       <c r="S217" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26T23:03:46Z</t>
+          <t>2026-09-27T23:13:02Z</t>
         </is>
       </c>
     </row>
@@ -19067,7 +19067,7 @@
       </c>
       <c r="S218" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26T23:03:46Z</t>
+          <t>2026-09-27T23:13:02Z</t>
         </is>
       </c>
     </row>
@@ -19152,7 +19152,7 @@
       </c>
       <c r="S219" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26T23:03:46Z</t>
+          <t>2026-09-27T23:13:02Z</t>
         </is>
       </c>
     </row>
@@ -19241,7 +19241,7 @@
       </c>
       <c r="S220" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26T23:03:46Z</t>
+          <t>2026-09-27T23:13:02Z</t>
         </is>
       </c>
     </row>
@@ -19330,7 +19330,7 @@
       </c>
       <c r="S221" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26T23:03:46Z</t>
+          <t>2026-09-27T23:13:02Z</t>
         </is>
       </c>
     </row>
@@ -19415,7 +19415,7 @@
       </c>
       <c r="S222" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26T23:03:46Z</t>
+          <t>2026-09-27T23:13:02Z</t>
         </is>
       </c>
     </row>
@@ -19504,7 +19504,7 @@
       </c>
       <c r="S223" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26T23:03:46Z</t>
+          <t>2026-09-27T23:13:02Z</t>
         </is>
       </c>
     </row>
@@ -19593,7 +19593,7 @@
       </c>
       <c r="S224" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26T23:03:46Z</t>
+          <t>2026-09-27T23:13:02Z</t>
         </is>
       </c>
     </row>
@@ -19678,7 +19678,7 @@
       </c>
       <c r="S225" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26T23:03:46Z</t>
+          <t>2026-09-27T23:13:02Z</t>
         </is>
       </c>
     </row>
@@ -19767,7 +19767,7 @@
       </c>
       <c r="S226" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26T23:03:46Z</t>
+          <t>2026-09-27T23:13:02Z</t>
         </is>
       </c>
     </row>
@@ -19856,7 +19856,7 @@
       </c>
       <c r="S227" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26T23:03:46Z</t>
+          <t>2026-09-27T23:13:02Z</t>
         </is>
       </c>
     </row>
@@ -19941,7 +19941,7 @@
       </c>
       <c r="S228" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26T23:03:46Z</t>
+          <t>2026-09-27T23:13:02Z</t>
         </is>
       </c>
     </row>
@@ -20030,7 +20030,7 @@
       </c>
       <c r="S229" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26T23:03:46Z</t>
+          <t>2026-09-27T23:13:02Z</t>
         </is>
       </c>
     </row>
@@ -20119,7 +20119,7 @@
       </c>
       <c r="S230" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26T23:03:46Z</t>
+          <t>2026-09-27T23:13:02Z</t>
         </is>
       </c>
     </row>
@@ -20204,7 +20204,7 @@
       </c>
       <c r="S231" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26T23:03:46Z</t>
+          <t>2026-09-27T23:13:02Z</t>
         </is>
       </c>
     </row>
@@ -20293,7 +20293,7 @@
       </c>
       <c r="S232" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26T23:03:46Z</t>
+          <t>2026-09-27T23:13:02Z</t>
         </is>
       </c>
     </row>
@@ -20382,7 +20382,7 @@
       </c>
       <c r="S233" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26T23:03:46Z</t>
+          <t>2026-09-27T23:13:02Z</t>
         </is>
       </c>
     </row>
@@ -20467,7 +20467,7 @@
       </c>
       <c r="S234" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26T23:03:46Z</t>
+          <t>2026-09-27T23:13:02Z</t>
         </is>
       </c>
     </row>
@@ -20556,7 +20556,7 @@
       </c>
       <c r="S235" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26T23:03:46Z</t>
+          <t>2026-09-27T23:13:02Z</t>
         </is>
       </c>
     </row>
@@ -20645,7 +20645,7 @@
       </c>
       <c r="S236" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26T23:03:46Z</t>
+          <t>2026-09-27T23:13:02Z</t>
         </is>
       </c>
     </row>
@@ -20730,7 +20730,7 @@
       </c>
       <c r="S237" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26T23:03:46Z</t>
+          <t>2026-09-27T23:13:02Z</t>
         </is>
       </c>
     </row>
@@ -20819,7 +20819,7 @@
       </c>
       <c r="S238" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26T23:03:46Z</t>
+          <t>2026-09-27T23:13:02Z</t>
         </is>
       </c>
     </row>
@@ -20908,7 +20908,7 @@
       </c>
       <c r="S239" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26T23:03:46Z</t>
+          <t>2026-09-27T23:13:02Z</t>
         </is>
       </c>
     </row>
@@ -20997,7 +20997,7 @@
       </c>
       <c r="S240" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26T23:03:46Z</t>
+          <t>2026-09-27T23:13:02Z</t>
         </is>
       </c>
     </row>
@@ -21086,7 +21086,7 @@
       </c>
       <c r="S241" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26T23:03:46Z</t>
+          <t>2026-09-27T23:13:02Z</t>
         </is>
       </c>
     </row>
@@ -21175,7 +21175,7 @@
       </c>
       <c r="S242" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26T23:03:46Z</t>
+          <t>2026-09-27T23:13:02Z</t>
         </is>
       </c>
     </row>
@@ -21264,7 +21264,7 @@
       </c>
       <c r="S243" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26T23:03:46Z</t>
+          <t>2026-09-27T23:13:02Z</t>
         </is>
       </c>
     </row>
@@ -21353,7 +21353,7 @@
       </c>
       <c r="S244" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26T23:03:46Z</t>
+          <t>2026-09-27T23:13:02Z</t>
         </is>
       </c>
     </row>
@@ -21442,7 +21442,7 @@
       </c>
       <c r="S245" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26T23:03:46Z</t>
+          <t>2026-09-27T23:13:02Z</t>
         </is>
       </c>
     </row>
@@ -21531,7 +21531,7 @@
       </c>
       <c r="S246" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26T23:03:46Z</t>
+          <t>2026-09-27T23:13:02Z</t>
         </is>
       </c>
     </row>
@@ -21620,7 +21620,7 @@
       </c>
       <c r="S247" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26T23:03:46Z</t>
+          <t>2026-09-27T23:13:02Z</t>
         </is>
       </c>
     </row>
@@ -21709,7 +21709,7 @@
       </c>
       <c r="S248" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26T23:03:46Z</t>
+          <t>2026-09-27T23:13:02Z</t>
         </is>
       </c>
     </row>
@@ -21798,7 +21798,7 @@
       </c>
       <c r="S249" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26T23:03:46Z</t>
+          <t>2026-09-27T23:13:02Z</t>
         </is>
       </c>
     </row>
@@ -21887,7 +21887,7 @@
       </c>
       <c r="S250" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26T23:03:46Z</t>
+          <t>2026-09-27T23:13:02Z</t>
         </is>
       </c>
     </row>
@@ -22019,7 +22019,7 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26T23:03:46Z</t>
+          <t>2026-09-27T23:13:02Z</t>
         </is>
       </c>
     </row>
@@ -22099,7 +22099,7 @@
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>{"dataset_id": "bcv_pib_sector_institucional_anual", "title": "Producto interno bruto por sector institucional anual", "table": "Variaciones porcentuales", "source_file": "5_2_1_si_anual.xlsx", "base": "2007", "price_type": "Precios constantes", "measure": "Variación porcentual interanual", "frequency": "Anual", "period": "2025", "year": 2025, "quarter": null, "classification": "Sector institucional", "component": "Impuestos netos sobre los productos", "value": 10.600260421283764, "unit": "Porcentaje", "status": "Preliminar", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/cuentas_macroeconomicas/5_2_1_si_anual.xlsx", "fetched_at": "2026-09-26T23:03:46Z"}</t>
+          <t>{"dataset_id": "bcv_pib_sector_institucional_anual", "title": "Producto interno bruto por sector institucional anual", "table": "Variaciones porcentuales", "source_file": "5_2_1_si_anual.xlsx", "base": "2007", "price_type": "Precios constantes", "measure": "Variación porcentual interanual", "frequency": "Anual", "period": "2025", "year": 2025, "quarter": null, "classification": "Sector institucional", "component": "Impuestos netos sobre los productos", "value": 10.600260421283764, "unit": "Porcentaje", "status": "Preliminar", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/cuentas_macroeconomicas/5_2_1_si_anual.xlsx", "fetched_at": "2026-09-27T23:13:02Z"}</t>
         </is>
       </c>
     </row>

--- a/assets/data/bcv/excel/ove_bcv_pib_sector_institucional_anual.xlsx
+++ b/assets/data/bcv/excel/ove_bcv_pib_sector_institucional_anual.xlsx
@@ -736,7 +736,7 @@
       </c>
       <c r="S7" s="4" t="inlineStr">
         <is>
-          <t>2026-09-27T23:13:02Z</t>
+          <t>2026-09-29T00:28:22Z</t>
         </is>
       </c>
     </row>
@@ -821,7 +821,7 @@
       </c>
       <c r="S8" s="4" t="inlineStr">
         <is>
-          <t>2026-09-27T23:13:02Z</t>
+          <t>2026-09-29T00:28:22Z</t>
         </is>
       </c>
     </row>
@@ -906,7 +906,7 @@
       </c>
       <c r="S9" s="4" t="inlineStr">
         <is>
-          <t>2026-09-27T23:13:02Z</t>
+          <t>2026-09-29T00:28:22Z</t>
         </is>
       </c>
     </row>
@@ -991,7 +991,7 @@
       </c>
       <c r="S10" s="4" t="inlineStr">
         <is>
-          <t>2026-09-27T23:13:02Z</t>
+          <t>2026-09-29T00:28:22Z</t>
         </is>
       </c>
     </row>
@@ -1076,7 +1076,7 @@
       </c>
       <c r="S11" s="4" t="inlineStr">
         <is>
-          <t>2026-09-27T23:13:02Z</t>
+          <t>2026-09-29T00:28:22Z</t>
         </is>
       </c>
     </row>
@@ -1161,7 +1161,7 @@
       </c>
       <c r="S12" s="4" t="inlineStr">
         <is>
-          <t>2026-09-27T23:13:02Z</t>
+          <t>2026-09-29T00:28:22Z</t>
         </is>
       </c>
     </row>
@@ -1246,7 +1246,7 @@
       </c>
       <c r="S13" s="4" t="inlineStr">
         <is>
-          <t>2026-09-27T23:13:02Z</t>
+          <t>2026-09-29T00:28:22Z</t>
         </is>
       </c>
     </row>
@@ -1331,7 +1331,7 @@
       </c>
       <c r="S14" s="4" t="inlineStr">
         <is>
-          <t>2026-09-27T23:13:02Z</t>
+          <t>2026-09-29T00:28:22Z</t>
         </is>
       </c>
     </row>
@@ -1416,7 +1416,7 @@
       </c>
       <c r="S15" s="4" t="inlineStr">
         <is>
-          <t>2026-09-27T23:13:02Z</t>
+          <t>2026-09-29T00:28:22Z</t>
         </is>
       </c>
     </row>
@@ -1501,7 +1501,7 @@
       </c>
       <c r="S16" s="4" t="inlineStr">
         <is>
-          <t>2026-09-27T23:13:02Z</t>
+          <t>2026-09-29T00:28:22Z</t>
         </is>
       </c>
     </row>
@@ -1586,7 +1586,7 @@
       </c>
       <c r="S17" s="4" t="inlineStr">
         <is>
-          <t>2026-09-27T23:13:02Z</t>
+          <t>2026-09-29T00:28:22Z</t>
         </is>
       </c>
     </row>
@@ -1671,7 +1671,7 @@
       </c>
       <c r="S18" s="4" t="inlineStr">
         <is>
-          <t>2026-09-27T23:13:02Z</t>
+          <t>2026-09-29T00:28:22Z</t>
         </is>
       </c>
     </row>
@@ -1756,7 +1756,7 @@
       </c>
       <c r="S19" s="4" t="inlineStr">
         <is>
-          <t>2026-09-27T23:13:02Z</t>
+          <t>2026-09-29T00:28:22Z</t>
         </is>
       </c>
     </row>
@@ -1841,7 +1841,7 @@
       </c>
       <c r="S20" s="4" t="inlineStr">
         <is>
-          <t>2026-09-27T23:13:02Z</t>
+          <t>2026-09-29T00:28:22Z</t>
         </is>
       </c>
     </row>
@@ -1926,7 +1926,7 @@
       </c>
       <c r="S21" s="4" t="inlineStr">
         <is>
-          <t>2026-09-27T23:13:02Z</t>
+          <t>2026-09-29T00:28:22Z</t>
         </is>
       </c>
     </row>
@@ -2011,7 +2011,7 @@
       </c>
       <c r="S22" s="4" t="inlineStr">
         <is>
-          <t>2026-09-27T23:13:02Z</t>
+          <t>2026-09-29T00:28:22Z</t>
         </is>
       </c>
     </row>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="S23" s="4" t="inlineStr">
         <is>
-          <t>2026-09-27T23:13:02Z</t>
+          <t>2026-09-29T00:28:22Z</t>
         </is>
       </c>
     </row>
@@ -2181,7 +2181,7 @@
       </c>
       <c r="S24" s="4" t="inlineStr">
         <is>
-          <t>2026-09-27T23:13:02Z</t>
+          <t>2026-09-29T00:28:22Z</t>
         </is>
       </c>
     </row>
@@ -2266,7 +2266,7 @@
       </c>
       <c r="S25" s="4" t="inlineStr">
         <is>
-          <t>2026-09-27T23:13:02Z</t>
+          <t>2026-09-29T00:28:22Z</t>
         </is>
       </c>
     </row>
@@ -2351,7 +2351,7 @@
       </c>
       <c r="S26" s="4" t="inlineStr">
         <is>
-          <t>2026-09-27T23:13:02Z</t>
+          <t>2026-09-29T00:28:22Z</t>
         </is>
       </c>
     </row>
@@ -2436,7 +2436,7 @@
       </c>
       <c r="S27" s="4" t="inlineStr">
         <is>
-          <t>2026-09-27T23:13:02Z</t>
+          <t>2026-09-29T00:28:22Z</t>
         </is>
       </c>
     </row>
@@ -2525,7 +2525,7 @@
       </c>
       <c r="S28" s="4" t="inlineStr">
         <is>
-          <t>2026-09-27T23:13:02Z</t>
+          <t>2026-09-29T00:28:22Z</t>
         </is>
       </c>
     </row>
@@ -2614,7 +2614,7 @@
       </c>
       <c r="S29" s="4" t="inlineStr">
         <is>
-          <t>2026-09-27T23:13:02Z</t>
+          <t>2026-09-29T00:28:22Z</t>
         </is>
       </c>
     </row>
@@ -2699,7 +2699,7 @@
       </c>
       <c r="S30" s="4" t="inlineStr">
         <is>
-          <t>2026-09-27T23:13:02Z</t>
+          <t>2026-09-29T00:28:22Z</t>
         </is>
       </c>
     </row>
@@ -2788,7 +2788,7 @@
       </c>
       <c r="S31" s="4" t="inlineStr">
         <is>
-          <t>2026-09-27T23:13:02Z</t>
+          <t>2026-09-29T00:28:22Z</t>
         </is>
       </c>
     </row>
@@ -2877,7 +2877,7 @@
       </c>
       <c r="S32" s="4" t="inlineStr">
         <is>
-          <t>2026-09-27T23:13:02Z</t>
+          <t>2026-09-29T00:28:22Z</t>
         </is>
       </c>
     </row>
@@ -2962,7 +2962,7 @@
       </c>
       <c r="S33" s="4" t="inlineStr">
         <is>
-          <t>2026-09-27T23:13:02Z</t>
+          <t>2026-09-29T00:28:22Z</t>
         </is>
       </c>
     </row>
@@ -3051,7 +3051,7 @@
       </c>
       <c r="S34" s="4" t="inlineStr">
         <is>
-          <t>2026-09-27T23:13:02Z</t>
+          <t>2026-09-29T00:28:22Z</t>
         </is>
       </c>
     </row>
@@ -3140,7 +3140,7 @@
       </c>
       <c r="S35" s="4" t="inlineStr">
         <is>
-          <t>2026-09-27T23:13:02Z</t>
+          <t>2026-09-29T00:28:22Z</t>
         </is>
       </c>
     </row>
@@ -3225,7 +3225,7 @@
       </c>
       <c r="S36" s="4" t="inlineStr">
         <is>
-          <t>2026-09-27T23:13:02Z</t>
+          <t>2026-09-29T00:28:22Z</t>
         </is>
       </c>
     </row>
@@ -3314,7 +3314,7 @@
       </c>
       <c r="S37" s="4" t="inlineStr">
         <is>
-          <t>2026-09-27T23:13:02Z</t>
+          <t>2026-09-29T00:28:22Z</t>
         </is>
       </c>
     </row>
@@ -3403,7 +3403,7 @@
       </c>
       <c r="S38" s="4" t="inlineStr">
         <is>
-          <t>2026-09-27T23:13:02Z</t>
+          <t>2026-09-29T00:28:22Z</t>
         </is>
       </c>
     </row>
@@ -3488,7 +3488,7 @@
       </c>
       <c r="S39" s="4" t="inlineStr">
         <is>
-          <t>2026-09-27T23:13:02Z</t>
+          <t>2026-09-29T00:28:22Z</t>
         </is>
       </c>
     </row>
@@ -3577,7 +3577,7 @@
       </c>
       <c r="S40" s="4" t="inlineStr">
         <is>
-          <t>2026-09-27T23:13:02Z</t>
+          <t>2026-09-29T00:28:22Z</t>
         </is>
       </c>
     </row>
@@ -3666,7 +3666,7 @@
       </c>
       <c r="S41" s="4" t="inlineStr">
         <is>
-          <t>2026-09-27T23:13:02Z</t>
+          <t>2026-09-29T00:28:22Z</t>
         </is>
       </c>
     </row>
@@ -3751,7 +3751,7 @@
       </c>
       <c r="S42" s="4" t="inlineStr">
         <is>
-          <t>2026-09-27T23:13:02Z</t>
+          <t>2026-09-29T00:28:22Z</t>
         </is>
       </c>
     </row>
@@ -3840,7 +3840,7 @@
       </c>
       <c r="S43" s="4" t="inlineStr">
         <is>
-          <t>2026-09-27T23:13:02Z</t>
+          <t>2026-09-29T00:28:22Z</t>
         </is>
       </c>
     </row>
@@ -3929,7 +3929,7 @@
       </c>
       <c r="S44" s="4" t="inlineStr">
         <is>
-          <t>2026-09-27T23:13:02Z</t>
+          <t>2026-09-29T00:28:22Z</t>
         </is>
       </c>
     </row>
@@ -4014,7 +4014,7 @@
       </c>
       <c r="S45" s="4" t="inlineStr">
         <is>
-          <t>2026-09-27T23:13:02Z</t>
+          <t>2026-09-29T00:28:22Z</t>
         </is>
       </c>
     </row>
@@ -4103,7 +4103,7 @@
       </c>
       <c r="S46" s="4" t="inlineStr">
         <is>
-          <t>2026-09-27T23:13:02Z</t>
+          <t>2026-09-29T00:28:22Z</t>
         </is>
       </c>
     </row>
@@ -4192,7 +4192,7 @@
       </c>
       <c r="S47" s="4" t="inlineStr">
         <is>
-          <t>2026-09-27T23:13:02Z</t>
+          <t>2026-09-29T00:28:22Z</t>
         </is>
       </c>
     </row>
@@ -4277,7 +4277,7 @@
       </c>
       <c r="S48" s="4" t="inlineStr">
         <is>
-          <t>2026-09-27T23:13:02Z</t>
+          <t>2026-09-29T00:28:22Z</t>
         </is>
       </c>
     </row>
@@ -4366,7 +4366,7 @@
       </c>
       <c r="S49" s="4" t="inlineStr">
         <is>
-          <t>2026-09-27T23:13:02Z</t>
+          <t>2026-09-29T00:28:22Z</t>
         </is>
       </c>
     </row>
@@ -4455,7 +4455,7 @@
       </c>
       <c r="S50" s="4" t="inlineStr">
         <is>
-          <t>2026-09-27T23:13:02Z</t>
+          <t>2026-09-29T00:28:22Z</t>
         </is>
       </c>
     </row>
@@ -4540,7 +4540,7 @@
       </c>
       <c r="S51" s="4" t="inlineStr">
         <is>
-          <t>2026-09-27T23:13:02Z</t>
+          <t>2026-09-29T00:28:22Z</t>
         </is>
       </c>
     </row>
@@ -4629,7 +4629,7 @@
       </c>
       <c r="S52" s="4" t="inlineStr">
         <is>
-          <t>2026-09-27T23:13:02Z</t>
+          <t>2026-09-29T00:28:22Z</t>
         </is>
       </c>
     </row>
@@ -4718,7 +4718,7 @@
       </c>
       <c r="S53" s="4" t="inlineStr">
         <is>
-          <t>2026-09-27T23:13:02Z</t>
+          <t>2026-09-29T00:28:22Z</t>
         </is>
       </c>
     </row>
@@ -4803,7 +4803,7 @@
       </c>
       <c r="S54" s="4" t="inlineStr">
         <is>
-          <t>2026-09-27T23:13:02Z</t>
+          <t>2026-09-29T00:28:22Z</t>
         </is>
       </c>
     </row>
@@ -4892,7 +4892,7 @@
       </c>
       <c r="S55" s="4" t="inlineStr">
         <is>
-          <t>2026-09-27T23:13:02Z</t>
+          <t>2026-09-29T00:28:22Z</t>
         </is>
       </c>
     </row>
@@ -4981,7 +4981,7 @@
       </c>
       <c r="S56" s="4" t="inlineStr">
         <is>
-          <t>2026-09-27T23:13:02Z</t>
+          <t>2026-09-29T00:28:22Z</t>
         </is>
       </c>
     </row>
@@ -5070,7 +5070,7 @@
       </c>
       <c r="S57" s="4" t="inlineStr">
         <is>
-          <t>2026-09-27T23:13:02Z</t>
+          <t>2026-09-29T00:28:22Z</t>
         </is>
       </c>
     </row>
@@ -5159,7 +5159,7 @@
       </c>
       <c r="S58" s="4" t="inlineStr">
         <is>
-          <t>2026-09-27T23:13:02Z</t>
+          <t>2026-09-29T00:28:22Z</t>
         </is>
       </c>
     </row>
@@ -5248,7 +5248,7 @@
       </c>
       <c r="S59" s="4" t="inlineStr">
         <is>
-          <t>2026-09-27T23:13:02Z</t>
+          <t>2026-09-29T00:28:22Z</t>
         </is>
       </c>
     </row>
@@ -5337,7 +5337,7 @@
       </c>
       <c r="S60" s="4" t="inlineStr">
         <is>
-          <t>2026-09-27T23:13:02Z</t>
+          <t>2026-09-29T00:28:22Z</t>
         </is>
       </c>
     </row>
@@ -5426,7 +5426,7 @@
       </c>
       <c r="S61" s="4" t="inlineStr">
         <is>
-          <t>2026-09-27T23:13:02Z</t>
+          <t>2026-09-29T00:28:22Z</t>
         </is>
       </c>
     </row>
@@ -5515,7 +5515,7 @@
       </c>
       <c r="S62" s="4" t="inlineStr">
         <is>
-          <t>2026-09-27T23:13:02Z</t>
+          <t>2026-09-29T00:28:22Z</t>
         </is>
       </c>
     </row>
@@ -5604,7 +5604,7 @@
       </c>
       <c r="S63" s="4" t="inlineStr">
         <is>
-          <t>2026-09-27T23:13:02Z</t>
+          <t>2026-09-29T00:28:22Z</t>
         </is>
       </c>
     </row>
@@ -5693,7 +5693,7 @@
       </c>
       <c r="S64" s="4" t="inlineStr">
         <is>
-          <t>2026-09-27T23:13:02Z</t>
+          <t>2026-09-29T00:28:22Z</t>
         </is>
       </c>
     </row>
@@ -5782,7 +5782,7 @@
       </c>
       <c r="S65" s="4" t="inlineStr">
         <is>
-          <t>2026-09-27T23:13:02Z</t>
+          <t>2026-09-29T00:28:22Z</t>
         </is>
       </c>
     </row>
@@ -5871,7 +5871,7 @@
       </c>
       <c r="S66" s="4" t="inlineStr">
         <is>
-          <t>2026-09-27T23:13:02Z</t>
+          <t>2026-09-29T00:28:22Z</t>
         </is>
       </c>
     </row>
@@ -5960,7 +5960,7 @@
       </c>
       <c r="S67" s="4" t="inlineStr">
         <is>
-          <t>2026-09-27T23:13:02Z</t>
+          <t>2026-09-29T00:28:22Z</t>
         </is>
       </c>
     </row>
@@ -6045,7 +6045,7 @@
       </c>
       <c r="S68" s="4" t="inlineStr">
         <is>
-          <t>2026-09-27T23:13:02Z</t>
+          <t>2026-09-29T00:28:22Z</t>
         </is>
       </c>
     </row>
@@ -6130,7 +6130,7 @@
       </c>
       <c r="S69" s="4" t="inlineStr">
         <is>
-          <t>2026-09-27T23:13:02Z</t>
+          <t>2026-09-29T00:28:22Z</t>
         </is>
       </c>
     </row>
@@ -6215,7 +6215,7 @@
       </c>
       <c r="S70" s="4" t="inlineStr">
         <is>
-          <t>2026-09-27T23:13:02Z</t>
+          <t>2026-09-29T00:28:22Z</t>
         </is>
       </c>
     </row>
@@ -6300,7 +6300,7 @@
       </c>
       <c r="S71" s="4" t="inlineStr">
         <is>
-          <t>2026-09-27T23:13:02Z</t>
+          <t>2026-09-29T00:28:22Z</t>
         </is>
       </c>
     </row>
@@ -6385,7 +6385,7 @@
       </c>
       <c r="S72" s="4" t="inlineStr">
         <is>
-          <t>2026-09-27T23:13:02Z</t>
+          <t>2026-09-29T00:28:22Z</t>
         </is>
       </c>
     </row>
@@ -6470,7 +6470,7 @@
       </c>
       <c r="S73" s="4" t="inlineStr">
         <is>
-          <t>2026-09-27T23:13:02Z</t>
+          <t>2026-09-29T00:28:22Z</t>
         </is>
       </c>
     </row>
@@ -6555,7 +6555,7 @@
       </c>
       <c r="S74" s="4" t="inlineStr">
         <is>
-          <t>2026-09-27T23:13:02Z</t>
+          <t>2026-09-29T00:28:22Z</t>
         </is>
       </c>
     </row>
@@ -6640,7 +6640,7 @@
       </c>
       <c r="S75" s="4" t="inlineStr">
         <is>
-          <t>2026-09-27T23:13:02Z</t>
+          <t>2026-09-29T00:28:22Z</t>
         </is>
       </c>
     </row>
@@ -6725,7 +6725,7 @@
       </c>
       <c r="S76" s="4" t="inlineStr">
         <is>
-          <t>2026-09-27T23:13:02Z</t>
+          <t>2026-09-29T00:28:22Z</t>
         </is>
       </c>
     </row>
@@ -6810,7 +6810,7 @@
       </c>
       <c r="S77" s="4" t="inlineStr">
         <is>
-          <t>2026-09-27T23:13:02Z</t>
+          <t>2026-09-29T00:28:22Z</t>
         </is>
       </c>
     </row>
@@ -6895,7 +6895,7 @@
       </c>
       <c r="S78" s="4" t="inlineStr">
         <is>
-          <t>2026-09-27T23:13:02Z</t>
+          <t>2026-09-29T00:28:22Z</t>
         </is>
       </c>
     </row>
@@ -6980,7 +6980,7 @@
       </c>
       <c r="S79" s="4" t="inlineStr">
         <is>
-          <t>2026-09-27T23:13:02Z</t>
+          <t>2026-09-29T00:28:22Z</t>
         </is>
       </c>
     </row>
@@ -7065,7 +7065,7 @@
       </c>
       <c r="S80" s="4" t="inlineStr">
         <is>
-          <t>2026-09-27T23:13:02Z</t>
+          <t>2026-09-29T00:28:22Z</t>
         </is>
       </c>
     </row>
@@ -7150,7 +7150,7 @@
       </c>
       <c r="S81" s="4" t="inlineStr">
         <is>
-          <t>2026-09-27T23:13:02Z</t>
+          <t>2026-09-29T00:28:22Z</t>
         </is>
       </c>
     </row>
@@ -7235,7 +7235,7 @@
       </c>
       <c r="S82" s="4" t="inlineStr">
         <is>
-          <t>2026-09-27T23:13:02Z</t>
+          <t>2026-09-29T00:28:22Z</t>
         </is>
       </c>
     </row>
@@ -7320,7 +7320,7 @@
       </c>
       <c r="S83" s="4" t="inlineStr">
         <is>
-          <t>2026-09-27T23:13:02Z</t>
+          <t>2026-09-29T00:28:22Z</t>
         </is>
       </c>
     </row>
@@ -7405,7 +7405,7 @@
       </c>
       <c r="S84" s="4" t="inlineStr">
         <is>
-          <t>2026-09-27T23:13:02Z</t>
+          <t>2026-09-29T00:28:22Z</t>
         </is>
       </c>
     </row>
@@ -7490,7 +7490,7 @@
       </c>
       <c r="S85" s="4" t="inlineStr">
         <is>
-          <t>2026-09-27T23:13:02Z</t>
+          <t>2026-09-29T00:28:22Z</t>
         </is>
       </c>
     </row>
@@ -7575,7 +7575,7 @@
       </c>
       <c r="S86" s="4" t="inlineStr">
         <is>
-          <t>2026-09-27T23:13:02Z</t>
+          <t>2026-09-29T00:28:22Z</t>
         </is>
       </c>
     </row>
@@ -7660,7 +7660,7 @@
       </c>
       <c r="S87" s="4" t="inlineStr">
         <is>
-          <t>2026-09-27T23:13:02Z</t>
+          <t>2026-09-29T00:28:22Z</t>
         </is>
       </c>
     </row>
@@ -7745,7 +7745,7 @@
       </c>
       <c r="S88" s="4" t="inlineStr">
         <is>
-          <t>2026-09-27T23:13:02Z</t>
+          <t>2026-09-29T00:28:22Z</t>
         </is>
       </c>
     </row>
@@ -7834,7 +7834,7 @@
       </c>
       <c r="S89" s="4" t="inlineStr">
         <is>
-          <t>2026-09-27T23:13:02Z</t>
+          <t>2026-09-29T00:28:22Z</t>
         </is>
       </c>
     </row>
@@ -7923,7 +7923,7 @@
       </c>
       <c r="S90" s="4" t="inlineStr">
         <is>
-          <t>2026-09-27T23:13:02Z</t>
+          <t>2026-09-29T00:28:22Z</t>
         </is>
       </c>
     </row>
@@ -8008,7 +8008,7 @@
       </c>
       <c r="S91" s="4" t="inlineStr">
         <is>
-          <t>2026-09-27T23:13:02Z</t>
+          <t>2026-09-29T00:28:22Z</t>
         </is>
       </c>
     </row>
@@ -8097,7 +8097,7 @@
       </c>
       <c r="S92" s="4" t="inlineStr">
         <is>
-          <t>2026-09-27T23:13:02Z</t>
+          <t>2026-09-29T00:28:22Z</t>
         </is>
       </c>
     </row>
@@ -8186,7 +8186,7 @@
       </c>
       <c r="S93" s="4" t="inlineStr">
         <is>
-          <t>2026-09-27T23:13:02Z</t>
+          <t>2026-09-29T00:28:22Z</t>
         </is>
       </c>
     </row>
@@ -8271,7 +8271,7 @@
       </c>
       <c r="S94" s="4" t="inlineStr">
         <is>
-          <t>2026-09-27T23:13:02Z</t>
+          <t>2026-09-29T00:28:22Z</t>
         </is>
       </c>
     </row>
@@ -8360,7 +8360,7 @@
       </c>
       <c r="S95" s="4" t="inlineStr">
         <is>
-          <t>2026-09-27T23:13:02Z</t>
+          <t>2026-09-29T00:28:22Z</t>
         </is>
       </c>
     </row>
@@ -8449,7 +8449,7 @@
       </c>
       <c r="S96" s="4" t="inlineStr">
         <is>
-          <t>2026-09-27T23:13:02Z</t>
+          <t>2026-09-29T00:28:22Z</t>
         </is>
       </c>
     </row>
@@ -8534,7 +8534,7 @@
       </c>
       <c r="S97" s="4" t="inlineStr">
         <is>
-          <t>2026-09-27T23:13:02Z</t>
+          <t>2026-09-29T00:28:22Z</t>
         </is>
       </c>
     </row>
@@ -8623,7 +8623,7 @@
       </c>
       <c r="S98" s="4" t="inlineStr">
         <is>
-          <t>2026-09-27T23:13:02Z</t>
+          <t>2026-09-29T00:28:22Z</t>
         </is>
       </c>
     </row>
@@ -8712,7 +8712,7 @@
       </c>
       <c r="S99" s="4" t="inlineStr">
         <is>
-          <t>2026-09-27T23:13:02Z</t>
+          <t>2026-09-29T00:28:22Z</t>
         </is>
       </c>
     </row>
@@ -8797,7 +8797,7 @@
       </c>
       <c r="S100" s="4" t="inlineStr">
         <is>
-          <t>2026-09-27T23:13:02Z</t>
+          <t>2026-09-29T00:28:22Z</t>
         </is>
       </c>
     </row>
@@ -8886,7 +8886,7 @@
       </c>
       <c r="S101" s="4" t="inlineStr">
         <is>
-          <t>2026-09-27T23:13:02Z</t>
+          <t>2026-09-29T00:28:22Z</t>
         </is>
       </c>
     </row>
@@ -8975,7 +8975,7 @@
       </c>
       <c r="S102" s="4" t="inlineStr">
         <is>
-          <t>2026-09-27T23:13:02Z</t>
+          <t>2026-09-29T00:28:22Z</t>
         </is>
       </c>
     </row>
@@ -9060,7 +9060,7 @@
       </c>
       <c r="S103" s="4" t="inlineStr">
         <is>
-          <t>2026-09-27T23:13:02Z</t>
+          <t>2026-09-29T00:28:22Z</t>
         </is>
       </c>
     </row>
@@ -9149,7 +9149,7 @@
       </c>
       <c r="S104" s="4" t="inlineStr">
         <is>
-          <t>2026-09-27T23:13:02Z</t>
+          <t>2026-09-29T00:28:22Z</t>
         </is>
       </c>
     </row>
@@ -9238,7 +9238,7 @@
       </c>
       <c r="S105" s="4" t="inlineStr">
         <is>
-          <t>2026-09-27T23:13:02Z</t>
+          <t>2026-09-29T00:28:22Z</t>
         </is>
       </c>
     </row>
@@ -9323,7 +9323,7 @@
       </c>
       <c r="S106" s="4" t="inlineStr">
         <is>
-          <t>2026-09-27T23:13:02Z</t>
+          <t>2026-09-29T00:28:22Z</t>
         </is>
       </c>
     </row>
@@ -9412,7 +9412,7 @@
       </c>
       <c r="S107" s="4" t="inlineStr">
         <is>
-          <t>2026-09-27T23:13:02Z</t>
+          <t>2026-09-29T00:28:22Z</t>
         </is>
       </c>
     </row>
@@ -9501,7 +9501,7 @@
       </c>
       <c r="S108" s="4" t="inlineStr">
         <is>
-          <t>2026-09-27T23:13:02Z</t>
+          <t>2026-09-29T00:28:22Z</t>
         </is>
       </c>
     </row>
@@ -9586,7 +9586,7 @@
       </c>
       <c r="S109" s="4" t="inlineStr">
         <is>
-          <t>2026-09-27T23:13:02Z</t>
+          <t>2026-09-29T00:28:22Z</t>
         </is>
       </c>
     </row>
@@ -9675,7 +9675,7 @@
       </c>
       <c r="S110" s="4" t="inlineStr">
         <is>
-          <t>2026-09-27T23:13:02Z</t>
+          <t>2026-09-29T00:28:22Z</t>
         </is>
       </c>
     </row>
@@ -9764,7 +9764,7 @@
       </c>
       <c r="S111" s="4" t="inlineStr">
         <is>
-          <t>2026-09-27T23:13:02Z</t>
+          <t>2026-09-29T00:28:22Z</t>
         </is>
       </c>
     </row>
@@ -9849,7 +9849,7 @@
       </c>
       <c r="S112" s="4" t="inlineStr">
         <is>
-          <t>2026-09-27T23:13:02Z</t>
+          <t>2026-09-29T00:28:22Z</t>
         </is>
       </c>
     </row>
@@ -9938,7 +9938,7 @@
       </c>
       <c r="S113" s="4" t="inlineStr">
         <is>
-          <t>2026-09-27T23:13:02Z</t>
+          <t>2026-09-29T00:28:22Z</t>
         </is>
       </c>
     </row>
@@ -10027,7 +10027,7 @@
       </c>
       <c r="S114" s="4" t="inlineStr">
         <is>
-          <t>2026-09-27T23:13:02Z</t>
+          <t>2026-09-29T00:28:22Z</t>
         </is>
       </c>
     </row>
@@ -10112,7 +10112,7 @@
       </c>
       <c r="S115" s="4" t="inlineStr">
         <is>
-          <t>2026-09-27T23:13:02Z</t>
+          <t>2026-09-29T00:28:22Z</t>
         </is>
       </c>
     </row>
@@ -10201,7 +10201,7 @@
       </c>
       <c r="S116" s="4" t="inlineStr">
         <is>
-          <t>2026-09-27T23:13:02Z</t>
+          <t>2026-09-29T00:28:22Z</t>
         </is>
       </c>
     </row>
@@ -10290,7 +10290,7 @@
       </c>
       <c r="S117" s="4" t="inlineStr">
         <is>
-          <t>2026-09-27T23:13:02Z</t>
+          <t>2026-09-29T00:28:22Z</t>
         </is>
       </c>
     </row>
@@ -10379,7 +10379,7 @@
       </c>
       <c r="S118" s="4" t="inlineStr">
         <is>
-          <t>2026-09-27T23:13:02Z</t>
+          <t>2026-09-29T00:28:22Z</t>
         </is>
       </c>
     </row>
@@ -10468,7 +10468,7 @@
       </c>
       <c r="S119" s="4" t="inlineStr">
         <is>
-          <t>2026-09-27T23:13:02Z</t>
+          <t>2026-09-29T00:28:22Z</t>
         </is>
       </c>
     </row>
@@ -10557,7 +10557,7 @@
       </c>
       <c r="S120" s="4" t="inlineStr">
         <is>
-          <t>2026-09-27T23:13:02Z</t>
+          <t>2026-09-29T00:28:22Z</t>
         </is>
       </c>
     </row>
@@ -10646,7 +10646,7 @@
       </c>
       <c r="S121" s="4" t="inlineStr">
         <is>
-          <t>2026-09-27T23:13:02Z</t>
+          <t>2026-09-29T00:28:22Z</t>
         </is>
       </c>
     </row>
@@ -10735,7 +10735,7 @@
       </c>
       <c r="S122" s="4" t="inlineStr">
         <is>
-          <t>2026-09-27T23:13:02Z</t>
+          <t>2026-09-29T00:28:22Z</t>
         </is>
       </c>
     </row>
@@ -10824,7 +10824,7 @@
       </c>
       <c r="S123" s="4" t="inlineStr">
         <is>
-          <t>2026-09-27T23:13:02Z</t>
+          <t>2026-09-29T00:28:22Z</t>
         </is>
       </c>
     </row>
@@ -10913,7 +10913,7 @@
       </c>
       <c r="S124" s="4" t="inlineStr">
         <is>
-          <t>2026-09-27T23:13:02Z</t>
+          <t>2026-09-29T00:28:22Z</t>
         </is>
       </c>
     </row>
@@ -11002,7 +11002,7 @@
       </c>
       <c r="S125" s="4" t="inlineStr">
         <is>
-          <t>2026-09-27T23:13:02Z</t>
+          <t>2026-09-29T00:28:22Z</t>
         </is>
       </c>
     </row>
@@ -11091,7 +11091,7 @@
       </c>
       <c r="S126" s="4" t="inlineStr">
         <is>
-          <t>2026-09-27T23:13:02Z</t>
+          <t>2026-09-29T00:28:22Z</t>
         </is>
       </c>
     </row>
@@ -11180,7 +11180,7 @@
       </c>
       <c r="S127" s="4" t="inlineStr">
         <is>
-          <t>2026-09-27T23:13:02Z</t>
+          <t>2026-09-29T00:28:22Z</t>
         </is>
       </c>
     </row>
@@ -11269,7 +11269,7 @@
       </c>
       <c r="S128" s="4" t="inlineStr">
         <is>
-          <t>2026-09-27T23:13:02Z</t>
+          <t>2026-09-29T00:28:22Z</t>
         </is>
       </c>
     </row>
@@ -11354,7 +11354,7 @@
       </c>
       <c r="S129" s="4" t="inlineStr">
         <is>
-          <t>2026-09-27T23:13:02Z</t>
+          <t>2026-09-29T00:28:22Z</t>
         </is>
       </c>
     </row>
@@ -11439,7 +11439,7 @@
       </c>
       <c r="S130" s="4" t="inlineStr">
         <is>
-          <t>2026-09-27T23:13:02Z</t>
+          <t>2026-09-29T00:28:22Z</t>
         </is>
       </c>
     </row>
@@ -11524,7 +11524,7 @@
       </c>
       <c r="S131" s="4" t="inlineStr">
         <is>
-          <t>2026-09-27T23:13:02Z</t>
+          <t>2026-09-29T00:28:22Z</t>
         </is>
       </c>
     </row>
@@ -11609,7 +11609,7 @@
       </c>
       <c r="S132" s="4" t="inlineStr">
         <is>
-          <t>2026-09-27T23:13:02Z</t>
+          <t>2026-09-29T00:28:22Z</t>
         </is>
       </c>
     </row>
@@ -11694,7 +11694,7 @@
       </c>
       <c r="S133" s="4" t="inlineStr">
         <is>
-          <t>2026-09-27T23:13:02Z</t>
+          <t>2026-09-29T00:28:22Z</t>
         </is>
       </c>
     </row>
@@ -11779,7 +11779,7 @@
       </c>
       <c r="S134" s="4" t="inlineStr">
         <is>
-          <t>2026-09-27T23:13:02Z</t>
+          <t>2026-09-29T00:28:22Z</t>
         </is>
       </c>
     </row>
@@ -11864,7 +11864,7 @@
       </c>
       <c r="S135" s="4" t="inlineStr">
         <is>
-          <t>2026-09-27T23:13:02Z</t>
+          <t>2026-09-29T00:28:22Z</t>
         </is>
       </c>
     </row>
@@ -11949,7 +11949,7 @@
       </c>
       <c r="S136" s="4" t="inlineStr">
         <is>
-          <t>2026-09-27T23:13:02Z</t>
+          <t>2026-09-29T00:28:22Z</t>
         </is>
       </c>
     </row>
@@ -12034,7 +12034,7 @@
       </c>
       <c r="S137" s="4" t="inlineStr">
         <is>
-          <t>2026-09-27T23:13:02Z</t>
+          <t>2026-09-29T00:28:22Z</t>
         </is>
       </c>
     </row>
@@ -12119,7 +12119,7 @@
       </c>
       <c r="S138" s="4" t="inlineStr">
         <is>
-          <t>2026-09-27T23:13:02Z</t>
+          <t>2026-09-29T00:28:22Z</t>
         </is>
       </c>
     </row>
@@ -12204,7 +12204,7 @@
       </c>
       <c r="S139" s="4" t="inlineStr">
         <is>
-          <t>2026-09-27T23:13:02Z</t>
+          <t>2026-09-29T00:28:22Z</t>
         </is>
       </c>
     </row>
@@ -12289,7 +12289,7 @@
       </c>
       <c r="S140" s="4" t="inlineStr">
         <is>
-          <t>2026-09-27T23:13:02Z</t>
+          <t>2026-09-29T00:28:22Z</t>
         </is>
       </c>
     </row>
@@ -12374,7 +12374,7 @@
       </c>
       <c r="S141" s="4" t="inlineStr">
         <is>
-          <t>2026-09-27T23:13:02Z</t>
+          <t>2026-09-29T00:28:22Z</t>
         </is>
       </c>
     </row>
@@ -12459,7 +12459,7 @@
       </c>
       <c r="S142" s="4" t="inlineStr">
         <is>
-          <t>2026-09-27T23:13:02Z</t>
+          <t>2026-09-29T00:28:22Z</t>
         </is>
       </c>
     </row>
@@ -12544,7 +12544,7 @@
       </c>
       <c r="S143" s="4" t="inlineStr">
         <is>
-          <t>2026-09-27T23:13:02Z</t>
+          <t>2026-09-29T00:28:22Z</t>
         </is>
       </c>
     </row>
@@ -12629,7 +12629,7 @@
       </c>
       <c r="S144" s="4" t="inlineStr">
         <is>
-          <t>2026-09-27T23:13:02Z</t>
+          <t>2026-09-29T00:28:22Z</t>
         </is>
       </c>
     </row>
@@ -12714,7 +12714,7 @@
       </c>
       <c r="S145" s="4" t="inlineStr">
         <is>
-          <t>2026-09-27T23:13:02Z</t>
+          <t>2026-09-29T00:28:22Z</t>
         </is>
       </c>
     </row>
@@ -12799,7 +12799,7 @@
       </c>
       <c r="S146" s="4" t="inlineStr">
         <is>
-          <t>2026-09-27T23:13:02Z</t>
+          <t>2026-09-29T00:28:22Z</t>
         </is>
       </c>
     </row>
@@ -12884,7 +12884,7 @@
       </c>
       <c r="S147" s="4" t="inlineStr">
         <is>
-          <t>2026-09-27T23:13:02Z</t>
+          <t>2026-09-29T00:28:22Z</t>
         </is>
       </c>
     </row>
@@ -12969,7 +12969,7 @@
       </c>
       <c r="S148" s="4" t="inlineStr">
         <is>
-          <t>2026-09-27T23:13:02Z</t>
+          <t>2026-09-29T00:28:22Z</t>
         </is>
       </c>
     </row>
@@ -13054,7 +13054,7 @@
       </c>
       <c r="S149" s="4" t="inlineStr">
         <is>
-          <t>2026-09-27T23:13:02Z</t>
+          <t>2026-09-29T00:28:22Z</t>
         </is>
       </c>
     </row>
@@ -13143,7 +13143,7 @@
       </c>
       <c r="S150" s="4" t="inlineStr">
         <is>
-          <t>2026-09-27T23:13:02Z</t>
+          <t>2026-09-29T00:28:22Z</t>
         </is>
       </c>
     </row>
@@ -13232,7 +13232,7 @@
       </c>
       <c r="S151" s="4" t="inlineStr">
         <is>
-          <t>2026-09-27T23:13:02Z</t>
+          <t>2026-09-29T00:28:22Z</t>
         </is>
       </c>
     </row>
@@ -13317,7 +13317,7 @@
       </c>
       <c r="S152" s="4" t="inlineStr">
         <is>
-          <t>2026-09-27T23:13:02Z</t>
+          <t>2026-09-29T00:28:22Z</t>
         </is>
       </c>
     </row>
@@ -13406,7 +13406,7 @@
       </c>
       <c r="S153" s="4" t="inlineStr">
         <is>
-          <t>2026-09-27T23:13:02Z</t>
+          <t>2026-09-29T00:28:22Z</t>
         </is>
       </c>
     </row>
@@ -13495,7 +13495,7 @@
       </c>
       <c r="S154" s="4" t="inlineStr">
         <is>
-          <t>2026-09-27T23:13:02Z</t>
+          <t>2026-09-29T00:28:22Z</t>
         </is>
       </c>
     </row>
@@ -13580,7 +13580,7 @@
       </c>
       <c r="S155" s="4" t="inlineStr">
         <is>
-          <t>2026-09-27T23:13:02Z</t>
+          <t>2026-09-29T00:28:22Z</t>
         </is>
       </c>
     </row>
@@ -13669,7 +13669,7 @@
       </c>
       <c r="S156" s="4" t="inlineStr">
         <is>
-          <t>2026-09-27T23:13:02Z</t>
+          <t>2026-09-29T00:28:22Z</t>
         </is>
       </c>
     </row>
@@ -13758,7 +13758,7 @@
       </c>
       <c r="S157" s="4" t="inlineStr">
         <is>
-          <t>2026-09-27T23:13:02Z</t>
+          <t>2026-09-29T00:28:22Z</t>
         </is>
       </c>
     </row>
@@ -13843,7 +13843,7 @@
       </c>
       <c r="S158" s="4" t="inlineStr">
         <is>
-          <t>2026-09-27T23:13:02Z</t>
+          <t>2026-09-29T00:28:22Z</t>
         </is>
       </c>
     </row>
@@ -13932,7 +13932,7 @@
       </c>
       <c r="S159" s="4" t="inlineStr">
         <is>
-          <t>2026-09-27T23:13:02Z</t>
+          <t>2026-09-29T00:28:22Z</t>
         </is>
       </c>
     </row>
@@ -14021,7 +14021,7 @@
       </c>
       <c r="S160" s="4" t="inlineStr">
         <is>
-          <t>2026-09-27T23:13:02Z</t>
+          <t>2026-09-29T00:28:22Z</t>
         </is>
       </c>
     </row>
@@ -14106,7 +14106,7 @@
       </c>
       <c r="S161" s="4" t="inlineStr">
         <is>
-          <t>2026-09-27T23:13:02Z</t>
+          <t>2026-09-29T00:28:22Z</t>
         </is>
       </c>
     </row>
@@ -14195,7 +14195,7 @@
       </c>
       <c r="S162" s="4" t="inlineStr">
         <is>
-          <t>2026-09-27T23:13:02Z</t>
+          <t>2026-09-29T00:28:22Z</t>
         </is>
       </c>
     </row>
@@ -14284,7 +14284,7 @@
       </c>
       <c r="S163" s="4" t="inlineStr">
         <is>
-          <t>2026-09-27T23:13:02Z</t>
+          <t>2026-09-29T00:28:22Z</t>
         </is>
       </c>
     </row>
@@ -14369,7 +14369,7 @@
       </c>
       <c r="S164" s="4" t="inlineStr">
         <is>
-          <t>2026-09-27T23:13:02Z</t>
+          <t>2026-09-29T00:28:22Z</t>
         </is>
       </c>
     </row>
@@ -14458,7 +14458,7 @@
       </c>
       <c r="S165" s="4" t="inlineStr">
         <is>
-          <t>2026-09-27T23:13:02Z</t>
+          <t>2026-09-29T00:28:22Z</t>
         </is>
       </c>
     </row>
@@ -14547,7 +14547,7 @@
       </c>
       <c r="S166" s="4" t="inlineStr">
         <is>
-          <t>2026-09-27T23:13:02Z</t>
+          <t>2026-09-29T00:28:22Z</t>
         </is>
       </c>
     </row>
@@ -14632,7 +14632,7 @@
       </c>
       <c r="S167" s="4" t="inlineStr">
         <is>
-          <t>2026-09-27T23:13:02Z</t>
+          <t>2026-09-29T00:28:22Z</t>
         </is>
       </c>
     </row>
@@ -14721,7 +14721,7 @@
       </c>
       <c r="S168" s="4" t="inlineStr">
         <is>
-          <t>2026-09-27T23:13:02Z</t>
+          <t>2026-09-29T00:28:22Z</t>
         </is>
       </c>
     </row>
@@ -14810,7 +14810,7 @@
       </c>
       <c r="S169" s="4" t="inlineStr">
         <is>
-          <t>2026-09-27T23:13:02Z</t>
+          <t>2026-09-29T00:28:22Z</t>
         </is>
       </c>
     </row>
@@ -14895,7 +14895,7 @@
       </c>
       <c r="S170" s="4" t="inlineStr">
         <is>
-          <t>2026-09-27T23:13:02Z</t>
+          <t>2026-09-29T00:28:22Z</t>
         </is>
       </c>
     </row>
@@ -14984,7 +14984,7 @@
       </c>
       <c r="S171" s="4" t="inlineStr">
         <is>
-          <t>2026-09-27T23:13:02Z</t>
+          <t>2026-09-29T00:28:22Z</t>
         </is>
       </c>
     </row>
@@ -15073,7 +15073,7 @@
       </c>
       <c r="S172" s="4" t="inlineStr">
         <is>
-          <t>2026-09-27T23:13:02Z</t>
+          <t>2026-09-29T00:28:22Z</t>
         </is>
       </c>
     </row>
@@ -15158,7 +15158,7 @@
       </c>
       <c r="S173" s="4" t="inlineStr">
         <is>
-          <t>2026-09-27T23:13:02Z</t>
+          <t>2026-09-29T00:28:22Z</t>
         </is>
       </c>
     </row>
@@ -15247,7 +15247,7 @@
       </c>
       <c r="S174" s="4" t="inlineStr">
         <is>
-          <t>2026-09-27T23:13:02Z</t>
+          <t>2026-09-29T00:28:22Z</t>
         </is>
       </c>
     </row>
@@ -15336,7 +15336,7 @@
       </c>
       <c r="S175" s="4" t="inlineStr">
         <is>
-          <t>2026-09-27T23:13:02Z</t>
+          <t>2026-09-29T00:28:22Z</t>
         </is>
       </c>
     </row>
@@ -15421,7 +15421,7 @@
       </c>
       <c r="S176" s="4" t="inlineStr">
         <is>
-          <t>2026-09-27T23:13:02Z</t>
+          <t>2026-09-29T00:28:22Z</t>
         </is>
       </c>
     </row>
@@ -15510,7 +15510,7 @@
       </c>
       <c r="S177" s="4" t="inlineStr">
         <is>
-          <t>2026-09-27T23:13:02Z</t>
+          <t>2026-09-29T00:28:22Z</t>
         </is>
       </c>
     </row>
@@ -15599,7 +15599,7 @@
       </c>
       <c r="S178" s="4" t="inlineStr">
         <is>
-          <t>2026-09-27T23:13:02Z</t>
+          <t>2026-09-29T00:28:22Z</t>
         </is>
       </c>
     </row>
@@ -15688,7 +15688,7 @@
       </c>
       <c r="S179" s="4" t="inlineStr">
         <is>
-          <t>2026-09-27T23:13:02Z</t>
+          <t>2026-09-29T00:28:22Z</t>
         </is>
       </c>
     </row>
@@ -15777,7 +15777,7 @@
       </c>
       <c r="S180" s="4" t="inlineStr">
         <is>
-          <t>2026-09-27T23:13:02Z</t>
+          <t>2026-09-29T00:28:22Z</t>
         </is>
       </c>
     </row>
@@ -15866,7 +15866,7 @@
       </c>
       <c r="S181" s="4" t="inlineStr">
         <is>
-          <t>2026-09-27T23:13:02Z</t>
+          <t>2026-09-29T00:28:22Z</t>
         </is>
       </c>
     </row>
@@ -15955,7 +15955,7 @@
       </c>
       <c r="S182" s="4" t="inlineStr">
         <is>
-          <t>2026-09-27T23:13:02Z</t>
+          <t>2026-09-29T00:28:22Z</t>
         </is>
       </c>
     </row>
@@ -16044,7 +16044,7 @@
       </c>
       <c r="S183" s="4" t="inlineStr">
         <is>
-          <t>2026-09-27T23:13:02Z</t>
+          <t>2026-09-29T00:28:22Z</t>
         </is>
       </c>
     </row>
@@ -16133,7 +16133,7 @@
       </c>
       <c r="S184" s="4" t="inlineStr">
         <is>
-          <t>2026-09-27T23:13:02Z</t>
+          <t>2026-09-29T00:28:22Z</t>
         </is>
       </c>
     </row>
@@ -16222,7 +16222,7 @@
       </c>
       <c r="S185" s="4" t="inlineStr">
         <is>
-          <t>2026-09-27T23:13:02Z</t>
+          <t>2026-09-29T00:28:22Z</t>
         </is>
       </c>
     </row>
@@ -16311,7 +16311,7 @@
       </c>
       <c r="S186" s="4" t="inlineStr">
         <is>
-          <t>2026-09-27T23:13:02Z</t>
+          <t>2026-09-29T00:28:22Z</t>
         </is>
       </c>
     </row>
@@ -16400,7 +16400,7 @@
       </c>
       <c r="S187" s="4" t="inlineStr">
         <is>
-          <t>2026-09-27T23:13:02Z</t>
+          <t>2026-09-29T00:28:22Z</t>
         </is>
       </c>
     </row>
@@ -16489,7 +16489,7 @@
       </c>
       <c r="S188" s="4" t="inlineStr">
         <is>
-          <t>2026-09-27T23:13:02Z</t>
+          <t>2026-09-29T00:28:22Z</t>
         </is>
       </c>
     </row>
@@ -16578,7 +16578,7 @@
       </c>
       <c r="S189" s="4" t="inlineStr">
         <is>
-          <t>2026-09-27T23:13:02Z</t>
+          <t>2026-09-29T00:28:22Z</t>
         </is>
       </c>
     </row>
@@ -16663,7 +16663,7 @@
       </c>
       <c r="S190" s="4" t="inlineStr">
         <is>
-          <t>2026-09-27T23:13:02Z</t>
+          <t>2026-09-29T00:28:22Z</t>
         </is>
       </c>
     </row>
@@ -16748,7 +16748,7 @@
       </c>
       <c r="S191" s="4" t="inlineStr">
         <is>
-          <t>2026-09-27T23:13:02Z</t>
+          <t>2026-09-29T00:28:22Z</t>
         </is>
       </c>
     </row>
@@ -16833,7 +16833,7 @@
       </c>
       <c r="S192" s="4" t="inlineStr">
         <is>
-          <t>2026-09-27T23:13:02Z</t>
+          <t>2026-09-29T00:28:22Z</t>
         </is>
       </c>
     </row>
@@ -16918,7 +16918,7 @@
       </c>
       <c r="S193" s="4" t="inlineStr">
         <is>
-          <t>2026-09-27T23:13:02Z</t>
+          <t>2026-09-29T00:28:22Z</t>
         </is>
       </c>
     </row>
@@ -17003,7 +17003,7 @@
       </c>
       <c r="S194" s="4" t="inlineStr">
         <is>
-          <t>2026-09-27T23:13:02Z</t>
+          <t>2026-09-29T00:28:22Z</t>
         </is>
       </c>
     </row>
@@ -17088,7 +17088,7 @@
       </c>
       <c r="S195" s="4" t="inlineStr">
         <is>
-          <t>2026-09-27T23:13:02Z</t>
+          <t>2026-09-29T00:28:22Z</t>
         </is>
       </c>
     </row>
@@ -17173,7 +17173,7 @@
       </c>
       <c r="S196" s="4" t="inlineStr">
         <is>
-          <t>2026-09-27T23:13:02Z</t>
+          <t>2026-09-29T00:28:22Z</t>
         </is>
       </c>
     </row>
@@ -17258,7 +17258,7 @@
       </c>
       <c r="S197" s="4" t="inlineStr">
         <is>
-          <t>2026-09-27T23:13:02Z</t>
+          <t>2026-09-29T00:28:22Z</t>
         </is>
       </c>
     </row>
@@ -17343,7 +17343,7 @@
       </c>
       <c r="S198" s="4" t="inlineStr">
         <is>
-          <t>2026-09-27T23:13:02Z</t>
+          <t>2026-09-29T00:28:22Z</t>
         </is>
       </c>
     </row>
@@ -17428,7 +17428,7 @@
       </c>
       <c r="S199" s="4" t="inlineStr">
         <is>
-          <t>2026-09-27T23:13:02Z</t>
+          <t>2026-09-29T00:28:22Z</t>
         </is>
       </c>
     </row>
@@ -17513,7 +17513,7 @@
       </c>
       <c r="S200" s="4" t="inlineStr">
         <is>
-          <t>2026-09-27T23:13:02Z</t>
+          <t>2026-09-29T00:28:22Z</t>
         </is>
       </c>
     </row>
@@ -17598,7 +17598,7 @@
       </c>
       <c r="S201" s="4" t="inlineStr">
         <is>
-          <t>2026-09-27T23:13:02Z</t>
+          <t>2026-09-29T00:28:22Z</t>
         </is>
       </c>
     </row>
@@ -17683,7 +17683,7 @@
       </c>
       <c r="S202" s="4" t="inlineStr">
         <is>
-          <t>2026-09-27T23:13:02Z</t>
+          <t>2026-09-29T00:28:22Z</t>
         </is>
       </c>
     </row>
@@ -17768,7 +17768,7 @@
       </c>
       <c r="S203" s="4" t="inlineStr">
         <is>
-          <t>2026-09-27T23:13:02Z</t>
+          <t>2026-09-29T00:28:22Z</t>
         </is>
       </c>
     </row>
@@ -17853,7 +17853,7 @@
       </c>
       <c r="S204" s="4" t="inlineStr">
         <is>
-          <t>2026-09-27T23:13:02Z</t>
+          <t>2026-09-29T00:28:22Z</t>
         </is>
       </c>
     </row>
@@ -17938,7 +17938,7 @@
       </c>
       <c r="S205" s="4" t="inlineStr">
         <is>
-          <t>2026-09-27T23:13:02Z</t>
+          <t>2026-09-29T00:28:22Z</t>
         </is>
       </c>
     </row>
@@ -18023,7 +18023,7 @@
       </c>
       <c r="S206" s="4" t="inlineStr">
         <is>
-          <t>2026-09-27T23:13:02Z</t>
+          <t>2026-09-29T00:28:22Z</t>
         </is>
       </c>
     </row>
@@ -18108,7 +18108,7 @@
       </c>
       <c r="S207" s="4" t="inlineStr">
         <is>
-          <t>2026-09-27T23:13:02Z</t>
+          <t>2026-09-29T00:28:22Z</t>
         </is>
       </c>
     </row>
@@ -18193,7 +18193,7 @@
       </c>
       <c r="S208" s="4" t="inlineStr">
         <is>
-          <t>2026-09-27T23:13:02Z</t>
+          <t>2026-09-29T00:28:22Z</t>
         </is>
       </c>
     </row>
@@ -18278,7 +18278,7 @@
       </c>
       <c r="S209" s="4" t="inlineStr">
         <is>
-          <t>2026-09-27T23:13:02Z</t>
+          <t>2026-09-29T00:28:22Z</t>
         </is>
       </c>
     </row>
@@ -18363,7 +18363,7 @@
       </c>
       <c r="S210" s="4" t="inlineStr">
         <is>
-          <t>2026-09-27T23:13:02Z</t>
+          <t>2026-09-29T00:28:22Z</t>
         </is>
       </c>
     </row>
@@ -18452,7 +18452,7 @@
       </c>
       <c r="S211" s="4" t="inlineStr">
         <is>
-          <t>2026-09-27T23:13:02Z</t>
+          <t>2026-09-29T00:28:22Z</t>
         </is>
       </c>
     </row>
@@ -18541,7 +18541,7 @@
       </c>
       <c r="S212" s="4" t="inlineStr">
         <is>
-          <t>2026-09-27T23:13:02Z</t>
+          <t>2026-09-29T00:28:22Z</t>
         </is>
       </c>
     </row>
@@ -18626,7 +18626,7 @@
       </c>
       <c r="S213" s="4" t="inlineStr">
         <is>
-          <t>2026-09-27T23:13:02Z</t>
+          <t>2026-09-29T00:28:22Z</t>
         </is>
       </c>
     </row>
@@ -18715,7 +18715,7 @@
       </c>
       <c r="S214" s="4" t="inlineStr">
         <is>
-          <t>2026-09-27T23:13:02Z</t>
+          <t>2026-09-29T00:28:22Z</t>
         </is>
       </c>
     </row>
@@ -18804,7 +18804,7 @@
       </c>
       <c r="S215" s="4" t="inlineStr">
         <is>
-          <t>2026-09-27T23:13:02Z</t>
+          <t>2026-09-29T00:28:22Z</t>
         </is>
       </c>
     </row>
@@ -18889,7 +18889,7 @@
       </c>
       <c r="S216" s="4" t="inlineStr">
         <is>
-          <t>2026-09-27T23:13:02Z</t>
+          <t>2026-09-29T00:28:22Z</t>
         </is>
       </c>
     </row>
@@ -18978,7 +18978,7 @@
       </c>
       <c r="S217" s="4" t="inlineStr">
         <is>
-          <t>2026-09-27T23:13:02Z</t>
+          <t>2026-09-29T00:28:22Z</t>
         </is>
       </c>
     </row>
@@ -19067,7 +19067,7 @@
       </c>
       <c r="S218" s="4" t="inlineStr">
         <is>
-          <t>2026-09-27T23:13:02Z</t>
+          <t>2026-09-29T00:28:22Z</t>
         </is>
       </c>
     </row>
@@ -19152,7 +19152,7 @@
       </c>
       <c r="S219" s="4" t="inlineStr">
         <is>
-          <t>2026-09-27T23:13:02Z</t>
+          <t>2026-09-29T00:28:22Z</t>
         </is>
       </c>
     </row>
@@ -19241,7 +19241,7 @@
       </c>
       <c r="S220" s="4" t="inlineStr">
         <is>
-          <t>2026-09-27T23:13:02Z</t>
+          <t>2026-09-29T00:28:22Z</t>
         </is>
       </c>
     </row>
@@ -19330,7 +19330,7 @@
       </c>
       <c r="S221" s="4" t="inlineStr">
         <is>
-          <t>2026-09-27T23:13:02Z</t>
+          <t>2026-09-29T00:28:22Z</t>
         </is>
       </c>
     </row>
@@ -19415,7 +19415,7 @@
       </c>
       <c r="S222" s="4" t="inlineStr">
         <is>
-          <t>2026-09-27T23:13:02Z</t>
+          <t>2026-09-29T00:28:22Z</t>
         </is>
       </c>
     </row>
@@ -19504,7 +19504,7 @@
       </c>
       <c r="S223" s="4" t="inlineStr">
         <is>
-          <t>2026-09-27T23:13:02Z</t>
+          <t>2026-09-29T00:28:22Z</t>
         </is>
       </c>
     </row>
@@ -19593,7 +19593,7 @@
       </c>
       <c r="S224" s="4" t="inlineStr">
         <is>
-          <t>2026-09-27T23:13:02Z</t>
+          <t>2026-09-29T00:28:22Z</t>
         </is>
       </c>
     </row>
@@ -19678,7 +19678,7 @@
       </c>
       <c r="S225" s="4" t="inlineStr">
         <is>
-          <t>2026-09-27T23:13:02Z</t>
+          <t>2026-09-29T00:28:22Z</t>
         </is>
       </c>
     </row>
@@ -19767,7 +19767,7 @@
       </c>
       <c r="S226" s="4" t="inlineStr">
         <is>
-          <t>2026-09-27T23:13:02Z</t>
+          <t>2026-09-29T00:28:22Z</t>
         </is>
       </c>
     </row>
@@ -19856,7 +19856,7 @@
       </c>
       <c r="S227" s="4" t="inlineStr">
         <is>
-          <t>2026-09-27T23:13:02Z</t>
+          <t>2026-09-29T00:28:22Z</t>
         </is>
       </c>
     </row>
@@ -19941,7 +19941,7 @@
       </c>
       <c r="S228" s="4" t="inlineStr">
         <is>
-          <t>2026-09-27T23:13:02Z</t>
+          <t>2026-09-29T00:28:22Z</t>
         </is>
       </c>
     </row>
@@ -20030,7 +20030,7 @@
       </c>
       <c r="S229" s="4" t="inlineStr">
         <is>
-          <t>2026-09-27T23:13:02Z</t>
+          <t>2026-09-29T00:28:22Z</t>
         </is>
       </c>
     </row>
@@ -20119,7 +20119,7 @@
       </c>
       <c r="S230" s="4" t="inlineStr">
         <is>
-          <t>2026-09-27T23:13:02Z</t>
+          <t>2026-09-29T00:28:22Z</t>
         </is>
       </c>
     </row>
@@ -20204,7 +20204,7 @@
       </c>
       <c r="S231" s="4" t="inlineStr">
         <is>
-          <t>2026-09-27T23:13:02Z</t>
+          <t>2026-09-29T00:28:22Z</t>
         </is>
       </c>
     </row>
@@ -20293,7 +20293,7 @@
       </c>
       <c r="S232" s="4" t="inlineStr">
         <is>
-          <t>2026-09-27T23:13:02Z</t>
+          <t>2026-09-29T00:28:22Z</t>
         </is>
       </c>
     </row>
@@ -20382,7 +20382,7 @@
       </c>
       <c r="S233" s="4" t="inlineStr">
         <is>
-          <t>2026-09-27T23:13:02Z</t>
+          <t>2026-09-29T00:28:22Z</t>
         </is>
       </c>
     </row>
@@ -20467,7 +20467,7 @@
       </c>
       <c r="S234" s="4" t="inlineStr">
         <is>
-          <t>2026-09-27T23:13:02Z</t>
+          <t>2026-09-29T00:28:22Z</t>
         </is>
       </c>
     </row>
@@ -20556,7 +20556,7 @@
       </c>
       <c r="S235" s="4" t="inlineStr">
         <is>
-          <t>2026-09-27T23:13:02Z</t>
+          <t>2026-09-29T00:28:22Z</t>
         </is>
       </c>
     </row>
@@ -20645,7 +20645,7 @@
       </c>
       <c r="S236" s="4" t="inlineStr">
         <is>
-          <t>2026-09-27T23:13:02Z</t>
+          <t>2026-09-29T00:28:22Z</t>
         </is>
       </c>
     </row>
@@ -20730,7 +20730,7 @@
       </c>
       <c r="S237" s="4" t="inlineStr">
         <is>
-          <t>2026-09-27T23:13:02Z</t>
+          <t>2026-09-29T00:28:22Z</t>
         </is>
       </c>
     </row>
@@ -20819,7 +20819,7 @@
       </c>
       <c r="S238" s="4" t="inlineStr">
         <is>
-          <t>2026-09-27T23:13:02Z</t>
+          <t>2026-09-29T00:28:22Z</t>
         </is>
       </c>
     </row>
@@ -20908,7 +20908,7 @@
       </c>
       <c r="S239" s="4" t="inlineStr">
         <is>
-          <t>2026-09-27T23:13:02Z</t>
+          <t>2026-09-29T00:28:22Z</t>
         </is>
       </c>
     </row>
@@ -20997,7 +20997,7 @@
       </c>
       <c r="S240" s="4" t="inlineStr">
         <is>
-          <t>2026-09-27T23:13:02Z</t>
+          <t>2026-09-29T00:28:22Z</t>
         </is>
       </c>
     </row>
@@ -21086,7 +21086,7 @@
       </c>
       <c r="S241" s="4" t="inlineStr">
         <is>
-          <t>2026-09-27T23:13:02Z</t>
+          <t>2026-09-29T00:28:22Z</t>
         </is>
       </c>
     </row>
@@ -21175,7 +21175,7 @@
       </c>
       <c r="S242" s="4" t="inlineStr">
         <is>
-          <t>2026-09-27T23:13:02Z</t>
+          <t>2026-09-29T00:28:22Z</t>
         </is>
       </c>
     </row>
@@ -21264,7 +21264,7 @@
       </c>
       <c r="S243" s="4" t="inlineStr">
         <is>
-          <t>2026-09-27T23:13:02Z</t>
+          <t>2026-09-29T00:28:22Z</t>
         </is>
       </c>
     </row>
@@ -21353,7 +21353,7 @@
       </c>
       <c r="S244" s="4" t="inlineStr">
         <is>
-          <t>2026-09-27T23:13:02Z</t>
+          <t>2026-09-29T00:28:22Z</t>
         </is>
       </c>
     </row>
@@ -21442,7 +21442,7 @@
       </c>
       <c r="S245" s="4" t="inlineStr">
         <is>
-          <t>2026-09-27T23:13:02Z</t>
+          <t>2026-09-29T00:28:22Z</t>
         </is>
       </c>
     </row>
@@ -21531,7 +21531,7 @@
       </c>
       <c r="S246" s="4" t="inlineStr">
         <is>
-          <t>2026-09-27T23:13:02Z</t>
+          <t>2026-09-29T00:28:22Z</t>
         </is>
       </c>
     </row>
@@ -21620,7 +21620,7 @@
       </c>
       <c r="S247" s="4" t="inlineStr">
         <is>
-          <t>2026-09-27T23:13:02Z</t>
+          <t>2026-09-29T00:28:22Z</t>
         </is>
       </c>
     </row>
@@ -21709,7 +21709,7 @@
       </c>
       <c r="S248" s="4" t="inlineStr">
         <is>
-          <t>2026-09-27T23:13:02Z</t>
+          <t>2026-09-29T00:28:22Z</t>
         </is>
       </c>
     </row>
@@ -21798,7 +21798,7 @@
       </c>
       <c r="S249" s="4" t="inlineStr">
         <is>
-          <t>2026-09-27T23:13:02Z</t>
+          <t>2026-09-29T00:28:22Z</t>
         </is>
       </c>
     </row>
@@ -21887,7 +21887,7 @@
       </c>
       <c r="S250" s="4" t="inlineStr">
         <is>
-          <t>2026-09-27T23:13:02Z</t>
+          <t>2026-09-29T00:28:22Z</t>
         </is>
       </c>
     </row>
@@ -22019,7 +22019,7 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>2026-09-27T23:13:02Z</t>
+          <t>2026-09-29T00:28:22Z</t>
         </is>
       </c>
     </row>
@@ -22099,7 +22099,7 @@
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>{"dataset_id": "bcv_pib_sector_institucional_anual", "title": "Producto interno bruto por sector institucional anual", "table": "Variaciones porcentuales", "source_file": "5_2_1_si_anual.xlsx", "base": "2007", "price_type": "Precios constantes", "measure": "Variación porcentual interanual", "frequency": "Anual", "period": "2025", "year": 2025, "quarter": null, "classification": "Sector institucional", "component": "Impuestos netos sobre los productos", "value": 10.600260421283764, "unit": "Porcentaje", "status": "Preliminar", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/cuentas_macroeconomicas/5_2_1_si_anual.xlsx", "fetched_at": "2026-09-27T23:13:02Z"}</t>
+          <t>{"dataset_id": "bcv_pib_sector_institucional_anual", "title": "Producto interno bruto por sector institucional anual", "table": "Variaciones porcentuales", "source_file": "5_2_1_si_anual.xlsx", "base": "2007", "price_type": "Precios constantes", "measure": "Variación porcentual interanual", "frequency": "Anual", "period": "2025", "year": 2025, "quarter": null, "classification": "Sector institucional", "component": "Impuestos netos sobre los productos", "value": 10.600260421283764, "unit": "Porcentaje", "status": "Preliminar", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/cuentas_macroeconomicas/5_2_1_si_anual.xlsx", "fetched_at": "2026-09-29T00:28:22Z"}</t>
         </is>
       </c>
     </row>

--- a/assets/data/bcv/excel/ove_bcv_pib_sector_institucional_anual.xlsx
+++ b/assets/data/bcv/excel/ove_bcv_pib_sector_institucional_anual.xlsx
@@ -736,7 +736,7 @@
       </c>
       <c r="S7" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T00:28:22Z</t>
+          <t>2026-09-29T23:51:57Z</t>
         </is>
       </c>
     </row>
@@ -821,7 +821,7 @@
       </c>
       <c r="S8" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T00:28:22Z</t>
+          <t>2026-09-29T23:51:57Z</t>
         </is>
       </c>
     </row>
@@ -906,7 +906,7 @@
       </c>
       <c r="S9" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T00:28:22Z</t>
+          <t>2026-09-29T23:51:57Z</t>
         </is>
       </c>
     </row>
@@ -991,7 +991,7 @@
       </c>
       <c r="S10" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T00:28:22Z</t>
+          <t>2026-09-29T23:51:57Z</t>
         </is>
       </c>
     </row>
@@ -1076,7 +1076,7 @@
       </c>
       <c r="S11" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T00:28:22Z</t>
+          <t>2026-09-29T23:51:57Z</t>
         </is>
       </c>
     </row>
@@ -1161,7 +1161,7 @@
       </c>
       <c r="S12" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T00:28:22Z</t>
+          <t>2026-09-29T23:51:57Z</t>
         </is>
       </c>
     </row>
@@ -1246,7 +1246,7 @@
       </c>
       <c r="S13" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T00:28:22Z</t>
+          <t>2026-09-29T23:51:57Z</t>
         </is>
       </c>
     </row>
@@ -1331,7 +1331,7 @@
       </c>
       <c r="S14" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T00:28:22Z</t>
+          <t>2026-09-29T23:51:57Z</t>
         </is>
       </c>
     </row>
@@ -1416,7 +1416,7 @@
       </c>
       <c r="S15" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T00:28:22Z</t>
+          <t>2026-09-29T23:51:57Z</t>
         </is>
       </c>
     </row>
@@ -1501,7 +1501,7 @@
       </c>
       <c r="S16" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T00:28:22Z</t>
+          <t>2026-09-29T23:51:57Z</t>
         </is>
       </c>
     </row>
@@ -1586,7 +1586,7 @@
       </c>
       <c r="S17" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T00:28:22Z</t>
+          <t>2026-09-29T23:51:57Z</t>
         </is>
       </c>
     </row>
@@ -1671,7 +1671,7 @@
       </c>
       <c r="S18" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T00:28:22Z</t>
+          <t>2026-09-29T23:51:57Z</t>
         </is>
       </c>
     </row>
@@ -1756,7 +1756,7 @@
       </c>
       <c r="S19" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T00:28:22Z</t>
+          <t>2026-09-29T23:51:57Z</t>
         </is>
       </c>
     </row>
@@ -1841,7 +1841,7 @@
       </c>
       <c r="S20" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T00:28:22Z</t>
+          <t>2026-09-29T23:51:57Z</t>
         </is>
       </c>
     </row>
@@ -1926,7 +1926,7 @@
       </c>
       <c r="S21" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T00:28:22Z</t>
+          <t>2026-09-29T23:51:57Z</t>
         </is>
       </c>
     </row>
@@ -2011,7 +2011,7 @@
       </c>
       <c r="S22" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T00:28:22Z</t>
+          <t>2026-09-29T23:51:57Z</t>
         </is>
       </c>
     </row>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="S23" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T00:28:22Z</t>
+          <t>2026-09-29T23:51:57Z</t>
         </is>
       </c>
     </row>
@@ -2181,7 +2181,7 @@
       </c>
       <c r="S24" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T00:28:22Z</t>
+          <t>2026-09-29T23:51:57Z</t>
         </is>
       </c>
     </row>
@@ -2266,7 +2266,7 @@
       </c>
       <c r="S25" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T00:28:22Z</t>
+          <t>2026-09-29T23:51:57Z</t>
         </is>
       </c>
     </row>
@@ -2351,7 +2351,7 @@
       </c>
       <c r="S26" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T00:28:22Z</t>
+          <t>2026-09-29T23:51:57Z</t>
         </is>
       </c>
     </row>
@@ -2436,7 +2436,7 @@
       </c>
       <c r="S27" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T00:28:22Z</t>
+          <t>2026-09-29T23:51:57Z</t>
         </is>
       </c>
     </row>
@@ -2525,7 +2525,7 @@
       </c>
       <c r="S28" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T00:28:22Z</t>
+          <t>2026-09-29T23:51:57Z</t>
         </is>
       </c>
     </row>
@@ -2614,7 +2614,7 @@
       </c>
       <c r="S29" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T00:28:22Z</t>
+          <t>2026-09-29T23:51:57Z</t>
         </is>
       </c>
     </row>
@@ -2699,7 +2699,7 @@
       </c>
       <c r="S30" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T00:28:22Z</t>
+          <t>2026-09-29T23:51:57Z</t>
         </is>
       </c>
     </row>
@@ -2788,7 +2788,7 @@
       </c>
       <c r="S31" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T00:28:22Z</t>
+          <t>2026-09-29T23:51:57Z</t>
         </is>
       </c>
     </row>
@@ -2877,7 +2877,7 @@
       </c>
       <c r="S32" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T00:28:22Z</t>
+          <t>2026-09-29T23:51:57Z</t>
         </is>
       </c>
     </row>
@@ -2962,7 +2962,7 @@
       </c>
       <c r="S33" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T00:28:22Z</t>
+          <t>2026-09-29T23:51:57Z</t>
         </is>
       </c>
     </row>
@@ -3051,7 +3051,7 @@
       </c>
       <c r="S34" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T00:28:22Z</t>
+          <t>2026-09-29T23:51:57Z</t>
         </is>
       </c>
     </row>
@@ -3140,7 +3140,7 @@
       </c>
       <c r="S35" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T00:28:22Z</t>
+          <t>2026-09-29T23:51:57Z</t>
         </is>
       </c>
     </row>
@@ -3225,7 +3225,7 @@
       </c>
       <c r="S36" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T00:28:22Z</t>
+          <t>2026-09-29T23:51:57Z</t>
         </is>
       </c>
     </row>
@@ -3314,7 +3314,7 @@
       </c>
       <c r="S37" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T00:28:22Z</t>
+          <t>2026-09-29T23:51:57Z</t>
         </is>
       </c>
     </row>
@@ -3403,7 +3403,7 @@
       </c>
       <c r="S38" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T00:28:22Z</t>
+          <t>2026-09-29T23:51:57Z</t>
         </is>
       </c>
     </row>
@@ -3488,7 +3488,7 @@
       </c>
       <c r="S39" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T00:28:22Z</t>
+          <t>2026-09-29T23:51:57Z</t>
         </is>
       </c>
     </row>
@@ -3577,7 +3577,7 @@
       </c>
       <c r="S40" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T00:28:22Z</t>
+          <t>2026-09-29T23:51:57Z</t>
         </is>
       </c>
     </row>
@@ -3666,7 +3666,7 @@
       </c>
       <c r="S41" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T00:28:22Z</t>
+          <t>2026-09-29T23:51:57Z</t>
         </is>
       </c>
     </row>
@@ -3751,7 +3751,7 @@
       </c>
       <c r="S42" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T00:28:22Z</t>
+          <t>2026-09-29T23:51:57Z</t>
         </is>
       </c>
     </row>
@@ -3840,7 +3840,7 @@
       </c>
       <c r="S43" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T00:28:22Z</t>
+          <t>2026-09-29T23:51:57Z</t>
         </is>
       </c>
     </row>
@@ -3929,7 +3929,7 @@
       </c>
       <c r="S44" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T00:28:22Z</t>
+          <t>2026-09-29T23:51:57Z</t>
         </is>
       </c>
     </row>
@@ -4014,7 +4014,7 @@
       </c>
       <c r="S45" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T00:28:22Z</t>
+          <t>2026-09-29T23:51:57Z</t>
         </is>
       </c>
     </row>
@@ -4103,7 +4103,7 @@
       </c>
       <c r="S46" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T00:28:22Z</t>
+          <t>2026-09-29T23:51:57Z</t>
         </is>
       </c>
     </row>
@@ -4192,7 +4192,7 @@
       </c>
       <c r="S47" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T00:28:22Z</t>
+          <t>2026-09-29T23:51:57Z</t>
         </is>
       </c>
     </row>
@@ -4277,7 +4277,7 @@
       </c>
       <c r="S48" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T00:28:22Z</t>
+          <t>2026-09-29T23:51:57Z</t>
         </is>
       </c>
     </row>
@@ -4366,7 +4366,7 @@
       </c>
       <c r="S49" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T00:28:22Z</t>
+          <t>2026-09-29T23:51:57Z</t>
         </is>
       </c>
     </row>
@@ -4455,7 +4455,7 @@
       </c>
       <c r="S50" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T00:28:22Z</t>
+          <t>2026-09-29T23:51:57Z</t>
         </is>
       </c>
     </row>
@@ -4540,7 +4540,7 @@
       </c>
       <c r="S51" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T00:28:22Z</t>
+          <t>2026-09-29T23:51:57Z</t>
         </is>
       </c>
     </row>
@@ -4629,7 +4629,7 @@
       </c>
       <c r="S52" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T00:28:22Z</t>
+          <t>2026-09-29T23:51:57Z</t>
         </is>
       </c>
     </row>
@@ -4718,7 +4718,7 @@
       </c>
       <c r="S53" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T00:28:22Z</t>
+          <t>2026-09-29T23:51:57Z</t>
         </is>
       </c>
     </row>
@@ -4803,7 +4803,7 @@
       </c>
       <c r="S54" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T00:28:22Z</t>
+          <t>2026-09-29T23:51:57Z</t>
         </is>
       </c>
     </row>
@@ -4892,7 +4892,7 @@
       </c>
       <c r="S55" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T00:28:22Z</t>
+          <t>2026-09-29T23:51:57Z</t>
         </is>
       </c>
     </row>
@@ -4981,7 +4981,7 @@
       </c>
       <c r="S56" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T00:28:22Z</t>
+          <t>2026-09-29T23:51:57Z</t>
         </is>
       </c>
     </row>
@@ -5070,7 +5070,7 @@
       </c>
       <c r="S57" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T00:28:22Z</t>
+          <t>2026-09-29T23:51:57Z</t>
         </is>
       </c>
     </row>
@@ -5159,7 +5159,7 @@
       </c>
       <c r="S58" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T00:28:22Z</t>
+          <t>2026-09-29T23:51:57Z</t>
         </is>
       </c>
     </row>
@@ -5248,7 +5248,7 @@
       </c>
       <c r="S59" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T00:28:22Z</t>
+          <t>2026-09-29T23:51:57Z</t>
         </is>
       </c>
     </row>
@@ -5337,7 +5337,7 @@
       </c>
       <c r="S60" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T00:28:22Z</t>
+          <t>2026-09-29T23:51:57Z</t>
         </is>
       </c>
     </row>
@@ -5426,7 +5426,7 @@
       </c>
       <c r="S61" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T00:28:22Z</t>
+          <t>2026-09-29T23:51:57Z</t>
         </is>
       </c>
     </row>
@@ -5515,7 +5515,7 @@
       </c>
       <c r="S62" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T00:28:22Z</t>
+          <t>2026-09-29T23:51:57Z</t>
         </is>
       </c>
     </row>
@@ -5604,7 +5604,7 @@
       </c>
       <c r="S63" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T00:28:22Z</t>
+          <t>2026-09-29T23:51:57Z</t>
         </is>
       </c>
     </row>
@@ -5693,7 +5693,7 @@
       </c>
       <c r="S64" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T00:28:22Z</t>
+          <t>2026-09-29T23:51:57Z</t>
         </is>
       </c>
     </row>
@@ -5782,7 +5782,7 @@
       </c>
       <c r="S65" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T00:28:22Z</t>
+          <t>2026-09-29T23:51:57Z</t>
         </is>
       </c>
     </row>
@@ -5871,7 +5871,7 @@
       </c>
       <c r="S66" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T00:28:22Z</t>
+          <t>2026-09-29T23:51:57Z</t>
         </is>
       </c>
     </row>
@@ -5960,7 +5960,7 @@
       </c>
       <c r="S67" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T00:28:22Z</t>
+          <t>2026-09-29T23:51:57Z</t>
         </is>
       </c>
     </row>
@@ -6045,7 +6045,7 @@
       </c>
       <c r="S68" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T00:28:22Z</t>
+          <t>2026-09-29T23:51:57Z</t>
         </is>
       </c>
     </row>
@@ -6130,7 +6130,7 @@
       </c>
       <c r="S69" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T00:28:22Z</t>
+          <t>2026-09-29T23:51:57Z</t>
         </is>
       </c>
     </row>
@@ -6215,7 +6215,7 @@
       </c>
       <c r="S70" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T00:28:22Z</t>
+          <t>2026-09-29T23:51:57Z</t>
         </is>
       </c>
     </row>
@@ -6300,7 +6300,7 @@
       </c>
       <c r="S71" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T00:28:22Z</t>
+          <t>2026-09-29T23:51:57Z</t>
         </is>
       </c>
     </row>
@@ -6385,7 +6385,7 @@
       </c>
       <c r="S72" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T00:28:22Z</t>
+          <t>2026-09-29T23:51:57Z</t>
         </is>
       </c>
     </row>
@@ -6470,7 +6470,7 @@
       </c>
       <c r="S73" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T00:28:22Z</t>
+          <t>2026-09-29T23:51:57Z</t>
         </is>
       </c>
     </row>
@@ -6555,7 +6555,7 @@
       </c>
       <c r="S74" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T00:28:22Z</t>
+          <t>2026-09-29T23:51:57Z</t>
         </is>
       </c>
     </row>
@@ -6640,7 +6640,7 @@
       </c>
       <c r="S75" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T00:28:22Z</t>
+          <t>2026-09-29T23:51:57Z</t>
         </is>
       </c>
     </row>
@@ -6725,7 +6725,7 @@
       </c>
       <c r="S76" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T00:28:22Z</t>
+          <t>2026-09-29T23:51:57Z</t>
         </is>
       </c>
     </row>
@@ -6810,7 +6810,7 @@
       </c>
       <c r="S77" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T00:28:22Z</t>
+          <t>2026-09-29T23:51:57Z</t>
         </is>
       </c>
     </row>
@@ -6895,7 +6895,7 @@
       </c>
       <c r="S78" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T00:28:22Z</t>
+          <t>2026-09-29T23:51:57Z</t>
         </is>
       </c>
     </row>
@@ -6980,7 +6980,7 @@
       </c>
       <c r="S79" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T00:28:22Z</t>
+          <t>2026-09-29T23:51:57Z</t>
         </is>
       </c>
     </row>
@@ -7065,7 +7065,7 @@
       </c>
       <c r="S80" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T00:28:22Z</t>
+          <t>2026-09-29T23:51:57Z</t>
         </is>
       </c>
     </row>
@@ -7150,7 +7150,7 @@
       </c>
       <c r="S81" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T00:28:22Z</t>
+          <t>2026-09-29T23:51:57Z</t>
         </is>
       </c>
     </row>
@@ -7235,7 +7235,7 @@
       </c>
       <c r="S82" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T00:28:22Z</t>
+          <t>2026-09-29T23:51:57Z</t>
         </is>
       </c>
     </row>
@@ -7320,7 +7320,7 @@
       </c>
       <c r="S83" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T00:28:22Z</t>
+          <t>2026-09-29T23:51:57Z</t>
         </is>
       </c>
     </row>
@@ -7405,7 +7405,7 @@
       </c>
       <c r="S84" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T00:28:22Z</t>
+          <t>2026-09-29T23:51:57Z</t>
         </is>
       </c>
     </row>
@@ -7490,7 +7490,7 @@
       </c>
       <c r="S85" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T00:28:22Z</t>
+          <t>2026-09-29T23:51:57Z</t>
         </is>
       </c>
     </row>
@@ -7575,7 +7575,7 @@
       </c>
       <c r="S86" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T00:28:22Z</t>
+          <t>2026-09-29T23:51:57Z</t>
         </is>
       </c>
     </row>
@@ -7660,7 +7660,7 @@
       </c>
       <c r="S87" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T00:28:22Z</t>
+          <t>2026-09-29T23:51:57Z</t>
         </is>
       </c>
     </row>
@@ -7745,7 +7745,7 @@
       </c>
       <c r="S88" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T00:28:22Z</t>
+          <t>2026-09-29T23:51:57Z</t>
         </is>
       </c>
     </row>
@@ -7834,7 +7834,7 @@
       </c>
       <c r="S89" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T00:28:22Z</t>
+          <t>2026-09-29T23:51:57Z</t>
         </is>
       </c>
     </row>
@@ -7923,7 +7923,7 @@
       </c>
       <c r="S90" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T00:28:22Z</t>
+          <t>2026-09-29T23:51:57Z</t>
         </is>
       </c>
     </row>
@@ -8008,7 +8008,7 @@
       </c>
       <c r="S91" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T00:28:22Z</t>
+          <t>2026-09-29T23:51:57Z</t>
         </is>
       </c>
     </row>
@@ -8097,7 +8097,7 @@
       </c>
       <c r="S92" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T00:28:22Z</t>
+          <t>2026-09-29T23:51:57Z</t>
         </is>
       </c>
     </row>
@@ -8186,7 +8186,7 @@
       </c>
       <c r="S93" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T00:28:22Z</t>
+          <t>2026-09-29T23:51:57Z</t>
         </is>
       </c>
     </row>
@@ -8271,7 +8271,7 @@
       </c>
       <c r="S94" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T00:28:22Z</t>
+          <t>2026-09-29T23:51:57Z</t>
         </is>
       </c>
     </row>
@@ -8360,7 +8360,7 @@
       </c>
       <c r="S95" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T00:28:22Z</t>
+          <t>2026-09-29T23:51:57Z</t>
         </is>
       </c>
     </row>
@@ -8449,7 +8449,7 @@
       </c>
       <c r="S96" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T00:28:22Z</t>
+          <t>2026-09-29T23:51:57Z</t>
         </is>
       </c>
     </row>
@@ -8534,7 +8534,7 @@
       </c>
       <c r="S97" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T00:28:22Z</t>
+          <t>2026-09-29T23:51:57Z</t>
         </is>
       </c>
     </row>
@@ -8623,7 +8623,7 @@
       </c>
       <c r="S98" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T00:28:22Z</t>
+          <t>2026-09-29T23:51:57Z</t>
         </is>
       </c>
     </row>
@@ -8712,7 +8712,7 @@
       </c>
       <c r="S99" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T00:28:22Z</t>
+          <t>2026-09-29T23:51:57Z</t>
         </is>
       </c>
     </row>
@@ -8797,7 +8797,7 @@
       </c>
       <c r="S100" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T00:28:22Z</t>
+          <t>2026-09-29T23:51:57Z</t>
         </is>
       </c>
     </row>
@@ -8886,7 +8886,7 @@
       </c>
       <c r="S101" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T00:28:22Z</t>
+          <t>2026-09-29T23:51:57Z</t>
         </is>
       </c>
     </row>
@@ -8975,7 +8975,7 @@
       </c>
       <c r="S102" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T00:28:22Z</t>
+          <t>2026-09-29T23:51:57Z</t>
         </is>
       </c>
     </row>
@@ -9060,7 +9060,7 @@
       </c>
       <c r="S103" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T00:28:22Z</t>
+          <t>2026-09-29T23:51:57Z</t>
         </is>
       </c>
     </row>
@@ -9149,7 +9149,7 @@
       </c>
       <c r="S104" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T00:28:22Z</t>
+          <t>2026-09-29T23:51:57Z</t>
         </is>
       </c>
     </row>
@@ -9238,7 +9238,7 @@
       </c>
       <c r="S105" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T00:28:22Z</t>
+          <t>2026-09-29T23:51:57Z</t>
         </is>
       </c>
     </row>
@@ -9323,7 +9323,7 @@
       </c>
       <c r="S106" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T00:28:22Z</t>
+          <t>2026-09-29T23:51:57Z</t>
         </is>
       </c>
     </row>
@@ -9412,7 +9412,7 @@
       </c>
       <c r="S107" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T00:28:22Z</t>
+          <t>2026-09-29T23:51:57Z</t>
         </is>
       </c>
     </row>
@@ -9501,7 +9501,7 @@
       </c>
       <c r="S108" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T00:28:22Z</t>
+          <t>2026-09-29T23:51:57Z</t>
         </is>
       </c>
     </row>
@@ -9586,7 +9586,7 @@
       </c>
       <c r="S109" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T00:28:22Z</t>
+          <t>2026-09-29T23:51:57Z</t>
         </is>
       </c>
     </row>
@@ -9675,7 +9675,7 @@
       </c>
       <c r="S110" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T00:28:22Z</t>
+          <t>2026-09-29T23:51:57Z</t>
         </is>
       </c>
     </row>
@@ -9764,7 +9764,7 @@
       </c>
       <c r="S111" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T00:28:22Z</t>
+          <t>2026-09-29T23:51:57Z</t>
         </is>
       </c>
     </row>
@@ -9849,7 +9849,7 @@
       </c>
       <c r="S112" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T00:28:22Z</t>
+          <t>2026-09-29T23:51:57Z</t>
         </is>
       </c>
     </row>
@@ -9938,7 +9938,7 @@
       </c>
       <c r="S113" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T00:28:22Z</t>
+          <t>2026-09-29T23:51:57Z</t>
         </is>
       </c>
     </row>
@@ -10027,7 +10027,7 @@
       </c>
       <c r="S114" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T00:28:22Z</t>
+          <t>2026-09-29T23:51:57Z</t>
         </is>
       </c>
     </row>
@@ -10112,7 +10112,7 @@
       </c>
       <c r="S115" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T00:28:22Z</t>
+          <t>2026-09-29T23:51:57Z</t>
         </is>
       </c>
     </row>
@@ -10201,7 +10201,7 @@
       </c>
       <c r="S116" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T00:28:22Z</t>
+          <t>2026-09-29T23:51:57Z</t>
         </is>
       </c>
     </row>
@@ -10290,7 +10290,7 @@
       </c>
       <c r="S117" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T00:28:22Z</t>
+          <t>2026-09-29T23:51:57Z</t>
         </is>
       </c>
     </row>
@@ -10379,7 +10379,7 @@
       </c>
       <c r="S118" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T00:28:22Z</t>
+          <t>2026-09-29T23:51:57Z</t>
         </is>
       </c>
     </row>
@@ -10468,7 +10468,7 @@
       </c>
       <c r="S119" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T00:28:22Z</t>
+          <t>2026-09-29T23:51:57Z</t>
         </is>
       </c>
     </row>
@@ -10557,7 +10557,7 @@
       </c>
       <c r="S120" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T00:28:22Z</t>
+          <t>2026-09-29T23:51:57Z</t>
         </is>
       </c>
     </row>
@@ -10646,7 +10646,7 @@
       </c>
       <c r="S121" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T00:28:22Z</t>
+          <t>2026-09-29T23:51:57Z</t>
         </is>
       </c>
     </row>
@@ -10735,7 +10735,7 @@
       </c>
       <c r="S122" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T00:28:22Z</t>
+          <t>2026-09-29T23:51:57Z</t>
         </is>
       </c>
     </row>
@@ -10824,7 +10824,7 @@
       </c>
       <c r="S123" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T00:28:22Z</t>
+          <t>2026-09-29T23:51:57Z</t>
         </is>
       </c>
     </row>
@@ -10913,7 +10913,7 @@
       </c>
       <c r="S124" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T00:28:22Z</t>
+          <t>2026-09-29T23:51:57Z</t>
         </is>
       </c>
     </row>
@@ -11002,7 +11002,7 @@
       </c>
       <c r="S125" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T00:28:22Z</t>
+          <t>2026-09-29T23:51:57Z</t>
         </is>
       </c>
     </row>
@@ -11091,7 +11091,7 @@
       </c>
       <c r="S126" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T00:28:22Z</t>
+          <t>2026-09-29T23:51:57Z</t>
         </is>
       </c>
     </row>
@@ -11180,7 +11180,7 @@
       </c>
       <c r="S127" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T00:28:22Z</t>
+          <t>2026-09-29T23:51:57Z</t>
         </is>
       </c>
     </row>
@@ -11269,7 +11269,7 @@
       </c>
       <c r="S128" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T00:28:22Z</t>
+          <t>2026-09-29T23:51:57Z</t>
         </is>
       </c>
     </row>
@@ -11354,7 +11354,7 @@
       </c>
       <c r="S129" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T00:28:22Z</t>
+          <t>2026-09-29T23:51:57Z</t>
         </is>
       </c>
     </row>
@@ -11439,7 +11439,7 @@
       </c>
       <c r="S130" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T00:28:22Z</t>
+          <t>2026-09-29T23:51:57Z</t>
         </is>
       </c>
     </row>
@@ -11524,7 +11524,7 @@
       </c>
       <c r="S131" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T00:28:22Z</t>
+          <t>2026-09-29T23:51:57Z</t>
         </is>
       </c>
     </row>
@@ -11609,7 +11609,7 @@
       </c>
       <c r="S132" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T00:28:22Z</t>
+          <t>2026-09-29T23:51:57Z</t>
         </is>
       </c>
     </row>
@@ -11694,7 +11694,7 @@
       </c>
       <c r="S133" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T00:28:22Z</t>
+          <t>2026-09-29T23:51:57Z</t>
         </is>
       </c>
     </row>
@@ -11779,7 +11779,7 @@
       </c>
       <c r="S134" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T00:28:22Z</t>
+          <t>2026-09-29T23:51:57Z</t>
         </is>
       </c>
     </row>
@@ -11864,7 +11864,7 @@
       </c>
       <c r="S135" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T00:28:22Z</t>
+          <t>2026-09-29T23:51:57Z</t>
         </is>
       </c>
     </row>
@@ -11949,7 +11949,7 @@
       </c>
       <c r="S136" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T00:28:22Z</t>
+          <t>2026-09-29T23:51:57Z</t>
         </is>
       </c>
     </row>
@@ -12034,7 +12034,7 @@
       </c>
       <c r="S137" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T00:28:22Z</t>
+          <t>2026-09-29T23:51:57Z</t>
         </is>
       </c>
     </row>
@@ -12119,7 +12119,7 @@
       </c>
       <c r="S138" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T00:28:22Z</t>
+          <t>2026-09-29T23:51:57Z</t>
         </is>
       </c>
     </row>
@@ -12204,7 +12204,7 @@
       </c>
       <c r="S139" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T00:28:22Z</t>
+          <t>2026-09-29T23:51:57Z</t>
         </is>
       </c>
     </row>
@@ -12289,7 +12289,7 @@
       </c>
       <c r="S140" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T00:28:22Z</t>
+          <t>2026-09-29T23:51:57Z</t>
         </is>
       </c>
     </row>
@@ -12374,7 +12374,7 @@
       </c>
       <c r="S141" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T00:28:22Z</t>
+          <t>2026-09-29T23:51:57Z</t>
         </is>
       </c>
     </row>
@@ -12459,7 +12459,7 @@
       </c>
       <c r="S142" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T00:28:22Z</t>
+          <t>2026-09-29T23:51:57Z</t>
         </is>
       </c>
     </row>
@@ -12544,7 +12544,7 @@
       </c>
       <c r="S143" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T00:28:22Z</t>
+          <t>2026-09-29T23:51:57Z</t>
         </is>
       </c>
     </row>
@@ -12629,7 +12629,7 @@
       </c>
       <c r="S144" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T00:28:22Z</t>
+          <t>2026-09-29T23:51:57Z</t>
         </is>
       </c>
     </row>
@@ -12714,7 +12714,7 @@
       </c>
       <c r="S145" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T00:28:22Z</t>
+          <t>2026-09-29T23:51:57Z</t>
         </is>
       </c>
     </row>
@@ -12799,7 +12799,7 @@
       </c>
       <c r="S146" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T00:28:22Z</t>
+          <t>2026-09-29T23:51:57Z</t>
         </is>
       </c>
     </row>
@@ -12884,7 +12884,7 @@
       </c>
       <c r="S147" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T00:28:22Z</t>
+          <t>2026-09-29T23:51:57Z</t>
         </is>
       </c>
     </row>
@@ -12969,7 +12969,7 @@
       </c>
       <c r="S148" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T00:28:22Z</t>
+          <t>2026-09-29T23:51:57Z</t>
         </is>
       </c>
     </row>
@@ -13054,7 +13054,7 @@
       </c>
       <c r="S149" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T00:28:22Z</t>
+          <t>2026-09-29T23:51:57Z</t>
         </is>
       </c>
     </row>
@@ -13143,7 +13143,7 @@
       </c>
       <c r="S150" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T00:28:22Z</t>
+          <t>2026-09-29T23:51:57Z</t>
         </is>
       </c>
     </row>
@@ -13232,7 +13232,7 @@
       </c>
       <c r="S151" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T00:28:22Z</t>
+          <t>2026-09-29T23:51:57Z</t>
         </is>
       </c>
     </row>
@@ -13317,7 +13317,7 @@
       </c>
       <c r="S152" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T00:28:22Z</t>
+          <t>2026-09-29T23:51:57Z</t>
         </is>
       </c>
     </row>
@@ -13406,7 +13406,7 @@
       </c>
       <c r="S153" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T00:28:22Z</t>
+          <t>2026-09-29T23:51:57Z</t>
         </is>
       </c>
     </row>
@@ -13495,7 +13495,7 @@
       </c>
       <c r="S154" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T00:28:22Z</t>
+          <t>2026-09-29T23:51:57Z</t>
         </is>
       </c>
     </row>
@@ -13580,7 +13580,7 @@
       </c>
       <c r="S155" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T00:28:22Z</t>
+          <t>2026-09-29T23:51:57Z</t>
         </is>
       </c>
     </row>
@@ -13669,7 +13669,7 @@
       </c>
       <c r="S156" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T00:28:22Z</t>
+          <t>2026-09-29T23:51:57Z</t>
         </is>
       </c>
     </row>
@@ -13758,7 +13758,7 @@
       </c>
       <c r="S157" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T00:28:22Z</t>
+          <t>2026-09-29T23:51:57Z</t>
         </is>
       </c>
     </row>
@@ -13843,7 +13843,7 @@
       </c>
       <c r="S158" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T00:28:22Z</t>
+          <t>2026-09-29T23:51:57Z</t>
         </is>
       </c>
     </row>
@@ -13932,7 +13932,7 @@
       </c>
       <c r="S159" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T00:28:22Z</t>
+          <t>2026-09-29T23:51:57Z</t>
         </is>
       </c>
     </row>
@@ -14021,7 +14021,7 @@
       </c>
       <c r="S160" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T00:28:22Z</t>
+          <t>2026-09-29T23:51:57Z</t>
         </is>
       </c>
     </row>
@@ -14106,7 +14106,7 @@
       </c>
       <c r="S161" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T00:28:22Z</t>
+          <t>2026-09-29T23:51:57Z</t>
         </is>
       </c>
     </row>
@@ -14195,7 +14195,7 @@
       </c>
       <c r="S162" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T00:28:22Z</t>
+          <t>2026-09-29T23:51:57Z</t>
         </is>
       </c>
     </row>
@@ -14284,7 +14284,7 @@
       </c>
       <c r="S163" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T00:28:22Z</t>
+          <t>2026-09-29T23:51:57Z</t>
         </is>
       </c>
     </row>
@@ -14369,7 +14369,7 @@
       </c>
       <c r="S164" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T00:28:22Z</t>
+          <t>2026-09-29T23:51:57Z</t>
         </is>
       </c>
     </row>
@@ -14458,7 +14458,7 @@
       </c>
       <c r="S165" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T00:28:22Z</t>
+          <t>2026-09-29T23:51:57Z</t>
         </is>
       </c>
     </row>
@@ -14547,7 +14547,7 @@
       </c>
       <c r="S166" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T00:28:22Z</t>
+          <t>2026-09-29T23:51:57Z</t>
         </is>
       </c>
     </row>
@@ -14632,7 +14632,7 @@
       </c>
       <c r="S167" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T00:28:22Z</t>
+          <t>2026-09-29T23:51:57Z</t>
         </is>
       </c>
     </row>
@@ -14721,7 +14721,7 @@
       </c>
       <c r="S168" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T00:28:22Z</t>
+          <t>2026-09-29T23:51:57Z</t>
         </is>
       </c>
     </row>
@@ -14810,7 +14810,7 @@
       </c>
       <c r="S169" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T00:28:22Z</t>
+          <t>2026-09-29T23:51:57Z</t>
         </is>
       </c>
     </row>
@@ -14895,7 +14895,7 @@
       </c>
       <c r="S170" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T00:28:22Z</t>
+          <t>2026-09-29T23:51:57Z</t>
         </is>
       </c>
     </row>
@@ -14984,7 +14984,7 @@
       </c>
       <c r="S171" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T00:28:22Z</t>
+          <t>2026-09-29T23:51:57Z</t>
         </is>
       </c>
     </row>
@@ -15073,7 +15073,7 @@
       </c>
       <c r="S172" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T00:28:22Z</t>
+          <t>2026-09-29T23:51:57Z</t>
         </is>
       </c>
     </row>
@@ -15158,7 +15158,7 @@
       </c>
       <c r="S173" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T00:28:22Z</t>
+          <t>2026-09-29T23:51:57Z</t>
         </is>
       </c>
     </row>
@@ -15247,7 +15247,7 @@
       </c>
       <c r="S174" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T00:28:22Z</t>
+          <t>2026-09-29T23:51:57Z</t>
         </is>
       </c>
     </row>
@@ -15336,7 +15336,7 @@
       </c>
       <c r="S175" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T00:28:22Z</t>
+          <t>2026-09-29T23:51:57Z</t>
         </is>
       </c>
     </row>
@@ -15421,7 +15421,7 @@
       </c>
       <c r="S176" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T00:28:22Z</t>
+          <t>2026-09-29T23:51:57Z</t>
         </is>
       </c>
     </row>
@@ -15510,7 +15510,7 @@
       </c>
       <c r="S177" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T00:28:22Z</t>
+          <t>2026-09-29T23:51:57Z</t>
         </is>
       </c>
     </row>
@@ -15599,7 +15599,7 @@
       </c>
       <c r="S178" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T00:28:22Z</t>
+          <t>2026-09-29T23:51:57Z</t>
         </is>
       </c>
     </row>
@@ -15688,7 +15688,7 @@
       </c>
       <c r="S179" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T00:28:22Z</t>
+          <t>2026-09-29T23:51:57Z</t>
         </is>
       </c>
     </row>
@@ -15777,7 +15777,7 @@
       </c>
       <c r="S180" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T00:28:22Z</t>
+          <t>2026-09-29T23:51:57Z</t>
         </is>
       </c>
     </row>
@@ -15866,7 +15866,7 @@
       </c>
       <c r="S181" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T00:28:22Z</t>
+          <t>2026-09-29T23:51:57Z</t>
         </is>
       </c>
     </row>
@@ -15955,7 +15955,7 @@
       </c>
       <c r="S182" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T00:28:22Z</t>
+          <t>2026-09-29T23:51:57Z</t>
         </is>
       </c>
     </row>
@@ -16044,7 +16044,7 @@
       </c>
       <c r="S183" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T00:28:22Z</t>
+          <t>2026-09-29T23:51:57Z</t>
         </is>
       </c>
     </row>
@@ -16133,7 +16133,7 @@
       </c>
       <c r="S184" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T00:28:22Z</t>
+          <t>2026-09-29T23:51:57Z</t>
         </is>
       </c>
     </row>
@@ -16222,7 +16222,7 @@
       </c>
       <c r="S185" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T00:28:22Z</t>
+          <t>2026-09-29T23:51:57Z</t>
         </is>
       </c>
     </row>
@@ -16311,7 +16311,7 @@
       </c>
       <c r="S186" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T00:28:22Z</t>
+          <t>2026-09-29T23:51:57Z</t>
         </is>
       </c>
     </row>
@@ -16400,7 +16400,7 @@
       </c>
       <c r="S187" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T00:28:22Z</t>
+          <t>2026-09-29T23:51:57Z</t>
         </is>
       </c>
     </row>
@@ -16489,7 +16489,7 @@
       </c>
       <c r="S188" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T00:28:22Z</t>
+          <t>2026-09-29T23:51:57Z</t>
         </is>
       </c>
     </row>
@@ -16578,7 +16578,7 @@
       </c>
       <c r="S189" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T00:28:22Z</t>
+          <t>2026-09-29T23:51:57Z</t>
         </is>
       </c>
     </row>
@@ -16663,7 +16663,7 @@
       </c>
       <c r="S190" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T00:28:22Z</t>
+          <t>2026-09-29T23:51:57Z</t>
         </is>
       </c>
     </row>
@@ -16748,7 +16748,7 @@
       </c>
       <c r="S191" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T00:28:22Z</t>
+          <t>2026-09-29T23:51:57Z</t>
         </is>
       </c>
     </row>
@@ -16833,7 +16833,7 @@
       </c>
       <c r="S192" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T00:28:22Z</t>
+          <t>2026-09-29T23:51:57Z</t>
         </is>
       </c>
     </row>
@@ -16918,7 +16918,7 @@
       </c>
       <c r="S193" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T00:28:22Z</t>
+          <t>2026-09-29T23:51:57Z</t>
         </is>
       </c>
     </row>
@@ -17003,7 +17003,7 @@
       </c>
       <c r="S194" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T00:28:22Z</t>
+          <t>2026-09-29T23:51:57Z</t>
         </is>
       </c>
     </row>
@@ -17088,7 +17088,7 @@
       </c>
       <c r="S195" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T00:28:22Z</t>
+          <t>2026-09-29T23:51:57Z</t>
         </is>
       </c>
     </row>
@@ -17173,7 +17173,7 @@
       </c>
       <c r="S196" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T00:28:22Z</t>
+          <t>2026-09-29T23:51:57Z</t>
         </is>
       </c>
     </row>
@@ -17258,7 +17258,7 @@
       </c>
       <c r="S197" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T00:28:22Z</t>
+          <t>2026-09-29T23:51:57Z</t>
         </is>
       </c>
     </row>
@@ -17343,7 +17343,7 @@
       </c>
       <c r="S198" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T00:28:22Z</t>
+          <t>2026-09-29T23:51:57Z</t>
         </is>
       </c>
     </row>
@@ -17428,7 +17428,7 @@
       </c>
       <c r="S199" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T00:28:22Z</t>
+          <t>2026-09-29T23:51:57Z</t>
         </is>
       </c>
     </row>
@@ -17513,7 +17513,7 @@
       </c>
       <c r="S200" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T00:28:22Z</t>
+          <t>2026-09-29T23:51:57Z</t>
         </is>
       </c>
     </row>
@@ -17598,7 +17598,7 @@
       </c>
       <c r="S201" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T00:28:22Z</t>
+          <t>2026-09-29T23:51:57Z</t>
         </is>
       </c>
     </row>
@@ -17683,7 +17683,7 @@
       </c>
       <c r="S202" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T00:28:22Z</t>
+          <t>2026-09-29T23:51:57Z</t>
         </is>
       </c>
     </row>
@@ -17768,7 +17768,7 @@
       </c>
       <c r="S203" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T00:28:22Z</t>
+          <t>2026-09-29T23:51:57Z</t>
         </is>
       </c>
     </row>
@@ -17853,7 +17853,7 @@
       </c>
       <c r="S204" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T00:28:22Z</t>
+          <t>2026-09-29T23:51:57Z</t>
         </is>
       </c>
     </row>
@@ -17938,7 +17938,7 @@
       </c>
       <c r="S205" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T00:28:22Z</t>
+          <t>2026-09-29T23:51:57Z</t>
         </is>
       </c>
     </row>
@@ -18023,7 +18023,7 @@
       </c>
       <c r="S206" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T00:28:22Z</t>
+          <t>2026-09-29T23:51:57Z</t>
         </is>
       </c>
     </row>
@@ -18108,7 +18108,7 @@
       </c>
       <c r="S207" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T00:28:22Z</t>
+          <t>2026-09-29T23:51:57Z</t>
         </is>
       </c>
     </row>
@@ -18193,7 +18193,7 @@
       </c>
       <c r="S208" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T00:28:22Z</t>
+          <t>2026-09-29T23:51:57Z</t>
         </is>
       </c>
     </row>
@@ -18278,7 +18278,7 @@
       </c>
       <c r="S209" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T00:28:22Z</t>
+          <t>2026-09-29T23:51:57Z</t>
         </is>
       </c>
     </row>
@@ -18363,7 +18363,7 @@
       </c>
       <c r="S210" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T00:28:22Z</t>
+          <t>2026-09-29T23:51:57Z</t>
         </is>
       </c>
     </row>
@@ -18452,7 +18452,7 @@
       </c>
       <c r="S211" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T00:28:22Z</t>
+          <t>2026-09-29T23:51:57Z</t>
         </is>
       </c>
     </row>
@@ -18541,7 +18541,7 @@
       </c>
       <c r="S212" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T00:28:22Z</t>
+          <t>2026-09-29T23:51:57Z</t>
         </is>
       </c>
     </row>
@@ -18626,7 +18626,7 @@
       </c>
       <c r="S213" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T00:28:22Z</t>
+          <t>2026-09-29T23:51:57Z</t>
         </is>
       </c>
     </row>
@@ -18715,7 +18715,7 @@
       </c>
       <c r="S214" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T00:28:22Z</t>
+          <t>2026-09-29T23:51:57Z</t>
         </is>
       </c>
     </row>
@@ -18804,7 +18804,7 @@
       </c>
       <c r="S215" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T00:28:22Z</t>
+          <t>2026-09-29T23:51:57Z</t>
         </is>
       </c>
     </row>
@@ -18889,7 +18889,7 @@
       </c>
       <c r="S216" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T00:28:22Z</t>
+          <t>2026-09-29T23:51:57Z</t>
         </is>
       </c>
     </row>
@@ -18978,7 +18978,7 @@
       </c>
       <c r="S217" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T00:28:22Z</t>
+          <t>2026-09-29T23:51:57Z</t>
         </is>
       </c>
     </row>
@@ -19067,7 +19067,7 @@
       </c>
       <c r="S218" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T00:28:22Z</t>
+          <t>2026-09-29T23:51:57Z</t>
         </is>
       </c>
     </row>
@@ -19152,7 +19152,7 @@
       </c>
       <c r="S219" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T00:28:22Z</t>
+          <t>2026-09-29T23:51:57Z</t>
         </is>
       </c>
     </row>
@@ -19241,7 +19241,7 @@
       </c>
       <c r="S220" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T00:28:22Z</t>
+          <t>2026-09-29T23:51:57Z</t>
         </is>
       </c>
     </row>
@@ -19330,7 +19330,7 @@
       </c>
       <c r="S221" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T00:28:22Z</t>
+          <t>2026-09-29T23:51:57Z</t>
         </is>
       </c>
     </row>
@@ -19415,7 +19415,7 @@
       </c>
       <c r="S222" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T00:28:22Z</t>
+          <t>2026-09-29T23:51:57Z</t>
         </is>
       </c>
     </row>
@@ -19504,7 +19504,7 @@
       </c>
       <c r="S223" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T00:28:22Z</t>
+          <t>2026-09-29T23:51:57Z</t>
         </is>
       </c>
     </row>
@@ -19593,7 +19593,7 @@
       </c>
       <c r="S224" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T00:28:22Z</t>
+          <t>2026-09-29T23:51:57Z</t>
         </is>
       </c>
     </row>
@@ -19678,7 +19678,7 @@
       </c>
       <c r="S225" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T00:28:22Z</t>
+          <t>2026-09-29T23:51:57Z</t>
         </is>
       </c>
     </row>
@@ -19767,7 +19767,7 @@
       </c>
       <c r="S226" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T00:28:22Z</t>
+          <t>2026-09-29T23:51:57Z</t>
         </is>
       </c>
     </row>
@@ -19856,7 +19856,7 @@
       </c>
       <c r="S227" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T00:28:22Z</t>
+          <t>2026-09-29T23:51:57Z</t>
         </is>
       </c>
     </row>
@@ -19941,7 +19941,7 @@
       </c>
       <c r="S228" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T00:28:22Z</t>
+          <t>2026-09-29T23:51:57Z</t>
         </is>
       </c>
     </row>
@@ -20030,7 +20030,7 @@
       </c>
       <c r="S229" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T00:28:22Z</t>
+          <t>2026-09-29T23:51:57Z</t>
         </is>
       </c>
     </row>
@@ -20119,7 +20119,7 @@
       </c>
       <c r="S230" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T00:28:22Z</t>
+          <t>2026-09-29T23:51:57Z</t>
         </is>
       </c>
     </row>
@@ -20204,7 +20204,7 @@
       </c>
       <c r="S231" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T00:28:22Z</t>
+          <t>2026-09-29T23:51:57Z</t>
         </is>
       </c>
     </row>
@@ -20293,7 +20293,7 @@
       </c>
       <c r="S232" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T00:28:22Z</t>
+          <t>2026-09-29T23:51:57Z</t>
         </is>
       </c>
     </row>
@@ -20382,7 +20382,7 @@
       </c>
       <c r="S233" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T00:28:22Z</t>
+          <t>2026-09-29T23:51:57Z</t>
         </is>
       </c>
     </row>
@@ -20467,7 +20467,7 @@
       </c>
       <c r="S234" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T00:28:22Z</t>
+          <t>2026-09-29T23:51:57Z</t>
         </is>
       </c>
     </row>
@@ -20556,7 +20556,7 @@
       </c>
       <c r="S235" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T00:28:22Z</t>
+          <t>2026-09-29T23:51:57Z</t>
         </is>
       </c>
     </row>
@@ -20645,7 +20645,7 @@
       </c>
       <c r="S236" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T00:28:22Z</t>
+          <t>2026-09-29T23:51:57Z</t>
         </is>
       </c>
     </row>
@@ -20730,7 +20730,7 @@
       </c>
       <c r="S237" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T00:28:22Z</t>
+          <t>2026-09-29T23:51:57Z</t>
         </is>
       </c>
     </row>
@@ -20819,7 +20819,7 @@
       </c>
       <c r="S238" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T00:28:22Z</t>
+          <t>2026-09-29T23:51:57Z</t>
         </is>
       </c>
     </row>
@@ -20908,7 +20908,7 @@
       </c>
       <c r="S239" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T00:28:22Z</t>
+          <t>2026-09-29T23:51:57Z</t>
         </is>
       </c>
     </row>
@@ -20997,7 +20997,7 @@
       </c>
       <c r="S240" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T00:28:22Z</t>
+          <t>2026-09-29T23:51:57Z</t>
         </is>
       </c>
     </row>
@@ -21086,7 +21086,7 @@
       </c>
       <c r="S241" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T00:28:22Z</t>
+          <t>2026-09-29T23:51:57Z</t>
         </is>
       </c>
     </row>
@@ -21175,7 +21175,7 @@
       </c>
       <c r="S242" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T00:28:22Z</t>
+          <t>2026-09-29T23:51:57Z</t>
         </is>
       </c>
     </row>
@@ -21264,7 +21264,7 @@
       </c>
       <c r="S243" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T00:28:22Z</t>
+          <t>2026-09-29T23:51:57Z</t>
         </is>
       </c>
     </row>
@@ -21353,7 +21353,7 @@
       </c>
       <c r="S244" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T00:28:22Z</t>
+          <t>2026-09-29T23:51:57Z</t>
         </is>
       </c>
     </row>
@@ -21442,7 +21442,7 @@
       </c>
       <c r="S245" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T00:28:22Z</t>
+          <t>2026-09-29T23:51:57Z</t>
         </is>
       </c>
     </row>
@@ -21531,7 +21531,7 @@
       </c>
       <c r="S246" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T00:28:22Z</t>
+          <t>2026-09-29T23:51:57Z</t>
         </is>
       </c>
     </row>
@@ -21620,7 +21620,7 @@
       </c>
       <c r="S247" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T00:28:22Z</t>
+          <t>2026-09-29T23:51:57Z</t>
         </is>
       </c>
     </row>
@@ -21709,7 +21709,7 @@
       </c>
       <c r="S248" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T00:28:22Z</t>
+          <t>2026-09-29T23:51:57Z</t>
         </is>
       </c>
     </row>
@@ -21798,7 +21798,7 @@
       </c>
       <c r="S249" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T00:28:22Z</t>
+          <t>2026-09-29T23:51:57Z</t>
         </is>
       </c>
     </row>
@@ -21887,7 +21887,7 @@
       </c>
       <c r="S250" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T00:28:22Z</t>
+          <t>2026-09-29T23:51:57Z</t>
         </is>
       </c>
     </row>
@@ -22019,7 +22019,7 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T00:28:22Z</t>
+          <t>2026-09-29T23:51:57Z</t>
         </is>
       </c>
     </row>
@@ -22099,7 +22099,7 @@
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>{"dataset_id": "bcv_pib_sector_institucional_anual", "title": "Producto interno bruto por sector institucional anual", "table": "Variaciones porcentuales", "source_file": "5_2_1_si_anual.xlsx", "base": "2007", "price_type": "Precios constantes", "measure": "Variación porcentual interanual", "frequency": "Anual", "period": "2025", "year": 2025, "quarter": null, "classification": "Sector institucional", "component": "Impuestos netos sobre los productos", "value": 10.600260421283764, "unit": "Porcentaje", "status": "Preliminar", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/cuentas_macroeconomicas/5_2_1_si_anual.xlsx", "fetched_at": "2026-09-29T00:28:22Z"}</t>
+          <t>{"dataset_id": "bcv_pib_sector_institucional_anual", "title": "Producto interno bruto por sector institucional anual", "table": "Variaciones porcentuales", "source_file": "5_2_1_si_anual.xlsx", "base": "2007", "price_type": "Precios constantes", "measure": "Variación porcentual interanual", "frequency": "Anual", "period": "2025", "year": 2025, "quarter": null, "classification": "Sector institucional", "component": "Impuestos netos sobre los productos", "value": 10.600260421283764, "unit": "Porcentaje", "status": "Preliminar", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/cuentas_macroeconomicas/5_2_1_si_anual.xlsx", "fetched_at": "2026-09-29T23:51:57Z"}</t>
         </is>
       </c>
     </row>

--- a/assets/data/bcv/excel/ove_bcv_pib_sector_institucional_anual.xlsx
+++ b/assets/data/bcv/excel/ove_bcv_pib_sector_institucional_anual.xlsx
@@ -736,7 +736,7 @@
       </c>
       <c r="S7" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T23:51:57Z</t>
+          <t>2026-10-01T00:02:20Z</t>
         </is>
       </c>
     </row>
@@ -821,7 +821,7 @@
       </c>
       <c r="S8" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T23:51:57Z</t>
+          <t>2026-10-01T00:02:20Z</t>
         </is>
       </c>
     </row>
@@ -906,7 +906,7 @@
       </c>
       <c r="S9" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T23:51:57Z</t>
+          <t>2026-10-01T00:02:20Z</t>
         </is>
       </c>
     </row>
@@ -991,7 +991,7 @@
       </c>
       <c r="S10" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T23:51:57Z</t>
+          <t>2026-10-01T00:02:20Z</t>
         </is>
       </c>
     </row>
@@ -1076,7 +1076,7 @@
       </c>
       <c r="S11" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T23:51:57Z</t>
+          <t>2026-10-01T00:02:20Z</t>
         </is>
       </c>
     </row>
@@ -1161,7 +1161,7 @@
       </c>
       <c r="S12" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T23:51:57Z</t>
+          <t>2026-10-01T00:02:20Z</t>
         </is>
       </c>
     </row>
@@ -1246,7 +1246,7 @@
       </c>
       <c r="S13" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T23:51:57Z</t>
+          <t>2026-10-01T00:02:20Z</t>
         </is>
       </c>
     </row>
@@ -1331,7 +1331,7 @@
       </c>
       <c r="S14" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T23:51:57Z</t>
+          <t>2026-10-01T00:02:20Z</t>
         </is>
       </c>
     </row>
@@ -1416,7 +1416,7 @@
       </c>
       <c r="S15" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T23:51:57Z</t>
+          <t>2026-10-01T00:02:20Z</t>
         </is>
       </c>
     </row>
@@ -1501,7 +1501,7 @@
       </c>
       <c r="S16" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T23:51:57Z</t>
+          <t>2026-10-01T00:02:20Z</t>
         </is>
       </c>
     </row>
@@ -1586,7 +1586,7 @@
       </c>
       <c r="S17" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T23:51:57Z</t>
+          <t>2026-10-01T00:02:20Z</t>
         </is>
       </c>
     </row>
@@ -1671,7 +1671,7 @@
       </c>
       <c r="S18" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T23:51:57Z</t>
+          <t>2026-10-01T00:02:20Z</t>
         </is>
       </c>
     </row>
@@ -1756,7 +1756,7 @@
       </c>
       <c r="S19" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T23:51:57Z</t>
+          <t>2026-10-01T00:02:20Z</t>
         </is>
       </c>
     </row>
@@ -1841,7 +1841,7 @@
       </c>
       <c r="S20" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T23:51:57Z</t>
+          <t>2026-10-01T00:02:20Z</t>
         </is>
       </c>
     </row>
@@ -1926,7 +1926,7 @@
       </c>
       <c r="S21" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T23:51:57Z</t>
+          <t>2026-10-01T00:02:20Z</t>
         </is>
       </c>
     </row>
@@ -2011,7 +2011,7 @@
       </c>
       <c r="S22" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T23:51:57Z</t>
+          <t>2026-10-01T00:02:20Z</t>
         </is>
       </c>
     </row>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="S23" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T23:51:57Z</t>
+          <t>2026-10-01T00:02:20Z</t>
         </is>
       </c>
     </row>
@@ -2181,7 +2181,7 @@
       </c>
       <c r="S24" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T23:51:57Z</t>
+          <t>2026-10-01T00:02:20Z</t>
         </is>
       </c>
     </row>
@@ -2266,7 +2266,7 @@
       </c>
       <c r="S25" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T23:51:57Z</t>
+          <t>2026-10-01T00:02:20Z</t>
         </is>
       </c>
     </row>
@@ -2351,7 +2351,7 @@
       </c>
       <c r="S26" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T23:51:57Z</t>
+          <t>2026-10-01T00:02:20Z</t>
         </is>
       </c>
     </row>
@@ -2436,7 +2436,7 @@
       </c>
       <c r="S27" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T23:51:57Z</t>
+          <t>2026-10-01T00:02:20Z</t>
         </is>
       </c>
     </row>
@@ -2525,7 +2525,7 @@
       </c>
       <c r="S28" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T23:51:57Z</t>
+          <t>2026-10-01T00:02:20Z</t>
         </is>
       </c>
     </row>
@@ -2614,7 +2614,7 @@
       </c>
       <c r="S29" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T23:51:57Z</t>
+          <t>2026-10-01T00:02:20Z</t>
         </is>
       </c>
     </row>
@@ -2699,7 +2699,7 @@
       </c>
       <c r="S30" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T23:51:57Z</t>
+          <t>2026-10-01T00:02:20Z</t>
         </is>
       </c>
     </row>
@@ -2788,7 +2788,7 @@
       </c>
       <c r="S31" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T23:51:57Z</t>
+          <t>2026-10-01T00:02:20Z</t>
         </is>
       </c>
     </row>
@@ -2877,7 +2877,7 @@
       </c>
       <c r="S32" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T23:51:57Z</t>
+          <t>2026-10-01T00:02:20Z</t>
         </is>
       </c>
     </row>
@@ -2962,7 +2962,7 @@
       </c>
       <c r="S33" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T23:51:57Z</t>
+          <t>2026-10-01T00:02:20Z</t>
         </is>
       </c>
     </row>
@@ -3051,7 +3051,7 @@
       </c>
       <c r="S34" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T23:51:57Z</t>
+          <t>2026-10-01T00:02:20Z</t>
         </is>
       </c>
     </row>
@@ -3140,7 +3140,7 @@
       </c>
       <c r="S35" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T23:51:57Z</t>
+          <t>2026-10-01T00:02:20Z</t>
         </is>
       </c>
     </row>
@@ -3225,7 +3225,7 @@
       </c>
       <c r="S36" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T23:51:57Z</t>
+          <t>2026-10-01T00:02:20Z</t>
         </is>
       </c>
     </row>
@@ -3314,7 +3314,7 @@
       </c>
       <c r="S37" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T23:51:57Z</t>
+          <t>2026-10-01T00:02:20Z</t>
         </is>
       </c>
     </row>
@@ -3403,7 +3403,7 @@
       </c>
       <c r="S38" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T23:51:57Z</t>
+          <t>2026-10-01T00:02:20Z</t>
         </is>
       </c>
     </row>
@@ -3488,7 +3488,7 @@
       </c>
       <c r="S39" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T23:51:57Z</t>
+          <t>2026-10-01T00:02:20Z</t>
         </is>
       </c>
     </row>
@@ -3577,7 +3577,7 @@
       </c>
       <c r="S40" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T23:51:57Z</t>
+          <t>2026-10-01T00:02:20Z</t>
         </is>
       </c>
     </row>
@@ -3666,7 +3666,7 @@
       </c>
       <c r="S41" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T23:51:57Z</t>
+          <t>2026-10-01T00:02:20Z</t>
         </is>
       </c>
     </row>
@@ -3751,7 +3751,7 @@
       </c>
       <c r="S42" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T23:51:57Z</t>
+          <t>2026-10-01T00:02:20Z</t>
         </is>
       </c>
     </row>
@@ -3840,7 +3840,7 @@
       </c>
       <c r="S43" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T23:51:57Z</t>
+          <t>2026-10-01T00:02:20Z</t>
         </is>
       </c>
     </row>
@@ -3929,7 +3929,7 @@
       </c>
       <c r="S44" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T23:51:57Z</t>
+          <t>2026-10-01T00:02:20Z</t>
         </is>
       </c>
     </row>
@@ -4014,7 +4014,7 @@
       </c>
       <c r="S45" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T23:51:57Z</t>
+          <t>2026-10-01T00:02:20Z</t>
         </is>
       </c>
     </row>
@@ -4103,7 +4103,7 @@
       </c>
       <c r="S46" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T23:51:57Z</t>
+          <t>2026-10-01T00:02:20Z</t>
         </is>
       </c>
     </row>
@@ -4192,7 +4192,7 @@
       </c>
       <c r="S47" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T23:51:57Z</t>
+          <t>2026-10-01T00:02:20Z</t>
         </is>
       </c>
     </row>
@@ -4277,7 +4277,7 @@
       </c>
       <c r="S48" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T23:51:57Z</t>
+          <t>2026-10-01T00:02:20Z</t>
         </is>
       </c>
     </row>
@@ -4366,7 +4366,7 @@
       </c>
       <c r="S49" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T23:51:57Z</t>
+          <t>2026-10-01T00:02:20Z</t>
         </is>
       </c>
     </row>
@@ -4455,7 +4455,7 @@
       </c>
       <c r="S50" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T23:51:57Z</t>
+          <t>2026-10-01T00:02:20Z</t>
         </is>
       </c>
     </row>
@@ -4540,7 +4540,7 @@
       </c>
       <c r="S51" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T23:51:57Z</t>
+          <t>2026-10-01T00:02:20Z</t>
         </is>
       </c>
     </row>
@@ -4629,7 +4629,7 @@
       </c>
       <c r="S52" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T23:51:57Z</t>
+          <t>2026-10-01T00:02:20Z</t>
         </is>
       </c>
     </row>
@@ -4718,7 +4718,7 @@
       </c>
       <c r="S53" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T23:51:57Z</t>
+          <t>2026-10-01T00:02:20Z</t>
         </is>
       </c>
     </row>
@@ -4803,7 +4803,7 @@
       </c>
       <c r="S54" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T23:51:57Z</t>
+          <t>2026-10-01T00:02:20Z</t>
         </is>
       </c>
     </row>
@@ -4892,7 +4892,7 @@
       </c>
       <c r="S55" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T23:51:57Z</t>
+          <t>2026-10-01T00:02:20Z</t>
         </is>
       </c>
     </row>
@@ -4981,7 +4981,7 @@
       </c>
       <c r="S56" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T23:51:57Z</t>
+          <t>2026-10-01T00:02:20Z</t>
         </is>
       </c>
     </row>
@@ -5070,7 +5070,7 @@
       </c>
       <c r="S57" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T23:51:57Z</t>
+          <t>2026-10-01T00:02:20Z</t>
         </is>
       </c>
     </row>
@@ -5159,7 +5159,7 @@
       </c>
       <c r="S58" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T23:51:57Z</t>
+          <t>2026-10-01T00:02:20Z</t>
         </is>
       </c>
     </row>
@@ -5248,7 +5248,7 @@
       </c>
       <c r="S59" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T23:51:57Z</t>
+          <t>2026-10-01T00:02:20Z</t>
         </is>
       </c>
     </row>
@@ -5337,7 +5337,7 @@
       </c>
       <c r="S60" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T23:51:57Z</t>
+          <t>2026-10-01T00:02:20Z</t>
         </is>
       </c>
     </row>
@@ -5426,7 +5426,7 @@
       </c>
       <c r="S61" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T23:51:57Z</t>
+          <t>2026-10-01T00:02:20Z</t>
         </is>
       </c>
     </row>
@@ -5515,7 +5515,7 @@
       </c>
       <c r="S62" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T23:51:57Z</t>
+          <t>2026-10-01T00:02:20Z</t>
         </is>
       </c>
     </row>
@@ -5604,7 +5604,7 @@
       </c>
       <c r="S63" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T23:51:57Z</t>
+          <t>2026-10-01T00:02:20Z</t>
         </is>
       </c>
     </row>
@@ -5693,7 +5693,7 @@
       </c>
       <c r="S64" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T23:51:57Z</t>
+          <t>2026-10-01T00:02:20Z</t>
         </is>
       </c>
     </row>
@@ -5782,7 +5782,7 @@
       </c>
       <c r="S65" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T23:51:57Z</t>
+          <t>2026-10-01T00:02:20Z</t>
         </is>
       </c>
     </row>
@@ -5871,7 +5871,7 @@
       </c>
       <c r="S66" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T23:51:57Z</t>
+          <t>2026-10-01T00:02:20Z</t>
         </is>
       </c>
     </row>
@@ -5960,7 +5960,7 @@
       </c>
       <c r="S67" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T23:51:57Z</t>
+          <t>2026-10-01T00:02:20Z</t>
         </is>
       </c>
     </row>
@@ -6045,7 +6045,7 @@
       </c>
       <c r="S68" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T23:51:57Z</t>
+          <t>2026-10-01T00:02:20Z</t>
         </is>
       </c>
     </row>
@@ -6130,7 +6130,7 @@
       </c>
       <c r="S69" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T23:51:57Z</t>
+          <t>2026-10-01T00:02:20Z</t>
         </is>
       </c>
     </row>
@@ -6215,7 +6215,7 @@
       </c>
       <c r="S70" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T23:51:57Z</t>
+          <t>2026-10-01T00:02:20Z</t>
         </is>
       </c>
     </row>
@@ -6300,7 +6300,7 @@
       </c>
       <c r="S71" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T23:51:57Z</t>
+          <t>2026-10-01T00:02:20Z</t>
         </is>
       </c>
     </row>
@@ -6385,7 +6385,7 @@
       </c>
       <c r="S72" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T23:51:57Z</t>
+          <t>2026-10-01T00:02:20Z</t>
         </is>
       </c>
     </row>
@@ -6470,7 +6470,7 @@
       </c>
       <c r="S73" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T23:51:57Z</t>
+          <t>2026-10-01T00:02:20Z</t>
         </is>
       </c>
     </row>
@@ -6555,7 +6555,7 @@
       </c>
       <c r="S74" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T23:51:57Z</t>
+          <t>2026-10-01T00:02:20Z</t>
         </is>
       </c>
     </row>
@@ -6640,7 +6640,7 @@
       </c>
       <c r="S75" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T23:51:57Z</t>
+          <t>2026-10-01T00:02:20Z</t>
         </is>
       </c>
     </row>
@@ -6725,7 +6725,7 @@
       </c>
       <c r="S76" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T23:51:57Z</t>
+          <t>2026-10-01T00:02:20Z</t>
         </is>
       </c>
     </row>
@@ -6810,7 +6810,7 @@
       </c>
       <c r="S77" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T23:51:57Z</t>
+          <t>2026-10-01T00:02:20Z</t>
         </is>
       </c>
     </row>
@@ -6895,7 +6895,7 @@
       </c>
       <c r="S78" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T23:51:57Z</t>
+          <t>2026-10-01T00:02:20Z</t>
         </is>
       </c>
     </row>
@@ -6980,7 +6980,7 @@
       </c>
       <c r="S79" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T23:51:57Z</t>
+          <t>2026-10-01T00:02:20Z</t>
         </is>
       </c>
     </row>
@@ -7065,7 +7065,7 @@
       </c>
       <c r="S80" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T23:51:57Z</t>
+          <t>2026-10-01T00:02:20Z</t>
         </is>
       </c>
     </row>
@@ -7150,7 +7150,7 @@
       </c>
       <c r="S81" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T23:51:57Z</t>
+          <t>2026-10-01T00:02:20Z</t>
         </is>
       </c>
     </row>
@@ -7235,7 +7235,7 @@
       </c>
       <c r="S82" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T23:51:57Z</t>
+          <t>2026-10-01T00:02:20Z</t>
         </is>
       </c>
     </row>
@@ -7320,7 +7320,7 @@
       </c>
       <c r="S83" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T23:51:57Z</t>
+          <t>2026-10-01T00:02:20Z</t>
         </is>
       </c>
     </row>
@@ -7405,7 +7405,7 @@
       </c>
       <c r="S84" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T23:51:57Z</t>
+          <t>2026-10-01T00:02:20Z</t>
         </is>
       </c>
     </row>
@@ -7490,7 +7490,7 @@
       </c>
       <c r="S85" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T23:51:57Z</t>
+          <t>2026-10-01T00:02:20Z</t>
         </is>
       </c>
     </row>
@@ -7575,7 +7575,7 @@
       </c>
       <c r="S86" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T23:51:57Z</t>
+          <t>2026-10-01T00:02:20Z</t>
         </is>
       </c>
     </row>
@@ -7660,7 +7660,7 @@
       </c>
       <c r="S87" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T23:51:57Z</t>
+          <t>2026-10-01T00:02:20Z</t>
         </is>
       </c>
     </row>
@@ -7745,7 +7745,7 @@
       </c>
       <c r="S88" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T23:51:57Z</t>
+          <t>2026-10-01T00:02:20Z</t>
         </is>
       </c>
     </row>
@@ -7834,7 +7834,7 @@
       </c>
       <c r="S89" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T23:51:57Z</t>
+          <t>2026-10-01T00:02:20Z</t>
         </is>
       </c>
     </row>
@@ -7923,7 +7923,7 @@
       </c>
       <c r="S90" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T23:51:57Z</t>
+          <t>2026-10-01T00:02:20Z</t>
         </is>
       </c>
     </row>
@@ -8008,7 +8008,7 @@
       </c>
       <c r="S91" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T23:51:57Z</t>
+          <t>2026-10-01T00:02:20Z</t>
         </is>
       </c>
     </row>
@@ -8097,7 +8097,7 @@
       </c>
       <c r="S92" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T23:51:57Z</t>
+          <t>2026-10-01T00:02:20Z</t>
         </is>
       </c>
     </row>
@@ -8186,7 +8186,7 @@
       </c>
       <c r="S93" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T23:51:57Z</t>
+          <t>2026-10-01T00:02:20Z</t>
         </is>
       </c>
     </row>
@@ -8271,7 +8271,7 @@
       </c>
       <c r="S94" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T23:51:57Z</t>
+          <t>2026-10-01T00:02:20Z</t>
         </is>
       </c>
     </row>
@@ -8360,7 +8360,7 @@
       </c>
       <c r="S95" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T23:51:57Z</t>
+          <t>2026-10-01T00:02:20Z</t>
         </is>
       </c>
     </row>
@@ -8449,7 +8449,7 @@
       </c>
       <c r="S96" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T23:51:57Z</t>
+          <t>2026-10-01T00:02:20Z</t>
         </is>
       </c>
     </row>
@@ -8534,7 +8534,7 @@
       </c>
       <c r="S97" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T23:51:57Z</t>
+          <t>2026-10-01T00:02:20Z</t>
         </is>
       </c>
     </row>
@@ -8623,7 +8623,7 @@
       </c>
       <c r="S98" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T23:51:57Z</t>
+          <t>2026-10-01T00:02:20Z</t>
         </is>
       </c>
     </row>
@@ -8712,7 +8712,7 @@
       </c>
       <c r="S99" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T23:51:57Z</t>
+          <t>2026-10-01T00:02:20Z</t>
         </is>
       </c>
     </row>
@@ -8797,7 +8797,7 @@
       </c>
       <c r="S100" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T23:51:57Z</t>
+          <t>2026-10-01T00:02:20Z</t>
         </is>
       </c>
     </row>
@@ -8886,7 +8886,7 @@
       </c>
       <c r="S101" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T23:51:57Z</t>
+          <t>2026-10-01T00:02:20Z</t>
         </is>
       </c>
     </row>
@@ -8975,7 +8975,7 @@
       </c>
       <c r="S102" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T23:51:57Z</t>
+          <t>2026-10-01T00:02:20Z</t>
         </is>
       </c>
     </row>
@@ -9060,7 +9060,7 @@
       </c>
       <c r="S103" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T23:51:57Z</t>
+          <t>2026-10-01T00:02:20Z</t>
         </is>
       </c>
     </row>
@@ -9149,7 +9149,7 @@
       </c>
       <c r="S104" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T23:51:57Z</t>
+          <t>2026-10-01T00:02:20Z</t>
         </is>
       </c>
     </row>
@@ -9238,7 +9238,7 @@
       </c>
       <c r="S105" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T23:51:57Z</t>
+          <t>2026-10-01T00:02:20Z</t>
         </is>
       </c>
     </row>
@@ -9323,7 +9323,7 @@
       </c>
       <c r="S106" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T23:51:57Z</t>
+          <t>2026-10-01T00:02:20Z</t>
         </is>
       </c>
     </row>
@@ -9412,7 +9412,7 @@
       </c>
       <c r="S107" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T23:51:57Z</t>
+          <t>2026-10-01T00:02:20Z</t>
         </is>
       </c>
     </row>
@@ -9501,7 +9501,7 @@
       </c>
       <c r="S108" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T23:51:57Z</t>
+          <t>2026-10-01T00:02:20Z</t>
         </is>
       </c>
     </row>
@@ -9586,7 +9586,7 @@
       </c>
       <c r="S109" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T23:51:57Z</t>
+          <t>2026-10-01T00:02:20Z</t>
         </is>
       </c>
     </row>
@@ -9675,7 +9675,7 @@
       </c>
       <c r="S110" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T23:51:57Z</t>
+          <t>2026-10-01T00:02:20Z</t>
         </is>
       </c>
     </row>
@@ -9764,7 +9764,7 @@
       </c>
       <c r="S111" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T23:51:57Z</t>
+          <t>2026-10-01T00:02:20Z</t>
         </is>
       </c>
     </row>
@@ -9849,7 +9849,7 @@
       </c>
       <c r="S112" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T23:51:57Z</t>
+          <t>2026-10-01T00:02:20Z</t>
         </is>
       </c>
     </row>
@@ -9938,7 +9938,7 @@
       </c>
       <c r="S113" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T23:51:57Z</t>
+          <t>2026-10-01T00:02:20Z</t>
         </is>
       </c>
     </row>
@@ -10027,7 +10027,7 @@
       </c>
       <c r="S114" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T23:51:57Z</t>
+          <t>2026-10-01T00:02:20Z</t>
         </is>
       </c>
     </row>
@@ -10112,7 +10112,7 @@
       </c>
       <c r="S115" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T23:51:57Z</t>
+          <t>2026-10-01T00:02:20Z</t>
         </is>
       </c>
     </row>
@@ -10201,7 +10201,7 @@
       </c>
       <c r="S116" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T23:51:57Z</t>
+          <t>2026-10-01T00:02:20Z</t>
         </is>
       </c>
     </row>
@@ -10290,7 +10290,7 @@
       </c>
       <c r="S117" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T23:51:57Z</t>
+          <t>2026-10-01T00:02:20Z</t>
         </is>
       </c>
     </row>
@@ -10379,7 +10379,7 @@
       </c>
       <c r="S118" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T23:51:57Z</t>
+          <t>2026-10-01T00:02:20Z</t>
         </is>
       </c>
     </row>
@@ -10468,7 +10468,7 @@
       </c>
       <c r="S119" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T23:51:57Z</t>
+          <t>2026-10-01T00:02:20Z</t>
         </is>
       </c>
     </row>
@@ -10557,7 +10557,7 @@
       </c>
       <c r="S120" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T23:51:57Z</t>
+          <t>2026-10-01T00:02:20Z</t>
         </is>
       </c>
     </row>
@@ -10646,7 +10646,7 @@
       </c>
       <c r="S121" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T23:51:57Z</t>
+          <t>2026-10-01T00:02:20Z</t>
         </is>
       </c>
     </row>
@@ -10735,7 +10735,7 @@
       </c>
       <c r="S122" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T23:51:57Z</t>
+          <t>2026-10-01T00:02:20Z</t>
         </is>
       </c>
     </row>
@@ -10824,7 +10824,7 @@
       </c>
       <c r="S123" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T23:51:57Z</t>
+          <t>2026-10-01T00:02:20Z</t>
         </is>
       </c>
     </row>
@@ -10913,7 +10913,7 @@
       </c>
       <c r="S124" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T23:51:57Z</t>
+          <t>2026-10-01T00:02:20Z</t>
         </is>
       </c>
     </row>
@@ -11002,7 +11002,7 @@
       </c>
       <c r="S125" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T23:51:57Z</t>
+          <t>2026-10-01T00:02:20Z</t>
         </is>
       </c>
     </row>
@@ -11091,7 +11091,7 @@
       </c>
       <c r="S126" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T23:51:57Z</t>
+          <t>2026-10-01T00:02:20Z</t>
         </is>
       </c>
     </row>
@@ -11180,7 +11180,7 @@
       </c>
       <c r="S127" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T23:51:57Z</t>
+          <t>2026-10-01T00:02:20Z</t>
         </is>
       </c>
     </row>
@@ -11269,7 +11269,7 @@
       </c>
       <c r="S128" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T23:51:57Z</t>
+          <t>2026-10-01T00:02:20Z</t>
         </is>
       </c>
     </row>
@@ -11354,7 +11354,7 @@
       </c>
       <c r="S129" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T23:51:57Z</t>
+          <t>2026-10-01T00:02:20Z</t>
         </is>
       </c>
     </row>
@@ -11439,7 +11439,7 @@
       </c>
       <c r="S130" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T23:51:57Z</t>
+          <t>2026-10-01T00:02:20Z</t>
         </is>
       </c>
     </row>
@@ -11524,7 +11524,7 @@
       </c>
       <c r="S131" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T23:51:57Z</t>
+          <t>2026-10-01T00:02:20Z</t>
         </is>
       </c>
     </row>
@@ -11609,7 +11609,7 @@
       </c>
       <c r="S132" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T23:51:57Z</t>
+          <t>2026-10-01T00:02:20Z</t>
         </is>
       </c>
     </row>
@@ -11694,7 +11694,7 @@
       </c>
       <c r="S133" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T23:51:57Z</t>
+          <t>2026-10-01T00:02:20Z</t>
         </is>
       </c>
     </row>
@@ -11779,7 +11779,7 @@
       </c>
       <c r="S134" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T23:51:57Z</t>
+          <t>2026-10-01T00:02:20Z</t>
         </is>
       </c>
     </row>
@@ -11864,7 +11864,7 @@
       </c>
       <c r="S135" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T23:51:57Z</t>
+          <t>2026-10-01T00:02:20Z</t>
         </is>
       </c>
     </row>
@@ -11949,7 +11949,7 @@
       </c>
       <c r="S136" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T23:51:57Z</t>
+          <t>2026-10-01T00:02:20Z</t>
         </is>
       </c>
     </row>
@@ -12034,7 +12034,7 @@
       </c>
       <c r="S137" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T23:51:57Z</t>
+          <t>2026-10-01T00:02:20Z</t>
         </is>
       </c>
     </row>
@@ -12119,7 +12119,7 @@
       </c>
       <c r="S138" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T23:51:57Z</t>
+          <t>2026-10-01T00:02:20Z</t>
         </is>
       </c>
     </row>
@@ -12204,7 +12204,7 @@
       </c>
       <c r="S139" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T23:51:57Z</t>
+          <t>2026-10-01T00:02:20Z</t>
         </is>
       </c>
     </row>
@@ -12289,7 +12289,7 @@
       </c>
       <c r="S140" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T23:51:57Z</t>
+          <t>2026-10-01T00:02:20Z</t>
         </is>
       </c>
     </row>
@@ -12374,7 +12374,7 @@
       </c>
       <c r="S141" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T23:51:57Z</t>
+          <t>2026-10-01T00:02:20Z</t>
         </is>
       </c>
     </row>
@@ -12459,7 +12459,7 @@
       </c>
       <c r="S142" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T23:51:57Z</t>
+          <t>2026-10-01T00:02:20Z</t>
         </is>
       </c>
     </row>
@@ -12544,7 +12544,7 @@
       </c>
       <c r="S143" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T23:51:57Z</t>
+          <t>2026-10-01T00:02:20Z</t>
         </is>
       </c>
     </row>
@@ -12629,7 +12629,7 @@
       </c>
       <c r="S144" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T23:51:57Z</t>
+          <t>2026-10-01T00:02:20Z</t>
         </is>
       </c>
     </row>
@@ -12714,7 +12714,7 @@
       </c>
       <c r="S145" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T23:51:57Z</t>
+          <t>2026-10-01T00:02:20Z</t>
         </is>
       </c>
     </row>
@@ -12799,7 +12799,7 @@
       </c>
       <c r="S146" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T23:51:57Z</t>
+          <t>2026-10-01T00:02:20Z</t>
         </is>
       </c>
     </row>
@@ -12884,7 +12884,7 @@
       </c>
       <c r="S147" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T23:51:57Z</t>
+          <t>2026-10-01T00:02:20Z</t>
         </is>
       </c>
     </row>
@@ -12969,7 +12969,7 @@
       </c>
       <c r="S148" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T23:51:57Z</t>
+          <t>2026-10-01T00:02:20Z</t>
         </is>
       </c>
     </row>
@@ -13054,7 +13054,7 @@
       </c>
       <c r="S149" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T23:51:57Z</t>
+          <t>2026-10-01T00:02:20Z</t>
         </is>
       </c>
     </row>
@@ -13143,7 +13143,7 @@
       </c>
       <c r="S150" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T23:51:57Z</t>
+          <t>2026-10-01T00:02:20Z</t>
         </is>
       </c>
     </row>
@@ -13232,7 +13232,7 @@
       </c>
       <c r="S151" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T23:51:57Z</t>
+          <t>2026-10-01T00:02:20Z</t>
         </is>
       </c>
     </row>
@@ -13317,7 +13317,7 @@
       </c>
       <c r="S152" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T23:51:57Z</t>
+          <t>2026-10-01T00:02:20Z</t>
         </is>
       </c>
     </row>
@@ -13406,7 +13406,7 @@
       </c>
       <c r="S153" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T23:51:57Z</t>
+          <t>2026-10-01T00:02:20Z</t>
         </is>
       </c>
     </row>
@@ -13495,7 +13495,7 @@
       </c>
       <c r="S154" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T23:51:57Z</t>
+          <t>2026-10-01T00:02:20Z</t>
         </is>
       </c>
     </row>
@@ -13580,7 +13580,7 @@
       </c>
       <c r="S155" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T23:51:57Z</t>
+          <t>2026-10-01T00:02:20Z</t>
         </is>
       </c>
     </row>
@@ -13669,7 +13669,7 @@
       </c>
       <c r="S156" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T23:51:57Z</t>
+          <t>2026-10-01T00:02:20Z</t>
         </is>
       </c>
     </row>
@@ -13758,7 +13758,7 @@
       </c>
       <c r="S157" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T23:51:57Z</t>
+          <t>2026-10-01T00:02:20Z</t>
         </is>
       </c>
     </row>
@@ -13843,7 +13843,7 @@
       </c>
       <c r="S158" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T23:51:57Z</t>
+          <t>2026-10-01T00:02:20Z</t>
         </is>
       </c>
     </row>
@@ -13932,7 +13932,7 @@
       </c>
       <c r="S159" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T23:51:57Z</t>
+          <t>2026-10-01T00:02:20Z</t>
         </is>
       </c>
     </row>
@@ -14021,7 +14021,7 @@
       </c>
       <c r="S160" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T23:51:57Z</t>
+          <t>2026-10-01T00:02:20Z</t>
         </is>
       </c>
     </row>
@@ -14106,7 +14106,7 @@
       </c>
       <c r="S161" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T23:51:57Z</t>
+          <t>2026-10-01T00:02:20Z</t>
         </is>
       </c>
     </row>
@@ -14195,7 +14195,7 @@
       </c>
       <c r="S162" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T23:51:57Z</t>
+          <t>2026-10-01T00:02:20Z</t>
         </is>
       </c>
     </row>
@@ -14284,7 +14284,7 @@
       </c>
       <c r="S163" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T23:51:57Z</t>
+          <t>2026-10-01T00:02:20Z</t>
         </is>
       </c>
     </row>
@@ -14369,7 +14369,7 @@
       </c>
       <c r="S164" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T23:51:57Z</t>
+          <t>2026-10-01T00:02:20Z</t>
         </is>
       </c>
     </row>
@@ -14458,7 +14458,7 @@
       </c>
       <c r="S165" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T23:51:57Z</t>
+          <t>2026-10-01T00:02:20Z</t>
         </is>
       </c>
     </row>
@@ -14547,7 +14547,7 @@
       </c>
       <c r="S166" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T23:51:57Z</t>
+          <t>2026-10-01T00:02:20Z</t>
         </is>
       </c>
     </row>
@@ -14632,7 +14632,7 @@
       </c>
       <c r="S167" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T23:51:57Z</t>
+          <t>2026-10-01T00:02:20Z</t>
         </is>
       </c>
     </row>
@@ -14721,7 +14721,7 @@
       </c>
       <c r="S168" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T23:51:57Z</t>
+          <t>2026-10-01T00:02:20Z</t>
         </is>
       </c>
     </row>
@@ -14810,7 +14810,7 @@
       </c>
       <c r="S169" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T23:51:57Z</t>
+          <t>2026-10-01T00:02:20Z</t>
         </is>
       </c>
     </row>
@@ -14895,7 +14895,7 @@
       </c>
       <c r="S170" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T23:51:57Z</t>
+          <t>2026-10-01T00:02:20Z</t>
         </is>
       </c>
     </row>
@@ -14984,7 +14984,7 @@
       </c>
       <c r="S171" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T23:51:57Z</t>
+          <t>2026-10-01T00:02:20Z</t>
         </is>
       </c>
     </row>
@@ -15073,7 +15073,7 @@
       </c>
       <c r="S172" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T23:51:57Z</t>
+          <t>2026-10-01T00:02:20Z</t>
         </is>
       </c>
     </row>
@@ -15158,7 +15158,7 @@
       </c>
       <c r="S173" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T23:51:57Z</t>
+          <t>2026-10-01T00:02:20Z</t>
         </is>
       </c>
     </row>
@@ -15247,7 +15247,7 @@
       </c>
       <c r="S174" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T23:51:57Z</t>
+          <t>2026-10-01T00:02:20Z</t>
         </is>
       </c>
     </row>
@@ -15336,7 +15336,7 @@
       </c>
       <c r="S175" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T23:51:57Z</t>
+          <t>2026-10-01T00:02:20Z</t>
         </is>
       </c>
     </row>
@@ -15421,7 +15421,7 @@
       </c>
       <c r="S176" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T23:51:57Z</t>
+          <t>2026-10-01T00:02:20Z</t>
         </is>
       </c>
     </row>
@@ -15510,7 +15510,7 @@
       </c>
       <c r="S177" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T23:51:57Z</t>
+          <t>2026-10-01T00:02:20Z</t>
         </is>
       </c>
     </row>
@@ -15599,7 +15599,7 @@
       </c>
       <c r="S178" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T23:51:57Z</t>
+          <t>2026-10-01T00:02:20Z</t>
         </is>
       </c>
     </row>
@@ -15688,7 +15688,7 @@
       </c>
       <c r="S179" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T23:51:57Z</t>
+          <t>2026-10-01T00:02:20Z</t>
         </is>
       </c>
     </row>
@@ -15777,7 +15777,7 @@
       </c>
       <c r="S180" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T23:51:57Z</t>
+          <t>2026-10-01T00:02:20Z</t>
         </is>
       </c>
     </row>
@@ -15866,7 +15866,7 @@
       </c>
       <c r="S181" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T23:51:57Z</t>
+          <t>2026-10-01T00:02:20Z</t>
         </is>
       </c>
     </row>
@@ -15955,7 +15955,7 @@
       </c>
       <c r="S182" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T23:51:57Z</t>
+          <t>2026-10-01T00:02:20Z</t>
         </is>
       </c>
     </row>
@@ -16044,7 +16044,7 @@
       </c>
       <c r="S183" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T23:51:57Z</t>
+          <t>2026-10-01T00:02:20Z</t>
         </is>
       </c>
     </row>
@@ -16133,7 +16133,7 @@
       </c>
       <c r="S184" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T23:51:57Z</t>
+          <t>2026-10-01T00:02:20Z</t>
         </is>
       </c>
     </row>
@@ -16222,7 +16222,7 @@
       </c>
       <c r="S185" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T23:51:57Z</t>
+          <t>2026-10-01T00:02:20Z</t>
         </is>
       </c>
     </row>
@@ -16311,7 +16311,7 @@
       </c>
       <c r="S186" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T23:51:57Z</t>
+          <t>2026-10-01T00:02:20Z</t>
         </is>
       </c>
     </row>
@@ -16400,7 +16400,7 @@
       </c>
       <c r="S187" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T23:51:57Z</t>
+          <t>2026-10-01T00:02:20Z</t>
         </is>
       </c>
     </row>
@@ -16489,7 +16489,7 @@
       </c>
       <c r="S188" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T23:51:57Z</t>
+          <t>2026-10-01T00:02:20Z</t>
         </is>
       </c>
     </row>
@@ -16578,7 +16578,7 @@
       </c>
       <c r="S189" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T23:51:57Z</t>
+          <t>2026-10-01T00:02:20Z</t>
         </is>
       </c>
     </row>
@@ -16663,7 +16663,7 @@
       </c>
       <c r="S190" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T23:51:57Z</t>
+          <t>2026-10-01T00:02:20Z</t>
         </is>
       </c>
     </row>
@@ -16748,7 +16748,7 @@
       </c>
       <c r="S191" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T23:51:57Z</t>
+          <t>2026-10-01T00:02:20Z</t>
         </is>
       </c>
     </row>
@@ -16833,7 +16833,7 @@
       </c>
       <c r="S192" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T23:51:57Z</t>
+          <t>2026-10-01T00:02:20Z</t>
         </is>
       </c>
     </row>
@@ -16918,7 +16918,7 @@
       </c>
       <c r="S193" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T23:51:57Z</t>
+          <t>2026-10-01T00:02:20Z</t>
         </is>
       </c>
     </row>
@@ -17003,7 +17003,7 @@
       </c>
       <c r="S194" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T23:51:57Z</t>
+          <t>2026-10-01T00:02:20Z</t>
         </is>
       </c>
     </row>
@@ -17088,7 +17088,7 @@
       </c>
       <c r="S195" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T23:51:57Z</t>
+          <t>2026-10-01T00:02:20Z</t>
         </is>
       </c>
     </row>
@@ -17173,7 +17173,7 @@
       </c>
       <c r="S196" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T23:51:57Z</t>
+          <t>2026-10-01T00:02:20Z</t>
         </is>
       </c>
     </row>
@@ -17258,7 +17258,7 @@
       </c>
       <c r="S197" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T23:51:57Z</t>
+          <t>2026-10-01T00:02:20Z</t>
         </is>
       </c>
     </row>
@@ -17343,7 +17343,7 @@
       </c>
       <c r="S198" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T23:51:57Z</t>
+          <t>2026-10-01T00:02:20Z</t>
         </is>
       </c>
     </row>
@@ -17428,7 +17428,7 @@
       </c>
       <c r="S199" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T23:51:57Z</t>
+          <t>2026-10-01T00:02:20Z</t>
         </is>
       </c>
     </row>
@@ -17513,7 +17513,7 @@
       </c>
       <c r="S200" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T23:51:57Z</t>
+          <t>2026-10-01T00:02:20Z</t>
         </is>
       </c>
     </row>
@@ -17598,7 +17598,7 @@
       </c>
       <c r="S201" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T23:51:57Z</t>
+          <t>2026-10-01T00:02:20Z</t>
         </is>
       </c>
     </row>
@@ -17683,7 +17683,7 @@
       </c>
       <c r="S202" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T23:51:57Z</t>
+          <t>2026-10-01T00:02:20Z</t>
         </is>
       </c>
     </row>
@@ -17768,7 +17768,7 @@
       </c>
       <c r="S203" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T23:51:57Z</t>
+          <t>2026-10-01T00:02:20Z</t>
         </is>
       </c>
     </row>
@@ -17853,7 +17853,7 @@
       </c>
       <c r="S204" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T23:51:57Z</t>
+          <t>2026-10-01T00:02:20Z</t>
         </is>
       </c>
     </row>
@@ -17938,7 +17938,7 @@
       </c>
       <c r="S205" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T23:51:57Z</t>
+          <t>2026-10-01T00:02:20Z</t>
         </is>
       </c>
     </row>
@@ -18023,7 +18023,7 @@
       </c>
       <c r="S206" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T23:51:57Z</t>
+          <t>2026-10-01T00:02:20Z</t>
         </is>
       </c>
     </row>
@@ -18108,7 +18108,7 @@
       </c>
       <c r="S207" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T23:51:57Z</t>
+          <t>2026-10-01T00:02:20Z</t>
         </is>
       </c>
     </row>
@@ -18193,7 +18193,7 @@
       </c>
       <c r="S208" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T23:51:57Z</t>
+          <t>2026-10-01T00:02:20Z</t>
         </is>
       </c>
     </row>
@@ -18278,7 +18278,7 @@
       </c>
       <c r="S209" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T23:51:57Z</t>
+          <t>2026-10-01T00:02:20Z</t>
         </is>
       </c>
     </row>
@@ -18363,7 +18363,7 @@
       </c>
       <c r="S210" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T23:51:57Z</t>
+          <t>2026-10-01T00:02:20Z</t>
         </is>
       </c>
     </row>
@@ -18452,7 +18452,7 @@
       </c>
       <c r="S211" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T23:51:57Z</t>
+          <t>2026-10-01T00:02:20Z</t>
         </is>
       </c>
     </row>
@@ -18541,7 +18541,7 @@
       </c>
       <c r="S212" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T23:51:57Z</t>
+          <t>2026-10-01T00:02:20Z</t>
         </is>
       </c>
     </row>
@@ -18626,7 +18626,7 @@
       </c>
       <c r="S213" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T23:51:57Z</t>
+          <t>2026-10-01T00:02:20Z</t>
         </is>
       </c>
     </row>
@@ -18715,7 +18715,7 @@
       </c>
       <c r="S214" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T23:51:57Z</t>
+          <t>2026-10-01T00:02:20Z</t>
         </is>
       </c>
     </row>
@@ -18804,7 +18804,7 @@
       </c>
       <c r="S215" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T23:51:57Z</t>
+          <t>2026-10-01T00:02:20Z</t>
         </is>
       </c>
     </row>
@@ -18889,7 +18889,7 @@
       </c>
       <c r="S216" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T23:51:57Z</t>
+          <t>2026-10-01T00:02:20Z</t>
         </is>
       </c>
     </row>
@@ -18978,7 +18978,7 @@
       </c>
       <c r="S217" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T23:51:57Z</t>
+          <t>2026-10-01T00:02:20Z</t>
         </is>
       </c>
     </row>
@@ -19067,7 +19067,7 @@
       </c>
       <c r="S218" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T23:51:57Z</t>
+          <t>2026-10-01T00:02:20Z</t>
         </is>
       </c>
     </row>
@@ -19152,7 +19152,7 @@
       </c>
       <c r="S219" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T23:51:57Z</t>
+          <t>2026-10-01T00:02:20Z</t>
         </is>
       </c>
     </row>
@@ -19241,7 +19241,7 @@
       </c>
       <c r="S220" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T23:51:57Z</t>
+          <t>2026-10-01T00:02:20Z</t>
         </is>
       </c>
     </row>
@@ -19330,7 +19330,7 @@
       </c>
       <c r="S221" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T23:51:57Z</t>
+          <t>2026-10-01T00:02:20Z</t>
         </is>
       </c>
     </row>
@@ -19415,7 +19415,7 @@
       </c>
       <c r="S222" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T23:51:57Z</t>
+          <t>2026-10-01T00:02:20Z</t>
         </is>
       </c>
     </row>
@@ -19504,7 +19504,7 @@
       </c>
       <c r="S223" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T23:51:57Z</t>
+          <t>2026-10-01T00:02:20Z</t>
         </is>
       </c>
     </row>
@@ -19593,7 +19593,7 @@
       </c>
       <c r="S224" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T23:51:57Z</t>
+          <t>2026-10-01T00:02:20Z</t>
         </is>
       </c>
     </row>
@@ -19678,7 +19678,7 @@
       </c>
       <c r="S225" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T23:51:57Z</t>
+          <t>2026-10-01T00:02:20Z</t>
         </is>
       </c>
     </row>
@@ -19767,7 +19767,7 @@
       </c>
       <c r="S226" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T23:51:57Z</t>
+          <t>2026-10-01T00:02:20Z</t>
         </is>
       </c>
     </row>
@@ -19856,7 +19856,7 @@
       </c>
       <c r="S227" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T23:51:57Z</t>
+          <t>2026-10-01T00:02:20Z</t>
         </is>
       </c>
     </row>
@@ -19941,7 +19941,7 @@
       </c>
       <c r="S228" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T23:51:57Z</t>
+          <t>2026-10-01T00:02:20Z</t>
         </is>
       </c>
     </row>
@@ -20030,7 +20030,7 @@
       </c>
       <c r="S229" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T23:51:57Z</t>
+          <t>2026-10-01T00:02:20Z</t>
         </is>
       </c>
     </row>
@@ -20119,7 +20119,7 @@
       </c>
       <c r="S230" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T23:51:57Z</t>
+          <t>2026-10-01T00:02:20Z</t>
         </is>
       </c>
     </row>
@@ -20204,7 +20204,7 @@
       </c>
       <c r="S231" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T23:51:57Z</t>
+          <t>2026-10-01T00:02:20Z</t>
         </is>
       </c>
     </row>
@@ -20293,7 +20293,7 @@
       </c>
       <c r="S232" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T23:51:57Z</t>
+          <t>2026-10-01T00:02:20Z</t>
         </is>
       </c>
     </row>
@@ -20382,7 +20382,7 @@
       </c>
       <c r="S233" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T23:51:57Z</t>
+          <t>2026-10-01T00:02:20Z</t>
         </is>
       </c>
     </row>
@@ -20467,7 +20467,7 @@
       </c>
       <c r="S234" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T23:51:57Z</t>
+          <t>2026-10-01T00:02:20Z</t>
         </is>
       </c>
     </row>
@@ -20556,7 +20556,7 @@
       </c>
       <c r="S235" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T23:51:57Z</t>
+          <t>2026-10-01T00:02:20Z</t>
         </is>
       </c>
     </row>
@@ -20645,7 +20645,7 @@
       </c>
       <c r="S236" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T23:51:57Z</t>
+          <t>2026-10-01T00:02:20Z</t>
         </is>
       </c>
     </row>
@@ -20730,7 +20730,7 @@
       </c>
       <c r="S237" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T23:51:57Z</t>
+          <t>2026-10-01T00:02:20Z</t>
         </is>
       </c>
     </row>
@@ -20819,7 +20819,7 @@
       </c>
       <c r="S238" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T23:51:57Z</t>
+          <t>2026-10-01T00:02:20Z</t>
         </is>
       </c>
     </row>
@@ -20908,7 +20908,7 @@
       </c>
       <c r="S239" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T23:51:57Z</t>
+          <t>2026-10-01T00:02:20Z</t>
         </is>
       </c>
     </row>
@@ -20997,7 +20997,7 @@
       </c>
       <c r="S240" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T23:51:57Z</t>
+          <t>2026-10-01T00:02:20Z</t>
         </is>
       </c>
     </row>
@@ -21086,7 +21086,7 @@
       </c>
       <c r="S241" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T23:51:57Z</t>
+          <t>2026-10-01T00:02:20Z</t>
         </is>
       </c>
     </row>
@@ -21175,7 +21175,7 @@
       </c>
       <c r="S242" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T23:51:57Z</t>
+          <t>2026-10-01T00:02:20Z</t>
         </is>
       </c>
     </row>
@@ -21264,7 +21264,7 @@
       </c>
       <c r="S243" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T23:51:57Z</t>
+          <t>2026-10-01T00:02:20Z</t>
         </is>
       </c>
     </row>
@@ -21353,7 +21353,7 @@
       </c>
       <c r="S244" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T23:51:57Z</t>
+          <t>2026-10-01T00:02:20Z</t>
         </is>
       </c>
     </row>
@@ -21442,7 +21442,7 @@
       </c>
       <c r="S245" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T23:51:57Z</t>
+          <t>2026-10-01T00:02:20Z</t>
         </is>
       </c>
     </row>
@@ -21531,7 +21531,7 @@
       </c>
       <c r="S246" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T23:51:57Z</t>
+          <t>2026-10-01T00:02:20Z</t>
         </is>
       </c>
     </row>
@@ -21620,7 +21620,7 @@
       </c>
       <c r="S247" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T23:51:57Z</t>
+          <t>2026-10-01T00:02:20Z</t>
         </is>
       </c>
     </row>
@@ -21709,7 +21709,7 @@
       </c>
       <c r="S248" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T23:51:57Z</t>
+          <t>2026-10-01T00:02:20Z</t>
         </is>
       </c>
     </row>
@@ -21798,7 +21798,7 @@
       </c>
       <c r="S249" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T23:51:57Z</t>
+          <t>2026-10-01T00:02:20Z</t>
         </is>
       </c>
     </row>
@@ -21887,7 +21887,7 @@
       </c>
       <c r="S250" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T23:51:57Z</t>
+          <t>2026-10-01T00:02:20Z</t>
         </is>
       </c>
     </row>
@@ -22019,7 +22019,7 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T23:51:57Z</t>
+          <t>2026-10-01T00:02:20Z</t>
         </is>
       </c>
     </row>
@@ -22099,7 +22099,7 @@
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>{"dataset_id": "bcv_pib_sector_institucional_anual", "title": "Producto interno bruto por sector institucional anual", "table": "Variaciones porcentuales", "source_file": "5_2_1_si_anual.xlsx", "base": "2007", "price_type": "Precios constantes", "measure": "Variación porcentual interanual", "frequency": "Anual", "period": "2025", "year": 2025, "quarter": null, "classification": "Sector institucional", "component": "Impuestos netos sobre los productos", "value": 10.600260421283764, "unit": "Porcentaje", "status": "Preliminar", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/cuentas_macroeconomicas/5_2_1_si_anual.xlsx", "fetched_at": "2026-09-29T23:51:57Z"}</t>
+          <t>{"dataset_id": "bcv_pib_sector_institucional_anual", "title": "Producto interno bruto por sector institucional anual", "table": "Variaciones porcentuales", "source_file": "5_2_1_si_anual.xlsx", "base": "2007", "price_type": "Precios constantes", "measure": "Variación porcentual interanual", "frequency": "Anual", "period": "2025", "year": 2025, "quarter": null, "classification": "Sector institucional", "component": "Impuestos netos sobre los productos", "value": 10.600260421283764, "unit": "Porcentaje", "status": "Preliminar", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/cuentas_macroeconomicas/5_2_1_si_anual.xlsx", "fetched_at": "2026-10-01T00:02:20Z"}</t>
         </is>
       </c>
     </row>

--- a/assets/data/bcv/excel/ove_bcv_pib_sector_institucional_anual.xlsx
+++ b/assets/data/bcv/excel/ove_bcv_pib_sector_institucional_anual.xlsx
@@ -736,7 +736,7 @@
       </c>
       <c r="S7" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01T00:02:20Z</t>
+          <t>2026-10-02T00:01:23Z</t>
         </is>
       </c>
     </row>
@@ -821,7 +821,7 @@
       </c>
       <c r="S8" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01T00:02:20Z</t>
+          <t>2026-10-02T00:01:23Z</t>
         </is>
       </c>
     </row>
@@ -906,7 +906,7 @@
       </c>
       <c r="S9" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01T00:02:20Z</t>
+          <t>2026-10-02T00:01:23Z</t>
         </is>
       </c>
     </row>
@@ -991,7 +991,7 @@
       </c>
       <c r="S10" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01T00:02:20Z</t>
+          <t>2026-10-02T00:01:23Z</t>
         </is>
       </c>
     </row>
@@ -1076,7 +1076,7 @@
       </c>
       <c r="S11" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01T00:02:20Z</t>
+          <t>2026-10-02T00:01:23Z</t>
         </is>
       </c>
     </row>
@@ -1161,7 +1161,7 @@
       </c>
       <c r="S12" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01T00:02:20Z</t>
+          <t>2026-10-02T00:01:23Z</t>
         </is>
       </c>
     </row>
@@ -1246,7 +1246,7 @@
       </c>
       <c r="S13" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01T00:02:20Z</t>
+          <t>2026-10-02T00:01:23Z</t>
         </is>
       </c>
     </row>
@@ -1331,7 +1331,7 @@
       </c>
       <c r="S14" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01T00:02:20Z</t>
+          <t>2026-10-02T00:01:23Z</t>
         </is>
       </c>
     </row>
@@ -1416,7 +1416,7 @@
       </c>
       <c r="S15" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01T00:02:20Z</t>
+          <t>2026-10-02T00:01:23Z</t>
         </is>
       </c>
     </row>
@@ -1501,7 +1501,7 @@
       </c>
       <c r="S16" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01T00:02:20Z</t>
+          <t>2026-10-02T00:01:23Z</t>
         </is>
       </c>
     </row>
@@ -1586,7 +1586,7 @@
       </c>
       <c r="S17" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01T00:02:20Z</t>
+          <t>2026-10-02T00:01:23Z</t>
         </is>
       </c>
     </row>
@@ -1671,7 +1671,7 @@
       </c>
       <c r="S18" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01T00:02:20Z</t>
+          <t>2026-10-02T00:01:23Z</t>
         </is>
       </c>
     </row>
@@ -1756,7 +1756,7 @@
       </c>
       <c r="S19" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01T00:02:20Z</t>
+          <t>2026-10-02T00:01:23Z</t>
         </is>
       </c>
     </row>
@@ -1841,7 +1841,7 @@
       </c>
       <c r="S20" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01T00:02:20Z</t>
+          <t>2026-10-02T00:01:23Z</t>
         </is>
       </c>
     </row>
@@ -1926,7 +1926,7 @@
       </c>
       <c r="S21" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01T00:02:20Z</t>
+          <t>2026-10-02T00:01:23Z</t>
         </is>
       </c>
     </row>
@@ -2011,7 +2011,7 @@
       </c>
       <c r="S22" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01T00:02:20Z</t>
+          <t>2026-10-02T00:01:23Z</t>
         </is>
       </c>
     </row>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="S23" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01T00:02:20Z</t>
+          <t>2026-10-02T00:01:23Z</t>
         </is>
       </c>
     </row>
@@ -2181,7 +2181,7 @@
       </c>
       <c r="S24" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01T00:02:20Z</t>
+          <t>2026-10-02T00:01:23Z</t>
         </is>
       </c>
     </row>
@@ -2266,7 +2266,7 @@
       </c>
       <c r="S25" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01T00:02:20Z</t>
+          <t>2026-10-02T00:01:23Z</t>
         </is>
       </c>
     </row>
@@ -2351,7 +2351,7 @@
       </c>
       <c r="S26" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01T00:02:20Z</t>
+          <t>2026-10-02T00:01:23Z</t>
         </is>
       </c>
     </row>
@@ -2436,7 +2436,7 @@
       </c>
       <c r="S27" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01T00:02:20Z</t>
+          <t>2026-10-02T00:01:23Z</t>
         </is>
       </c>
     </row>
@@ -2525,7 +2525,7 @@
       </c>
       <c r="S28" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01T00:02:20Z</t>
+          <t>2026-10-02T00:01:23Z</t>
         </is>
       </c>
     </row>
@@ -2614,7 +2614,7 @@
       </c>
       <c r="S29" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01T00:02:20Z</t>
+          <t>2026-10-02T00:01:23Z</t>
         </is>
       </c>
     </row>
@@ -2699,7 +2699,7 @@
       </c>
       <c r="S30" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01T00:02:20Z</t>
+          <t>2026-10-02T00:01:23Z</t>
         </is>
       </c>
     </row>
@@ -2788,7 +2788,7 @@
       </c>
       <c r="S31" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01T00:02:20Z</t>
+          <t>2026-10-02T00:01:23Z</t>
         </is>
       </c>
     </row>
@@ -2877,7 +2877,7 @@
       </c>
       <c r="S32" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01T00:02:20Z</t>
+          <t>2026-10-02T00:01:23Z</t>
         </is>
       </c>
     </row>
@@ -2962,7 +2962,7 @@
       </c>
       <c r="S33" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01T00:02:20Z</t>
+          <t>2026-10-02T00:01:23Z</t>
         </is>
       </c>
     </row>
@@ -3051,7 +3051,7 @@
       </c>
       <c r="S34" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01T00:02:20Z</t>
+          <t>2026-10-02T00:01:23Z</t>
         </is>
       </c>
     </row>
@@ -3140,7 +3140,7 @@
       </c>
       <c r="S35" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01T00:02:20Z</t>
+          <t>2026-10-02T00:01:23Z</t>
         </is>
       </c>
     </row>
@@ -3225,7 +3225,7 @@
       </c>
       <c r="S36" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01T00:02:20Z</t>
+          <t>2026-10-02T00:01:23Z</t>
         </is>
       </c>
     </row>
@@ -3314,7 +3314,7 @@
       </c>
       <c r="S37" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01T00:02:20Z</t>
+          <t>2026-10-02T00:01:23Z</t>
         </is>
       </c>
     </row>
@@ -3403,7 +3403,7 @@
       </c>
       <c r="S38" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01T00:02:20Z</t>
+          <t>2026-10-02T00:01:23Z</t>
         </is>
       </c>
     </row>
@@ -3488,7 +3488,7 @@
       </c>
       <c r="S39" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01T00:02:20Z</t>
+          <t>2026-10-02T00:01:23Z</t>
         </is>
       </c>
     </row>
@@ -3577,7 +3577,7 @@
       </c>
       <c r="S40" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01T00:02:20Z</t>
+          <t>2026-10-02T00:01:23Z</t>
         </is>
       </c>
     </row>
@@ -3666,7 +3666,7 @@
       </c>
       <c r="S41" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01T00:02:20Z</t>
+          <t>2026-10-02T00:01:23Z</t>
         </is>
       </c>
     </row>
@@ -3751,7 +3751,7 @@
       </c>
       <c r="S42" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01T00:02:20Z</t>
+          <t>2026-10-02T00:01:23Z</t>
         </is>
       </c>
     </row>
@@ -3840,7 +3840,7 @@
       </c>
       <c r="S43" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01T00:02:20Z</t>
+          <t>2026-10-02T00:01:23Z</t>
         </is>
       </c>
     </row>
@@ -3929,7 +3929,7 @@
       </c>
       <c r="S44" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01T00:02:20Z</t>
+          <t>2026-10-02T00:01:23Z</t>
         </is>
       </c>
     </row>
@@ -4014,7 +4014,7 @@
       </c>
       <c r="S45" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01T00:02:20Z</t>
+          <t>2026-10-02T00:01:23Z</t>
         </is>
       </c>
     </row>
@@ -4103,7 +4103,7 @@
       </c>
       <c r="S46" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01T00:02:20Z</t>
+          <t>2026-10-02T00:01:23Z</t>
         </is>
       </c>
     </row>
@@ -4192,7 +4192,7 @@
       </c>
       <c r="S47" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01T00:02:20Z</t>
+          <t>2026-10-02T00:01:23Z</t>
         </is>
       </c>
     </row>
@@ -4277,7 +4277,7 @@
       </c>
       <c r="S48" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01T00:02:20Z</t>
+          <t>2026-10-02T00:01:23Z</t>
         </is>
       </c>
     </row>
@@ -4366,7 +4366,7 @@
       </c>
       <c r="S49" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01T00:02:20Z</t>
+          <t>2026-10-02T00:01:23Z</t>
         </is>
       </c>
     </row>
@@ -4455,7 +4455,7 @@
       </c>
       <c r="S50" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01T00:02:20Z</t>
+          <t>2026-10-02T00:01:23Z</t>
         </is>
       </c>
     </row>
@@ -4540,7 +4540,7 @@
       </c>
       <c r="S51" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01T00:02:20Z</t>
+          <t>2026-10-02T00:01:23Z</t>
         </is>
       </c>
     </row>
@@ -4629,7 +4629,7 @@
       </c>
       <c r="S52" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01T00:02:20Z</t>
+          <t>2026-10-02T00:01:23Z</t>
         </is>
       </c>
     </row>
@@ -4718,7 +4718,7 @@
       </c>
       <c r="S53" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01T00:02:20Z</t>
+          <t>2026-10-02T00:01:23Z</t>
         </is>
       </c>
     </row>
@@ -4803,7 +4803,7 @@
       </c>
       <c r="S54" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01T00:02:20Z</t>
+          <t>2026-10-02T00:01:23Z</t>
         </is>
       </c>
     </row>
@@ -4892,7 +4892,7 @@
       </c>
       <c r="S55" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01T00:02:20Z</t>
+          <t>2026-10-02T00:01:23Z</t>
         </is>
       </c>
     </row>
@@ -4981,7 +4981,7 @@
       </c>
       <c r="S56" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01T00:02:20Z</t>
+          <t>2026-10-02T00:01:23Z</t>
         </is>
       </c>
     </row>
@@ -5070,7 +5070,7 @@
       </c>
       <c r="S57" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01T00:02:20Z</t>
+          <t>2026-10-02T00:01:23Z</t>
         </is>
       </c>
     </row>
@@ -5159,7 +5159,7 @@
       </c>
       <c r="S58" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01T00:02:20Z</t>
+          <t>2026-10-02T00:01:23Z</t>
         </is>
       </c>
     </row>
@@ -5248,7 +5248,7 @@
       </c>
       <c r="S59" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01T00:02:20Z</t>
+          <t>2026-10-02T00:01:23Z</t>
         </is>
       </c>
     </row>
@@ -5337,7 +5337,7 @@
       </c>
       <c r="S60" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01T00:02:20Z</t>
+          <t>2026-10-02T00:01:23Z</t>
         </is>
       </c>
     </row>
@@ -5426,7 +5426,7 @@
       </c>
       <c r="S61" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01T00:02:20Z</t>
+          <t>2026-10-02T00:01:23Z</t>
         </is>
       </c>
     </row>
@@ -5515,7 +5515,7 @@
       </c>
       <c r="S62" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01T00:02:20Z</t>
+          <t>2026-10-02T00:01:23Z</t>
         </is>
       </c>
     </row>
@@ -5604,7 +5604,7 @@
       </c>
       <c r="S63" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01T00:02:20Z</t>
+          <t>2026-10-02T00:01:23Z</t>
         </is>
       </c>
     </row>
@@ -5693,7 +5693,7 @@
       </c>
       <c r="S64" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01T00:02:20Z</t>
+          <t>2026-10-02T00:01:23Z</t>
         </is>
       </c>
     </row>
@@ -5782,7 +5782,7 @@
       </c>
       <c r="S65" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01T00:02:20Z</t>
+          <t>2026-10-02T00:01:23Z</t>
         </is>
       </c>
     </row>
@@ -5871,7 +5871,7 @@
       </c>
       <c r="S66" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01T00:02:20Z</t>
+          <t>2026-10-02T00:01:23Z</t>
         </is>
       </c>
     </row>
@@ -5960,7 +5960,7 @@
       </c>
       <c r="S67" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01T00:02:20Z</t>
+          <t>2026-10-02T00:01:23Z</t>
         </is>
       </c>
     </row>
@@ -6045,7 +6045,7 @@
       </c>
       <c r="S68" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01T00:02:20Z</t>
+          <t>2026-10-02T00:01:23Z</t>
         </is>
       </c>
     </row>
@@ -6130,7 +6130,7 @@
       </c>
       <c r="S69" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01T00:02:20Z</t>
+          <t>2026-10-02T00:01:23Z</t>
         </is>
       </c>
     </row>
@@ -6215,7 +6215,7 @@
       </c>
       <c r="S70" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01T00:02:20Z</t>
+          <t>2026-10-02T00:01:23Z</t>
         </is>
       </c>
     </row>
@@ -6300,7 +6300,7 @@
       </c>
       <c r="S71" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01T00:02:20Z</t>
+          <t>2026-10-02T00:01:23Z</t>
         </is>
       </c>
     </row>
@@ -6385,7 +6385,7 @@
       </c>
       <c r="S72" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01T00:02:20Z</t>
+          <t>2026-10-02T00:01:23Z</t>
         </is>
       </c>
     </row>
@@ -6470,7 +6470,7 @@
       </c>
       <c r="S73" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01T00:02:20Z</t>
+          <t>2026-10-02T00:01:23Z</t>
         </is>
       </c>
     </row>
@@ -6555,7 +6555,7 @@
       </c>
       <c r="S74" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01T00:02:20Z</t>
+          <t>2026-10-02T00:01:23Z</t>
         </is>
       </c>
     </row>
@@ -6640,7 +6640,7 @@
       </c>
       <c r="S75" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01T00:02:20Z</t>
+          <t>2026-10-02T00:01:23Z</t>
         </is>
       </c>
     </row>
@@ -6725,7 +6725,7 @@
       </c>
       <c r="S76" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01T00:02:20Z</t>
+          <t>2026-10-02T00:01:23Z</t>
         </is>
       </c>
     </row>
@@ -6810,7 +6810,7 @@
       </c>
       <c r="S77" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01T00:02:20Z</t>
+          <t>2026-10-02T00:01:23Z</t>
         </is>
       </c>
     </row>
@@ -6895,7 +6895,7 @@
       </c>
       <c r="S78" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01T00:02:20Z</t>
+          <t>2026-10-02T00:01:23Z</t>
         </is>
       </c>
     </row>
@@ -6980,7 +6980,7 @@
       </c>
       <c r="S79" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01T00:02:20Z</t>
+          <t>2026-10-02T00:01:23Z</t>
         </is>
       </c>
     </row>
@@ -7065,7 +7065,7 @@
       </c>
       <c r="S80" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01T00:02:20Z</t>
+          <t>2026-10-02T00:01:23Z</t>
         </is>
       </c>
     </row>
@@ -7150,7 +7150,7 @@
       </c>
       <c r="S81" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01T00:02:20Z</t>
+          <t>2026-10-02T00:01:23Z</t>
         </is>
       </c>
     </row>
@@ -7235,7 +7235,7 @@
       </c>
       <c r="S82" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01T00:02:20Z</t>
+          <t>2026-10-02T00:01:23Z</t>
         </is>
       </c>
     </row>
@@ -7320,7 +7320,7 @@
       </c>
       <c r="S83" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01T00:02:20Z</t>
+          <t>2026-10-02T00:01:23Z</t>
         </is>
       </c>
     </row>
@@ -7405,7 +7405,7 @@
       </c>
       <c r="S84" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01T00:02:20Z</t>
+          <t>2026-10-02T00:01:23Z</t>
         </is>
       </c>
     </row>
@@ -7490,7 +7490,7 @@
       </c>
       <c r="S85" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01T00:02:20Z</t>
+          <t>2026-10-02T00:01:23Z</t>
         </is>
       </c>
     </row>
@@ -7575,7 +7575,7 @@
       </c>
       <c r="S86" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01T00:02:20Z</t>
+          <t>2026-10-02T00:01:23Z</t>
         </is>
       </c>
     </row>
@@ -7660,7 +7660,7 @@
       </c>
       <c r="S87" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01T00:02:20Z</t>
+          <t>2026-10-02T00:01:23Z</t>
         </is>
       </c>
     </row>
@@ -7745,7 +7745,7 @@
       </c>
       <c r="S88" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01T00:02:20Z</t>
+          <t>2026-10-02T00:01:23Z</t>
         </is>
       </c>
     </row>
@@ -7834,7 +7834,7 @@
       </c>
       <c r="S89" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01T00:02:20Z</t>
+          <t>2026-10-02T00:01:23Z</t>
         </is>
       </c>
     </row>
@@ -7923,7 +7923,7 @@
       </c>
       <c r="S90" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01T00:02:20Z</t>
+          <t>2026-10-02T00:01:23Z</t>
         </is>
       </c>
     </row>
@@ -8008,7 +8008,7 @@
       </c>
       <c r="S91" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01T00:02:20Z</t>
+          <t>2026-10-02T00:01:23Z</t>
         </is>
       </c>
     </row>
@@ -8097,7 +8097,7 @@
       </c>
       <c r="S92" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01T00:02:20Z</t>
+          <t>2026-10-02T00:01:23Z</t>
         </is>
       </c>
     </row>
@@ -8186,7 +8186,7 @@
       </c>
       <c r="S93" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01T00:02:20Z</t>
+          <t>2026-10-02T00:01:23Z</t>
         </is>
       </c>
     </row>
@@ -8271,7 +8271,7 @@
       </c>
       <c r="S94" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01T00:02:20Z</t>
+          <t>2026-10-02T00:01:23Z</t>
         </is>
       </c>
     </row>
@@ -8360,7 +8360,7 @@
       </c>
       <c r="S95" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01T00:02:20Z</t>
+          <t>2026-10-02T00:01:23Z</t>
         </is>
       </c>
     </row>
@@ -8449,7 +8449,7 @@
       </c>
       <c r="S96" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01T00:02:20Z</t>
+          <t>2026-10-02T00:01:23Z</t>
         </is>
       </c>
     </row>
@@ -8534,7 +8534,7 @@
       </c>
       <c r="S97" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01T00:02:20Z</t>
+          <t>2026-10-02T00:01:23Z</t>
         </is>
       </c>
     </row>
@@ -8623,7 +8623,7 @@
       </c>
       <c r="S98" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01T00:02:20Z</t>
+          <t>2026-10-02T00:01:23Z</t>
         </is>
       </c>
     </row>
@@ -8712,7 +8712,7 @@
       </c>
       <c r="S99" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01T00:02:20Z</t>
+          <t>2026-10-02T00:01:23Z</t>
         </is>
       </c>
     </row>
@@ -8797,7 +8797,7 @@
       </c>
       <c r="S100" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01T00:02:20Z</t>
+          <t>2026-10-02T00:01:23Z</t>
         </is>
       </c>
     </row>
@@ -8886,7 +8886,7 @@
       </c>
       <c r="S101" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01T00:02:20Z</t>
+          <t>2026-10-02T00:01:23Z</t>
         </is>
       </c>
     </row>
@@ -8975,7 +8975,7 @@
       </c>
       <c r="S102" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01T00:02:20Z</t>
+          <t>2026-10-02T00:01:23Z</t>
         </is>
       </c>
     </row>
@@ -9060,7 +9060,7 @@
       </c>
       <c r="S103" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01T00:02:20Z</t>
+          <t>2026-10-02T00:01:23Z</t>
         </is>
       </c>
     </row>
@@ -9149,7 +9149,7 @@
       </c>
       <c r="S104" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01T00:02:20Z</t>
+          <t>2026-10-02T00:01:23Z</t>
         </is>
       </c>
     </row>
@@ -9238,7 +9238,7 @@
       </c>
       <c r="S105" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01T00:02:20Z</t>
+          <t>2026-10-02T00:01:23Z</t>
         </is>
       </c>
     </row>
@@ -9323,7 +9323,7 @@
       </c>
       <c r="S106" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01T00:02:20Z</t>
+          <t>2026-10-02T00:01:23Z</t>
         </is>
       </c>
     </row>
@@ -9412,7 +9412,7 @@
       </c>
       <c r="S107" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01T00:02:20Z</t>
+          <t>2026-10-02T00:01:23Z</t>
         </is>
       </c>
     </row>
@@ -9501,7 +9501,7 @@
       </c>
       <c r="S108" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01T00:02:20Z</t>
+          <t>2026-10-02T00:01:23Z</t>
         </is>
       </c>
     </row>
@@ -9586,7 +9586,7 @@
       </c>
       <c r="S109" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01T00:02:20Z</t>
+          <t>2026-10-02T00:01:23Z</t>
         </is>
       </c>
     </row>
@@ -9675,7 +9675,7 @@
       </c>
       <c r="S110" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01T00:02:20Z</t>
+          <t>2026-10-02T00:01:23Z</t>
         </is>
       </c>
     </row>
@@ -9764,7 +9764,7 @@
       </c>
       <c r="S111" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01T00:02:20Z</t>
+          <t>2026-10-02T00:01:23Z</t>
         </is>
       </c>
     </row>
@@ -9849,7 +9849,7 @@
       </c>
       <c r="S112" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01T00:02:20Z</t>
+          <t>2026-10-02T00:01:23Z</t>
         </is>
       </c>
     </row>
@@ -9938,7 +9938,7 @@
       </c>
       <c r="S113" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01T00:02:20Z</t>
+          <t>2026-10-02T00:01:23Z</t>
         </is>
       </c>
     </row>
@@ -10027,7 +10027,7 @@
       </c>
       <c r="S114" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01T00:02:20Z</t>
+          <t>2026-10-02T00:01:23Z</t>
         </is>
       </c>
     </row>
@@ -10112,7 +10112,7 @@
       </c>
       <c r="S115" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01T00:02:20Z</t>
+          <t>2026-10-02T00:01:23Z</t>
         </is>
       </c>
     </row>
@@ -10201,7 +10201,7 @@
       </c>
       <c r="S116" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01T00:02:20Z</t>
+          <t>2026-10-02T00:01:23Z</t>
         </is>
       </c>
     </row>
@@ -10290,7 +10290,7 @@
       </c>
       <c r="S117" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01T00:02:20Z</t>
+          <t>2026-10-02T00:01:23Z</t>
         </is>
       </c>
     </row>
@@ -10379,7 +10379,7 @@
       </c>
       <c r="S118" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01T00:02:20Z</t>
+          <t>2026-10-02T00:01:23Z</t>
         </is>
       </c>
     </row>
@@ -10468,7 +10468,7 @@
       </c>
       <c r="S119" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01T00:02:20Z</t>
+          <t>2026-10-02T00:01:23Z</t>
         </is>
       </c>
     </row>
@@ -10557,7 +10557,7 @@
       </c>
       <c r="S120" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01T00:02:20Z</t>
+          <t>2026-10-02T00:01:23Z</t>
         </is>
       </c>
     </row>
@@ -10646,7 +10646,7 @@
       </c>
       <c r="S121" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01T00:02:20Z</t>
+          <t>2026-10-02T00:01:23Z</t>
         </is>
       </c>
     </row>
@@ -10735,7 +10735,7 @@
       </c>
       <c r="S122" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01T00:02:20Z</t>
+          <t>2026-10-02T00:01:23Z</t>
         </is>
       </c>
     </row>
@@ -10824,7 +10824,7 @@
       </c>
       <c r="S123" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01T00:02:20Z</t>
+          <t>2026-10-02T00:01:23Z</t>
         </is>
       </c>
     </row>
@@ -10913,7 +10913,7 @@
       </c>
       <c r="S124" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01T00:02:20Z</t>
+          <t>2026-10-02T00:01:23Z</t>
         </is>
       </c>
     </row>
@@ -11002,7 +11002,7 @@
       </c>
       <c r="S125" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01T00:02:20Z</t>
+          <t>2026-10-02T00:01:23Z</t>
         </is>
       </c>
     </row>
@@ -11091,7 +11091,7 @@
       </c>
       <c r="S126" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01T00:02:20Z</t>
+          <t>2026-10-02T00:01:23Z</t>
         </is>
       </c>
     </row>
@@ -11180,7 +11180,7 @@
       </c>
       <c r="S127" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01T00:02:20Z</t>
+          <t>2026-10-02T00:01:23Z</t>
         </is>
       </c>
     </row>
@@ -11269,7 +11269,7 @@
       </c>
       <c r="S128" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01T00:02:20Z</t>
+          <t>2026-10-02T00:01:23Z</t>
         </is>
       </c>
     </row>
@@ -11354,7 +11354,7 @@
       </c>
       <c r="S129" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01T00:02:20Z</t>
+          <t>2026-10-02T00:01:23Z</t>
         </is>
       </c>
     </row>
@@ -11439,7 +11439,7 @@
       </c>
       <c r="S130" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01T00:02:20Z</t>
+          <t>2026-10-02T00:01:23Z</t>
         </is>
       </c>
     </row>
@@ -11524,7 +11524,7 @@
       </c>
       <c r="S131" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01T00:02:20Z</t>
+          <t>2026-10-02T00:01:23Z</t>
         </is>
       </c>
     </row>
@@ -11609,7 +11609,7 @@
       </c>
       <c r="S132" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01T00:02:20Z</t>
+          <t>2026-10-02T00:01:23Z</t>
         </is>
       </c>
     </row>
@@ -11694,7 +11694,7 @@
       </c>
       <c r="S133" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01T00:02:20Z</t>
+          <t>2026-10-02T00:01:23Z</t>
         </is>
       </c>
     </row>
@@ -11779,7 +11779,7 @@
       </c>
       <c r="S134" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01T00:02:20Z</t>
+          <t>2026-10-02T00:01:23Z</t>
         </is>
       </c>
     </row>
@@ -11864,7 +11864,7 @@
       </c>
       <c r="S135" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01T00:02:20Z</t>
+          <t>2026-10-02T00:01:23Z</t>
         </is>
       </c>
     </row>
@@ -11949,7 +11949,7 @@
       </c>
       <c r="S136" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01T00:02:20Z</t>
+          <t>2026-10-02T00:01:23Z</t>
         </is>
       </c>
     </row>
@@ -12034,7 +12034,7 @@
       </c>
       <c r="S137" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01T00:02:20Z</t>
+          <t>2026-10-02T00:01:23Z</t>
         </is>
       </c>
     </row>
@@ -12119,7 +12119,7 @@
       </c>
       <c r="S138" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01T00:02:20Z</t>
+          <t>2026-10-02T00:01:23Z</t>
         </is>
       </c>
     </row>
@@ -12204,7 +12204,7 @@
       </c>
       <c r="S139" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01T00:02:20Z</t>
+          <t>2026-10-02T00:01:23Z</t>
         </is>
       </c>
     </row>
@@ -12289,7 +12289,7 @@
       </c>
       <c r="S140" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01T00:02:20Z</t>
+          <t>2026-10-02T00:01:23Z</t>
         </is>
       </c>
     </row>
@@ -12374,7 +12374,7 @@
       </c>
       <c r="S141" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01T00:02:20Z</t>
+          <t>2026-10-02T00:01:23Z</t>
         </is>
       </c>
     </row>
@@ -12459,7 +12459,7 @@
       </c>
       <c r="S142" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01T00:02:20Z</t>
+          <t>2026-10-02T00:01:23Z</t>
         </is>
       </c>
     </row>
@@ -12544,7 +12544,7 @@
       </c>
       <c r="S143" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01T00:02:20Z</t>
+          <t>2026-10-02T00:01:23Z</t>
         </is>
       </c>
     </row>
@@ -12629,7 +12629,7 @@
       </c>
       <c r="S144" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01T00:02:20Z</t>
+          <t>2026-10-02T00:01:23Z</t>
         </is>
       </c>
     </row>
@@ -12714,7 +12714,7 @@
       </c>
       <c r="S145" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01T00:02:20Z</t>
+          <t>2026-10-02T00:01:23Z</t>
         </is>
       </c>
     </row>
@@ -12799,7 +12799,7 @@
       </c>
       <c r="S146" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01T00:02:20Z</t>
+          <t>2026-10-02T00:01:23Z</t>
         </is>
       </c>
     </row>
@@ -12884,7 +12884,7 @@
       </c>
       <c r="S147" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01T00:02:20Z</t>
+          <t>2026-10-02T00:01:23Z</t>
         </is>
       </c>
     </row>
@@ -12969,7 +12969,7 @@
       </c>
       <c r="S148" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01T00:02:20Z</t>
+          <t>2026-10-02T00:01:23Z</t>
         </is>
       </c>
     </row>
@@ -13054,7 +13054,7 @@
       </c>
       <c r="S149" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01T00:02:20Z</t>
+          <t>2026-10-02T00:01:23Z</t>
         </is>
       </c>
     </row>
@@ -13143,7 +13143,7 @@
       </c>
       <c r="S150" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01T00:02:20Z</t>
+          <t>2026-10-02T00:01:23Z</t>
         </is>
       </c>
     </row>
@@ -13232,7 +13232,7 @@
       </c>
       <c r="S151" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01T00:02:20Z</t>
+          <t>2026-10-02T00:01:23Z</t>
         </is>
       </c>
     </row>
@@ -13317,7 +13317,7 @@
       </c>
       <c r="S152" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01T00:02:20Z</t>
+          <t>2026-10-02T00:01:23Z</t>
         </is>
       </c>
     </row>
@@ -13406,7 +13406,7 @@
       </c>
       <c r="S153" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01T00:02:20Z</t>
+          <t>2026-10-02T00:01:23Z</t>
         </is>
       </c>
     </row>
@@ -13495,7 +13495,7 @@
       </c>
       <c r="S154" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01T00:02:20Z</t>
+          <t>2026-10-02T00:01:23Z</t>
         </is>
       </c>
     </row>
@@ -13580,7 +13580,7 @@
       </c>
       <c r="S155" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01T00:02:20Z</t>
+          <t>2026-10-02T00:01:23Z</t>
         </is>
       </c>
     </row>
@@ -13669,7 +13669,7 @@
       </c>
       <c r="S156" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01T00:02:20Z</t>
+          <t>2026-10-02T00:01:23Z</t>
         </is>
       </c>
     </row>
@@ -13758,7 +13758,7 @@
       </c>
       <c r="S157" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01T00:02:20Z</t>
+          <t>2026-10-02T00:01:23Z</t>
         </is>
       </c>
     </row>
@@ -13843,7 +13843,7 @@
       </c>
       <c r="S158" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01T00:02:20Z</t>
+          <t>2026-10-02T00:01:23Z</t>
         </is>
       </c>
     </row>
@@ -13932,7 +13932,7 @@
       </c>
       <c r="S159" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01T00:02:20Z</t>
+          <t>2026-10-02T00:01:23Z</t>
         </is>
       </c>
     </row>
@@ -14021,7 +14021,7 @@
       </c>
       <c r="S160" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01T00:02:20Z</t>
+          <t>2026-10-02T00:01:23Z</t>
         </is>
       </c>
     </row>
@@ -14106,7 +14106,7 @@
       </c>
       <c r="S161" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01T00:02:20Z</t>
+          <t>2026-10-02T00:01:23Z</t>
         </is>
       </c>
     </row>
@@ -14195,7 +14195,7 @@
       </c>
       <c r="S162" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01T00:02:20Z</t>
+          <t>2026-10-02T00:01:23Z</t>
         </is>
       </c>
     </row>
@@ -14284,7 +14284,7 @@
       </c>
       <c r="S163" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01T00:02:20Z</t>
+          <t>2026-10-02T00:01:23Z</t>
         </is>
       </c>
     </row>
@@ -14369,7 +14369,7 @@
       </c>
       <c r="S164" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01T00:02:20Z</t>
+          <t>2026-10-02T00:01:23Z</t>
         </is>
       </c>
     </row>
@@ -14458,7 +14458,7 @@
       </c>
       <c r="S165" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01T00:02:20Z</t>
+          <t>2026-10-02T00:01:23Z</t>
         </is>
       </c>
     </row>
@@ -14547,7 +14547,7 @@
       </c>
       <c r="S166" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01T00:02:20Z</t>
+          <t>2026-10-02T00:01:23Z</t>
         </is>
       </c>
     </row>
@@ -14632,7 +14632,7 @@
       </c>
       <c r="S167" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01T00:02:20Z</t>
+          <t>2026-10-02T00:01:23Z</t>
         </is>
       </c>
     </row>
@@ -14721,7 +14721,7 @@
       </c>
       <c r="S168" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01T00:02:20Z</t>
+          <t>2026-10-02T00:01:23Z</t>
         </is>
       </c>
     </row>
@@ -14810,7 +14810,7 @@
       </c>
       <c r="S169" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01T00:02:20Z</t>
+          <t>2026-10-02T00:01:23Z</t>
         </is>
       </c>
     </row>
@@ -14895,7 +14895,7 @@
       </c>
       <c r="S170" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01T00:02:20Z</t>
+          <t>2026-10-02T00:01:23Z</t>
         </is>
       </c>
     </row>
@@ -14984,7 +14984,7 @@
       </c>
       <c r="S171" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01T00:02:20Z</t>
+          <t>2026-10-02T00:01:23Z</t>
         </is>
       </c>
     </row>
@@ -15073,7 +15073,7 @@
       </c>
       <c r="S172" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01T00:02:20Z</t>
+          <t>2026-10-02T00:01:23Z</t>
         </is>
       </c>
     </row>
@@ -15158,7 +15158,7 @@
       </c>
       <c r="S173" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01T00:02:20Z</t>
+          <t>2026-10-02T00:01:23Z</t>
         </is>
       </c>
     </row>
@@ -15247,7 +15247,7 @@
       </c>
       <c r="S174" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01T00:02:20Z</t>
+          <t>2026-10-02T00:01:23Z</t>
         </is>
       </c>
     </row>
@@ -15336,7 +15336,7 @@
       </c>
       <c r="S175" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01T00:02:20Z</t>
+          <t>2026-10-02T00:01:23Z</t>
         </is>
       </c>
     </row>
@@ -15421,7 +15421,7 @@
       </c>
       <c r="S176" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01T00:02:20Z</t>
+          <t>2026-10-02T00:01:23Z</t>
         </is>
       </c>
     </row>
@@ -15510,7 +15510,7 @@
       </c>
       <c r="S177" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01T00:02:20Z</t>
+          <t>2026-10-02T00:01:23Z</t>
         </is>
       </c>
     </row>
@@ -15599,7 +15599,7 @@
       </c>
       <c r="S178" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01T00:02:20Z</t>
+          <t>2026-10-02T00:01:23Z</t>
         </is>
       </c>
     </row>
@@ -15688,7 +15688,7 @@
       </c>
       <c r="S179" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01T00:02:20Z</t>
+          <t>2026-10-02T00:01:23Z</t>
         </is>
       </c>
     </row>
@@ -15777,7 +15777,7 @@
       </c>
       <c r="S180" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01T00:02:20Z</t>
+          <t>2026-10-02T00:01:23Z</t>
         </is>
       </c>
     </row>
@@ -15866,7 +15866,7 @@
       </c>
       <c r="S181" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01T00:02:20Z</t>
+          <t>2026-10-02T00:01:23Z</t>
         </is>
       </c>
     </row>
@@ -15955,7 +15955,7 @@
       </c>
       <c r="S182" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01T00:02:20Z</t>
+          <t>2026-10-02T00:01:23Z</t>
         </is>
       </c>
     </row>
@@ -16044,7 +16044,7 @@
       </c>
       <c r="S183" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01T00:02:20Z</t>
+          <t>2026-10-02T00:01:23Z</t>
         </is>
       </c>
     </row>
@@ -16133,7 +16133,7 @@
       </c>
       <c r="S184" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01T00:02:20Z</t>
+          <t>2026-10-02T00:01:23Z</t>
         </is>
       </c>
     </row>
@@ -16222,7 +16222,7 @@
       </c>
       <c r="S185" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01T00:02:20Z</t>
+          <t>2026-10-02T00:01:23Z</t>
         </is>
       </c>
     </row>
@@ -16311,7 +16311,7 @@
       </c>
       <c r="S186" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01T00:02:20Z</t>
+          <t>2026-10-02T00:01:23Z</t>
         </is>
       </c>
     </row>
@@ -16400,7 +16400,7 @@
       </c>
       <c r="S187" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01T00:02:20Z</t>
+          <t>2026-10-02T00:01:23Z</t>
         </is>
       </c>
     </row>
@@ -16489,7 +16489,7 @@
       </c>
       <c r="S188" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01T00:02:20Z</t>
+          <t>2026-10-02T00:01:23Z</t>
         </is>
       </c>
     </row>
@@ -16578,7 +16578,7 @@
       </c>
       <c r="S189" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01T00:02:20Z</t>
+          <t>2026-10-02T00:01:23Z</t>
         </is>
       </c>
     </row>
@@ -16663,7 +16663,7 @@
       </c>
       <c r="S190" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01T00:02:20Z</t>
+          <t>2026-10-02T00:01:23Z</t>
         </is>
       </c>
     </row>
@@ -16748,7 +16748,7 @@
       </c>
       <c r="S191" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01T00:02:20Z</t>
+          <t>2026-10-02T00:01:23Z</t>
         </is>
       </c>
     </row>
@@ -16833,7 +16833,7 @@
       </c>
       <c r="S192" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01T00:02:20Z</t>
+          <t>2026-10-02T00:01:23Z</t>
         </is>
       </c>
     </row>
@@ -16918,7 +16918,7 @@
       </c>
       <c r="S193" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01T00:02:20Z</t>
+          <t>2026-10-02T00:01:23Z</t>
         </is>
       </c>
     </row>
@@ -17003,7 +17003,7 @@
       </c>
       <c r="S194" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01T00:02:20Z</t>
+          <t>2026-10-02T00:01:23Z</t>
         </is>
       </c>
     </row>
@@ -17088,7 +17088,7 @@
       </c>
       <c r="S195" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01T00:02:20Z</t>
+          <t>2026-10-02T00:01:23Z</t>
         </is>
       </c>
     </row>
@@ -17173,7 +17173,7 @@
       </c>
       <c r="S196" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01T00:02:20Z</t>
+          <t>2026-10-02T00:01:23Z</t>
         </is>
       </c>
     </row>
@@ -17258,7 +17258,7 @@
       </c>
       <c r="S197" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01T00:02:20Z</t>
+          <t>2026-10-02T00:01:23Z</t>
         </is>
       </c>
     </row>
@@ -17343,7 +17343,7 @@
       </c>
       <c r="S198" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01T00:02:20Z</t>
+          <t>2026-10-02T00:01:23Z</t>
         </is>
       </c>
     </row>
@@ -17428,7 +17428,7 @@
       </c>
       <c r="S199" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01T00:02:20Z</t>
+          <t>2026-10-02T00:01:23Z</t>
         </is>
       </c>
     </row>
@@ -17513,7 +17513,7 @@
       </c>
       <c r="S200" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01T00:02:20Z</t>
+          <t>2026-10-02T00:01:23Z</t>
         </is>
       </c>
     </row>
@@ -17598,7 +17598,7 @@
       </c>
       <c r="S201" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01T00:02:20Z</t>
+          <t>2026-10-02T00:01:23Z</t>
         </is>
       </c>
     </row>
@@ -17683,7 +17683,7 @@
       </c>
       <c r="S202" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01T00:02:20Z</t>
+          <t>2026-10-02T00:01:23Z</t>
         </is>
       </c>
     </row>
@@ -17768,7 +17768,7 @@
       </c>
       <c r="S203" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01T00:02:20Z</t>
+          <t>2026-10-02T00:01:23Z</t>
         </is>
       </c>
     </row>
@@ -17853,7 +17853,7 @@
       </c>
       <c r="S204" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01T00:02:20Z</t>
+          <t>2026-10-02T00:01:23Z</t>
         </is>
       </c>
     </row>
@@ -17938,7 +17938,7 @@
       </c>
       <c r="S205" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01T00:02:20Z</t>
+          <t>2026-10-02T00:01:23Z</t>
         </is>
       </c>
     </row>
@@ -18023,7 +18023,7 @@
       </c>
       <c r="S206" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01T00:02:20Z</t>
+          <t>2026-10-02T00:01:23Z</t>
         </is>
       </c>
     </row>
@@ -18108,7 +18108,7 @@
       </c>
       <c r="S207" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01T00:02:20Z</t>
+          <t>2026-10-02T00:01:23Z</t>
         </is>
       </c>
     </row>
@@ -18193,7 +18193,7 @@
       </c>
       <c r="S208" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01T00:02:20Z</t>
+          <t>2026-10-02T00:01:23Z</t>
         </is>
       </c>
     </row>
@@ -18278,7 +18278,7 @@
       </c>
       <c r="S209" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01T00:02:20Z</t>
+          <t>2026-10-02T00:01:23Z</t>
         </is>
       </c>
     </row>
@@ -18363,7 +18363,7 @@
       </c>
       <c r="S210" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01T00:02:20Z</t>
+          <t>2026-10-02T00:01:23Z</t>
         </is>
       </c>
     </row>
@@ -18452,7 +18452,7 @@
       </c>
       <c r="S211" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01T00:02:20Z</t>
+          <t>2026-10-02T00:01:23Z</t>
         </is>
       </c>
     </row>
@@ -18541,7 +18541,7 @@
       </c>
       <c r="S212" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01T00:02:20Z</t>
+          <t>2026-10-02T00:01:23Z</t>
         </is>
       </c>
     </row>
@@ -18626,7 +18626,7 @@
       </c>
       <c r="S213" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01T00:02:20Z</t>
+          <t>2026-10-02T00:01:23Z</t>
         </is>
       </c>
     </row>
@@ -18715,7 +18715,7 @@
       </c>
       <c r="S214" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01T00:02:20Z</t>
+          <t>2026-10-02T00:01:23Z</t>
         </is>
       </c>
     </row>
@@ -18804,7 +18804,7 @@
       </c>
       <c r="S215" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01T00:02:20Z</t>
+          <t>2026-10-02T00:01:23Z</t>
         </is>
       </c>
     </row>
@@ -18889,7 +18889,7 @@
       </c>
       <c r="S216" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01T00:02:20Z</t>
+          <t>2026-10-02T00:01:23Z</t>
         </is>
       </c>
     </row>
@@ -18978,7 +18978,7 @@
       </c>
       <c r="S217" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01T00:02:20Z</t>
+          <t>2026-10-02T00:01:23Z</t>
         </is>
       </c>
     </row>
@@ -19067,7 +19067,7 @@
       </c>
       <c r="S218" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01T00:02:20Z</t>
+          <t>2026-10-02T00:01:23Z</t>
         </is>
       </c>
     </row>
@@ -19152,7 +19152,7 @@
       </c>
       <c r="S219" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01T00:02:20Z</t>
+          <t>2026-10-02T00:01:23Z</t>
         </is>
       </c>
     </row>
@@ -19241,7 +19241,7 @@
       </c>
       <c r="S220" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01T00:02:20Z</t>
+          <t>2026-10-02T00:01:23Z</t>
         </is>
       </c>
     </row>
@@ -19330,7 +19330,7 @@
       </c>
       <c r="S221" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01T00:02:20Z</t>
+          <t>2026-10-02T00:01:23Z</t>
         </is>
       </c>
     </row>
@@ -19415,7 +19415,7 @@
       </c>
       <c r="S222" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01T00:02:20Z</t>
+          <t>2026-10-02T00:01:23Z</t>
         </is>
       </c>
     </row>
@@ -19504,7 +19504,7 @@
       </c>
       <c r="S223" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01T00:02:20Z</t>
+          <t>2026-10-02T00:01:23Z</t>
         </is>
       </c>
     </row>
@@ -19593,7 +19593,7 @@
       </c>
       <c r="S224" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01T00:02:20Z</t>
+          <t>2026-10-02T00:01:23Z</t>
         </is>
       </c>
     </row>
@@ -19678,7 +19678,7 @@
       </c>
       <c r="S225" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01T00:02:20Z</t>
+          <t>2026-10-02T00:01:23Z</t>
         </is>
       </c>
     </row>
@@ -19767,7 +19767,7 @@
       </c>
       <c r="S226" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01T00:02:20Z</t>
+          <t>2026-10-02T00:01:23Z</t>
         </is>
       </c>
     </row>
@@ -19856,7 +19856,7 @@
       </c>
       <c r="S227" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01T00:02:20Z</t>
+          <t>2026-10-02T00:01:23Z</t>
         </is>
       </c>
     </row>
@@ -19941,7 +19941,7 @@
       </c>
       <c r="S228" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01T00:02:20Z</t>
+          <t>2026-10-02T00:01:23Z</t>
         </is>
       </c>
     </row>
@@ -20030,7 +20030,7 @@
       </c>
       <c r="S229" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01T00:02:20Z</t>
+          <t>2026-10-02T00:01:23Z</t>
         </is>
       </c>
     </row>
@@ -20119,7 +20119,7 @@
       </c>
       <c r="S230" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01T00:02:20Z</t>
+          <t>2026-10-02T00:01:23Z</t>
         </is>
       </c>
     </row>
@@ -20204,7 +20204,7 @@
       </c>
       <c r="S231" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01T00:02:20Z</t>
+          <t>2026-10-02T00:01:23Z</t>
         </is>
       </c>
     </row>
@@ -20293,7 +20293,7 @@
       </c>
       <c r="S232" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01T00:02:20Z</t>
+          <t>2026-10-02T00:01:23Z</t>
         </is>
       </c>
     </row>
@@ -20382,7 +20382,7 @@
       </c>
       <c r="S233" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01T00:02:20Z</t>
+          <t>2026-10-02T00:01:23Z</t>
         </is>
       </c>
     </row>
@@ -20467,7 +20467,7 @@
       </c>
       <c r="S234" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01T00:02:20Z</t>
+          <t>2026-10-02T00:01:23Z</t>
         </is>
       </c>
     </row>
@@ -20556,7 +20556,7 @@
       </c>
       <c r="S235" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01T00:02:20Z</t>
+          <t>2026-10-02T00:01:23Z</t>
         </is>
       </c>
     </row>
@@ -20645,7 +20645,7 @@
       </c>
       <c r="S236" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01T00:02:20Z</t>
+          <t>2026-10-02T00:01:23Z</t>
         </is>
       </c>
     </row>
@@ -20730,7 +20730,7 @@
       </c>
       <c r="S237" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01T00:02:20Z</t>
+          <t>2026-10-02T00:01:23Z</t>
         </is>
       </c>
     </row>
@@ -20819,7 +20819,7 @@
       </c>
       <c r="S238" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01T00:02:20Z</t>
+          <t>2026-10-02T00:01:23Z</t>
         </is>
       </c>
     </row>
@@ -20908,7 +20908,7 @@
       </c>
       <c r="S239" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01T00:02:20Z</t>
+          <t>2026-10-02T00:01:23Z</t>
         </is>
       </c>
     </row>
@@ -20997,7 +20997,7 @@
       </c>
       <c r="S240" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01T00:02:20Z</t>
+          <t>2026-10-02T00:01:23Z</t>
         </is>
       </c>
     </row>
@@ -21086,7 +21086,7 @@
       </c>
       <c r="S241" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01T00:02:20Z</t>
+          <t>2026-10-02T00:01:23Z</t>
         </is>
       </c>
     </row>
@@ -21175,7 +21175,7 @@
       </c>
       <c r="S242" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01T00:02:20Z</t>
+          <t>2026-10-02T00:01:23Z</t>
         </is>
       </c>
     </row>
@@ -21264,7 +21264,7 @@
       </c>
       <c r="S243" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01T00:02:20Z</t>
+          <t>2026-10-02T00:01:23Z</t>
         </is>
       </c>
     </row>
@@ -21353,7 +21353,7 @@
       </c>
       <c r="S244" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01T00:02:20Z</t>
+          <t>2026-10-02T00:01:23Z</t>
         </is>
       </c>
     </row>
@@ -21442,7 +21442,7 @@
       </c>
       <c r="S245" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01T00:02:20Z</t>
+          <t>2026-10-02T00:01:23Z</t>
         </is>
       </c>
     </row>
@@ -21531,7 +21531,7 @@
       </c>
       <c r="S246" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01T00:02:20Z</t>
+          <t>2026-10-02T00:01:23Z</t>
         </is>
       </c>
     </row>
@@ -21620,7 +21620,7 @@
       </c>
       <c r="S247" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01T00:02:20Z</t>
+          <t>2026-10-02T00:01:23Z</t>
         </is>
       </c>
     </row>
@@ -21709,7 +21709,7 @@
       </c>
       <c r="S248" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01T00:02:20Z</t>
+          <t>2026-10-02T00:01:23Z</t>
         </is>
       </c>
     </row>
@@ -21798,7 +21798,7 @@
       </c>
       <c r="S249" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01T00:02:20Z</t>
+          <t>2026-10-02T00:01:23Z</t>
         </is>
       </c>
     </row>
@@ -21887,7 +21887,7 @@
       </c>
       <c r="S250" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01T00:02:20Z</t>
+          <t>2026-10-02T00:01:23Z</t>
         </is>
       </c>
     </row>
@@ -22019,7 +22019,7 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01T00:02:20Z</t>
+          <t>2026-10-02T00:01:23Z</t>
         </is>
       </c>
     </row>
@@ -22099,7 +22099,7 @@
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>{"dataset_id": "bcv_pib_sector_institucional_anual", "title": "Producto interno bruto por sector institucional anual", "table": "Variaciones porcentuales", "source_file": "5_2_1_si_anual.xlsx", "base": "2007", "price_type": "Precios constantes", "measure": "Variación porcentual interanual", "frequency": "Anual", "period": "2025", "year": 2025, "quarter": null, "classification": "Sector institucional", "component": "Impuestos netos sobre los productos", "value": 10.600260421283764, "unit": "Porcentaje", "status": "Preliminar", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/cuentas_macroeconomicas/5_2_1_si_anual.xlsx", "fetched_at": "2026-10-01T00:02:20Z"}</t>
+          <t>{"dataset_id": "bcv_pib_sector_institucional_anual", "title": "Producto interno bruto por sector institucional anual", "table": "Variaciones porcentuales", "source_file": "5_2_1_si_anual.xlsx", "base": "2007", "price_type": "Precios constantes", "measure": "Variación porcentual interanual", "frequency": "Anual", "period": "2025", "year": 2025, "quarter": null, "classification": "Sector institucional", "component": "Impuestos netos sobre los productos", "value": 10.600260421283764, "unit": "Porcentaje", "status": "Preliminar", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/cuentas_macroeconomicas/5_2_1_si_anual.xlsx", "fetched_at": "2026-10-02T00:01:23Z"}</t>
         </is>
       </c>
     </row>

--- a/assets/data/bcv/excel/ove_bcv_pib_sector_institucional_anual.xlsx
+++ b/assets/data/bcv/excel/ove_bcv_pib_sector_institucional_anual.xlsx
@@ -736,7 +736,7 @@
       </c>
       <c r="S7" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T00:01:23Z</t>
+          <t>2026-10-02T18:24:24Z</t>
         </is>
       </c>
     </row>
@@ -821,7 +821,7 @@
       </c>
       <c r="S8" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T00:01:23Z</t>
+          <t>2026-10-02T18:24:24Z</t>
         </is>
       </c>
     </row>
@@ -906,7 +906,7 @@
       </c>
       <c r="S9" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T00:01:23Z</t>
+          <t>2026-10-02T18:24:24Z</t>
         </is>
       </c>
     </row>
@@ -991,7 +991,7 @@
       </c>
       <c r="S10" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T00:01:23Z</t>
+          <t>2026-10-02T18:24:24Z</t>
         </is>
       </c>
     </row>
@@ -1076,7 +1076,7 @@
       </c>
       <c r="S11" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T00:01:23Z</t>
+          <t>2026-10-02T18:24:24Z</t>
         </is>
       </c>
     </row>
@@ -1161,7 +1161,7 @@
       </c>
       <c r="S12" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T00:01:23Z</t>
+          <t>2026-10-02T18:24:24Z</t>
         </is>
       </c>
     </row>
@@ -1246,7 +1246,7 @@
       </c>
       <c r="S13" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T00:01:23Z</t>
+          <t>2026-10-02T18:24:24Z</t>
         </is>
       </c>
     </row>
@@ -1331,7 +1331,7 @@
       </c>
       <c r="S14" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T00:01:23Z</t>
+          <t>2026-10-02T18:24:24Z</t>
         </is>
       </c>
     </row>
@@ -1416,7 +1416,7 @@
       </c>
       <c r="S15" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T00:01:23Z</t>
+          <t>2026-10-02T18:24:24Z</t>
         </is>
       </c>
     </row>
@@ -1501,7 +1501,7 @@
       </c>
       <c r="S16" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T00:01:23Z</t>
+          <t>2026-10-02T18:24:24Z</t>
         </is>
       </c>
     </row>
@@ -1586,7 +1586,7 @@
       </c>
       <c r="S17" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T00:01:23Z</t>
+          <t>2026-10-02T18:24:24Z</t>
         </is>
       </c>
     </row>
@@ -1671,7 +1671,7 @@
       </c>
       <c r="S18" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T00:01:23Z</t>
+          <t>2026-10-02T18:24:24Z</t>
         </is>
       </c>
     </row>
@@ -1756,7 +1756,7 @@
       </c>
       <c r="S19" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T00:01:23Z</t>
+          <t>2026-10-02T18:24:24Z</t>
         </is>
       </c>
     </row>
@@ -1841,7 +1841,7 @@
       </c>
       <c r="S20" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T00:01:23Z</t>
+          <t>2026-10-02T18:24:24Z</t>
         </is>
       </c>
     </row>
@@ -1926,7 +1926,7 @@
       </c>
       <c r="S21" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T00:01:23Z</t>
+          <t>2026-10-02T18:24:24Z</t>
         </is>
       </c>
     </row>
@@ -2011,7 +2011,7 @@
       </c>
       <c r="S22" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T00:01:23Z</t>
+          <t>2026-10-02T18:24:24Z</t>
         </is>
       </c>
     </row>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="S23" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T00:01:23Z</t>
+          <t>2026-10-02T18:24:24Z</t>
         </is>
       </c>
     </row>
@@ -2181,7 +2181,7 @@
       </c>
       <c r="S24" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T00:01:23Z</t>
+          <t>2026-10-02T18:24:24Z</t>
         </is>
       </c>
     </row>
@@ -2266,7 +2266,7 @@
       </c>
       <c r="S25" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T00:01:23Z</t>
+          <t>2026-10-02T18:24:24Z</t>
         </is>
       </c>
     </row>
@@ -2351,7 +2351,7 @@
       </c>
       <c r="S26" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T00:01:23Z</t>
+          <t>2026-10-02T18:24:24Z</t>
         </is>
       </c>
     </row>
@@ -2436,7 +2436,7 @@
       </c>
       <c r="S27" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T00:01:23Z</t>
+          <t>2026-10-02T18:24:24Z</t>
         </is>
       </c>
     </row>
@@ -2525,7 +2525,7 @@
       </c>
       <c r="S28" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T00:01:23Z</t>
+          <t>2026-10-02T18:24:24Z</t>
         </is>
       </c>
     </row>
@@ -2614,7 +2614,7 @@
       </c>
       <c r="S29" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T00:01:23Z</t>
+          <t>2026-10-02T18:24:24Z</t>
         </is>
       </c>
     </row>
@@ -2699,7 +2699,7 @@
       </c>
       <c r="S30" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T00:01:23Z</t>
+          <t>2026-10-02T18:24:24Z</t>
         </is>
       </c>
     </row>
@@ -2788,7 +2788,7 @@
       </c>
       <c r="S31" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T00:01:23Z</t>
+          <t>2026-10-02T18:24:24Z</t>
         </is>
       </c>
     </row>
@@ -2877,7 +2877,7 @@
       </c>
       <c r="S32" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T00:01:23Z</t>
+          <t>2026-10-02T18:24:24Z</t>
         </is>
       </c>
     </row>
@@ -2962,7 +2962,7 @@
       </c>
       <c r="S33" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T00:01:23Z</t>
+          <t>2026-10-02T18:24:24Z</t>
         </is>
       </c>
     </row>
@@ -3051,7 +3051,7 @@
       </c>
       <c r="S34" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T00:01:23Z</t>
+          <t>2026-10-02T18:24:24Z</t>
         </is>
       </c>
     </row>
@@ -3140,7 +3140,7 @@
       </c>
       <c r="S35" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T00:01:23Z</t>
+          <t>2026-10-02T18:24:24Z</t>
         </is>
       </c>
     </row>
@@ -3225,7 +3225,7 @@
       </c>
       <c r="S36" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T00:01:23Z</t>
+          <t>2026-10-02T18:24:24Z</t>
         </is>
       </c>
     </row>
@@ -3314,7 +3314,7 @@
       </c>
       <c r="S37" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T00:01:23Z</t>
+          <t>2026-10-02T18:24:24Z</t>
         </is>
       </c>
     </row>
@@ -3403,7 +3403,7 @@
       </c>
       <c r="S38" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T00:01:23Z</t>
+          <t>2026-10-02T18:24:24Z</t>
         </is>
       </c>
     </row>
@@ -3488,7 +3488,7 @@
       </c>
       <c r="S39" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T00:01:23Z</t>
+          <t>2026-10-02T18:24:24Z</t>
         </is>
       </c>
     </row>
@@ -3577,7 +3577,7 @@
       </c>
       <c r="S40" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T00:01:23Z</t>
+          <t>2026-10-02T18:24:24Z</t>
         </is>
       </c>
     </row>
@@ -3666,7 +3666,7 @@
       </c>
       <c r="S41" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T00:01:23Z</t>
+          <t>2026-10-02T18:24:24Z</t>
         </is>
       </c>
     </row>
@@ -3751,7 +3751,7 @@
       </c>
       <c r="S42" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T00:01:23Z</t>
+          <t>2026-10-02T18:24:24Z</t>
         </is>
       </c>
     </row>
@@ -3840,7 +3840,7 @@
       </c>
       <c r="S43" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T00:01:23Z</t>
+          <t>2026-10-02T18:24:24Z</t>
         </is>
       </c>
     </row>
@@ -3929,7 +3929,7 @@
       </c>
       <c r="S44" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T00:01:23Z</t>
+          <t>2026-10-02T18:24:24Z</t>
         </is>
       </c>
     </row>
@@ -4014,7 +4014,7 @@
       </c>
       <c r="S45" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T00:01:23Z</t>
+          <t>2026-10-02T18:24:24Z</t>
         </is>
       </c>
     </row>
@@ -4103,7 +4103,7 @@
       </c>
       <c r="S46" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T00:01:23Z</t>
+          <t>2026-10-02T18:24:24Z</t>
         </is>
       </c>
     </row>
@@ -4192,7 +4192,7 @@
       </c>
       <c r="S47" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T00:01:23Z</t>
+          <t>2026-10-02T18:24:24Z</t>
         </is>
       </c>
     </row>
@@ -4277,7 +4277,7 @@
       </c>
       <c r="S48" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T00:01:23Z</t>
+          <t>2026-10-02T18:24:24Z</t>
         </is>
       </c>
     </row>
@@ -4366,7 +4366,7 @@
       </c>
       <c r="S49" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T00:01:23Z</t>
+          <t>2026-10-02T18:24:24Z</t>
         </is>
       </c>
     </row>
@@ -4455,7 +4455,7 @@
       </c>
       <c r="S50" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T00:01:23Z</t>
+          <t>2026-10-02T18:24:24Z</t>
         </is>
       </c>
     </row>
@@ -4540,7 +4540,7 @@
       </c>
       <c r="S51" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T00:01:23Z</t>
+          <t>2026-10-02T18:24:24Z</t>
         </is>
       </c>
     </row>
@@ -4629,7 +4629,7 @@
       </c>
       <c r="S52" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T00:01:23Z</t>
+          <t>2026-10-02T18:24:24Z</t>
         </is>
       </c>
     </row>
@@ -4718,7 +4718,7 @@
       </c>
       <c r="S53" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T00:01:23Z</t>
+          <t>2026-10-02T18:24:24Z</t>
         </is>
       </c>
     </row>
@@ -4803,7 +4803,7 @@
       </c>
       <c r="S54" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T00:01:23Z</t>
+          <t>2026-10-02T18:24:24Z</t>
         </is>
       </c>
     </row>
@@ -4892,7 +4892,7 @@
       </c>
       <c r="S55" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T00:01:23Z</t>
+          <t>2026-10-02T18:24:24Z</t>
         </is>
       </c>
     </row>
@@ -4981,7 +4981,7 @@
       </c>
       <c r="S56" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T00:01:23Z</t>
+          <t>2026-10-02T18:24:24Z</t>
         </is>
       </c>
     </row>
@@ -5070,7 +5070,7 @@
       </c>
       <c r="S57" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T00:01:23Z</t>
+          <t>2026-10-02T18:24:24Z</t>
         </is>
       </c>
     </row>
@@ -5159,7 +5159,7 @@
       </c>
       <c r="S58" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T00:01:23Z</t>
+          <t>2026-10-02T18:24:24Z</t>
         </is>
       </c>
     </row>
@@ -5248,7 +5248,7 @@
       </c>
       <c r="S59" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T00:01:23Z</t>
+          <t>2026-10-02T18:24:24Z</t>
         </is>
       </c>
     </row>
@@ -5337,7 +5337,7 @@
       </c>
       <c r="S60" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T00:01:23Z</t>
+          <t>2026-10-02T18:24:24Z</t>
         </is>
       </c>
     </row>
@@ -5426,7 +5426,7 @@
       </c>
       <c r="S61" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T00:01:23Z</t>
+          <t>2026-10-02T18:24:24Z</t>
         </is>
       </c>
     </row>
@@ -5515,7 +5515,7 @@
       </c>
       <c r="S62" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T00:01:23Z</t>
+          <t>2026-10-02T18:24:24Z</t>
         </is>
       </c>
     </row>
@@ -5604,7 +5604,7 @@
       </c>
       <c r="S63" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T00:01:23Z</t>
+          <t>2026-10-02T18:24:24Z</t>
         </is>
       </c>
     </row>
@@ -5693,7 +5693,7 @@
       </c>
       <c r="S64" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T00:01:23Z</t>
+          <t>2026-10-02T18:24:24Z</t>
         </is>
       </c>
     </row>
@@ -5782,7 +5782,7 @@
       </c>
       <c r="S65" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T00:01:23Z</t>
+          <t>2026-10-02T18:24:24Z</t>
         </is>
       </c>
     </row>
@@ -5871,7 +5871,7 @@
       </c>
       <c r="S66" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T00:01:23Z</t>
+          <t>2026-10-02T18:24:24Z</t>
         </is>
       </c>
     </row>
@@ -5960,7 +5960,7 @@
       </c>
       <c r="S67" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T00:01:23Z</t>
+          <t>2026-10-02T18:24:24Z</t>
         </is>
       </c>
     </row>
@@ -6045,7 +6045,7 @@
       </c>
       <c r="S68" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T00:01:23Z</t>
+          <t>2026-10-02T18:24:24Z</t>
         </is>
       </c>
     </row>
@@ -6130,7 +6130,7 @@
       </c>
       <c r="S69" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T00:01:23Z</t>
+          <t>2026-10-02T18:24:24Z</t>
         </is>
       </c>
     </row>
@@ -6215,7 +6215,7 @@
       </c>
       <c r="S70" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T00:01:23Z</t>
+          <t>2026-10-02T18:24:24Z</t>
         </is>
       </c>
     </row>
@@ -6300,7 +6300,7 @@
       </c>
       <c r="S71" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T00:01:23Z</t>
+          <t>2026-10-02T18:24:24Z</t>
         </is>
       </c>
     </row>
@@ -6385,7 +6385,7 @@
       </c>
       <c r="S72" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T00:01:23Z</t>
+          <t>2026-10-02T18:24:24Z</t>
         </is>
       </c>
     </row>
@@ -6470,7 +6470,7 @@
       </c>
       <c r="S73" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T00:01:23Z</t>
+          <t>2026-10-02T18:24:24Z</t>
         </is>
       </c>
     </row>
@@ -6555,7 +6555,7 @@
       </c>
       <c r="S74" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T00:01:23Z</t>
+          <t>2026-10-02T18:24:24Z</t>
         </is>
       </c>
     </row>
@@ -6640,7 +6640,7 @@
       </c>
       <c r="S75" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T00:01:23Z</t>
+          <t>2026-10-02T18:24:24Z</t>
         </is>
       </c>
     </row>
@@ -6725,7 +6725,7 @@
       </c>
       <c r="S76" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T00:01:23Z</t>
+          <t>2026-10-02T18:24:24Z</t>
         </is>
       </c>
     </row>
@@ -6810,7 +6810,7 @@
       </c>
       <c r="S77" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T00:01:23Z</t>
+          <t>2026-10-02T18:24:24Z</t>
         </is>
       </c>
     </row>
@@ -6895,7 +6895,7 @@
       </c>
       <c r="S78" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T00:01:23Z</t>
+          <t>2026-10-02T18:24:24Z</t>
         </is>
       </c>
     </row>
@@ -6980,7 +6980,7 @@
       </c>
       <c r="S79" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T00:01:23Z</t>
+          <t>2026-10-02T18:24:24Z</t>
         </is>
       </c>
     </row>
@@ -7065,7 +7065,7 @@
       </c>
       <c r="S80" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T00:01:23Z</t>
+          <t>2026-10-02T18:24:24Z</t>
         </is>
       </c>
     </row>
@@ -7150,7 +7150,7 @@
       </c>
       <c r="S81" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T00:01:23Z</t>
+          <t>2026-10-02T18:24:24Z</t>
         </is>
       </c>
     </row>
@@ -7235,7 +7235,7 @@
       </c>
       <c r="S82" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T00:01:23Z</t>
+          <t>2026-10-02T18:24:24Z</t>
         </is>
       </c>
     </row>
@@ -7320,7 +7320,7 @@
       </c>
       <c r="S83" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T00:01:23Z</t>
+          <t>2026-10-02T18:24:24Z</t>
         </is>
       </c>
     </row>
@@ -7405,7 +7405,7 @@
       </c>
       <c r="S84" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T00:01:23Z</t>
+          <t>2026-10-02T18:24:24Z</t>
         </is>
       </c>
     </row>
@@ -7490,7 +7490,7 @@
       </c>
       <c r="S85" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T00:01:23Z</t>
+          <t>2026-10-02T18:24:24Z</t>
         </is>
       </c>
     </row>
@@ -7575,7 +7575,7 @@
       </c>
       <c r="S86" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T00:01:23Z</t>
+          <t>2026-10-02T18:24:24Z</t>
         </is>
       </c>
     </row>
@@ -7660,7 +7660,7 @@
       </c>
       <c r="S87" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T00:01:23Z</t>
+          <t>2026-10-02T18:24:24Z</t>
         </is>
       </c>
     </row>
@@ -7745,7 +7745,7 @@
       </c>
       <c r="S88" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T00:01:23Z</t>
+          <t>2026-10-02T18:24:24Z</t>
         </is>
       </c>
     </row>
@@ -7834,7 +7834,7 @@
       </c>
       <c r="S89" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T00:01:23Z</t>
+          <t>2026-10-02T18:24:24Z</t>
         </is>
       </c>
     </row>
@@ -7923,7 +7923,7 @@
       </c>
       <c r="S90" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T00:01:23Z</t>
+          <t>2026-10-02T18:24:24Z</t>
         </is>
       </c>
     </row>
@@ -8008,7 +8008,7 @@
       </c>
       <c r="S91" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T00:01:23Z</t>
+          <t>2026-10-02T18:24:24Z</t>
         </is>
       </c>
     </row>
@@ -8097,7 +8097,7 @@
       </c>
       <c r="S92" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T00:01:23Z</t>
+          <t>2026-10-02T18:24:24Z</t>
         </is>
       </c>
     </row>
@@ -8186,7 +8186,7 @@
       </c>
       <c r="S93" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T00:01:23Z</t>
+          <t>2026-10-02T18:24:24Z</t>
         </is>
       </c>
     </row>
@@ -8271,7 +8271,7 @@
       </c>
       <c r="S94" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T00:01:23Z</t>
+          <t>2026-10-02T18:24:24Z</t>
         </is>
       </c>
     </row>
@@ -8360,7 +8360,7 @@
       </c>
       <c r="S95" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T00:01:23Z</t>
+          <t>2026-10-02T18:24:24Z</t>
         </is>
       </c>
     </row>
@@ -8449,7 +8449,7 @@
       </c>
       <c r="S96" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T00:01:23Z</t>
+          <t>2026-10-02T18:24:24Z</t>
         </is>
       </c>
     </row>
@@ -8534,7 +8534,7 @@
       </c>
       <c r="S97" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T00:01:23Z</t>
+          <t>2026-10-02T18:24:24Z</t>
         </is>
       </c>
     </row>
@@ -8623,7 +8623,7 @@
       </c>
       <c r="S98" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T00:01:23Z</t>
+          <t>2026-10-02T18:24:24Z</t>
         </is>
       </c>
     </row>
@@ -8712,7 +8712,7 @@
       </c>
       <c r="S99" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T00:01:23Z</t>
+          <t>2026-10-02T18:24:24Z</t>
         </is>
       </c>
     </row>
@@ -8797,7 +8797,7 @@
       </c>
       <c r="S100" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T00:01:23Z</t>
+          <t>2026-10-02T18:24:24Z</t>
         </is>
       </c>
     </row>
@@ -8886,7 +8886,7 @@
       </c>
       <c r="S101" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T00:01:23Z</t>
+          <t>2026-10-02T18:24:24Z</t>
         </is>
       </c>
     </row>
@@ -8975,7 +8975,7 @@
       </c>
       <c r="S102" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T00:01:23Z</t>
+          <t>2026-10-02T18:24:24Z</t>
         </is>
       </c>
     </row>
@@ -9060,7 +9060,7 @@
       </c>
       <c r="S103" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T00:01:23Z</t>
+          <t>2026-10-02T18:24:24Z</t>
         </is>
       </c>
     </row>
@@ -9149,7 +9149,7 @@
       </c>
       <c r="S104" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T00:01:23Z</t>
+          <t>2026-10-02T18:24:24Z</t>
         </is>
       </c>
     </row>
@@ -9238,7 +9238,7 @@
       </c>
       <c r="S105" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T00:01:23Z</t>
+          <t>2026-10-02T18:24:24Z</t>
         </is>
       </c>
     </row>
@@ -9323,7 +9323,7 @@
       </c>
       <c r="S106" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T00:01:23Z</t>
+          <t>2026-10-02T18:24:24Z</t>
         </is>
       </c>
     </row>
@@ -9412,7 +9412,7 @@
       </c>
       <c r="S107" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T00:01:23Z</t>
+          <t>2026-10-02T18:24:24Z</t>
         </is>
       </c>
     </row>
@@ -9501,7 +9501,7 @@
       </c>
       <c r="S108" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T00:01:23Z</t>
+          <t>2026-10-02T18:24:24Z</t>
         </is>
       </c>
     </row>
@@ -9586,7 +9586,7 @@
       </c>
       <c r="S109" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T00:01:23Z</t>
+          <t>2026-10-02T18:24:24Z</t>
         </is>
       </c>
     </row>
@@ -9675,7 +9675,7 @@
       </c>
       <c r="S110" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T00:01:23Z</t>
+          <t>2026-10-02T18:24:24Z</t>
         </is>
       </c>
     </row>
@@ -9764,7 +9764,7 @@
       </c>
       <c r="S111" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T00:01:23Z</t>
+          <t>2026-10-02T18:24:24Z</t>
         </is>
       </c>
     </row>
@@ -9849,7 +9849,7 @@
       </c>
       <c r="S112" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T00:01:23Z</t>
+          <t>2026-10-02T18:24:24Z</t>
         </is>
       </c>
     </row>
@@ -9938,7 +9938,7 @@
       </c>
       <c r="S113" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T00:01:23Z</t>
+          <t>2026-10-02T18:24:24Z</t>
         </is>
       </c>
     </row>
@@ -10027,7 +10027,7 @@
       </c>
       <c r="S114" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T00:01:23Z</t>
+          <t>2026-10-02T18:24:24Z</t>
         </is>
       </c>
     </row>
@@ -10112,7 +10112,7 @@
       </c>
       <c r="S115" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T00:01:23Z</t>
+          <t>2026-10-02T18:24:24Z</t>
         </is>
       </c>
     </row>
@@ -10201,7 +10201,7 @@
       </c>
       <c r="S116" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T00:01:23Z</t>
+          <t>2026-10-02T18:24:24Z</t>
         </is>
       </c>
     </row>
@@ -10290,7 +10290,7 @@
       </c>
       <c r="S117" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T00:01:23Z</t>
+          <t>2026-10-02T18:24:24Z</t>
         </is>
       </c>
     </row>
@@ -10379,7 +10379,7 @@
       </c>
       <c r="S118" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T00:01:23Z</t>
+          <t>2026-10-02T18:24:24Z</t>
         </is>
       </c>
     </row>
@@ -10468,7 +10468,7 @@
       </c>
       <c r="S119" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T00:01:23Z</t>
+          <t>2026-10-02T18:24:24Z</t>
         </is>
       </c>
     </row>
@@ -10557,7 +10557,7 @@
       </c>
       <c r="S120" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T00:01:23Z</t>
+          <t>2026-10-02T18:24:24Z</t>
         </is>
       </c>
     </row>
@@ -10646,7 +10646,7 @@
       </c>
       <c r="S121" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T00:01:23Z</t>
+          <t>2026-10-02T18:24:24Z</t>
         </is>
       </c>
     </row>
@@ -10735,7 +10735,7 @@
       </c>
       <c r="S122" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T00:01:23Z</t>
+          <t>2026-10-02T18:24:24Z</t>
         </is>
       </c>
     </row>
@@ -10824,7 +10824,7 @@
       </c>
       <c r="S123" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T00:01:23Z</t>
+          <t>2026-10-02T18:24:24Z</t>
         </is>
       </c>
     </row>
@@ -10913,7 +10913,7 @@
       </c>
       <c r="S124" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T00:01:23Z</t>
+          <t>2026-10-02T18:24:24Z</t>
         </is>
       </c>
     </row>
@@ -11002,7 +11002,7 @@
       </c>
       <c r="S125" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T00:01:23Z</t>
+          <t>2026-10-02T18:24:24Z</t>
         </is>
       </c>
     </row>
@@ -11091,7 +11091,7 @@
       </c>
       <c r="S126" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T00:01:23Z</t>
+          <t>2026-10-02T18:24:24Z</t>
         </is>
       </c>
     </row>
@@ -11180,7 +11180,7 @@
       </c>
       <c r="S127" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T00:01:23Z</t>
+          <t>2026-10-02T18:24:24Z</t>
         </is>
       </c>
     </row>
@@ -11269,7 +11269,7 @@
       </c>
       <c r="S128" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T00:01:23Z</t>
+          <t>2026-10-02T18:24:24Z</t>
         </is>
       </c>
     </row>
@@ -11354,7 +11354,7 @@
       </c>
       <c r="S129" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T00:01:23Z</t>
+          <t>2026-10-02T18:24:24Z</t>
         </is>
       </c>
     </row>
@@ -11439,7 +11439,7 @@
       </c>
       <c r="S130" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T00:01:23Z</t>
+          <t>2026-10-02T18:24:24Z</t>
         </is>
       </c>
     </row>
@@ -11524,7 +11524,7 @@
       </c>
       <c r="S131" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T00:01:23Z</t>
+          <t>2026-10-02T18:24:24Z</t>
         </is>
       </c>
     </row>
@@ -11609,7 +11609,7 @@
       </c>
       <c r="S132" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T00:01:23Z</t>
+          <t>2026-10-02T18:24:24Z</t>
         </is>
       </c>
     </row>
@@ -11694,7 +11694,7 @@
       </c>
       <c r="S133" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T00:01:23Z</t>
+          <t>2026-10-02T18:24:24Z</t>
         </is>
       </c>
     </row>
@@ -11779,7 +11779,7 @@
       </c>
       <c r="S134" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T00:01:23Z</t>
+          <t>2026-10-02T18:24:24Z</t>
         </is>
       </c>
     </row>
@@ -11864,7 +11864,7 @@
       </c>
       <c r="S135" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T00:01:23Z</t>
+          <t>2026-10-02T18:24:24Z</t>
         </is>
       </c>
     </row>
@@ -11949,7 +11949,7 @@
       </c>
       <c r="S136" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T00:01:23Z</t>
+          <t>2026-10-02T18:24:24Z</t>
         </is>
       </c>
     </row>
@@ -12034,7 +12034,7 @@
       </c>
       <c r="S137" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T00:01:23Z</t>
+          <t>2026-10-02T18:24:24Z</t>
         </is>
       </c>
     </row>
@@ -12119,7 +12119,7 @@
       </c>
       <c r="S138" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T00:01:23Z</t>
+          <t>2026-10-02T18:24:24Z</t>
         </is>
       </c>
     </row>
@@ -12204,7 +12204,7 @@
       </c>
       <c r="S139" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T00:01:23Z</t>
+          <t>2026-10-02T18:24:24Z</t>
         </is>
       </c>
     </row>
@@ -12289,7 +12289,7 @@
       </c>
       <c r="S140" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T00:01:23Z</t>
+          <t>2026-10-02T18:24:24Z</t>
         </is>
       </c>
     </row>
@@ -12374,7 +12374,7 @@
       </c>
       <c r="S141" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T00:01:23Z</t>
+          <t>2026-10-02T18:24:24Z</t>
         </is>
       </c>
     </row>
@@ -12459,7 +12459,7 @@
       </c>
       <c r="S142" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T00:01:23Z</t>
+          <t>2026-10-02T18:24:24Z</t>
         </is>
       </c>
     </row>
@@ -12544,7 +12544,7 @@
       </c>
       <c r="S143" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T00:01:23Z</t>
+          <t>2026-10-02T18:24:24Z</t>
         </is>
       </c>
     </row>
@@ -12629,7 +12629,7 @@
       </c>
       <c r="S144" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T00:01:23Z</t>
+          <t>2026-10-02T18:24:24Z</t>
         </is>
       </c>
     </row>
@@ -12714,7 +12714,7 @@
       </c>
       <c r="S145" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T00:01:23Z</t>
+          <t>2026-10-02T18:24:24Z</t>
         </is>
       </c>
     </row>
@@ -12799,7 +12799,7 @@
       </c>
       <c r="S146" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T00:01:23Z</t>
+          <t>2026-10-02T18:24:24Z</t>
         </is>
       </c>
     </row>
@@ -12884,7 +12884,7 @@
       </c>
       <c r="S147" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T00:01:23Z</t>
+          <t>2026-10-02T18:24:24Z</t>
         </is>
       </c>
     </row>
@@ -12969,7 +12969,7 @@
       </c>
       <c r="S148" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T00:01:23Z</t>
+          <t>2026-10-02T18:24:24Z</t>
         </is>
       </c>
     </row>
@@ -13054,7 +13054,7 @@
       </c>
       <c r="S149" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T00:01:23Z</t>
+          <t>2026-10-02T18:24:24Z</t>
         </is>
       </c>
     </row>
@@ -13143,7 +13143,7 @@
       </c>
       <c r="S150" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T00:01:23Z</t>
+          <t>2026-10-02T18:24:24Z</t>
         </is>
       </c>
     </row>
@@ -13232,7 +13232,7 @@
       </c>
       <c r="S151" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T00:01:23Z</t>
+          <t>2026-10-02T18:24:24Z</t>
         </is>
       </c>
     </row>
@@ -13317,7 +13317,7 @@
       </c>
       <c r="S152" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T00:01:23Z</t>
+          <t>2026-10-02T18:24:24Z</t>
         </is>
       </c>
     </row>
@@ -13406,7 +13406,7 @@
       </c>
       <c r="S153" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T00:01:23Z</t>
+          <t>2026-10-02T18:24:24Z</t>
         </is>
       </c>
     </row>
@@ -13495,7 +13495,7 @@
       </c>
       <c r="S154" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T00:01:23Z</t>
+          <t>2026-10-02T18:24:24Z</t>
         </is>
       </c>
     </row>
@@ -13580,7 +13580,7 @@
       </c>
       <c r="S155" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T00:01:23Z</t>
+          <t>2026-10-02T18:24:24Z</t>
         </is>
       </c>
     </row>
@@ -13669,7 +13669,7 @@
       </c>
       <c r="S156" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T00:01:23Z</t>
+          <t>2026-10-02T18:24:24Z</t>
         </is>
       </c>
     </row>
@@ -13758,7 +13758,7 @@
       </c>
       <c r="S157" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T00:01:23Z</t>
+          <t>2026-10-02T18:24:24Z</t>
         </is>
       </c>
     </row>
@@ -13843,7 +13843,7 @@
       </c>
       <c r="S158" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T00:01:23Z</t>
+          <t>2026-10-02T18:24:24Z</t>
         </is>
       </c>
     </row>
@@ -13932,7 +13932,7 @@
       </c>
       <c r="S159" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T00:01:23Z</t>
+          <t>2026-10-02T18:24:24Z</t>
         </is>
       </c>
     </row>
@@ -14021,7 +14021,7 @@
       </c>
       <c r="S160" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T00:01:23Z</t>
+          <t>2026-10-02T18:24:24Z</t>
         </is>
       </c>
     </row>
@@ -14106,7 +14106,7 @@
       </c>
       <c r="S161" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T00:01:23Z</t>
+          <t>2026-10-02T18:24:24Z</t>
         </is>
       </c>
     </row>
@@ -14195,7 +14195,7 @@
       </c>
       <c r="S162" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T00:01:23Z</t>
+          <t>2026-10-02T18:24:24Z</t>
         </is>
       </c>
     </row>
@@ -14284,7 +14284,7 @@
       </c>
       <c r="S163" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T00:01:23Z</t>
+          <t>2026-10-02T18:24:24Z</t>
         </is>
       </c>
     </row>
@@ -14369,7 +14369,7 @@
       </c>
       <c r="S164" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T00:01:23Z</t>
+          <t>2026-10-02T18:24:24Z</t>
         </is>
       </c>
     </row>
@@ -14458,7 +14458,7 @@
       </c>
       <c r="S165" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T00:01:23Z</t>
+          <t>2026-10-02T18:24:24Z</t>
         </is>
       </c>
     </row>
@@ -14547,7 +14547,7 @@
       </c>
       <c r="S166" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T00:01:23Z</t>
+          <t>2026-10-02T18:24:24Z</t>
         </is>
       </c>
     </row>
@@ -14632,7 +14632,7 @@
       </c>
       <c r="S167" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T00:01:23Z</t>
+          <t>2026-10-02T18:24:24Z</t>
         </is>
       </c>
     </row>
@@ -14721,7 +14721,7 @@
       </c>
       <c r="S168" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T00:01:23Z</t>
+          <t>2026-10-02T18:24:24Z</t>
         </is>
       </c>
     </row>
@@ -14810,7 +14810,7 @@
       </c>
       <c r="S169" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T00:01:23Z</t>
+          <t>2026-10-02T18:24:24Z</t>
         </is>
       </c>
     </row>
@@ -14895,7 +14895,7 @@
       </c>
       <c r="S170" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T00:01:23Z</t>
+          <t>2026-10-02T18:24:24Z</t>
         </is>
       </c>
     </row>
@@ -14984,7 +14984,7 @@
       </c>
       <c r="S171" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T00:01:23Z</t>
+          <t>2026-10-02T18:24:24Z</t>
         </is>
       </c>
     </row>
@@ -15073,7 +15073,7 @@
       </c>
       <c r="S172" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T00:01:23Z</t>
+          <t>2026-10-02T18:24:24Z</t>
         </is>
       </c>
     </row>
@@ -15158,7 +15158,7 @@
       </c>
       <c r="S173" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T00:01:23Z</t>
+          <t>2026-10-02T18:24:24Z</t>
         </is>
       </c>
     </row>
@@ -15247,7 +15247,7 @@
       </c>
       <c r="S174" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T00:01:23Z</t>
+          <t>2026-10-02T18:24:24Z</t>
         </is>
       </c>
     </row>
@@ -15336,7 +15336,7 @@
       </c>
       <c r="S175" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T00:01:23Z</t>
+          <t>2026-10-02T18:24:24Z</t>
         </is>
       </c>
     </row>
@@ -15421,7 +15421,7 @@
       </c>
       <c r="S176" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T00:01:23Z</t>
+          <t>2026-10-02T18:24:24Z</t>
         </is>
       </c>
     </row>
@@ -15510,7 +15510,7 @@
       </c>
       <c r="S177" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T00:01:23Z</t>
+          <t>2026-10-02T18:24:24Z</t>
         </is>
       </c>
     </row>
@@ -15599,7 +15599,7 @@
       </c>
       <c r="S178" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T00:01:23Z</t>
+          <t>2026-10-02T18:24:24Z</t>
         </is>
       </c>
     </row>
@@ -15688,7 +15688,7 @@
       </c>
       <c r="S179" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T00:01:23Z</t>
+          <t>2026-10-02T18:24:24Z</t>
         </is>
       </c>
     </row>
@@ -15777,7 +15777,7 @@
       </c>
       <c r="S180" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T00:01:23Z</t>
+          <t>2026-10-02T18:24:24Z</t>
         </is>
       </c>
     </row>
@@ -15866,7 +15866,7 @@
       </c>
       <c r="S181" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T00:01:23Z</t>
+          <t>2026-10-02T18:24:24Z</t>
         </is>
       </c>
     </row>
@@ -15955,7 +15955,7 @@
       </c>
       <c r="S182" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T00:01:23Z</t>
+          <t>2026-10-02T18:24:24Z</t>
         </is>
       </c>
     </row>
@@ -16044,7 +16044,7 @@
       </c>
       <c r="S183" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T00:01:23Z</t>
+          <t>2026-10-02T18:24:24Z</t>
         </is>
       </c>
     </row>
@@ -16133,7 +16133,7 @@
       </c>
       <c r="S184" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T00:01:23Z</t>
+          <t>2026-10-02T18:24:24Z</t>
         </is>
       </c>
     </row>
@@ -16222,7 +16222,7 @@
       </c>
       <c r="S185" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T00:01:23Z</t>
+          <t>2026-10-02T18:24:24Z</t>
         </is>
       </c>
     </row>
@@ -16311,7 +16311,7 @@
       </c>
       <c r="S186" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T00:01:23Z</t>
+          <t>2026-10-02T18:24:24Z</t>
         </is>
       </c>
     </row>
@@ -16400,7 +16400,7 @@
       </c>
       <c r="S187" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T00:01:23Z</t>
+          <t>2026-10-02T18:24:24Z</t>
         </is>
       </c>
     </row>
@@ -16489,7 +16489,7 @@
       </c>
       <c r="S188" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T00:01:23Z</t>
+          <t>2026-10-02T18:24:24Z</t>
         </is>
       </c>
     </row>
@@ -16578,7 +16578,7 @@
       </c>
       <c r="S189" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T00:01:23Z</t>
+          <t>2026-10-02T18:24:24Z</t>
         </is>
       </c>
     </row>
@@ -16663,7 +16663,7 @@
       </c>
       <c r="S190" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T00:01:23Z</t>
+          <t>2026-10-02T18:24:24Z</t>
         </is>
       </c>
     </row>
@@ -16748,7 +16748,7 @@
       </c>
       <c r="S191" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T00:01:23Z</t>
+          <t>2026-10-02T18:24:24Z</t>
         </is>
       </c>
     </row>
@@ -16833,7 +16833,7 @@
       </c>
       <c r="S192" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T00:01:23Z</t>
+          <t>2026-10-02T18:24:24Z</t>
         </is>
       </c>
     </row>
@@ -16918,7 +16918,7 @@
       </c>
       <c r="S193" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T00:01:23Z</t>
+          <t>2026-10-02T18:24:24Z</t>
         </is>
       </c>
     </row>
@@ -17003,7 +17003,7 @@
       </c>
       <c r="S194" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T00:01:23Z</t>
+          <t>2026-10-02T18:24:24Z</t>
         </is>
       </c>
     </row>
@@ -17088,7 +17088,7 @@
       </c>
       <c r="S195" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T00:01:23Z</t>
+          <t>2026-10-02T18:24:24Z</t>
         </is>
       </c>
     </row>
@@ -17173,7 +17173,7 @@
       </c>
       <c r="S196" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T00:01:23Z</t>
+          <t>2026-10-02T18:24:24Z</t>
         </is>
       </c>
     </row>
@@ -17258,7 +17258,7 @@
       </c>
       <c r="S197" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T00:01:23Z</t>
+          <t>2026-10-02T18:24:24Z</t>
         </is>
       </c>
     </row>
@@ -17343,7 +17343,7 @@
       </c>
       <c r="S198" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T00:01:23Z</t>
+          <t>2026-10-02T18:24:24Z</t>
         </is>
       </c>
     </row>
@@ -17428,7 +17428,7 @@
       </c>
       <c r="S199" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T00:01:23Z</t>
+          <t>2026-10-02T18:24:24Z</t>
         </is>
       </c>
     </row>
@@ -17513,7 +17513,7 @@
       </c>
       <c r="S200" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T00:01:23Z</t>
+          <t>2026-10-02T18:24:24Z</t>
         </is>
       </c>
     </row>
@@ -17598,7 +17598,7 @@
       </c>
       <c r="S201" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T00:01:23Z</t>
+          <t>2026-10-02T18:24:24Z</t>
         </is>
       </c>
     </row>
@@ -17683,7 +17683,7 @@
       </c>
       <c r="S202" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T00:01:23Z</t>
+          <t>2026-10-02T18:24:24Z</t>
         </is>
       </c>
     </row>
@@ -17768,7 +17768,7 @@
       </c>
       <c r="S203" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T00:01:23Z</t>
+          <t>2026-10-02T18:24:24Z</t>
         </is>
       </c>
     </row>
@@ -17853,7 +17853,7 @@
       </c>
       <c r="S204" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T00:01:23Z</t>
+          <t>2026-10-02T18:24:24Z</t>
         </is>
       </c>
     </row>
@@ -17938,7 +17938,7 @@
       </c>
       <c r="S205" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T00:01:23Z</t>
+          <t>2026-10-02T18:24:24Z</t>
         </is>
       </c>
     </row>
@@ -18023,7 +18023,7 @@
       </c>
       <c r="S206" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T00:01:23Z</t>
+          <t>2026-10-02T18:24:24Z</t>
         </is>
       </c>
     </row>
@@ -18108,7 +18108,7 @@
       </c>
       <c r="S207" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T00:01:23Z</t>
+          <t>2026-10-02T18:24:24Z</t>
         </is>
       </c>
     </row>
@@ -18193,7 +18193,7 @@
       </c>
       <c r="S208" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T00:01:23Z</t>
+          <t>2026-10-02T18:24:24Z</t>
         </is>
       </c>
     </row>
@@ -18278,7 +18278,7 @@
       </c>
       <c r="S209" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T00:01:23Z</t>
+          <t>2026-10-02T18:24:24Z</t>
         </is>
       </c>
     </row>
@@ -18363,7 +18363,7 @@
       </c>
       <c r="S210" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T00:01:23Z</t>
+          <t>2026-10-02T18:24:24Z</t>
         </is>
       </c>
     </row>
@@ -18452,7 +18452,7 @@
       </c>
       <c r="S211" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T00:01:23Z</t>
+          <t>2026-10-02T18:24:24Z</t>
         </is>
       </c>
     </row>
@@ -18541,7 +18541,7 @@
       </c>
       <c r="S212" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T00:01:23Z</t>
+          <t>2026-10-02T18:24:24Z</t>
         </is>
       </c>
     </row>
@@ -18626,7 +18626,7 @@
       </c>
       <c r="S213" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T00:01:23Z</t>
+          <t>2026-10-02T18:24:24Z</t>
         </is>
       </c>
     </row>
@@ -18715,7 +18715,7 @@
       </c>
       <c r="S214" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T00:01:23Z</t>
+          <t>2026-10-02T18:24:24Z</t>
         </is>
       </c>
     </row>
@@ -18804,7 +18804,7 @@
       </c>
       <c r="S215" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T00:01:23Z</t>
+          <t>2026-10-02T18:24:24Z</t>
         </is>
       </c>
     </row>
@@ -18889,7 +18889,7 @@
       </c>
       <c r="S216" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T00:01:23Z</t>
+          <t>2026-10-02T18:24:24Z</t>
         </is>
       </c>
     </row>
@@ -18978,7 +18978,7 @@
       </c>
       <c r="S217" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T00:01:23Z</t>
+          <t>2026-10-02T18:24:24Z</t>
         </is>
       </c>
     </row>
@@ -19067,7 +19067,7 @@
       </c>
       <c r="S218" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T00:01:23Z</t>
+          <t>2026-10-02T18:24:24Z</t>
         </is>
       </c>
     </row>
@@ -19152,7 +19152,7 @@
       </c>
       <c r="S219" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T00:01:23Z</t>
+          <t>2026-10-02T18:24:24Z</t>
         </is>
       </c>
     </row>
@@ -19241,7 +19241,7 @@
       </c>
       <c r="S220" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T00:01:23Z</t>
+          <t>2026-10-02T18:24:24Z</t>
         </is>
       </c>
     </row>
@@ -19330,7 +19330,7 @@
       </c>
       <c r="S221" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T00:01:23Z</t>
+          <t>2026-10-02T18:24:24Z</t>
         </is>
       </c>
     </row>
@@ -19415,7 +19415,7 @@
       </c>
       <c r="S222" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T00:01:23Z</t>
+          <t>2026-10-02T18:24:24Z</t>
         </is>
       </c>
     </row>
@@ -19504,7 +19504,7 @@
       </c>
       <c r="S223" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T00:01:23Z</t>
+          <t>2026-10-02T18:24:24Z</t>
         </is>
       </c>
     </row>
@@ -19593,7 +19593,7 @@
       </c>
       <c r="S224" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T00:01:23Z</t>
+          <t>2026-10-02T18:24:24Z</t>
         </is>
       </c>
     </row>
@@ -19678,7 +19678,7 @@
       </c>
       <c r="S225" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T00:01:23Z</t>
+          <t>2026-10-02T18:24:24Z</t>
         </is>
       </c>
     </row>
@@ -19767,7 +19767,7 @@
       </c>
       <c r="S226" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T00:01:23Z</t>
+          <t>2026-10-02T18:24:24Z</t>
         </is>
       </c>
     </row>
@@ -19856,7 +19856,7 @@
       </c>
       <c r="S227" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T00:01:23Z</t>
+          <t>2026-10-02T18:24:24Z</t>
         </is>
       </c>
     </row>
@@ -19941,7 +19941,7 @@
       </c>
       <c r="S228" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T00:01:23Z</t>
+          <t>2026-10-02T18:24:24Z</t>
         </is>
       </c>
     </row>
@@ -20030,7 +20030,7 @@
       </c>
       <c r="S229" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T00:01:23Z</t>
+          <t>2026-10-02T18:24:24Z</t>
         </is>
       </c>
     </row>
@@ -20119,7 +20119,7 @@
       </c>
       <c r="S230" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T00:01:23Z</t>
+          <t>2026-10-02T18:24:24Z</t>
         </is>
       </c>
     </row>
@@ -20204,7 +20204,7 @@
       </c>
       <c r="S231" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T00:01:23Z</t>
+          <t>2026-10-02T18:24:24Z</t>
         </is>
       </c>
     </row>
@@ -20293,7 +20293,7 @@
       </c>
       <c r="S232" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T00:01:23Z</t>
+          <t>2026-10-02T18:24:24Z</t>
         </is>
       </c>
     </row>
@@ -20382,7 +20382,7 @@
       </c>
       <c r="S233" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T00:01:23Z</t>
+          <t>2026-10-02T18:24:24Z</t>
         </is>
       </c>
     </row>
@@ -20467,7 +20467,7 @@
       </c>
       <c r="S234" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T00:01:23Z</t>
+          <t>2026-10-02T18:24:24Z</t>
         </is>
       </c>
     </row>
@@ -20556,7 +20556,7 @@
       </c>
       <c r="S235" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T00:01:23Z</t>
+          <t>2026-10-02T18:24:24Z</t>
         </is>
       </c>
     </row>
@@ -20645,7 +20645,7 @@
       </c>
       <c r="S236" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T00:01:23Z</t>
+          <t>2026-10-02T18:24:24Z</t>
         </is>
       </c>
     </row>
@@ -20730,7 +20730,7 @@
       </c>
       <c r="S237" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T00:01:23Z</t>
+          <t>2026-10-02T18:24:24Z</t>
         </is>
       </c>
     </row>
@@ -20819,7 +20819,7 @@
       </c>
       <c r="S238" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T00:01:23Z</t>
+          <t>2026-10-02T18:24:24Z</t>
         </is>
       </c>
     </row>
@@ -20908,7 +20908,7 @@
       </c>
       <c r="S239" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T00:01:23Z</t>
+          <t>2026-10-02T18:24:24Z</t>
         </is>
       </c>
     </row>
@@ -20997,7 +20997,7 @@
       </c>
       <c r="S240" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T00:01:23Z</t>
+          <t>2026-10-02T18:24:24Z</t>
         </is>
       </c>
     </row>
@@ -21086,7 +21086,7 @@
       </c>
       <c r="S241" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T00:01:23Z</t>
+          <t>2026-10-02T18:24:24Z</t>
         </is>
       </c>
     </row>
@@ -21175,7 +21175,7 @@
       </c>
       <c r="S242" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T00:01:23Z</t>
+          <t>2026-10-02T18:24:24Z</t>
         </is>
       </c>
     </row>
@@ -21264,7 +21264,7 @@
       </c>
       <c r="S243" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T00:01:23Z</t>
+          <t>2026-10-02T18:24:24Z</t>
         </is>
       </c>
     </row>
@@ -21353,7 +21353,7 @@
       </c>
       <c r="S244" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T00:01:23Z</t>
+          <t>2026-10-02T18:24:24Z</t>
         </is>
       </c>
     </row>
@@ -21442,7 +21442,7 @@
       </c>
       <c r="S245" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T00:01:23Z</t>
+          <t>2026-10-02T18:24:24Z</t>
         </is>
       </c>
     </row>
@@ -21531,7 +21531,7 @@
       </c>
       <c r="S246" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T00:01:23Z</t>
+          <t>2026-10-02T18:24:24Z</t>
         </is>
       </c>
     </row>
@@ -21620,7 +21620,7 @@
       </c>
       <c r="S247" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T00:01:23Z</t>
+          <t>2026-10-02T18:24:24Z</t>
         </is>
       </c>
     </row>
@@ -21709,7 +21709,7 @@
       </c>
       <c r="S248" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T00:01:23Z</t>
+          <t>2026-10-02T18:24:24Z</t>
         </is>
       </c>
     </row>
@@ -21798,7 +21798,7 @@
       </c>
       <c r="S249" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T00:01:23Z</t>
+          <t>2026-10-02T18:24:24Z</t>
         </is>
       </c>
     </row>
@@ -21887,7 +21887,7 @@
       </c>
       <c r="S250" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T00:01:23Z</t>
+          <t>2026-10-02T18:24:24Z</t>
         </is>
       </c>
     </row>
@@ -22019,7 +22019,7 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T00:01:23Z</t>
+          <t>2026-10-02T18:24:24Z</t>
         </is>
       </c>
     </row>
@@ -22099,7 +22099,7 @@
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>{"dataset_id": "bcv_pib_sector_institucional_anual", "title": "Producto interno bruto por sector institucional anual", "table": "Variaciones porcentuales", "source_file": "5_2_1_si_anual.xlsx", "base": "2007", "price_type": "Precios constantes", "measure": "Variación porcentual interanual", "frequency": "Anual", "period": "2025", "year": 2025, "quarter": null, "classification": "Sector institucional", "component": "Impuestos netos sobre los productos", "value": 10.600260421283764, "unit": "Porcentaje", "status": "Preliminar", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/cuentas_macroeconomicas/5_2_1_si_anual.xlsx", "fetched_at": "2026-10-02T00:01:23Z"}</t>
+          <t>{"dataset_id": "bcv_pib_sector_institucional_anual", "title": "Producto interno bruto por sector institucional anual", "table": "Variaciones porcentuales", "source_file": "5_2_1_si_anual.xlsx", "base": "2007", "price_type": "Precios constantes", "measure": "Variación porcentual interanual", "frequency": "Anual", "period": "2025", "year": 2025, "quarter": null, "classification": "Sector institucional", "component": "Impuestos netos sobre los productos", "value": 10.600260421283764, "unit": "Porcentaje", "status": "Preliminar", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/cuentas_macroeconomicas/5_2_1_si_anual.xlsx", "fetched_at": "2026-10-02T18:24:24Z"}</t>
         </is>
       </c>
     </row>

--- a/assets/data/bcv/excel/ove_bcv_pib_sector_institucional_anual.xlsx
+++ b/assets/data/bcv/excel/ove_bcv_pib_sector_institucional_anual.xlsx
@@ -736,7 +736,7 @@
       </c>
       <c r="S7" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T18:24:24Z</t>
+          <t>2026-10-02T23:55:31Z</t>
         </is>
       </c>
     </row>
@@ -821,7 +821,7 @@
       </c>
       <c r="S8" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T18:24:24Z</t>
+          <t>2026-10-02T23:55:31Z</t>
         </is>
       </c>
     </row>
@@ -906,7 +906,7 @@
       </c>
       <c r="S9" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T18:24:24Z</t>
+          <t>2026-10-02T23:55:31Z</t>
         </is>
       </c>
     </row>
@@ -991,7 +991,7 @@
       </c>
       <c r="S10" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T18:24:24Z</t>
+          <t>2026-10-02T23:55:31Z</t>
         </is>
       </c>
     </row>
@@ -1076,7 +1076,7 @@
       </c>
       <c r="S11" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T18:24:24Z</t>
+          <t>2026-10-02T23:55:31Z</t>
         </is>
       </c>
     </row>
@@ -1161,7 +1161,7 @@
       </c>
       <c r="S12" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T18:24:24Z</t>
+          <t>2026-10-02T23:55:31Z</t>
         </is>
       </c>
     </row>
@@ -1246,7 +1246,7 @@
       </c>
       <c r="S13" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T18:24:24Z</t>
+          <t>2026-10-02T23:55:31Z</t>
         </is>
       </c>
     </row>
@@ -1331,7 +1331,7 @@
       </c>
       <c r="S14" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T18:24:24Z</t>
+          <t>2026-10-02T23:55:31Z</t>
         </is>
       </c>
     </row>
@@ -1416,7 +1416,7 @@
       </c>
       <c r="S15" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T18:24:24Z</t>
+          <t>2026-10-02T23:55:31Z</t>
         </is>
       </c>
     </row>
@@ -1501,7 +1501,7 @@
       </c>
       <c r="S16" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T18:24:24Z</t>
+          <t>2026-10-02T23:55:31Z</t>
         </is>
       </c>
     </row>
@@ -1586,7 +1586,7 @@
       </c>
       <c r="S17" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T18:24:24Z</t>
+          <t>2026-10-02T23:55:31Z</t>
         </is>
       </c>
     </row>
@@ -1671,7 +1671,7 @@
       </c>
       <c r="S18" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T18:24:24Z</t>
+          <t>2026-10-02T23:55:31Z</t>
         </is>
       </c>
     </row>
@@ -1756,7 +1756,7 @@
       </c>
       <c r="S19" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T18:24:24Z</t>
+          <t>2026-10-02T23:55:31Z</t>
         </is>
       </c>
     </row>
@@ -1841,7 +1841,7 @@
       </c>
       <c r="S20" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T18:24:24Z</t>
+          <t>2026-10-02T23:55:31Z</t>
         </is>
       </c>
     </row>
@@ -1926,7 +1926,7 @@
       </c>
       <c r="S21" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T18:24:24Z</t>
+          <t>2026-10-02T23:55:31Z</t>
         </is>
       </c>
     </row>
@@ -2011,7 +2011,7 @@
       </c>
       <c r="S22" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T18:24:24Z</t>
+          <t>2026-10-02T23:55:31Z</t>
         </is>
       </c>
     </row>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="S23" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T18:24:24Z</t>
+          <t>2026-10-02T23:55:31Z</t>
         </is>
       </c>
     </row>
@@ -2181,7 +2181,7 @@
       </c>
       <c r="S24" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T18:24:24Z</t>
+          <t>2026-10-02T23:55:31Z</t>
         </is>
       </c>
     </row>
@@ -2266,7 +2266,7 @@
       </c>
       <c r="S25" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T18:24:24Z</t>
+          <t>2026-10-02T23:55:31Z</t>
         </is>
       </c>
     </row>
@@ -2351,7 +2351,7 @@
       </c>
       <c r="S26" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T18:24:24Z</t>
+          <t>2026-10-02T23:55:31Z</t>
         </is>
       </c>
     </row>
@@ -2436,7 +2436,7 @@
       </c>
       <c r="S27" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T18:24:24Z</t>
+          <t>2026-10-02T23:55:31Z</t>
         </is>
       </c>
     </row>
@@ -2525,7 +2525,7 @@
       </c>
       <c r="S28" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T18:24:24Z</t>
+          <t>2026-10-02T23:55:31Z</t>
         </is>
       </c>
     </row>
@@ -2614,7 +2614,7 @@
       </c>
       <c r="S29" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T18:24:24Z</t>
+          <t>2026-10-02T23:55:31Z</t>
         </is>
       </c>
     </row>
@@ -2699,7 +2699,7 @@
       </c>
       <c r="S30" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T18:24:24Z</t>
+          <t>2026-10-02T23:55:31Z</t>
         </is>
       </c>
     </row>
@@ -2788,7 +2788,7 @@
       </c>
       <c r="S31" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T18:24:24Z</t>
+          <t>2026-10-02T23:55:31Z</t>
         </is>
       </c>
     </row>
@@ -2877,7 +2877,7 @@
       </c>
       <c r="S32" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T18:24:24Z</t>
+          <t>2026-10-02T23:55:31Z</t>
         </is>
       </c>
     </row>
@@ -2962,7 +2962,7 @@
       </c>
       <c r="S33" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T18:24:24Z</t>
+          <t>2026-10-02T23:55:31Z</t>
         </is>
       </c>
     </row>
@@ -3051,7 +3051,7 @@
       </c>
       <c r="S34" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T18:24:24Z</t>
+          <t>2026-10-02T23:55:31Z</t>
         </is>
       </c>
     </row>
@@ -3140,7 +3140,7 @@
       </c>
       <c r="S35" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T18:24:24Z</t>
+          <t>2026-10-02T23:55:31Z</t>
         </is>
       </c>
     </row>
@@ -3225,7 +3225,7 @@
       </c>
       <c r="S36" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T18:24:24Z</t>
+          <t>2026-10-02T23:55:31Z</t>
         </is>
       </c>
     </row>
@@ -3314,7 +3314,7 @@
       </c>
       <c r="S37" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T18:24:24Z</t>
+          <t>2026-10-02T23:55:31Z</t>
         </is>
       </c>
     </row>
@@ -3403,7 +3403,7 @@
       </c>
       <c r="S38" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T18:24:24Z</t>
+          <t>2026-10-02T23:55:31Z</t>
         </is>
       </c>
     </row>
@@ -3488,7 +3488,7 @@
       </c>
       <c r="S39" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T18:24:24Z</t>
+          <t>2026-10-02T23:55:31Z</t>
         </is>
       </c>
     </row>
@@ -3577,7 +3577,7 @@
       </c>
       <c r="S40" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T18:24:24Z</t>
+          <t>2026-10-02T23:55:31Z</t>
         </is>
       </c>
     </row>
@@ -3666,7 +3666,7 @@
       </c>
       <c r="S41" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T18:24:24Z</t>
+          <t>2026-10-02T23:55:31Z</t>
         </is>
       </c>
     </row>
@@ -3751,7 +3751,7 @@
       </c>
       <c r="S42" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T18:24:24Z</t>
+          <t>2026-10-02T23:55:31Z</t>
         </is>
       </c>
     </row>
@@ -3840,7 +3840,7 @@
       </c>
       <c r="S43" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T18:24:24Z</t>
+          <t>2026-10-02T23:55:31Z</t>
         </is>
       </c>
     </row>
@@ -3929,7 +3929,7 @@
       </c>
       <c r="S44" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T18:24:24Z</t>
+          <t>2026-10-02T23:55:31Z</t>
         </is>
       </c>
     </row>
@@ -4014,7 +4014,7 @@
       </c>
       <c r="S45" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T18:24:24Z</t>
+          <t>2026-10-02T23:55:31Z</t>
         </is>
       </c>
     </row>
@@ -4103,7 +4103,7 @@
       </c>
       <c r="S46" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T18:24:24Z</t>
+          <t>2026-10-02T23:55:31Z</t>
         </is>
       </c>
     </row>
@@ -4192,7 +4192,7 @@
       </c>
       <c r="S47" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T18:24:24Z</t>
+          <t>2026-10-02T23:55:31Z</t>
         </is>
       </c>
     </row>
@@ -4277,7 +4277,7 @@
       </c>
       <c r="S48" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T18:24:24Z</t>
+          <t>2026-10-02T23:55:31Z</t>
         </is>
       </c>
     </row>
@@ -4366,7 +4366,7 @@
       </c>
       <c r="S49" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T18:24:24Z</t>
+          <t>2026-10-02T23:55:31Z</t>
         </is>
       </c>
     </row>
@@ -4455,7 +4455,7 @@
       </c>
       <c r="S50" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T18:24:24Z</t>
+          <t>2026-10-02T23:55:31Z</t>
         </is>
       </c>
     </row>
@@ -4540,7 +4540,7 @@
       </c>
       <c r="S51" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T18:24:24Z</t>
+          <t>2026-10-02T23:55:31Z</t>
         </is>
       </c>
     </row>
@@ -4629,7 +4629,7 @@
       </c>
       <c r="S52" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T18:24:24Z</t>
+          <t>2026-10-02T23:55:31Z</t>
         </is>
       </c>
     </row>
@@ -4718,7 +4718,7 @@
       </c>
       <c r="S53" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T18:24:24Z</t>
+          <t>2026-10-02T23:55:31Z</t>
         </is>
       </c>
     </row>
@@ -4803,7 +4803,7 @@
       </c>
       <c r="S54" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T18:24:24Z</t>
+          <t>2026-10-02T23:55:31Z</t>
         </is>
       </c>
     </row>
@@ -4892,7 +4892,7 @@
       </c>
       <c r="S55" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T18:24:24Z</t>
+          <t>2026-10-02T23:55:31Z</t>
         </is>
       </c>
     </row>
@@ -4981,7 +4981,7 @@
       </c>
       <c r="S56" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T18:24:24Z</t>
+          <t>2026-10-02T23:55:31Z</t>
         </is>
       </c>
     </row>
@@ -5070,7 +5070,7 @@
       </c>
       <c r="S57" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T18:24:24Z</t>
+          <t>2026-10-02T23:55:31Z</t>
         </is>
       </c>
     </row>
@@ -5159,7 +5159,7 @@
       </c>
       <c r="S58" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T18:24:24Z</t>
+          <t>2026-10-02T23:55:31Z</t>
         </is>
       </c>
     </row>
@@ -5248,7 +5248,7 @@
       </c>
       <c r="S59" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T18:24:24Z</t>
+          <t>2026-10-02T23:55:31Z</t>
         </is>
       </c>
     </row>
@@ -5337,7 +5337,7 @@
       </c>
       <c r="S60" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T18:24:24Z</t>
+          <t>2026-10-02T23:55:31Z</t>
         </is>
       </c>
     </row>
@@ -5426,7 +5426,7 @@
       </c>
       <c r="S61" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T18:24:24Z</t>
+          <t>2026-10-02T23:55:31Z</t>
         </is>
       </c>
     </row>
@@ -5515,7 +5515,7 @@
       </c>
       <c r="S62" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T18:24:24Z</t>
+          <t>2026-10-02T23:55:31Z</t>
         </is>
       </c>
     </row>
@@ -5604,7 +5604,7 @@
       </c>
       <c r="S63" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T18:24:24Z</t>
+          <t>2026-10-02T23:55:31Z</t>
         </is>
       </c>
     </row>
@@ -5693,7 +5693,7 @@
       </c>
       <c r="S64" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T18:24:24Z</t>
+          <t>2026-10-02T23:55:31Z</t>
         </is>
       </c>
     </row>
@@ -5782,7 +5782,7 @@
       </c>
       <c r="S65" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T18:24:24Z</t>
+          <t>2026-10-02T23:55:31Z</t>
         </is>
       </c>
     </row>
@@ -5871,7 +5871,7 @@
       </c>
       <c r="S66" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T18:24:24Z</t>
+          <t>2026-10-02T23:55:31Z</t>
         </is>
       </c>
     </row>
@@ -5960,7 +5960,7 @@
       </c>
       <c r="S67" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T18:24:24Z</t>
+          <t>2026-10-02T23:55:31Z</t>
         </is>
       </c>
     </row>
@@ -6045,7 +6045,7 @@
       </c>
       <c r="S68" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T18:24:24Z</t>
+          <t>2026-10-02T23:55:31Z</t>
         </is>
       </c>
     </row>
@@ -6130,7 +6130,7 @@
       </c>
       <c r="S69" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T18:24:24Z</t>
+          <t>2026-10-02T23:55:31Z</t>
         </is>
       </c>
     </row>
@@ -6215,7 +6215,7 @@
       </c>
       <c r="S70" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T18:24:24Z</t>
+          <t>2026-10-02T23:55:31Z</t>
         </is>
       </c>
     </row>
@@ -6300,7 +6300,7 @@
       </c>
       <c r="S71" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T18:24:24Z</t>
+          <t>2026-10-02T23:55:31Z</t>
         </is>
       </c>
     </row>
@@ -6385,7 +6385,7 @@
       </c>
       <c r="S72" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T18:24:24Z</t>
+          <t>2026-10-02T23:55:31Z</t>
         </is>
       </c>
     </row>
@@ -6470,7 +6470,7 @@
       </c>
       <c r="S73" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T18:24:24Z</t>
+          <t>2026-10-02T23:55:31Z</t>
         </is>
       </c>
     </row>
@@ -6555,7 +6555,7 @@
       </c>
       <c r="S74" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T18:24:24Z</t>
+          <t>2026-10-02T23:55:31Z</t>
         </is>
       </c>
     </row>
@@ -6640,7 +6640,7 @@
       </c>
       <c r="S75" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T18:24:24Z</t>
+          <t>2026-10-02T23:55:31Z</t>
         </is>
       </c>
     </row>
@@ -6725,7 +6725,7 @@
       </c>
       <c r="S76" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T18:24:24Z</t>
+          <t>2026-10-02T23:55:31Z</t>
         </is>
       </c>
     </row>
@@ -6810,7 +6810,7 @@
       </c>
       <c r="S77" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T18:24:24Z</t>
+          <t>2026-10-02T23:55:31Z</t>
         </is>
       </c>
     </row>
@@ -6895,7 +6895,7 @@
       </c>
       <c r="S78" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T18:24:24Z</t>
+          <t>2026-10-02T23:55:31Z</t>
         </is>
       </c>
     </row>
@@ -6980,7 +6980,7 @@
       </c>
       <c r="S79" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T18:24:24Z</t>
+          <t>2026-10-02T23:55:31Z</t>
         </is>
       </c>
     </row>
@@ -7065,7 +7065,7 @@
       </c>
       <c r="S80" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T18:24:24Z</t>
+          <t>2026-10-02T23:55:31Z</t>
         </is>
       </c>
     </row>
@@ -7150,7 +7150,7 @@
       </c>
       <c r="S81" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T18:24:24Z</t>
+          <t>2026-10-02T23:55:31Z</t>
         </is>
       </c>
     </row>
@@ -7235,7 +7235,7 @@
       </c>
       <c r="S82" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T18:24:24Z</t>
+          <t>2026-10-02T23:55:31Z</t>
         </is>
       </c>
     </row>
@@ -7320,7 +7320,7 @@
       </c>
       <c r="S83" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T18:24:24Z</t>
+          <t>2026-10-02T23:55:31Z</t>
         </is>
       </c>
     </row>
@@ -7405,7 +7405,7 @@
       </c>
       <c r="S84" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T18:24:24Z</t>
+          <t>2026-10-02T23:55:31Z</t>
         </is>
       </c>
     </row>
@@ -7490,7 +7490,7 @@
       </c>
       <c r="S85" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T18:24:24Z</t>
+          <t>2026-10-02T23:55:31Z</t>
         </is>
       </c>
     </row>
@@ -7575,7 +7575,7 @@
       </c>
       <c r="S86" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T18:24:24Z</t>
+          <t>2026-10-02T23:55:31Z</t>
         </is>
       </c>
     </row>
@@ -7660,7 +7660,7 @@
       </c>
       <c r="S87" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T18:24:24Z</t>
+          <t>2026-10-02T23:55:31Z</t>
         </is>
       </c>
     </row>
@@ -7745,7 +7745,7 @@
       </c>
       <c r="S88" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T18:24:24Z</t>
+          <t>2026-10-02T23:55:31Z</t>
         </is>
       </c>
     </row>
@@ -7834,7 +7834,7 @@
       </c>
       <c r="S89" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T18:24:24Z</t>
+          <t>2026-10-02T23:55:31Z</t>
         </is>
       </c>
     </row>
@@ -7923,7 +7923,7 @@
       </c>
       <c r="S90" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T18:24:24Z</t>
+          <t>2026-10-02T23:55:31Z</t>
         </is>
       </c>
     </row>
@@ -8008,7 +8008,7 @@
       </c>
       <c r="S91" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T18:24:24Z</t>
+          <t>2026-10-02T23:55:31Z</t>
         </is>
       </c>
     </row>
@@ -8097,7 +8097,7 @@
       </c>
       <c r="S92" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T18:24:24Z</t>
+          <t>2026-10-02T23:55:31Z</t>
         </is>
       </c>
     </row>
@@ -8186,7 +8186,7 @@
       </c>
       <c r="S93" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T18:24:24Z</t>
+          <t>2026-10-02T23:55:31Z</t>
         </is>
       </c>
     </row>
@@ -8271,7 +8271,7 @@
       </c>
       <c r="S94" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T18:24:24Z</t>
+          <t>2026-10-02T23:55:31Z</t>
         </is>
       </c>
     </row>
@@ -8360,7 +8360,7 @@
       </c>
       <c r="S95" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T18:24:24Z</t>
+          <t>2026-10-02T23:55:31Z</t>
         </is>
       </c>
     </row>
@@ -8449,7 +8449,7 @@
       </c>
       <c r="S96" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T18:24:24Z</t>
+          <t>2026-10-02T23:55:31Z</t>
         </is>
       </c>
     </row>
@@ -8534,7 +8534,7 @@
       </c>
       <c r="S97" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T18:24:24Z</t>
+          <t>2026-10-02T23:55:31Z</t>
         </is>
       </c>
     </row>
@@ -8623,7 +8623,7 @@
       </c>
       <c r="S98" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T18:24:24Z</t>
+          <t>2026-10-02T23:55:31Z</t>
         </is>
       </c>
     </row>
@@ -8712,7 +8712,7 @@
       </c>
       <c r="S99" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T18:24:24Z</t>
+          <t>2026-10-02T23:55:31Z</t>
         </is>
       </c>
     </row>
@@ -8797,7 +8797,7 @@
       </c>
       <c r="S100" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T18:24:24Z</t>
+          <t>2026-10-02T23:55:31Z</t>
         </is>
       </c>
     </row>
@@ -8886,7 +8886,7 @@
       </c>
       <c r="S101" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T18:24:24Z</t>
+          <t>2026-10-02T23:55:31Z</t>
         </is>
       </c>
     </row>
@@ -8975,7 +8975,7 @@
       </c>
       <c r="S102" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T18:24:24Z</t>
+          <t>2026-10-02T23:55:31Z</t>
         </is>
       </c>
     </row>
@@ -9060,7 +9060,7 @@
       </c>
       <c r="S103" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T18:24:24Z</t>
+          <t>2026-10-02T23:55:31Z</t>
         </is>
       </c>
     </row>
@@ -9149,7 +9149,7 @@
       </c>
       <c r="S104" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T18:24:24Z</t>
+          <t>2026-10-02T23:55:31Z</t>
         </is>
       </c>
     </row>
@@ -9238,7 +9238,7 @@
       </c>
       <c r="S105" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T18:24:24Z</t>
+          <t>2026-10-02T23:55:31Z</t>
         </is>
       </c>
     </row>
@@ -9323,7 +9323,7 @@
       </c>
       <c r="S106" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T18:24:24Z</t>
+          <t>2026-10-02T23:55:31Z</t>
         </is>
       </c>
     </row>
@@ -9412,7 +9412,7 @@
       </c>
       <c r="S107" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T18:24:24Z</t>
+          <t>2026-10-02T23:55:31Z</t>
         </is>
       </c>
     </row>
@@ -9501,7 +9501,7 @@
       </c>
       <c r="S108" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T18:24:24Z</t>
+          <t>2026-10-02T23:55:31Z</t>
         </is>
       </c>
     </row>
@@ -9586,7 +9586,7 @@
       </c>
       <c r="S109" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T18:24:24Z</t>
+          <t>2026-10-02T23:55:31Z</t>
         </is>
       </c>
     </row>
@@ -9675,7 +9675,7 @@
       </c>
       <c r="S110" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T18:24:24Z</t>
+          <t>2026-10-02T23:55:31Z</t>
         </is>
       </c>
     </row>
@@ -9764,7 +9764,7 @@
       </c>
       <c r="S111" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T18:24:24Z</t>
+          <t>2026-10-02T23:55:31Z</t>
         </is>
       </c>
     </row>
@@ -9849,7 +9849,7 @@
       </c>
       <c r="S112" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T18:24:24Z</t>
+          <t>2026-10-02T23:55:31Z</t>
         </is>
       </c>
     </row>
@@ -9938,7 +9938,7 @@
       </c>
       <c r="S113" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T18:24:24Z</t>
+          <t>2026-10-02T23:55:31Z</t>
         </is>
       </c>
     </row>
@@ -10027,7 +10027,7 @@
       </c>
       <c r="S114" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T18:24:24Z</t>
+          <t>2026-10-02T23:55:31Z</t>
         </is>
       </c>
     </row>
@@ -10112,7 +10112,7 @@
       </c>
       <c r="S115" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T18:24:24Z</t>
+          <t>2026-10-02T23:55:31Z</t>
         </is>
       </c>
     </row>
@@ -10201,7 +10201,7 @@
       </c>
       <c r="S116" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T18:24:24Z</t>
+          <t>2026-10-02T23:55:31Z</t>
         </is>
       </c>
     </row>
@@ -10290,7 +10290,7 @@
       </c>
       <c r="S117" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T18:24:24Z</t>
+          <t>2026-10-02T23:55:31Z</t>
         </is>
       </c>
     </row>
@@ -10379,7 +10379,7 @@
       </c>
       <c r="S118" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T18:24:24Z</t>
+          <t>2026-10-02T23:55:31Z</t>
         </is>
       </c>
     </row>
@@ -10468,7 +10468,7 @@
       </c>
       <c r="S119" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T18:24:24Z</t>
+          <t>2026-10-02T23:55:31Z</t>
         </is>
       </c>
     </row>
@@ -10557,7 +10557,7 @@
       </c>
       <c r="S120" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T18:24:24Z</t>
+          <t>2026-10-02T23:55:31Z</t>
         </is>
       </c>
     </row>
@@ -10646,7 +10646,7 @@
       </c>
       <c r="S121" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T18:24:24Z</t>
+          <t>2026-10-02T23:55:31Z</t>
         </is>
       </c>
     </row>
@@ -10735,7 +10735,7 @@
       </c>
       <c r="S122" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T18:24:24Z</t>
+          <t>2026-10-02T23:55:31Z</t>
         </is>
       </c>
     </row>
@@ -10824,7 +10824,7 @@
       </c>
       <c r="S123" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T18:24:24Z</t>
+          <t>2026-10-02T23:55:31Z</t>
         </is>
       </c>
     </row>
@@ -10913,7 +10913,7 @@
       </c>
       <c r="S124" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T18:24:24Z</t>
+          <t>2026-10-02T23:55:31Z</t>
         </is>
       </c>
     </row>
@@ -11002,7 +11002,7 @@
       </c>
       <c r="S125" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T18:24:24Z</t>
+          <t>2026-10-02T23:55:31Z</t>
         </is>
       </c>
     </row>
@@ -11091,7 +11091,7 @@
       </c>
       <c r="S126" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T18:24:24Z</t>
+          <t>2026-10-02T23:55:31Z</t>
         </is>
       </c>
     </row>
@@ -11180,7 +11180,7 @@
       </c>
       <c r="S127" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T18:24:24Z</t>
+          <t>2026-10-02T23:55:31Z</t>
         </is>
       </c>
     </row>
@@ -11269,7 +11269,7 @@
       </c>
       <c r="S128" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T18:24:24Z</t>
+          <t>2026-10-02T23:55:31Z</t>
         </is>
       </c>
     </row>
@@ -11354,7 +11354,7 @@
       </c>
       <c r="S129" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T18:24:24Z</t>
+          <t>2026-10-02T23:55:31Z</t>
         </is>
       </c>
     </row>
@@ -11439,7 +11439,7 @@
       </c>
       <c r="S130" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T18:24:24Z</t>
+          <t>2026-10-02T23:55:31Z</t>
         </is>
       </c>
     </row>
@@ -11524,7 +11524,7 @@
       </c>
       <c r="S131" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T18:24:24Z</t>
+          <t>2026-10-02T23:55:31Z</t>
         </is>
       </c>
     </row>
@@ -11609,7 +11609,7 @@
       </c>
       <c r="S132" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T18:24:24Z</t>
+          <t>2026-10-02T23:55:31Z</t>
         </is>
       </c>
     </row>
@@ -11694,7 +11694,7 @@
       </c>
       <c r="S133" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T18:24:24Z</t>
+          <t>2026-10-02T23:55:31Z</t>
         </is>
       </c>
     </row>
@@ -11779,7 +11779,7 @@
       </c>
       <c r="S134" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T18:24:24Z</t>
+          <t>2026-10-02T23:55:31Z</t>
         </is>
       </c>
     </row>
@@ -11864,7 +11864,7 @@
       </c>
       <c r="S135" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T18:24:24Z</t>
+          <t>2026-10-02T23:55:31Z</t>
         </is>
       </c>
     </row>
@@ -11949,7 +11949,7 @@
       </c>
       <c r="S136" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T18:24:24Z</t>
+          <t>2026-10-02T23:55:31Z</t>
         </is>
       </c>
     </row>
@@ -12034,7 +12034,7 @@
       </c>
       <c r="S137" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T18:24:24Z</t>
+          <t>2026-10-02T23:55:31Z</t>
         </is>
       </c>
     </row>
@@ -12119,7 +12119,7 @@
       </c>
       <c r="S138" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T18:24:24Z</t>
+          <t>2026-10-02T23:55:31Z</t>
         </is>
       </c>
     </row>
@@ -12204,7 +12204,7 @@
       </c>
       <c r="S139" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T18:24:24Z</t>
+          <t>2026-10-02T23:55:31Z</t>
         </is>
       </c>
     </row>
@@ -12289,7 +12289,7 @@
       </c>
       <c r="S140" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T18:24:24Z</t>
+          <t>2026-10-02T23:55:31Z</t>
         </is>
       </c>
     </row>
@@ -12374,7 +12374,7 @@
       </c>
       <c r="S141" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T18:24:24Z</t>
+          <t>2026-10-02T23:55:31Z</t>
         </is>
       </c>
     </row>
@@ -12459,7 +12459,7 @@
       </c>
       <c r="S142" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T18:24:24Z</t>
+          <t>2026-10-02T23:55:31Z</t>
         </is>
       </c>
     </row>
@@ -12544,7 +12544,7 @@
       </c>
       <c r="S143" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T18:24:24Z</t>
+          <t>2026-10-02T23:55:31Z</t>
         </is>
       </c>
     </row>
@@ -12629,7 +12629,7 @@
       </c>
       <c r="S144" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T18:24:24Z</t>
+          <t>2026-10-02T23:55:31Z</t>
         </is>
       </c>
     </row>
@@ -12714,7 +12714,7 @@
       </c>
       <c r="S145" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T18:24:24Z</t>
+          <t>2026-10-02T23:55:31Z</t>
         </is>
       </c>
     </row>
@@ -12799,7 +12799,7 @@
       </c>
       <c r="S146" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T18:24:24Z</t>
+          <t>2026-10-02T23:55:31Z</t>
         </is>
       </c>
     </row>
@@ -12884,7 +12884,7 @@
       </c>
       <c r="S147" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T18:24:24Z</t>
+          <t>2026-10-02T23:55:31Z</t>
         </is>
       </c>
     </row>
@@ -12969,7 +12969,7 @@
       </c>
       <c r="S148" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T18:24:24Z</t>
+          <t>2026-10-02T23:55:31Z</t>
         </is>
       </c>
     </row>
@@ -13054,7 +13054,7 @@
       </c>
       <c r="S149" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T18:24:24Z</t>
+          <t>2026-10-02T23:55:31Z</t>
         </is>
       </c>
     </row>
@@ -13143,7 +13143,7 @@
       </c>
       <c r="S150" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T18:24:24Z</t>
+          <t>2026-10-02T23:55:31Z</t>
         </is>
       </c>
     </row>
@@ -13232,7 +13232,7 @@
       </c>
       <c r="S151" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T18:24:24Z</t>
+          <t>2026-10-02T23:55:31Z</t>
         </is>
       </c>
     </row>
@@ -13317,7 +13317,7 @@
       </c>
       <c r="S152" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T18:24:24Z</t>
+          <t>2026-10-02T23:55:31Z</t>
         </is>
       </c>
     </row>
@@ -13406,7 +13406,7 @@
       </c>
       <c r="S153" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T18:24:24Z</t>
+          <t>2026-10-02T23:55:31Z</t>
         </is>
       </c>
     </row>
@@ -13495,7 +13495,7 @@
       </c>
       <c r="S154" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T18:24:24Z</t>
+          <t>2026-10-02T23:55:31Z</t>
         </is>
       </c>
     </row>
@@ -13580,7 +13580,7 @@
       </c>
       <c r="S155" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T18:24:24Z</t>
+          <t>2026-10-02T23:55:31Z</t>
         </is>
       </c>
     </row>
@@ -13669,7 +13669,7 @@
       </c>
       <c r="S156" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T18:24:24Z</t>
+          <t>2026-10-02T23:55:31Z</t>
         </is>
       </c>
     </row>
@@ -13758,7 +13758,7 @@
       </c>
       <c r="S157" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T18:24:24Z</t>
+          <t>2026-10-02T23:55:31Z</t>
         </is>
       </c>
     </row>
@@ -13843,7 +13843,7 @@
       </c>
       <c r="S158" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T18:24:24Z</t>
+          <t>2026-10-02T23:55:31Z</t>
         </is>
       </c>
     </row>
@@ -13932,7 +13932,7 @@
       </c>
       <c r="S159" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T18:24:24Z</t>
+          <t>2026-10-02T23:55:31Z</t>
         </is>
       </c>
     </row>
@@ -14021,7 +14021,7 @@
       </c>
       <c r="S160" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T18:24:24Z</t>
+          <t>2026-10-02T23:55:31Z</t>
         </is>
       </c>
     </row>
@@ -14106,7 +14106,7 @@
       </c>
       <c r="S161" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T18:24:24Z</t>
+          <t>2026-10-02T23:55:31Z</t>
         </is>
       </c>
     </row>
@@ -14195,7 +14195,7 @@
       </c>
       <c r="S162" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T18:24:24Z</t>
+          <t>2026-10-02T23:55:31Z</t>
         </is>
       </c>
     </row>
@@ -14284,7 +14284,7 @@
       </c>
       <c r="S163" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T18:24:24Z</t>
+          <t>2026-10-02T23:55:31Z</t>
         </is>
       </c>
     </row>
@@ -14369,7 +14369,7 @@
       </c>
       <c r="S164" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T18:24:24Z</t>
+          <t>2026-10-02T23:55:31Z</t>
         </is>
       </c>
     </row>
@@ -14458,7 +14458,7 @@
       </c>
       <c r="S165" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T18:24:24Z</t>
+          <t>2026-10-02T23:55:31Z</t>
         </is>
       </c>
     </row>
@@ -14547,7 +14547,7 @@
       </c>
       <c r="S166" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T18:24:24Z</t>
+          <t>2026-10-02T23:55:31Z</t>
         </is>
       </c>
     </row>
@@ -14632,7 +14632,7 @@
       </c>
       <c r="S167" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T18:24:24Z</t>
+          <t>2026-10-02T23:55:31Z</t>
         </is>
       </c>
     </row>
@@ -14721,7 +14721,7 @@
       </c>
       <c r="S168" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T18:24:24Z</t>
+          <t>2026-10-02T23:55:31Z</t>
         </is>
       </c>
     </row>
@@ -14810,7 +14810,7 @@
       </c>
       <c r="S169" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T18:24:24Z</t>
+          <t>2026-10-02T23:55:31Z</t>
         </is>
       </c>
     </row>
@@ -14895,7 +14895,7 @@
       </c>
       <c r="S170" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T18:24:24Z</t>
+          <t>2026-10-02T23:55:31Z</t>
         </is>
       </c>
     </row>
@@ -14984,7 +14984,7 @@
       </c>
       <c r="S171" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T18:24:24Z</t>
+          <t>2026-10-02T23:55:31Z</t>
         </is>
       </c>
     </row>
@@ -15073,7 +15073,7 @@
       </c>
       <c r="S172" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T18:24:24Z</t>
+          <t>2026-10-02T23:55:31Z</t>
         </is>
       </c>
     </row>
@@ -15158,7 +15158,7 @@
       </c>
       <c r="S173" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T18:24:24Z</t>
+          <t>2026-10-02T23:55:31Z</t>
         </is>
       </c>
     </row>
@@ -15247,7 +15247,7 @@
       </c>
       <c r="S174" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T18:24:24Z</t>
+          <t>2026-10-02T23:55:31Z</t>
         </is>
       </c>
     </row>
@@ -15336,7 +15336,7 @@
       </c>
       <c r="S175" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T18:24:24Z</t>
+          <t>2026-10-02T23:55:31Z</t>
         </is>
       </c>
     </row>
@@ -15421,7 +15421,7 @@
       </c>
       <c r="S176" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T18:24:24Z</t>
+          <t>2026-10-02T23:55:31Z</t>
         </is>
       </c>
     </row>
@@ -15510,7 +15510,7 @@
       </c>
       <c r="S177" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T18:24:24Z</t>
+          <t>2026-10-02T23:55:31Z</t>
         </is>
       </c>
     </row>
@@ -15599,7 +15599,7 @@
       </c>
       <c r="S178" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T18:24:24Z</t>
+          <t>2026-10-02T23:55:31Z</t>
         </is>
       </c>
     </row>
@@ -15688,7 +15688,7 @@
       </c>
       <c r="S179" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T18:24:24Z</t>
+          <t>2026-10-02T23:55:31Z</t>
         </is>
       </c>
     </row>
@@ -15777,7 +15777,7 @@
       </c>
       <c r="S180" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T18:24:24Z</t>
+          <t>2026-10-02T23:55:31Z</t>
         </is>
       </c>
     </row>
@@ -15866,7 +15866,7 @@
       </c>
       <c r="S181" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T18:24:24Z</t>
+          <t>2026-10-02T23:55:31Z</t>
         </is>
       </c>
     </row>
@@ -15955,7 +15955,7 @@
       </c>
       <c r="S182" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T18:24:24Z</t>
+          <t>2026-10-02T23:55:31Z</t>
         </is>
       </c>
     </row>
@@ -16044,7 +16044,7 @@
       </c>
       <c r="S183" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T18:24:24Z</t>
+          <t>2026-10-02T23:55:31Z</t>
         </is>
       </c>
     </row>
@@ -16133,7 +16133,7 @@
       </c>
       <c r="S184" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T18:24:24Z</t>
+          <t>2026-10-02T23:55:31Z</t>
         </is>
       </c>
     </row>
@@ -16222,7 +16222,7 @@
       </c>
       <c r="S185" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T18:24:24Z</t>
+          <t>2026-10-02T23:55:31Z</t>
         </is>
       </c>
     </row>
@@ -16311,7 +16311,7 @@
       </c>
       <c r="S186" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T18:24:24Z</t>
+          <t>2026-10-02T23:55:31Z</t>
         </is>
       </c>
     </row>
@@ -16400,7 +16400,7 @@
       </c>
       <c r="S187" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T18:24:24Z</t>
+          <t>2026-10-02T23:55:31Z</t>
         </is>
       </c>
     </row>
@@ -16489,7 +16489,7 @@
       </c>
       <c r="S188" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T18:24:24Z</t>
+          <t>2026-10-02T23:55:31Z</t>
         </is>
       </c>
     </row>
@@ -16578,7 +16578,7 @@
       </c>
       <c r="S189" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T18:24:24Z</t>
+          <t>2026-10-02T23:55:31Z</t>
         </is>
       </c>
     </row>
@@ -16663,7 +16663,7 @@
       </c>
       <c r="S190" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T18:24:24Z</t>
+          <t>2026-10-02T23:55:31Z</t>
         </is>
       </c>
     </row>
@@ -16748,7 +16748,7 @@
       </c>
       <c r="S191" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T18:24:24Z</t>
+          <t>2026-10-02T23:55:31Z</t>
         </is>
       </c>
     </row>
@@ -16833,7 +16833,7 @@
       </c>
       <c r="S192" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T18:24:24Z</t>
+          <t>2026-10-02T23:55:31Z</t>
         </is>
       </c>
     </row>
@@ -16918,7 +16918,7 @@
       </c>
       <c r="S193" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T18:24:24Z</t>
+          <t>2026-10-02T23:55:31Z</t>
         </is>
       </c>
     </row>
@@ -17003,7 +17003,7 @@
       </c>
       <c r="S194" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T18:24:24Z</t>
+          <t>2026-10-02T23:55:31Z</t>
         </is>
       </c>
     </row>
@@ -17088,7 +17088,7 @@
       </c>
       <c r="S195" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T18:24:24Z</t>
+          <t>2026-10-02T23:55:31Z</t>
         </is>
       </c>
     </row>
@@ -17173,7 +17173,7 @@
       </c>
       <c r="S196" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T18:24:24Z</t>
+          <t>2026-10-02T23:55:31Z</t>
         </is>
       </c>
     </row>
@@ -17258,7 +17258,7 @@
       </c>
       <c r="S197" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T18:24:24Z</t>
+          <t>2026-10-02T23:55:31Z</t>
         </is>
       </c>
     </row>
@@ -17343,7 +17343,7 @@
       </c>
       <c r="S198" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T18:24:24Z</t>
+          <t>2026-10-02T23:55:31Z</t>
         </is>
       </c>
     </row>
@@ -17428,7 +17428,7 @@
       </c>
       <c r="S199" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T18:24:24Z</t>
+          <t>2026-10-02T23:55:31Z</t>
         </is>
       </c>
     </row>
@@ -17513,7 +17513,7 @@
       </c>
       <c r="S200" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T18:24:24Z</t>
+          <t>2026-10-02T23:55:31Z</t>
         </is>
       </c>
     </row>
@@ -17598,7 +17598,7 @@
       </c>
       <c r="S201" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T18:24:24Z</t>
+          <t>2026-10-02T23:55:31Z</t>
         </is>
       </c>
     </row>
@@ -17683,7 +17683,7 @@
       </c>
       <c r="S202" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T18:24:24Z</t>
+          <t>2026-10-02T23:55:31Z</t>
         </is>
       </c>
     </row>
@@ -17768,7 +17768,7 @@
       </c>
       <c r="S203" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T18:24:24Z</t>
+          <t>2026-10-02T23:55:31Z</t>
         </is>
       </c>
     </row>
@@ -17853,7 +17853,7 @@
       </c>
       <c r="S204" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T18:24:24Z</t>
+          <t>2026-10-02T23:55:31Z</t>
         </is>
       </c>
     </row>
@@ -17938,7 +17938,7 @@
       </c>
       <c r="S205" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T18:24:24Z</t>
+          <t>2026-10-02T23:55:31Z</t>
         </is>
       </c>
     </row>
@@ -18023,7 +18023,7 @@
       </c>
       <c r="S206" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T18:24:24Z</t>
+          <t>2026-10-02T23:55:31Z</t>
         </is>
       </c>
     </row>
@@ -18108,7 +18108,7 @@
       </c>
       <c r="S207" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T18:24:24Z</t>
+          <t>2026-10-02T23:55:31Z</t>
         </is>
       </c>
     </row>
@@ -18193,7 +18193,7 @@
       </c>
       <c r="S208" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T18:24:24Z</t>
+          <t>2026-10-02T23:55:31Z</t>
         </is>
       </c>
     </row>
@@ -18278,7 +18278,7 @@
       </c>
       <c r="S209" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T18:24:24Z</t>
+          <t>2026-10-02T23:55:31Z</t>
         </is>
       </c>
     </row>
@@ -18363,7 +18363,7 @@
       </c>
       <c r="S210" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T18:24:24Z</t>
+          <t>2026-10-02T23:55:31Z</t>
         </is>
       </c>
     </row>
@@ -18452,7 +18452,7 @@
       </c>
       <c r="S211" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T18:24:24Z</t>
+          <t>2026-10-02T23:55:31Z</t>
         </is>
       </c>
     </row>
@@ -18541,7 +18541,7 @@
       </c>
       <c r="S212" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T18:24:24Z</t>
+          <t>2026-10-02T23:55:31Z</t>
         </is>
       </c>
     </row>
@@ -18626,7 +18626,7 @@
       </c>
       <c r="S213" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T18:24:24Z</t>
+          <t>2026-10-02T23:55:31Z</t>
         </is>
       </c>
     </row>
@@ -18715,7 +18715,7 @@
       </c>
       <c r="S214" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T18:24:24Z</t>
+          <t>2026-10-02T23:55:31Z</t>
         </is>
       </c>
     </row>
@@ -18804,7 +18804,7 @@
       </c>
       <c r="S215" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T18:24:24Z</t>
+          <t>2026-10-02T23:55:31Z</t>
         </is>
       </c>
     </row>
@@ -18889,7 +18889,7 @@
       </c>
       <c r="S216" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T18:24:24Z</t>
+          <t>2026-10-02T23:55:31Z</t>
         </is>
       </c>
     </row>
@@ -18978,7 +18978,7 @@
       </c>
       <c r="S217" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T18:24:24Z</t>
+          <t>2026-10-02T23:55:31Z</t>
         </is>
       </c>
     </row>
@@ -19067,7 +19067,7 @@
       </c>
       <c r="S218" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T18:24:24Z</t>
+          <t>2026-10-02T23:55:31Z</t>
         </is>
       </c>
     </row>
@@ -19152,7 +19152,7 @@
       </c>
       <c r="S219" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T18:24:24Z</t>
+          <t>2026-10-02T23:55:31Z</t>
         </is>
       </c>
     </row>
@@ -19241,7 +19241,7 @@
       </c>
       <c r="S220" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T18:24:24Z</t>
+          <t>2026-10-02T23:55:31Z</t>
         </is>
       </c>
     </row>
@@ -19330,7 +19330,7 @@
       </c>
       <c r="S221" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T18:24:24Z</t>
+          <t>2026-10-02T23:55:31Z</t>
         </is>
       </c>
     </row>
@@ -19415,7 +19415,7 @@
       </c>
       <c r="S222" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T18:24:24Z</t>
+          <t>2026-10-02T23:55:31Z</t>
         </is>
       </c>
     </row>
@@ -19504,7 +19504,7 @@
       </c>
       <c r="S223" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T18:24:24Z</t>
+          <t>2026-10-02T23:55:31Z</t>
         </is>
       </c>
     </row>
@@ -19593,7 +19593,7 @@
       </c>
       <c r="S224" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T18:24:24Z</t>
+          <t>2026-10-02T23:55:31Z</t>
         </is>
       </c>
     </row>
@@ -19678,7 +19678,7 @@
       </c>
       <c r="S225" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T18:24:24Z</t>
+          <t>2026-10-02T23:55:31Z</t>
         </is>
       </c>
     </row>
@@ -19767,7 +19767,7 @@
       </c>
       <c r="S226" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T18:24:24Z</t>
+          <t>2026-10-02T23:55:31Z</t>
         </is>
       </c>
     </row>
@@ -19856,7 +19856,7 @@
       </c>
       <c r="S227" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T18:24:24Z</t>
+          <t>2026-10-02T23:55:31Z</t>
         </is>
       </c>
     </row>
@@ -19941,7 +19941,7 @@
       </c>
       <c r="S228" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T18:24:24Z</t>
+          <t>2026-10-02T23:55:31Z</t>
         </is>
       </c>
     </row>
@@ -20030,7 +20030,7 @@
       </c>
       <c r="S229" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T18:24:24Z</t>
+          <t>2026-10-02T23:55:31Z</t>
         </is>
       </c>
     </row>
@@ -20119,7 +20119,7 @@
       </c>
       <c r="S230" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T18:24:24Z</t>
+          <t>2026-10-02T23:55:31Z</t>
         </is>
       </c>
     </row>
@@ -20204,7 +20204,7 @@
       </c>
       <c r="S231" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T18:24:24Z</t>
+          <t>2026-10-02T23:55:31Z</t>
         </is>
       </c>
     </row>
@@ -20293,7 +20293,7 @@
       </c>
       <c r="S232" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T18:24:24Z</t>
+          <t>2026-10-02T23:55:31Z</t>
         </is>
       </c>
     </row>
@@ -20382,7 +20382,7 @@
       </c>
       <c r="S233" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T18:24:24Z</t>
+          <t>2026-10-02T23:55:31Z</t>
         </is>
       </c>
     </row>
@@ -20467,7 +20467,7 @@
       </c>
       <c r="S234" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T18:24:24Z</t>
+          <t>2026-10-02T23:55:31Z</t>
         </is>
       </c>
     </row>
@@ -20556,7 +20556,7 @@
       </c>
       <c r="S235" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T18:24:24Z</t>
+          <t>2026-10-02T23:55:31Z</t>
         </is>
       </c>
     </row>
@@ -20645,7 +20645,7 @@
       </c>
       <c r="S236" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T18:24:24Z</t>
+          <t>2026-10-02T23:55:31Z</t>
         </is>
       </c>
     </row>
@@ -20730,7 +20730,7 @@
       </c>
       <c r="S237" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T18:24:24Z</t>
+          <t>2026-10-02T23:55:31Z</t>
         </is>
       </c>
     </row>
@@ -20819,7 +20819,7 @@
       </c>
       <c r="S238" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T18:24:24Z</t>
+          <t>2026-10-02T23:55:31Z</t>
         </is>
       </c>
     </row>
@@ -20908,7 +20908,7 @@
       </c>
       <c r="S239" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T18:24:24Z</t>
+          <t>2026-10-02T23:55:31Z</t>
         </is>
       </c>
     </row>
@@ -20997,7 +20997,7 @@
       </c>
       <c r="S240" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T18:24:24Z</t>
+          <t>2026-10-02T23:55:31Z</t>
         </is>
       </c>
     </row>
@@ -21086,7 +21086,7 @@
       </c>
       <c r="S241" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T18:24:24Z</t>
+          <t>2026-10-02T23:55:31Z</t>
         </is>
       </c>
     </row>
@@ -21175,7 +21175,7 @@
       </c>
       <c r="S242" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T18:24:24Z</t>
+          <t>2026-10-02T23:55:31Z</t>
         </is>
       </c>
     </row>
@@ -21264,7 +21264,7 @@
       </c>
       <c r="S243" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T18:24:24Z</t>
+          <t>2026-10-02T23:55:31Z</t>
         </is>
       </c>
     </row>
@@ -21353,7 +21353,7 @@
       </c>
       <c r="S244" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T18:24:24Z</t>
+          <t>2026-10-02T23:55:31Z</t>
         </is>
       </c>
     </row>
@@ -21442,7 +21442,7 @@
       </c>
       <c r="S245" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T18:24:24Z</t>
+          <t>2026-10-02T23:55:31Z</t>
         </is>
       </c>
     </row>
@@ -21531,7 +21531,7 @@
       </c>
       <c r="S246" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T18:24:24Z</t>
+          <t>2026-10-02T23:55:31Z</t>
         </is>
       </c>
     </row>
@@ -21620,7 +21620,7 @@
       </c>
       <c r="S247" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T18:24:24Z</t>
+          <t>2026-10-02T23:55:31Z</t>
         </is>
       </c>
     </row>
@@ -21709,7 +21709,7 @@
       </c>
       <c r="S248" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T18:24:24Z</t>
+          <t>2026-10-02T23:55:31Z</t>
         </is>
       </c>
     </row>
@@ -21798,7 +21798,7 @@
       </c>
       <c r="S249" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T18:24:24Z</t>
+          <t>2026-10-02T23:55:31Z</t>
         </is>
       </c>
     </row>
@@ -21887,7 +21887,7 @@
       </c>
       <c r="S250" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T18:24:24Z</t>
+          <t>2026-10-02T23:55:31Z</t>
         </is>
       </c>
     </row>
@@ -22019,7 +22019,7 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T18:24:24Z</t>
+          <t>2026-10-02T23:55:31Z</t>
         </is>
       </c>
     </row>
@@ -22099,7 +22099,7 @@
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>{"dataset_id": "bcv_pib_sector_institucional_anual", "title": "Producto interno bruto por sector institucional anual", "table": "Variaciones porcentuales", "source_file": "5_2_1_si_anual.xlsx", "base": "2007", "price_type": "Precios constantes", "measure": "Variación porcentual interanual", "frequency": "Anual", "period": "2025", "year": 2025, "quarter": null, "classification": "Sector institucional", "component": "Impuestos netos sobre los productos", "value": 10.600260421283764, "unit": "Porcentaje", "status": "Preliminar", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/cuentas_macroeconomicas/5_2_1_si_anual.xlsx", "fetched_at": "2026-10-02T18:24:24Z"}</t>
+          <t>{"dataset_id": "bcv_pib_sector_institucional_anual", "title": "Producto interno bruto por sector institucional anual", "table": "Variaciones porcentuales", "source_file": "5_2_1_si_anual.xlsx", "base": "2007", "price_type": "Precios constantes", "measure": "Variación porcentual interanual", "frequency": "Anual", "period": "2025", "year": 2025, "quarter": null, "classification": "Sector institucional", "component": "Impuestos netos sobre los productos", "value": 10.600260421283764, "unit": "Porcentaje", "status": "Preliminar", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/cuentas_macroeconomicas/5_2_1_si_anual.xlsx", "fetched_at": "2026-10-02T23:55:31Z"}</t>
         </is>
       </c>
     </row>

--- a/assets/data/bcv/excel/ove_bcv_pib_sector_institucional_anual.xlsx
+++ b/assets/data/bcv/excel/ove_bcv_pib_sector_institucional_anual.xlsx
@@ -736,7 +736,7 @@
       </c>
       <c r="S7" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T23:55:31Z</t>
+          <t>2026-10-03T23:14:13Z</t>
         </is>
       </c>
     </row>
@@ -821,7 +821,7 @@
       </c>
       <c r="S8" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T23:55:31Z</t>
+          <t>2026-10-03T23:14:13Z</t>
         </is>
       </c>
     </row>
@@ -906,7 +906,7 @@
       </c>
       <c r="S9" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T23:55:31Z</t>
+          <t>2026-10-03T23:14:13Z</t>
         </is>
       </c>
     </row>
@@ -991,7 +991,7 @@
       </c>
       <c r="S10" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T23:55:31Z</t>
+          <t>2026-10-03T23:14:13Z</t>
         </is>
       </c>
     </row>
@@ -1076,7 +1076,7 @@
       </c>
       <c r="S11" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T23:55:31Z</t>
+          <t>2026-10-03T23:14:13Z</t>
         </is>
       </c>
     </row>
@@ -1161,7 +1161,7 @@
       </c>
       <c r="S12" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T23:55:31Z</t>
+          <t>2026-10-03T23:14:13Z</t>
         </is>
       </c>
     </row>
@@ -1246,7 +1246,7 @@
       </c>
       <c r="S13" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T23:55:31Z</t>
+          <t>2026-10-03T23:14:13Z</t>
         </is>
       </c>
     </row>
@@ -1331,7 +1331,7 @@
       </c>
       <c r="S14" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T23:55:31Z</t>
+          <t>2026-10-03T23:14:13Z</t>
         </is>
       </c>
     </row>
@@ -1416,7 +1416,7 @@
       </c>
       <c r="S15" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T23:55:31Z</t>
+          <t>2026-10-03T23:14:13Z</t>
         </is>
       </c>
     </row>
@@ -1501,7 +1501,7 @@
       </c>
       <c r="S16" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T23:55:31Z</t>
+          <t>2026-10-03T23:14:13Z</t>
         </is>
       </c>
     </row>
@@ -1586,7 +1586,7 @@
       </c>
       <c r="S17" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T23:55:31Z</t>
+          <t>2026-10-03T23:14:13Z</t>
         </is>
       </c>
     </row>
@@ -1671,7 +1671,7 @@
       </c>
       <c r="S18" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T23:55:31Z</t>
+          <t>2026-10-03T23:14:13Z</t>
         </is>
       </c>
     </row>
@@ -1756,7 +1756,7 @@
       </c>
       <c r="S19" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T23:55:31Z</t>
+          <t>2026-10-03T23:14:13Z</t>
         </is>
       </c>
     </row>
@@ -1841,7 +1841,7 @@
       </c>
       <c r="S20" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T23:55:31Z</t>
+          <t>2026-10-03T23:14:13Z</t>
         </is>
       </c>
     </row>
@@ -1926,7 +1926,7 @@
       </c>
       <c r="S21" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T23:55:31Z</t>
+          <t>2026-10-03T23:14:13Z</t>
         </is>
       </c>
     </row>
@@ -2011,7 +2011,7 @@
       </c>
       <c r="S22" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T23:55:31Z</t>
+          <t>2026-10-03T23:14:13Z</t>
         </is>
       </c>
     </row>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="S23" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T23:55:31Z</t>
+          <t>2026-10-03T23:14:13Z</t>
         </is>
       </c>
     </row>
@@ -2181,7 +2181,7 @@
       </c>
       <c r="S24" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T23:55:31Z</t>
+          <t>2026-10-03T23:14:13Z</t>
         </is>
       </c>
     </row>
@@ -2266,7 +2266,7 @@
       </c>
       <c r="S25" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T23:55:31Z</t>
+          <t>2026-10-03T23:14:13Z</t>
         </is>
       </c>
     </row>
@@ -2351,7 +2351,7 @@
       </c>
       <c r="S26" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T23:55:31Z</t>
+          <t>2026-10-03T23:14:13Z</t>
         </is>
       </c>
     </row>
@@ -2436,7 +2436,7 @@
       </c>
       <c r="S27" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T23:55:31Z</t>
+          <t>2026-10-03T23:14:13Z</t>
         </is>
       </c>
     </row>
@@ -2525,7 +2525,7 @@
       </c>
       <c r="S28" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T23:55:31Z</t>
+          <t>2026-10-03T23:14:13Z</t>
         </is>
       </c>
     </row>
@@ -2614,7 +2614,7 @@
       </c>
       <c r="S29" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T23:55:31Z</t>
+          <t>2026-10-03T23:14:13Z</t>
         </is>
       </c>
     </row>
@@ -2699,7 +2699,7 @@
       </c>
       <c r="S30" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T23:55:31Z</t>
+          <t>2026-10-03T23:14:13Z</t>
         </is>
       </c>
     </row>
@@ -2788,7 +2788,7 @@
       </c>
       <c r="S31" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T23:55:31Z</t>
+          <t>2026-10-03T23:14:13Z</t>
         </is>
       </c>
     </row>
@@ -2877,7 +2877,7 @@
       </c>
       <c r="S32" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T23:55:31Z</t>
+          <t>2026-10-03T23:14:13Z</t>
         </is>
       </c>
     </row>
@@ -2962,7 +2962,7 @@
       </c>
       <c r="S33" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T23:55:31Z</t>
+          <t>2026-10-03T23:14:13Z</t>
         </is>
       </c>
     </row>
@@ -3051,7 +3051,7 @@
       </c>
       <c r="S34" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T23:55:31Z</t>
+          <t>2026-10-03T23:14:13Z</t>
         </is>
       </c>
     </row>
@@ -3140,7 +3140,7 @@
       </c>
       <c r="S35" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T23:55:31Z</t>
+          <t>2026-10-03T23:14:13Z</t>
         </is>
       </c>
     </row>
@@ -3225,7 +3225,7 @@
       </c>
       <c r="S36" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T23:55:31Z</t>
+          <t>2026-10-03T23:14:13Z</t>
         </is>
       </c>
     </row>
@@ -3314,7 +3314,7 @@
       </c>
       <c r="S37" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T23:55:31Z</t>
+          <t>2026-10-03T23:14:13Z</t>
         </is>
       </c>
     </row>
@@ -3403,7 +3403,7 @@
       </c>
       <c r="S38" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T23:55:31Z</t>
+          <t>2026-10-03T23:14:13Z</t>
         </is>
       </c>
     </row>
@@ -3488,7 +3488,7 @@
       </c>
       <c r="S39" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T23:55:31Z</t>
+          <t>2026-10-03T23:14:13Z</t>
         </is>
       </c>
     </row>
@@ -3577,7 +3577,7 @@
       </c>
       <c r="S40" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T23:55:31Z</t>
+          <t>2026-10-03T23:14:13Z</t>
         </is>
       </c>
     </row>
@@ -3666,7 +3666,7 @@
       </c>
       <c r="S41" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T23:55:31Z</t>
+          <t>2026-10-03T23:14:13Z</t>
         </is>
       </c>
     </row>
@@ -3751,7 +3751,7 @@
       </c>
       <c r="S42" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T23:55:31Z</t>
+          <t>2026-10-03T23:14:13Z</t>
         </is>
       </c>
     </row>
@@ -3840,7 +3840,7 @@
       </c>
       <c r="S43" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T23:55:31Z</t>
+          <t>2026-10-03T23:14:13Z</t>
         </is>
       </c>
     </row>
@@ -3929,7 +3929,7 @@
       </c>
       <c r="S44" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T23:55:31Z</t>
+          <t>2026-10-03T23:14:13Z</t>
         </is>
       </c>
     </row>
@@ -4014,7 +4014,7 @@
       </c>
       <c r="S45" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T23:55:31Z</t>
+          <t>2026-10-03T23:14:13Z</t>
         </is>
       </c>
     </row>
@@ -4103,7 +4103,7 @@
       </c>
       <c r="S46" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T23:55:31Z</t>
+          <t>2026-10-03T23:14:13Z</t>
         </is>
       </c>
     </row>
@@ -4192,7 +4192,7 @@
       </c>
       <c r="S47" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T23:55:31Z</t>
+          <t>2026-10-03T23:14:13Z</t>
         </is>
       </c>
     </row>
@@ -4277,7 +4277,7 @@
       </c>
       <c r="S48" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T23:55:31Z</t>
+          <t>2026-10-03T23:14:13Z</t>
         </is>
       </c>
     </row>
@@ -4366,7 +4366,7 @@
       </c>
       <c r="S49" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T23:55:31Z</t>
+          <t>2026-10-03T23:14:13Z</t>
         </is>
       </c>
     </row>
@@ -4455,7 +4455,7 @@
       </c>
       <c r="S50" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T23:55:31Z</t>
+          <t>2026-10-03T23:14:13Z</t>
         </is>
       </c>
     </row>
@@ -4540,7 +4540,7 @@
       </c>
       <c r="S51" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T23:55:31Z</t>
+          <t>2026-10-03T23:14:13Z</t>
         </is>
       </c>
     </row>
@@ -4629,7 +4629,7 @@
       </c>
       <c r="S52" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T23:55:31Z</t>
+          <t>2026-10-03T23:14:13Z</t>
         </is>
       </c>
     </row>
@@ -4718,7 +4718,7 @@
       </c>
       <c r="S53" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T23:55:31Z</t>
+          <t>2026-10-03T23:14:13Z</t>
         </is>
       </c>
     </row>
@@ -4803,7 +4803,7 @@
       </c>
       <c r="S54" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T23:55:31Z</t>
+          <t>2026-10-03T23:14:13Z</t>
         </is>
       </c>
     </row>
@@ -4892,7 +4892,7 @@
       </c>
       <c r="S55" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T23:55:31Z</t>
+          <t>2026-10-03T23:14:13Z</t>
         </is>
       </c>
     </row>
@@ -4981,7 +4981,7 @@
       </c>
       <c r="S56" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T23:55:31Z</t>
+          <t>2026-10-03T23:14:13Z</t>
         </is>
       </c>
     </row>
@@ -5070,7 +5070,7 @@
       </c>
       <c r="S57" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T23:55:31Z</t>
+          <t>2026-10-03T23:14:13Z</t>
         </is>
       </c>
     </row>
@@ -5159,7 +5159,7 @@
       </c>
       <c r="S58" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T23:55:31Z</t>
+          <t>2026-10-03T23:14:13Z</t>
         </is>
       </c>
     </row>
@@ -5248,7 +5248,7 @@
       </c>
       <c r="S59" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T23:55:31Z</t>
+          <t>2026-10-03T23:14:13Z</t>
         </is>
       </c>
     </row>
@@ -5337,7 +5337,7 @@
       </c>
       <c r="S60" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T23:55:31Z</t>
+          <t>2026-10-03T23:14:13Z</t>
         </is>
       </c>
     </row>
@@ -5426,7 +5426,7 @@
       </c>
       <c r="S61" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T23:55:31Z</t>
+          <t>2026-10-03T23:14:13Z</t>
         </is>
       </c>
     </row>
@@ -5515,7 +5515,7 @@
       </c>
       <c r="S62" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T23:55:31Z</t>
+          <t>2026-10-03T23:14:13Z</t>
         </is>
       </c>
     </row>
@@ -5604,7 +5604,7 @@
       </c>
       <c r="S63" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T23:55:31Z</t>
+          <t>2026-10-03T23:14:13Z</t>
         </is>
       </c>
     </row>
@@ -5693,7 +5693,7 @@
       </c>
       <c r="S64" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T23:55:31Z</t>
+          <t>2026-10-03T23:14:13Z</t>
         </is>
       </c>
     </row>
@@ -5782,7 +5782,7 @@
       </c>
       <c r="S65" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T23:55:31Z</t>
+          <t>2026-10-03T23:14:13Z</t>
         </is>
       </c>
     </row>
@@ -5871,7 +5871,7 @@
       </c>
       <c r="S66" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T23:55:31Z</t>
+          <t>2026-10-03T23:14:13Z</t>
         </is>
       </c>
     </row>
@@ -5960,7 +5960,7 @@
       </c>
       <c r="S67" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T23:55:31Z</t>
+          <t>2026-10-03T23:14:13Z</t>
         </is>
       </c>
     </row>
@@ -6045,7 +6045,7 @@
       </c>
       <c r="S68" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T23:55:31Z</t>
+          <t>2026-10-03T23:14:13Z</t>
         </is>
       </c>
     </row>
@@ -6130,7 +6130,7 @@
       </c>
       <c r="S69" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T23:55:31Z</t>
+          <t>2026-10-03T23:14:13Z</t>
         </is>
       </c>
     </row>
@@ -6215,7 +6215,7 @@
       </c>
       <c r="S70" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T23:55:31Z</t>
+          <t>2026-10-03T23:14:13Z</t>
         </is>
       </c>
     </row>
@@ -6300,7 +6300,7 @@
       </c>
       <c r="S71" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T23:55:31Z</t>
+          <t>2026-10-03T23:14:13Z</t>
         </is>
       </c>
     </row>
@@ -6385,7 +6385,7 @@
       </c>
       <c r="S72" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T23:55:31Z</t>
+          <t>2026-10-03T23:14:13Z</t>
         </is>
       </c>
     </row>
@@ -6470,7 +6470,7 @@
       </c>
       <c r="S73" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T23:55:31Z</t>
+          <t>2026-10-03T23:14:13Z</t>
         </is>
       </c>
     </row>
@@ -6555,7 +6555,7 @@
       </c>
       <c r="S74" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T23:55:31Z</t>
+          <t>2026-10-03T23:14:13Z</t>
         </is>
       </c>
     </row>
@@ -6640,7 +6640,7 @@
       </c>
       <c r="S75" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T23:55:31Z</t>
+          <t>2026-10-03T23:14:13Z</t>
         </is>
       </c>
     </row>
@@ -6725,7 +6725,7 @@
       </c>
       <c r="S76" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T23:55:31Z</t>
+          <t>2026-10-03T23:14:13Z</t>
         </is>
       </c>
     </row>
@@ -6810,7 +6810,7 @@
       </c>
       <c r="S77" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T23:55:31Z</t>
+          <t>2026-10-03T23:14:13Z</t>
         </is>
       </c>
     </row>
@@ -6895,7 +6895,7 @@
       </c>
       <c r="S78" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T23:55:31Z</t>
+          <t>2026-10-03T23:14:13Z</t>
         </is>
       </c>
     </row>
@@ -6980,7 +6980,7 @@
       </c>
       <c r="S79" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T23:55:31Z</t>
+          <t>2026-10-03T23:14:13Z</t>
         </is>
       </c>
     </row>
@@ -7065,7 +7065,7 @@
       </c>
       <c r="S80" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T23:55:31Z</t>
+          <t>2026-10-03T23:14:13Z</t>
         </is>
       </c>
     </row>
@@ -7150,7 +7150,7 @@
       </c>
       <c r="S81" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T23:55:31Z</t>
+          <t>2026-10-03T23:14:13Z</t>
         </is>
       </c>
     </row>
@@ -7235,7 +7235,7 @@
       </c>
       <c r="S82" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T23:55:31Z</t>
+          <t>2026-10-03T23:14:13Z</t>
         </is>
       </c>
     </row>
@@ -7320,7 +7320,7 @@
       </c>
       <c r="S83" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T23:55:31Z</t>
+          <t>2026-10-03T23:14:13Z</t>
         </is>
       </c>
     </row>
@@ -7405,7 +7405,7 @@
       </c>
       <c r="S84" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T23:55:31Z</t>
+          <t>2026-10-03T23:14:13Z</t>
         </is>
       </c>
     </row>
@@ -7490,7 +7490,7 @@
       </c>
       <c r="S85" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T23:55:31Z</t>
+          <t>2026-10-03T23:14:13Z</t>
         </is>
       </c>
     </row>
@@ -7575,7 +7575,7 @@
       </c>
       <c r="S86" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T23:55:31Z</t>
+          <t>2026-10-03T23:14:13Z</t>
         </is>
       </c>
     </row>
@@ -7660,7 +7660,7 @@
       </c>
       <c r="S87" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T23:55:31Z</t>
+          <t>2026-10-03T23:14:13Z</t>
         </is>
       </c>
     </row>
@@ -7745,7 +7745,7 @@
       </c>
       <c r="S88" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T23:55:31Z</t>
+          <t>2026-10-03T23:14:13Z</t>
         </is>
       </c>
     </row>
@@ -7834,7 +7834,7 @@
       </c>
       <c r="S89" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T23:55:31Z</t>
+          <t>2026-10-03T23:14:13Z</t>
         </is>
       </c>
     </row>
@@ -7923,7 +7923,7 @@
       </c>
       <c r="S90" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T23:55:31Z</t>
+          <t>2026-10-03T23:14:13Z</t>
         </is>
       </c>
     </row>
@@ -8008,7 +8008,7 @@
       </c>
       <c r="S91" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T23:55:31Z</t>
+          <t>2026-10-03T23:14:13Z</t>
         </is>
       </c>
     </row>
@@ -8097,7 +8097,7 @@
       </c>
       <c r="S92" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T23:55:31Z</t>
+          <t>2026-10-03T23:14:13Z</t>
         </is>
       </c>
     </row>
@@ -8186,7 +8186,7 @@
       </c>
       <c r="S93" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T23:55:31Z</t>
+          <t>2026-10-03T23:14:13Z</t>
         </is>
       </c>
     </row>
@@ -8271,7 +8271,7 @@
       </c>
       <c r="S94" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T23:55:31Z</t>
+          <t>2026-10-03T23:14:13Z</t>
         </is>
       </c>
     </row>
@@ -8360,7 +8360,7 @@
       </c>
       <c r="S95" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T23:55:31Z</t>
+          <t>2026-10-03T23:14:13Z</t>
         </is>
       </c>
     </row>
@@ -8449,7 +8449,7 @@
       </c>
       <c r="S96" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T23:55:31Z</t>
+          <t>2026-10-03T23:14:13Z</t>
         </is>
       </c>
     </row>
@@ -8534,7 +8534,7 @@
       </c>
       <c r="S97" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T23:55:31Z</t>
+          <t>2026-10-03T23:14:13Z</t>
         </is>
       </c>
     </row>
@@ -8623,7 +8623,7 @@
       </c>
       <c r="S98" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T23:55:31Z</t>
+          <t>2026-10-03T23:14:13Z</t>
         </is>
       </c>
     </row>
@@ -8712,7 +8712,7 @@
       </c>
       <c r="S99" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T23:55:31Z</t>
+          <t>2026-10-03T23:14:13Z</t>
         </is>
       </c>
     </row>
@@ -8797,7 +8797,7 @@
       </c>
       <c r="S100" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T23:55:31Z</t>
+          <t>2026-10-03T23:14:13Z</t>
         </is>
       </c>
     </row>
@@ -8886,7 +8886,7 @@
       </c>
       <c r="S101" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T23:55:31Z</t>
+          <t>2026-10-03T23:14:13Z</t>
         </is>
       </c>
     </row>
@@ -8975,7 +8975,7 @@
       </c>
       <c r="S102" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T23:55:31Z</t>
+          <t>2026-10-03T23:14:13Z</t>
         </is>
       </c>
     </row>
@@ -9060,7 +9060,7 @@
       </c>
       <c r="S103" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T23:55:31Z</t>
+          <t>2026-10-03T23:14:13Z</t>
         </is>
       </c>
     </row>
@@ -9149,7 +9149,7 @@
       </c>
       <c r="S104" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T23:55:31Z</t>
+          <t>2026-10-03T23:14:13Z</t>
         </is>
       </c>
     </row>
@@ -9238,7 +9238,7 @@
       </c>
       <c r="S105" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T23:55:31Z</t>
+          <t>2026-10-03T23:14:13Z</t>
         </is>
       </c>
     </row>
@@ -9323,7 +9323,7 @@
       </c>
       <c r="S106" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T23:55:31Z</t>
+          <t>2026-10-03T23:14:13Z</t>
         </is>
       </c>
     </row>
@@ -9412,7 +9412,7 @@
       </c>
       <c r="S107" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T23:55:31Z</t>
+          <t>2026-10-03T23:14:13Z</t>
         </is>
       </c>
     </row>
@@ -9501,7 +9501,7 @@
       </c>
       <c r="S108" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T23:55:31Z</t>
+          <t>2026-10-03T23:14:13Z</t>
         </is>
       </c>
     </row>
@@ -9586,7 +9586,7 @@
       </c>
       <c r="S109" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T23:55:31Z</t>
+          <t>2026-10-03T23:14:13Z</t>
         </is>
       </c>
     </row>
@@ -9675,7 +9675,7 @@
       </c>
       <c r="S110" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T23:55:31Z</t>
+          <t>2026-10-03T23:14:13Z</t>
         </is>
       </c>
     </row>
@@ -9764,7 +9764,7 @@
       </c>
       <c r="S111" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T23:55:31Z</t>
+          <t>2026-10-03T23:14:13Z</t>
         </is>
       </c>
     </row>
@@ -9849,7 +9849,7 @@
       </c>
       <c r="S112" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T23:55:31Z</t>
+          <t>2026-10-03T23:14:13Z</t>
         </is>
       </c>
     </row>
@@ -9938,7 +9938,7 @@
       </c>
       <c r="S113" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T23:55:31Z</t>
+          <t>2026-10-03T23:14:13Z</t>
         </is>
       </c>
     </row>
@@ -10027,7 +10027,7 @@
       </c>
       <c r="S114" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T23:55:31Z</t>
+          <t>2026-10-03T23:14:13Z</t>
         </is>
       </c>
     </row>
@@ -10112,7 +10112,7 @@
       </c>
       <c r="S115" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T23:55:31Z</t>
+          <t>2026-10-03T23:14:13Z</t>
         </is>
       </c>
     </row>
@@ -10201,7 +10201,7 @@
       </c>
       <c r="S116" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T23:55:31Z</t>
+          <t>2026-10-03T23:14:13Z</t>
         </is>
       </c>
     </row>
@@ -10290,7 +10290,7 @@
       </c>
       <c r="S117" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T23:55:31Z</t>
+          <t>2026-10-03T23:14:13Z</t>
         </is>
       </c>
     </row>
@@ -10379,7 +10379,7 @@
       </c>
       <c r="S118" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T23:55:31Z</t>
+          <t>2026-10-03T23:14:13Z</t>
         </is>
       </c>
     </row>
@@ -10468,7 +10468,7 @@
       </c>
       <c r="S119" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T23:55:31Z</t>
+          <t>2026-10-03T23:14:13Z</t>
         </is>
       </c>
     </row>
@@ -10557,7 +10557,7 @@
       </c>
       <c r="S120" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T23:55:31Z</t>
+          <t>2026-10-03T23:14:13Z</t>
         </is>
       </c>
     </row>
@@ -10646,7 +10646,7 @@
       </c>
       <c r="S121" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T23:55:31Z</t>
+          <t>2026-10-03T23:14:13Z</t>
         </is>
       </c>
     </row>
@@ -10735,7 +10735,7 @@
       </c>
       <c r="S122" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T23:55:31Z</t>
+          <t>2026-10-03T23:14:13Z</t>
         </is>
       </c>
     </row>
@@ -10824,7 +10824,7 @@
       </c>
       <c r="S123" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T23:55:31Z</t>
+          <t>2026-10-03T23:14:13Z</t>
         </is>
       </c>
     </row>
@@ -10913,7 +10913,7 @@
       </c>
       <c r="S124" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T23:55:31Z</t>
+          <t>2026-10-03T23:14:13Z</t>
         </is>
       </c>
     </row>
@@ -11002,7 +11002,7 @@
       </c>
       <c r="S125" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T23:55:31Z</t>
+          <t>2026-10-03T23:14:13Z</t>
         </is>
       </c>
     </row>
@@ -11091,7 +11091,7 @@
       </c>
       <c r="S126" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T23:55:31Z</t>
+          <t>2026-10-03T23:14:13Z</t>
         </is>
       </c>
     </row>
@@ -11180,7 +11180,7 @@
       </c>
       <c r="S127" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T23:55:31Z</t>
+          <t>2026-10-03T23:14:13Z</t>
         </is>
       </c>
     </row>
@@ -11269,7 +11269,7 @@
       </c>
       <c r="S128" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T23:55:31Z</t>
+          <t>2026-10-03T23:14:13Z</t>
         </is>
       </c>
     </row>
@@ -11354,7 +11354,7 @@
       </c>
       <c r="S129" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T23:55:31Z</t>
+          <t>2026-10-03T23:14:13Z</t>
         </is>
       </c>
     </row>
@@ -11439,7 +11439,7 @@
       </c>
       <c r="S130" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T23:55:31Z</t>
+          <t>2026-10-03T23:14:13Z</t>
         </is>
       </c>
     </row>
@@ -11524,7 +11524,7 @@
       </c>
       <c r="S131" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T23:55:31Z</t>
+          <t>2026-10-03T23:14:13Z</t>
         </is>
       </c>
     </row>
@@ -11609,7 +11609,7 @@
       </c>
       <c r="S132" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T23:55:31Z</t>
+          <t>2026-10-03T23:14:13Z</t>
         </is>
       </c>
     </row>
@@ -11694,7 +11694,7 @@
       </c>
       <c r="S133" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T23:55:31Z</t>
+          <t>2026-10-03T23:14:13Z</t>
         </is>
       </c>
     </row>
@@ -11779,7 +11779,7 @@
       </c>
       <c r="S134" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T23:55:31Z</t>
+          <t>2026-10-03T23:14:13Z</t>
         </is>
       </c>
     </row>
@@ -11864,7 +11864,7 @@
       </c>
       <c r="S135" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T23:55:31Z</t>
+          <t>2026-10-03T23:14:13Z</t>
         </is>
       </c>
     </row>
@@ -11949,7 +11949,7 @@
       </c>
       <c r="S136" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T23:55:31Z</t>
+          <t>2026-10-03T23:14:13Z</t>
         </is>
       </c>
     </row>
@@ -12034,7 +12034,7 @@
       </c>
       <c r="S137" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T23:55:31Z</t>
+          <t>2026-10-03T23:14:13Z</t>
         </is>
       </c>
     </row>
@@ -12119,7 +12119,7 @@
       </c>
       <c r="S138" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T23:55:31Z</t>
+          <t>2026-10-03T23:14:13Z</t>
         </is>
       </c>
     </row>
@@ -12204,7 +12204,7 @@
       </c>
       <c r="S139" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T23:55:31Z</t>
+          <t>2026-10-03T23:14:13Z</t>
         </is>
       </c>
     </row>
@@ -12289,7 +12289,7 @@
       </c>
       <c r="S140" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T23:55:31Z</t>
+          <t>2026-10-03T23:14:13Z</t>
         </is>
       </c>
     </row>
@@ -12374,7 +12374,7 @@
       </c>
       <c r="S141" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T23:55:31Z</t>
+          <t>2026-10-03T23:14:13Z</t>
         </is>
       </c>
     </row>
@@ -12459,7 +12459,7 @@
       </c>
       <c r="S142" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T23:55:31Z</t>
+          <t>2026-10-03T23:14:13Z</t>
         </is>
       </c>
     </row>
@@ -12544,7 +12544,7 @@
       </c>
       <c r="S143" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T23:55:31Z</t>
+          <t>2026-10-03T23:14:13Z</t>
         </is>
       </c>
     </row>
@@ -12629,7 +12629,7 @@
       </c>
       <c r="S144" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T23:55:31Z</t>
+          <t>2026-10-03T23:14:13Z</t>
         </is>
       </c>
     </row>
@@ -12714,7 +12714,7 @@
       </c>
       <c r="S145" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T23:55:31Z</t>
+          <t>2026-10-03T23:14:13Z</t>
         </is>
       </c>
     </row>
@@ -12799,7 +12799,7 @@
       </c>
       <c r="S146" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T23:55:31Z</t>
+          <t>2026-10-03T23:14:13Z</t>
         </is>
       </c>
     </row>
@@ -12884,7 +12884,7 @@
       </c>
       <c r="S147" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T23:55:31Z</t>
+          <t>2026-10-03T23:14:13Z</t>
         </is>
       </c>
     </row>
@@ -12969,7 +12969,7 @@
       </c>
       <c r="S148" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T23:55:31Z</t>
+          <t>2026-10-03T23:14:13Z</t>
         </is>
       </c>
     </row>
@@ -13054,7 +13054,7 @@
       </c>
       <c r="S149" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T23:55:31Z</t>
+          <t>2026-10-03T23:14:13Z</t>
         </is>
       </c>
     </row>
@@ -13143,7 +13143,7 @@
       </c>
       <c r="S150" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T23:55:31Z</t>
+          <t>2026-10-03T23:14:13Z</t>
         </is>
       </c>
     </row>
@@ -13232,7 +13232,7 @@
       </c>
       <c r="S151" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T23:55:31Z</t>
+          <t>2026-10-03T23:14:13Z</t>
         </is>
       </c>
     </row>
@@ -13317,7 +13317,7 @@
       </c>
       <c r="S152" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T23:55:31Z</t>
+          <t>2026-10-03T23:14:13Z</t>
         </is>
       </c>
     </row>
@@ -13406,7 +13406,7 @@
       </c>
       <c r="S153" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T23:55:31Z</t>
+          <t>2026-10-03T23:14:13Z</t>
         </is>
       </c>
     </row>
@@ -13495,7 +13495,7 @@
       </c>
       <c r="S154" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T23:55:31Z</t>
+          <t>2026-10-03T23:14:13Z</t>
         </is>
       </c>
     </row>
@@ -13580,7 +13580,7 @@
       </c>
       <c r="S155" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T23:55:31Z</t>
+          <t>2026-10-03T23:14:13Z</t>
         </is>
       </c>
     </row>
@@ -13669,7 +13669,7 @@
       </c>
       <c r="S156" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T23:55:31Z</t>
+          <t>2026-10-03T23:14:13Z</t>
         </is>
       </c>
     </row>
@@ -13758,7 +13758,7 @@
       </c>
       <c r="S157" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T23:55:31Z</t>
+          <t>2026-10-03T23:14:13Z</t>
         </is>
       </c>
     </row>
@@ -13843,7 +13843,7 @@
       </c>
       <c r="S158" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T23:55:31Z</t>
+          <t>2026-10-03T23:14:13Z</t>
         </is>
       </c>
     </row>
@@ -13932,7 +13932,7 @@
       </c>
       <c r="S159" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T23:55:31Z</t>
+          <t>2026-10-03T23:14:13Z</t>
         </is>
       </c>
     </row>
@@ -14021,7 +14021,7 @@
       </c>
       <c r="S160" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T23:55:31Z</t>
+          <t>2026-10-03T23:14:13Z</t>
         </is>
       </c>
     </row>
@@ -14106,7 +14106,7 @@
       </c>
       <c r="S161" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T23:55:31Z</t>
+          <t>2026-10-03T23:14:13Z</t>
         </is>
       </c>
     </row>
@@ -14195,7 +14195,7 @@
       </c>
       <c r="S162" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T23:55:31Z</t>
+          <t>2026-10-03T23:14:13Z</t>
         </is>
       </c>
     </row>
@@ -14284,7 +14284,7 @@
       </c>
       <c r="S163" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T23:55:31Z</t>
+          <t>2026-10-03T23:14:13Z</t>
         </is>
       </c>
     </row>
@@ -14369,7 +14369,7 @@
       </c>
       <c r="S164" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T23:55:31Z</t>
+          <t>2026-10-03T23:14:13Z</t>
         </is>
       </c>
     </row>
@@ -14458,7 +14458,7 @@
       </c>
       <c r="S165" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T23:55:31Z</t>
+          <t>2026-10-03T23:14:13Z</t>
         </is>
       </c>
     </row>
@@ -14547,7 +14547,7 @@
       </c>
       <c r="S166" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T23:55:31Z</t>
+          <t>2026-10-03T23:14:13Z</t>
         </is>
       </c>
     </row>
@@ -14632,7 +14632,7 @@
       </c>
       <c r="S167" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T23:55:31Z</t>
+          <t>2026-10-03T23:14:13Z</t>
         </is>
       </c>
     </row>
@@ -14721,7 +14721,7 @@
       </c>
       <c r="S168" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T23:55:31Z</t>
+          <t>2026-10-03T23:14:13Z</t>
         </is>
       </c>
     </row>
@@ -14810,7 +14810,7 @@
       </c>
       <c r="S169" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T23:55:31Z</t>
+          <t>2026-10-03T23:14:13Z</t>
         </is>
       </c>
     </row>
@@ -14895,7 +14895,7 @@
       </c>
       <c r="S170" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T23:55:31Z</t>
+          <t>2026-10-03T23:14:13Z</t>
         </is>
       </c>
     </row>
@@ -14984,7 +14984,7 @@
       </c>
       <c r="S171" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T23:55:31Z</t>
+          <t>2026-10-03T23:14:13Z</t>
         </is>
       </c>
     </row>
@@ -15073,7 +15073,7 @@
       </c>
       <c r="S172" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T23:55:31Z</t>
+          <t>2026-10-03T23:14:13Z</t>
         </is>
       </c>
     </row>
@@ -15158,7 +15158,7 @@
       </c>
       <c r="S173" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T23:55:31Z</t>
+          <t>2026-10-03T23:14:13Z</t>
         </is>
       </c>
     </row>
@@ -15247,7 +15247,7 @@
       </c>
       <c r="S174" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T23:55:31Z</t>
+          <t>2026-10-03T23:14:13Z</t>
         </is>
       </c>
     </row>
@@ -15336,7 +15336,7 @@
       </c>
       <c r="S175" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T23:55:31Z</t>
+          <t>2026-10-03T23:14:13Z</t>
         </is>
       </c>
     </row>
@@ -15421,7 +15421,7 @@
       </c>
       <c r="S176" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T23:55:31Z</t>
+          <t>2026-10-03T23:14:13Z</t>
         </is>
       </c>
     </row>
@@ -15510,7 +15510,7 @@
       </c>
       <c r="S177" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T23:55:31Z</t>
+          <t>2026-10-03T23:14:13Z</t>
         </is>
       </c>
     </row>
@@ -15599,7 +15599,7 @@
       </c>
       <c r="S178" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T23:55:31Z</t>
+          <t>2026-10-03T23:14:13Z</t>
         </is>
       </c>
     </row>
@@ -15688,7 +15688,7 @@
       </c>
       <c r="S179" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T23:55:31Z</t>
+          <t>2026-10-03T23:14:13Z</t>
         </is>
       </c>
     </row>
@@ -15777,7 +15777,7 @@
       </c>
       <c r="S180" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T23:55:31Z</t>
+          <t>2026-10-03T23:14:13Z</t>
         </is>
       </c>
     </row>
@@ -15866,7 +15866,7 @@
       </c>
       <c r="S181" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T23:55:31Z</t>
+          <t>2026-10-03T23:14:13Z</t>
         </is>
       </c>
     </row>
@@ -15955,7 +15955,7 @@
       </c>
       <c r="S182" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T23:55:31Z</t>
+          <t>2026-10-03T23:14:13Z</t>
         </is>
       </c>
     </row>
@@ -16044,7 +16044,7 @@
       </c>
       <c r="S183" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T23:55:31Z</t>
+          <t>2026-10-03T23:14:13Z</t>
         </is>
       </c>
     </row>
@@ -16133,7 +16133,7 @@
       </c>
       <c r="S184" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T23:55:31Z</t>
+          <t>2026-10-03T23:14:13Z</t>
         </is>
       </c>
     </row>
@@ -16222,7 +16222,7 @@
       </c>
       <c r="S185" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T23:55:31Z</t>
+          <t>2026-10-03T23:14:13Z</t>
         </is>
       </c>
     </row>
@@ -16311,7 +16311,7 @@
       </c>
       <c r="S186" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T23:55:31Z</t>
+          <t>2026-10-03T23:14:13Z</t>
         </is>
       </c>
     </row>
@@ -16400,7 +16400,7 @@
       </c>
       <c r="S187" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T23:55:31Z</t>
+          <t>2026-10-03T23:14:13Z</t>
         </is>
       </c>
     </row>
@@ -16489,7 +16489,7 @@
       </c>
       <c r="S188" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T23:55:31Z</t>
+          <t>2026-10-03T23:14:13Z</t>
         </is>
       </c>
     </row>
@@ -16578,7 +16578,7 @@
       </c>
       <c r="S189" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T23:55:31Z</t>
+          <t>2026-10-03T23:14:13Z</t>
         </is>
       </c>
     </row>
@@ -16663,7 +16663,7 @@
       </c>
       <c r="S190" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T23:55:31Z</t>
+          <t>2026-10-03T23:14:13Z</t>
         </is>
       </c>
     </row>
@@ -16748,7 +16748,7 @@
       </c>
       <c r="S191" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T23:55:31Z</t>
+          <t>2026-10-03T23:14:13Z</t>
         </is>
       </c>
     </row>
@@ -16833,7 +16833,7 @@
       </c>
       <c r="S192" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T23:55:31Z</t>
+          <t>2026-10-03T23:14:13Z</t>
         </is>
       </c>
     </row>
@@ -16918,7 +16918,7 @@
       </c>
       <c r="S193" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T23:55:31Z</t>
+          <t>2026-10-03T23:14:13Z</t>
         </is>
       </c>
     </row>
@@ -17003,7 +17003,7 @@
       </c>
       <c r="S194" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T23:55:31Z</t>
+          <t>2026-10-03T23:14:13Z</t>
         </is>
       </c>
     </row>
@@ -17088,7 +17088,7 @@
       </c>
       <c r="S195" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T23:55:31Z</t>
+          <t>2026-10-03T23:14:13Z</t>
         </is>
       </c>
     </row>
@@ -17173,7 +17173,7 @@
       </c>
       <c r="S196" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T23:55:31Z</t>
+          <t>2026-10-03T23:14:13Z</t>
         </is>
       </c>
     </row>
@@ -17258,7 +17258,7 @@
       </c>
       <c r="S197" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T23:55:31Z</t>
+          <t>2026-10-03T23:14:13Z</t>
         </is>
       </c>
     </row>
@@ -17343,7 +17343,7 @@
       </c>
       <c r="S198" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T23:55:31Z</t>
+          <t>2026-10-03T23:14:13Z</t>
         </is>
       </c>
     </row>
@@ -17428,7 +17428,7 @@
       </c>
       <c r="S199" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T23:55:31Z</t>
+          <t>2026-10-03T23:14:13Z</t>
         </is>
       </c>
     </row>
@@ -17513,7 +17513,7 @@
       </c>
       <c r="S200" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T23:55:31Z</t>
+          <t>2026-10-03T23:14:13Z</t>
         </is>
       </c>
     </row>
@@ -17598,7 +17598,7 @@
       </c>
       <c r="S201" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T23:55:31Z</t>
+          <t>2026-10-03T23:14:13Z</t>
         </is>
       </c>
     </row>
@@ -17683,7 +17683,7 @@
       </c>
       <c r="S202" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T23:55:31Z</t>
+          <t>2026-10-03T23:14:13Z</t>
         </is>
       </c>
     </row>
@@ -17768,7 +17768,7 @@
       </c>
       <c r="S203" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T23:55:31Z</t>
+          <t>2026-10-03T23:14:13Z</t>
         </is>
       </c>
     </row>
@@ -17853,7 +17853,7 @@
       </c>
       <c r="S204" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T23:55:31Z</t>
+          <t>2026-10-03T23:14:13Z</t>
         </is>
       </c>
     </row>
@@ -17938,7 +17938,7 @@
       </c>
       <c r="S205" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T23:55:31Z</t>
+          <t>2026-10-03T23:14:13Z</t>
         </is>
       </c>
     </row>
@@ -18023,7 +18023,7 @@
       </c>
       <c r="S206" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T23:55:31Z</t>
+          <t>2026-10-03T23:14:13Z</t>
         </is>
       </c>
     </row>
@@ -18108,7 +18108,7 @@
       </c>
       <c r="S207" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T23:55:31Z</t>
+          <t>2026-10-03T23:14:13Z</t>
         </is>
       </c>
     </row>
@@ -18193,7 +18193,7 @@
       </c>
       <c r="S208" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T23:55:31Z</t>
+          <t>2026-10-03T23:14:13Z</t>
         </is>
       </c>
     </row>
@@ -18278,7 +18278,7 @@
       </c>
       <c r="S209" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T23:55:31Z</t>
+          <t>2026-10-03T23:14:13Z</t>
         </is>
       </c>
     </row>
@@ -18363,7 +18363,7 @@
       </c>
       <c r="S210" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T23:55:31Z</t>
+          <t>2026-10-03T23:14:13Z</t>
         </is>
       </c>
     </row>
@@ -18452,7 +18452,7 @@
       </c>
       <c r="S211" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T23:55:31Z</t>
+          <t>2026-10-03T23:14:13Z</t>
         </is>
       </c>
     </row>
@@ -18541,7 +18541,7 @@
       </c>
       <c r="S212" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T23:55:31Z</t>
+          <t>2026-10-03T23:14:13Z</t>
         </is>
       </c>
     </row>
@@ -18626,7 +18626,7 @@
       </c>
       <c r="S213" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T23:55:31Z</t>
+          <t>2026-10-03T23:14:13Z</t>
         </is>
       </c>
     </row>
@@ -18715,7 +18715,7 @@
       </c>
       <c r="S214" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T23:55:31Z</t>
+          <t>2026-10-03T23:14:13Z</t>
         </is>
       </c>
     </row>
@@ -18804,7 +18804,7 @@
       </c>
       <c r="S215" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T23:55:31Z</t>
+          <t>2026-10-03T23:14:13Z</t>
         </is>
       </c>
     </row>
@@ -18889,7 +18889,7 @@
       </c>
       <c r="S216" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T23:55:31Z</t>
+          <t>2026-10-03T23:14:13Z</t>
         </is>
       </c>
     </row>
@@ -18978,7 +18978,7 @@
       </c>
       <c r="S217" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T23:55:31Z</t>
+          <t>2026-10-03T23:14:13Z</t>
         </is>
       </c>
     </row>
@@ -19067,7 +19067,7 @@
       </c>
       <c r="S218" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T23:55:31Z</t>
+          <t>2026-10-03T23:14:13Z</t>
         </is>
       </c>
     </row>
@@ -19152,7 +19152,7 @@
       </c>
       <c r="S219" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T23:55:31Z</t>
+          <t>2026-10-03T23:14:13Z</t>
         </is>
       </c>
     </row>
@@ -19241,7 +19241,7 @@
       </c>
       <c r="S220" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T23:55:31Z</t>
+          <t>2026-10-03T23:14:13Z</t>
         </is>
       </c>
     </row>
@@ -19330,7 +19330,7 @@
       </c>
       <c r="S221" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T23:55:31Z</t>
+          <t>2026-10-03T23:14:13Z</t>
         </is>
       </c>
     </row>
@@ -19415,7 +19415,7 @@
       </c>
       <c r="S222" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T23:55:31Z</t>
+          <t>2026-10-03T23:14:13Z</t>
         </is>
       </c>
     </row>
@@ -19504,7 +19504,7 @@
       </c>
       <c r="S223" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T23:55:31Z</t>
+          <t>2026-10-03T23:14:13Z</t>
         </is>
       </c>
     </row>
@@ -19593,7 +19593,7 @@
       </c>
       <c r="S224" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T23:55:31Z</t>
+          <t>2026-10-03T23:14:13Z</t>
         </is>
       </c>
     </row>
@@ -19678,7 +19678,7 @@
       </c>
       <c r="S225" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T23:55:31Z</t>
+          <t>2026-10-03T23:14:13Z</t>
         </is>
       </c>
     </row>
@@ -19767,7 +19767,7 @@
       </c>
       <c r="S226" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T23:55:31Z</t>
+          <t>2026-10-03T23:14:13Z</t>
         </is>
       </c>
     </row>
@@ -19856,7 +19856,7 @@
       </c>
       <c r="S227" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T23:55:31Z</t>
+          <t>2026-10-03T23:14:13Z</t>
         </is>
       </c>
     </row>
@@ -19941,7 +19941,7 @@
       </c>
       <c r="S228" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T23:55:31Z</t>
+          <t>2026-10-03T23:14:13Z</t>
         </is>
       </c>
     </row>
@@ -20030,7 +20030,7 @@
       </c>
       <c r="S229" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T23:55:31Z</t>
+          <t>2026-10-03T23:14:13Z</t>
         </is>
       </c>
     </row>
@@ -20119,7 +20119,7 @@
       </c>
       <c r="S230" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T23:55:31Z</t>
+          <t>2026-10-03T23:14:13Z</t>
         </is>
       </c>
     </row>
@@ -20204,7 +20204,7 @@
       </c>
       <c r="S231" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T23:55:31Z</t>
+          <t>2026-10-03T23:14:13Z</t>
         </is>
       </c>
     </row>
@@ -20293,7 +20293,7 @@
       </c>
       <c r="S232" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T23:55:31Z</t>
+          <t>2026-10-03T23:14:13Z</t>
         </is>
       </c>
     </row>
@@ -20382,7 +20382,7 @@
       </c>
       <c r="S233" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T23:55:31Z</t>
+          <t>2026-10-03T23:14:13Z</t>
         </is>
       </c>
     </row>
@@ -20467,7 +20467,7 @@
       </c>
       <c r="S234" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T23:55:31Z</t>
+          <t>2026-10-03T23:14:13Z</t>
         </is>
       </c>
     </row>
@@ -20556,7 +20556,7 @@
       </c>
       <c r="S235" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T23:55:31Z</t>
+          <t>2026-10-03T23:14:13Z</t>
         </is>
       </c>
     </row>
@@ -20645,7 +20645,7 @@
       </c>
       <c r="S236" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T23:55:31Z</t>
+          <t>2026-10-03T23:14:13Z</t>
         </is>
       </c>
     </row>
@@ -20730,7 +20730,7 @@
       </c>
       <c r="S237" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T23:55:31Z</t>
+          <t>2026-10-03T23:14:13Z</t>
         </is>
       </c>
     </row>
@@ -20819,7 +20819,7 @@
       </c>
       <c r="S238" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T23:55:31Z</t>
+          <t>2026-10-03T23:14:13Z</t>
         </is>
       </c>
     </row>
@@ -20908,7 +20908,7 @@
       </c>
       <c r="S239" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T23:55:31Z</t>
+          <t>2026-10-03T23:14:13Z</t>
         </is>
       </c>
     </row>
@@ -20997,7 +20997,7 @@
       </c>
       <c r="S240" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T23:55:31Z</t>
+          <t>2026-10-03T23:14:13Z</t>
         </is>
       </c>
     </row>
@@ -21086,7 +21086,7 @@
       </c>
       <c r="S241" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T23:55:31Z</t>
+          <t>2026-10-03T23:14:13Z</t>
         </is>
       </c>
     </row>
@@ -21175,7 +21175,7 @@
       </c>
       <c r="S242" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T23:55:31Z</t>
+          <t>2026-10-03T23:14:13Z</t>
         </is>
       </c>
     </row>
@@ -21264,7 +21264,7 @@
       </c>
       <c r="S243" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T23:55:31Z</t>
+          <t>2026-10-03T23:14:13Z</t>
         </is>
       </c>
     </row>
@@ -21353,7 +21353,7 @@
       </c>
       <c r="S244" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T23:55:31Z</t>
+          <t>2026-10-03T23:14:13Z</t>
         </is>
       </c>
     </row>
@@ -21442,7 +21442,7 @@
       </c>
       <c r="S245" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T23:55:31Z</t>
+          <t>2026-10-03T23:14:13Z</t>
         </is>
       </c>
     </row>
@@ -21531,7 +21531,7 @@
       </c>
       <c r="S246" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T23:55:31Z</t>
+          <t>2026-10-03T23:14:13Z</t>
         </is>
       </c>
     </row>
@@ -21620,7 +21620,7 @@
       </c>
       <c r="S247" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T23:55:31Z</t>
+          <t>2026-10-03T23:14:13Z</t>
         </is>
       </c>
     </row>
@@ -21709,7 +21709,7 @@
       </c>
       <c r="S248" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T23:55:31Z</t>
+          <t>2026-10-03T23:14:13Z</t>
         </is>
       </c>
     </row>
@@ -21798,7 +21798,7 @@
       </c>
       <c r="S249" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T23:55:31Z</t>
+          <t>2026-10-03T23:14:13Z</t>
         </is>
       </c>
     </row>
@@ -21887,7 +21887,7 @@
       </c>
       <c r="S250" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T23:55:31Z</t>
+          <t>2026-10-03T23:14:13Z</t>
         </is>
       </c>
     </row>
@@ -22019,7 +22019,7 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T23:55:31Z</t>
+          <t>2026-10-03T23:14:13Z</t>
         </is>
       </c>
     </row>
@@ -22099,7 +22099,7 @@
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>{"dataset_id": "bcv_pib_sector_institucional_anual", "title": "Producto interno bruto por sector institucional anual", "table": "Variaciones porcentuales", "source_file": "5_2_1_si_anual.xlsx", "base": "2007", "price_type": "Precios constantes", "measure": "Variación porcentual interanual", "frequency": "Anual", "period": "2025", "year": 2025, "quarter": null, "classification": "Sector institucional", "component": "Impuestos netos sobre los productos", "value": 10.600260421283764, "unit": "Porcentaje", "status": "Preliminar", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/cuentas_macroeconomicas/5_2_1_si_anual.xlsx", "fetched_at": "2026-10-02T23:55:31Z"}</t>
+          <t>{"dataset_id": "bcv_pib_sector_institucional_anual", "title": "Producto interno bruto por sector institucional anual", "table": "Variaciones porcentuales", "source_file": "5_2_1_si_anual.xlsx", "base": "2007", "price_type": "Precios constantes", "measure": "Variación porcentual interanual", "frequency": "Anual", "period": "2025", "year": 2025, "quarter": null, "classification": "Sector institucional", "component": "Impuestos netos sobre los productos", "value": 10.600260421283764, "unit": "Porcentaje", "status": "Preliminar", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/cuentas_macroeconomicas/5_2_1_si_anual.xlsx", "fetched_at": "2026-10-03T23:14:13Z"}</t>
         </is>
       </c>
     </row>

--- a/assets/data/bcv/excel/ove_bcv_pib_sector_institucional_anual.xlsx
+++ b/assets/data/bcv/excel/ove_bcv_pib_sector_institucional_anual.xlsx
@@ -736,7 +736,7 @@
       </c>
       <c r="S7" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03T23:14:13Z</t>
+          <t>2026-10-04T23:25:19Z</t>
         </is>
       </c>
     </row>
@@ -821,7 +821,7 @@
       </c>
       <c r="S8" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03T23:14:13Z</t>
+          <t>2026-10-04T23:25:19Z</t>
         </is>
       </c>
     </row>
@@ -906,7 +906,7 @@
       </c>
       <c r="S9" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03T23:14:13Z</t>
+          <t>2026-10-04T23:25:19Z</t>
         </is>
       </c>
     </row>
@@ -991,7 +991,7 @@
       </c>
       <c r="S10" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03T23:14:13Z</t>
+          <t>2026-10-04T23:25:19Z</t>
         </is>
       </c>
     </row>
@@ -1076,7 +1076,7 @@
       </c>
       <c r="S11" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03T23:14:13Z</t>
+          <t>2026-10-04T23:25:19Z</t>
         </is>
       </c>
     </row>
@@ -1161,7 +1161,7 @@
       </c>
       <c r="S12" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03T23:14:13Z</t>
+          <t>2026-10-04T23:25:19Z</t>
         </is>
       </c>
     </row>
@@ -1246,7 +1246,7 @@
       </c>
       <c r="S13" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03T23:14:13Z</t>
+          <t>2026-10-04T23:25:19Z</t>
         </is>
       </c>
     </row>
@@ -1331,7 +1331,7 @@
       </c>
       <c r="S14" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03T23:14:13Z</t>
+          <t>2026-10-04T23:25:19Z</t>
         </is>
       </c>
     </row>
@@ -1416,7 +1416,7 @@
       </c>
       <c r="S15" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03T23:14:13Z</t>
+          <t>2026-10-04T23:25:19Z</t>
         </is>
       </c>
     </row>
@@ -1501,7 +1501,7 @@
       </c>
       <c r="S16" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03T23:14:13Z</t>
+          <t>2026-10-04T23:25:19Z</t>
         </is>
       </c>
     </row>
@@ -1586,7 +1586,7 @@
       </c>
       <c r="S17" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03T23:14:13Z</t>
+          <t>2026-10-04T23:25:19Z</t>
         </is>
       </c>
     </row>
@@ -1671,7 +1671,7 @@
       </c>
       <c r="S18" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03T23:14:13Z</t>
+          <t>2026-10-04T23:25:19Z</t>
         </is>
       </c>
     </row>
@@ -1756,7 +1756,7 @@
       </c>
       <c r="S19" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03T23:14:13Z</t>
+          <t>2026-10-04T23:25:19Z</t>
         </is>
       </c>
     </row>
@@ -1841,7 +1841,7 @@
       </c>
       <c r="S20" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03T23:14:13Z</t>
+          <t>2026-10-04T23:25:19Z</t>
         </is>
       </c>
     </row>
@@ -1926,7 +1926,7 @@
       </c>
       <c r="S21" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03T23:14:13Z</t>
+          <t>2026-10-04T23:25:19Z</t>
         </is>
       </c>
     </row>
@@ -2011,7 +2011,7 @@
       </c>
       <c r="S22" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03T23:14:13Z</t>
+          <t>2026-10-04T23:25:19Z</t>
         </is>
       </c>
     </row>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="S23" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03T23:14:13Z</t>
+          <t>2026-10-04T23:25:19Z</t>
         </is>
       </c>
     </row>
@@ -2181,7 +2181,7 @@
       </c>
       <c r="S24" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03T23:14:13Z</t>
+          <t>2026-10-04T23:25:19Z</t>
         </is>
       </c>
     </row>
@@ -2266,7 +2266,7 @@
       </c>
       <c r="S25" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03T23:14:13Z</t>
+          <t>2026-10-04T23:25:19Z</t>
         </is>
       </c>
     </row>
@@ -2351,7 +2351,7 @@
       </c>
       <c r="S26" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03T23:14:13Z</t>
+          <t>2026-10-04T23:25:19Z</t>
         </is>
       </c>
     </row>
@@ -2436,7 +2436,7 @@
       </c>
       <c r="S27" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03T23:14:13Z</t>
+          <t>2026-10-04T23:25:19Z</t>
         </is>
       </c>
     </row>
@@ -2525,7 +2525,7 @@
       </c>
       <c r="S28" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03T23:14:13Z</t>
+          <t>2026-10-04T23:25:19Z</t>
         </is>
       </c>
     </row>
@@ -2614,7 +2614,7 @@
       </c>
       <c r="S29" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03T23:14:13Z</t>
+          <t>2026-10-04T23:25:19Z</t>
         </is>
       </c>
     </row>
@@ -2699,7 +2699,7 @@
       </c>
       <c r="S30" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03T23:14:13Z</t>
+          <t>2026-10-04T23:25:19Z</t>
         </is>
       </c>
     </row>
@@ -2788,7 +2788,7 @@
       </c>
       <c r="S31" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03T23:14:13Z</t>
+          <t>2026-10-04T23:25:19Z</t>
         </is>
       </c>
     </row>
@@ -2877,7 +2877,7 @@
       </c>
       <c r="S32" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03T23:14:13Z</t>
+          <t>2026-10-04T23:25:19Z</t>
         </is>
       </c>
     </row>
@@ -2962,7 +2962,7 @@
       </c>
       <c r="S33" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03T23:14:13Z</t>
+          <t>2026-10-04T23:25:19Z</t>
         </is>
       </c>
     </row>
@@ -3051,7 +3051,7 @@
       </c>
       <c r="S34" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03T23:14:13Z</t>
+          <t>2026-10-04T23:25:19Z</t>
         </is>
       </c>
     </row>
@@ -3140,7 +3140,7 @@
       </c>
       <c r="S35" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03T23:14:13Z</t>
+          <t>2026-10-04T23:25:19Z</t>
         </is>
       </c>
     </row>
@@ -3225,7 +3225,7 @@
       </c>
       <c r="S36" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03T23:14:13Z</t>
+          <t>2026-10-04T23:25:19Z</t>
         </is>
       </c>
     </row>
@@ -3314,7 +3314,7 @@
       </c>
       <c r="S37" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03T23:14:13Z</t>
+          <t>2026-10-04T23:25:19Z</t>
         </is>
       </c>
     </row>
@@ -3403,7 +3403,7 @@
       </c>
       <c r="S38" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03T23:14:13Z</t>
+          <t>2026-10-04T23:25:19Z</t>
         </is>
       </c>
     </row>
@@ -3488,7 +3488,7 @@
       </c>
       <c r="S39" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03T23:14:13Z</t>
+          <t>2026-10-04T23:25:19Z</t>
         </is>
       </c>
     </row>
@@ -3577,7 +3577,7 @@
       </c>
       <c r="S40" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03T23:14:13Z</t>
+          <t>2026-10-04T23:25:19Z</t>
         </is>
       </c>
     </row>
@@ -3666,7 +3666,7 @@
       </c>
       <c r="S41" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03T23:14:13Z</t>
+          <t>2026-10-04T23:25:19Z</t>
         </is>
       </c>
     </row>
@@ -3751,7 +3751,7 @@
       </c>
       <c r="S42" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03T23:14:13Z</t>
+          <t>2026-10-04T23:25:19Z</t>
         </is>
       </c>
     </row>
@@ -3840,7 +3840,7 @@
       </c>
       <c r="S43" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03T23:14:13Z</t>
+          <t>2026-10-04T23:25:19Z</t>
         </is>
       </c>
     </row>
@@ -3929,7 +3929,7 @@
       </c>
       <c r="S44" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03T23:14:13Z</t>
+          <t>2026-10-04T23:25:19Z</t>
         </is>
       </c>
     </row>
@@ -4014,7 +4014,7 @@
       </c>
       <c r="S45" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03T23:14:13Z</t>
+          <t>2026-10-04T23:25:19Z</t>
         </is>
       </c>
     </row>
@@ -4103,7 +4103,7 @@
       </c>
       <c r="S46" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03T23:14:13Z</t>
+          <t>2026-10-04T23:25:19Z</t>
         </is>
       </c>
     </row>
@@ -4192,7 +4192,7 @@
       </c>
       <c r="S47" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03T23:14:13Z</t>
+          <t>2026-10-04T23:25:19Z</t>
         </is>
       </c>
     </row>
@@ -4277,7 +4277,7 @@
       </c>
       <c r="S48" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03T23:14:13Z</t>
+          <t>2026-10-04T23:25:19Z</t>
         </is>
       </c>
     </row>
@@ -4366,7 +4366,7 @@
       </c>
       <c r="S49" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03T23:14:13Z</t>
+          <t>2026-10-04T23:25:19Z</t>
         </is>
       </c>
     </row>
@@ -4455,7 +4455,7 @@
       </c>
       <c r="S50" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03T23:14:13Z</t>
+          <t>2026-10-04T23:25:19Z</t>
         </is>
       </c>
     </row>
@@ -4540,7 +4540,7 @@
       </c>
       <c r="S51" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03T23:14:13Z</t>
+          <t>2026-10-04T23:25:19Z</t>
         </is>
       </c>
     </row>
@@ -4629,7 +4629,7 @@
       </c>
       <c r="S52" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03T23:14:13Z</t>
+          <t>2026-10-04T23:25:19Z</t>
         </is>
       </c>
     </row>
@@ -4718,7 +4718,7 @@
       </c>
       <c r="S53" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03T23:14:13Z</t>
+          <t>2026-10-04T23:25:19Z</t>
         </is>
       </c>
     </row>
@@ -4803,7 +4803,7 @@
       </c>
       <c r="S54" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03T23:14:13Z</t>
+          <t>2026-10-04T23:25:19Z</t>
         </is>
       </c>
     </row>
@@ -4892,7 +4892,7 @@
       </c>
       <c r="S55" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03T23:14:13Z</t>
+          <t>2026-10-04T23:25:19Z</t>
         </is>
       </c>
     </row>
@@ -4981,7 +4981,7 @@
       </c>
       <c r="S56" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03T23:14:13Z</t>
+          <t>2026-10-04T23:25:19Z</t>
         </is>
       </c>
     </row>
@@ -5070,7 +5070,7 @@
       </c>
       <c r="S57" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03T23:14:13Z</t>
+          <t>2026-10-04T23:25:19Z</t>
         </is>
       </c>
     </row>
@@ -5159,7 +5159,7 @@
       </c>
       <c r="S58" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03T23:14:13Z</t>
+          <t>2026-10-04T23:25:19Z</t>
         </is>
       </c>
     </row>
@@ -5248,7 +5248,7 @@
       </c>
       <c r="S59" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03T23:14:13Z</t>
+          <t>2026-10-04T23:25:19Z</t>
         </is>
       </c>
     </row>
@@ -5337,7 +5337,7 @@
       </c>
       <c r="S60" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03T23:14:13Z</t>
+          <t>2026-10-04T23:25:19Z</t>
         </is>
       </c>
     </row>
@@ -5426,7 +5426,7 @@
       </c>
       <c r="S61" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03T23:14:13Z</t>
+          <t>2026-10-04T23:25:19Z</t>
         </is>
       </c>
     </row>
@@ -5515,7 +5515,7 @@
       </c>
       <c r="S62" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03T23:14:13Z</t>
+          <t>2026-10-04T23:25:19Z</t>
         </is>
       </c>
     </row>
@@ -5604,7 +5604,7 @@
       </c>
       <c r="S63" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03T23:14:13Z</t>
+          <t>2026-10-04T23:25:19Z</t>
         </is>
       </c>
     </row>
@@ -5693,7 +5693,7 @@
       </c>
       <c r="S64" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03T23:14:13Z</t>
+          <t>2026-10-04T23:25:19Z</t>
         </is>
       </c>
     </row>
@@ -5782,7 +5782,7 @@
       </c>
       <c r="S65" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03T23:14:13Z</t>
+          <t>2026-10-04T23:25:19Z</t>
         </is>
       </c>
     </row>
@@ -5871,7 +5871,7 @@
       </c>
       <c r="S66" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03T23:14:13Z</t>
+          <t>2026-10-04T23:25:19Z</t>
         </is>
       </c>
     </row>
@@ -5960,7 +5960,7 @@
       </c>
       <c r="S67" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03T23:14:13Z</t>
+          <t>2026-10-04T23:25:19Z</t>
         </is>
       </c>
     </row>
@@ -6045,7 +6045,7 @@
       </c>
       <c r="S68" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03T23:14:13Z</t>
+          <t>2026-10-04T23:25:19Z</t>
         </is>
       </c>
     </row>
@@ -6130,7 +6130,7 @@
       </c>
       <c r="S69" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03T23:14:13Z</t>
+          <t>2026-10-04T23:25:19Z</t>
         </is>
       </c>
     </row>
@@ -6215,7 +6215,7 @@
       </c>
       <c r="S70" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03T23:14:13Z</t>
+          <t>2026-10-04T23:25:19Z</t>
         </is>
       </c>
     </row>
@@ -6300,7 +6300,7 @@
       </c>
       <c r="S71" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03T23:14:13Z</t>
+          <t>2026-10-04T23:25:19Z</t>
         </is>
       </c>
     </row>
@@ -6385,7 +6385,7 @@
       </c>
       <c r="S72" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03T23:14:13Z</t>
+          <t>2026-10-04T23:25:19Z</t>
         </is>
       </c>
     </row>
@@ -6470,7 +6470,7 @@
       </c>
       <c r="S73" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03T23:14:13Z</t>
+          <t>2026-10-04T23:25:19Z</t>
         </is>
       </c>
     </row>
@@ -6555,7 +6555,7 @@
       </c>
       <c r="S74" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03T23:14:13Z</t>
+          <t>2026-10-04T23:25:19Z</t>
         </is>
       </c>
     </row>
@@ -6640,7 +6640,7 @@
       </c>
       <c r="S75" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03T23:14:13Z</t>
+          <t>2026-10-04T23:25:19Z</t>
         </is>
       </c>
     </row>
@@ -6725,7 +6725,7 @@
       </c>
       <c r="S76" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03T23:14:13Z</t>
+          <t>2026-10-04T23:25:19Z</t>
         </is>
       </c>
     </row>
@@ -6810,7 +6810,7 @@
       </c>
       <c r="S77" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03T23:14:13Z</t>
+          <t>2026-10-04T23:25:19Z</t>
         </is>
       </c>
     </row>
@@ -6895,7 +6895,7 @@
       </c>
       <c r="S78" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03T23:14:13Z</t>
+          <t>2026-10-04T23:25:19Z</t>
         </is>
       </c>
     </row>
@@ -6980,7 +6980,7 @@
       </c>
       <c r="S79" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03T23:14:13Z</t>
+          <t>2026-10-04T23:25:19Z</t>
         </is>
       </c>
     </row>
@@ -7065,7 +7065,7 @@
       </c>
       <c r="S80" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03T23:14:13Z</t>
+          <t>2026-10-04T23:25:19Z</t>
         </is>
       </c>
     </row>
@@ -7150,7 +7150,7 @@
       </c>
       <c r="S81" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03T23:14:13Z</t>
+          <t>2026-10-04T23:25:19Z</t>
         </is>
       </c>
     </row>
@@ -7235,7 +7235,7 @@
       </c>
       <c r="S82" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03T23:14:13Z</t>
+          <t>2026-10-04T23:25:19Z</t>
         </is>
       </c>
     </row>
@@ -7320,7 +7320,7 @@
       </c>
       <c r="S83" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03T23:14:13Z</t>
+          <t>2026-10-04T23:25:19Z</t>
         </is>
       </c>
     </row>
@@ -7405,7 +7405,7 @@
       </c>
       <c r="S84" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03T23:14:13Z</t>
+          <t>2026-10-04T23:25:19Z</t>
         </is>
       </c>
     </row>
@@ -7490,7 +7490,7 @@
       </c>
       <c r="S85" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03T23:14:13Z</t>
+          <t>2026-10-04T23:25:19Z</t>
         </is>
       </c>
     </row>
@@ -7575,7 +7575,7 @@
       </c>
       <c r="S86" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03T23:14:13Z</t>
+          <t>2026-10-04T23:25:19Z</t>
         </is>
       </c>
     </row>
@@ -7660,7 +7660,7 @@
       </c>
       <c r="S87" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03T23:14:13Z</t>
+          <t>2026-10-04T23:25:19Z</t>
         </is>
       </c>
     </row>
@@ -7745,7 +7745,7 @@
       </c>
       <c r="S88" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03T23:14:13Z</t>
+          <t>2026-10-04T23:25:19Z</t>
         </is>
       </c>
     </row>
@@ -7834,7 +7834,7 @@
       </c>
       <c r="S89" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03T23:14:13Z</t>
+          <t>2026-10-04T23:25:19Z</t>
         </is>
       </c>
     </row>
@@ -7923,7 +7923,7 @@
       </c>
       <c r="S90" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03T23:14:13Z</t>
+          <t>2026-10-04T23:25:19Z</t>
         </is>
       </c>
     </row>
@@ -8008,7 +8008,7 @@
       </c>
       <c r="S91" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03T23:14:13Z</t>
+          <t>2026-10-04T23:25:19Z</t>
         </is>
       </c>
     </row>
@@ -8097,7 +8097,7 @@
       </c>
       <c r="S92" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03T23:14:13Z</t>
+          <t>2026-10-04T23:25:19Z</t>
         </is>
       </c>
     </row>
@@ -8186,7 +8186,7 @@
       </c>
       <c r="S93" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03T23:14:13Z</t>
+          <t>2026-10-04T23:25:19Z</t>
         </is>
       </c>
     </row>
@@ -8271,7 +8271,7 @@
       </c>
       <c r="S94" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03T23:14:13Z</t>
+          <t>2026-10-04T23:25:19Z</t>
         </is>
       </c>
     </row>
@@ -8360,7 +8360,7 @@
       </c>
       <c r="S95" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03T23:14:13Z</t>
+          <t>2026-10-04T23:25:19Z</t>
         </is>
       </c>
     </row>
@@ -8449,7 +8449,7 @@
       </c>
       <c r="S96" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03T23:14:13Z</t>
+          <t>2026-10-04T23:25:19Z</t>
         </is>
       </c>
     </row>
@@ -8534,7 +8534,7 @@
       </c>
       <c r="S97" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03T23:14:13Z</t>
+          <t>2026-10-04T23:25:19Z</t>
         </is>
       </c>
     </row>
@@ -8623,7 +8623,7 @@
       </c>
       <c r="S98" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03T23:14:13Z</t>
+          <t>2026-10-04T23:25:19Z</t>
         </is>
       </c>
     </row>
@@ -8712,7 +8712,7 @@
       </c>
       <c r="S99" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03T23:14:13Z</t>
+          <t>2026-10-04T23:25:19Z</t>
         </is>
       </c>
     </row>
@@ -8797,7 +8797,7 @@
       </c>
       <c r="S100" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03T23:14:13Z</t>
+          <t>2026-10-04T23:25:19Z</t>
         </is>
       </c>
     </row>
@@ -8886,7 +8886,7 @@
       </c>
       <c r="S101" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03T23:14:13Z</t>
+          <t>2026-10-04T23:25:19Z</t>
         </is>
       </c>
     </row>
@@ -8975,7 +8975,7 @@
       </c>
       <c r="S102" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03T23:14:13Z</t>
+          <t>2026-10-04T23:25:19Z</t>
         </is>
       </c>
     </row>
@@ -9060,7 +9060,7 @@
       </c>
       <c r="S103" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03T23:14:13Z</t>
+          <t>2026-10-04T23:25:19Z</t>
         </is>
       </c>
     </row>
@@ -9149,7 +9149,7 @@
       </c>
       <c r="S104" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03T23:14:13Z</t>
+          <t>2026-10-04T23:25:19Z</t>
         </is>
       </c>
     </row>
@@ -9238,7 +9238,7 @@
       </c>
       <c r="S105" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03T23:14:13Z</t>
+          <t>2026-10-04T23:25:19Z</t>
         </is>
       </c>
     </row>
@@ -9323,7 +9323,7 @@
       </c>
       <c r="S106" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03T23:14:13Z</t>
+          <t>2026-10-04T23:25:19Z</t>
         </is>
       </c>
     </row>
@@ -9412,7 +9412,7 @@
       </c>
       <c r="S107" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03T23:14:13Z</t>
+          <t>2026-10-04T23:25:19Z</t>
         </is>
       </c>
     </row>
@@ -9501,7 +9501,7 @@
       </c>
       <c r="S108" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03T23:14:13Z</t>
+          <t>2026-10-04T23:25:19Z</t>
         </is>
       </c>
     </row>
@@ -9586,7 +9586,7 @@
       </c>
       <c r="S109" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03T23:14:13Z</t>
+          <t>2026-10-04T23:25:19Z</t>
         </is>
       </c>
     </row>
@@ -9675,7 +9675,7 @@
       </c>
       <c r="S110" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03T23:14:13Z</t>
+          <t>2026-10-04T23:25:19Z</t>
         </is>
       </c>
     </row>
@@ -9764,7 +9764,7 @@
       </c>
       <c r="S111" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03T23:14:13Z</t>
+          <t>2026-10-04T23:25:19Z</t>
         </is>
       </c>
     </row>
@@ -9849,7 +9849,7 @@
       </c>
       <c r="S112" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03T23:14:13Z</t>
+          <t>2026-10-04T23:25:19Z</t>
         </is>
       </c>
     </row>
@@ -9938,7 +9938,7 @@
       </c>
       <c r="S113" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03T23:14:13Z</t>
+          <t>2026-10-04T23:25:19Z</t>
         </is>
       </c>
     </row>
@@ -10027,7 +10027,7 @@
       </c>
       <c r="S114" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03T23:14:13Z</t>
+          <t>2026-10-04T23:25:19Z</t>
         </is>
       </c>
     </row>
@@ -10112,7 +10112,7 @@
       </c>
       <c r="S115" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03T23:14:13Z</t>
+          <t>2026-10-04T23:25:19Z</t>
         </is>
       </c>
     </row>
@@ -10201,7 +10201,7 @@
       </c>
       <c r="S116" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03T23:14:13Z</t>
+          <t>2026-10-04T23:25:19Z</t>
         </is>
       </c>
     </row>
@@ -10290,7 +10290,7 @@
       </c>
       <c r="S117" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03T23:14:13Z</t>
+          <t>2026-10-04T23:25:19Z</t>
         </is>
       </c>
     </row>
@@ -10379,7 +10379,7 @@
       </c>
       <c r="S118" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03T23:14:13Z</t>
+          <t>2026-10-04T23:25:19Z</t>
         </is>
       </c>
     </row>
@@ -10468,7 +10468,7 @@
       </c>
       <c r="S119" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03T23:14:13Z</t>
+          <t>2026-10-04T23:25:19Z</t>
         </is>
       </c>
     </row>
@@ -10557,7 +10557,7 @@
       </c>
       <c r="S120" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03T23:14:13Z</t>
+          <t>2026-10-04T23:25:19Z</t>
         </is>
       </c>
     </row>
@@ -10646,7 +10646,7 @@
       </c>
       <c r="S121" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03T23:14:13Z</t>
+          <t>2026-10-04T23:25:19Z</t>
         </is>
       </c>
     </row>
@@ -10735,7 +10735,7 @@
       </c>
       <c r="S122" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03T23:14:13Z</t>
+          <t>2026-10-04T23:25:19Z</t>
         </is>
       </c>
     </row>
@@ -10824,7 +10824,7 @@
       </c>
       <c r="S123" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03T23:14:13Z</t>
+          <t>2026-10-04T23:25:19Z</t>
         </is>
       </c>
     </row>
@@ -10913,7 +10913,7 @@
       </c>
       <c r="S124" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03T23:14:13Z</t>
+          <t>2026-10-04T23:25:19Z</t>
         </is>
       </c>
     </row>
@@ -11002,7 +11002,7 @@
       </c>
       <c r="S125" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03T23:14:13Z</t>
+          <t>2026-10-04T23:25:19Z</t>
         </is>
       </c>
     </row>
@@ -11091,7 +11091,7 @@
       </c>
       <c r="S126" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03T23:14:13Z</t>
+          <t>2026-10-04T23:25:19Z</t>
         </is>
       </c>
     </row>
@@ -11180,7 +11180,7 @@
       </c>
       <c r="S127" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03T23:14:13Z</t>
+          <t>2026-10-04T23:25:19Z</t>
         </is>
       </c>
     </row>
@@ -11269,7 +11269,7 @@
       </c>
       <c r="S128" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03T23:14:13Z</t>
+          <t>2026-10-04T23:25:19Z</t>
         </is>
       </c>
     </row>
@@ -11354,7 +11354,7 @@
       </c>
       <c r="S129" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03T23:14:13Z</t>
+          <t>2026-10-04T23:25:19Z</t>
         </is>
       </c>
     </row>
@@ -11439,7 +11439,7 @@
       </c>
       <c r="S130" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03T23:14:13Z</t>
+          <t>2026-10-04T23:25:19Z</t>
         </is>
       </c>
     </row>
@@ -11524,7 +11524,7 @@
       </c>
       <c r="S131" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03T23:14:13Z</t>
+          <t>2026-10-04T23:25:19Z</t>
         </is>
       </c>
     </row>
@@ -11609,7 +11609,7 @@
       </c>
       <c r="S132" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03T23:14:13Z</t>
+          <t>2026-10-04T23:25:19Z</t>
         </is>
       </c>
     </row>
@@ -11694,7 +11694,7 @@
       </c>
       <c r="S133" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03T23:14:13Z</t>
+          <t>2026-10-04T23:25:19Z</t>
         </is>
       </c>
     </row>
@@ -11779,7 +11779,7 @@
       </c>
       <c r="S134" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03T23:14:13Z</t>
+          <t>2026-10-04T23:25:19Z</t>
         </is>
       </c>
     </row>
@@ -11864,7 +11864,7 @@
       </c>
       <c r="S135" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03T23:14:13Z</t>
+          <t>2026-10-04T23:25:19Z</t>
         </is>
       </c>
     </row>
@@ -11949,7 +11949,7 @@
       </c>
       <c r="S136" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03T23:14:13Z</t>
+          <t>2026-10-04T23:25:19Z</t>
         </is>
       </c>
     </row>
@@ -12034,7 +12034,7 @@
       </c>
       <c r="S137" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03T23:14:13Z</t>
+          <t>2026-10-04T23:25:19Z</t>
         </is>
       </c>
     </row>
@@ -12119,7 +12119,7 @@
       </c>
       <c r="S138" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03T23:14:13Z</t>
+          <t>2026-10-04T23:25:19Z</t>
         </is>
       </c>
     </row>
@@ -12204,7 +12204,7 @@
       </c>
       <c r="S139" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03T23:14:13Z</t>
+          <t>2026-10-04T23:25:19Z</t>
         </is>
       </c>
     </row>
@@ -12289,7 +12289,7 @@
       </c>
       <c r="S140" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03T23:14:13Z</t>
+          <t>2026-10-04T23:25:19Z</t>
         </is>
       </c>
     </row>
@@ -12374,7 +12374,7 @@
       </c>
       <c r="S141" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03T23:14:13Z</t>
+          <t>2026-10-04T23:25:19Z</t>
         </is>
       </c>
     </row>
@@ -12459,7 +12459,7 @@
       </c>
       <c r="S142" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03T23:14:13Z</t>
+          <t>2026-10-04T23:25:19Z</t>
         </is>
       </c>
     </row>
@@ -12544,7 +12544,7 @@
       </c>
       <c r="S143" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03T23:14:13Z</t>
+          <t>2026-10-04T23:25:19Z</t>
         </is>
       </c>
     </row>
@@ -12629,7 +12629,7 @@
       </c>
       <c r="S144" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03T23:14:13Z</t>
+          <t>2026-10-04T23:25:19Z</t>
         </is>
       </c>
     </row>
@@ -12714,7 +12714,7 @@
       </c>
       <c r="S145" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03T23:14:13Z</t>
+          <t>2026-10-04T23:25:19Z</t>
         </is>
       </c>
     </row>
@@ -12799,7 +12799,7 @@
       </c>
       <c r="S146" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03T23:14:13Z</t>
+          <t>2026-10-04T23:25:19Z</t>
         </is>
       </c>
     </row>
@@ -12884,7 +12884,7 @@
       </c>
       <c r="S147" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03T23:14:13Z</t>
+          <t>2026-10-04T23:25:19Z</t>
         </is>
       </c>
     </row>
@@ -12969,7 +12969,7 @@
       </c>
       <c r="S148" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03T23:14:13Z</t>
+          <t>2026-10-04T23:25:19Z</t>
         </is>
       </c>
     </row>
@@ -13054,7 +13054,7 @@
       </c>
       <c r="S149" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03T23:14:13Z</t>
+          <t>2026-10-04T23:25:19Z</t>
         </is>
       </c>
     </row>
@@ -13143,7 +13143,7 @@
       </c>
       <c r="S150" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03T23:14:13Z</t>
+          <t>2026-10-04T23:25:19Z</t>
         </is>
       </c>
     </row>
@@ -13232,7 +13232,7 @@
       </c>
       <c r="S151" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03T23:14:13Z</t>
+          <t>2026-10-04T23:25:19Z</t>
         </is>
       </c>
     </row>
@@ -13317,7 +13317,7 @@
       </c>
       <c r="S152" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03T23:14:13Z</t>
+          <t>2026-10-04T23:25:19Z</t>
         </is>
       </c>
     </row>
@@ -13406,7 +13406,7 @@
       </c>
       <c r="S153" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03T23:14:13Z</t>
+          <t>2026-10-04T23:25:19Z</t>
         </is>
       </c>
     </row>
@@ -13495,7 +13495,7 @@
       </c>
       <c r="S154" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03T23:14:13Z</t>
+          <t>2026-10-04T23:25:19Z</t>
         </is>
       </c>
     </row>
@@ -13580,7 +13580,7 @@
       </c>
       <c r="S155" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03T23:14:13Z</t>
+          <t>2026-10-04T23:25:19Z</t>
         </is>
       </c>
     </row>
@@ -13669,7 +13669,7 @@
       </c>
       <c r="S156" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03T23:14:13Z</t>
+          <t>2026-10-04T23:25:19Z</t>
         </is>
       </c>
     </row>
@@ -13758,7 +13758,7 @@
       </c>
       <c r="S157" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03T23:14:13Z</t>
+          <t>2026-10-04T23:25:19Z</t>
         </is>
       </c>
     </row>
@@ -13843,7 +13843,7 @@
       </c>
       <c r="S158" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03T23:14:13Z</t>
+          <t>2026-10-04T23:25:19Z</t>
         </is>
       </c>
     </row>
@@ -13932,7 +13932,7 @@
       </c>
       <c r="S159" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03T23:14:13Z</t>
+          <t>2026-10-04T23:25:19Z</t>
         </is>
       </c>
     </row>
@@ -14021,7 +14021,7 @@
       </c>
       <c r="S160" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03T23:14:13Z</t>
+          <t>2026-10-04T23:25:19Z</t>
         </is>
       </c>
     </row>
@@ -14106,7 +14106,7 @@
       </c>
       <c r="S161" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03T23:14:13Z</t>
+          <t>2026-10-04T23:25:19Z</t>
         </is>
       </c>
     </row>
@@ -14195,7 +14195,7 @@
       </c>
       <c r="S162" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03T23:14:13Z</t>
+          <t>2026-10-04T23:25:19Z</t>
         </is>
       </c>
     </row>
@@ -14284,7 +14284,7 @@
       </c>
       <c r="S163" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03T23:14:13Z</t>
+          <t>2026-10-04T23:25:19Z</t>
         </is>
       </c>
     </row>
@@ -14369,7 +14369,7 @@
       </c>
       <c r="S164" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03T23:14:13Z</t>
+          <t>2026-10-04T23:25:19Z</t>
         </is>
       </c>
     </row>
@@ -14458,7 +14458,7 @@
       </c>
       <c r="S165" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03T23:14:13Z</t>
+          <t>2026-10-04T23:25:19Z</t>
         </is>
       </c>
     </row>
@@ -14547,7 +14547,7 @@
       </c>
       <c r="S166" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03T23:14:13Z</t>
+          <t>2026-10-04T23:25:19Z</t>
         </is>
       </c>
     </row>
@@ -14632,7 +14632,7 @@
       </c>
       <c r="S167" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03T23:14:13Z</t>
+          <t>2026-10-04T23:25:19Z</t>
         </is>
       </c>
     </row>
@@ -14721,7 +14721,7 @@
       </c>
       <c r="S168" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03T23:14:13Z</t>
+          <t>2026-10-04T23:25:19Z</t>
         </is>
       </c>
     </row>
@@ -14810,7 +14810,7 @@
       </c>
       <c r="S169" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03T23:14:13Z</t>
+          <t>2026-10-04T23:25:19Z</t>
         </is>
       </c>
     </row>
@@ -14895,7 +14895,7 @@
       </c>
       <c r="S170" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03T23:14:13Z</t>
+          <t>2026-10-04T23:25:19Z</t>
         </is>
       </c>
     </row>
@@ -14984,7 +14984,7 @@
       </c>
       <c r="S171" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03T23:14:13Z</t>
+          <t>2026-10-04T23:25:19Z</t>
         </is>
       </c>
     </row>
@@ -15073,7 +15073,7 @@
       </c>
       <c r="S172" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03T23:14:13Z</t>
+          <t>2026-10-04T23:25:19Z</t>
         </is>
       </c>
     </row>
@@ -15158,7 +15158,7 @@
       </c>
       <c r="S173" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03T23:14:13Z</t>
+          <t>2026-10-04T23:25:19Z</t>
         </is>
       </c>
     </row>
@@ -15247,7 +15247,7 @@
       </c>
       <c r="S174" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03T23:14:13Z</t>
+          <t>2026-10-04T23:25:19Z</t>
         </is>
       </c>
     </row>
@@ -15336,7 +15336,7 @@
       </c>
       <c r="S175" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03T23:14:13Z</t>
+          <t>2026-10-04T23:25:19Z</t>
         </is>
       </c>
     </row>
@@ -15421,7 +15421,7 @@
       </c>
       <c r="S176" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03T23:14:13Z</t>
+          <t>2026-10-04T23:25:19Z</t>
         </is>
       </c>
     </row>
@@ -15510,7 +15510,7 @@
       </c>
       <c r="S177" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03T23:14:13Z</t>
+          <t>2026-10-04T23:25:19Z</t>
         </is>
       </c>
     </row>
@@ -15599,7 +15599,7 @@
       </c>
       <c r="S178" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03T23:14:13Z</t>
+          <t>2026-10-04T23:25:19Z</t>
         </is>
       </c>
     </row>
@@ -15688,7 +15688,7 @@
       </c>
       <c r="S179" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03T23:14:13Z</t>
+          <t>2026-10-04T23:25:19Z</t>
         </is>
       </c>
     </row>
@@ -15777,7 +15777,7 @@
       </c>
       <c r="S180" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03T23:14:13Z</t>
+          <t>2026-10-04T23:25:19Z</t>
         </is>
       </c>
     </row>
@@ -15866,7 +15866,7 @@
       </c>
       <c r="S181" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03T23:14:13Z</t>
+          <t>2026-10-04T23:25:19Z</t>
         </is>
       </c>
     </row>
@@ -15955,7 +15955,7 @@
       </c>
       <c r="S182" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03T23:14:13Z</t>
+          <t>2026-10-04T23:25:19Z</t>
         </is>
       </c>
     </row>
@@ -16044,7 +16044,7 @@
       </c>
       <c r="S183" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03T23:14:13Z</t>
+          <t>2026-10-04T23:25:19Z</t>
         </is>
       </c>
     </row>
@@ -16133,7 +16133,7 @@
       </c>
       <c r="S184" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03T23:14:13Z</t>
+          <t>2026-10-04T23:25:19Z</t>
         </is>
       </c>
     </row>
@@ -16222,7 +16222,7 @@
       </c>
       <c r="S185" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03T23:14:13Z</t>
+          <t>2026-10-04T23:25:19Z</t>
         </is>
       </c>
     </row>
@@ -16311,7 +16311,7 @@
       </c>
       <c r="S186" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03T23:14:13Z</t>
+          <t>2026-10-04T23:25:19Z</t>
         </is>
       </c>
     </row>
@@ -16400,7 +16400,7 @@
       </c>
       <c r="S187" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03T23:14:13Z</t>
+          <t>2026-10-04T23:25:19Z</t>
         </is>
       </c>
     </row>
@@ -16489,7 +16489,7 @@
       </c>
       <c r="S188" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03T23:14:13Z</t>
+          <t>2026-10-04T23:25:19Z</t>
         </is>
       </c>
     </row>
@@ -16578,7 +16578,7 @@
       </c>
       <c r="S189" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03T23:14:13Z</t>
+          <t>2026-10-04T23:25:19Z</t>
         </is>
       </c>
     </row>
@@ -16663,7 +16663,7 @@
       </c>
       <c r="S190" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03T23:14:13Z</t>
+          <t>2026-10-04T23:25:19Z</t>
         </is>
       </c>
     </row>
@@ -16748,7 +16748,7 @@
       </c>
       <c r="S191" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03T23:14:13Z</t>
+          <t>2026-10-04T23:25:19Z</t>
         </is>
       </c>
     </row>
@@ -16833,7 +16833,7 @@
       </c>
       <c r="S192" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03T23:14:13Z</t>
+          <t>2026-10-04T23:25:19Z</t>
         </is>
       </c>
     </row>
@@ -16918,7 +16918,7 @@
       </c>
       <c r="S193" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03T23:14:13Z</t>
+          <t>2026-10-04T23:25:19Z</t>
         </is>
       </c>
     </row>
@@ -17003,7 +17003,7 @@
       </c>
       <c r="S194" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03T23:14:13Z</t>
+          <t>2026-10-04T23:25:19Z</t>
         </is>
       </c>
     </row>
@@ -17088,7 +17088,7 @@
       </c>
       <c r="S195" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03T23:14:13Z</t>
+          <t>2026-10-04T23:25:19Z</t>
         </is>
       </c>
     </row>
@@ -17173,7 +17173,7 @@
       </c>
       <c r="S196" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03T23:14:13Z</t>
+          <t>2026-10-04T23:25:19Z</t>
         </is>
       </c>
     </row>
@@ -17258,7 +17258,7 @@
       </c>
       <c r="S197" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03T23:14:13Z</t>
+          <t>2026-10-04T23:25:19Z</t>
         </is>
       </c>
     </row>
@@ -17343,7 +17343,7 @@
       </c>
       <c r="S198" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03T23:14:13Z</t>
+          <t>2026-10-04T23:25:19Z</t>
         </is>
       </c>
     </row>
@@ -17428,7 +17428,7 @@
       </c>
       <c r="S199" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03T23:14:13Z</t>
+          <t>2026-10-04T23:25:19Z</t>
         </is>
       </c>
     </row>
@@ -17513,7 +17513,7 @@
       </c>
       <c r="S200" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03T23:14:13Z</t>
+          <t>2026-10-04T23:25:19Z</t>
         </is>
       </c>
     </row>
@@ -17598,7 +17598,7 @@
       </c>
       <c r="S201" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03T23:14:13Z</t>
+          <t>2026-10-04T23:25:19Z</t>
         </is>
       </c>
     </row>
@@ -17683,7 +17683,7 @@
       </c>
       <c r="S202" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03T23:14:13Z</t>
+          <t>2026-10-04T23:25:19Z</t>
         </is>
       </c>
     </row>
@@ -17768,7 +17768,7 @@
       </c>
       <c r="S203" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03T23:14:13Z</t>
+          <t>2026-10-04T23:25:19Z</t>
         </is>
       </c>
     </row>
@@ -17853,7 +17853,7 @@
       </c>
       <c r="S204" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03T23:14:13Z</t>
+          <t>2026-10-04T23:25:19Z</t>
         </is>
       </c>
     </row>
@@ -17938,7 +17938,7 @@
       </c>
       <c r="S205" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03T23:14:13Z</t>
+          <t>2026-10-04T23:25:19Z</t>
         </is>
       </c>
     </row>
@@ -18023,7 +18023,7 @@
       </c>
       <c r="S206" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03T23:14:13Z</t>
+          <t>2026-10-04T23:25:19Z</t>
         </is>
       </c>
     </row>
@@ -18108,7 +18108,7 @@
       </c>
       <c r="S207" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03T23:14:13Z</t>
+          <t>2026-10-04T23:25:19Z</t>
         </is>
       </c>
     </row>
@@ -18193,7 +18193,7 @@
       </c>
       <c r="S208" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03T23:14:13Z</t>
+          <t>2026-10-04T23:25:19Z</t>
         </is>
       </c>
     </row>
@@ -18278,7 +18278,7 @@
       </c>
       <c r="S209" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03T23:14:13Z</t>
+          <t>2026-10-04T23:25:19Z</t>
         </is>
       </c>
     </row>
@@ -18363,7 +18363,7 @@
       </c>
       <c r="S210" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03T23:14:13Z</t>
+          <t>2026-10-04T23:25:19Z</t>
         </is>
       </c>
     </row>
@@ -18452,7 +18452,7 @@
       </c>
       <c r="S211" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03T23:14:13Z</t>
+          <t>2026-10-04T23:25:19Z</t>
         </is>
       </c>
     </row>
@@ -18541,7 +18541,7 @@
       </c>
       <c r="S212" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03T23:14:13Z</t>
+          <t>2026-10-04T23:25:19Z</t>
         </is>
       </c>
     </row>
@@ -18626,7 +18626,7 @@
       </c>
       <c r="S213" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03T23:14:13Z</t>
+          <t>2026-10-04T23:25:19Z</t>
         </is>
       </c>
     </row>
@@ -18715,7 +18715,7 @@
       </c>
       <c r="S214" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03T23:14:13Z</t>
+          <t>2026-10-04T23:25:19Z</t>
         </is>
       </c>
     </row>
@@ -18804,7 +18804,7 @@
       </c>
       <c r="S215" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03T23:14:13Z</t>
+          <t>2026-10-04T23:25:19Z</t>
         </is>
       </c>
     </row>
@@ -18889,7 +18889,7 @@
       </c>
       <c r="S216" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03T23:14:13Z</t>
+          <t>2026-10-04T23:25:19Z</t>
         </is>
       </c>
     </row>
@@ -18978,7 +18978,7 @@
       </c>
       <c r="S217" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03T23:14:13Z</t>
+          <t>2026-10-04T23:25:19Z</t>
         </is>
       </c>
     </row>
@@ -19067,7 +19067,7 @@
       </c>
       <c r="S218" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03T23:14:13Z</t>
+          <t>2026-10-04T23:25:19Z</t>
         </is>
       </c>
     </row>
@@ -19152,7 +19152,7 @@
       </c>
       <c r="S219" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03T23:14:13Z</t>
+          <t>2026-10-04T23:25:19Z</t>
         </is>
       </c>
     </row>
@@ -19241,7 +19241,7 @@
       </c>
       <c r="S220" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03T23:14:13Z</t>
+          <t>2026-10-04T23:25:19Z</t>
         </is>
       </c>
     </row>
@@ -19330,7 +19330,7 @@
       </c>
       <c r="S221" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03T23:14:13Z</t>
+          <t>2026-10-04T23:25:19Z</t>
         </is>
       </c>
     </row>
@@ -19415,7 +19415,7 @@
       </c>
       <c r="S222" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03T23:14:13Z</t>
+          <t>2026-10-04T23:25:19Z</t>
         </is>
       </c>
     </row>
@@ -19504,7 +19504,7 @@
       </c>
       <c r="S223" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03T23:14:13Z</t>
+          <t>2026-10-04T23:25:19Z</t>
         </is>
       </c>
     </row>
@@ -19593,7 +19593,7 @@
       </c>
       <c r="S224" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03T23:14:13Z</t>
+          <t>2026-10-04T23:25:19Z</t>
         </is>
       </c>
     </row>
@@ -19678,7 +19678,7 @@
       </c>
       <c r="S225" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03T23:14:13Z</t>
+          <t>2026-10-04T23:25:19Z</t>
         </is>
       </c>
     </row>
@@ -19767,7 +19767,7 @@
       </c>
       <c r="S226" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03T23:14:13Z</t>
+          <t>2026-10-04T23:25:19Z</t>
         </is>
       </c>
     </row>
@@ -19856,7 +19856,7 @@
       </c>
       <c r="S227" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03T23:14:13Z</t>
+          <t>2026-10-04T23:25:19Z</t>
         </is>
       </c>
     </row>
@@ -19941,7 +19941,7 @@
       </c>
       <c r="S228" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03T23:14:13Z</t>
+          <t>2026-10-04T23:25:19Z</t>
         </is>
       </c>
     </row>
@@ -20030,7 +20030,7 @@
       </c>
       <c r="S229" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03T23:14:13Z</t>
+          <t>2026-10-04T23:25:19Z</t>
         </is>
       </c>
     </row>
@@ -20119,7 +20119,7 @@
       </c>
       <c r="S230" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03T23:14:13Z</t>
+          <t>2026-10-04T23:25:19Z</t>
         </is>
       </c>
     </row>
@@ -20204,7 +20204,7 @@
       </c>
       <c r="S231" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03T23:14:13Z</t>
+          <t>2026-10-04T23:25:19Z</t>
         </is>
       </c>
     </row>
@@ -20293,7 +20293,7 @@
       </c>
       <c r="S232" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03T23:14:13Z</t>
+          <t>2026-10-04T23:25:19Z</t>
         </is>
       </c>
     </row>
@@ -20382,7 +20382,7 @@
       </c>
       <c r="S233" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03T23:14:13Z</t>
+          <t>2026-10-04T23:25:19Z</t>
         </is>
       </c>
     </row>
@@ -20467,7 +20467,7 @@
       </c>
       <c r="S234" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03T23:14:13Z</t>
+          <t>2026-10-04T23:25:19Z</t>
         </is>
       </c>
     </row>
@@ -20556,7 +20556,7 @@
       </c>
       <c r="S235" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03T23:14:13Z</t>
+          <t>2026-10-04T23:25:19Z</t>
         </is>
       </c>
     </row>
@@ -20645,7 +20645,7 @@
       </c>
       <c r="S236" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03T23:14:13Z</t>
+          <t>2026-10-04T23:25:19Z</t>
         </is>
       </c>
     </row>
@@ -20730,7 +20730,7 @@
       </c>
       <c r="S237" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03T23:14:13Z</t>
+          <t>2026-10-04T23:25:19Z</t>
         </is>
       </c>
     </row>
@@ -20819,7 +20819,7 @@
       </c>
       <c r="S238" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03T23:14:13Z</t>
+          <t>2026-10-04T23:25:19Z</t>
         </is>
       </c>
     </row>
@@ -20908,7 +20908,7 @@
       </c>
       <c r="S239" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03T23:14:13Z</t>
+          <t>2026-10-04T23:25:19Z</t>
         </is>
       </c>
     </row>
@@ -20997,7 +20997,7 @@
       </c>
       <c r="S240" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03T23:14:13Z</t>
+          <t>2026-10-04T23:25:19Z</t>
         </is>
       </c>
     </row>
@@ -21086,7 +21086,7 @@
       </c>
       <c r="S241" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03T23:14:13Z</t>
+          <t>2026-10-04T23:25:19Z</t>
         </is>
       </c>
     </row>
@@ -21175,7 +21175,7 @@
       </c>
       <c r="S242" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03T23:14:13Z</t>
+          <t>2026-10-04T23:25:19Z</t>
         </is>
       </c>
     </row>
@@ -21264,7 +21264,7 @@
       </c>
       <c r="S243" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03T23:14:13Z</t>
+          <t>2026-10-04T23:25:19Z</t>
         </is>
       </c>
     </row>
@@ -21353,7 +21353,7 @@
       </c>
       <c r="S244" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03T23:14:13Z</t>
+          <t>2026-10-04T23:25:19Z</t>
         </is>
       </c>
     </row>
@@ -21442,7 +21442,7 @@
       </c>
       <c r="S245" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03T23:14:13Z</t>
+          <t>2026-10-04T23:25:19Z</t>
         </is>
       </c>
     </row>
@@ -21531,7 +21531,7 @@
       </c>
       <c r="S246" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03T23:14:13Z</t>
+          <t>2026-10-04T23:25:19Z</t>
         </is>
       </c>
     </row>
@@ -21620,7 +21620,7 @@
       </c>
       <c r="S247" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03T23:14:13Z</t>
+          <t>2026-10-04T23:25:19Z</t>
         </is>
       </c>
     </row>
@@ -21709,7 +21709,7 @@
       </c>
       <c r="S248" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03T23:14:13Z</t>
+          <t>2026-10-04T23:25:19Z</t>
         </is>
       </c>
     </row>
@@ -21798,7 +21798,7 @@
       </c>
       <c r="S249" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03T23:14:13Z</t>
+          <t>2026-10-04T23:25:19Z</t>
         </is>
       </c>
     </row>
@@ -21887,7 +21887,7 @@
       </c>
       <c r="S250" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03T23:14:13Z</t>
+          <t>2026-10-04T23:25:19Z</t>
         </is>
       </c>
     </row>
@@ -22019,7 +22019,7 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03T23:14:13Z</t>
+          <t>2026-10-04T23:25:19Z</t>
         </is>
       </c>
     </row>
@@ -22099,7 +22099,7 @@
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>{"dataset_id": "bcv_pib_sector_institucional_anual", "title": "Producto interno bruto por sector institucional anual", "table": "Variaciones porcentuales", "source_file": "5_2_1_si_anual.xlsx", "base": "2007", "price_type": "Precios constantes", "measure": "Variación porcentual interanual", "frequency": "Anual", "period": "2025", "year": 2025, "quarter": null, "classification": "Sector institucional", "component": "Impuestos netos sobre los productos", "value": 10.600260421283764, "unit": "Porcentaje", "status": "Preliminar", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/cuentas_macroeconomicas/5_2_1_si_anual.xlsx", "fetched_at": "2026-10-03T23:14:13Z"}</t>
+          <t>{"dataset_id": "bcv_pib_sector_institucional_anual", "title": "Producto interno bruto por sector institucional anual", "table": "Variaciones porcentuales", "source_file": "5_2_1_si_anual.xlsx", "base": "2007", "price_type": "Precios constantes", "measure": "Variación porcentual interanual", "frequency": "Anual", "period": "2025", "year": 2025, "quarter": null, "classification": "Sector institucional", "component": "Impuestos netos sobre los productos", "value": 10.600260421283764, "unit": "Porcentaje", "status": "Preliminar", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/cuentas_macroeconomicas/5_2_1_si_anual.xlsx", "fetched_at": "2026-10-04T23:25:19Z"}</t>
         </is>
       </c>
     </row>

--- a/assets/data/bcv/excel/ove_bcv_pib_sector_institucional_anual.xlsx
+++ b/assets/data/bcv/excel/ove_bcv_pib_sector_institucional_anual.xlsx
@@ -736,7 +736,7 @@
       </c>
       <c r="S7" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04T23:25:19Z</t>
+          <t>2026-10-06T01:22:21Z</t>
         </is>
       </c>
     </row>
@@ -821,7 +821,7 @@
       </c>
       <c r="S8" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04T23:25:19Z</t>
+          <t>2026-10-06T01:22:21Z</t>
         </is>
       </c>
     </row>
@@ -906,7 +906,7 @@
       </c>
       <c r="S9" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04T23:25:19Z</t>
+          <t>2026-10-06T01:22:21Z</t>
         </is>
       </c>
     </row>
@@ -991,7 +991,7 @@
       </c>
       <c r="S10" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04T23:25:19Z</t>
+          <t>2026-10-06T01:22:21Z</t>
         </is>
       </c>
     </row>
@@ -1076,7 +1076,7 @@
       </c>
       <c r="S11" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04T23:25:19Z</t>
+          <t>2026-10-06T01:22:21Z</t>
         </is>
       </c>
     </row>
@@ -1161,7 +1161,7 @@
       </c>
       <c r="S12" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04T23:25:19Z</t>
+          <t>2026-10-06T01:22:21Z</t>
         </is>
       </c>
     </row>
@@ -1246,7 +1246,7 @@
       </c>
       <c r="S13" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04T23:25:19Z</t>
+          <t>2026-10-06T01:22:21Z</t>
         </is>
       </c>
     </row>
@@ -1331,7 +1331,7 @@
       </c>
       <c r="S14" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04T23:25:19Z</t>
+          <t>2026-10-06T01:22:21Z</t>
         </is>
       </c>
     </row>
@@ -1416,7 +1416,7 @@
       </c>
       <c r="S15" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04T23:25:19Z</t>
+          <t>2026-10-06T01:22:21Z</t>
         </is>
       </c>
     </row>
@@ -1501,7 +1501,7 @@
       </c>
       <c r="S16" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04T23:25:19Z</t>
+          <t>2026-10-06T01:22:21Z</t>
         </is>
       </c>
     </row>
@@ -1586,7 +1586,7 @@
       </c>
       <c r="S17" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04T23:25:19Z</t>
+          <t>2026-10-06T01:22:21Z</t>
         </is>
       </c>
     </row>
@@ -1671,7 +1671,7 @@
       </c>
       <c r="S18" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04T23:25:19Z</t>
+          <t>2026-10-06T01:22:21Z</t>
         </is>
       </c>
     </row>
@@ -1756,7 +1756,7 @@
       </c>
       <c r="S19" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04T23:25:19Z</t>
+          <t>2026-10-06T01:22:21Z</t>
         </is>
       </c>
     </row>
@@ -1841,7 +1841,7 @@
       </c>
       <c r="S20" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04T23:25:19Z</t>
+          <t>2026-10-06T01:22:21Z</t>
         </is>
       </c>
     </row>
@@ -1926,7 +1926,7 @@
       </c>
       <c r="S21" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04T23:25:19Z</t>
+          <t>2026-10-06T01:22:21Z</t>
         </is>
       </c>
     </row>
@@ -2011,7 +2011,7 @@
       </c>
       <c r="S22" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04T23:25:19Z</t>
+          <t>2026-10-06T01:22:21Z</t>
         </is>
       </c>
     </row>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="S23" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04T23:25:19Z</t>
+          <t>2026-10-06T01:22:21Z</t>
         </is>
       </c>
     </row>
@@ -2181,7 +2181,7 @@
       </c>
       <c r="S24" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04T23:25:19Z</t>
+          <t>2026-10-06T01:22:21Z</t>
         </is>
       </c>
     </row>
@@ -2266,7 +2266,7 @@
       </c>
       <c r="S25" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04T23:25:19Z</t>
+          <t>2026-10-06T01:22:21Z</t>
         </is>
       </c>
     </row>
@@ -2351,7 +2351,7 @@
       </c>
       <c r="S26" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04T23:25:19Z</t>
+          <t>2026-10-06T01:22:21Z</t>
         </is>
       </c>
     </row>
@@ -2436,7 +2436,7 @@
       </c>
       <c r="S27" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04T23:25:19Z</t>
+          <t>2026-10-06T01:22:21Z</t>
         </is>
       </c>
     </row>
@@ -2525,7 +2525,7 @@
       </c>
       <c r="S28" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04T23:25:19Z</t>
+          <t>2026-10-06T01:22:21Z</t>
         </is>
       </c>
     </row>
@@ -2614,7 +2614,7 @@
       </c>
       <c r="S29" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04T23:25:19Z</t>
+          <t>2026-10-06T01:22:21Z</t>
         </is>
       </c>
     </row>
@@ -2699,7 +2699,7 @@
       </c>
       <c r="S30" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04T23:25:19Z</t>
+          <t>2026-10-06T01:22:21Z</t>
         </is>
       </c>
     </row>
@@ -2788,7 +2788,7 @@
       </c>
       <c r="S31" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04T23:25:19Z</t>
+          <t>2026-10-06T01:22:21Z</t>
         </is>
       </c>
     </row>
@@ -2877,7 +2877,7 @@
       </c>
       <c r="S32" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04T23:25:19Z</t>
+          <t>2026-10-06T01:22:21Z</t>
         </is>
       </c>
     </row>
@@ -2962,7 +2962,7 @@
       </c>
       <c r="S33" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04T23:25:19Z</t>
+          <t>2026-10-06T01:22:21Z</t>
         </is>
       </c>
     </row>
@@ -3051,7 +3051,7 @@
       </c>
       <c r="S34" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04T23:25:19Z</t>
+          <t>2026-10-06T01:22:21Z</t>
         </is>
       </c>
     </row>
@@ -3140,7 +3140,7 @@
       </c>
       <c r="S35" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04T23:25:19Z</t>
+          <t>2026-10-06T01:22:21Z</t>
         </is>
       </c>
     </row>
@@ -3225,7 +3225,7 @@
       </c>
       <c r="S36" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04T23:25:19Z</t>
+          <t>2026-10-06T01:22:21Z</t>
         </is>
       </c>
     </row>
@@ -3314,7 +3314,7 @@
       </c>
       <c r="S37" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04T23:25:19Z</t>
+          <t>2026-10-06T01:22:21Z</t>
         </is>
       </c>
     </row>
@@ -3403,7 +3403,7 @@
       </c>
       <c r="S38" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04T23:25:19Z</t>
+          <t>2026-10-06T01:22:21Z</t>
         </is>
       </c>
     </row>
@@ -3488,7 +3488,7 @@
       </c>
       <c r="S39" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04T23:25:19Z</t>
+          <t>2026-10-06T01:22:21Z</t>
         </is>
       </c>
     </row>
@@ -3577,7 +3577,7 @@
       </c>
       <c r="S40" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04T23:25:19Z</t>
+          <t>2026-10-06T01:22:21Z</t>
         </is>
       </c>
     </row>
@@ -3666,7 +3666,7 @@
       </c>
       <c r="S41" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04T23:25:19Z</t>
+          <t>2026-10-06T01:22:21Z</t>
         </is>
       </c>
     </row>
@@ -3751,7 +3751,7 @@
       </c>
       <c r="S42" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04T23:25:19Z</t>
+          <t>2026-10-06T01:22:21Z</t>
         </is>
       </c>
     </row>
@@ -3840,7 +3840,7 @@
       </c>
       <c r="S43" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04T23:25:19Z</t>
+          <t>2026-10-06T01:22:21Z</t>
         </is>
       </c>
     </row>
@@ -3929,7 +3929,7 @@
       </c>
       <c r="S44" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04T23:25:19Z</t>
+          <t>2026-10-06T01:22:21Z</t>
         </is>
       </c>
     </row>
@@ -4014,7 +4014,7 @@
       </c>
       <c r="S45" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04T23:25:19Z</t>
+          <t>2026-10-06T01:22:21Z</t>
         </is>
       </c>
     </row>
@@ -4103,7 +4103,7 @@
       </c>
       <c r="S46" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04T23:25:19Z</t>
+          <t>2026-10-06T01:22:21Z</t>
         </is>
       </c>
     </row>
@@ -4192,7 +4192,7 @@
       </c>
       <c r="S47" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04T23:25:19Z</t>
+          <t>2026-10-06T01:22:21Z</t>
         </is>
       </c>
     </row>
@@ -4277,7 +4277,7 @@
       </c>
       <c r="S48" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04T23:25:19Z</t>
+          <t>2026-10-06T01:22:21Z</t>
         </is>
       </c>
     </row>
@@ -4366,7 +4366,7 @@
       </c>
       <c r="S49" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04T23:25:19Z</t>
+          <t>2026-10-06T01:22:21Z</t>
         </is>
       </c>
     </row>
@@ -4455,7 +4455,7 @@
       </c>
       <c r="S50" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04T23:25:19Z</t>
+          <t>2026-10-06T01:22:21Z</t>
         </is>
       </c>
     </row>
@@ -4540,7 +4540,7 @@
       </c>
       <c r="S51" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04T23:25:19Z</t>
+          <t>2026-10-06T01:22:21Z</t>
         </is>
       </c>
     </row>
@@ -4629,7 +4629,7 @@
       </c>
       <c r="S52" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04T23:25:19Z</t>
+          <t>2026-10-06T01:22:21Z</t>
         </is>
       </c>
     </row>
@@ -4718,7 +4718,7 @@
       </c>
       <c r="S53" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04T23:25:19Z</t>
+          <t>2026-10-06T01:22:21Z</t>
         </is>
       </c>
     </row>
@@ -4803,7 +4803,7 @@
       </c>
       <c r="S54" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04T23:25:19Z</t>
+          <t>2026-10-06T01:22:21Z</t>
         </is>
       </c>
     </row>
@@ -4892,7 +4892,7 @@
       </c>
       <c r="S55" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04T23:25:19Z</t>
+          <t>2026-10-06T01:22:21Z</t>
         </is>
       </c>
     </row>
@@ -4981,7 +4981,7 @@
       </c>
       <c r="S56" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04T23:25:19Z</t>
+          <t>2026-10-06T01:22:21Z</t>
         </is>
       </c>
     </row>
@@ -5070,7 +5070,7 @@
       </c>
       <c r="S57" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04T23:25:19Z</t>
+          <t>2026-10-06T01:22:21Z</t>
         </is>
       </c>
     </row>
@@ -5159,7 +5159,7 @@
       </c>
       <c r="S58" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04T23:25:19Z</t>
+          <t>2026-10-06T01:22:21Z</t>
         </is>
       </c>
     </row>
@@ -5248,7 +5248,7 @@
       </c>
       <c r="S59" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04T23:25:19Z</t>
+          <t>2026-10-06T01:22:21Z</t>
         </is>
       </c>
     </row>
@@ -5337,7 +5337,7 @@
       </c>
       <c r="S60" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04T23:25:19Z</t>
+          <t>2026-10-06T01:22:21Z</t>
         </is>
       </c>
     </row>
@@ -5426,7 +5426,7 @@
       </c>
       <c r="S61" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04T23:25:19Z</t>
+          <t>2026-10-06T01:22:21Z</t>
         </is>
       </c>
     </row>
@@ -5515,7 +5515,7 @@
       </c>
       <c r="S62" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04T23:25:19Z</t>
+          <t>2026-10-06T01:22:21Z</t>
         </is>
       </c>
     </row>
@@ -5604,7 +5604,7 @@
       </c>
       <c r="S63" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04T23:25:19Z</t>
+          <t>2026-10-06T01:22:21Z</t>
         </is>
       </c>
     </row>
@@ -5693,7 +5693,7 @@
       </c>
       <c r="S64" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04T23:25:19Z</t>
+          <t>2026-10-06T01:22:21Z</t>
         </is>
       </c>
     </row>
@@ -5782,7 +5782,7 @@
       </c>
       <c r="S65" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04T23:25:19Z</t>
+          <t>2026-10-06T01:22:21Z</t>
         </is>
       </c>
     </row>
@@ -5871,7 +5871,7 @@
       </c>
       <c r="S66" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04T23:25:19Z</t>
+          <t>2026-10-06T01:22:21Z</t>
         </is>
       </c>
     </row>
@@ -5960,7 +5960,7 @@
       </c>
       <c r="S67" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04T23:25:19Z</t>
+          <t>2026-10-06T01:22:21Z</t>
         </is>
       </c>
     </row>
@@ -6045,7 +6045,7 @@
       </c>
       <c r="S68" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04T23:25:19Z</t>
+          <t>2026-10-06T01:22:21Z</t>
         </is>
       </c>
     </row>
@@ -6130,7 +6130,7 @@
       </c>
       <c r="S69" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04T23:25:19Z</t>
+          <t>2026-10-06T01:22:21Z</t>
         </is>
       </c>
     </row>
@@ -6215,7 +6215,7 @@
       </c>
       <c r="S70" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04T23:25:19Z</t>
+          <t>2026-10-06T01:22:21Z</t>
         </is>
       </c>
     </row>
@@ -6300,7 +6300,7 @@
       </c>
       <c r="S71" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04T23:25:19Z</t>
+          <t>2026-10-06T01:22:21Z</t>
         </is>
       </c>
     </row>
@@ -6385,7 +6385,7 @@
       </c>
       <c r="S72" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04T23:25:19Z</t>
+          <t>2026-10-06T01:22:21Z</t>
         </is>
       </c>
     </row>
@@ -6470,7 +6470,7 @@
       </c>
       <c r="S73" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04T23:25:19Z</t>
+          <t>2026-10-06T01:22:21Z</t>
         </is>
       </c>
     </row>
@@ -6555,7 +6555,7 @@
       </c>
       <c r="S74" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04T23:25:19Z</t>
+          <t>2026-10-06T01:22:21Z</t>
         </is>
       </c>
     </row>
@@ -6640,7 +6640,7 @@
       </c>
       <c r="S75" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04T23:25:19Z</t>
+          <t>2026-10-06T01:22:21Z</t>
         </is>
       </c>
     </row>
@@ -6725,7 +6725,7 @@
       </c>
       <c r="S76" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04T23:25:19Z</t>
+          <t>2026-10-06T01:22:21Z</t>
         </is>
       </c>
     </row>
@@ -6810,7 +6810,7 @@
       </c>
       <c r="S77" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04T23:25:19Z</t>
+          <t>2026-10-06T01:22:21Z</t>
         </is>
       </c>
     </row>
@@ -6895,7 +6895,7 @@
       </c>
       <c r="S78" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04T23:25:19Z</t>
+          <t>2026-10-06T01:22:21Z</t>
         </is>
       </c>
     </row>
@@ -6980,7 +6980,7 @@
       </c>
       <c r="S79" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04T23:25:19Z</t>
+          <t>2026-10-06T01:22:21Z</t>
         </is>
       </c>
     </row>
@@ -7065,7 +7065,7 @@
       </c>
       <c r="S80" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04T23:25:19Z</t>
+          <t>2026-10-06T01:22:21Z</t>
         </is>
       </c>
     </row>
@@ -7150,7 +7150,7 @@
       </c>
       <c r="S81" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04T23:25:19Z</t>
+          <t>2026-10-06T01:22:21Z</t>
         </is>
       </c>
     </row>
@@ -7235,7 +7235,7 @@
       </c>
       <c r="S82" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04T23:25:19Z</t>
+          <t>2026-10-06T01:22:21Z</t>
         </is>
       </c>
     </row>
@@ -7320,7 +7320,7 @@
       </c>
       <c r="S83" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04T23:25:19Z</t>
+          <t>2026-10-06T01:22:21Z</t>
         </is>
       </c>
     </row>
@@ -7405,7 +7405,7 @@
       </c>
       <c r="S84" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04T23:25:19Z</t>
+          <t>2026-10-06T01:22:21Z</t>
         </is>
       </c>
     </row>
@@ -7490,7 +7490,7 @@
       </c>
       <c r="S85" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04T23:25:19Z</t>
+          <t>2026-10-06T01:22:21Z</t>
         </is>
       </c>
     </row>
@@ -7575,7 +7575,7 @@
       </c>
       <c r="S86" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04T23:25:19Z</t>
+          <t>2026-10-06T01:22:21Z</t>
         </is>
       </c>
     </row>
@@ -7660,7 +7660,7 @@
       </c>
       <c r="S87" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04T23:25:19Z</t>
+          <t>2026-10-06T01:22:21Z</t>
         </is>
       </c>
     </row>
@@ -7745,7 +7745,7 @@
       </c>
       <c r="S88" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04T23:25:19Z</t>
+          <t>2026-10-06T01:22:21Z</t>
         </is>
       </c>
     </row>
@@ -7834,7 +7834,7 @@
       </c>
       <c r="S89" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04T23:25:19Z</t>
+          <t>2026-10-06T01:22:21Z</t>
         </is>
       </c>
     </row>
@@ -7923,7 +7923,7 @@
       </c>
       <c r="S90" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04T23:25:19Z</t>
+          <t>2026-10-06T01:22:21Z</t>
         </is>
       </c>
     </row>
@@ -8008,7 +8008,7 @@
       </c>
       <c r="S91" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04T23:25:19Z</t>
+          <t>2026-10-06T01:22:21Z</t>
         </is>
       </c>
     </row>
@@ -8097,7 +8097,7 @@
       </c>
       <c r="S92" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04T23:25:19Z</t>
+          <t>2026-10-06T01:22:21Z</t>
         </is>
       </c>
     </row>
@@ -8186,7 +8186,7 @@
       </c>
       <c r="S93" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04T23:25:19Z</t>
+          <t>2026-10-06T01:22:21Z</t>
         </is>
       </c>
     </row>
@@ -8271,7 +8271,7 @@
       </c>
       <c r="S94" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04T23:25:19Z</t>
+          <t>2026-10-06T01:22:21Z</t>
         </is>
       </c>
     </row>
@@ -8360,7 +8360,7 @@
       </c>
       <c r="S95" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04T23:25:19Z</t>
+          <t>2026-10-06T01:22:21Z</t>
         </is>
       </c>
     </row>
@@ -8449,7 +8449,7 @@
       </c>
       <c r="S96" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04T23:25:19Z</t>
+          <t>2026-10-06T01:22:21Z</t>
         </is>
       </c>
     </row>
@@ -8534,7 +8534,7 @@
       </c>
       <c r="S97" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04T23:25:19Z</t>
+          <t>2026-10-06T01:22:21Z</t>
         </is>
       </c>
     </row>
@@ -8623,7 +8623,7 @@
       </c>
       <c r="S98" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04T23:25:19Z</t>
+          <t>2026-10-06T01:22:21Z</t>
         </is>
       </c>
     </row>
@@ -8712,7 +8712,7 @@
       </c>
       <c r="S99" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04T23:25:19Z</t>
+          <t>2026-10-06T01:22:21Z</t>
         </is>
       </c>
     </row>
@@ -8797,7 +8797,7 @@
       </c>
       <c r="S100" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04T23:25:19Z</t>
+          <t>2026-10-06T01:22:21Z</t>
         </is>
       </c>
     </row>
@@ -8886,7 +8886,7 @@
       </c>
       <c r="S101" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04T23:25:19Z</t>
+          <t>2026-10-06T01:22:21Z</t>
         </is>
       </c>
     </row>
@@ -8975,7 +8975,7 @@
       </c>
       <c r="S102" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04T23:25:19Z</t>
+          <t>2026-10-06T01:22:21Z</t>
         </is>
       </c>
     </row>
@@ -9060,7 +9060,7 @@
       </c>
       <c r="S103" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04T23:25:19Z</t>
+          <t>2026-10-06T01:22:21Z</t>
         </is>
       </c>
     </row>
@@ -9149,7 +9149,7 @@
       </c>
       <c r="S104" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04T23:25:19Z</t>
+          <t>2026-10-06T01:22:21Z</t>
         </is>
       </c>
     </row>
@@ -9238,7 +9238,7 @@
       </c>
       <c r="S105" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04T23:25:19Z</t>
+          <t>2026-10-06T01:22:21Z</t>
         </is>
       </c>
     </row>
@@ -9323,7 +9323,7 @@
       </c>
       <c r="S106" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04T23:25:19Z</t>
+          <t>2026-10-06T01:22:21Z</t>
         </is>
       </c>
     </row>
@@ -9412,7 +9412,7 @@
       </c>
       <c r="S107" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04T23:25:19Z</t>
+          <t>2026-10-06T01:22:21Z</t>
         </is>
       </c>
     </row>
@@ -9501,7 +9501,7 @@
       </c>
       <c r="S108" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04T23:25:19Z</t>
+          <t>2026-10-06T01:22:21Z</t>
         </is>
       </c>
     </row>
@@ -9586,7 +9586,7 @@
       </c>
       <c r="S109" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04T23:25:19Z</t>
+          <t>2026-10-06T01:22:21Z</t>
         </is>
       </c>
     </row>
@@ -9675,7 +9675,7 @@
       </c>
       <c r="S110" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04T23:25:19Z</t>
+          <t>2026-10-06T01:22:21Z</t>
         </is>
       </c>
     </row>
@@ -9764,7 +9764,7 @@
       </c>
       <c r="S111" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04T23:25:19Z</t>
+          <t>2026-10-06T01:22:21Z</t>
         </is>
       </c>
     </row>
@@ -9849,7 +9849,7 @@
       </c>
       <c r="S112" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04T23:25:19Z</t>
+          <t>2026-10-06T01:22:21Z</t>
         </is>
       </c>
     </row>
@@ -9938,7 +9938,7 @@
       </c>
       <c r="S113" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04T23:25:19Z</t>
+          <t>2026-10-06T01:22:21Z</t>
         </is>
       </c>
     </row>
@@ -10027,7 +10027,7 @@
       </c>
       <c r="S114" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04T23:25:19Z</t>
+          <t>2026-10-06T01:22:21Z</t>
         </is>
       </c>
     </row>
@@ -10112,7 +10112,7 @@
       </c>
       <c r="S115" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04T23:25:19Z</t>
+          <t>2026-10-06T01:22:21Z</t>
         </is>
       </c>
     </row>
@@ -10201,7 +10201,7 @@
       </c>
       <c r="S116" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04T23:25:19Z</t>
+          <t>2026-10-06T01:22:21Z</t>
         </is>
       </c>
     </row>
@@ -10290,7 +10290,7 @@
       </c>
       <c r="S117" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04T23:25:19Z</t>
+          <t>2026-10-06T01:22:21Z</t>
         </is>
       </c>
     </row>
@@ -10379,7 +10379,7 @@
       </c>
       <c r="S118" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04T23:25:19Z</t>
+          <t>2026-10-06T01:22:21Z</t>
         </is>
       </c>
     </row>
@@ -10468,7 +10468,7 @@
       </c>
       <c r="S119" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04T23:25:19Z</t>
+          <t>2026-10-06T01:22:21Z</t>
         </is>
       </c>
     </row>
@@ -10557,7 +10557,7 @@
       </c>
       <c r="S120" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04T23:25:19Z</t>
+          <t>2026-10-06T01:22:21Z</t>
         </is>
       </c>
     </row>
@@ -10646,7 +10646,7 @@
       </c>
       <c r="S121" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04T23:25:19Z</t>
+          <t>2026-10-06T01:22:21Z</t>
         </is>
       </c>
     </row>
@@ -10735,7 +10735,7 @@
       </c>
       <c r="S122" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04T23:25:19Z</t>
+          <t>2026-10-06T01:22:21Z</t>
         </is>
       </c>
     </row>
@@ -10824,7 +10824,7 @@
       </c>
       <c r="S123" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04T23:25:19Z</t>
+          <t>2026-10-06T01:22:21Z</t>
         </is>
       </c>
     </row>
@@ -10913,7 +10913,7 @@
       </c>
       <c r="S124" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04T23:25:19Z</t>
+          <t>2026-10-06T01:22:21Z</t>
         </is>
       </c>
     </row>
@@ -11002,7 +11002,7 @@
       </c>
       <c r="S125" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04T23:25:19Z</t>
+          <t>2026-10-06T01:22:21Z</t>
         </is>
       </c>
     </row>
@@ -11091,7 +11091,7 @@
       </c>
       <c r="S126" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04T23:25:19Z</t>
+          <t>2026-10-06T01:22:21Z</t>
         </is>
       </c>
     </row>
@@ -11180,7 +11180,7 @@
       </c>
       <c r="S127" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04T23:25:19Z</t>
+          <t>2026-10-06T01:22:21Z</t>
         </is>
       </c>
     </row>
@@ -11269,7 +11269,7 @@
       </c>
       <c r="S128" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04T23:25:19Z</t>
+          <t>2026-10-06T01:22:21Z</t>
         </is>
       </c>
     </row>
@@ -11354,7 +11354,7 @@
       </c>
       <c r="S129" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04T23:25:19Z</t>
+          <t>2026-10-06T01:22:21Z</t>
         </is>
       </c>
     </row>
@@ -11439,7 +11439,7 @@
       </c>
       <c r="S130" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04T23:25:19Z</t>
+          <t>2026-10-06T01:22:21Z</t>
         </is>
       </c>
     </row>
@@ -11524,7 +11524,7 @@
       </c>
       <c r="S131" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04T23:25:19Z</t>
+          <t>2026-10-06T01:22:21Z</t>
         </is>
       </c>
     </row>
@@ -11609,7 +11609,7 @@
       </c>
       <c r="S132" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04T23:25:19Z</t>
+          <t>2026-10-06T01:22:21Z</t>
         </is>
       </c>
     </row>
@@ -11694,7 +11694,7 @@
       </c>
       <c r="S133" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04T23:25:19Z</t>
+          <t>2026-10-06T01:22:21Z</t>
         </is>
       </c>
     </row>
@@ -11779,7 +11779,7 @@
       </c>
       <c r="S134" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04T23:25:19Z</t>
+          <t>2026-10-06T01:22:21Z</t>
         </is>
       </c>
     </row>
@@ -11864,7 +11864,7 @@
       </c>
       <c r="S135" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04T23:25:19Z</t>
+          <t>2026-10-06T01:22:21Z</t>
         </is>
       </c>
     </row>
@@ -11949,7 +11949,7 @@
       </c>
       <c r="S136" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04T23:25:19Z</t>
+          <t>2026-10-06T01:22:21Z</t>
         </is>
       </c>
     </row>
@@ -12034,7 +12034,7 @@
       </c>
       <c r="S137" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04T23:25:19Z</t>
+          <t>2026-10-06T01:22:21Z</t>
         </is>
       </c>
     </row>
@@ -12119,7 +12119,7 @@
       </c>
       <c r="S138" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04T23:25:19Z</t>
+          <t>2026-10-06T01:22:21Z</t>
         </is>
       </c>
     </row>
@@ -12204,7 +12204,7 @@
       </c>
       <c r="S139" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04T23:25:19Z</t>
+          <t>2026-10-06T01:22:21Z</t>
         </is>
       </c>
     </row>
@@ -12289,7 +12289,7 @@
       </c>
       <c r="S140" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04T23:25:19Z</t>
+          <t>2026-10-06T01:22:21Z</t>
         </is>
       </c>
     </row>
@@ -12374,7 +12374,7 @@
       </c>
       <c r="S141" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04T23:25:19Z</t>
+          <t>2026-10-06T01:22:21Z</t>
         </is>
       </c>
     </row>
@@ -12459,7 +12459,7 @@
       </c>
       <c r="S142" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04T23:25:19Z</t>
+          <t>2026-10-06T01:22:21Z</t>
         </is>
       </c>
     </row>
@@ -12544,7 +12544,7 @@
       </c>
       <c r="S143" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04T23:25:19Z</t>
+          <t>2026-10-06T01:22:21Z</t>
         </is>
       </c>
     </row>
@@ -12629,7 +12629,7 @@
       </c>
       <c r="S144" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04T23:25:19Z</t>
+          <t>2026-10-06T01:22:21Z</t>
         </is>
       </c>
     </row>
@@ -12714,7 +12714,7 @@
       </c>
       <c r="S145" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04T23:25:19Z</t>
+          <t>2026-10-06T01:22:21Z</t>
         </is>
       </c>
     </row>
@@ -12799,7 +12799,7 @@
       </c>
       <c r="S146" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04T23:25:19Z</t>
+          <t>2026-10-06T01:22:21Z</t>
         </is>
       </c>
     </row>
@@ -12884,7 +12884,7 @@
       </c>
       <c r="S147" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04T23:25:19Z</t>
+          <t>2026-10-06T01:22:21Z</t>
         </is>
       </c>
     </row>
@@ -12969,7 +12969,7 @@
       </c>
       <c r="S148" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04T23:25:19Z</t>
+          <t>2026-10-06T01:22:21Z</t>
         </is>
       </c>
     </row>
@@ -13054,7 +13054,7 @@
       </c>
       <c r="S149" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04T23:25:19Z</t>
+          <t>2026-10-06T01:22:21Z</t>
         </is>
       </c>
     </row>
@@ -13143,7 +13143,7 @@
       </c>
       <c r="S150" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04T23:25:19Z</t>
+          <t>2026-10-06T01:22:21Z</t>
         </is>
       </c>
     </row>
@@ -13232,7 +13232,7 @@
       </c>
       <c r="S151" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04T23:25:19Z</t>
+          <t>2026-10-06T01:22:21Z</t>
         </is>
       </c>
     </row>
@@ -13317,7 +13317,7 @@
       </c>
       <c r="S152" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04T23:25:19Z</t>
+          <t>2026-10-06T01:22:21Z</t>
         </is>
       </c>
     </row>
@@ -13406,7 +13406,7 @@
       </c>
       <c r="S153" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04T23:25:19Z</t>
+          <t>2026-10-06T01:22:21Z</t>
         </is>
       </c>
     </row>
@@ -13495,7 +13495,7 @@
       </c>
       <c r="S154" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04T23:25:19Z</t>
+          <t>2026-10-06T01:22:21Z</t>
         </is>
       </c>
     </row>
@@ -13580,7 +13580,7 @@
       </c>
       <c r="S155" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04T23:25:19Z</t>
+          <t>2026-10-06T01:22:21Z</t>
         </is>
       </c>
     </row>
@@ -13669,7 +13669,7 @@
       </c>
       <c r="S156" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04T23:25:19Z</t>
+          <t>2026-10-06T01:22:21Z</t>
         </is>
       </c>
     </row>
@@ -13758,7 +13758,7 @@
       </c>
       <c r="S157" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04T23:25:19Z</t>
+          <t>2026-10-06T01:22:21Z</t>
         </is>
       </c>
     </row>
@@ -13843,7 +13843,7 @@
       </c>
       <c r="S158" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04T23:25:19Z</t>
+          <t>2026-10-06T01:22:21Z</t>
         </is>
       </c>
     </row>
@@ -13932,7 +13932,7 @@
       </c>
       <c r="S159" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04T23:25:19Z</t>
+          <t>2026-10-06T01:22:21Z</t>
         </is>
       </c>
     </row>
@@ -14021,7 +14021,7 @@
       </c>
       <c r="S160" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04T23:25:19Z</t>
+          <t>2026-10-06T01:22:21Z</t>
         </is>
       </c>
     </row>
@@ -14106,7 +14106,7 @@
       </c>
       <c r="S161" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04T23:25:19Z</t>
+          <t>2026-10-06T01:22:21Z</t>
         </is>
       </c>
     </row>
@@ -14195,7 +14195,7 @@
       </c>
       <c r="S162" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04T23:25:19Z</t>
+          <t>2026-10-06T01:22:21Z</t>
         </is>
       </c>
     </row>
@@ -14284,7 +14284,7 @@
       </c>
       <c r="S163" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04T23:25:19Z</t>
+          <t>2026-10-06T01:22:21Z</t>
         </is>
       </c>
     </row>
@@ -14369,7 +14369,7 @@
       </c>
       <c r="S164" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04T23:25:19Z</t>
+          <t>2026-10-06T01:22:21Z</t>
         </is>
       </c>
     </row>
@@ -14458,7 +14458,7 @@
       </c>
       <c r="S165" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04T23:25:19Z</t>
+          <t>2026-10-06T01:22:21Z</t>
         </is>
       </c>
     </row>
@@ -14547,7 +14547,7 @@
       </c>
       <c r="S166" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04T23:25:19Z</t>
+          <t>2026-10-06T01:22:21Z</t>
         </is>
       </c>
     </row>
@@ -14632,7 +14632,7 @@
       </c>
       <c r="S167" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04T23:25:19Z</t>
+          <t>2026-10-06T01:22:21Z</t>
         </is>
       </c>
     </row>
@@ -14721,7 +14721,7 @@
       </c>
       <c r="S168" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04T23:25:19Z</t>
+          <t>2026-10-06T01:22:21Z</t>
         </is>
       </c>
     </row>
@@ -14810,7 +14810,7 @@
       </c>
       <c r="S169" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04T23:25:19Z</t>
+          <t>2026-10-06T01:22:21Z</t>
         </is>
       </c>
     </row>
@@ -14895,7 +14895,7 @@
       </c>
       <c r="S170" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04T23:25:19Z</t>
+          <t>2026-10-06T01:22:21Z</t>
         </is>
       </c>
     </row>
@@ -14984,7 +14984,7 @@
       </c>
       <c r="S171" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04T23:25:19Z</t>
+          <t>2026-10-06T01:22:21Z</t>
         </is>
       </c>
     </row>
@@ -15073,7 +15073,7 @@
       </c>
       <c r="S172" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04T23:25:19Z</t>
+          <t>2026-10-06T01:22:21Z</t>
         </is>
       </c>
     </row>
@@ -15158,7 +15158,7 @@
       </c>
       <c r="S173" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04T23:25:19Z</t>
+          <t>2026-10-06T01:22:21Z</t>
         </is>
       </c>
     </row>
@@ -15247,7 +15247,7 @@
       </c>
       <c r="S174" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04T23:25:19Z</t>
+          <t>2026-10-06T01:22:21Z</t>
         </is>
       </c>
     </row>
@@ -15336,7 +15336,7 @@
       </c>
       <c r="S175" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04T23:25:19Z</t>
+          <t>2026-10-06T01:22:21Z</t>
         </is>
       </c>
     </row>
@@ -15421,7 +15421,7 @@
       </c>
       <c r="S176" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04T23:25:19Z</t>
+          <t>2026-10-06T01:22:21Z</t>
         </is>
       </c>
     </row>
@@ -15510,7 +15510,7 @@
       </c>
       <c r="S177" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04T23:25:19Z</t>
+          <t>2026-10-06T01:22:21Z</t>
         </is>
       </c>
     </row>
@@ -15599,7 +15599,7 @@
       </c>
       <c r="S178" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04T23:25:19Z</t>
+          <t>2026-10-06T01:22:21Z</t>
         </is>
       </c>
     </row>
@@ -15688,7 +15688,7 @@
       </c>
       <c r="S179" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04T23:25:19Z</t>
+          <t>2026-10-06T01:22:21Z</t>
         </is>
       </c>
     </row>
@@ -15777,7 +15777,7 @@
       </c>
       <c r="S180" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04T23:25:19Z</t>
+          <t>2026-10-06T01:22:21Z</t>
         </is>
       </c>
     </row>
@@ -15866,7 +15866,7 @@
       </c>
       <c r="S181" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04T23:25:19Z</t>
+          <t>2026-10-06T01:22:21Z</t>
         </is>
       </c>
     </row>
@@ -15955,7 +15955,7 @@
       </c>
       <c r="S182" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04T23:25:19Z</t>
+          <t>2026-10-06T01:22:21Z</t>
         </is>
       </c>
     </row>
@@ -16044,7 +16044,7 @@
       </c>
       <c r="S183" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04T23:25:19Z</t>
+          <t>2026-10-06T01:22:21Z</t>
         </is>
       </c>
     </row>
@@ -16133,7 +16133,7 @@
       </c>
       <c r="S184" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04T23:25:19Z</t>
+          <t>2026-10-06T01:22:21Z</t>
         </is>
       </c>
     </row>
@@ -16222,7 +16222,7 @@
       </c>
       <c r="S185" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04T23:25:19Z</t>
+          <t>2026-10-06T01:22:21Z</t>
         </is>
       </c>
     </row>
@@ -16311,7 +16311,7 @@
       </c>
       <c r="S186" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04T23:25:19Z</t>
+          <t>2026-10-06T01:22:21Z</t>
         </is>
       </c>
     </row>
@@ -16400,7 +16400,7 @@
       </c>
       <c r="S187" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04T23:25:19Z</t>
+          <t>2026-10-06T01:22:21Z</t>
         </is>
       </c>
     </row>
@@ -16489,7 +16489,7 @@
       </c>
       <c r="S188" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04T23:25:19Z</t>
+          <t>2026-10-06T01:22:21Z</t>
         </is>
       </c>
     </row>
@@ -16578,7 +16578,7 @@
       </c>
       <c r="S189" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04T23:25:19Z</t>
+          <t>2026-10-06T01:22:21Z</t>
         </is>
       </c>
     </row>
@@ -16663,7 +16663,7 @@
       </c>
       <c r="S190" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04T23:25:19Z</t>
+          <t>2026-10-06T01:22:21Z</t>
         </is>
       </c>
     </row>
@@ -16748,7 +16748,7 @@
       </c>
       <c r="S191" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04T23:25:19Z</t>
+          <t>2026-10-06T01:22:21Z</t>
         </is>
       </c>
     </row>
@@ -16833,7 +16833,7 @@
       </c>
       <c r="S192" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04T23:25:19Z</t>
+          <t>2026-10-06T01:22:21Z</t>
         </is>
       </c>
     </row>
@@ -16918,7 +16918,7 @@
       </c>
       <c r="S193" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04T23:25:19Z</t>
+          <t>2026-10-06T01:22:21Z</t>
         </is>
       </c>
     </row>
@@ -17003,7 +17003,7 @@
       </c>
       <c r="S194" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04T23:25:19Z</t>
+          <t>2026-10-06T01:22:21Z</t>
         </is>
       </c>
     </row>
@@ -17088,7 +17088,7 @@
       </c>
       <c r="S195" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04T23:25:19Z</t>
+          <t>2026-10-06T01:22:21Z</t>
         </is>
       </c>
     </row>
@@ -17173,7 +17173,7 @@
       </c>
       <c r="S196" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04T23:25:19Z</t>
+          <t>2026-10-06T01:22:21Z</t>
         </is>
       </c>
     </row>
@@ -17258,7 +17258,7 @@
       </c>
       <c r="S197" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04T23:25:19Z</t>
+          <t>2026-10-06T01:22:21Z</t>
         </is>
       </c>
     </row>
@@ -17343,7 +17343,7 @@
       </c>
       <c r="S198" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04T23:25:19Z</t>
+          <t>2026-10-06T01:22:21Z</t>
         </is>
       </c>
     </row>
@@ -17428,7 +17428,7 @@
       </c>
       <c r="S199" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04T23:25:19Z</t>
+          <t>2026-10-06T01:22:21Z</t>
         </is>
       </c>
     </row>
@@ -17513,7 +17513,7 @@
       </c>
       <c r="S200" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04T23:25:19Z</t>
+          <t>2026-10-06T01:22:21Z</t>
         </is>
       </c>
     </row>
@@ -17598,7 +17598,7 @@
       </c>
       <c r="S201" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04T23:25:19Z</t>
+          <t>2026-10-06T01:22:21Z</t>
         </is>
       </c>
     </row>
@@ -17683,7 +17683,7 @@
       </c>
       <c r="S202" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04T23:25:19Z</t>
+          <t>2026-10-06T01:22:21Z</t>
         </is>
       </c>
     </row>
@@ -17768,7 +17768,7 @@
       </c>
       <c r="S203" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04T23:25:19Z</t>
+          <t>2026-10-06T01:22:21Z</t>
         </is>
       </c>
     </row>
@@ -17853,7 +17853,7 @@
       </c>
       <c r="S204" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04T23:25:19Z</t>
+          <t>2026-10-06T01:22:21Z</t>
         </is>
       </c>
     </row>
@@ -17938,7 +17938,7 @@
       </c>
       <c r="S205" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04T23:25:19Z</t>
+          <t>2026-10-06T01:22:21Z</t>
         </is>
       </c>
     </row>
@@ -18023,7 +18023,7 @@
       </c>
       <c r="S206" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04T23:25:19Z</t>
+          <t>2026-10-06T01:22:21Z</t>
         </is>
       </c>
     </row>
@@ -18108,7 +18108,7 @@
       </c>
       <c r="S207" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04T23:25:19Z</t>
+          <t>2026-10-06T01:22:21Z</t>
         </is>
       </c>
     </row>
@@ -18193,7 +18193,7 @@
       </c>
       <c r="S208" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04T23:25:19Z</t>
+          <t>2026-10-06T01:22:21Z</t>
         </is>
       </c>
     </row>
@@ -18278,7 +18278,7 @@
       </c>
       <c r="S209" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04T23:25:19Z</t>
+          <t>2026-10-06T01:22:21Z</t>
         </is>
       </c>
     </row>
@@ -18363,7 +18363,7 @@
       </c>
       <c r="S210" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04T23:25:19Z</t>
+          <t>2026-10-06T01:22:21Z</t>
         </is>
       </c>
     </row>
@@ -18452,7 +18452,7 @@
       </c>
       <c r="S211" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04T23:25:19Z</t>
+          <t>2026-10-06T01:22:21Z</t>
         </is>
       </c>
     </row>
@@ -18541,7 +18541,7 @@
       </c>
       <c r="S212" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04T23:25:19Z</t>
+          <t>2026-10-06T01:22:21Z</t>
         </is>
       </c>
     </row>
@@ -18626,7 +18626,7 @@
       </c>
       <c r="S213" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04T23:25:19Z</t>
+          <t>2026-10-06T01:22:21Z</t>
         </is>
       </c>
     </row>
@@ -18715,7 +18715,7 @@
       </c>
       <c r="S214" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04T23:25:19Z</t>
+          <t>2026-10-06T01:22:21Z</t>
         </is>
       </c>
     </row>
@@ -18804,7 +18804,7 @@
       </c>
       <c r="S215" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04T23:25:19Z</t>
+          <t>2026-10-06T01:22:21Z</t>
         </is>
       </c>
     </row>
@@ -18889,7 +18889,7 @@
       </c>
       <c r="S216" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04T23:25:19Z</t>
+          <t>2026-10-06T01:22:21Z</t>
         </is>
       </c>
     </row>
@@ -18978,7 +18978,7 @@
       </c>
       <c r="S217" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04T23:25:19Z</t>
+          <t>2026-10-06T01:22:21Z</t>
         </is>
       </c>
     </row>
@@ -19067,7 +19067,7 @@
       </c>
       <c r="S218" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04T23:25:19Z</t>
+          <t>2026-10-06T01:22:21Z</t>
         </is>
       </c>
     </row>
@@ -19152,7 +19152,7 @@
       </c>
       <c r="S219" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04T23:25:19Z</t>
+          <t>2026-10-06T01:22:21Z</t>
         </is>
       </c>
     </row>
@@ -19241,7 +19241,7 @@
       </c>
       <c r="S220" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04T23:25:19Z</t>
+          <t>2026-10-06T01:22:21Z</t>
         </is>
       </c>
     </row>
@@ -19330,7 +19330,7 @@
       </c>
       <c r="S221" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04T23:25:19Z</t>
+          <t>2026-10-06T01:22:21Z</t>
         </is>
       </c>
     </row>
@@ -19415,7 +19415,7 @@
       </c>
       <c r="S222" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04T23:25:19Z</t>
+          <t>2026-10-06T01:22:21Z</t>
         </is>
       </c>
     </row>
@@ -19504,7 +19504,7 @@
       </c>
       <c r="S223" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04T23:25:19Z</t>
+          <t>2026-10-06T01:22:21Z</t>
         </is>
       </c>
     </row>
@@ -19593,7 +19593,7 @@
       </c>
       <c r="S224" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04T23:25:19Z</t>
+          <t>2026-10-06T01:22:21Z</t>
         </is>
       </c>
     </row>
@@ -19678,7 +19678,7 @@
       </c>
       <c r="S225" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04T23:25:19Z</t>
+          <t>2026-10-06T01:22:21Z</t>
         </is>
       </c>
     </row>
@@ -19767,7 +19767,7 @@
       </c>
       <c r="S226" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04T23:25:19Z</t>
+          <t>2026-10-06T01:22:21Z</t>
         </is>
       </c>
     </row>
@@ -19856,7 +19856,7 @@
       </c>
       <c r="S227" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04T23:25:19Z</t>
+          <t>2026-10-06T01:22:21Z</t>
         </is>
       </c>
     </row>
@@ -19941,7 +19941,7 @@
       </c>
       <c r="S228" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04T23:25:19Z</t>
+          <t>2026-10-06T01:22:21Z</t>
         </is>
       </c>
     </row>
@@ -20030,7 +20030,7 @@
       </c>
       <c r="S229" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04T23:25:19Z</t>
+          <t>2026-10-06T01:22:21Z</t>
         </is>
       </c>
     </row>
@@ -20119,7 +20119,7 @@
       </c>
       <c r="S230" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04T23:25:19Z</t>
+          <t>2026-10-06T01:22:21Z</t>
         </is>
       </c>
     </row>
@@ -20204,7 +20204,7 @@
       </c>
       <c r="S231" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04T23:25:19Z</t>
+          <t>2026-10-06T01:22:21Z</t>
         </is>
       </c>
     </row>
@@ -20293,7 +20293,7 @@
       </c>
       <c r="S232" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04T23:25:19Z</t>
+          <t>2026-10-06T01:22:21Z</t>
         </is>
       </c>
     </row>
@@ -20382,7 +20382,7 @@
       </c>
       <c r="S233" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04T23:25:19Z</t>
+          <t>2026-10-06T01:22:21Z</t>
         </is>
       </c>
     </row>
@@ -20467,7 +20467,7 @@
       </c>
       <c r="S234" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04T23:25:19Z</t>
+          <t>2026-10-06T01:22:21Z</t>
         </is>
       </c>
     </row>
@@ -20556,7 +20556,7 @@
       </c>
       <c r="S235" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04T23:25:19Z</t>
+          <t>2026-10-06T01:22:21Z</t>
         </is>
       </c>
     </row>
@@ -20645,7 +20645,7 @@
       </c>
       <c r="S236" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04T23:25:19Z</t>
+          <t>2026-10-06T01:22:21Z</t>
         </is>
       </c>
     </row>
@@ -20730,7 +20730,7 @@
       </c>
       <c r="S237" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04T23:25:19Z</t>
+          <t>2026-10-06T01:22:21Z</t>
         </is>
       </c>
     </row>
@@ -20819,7 +20819,7 @@
       </c>
       <c r="S238" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04T23:25:19Z</t>
+          <t>2026-10-06T01:22:21Z</t>
         </is>
       </c>
     </row>
@@ -20908,7 +20908,7 @@
       </c>
       <c r="S239" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04T23:25:19Z</t>
+          <t>2026-10-06T01:22:21Z</t>
         </is>
       </c>
     </row>
@@ -20997,7 +20997,7 @@
       </c>
       <c r="S240" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04T23:25:19Z</t>
+          <t>2026-10-06T01:22:21Z</t>
         </is>
       </c>
     </row>
@@ -21086,7 +21086,7 @@
       </c>
       <c r="S241" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04T23:25:19Z</t>
+          <t>2026-10-06T01:22:21Z</t>
         </is>
       </c>
     </row>
@@ -21175,7 +21175,7 @@
       </c>
       <c r="S242" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04T23:25:19Z</t>
+          <t>2026-10-06T01:22:21Z</t>
         </is>
       </c>
     </row>
@@ -21264,7 +21264,7 @@
       </c>
       <c r="S243" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04T23:25:19Z</t>
+          <t>2026-10-06T01:22:21Z</t>
         </is>
       </c>
     </row>
@@ -21353,7 +21353,7 @@
       </c>
       <c r="S244" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04T23:25:19Z</t>
+          <t>2026-10-06T01:22:21Z</t>
         </is>
       </c>
     </row>
@@ -21442,7 +21442,7 @@
       </c>
       <c r="S245" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04T23:25:19Z</t>
+          <t>2026-10-06T01:22:21Z</t>
         </is>
       </c>
     </row>
@@ -21531,7 +21531,7 @@
       </c>
       <c r="S246" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04T23:25:19Z</t>
+          <t>2026-10-06T01:22:21Z</t>
         </is>
       </c>
     </row>
@@ -21620,7 +21620,7 @@
       </c>
       <c r="S247" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04T23:25:19Z</t>
+          <t>2026-10-06T01:22:21Z</t>
         </is>
       </c>
     </row>
@@ -21709,7 +21709,7 @@
       </c>
       <c r="S248" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04T23:25:19Z</t>
+          <t>2026-10-06T01:22:21Z</t>
         </is>
       </c>
     </row>
@@ -21798,7 +21798,7 @@
       </c>
       <c r="S249" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04T23:25:19Z</t>
+          <t>2026-10-06T01:22:21Z</t>
         </is>
       </c>
     </row>
@@ -21887,7 +21887,7 @@
       </c>
       <c r="S250" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04T23:25:19Z</t>
+          <t>2026-10-06T01:22:21Z</t>
         </is>
       </c>
     </row>
@@ -22019,7 +22019,7 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04T23:25:19Z</t>
+          <t>2026-10-06T01:22:21Z</t>
         </is>
       </c>
     </row>
@@ -22099,7 +22099,7 @@
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>{"dataset_id": "bcv_pib_sector_institucional_anual", "title": "Producto interno bruto por sector institucional anual", "table": "Variaciones porcentuales", "source_file": "5_2_1_si_anual.xlsx", "base": "2007", "price_type": "Precios constantes", "measure": "Variación porcentual interanual", "frequency": "Anual", "period": "2025", "year": 2025, "quarter": null, "classification": "Sector institucional", "component": "Impuestos netos sobre los productos", "value": 10.600260421283764, "unit": "Porcentaje", "status": "Preliminar", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/cuentas_macroeconomicas/5_2_1_si_anual.xlsx", "fetched_at": "2026-10-04T23:25:19Z"}</t>
+          <t>{"dataset_id": "bcv_pib_sector_institucional_anual", "title": "Producto interno bruto por sector institucional anual", "table": "Variaciones porcentuales", "source_file": "5_2_1_si_anual.xlsx", "base": "2007", "price_type": "Precios constantes", "measure": "Variación porcentual interanual", "frequency": "Anual", "period": "2025", "year": 2025, "quarter": null, "classification": "Sector institucional", "component": "Impuestos netos sobre los productos", "value": 10.600260421283764, "unit": "Porcentaje", "status": "Preliminar", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/cuentas_macroeconomicas/5_2_1_si_anual.xlsx", "fetched_at": "2026-10-06T01:22:21Z"}</t>
         </is>
       </c>
     </row>

--- a/assets/data/bcv/excel/ove_bcv_pib_sector_institucional_anual.xlsx
+++ b/assets/data/bcv/excel/ove_bcv_pib_sector_institucional_anual.xlsx
@@ -736,7 +736,7 @@
       </c>
       <c r="S7" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T01:22:21Z</t>
+          <t>2026-10-06T23:57:00Z</t>
         </is>
       </c>
     </row>
@@ -821,7 +821,7 @@
       </c>
       <c r="S8" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T01:22:21Z</t>
+          <t>2026-10-06T23:57:00Z</t>
         </is>
       </c>
     </row>
@@ -906,7 +906,7 @@
       </c>
       <c r="S9" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T01:22:21Z</t>
+          <t>2026-10-06T23:57:00Z</t>
         </is>
       </c>
     </row>
@@ -991,7 +991,7 @@
       </c>
       <c r="S10" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T01:22:21Z</t>
+          <t>2026-10-06T23:57:00Z</t>
         </is>
       </c>
     </row>
@@ -1076,7 +1076,7 @@
       </c>
       <c r="S11" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T01:22:21Z</t>
+          <t>2026-10-06T23:57:00Z</t>
         </is>
       </c>
     </row>
@@ -1161,7 +1161,7 @@
       </c>
       <c r="S12" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T01:22:21Z</t>
+          <t>2026-10-06T23:57:00Z</t>
         </is>
       </c>
     </row>
@@ -1246,7 +1246,7 @@
       </c>
       <c r="S13" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T01:22:21Z</t>
+          <t>2026-10-06T23:57:00Z</t>
         </is>
       </c>
     </row>
@@ -1331,7 +1331,7 @@
       </c>
       <c r="S14" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T01:22:21Z</t>
+          <t>2026-10-06T23:57:00Z</t>
         </is>
       </c>
     </row>
@@ -1416,7 +1416,7 @@
       </c>
       <c r="S15" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T01:22:21Z</t>
+          <t>2026-10-06T23:57:00Z</t>
         </is>
       </c>
     </row>
@@ -1501,7 +1501,7 @@
       </c>
       <c r="S16" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T01:22:21Z</t>
+          <t>2026-10-06T23:57:00Z</t>
         </is>
       </c>
     </row>
@@ -1586,7 +1586,7 @@
       </c>
       <c r="S17" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T01:22:21Z</t>
+          <t>2026-10-06T23:57:00Z</t>
         </is>
       </c>
     </row>
@@ -1671,7 +1671,7 @@
       </c>
       <c r="S18" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T01:22:21Z</t>
+          <t>2026-10-06T23:57:00Z</t>
         </is>
       </c>
     </row>
@@ -1756,7 +1756,7 @@
       </c>
       <c r="S19" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T01:22:21Z</t>
+          <t>2026-10-06T23:57:00Z</t>
         </is>
       </c>
     </row>
@@ -1841,7 +1841,7 @@
       </c>
       <c r="S20" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T01:22:21Z</t>
+          <t>2026-10-06T23:57:00Z</t>
         </is>
       </c>
     </row>
@@ -1926,7 +1926,7 @@
       </c>
       <c r="S21" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T01:22:21Z</t>
+          <t>2026-10-06T23:57:00Z</t>
         </is>
       </c>
     </row>
@@ -2011,7 +2011,7 @@
       </c>
       <c r="S22" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T01:22:21Z</t>
+          <t>2026-10-06T23:57:00Z</t>
         </is>
       </c>
     </row>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="S23" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T01:22:21Z</t>
+          <t>2026-10-06T23:57:00Z</t>
         </is>
       </c>
     </row>
@@ -2181,7 +2181,7 @@
       </c>
       <c r="S24" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T01:22:21Z</t>
+          <t>2026-10-06T23:57:00Z</t>
         </is>
       </c>
     </row>
@@ -2266,7 +2266,7 @@
       </c>
       <c r="S25" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T01:22:21Z</t>
+          <t>2026-10-06T23:57:00Z</t>
         </is>
       </c>
     </row>
@@ -2351,7 +2351,7 @@
       </c>
       <c r="S26" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T01:22:21Z</t>
+          <t>2026-10-06T23:57:00Z</t>
         </is>
       </c>
     </row>
@@ -2436,7 +2436,7 @@
       </c>
       <c r="S27" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T01:22:21Z</t>
+          <t>2026-10-06T23:57:00Z</t>
         </is>
       </c>
     </row>
@@ -2525,7 +2525,7 @@
       </c>
       <c r="S28" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T01:22:21Z</t>
+          <t>2026-10-06T23:57:00Z</t>
         </is>
       </c>
     </row>
@@ -2614,7 +2614,7 @@
       </c>
       <c r="S29" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T01:22:21Z</t>
+          <t>2026-10-06T23:57:00Z</t>
         </is>
       </c>
     </row>
@@ -2699,7 +2699,7 @@
       </c>
       <c r="S30" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T01:22:21Z</t>
+          <t>2026-10-06T23:57:00Z</t>
         </is>
       </c>
     </row>
@@ -2788,7 +2788,7 @@
       </c>
       <c r="S31" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T01:22:21Z</t>
+          <t>2026-10-06T23:57:00Z</t>
         </is>
       </c>
     </row>
@@ -2877,7 +2877,7 @@
       </c>
       <c r="S32" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T01:22:21Z</t>
+          <t>2026-10-06T23:57:00Z</t>
         </is>
       </c>
     </row>
@@ -2962,7 +2962,7 @@
       </c>
       <c r="S33" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T01:22:21Z</t>
+          <t>2026-10-06T23:57:00Z</t>
         </is>
       </c>
     </row>
@@ -3051,7 +3051,7 @@
       </c>
       <c r="S34" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T01:22:21Z</t>
+          <t>2026-10-06T23:57:00Z</t>
         </is>
       </c>
     </row>
@@ -3140,7 +3140,7 @@
       </c>
       <c r="S35" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T01:22:21Z</t>
+          <t>2026-10-06T23:57:00Z</t>
         </is>
       </c>
     </row>
@@ -3225,7 +3225,7 @@
       </c>
       <c r="S36" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T01:22:21Z</t>
+          <t>2026-10-06T23:57:00Z</t>
         </is>
       </c>
     </row>
@@ -3314,7 +3314,7 @@
       </c>
       <c r="S37" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T01:22:21Z</t>
+          <t>2026-10-06T23:57:00Z</t>
         </is>
       </c>
     </row>
@@ -3403,7 +3403,7 @@
       </c>
       <c r="S38" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T01:22:21Z</t>
+          <t>2026-10-06T23:57:00Z</t>
         </is>
       </c>
     </row>
@@ -3488,7 +3488,7 @@
       </c>
       <c r="S39" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T01:22:21Z</t>
+          <t>2026-10-06T23:57:00Z</t>
         </is>
       </c>
     </row>
@@ -3577,7 +3577,7 @@
       </c>
       <c r="S40" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T01:22:21Z</t>
+          <t>2026-10-06T23:57:00Z</t>
         </is>
       </c>
     </row>
@@ -3666,7 +3666,7 @@
       </c>
       <c r="S41" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T01:22:21Z</t>
+          <t>2026-10-06T23:57:00Z</t>
         </is>
       </c>
     </row>
@@ -3751,7 +3751,7 @@
       </c>
       <c r="S42" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T01:22:21Z</t>
+          <t>2026-10-06T23:57:00Z</t>
         </is>
       </c>
     </row>
@@ -3840,7 +3840,7 @@
       </c>
       <c r="S43" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T01:22:21Z</t>
+          <t>2026-10-06T23:57:00Z</t>
         </is>
       </c>
     </row>
@@ -3929,7 +3929,7 @@
       </c>
       <c r="S44" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T01:22:21Z</t>
+          <t>2026-10-06T23:57:00Z</t>
         </is>
       </c>
     </row>
@@ -4014,7 +4014,7 @@
       </c>
       <c r="S45" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T01:22:21Z</t>
+          <t>2026-10-06T23:57:00Z</t>
         </is>
       </c>
     </row>
@@ -4103,7 +4103,7 @@
       </c>
       <c r="S46" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T01:22:21Z</t>
+          <t>2026-10-06T23:57:00Z</t>
         </is>
       </c>
     </row>
@@ -4192,7 +4192,7 @@
       </c>
       <c r="S47" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T01:22:21Z</t>
+          <t>2026-10-06T23:57:00Z</t>
         </is>
       </c>
     </row>
@@ -4277,7 +4277,7 @@
       </c>
       <c r="S48" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T01:22:21Z</t>
+          <t>2026-10-06T23:57:00Z</t>
         </is>
       </c>
     </row>
@@ -4366,7 +4366,7 @@
       </c>
       <c r="S49" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T01:22:21Z</t>
+          <t>2026-10-06T23:57:00Z</t>
         </is>
       </c>
     </row>
@@ -4455,7 +4455,7 @@
       </c>
       <c r="S50" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T01:22:21Z</t>
+          <t>2026-10-06T23:57:00Z</t>
         </is>
       </c>
     </row>
@@ -4540,7 +4540,7 @@
       </c>
       <c r="S51" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T01:22:21Z</t>
+          <t>2026-10-06T23:57:00Z</t>
         </is>
       </c>
     </row>
@@ -4629,7 +4629,7 @@
       </c>
       <c r="S52" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T01:22:21Z</t>
+          <t>2026-10-06T23:57:00Z</t>
         </is>
       </c>
     </row>
@@ -4718,7 +4718,7 @@
       </c>
       <c r="S53" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T01:22:21Z</t>
+          <t>2026-10-06T23:57:00Z</t>
         </is>
       </c>
     </row>
@@ -4803,7 +4803,7 @@
       </c>
       <c r="S54" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T01:22:21Z</t>
+          <t>2026-10-06T23:57:00Z</t>
         </is>
       </c>
     </row>
@@ -4892,7 +4892,7 @@
       </c>
       <c r="S55" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T01:22:21Z</t>
+          <t>2026-10-06T23:57:00Z</t>
         </is>
       </c>
     </row>
@@ -4981,7 +4981,7 @@
       </c>
       <c r="S56" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T01:22:21Z</t>
+          <t>2026-10-06T23:57:00Z</t>
         </is>
       </c>
     </row>
@@ -5070,7 +5070,7 @@
       </c>
       <c r="S57" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T01:22:21Z</t>
+          <t>2026-10-06T23:57:00Z</t>
         </is>
       </c>
     </row>
@@ -5159,7 +5159,7 @@
       </c>
       <c r="S58" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T01:22:21Z</t>
+          <t>2026-10-06T23:57:00Z</t>
         </is>
       </c>
     </row>
@@ -5248,7 +5248,7 @@
       </c>
       <c r="S59" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T01:22:21Z</t>
+          <t>2026-10-06T23:57:00Z</t>
         </is>
       </c>
     </row>
@@ -5337,7 +5337,7 @@
       </c>
       <c r="S60" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T01:22:21Z</t>
+          <t>2026-10-06T23:57:00Z</t>
         </is>
       </c>
     </row>
@@ -5426,7 +5426,7 @@
       </c>
       <c r="S61" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T01:22:21Z</t>
+          <t>2026-10-06T23:57:00Z</t>
         </is>
       </c>
     </row>
@@ -5515,7 +5515,7 @@
       </c>
       <c r="S62" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T01:22:21Z</t>
+          <t>2026-10-06T23:57:00Z</t>
         </is>
       </c>
     </row>
@@ -5604,7 +5604,7 @@
       </c>
       <c r="S63" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T01:22:21Z</t>
+          <t>2026-10-06T23:57:00Z</t>
         </is>
       </c>
     </row>
@@ -5693,7 +5693,7 @@
       </c>
       <c r="S64" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T01:22:21Z</t>
+          <t>2026-10-06T23:57:00Z</t>
         </is>
       </c>
     </row>
@@ -5782,7 +5782,7 @@
       </c>
       <c r="S65" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T01:22:21Z</t>
+          <t>2026-10-06T23:57:00Z</t>
         </is>
       </c>
     </row>
@@ -5871,7 +5871,7 @@
       </c>
       <c r="S66" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T01:22:21Z</t>
+          <t>2026-10-06T23:57:00Z</t>
         </is>
       </c>
     </row>
@@ -5960,7 +5960,7 @@
       </c>
       <c r="S67" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T01:22:21Z</t>
+          <t>2026-10-06T23:57:00Z</t>
         </is>
       </c>
     </row>
@@ -6045,7 +6045,7 @@
       </c>
       <c r="S68" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T01:22:21Z</t>
+          <t>2026-10-06T23:57:00Z</t>
         </is>
       </c>
     </row>
@@ -6130,7 +6130,7 @@
       </c>
       <c r="S69" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T01:22:21Z</t>
+          <t>2026-10-06T23:57:00Z</t>
         </is>
       </c>
     </row>
@@ -6215,7 +6215,7 @@
       </c>
       <c r="S70" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T01:22:21Z</t>
+          <t>2026-10-06T23:57:00Z</t>
         </is>
       </c>
     </row>
@@ -6300,7 +6300,7 @@
       </c>
       <c r="S71" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T01:22:21Z</t>
+          <t>2026-10-06T23:57:00Z</t>
         </is>
       </c>
     </row>
@@ -6385,7 +6385,7 @@
       </c>
       <c r="S72" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T01:22:21Z</t>
+          <t>2026-10-06T23:57:00Z</t>
         </is>
       </c>
     </row>
@@ -6470,7 +6470,7 @@
       </c>
       <c r="S73" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T01:22:21Z</t>
+          <t>2026-10-06T23:57:00Z</t>
         </is>
       </c>
     </row>
@@ -6555,7 +6555,7 @@
       </c>
       <c r="S74" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T01:22:21Z</t>
+          <t>2026-10-06T23:57:00Z</t>
         </is>
       </c>
     </row>
@@ -6640,7 +6640,7 @@
       </c>
       <c r="S75" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T01:22:21Z</t>
+          <t>2026-10-06T23:57:00Z</t>
         </is>
       </c>
     </row>
@@ -6725,7 +6725,7 @@
       </c>
       <c r="S76" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T01:22:21Z</t>
+          <t>2026-10-06T23:57:00Z</t>
         </is>
       </c>
     </row>
@@ -6810,7 +6810,7 @@
       </c>
       <c r="S77" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T01:22:21Z</t>
+          <t>2026-10-06T23:57:00Z</t>
         </is>
       </c>
     </row>
@@ -6895,7 +6895,7 @@
       </c>
       <c r="S78" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T01:22:21Z</t>
+          <t>2026-10-06T23:57:00Z</t>
         </is>
       </c>
     </row>
@@ -6980,7 +6980,7 @@
       </c>
       <c r="S79" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T01:22:21Z</t>
+          <t>2026-10-06T23:57:00Z</t>
         </is>
       </c>
     </row>
@@ -7065,7 +7065,7 @@
       </c>
       <c r="S80" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T01:22:21Z</t>
+          <t>2026-10-06T23:57:00Z</t>
         </is>
       </c>
     </row>
@@ -7150,7 +7150,7 @@
       </c>
       <c r="S81" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T01:22:21Z</t>
+          <t>2026-10-06T23:57:00Z</t>
         </is>
       </c>
     </row>
@@ -7235,7 +7235,7 @@
       </c>
       <c r="S82" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T01:22:21Z</t>
+          <t>2026-10-06T23:57:00Z</t>
         </is>
       </c>
     </row>
@@ -7320,7 +7320,7 @@
       </c>
       <c r="S83" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T01:22:21Z</t>
+          <t>2026-10-06T23:57:00Z</t>
         </is>
       </c>
     </row>
@@ -7405,7 +7405,7 @@
       </c>
       <c r="S84" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T01:22:21Z</t>
+          <t>2026-10-06T23:57:00Z</t>
         </is>
       </c>
     </row>
@@ -7490,7 +7490,7 @@
       </c>
       <c r="S85" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T01:22:21Z</t>
+          <t>2026-10-06T23:57:00Z</t>
         </is>
       </c>
     </row>
@@ -7575,7 +7575,7 @@
       </c>
       <c r="S86" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T01:22:21Z</t>
+          <t>2026-10-06T23:57:00Z</t>
         </is>
       </c>
     </row>
@@ -7660,7 +7660,7 @@
       </c>
       <c r="S87" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T01:22:21Z</t>
+          <t>2026-10-06T23:57:00Z</t>
         </is>
       </c>
     </row>
@@ -7745,7 +7745,7 @@
       </c>
       <c r="S88" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T01:22:21Z</t>
+          <t>2026-10-06T23:57:00Z</t>
         </is>
       </c>
     </row>
@@ -7834,7 +7834,7 @@
       </c>
       <c r="S89" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T01:22:21Z</t>
+          <t>2026-10-06T23:57:00Z</t>
         </is>
       </c>
     </row>
@@ -7923,7 +7923,7 @@
       </c>
       <c r="S90" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T01:22:21Z</t>
+          <t>2026-10-06T23:57:00Z</t>
         </is>
       </c>
     </row>
@@ -8008,7 +8008,7 @@
       </c>
       <c r="S91" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T01:22:21Z</t>
+          <t>2026-10-06T23:57:00Z</t>
         </is>
       </c>
     </row>
@@ -8097,7 +8097,7 @@
       </c>
       <c r="S92" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T01:22:21Z</t>
+          <t>2026-10-06T23:57:00Z</t>
         </is>
       </c>
     </row>
@@ -8186,7 +8186,7 @@
       </c>
       <c r="S93" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T01:22:21Z</t>
+          <t>2026-10-06T23:57:00Z</t>
         </is>
       </c>
     </row>
@@ -8271,7 +8271,7 @@
       </c>
       <c r="S94" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T01:22:21Z</t>
+          <t>2026-10-06T23:57:00Z</t>
         </is>
       </c>
     </row>
@@ -8360,7 +8360,7 @@
       </c>
       <c r="S95" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T01:22:21Z</t>
+          <t>2026-10-06T23:57:00Z</t>
         </is>
       </c>
     </row>
@@ -8449,7 +8449,7 @@
       </c>
       <c r="S96" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T01:22:21Z</t>
+          <t>2026-10-06T23:57:00Z</t>
         </is>
       </c>
     </row>
@@ -8534,7 +8534,7 @@
       </c>
       <c r="S97" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T01:22:21Z</t>
+          <t>2026-10-06T23:57:00Z</t>
         </is>
       </c>
     </row>
@@ -8623,7 +8623,7 @@
       </c>
       <c r="S98" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T01:22:21Z</t>
+          <t>2026-10-06T23:57:00Z</t>
         </is>
       </c>
     </row>
@@ -8712,7 +8712,7 @@
       </c>
       <c r="S99" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T01:22:21Z</t>
+          <t>2026-10-06T23:57:00Z</t>
         </is>
       </c>
     </row>
@@ -8797,7 +8797,7 @@
       </c>
       <c r="S100" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T01:22:21Z</t>
+          <t>2026-10-06T23:57:00Z</t>
         </is>
       </c>
     </row>
@@ -8886,7 +8886,7 @@
       </c>
       <c r="S101" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T01:22:21Z</t>
+          <t>2026-10-06T23:57:00Z</t>
         </is>
       </c>
     </row>
@@ -8975,7 +8975,7 @@
       </c>
       <c r="S102" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T01:22:21Z</t>
+          <t>2026-10-06T23:57:00Z</t>
         </is>
       </c>
     </row>
@@ -9060,7 +9060,7 @@
       </c>
       <c r="S103" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T01:22:21Z</t>
+          <t>2026-10-06T23:57:00Z</t>
         </is>
       </c>
     </row>
@@ -9149,7 +9149,7 @@
       </c>
       <c r="S104" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T01:22:21Z</t>
+          <t>2026-10-06T23:57:00Z</t>
         </is>
       </c>
     </row>
@@ -9238,7 +9238,7 @@
       </c>
       <c r="S105" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T01:22:21Z</t>
+          <t>2026-10-06T23:57:00Z</t>
         </is>
       </c>
     </row>
@@ -9323,7 +9323,7 @@
       </c>
       <c r="S106" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T01:22:21Z</t>
+          <t>2026-10-06T23:57:00Z</t>
         </is>
       </c>
     </row>
@@ -9412,7 +9412,7 @@
       </c>
       <c r="S107" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T01:22:21Z</t>
+          <t>2026-10-06T23:57:00Z</t>
         </is>
       </c>
     </row>
@@ -9501,7 +9501,7 @@
       </c>
       <c r="S108" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T01:22:21Z</t>
+          <t>2026-10-06T23:57:00Z</t>
         </is>
       </c>
     </row>
@@ -9586,7 +9586,7 @@
       </c>
       <c r="S109" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T01:22:21Z</t>
+          <t>2026-10-06T23:57:00Z</t>
         </is>
       </c>
     </row>
@@ -9675,7 +9675,7 @@
       </c>
       <c r="S110" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T01:22:21Z</t>
+          <t>2026-10-06T23:57:00Z</t>
         </is>
       </c>
     </row>
@@ -9764,7 +9764,7 @@
       </c>
       <c r="S111" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T01:22:21Z</t>
+          <t>2026-10-06T23:57:00Z</t>
         </is>
       </c>
     </row>
@@ -9849,7 +9849,7 @@
       </c>
       <c r="S112" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T01:22:21Z</t>
+          <t>2026-10-06T23:57:00Z</t>
         </is>
       </c>
     </row>
@@ -9938,7 +9938,7 @@
       </c>
       <c r="S113" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T01:22:21Z</t>
+          <t>2026-10-06T23:57:00Z</t>
         </is>
       </c>
     </row>
@@ -10027,7 +10027,7 @@
       </c>
       <c r="S114" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T01:22:21Z</t>
+          <t>2026-10-06T23:57:00Z</t>
         </is>
       </c>
     </row>
@@ -10112,7 +10112,7 @@
       </c>
       <c r="S115" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T01:22:21Z</t>
+          <t>2026-10-06T23:57:00Z</t>
         </is>
       </c>
     </row>
@@ -10201,7 +10201,7 @@
       </c>
       <c r="S116" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T01:22:21Z</t>
+          <t>2026-10-06T23:57:00Z</t>
         </is>
       </c>
     </row>
@@ -10290,7 +10290,7 @@
       </c>
       <c r="S117" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T01:22:21Z</t>
+          <t>2026-10-06T23:57:00Z</t>
         </is>
       </c>
     </row>
@@ -10379,7 +10379,7 @@
       </c>
       <c r="S118" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T01:22:21Z</t>
+          <t>2026-10-06T23:57:00Z</t>
         </is>
       </c>
     </row>
@@ -10468,7 +10468,7 @@
       </c>
       <c r="S119" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T01:22:21Z</t>
+          <t>2026-10-06T23:57:00Z</t>
         </is>
       </c>
     </row>
@@ -10557,7 +10557,7 @@
       </c>
       <c r="S120" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T01:22:21Z</t>
+          <t>2026-10-06T23:57:00Z</t>
         </is>
       </c>
     </row>
@@ -10646,7 +10646,7 @@
       </c>
       <c r="S121" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T01:22:21Z</t>
+          <t>2026-10-06T23:57:00Z</t>
         </is>
       </c>
     </row>
@@ -10735,7 +10735,7 @@
       </c>
       <c r="S122" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T01:22:21Z</t>
+          <t>2026-10-06T23:57:00Z</t>
         </is>
       </c>
     </row>
@@ -10824,7 +10824,7 @@
       </c>
       <c r="S123" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T01:22:21Z</t>
+          <t>2026-10-06T23:57:00Z</t>
         </is>
       </c>
     </row>
@@ -10913,7 +10913,7 @@
       </c>
       <c r="S124" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T01:22:21Z</t>
+          <t>2026-10-06T23:57:00Z</t>
         </is>
       </c>
     </row>
@@ -11002,7 +11002,7 @@
       </c>
       <c r="S125" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T01:22:21Z</t>
+          <t>2026-10-06T23:57:00Z</t>
         </is>
       </c>
     </row>
@@ -11091,7 +11091,7 @@
       </c>
       <c r="S126" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T01:22:21Z</t>
+          <t>2026-10-06T23:57:00Z</t>
         </is>
       </c>
     </row>
@@ -11180,7 +11180,7 @@
       </c>
       <c r="S127" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T01:22:21Z</t>
+          <t>2026-10-06T23:57:00Z</t>
         </is>
       </c>
     </row>
@@ -11269,7 +11269,7 @@
       </c>
       <c r="S128" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T01:22:21Z</t>
+          <t>2026-10-06T23:57:00Z</t>
         </is>
       </c>
     </row>
@@ -11354,7 +11354,7 @@
       </c>
       <c r="S129" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T01:22:21Z</t>
+          <t>2026-10-06T23:57:00Z</t>
         </is>
       </c>
     </row>
@@ -11439,7 +11439,7 @@
       </c>
       <c r="S130" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T01:22:21Z</t>
+          <t>2026-10-06T23:57:00Z</t>
         </is>
       </c>
     </row>
@@ -11524,7 +11524,7 @@
       </c>
       <c r="S131" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T01:22:21Z</t>
+          <t>2026-10-06T23:57:00Z</t>
         </is>
       </c>
     </row>
@@ -11609,7 +11609,7 @@
       </c>
       <c r="S132" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T01:22:21Z</t>
+          <t>2026-10-06T23:57:00Z</t>
         </is>
       </c>
     </row>
@@ -11694,7 +11694,7 @@
       </c>
       <c r="S133" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T01:22:21Z</t>
+          <t>2026-10-06T23:57:00Z</t>
         </is>
       </c>
     </row>
@@ -11779,7 +11779,7 @@
       </c>
       <c r="S134" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T01:22:21Z</t>
+          <t>2026-10-06T23:57:00Z</t>
         </is>
       </c>
     </row>
@@ -11864,7 +11864,7 @@
       </c>
       <c r="S135" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T01:22:21Z</t>
+          <t>2026-10-06T23:57:00Z</t>
         </is>
       </c>
     </row>
@@ -11949,7 +11949,7 @@
       </c>
       <c r="S136" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T01:22:21Z</t>
+          <t>2026-10-06T23:57:00Z</t>
         </is>
       </c>
     </row>
@@ -12034,7 +12034,7 @@
       </c>
       <c r="S137" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T01:22:21Z</t>
+          <t>2026-10-06T23:57:00Z</t>
         </is>
       </c>
     </row>
@@ -12119,7 +12119,7 @@
       </c>
       <c r="S138" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T01:22:21Z</t>
+          <t>2026-10-06T23:57:00Z</t>
         </is>
       </c>
     </row>
@@ -12204,7 +12204,7 @@
       </c>
       <c r="S139" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T01:22:21Z</t>
+          <t>2026-10-06T23:57:00Z</t>
         </is>
       </c>
     </row>
@@ -12289,7 +12289,7 @@
       </c>
       <c r="S140" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T01:22:21Z</t>
+          <t>2026-10-06T23:57:00Z</t>
         </is>
       </c>
     </row>
@@ -12374,7 +12374,7 @@
       </c>
       <c r="S141" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T01:22:21Z</t>
+          <t>2026-10-06T23:57:00Z</t>
         </is>
       </c>
     </row>
@@ -12459,7 +12459,7 @@
       </c>
       <c r="S142" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T01:22:21Z</t>
+          <t>2026-10-06T23:57:00Z</t>
         </is>
       </c>
     </row>
@@ -12544,7 +12544,7 @@
       </c>
       <c r="S143" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T01:22:21Z</t>
+          <t>2026-10-06T23:57:00Z</t>
         </is>
       </c>
     </row>
@@ -12629,7 +12629,7 @@
       </c>
       <c r="S144" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T01:22:21Z</t>
+          <t>2026-10-06T23:57:00Z</t>
         </is>
       </c>
     </row>
@@ -12714,7 +12714,7 @@
       </c>
       <c r="S145" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T01:22:21Z</t>
+          <t>2026-10-06T23:57:00Z</t>
         </is>
       </c>
     </row>
@@ -12799,7 +12799,7 @@
       </c>
       <c r="S146" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T01:22:21Z</t>
+          <t>2026-10-06T23:57:00Z</t>
         </is>
       </c>
     </row>
@@ -12884,7 +12884,7 @@
       </c>
       <c r="S147" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T01:22:21Z</t>
+          <t>2026-10-06T23:57:00Z</t>
         </is>
       </c>
     </row>
@@ -12969,7 +12969,7 @@
       </c>
       <c r="S148" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T01:22:21Z</t>
+          <t>2026-10-06T23:57:00Z</t>
         </is>
       </c>
     </row>
@@ -13054,7 +13054,7 @@
       </c>
       <c r="S149" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T01:22:21Z</t>
+          <t>2026-10-06T23:57:00Z</t>
         </is>
       </c>
     </row>
@@ -13143,7 +13143,7 @@
       </c>
       <c r="S150" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T01:22:21Z</t>
+          <t>2026-10-06T23:57:00Z</t>
         </is>
       </c>
     </row>
@@ -13232,7 +13232,7 @@
       </c>
       <c r="S151" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T01:22:21Z</t>
+          <t>2026-10-06T23:57:00Z</t>
         </is>
       </c>
     </row>
@@ -13317,7 +13317,7 @@
       </c>
       <c r="S152" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T01:22:21Z</t>
+          <t>2026-10-06T23:57:00Z</t>
         </is>
       </c>
     </row>
@@ -13406,7 +13406,7 @@
       </c>
       <c r="S153" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T01:22:21Z</t>
+          <t>2026-10-06T23:57:00Z</t>
         </is>
       </c>
     </row>
@@ -13495,7 +13495,7 @@
       </c>
       <c r="S154" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T01:22:21Z</t>
+          <t>2026-10-06T23:57:00Z</t>
         </is>
       </c>
     </row>
@@ -13580,7 +13580,7 @@
       </c>
       <c r="S155" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T01:22:21Z</t>
+          <t>2026-10-06T23:57:00Z</t>
         </is>
       </c>
     </row>
@@ -13669,7 +13669,7 @@
       </c>
       <c r="S156" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T01:22:21Z</t>
+          <t>2026-10-06T23:57:00Z</t>
         </is>
       </c>
     </row>
@@ -13758,7 +13758,7 @@
       </c>
       <c r="S157" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T01:22:21Z</t>
+          <t>2026-10-06T23:57:00Z</t>
         </is>
       </c>
     </row>
@@ -13843,7 +13843,7 @@
       </c>
       <c r="S158" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T01:22:21Z</t>
+          <t>2026-10-06T23:57:00Z</t>
         </is>
       </c>
     </row>
@@ -13932,7 +13932,7 @@
       </c>
       <c r="S159" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T01:22:21Z</t>
+          <t>2026-10-06T23:57:00Z</t>
         </is>
       </c>
     </row>
@@ -14021,7 +14021,7 @@
       </c>
       <c r="S160" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T01:22:21Z</t>
+          <t>2026-10-06T23:57:00Z</t>
         </is>
       </c>
     </row>
@@ -14106,7 +14106,7 @@
       </c>
       <c r="S161" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T01:22:21Z</t>
+          <t>2026-10-06T23:57:00Z</t>
         </is>
       </c>
     </row>
@@ -14195,7 +14195,7 @@
       </c>
       <c r="S162" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T01:22:21Z</t>
+          <t>2026-10-06T23:57:00Z</t>
         </is>
       </c>
     </row>
@@ -14284,7 +14284,7 @@
       </c>
       <c r="S163" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T01:22:21Z</t>
+          <t>2026-10-06T23:57:00Z</t>
         </is>
       </c>
     </row>
@@ -14369,7 +14369,7 @@
       </c>
       <c r="S164" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T01:22:21Z</t>
+          <t>2026-10-06T23:57:00Z</t>
         </is>
       </c>
     </row>
@@ -14458,7 +14458,7 @@
       </c>
       <c r="S165" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T01:22:21Z</t>
+          <t>2026-10-06T23:57:00Z</t>
         </is>
       </c>
     </row>
@@ -14547,7 +14547,7 @@
       </c>
       <c r="S166" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T01:22:21Z</t>
+          <t>2026-10-06T23:57:00Z</t>
         </is>
       </c>
     </row>
@@ -14632,7 +14632,7 @@
       </c>
       <c r="S167" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T01:22:21Z</t>
+          <t>2026-10-06T23:57:00Z</t>
         </is>
       </c>
     </row>
@@ -14721,7 +14721,7 @@
       </c>
       <c r="S168" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T01:22:21Z</t>
+          <t>2026-10-06T23:57:00Z</t>
         </is>
       </c>
     </row>
@@ -14810,7 +14810,7 @@
       </c>
       <c r="S169" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T01:22:21Z</t>
+          <t>2026-10-06T23:57:00Z</t>
         </is>
       </c>
     </row>
@@ -14895,7 +14895,7 @@
       </c>
       <c r="S170" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T01:22:21Z</t>
+          <t>2026-10-06T23:57:00Z</t>
         </is>
       </c>
     </row>
@@ -14984,7 +14984,7 @@
       </c>
       <c r="S171" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T01:22:21Z</t>
+          <t>2026-10-06T23:57:00Z</t>
         </is>
       </c>
     </row>
@@ -15073,7 +15073,7 @@
       </c>
       <c r="S172" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T01:22:21Z</t>
+          <t>2026-10-06T23:57:00Z</t>
         </is>
       </c>
     </row>
@@ -15158,7 +15158,7 @@
       </c>
       <c r="S173" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T01:22:21Z</t>
+          <t>2026-10-06T23:57:00Z</t>
         </is>
       </c>
     </row>
@@ -15247,7 +15247,7 @@
       </c>
       <c r="S174" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T01:22:21Z</t>
+          <t>2026-10-06T23:57:00Z</t>
         </is>
       </c>
     </row>
@@ -15336,7 +15336,7 @@
       </c>
       <c r="S175" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T01:22:21Z</t>
+          <t>2026-10-06T23:57:00Z</t>
         </is>
       </c>
     </row>
@@ -15421,7 +15421,7 @@
       </c>
       <c r="S176" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T01:22:21Z</t>
+          <t>2026-10-06T23:57:00Z</t>
         </is>
       </c>
     </row>
@@ -15510,7 +15510,7 @@
       </c>
       <c r="S177" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T01:22:21Z</t>
+          <t>2026-10-06T23:57:00Z</t>
         </is>
       </c>
     </row>
@@ -15599,7 +15599,7 @@
       </c>
       <c r="S178" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T01:22:21Z</t>
+          <t>2026-10-06T23:57:00Z</t>
         </is>
       </c>
     </row>
@@ -15688,7 +15688,7 @@
       </c>
       <c r="S179" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T01:22:21Z</t>
+          <t>2026-10-06T23:57:00Z</t>
         </is>
       </c>
     </row>
@@ -15777,7 +15777,7 @@
       </c>
       <c r="S180" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T01:22:21Z</t>
+          <t>2026-10-06T23:57:00Z</t>
         </is>
       </c>
     </row>
@@ -15866,7 +15866,7 @@
       </c>
       <c r="S181" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T01:22:21Z</t>
+          <t>2026-10-06T23:57:00Z</t>
         </is>
       </c>
     </row>
@@ -15955,7 +15955,7 @@
       </c>
       <c r="S182" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T01:22:21Z</t>
+          <t>2026-10-06T23:57:00Z</t>
         </is>
       </c>
     </row>
@@ -16044,7 +16044,7 @@
       </c>
       <c r="S183" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T01:22:21Z</t>
+          <t>2026-10-06T23:57:00Z</t>
         </is>
       </c>
     </row>
@@ -16133,7 +16133,7 @@
       </c>
       <c r="S184" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T01:22:21Z</t>
+          <t>2026-10-06T23:57:00Z</t>
         </is>
       </c>
     </row>
@@ -16222,7 +16222,7 @@
       </c>
       <c r="S185" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T01:22:21Z</t>
+          <t>2026-10-06T23:57:00Z</t>
         </is>
       </c>
     </row>
@@ -16311,7 +16311,7 @@
       </c>
       <c r="S186" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T01:22:21Z</t>
+          <t>2026-10-06T23:57:00Z</t>
         </is>
       </c>
     </row>
@@ -16400,7 +16400,7 @@
       </c>
       <c r="S187" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T01:22:21Z</t>
+          <t>2026-10-06T23:57:00Z</t>
         </is>
       </c>
     </row>
@@ -16489,7 +16489,7 @@
       </c>
       <c r="S188" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T01:22:21Z</t>
+          <t>2026-10-06T23:57:00Z</t>
         </is>
       </c>
     </row>
@@ -16578,7 +16578,7 @@
       </c>
       <c r="S189" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T01:22:21Z</t>
+          <t>2026-10-06T23:57:00Z</t>
         </is>
       </c>
     </row>
@@ -16663,7 +16663,7 @@
       </c>
       <c r="S190" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T01:22:21Z</t>
+          <t>2026-10-06T23:57:00Z</t>
         </is>
       </c>
     </row>
@@ -16748,7 +16748,7 @@
       </c>
       <c r="S191" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T01:22:21Z</t>
+          <t>2026-10-06T23:57:00Z</t>
         </is>
       </c>
     </row>
@@ -16833,7 +16833,7 @@
       </c>
       <c r="S192" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T01:22:21Z</t>
+          <t>2026-10-06T23:57:00Z</t>
         </is>
       </c>
     </row>
@@ -16918,7 +16918,7 @@
       </c>
       <c r="S193" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T01:22:21Z</t>
+          <t>2026-10-06T23:57:00Z</t>
         </is>
       </c>
     </row>
@@ -17003,7 +17003,7 @@
       </c>
       <c r="S194" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T01:22:21Z</t>
+          <t>2026-10-06T23:57:00Z</t>
         </is>
       </c>
     </row>
@@ -17088,7 +17088,7 @@
       </c>
       <c r="S195" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T01:22:21Z</t>
+          <t>2026-10-06T23:57:00Z</t>
         </is>
       </c>
     </row>
@@ -17173,7 +17173,7 @@
       </c>
       <c r="S196" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T01:22:21Z</t>
+          <t>2026-10-06T23:57:00Z</t>
         </is>
       </c>
     </row>
@@ -17258,7 +17258,7 @@
       </c>
       <c r="S197" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T01:22:21Z</t>
+          <t>2026-10-06T23:57:00Z</t>
         </is>
       </c>
     </row>
@@ -17343,7 +17343,7 @@
       </c>
       <c r="S198" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T01:22:21Z</t>
+          <t>2026-10-06T23:57:00Z</t>
         </is>
       </c>
     </row>
@@ -17428,7 +17428,7 @@
       </c>
       <c r="S199" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T01:22:21Z</t>
+          <t>2026-10-06T23:57:00Z</t>
         </is>
       </c>
     </row>
@@ -17513,7 +17513,7 @@
       </c>
       <c r="S200" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T01:22:21Z</t>
+          <t>2026-10-06T23:57:00Z</t>
         </is>
       </c>
     </row>
@@ -17598,7 +17598,7 @@
       </c>
       <c r="S201" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T01:22:21Z</t>
+          <t>2026-10-06T23:57:00Z</t>
         </is>
       </c>
     </row>
@@ -17683,7 +17683,7 @@
       </c>
       <c r="S202" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T01:22:21Z</t>
+          <t>2026-10-06T23:57:00Z</t>
         </is>
       </c>
     </row>
@@ -17768,7 +17768,7 @@
       </c>
       <c r="S203" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T01:22:21Z</t>
+          <t>2026-10-06T23:57:00Z</t>
         </is>
       </c>
     </row>
@@ -17853,7 +17853,7 @@
       </c>
       <c r="S204" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T01:22:21Z</t>
+          <t>2026-10-06T23:57:00Z</t>
         </is>
       </c>
     </row>
@@ -17938,7 +17938,7 @@
       </c>
       <c r="S205" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T01:22:21Z</t>
+          <t>2026-10-06T23:57:00Z</t>
         </is>
       </c>
     </row>
@@ -18023,7 +18023,7 @@
       </c>
       <c r="S206" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T01:22:21Z</t>
+          <t>2026-10-06T23:57:00Z</t>
         </is>
       </c>
     </row>
@@ -18108,7 +18108,7 @@
       </c>
       <c r="S207" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T01:22:21Z</t>
+          <t>2026-10-06T23:57:00Z</t>
         </is>
       </c>
     </row>
@@ -18193,7 +18193,7 @@
       </c>
       <c r="S208" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T01:22:21Z</t>
+          <t>2026-10-06T23:57:00Z</t>
         </is>
       </c>
     </row>
@@ -18278,7 +18278,7 @@
       </c>
       <c r="S209" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T01:22:21Z</t>
+          <t>2026-10-06T23:57:00Z</t>
         </is>
       </c>
     </row>
@@ -18363,7 +18363,7 @@
       </c>
       <c r="S210" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T01:22:21Z</t>
+          <t>2026-10-06T23:57:00Z</t>
         </is>
       </c>
     </row>
@@ -18452,7 +18452,7 @@
       </c>
       <c r="S211" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T01:22:21Z</t>
+          <t>2026-10-06T23:57:00Z</t>
         </is>
       </c>
     </row>
@@ -18541,7 +18541,7 @@
       </c>
       <c r="S212" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T01:22:21Z</t>
+          <t>2026-10-06T23:57:00Z</t>
         </is>
       </c>
     </row>
@@ -18626,7 +18626,7 @@
       </c>
       <c r="S213" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T01:22:21Z</t>
+          <t>2026-10-06T23:57:00Z</t>
         </is>
       </c>
     </row>
@@ -18715,7 +18715,7 @@
       </c>
       <c r="S214" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T01:22:21Z</t>
+          <t>2026-10-06T23:57:00Z</t>
         </is>
       </c>
     </row>
@@ -18804,7 +18804,7 @@
       </c>
       <c r="S215" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T01:22:21Z</t>
+          <t>2026-10-06T23:57:00Z</t>
         </is>
       </c>
     </row>
@@ -18889,7 +18889,7 @@
       </c>
       <c r="S216" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T01:22:21Z</t>
+          <t>2026-10-06T23:57:00Z</t>
         </is>
       </c>
     </row>
@@ -18978,7 +18978,7 @@
       </c>
       <c r="S217" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T01:22:21Z</t>
+          <t>2026-10-06T23:57:00Z</t>
         </is>
       </c>
     </row>
@@ -19067,7 +19067,7 @@
       </c>
       <c r="S218" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T01:22:21Z</t>
+          <t>2026-10-06T23:57:00Z</t>
         </is>
       </c>
     </row>
@@ -19152,7 +19152,7 @@
       </c>
       <c r="S219" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T01:22:21Z</t>
+          <t>2026-10-06T23:57:00Z</t>
         </is>
       </c>
     </row>
@@ -19241,7 +19241,7 @@
       </c>
       <c r="S220" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T01:22:21Z</t>
+          <t>2026-10-06T23:57:00Z</t>
         </is>
       </c>
     </row>
@@ -19330,7 +19330,7 @@
       </c>
       <c r="S221" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T01:22:21Z</t>
+          <t>2026-10-06T23:57:00Z</t>
         </is>
       </c>
     </row>
@@ -19415,7 +19415,7 @@
       </c>
       <c r="S222" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T01:22:21Z</t>
+          <t>2026-10-06T23:57:00Z</t>
         </is>
       </c>
     </row>
@@ -19504,7 +19504,7 @@
       </c>
       <c r="S223" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T01:22:21Z</t>
+          <t>2026-10-06T23:57:00Z</t>
         </is>
       </c>
     </row>
@@ -19593,7 +19593,7 @@
       </c>
       <c r="S224" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T01:22:21Z</t>
+          <t>2026-10-06T23:57:00Z</t>
         </is>
       </c>
     </row>
@@ -19678,7 +19678,7 @@
       </c>
       <c r="S225" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T01:22:21Z</t>
+          <t>2026-10-06T23:57:00Z</t>
         </is>
       </c>
     </row>
@@ -19767,7 +19767,7 @@
       </c>
       <c r="S226" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T01:22:21Z</t>
+          <t>2026-10-06T23:57:00Z</t>
         </is>
       </c>
     </row>
@@ -19856,7 +19856,7 @@
       </c>
       <c r="S227" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T01:22:21Z</t>
+          <t>2026-10-06T23:57:00Z</t>
         </is>
       </c>
     </row>
@@ -19941,7 +19941,7 @@
       </c>
       <c r="S228" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T01:22:21Z</t>
+          <t>2026-10-06T23:57:00Z</t>
         </is>
       </c>
     </row>
@@ -20030,7 +20030,7 @@
       </c>
       <c r="S229" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T01:22:21Z</t>
+          <t>2026-10-06T23:57:00Z</t>
         </is>
       </c>
     </row>
@@ -20119,7 +20119,7 @@
       </c>
       <c r="S230" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T01:22:21Z</t>
+          <t>2026-10-06T23:57:00Z</t>
         </is>
       </c>
     </row>
@@ -20204,7 +20204,7 @@
       </c>
       <c r="S231" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T01:22:21Z</t>
+          <t>2026-10-06T23:57:00Z</t>
         </is>
       </c>
     </row>
@@ -20293,7 +20293,7 @@
       </c>
       <c r="S232" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T01:22:21Z</t>
+          <t>2026-10-06T23:57:00Z</t>
         </is>
       </c>
     </row>
@@ -20382,7 +20382,7 @@
       </c>
       <c r="S233" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T01:22:21Z</t>
+          <t>2026-10-06T23:57:00Z</t>
         </is>
       </c>
     </row>
@@ -20467,7 +20467,7 @@
       </c>
       <c r="S234" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T01:22:21Z</t>
+          <t>2026-10-06T23:57:00Z</t>
         </is>
       </c>
     </row>
@@ -20556,7 +20556,7 @@
       </c>
       <c r="S235" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T01:22:21Z</t>
+          <t>2026-10-06T23:57:00Z</t>
         </is>
       </c>
     </row>
@@ -20645,7 +20645,7 @@
       </c>
       <c r="S236" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T01:22:21Z</t>
+          <t>2026-10-06T23:57:00Z</t>
         </is>
       </c>
     </row>
@@ -20730,7 +20730,7 @@
       </c>
       <c r="S237" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T01:22:21Z</t>
+          <t>2026-10-06T23:57:00Z</t>
         </is>
       </c>
     </row>
@@ -20819,7 +20819,7 @@
       </c>
       <c r="S238" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T01:22:21Z</t>
+          <t>2026-10-06T23:57:00Z</t>
         </is>
       </c>
     </row>
@@ -20908,7 +20908,7 @@
       </c>
       <c r="S239" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T01:22:21Z</t>
+          <t>2026-10-06T23:57:00Z</t>
         </is>
       </c>
     </row>
@@ -20997,7 +20997,7 @@
       </c>
       <c r="S240" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T01:22:21Z</t>
+          <t>2026-10-06T23:57:00Z</t>
         </is>
       </c>
     </row>
@@ -21086,7 +21086,7 @@
       </c>
       <c r="S241" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T01:22:21Z</t>
+          <t>2026-10-06T23:57:00Z</t>
         </is>
       </c>
     </row>
@@ -21175,7 +21175,7 @@
       </c>
       <c r="S242" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T01:22:21Z</t>
+          <t>2026-10-06T23:57:00Z</t>
         </is>
       </c>
     </row>
@@ -21264,7 +21264,7 @@
       </c>
       <c r="S243" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T01:22:21Z</t>
+          <t>2026-10-06T23:57:00Z</t>
         </is>
       </c>
     </row>
@@ -21353,7 +21353,7 @@
       </c>
       <c r="S244" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T01:22:21Z</t>
+          <t>2026-10-06T23:57:00Z</t>
         </is>
       </c>
     </row>
@@ -21442,7 +21442,7 @@
       </c>
       <c r="S245" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T01:22:21Z</t>
+          <t>2026-10-06T23:57:00Z</t>
         </is>
       </c>
     </row>
@@ -21531,7 +21531,7 @@
       </c>
       <c r="S246" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T01:22:21Z</t>
+          <t>2026-10-06T23:57:00Z</t>
         </is>
       </c>
     </row>
@@ -21620,7 +21620,7 @@
       </c>
       <c r="S247" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T01:22:21Z</t>
+          <t>2026-10-06T23:57:00Z</t>
         </is>
       </c>
     </row>
@@ -21709,7 +21709,7 @@
       </c>
       <c r="S248" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T01:22:21Z</t>
+          <t>2026-10-06T23:57:00Z</t>
         </is>
       </c>
     </row>
@@ -21798,7 +21798,7 @@
       </c>
       <c r="S249" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T01:22:21Z</t>
+          <t>2026-10-06T23:57:00Z</t>
         </is>
       </c>
     </row>
@@ -21887,7 +21887,7 @@
       </c>
       <c r="S250" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T01:22:21Z</t>
+          <t>2026-10-06T23:57:00Z</t>
         </is>
       </c>
     </row>
@@ -22019,7 +22019,7 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T01:22:21Z</t>
+          <t>2026-10-06T23:57:00Z</t>
         </is>
       </c>
     </row>
@@ -22099,7 +22099,7 @@
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>{"dataset_id": "bcv_pib_sector_institucional_anual", "title": "Producto interno bruto por sector institucional anual", "table": "Variaciones porcentuales", "source_file": "5_2_1_si_anual.xlsx", "base": "2007", "price_type": "Precios constantes", "measure": "Variación porcentual interanual", "frequency": "Anual", "period": "2025", "year": 2025, "quarter": null, "classification": "Sector institucional", "component": "Impuestos netos sobre los productos", "value": 10.600260421283764, "unit": "Porcentaje", "status": "Preliminar", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/cuentas_macroeconomicas/5_2_1_si_anual.xlsx", "fetched_at": "2026-10-06T01:22:21Z"}</t>
+          <t>{"dataset_id": "bcv_pib_sector_institucional_anual", "title": "Producto interno bruto por sector institucional anual", "table": "Variaciones porcentuales", "source_file": "5_2_1_si_anual.xlsx", "base": "2007", "price_type": "Precios constantes", "measure": "Variación porcentual interanual", "frequency": "Anual", "period": "2025", "year": 2025, "quarter": null, "classification": "Sector institucional", "component": "Impuestos netos sobre los productos", "value": 10.600260421283764, "unit": "Porcentaje", "status": "Preliminar", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/cuentas_macroeconomicas/5_2_1_si_anual.xlsx", "fetched_at": "2026-10-06T23:57:00Z"}</t>
         </is>
       </c>
     </row>

--- a/assets/data/bcv/excel/ove_bcv_pib_sector_institucional_anual.xlsx
+++ b/assets/data/bcv/excel/ove_bcv_pib_sector_institucional_anual.xlsx
@@ -736,7 +736,7 @@
       </c>
       <c r="S7" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T23:57:00Z</t>
+          <t>2026-10-07T19:19:48Z</t>
         </is>
       </c>
     </row>
@@ -821,7 +821,7 @@
       </c>
       <c r="S8" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T23:57:00Z</t>
+          <t>2026-10-07T19:19:48Z</t>
         </is>
       </c>
     </row>
@@ -906,7 +906,7 @@
       </c>
       <c r="S9" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T23:57:00Z</t>
+          <t>2026-10-07T19:19:48Z</t>
         </is>
       </c>
     </row>
@@ -991,7 +991,7 @@
       </c>
       <c r="S10" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T23:57:00Z</t>
+          <t>2026-10-07T19:19:48Z</t>
         </is>
       </c>
     </row>
@@ -1076,7 +1076,7 @@
       </c>
       <c r="S11" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T23:57:00Z</t>
+          <t>2026-10-07T19:19:48Z</t>
         </is>
       </c>
     </row>
@@ -1161,7 +1161,7 @@
       </c>
       <c r="S12" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T23:57:00Z</t>
+          <t>2026-10-07T19:19:48Z</t>
         </is>
       </c>
     </row>
@@ -1246,7 +1246,7 @@
       </c>
       <c r="S13" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T23:57:00Z</t>
+          <t>2026-10-07T19:19:48Z</t>
         </is>
       </c>
     </row>
@@ -1331,7 +1331,7 @@
       </c>
       <c r="S14" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T23:57:00Z</t>
+          <t>2026-10-07T19:19:48Z</t>
         </is>
       </c>
     </row>
@@ -1416,7 +1416,7 @@
       </c>
       <c r="S15" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T23:57:00Z</t>
+          <t>2026-10-07T19:19:48Z</t>
         </is>
       </c>
     </row>
@@ -1501,7 +1501,7 @@
       </c>
       <c r="S16" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T23:57:00Z</t>
+          <t>2026-10-07T19:19:48Z</t>
         </is>
       </c>
     </row>
@@ -1586,7 +1586,7 @@
       </c>
       <c r="S17" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T23:57:00Z</t>
+          <t>2026-10-07T19:19:48Z</t>
         </is>
       </c>
     </row>
@@ -1671,7 +1671,7 @@
       </c>
       <c r="S18" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T23:57:00Z</t>
+          <t>2026-10-07T19:19:48Z</t>
         </is>
       </c>
     </row>
@@ -1756,7 +1756,7 @@
       </c>
       <c r="S19" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T23:57:00Z</t>
+          <t>2026-10-07T19:19:48Z</t>
         </is>
       </c>
     </row>
@@ -1841,7 +1841,7 @@
       </c>
       <c r="S20" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T23:57:00Z</t>
+          <t>2026-10-07T19:19:48Z</t>
         </is>
       </c>
     </row>
@@ -1926,7 +1926,7 @@
       </c>
       <c r="S21" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T23:57:00Z</t>
+          <t>2026-10-07T19:19:48Z</t>
         </is>
       </c>
     </row>
@@ -2011,7 +2011,7 @@
       </c>
       <c r="S22" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T23:57:00Z</t>
+          <t>2026-10-07T19:19:48Z</t>
         </is>
       </c>
     </row>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="S23" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T23:57:00Z</t>
+          <t>2026-10-07T19:19:48Z</t>
         </is>
       </c>
     </row>
@@ -2181,7 +2181,7 @@
       </c>
       <c r="S24" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T23:57:00Z</t>
+          <t>2026-10-07T19:19:48Z</t>
         </is>
       </c>
     </row>
@@ -2266,7 +2266,7 @@
       </c>
       <c r="S25" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T23:57:00Z</t>
+          <t>2026-10-07T19:19:48Z</t>
         </is>
       </c>
     </row>
@@ -2351,7 +2351,7 @@
       </c>
       <c r="S26" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T23:57:00Z</t>
+          <t>2026-10-07T19:19:48Z</t>
         </is>
       </c>
     </row>
@@ -2436,7 +2436,7 @@
       </c>
       <c r="S27" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T23:57:00Z</t>
+          <t>2026-10-07T19:19:48Z</t>
         </is>
       </c>
     </row>
@@ -2525,7 +2525,7 @@
       </c>
       <c r="S28" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T23:57:00Z</t>
+          <t>2026-10-07T19:19:48Z</t>
         </is>
       </c>
     </row>
@@ -2614,7 +2614,7 @@
       </c>
       <c r="S29" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T23:57:00Z</t>
+          <t>2026-10-07T19:19:48Z</t>
         </is>
       </c>
     </row>
@@ -2699,7 +2699,7 @@
       </c>
       <c r="S30" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T23:57:00Z</t>
+          <t>2026-10-07T19:19:48Z</t>
         </is>
       </c>
     </row>
@@ -2788,7 +2788,7 @@
       </c>
       <c r="S31" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T23:57:00Z</t>
+          <t>2026-10-07T19:19:48Z</t>
         </is>
       </c>
     </row>
@@ -2877,7 +2877,7 @@
       </c>
       <c r="S32" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T23:57:00Z</t>
+          <t>2026-10-07T19:19:48Z</t>
         </is>
       </c>
     </row>
@@ -2962,7 +2962,7 @@
       </c>
       <c r="S33" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T23:57:00Z</t>
+          <t>2026-10-07T19:19:48Z</t>
         </is>
       </c>
     </row>
@@ -3051,7 +3051,7 @@
       </c>
       <c r="S34" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T23:57:00Z</t>
+          <t>2026-10-07T19:19:48Z</t>
         </is>
       </c>
     </row>
@@ -3140,7 +3140,7 @@
       </c>
       <c r="S35" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T23:57:00Z</t>
+          <t>2026-10-07T19:19:48Z</t>
         </is>
       </c>
     </row>
@@ -3225,7 +3225,7 @@
       </c>
       <c r="S36" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T23:57:00Z</t>
+          <t>2026-10-07T19:19:48Z</t>
         </is>
       </c>
     </row>
@@ -3314,7 +3314,7 @@
       </c>
       <c r="S37" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T23:57:00Z</t>
+          <t>2026-10-07T19:19:48Z</t>
         </is>
       </c>
     </row>
@@ -3403,7 +3403,7 @@
       </c>
       <c r="S38" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T23:57:00Z</t>
+          <t>2026-10-07T19:19:48Z</t>
         </is>
       </c>
     </row>
@@ -3488,7 +3488,7 @@
       </c>
       <c r="S39" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T23:57:00Z</t>
+          <t>2026-10-07T19:19:48Z</t>
         </is>
       </c>
     </row>
@@ -3577,7 +3577,7 @@
       </c>
       <c r="S40" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T23:57:00Z</t>
+          <t>2026-10-07T19:19:48Z</t>
         </is>
       </c>
     </row>
@@ -3666,7 +3666,7 @@
       </c>
       <c r="S41" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T23:57:00Z</t>
+          <t>2026-10-07T19:19:48Z</t>
         </is>
       </c>
     </row>
@@ -3751,7 +3751,7 @@
       </c>
       <c r="S42" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T23:57:00Z</t>
+          <t>2026-10-07T19:19:48Z</t>
         </is>
       </c>
     </row>
@@ -3840,7 +3840,7 @@
       </c>
       <c r="S43" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T23:57:00Z</t>
+          <t>2026-10-07T19:19:48Z</t>
         </is>
       </c>
     </row>
@@ -3929,7 +3929,7 @@
       </c>
       <c r="S44" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T23:57:00Z</t>
+          <t>2026-10-07T19:19:48Z</t>
         </is>
       </c>
     </row>
@@ -4014,7 +4014,7 @@
       </c>
       <c r="S45" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T23:57:00Z</t>
+          <t>2026-10-07T19:19:48Z</t>
         </is>
       </c>
     </row>
@@ -4103,7 +4103,7 @@
       </c>
       <c r="S46" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T23:57:00Z</t>
+          <t>2026-10-07T19:19:48Z</t>
         </is>
       </c>
     </row>
@@ -4192,7 +4192,7 @@
       </c>
       <c r="S47" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T23:57:00Z</t>
+          <t>2026-10-07T19:19:48Z</t>
         </is>
       </c>
     </row>
@@ -4277,7 +4277,7 @@
       </c>
       <c r="S48" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T23:57:00Z</t>
+          <t>2026-10-07T19:19:48Z</t>
         </is>
       </c>
     </row>
@@ -4366,7 +4366,7 @@
       </c>
       <c r="S49" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T23:57:00Z</t>
+          <t>2026-10-07T19:19:48Z</t>
         </is>
       </c>
     </row>
@@ -4455,7 +4455,7 @@
       </c>
       <c r="S50" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T23:57:00Z</t>
+          <t>2026-10-07T19:19:48Z</t>
         </is>
       </c>
     </row>
@@ -4540,7 +4540,7 @@
       </c>
       <c r="S51" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T23:57:00Z</t>
+          <t>2026-10-07T19:19:48Z</t>
         </is>
       </c>
     </row>
@@ -4629,7 +4629,7 @@
       </c>
       <c r="S52" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T23:57:00Z</t>
+          <t>2026-10-07T19:19:48Z</t>
         </is>
       </c>
     </row>
@@ -4718,7 +4718,7 @@
       </c>
       <c r="S53" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T23:57:00Z</t>
+          <t>2026-10-07T19:19:48Z</t>
         </is>
       </c>
     </row>
@@ -4803,7 +4803,7 @@
       </c>
       <c r="S54" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T23:57:00Z</t>
+          <t>2026-10-07T19:19:48Z</t>
         </is>
       </c>
     </row>
@@ -4892,7 +4892,7 @@
       </c>
       <c r="S55" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T23:57:00Z</t>
+          <t>2026-10-07T19:19:48Z</t>
         </is>
       </c>
     </row>
@@ -4981,7 +4981,7 @@
       </c>
       <c r="S56" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T23:57:00Z</t>
+          <t>2026-10-07T19:19:48Z</t>
         </is>
       </c>
     </row>
@@ -5070,7 +5070,7 @@
       </c>
       <c r="S57" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T23:57:00Z</t>
+          <t>2026-10-07T19:19:48Z</t>
         </is>
       </c>
     </row>
@@ -5159,7 +5159,7 @@
       </c>
       <c r="S58" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T23:57:00Z</t>
+          <t>2026-10-07T19:19:48Z</t>
         </is>
       </c>
     </row>
@@ -5248,7 +5248,7 @@
       </c>
       <c r="S59" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T23:57:00Z</t>
+          <t>2026-10-07T19:19:48Z</t>
         </is>
       </c>
     </row>
@@ -5337,7 +5337,7 @@
       </c>
       <c r="S60" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T23:57:00Z</t>
+          <t>2026-10-07T19:19:48Z</t>
         </is>
       </c>
     </row>
@@ -5426,7 +5426,7 @@
       </c>
       <c r="S61" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T23:57:00Z</t>
+          <t>2026-10-07T19:19:48Z</t>
         </is>
       </c>
     </row>
@@ -5515,7 +5515,7 @@
       </c>
       <c r="S62" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T23:57:00Z</t>
+          <t>2026-10-07T19:19:48Z</t>
         </is>
       </c>
     </row>
@@ -5604,7 +5604,7 @@
       </c>
       <c r="S63" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T23:57:00Z</t>
+          <t>2026-10-07T19:19:48Z</t>
         </is>
       </c>
     </row>
@@ -5693,7 +5693,7 @@
       </c>
       <c r="S64" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T23:57:00Z</t>
+          <t>2026-10-07T19:19:48Z</t>
         </is>
       </c>
     </row>
@@ -5782,7 +5782,7 @@
       </c>
       <c r="S65" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T23:57:00Z</t>
+          <t>2026-10-07T19:19:48Z</t>
         </is>
       </c>
     </row>
@@ -5871,7 +5871,7 @@
       </c>
       <c r="S66" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T23:57:00Z</t>
+          <t>2026-10-07T19:19:48Z</t>
         </is>
       </c>
     </row>
@@ -5960,7 +5960,7 @@
       </c>
       <c r="S67" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T23:57:00Z</t>
+          <t>2026-10-07T19:19:48Z</t>
         </is>
       </c>
     </row>
@@ -6045,7 +6045,7 @@
       </c>
       <c r="S68" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T23:57:00Z</t>
+          <t>2026-10-07T19:19:48Z</t>
         </is>
       </c>
     </row>
@@ -6130,7 +6130,7 @@
       </c>
       <c r="S69" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T23:57:00Z</t>
+          <t>2026-10-07T19:19:48Z</t>
         </is>
       </c>
     </row>
@@ -6215,7 +6215,7 @@
       </c>
       <c r="S70" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T23:57:00Z</t>
+          <t>2026-10-07T19:19:48Z</t>
         </is>
       </c>
     </row>
@@ -6300,7 +6300,7 @@
       </c>
       <c r="S71" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T23:57:00Z</t>
+          <t>2026-10-07T19:19:48Z</t>
         </is>
       </c>
     </row>
@@ -6385,7 +6385,7 @@
       </c>
       <c r="S72" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T23:57:00Z</t>
+          <t>2026-10-07T19:19:48Z</t>
         </is>
       </c>
     </row>
@@ -6470,7 +6470,7 @@
       </c>
       <c r="S73" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T23:57:00Z</t>
+          <t>2026-10-07T19:19:48Z</t>
         </is>
       </c>
     </row>
@@ -6555,7 +6555,7 @@
       </c>
       <c r="S74" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T23:57:00Z</t>
+          <t>2026-10-07T19:19:48Z</t>
         </is>
       </c>
     </row>
@@ -6640,7 +6640,7 @@
       </c>
       <c r="S75" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T23:57:00Z</t>
+          <t>2026-10-07T19:19:48Z</t>
         </is>
       </c>
     </row>
@@ -6725,7 +6725,7 @@
       </c>
       <c r="S76" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T23:57:00Z</t>
+          <t>2026-10-07T19:19:48Z</t>
         </is>
       </c>
     </row>
@@ -6810,7 +6810,7 @@
       </c>
       <c r="S77" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T23:57:00Z</t>
+          <t>2026-10-07T19:19:48Z</t>
         </is>
       </c>
     </row>
@@ -6895,7 +6895,7 @@
       </c>
       <c r="S78" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T23:57:00Z</t>
+          <t>2026-10-07T19:19:48Z</t>
         </is>
       </c>
     </row>
@@ -6980,7 +6980,7 @@
       </c>
       <c r="S79" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T23:57:00Z</t>
+          <t>2026-10-07T19:19:48Z</t>
         </is>
       </c>
     </row>
@@ -7065,7 +7065,7 @@
       </c>
       <c r="S80" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T23:57:00Z</t>
+          <t>2026-10-07T19:19:48Z</t>
         </is>
       </c>
     </row>
@@ -7150,7 +7150,7 @@
       </c>
       <c r="S81" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T23:57:00Z</t>
+          <t>2026-10-07T19:19:48Z</t>
         </is>
       </c>
     </row>
@@ -7235,7 +7235,7 @@
       </c>
       <c r="S82" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T23:57:00Z</t>
+          <t>2026-10-07T19:19:48Z</t>
         </is>
       </c>
     </row>
@@ -7320,7 +7320,7 @@
       </c>
       <c r="S83" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T23:57:00Z</t>
+          <t>2026-10-07T19:19:48Z</t>
         </is>
       </c>
     </row>
@@ -7405,7 +7405,7 @@
       </c>
       <c r="S84" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T23:57:00Z</t>
+          <t>2026-10-07T19:19:48Z</t>
         </is>
       </c>
     </row>
@@ -7490,7 +7490,7 @@
       </c>
       <c r="S85" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T23:57:00Z</t>
+          <t>2026-10-07T19:19:48Z</t>
         </is>
       </c>
     </row>
@@ -7575,7 +7575,7 @@
       </c>
       <c r="S86" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T23:57:00Z</t>
+          <t>2026-10-07T19:19:48Z</t>
         </is>
       </c>
     </row>
@@ -7660,7 +7660,7 @@
       </c>
       <c r="S87" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T23:57:00Z</t>
+          <t>2026-10-07T19:19:48Z</t>
         </is>
       </c>
     </row>
@@ -7745,7 +7745,7 @@
       </c>
       <c r="S88" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T23:57:00Z</t>
+          <t>2026-10-07T19:19:48Z</t>
         </is>
       </c>
     </row>
@@ -7834,7 +7834,7 @@
       </c>
       <c r="S89" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T23:57:00Z</t>
+          <t>2026-10-07T19:19:48Z</t>
         </is>
       </c>
     </row>
@@ -7923,7 +7923,7 @@
       </c>
       <c r="S90" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T23:57:00Z</t>
+          <t>2026-10-07T19:19:48Z</t>
         </is>
       </c>
     </row>
@@ -8008,7 +8008,7 @@
       </c>
       <c r="S91" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T23:57:00Z</t>
+          <t>2026-10-07T19:19:48Z</t>
         </is>
       </c>
     </row>
@@ -8097,7 +8097,7 @@
       </c>
       <c r="S92" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T23:57:00Z</t>
+          <t>2026-10-07T19:19:48Z</t>
         </is>
       </c>
     </row>
@@ -8186,7 +8186,7 @@
       </c>
       <c r="S93" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T23:57:00Z</t>
+          <t>2026-10-07T19:19:48Z</t>
         </is>
       </c>
     </row>
@@ -8271,7 +8271,7 @@
       </c>
       <c r="S94" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T23:57:00Z</t>
+          <t>2026-10-07T19:19:48Z</t>
         </is>
       </c>
     </row>
@@ -8360,7 +8360,7 @@
       </c>
       <c r="S95" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T23:57:00Z</t>
+          <t>2026-10-07T19:19:48Z</t>
         </is>
       </c>
     </row>
@@ -8449,7 +8449,7 @@
       </c>
       <c r="S96" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T23:57:00Z</t>
+          <t>2026-10-07T19:19:48Z</t>
         </is>
       </c>
     </row>
@@ -8534,7 +8534,7 @@
       </c>
       <c r="S97" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T23:57:00Z</t>
+          <t>2026-10-07T19:19:48Z</t>
         </is>
       </c>
     </row>
@@ -8623,7 +8623,7 @@
       </c>
       <c r="S98" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T23:57:00Z</t>
+          <t>2026-10-07T19:19:48Z</t>
         </is>
       </c>
     </row>
@@ -8712,7 +8712,7 @@
       </c>
       <c r="S99" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T23:57:00Z</t>
+          <t>2026-10-07T19:19:48Z</t>
         </is>
       </c>
     </row>
@@ -8797,7 +8797,7 @@
       </c>
       <c r="S100" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T23:57:00Z</t>
+          <t>2026-10-07T19:19:48Z</t>
         </is>
       </c>
     </row>
@@ -8886,7 +8886,7 @@
       </c>
       <c r="S101" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T23:57:00Z</t>
+          <t>2026-10-07T19:19:48Z</t>
         </is>
       </c>
     </row>
@@ -8975,7 +8975,7 @@
       </c>
       <c r="S102" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T23:57:00Z</t>
+          <t>2026-10-07T19:19:48Z</t>
         </is>
       </c>
     </row>
@@ -9060,7 +9060,7 @@
       </c>
       <c r="S103" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T23:57:00Z</t>
+          <t>2026-10-07T19:19:48Z</t>
         </is>
       </c>
     </row>
@@ -9149,7 +9149,7 @@
       </c>
       <c r="S104" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T23:57:00Z</t>
+          <t>2026-10-07T19:19:48Z</t>
         </is>
       </c>
     </row>
@@ -9238,7 +9238,7 @@
       </c>
       <c r="S105" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T23:57:00Z</t>
+          <t>2026-10-07T19:19:48Z</t>
         </is>
       </c>
     </row>
@@ -9323,7 +9323,7 @@
       </c>
       <c r="S106" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T23:57:00Z</t>
+          <t>2026-10-07T19:19:48Z</t>
         </is>
       </c>
     </row>
@@ -9412,7 +9412,7 @@
       </c>
       <c r="S107" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T23:57:00Z</t>
+          <t>2026-10-07T19:19:48Z</t>
         </is>
       </c>
     </row>
@@ -9501,7 +9501,7 @@
       </c>
       <c r="S108" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T23:57:00Z</t>
+          <t>2026-10-07T19:19:48Z</t>
         </is>
       </c>
     </row>
@@ -9586,7 +9586,7 @@
       </c>
       <c r="S109" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T23:57:00Z</t>
+          <t>2026-10-07T19:19:48Z</t>
         </is>
       </c>
     </row>
@@ -9675,7 +9675,7 @@
       </c>
       <c r="S110" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T23:57:00Z</t>
+          <t>2026-10-07T19:19:48Z</t>
         </is>
       </c>
     </row>
@@ -9764,7 +9764,7 @@
       </c>
       <c r="S111" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T23:57:00Z</t>
+          <t>2026-10-07T19:19:48Z</t>
         </is>
       </c>
     </row>
@@ -9849,7 +9849,7 @@
       </c>
       <c r="S112" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T23:57:00Z</t>
+          <t>2026-10-07T19:19:48Z</t>
         </is>
       </c>
     </row>
@@ -9938,7 +9938,7 @@
       </c>
       <c r="S113" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T23:57:00Z</t>
+          <t>2026-10-07T19:19:48Z</t>
         </is>
       </c>
     </row>
@@ -10027,7 +10027,7 @@
       </c>
       <c r="S114" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T23:57:00Z</t>
+          <t>2026-10-07T19:19:48Z</t>
         </is>
       </c>
     </row>
@@ -10112,7 +10112,7 @@
       </c>
       <c r="S115" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T23:57:00Z</t>
+          <t>2026-10-07T19:19:48Z</t>
         </is>
       </c>
     </row>
@@ -10201,7 +10201,7 @@
       </c>
       <c r="S116" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T23:57:00Z</t>
+          <t>2026-10-07T19:19:48Z</t>
         </is>
       </c>
     </row>
@@ -10290,7 +10290,7 @@
       </c>
       <c r="S117" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T23:57:00Z</t>
+          <t>2026-10-07T19:19:48Z</t>
         </is>
       </c>
     </row>
@@ -10379,7 +10379,7 @@
       </c>
       <c r="S118" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T23:57:00Z</t>
+          <t>2026-10-07T19:19:48Z</t>
         </is>
       </c>
     </row>
@@ -10468,7 +10468,7 @@
       </c>
       <c r="S119" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T23:57:00Z</t>
+          <t>2026-10-07T19:19:48Z</t>
         </is>
       </c>
     </row>
@@ -10557,7 +10557,7 @@
       </c>
       <c r="S120" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T23:57:00Z</t>
+          <t>2026-10-07T19:19:48Z</t>
         </is>
       </c>
     </row>
@@ -10646,7 +10646,7 @@
       </c>
       <c r="S121" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T23:57:00Z</t>
+          <t>2026-10-07T19:19:48Z</t>
         </is>
       </c>
     </row>
@@ -10735,7 +10735,7 @@
       </c>
       <c r="S122" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T23:57:00Z</t>
+          <t>2026-10-07T19:19:48Z</t>
         </is>
       </c>
     </row>
@@ -10824,7 +10824,7 @@
       </c>
       <c r="S123" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T23:57:00Z</t>
+          <t>2026-10-07T19:19:48Z</t>
         </is>
       </c>
     </row>
@@ -10913,7 +10913,7 @@
       </c>
       <c r="S124" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T23:57:00Z</t>
+          <t>2026-10-07T19:19:48Z</t>
         </is>
       </c>
     </row>
@@ -11002,7 +11002,7 @@
       </c>
       <c r="S125" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T23:57:00Z</t>
+          <t>2026-10-07T19:19:48Z</t>
         </is>
       </c>
     </row>
@@ -11091,7 +11091,7 @@
       </c>
       <c r="S126" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T23:57:00Z</t>
+          <t>2026-10-07T19:19:48Z</t>
         </is>
       </c>
     </row>
@@ -11180,7 +11180,7 @@
       </c>
       <c r="S127" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T23:57:00Z</t>
+          <t>2026-10-07T19:19:48Z</t>
         </is>
       </c>
     </row>
@@ -11269,7 +11269,7 @@
       </c>
       <c r="S128" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T23:57:00Z</t>
+          <t>2026-10-07T19:19:48Z</t>
         </is>
       </c>
     </row>
@@ -11354,7 +11354,7 @@
       </c>
       <c r="S129" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T23:57:00Z</t>
+          <t>2026-10-07T19:19:48Z</t>
         </is>
       </c>
     </row>
@@ -11439,7 +11439,7 @@
       </c>
       <c r="S130" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T23:57:00Z</t>
+          <t>2026-10-07T19:19:48Z</t>
         </is>
       </c>
     </row>
@@ -11524,7 +11524,7 @@
       </c>
       <c r="S131" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T23:57:00Z</t>
+          <t>2026-10-07T19:19:48Z</t>
         </is>
       </c>
     </row>
@@ -11609,7 +11609,7 @@
       </c>
       <c r="S132" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T23:57:00Z</t>
+          <t>2026-10-07T19:19:48Z</t>
         </is>
       </c>
     </row>
@@ -11694,7 +11694,7 @@
       </c>
       <c r="S133" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T23:57:00Z</t>
+          <t>2026-10-07T19:19:48Z</t>
         </is>
       </c>
     </row>
@@ -11779,7 +11779,7 @@
       </c>
       <c r="S134" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T23:57:00Z</t>
+          <t>2026-10-07T19:19:48Z</t>
         </is>
       </c>
     </row>
@@ -11864,7 +11864,7 @@
       </c>
       <c r="S135" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T23:57:00Z</t>
+          <t>2026-10-07T19:19:48Z</t>
         </is>
       </c>
     </row>
@@ -11949,7 +11949,7 @@
       </c>
       <c r="S136" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T23:57:00Z</t>
+          <t>2026-10-07T19:19:48Z</t>
         </is>
       </c>
     </row>
@@ -12034,7 +12034,7 @@
       </c>
       <c r="S137" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T23:57:00Z</t>
+          <t>2026-10-07T19:19:48Z</t>
         </is>
       </c>
     </row>
@@ -12119,7 +12119,7 @@
       </c>
       <c r="S138" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T23:57:00Z</t>
+          <t>2026-10-07T19:19:48Z</t>
         </is>
       </c>
     </row>
@@ -12204,7 +12204,7 @@
       </c>
       <c r="S139" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T23:57:00Z</t>
+          <t>2026-10-07T19:19:48Z</t>
         </is>
       </c>
     </row>
@@ -12289,7 +12289,7 @@
       </c>
       <c r="S140" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T23:57:00Z</t>
+          <t>2026-10-07T19:19:48Z</t>
         </is>
       </c>
     </row>
@@ -12374,7 +12374,7 @@
       </c>
       <c r="S141" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T23:57:00Z</t>
+          <t>2026-10-07T19:19:48Z</t>
         </is>
       </c>
     </row>
@@ -12459,7 +12459,7 @@
       </c>
       <c r="S142" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T23:57:00Z</t>
+          <t>2026-10-07T19:19:48Z</t>
         </is>
       </c>
     </row>
@@ -12544,7 +12544,7 @@
       </c>
       <c r="S143" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T23:57:00Z</t>
+          <t>2026-10-07T19:19:48Z</t>
         </is>
       </c>
     </row>
@@ -12629,7 +12629,7 @@
       </c>
       <c r="S144" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T23:57:00Z</t>
+          <t>2026-10-07T19:19:48Z</t>
         </is>
       </c>
     </row>
@@ -12714,7 +12714,7 @@
       </c>
       <c r="S145" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T23:57:00Z</t>
+          <t>2026-10-07T19:19:48Z</t>
         </is>
       </c>
     </row>
@@ -12799,7 +12799,7 @@
       </c>
       <c r="S146" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T23:57:00Z</t>
+          <t>2026-10-07T19:19:48Z</t>
         </is>
       </c>
     </row>
@@ -12884,7 +12884,7 @@
       </c>
       <c r="S147" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T23:57:00Z</t>
+          <t>2026-10-07T19:19:48Z</t>
         </is>
       </c>
     </row>
@@ -12969,7 +12969,7 @@
       </c>
       <c r="S148" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T23:57:00Z</t>
+          <t>2026-10-07T19:19:48Z</t>
         </is>
       </c>
     </row>
@@ -13054,7 +13054,7 @@
       </c>
       <c r="S149" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T23:57:00Z</t>
+          <t>2026-10-07T19:19:48Z</t>
         </is>
       </c>
     </row>
@@ -13143,7 +13143,7 @@
       </c>
       <c r="S150" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T23:57:00Z</t>
+          <t>2026-10-07T19:19:48Z</t>
         </is>
       </c>
     </row>
@@ -13232,7 +13232,7 @@
       </c>
       <c r="S151" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T23:57:00Z</t>
+          <t>2026-10-07T19:19:48Z</t>
         </is>
       </c>
     </row>
@@ -13317,7 +13317,7 @@
       </c>
       <c r="S152" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T23:57:00Z</t>
+          <t>2026-10-07T19:19:48Z</t>
         </is>
       </c>
     </row>
@@ -13406,7 +13406,7 @@
       </c>
       <c r="S153" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T23:57:00Z</t>
+          <t>2026-10-07T19:19:48Z</t>
         </is>
       </c>
     </row>
@@ -13495,7 +13495,7 @@
       </c>
       <c r="S154" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T23:57:00Z</t>
+          <t>2026-10-07T19:19:48Z</t>
         </is>
       </c>
     </row>
@@ -13580,7 +13580,7 @@
       </c>
       <c r="S155" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T23:57:00Z</t>
+          <t>2026-10-07T19:19:48Z</t>
         </is>
       </c>
     </row>
@@ -13669,7 +13669,7 @@
       </c>
       <c r="S156" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T23:57:00Z</t>
+          <t>2026-10-07T19:19:48Z</t>
         </is>
       </c>
     </row>
@@ -13758,7 +13758,7 @@
       </c>
       <c r="S157" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T23:57:00Z</t>
+          <t>2026-10-07T19:19:48Z</t>
         </is>
       </c>
     </row>
@@ -13843,7 +13843,7 @@
       </c>
       <c r="S158" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T23:57:00Z</t>
+          <t>2026-10-07T19:19:48Z</t>
         </is>
       </c>
     </row>
@@ -13932,7 +13932,7 @@
       </c>
       <c r="S159" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T23:57:00Z</t>
+          <t>2026-10-07T19:19:48Z</t>
         </is>
       </c>
     </row>
@@ -14021,7 +14021,7 @@
       </c>
       <c r="S160" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T23:57:00Z</t>
+          <t>2026-10-07T19:19:48Z</t>
         </is>
       </c>
     </row>
@@ -14106,7 +14106,7 @@
       </c>
       <c r="S161" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T23:57:00Z</t>
+          <t>2026-10-07T19:19:48Z</t>
         </is>
       </c>
     </row>
@@ -14195,7 +14195,7 @@
       </c>
       <c r="S162" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T23:57:00Z</t>
+          <t>2026-10-07T19:19:48Z</t>
         </is>
       </c>
     </row>
@@ -14284,7 +14284,7 @@
       </c>
       <c r="S163" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T23:57:00Z</t>
+          <t>2026-10-07T19:19:48Z</t>
         </is>
       </c>
     </row>
@@ -14369,7 +14369,7 @@
       </c>
       <c r="S164" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T23:57:00Z</t>
+          <t>2026-10-07T19:19:48Z</t>
         </is>
       </c>
     </row>
@@ -14458,7 +14458,7 @@
       </c>
       <c r="S165" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T23:57:00Z</t>
+          <t>2026-10-07T19:19:48Z</t>
         </is>
       </c>
     </row>
@@ -14547,7 +14547,7 @@
       </c>
       <c r="S166" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T23:57:00Z</t>
+          <t>2026-10-07T19:19:48Z</t>
         </is>
       </c>
     </row>
@@ -14632,7 +14632,7 @@
       </c>
       <c r="S167" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T23:57:00Z</t>
+          <t>2026-10-07T19:19:48Z</t>
         </is>
       </c>
     </row>
@@ -14721,7 +14721,7 @@
       </c>
       <c r="S168" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T23:57:00Z</t>
+          <t>2026-10-07T19:19:48Z</t>
         </is>
       </c>
     </row>
@@ -14810,7 +14810,7 @@
       </c>
       <c r="S169" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T23:57:00Z</t>
+          <t>2026-10-07T19:19:48Z</t>
         </is>
       </c>
     </row>
@@ -14895,7 +14895,7 @@
       </c>
       <c r="S170" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T23:57:00Z</t>
+          <t>2026-10-07T19:19:48Z</t>
         </is>
       </c>
     </row>
@@ -14984,7 +14984,7 @@
       </c>
       <c r="S171" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T23:57:00Z</t>
+          <t>2026-10-07T19:19:48Z</t>
         </is>
       </c>
     </row>
@@ -15073,7 +15073,7 @@
       </c>
       <c r="S172" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T23:57:00Z</t>
+          <t>2026-10-07T19:19:48Z</t>
         </is>
       </c>
     </row>
@@ -15158,7 +15158,7 @@
       </c>
       <c r="S173" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T23:57:00Z</t>
+          <t>2026-10-07T19:19:48Z</t>
         </is>
       </c>
     </row>
@@ -15247,7 +15247,7 @@
       </c>
       <c r="S174" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T23:57:00Z</t>
+          <t>2026-10-07T19:19:48Z</t>
         </is>
       </c>
     </row>
@@ -15336,7 +15336,7 @@
       </c>
       <c r="S175" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T23:57:00Z</t>
+          <t>2026-10-07T19:19:48Z</t>
         </is>
       </c>
     </row>
@@ -15421,7 +15421,7 @@
       </c>
       <c r="S176" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T23:57:00Z</t>
+          <t>2026-10-07T19:19:48Z</t>
         </is>
       </c>
     </row>
@@ -15510,7 +15510,7 @@
       </c>
       <c r="S177" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T23:57:00Z</t>
+          <t>2026-10-07T19:19:48Z</t>
         </is>
       </c>
     </row>
@@ -15599,7 +15599,7 @@
       </c>
       <c r="S178" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T23:57:00Z</t>
+          <t>2026-10-07T19:19:48Z</t>
         </is>
       </c>
     </row>
@@ -15688,7 +15688,7 @@
       </c>
       <c r="S179" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T23:57:00Z</t>
+          <t>2026-10-07T19:19:48Z</t>
         </is>
       </c>
     </row>
@@ -15777,7 +15777,7 @@
       </c>
       <c r="S180" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T23:57:00Z</t>
+          <t>2026-10-07T19:19:48Z</t>
         </is>
       </c>
     </row>
@@ -15866,7 +15866,7 @@
       </c>
       <c r="S181" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T23:57:00Z</t>
+          <t>2026-10-07T19:19:48Z</t>
         </is>
       </c>
     </row>
@@ -15955,7 +15955,7 @@
       </c>
       <c r="S182" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T23:57:00Z</t>
+          <t>2026-10-07T19:19:48Z</t>
         </is>
       </c>
     </row>
@@ -16044,7 +16044,7 @@
       </c>
       <c r="S183" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T23:57:00Z</t>
+          <t>2026-10-07T19:19:48Z</t>
         </is>
       </c>
     </row>
@@ -16133,7 +16133,7 @@
       </c>
       <c r="S184" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T23:57:00Z</t>
+          <t>2026-10-07T19:19:48Z</t>
         </is>
       </c>
     </row>
@@ -16222,7 +16222,7 @@
       </c>
       <c r="S185" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T23:57:00Z</t>
+          <t>2026-10-07T19:19:48Z</t>
         </is>
       </c>
     </row>
@@ -16311,7 +16311,7 @@
       </c>
       <c r="S186" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T23:57:00Z</t>
+          <t>2026-10-07T19:19:48Z</t>
         </is>
       </c>
     </row>
@@ -16400,7 +16400,7 @@
       </c>
       <c r="S187" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T23:57:00Z</t>
+          <t>2026-10-07T19:19:48Z</t>
         </is>
       </c>
     </row>
@@ -16489,7 +16489,7 @@
       </c>
       <c r="S188" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T23:57:00Z</t>
+          <t>2026-10-07T19:19:48Z</t>
         </is>
       </c>
     </row>
@@ -16578,7 +16578,7 @@
       </c>
       <c r="S189" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T23:57:00Z</t>
+          <t>2026-10-07T19:19:48Z</t>
         </is>
       </c>
     </row>
@@ -16663,7 +16663,7 @@
       </c>
       <c r="S190" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T23:57:00Z</t>
+          <t>2026-10-07T19:19:48Z</t>
         </is>
       </c>
     </row>
@@ -16748,7 +16748,7 @@
       </c>
       <c r="S191" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T23:57:00Z</t>
+          <t>2026-10-07T19:19:48Z</t>
         </is>
       </c>
     </row>
@@ -16833,7 +16833,7 @@
       </c>
       <c r="S192" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T23:57:00Z</t>
+          <t>2026-10-07T19:19:48Z</t>
         </is>
       </c>
     </row>
@@ -16918,7 +16918,7 @@
       </c>
       <c r="S193" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T23:57:00Z</t>
+          <t>2026-10-07T19:19:48Z</t>
         </is>
       </c>
     </row>
@@ -17003,7 +17003,7 @@
       </c>
       <c r="S194" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T23:57:00Z</t>
+          <t>2026-10-07T19:19:48Z</t>
         </is>
       </c>
     </row>
@@ -17088,7 +17088,7 @@
       </c>
       <c r="S195" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T23:57:00Z</t>
+          <t>2026-10-07T19:19:48Z</t>
         </is>
       </c>
     </row>
@@ -17173,7 +17173,7 @@
       </c>
       <c r="S196" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T23:57:00Z</t>
+          <t>2026-10-07T19:19:48Z</t>
         </is>
       </c>
     </row>
@@ -17258,7 +17258,7 @@
       </c>
       <c r="S197" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T23:57:00Z</t>
+          <t>2026-10-07T19:19:48Z</t>
         </is>
       </c>
     </row>
@@ -17343,7 +17343,7 @@
       </c>
       <c r="S198" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T23:57:00Z</t>
+          <t>2026-10-07T19:19:48Z</t>
         </is>
       </c>
     </row>
@@ -17428,7 +17428,7 @@
       </c>
       <c r="S199" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T23:57:00Z</t>
+          <t>2026-10-07T19:19:48Z</t>
         </is>
       </c>
     </row>
@@ -17513,7 +17513,7 @@
       </c>
       <c r="S200" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T23:57:00Z</t>
+          <t>2026-10-07T19:19:48Z</t>
         </is>
       </c>
     </row>
@@ -17598,7 +17598,7 @@
       </c>
       <c r="S201" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T23:57:00Z</t>
+          <t>2026-10-07T19:19:48Z</t>
         </is>
       </c>
     </row>
@@ -17683,7 +17683,7 @@
       </c>
       <c r="S202" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T23:57:00Z</t>
+          <t>2026-10-07T19:19:48Z</t>
         </is>
       </c>
     </row>
@@ -17768,7 +17768,7 @@
       </c>
       <c r="S203" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T23:57:00Z</t>
+          <t>2026-10-07T19:19:48Z</t>
         </is>
       </c>
     </row>
@@ -17853,7 +17853,7 @@
       </c>
       <c r="S204" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T23:57:00Z</t>
+          <t>2026-10-07T19:19:48Z</t>
         </is>
       </c>
     </row>
@@ -17938,7 +17938,7 @@
       </c>
       <c r="S205" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T23:57:00Z</t>
+          <t>2026-10-07T19:19:48Z</t>
         </is>
       </c>
     </row>
@@ -18023,7 +18023,7 @@
       </c>
       <c r="S206" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T23:57:00Z</t>
+          <t>2026-10-07T19:19:48Z</t>
         </is>
       </c>
     </row>
@@ -18108,7 +18108,7 @@
       </c>
       <c r="S207" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T23:57:00Z</t>
+          <t>2026-10-07T19:19:48Z</t>
         </is>
       </c>
     </row>
@@ -18193,7 +18193,7 @@
       </c>
       <c r="S208" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T23:57:00Z</t>
+          <t>2026-10-07T19:19:48Z</t>
         </is>
       </c>
     </row>
@@ -18278,7 +18278,7 @@
       </c>
       <c r="S209" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T23:57:00Z</t>
+          <t>2026-10-07T19:19:48Z</t>
         </is>
       </c>
     </row>
@@ -18363,7 +18363,7 @@
       </c>
       <c r="S210" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T23:57:00Z</t>
+          <t>2026-10-07T19:19:48Z</t>
         </is>
       </c>
     </row>
@@ -18452,7 +18452,7 @@
       </c>
       <c r="S211" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T23:57:00Z</t>
+          <t>2026-10-07T19:19:48Z</t>
         </is>
       </c>
     </row>
@@ -18541,7 +18541,7 @@
       </c>
       <c r="S212" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T23:57:00Z</t>
+          <t>2026-10-07T19:19:48Z</t>
         </is>
       </c>
     </row>
@@ -18626,7 +18626,7 @@
       </c>
       <c r="S213" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T23:57:00Z</t>
+          <t>2026-10-07T19:19:48Z</t>
         </is>
       </c>
     </row>
@@ -18715,7 +18715,7 @@
       </c>
       <c r="S214" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T23:57:00Z</t>
+          <t>2026-10-07T19:19:48Z</t>
         </is>
       </c>
     </row>
@@ -18804,7 +18804,7 @@
       </c>
       <c r="S215" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T23:57:00Z</t>
+          <t>2026-10-07T19:19:48Z</t>
         </is>
       </c>
     </row>
@@ -18889,7 +18889,7 @@
       </c>
       <c r="S216" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T23:57:00Z</t>
+          <t>2026-10-07T19:19:48Z</t>
         </is>
       </c>
     </row>
@@ -18978,7 +18978,7 @@
       </c>
       <c r="S217" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T23:57:00Z</t>
+          <t>2026-10-07T19:19:48Z</t>
         </is>
       </c>
     </row>
@@ -19067,7 +19067,7 @@
       </c>
       <c r="S218" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T23:57:00Z</t>
+          <t>2026-10-07T19:19:48Z</t>
         </is>
       </c>
     </row>
@@ -19152,7 +19152,7 @@
       </c>
       <c r="S219" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T23:57:00Z</t>
+          <t>2026-10-07T19:19:48Z</t>
         </is>
       </c>
     </row>
@@ -19241,7 +19241,7 @@
       </c>
       <c r="S220" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T23:57:00Z</t>
+          <t>2026-10-07T19:19:48Z</t>
         </is>
       </c>
     </row>
@@ -19330,7 +19330,7 @@
       </c>
       <c r="S221" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T23:57:00Z</t>
+          <t>2026-10-07T19:19:48Z</t>
         </is>
       </c>
     </row>
@@ -19415,7 +19415,7 @@
       </c>
       <c r="S222" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T23:57:00Z</t>
+          <t>2026-10-07T19:19:48Z</t>
         </is>
       </c>
     </row>
@@ -19504,7 +19504,7 @@
       </c>
       <c r="S223" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T23:57:00Z</t>
+          <t>2026-10-07T19:19:48Z</t>
         </is>
       </c>
     </row>
@@ -19593,7 +19593,7 @@
       </c>
       <c r="S224" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T23:57:00Z</t>
+          <t>2026-10-07T19:19:48Z</t>
         </is>
       </c>
     </row>
@@ -19678,7 +19678,7 @@
       </c>
       <c r="S225" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T23:57:00Z</t>
+          <t>2026-10-07T19:19:48Z</t>
         </is>
       </c>
     </row>
@@ -19767,7 +19767,7 @@
       </c>
       <c r="S226" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T23:57:00Z</t>
+          <t>2026-10-07T19:19:48Z</t>
         </is>
       </c>
     </row>
@@ -19856,7 +19856,7 @@
       </c>
       <c r="S227" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T23:57:00Z</t>
+          <t>2026-10-07T19:19:48Z</t>
         </is>
       </c>
     </row>
@@ -19941,7 +19941,7 @@
       </c>
       <c r="S228" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T23:57:00Z</t>
+          <t>2026-10-07T19:19:48Z</t>
         </is>
       </c>
     </row>
@@ -20030,7 +20030,7 @@
       </c>
       <c r="S229" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T23:57:00Z</t>
+          <t>2026-10-07T19:19:48Z</t>
         </is>
       </c>
     </row>
@@ -20119,7 +20119,7 @@
       </c>
       <c r="S230" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T23:57:00Z</t>
+          <t>2026-10-07T19:19:48Z</t>
         </is>
       </c>
     </row>
@@ -20204,7 +20204,7 @@
       </c>
       <c r="S231" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T23:57:00Z</t>
+          <t>2026-10-07T19:19:48Z</t>
         </is>
       </c>
     </row>
@@ -20293,7 +20293,7 @@
       </c>
       <c r="S232" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T23:57:00Z</t>
+          <t>2026-10-07T19:19:48Z</t>
         </is>
       </c>
     </row>
@@ -20382,7 +20382,7 @@
       </c>
       <c r="S233" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T23:57:00Z</t>
+          <t>2026-10-07T19:19:48Z</t>
         </is>
       </c>
     </row>
@@ -20467,7 +20467,7 @@
       </c>
       <c r="S234" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T23:57:00Z</t>
+          <t>2026-10-07T19:19:48Z</t>
         </is>
       </c>
     </row>
@@ -20556,7 +20556,7 @@
       </c>
       <c r="S235" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T23:57:00Z</t>
+          <t>2026-10-07T19:19:48Z</t>
         </is>
       </c>
     </row>
@@ -20645,7 +20645,7 @@
       </c>
       <c r="S236" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T23:57:00Z</t>
+          <t>2026-10-07T19:19:48Z</t>
         </is>
       </c>
     </row>
@@ -20730,7 +20730,7 @@
       </c>
       <c r="S237" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T23:57:00Z</t>
+          <t>2026-10-07T19:19:48Z</t>
         </is>
       </c>
     </row>
@@ -20819,7 +20819,7 @@
       </c>
       <c r="S238" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T23:57:00Z</t>
+          <t>2026-10-07T19:19:48Z</t>
         </is>
       </c>
     </row>
@@ -20908,7 +20908,7 @@
       </c>
       <c r="S239" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T23:57:00Z</t>
+          <t>2026-10-07T19:19:48Z</t>
         </is>
       </c>
     </row>
@@ -20997,7 +20997,7 @@
       </c>
       <c r="S240" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T23:57:00Z</t>
+          <t>2026-10-07T19:19:48Z</t>
         </is>
       </c>
     </row>
@@ -21086,7 +21086,7 @@
       </c>
       <c r="S241" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T23:57:00Z</t>
+          <t>2026-10-07T19:19:48Z</t>
         </is>
       </c>
     </row>
@@ -21175,7 +21175,7 @@
       </c>
       <c r="S242" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T23:57:00Z</t>
+          <t>2026-10-07T19:19:48Z</t>
         </is>
       </c>
     </row>
@@ -21264,7 +21264,7 @@
       </c>
       <c r="S243" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T23:57:00Z</t>
+          <t>2026-10-07T19:19:48Z</t>
         </is>
       </c>
     </row>
@@ -21353,7 +21353,7 @@
       </c>
       <c r="S244" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T23:57:00Z</t>
+          <t>2026-10-07T19:19:48Z</t>
         </is>
       </c>
     </row>
@@ -21442,7 +21442,7 @@
       </c>
       <c r="S245" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T23:57:00Z</t>
+          <t>2026-10-07T19:19:48Z</t>
         </is>
       </c>
     </row>
@@ -21531,7 +21531,7 @@
       </c>
       <c r="S246" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T23:57:00Z</t>
+          <t>2026-10-07T19:19:48Z</t>
         </is>
       </c>
     </row>
@@ -21620,7 +21620,7 @@
       </c>
       <c r="S247" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T23:57:00Z</t>
+          <t>2026-10-07T19:19:48Z</t>
         </is>
       </c>
     </row>
@@ -21709,7 +21709,7 @@
       </c>
       <c r="S248" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T23:57:00Z</t>
+          <t>2026-10-07T19:19:48Z</t>
         </is>
       </c>
     </row>
@@ -21798,7 +21798,7 @@
       </c>
       <c r="S249" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T23:57:00Z</t>
+          <t>2026-10-07T19:19:48Z</t>
         </is>
       </c>
     </row>
@@ -21887,7 +21887,7 @@
       </c>
       <c r="S250" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T23:57:00Z</t>
+          <t>2026-10-07T19:19:48Z</t>
         </is>
       </c>
     </row>
@@ -22019,7 +22019,7 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T23:57:00Z</t>
+          <t>2026-10-07T19:19:48Z</t>
         </is>
       </c>
     </row>
@@ -22099,7 +22099,7 @@
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>{"dataset_id": "bcv_pib_sector_institucional_anual", "title": "Producto interno bruto por sector institucional anual", "table": "Variaciones porcentuales", "source_file": "5_2_1_si_anual.xlsx", "base": "2007", "price_type": "Precios constantes", "measure": "Variación porcentual interanual", "frequency": "Anual", "period": "2025", "year": 2025, "quarter": null, "classification": "Sector institucional", "component": "Impuestos netos sobre los productos", "value": 10.600260421283764, "unit": "Porcentaje", "status": "Preliminar", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/cuentas_macroeconomicas/5_2_1_si_anual.xlsx", "fetched_at": "2026-10-06T23:57:00Z"}</t>
+          <t>{"dataset_id": "bcv_pib_sector_institucional_anual", "title": "Producto interno bruto por sector institucional anual", "table": "Variaciones porcentuales", "source_file": "5_2_1_si_anual.xlsx", "base": "2007", "price_type": "Precios constantes", "measure": "Variación porcentual interanual", "frequency": "Anual", "period": "2025", "year": 2025, "quarter": null, "classification": "Sector institucional", "component": "Impuestos netos sobre los productos", "value": 10.600260421283764, "unit": "Porcentaje", "status": "Preliminar", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/cuentas_macroeconomicas/5_2_1_si_anual.xlsx", "fetched_at": "2026-10-07T19:19:48Z"}</t>
         </is>
       </c>
     </row>

--- a/assets/data/bcv/excel/ove_bcv_pib_sector_institucional_anual.xlsx
+++ b/assets/data/bcv/excel/ove_bcv_pib_sector_institucional_anual.xlsx
@@ -736,7 +736,7 @@
       </c>
       <c r="S7" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07T19:19:48Z</t>
+          <t>2026-10-08T00:18:15Z</t>
         </is>
       </c>
     </row>
@@ -821,7 +821,7 @@
       </c>
       <c r="S8" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07T19:19:48Z</t>
+          <t>2026-10-08T00:18:15Z</t>
         </is>
       </c>
     </row>
@@ -906,7 +906,7 @@
       </c>
       <c r="S9" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07T19:19:48Z</t>
+          <t>2026-10-08T00:18:15Z</t>
         </is>
       </c>
     </row>
@@ -991,7 +991,7 @@
       </c>
       <c r="S10" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07T19:19:48Z</t>
+          <t>2026-10-08T00:18:15Z</t>
         </is>
       </c>
     </row>
@@ -1076,7 +1076,7 @@
       </c>
       <c r="S11" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07T19:19:48Z</t>
+          <t>2026-10-08T00:18:15Z</t>
         </is>
       </c>
     </row>
@@ -1161,7 +1161,7 @@
       </c>
       <c r="S12" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07T19:19:48Z</t>
+          <t>2026-10-08T00:18:15Z</t>
         </is>
       </c>
     </row>
@@ -1246,7 +1246,7 @@
       </c>
       <c r="S13" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07T19:19:48Z</t>
+          <t>2026-10-08T00:18:15Z</t>
         </is>
       </c>
     </row>
@@ -1331,7 +1331,7 @@
       </c>
       <c r="S14" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07T19:19:48Z</t>
+          <t>2026-10-08T00:18:15Z</t>
         </is>
       </c>
     </row>
@@ -1416,7 +1416,7 @@
       </c>
       <c r="S15" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07T19:19:48Z</t>
+          <t>2026-10-08T00:18:15Z</t>
         </is>
       </c>
     </row>
@@ -1501,7 +1501,7 @@
       </c>
       <c r="S16" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07T19:19:48Z</t>
+          <t>2026-10-08T00:18:15Z</t>
         </is>
       </c>
     </row>
@@ -1586,7 +1586,7 @@
       </c>
       <c r="S17" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07T19:19:48Z</t>
+          <t>2026-10-08T00:18:15Z</t>
         </is>
       </c>
     </row>
@@ -1671,7 +1671,7 @@
       </c>
       <c r="S18" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07T19:19:48Z</t>
+          <t>2026-10-08T00:18:15Z</t>
         </is>
       </c>
     </row>
@@ -1756,7 +1756,7 @@
       </c>
       <c r="S19" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07T19:19:48Z</t>
+          <t>2026-10-08T00:18:15Z</t>
         </is>
       </c>
     </row>
@@ -1841,7 +1841,7 @@
       </c>
       <c r="S20" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07T19:19:48Z</t>
+          <t>2026-10-08T00:18:15Z</t>
         </is>
       </c>
     </row>
@@ -1926,7 +1926,7 @@
       </c>
       <c r="S21" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07T19:19:48Z</t>
+          <t>2026-10-08T00:18:15Z</t>
         </is>
       </c>
     </row>
@@ -2011,7 +2011,7 @@
       </c>
       <c r="S22" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07T19:19:48Z</t>
+          <t>2026-10-08T00:18:15Z</t>
         </is>
       </c>
     </row>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="S23" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07T19:19:48Z</t>
+          <t>2026-10-08T00:18:15Z</t>
         </is>
       </c>
     </row>
@@ -2181,7 +2181,7 @@
       </c>
       <c r="S24" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07T19:19:48Z</t>
+          <t>2026-10-08T00:18:15Z</t>
         </is>
       </c>
     </row>
@@ -2266,7 +2266,7 @@
       </c>
       <c r="S25" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07T19:19:48Z</t>
+          <t>2026-10-08T00:18:15Z</t>
         </is>
       </c>
     </row>
@@ -2351,7 +2351,7 @@
       </c>
       <c r="S26" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07T19:19:48Z</t>
+          <t>2026-10-08T00:18:15Z</t>
         </is>
       </c>
     </row>
@@ -2436,7 +2436,7 @@
       </c>
       <c r="S27" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07T19:19:48Z</t>
+          <t>2026-10-08T00:18:15Z</t>
         </is>
       </c>
     </row>
@@ -2525,7 +2525,7 @@
       </c>
       <c r="S28" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07T19:19:48Z</t>
+          <t>2026-10-08T00:18:15Z</t>
         </is>
       </c>
     </row>
@@ -2614,7 +2614,7 @@
       </c>
       <c r="S29" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07T19:19:48Z</t>
+          <t>2026-10-08T00:18:15Z</t>
         </is>
       </c>
     </row>
@@ -2699,7 +2699,7 @@
       </c>
       <c r="S30" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07T19:19:48Z</t>
+          <t>2026-10-08T00:18:15Z</t>
         </is>
       </c>
     </row>
@@ -2788,7 +2788,7 @@
       </c>
       <c r="S31" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07T19:19:48Z</t>
+          <t>2026-10-08T00:18:15Z</t>
         </is>
       </c>
     </row>
@@ -2877,7 +2877,7 @@
       </c>
       <c r="S32" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07T19:19:48Z</t>
+          <t>2026-10-08T00:18:15Z</t>
         </is>
       </c>
     </row>
@@ -2962,7 +2962,7 @@
       </c>
       <c r="S33" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07T19:19:48Z</t>
+          <t>2026-10-08T00:18:15Z</t>
         </is>
       </c>
     </row>
@@ -3051,7 +3051,7 @@
       </c>
       <c r="S34" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07T19:19:48Z</t>
+          <t>2026-10-08T00:18:15Z</t>
         </is>
       </c>
     </row>
@@ -3140,7 +3140,7 @@
       </c>
       <c r="S35" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07T19:19:48Z</t>
+          <t>2026-10-08T00:18:15Z</t>
         </is>
       </c>
     </row>
@@ -3225,7 +3225,7 @@
       </c>
       <c r="S36" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07T19:19:48Z</t>
+          <t>2026-10-08T00:18:15Z</t>
         </is>
       </c>
     </row>
@@ -3314,7 +3314,7 @@
       </c>
       <c r="S37" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07T19:19:48Z</t>
+          <t>2026-10-08T00:18:15Z</t>
         </is>
       </c>
     </row>
@@ -3403,7 +3403,7 @@
       </c>
       <c r="S38" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07T19:19:48Z</t>
+          <t>2026-10-08T00:18:15Z</t>
         </is>
       </c>
     </row>
@@ -3488,7 +3488,7 @@
       </c>
       <c r="S39" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07T19:19:48Z</t>
+          <t>2026-10-08T00:18:15Z</t>
         </is>
       </c>
     </row>
@@ -3577,7 +3577,7 @@
       </c>
       <c r="S40" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07T19:19:48Z</t>
+          <t>2026-10-08T00:18:15Z</t>
         </is>
       </c>
     </row>
@@ -3666,7 +3666,7 @@
       </c>
       <c r="S41" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07T19:19:48Z</t>
+          <t>2026-10-08T00:18:15Z</t>
         </is>
       </c>
     </row>
@@ -3751,7 +3751,7 @@
       </c>
       <c r="S42" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07T19:19:48Z</t>
+          <t>2026-10-08T00:18:15Z</t>
         </is>
       </c>
     </row>
@@ -3840,7 +3840,7 @@
       </c>
       <c r="S43" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07T19:19:48Z</t>
+          <t>2026-10-08T00:18:15Z</t>
         </is>
       </c>
     </row>
@@ -3929,7 +3929,7 @@
       </c>
       <c r="S44" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07T19:19:48Z</t>
+          <t>2026-10-08T00:18:15Z</t>
         </is>
       </c>
     </row>
@@ -4014,7 +4014,7 @@
       </c>
       <c r="S45" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07T19:19:48Z</t>
+          <t>2026-10-08T00:18:15Z</t>
         </is>
       </c>
     </row>
@@ -4103,7 +4103,7 @@
       </c>
       <c r="S46" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07T19:19:48Z</t>
+          <t>2026-10-08T00:18:15Z</t>
         </is>
       </c>
     </row>
@@ -4192,7 +4192,7 @@
       </c>
       <c r="S47" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07T19:19:48Z</t>
+          <t>2026-10-08T00:18:15Z</t>
         </is>
       </c>
     </row>
@@ -4277,7 +4277,7 @@
       </c>
       <c r="S48" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07T19:19:48Z</t>
+          <t>2026-10-08T00:18:15Z</t>
         </is>
       </c>
     </row>
@@ -4366,7 +4366,7 @@
       </c>
       <c r="S49" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07T19:19:48Z</t>
+          <t>2026-10-08T00:18:15Z</t>
         </is>
       </c>
     </row>
@@ -4455,7 +4455,7 @@
       </c>
       <c r="S50" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07T19:19:48Z</t>
+          <t>2026-10-08T00:18:15Z</t>
         </is>
       </c>
     </row>
@@ -4540,7 +4540,7 @@
       </c>
       <c r="S51" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07T19:19:48Z</t>
+          <t>2026-10-08T00:18:15Z</t>
         </is>
       </c>
     </row>
@@ -4629,7 +4629,7 @@
       </c>
       <c r="S52" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07T19:19:48Z</t>
+          <t>2026-10-08T00:18:15Z</t>
         </is>
       </c>
     </row>
@@ -4718,7 +4718,7 @@
       </c>
       <c r="S53" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07T19:19:48Z</t>
+          <t>2026-10-08T00:18:15Z</t>
         </is>
       </c>
     </row>
@@ -4803,7 +4803,7 @@
       </c>
       <c r="S54" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07T19:19:48Z</t>
+          <t>2026-10-08T00:18:15Z</t>
         </is>
       </c>
     </row>
@@ -4892,7 +4892,7 @@
       </c>
       <c r="S55" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07T19:19:48Z</t>
+          <t>2026-10-08T00:18:15Z</t>
         </is>
       </c>
     </row>
@@ -4981,7 +4981,7 @@
       </c>
       <c r="S56" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07T19:19:48Z</t>
+          <t>2026-10-08T00:18:15Z</t>
         </is>
       </c>
     </row>
@@ -5070,7 +5070,7 @@
       </c>
       <c r="S57" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07T19:19:48Z</t>
+          <t>2026-10-08T00:18:15Z</t>
         </is>
       </c>
     </row>
@@ -5159,7 +5159,7 @@
       </c>
       <c r="S58" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07T19:19:48Z</t>
+          <t>2026-10-08T00:18:15Z</t>
         </is>
       </c>
     </row>
@@ -5248,7 +5248,7 @@
       </c>
       <c r="S59" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07T19:19:48Z</t>
+          <t>2026-10-08T00:18:15Z</t>
         </is>
       </c>
     </row>
@@ -5337,7 +5337,7 @@
       </c>
       <c r="S60" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07T19:19:48Z</t>
+          <t>2026-10-08T00:18:15Z</t>
         </is>
       </c>
     </row>
@@ -5426,7 +5426,7 @@
       </c>
       <c r="S61" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07T19:19:48Z</t>
+          <t>2026-10-08T00:18:15Z</t>
         </is>
       </c>
     </row>
@@ -5515,7 +5515,7 @@
       </c>
       <c r="S62" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07T19:19:48Z</t>
+          <t>2026-10-08T00:18:15Z</t>
         </is>
       </c>
     </row>
@@ -5604,7 +5604,7 @@
       </c>
       <c r="S63" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07T19:19:48Z</t>
+          <t>2026-10-08T00:18:15Z</t>
         </is>
       </c>
     </row>
@@ -5693,7 +5693,7 @@
       </c>
       <c r="S64" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07T19:19:48Z</t>
+          <t>2026-10-08T00:18:15Z</t>
         </is>
       </c>
     </row>
@@ -5782,7 +5782,7 @@
       </c>
       <c r="S65" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07T19:19:48Z</t>
+          <t>2026-10-08T00:18:15Z</t>
         </is>
       </c>
     </row>
@@ -5871,7 +5871,7 @@
       </c>
       <c r="S66" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07T19:19:48Z</t>
+          <t>2026-10-08T00:18:15Z</t>
         </is>
       </c>
     </row>
@@ -5960,7 +5960,7 @@
       </c>
       <c r="S67" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07T19:19:48Z</t>
+          <t>2026-10-08T00:18:15Z</t>
         </is>
       </c>
     </row>
@@ -6045,7 +6045,7 @@
       </c>
       <c r="S68" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07T19:19:48Z</t>
+          <t>2026-10-08T00:18:15Z</t>
         </is>
       </c>
     </row>
@@ -6130,7 +6130,7 @@
       </c>
       <c r="S69" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07T19:19:48Z</t>
+          <t>2026-10-08T00:18:15Z</t>
         </is>
       </c>
     </row>
@@ -6215,7 +6215,7 @@
       </c>
       <c r="S70" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07T19:19:48Z</t>
+          <t>2026-10-08T00:18:15Z</t>
         </is>
       </c>
     </row>
@@ -6300,7 +6300,7 @@
       </c>
       <c r="S71" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07T19:19:48Z</t>
+          <t>2026-10-08T00:18:15Z</t>
         </is>
       </c>
     </row>
@@ -6385,7 +6385,7 @@
       </c>
       <c r="S72" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07T19:19:48Z</t>
+          <t>2026-10-08T00:18:15Z</t>
         </is>
       </c>
     </row>
@@ -6470,7 +6470,7 @@
       </c>
       <c r="S73" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07T19:19:48Z</t>
+          <t>2026-10-08T00:18:15Z</t>
         </is>
       </c>
     </row>
@@ -6555,7 +6555,7 @@
       </c>
       <c r="S74" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07T19:19:48Z</t>
+          <t>2026-10-08T00:18:15Z</t>
         </is>
       </c>
     </row>
@@ -6640,7 +6640,7 @@
       </c>
       <c r="S75" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07T19:19:48Z</t>
+          <t>2026-10-08T00:18:15Z</t>
         </is>
       </c>
     </row>
@@ -6725,7 +6725,7 @@
       </c>
       <c r="S76" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07T19:19:48Z</t>
+          <t>2026-10-08T00:18:15Z</t>
         </is>
       </c>
     </row>
@@ -6810,7 +6810,7 @@
       </c>
       <c r="S77" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07T19:19:48Z</t>
+          <t>2026-10-08T00:18:15Z</t>
         </is>
       </c>
     </row>
@@ -6895,7 +6895,7 @@
       </c>
       <c r="S78" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07T19:19:48Z</t>
+          <t>2026-10-08T00:18:15Z</t>
         </is>
       </c>
     </row>
@@ -6980,7 +6980,7 @@
       </c>
       <c r="S79" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07T19:19:48Z</t>
+          <t>2026-10-08T00:18:15Z</t>
         </is>
       </c>
     </row>
@@ -7065,7 +7065,7 @@
       </c>
       <c r="S80" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07T19:19:48Z</t>
+          <t>2026-10-08T00:18:15Z</t>
         </is>
       </c>
     </row>
@@ -7150,7 +7150,7 @@
       </c>
       <c r="S81" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07T19:19:48Z</t>
+          <t>2026-10-08T00:18:15Z</t>
         </is>
       </c>
     </row>
@@ -7235,7 +7235,7 @@
       </c>
       <c r="S82" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07T19:19:48Z</t>
+          <t>2026-10-08T00:18:15Z</t>
         </is>
       </c>
     </row>
@@ -7320,7 +7320,7 @@
       </c>
       <c r="S83" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07T19:19:48Z</t>
+          <t>2026-10-08T00:18:15Z</t>
         </is>
       </c>
     </row>
@@ -7405,7 +7405,7 @@
       </c>
       <c r="S84" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07T19:19:48Z</t>
+          <t>2026-10-08T00:18:15Z</t>
         </is>
       </c>
     </row>
@@ -7490,7 +7490,7 @@
       </c>
       <c r="S85" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07T19:19:48Z</t>
+          <t>2026-10-08T00:18:15Z</t>
         </is>
       </c>
     </row>
@@ -7575,7 +7575,7 @@
       </c>
       <c r="S86" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07T19:19:48Z</t>
+          <t>2026-10-08T00:18:15Z</t>
         </is>
       </c>
     </row>
@@ -7660,7 +7660,7 @@
       </c>
       <c r="S87" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07T19:19:48Z</t>
+          <t>2026-10-08T00:18:15Z</t>
         </is>
       </c>
     </row>
@@ -7745,7 +7745,7 @@
       </c>
       <c r="S88" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07T19:19:48Z</t>
+          <t>2026-10-08T00:18:15Z</t>
         </is>
       </c>
     </row>
@@ -7834,7 +7834,7 @@
       </c>
       <c r="S89" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07T19:19:48Z</t>
+          <t>2026-10-08T00:18:15Z</t>
         </is>
       </c>
     </row>
@@ -7923,7 +7923,7 @@
       </c>
       <c r="S90" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07T19:19:48Z</t>
+          <t>2026-10-08T00:18:15Z</t>
         </is>
       </c>
     </row>
@@ -8008,7 +8008,7 @@
       </c>
       <c r="S91" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07T19:19:48Z</t>
+          <t>2026-10-08T00:18:15Z</t>
         </is>
       </c>
     </row>
@@ -8097,7 +8097,7 @@
       </c>
       <c r="S92" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07T19:19:48Z</t>
+          <t>2026-10-08T00:18:15Z</t>
         </is>
       </c>
     </row>
@@ -8186,7 +8186,7 @@
       </c>
       <c r="S93" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07T19:19:48Z</t>
+          <t>2026-10-08T00:18:15Z</t>
         </is>
       </c>
     </row>
@@ -8271,7 +8271,7 @@
       </c>
       <c r="S94" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07T19:19:48Z</t>
+          <t>2026-10-08T00:18:15Z</t>
         </is>
       </c>
     </row>
@@ -8360,7 +8360,7 @@
       </c>
       <c r="S95" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07T19:19:48Z</t>
+          <t>2026-10-08T00:18:15Z</t>
         </is>
       </c>
     </row>
@@ -8449,7 +8449,7 @@
       </c>
       <c r="S96" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07T19:19:48Z</t>
+          <t>2026-10-08T00:18:15Z</t>
         </is>
       </c>
     </row>
@@ -8534,7 +8534,7 @@
       </c>
       <c r="S97" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07T19:19:48Z</t>
+          <t>2026-10-08T00:18:15Z</t>
         </is>
       </c>
     </row>
@@ -8623,7 +8623,7 @@
       </c>
       <c r="S98" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07T19:19:48Z</t>
+          <t>2026-10-08T00:18:15Z</t>
         </is>
       </c>
     </row>
@@ -8712,7 +8712,7 @@
       </c>
       <c r="S99" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07T19:19:48Z</t>
+          <t>2026-10-08T00:18:15Z</t>
         </is>
       </c>
     </row>
@@ -8797,7 +8797,7 @@
       </c>
       <c r="S100" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07T19:19:48Z</t>
+          <t>2026-10-08T00:18:15Z</t>
         </is>
       </c>
     </row>
@@ -8886,7 +8886,7 @@
       </c>
       <c r="S101" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07T19:19:48Z</t>
+          <t>2026-10-08T00:18:15Z</t>
         </is>
       </c>
     </row>
@@ -8975,7 +8975,7 @@
       </c>
       <c r="S102" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07T19:19:48Z</t>
+          <t>2026-10-08T00:18:15Z</t>
         </is>
       </c>
     </row>
@@ -9060,7 +9060,7 @@
       </c>
       <c r="S103" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07T19:19:48Z</t>
+          <t>2026-10-08T00:18:15Z</t>
         </is>
       </c>
     </row>
@@ -9149,7 +9149,7 @@
       </c>
       <c r="S104" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07T19:19:48Z</t>
+          <t>2026-10-08T00:18:15Z</t>
         </is>
       </c>
     </row>
@@ -9238,7 +9238,7 @@
       </c>
       <c r="S105" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07T19:19:48Z</t>
+          <t>2026-10-08T00:18:15Z</t>
         </is>
       </c>
     </row>
@@ -9323,7 +9323,7 @@
       </c>
       <c r="S106" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07T19:19:48Z</t>
+          <t>2026-10-08T00:18:15Z</t>
         </is>
       </c>
     </row>
@@ -9412,7 +9412,7 @@
       </c>
       <c r="S107" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07T19:19:48Z</t>
+          <t>2026-10-08T00:18:15Z</t>
         </is>
       </c>
     </row>
@@ -9501,7 +9501,7 @@
       </c>
       <c r="S108" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07T19:19:48Z</t>
+          <t>2026-10-08T00:18:15Z</t>
         </is>
       </c>
     </row>
@@ -9586,7 +9586,7 @@
       </c>
       <c r="S109" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07T19:19:48Z</t>
+          <t>2026-10-08T00:18:15Z</t>
         </is>
       </c>
     </row>
@@ -9675,7 +9675,7 @@
       </c>
       <c r="S110" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07T19:19:48Z</t>
+          <t>2026-10-08T00:18:15Z</t>
         </is>
       </c>
     </row>
@@ -9764,7 +9764,7 @@
       </c>
       <c r="S111" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07T19:19:48Z</t>
+          <t>2026-10-08T00:18:15Z</t>
         </is>
       </c>
     </row>
@@ -9849,7 +9849,7 @@
       </c>
       <c r="S112" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07T19:19:48Z</t>
+          <t>2026-10-08T00:18:15Z</t>
         </is>
       </c>
     </row>
@@ -9938,7 +9938,7 @@
       </c>
       <c r="S113" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07T19:19:48Z</t>
+          <t>2026-10-08T00:18:15Z</t>
         </is>
       </c>
     </row>
@@ -10027,7 +10027,7 @@
       </c>
       <c r="S114" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07T19:19:48Z</t>
+          <t>2026-10-08T00:18:15Z</t>
         </is>
       </c>
     </row>
@@ -10112,7 +10112,7 @@
       </c>
       <c r="S115" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07T19:19:48Z</t>
+          <t>2026-10-08T00:18:15Z</t>
         </is>
       </c>
     </row>
@@ -10201,7 +10201,7 @@
       </c>
       <c r="S116" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07T19:19:48Z</t>
+          <t>2026-10-08T00:18:15Z</t>
         </is>
       </c>
     </row>
@@ -10290,7 +10290,7 @@
       </c>
       <c r="S117" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07T19:19:48Z</t>
+          <t>2026-10-08T00:18:15Z</t>
         </is>
       </c>
     </row>
@@ -10379,7 +10379,7 @@
       </c>
       <c r="S118" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07T19:19:48Z</t>
+          <t>2026-10-08T00:18:15Z</t>
         </is>
       </c>
     </row>
@@ -10468,7 +10468,7 @@
       </c>
       <c r="S119" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07T19:19:48Z</t>
+          <t>2026-10-08T00:18:15Z</t>
         </is>
       </c>
     </row>
@@ -10557,7 +10557,7 @@
       </c>
       <c r="S120" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07T19:19:48Z</t>
+          <t>2026-10-08T00:18:15Z</t>
         </is>
       </c>
     </row>
@@ -10646,7 +10646,7 @@
       </c>
       <c r="S121" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07T19:19:48Z</t>
+          <t>2026-10-08T00:18:15Z</t>
         </is>
       </c>
     </row>
@@ -10735,7 +10735,7 @@
       </c>
       <c r="S122" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07T19:19:48Z</t>
+          <t>2026-10-08T00:18:15Z</t>
         </is>
       </c>
     </row>
@@ -10824,7 +10824,7 @@
       </c>
       <c r="S123" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07T19:19:48Z</t>
+          <t>2026-10-08T00:18:15Z</t>
         </is>
       </c>
     </row>
@@ -10913,7 +10913,7 @@
       </c>
       <c r="S124" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07T19:19:48Z</t>
+          <t>2026-10-08T00:18:15Z</t>
         </is>
       </c>
     </row>
@@ -11002,7 +11002,7 @@
       </c>
       <c r="S125" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07T19:19:48Z</t>
+          <t>2026-10-08T00:18:15Z</t>
         </is>
       </c>
     </row>
@@ -11091,7 +11091,7 @@
       </c>
       <c r="S126" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07T19:19:48Z</t>
+          <t>2026-10-08T00:18:15Z</t>
         </is>
       </c>
     </row>
@@ -11180,7 +11180,7 @@
       </c>
       <c r="S127" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07T19:19:48Z</t>
+          <t>2026-10-08T00:18:15Z</t>
         </is>
       </c>
     </row>
@@ -11269,7 +11269,7 @@
       </c>
       <c r="S128" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07T19:19:48Z</t>
+          <t>2026-10-08T00:18:15Z</t>
         </is>
       </c>
     </row>
@@ -11354,7 +11354,7 @@
       </c>
       <c r="S129" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07T19:19:48Z</t>
+          <t>2026-10-08T00:18:15Z</t>
         </is>
       </c>
     </row>
@@ -11439,7 +11439,7 @@
       </c>
       <c r="S130" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07T19:19:48Z</t>
+          <t>2026-10-08T00:18:15Z</t>
         </is>
       </c>
     </row>
@@ -11524,7 +11524,7 @@
       </c>
       <c r="S131" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07T19:19:48Z</t>
+          <t>2026-10-08T00:18:15Z</t>
         </is>
       </c>
     </row>
@@ -11609,7 +11609,7 @@
       </c>
       <c r="S132" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07T19:19:48Z</t>
+          <t>2026-10-08T00:18:15Z</t>
         </is>
       </c>
     </row>
@@ -11694,7 +11694,7 @@
       </c>
       <c r="S133" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07T19:19:48Z</t>
+          <t>2026-10-08T00:18:15Z</t>
         </is>
       </c>
     </row>
@@ -11779,7 +11779,7 @@
       </c>
       <c r="S134" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07T19:19:48Z</t>
+          <t>2026-10-08T00:18:15Z</t>
         </is>
       </c>
     </row>
@@ -11864,7 +11864,7 @@
       </c>
       <c r="S135" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07T19:19:48Z</t>
+          <t>2026-10-08T00:18:15Z</t>
         </is>
       </c>
     </row>
@@ -11949,7 +11949,7 @@
       </c>
       <c r="S136" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07T19:19:48Z</t>
+          <t>2026-10-08T00:18:15Z</t>
         </is>
       </c>
     </row>
@@ -12034,7 +12034,7 @@
       </c>
       <c r="S137" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07T19:19:48Z</t>
+          <t>2026-10-08T00:18:15Z</t>
         </is>
       </c>
     </row>
@@ -12119,7 +12119,7 @@
       </c>
       <c r="S138" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07T19:19:48Z</t>
+          <t>2026-10-08T00:18:15Z</t>
         </is>
       </c>
     </row>
@@ -12204,7 +12204,7 @@
       </c>
       <c r="S139" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07T19:19:48Z</t>
+          <t>2026-10-08T00:18:15Z</t>
         </is>
       </c>
     </row>
@@ -12289,7 +12289,7 @@
       </c>
       <c r="S140" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07T19:19:48Z</t>
+          <t>2026-10-08T00:18:15Z</t>
         </is>
       </c>
     </row>
@@ -12374,7 +12374,7 @@
       </c>
       <c r="S141" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07T19:19:48Z</t>
+          <t>2026-10-08T00:18:15Z</t>
         </is>
       </c>
     </row>
@@ -12459,7 +12459,7 @@
       </c>
       <c r="S142" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07T19:19:48Z</t>
+          <t>2026-10-08T00:18:15Z</t>
         </is>
       </c>
     </row>
@@ -12544,7 +12544,7 @@
       </c>
       <c r="S143" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07T19:19:48Z</t>
+          <t>2026-10-08T00:18:15Z</t>
         </is>
       </c>
     </row>
@@ -12629,7 +12629,7 @@
       </c>
       <c r="S144" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07T19:19:48Z</t>
+          <t>2026-10-08T00:18:15Z</t>
         </is>
       </c>
     </row>
@@ -12714,7 +12714,7 @@
       </c>
       <c r="S145" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07T19:19:48Z</t>
+          <t>2026-10-08T00:18:15Z</t>
         </is>
       </c>
     </row>
@@ -12799,7 +12799,7 @@
       </c>
       <c r="S146" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07T19:19:48Z</t>
+          <t>2026-10-08T00:18:15Z</t>
         </is>
       </c>
     </row>
@@ -12884,7 +12884,7 @@
       </c>
       <c r="S147" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07T19:19:48Z</t>
+          <t>2026-10-08T00:18:15Z</t>
         </is>
       </c>
     </row>
@@ -12969,7 +12969,7 @@
       </c>
       <c r="S148" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07T19:19:48Z</t>
+          <t>2026-10-08T00:18:15Z</t>
         </is>
       </c>
     </row>
@@ -13054,7 +13054,7 @@
       </c>
       <c r="S149" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07T19:19:48Z</t>
+          <t>2026-10-08T00:18:15Z</t>
         </is>
       </c>
     </row>
@@ -13143,7 +13143,7 @@
       </c>
       <c r="S150" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07T19:19:48Z</t>
+          <t>2026-10-08T00:18:15Z</t>
         </is>
       </c>
     </row>
@@ -13232,7 +13232,7 @@
       </c>
       <c r="S151" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07T19:19:48Z</t>
+          <t>2026-10-08T00:18:15Z</t>
         </is>
       </c>
     </row>
@@ -13317,7 +13317,7 @@
       </c>
       <c r="S152" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07T19:19:48Z</t>
+          <t>2026-10-08T00:18:15Z</t>
         </is>
       </c>
     </row>
@@ -13406,7 +13406,7 @@
       </c>
       <c r="S153" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07T19:19:48Z</t>
+          <t>2026-10-08T00:18:15Z</t>
         </is>
       </c>
     </row>
@@ -13495,7 +13495,7 @@
       </c>
       <c r="S154" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07T19:19:48Z</t>
+          <t>2026-10-08T00:18:15Z</t>
         </is>
       </c>
     </row>
@@ -13580,7 +13580,7 @@
       </c>
       <c r="S155" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07T19:19:48Z</t>
+          <t>2026-10-08T00:18:15Z</t>
         </is>
       </c>
     </row>
@@ -13669,7 +13669,7 @@
       </c>
       <c r="S156" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07T19:19:48Z</t>
+          <t>2026-10-08T00:18:15Z</t>
         </is>
       </c>
     </row>
@@ -13758,7 +13758,7 @@
       </c>
       <c r="S157" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07T19:19:48Z</t>
+          <t>2026-10-08T00:18:15Z</t>
         </is>
       </c>
     </row>
@@ -13843,7 +13843,7 @@
       </c>
       <c r="S158" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07T19:19:48Z</t>
+          <t>2026-10-08T00:18:15Z</t>
         </is>
       </c>
     </row>
@@ -13932,7 +13932,7 @@
       </c>
       <c r="S159" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07T19:19:48Z</t>
+          <t>2026-10-08T00:18:15Z</t>
         </is>
       </c>
     </row>
@@ -14021,7 +14021,7 @@
       </c>
       <c r="S160" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07T19:19:48Z</t>
+          <t>2026-10-08T00:18:15Z</t>
         </is>
       </c>
     </row>
@@ -14106,7 +14106,7 @@
       </c>
       <c r="S161" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07T19:19:48Z</t>
+          <t>2026-10-08T00:18:15Z</t>
         </is>
       </c>
     </row>
@@ -14195,7 +14195,7 @@
       </c>
       <c r="S162" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07T19:19:48Z</t>
+          <t>2026-10-08T00:18:15Z</t>
         </is>
       </c>
     </row>
@@ -14284,7 +14284,7 @@
       </c>
       <c r="S163" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07T19:19:48Z</t>
+          <t>2026-10-08T00:18:15Z</t>
         </is>
       </c>
     </row>
@@ -14369,7 +14369,7 @@
       </c>
       <c r="S164" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07T19:19:48Z</t>
+          <t>2026-10-08T00:18:15Z</t>
         </is>
       </c>
     </row>
@@ -14458,7 +14458,7 @@
       </c>
       <c r="S165" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07T19:19:48Z</t>
+          <t>2026-10-08T00:18:15Z</t>
         </is>
       </c>
     </row>
@@ -14547,7 +14547,7 @@
       </c>
       <c r="S166" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07T19:19:48Z</t>
+          <t>2026-10-08T00:18:15Z</t>
         </is>
       </c>
     </row>
@@ -14632,7 +14632,7 @@
       </c>
       <c r="S167" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07T19:19:48Z</t>
+          <t>2026-10-08T00:18:15Z</t>
         </is>
       </c>
     </row>
@@ -14721,7 +14721,7 @@
       </c>
       <c r="S168" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07T19:19:48Z</t>
+          <t>2026-10-08T00:18:15Z</t>
         </is>
       </c>
     </row>
@@ -14810,7 +14810,7 @@
       </c>
       <c r="S169" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07T19:19:48Z</t>
+          <t>2026-10-08T00:18:15Z</t>
         </is>
       </c>
     </row>
@@ -14895,7 +14895,7 @@
       </c>
       <c r="S170" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07T19:19:48Z</t>
+          <t>2026-10-08T00:18:15Z</t>
         </is>
       </c>
     </row>
@@ -14984,7 +14984,7 @@
       </c>
       <c r="S171" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07T19:19:48Z</t>
+          <t>2026-10-08T00:18:15Z</t>
         </is>
       </c>
     </row>
@@ -15073,7 +15073,7 @@
       </c>
       <c r="S172" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07T19:19:48Z</t>
+          <t>2026-10-08T00:18:15Z</t>
         </is>
       </c>
     </row>
@@ -15158,7 +15158,7 @@
       </c>
       <c r="S173" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07T19:19:48Z</t>
+          <t>2026-10-08T00:18:15Z</t>
         </is>
       </c>
     </row>
@@ -15247,7 +15247,7 @@
       </c>
       <c r="S174" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07T19:19:48Z</t>
+          <t>2026-10-08T00:18:15Z</t>
         </is>
       </c>
     </row>
@@ -15336,7 +15336,7 @@
       </c>
       <c r="S175" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07T19:19:48Z</t>
+          <t>2026-10-08T00:18:15Z</t>
         </is>
       </c>
     </row>
@@ -15421,7 +15421,7 @@
       </c>
       <c r="S176" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07T19:19:48Z</t>
+          <t>2026-10-08T00:18:15Z</t>
         </is>
       </c>
     </row>
@@ -15510,7 +15510,7 @@
       </c>
       <c r="S177" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07T19:19:48Z</t>
+          <t>2026-10-08T00:18:15Z</t>
         </is>
       </c>
     </row>
@@ -15599,7 +15599,7 @@
       </c>
       <c r="S178" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07T19:19:48Z</t>
+          <t>2026-10-08T00:18:15Z</t>
         </is>
       </c>
     </row>
@@ -15688,7 +15688,7 @@
       </c>
       <c r="S179" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07T19:19:48Z</t>
+          <t>2026-10-08T00:18:15Z</t>
         </is>
       </c>
     </row>
@@ -15777,7 +15777,7 @@
       </c>
       <c r="S180" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07T19:19:48Z</t>
+          <t>2026-10-08T00:18:15Z</t>
         </is>
       </c>
     </row>
@@ -15866,7 +15866,7 @@
       </c>
       <c r="S181" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07T19:19:48Z</t>
+          <t>2026-10-08T00:18:15Z</t>
         </is>
       </c>
     </row>
@@ -15955,7 +15955,7 @@
       </c>
       <c r="S182" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07T19:19:48Z</t>
+          <t>2026-10-08T00:18:15Z</t>
         </is>
       </c>
     </row>
@@ -16044,7 +16044,7 @@
       </c>
       <c r="S183" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07T19:19:48Z</t>
+          <t>2026-10-08T00:18:15Z</t>
         </is>
       </c>
     </row>
@@ -16133,7 +16133,7 @@
       </c>
       <c r="S184" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07T19:19:48Z</t>
+          <t>2026-10-08T00:18:15Z</t>
         </is>
       </c>
     </row>
@@ -16222,7 +16222,7 @@
       </c>
       <c r="S185" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07T19:19:48Z</t>
+          <t>2026-10-08T00:18:15Z</t>
         </is>
       </c>
     </row>
@@ -16311,7 +16311,7 @@
       </c>
       <c r="S186" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07T19:19:48Z</t>
+          <t>2026-10-08T00:18:15Z</t>
         </is>
       </c>
     </row>
@@ -16400,7 +16400,7 @@
       </c>
       <c r="S187" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07T19:19:48Z</t>
+          <t>2026-10-08T00:18:15Z</t>
         </is>
       </c>
     </row>
@@ -16489,7 +16489,7 @@
       </c>
       <c r="S188" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07T19:19:48Z</t>
+          <t>2026-10-08T00:18:15Z</t>
         </is>
       </c>
     </row>
@@ -16578,7 +16578,7 @@
       </c>
       <c r="S189" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07T19:19:48Z</t>
+          <t>2026-10-08T00:18:15Z</t>
         </is>
       </c>
     </row>
@@ -16663,7 +16663,7 @@
       </c>
       <c r="S190" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07T19:19:48Z</t>
+          <t>2026-10-08T00:18:15Z</t>
         </is>
       </c>
     </row>
@@ -16748,7 +16748,7 @@
       </c>
       <c r="S191" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07T19:19:48Z</t>
+          <t>2026-10-08T00:18:15Z</t>
         </is>
       </c>
     </row>
@@ -16833,7 +16833,7 @@
       </c>
       <c r="S192" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07T19:19:48Z</t>
+          <t>2026-10-08T00:18:15Z</t>
         </is>
       </c>
     </row>
@@ -16918,7 +16918,7 @@
       </c>
       <c r="S193" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07T19:19:48Z</t>
+          <t>2026-10-08T00:18:15Z</t>
         </is>
       </c>
     </row>
@@ -17003,7 +17003,7 @@
       </c>
       <c r="S194" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07T19:19:48Z</t>
+          <t>2026-10-08T00:18:15Z</t>
         </is>
       </c>
     </row>
@@ -17088,7 +17088,7 @@
       </c>
       <c r="S195" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07T19:19:48Z</t>
+          <t>2026-10-08T00:18:15Z</t>
         </is>
       </c>
     </row>
@@ -17173,7 +17173,7 @@
       </c>
       <c r="S196" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07T19:19:48Z</t>
+          <t>2026-10-08T00:18:15Z</t>
         </is>
       </c>
     </row>
@@ -17258,7 +17258,7 @@
       </c>
       <c r="S197" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07T19:19:48Z</t>
+          <t>2026-10-08T00:18:15Z</t>
         </is>
       </c>
     </row>
@@ -17343,7 +17343,7 @@
       </c>
       <c r="S198" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07T19:19:48Z</t>
+          <t>2026-10-08T00:18:15Z</t>
         </is>
       </c>
     </row>
@@ -17428,7 +17428,7 @@
       </c>
       <c r="S199" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07T19:19:48Z</t>
+          <t>2026-10-08T00:18:15Z</t>
         </is>
       </c>
     </row>
@@ -17513,7 +17513,7 @@
       </c>
       <c r="S200" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07T19:19:48Z</t>
+          <t>2026-10-08T00:18:15Z</t>
         </is>
       </c>
     </row>
@@ -17598,7 +17598,7 @@
       </c>
       <c r="S201" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07T19:19:48Z</t>
+          <t>2026-10-08T00:18:15Z</t>
         </is>
       </c>
     </row>
@@ -17683,7 +17683,7 @@
       </c>
       <c r="S202" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07T19:19:48Z</t>
+          <t>2026-10-08T00:18:15Z</t>
         </is>
       </c>
     </row>
@@ -17768,7 +17768,7 @@
       </c>
       <c r="S203" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07T19:19:48Z</t>
+          <t>2026-10-08T00:18:15Z</t>
         </is>
       </c>
     </row>
@@ -17853,7 +17853,7 @@
       </c>
       <c r="S204" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07T19:19:48Z</t>
+          <t>2026-10-08T00:18:15Z</t>
         </is>
       </c>
     </row>
@@ -17938,7 +17938,7 @@
       </c>
       <c r="S205" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07T19:19:48Z</t>
+          <t>2026-10-08T00:18:15Z</t>
         </is>
       </c>
     </row>
@@ -18023,7 +18023,7 @@
       </c>
       <c r="S206" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07T19:19:48Z</t>
+          <t>2026-10-08T00:18:15Z</t>
         </is>
       </c>
     </row>
@@ -18108,7 +18108,7 @@
       </c>
       <c r="S207" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07T19:19:48Z</t>
+          <t>2026-10-08T00:18:15Z</t>
         </is>
       </c>
     </row>
@@ -18193,7 +18193,7 @@
       </c>
       <c r="S208" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07T19:19:48Z</t>
+          <t>2026-10-08T00:18:15Z</t>
         </is>
       </c>
     </row>
@@ -18278,7 +18278,7 @@
       </c>
       <c r="S209" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07T19:19:48Z</t>
+          <t>2026-10-08T00:18:15Z</t>
         </is>
       </c>
     </row>
@@ -18363,7 +18363,7 @@
       </c>
       <c r="S210" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07T19:19:48Z</t>
+          <t>2026-10-08T00:18:15Z</t>
         </is>
       </c>
     </row>
@@ -18452,7 +18452,7 @@
       </c>
       <c r="S211" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07T19:19:48Z</t>
+          <t>2026-10-08T00:18:15Z</t>
         </is>
       </c>
     </row>
@@ -18541,7 +18541,7 @@
       </c>
       <c r="S212" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07T19:19:48Z</t>
+          <t>2026-10-08T00:18:15Z</t>
         </is>
       </c>
     </row>
@@ -18626,7 +18626,7 @@
       </c>
       <c r="S213" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07T19:19:48Z</t>
+          <t>2026-10-08T00:18:15Z</t>
         </is>
       </c>
     </row>
@@ -18715,7 +18715,7 @@
       </c>
       <c r="S214" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07T19:19:48Z</t>
+          <t>2026-10-08T00:18:15Z</t>
         </is>
       </c>
     </row>
@@ -18804,7 +18804,7 @@
       </c>
       <c r="S215" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07T19:19:48Z</t>
+          <t>2026-10-08T00:18:15Z</t>
         </is>
       </c>
     </row>
@@ -18889,7 +18889,7 @@
       </c>
       <c r="S216" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07T19:19:48Z</t>
+          <t>2026-10-08T00:18:15Z</t>
         </is>
       </c>
     </row>
@@ -18978,7 +18978,7 @@
       </c>
       <c r="S217" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07T19:19:48Z</t>
+          <t>2026-10-08T00:18:15Z</t>
         </is>
       </c>
     </row>
@@ -19067,7 +19067,7 @@
       </c>
       <c r="S218" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07T19:19:48Z</t>
+          <t>2026-10-08T00:18:15Z</t>
         </is>
       </c>
     </row>
@@ -19152,7 +19152,7 @@
       </c>
       <c r="S219" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07T19:19:48Z</t>
+          <t>2026-10-08T00:18:15Z</t>
         </is>
       </c>
     </row>
@@ -19241,7 +19241,7 @@
       </c>
       <c r="S220" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07T19:19:48Z</t>
+          <t>2026-10-08T00:18:15Z</t>
         </is>
       </c>
     </row>
@@ -19330,7 +19330,7 @@
       </c>
       <c r="S221" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07T19:19:48Z</t>
+          <t>2026-10-08T00:18:15Z</t>
         </is>
       </c>
     </row>
@@ -19415,7 +19415,7 @@
       </c>
       <c r="S222" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07T19:19:48Z</t>
+          <t>2026-10-08T00:18:15Z</t>
         </is>
       </c>
     </row>
@@ -19504,7 +19504,7 @@
       </c>
       <c r="S223" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07T19:19:48Z</t>
+          <t>2026-10-08T00:18:15Z</t>
         </is>
       </c>
     </row>
@@ -19593,7 +19593,7 @@
       </c>
       <c r="S224" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07T19:19:48Z</t>
+          <t>2026-10-08T00:18:15Z</t>
         </is>
       </c>
     </row>
@@ -19678,7 +19678,7 @@
       </c>
       <c r="S225" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07T19:19:48Z</t>
+          <t>2026-10-08T00:18:15Z</t>
         </is>
       </c>
     </row>
@@ -19767,7 +19767,7 @@
       </c>
       <c r="S226" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07T19:19:48Z</t>
+          <t>2026-10-08T00:18:15Z</t>
         </is>
       </c>
     </row>
@@ -19856,7 +19856,7 @@
       </c>
       <c r="S227" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07T19:19:48Z</t>
+          <t>2026-10-08T00:18:15Z</t>
         </is>
       </c>
     </row>
@@ -19941,7 +19941,7 @@
       </c>
       <c r="S228" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07T19:19:48Z</t>
+          <t>2026-10-08T00:18:15Z</t>
         </is>
       </c>
     </row>
@@ -20030,7 +20030,7 @@
       </c>
       <c r="S229" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07T19:19:48Z</t>
+          <t>2026-10-08T00:18:15Z</t>
         </is>
       </c>
     </row>
@@ -20119,7 +20119,7 @@
       </c>
       <c r="S230" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07T19:19:48Z</t>
+          <t>2026-10-08T00:18:15Z</t>
         </is>
       </c>
     </row>
@@ -20204,7 +20204,7 @@
       </c>
       <c r="S231" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07T19:19:48Z</t>
+          <t>2026-10-08T00:18:15Z</t>
         </is>
       </c>
     </row>
@@ -20293,7 +20293,7 @@
       </c>
       <c r="S232" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07T19:19:48Z</t>
+          <t>2026-10-08T00:18:15Z</t>
         </is>
       </c>
     </row>
@@ -20382,7 +20382,7 @@
       </c>
       <c r="S233" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07T19:19:48Z</t>
+          <t>2026-10-08T00:18:15Z</t>
         </is>
       </c>
     </row>
@@ -20467,7 +20467,7 @@
       </c>
       <c r="S234" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07T19:19:48Z</t>
+          <t>2026-10-08T00:18:15Z</t>
         </is>
       </c>
     </row>
@@ -20556,7 +20556,7 @@
       </c>
       <c r="S235" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07T19:19:48Z</t>
+          <t>2026-10-08T00:18:15Z</t>
         </is>
       </c>
     </row>
@@ -20645,7 +20645,7 @@
       </c>
       <c r="S236" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07T19:19:48Z</t>
+          <t>2026-10-08T00:18:15Z</t>
         </is>
       </c>
     </row>
@@ -20730,7 +20730,7 @@
       </c>
       <c r="S237" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07T19:19:48Z</t>
+          <t>2026-10-08T00:18:15Z</t>
         </is>
       </c>
     </row>
@@ -20819,7 +20819,7 @@
       </c>
       <c r="S238" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07T19:19:48Z</t>
+          <t>2026-10-08T00:18:15Z</t>
         </is>
       </c>
     </row>
@@ -20908,7 +20908,7 @@
       </c>
       <c r="S239" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07T19:19:48Z</t>
+          <t>2026-10-08T00:18:15Z</t>
         </is>
       </c>
     </row>
@@ -20997,7 +20997,7 @@
       </c>
       <c r="S240" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07T19:19:48Z</t>
+          <t>2026-10-08T00:18:15Z</t>
         </is>
       </c>
     </row>
@@ -21086,7 +21086,7 @@
       </c>
       <c r="S241" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07T19:19:48Z</t>
+          <t>2026-10-08T00:18:15Z</t>
         </is>
       </c>
     </row>
@@ -21175,7 +21175,7 @@
       </c>
       <c r="S242" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07T19:19:48Z</t>
+          <t>2026-10-08T00:18:15Z</t>
         </is>
       </c>
     </row>
@@ -21264,7 +21264,7 @@
       </c>
       <c r="S243" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07T19:19:48Z</t>
+          <t>2026-10-08T00:18:15Z</t>
         </is>
       </c>
     </row>
@@ -21353,7 +21353,7 @@
       </c>
       <c r="S244" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07T19:19:48Z</t>
+          <t>2026-10-08T00:18:15Z</t>
         </is>
       </c>
     </row>
@@ -21442,7 +21442,7 @@
       </c>
       <c r="S245" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07T19:19:48Z</t>
+          <t>2026-10-08T00:18:15Z</t>
         </is>
       </c>
     </row>
@@ -21531,7 +21531,7 @@
       </c>
       <c r="S246" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07T19:19:48Z</t>
+          <t>2026-10-08T00:18:15Z</t>
         </is>
       </c>
     </row>
@@ -21620,7 +21620,7 @@
       </c>
       <c r="S247" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07T19:19:48Z</t>
+          <t>2026-10-08T00:18:15Z</t>
         </is>
       </c>
     </row>
@@ -21709,7 +21709,7 @@
       </c>
       <c r="S248" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07T19:19:48Z</t>
+          <t>2026-10-08T00:18:15Z</t>
         </is>
       </c>
     </row>
@@ -21798,7 +21798,7 @@
       </c>
       <c r="S249" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07T19:19:48Z</t>
+          <t>2026-10-08T00:18:15Z</t>
         </is>
       </c>
     </row>
@@ -21887,7 +21887,7 @@
       </c>
       <c r="S250" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07T19:19:48Z</t>
+          <t>2026-10-08T00:18:15Z</t>
         </is>
       </c>
     </row>
@@ -22019,7 +22019,7 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07T19:19:48Z</t>
+          <t>2026-10-08T00:18:15Z</t>
         </is>
       </c>
     </row>
@@ -22099,7 +22099,7 @@
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>{"dataset_id": "bcv_pib_sector_institucional_anual", "title": "Producto interno bruto por sector institucional anual", "table": "Variaciones porcentuales", "source_file": "5_2_1_si_anual.xlsx", "base": "2007", "price_type": "Precios constantes", "measure": "Variación porcentual interanual", "frequency": "Anual", "period": "2025", "year": 2025, "quarter": null, "classification": "Sector institucional", "component": "Impuestos netos sobre los productos", "value": 10.600260421283764, "unit": "Porcentaje", "status": "Preliminar", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/cuentas_macroeconomicas/5_2_1_si_anual.xlsx", "fetched_at": "2026-10-07T19:19:48Z"}</t>
+          <t>{"dataset_id": "bcv_pib_sector_institucional_anual", "title": "Producto interno bruto por sector institucional anual", "table": "Variaciones porcentuales", "source_file": "5_2_1_si_anual.xlsx", "base": "2007", "price_type": "Precios constantes", "measure": "Variación porcentual interanual", "frequency": "Anual", "period": "2025", "year": 2025, "quarter": null, "classification": "Sector institucional", "component": "Impuestos netos sobre los productos", "value": 10.600260421283764, "unit": "Porcentaje", "status": "Preliminar", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/cuentas_macroeconomicas/5_2_1_si_anual.xlsx", "fetched_at": "2026-10-08T00:18:15Z"}</t>
         </is>
       </c>
     </row>

--- a/assets/data/bcv/excel/ove_bcv_pib_sector_institucional_anual.xlsx
+++ b/assets/data/bcv/excel/ove_bcv_pib_sector_institucional_anual.xlsx
@@ -736,7 +736,7 @@
       </c>
       <c r="S7" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08T00:18:15Z</t>
+          <t>2026-10-09T00:32:03Z</t>
         </is>
       </c>
     </row>
@@ -821,7 +821,7 @@
       </c>
       <c r="S8" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08T00:18:15Z</t>
+          <t>2026-10-09T00:32:03Z</t>
         </is>
       </c>
     </row>
@@ -906,7 +906,7 @@
       </c>
       <c r="S9" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08T00:18:15Z</t>
+          <t>2026-10-09T00:32:03Z</t>
         </is>
       </c>
     </row>
@@ -991,7 +991,7 @@
       </c>
       <c r="S10" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08T00:18:15Z</t>
+          <t>2026-10-09T00:32:03Z</t>
         </is>
       </c>
     </row>
@@ -1076,7 +1076,7 @@
       </c>
       <c r="S11" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08T00:18:15Z</t>
+          <t>2026-10-09T00:32:03Z</t>
         </is>
       </c>
     </row>
@@ -1161,7 +1161,7 @@
       </c>
       <c r="S12" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08T00:18:15Z</t>
+          <t>2026-10-09T00:32:03Z</t>
         </is>
       </c>
     </row>
@@ -1246,7 +1246,7 @@
       </c>
       <c r="S13" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08T00:18:15Z</t>
+          <t>2026-10-09T00:32:03Z</t>
         </is>
       </c>
     </row>
@@ -1331,7 +1331,7 @@
       </c>
       <c r="S14" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08T00:18:15Z</t>
+          <t>2026-10-09T00:32:03Z</t>
         </is>
       </c>
     </row>
@@ -1416,7 +1416,7 @@
       </c>
       <c r="S15" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08T00:18:15Z</t>
+          <t>2026-10-09T00:32:03Z</t>
         </is>
       </c>
     </row>
@@ -1501,7 +1501,7 @@
       </c>
       <c r="S16" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08T00:18:15Z</t>
+          <t>2026-10-09T00:32:03Z</t>
         </is>
       </c>
     </row>
@@ -1586,7 +1586,7 @@
       </c>
       <c r="S17" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08T00:18:15Z</t>
+          <t>2026-10-09T00:32:03Z</t>
         </is>
       </c>
     </row>
@@ -1671,7 +1671,7 @@
       </c>
       <c r="S18" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08T00:18:15Z</t>
+          <t>2026-10-09T00:32:03Z</t>
         </is>
       </c>
     </row>
@@ -1756,7 +1756,7 @@
       </c>
       <c r="S19" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08T00:18:15Z</t>
+          <t>2026-10-09T00:32:03Z</t>
         </is>
       </c>
     </row>
@@ -1841,7 +1841,7 @@
       </c>
       <c r="S20" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08T00:18:15Z</t>
+          <t>2026-10-09T00:32:03Z</t>
         </is>
       </c>
     </row>
@@ -1926,7 +1926,7 @@
       </c>
       <c r="S21" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08T00:18:15Z</t>
+          <t>2026-10-09T00:32:03Z</t>
         </is>
       </c>
     </row>
@@ -2011,7 +2011,7 @@
       </c>
       <c r="S22" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08T00:18:15Z</t>
+          <t>2026-10-09T00:32:03Z</t>
         </is>
       </c>
     </row>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="S23" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08T00:18:15Z</t>
+          <t>2026-10-09T00:32:03Z</t>
         </is>
       </c>
     </row>
@@ -2181,7 +2181,7 @@
       </c>
       <c r="S24" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08T00:18:15Z</t>
+          <t>2026-10-09T00:32:03Z</t>
         </is>
       </c>
     </row>
@@ -2266,7 +2266,7 @@
       </c>
       <c r="S25" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08T00:18:15Z</t>
+          <t>2026-10-09T00:32:03Z</t>
         </is>
       </c>
     </row>
@@ -2351,7 +2351,7 @@
       </c>
       <c r="S26" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08T00:18:15Z</t>
+          <t>2026-10-09T00:32:03Z</t>
         </is>
       </c>
     </row>
@@ -2436,7 +2436,7 @@
       </c>
       <c r="S27" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08T00:18:15Z</t>
+          <t>2026-10-09T00:32:03Z</t>
         </is>
       </c>
     </row>
@@ -2525,7 +2525,7 @@
       </c>
       <c r="S28" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08T00:18:15Z</t>
+          <t>2026-10-09T00:32:03Z</t>
         </is>
       </c>
     </row>
@@ -2614,7 +2614,7 @@
       </c>
       <c r="S29" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08T00:18:15Z</t>
+          <t>2026-10-09T00:32:03Z</t>
         </is>
       </c>
     </row>
@@ -2699,7 +2699,7 @@
       </c>
       <c r="S30" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08T00:18:15Z</t>
+          <t>2026-10-09T00:32:03Z</t>
         </is>
       </c>
     </row>
@@ -2788,7 +2788,7 @@
       </c>
       <c r="S31" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08T00:18:15Z</t>
+          <t>2026-10-09T00:32:03Z</t>
         </is>
       </c>
     </row>
@@ -2877,7 +2877,7 @@
       </c>
       <c r="S32" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08T00:18:15Z</t>
+          <t>2026-10-09T00:32:03Z</t>
         </is>
       </c>
     </row>
@@ -2962,7 +2962,7 @@
       </c>
       <c r="S33" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08T00:18:15Z</t>
+          <t>2026-10-09T00:32:03Z</t>
         </is>
       </c>
     </row>
@@ -3051,7 +3051,7 @@
       </c>
       <c r="S34" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08T00:18:15Z</t>
+          <t>2026-10-09T00:32:03Z</t>
         </is>
       </c>
     </row>
@@ -3140,7 +3140,7 @@
       </c>
       <c r="S35" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08T00:18:15Z</t>
+          <t>2026-10-09T00:32:03Z</t>
         </is>
       </c>
     </row>
@@ -3225,7 +3225,7 @@
       </c>
       <c r="S36" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08T00:18:15Z</t>
+          <t>2026-10-09T00:32:03Z</t>
         </is>
       </c>
     </row>
@@ -3314,7 +3314,7 @@
       </c>
       <c r="S37" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08T00:18:15Z</t>
+          <t>2026-10-09T00:32:03Z</t>
         </is>
       </c>
     </row>
@@ -3403,7 +3403,7 @@
       </c>
       <c r="S38" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08T00:18:15Z</t>
+          <t>2026-10-09T00:32:03Z</t>
         </is>
       </c>
     </row>
@@ -3488,7 +3488,7 @@
       </c>
       <c r="S39" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08T00:18:15Z</t>
+          <t>2026-10-09T00:32:03Z</t>
         </is>
       </c>
     </row>
@@ -3577,7 +3577,7 @@
       </c>
       <c r="S40" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08T00:18:15Z</t>
+          <t>2026-10-09T00:32:03Z</t>
         </is>
       </c>
     </row>
@@ -3666,7 +3666,7 @@
       </c>
       <c r="S41" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08T00:18:15Z</t>
+          <t>2026-10-09T00:32:03Z</t>
         </is>
       </c>
     </row>
@@ -3751,7 +3751,7 @@
       </c>
       <c r="S42" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08T00:18:15Z</t>
+          <t>2026-10-09T00:32:03Z</t>
         </is>
       </c>
     </row>
@@ -3840,7 +3840,7 @@
       </c>
       <c r="S43" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08T00:18:15Z</t>
+          <t>2026-10-09T00:32:03Z</t>
         </is>
       </c>
     </row>
@@ -3929,7 +3929,7 @@
       </c>
       <c r="S44" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08T00:18:15Z</t>
+          <t>2026-10-09T00:32:03Z</t>
         </is>
       </c>
     </row>
@@ -4014,7 +4014,7 @@
       </c>
       <c r="S45" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08T00:18:15Z</t>
+          <t>2026-10-09T00:32:03Z</t>
         </is>
       </c>
     </row>
@@ -4103,7 +4103,7 @@
       </c>
       <c r="S46" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08T00:18:15Z</t>
+          <t>2026-10-09T00:32:03Z</t>
         </is>
       </c>
     </row>
@@ -4192,7 +4192,7 @@
       </c>
       <c r="S47" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08T00:18:15Z</t>
+          <t>2026-10-09T00:32:03Z</t>
         </is>
       </c>
     </row>
@@ -4277,7 +4277,7 @@
       </c>
       <c r="S48" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08T00:18:15Z</t>
+          <t>2026-10-09T00:32:03Z</t>
         </is>
       </c>
     </row>
@@ -4366,7 +4366,7 @@
       </c>
       <c r="S49" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08T00:18:15Z</t>
+          <t>2026-10-09T00:32:03Z</t>
         </is>
       </c>
     </row>
@@ -4455,7 +4455,7 @@
       </c>
       <c r="S50" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08T00:18:15Z</t>
+          <t>2026-10-09T00:32:03Z</t>
         </is>
       </c>
     </row>
@@ -4540,7 +4540,7 @@
       </c>
       <c r="S51" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08T00:18:15Z</t>
+          <t>2026-10-09T00:32:03Z</t>
         </is>
       </c>
     </row>
@@ -4629,7 +4629,7 @@
       </c>
       <c r="S52" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08T00:18:15Z</t>
+          <t>2026-10-09T00:32:03Z</t>
         </is>
       </c>
     </row>
@@ -4718,7 +4718,7 @@
       </c>
       <c r="S53" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08T00:18:15Z</t>
+          <t>2026-10-09T00:32:03Z</t>
         </is>
       </c>
     </row>
@@ -4803,7 +4803,7 @@
       </c>
       <c r="S54" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08T00:18:15Z</t>
+          <t>2026-10-09T00:32:03Z</t>
         </is>
       </c>
     </row>
@@ -4892,7 +4892,7 @@
       </c>
       <c r="S55" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08T00:18:15Z</t>
+          <t>2026-10-09T00:32:03Z</t>
         </is>
       </c>
     </row>
@@ -4981,7 +4981,7 @@
       </c>
       <c r="S56" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08T00:18:15Z</t>
+          <t>2026-10-09T00:32:03Z</t>
         </is>
       </c>
     </row>
@@ -5070,7 +5070,7 @@
       </c>
       <c r="S57" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08T00:18:15Z</t>
+          <t>2026-10-09T00:32:03Z</t>
         </is>
       </c>
     </row>
@@ -5159,7 +5159,7 @@
       </c>
       <c r="S58" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08T00:18:15Z</t>
+          <t>2026-10-09T00:32:03Z</t>
         </is>
       </c>
     </row>
@@ -5248,7 +5248,7 @@
       </c>
       <c r="S59" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08T00:18:15Z</t>
+          <t>2026-10-09T00:32:03Z</t>
         </is>
       </c>
     </row>
@@ -5337,7 +5337,7 @@
       </c>
       <c r="S60" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08T00:18:15Z</t>
+          <t>2026-10-09T00:32:03Z</t>
         </is>
       </c>
     </row>
@@ -5426,7 +5426,7 @@
       </c>
       <c r="S61" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08T00:18:15Z</t>
+          <t>2026-10-09T00:32:03Z</t>
         </is>
       </c>
     </row>
@@ -5515,7 +5515,7 @@
       </c>
       <c r="S62" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08T00:18:15Z</t>
+          <t>2026-10-09T00:32:03Z</t>
         </is>
       </c>
     </row>
@@ -5604,7 +5604,7 @@
       </c>
       <c r="S63" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08T00:18:15Z</t>
+          <t>2026-10-09T00:32:03Z</t>
         </is>
       </c>
     </row>
@@ -5693,7 +5693,7 @@
       </c>
       <c r="S64" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08T00:18:15Z</t>
+          <t>2026-10-09T00:32:03Z</t>
         </is>
       </c>
     </row>
@@ -5782,7 +5782,7 @@
       </c>
       <c r="S65" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08T00:18:15Z</t>
+          <t>2026-10-09T00:32:03Z</t>
         </is>
       </c>
     </row>
@@ -5871,7 +5871,7 @@
       </c>
       <c r="S66" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08T00:18:15Z</t>
+          <t>2026-10-09T00:32:03Z</t>
         </is>
       </c>
     </row>
@@ -5960,7 +5960,7 @@
       </c>
       <c r="S67" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08T00:18:15Z</t>
+          <t>2026-10-09T00:32:03Z</t>
         </is>
       </c>
     </row>
@@ -6045,7 +6045,7 @@
       </c>
       <c r="S68" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08T00:18:15Z</t>
+          <t>2026-10-09T00:32:03Z</t>
         </is>
       </c>
     </row>
@@ -6130,7 +6130,7 @@
       </c>
       <c r="S69" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08T00:18:15Z</t>
+          <t>2026-10-09T00:32:03Z</t>
         </is>
       </c>
     </row>
@@ -6215,7 +6215,7 @@
       </c>
       <c r="S70" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08T00:18:15Z</t>
+          <t>2026-10-09T00:32:03Z</t>
         </is>
       </c>
     </row>
@@ -6300,7 +6300,7 @@
       </c>
       <c r="S71" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08T00:18:15Z</t>
+          <t>2026-10-09T00:32:03Z</t>
         </is>
       </c>
     </row>
@@ -6385,7 +6385,7 @@
       </c>
       <c r="S72" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08T00:18:15Z</t>
+          <t>2026-10-09T00:32:03Z</t>
         </is>
       </c>
     </row>
@@ -6470,7 +6470,7 @@
       </c>
       <c r="S73" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08T00:18:15Z</t>
+          <t>2026-10-09T00:32:03Z</t>
         </is>
       </c>
     </row>
@@ -6555,7 +6555,7 @@
       </c>
       <c r="S74" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08T00:18:15Z</t>
+          <t>2026-10-09T00:32:03Z</t>
         </is>
       </c>
     </row>
@@ -6640,7 +6640,7 @@
       </c>
       <c r="S75" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08T00:18:15Z</t>
+          <t>2026-10-09T00:32:03Z</t>
         </is>
       </c>
     </row>
@@ -6725,7 +6725,7 @@
       </c>
       <c r="S76" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08T00:18:15Z</t>
+          <t>2026-10-09T00:32:03Z</t>
         </is>
       </c>
     </row>
@@ -6810,7 +6810,7 @@
       </c>
       <c r="S77" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08T00:18:15Z</t>
+          <t>2026-10-09T00:32:03Z</t>
         </is>
       </c>
     </row>
@@ -6895,7 +6895,7 @@
       </c>
       <c r="S78" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08T00:18:15Z</t>
+          <t>2026-10-09T00:32:03Z</t>
         </is>
       </c>
     </row>
@@ -6980,7 +6980,7 @@
       </c>
       <c r="S79" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08T00:18:15Z</t>
+          <t>2026-10-09T00:32:03Z</t>
         </is>
       </c>
     </row>
@@ -7065,7 +7065,7 @@
       </c>
       <c r="S80" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08T00:18:15Z</t>
+          <t>2026-10-09T00:32:03Z</t>
         </is>
       </c>
     </row>
@@ -7150,7 +7150,7 @@
       </c>
       <c r="S81" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08T00:18:15Z</t>
+          <t>2026-10-09T00:32:03Z</t>
         </is>
       </c>
     </row>
@@ -7235,7 +7235,7 @@
       </c>
       <c r="S82" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08T00:18:15Z</t>
+          <t>2026-10-09T00:32:03Z</t>
         </is>
       </c>
     </row>
@@ -7320,7 +7320,7 @@
       </c>
       <c r="S83" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08T00:18:15Z</t>
+          <t>2026-10-09T00:32:03Z</t>
         </is>
       </c>
     </row>
@@ -7405,7 +7405,7 @@
       </c>
       <c r="S84" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08T00:18:15Z</t>
+          <t>2026-10-09T00:32:03Z</t>
         </is>
       </c>
     </row>
@@ -7490,7 +7490,7 @@
       </c>
       <c r="S85" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08T00:18:15Z</t>
+          <t>2026-10-09T00:32:03Z</t>
         </is>
       </c>
     </row>
@@ -7575,7 +7575,7 @@
       </c>
       <c r="S86" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08T00:18:15Z</t>
+          <t>2026-10-09T00:32:03Z</t>
         </is>
       </c>
     </row>
@@ -7660,7 +7660,7 @@
       </c>
       <c r="S87" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08T00:18:15Z</t>
+          <t>2026-10-09T00:32:03Z</t>
         </is>
       </c>
     </row>
@@ -7745,7 +7745,7 @@
       </c>
       <c r="S88" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08T00:18:15Z</t>
+          <t>2026-10-09T00:32:03Z</t>
         </is>
       </c>
     </row>
@@ -7834,7 +7834,7 @@
       </c>
       <c r="S89" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08T00:18:15Z</t>
+          <t>2026-10-09T00:32:03Z</t>
         </is>
       </c>
     </row>
@@ -7923,7 +7923,7 @@
       </c>
       <c r="S90" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08T00:18:15Z</t>
+          <t>2026-10-09T00:32:03Z</t>
         </is>
       </c>
     </row>
@@ -8008,7 +8008,7 @@
       </c>
       <c r="S91" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08T00:18:15Z</t>
+          <t>2026-10-09T00:32:03Z</t>
         </is>
       </c>
     </row>
@@ -8097,7 +8097,7 @@
       </c>
       <c r="S92" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08T00:18:15Z</t>
+          <t>2026-10-09T00:32:03Z</t>
         </is>
       </c>
     </row>
@@ -8186,7 +8186,7 @@
       </c>
       <c r="S93" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08T00:18:15Z</t>
+          <t>2026-10-09T00:32:03Z</t>
         </is>
       </c>
     </row>
@@ -8271,7 +8271,7 @@
       </c>
       <c r="S94" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08T00:18:15Z</t>
+          <t>2026-10-09T00:32:03Z</t>
         </is>
       </c>
     </row>
@@ -8360,7 +8360,7 @@
       </c>
       <c r="S95" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08T00:18:15Z</t>
+          <t>2026-10-09T00:32:03Z</t>
         </is>
       </c>
     </row>
@@ -8449,7 +8449,7 @@
       </c>
       <c r="S96" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08T00:18:15Z</t>
+          <t>2026-10-09T00:32:03Z</t>
         </is>
       </c>
     </row>
@@ -8534,7 +8534,7 @@
       </c>
       <c r="S97" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08T00:18:15Z</t>
+          <t>2026-10-09T00:32:03Z</t>
         </is>
       </c>
     </row>
@@ -8623,7 +8623,7 @@
       </c>
       <c r="S98" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08T00:18:15Z</t>
+          <t>2026-10-09T00:32:03Z</t>
         </is>
       </c>
     </row>
@@ -8712,7 +8712,7 @@
       </c>
       <c r="S99" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08T00:18:15Z</t>
+          <t>2026-10-09T00:32:03Z</t>
         </is>
       </c>
     </row>
@@ -8797,7 +8797,7 @@
       </c>
       <c r="S100" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08T00:18:15Z</t>
+          <t>2026-10-09T00:32:03Z</t>
         </is>
       </c>
     </row>
@@ -8886,7 +8886,7 @@
       </c>
       <c r="S101" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08T00:18:15Z</t>
+          <t>2026-10-09T00:32:03Z</t>
         </is>
       </c>
     </row>
@@ -8975,7 +8975,7 @@
       </c>
       <c r="S102" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08T00:18:15Z</t>
+          <t>2026-10-09T00:32:03Z</t>
         </is>
       </c>
     </row>
@@ -9060,7 +9060,7 @@
       </c>
       <c r="S103" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08T00:18:15Z</t>
+          <t>2026-10-09T00:32:03Z</t>
         </is>
       </c>
     </row>
@@ -9149,7 +9149,7 @@
       </c>
       <c r="S104" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08T00:18:15Z</t>
+          <t>2026-10-09T00:32:03Z</t>
         </is>
       </c>
     </row>
@@ -9238,7 +9238,7 @@
       </c>
       <c r="S105" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08T00:18:15Z</t>
+          <t>2026-10-09T00:32:03Z</t>
         </is>
       </c>
     </row>
@@ -9323,7 +9323,7 @@
       </c>
       <c r="S106" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08T00:18:15Z</t>
+          <t>2026-10-09T00:32:03Z</t>
         </is>
       </c>
     </row>
@@ -9412,7 +9412,7 @@
       </c>
       <c r="S107" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08T00:18:15Z</t>
+          <t>2026-10-09T00:32:03Z</t>
         </is>
       </c>
     </row>
@@ -9501,7 +9501,7 @@
       </c>
       <c r="S108" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08T00:18:15Z</t>
+          <t>2026-10-09T00:32:03Z</t>
         </is>
       </c>
     </row>
@@ -9586,7 +9586,7 @@
       </c>
       <c r="S109" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08T00:18:15Z</t>
+          <t>2026-10-09T00:32:03Z</t>
         </is>
       </c>
     </row>
@@ -9675,7 +9675,7 @@
       </c>
       <c r="S110" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08T00:18:15Z</t>
+          <t>2026-10-09T00:32:03Z</t>
         </is>
       </c>
     </row>
@@ -9764,7 +9764,7 @@
       </c>
       <c r="S111" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08T00:18:15Z</t>
+          <t>2026-10-09T00:32:03Z</t>
         </is>
       </c>
     </row>
@@ -9849,7 +9849,7 @@
       </c>
       <c r="S112" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08T00:18:15Z</t>
+          <t>2026-10-09T00:32:03Z</t>
         </is>
       </c>
     </row>
@@ -9938,7 +9938,7 @@
       </c>
       <c r="S113" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08T00:18:15Z</t>
+          <t>2026-10-09T00:32:03Z</t>
         </is>
       </c>
     </row>
@@ -10027,7 +10027,7 @@
       </c>
       <c r="S114" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08T00:18:15Z</t>
+          <t>2026-10-09T00:32:03Z</t>
         </is>
       </c>
     </row>
@@ -10112,7 +10112,7 @@
       </c>
       <c r="S115" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08T00:18:15Z</t>
+          <t>2026-10-09T00:32:03Z</t>
         </is>
       </c>
     </row>
@@ -10201,7 +10201,7 @@
       </c>
       <c r="S116" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08T00:18:15Z</t>
+          <t>2026-10-09T00:32:03Z</t>
         </is>
       </c>
     </row>
@@ -10290,7 +10290,7 @@
       </c>
       <c r="S117" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08T00:18:15Z</t>
+          <t>2026-10-09T00:32:03Z</t>
         </is>
       </c>
     </row>
@@ -10379,7 +10379,7 @@
       </c>
       <c r="S118" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08T00:18:15Z</t>
+          <t>2026-10-09T00:32:03Z</t>
         </is>
       </c>
     </row>
@@ -10468,7 +10468,7 @@
       </c>
       <c r="S119" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08T00:18:15Z</t>
+          <t>2026-10-09T00:32:03Z</t>
         </is>
       </c>
     </row>
@@ -10557,7 +10557,7 @@
       </c>
       <c r="S120" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08T00:18:15Z</t>
+          <t>2026-10-09T00:32:03Z</t>
         </is>
       </c>
     </row>
@@ -10646,7 +10646,7 @@
       </c>
       <c r="S121" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08T00:18:15Z</t>
+          <t>2026-10-09T00:32:03Z</t>
         </is>
       </c>
     </row>
@@ -10735,7 +10735,7 @@
       </c>
       <c r="S122" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08T00:18:15Z</t>
+          <t>2026-10-09T00:32:03Z</t>
         </is>
       </c>
     </row>
@@ -10824,7 +10824,7 @@
       </c>
       <c r="S123" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08T00:18:15Z</t>
+          <t>2026-10-09T00:32:03Z</t>
         </is>
       </c>
     </row>
@@ -10913,7 +10913,7 @@
       </c>
       <c r="S124" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08T00:18:15Z</t>
+          <t>2026-10-09T00:32:03Z</t>
         </is>
       </c>
     </row>
@@ -11002,7 +11002,7 @@
       </c>
       <c r="S125" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08T00:18:15Z</t>
+          <t>2026-10-09T00:32:03Z</t>
         </is>
       </c>
     </row>
@@ -11091,7 +11091,7 @@
       </c>
       <c r="S126" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08T00:18:15Z</t>
+          <t>2026-10-09T00:32:03Z</t>
         </is>
       </c>
     </row>
@@ -11180,7 +11180,7 @@
       </c>
       <c r="S127" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08T00:18:15Z</t>
+          <t>2026-10-09T00:32:03Z</t>
         </is>
       </c>
     </row>
@@ -11269,7 +11269,7 @@
       </c>
       <c r="S128" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08T00:18:15Z</t>
+          <t>2026-10-09T00:32:03Z</t>
         </is>
       </c>
     </row>
@@ -11354,7 +11354,7 @@
       </c>
       <c r="S129" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08T00:18:15Z</t>
+          <t>2026-10-09T00:32:03Z</t>
         </is>
       </c>
     </row>
@@ -11439,7 +11439,7 @@
       </c>
       <c r="S130" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08T00:18:15Z</t>
+          <t>2026-10-09T00:32:03Z</t>
         </is>
       </c>
     </row>
@@ -11524,7 +11524,7 @@
       </c>
       <c r="S131" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08T00:18:15Z</t>
+          <t>2026-10-09T00:32:03Z</t>
         </is>
       </c>
     </row>
@@ -11609,7 +11609,7 @@
       </c>
       <c r="S132" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08T00:18:15Z</t>
+          <t>2026-10-09T00:32:03Z</t>
         </is>
       </c>
     </row>
@@ -11694,7 +11694,7 @@
       </c>
       <c r="S133" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08T00:18:15Z</t>
+          <t>2026-10-09T00:32:03Z</t>
         </is>
       </c>
     </row>
@@ -11779,7 +11779,7 @@
       </c>
       <c r="S134" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08T00:18:15Z</t>
+          <t>2026-10-09T00:32:03Z</t>
         </is>
       </c>
     </row>
@@ -11864,7 +11864,7 @@
       </c>
       <c r="S135" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08T00:18:15Z</t>
+          <t>2026-10-09T00:32:03Z</t>
         </is>
       </c>
     </row>
@@ -11949,7 +11949,7 @@
       </c>
       <c r="S136" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08T00:18:15Z</t>
+          <t>2026-10-09T00:32:03Z</t>
         </is>
       </c>
     </row>
@@ -12034,7 +12034,7 @@
       </c>
       <c r="S137" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08T00:18:15Z</t>
+          <t>2026-10-09T00:32:03Z</t>
         </is>
       </c>
     </row>
@@ -12119,7 +12119,7 @@
       </c>
       <c r="S138" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08T00:18:15Z</t>
+          <t>2026-10-09T00:32:03Z</t>
         </is>
       </c>
     </row>
@@ -12204,7 +12204,7 @@
       </c>
       <c r="S139" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08T00:18:15Z</t>
+          <t>2026-10-09T00:32:03Z</t>
         </is>
       </c>
     </row>
@@ -12289,7 +12289,7 @@
       </c>
       <c r="S140" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08T00:18:15Z</t>
+          <t>2026-10-09T00:32:03Z</t>
         </is>
       </c>
     </row>
@@ -12374,7 +12374,7 @@
       </c>
       <c r="S141" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08T00:18:15Z</t>
+          <t>2026-10-09T00:32:03Z</t>
         </is>
       </c>
     </row>
@@ -12459,7 +12459,7 @@
       </c>
       <c r="S142" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08T00:18:15Z</t>
+          <t>2026-10-09T00:32:03Z</t>
         </is>
       </c>
     </row>
@@ -12544,7 +12544,7 @@
       </c>
       <c r="S143" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08T00:18:15Z</t>
+          <t>2026-10-09T00:32:03Z</t>
         </is>
       </c>
     </row>
@@ -12629,7 +12629,7 @@
       </c>
       <c r="S144" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08T00:18:15Z</t>
+          <t>2026-10-09T00:32:03Z</t>
         </is>
       </c>
     </row>
@@ -12714,7 +12714,7 @@
       </c>
       <c r="S145" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08T00:18:15Z</t>
+          <t>2026-10-09T00:32:03Z</t>
         </is>
       </c>
     </row>
@@ -12799,7 +12799,7 @@
       </c>
       <c r="S146" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08T00:18:15Z</t>
+          <t>2026-10-09T00:32:03Z</t>
         </is>
       </c>
     </row>
@@ -12884,7 +12884,7 @@
       </c>
       <c r="S147" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08T00:18:15Z</t>
+          <t>2026-10-09T00:32:03Z</t>
         </is>
       </c>
     </row>
@@ -12969,7 +12969,7 @@
       </c>
       <c r="S148" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08T00:18:15Z</t>
+          <t>2026-10-09T00:32:03Z</t>
         </is>
       </c>
     </row>
@@ -13054,7 +13054,7 @@
       </c>
       <c r="S149" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08T00:18:15Z</t>
+          <t>2026-10-09T00:32:03Z</t>
         </is>
       </c>
     </row>
@@ -13143,7 +13143,7 @@
       </c>
       <c r="S150" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08T00:18:15Z</t>
+          <t>2026-10-09T00:32:03Z</t>
         </is>
       </c>
     </row>
@@ -13232,7 +13232,7 @@
       </c>
       <c r="S151" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08T00:18:15Z</t>
+          <t>2026-10-09T00:32:03Z</t>
         </is>
       </c>
     </row>
@@ -13317,7 +13317,7 @@
       </c>
       <c r="S152" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08T00:18:15Z</t>
+          <t>2026-10-09T00:32:03Z</t>
         </is>
       </c>
     </row>
@@ -13406,7 +13406,7 @@
       </c>
       <c r="S153" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08T00:18:15Z</t>
+          <t>2026-10-09T00:32:03Z</t>
         </is>
       </c>
     </row>
@@ -13495,7 +13495,7 @@
       </c>
       <c r="S154" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08T00:18:15Z</t>
+          <t>2026-10-09T00:32:03Z</t>
         </is>
       </c>
     </row>
@@ -13580,7 +13580,7 @@
       </c>
       <c r="S155" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08T00:18:15Z</t>
+          <t>2026-10-09T00:32:03Z</t>
         </is>
       </c>
     </row>
@@ -13669,7 +13669,7 @@
       </c>
       <c r="S156" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08T00:18:15Z</t>
+          <t>2026-10-09T00:32:03Z</t>
         </is>
       </c>
     </row>
@@ -13758,7 +13758,7 @@
       </c>
       <c r="S157" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08T00:18:15Z</t>
+          <t>2026-10-09T00:32:03Z</t>
         </is>
       </c>
     </row>
@@ -13843,7 +13843,7 @@
       </c>
       <c r="S158" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08T00:18:15Z</t>
+          <t>2026-10-09T00:32:03Z</t>
         </is>
       </c>
     </row>
@@ -13932,7 +13932,7 @@
       </c>
       <c r="S159" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08T00:18:15Z</t>
+          <t>2026-10-09T00:32:03Z</t>
         </is>
       </c>
     </row>
@@ -14021,7 +14021,7 @@
       </c>
       <c r="S160" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08T00:18:15Z</t>
+          <t>2026-10-09T00:32:03Z</t>
         </is>
       </c>
     </row>
@@ -14106,7 +14106,7 @@
       </c>
       <c r="S161" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08T00:18:15Z</t>
+          <t>2026-10-09T00:32:03Z</t>
         </is>
       </c>
     </row>
@@ -14195,7 +14195,7 @@
       </c>
       <c r="S162" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08T00:18:15Z</t>
+          <t>2026-10-09T00:32:03Z</t>
         </is>
       </c>
     </row>
@@ -14284,7 +14284,7 @@
       </c>
       <c r="S163" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08T00:18:15Z</t>
+          <t>2026-10-09T00:32:03Z</t>
         </is>
       </c>
     </row>
@@ -14369,7 +14369,7 @@
       </c>
       <c r="S164" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08T00:18:15Z</t>
+          <t>2026-10-09T00:32:03Z</t>
         </is>
       </c>
     </row>
@@ -14458,7 +14458,7 @@
       </c>
       <c r="S165" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08T00:18:15Z</t>
+          <t>2026-10-09T00:32:03Z</t>
         </is>
       </c>
     </row>
@@ -14547,7 +14547,7 @@
       </c>
       <c r="S166" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08T00:18:15Z</t>
+          <t>2026-10-09T00:32:03Z</t>
         </is>
       </c>
     </row>
@@ -14632,7 +14632,7 @@
       </c>
       <c r="S167" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08T00:18:15Z</t>
+          <t>2026-10-09T00:32:03Z</t>
         </is>
       </c>
     </row>
@@ -14721,7 +14721,7 @@
       </c>
       <c r="S168" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08T00:18:15Z</t>
+          <t>2026-10-09T00:32:03Z</t>
         </is>
       </c>
     </row>
@@ -14810,7 +14810,7 @@
       </c>
       <c r="S169" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08T00:18:15Z</t>
+          <t>2026-10-09T00:32:03Z</t>
         </is>
       </c>
     </row>
@@ -14895,7 +14895,7 @@
       </c>
       <c r="S170" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08T00:18:15Z</t>
+          <t>2026-10-09T00:32:03Z</t>
         </is>
       </c>
     </row>
@@ -14984,7 +14984,7 @@
       </c>
       <c r="S171" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08T00:18:15Z</t>
+          <t>2026-10-09T00:32:03Z</t>
         </is>
       </c>
     </row>
@@ -15073,7 +15073,7 @@
       </c>
       <c r="S172" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08T00:18:15Z</t>
+          <t>2026-10-09T00:32:03Z</t>
         </is>
       </c>
     </row>
@@ -15158,7 +15158,7 @@
       </c>
       <c r="S173" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08T00:18:15Z</t>
+          <t>2026-10-09T00:32:03Z</t>
         </is>
       </c>
     </row>
@@ -15247,7 +15247,7 @@
       </c>
       <c r="S174" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08T00:18:15Z</t>
+          <t>2026-10-09T00:32:03Z</t>
         </is>
       </c>
     </row>
@@ -15336,7 +15336,7 @@
       </c>
       <c r="S175" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08T00:18:15Z</t>
+          <t>2026-10-09T00:32:03Z</t>
         </is>
       </c>
     </row>
@@ -15421,7 +15421,7 @@
       </c>
       <c r="S176" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08T00:18:15Z</t>
+          <t>2026-10-09T00:32:03Z</t>
         </is>
       </c>
     </row>
@@ -15510,7 +15510,7 @@
       </c>
       <c r="S177" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08T00:18:15Z</t>
+          <t>2026-10-09T00:32:03Z</t>
         </is>
       </c>
     </row>
@@ -15599,7 +15599,7 @@
       </c>
       <c r="S178" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08T00:18:15Z</t>
+          <t>2026-10-09T00:32:03Z</t>
         </is>
       </c>
     </row>
@@ -15688,7 +15688,7 @@
       </c>
       <c r="S179" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08T00:18:15Z</t>
+          <t>2026-10-09T00:32:03Z</t>
         </is>
       </c>
     </row>
@@ -15777,7 +15777,7 @@
       </c>
       <c r="S180" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08T00:18:15Z</t>
+          <t>2026-10-09T00:32:03Z</t>
         </is>
       </c>
     </row>
@@ -15866,7 +15866,7 @@
       </c>
       <c r="S181" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08T00:18:15Z</t>
+          <t>2026-10-09T00:32:03Z</t>
         </is>
       </c>
     </row>
@@ -15955,7 +15955,7 @@
       </c>
       <c r="S182" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08T00:18:15Z</t>
+          <t>2026-10-09T00:32:03Z</t>
         </is>
       </c>
     </row>
@@ -16044,7 +16044,7 @@
       </c>
       <c r="S183" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08T00:18:15Z</t>
+          <t>2026-10-09T00:32:03Z</t>
         </is>
       </c>
     </row>
@@ -16133,7 +16133,7 @@
       </c>
       <c r="S184" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08T00:18:15Z</t>
+          <t>2026-10-09T00:32:03Z</t>
         </is>
       </c>
     </row>
@@ -16222,7 +16222,7 @@
       </c>
       <c r="S185" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08T00:18:15Z</t>
+          <t>2026-10-09T00:32:03Z</t>
         </is>
       </c>
     </row>
@@ -16311,7 +16311,7 @@
       </c>
       <c r="S186" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08T00:18:15Z</t>
+          <t>2026-10-09T00:32:03Z</t>
         </is>
       </c>
     </row>
@@ -16400,7 +16400,7 @@
       </c>
       <c r="S187" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08T00:18:15Z</t>
+          <t>2026-10-09T00:32:03Z</t>
         </is>
       </c>
     </row>
@@ -16489,7 +16489,7 @@
       </c>
       <c r="S188" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08T00:18:15Z</t>
+          <t>2026-10-09T00:32:03Z</t>
         </is>
       </c>
     </row>
@@ -16578,7 +16578,7 @@
       </c>
       <c r="S189" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08T00:18:15Z</t>
+          <t>2026-10-09T00:32:03Z</t>
         </is>
       </c>
     </row>
@@ -16663,7 +16663,7 @@
       </c>
       <c r="S190" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08T00:18:15Z</t>
+          <t>2026-10-09T00:32:03Z</t>
         </is>
       </c>
     </row>
@@ -16748,7 +16748,7 @@
       </c>
       <c r="S191" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08T00:18:15Z</t>
+          <t>2026-10-09T00:32:03Z</t>
         </is>
       </c>
     </row>
@@ -16833,7 +16833,7 @@
       </c>
       <c r="S192" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08T00:18:15Z</t>
+          <t>2026-10-09T00:32:03Z</t>
         </is>
       </c>
     </row>
@@ -16918,7 +16918,7 @@
       </c>
       <c r="S193" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08T00:18:15Z</t>
+          <t>2026-10-09T00:32:03Z</t>
         </is>
       </c>
     </row>
@@ -17003,7 +17003,7 @@
       </c>
       <c r="S194" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08T00:18:15Z</t>
+          <t>2026-10-09T00:32:03Z</t>
         </is>
       </c>
     </row>
@@ -17088,7 +17088,7 @@
       </c>
       <c r="S195" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08T00:18:15Z</t>
+          <t>2026-10-09T00:32:03Z</t>
         </is>
       </c>
     </row>
@@ -17173,7 +17173,7 @@
       </c>
       <c r="S196" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08T00:18:15Z</t>
+          <t>2026-10-09T00:32:03Z</t>
         </is>
       </c>
     </row>
@@ -17258,7 +17258,7 @@
       </c>
       <c r="S197" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08T00:18:15Z</t>
+          <t>2026-10-09T00:32:03Z</t>
         </is>
       </c>
     </row>
@@ -17343,7 +17343,7 @@
       </c>
       <c r="S198" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08T00:18:15Z</t>
+          <t>2026-10-09T00:32:03Z</t>
         </is>
       </c>
     </row>
@@ -17428,7 +17428,7 @@
       </c>
       <c r="S199" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08T00:18:15Z</t>
+          <t>2026-10-09T00:32:03Z</t>
         </is>
       </c>
     </row>
@@ -17513,7 +17513,7 @@
       </c>
       <c r="S200" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08T00:18:15Z</t>
+          <t>2026-10-09T00:32:03Z</t>
         </is>
       </c>
     </row>
@@ -17598,7 +17598,7 @@
       </c>
       <c r="S201" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08T00:18:15Z</t>
+          <t>2026-10-09T00:32:03Z</t>
         </is>
       </c>
     </row>
@@ -17683,7 +17683,7 @@
       </c>
       <c r="S202" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08T00:18:15Z</t>
+          <t>2026-10-09T00:32:03Z</t>
         </is>
       </c>
     </row>
@@ -17768,7 +17768,7 @@
       </c>
       <c r="S203" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08T00:18:15Z</t>
+          <t>2026-10-09T00:32:03Z</t>
         </is>
       </c>
     </row>
@@ -17853,7 +17853,7 @@
       </c>
       <c r="S204" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08T00:18:15Z</t>
+          <t>2026-10-09T00:32:03Z</t>
         </is>
       </c>
     </row>
@@ -17938,7 +17938,7 @@
       </c>
       <c r="S205" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08T00:18:15Z</t>
+          <t>2026-10-09T00:32:03Z</t>
         </is>
       </c>
     </row>
@@ -18023,7 +18023,7 @@
       </c>
       <c r="S206" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08T00:18:15Z</t>
+          <t>2026-10-09T00:32:03Z</t>
         </is>
       </c>
     </row>
@@ -18108,7 +18108,7 @@
       </c>
       <c r="S207" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08T00:18:15Z</t>
+          <t>2026-10-09T00:32:03Z</t>
         </is>
       </c>
     </row>
@@ -18193,7 +18193,7 @@
       </c>
       <c r="S208" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08T00:18:15Z</t>
+          <t>2026-10-09T00:32:03Z</t>
         </is>
       </c>
     </row>
@@ -18278,7 +18278,7 @@
       </c>
       <c r="S209" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08T00:18:15Z</t>
+          <t>2026-10-09T00:32:03Z</t>
         </is>
       </c>
     </row>
@@ -18363,7 +18363,7 @@
       </c>
       <c r="S210" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08T00:18:15Z</t>
+          <t>2026-10-09T00:32:03Z</t>
         </is>
       </c>
     </row>
@@ -18452,7 +18452,7 @@
       </c>
       <c r="S211" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08T00:18:15Z</t>
+          <t>2026-10-09T00:32:03Z</t>
         </is>
       </c>
     </row>
@@ -18541,7 +18541,7 @@
       </c>
       <c r="S212" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08T00:18:15Z</t>
+          <t>2026-10-09T00:32:03Z</t>
         </is>
       </c>
     </row>
@@ -18626,7 +18626,7 @@
       </c>
       <c r="S213" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08T00:18:15Z</t>
+          <t>2026-10-09T00:32:03Z</t>
         </is>
       </c>
     </row>
@@ -18715,7 +18715,7 @@
       </c>
       <c r="S214" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08T00:18:15Z</t>
+          <t>2026-10-09T00:32:03Z</t>
         </is>
       </c>
     </row>
@@ -18804,7 +18804,7 @@
       </c>
       <c r="S215" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08T00:18:15Z</t>
+          <t>2026-10-09T00:32:03Z</t>
         </is>
       </c>
     </row>
@@ -18889,7 +18889,7 @@
       </c>
       <c r="S216" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08T00:18:15Z</t>
+          <t>2026-10-09T00:32:03Z</t>
         </is>
       </c>
     </row>
@@ -18978,7 +18978,7 @@
       </c>
       <c r="S217" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08T00:18:15Z</t>
+          <t>2026-10-09T00:32:03Z</t>
         </is>
       </c>
     </row>
@@ -19067,7 +19067,7 @@
       </c>
       <c r="S218" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08T00:18:15Z</t>
+          <t>2026-10-09T00:32:03Z</t>
         </is>
       </c>
     </row>
@@ -19152,7 +19152,7 @@
       </c>
       <c r="S219" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08T00:18:15Z</t>
+          <t>2026-10-09T00:32:03Z</t>
         </is>
       </c>
     </row>
@@ -19241,7 +19241,7 @@
       </c>
       <c r="S220" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08T00:18:15Z</t>
+          <t>2026-10-09T00:32:03Z</t>
         </is>
       </c>
     </row>
@@ -19330,7 +19330,7 @@
       </c>
       <c r="S221" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08T00:18:15Z</t>
+          <t>2026-10-09T00:32:03Z</t>
         </is>
       </c>
     </row>
@@ -19415,7 +19415,7 @@
       </c>
       <c r="S222" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08T00:18:15Z</t>
+          <t>2026-10-09T00:32:03Z</t>
         </is>
       </c>
     </row>
@@ -19504,7 +19504,7 @@
       </c>
       <c r="S223" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08T00:18:15Z</t>
+          <t>2026-10-09T00:32:03Z</t>
         </is>
       </c>
     </row>
@@ -19593,7 +19593,7 @@
       </c>
       <c r="S224" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08T00:18:15Z</t>
+          <t>2026-10-09T00:32:03Z</t>
         </is>
       </c>
     </row>
@@ -19678,7 +19678,7 @@
       </c>
       <c r="S225" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08T00:18:15Z</t>
+          <t>2026-10-09T00:32:03Z</t>
         </is>
       </c>
     </row>
@@ -19767,7 +19767,7 @@
       </c>
       <c r="S226" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08T00:18:15Z</t>
+          <t>2026-10-09T00:32:03Z</t>
         </is>
       </c>
     </row>
@@ -19856,7 +19856,7 @@
       </c>
       <c r="S227" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08T00:18:15Z</t>
+          <t>2026-10-09T00:32:03Z</t>
         </is>
       </c>
     </row>
@@ -19941,7 +19941,7 @@
       </c>
       <c r="S228" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08T00:18:15Z</t>
+          <t>2026-10-09T00:32:03Z</t>
         </is>
       </c>
     </row>
@@ -20030,7 +20030,7 @@
       </c>
       <c r="S229" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08T00:18:15Z</t>
+          <t>2026-10-09T00:32:03Z</t>
         </is>
       </c>
     </row>
@@ -20119,7 +20119,7 @@
       </c>
       <c r="S230" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08T00:18:15Z</t>
+          <t>2026-10-09T00:32:03Z</t>
         </is>
       </c>
     </row>
@@ -20204,7 +20204,7 @@
       </c>
       <c r="S231" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08T00:18:15Z</t>
+          <t>2026-10-09T00:32:03Z</t>
         </is>
       </c>
     </row>
@@ -20293,7 +20293,7 @@
       </c>
       <c r="S232" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08T00:18:15Z</t>
+          <t>2026-10-09T00:32:03Z</t>
         </is>
       </c>
     </row>
@@ -20382,7 +20382,7 @@
       </c>
       <c r="S233" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08T00:18:15Z</t>
+          <t>2026-10-09T00:32:03Z</t>
         </is>
       </c>
     </row>
@@ -20467,7 +20467,7 @@
       </c>
       <c r="S234" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08T00:18:15Z</t>
+          <t>2026-10-09T00:32:03Z</t>
         </is>
       </c>
     </row>
@@ -20556,7 +20556,7 @@
       </c>
       <c r="S235" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08T00:18:15Z</t>
+          <t>2026-10-09T00:32:03Z</t>
         </is>
       </c>
     </row>
@@ -20645,7 +20645,7 @@
       </c>
       <c r="S236" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08T00:18:15Z</t>
+          <t>2026-10-09T00:32:03Z</t>
         </is>
       </c>
     </row>
@@ -20730,7 +20730,7 @@
       </c>
       <c r="S237" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08T00:18:15Z</t>
+          <t>2026-10-09T00:32:03Z</t>
         </is>
       </c>
     </row>
@@ -20819,7 +20819,7 @@
       </c>
       <c r="S238" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08T00:18:15Z</t>
+          <t>2026-10-09T00:32:03Z</t>
         </is>
       </c>
     </row>
@@ -20908,7 +20908,7 @@
       </c>
       <c r="S239" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08T00:18:15Z</t>
+          <t>2026-10-09T00:32:03Z</t>
         </is>
       </c>
     </row>
@@ -20997,7 +20997,7 @@
       </c>
       <c r="S240" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08T00:18:15Z</t>
+          <t>2026-10-09T00:32:03Z</t>
         </is>
       </c>
     </row>
@@ -21086,7 +21086,7 @@
       </c>
       <c r="S241" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08T00:18:15Z</t>
+          <t>2026-10-09T00:32:03Z</t>
         </is>
       </c>
     </row>
@@ -21175,7 +21175,7 @@
       </c>
       <c r="S242" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08T00:18:15Z</t>
+          <t>2026-10-09T00:32:03Z</t>
         </is>
       </c>
     </row>
@@ -21264,7 +21264,7 @@
       </c>
       <c r="S243" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08T00:18:15Z</t>
+          <t>2026-10-09T00:32:03Z</t>
         </is>
       </c>
     </row>
@@ -21353,7 +21353,7 @@
       </c>
       <c r="S244" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08T00:18:15Z</t>
+          <t>2026-10-09T00:32:03Z</t>
         </is>
       </c>
     </row>
@@ -21442,7 +21442,7 @@
       </c>
       <c r="S245" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08T00:18:15Z</t>
+          <t>2026-10-09T00:32:03Z</t>
         </is>
       </c>
     </row>
@@ -21531,7 +21531,7 @@
       </c>
       <c r="S246" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08T00:18:15Z</t>
+          <t>2026-10-09T00:32:03Z</t>
         </is>
       </c>
     </row>
@@ -21620,7 +21620,7 @@
       </c>
       <c r="S247" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08T00:18:15Z</t>
+          <t>2026-10-09T00:32:03Z</t>
         </is>
       </c>
     </row>
@@ -21709,7 +21709,7 @@
       </c>
       <c r="S248" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08T00:18:15Z</t>
+          <t>2026-10-09T00:32:03Z</t>
         </is>
       </c>
     </row>
@@ -21798,7 +21798,7 @@
       </c>
       <c r="S249" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08T00:18:15Z</t>
+          <t>2026-10-09T00:32:03Z</t>
         </is>
       </c>
     </row>
@@ -21887,7 +21887,7 @@
       </c>
       <c r="S250" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08T00:18:15Z</t>
+          <t>2026-10-09T00:32:03Z</t>
         </is>
       </c>
     </row>
@@ -22019,7 +22019,7 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08T00:18:15Z</t>
+          <t>2026-10-09T00:32:03Z</t>
         </is>
       </c>
     </row>
@@ -22099,7 +22099,7 @@
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>{"dataset_id": "bcv_pib_sector_institucional_anual", "title": "Producto interno bruto por sector institucional anual", "table": "Variaciones porcentuales", "source_file": "5_2_1_si_anual.xlsx", "base": "2007", "price_type": "Precios constantes", "measure": "Variación porcentual interanual", "frequency": "Anual", "period": "2025", "year": 2025, "quarter": null, "classification": "Sector institucional", "component": "Impuestos netos sobre los productos", "value": 10.600260421283764, "unit": "Porcentaje", "status": "Preliminar", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/cuentas_macroeconomicas/5_2_1_si_anual.xlsx", "fetched_at": "2026-10-08T00:18:15Z"}</t>
+          <t>{"dataset_id": "bcv_pib_sector_institucional_anual", "title": "Producto interno bruto por sector institucional anual", "table": "Variaciones porcentuales", "source_file": "5_2_1_si_anual.xlsx", "base": "2007", "price_type": "Precios constantes", "measure": "Variación porcentual interanual", "frequency": "Anual", "period": "2025", "year": 2025, "quarter": null, "classification": "Sector institucional", "component": "Impuestos netos sobre los productos", "value": 10.600260421283764, "unit": "Porcentaje", "status": "Preliminar", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/cuentas_macroeconomicas/5_2_1_si_anual.xlsx", "fetched_at": "2026-10-09T00:32:03Z"}</t>
         </is>
       </c>
     </row>

--- a/assets/data/bcv/excel/ove_bcv_pib_sector_institucional_anual.xlsx
+++ b/assets/data/bcv/excel/ove_bcv_pib_sector_institucional_anual.xlsx
@@ -736,7 +736,7 @@
       </c>
       <c r="S7" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09T00:32:03Z</t>
+          <t>2026-10-10T00:11:25Z</t>
         </is>
       </c>
     </row>
@@ -821,7 +821,7 @@
       </c>
       <c r="S8" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09T00:32:03Z</t>
+          <t>2026-10-10T00:11:25Z</t>
         </is>
       </c>
     </row>
@@ -906,7 +906,7 @@
       </c>
       <c r="S9" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09T00:32:03Z</t>
+          <t>2026-10-10T00:11:25Z</t>
         </is>
       </c>
     </row>
@@ -991,7 +991,7 @@
       </c>
       <c r="S10" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09T00:32:03Z</t>
+          <t>2026-10-10T00:11:25Z</t>
         </is>
       </c>
     </row>
@@ -1076,7 +1076,7 @@
       </c>
       <c r="S11" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09T00:32:03Z</t>
+          <t>2026-10-10T00:11:25Z</t>
         </is>
       </c>
     </row>
@@ -1161,7 +1161,7 @@
       </c>
       <c r="S12" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09T00:32:03Z</t>
+          <t>2026-10-10T00:11:25Z</t>
         </is>
       </c>
     </row>
@@ -1246,7 +1246,7 @@
       </c>
       <c r="S13" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09T00:32:03Z</t>
+          <t>2026-10-10T00:11:25Z</t>
         </is>
       </c>
     </row>
@@ -1331,7 +1331,7 @@
       </c>
       <c r="S14" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09T00:32:03Z</t>
+          <t>2026-10-10T00:11:25Z</t>
         </is>
       </c>
     </row>
@@ -1416,7 +1416,7 @@
       </c>
       <c r="S15" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09T00:32:03Z</t>
+          <t>2026-10-10T00:11:25Z</t>
         </is>
       </c>
     </row>
@@ -1501,7 +1501,7 @@
       </c>
       <c r="S16" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09T00:32:03Z</t>
+          <t>2026-10-10T00:11:25Z</t>
         </is>
       </c>
     </row>
@@ -1586,7 +1586,7 @@
       </c>
       <c r="S17" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09T00:32:03Z</t>
+          <t>2026-10-10T00:11:25Z</t>
         </is>
       </c>
     </row>
@@ -1671,7 +1671,7 @@
       </c>
       <c r="S18" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09T00:32:03Z</t>
+          <t>2026-10-10T00:11:25Z</t>
         </is>
       </c>
     </row>
@@ -1756,7 +1756,7 @@
       </c>
       <c r="S19" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09T00:32:03Z</t>
+          <t>2026-10-10T00:11:25Z</t>
         </is>
       </c>
     </row>
@@ -1841,7 +1841,7 @@
       </c>
       <c r="S20" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09T00:32:03Z</t>
+          <t>2026-10-10T00:11:25Z</t>
         </is>
       </c>
     </row>
@@ -1926,7 +1926,7 @@
       </c>
       <c r="S21" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09T00:32:03Z</t>
+          <t>2026-10-10T00:11:25Z</t>
         </is>
       </c>
     </row>
@@ -2011,7 +2011,7 @@
       </c>
       <c r="S22" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09T00:32:03Z</t>
+          <t>2026-10-10T00:11:25Z</t>
         </is>
       </c>
     </row>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="S23" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09T00:32:03Z</t>
+          <t>2026-10-10T00:11:25Z</t>
         </is>
       </c>
     </row>
@@ -2181,7 +2181,7 @@
       </c>
       <c r="S24" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09T00:32:03Z</t>
+          <t>2026-10-10T00:11:25Z</t>
         </is>
       </c>
     </row>
@@ -2266,7 +2266,7 @@
       </c>
       <c r="S25" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09T00:32:03Z</t>
+          <t>2026-10-10T00:11:25Z</t>
         </is>
       </c>
     </row>
@@ -2351,7 +2351,7 @@
       </c>
       <c r="S26" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09T00:32:03Z</t>
+          <t>2026-10-10T00:11:25Z</t>
         </is>
       </c>
     </row>
@@ -2436,7 +2436,7 @@
       </c>
       <c r="S27" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09T00:32:03Z</t>
+          <t>2026-10-10T00:11:25Z</t>
         </is>
       </c>
     </row>
@@ -2525,7 +2525,7 @@
       </c>
       <c r="S28" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09T00:32:03Z</t>
+          <t>2026-10-10T00:11:25Z</t>
         </is>
       </c>
     </row>
@@ -2614,7 +2614,7 @@
       </c>
       <c r="S29" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09T00:32:03Z</t>
+          <t>2026-10-10T00:11:25Z</t>
         </is>
       </c>
     </row>
@@ -2699,7 +2699,7 @@
       </c>
       <c r="S30" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09T00:32:03Z</t>
+          <t>2026-10-10T00:11:25Z</t>
         </is>
       </c>
     </row>
@@ -2788,7 +2788,7 @@
       </c>
       <c r="S31" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09T00:32:03Z</t>
+          <t>2026-10-10T00:11:25Z</t>
         </is>
       </c>
     </row>
@@ -2877,7 +2877,7 @@
       </c>
       <c r="S32" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09T00:32:03Z</t>
+          <t>2026-10-10T00:11:25Z</t>
         </is>
       </c>
     </row>
@@ -2962,7 +2962,7 @@
       </c>
       <c r="S33" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09T00:32:03Z</t>
+          <t>2026-10-10T00:11:25Z</t>
         </is>
       </c>
     </row>
@@ -3051,7 +3051,7 @@
       </c>
       <c r="S34" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09T00:32:03Z</t>
+          <t>2026-10-10T00:11:25Z</t>
         </is>
       </c>
     </row>
@@ -3140,7 +3140,7 @@
       </c>
       <c r="S35" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09T00:32:03Z</t>
+          <t>2026-10-10T00:11:25Z</t>
         </is>
       </c>
     </row>
@@ -3225,7 +3225,7 @@
       </c>
       <c r="S36" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09T00:32:03Z</t>
+          <t>2026-10-10T00:11:25Z</t>
         </is>
       </c>
     </row>
@@ -3314,7 +3314,7 @@
       </c>
       <c r="S37" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09T00:32:03Z</t>
+          <t>2026-10-10T00:11:25Z</t>
         </is>
       </c>
     </row>
@@ -3403,7 +3403,7 @@
       </c>
       <c r="S38" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09T00:32:03Z</t>
+          <t>2026-10-10T00:11:25Z</t>
         </is>
       </c>
     </row>
@@ -3488,7 +3488,7 @@
       </c>
       <c r="S39" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09T00:32:03Z</t>
+          <t>2026-10-10T00:11:25Z</t>
         </is>
       </c>
     </row>
@@ -3577,7 +3577,7 @@
       </c>
       <c r="S40" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09T00:32:03Z</t>
+          <t>2026-10-10T00:11:25Z</t>
         </is>
       </c>
     </row>
@@ -3666,7 +3666,7 @@
       </c>
       <c r="S41" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09T00:32:03Z</t>
+          <t>2026-10-10T00:11:25Z</t>
         </is>
       </c>
     </row>
@@ -3751,7 +3751,7 @@
       </c>
       <c r="S42" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09T00:32:03Z</t>
+          <t>2026-10-10T00:11:25Z</t>
         </is>
       </c>
     </row>
@@ -3840,7 +3840,7 @@
       </c>
       <c r="S43" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09T00:32:03Z</t>
+          <t>2026-10-10T00:11:25Z</t>
         </is>
       </c>
     </row>
@@ -3929,7 +3929,7 @@
       </c>
       <c r="S44" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09T00:32:03Z</t>
+          <t>2026-10-10T00:11:25Z</t>
         </is>
       </c>
     </row>
@@ -4014,7 +4014,7 @@
       </c>
       <c r="S45" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09T00:32:03Z</t>
+          <t>2026-10-10T00:11:25Z</t>
         </is>
       </c>
     </row>
@@ -4103,7 +4103,7 @@
       </c>
       <c r="S46" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09T00:32:03Z</t>
+          <t>2026-10-10T00:11:25Z</t>
         </is>
       </c>
     </row>
@@ -4192,7 +4192,7 @@
       </c>
       <c r="S47" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09T00:32:03Z</t>
+          <t>2026-10-10T00:11:25Z</t>
         </is>
       </c>
     </row>
@@ -4277,7 +4277,7 @@
       </c>
       <c r="S48" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09T00:32:03Z</t>
+          <t>2026-10-10T00:11:25Z</t>
         </is>
       </c>
     </row>
@@ -4366,7 +4366,7 @@
       </c>
       <c r="S49" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09T00:32:03Z</t>
+          <t>2026-10-10T00:11:25Z</t>
         </is>
       </c>
     </row>
@@ -4455,7 +4455,7 @@
       </c>
       <c r="S50" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09T00:32:03Z</t>
+          <t>2026-10-10T00:11:25Z</t>
         </is>
       </c>
     </row>
@@ -4540,7 +4540,7 @@
       </c>
       <c r="S51" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09T00:32:03Z</t>
+          <t>2026-10-10T00:11:25Z</t>
         </is>
       </c>
     </row>
@@ -4629,7 +4629,7 @@
       </c>
       <c r="S52" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09T00:32:03Z</t>
+          <t>2026-10-10T00:11:25Z</t>
         </is>
       </c>
     </row>
@@ -4718,7 +4718,7 @@
       </c>
       <c r="S53" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09T00:32:03Z</t>
+          <t>2026-10-10T00:11:25Z</t>
         </is>
       </c>
     </row>
@@ -4803,7 +4803,7 @@
       </c>
       <c r="S54" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09T00:32:03Z</t>
+          <t>2026-10-10T00:11:25Z</t>
         </is>
       </c>
     </row>
@@ -4892,7 +4892,7 @@
       </c>
       <c r="S55" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09T00:32:03Z</t>
+          <t>2026-10-10T00:11:25Z</t>
         </is>
       </c>
     </row>
@@ -4981,7 +4981,7 @@
       </c>
       <c r="S56" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09T00:32:03Z</t>
+          <t>2026-10-10T00:11:25Z</t>
         </is>
       </c>
     </row>
@@ -5070,7 +5070,7 @@
       </c>
       <c r="S57" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09T00:32:03Z</t>
+          <t>2026-10-10T00:11:25Z</t>
         </is>
       </c>
     </row>
@@ -5159,7 +5159,7 @@
       </c>
       <c r="S58" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09T00:32:03Z</t>
+          <t>2026-10-10T00:11:25Z</t>
         </is>
       </c>
     </row>
@@ -5248,7 +5248,7 @@
       </c>
       <c r="S59" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09T00:32:03Z</t>
+          <t>2026-10-10T00:11:25Z</t>
         </is>
       </c>
     </row>
@@ -5337,7 +5337,7 @@
       </c>
       <c r="S60" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09T00:32:03Z</t>
+          <t>2026-10-10T00:11:25Z</t>
         </is>
       </c>
     </row>
@@ -5426,7 +5426,7 @@
       </c>
       <c r="S61" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09T00:32:03Z</t>
+          <t>2026-10-10T00:11:25Z</t>
         </is>
       </c>
     </row>
@@ -5515,7 +5515,7 @@
       </c>
       <c r="S62" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09T00:32:03Z</t>
+          <t>2026-10-10T00:11:25Z</t>
         </is>
       </c>
     </row>
@@ -5604,7 +5604,7 @@
       </c>
       <c r="S63" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09T00:32:03Z</t>
+          <t>2026-10-10T00:11:25Z</t>
         </is>
       </c>
     </row>
@@ -5693,7 +5693,7 @@
       </c>
       <c r="S64" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09T00:32:03Z</t>
+          <t>2026-10-10T00:11:25Z</t>
         </is>
       </c>
     </row>
@@ -5782,7 +5782,7 @@
       </c>
       <c r="S65" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09T00:32:03Z</t>
+          <t>2026-10-10T00:11:25Z</t>
         </is>
       </c>
     </row>
@@ -5871,7 +5871,7 @@
       </c>
       <c r="S66" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09T00:32:03Z</t>
+          <t>2026-10-10T00:11:25Z</t>
         </is>
       </c>
     </row>
@@ -5960,7 +5960,7 @@
       </c>
       <c r="S67" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09T00:32:03Z</t>
+          <t>2026-10-10T00:11:25Z</t>
         </is>
       </c>
     </row>
@@ -6045,7 +6045,7 @@
       </c>
       <c r="S68" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09T00:32:03Z</t>
+          <t>2026-10-10T00:11:25Z</t>
         </is>
       </c>
     </row>
@@ -6130,7 +6130,7 @@
       </c>
       <c r="S69" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09T00:32:03Z</t>
+          <t>2026-10-10T00:11:25Z</t>
         </is>
       </c>
     </row>
@@ -6215,7 +6215,7 @@
       </c>
       <c r="S70" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09T00:32:03Z</t>
+          <t>2026-10-10T00:11:25Z</t>
         </is>
       </c>
     </row>
@@ -6300,7 +6300,7 @@
       </c>
       <c r="S71" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09T00:32:03Z</t>
+          <t>2026-10-10T00:11:25Z</t>
         </is>
       </c>
     </row>
@@ -6385,7 +6385,7 @@
       </c>
       <c r="S72" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09T00:32:03Z</t>
+          <t>2026-10-10T00:11:25Z</t>
         </is>
       </c>
     </row>
@@ -6470,7 +6470,7 @@
       </c>
       <c r="S73" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09T00:32:03Z</t>
+          <t>2026-10-10T00:11:25Z</t>
         </is>
       </c>
     </row>
@@ -6555,7 +6555,7 @@
       </c>
       <c r="S74" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09T00:32:03Z</t>
+          <t>2026-10-10T00:11:25Z</t>
         </is>
       </c>
     </row>
@@ -6640,7 +6640,7 @@
       </c>
       <c r="S75" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09T00:32:03Z</t>
+          <t>2026-10-10T00:11:25Z</t>
         </is>
       </c>
     </row>
@@ -6725,7 +6725,7 @@
       </c>
       <c r="S76" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09T00:32:03Z</t>
+          <t>2026-10-10T00:11:25Z</t>
         </is>
       </c>
     </row>
@@ -6810,7 +6810,7 @@
       </c>
       <c r="S77" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09T00:32:03Z</t>
+          <t>2026-10-10T00:11:25Z</t>
         </is>
       </c>
     </row>
@@ -6895,7 +6895,7 @@
       </c>
       <c r="S78" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09T00:32:03Z</t>
+          <t>2026-10-10T00:11:25Z</t>
         </is>
       </c>
     </row>
@@ -6980,7 +6980,7 @@
       </c>
       <c r="S79" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09T00:32:03Z</t>
+          <t>2026-10-10T00:11:25Z</t>
         </is>
       </c>
     </row>
@@ -7065,7 +7065,7 @@
       </c>
       <c r="S80" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09T00:32:03Z</t>
+          <t>2026-10-10T00:11:25Z</t>
         </is>
       </c>
     </row>
@@ -7150,7 +7150,7 @@
       </c>
       <c r="S81" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09T00:32:03Z</t>
+          <t>2026-10-10T00:11:25Z</t>
         </is>
       </c>
     </row>
@@ -7235,7 +7235,7 @@
       </c>
       <c r="S82" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09T00:32:03Z</t>
+          <t>2026-10-10T00:11:25Z</t>
         </is>
       </c>
     </row>
@@ -7320,7 +7320,7 @@
       </c>
       <c r="S83" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09T00:32:03Z</t>
+          <t>2026-10-10T00:11:25Z</t>
         </is>
       </c>
     </row>
@@ -7405,7 +7405,7 @@
       </c>
       <c r="S84" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09T00:32:03Z</t>
+          <t>2026-10-10T00:11:25Z</t>
         </is>
       </c>
     </row>
@@ -7490,7 +7490,7 @@
       </c>
       <c r="S85" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09T00:32:03Z</t>
+          <t>2026-10-10T00:11:25Z</t>
         </is>
       </c>
     </row>
@@ -7575,7 +7575,7 @@
       </c>
       <c r="S86" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09T00:32:03Z</t>
+          <t>2026-10-10T00:11:25Z</t>
         </is>
       </c>
     </row>
@@ -7660,7 +7660,7 @@
       </c>
       <c r="S87" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09T00:32:03Z</t>
+          <t>2026-10-10T00:11:25Z</t>
         </is>
       </c>
     </row>
@@ -7745,7 +7745,7 @@
       </c>
       <c r="S88" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09T00:32:03Z</t>
+          <t>2026-10-10T00:11:25Z</t>
         </is>
       </c>
     </row>
@@ -7834,7 +7834,7 @@
       </c>
       <c r="S89" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09T00:32:03Z</t>
+          <t>2026-10-10T00:11:25Z</t>
         </is>
       </c>
     </row>
@@ -7923,7 +7923,7 @@
       </c>
       <c r="S90" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09T00:32:03Z</t>
+          <t>2026-10-10T00:11:25Z</t>
         </is>
       </c>
     </row>
@@ -8008,7 +8008,7 @@
       </c>
       <c r="S91" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09T00:32:03Z</t>
+          <t>2026-10-10T00:11:25Z</t>
         </is>
       </c>
     </row>
@@ -8097,7 +8097,7 @@
       </c>
       <c r="S92" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09T00:32:03Z</t>
+          <t>2026-10-10T00:11:25Z</t>
         </is>
       </c>
     </row>
@@ -8186,7 +8186,7 @@
       </c>
       <c r="S93" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09T00:32:03Z</t>
+          <t>2026-10-10T00:11:25Z</t>
         </is>
       </c>
     </row>
@@ -8271,7 +8271,7 @@
       </c>
       <c r="S94" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09T00:32:03Z</t>
+          <t>2026-10-10T00:11:25Z</t>
         </is>
       </c>
     </row>
@@ -8360,7 +8360,7 @@
       </c>
       <c r="S95" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09T00:32:03Z</t>
+          <t>2026-10-10T00:11:25Z</t>
         </is>
       </c>
     </row>
@@ -8449,7 +8449,7 @@
       </c>
       <c r="S96" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09T00:32:03Z</t>
+          <t>2026-10-10T00:11:25Z</t>
         </is>
       </c>
     </row>
@@ -8534,7 +8534,7 @@
       </c>
       <c r="S97" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09T00:32:03Z</t>
+          <t>2026-10-10T00:11:25Z</t>
         </is>
       </c>
     </row>
@@ -8623,7 +8623,7 @@
       </c>
       <c r="S98" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09T00:32:03Z</t>
+          <t>2026-10-10T00:11:25Z</t>
         </is>
       </c>
     </row>
@@ -8712,7 +8712,7 @@
       </c>
       <c r="S99" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09T00:32:03Z</t>
+          <t>2026-10-10T00:11:25Z</t>
         </is>
       </c>
     </row>
@@ -8797,7 +8797,7 @@
       </c>
       <c r="S100" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09T00:32:03Z</t>
+          <t>2026-10-10T00:11:25Z</t>
         </is>
       </c>
     </row>
@@ -8886,7 +8886,7 @@
       </c>
       <c r="S101" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09T00:32:03Z</t>
+          <t>2026-10-10T00:11:25Z</t>
         </is>
       </c>
     </row>
@@ -8975,7 +8975,7 @@
       </c>
       <c r="S102" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09T00:32:03Z</t>
+          <t>2026-10-10T00:11:25Z</t>
         </is>
       </c>
     </row>
@@ -9060,7 +9060,7 @@
       </c>
       <c r="S103" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09T00:32:03Z</t>
+          <t>2026-10-10T00:11:25Z</t>
         </is>
       </c>
     </row>
@@ -9149,7 +9149,7 @@
       </c>
       <c r="S104" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09T00:32:03Z</t>
+          <t>2026-10-10T00:11:25Z</t>
         </is>
       </c>
     </row>
@@ -9238,7 +9238,7 @@
       </c>
       <c r="S105" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09T00:32:03Z</t>
+          <t>2026-10-10T00:11:25Z</t>
         </is>
       </c>
     </row>
@@ -9323,7 +9323,7 @@
       </c>
       <c r="S106" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09T00:32:03Z</t>
+          <t>2026-10-10T00:11:25Z</t>
         </is>
       </c>
     </row>
@@ -9412,7 +9412,7 @@
       </c>
       <c r="S107" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09T00:32:03Z</t>
+          <t>2026-10-10T00:11:25Z</t>
         </is>
       </c>
     </row>
@@ -9501,7 +9501,7 @@
       </c>
       <c r="S108" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09T00:32:03Z</t>
+          <t>2026-10-10T00:11:25Z</t>
         </is>
       </c>
     </row>
@@ -9586,7 +9586,7 @@
       </c>
       <c r="S109" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09T00:32:03Z</t>
+          <t>2026-10-10T00:11:25Z</t>
         </is>
       </c>
     </row>
@@ -9675,7 +9675,7 @@
       </c>
       <c r="S110" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09T00:32:03Z</t>
+          <t>2026-10-10T00:11:25Z</t>
         </is>
       </c>
     </row>
@@ -9764,7 +9764,7 @@
       </c>
       <c r="S111" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09T00:32:03Z</t>
+          <t>2026-10-10T00:11:25Z</t>
         </is>
       </c>
     </row>
@@ -9849,7 +9849,7 @@
       </c>
       <c r="S112" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09T00:32:03Z</t>
+          <t>2026-10-10T00:11:25Z</t>
         </is>
       </c>
     </row>
@@ -9938,7 +9938,7 @@
       </c>
       <c r="S113" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09T00:32:03Z</t>
+          <t>2026-10-10T00:11:25Z</t>
         </is>
       </c>
     </row>
@@ -10027,7 +10027,7 @@
       </c>
       <c r="S114" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09T00:32:03Z</t>
+          <t>2026-10-10T00:11:25Z</t>
         </is>
       </c>
     </row>
@@ -10112,7 +10112,7 @@
       </c>
       <c r="S115" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09T00:32:03Z</t>
+          <t>2026-10-10T00:11:25Z</t>
         </is>
       </c>
     </row>
@@ -10201,7 +10201,7 @@
       </c>
       <c r="S116" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09T00:32:03Z</t>
+          <t>2026-10-10T00:11:25Z</t>
         </is>
       </c>
     </row>
@@ -10290,7 +10290,7 @@
       </c>
       <c r="S117" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09T00:32:03Z</t>
+          <t>2026-10-10T00:11:25Z</t>
         </is>
       </c>
     </row>
@@ -10379,7 +10379,7 @@
       </c>
       <c r="S118" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09T00:32:03Z</t>
+          <t>2026-10-10T00:11:25Z</t>
         </is>
       </c>
     </row>
@@ -10468,7 +10468,7 @@
       </c>
       <c r="S119" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09T00:32:03Z</t>
+          <t>2026-10-10T00:11:25Z</t>
         </is>
       </c>
     </row>
@@ -10557,7 +10557,7 @@
       </c>
       <c r="S120" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09T00:32:03Z</t>
+          <t>2026-10-10T00:11:25Z</t>
         </is>
       </c>
     </row>
@@ -10646,7 +10646,7 @@
       </c>
       <c r="S121" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09T00:32:03Z</t>
+          <t>2026-10-10T00:11:25Z</t>
         </is>
       </c>
     </row>
@@ -10735,7 +10735,7 @@
       </c>
       <c r="S122" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09T00:32:03Z</t>
+          <t>2026-10-10T00:11:25Z</t>
         </is>
       </c>
     </row>
@@ -10824,7 +10824,7 @@
       </c>
       <c r="S123" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09T00:32:03Z</t>
+          <t>2026-10-10T00:11:25Z</t>
         </is>
       </c>
     </row>
@@ -10913,7 +10913,7 @@
       </c>
       <c r="S124" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09T00:32:03Z</t>
+          <t>2026-10-10T00:11:25Z</t>
         </is>
       </c>
     </row>
@@ -11002,7 +11002,7 @@
       </c>
       <c r="S125" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09T00:32:03Z</t>
+          <t>2026-10-10T00:11:25Z</t>
         </is>
       </c>
     </row>
@@ -11091,7 +11091,7 @@
       </c>
       <c r="S126" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09T00:32:03Z</t>
+          <t>2026-10-10T00:11:25Z</t>
         </is>
       </c>
     </row>
@@ -11180,7 +11180,7 @@
       </c>
       <c r="S127" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09T00:32:03Z</t>
+          <t>2026-10-10T00:11:25Z</t>
         </is>
       </c>
     </row>
@@ -11269,7 +11269,7 @@
       </c>
       <c r="S128" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09T00:32:03Z</t>
+          <t>2026-10-10T00:11:25Z</t>
         </is>
       </c>
     </row>
@@ -11354,7 +11354,7 @@
       </c>
       <c r="S129" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09T00:32:03Z</t>
+          <t>2026-10-10T00:11:25Z</t>
         </is>
       </c>
     </row>
@@ -11439,7 +11439,7 @@
       </c>
       <c r="S130" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09T00:32:03Z</t>
+          <t>2026-10-10T00:11:25Z</t>
         </is>
       </c>
     </row>
@@ -11524,7 +11524,7 @@
       </c>
       <c r="S131" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09T00:32:03Z</t>
+          <t>2026-10-10T00:11:25Z</t>
         </is>
       </c>
     </row>
@@ -11609,7 +11609,7 @@
       </c>
       <c r="S132" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09T00:32:03Z</t>
+          <t>2026-10-10T00:11:25Z</t>
         </is>
       </c>
     </row>
@@ -11694,7 +11694,7 @@
       </c>
       <c r="S133" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09T00:32:03Z</t>
+          <t>2026-10-10T00:11:25Z</t>
         </is>
       </c>
     </row>
@@ -11779,7 +11779,7 @@
       </c>
       <c r="S134" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09T00:32:03Z</t>
+          <t>2026-10-10T00:11:25Z</t>
         </is>
       </c>
     </row>
@@ -11864,7 +11864,7 @@
       </c>
       <c r="S135" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09T00:32:03Z</t>
+          <t>2026-10-10T00:11:25Z</t>
         </is>
       </c>
     </row>
@@ -11949,7 +11949,7 @@
       </c>
       <c r="S136" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09T00:32:03Z</t>
+          <t>2026-10-10T00:11:25Z</t>
         </is>
       </c>
     </row>
@@ -12034,7 +12034,7 @@
       </c>
       <c r="S137" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09T00:32:03Z</t>
+          <t>2026-10-10T00:11:25Z</t>
         </is>
       </c>
     </row>
@@ -12119,7 +12119,7 @@
       </c>
       <c r="S138" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09T00:32:03Z</t>
+          <t>2026-10-10T00:11:25Z</t>
         </is>
       </c>
     </row>
@@ -12204,7 +12204,7 @@
       </c>
       <c r="S139" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09T00:32:03Z</t>
+          <t>2026-10-10T00:11:25Z</t>
         </is>
       </c>
     </row>
@@ -12289,7 +12289,7 @@
       </c>
       <c r="S140" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09T00:32:03Z</t>
+          <t>2026-10-10T00:11:25Z</t>
         </is>
       </c>
     </row>
@@ -12374,7 +12374,7 @@
       </c>
       <c r="S141" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09T00:32:03Z</t>
+          <t>2026-10-10T00:11:25Z</t>
         </is>
       </c>
     </row>
@@ -12459,7 +12459,7 @@
       </c>
       <c r="S142" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09T00:32:03Z</t>
+          <t>2026-10-10T00:11:25Z</t>
         </is>
       </c>
     </row>
@@ -12544,7 +12544,7 @@
       </c>
       <c r="S143" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09T00:32:03Z</t>
+          <t>2026-10-10T00:11:25Z</t>
         </is>
       </c>
     </row>
@@ -12629,7 +12629,7 @@
       </c>
       <c r="S144" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09T00:32:03Z</t>
+          <t>2026-10-10T00:11:25Z</t>
         </is>
       </c>
     </row>
@@ -12714,7 +12714,7 @@
       </c>
       <c r="S145" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09T00:32:03Z</t>
+          <t>2026-10-10T00:11:25Z</t>
         </is>
       </c>
     </row>
@@ -12799,7 +12799,7 @@
       </c>
       <c r="S146" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09T00:32:03Z</t>
+          <t>2026-10-10T00:11:25Z</t>
         </is>
       </c>
     </row>
@@ -12884,7 +12884,7 @@
       </c>
       <c r="S147" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09T00:32:03Z</t>
+          <t>2026-10-10T00:11:25Z</t>
         </is>
       </c>
     </row>
@@ -12969,7 +12969,7 @@
       </c>
       <c r="S148" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09T00:32:03Z</t>
+          <t>2026-10-10T00:11:25Z</t>
         </is>
       </c>
     </row>
@@ -13054,7 +13054,7 @@
       </c>
       <c r="S149" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09T00:32:03Z</t>
+          <t>2026-10-10T00:11:25Z</t>
         </is>
       </c>
     </row>
@@ -13143,7 +13143,7 @@
       </c>
       <c r="S150" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09T00:32:03Z</t>
+          <t>2026-10-10T00:11:25Z</t>
         </is>
       </c>
     </row>
@@ -13232,7 +13232,7 @@
       </c>
       <c r="S151" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09T00:32:03Z</t>
+          <t>2026-10-10T00:11:25Z</t>
         </is>
       </c>
     </row>
@@ -13317,7 +13317,7 @@
       </c>
       <c r="S152" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09T00:32:03Z</t>
+          <t>2026-10-10T00:11:25Z</t>
         </is>
       </c>
     </row>
@@ -13406,7 +13406,7 @@
       </c>
       <c r="S153" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09T00:32:03Z</t>
+          <t>2026-10-10T00:11:25Z</t>
         </is>
       </c>
     </row>
@@ -13495,7 +13495,7 @@
       </c>
       <c r="S154" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09T00:32:03Z</t>
+          <t>2026-10-10T00:11:25Z</t>
         </is>
       </c>
     </row>
@@ -13580,7 +13580,7 @@
       </c>
       <c r="S155" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09T00:32:03Z</t>
+          <t>2026-10-10T00:11:25Z</t>
         </is>
       </c>
     </row>
@@ -13669,7 +13669,7 @@
       </c>
       <c r="S156" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09T00:32:03Z</t>
+          <t>2026-10-10T00:11:25Z</t>
         </is>
       </c>
     </row>
@@ -13758,7 +13758,7 @@
       </c>
       <c r="S157" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09T00:32:03Z</t>
+          <t>2026-10-10T00:11:25Z</t>
         </is>
       </c>
     </row>
@@ -13843,7 +13843,7 @@
       </c>
       <c r="S158" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09T00:32:03Z</t>
+          <t>2026-10-10T00:11:25Z</t>
         </is>
       </c>
     </row>
@@ -13932,7 +13932,7 @@
       </c>
       <c r="S159" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09T00:32:03Z</t>
+          <t>2026-10-10T00:11:25Z</t>
         </is>
       </c>
     </row>
@@ -14021,7 +14021,7 @@
       </c>
       <c r="S160" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09T00:32:03Z</t>
+          <t>2026-10-10T00:11:25Z</t>
         </is>
       </c>
     </row>
@@ -14106,7 +14106,7 @@
       </c>
       <c r="S161" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09T00:32:03Z</t>
+          <t>2026-10-10T00:11:25Z</t>
         </is>
       </c>
     </row>
@@ -14195,7 +14195,7 @@
       </c>
       <c r="S162" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09T00:32:03Z</t>
+          <t>2026-10-10T00:11:25Z</t>
         </is>
       </c>
     </row>
@@ -14284,7 +14284,7 @@
       </c>
       <c r="S163" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09T00:32:03Z</t>
+          <t>2026-10-10T00:11:25Z</t>
         </is>
       </c>
     </row>
@@ -14369,7 +14369,7 @@
       </c>
       <c r="S164" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09T00:32:03Z</t>
+          <t>2026-10-10T00:11:25Z</t>
         </is>
       </c>
     </row>
@@ -14458,7 +14458,7 @@
       </c>
       <c r="S165" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09T00:32:03Z</t>
+          <t>2026-10-10T00:11:25Z</t>
         </is>
       </c>
     </row>
@@ -14547,7 +14547,7 @@
       </c>
       <c r="S166" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09T00:32:03Z</t>
+          <t>2026-10-10T00:11:25Z</t>
         </is>
       </c>
     </row>
@@ -14632,7 +14632,7 @@
       </c>
       <c r="S167" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09T00:32:03Z</t>
+          <t>2026-10-10T00:11:25Z</t>
         </is>
       </c>
     </row>
@@ -14721,7 +14721,7 @@
       </c>
       <c r="S168" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09T00:32:03Z</t>
+          <t>2026-10-10T00:11:25Z</t>
         </is>
       </c>
     </row>
@@ -14810,7 +14810,7 @@
       </c>
       <c r="S169" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09T00:32:03Z</t>
+          <t>2026-10-10T00:11:25Z</t>
         </is>
       </c>
     </row>
@@ -14895,7 +14895,7 @@
       </c>
       <c r="S170" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09T00:32:03Z</t>
+          <t>2026-10-10T00:11:25Z</t>
         </is>
       </c>
     </row>
@@ -14984,7 +14984,7 @@
       </c>
       <c r="S171" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09T00:32:03Z</t>
+          <t>2026-10-10T00:11:25Z</t>
         </is>
       </c>
     </row>
@@ -15073,7 +15073,7 @@
       </c>
       <c r="S172" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09T00:32:03Z</t>
+          <t>2026-10-10T00:11:25Z</t>
         </is>
       </c>
     </row>
@@ -15158,7 +15158,7 @@
       </c>
       <c r="S173" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09T00:32:03Z</t>
+          <t>2026-10-10T00:11:25Z</t>
         </is>
       </c>
     </row>
@@ -15247,7 +15247,7 @@
       </c>
       <c r="S174" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09T00:32:03Z</t>
+          <t>2026-10-10T00:11:25Z</t>
         </is>
       </c>
     </row>
@@ -15336,7 +15336,7 @@
       </c>
       <c r="S175" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09T00:32:03Z</t>
+          <t>2026-10-10T00:11:25Z</t>
         </is>
       </c>
     </row>
@@ -15421,7 +15421,7 @@
       </c>
       <c r="S176" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09T00:32:03Z</t>
+          <t>2026-10-10T00:11:25Z</t>
         </is>
       </c>
     </row>
@@ -15510,7 +15510,7 @@
       </c>
       <c r="S177" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09T00:32:03Z</t>
+          <t>2026-10-10T00:11:25Z</t>
         </is>
       </c>
     </row>
@@ -15599,7 +15599,7 @@
       </c>
       <c r="S178" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09T00:32:03Z</t>
+          <t>2026-10-10T00:11:25Z</t>
         </is>
       </c>
     </row>
@@ -15688,7 +15688,7 @@
       </c>
       <c r="S179" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09T00:32:03Z</t>
+          <t>2026-10-10T00:11:25Z</t>
         </is>
       </c>
     </row>
@@ -15777,7 +15777,7 @@
       </c>
       <c r="S180" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09T00:32:03Z</t>
+          <t>2026-10-10T00:11:25Z</t>
         </is>
       </c>
     </row>
@@ -15866,7 +15866,7 @@
       </c>
       <c r="S181" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09T00:32:03Z</t>
+          <t>2026-10-10T00:11:25Z</t>
         </is>
       </c>
     </row>
@@ -15955,7 +15955,7 @@
       </c>
       <c r="S182" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09T00:32:03Z</t>
+          <t>2026-10-10T00:11:25Z</t>
         </is>
       </c>
     </row>
@@ -16044,7 +16044,7 @@
       </c>
       <c r="S183" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09T00:32:03Z</t>
+          <t>2026-10-10T00:11:25Z</t>
         </is>
       </c>
     </row>
@@ -16133,7 +16133,7 @@
       </c>
       <c r="S184" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09T00:32:03Z</t>
+          <t>2026-10-10T00:11:25Z</t>
         </is>
       </c>
     </row>
@@ -16222,7 +16222,7 @@
       </c>
       <c r="S185" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09T00:32:03Z</t>
+          <t>2026-10-10T00:11:25Z</t>
         </is>
       </c>
     </row>
@@ -16311,7 +16311,7 @@
       </c>
       <c r="S186" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09T00:32:03Z</t>
+          <t>2026-10-10T00:11:25Z</t>
         </is>
       </c>
     </row>
@@ -16400,7 +16400,7 @@
       </c>
       <c r="S187" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09T00:32:03Z</t>
+          <t>2026-10-10T00:11:25Z</t>
         </is>
       </c>
     </row>
@@ -16489,7 +16489,7 @@
       </c>
       <c r="S188" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09T00:32:03Z</t>
+          <t>2026-10-10T00:11:25Z</t>
         </is>
       </c>
     </row>
@@ -16578,7 +16578,7 @@
       </c>
       <c r="S189" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09T00:32:03Z</t>
+          <t>2026-10-10T00:11:25Z</t>
         </is>
       </c>
     </row>
@@ -16663,7 +16663,7 @@
       </c>
       <c r="S190" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09T00:32:03Z</t>
+          <t>2026-10-10T00:11:25Z</t>
         </is>
       </c>
     </row>
@@ -16748,7 +16748,7 @@
       </c>
       <c r="S191" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09T00:32:03Z</t>
+          <t>2026-10-10T00:11:25Z</t>
         </is>
       </c>
     </row>
@@ -16833,7 +16833,7 @@
       </c>
       <c r="S192" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09T00:32:03Z</t>
+          <t>2026-10-10T00:11:25Z</t>
         </is>
       </c>
     </row>
@@ -16918,7 +16918,7 @@
       </c>
       <c r="S193" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09T00:32:03Z</t>
+          <t>2026-10-10T00:11:25Z</t>
         </is>
       </c>
     </row>
@@ -17003,7 +17003,7 @@
       </c>
       <c r="S194" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09T00:32:03Z</t>
+          <t>2026-10-10T00:11:25Z</t>
         </is>
       </c>
     </row>
@@ -17088,7 +17088,7 @@
       </c>
       <c r="S195" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09T00:32:03Z</t>
+          <t>2026-10-10T00:11:25Z</t>
         </is>
       </c>
     </row>
@@ -17173,7 +17173,7 @@
       </c>
       <c r="S196" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09T00:32:03Z</t>
+          <t>2026-10-10T00:11:25Z</t>
         </is>
       </c>
     </row>
@@ -17258,7 +17258,7 @@
       </c>
       <c r="S197" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09T00:32:03Z</t>
+          <t>2026-10-10T00:11:25Z</t>
         </is>
       </c>
     </row>
@@ -17343,7 +17343,7 @@
       </c>
       <c r="S198" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09T00:32:03Z</t>
+          <t>2026-10-10T00:11:25Z</t>
         </is>
       </c>
     </row>
@@ -17428,7 +17428,7 @@
       </c>
       <c r="S199" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09T00:32:03Z</t>
+          <t>2026-10-10T00:11:25Z</t>
         </is>
       </c>
     </row>
@@ -17513,7 +17513,7 @@
       </c>
       <c r="S200" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09T00:32:03Z</t>
+          <t>2026-10-10T00:11:25Z</t>
         </is>
       </c>
     </row>
@@ -17598,7 +17598,7 @@
       </c>
       <c r="S201" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09T00:32:03Z</t>
+          <t>2026-10-10T00:11:25Z</t>
         </is>
       </c>
     </row>
@@ -17683,7 +17683,7 @@
       </c>
       <c r="S202" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09T00:32:03Z</t>
+          <t>2026-10-10T00:11:25Z</t>
         </is>
       </c>
     </row>
@@ -17768,7 +17768,7 @@
       </c>
       <c r="S203" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09T00:32:03Z</t>
+          <t>2026-10-10T00:11:25Z</t>
         </is>
       </c>
     </row>
@@ -17853,7 +17853,7 @@
       </c>
       <c r="S204" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09T00:32:03Z</t>
+          <t>2026-10-10T00:11:25Z</t>
         </is>
       </c>
     </row>
@@ -17938,7 +17938,7 @@
       </c>
       <c r="S205" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09T00:32:03Z</t>
+          <t>2026-10-10T00:11:25Z</t>
         </is>
       </c>
     </row>
@@ -18023,7 +18023,7 @@
       </c>
       <c r="S206" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09T00:32:03Z</t>
+          <t>2026-10-10T00:11:25Z</t>
         </is>
       </c>
     </row>
@@ -18108,7 +18108,7 @@
       </c>
       <c r="S207" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09T00:32:03Z</t>
+          <t>2026-10-10T00:11:25Z</t>
         </is>
       </c>
     </row>
@@ -18193,7 +18193,7 @@
       </c>
       <c r="S208" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09T00:32:03Z</t>
+          <t>2026-10-10T00:11:25Z</t>
         </is>
       </c>
     </row>
@@ -18278,7 +18278,7 @@
       </c>
       <c r="S209" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09T00:32:03Z</t>
+          <t>2026-10-10T00:11:25Z</t>
         </is>
       </c>
     </row>
@@ -18363,7 +18363,7 @@
       </c>
       <c r="S210" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09T00:32:03Z</t>
+          <t>2026-10-10T00:11:25Z</t>
         </is>
       </c>
     </row>
@@ -18452,7 +18452,7 @@
       </c>
       <c r="S211" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09T00:32:03Z</t>
+          <t>2026-10-10T00:11:25Z</t>
         </is>
       </c>
     </row>
@@ -18541,7 +18541,7 @@
       </c>
       <c r="S212" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09T00:32:03Z</t>
+          <t>2026-10-10T00:11:25Z</t>
         </is>
       </c>
     </row>
@@ -18626,7 +18626,7 @@
       </c>
       <c r="S213" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09T00:32:03Z</t>
+          <t>2026-10-10T00:11:25Z</t>
         </is>
       </c>
     </row>
@@ -18715,7 +18715,7 @@
       </c>
       <c r="S214" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09T00:32:03Z</t>
+          <t>2026-10-10T00:11:25Z</t>
         </is>
       </c>
     </row>
@@ -18804,7 +18804,7 @@
       </c>
       <c r="S215" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09T00:32:03Z</t>
+          <t>2026-10-10T00:11:25Z</t>
         </is>
       </c>
     </row>
@@ -18889,7 +18889,7 @@
       </c>
       <c r="S216" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09T00:32:03Z</t>
+          <t>2026-10-10T00:11:25Z</t>
         </is>
       </c>
     </row>
@@ -18978,7 +18978,7 @@
       </c>
       <c r="S217" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09T00:32:03Z</t>
+          <t>2026-10-10T00:11:25Z</t>
         </is>
       </c>
     </row>
@@ -19067,7 +19067,7 @@
       </c>
       <c r="S218" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09T00:32:03Z</t>
+          <t>2026-10-10T00:11:25Z</t>
         </is>
       </c>
     </row>
@@ -19152,7 +19152,7 @@
       </c>
       <c r="S219" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09T00:32:03Z</t>
+          <t>2026-10-10T00:11:25Z</t>
         </is>
       </c>
     </row>
@@ -19241,7 +19241,7 @@
       </c>
       <c r="S220" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09T00:32:03Z</t>
+          <t>2026-10-10T00:11:25Z</t>
         </is>
       </c>
     </row>
@@ -19330,7 +19330,7 @@
       </c>
       <c r="S221" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09T00:32:03Z</t>
+          <t>2026-10-10T00:11:25Z</t>
         </is>
       </c>
     </row>
@@ -19415,7 +19415,7 @@
       </c>
       <c r="S222" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09T00:32:03Z</t>
+          <t>2026-10-10T00:11:25Z</t>
         </is>
       </c>
     </row>
@@ -19504,7 +19504,7 @@
       </c>
       <c r="S223" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09T00:32:03Z</t>
+          <t>2026-10-10T00:11:25Z</t>
         </is>
       </c>
     </row>
@@ -19593,7 +19593,7 @@
       </c>
       <c r="S224" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09T00:32:03Z</t>
+          <t>2026-10-10T00:11:25Z</t>
         </is>
       </c>
     </row>
@@ -19678,7 +19678,7 @@
       </c>
       <c r="S225" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09T00:32:03Z</t>
+          <t>2026-10-10T00:11:25Z</t>
         </is>
       </c>
     </row>
@@ -19767,7 +19767,7 @@
       </c>
       <c r="S226" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09T00:32:03Z</t>
+          <t>2026-10-10T00:11:25Z</t>
         </is>
       </c>
     </row>
@@ -19856,7 +19856,7 @@
       </c>
       <c r="S227" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09T00:32:03Z</t>
+          <t>2026-10-10T00:11:25Z</t>
         </is>
       </c>
     </row>
@@ -19941,7 +19941,7 @@
       </c>
       <c r="S228" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09T00:32:03Z</t>
+          <t>2026-10-10T00:11:25Z</t>
         </is>
       </c>
     </row>
@@ -20030,7 +20030,7 @@
       </c>
       <c r="S229" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09T00:32:03Z</t>
+          <t>2026-10-10T00:11:25Z</t>
         </is>
       </c>
     </row>
@@ -20119,7 +20119,7 @@
       </c>
       <c r="S230" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09T00:32:03Z</t>
+          <t>2026-10-10T00:11:25Z</t>
         </is>
       </c>
     </row>
@@ -20204,7 +20204,7 @@
       </c>
       <c r="S231" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09T00:32:03Z</t>
+          <t>2026-10-10T00:11:25Z</t>
         </is>
       </c>
     </row>
@@ -20293,7 +20293,7 @@
       </c>
       <c r="S232" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09T00:32:03Z</t>
+          <t>2026-10-10T00:11:25Z</t>
         </is>
       </c>
     </row>
@@ -20382,7 +20382,7 @@
       </c>
       <c r="S233" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09T00:32:03Z</t>
+          <t>2026-10-10T00:11:25Z</t>
         </is>
       </c>
     </row>
@@ -20467,7 +20467,7 @@
       </c>
       <c r="S234" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09T00:32:03Z</t>
+          <t>2026-10-10T00:11:25Z</t>
         </is>
       </c>
     </row>
@@ -20556,7 +20556,7 @@
       </c>
       <c r="S235" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09T00:32:03Z</t>
+          <t>2026-10-10T00:11:25Z</t>
         </is>
       </c>
     </row>
@@ -20645,7 +20645,7 @@
       </c>
       <c r="S236" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09T00:32:03Z</t>
+          <t>2026-10-10T00:11:25Z</t>
         </is>
       </c>
     </row>
@@ -20730,7 +20730,7 @@
       </c>
       <c r="S237" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09T00:32:03Z</t>
+          <t>2026-10-10T00:11:25Z</t>
         </is>
       </c>
     </row>
@@ -20819,7 +20819,7 @@
       </c>
       <c r="S238" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09T00:32:03Z</t>
+          <t>2026-10-10T00:11:25Z</t>
         </is>
       </c>
     </row>
@@ -20908,7 +20908,7 @@
       </c>
       <c r="S239" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09T00:32:03Z</t>
+          <t>2026-10-10T00:11:25Z</t>
         </is>
       </c>
     </row>
@@ -20997,7 +20997,7 @@
       </c>
       <c r="S240" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09T00:32:03Z</t>
+          <t>2026-10-10T00:11:25Z</t>
         </is>
       </c>
     </row>
@@ -21086,7 +21086,7 @@
       </c>
       <c r="S241" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09T00:32:03Z</t>
+          <t>2026-10-10T00:11:25Z</t>
         </is>
       </c>
     </row>
@@ -21175,7 +21175,7 @@
       </c>
       <c r="S242" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09T00:32:03Z</t>
+          <t>2026-10-10T00:11:25Z</t>
         </is>
       </c>
     </row>
@@ -21264,7 +21264,7 @@
       </c>
       <c r="S243" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09T00:32:03Z</t>
+          <t>2026-10-10T00:11:25Z</t>
         </is>
       </c>
     </row>
@@ -21353,7 +21353,7 @@
       </c>
       <c r="S244" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09T00:32:03Z</t>
+          <t>2026-10-10T00:11:25Z</t>
         </is>
       </c>
     </row>
@@ -21442,7 +21442,7 @@
       </c>
       <c r="S245" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09T00:32:03Z</t>
+          <t>2026-10-10T00:11:25Z</t>
         </is>
       </c>
     </row>
@@ -21531,7 +21531,7 @@
       </c>
       <c r="S246" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09T00:32:03Z</t>
+          <t>2026-10-10T00:11:25Z</t>
         </is>
       </c>
     </row>
@@ -21620,7 +21620,7 @@
       </c>
       <c r="S247" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09T00:32:03Z</t>
+          <t>2026-10-10T00:11:25Z</t>
         </is>
       </c>
     </row>
@@ -21709,7 +21709,7 @@
       </c>
       <c r="S248" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09T00:32:03Z</t>
+          <t>2026-10-10T00:11:25Z</t>
         </is>
       </c>
     </row>
@@ -21798,7 +21798,7 @@
       </c>
       <c r="S249" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09T00:32:03Z</t>
+          <t>2026-10-10T00:11:25Z</t>
         </is>
       </c>
     </row>
@@ -21887,7 +21887,7 @@
       </c>
       <c r="S250" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09T00:32:03Z</t>
+          <t>2026-10-10T00:11:25Z</t>
         </is>
       </c>
     </row>
@@ -22019,7 +22019,7 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09T00:32:03Z</t>
+          <t>2026-10-10T00:11:25Z</t>
         </is>
       </c>
     </row>
@@ -22099,7 +22099,7 @@
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>{"dataset_id": "bcv_pib_sector_institucional_anual", "title": "Producto interno bruto por sector institucional anual", "table": "Variaciones porcentuales", "source_file": "5_2_1_si_anual.xlsx", "base": "2007", "price_type": "Precios constantes", "measure": "Variación porcentual interanual", "frequency": "Anual", "period": "2025", "year": 2025, "quarter": null, "classification": "Sector institucional", "component": "Impuestos netos sobre los productos", "value": 10.600260421283764, "unit": "Porcentaje", "status": "Preliminar", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/cuentas_macroeconomicas/5_2_1_si_anual.xlsx", "fetched_at": "2026-10-09T00:32:03Z"}</t>
+          <t>{"dataset_id": "bcv_pib_sector_institucional_anual", "title": "Producto interno bruto por sector institucional anual", "table": "Variaciones porcentuales", "source_file": "5_2_1_si_anual.xlsx", "base": "2007", "price_type": "Precios constantes", "measure": "Variación porcentual interanual", "frequency": "Anual", "period": "2025", "year": 2025, "quarter": null, "classification": "Sector institucional", "component": "Impuestos netos sobre los productos", "value": 10.600260421283764, "unit": "Porcentaje", "status": "Preliminar", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/cuentas_macroeconomicas/5_2_1_si_anual.xlsx", "fetched_at": "2026-10-10T00:11:25Z"}</t>
         </is>
       </c>
     </row>

--- a/assets/data/bcv/excel/ove_bcv_pib_sector_institucional_anual.xlsx
+++ b/assets/data/bcv/excel/ove_bcv_pib_sector_institucional_anual.xlsx
@@ -736,7 +736,7 @@
       </c>
       <c r="S7" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:25Z</t>
+          <t>2026-10-10T23:42:25Z</t>
         </is>
       </c>
     </row>
@@ -821,7 +821,7 @@
       </c>
       <c r="S8" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:25Z</t>
+          <t>2026-10-10T23:42:25Z</t>
         </is>
       </c>
     </row>
@@ -906,7 +906,7 @@
       </c>
       <c r="S9" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:25Z</t>
+          <t>2026-10-10T23:42:25Z</t>
         </is>
       </c>
     </row>
@@ -991,7 +991,7 @@
       </c>
       <c r="S10" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:25Z</t>
+          <t>2026-10-10T23:42:25Z</t>
         </is>
       </c>
     </row>
@@ -1076,7 +1076,7 @@
       </c>
       <c r="S11" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:25Z</t>
+          <t>2026-10-10T23:42:25Z</t>
         </is>
       </c>
     </row>
@@ -1161,7 +1161,7 @@
       </c>
       <c r="S12" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:25Z</t>
+          <t>2026-10-10T23:42:25Z</t>
         </is>
       </c>
     </row>
@@ -1246,7 +1246,7 @@
       </c>
       <c r="S13" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:25Z</t>
+          <t>2026-10-10T23:42:25Z</t>
         </is>
       </c>
     </row>
@@ -1331,7 +1331,7 @@
       </c>
       <c r="S14" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:25Z</t>
+          <t>2026-10-10T23:42:25Z</t>
         </is>
       </c>
     </row>
@@ -1416,7 +1416,7 @@
       </c>
       <c r="S15" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:25Z</t>
+          <t>2026-10-10T23:42:25Z</t>
         </is>
       </c>
     </row>
@@ -1501,7 +1501,7 @@
       </c>
       <c r="S16" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:25Z</t>
+          <t>2026-10-10T23:42:25Z</t>
         </is>
       </c>
     </row>
@@ -1586,7 +1586,7 @@
       </c>
       <c r="S17" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:25Z</t>
+          <t>2026-10-10T23:42:25Z</t>
         </is>
       </c>
     </row>
@@ -1671,7 +1671,7 @@
       </c>
       <c r="S18" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:25Z</t>
+          <t>2026-10-10T23:42:25Z</t>
         </is>
       </c>
     </row>
@@ -1756,7 +1756,7 @@
       </c>
       <c r="S19" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:25Z</t>
+          <t>2026-10-10T23:42:25Z</t>
         </is>
       </c>
     </row>
@@ -1841,7 +1841,7 @@
       </c>
       <c r="S20" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:25Z</t>
+          <t>2026-10-10T23:42:25Z</t>
         </is>
       </c>
     </row>
@@ -1926,7 +1926,7 @@
       </c>
       <c r="S21" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:25Z</t>
+          <t>2026-10-10T23:42:25Z</t>
         </is>
       </c>
     </row>
@@ -2011,7 +2011,7 @@
       </c>
       <c r="S22" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:25Z</t>
+          <t>2026-10-10T23:42:25Z</t>
         </is>
       </c>
     </row>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="S23" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:25Z</t>
+          <t>2026-10-10T23:42:25Z</t>
         </is>
       </c>
     </row>
@@ -2181,7 +2181,7 @@
       </c>
       <c r="S24" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:25Z</t>
+          <t>2026-10-10T23:42:25Z</t>
         </is>
       </c>
     </row>
@@ -2266,7 +2266,7 @@
       </c>
       <c r="S25" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:25Z</t>
+          <t>2026-10-10T23:42:25Z</t>
         </is>
       </c>
     </row>
@@ -2351,7 +2351,7 @@
       </c>
       <c r="S26" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:25Z</t>
+          <t>2026-10-10T23:42:25Z</t>
         </is>
       </c>
     </row>
@@ -2436,7 +2436,7 @@
       </c>
       <c r="S27" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:25Z</t>
+          <t>2026-10-10T23:42:25Z</t>
         </is>
       </c>
     </row>
@@ -2525,7 +2525,7 @@
       </c>
       <c r="S28" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:25Z</t>
+          <t>2026-10-10T23:42:25Z</t>
         </is>
       </c>
     </row>
@@ -2614,7 +2614,7 @@
       </c>
       <c r="S29" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:25Z</t>
+          <t>2026-10-10T23:42:25Z</t>
         </is>
       </c>
     </row>
@@ -2699,7 +2699,7 @@
       </c>
       <c r="S30" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:25Z</t>
+          <t>2026-10-10T23:42:25Z</t>
         </is>
       </c>
     </row>
@@ -2788,7 +2788,7 @@
       </c>
       <c r="S31" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:25Z</t>
+          <t>2026-10-10T23:42:25Z</t>
         </is>
       </c>
     </row>
@@ -2877,7 +2877,7 @@
       </c>
       <c r="S32" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:25Z</t>
+          <t>2026-10-10T23:42:25Z</t>
         </is>
       </c>
     </row>
@@ -2962,7 +2962,7 @@
       </c>
       <c r="S33" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:25Z</t>
+          <t>2026-10-10T23:42:25Z</t>
         </is>
       </c>
     </row>
@@ -3051,7 +3051,7 @@
       </c>
       <c r="S34" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:25Z</t>
+          <t>2026-10-10T23:42:25Z</t>
         </is>
       </c>
     </row>
@@ -3140,7 +3140,7 @@
       </c>
       <c r="S35" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:25Z</t>
+          <t>2026-10-10T23:42:25Z</t>
         </is>
       </c>
     </row>
@@ -3225,7 +3225,7 @@
       </c>
       <c r="S36" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:25Z</t>
+          <t>2026-10-10T23:42:25Z</t>
         </is>
       </c>
     </row>
@@ -3314,7 +3314,7 @@
       </c>
       <c r="S37" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:25Z</t>
+          <t>2026-10-10T23:42:25Z</t>
         </is>
       </c>
     </row>
@@ -3403,7 +3403,7 @@
       </c>
       <c r="S38" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:25Z</t>
+          <t>2026-10-10T23:42:25Z</t>
         </is>
       </c>
     </row>
@@ -3488,7 +3488,7 @@
       </c>
       <c r="S39" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:25Z</t>
+          <t>2026-10-10T23:42:25Z</t>
         </is>
       </c>
     </row>
@@ -3577,7 +3577,7 @@
       </c>
       <c r="S40" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:25Z</t>
+          <t>2026-10-10T23:42:25Z</t>
         </is>
       </c>
     </row>
@@ -3666,7 +3666,7 @@
       </c>
       <c r="S41" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:25Z</t>
+          <t>2026-10-10T23:42:25Z</t>
         </is>
       </c>
     </row>
@@ -3751,7 +3751,7 @@
       </c>
       <c r="S42" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:25Z</t>
+          <t>2026-10-10T23:42:25Z</t>
         </is>
       </c>
     </row>
@@ -3840,7 +3840,7 @@
       </c>
       <c r="S43" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:25Z</t>
+          <t>2026-10-10T23:42:25Z</t>
         </is>
       </c>
     </row>
@@ -3929,7 +3929,7 @@
       </c>
       <c r="S44" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:25Z</t>
+          <t>2026-10-10T23:42:25Z</t>
         </is>
       </c>
     </row>
@@ -4014,7 +4014,7 @@
       </c>
       <c r="S45" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:25Z</t>
+          <t>2026-10-10T23:42:25Z</t>
         </is>
       </c>
     </row>
@@ -4103,7 +4103,7 @@
       </c>
       <c r="S46" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:25Z</t>
+          <t>2026-10-10T23:42:25Z</t>
         </is>
       </c>
     </row>
@@ -4192,7 +4192,7 @@
       </c>
       <c r="S47" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:25Z</t>
+          <t>2026-10-10T23:42:25Z</t>
         </is>
       </c>
     </row>
@@ -4277,7 +4277,7 @@
       </c>
       <c r="S48" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:25Z</t>
+          <t>2026-10-10T23:42:25Z</t>
         </is>
       </c>
     </row>
@@ -4366,7 +4366,7 @@
       </c>
       <c r="S49" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:25Z</t>
+          <t>2026-10-10T23:42:25Z</t>
         </is>
       </c>
     </row>
@@ -4455,7 +4455,7 @@
       </c>
       <c r="S50" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:25Z</t>
+          <t>2026-10-10T23:42:25Z</t>
         </is>
       </c>
     </row>
@@ -4540,7 +4540,7 @@
       </c>
       <c r="S51" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:25Z</t>
+          <t>2026-10-10T23:42:25Z</t>
         </is>
       </c>
     </row>
@@ -4629,7 +4629,7 @@
       </c>
       <c r="S52" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:25Z</t>
+          <t>2026-10-10T23:42:25Z</t>
         </is>
       </c>
     </row>
@@ -4718,7 +4718,7 @@
       </c>
       <c r="S53" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:25Z</t>
+          <t>2026-10-10T23:42:25Z</t>
         </is>
       </c>
     </row>
@@ -4803,7 +4803,7 @@
       </c>
       <c r="S54" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:25Z</t>
+          <t>2026-10-10T23:42:25Z</t>
         </is>
       </c>
     </row>
@@ -4892,7 +4892,7 @@
       </c>
       <c r="S55" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:25Z</t>
+          <t>2026-10-10T23:42:25Z</t>
         </is>
       </c>
     </row>
@@ -4981,7 +4981,7 @@
       </c>
       <c r="S56" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:25Z</t>
+          <t>2026-10-10T23:42:25Z</t>
         </is>
       </c>
     </row>
@@ -5070,7 +5070,7 @@
       </c>
       <c r="S57" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:25Z</t>
+          <t>2026-10-10T23:42:25Z</t>
         </is>
       </c>
     </row>
@@ -5159,7 +5159,7 @@
       </c>
       <c r="S58" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:25Z</t>
+          <t>2026-10-10T23:42:25Z</t>
         </is>
       </c>
     </row>
@@ -5248,7 +5248,7 @@
       </c>
       <c r="S59" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:25Z</t>
+          <t>2026-10-10T23:42:25Z</t>
         </is>
       </c>
     </row>
@@ -5337,7 +5337,7 @@
       </c>
       <c r="S60" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:25Z</t>
+          <t>2026-10-10T23:42:25Z</t>
         </is>
       </c>
     </row>
@@ -5426,7 +5426,7 @@
       </c>
       <c r="S61" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:25Z</t>
+          <t>2026-10-10T23:42:25Z</t>
         </is>
       </c>
     </row>
@@ -5515,7 +5515,7 @@
       </c>
       <c r="S62" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:25Z</t>
+          <t>2026-10-10T23:42:25Z</t>
         </is>
       </c>
     </row>
@@ -5604,7 +5604,7 @@
       </c>
       <c r="S63" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:25Z</t>
+          <t>2026-10-10T23:42:25Z</t>
         </is>
       </c>
     </row>
@@ -5693,7 +5693,7 @@
       </c>
       <c r="S64" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:25Z</t>
+          <t>2026-10-10T23:42:25Z</t>
         </is>
       </c>
     </row>
@@ -5782,7 +5782,7 @@
       </c>
       <c r="S65" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:25Z</t>
+          <t>2026-10-10T23:42:25Z</t>
         </is>
       </c>
     </row>
@@ -5871,7 +5871,7 @@
       </c>
       <c r="S66" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:25Z</t>
+          <t>2026-10-10T23:42:25Z</t>
         </is>
       </c>
     </row>
@@ -5960,7 +5960,7 @@
       </c>
       <c r="S67" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:25Z</t>
+          <t>2026-10-10T23:42:25Z</t>
         </is>
       </c>
     </row>
@@ -6045,7 +6045,7 @@
       </c>
       <c r="S68" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:25Z</t>
+          <t>2026-10-10T23:42:25Z</t>
         </is>
       </c>
     </row>
@@ -6130,7 +6130,7 @@
       </c>
       <c r="S69" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:25Z</t>
+          <t>2026-10-10T23:42:25Z</t>
         </is>
       </c>
     </row>
@@ -6215,7 +6215,7 @@
       </c>
       <c r="S70" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:25Z</t>
+          <t>2026-10-10T23:42:25Z</t>
         </is>
       </c>
     </row>
@@ -6300,7 +6300,7 @@
       </c>
       <c r="S71" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:25Z</t>
+          <t>2026-10-10T23:42:25Z</t>
         </is>
       </c>
     </row>
@@ -6385,7 +6385,7 @@
       </c>
       <c r="S72" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:25Z</t>
+          <t>2026-10-10T23:42:25Z</t>
         </is>
       </c>
     </row>
@@ -6470,7 +6470,7 @@
       </c>
       <c r="S73" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:25Z</t>
+          <t>2026-10-10T23:42:25Z</t>
         </is>
       </c>
     </row>
@@ -6555,7 +6555,7 @@
       </c>
       <c r="S74" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:25Z</t>
+          <t>2026-10-10T23:42:25Z</t>
         </is>
       </c>
     </row>
@@ -6640,7 +6640,7 @@
       </c>
       <c r="S75" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:25Z</t>
+          <t>2026-10-10T23:42:25Z</t>
         </is>
       </c>
     </row>
@@ -6725,7 +6725,7 @@
       </c>
       <c r="S76" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:25Z</t>
+          <t>2026-10-10T23:42:25Z</t>
         </is>
       </c>
     </row>
@@ -6810,7 +6810,7 @@
       </c>
       <c r="S77" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:25Z</t>
+          <t>2026-10-10T23:42:25Z</t>
         </is>
       </c>
     </row>
@@ -6895,7 +6895,7 @@
       </c>
       <c r="S78" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:25Z</t>
+          <t>2026-10-10T23:42:25Z</t>
         </is>
       </c>
     </row>
@@ -6980,7 +6980,7 @@
       </c>
       <c r="S79" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:25Z</t>
+          <t>2026-10-10T23:42:25Z</t>
         </is>
       </c>
     </row>
@@ -7065,7 +7065,7 @@
       </c>
       <c r="S80" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:25Z</t>
+          <t>2026-10-10T23:42:25Z</t>
         </is>
       </c>
     </row>
@@ -7150,7 +7150,7 @@
       </c>
       <c r="S81" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:25Z</t>
+          <t>2026-10-10T23:42:25Z</t>
         </is>
       </c>
     </row>
@@ -7235,7 +7235,7 @@
       </c>
       <c r="S82" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:25Z</t>
+          <t>2026-10-10T23:42:25Z</t>
         </is>
       </c>
     </row>
@@ -7320,7 +7320,7 @@
       </c>
       <c r="S83" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:25Z</t>
+          <t>2026-10-10T23:42:25Z</t>
         </is>
       </c>
     </row>
@@ -7405,7 +7405,7 @@
       </c>
       <c r="S84" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:25Z</t>
+          <t>2026-10-10T23:42:25Z</t>
         </is>
       </c>
     </row>
@@ -7490,7 +7490,7 @@
       </c>
       <c r="S85" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:25Z</t>
+          <t>2026-10-10T23:42:25Z</t>
         </is>
       </c>
     </row>
@@ -7575,7 +7575,7 @@
       </c>
       <c r="S86" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:25Z</t>
+          <t>2026-10-10T23:42:25Z</t>
         </is>
       </c>
     </row>
@@ -7660,7 +7660,7 @@
       </c>
       <c r="S87" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:25Z</t>
+          <t>2026-10-10T23:42:25Z</t>
         </is>
       </c>
     </row>
@@ -7745,7 +7745,7 @@
       </c>
       <c r="S88" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:25Z</t>
+          <t>2026-10-10T23:42:25Z</t>
         </is>
       </c>
     </row>
@@ -7834,7 +7834,7 @@
       </c>
       <c r="S89" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:25Z</t>
+          <t>2026-10-10T23:42:25Z</t>
         </is>
       </c>
     </row>
@@ -7923,7 +7923,7 @@
       </c>
       <c r="S90" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:25Z</t>
+          <t>2026-10-10T23:42:25Z</t>
         </is>
       </c>
     </row>
@@ -8008,7 +8008,7 @@
       </c>
       <c r="S91" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:25Z</t>
+          <t>2026-10-10T23:42:25Z</t>
         </is>
       </c>
     </row>
@@ -8097,7 +8097,7 @@
       </c>
       <c r="S92" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:25Z</t>
+          <t>2026-10-10T23:42:25Z</t>
         </is>
       </c>
     </row>
@@ -8186,7 +8186,7 @@
       </c>
       <c r="S93" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:25Z</t>
+          <t>2026-10-10T23:42:25Z</t>
         </is>
       </c>
     </row>
@@ -8271,7 +8271,7 @@
       </c>
       <c r="S94" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:25Z</t>
+          <t>2026-10-10T23:42:25Z</t>
         </is>
       </c>
     </row>
@@ -8360,7 +8360,7 @@
       </c>
       <c r="S95" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:25Z</t>
+          <t>2026-10-10T23:42:25Z</t>
         </is>
       </c>
     </row>
@@ -8449,7 +8449,7 @@
       </c>
       <c r="S96" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:25Z</t>
+          <t>2026-10-10T23:42:25Z</t>
         </is>
       </c>
     </row>
@@ -8534,7 +8534,7 @@
       </c>
       <c r="S97" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:25Z</t>
+          <t>2026-10-10T23:42:25Z</t>
         </is>
       </c>
     </row>
@@ -8623,7 +8623,7 @@
       </c>
       <c r="S98" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:25Z</t>
+          <t>2026-10-10T23:42:25Z</t>
         </is>
       </c>
     </row>
@@ -8712,7 +8712,7 @@
       </c>
       <c r="S99" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:25Z</t>
+          <t>2026-10-10T23:42:25Z</t>
         </is>
       </c>
     </row>
@@ -8797,7 +8797,7 @@
       </c>
       <c r="S100" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:25Z</t>
+          <t>2026-10-10T23:42:25Z</t>
         </is>
       </c>
     </row>
@@ -8886,7 +8886,7 @@
       </c>
       <c r="S101" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:25Z</t>
+          <t>2026-10-10T23:42:25Z</t>
         </is>
       </c>
     </row>
@@ -8975,7 +8975,7 @@
       </c>
       <c r="S102" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:25Z</t>
+          <t>2026-10-10T23:42:25Z</t>
         </is>
       </c>
     </row>
@@ -9060,7 +9060,7 @@
       </c>
       <c r="S103" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:25Z</t>
+          <t>2026-10-10T23:42:25Z</t>
         </is>
       </c>
     </row>
@@ -9149,7 +9149,7 @@
       </c>
       <c r="S104" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:25Z</t>
+          <t>2026-10-10T23:42:25Z</t>
         </is>
       </c>
     </row>
@@ -9238,7 +9238,7 @@
       </c>
       <c r="S105" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:25Z</t>
+          <t>2026-10-10T23:42:25Z</t>
         </is>
       </c>
     </row>
@@ -9323,7 +9323,7 @@
       </c>
       <c r="S106" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:25Z</t>
+          <t>2026-10-10T23:42:25Z</t>
         </is>
       </c>
     </row>
@@ -9412,7 +9412,7 @@
       </c>
       <c r="S107" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:25Z</t>
+          <t>2026-10-10T23:42:25Z</t>
         </is>
       </c>
     </row>
@@ -9501,7 +9501,7 @@
       </c>
       <c r="S108" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:25Z</t>
+          <t>2026-10-10T23:42:25Z</t>
         </is>
       </c>
     </row>
@@ -9586,7 +9586,7 @@
       </c>
       <c r="S109" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:25Z</t>
+          <t>2026-10-10T23:42:25Z</t>
         </is>
       </c>
     </row>
@@ -9675,7 +9675,7 @@
       </c>
       <c r="S110" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:25Z</t>
+          <t>2026-10-10T23:42:25Z</t>
         </is>
       </c>
     </row>
@@ -9764,7 +9764,7 @@
       </c>
       <c r="S111" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:25Z</t>
+          <t>2026-10-10T23:42:25Z</t>
         </is>
       </c>
     </row>
@@ -9849,7 +9849,7 @@
       </c>
       <c r="S112" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:25Z</t>
+          <t>2026-10-10T23:42:25Z</t>
         </is>
       </c>
     </row>
@@ -9938,7 +9938,7 @@
       </c>
       <c r="S113" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:25Z</t>
+          <t>2026-10-10T23:42:25Z</t>
         </is>
       </c>
     </row>
@@ -10027,7 +10027,7 @@
       </c>
       <c r="S114" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:25Z</t>
+          <t>2026-10-10T23:42:25Z</t>
         </is>
       </c>
     </row>
@@ -10112,7 +10112,7 @@
       </c>
       <c r="S115" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:25Z</t>
+          <t>2026-10-10T23:42:25Z</t>
         </is>
       </c>
     </row>
@@ -10201,7 +10201,7 @@
       </c>
       <c r="S116" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:25Z</t>
+          <t>2026-10-10T23:42:25Z</t>
         </is>
       </c>
     </row>
@@ -10290,7 +10290,7 @@
       </c>
       <c r="S117" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:25Z</t>
+          <t>2026-10-10T23:42:25Z</t>
         </is>
       </c>
     </row>
@@ -10379,7 +10379,7 @@
       </c>
       <c r="S118" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:25Z</t>
+          <t>2026-10-10T23:42:25Z</t>
         </is>
       </c>
     </row>
@@ -10468,7 +10468,7 @@
       </c>
       <c r="S119" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:25Z</t>
+          <t>2026-10-10T23:42:25Z</t>
         </is>
       </c>
     </row>
@@ -10557,7 +10557,7 @@
       </c>
       <c r="S120" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:25Z</t>
+          <t>2026-10-10T23:42:25Z</t>
         </is>
       </c>
     </row>
@@ -10646,7 +10646,7 @@
       </c>
       <c r="S121" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:25Z</t>
+          <t>2026-10-10T23:42:25Z</t>
         </is>
       </c>
     </row>
@@ -10735,7 +10735,7 @@
       </c>
       <c r="S122" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:25Z</t>
+          <t>2026-10-10T23:42:25Z</t>
         </is>
       </c>
     </row>
@@ -10824,7 +10824,7 @@
       </c>
       <c r="S123" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:25Z</t>
+          <t>2026-10-10T23:42:25Z</t>
         </is>
       </c>
     </row>
@@ -10913,7 +10913,7 @@
       </c>
       <c r="S124" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:25Z</t>
+          <t>2026-10-10T23:42:25Z</t>
         </is>
       </c>
     </row>
@@ -11002,7 +11002,7 @@
       </c>
       <c r="S125" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:25Z</t>
+          <t>2026-10-10T23:42:25Z</t>
         </is>
       </c>
     </row>
@@ -11091,7 +11091,7 @@
       </c>
       <c r="S126" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:25Z</t>
+          <t>2026-10-10T23:42:25Z</t>
         </is>
       </c>
     </row>
@@ -11180,7 +11180,7 @@
       </c>
       <c r="S127" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:25Z</t>
+          <t>2026-10-10T23:42:25Z</t>
         </is>
       </c>
     </row>
@@ -11269,7 +11269,7 @@
       </c>
       <c r="S128" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:25Z</t>
+          <t>2026-10-10T23:42:25Z</t>
         </is>
       </c>
     </row>
@@ -11354,7 +11354,7 @@
       </c>
       <c r="S129" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:25Z</t>
+          <t>2026-10-10T23:42:25Z</t>
         </is>
       </c>
     </row>
@@ -11439,7 +11439,7 @@
       </c>
       <c r="S130" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:25Z</t>
+          <t>2026-10-10T23:42:25Z</t>
         </is>
       </c>
     </row>
@@ -11524,7 +11524,7 @@
       </c>
       <c r="S131" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:25Z</t>
+          <t>2026-10-10T23:42:25Z</t>
         </is>
       </c>
     </row>
@@ -11609,7 +11609,7 @@
       </c>
       <c r="S132" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:25Z</t>
+          <t>2026-10-10T23:42:25Z</t>
         </is>
       </c>
     </row>
@@ -11694,7 +11694,7 @@
       </c>
       <c r="S133" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:25Z</t>
+          <t>2026-10-10T23:42:25Z</t>
         </is>
       </c>
     </row>
@@ -11779,7 +11779,7 @@
       </c>
       <c r="S134" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:25Z</t>
+          <t>2026-10-10T23:42:25Z</t>
         </is>
       </c>
     </row>
@@ -11864,7 +11864,7 @@
       </c>
       <c r="S135" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:25Z</t>
+          <t>2026-10-10T23:42:25Z</t>
         </is>
       </c>
     </row>
@@ -11949,7 +11949,7 @@
       </c>
       <c r="S136" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:25Z</t>
+          <t>2026-10-10T23:42:25Z</t>
         </is>
       </c>
     </row>
@@ -12034,7 +12034,7 @@
       </c>
       <c r="S137" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:25Z</t>
+          <t>2026-10-10T23:42:25Z</t>
         </is>
       </c>
     </row>
@@ -12119,7 +12119,7 @@
       </c>
       <c r="S138" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:25Z</t>
+          <t>2026-10-10T23:42:25Z</t>
         </is>
       </c>
     </row>
@@ -12204,7 +12204,7 @@
       </c>
       <c r="S139" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:25Z</t>
+          <t>2026-10-10T23:42:25Z</t>
         </is>
       </c>
     </row>
@@ -12289,7 +12289,7 @@
       </c>
       <c r="S140" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:25Z</t>
+          <t>2026-10-10T23:42:25Z</t>
         </is>
       </c>
     </row>
@@ -12374,7 +12374,7 @@
       </c>
       <c r="S141" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:25Z</t>
+          <t>2026-10-10T23:42:25Z</t>
         </is>
       </c>
     </row>
@@ -12459,7 +12459,7 @@
       </c>
       <c r="S142" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:25Z</t>
+          <t>2026-10-10T23:42:25Z</t>
         </is>
       </c>
     </row>
@@ -12544,7 +12544,7 @@
       </c>
       <c r="S143" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:25Z</t>
+          <t>2026-10-10T23:42:25Z</t>
         </is>
       </c>
     </row>
@@ -12629,7 +12629,7 @@
       </c>
       <c r="S144" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:25Z</t>
+          <t>2026-10-10T23:42:25Z</t>
         </is>
       </c>
     </row>
@@ -12714,7 +12714,7 @@
       </c>
       <c r="S145" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:25Z</t>
+          <t>2026-10-10T23:42:25Z</t>
         </is>
       </c>
     </row>
@@ -12799,7 +12799,7 @@
       </c>
       <c r="S146" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:25Z</t>
+          <t>2026-10-10T23:42:25Z</t>
         </is>
       </c>
     </row>
@@ -12884,7 +12884,7 @@
       </c>
       <c r="S147" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:25Z</t>
+          <t>2026-10-10T23:42:25Z</t>
         </is>
       </c>
     </row>
@@ -12969,7 +12969,7 @@
       </c>
       <c r="S148" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:25Z</t>
+          <t>2026-10-10T23:42:25Z</t>
         </is>
       </c>
     </row>
@@ -13054,7 +13054,7 @@
       </c>
       <c r="S149" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:25Z</t>
+          <t>2026-10-10T23:42:25Z</t>
         </is>
       </c>
     </row>
@@ -13143,7 +13143,7 @@
       </c>
       <c r="S150" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:25Z</t>
+          <t>2026-10-10T23:42:25Z</t>
         </is>
       </c>
     </row>
@@ -13232,7 +13232,7 @@
       </c>
       <c r="S151" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:25Z</t>
+          <t>2026-10-10T23:42:25Z</t>
         </is>
       </c>
     </row>
@@ -13317,7 +13317,7 @@
       </c>
       <c r="S152" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:25Z</t>
+          <t>2026-10-10T23:42:25Z</t>
         </is>
       </c>
     </row>
@@ -13406,7 +13406,7 @@
       </c>
       <c r="S153" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:25Z</t>
+          <t>2026-10-10T23:42:25Z</t>
         </is>
       </c>
     </row>
@@ -13495,7 +13495,7 @@
       </c>
       <c r="S154" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:25Z</t>
+          <t>2026-10-10T23:42:25Z</t>
         </is>
       </c>
     </row>
@@ -13580,7 +13580,7 @@
       </c>
       <c r="S155" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:25Z</t>
+          <t>2026-10-10T23:42:25Z</t>
         </is>
       </c>
     </row>
@@ -13669,7 +13669,7 @@
       </c>
       <c r="S156" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:25Z</t>
+          <t>2026-10-10T23:42:25Z</t>
         </is>
       </c>
     </row>
@@ -13758,7 +13758,7 @@
       </c>
       <c r="S157" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:25Z</t>
+          <t>2026-10-10T23:42:25Z</t>
         </is>
       </c>
     </row>
@@ -13843,7 +13843,7 @@
       </c>
       <c r="S158" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:25Z</t>
+          <t>2026-10-10T23:42:25Z</t>
         </is>
       </c>
     </row>
@@ -13932,7 +13932,7 @@
       </c>
       <c r="S159" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:25Z</t>
+          <t>2026-10-10T23:42:25Z</t>
         </is>
       </c>
     </row>
@@ -14021,7 +14021,7 @@
       </c>
       <c r="S160" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:25Z</t>
+          <t>2026-10-10T23:42:25Z</t>
         </is>
       </c>
     </row>
@@ -14106,7 +14106,7 @@
       </c>
       <c r="S161" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:25Z</t>
+          <t>2026-10-10T23:42:25Z</t>
         </is>
       </c>
     </row>
@@ -14195,7 +14195,7 @@
       </c>
       <c r="S162" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:25Z</t>
+          <t>2026-10-10T23:42:25Z</t>
         </is>
       </c>
     </row>
@@ -14284,7 +14284,7 @@
       </c>
       <c r="S163" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:25Z</t>
+          <t>2026-10-10T23:42:25Z</t>
         </is>
       </c>
     </row>
@@ -14369,7 +14369,7 @@
       </c>
       <c r="S164" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:25Z</t>
+          <t>2026-10-10T23:42:25Z</t>
         </is>
       </c>
     </row>
@@ -14458,7 +14458,7 @@
       </c>
       <c r="S165" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:25Z</t>
+          <t>2026-10-10T23:42:25Z</t>
         </is>
       </c>
     </row>
@@ -14547,7 +14547,7 @@
       </c>
       <c r="S166" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:25Z</t>
+          <t>2026-10-10T23:42:25Z</t>
         </is>
       </c>
     </row>
@@ -14632,7 +14632,7 @@
       </c>
       <c r="S167" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:25Z</t>
+          <t>2026-10-10T23:42:25Z</t>
         </is>
       </c>
     </row>
@@ -14721,7 +14721,7 @@
       </c>
       <c r="S168" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:25Z</t>
+          <t>2026-10-10T23:42:25Z</t>
         </is>
       </c>
     </row>
@@ -14810,7 +14810,7 @@
       </c>
       <c r="S169" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:25Z</t>
+          <t>2026-10-10T23:42:25Z</t>
         </is>
       </c>
     </row>
@@ -14895,7 +14895,7 @@
       </c>
       <c r="S170" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:25Z</t>
+          <t>2026-10-10T23:42:25Z</t>
         </is>
       </c>
     </row>
@@ -14984,7 +14984,7 @@
       </c>
       <c r="S171" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:25Z</t>
+          <t>2026-10-10T23:42:25Z</t>
         </is>
       </c>
     </row>
@@ -15073,7 +15073,7 @@
       </c>
       <c r="S172" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:25Z</t>
+          <t>2026-10-10T23:42:25Z</t>
         </is>
       </c>
     </row>
@@ -15158,7 +15158,7 @@
       </c>
       <c r="S173" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:25Z</t>
+          <t>2026-10-10T23:42:25Z</t>
         </is>
       </c>
     </row>
@@ -15247,7 +15247,7 @@
       </c>
       <c r="S174" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:25Z</t>
+          <t>2026-10-10T23:42:25Z</t>
         </is>
       </c>
     </row>
@@ -15336,7 +15336,7 @@
       </c>
       <c r="S175" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:25Z</t>
+          <t>2026-10-10T23:42:25Z</t>
         </is>
       </c>
     </row>
@@ -15421,7 +15421,7 @@
       </c>
       <c r="S176" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:25Z</t>
+          <t>2026-10-10T23:42:25Z</t>
         </is>
       </c>
     </row>
@@ -15510,7 +15510,7 @@
       </c>
       <c r="S177" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:25Z</t>
+          <t>2026-10-10T23:42:25Z</t>
         </is>
       </c>
     </row>
@@ -15599,7 +15599,7 @@
       </c>
       <c r="S178" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:25Z</t>
+          <t>2026-10-10T23:42:25Z</t>
         </is>
       </c>
     </row>
@@ -15688,7 +15688,7 @@
       </c>
       <c r="S179" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:25Z</t>
+          <t>2026-10-10T23:42:25Z</t>
         </is>
       </c>
     </row>
@@ -15777,7 +15777,7 @@
       </c>
       <c r="S180" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:25Z</t>
+          <t>2026-10-10T23:42:25Z</t>
         </is>
       </c>
     </row>
@@ -15866,7 +15866,7 @@
       </c>
       <c r="S181" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:25Z</t>
+          <t>2026-10-10T23:42:25Z</t>
         </is>
       </c>
     </row>
@@ -15955,7 +15955,7 @@
       </c>
       <c r="S182" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:25Z</t>
+          <t>2026-10-10T23:42:25Z</t>
         </is>
       </c>
     </row>
@@ -16044,7 +16044,7 @@
       </c>
       <c r="S183" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:25Z</t>
+          <t>2026-10-10T23:42:25Z</t>
         </is>
       </c>
     </row>
@@ -16133,7 +16133,7 @@
       </c>
       <c r="S184" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:25Z</t>
+          <t>2026-10-10T23:42:25Z</t>
         </is>
       </c>
     </row>
@@ -16222,7 +16222,7 @@
       </c>
       <c r="S185" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:25Z</t>
+          <t>2026-10-10T23:42:25Z</t>
         </is>
       </c>
     </row>
@@ -16311,7 +16311,7 @@
       </c>
       <c r="S186" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:25Z</t>
+          <t>2026-10-10T23:42:25Z</t>
         </is>
       </c>
     </row>
@@ -16400,7 +16400,7 @@
       </c>
       <c r="S187" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:25Z</t>
+          <t>2026-10-10T23:42:25Z</t>
         </is>
       </c>
     </row>
@@ -16489,7 +16489,7 @@
       </c>
       <c r="S188" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:25Z</t>
+          <t>2026-10-10T23:42:25Z</t>
         </is>
       </c>
     </row>
@@ -16578,7 +16578,7 @@
       </c>
       <c r="S189" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:25Z</t>
+          <t>2026-10-10T23:42:25Z</t>
         </is>
       </c>
     </row>
@@ -16663,7 +16663,7 @@
       </c>
       <c r="S190" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:25Z</t>
+          <t>2026-10-10T23:42:25Z</t>
         </is>
       </c>
     </row>
@@ -16748,7 +16748,7 @@
       </c>
       <c r="S191" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:25Z</t>
+          <t>2026-10-10T23:42:25Z</t>
         </is>
       </c>
     </row>
@@ -16833,7 +16833,7 @@
       </c>
       <c r="S192" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:25Z</t>
+          <t>2026-10-10T23:42:25Z</t>
         </is>
       </c>
     </row>
@@ -16918,7 +16918,7 @@
       </c>
       <c r="S193" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:25Z</t>
+          <t>2026-10-10T23:42:25Z</t>
         </is>
       </c>
     </row>
@@ -17003,7 +17003,7 @@
       </c>
       <c r="S194" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:25Z</t>
+          <t>2026-10-10T23:42:25Z</t>
         </is>
       </c>
     </row>
@@ -17088,7 +17088,7 @@
       </c>
       <c r="S195" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:25Z</t>
+          <t>2026-10-10T23:42:25Z</t>
         </is>
       </c>
     </row>
@@ -17173,7 +17173,7 @@
       </c>
       <c r="S196" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:25Z</t>
+          <t>2026-10-10T23:42:25Z</t>
         </is>
       </c>
     </row>
@@ -17258,7 +17258,7 @@
       </c>
       <c r="S197" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:25Z</t>
+          <t>2026-10-10T23:42:25Z</t>
         </is>
       </c>
     </row>
@@ -17343,7 +17343,7 @@
       </c>
       <c r="S198" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:25Z</t>
+          <t>2026-10-10T23:42:25Z</t>
         </is>
       </c>
     </row>
@@ -17428,7 +17428,7 @@
       </c>
       <c r="S199" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:25Z</t>
+          <t>2026-10-10T23:42:25Z</t>
         </is>
       </c>
     </row>
@@ -17513,7 +17513,7 @@
       </c>
       <c r="S200" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:25Z</t>
+          <t>2026-10-10T23:42:25Z</t>
         </is>
       </c>
     </row>
@@ -17598,7 +17598,7 @@
       </c>
       <c r="S201" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:25Z</t>
+          <t>2026-10-10T23:42:25Z</t>
         </is>
       </c>
     </row>
@@ -17683,7 +17683,7 @@
       </c>
       <c r="S202" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:25Z</t>
+          <t>2026-10-10T23:42:25Z</t>
         </is>
       </c>
     </row>
@@ -17768,7 +17768,7 @@
       </c>
       <c r="S203" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:25Z</t>
+          <t>2026-10-10T23:42:25Z</t>
         </is>
       </c>
     </row>
@@ -17853,7 +17853,7 @@
       </c>
       <c r="S204" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:25Z</t>
+          <t>2026-10-10T23:42:25Z</t>
         </is>
       </c>
     </row>
@@ -17938,7 +17938,7 @@
       </c>
       <c r="S205" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:25Z</t>
+          <t>2026-10-10T23:42:25Z</t>
         </is>
       </c>
     </row>
@@ -18023,7 +18023,7 @@
       </c>
       <c r="S206" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:25Z</t>
+          <t>2026-10-10T23:42:25Z</t>
         </is>
       </c>
     </row>
@@ -18108,7 +18108,7 @@
       </c>
       <c r="S207" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:25Z</t>
+          <t>2026-10-10T23:42:25Z</t>
         </is>
       </c>
     </row>
@@ -18193,7 +18193,7 @@
       </c>
       <c r="S208" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:25Z</t>
+          <t>2026-10-10T23:42:25Z</t>
         </is>
       </c>
     </row>
@@ -18278,7 +18278,7 @@
       </c>
       <c r="S209" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:25Z</t>
+          <t>2026-10-10T23:42:25Z</t>
         </is>
       </c>
     </row>
@@ -18363,7 +18363,7 @@
       </c>
       <c r="S210" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:25Z</t>
+          <t>2026-10-10T23:42:25Z</t>
         </is>
       </c>
     </row>
@@ -18452,7 +18452,7 @@
       </c>
       <c r="S211" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:25Z</t>
+          <t>2026-10-10T23:42:25Z</t>
         </is>
       </c>
     </row>
@@ -18541,7 +18541,7 @@
       </c>
       <c r="S212" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:25Z</t>
+          <t>2026-10-10T23:42:25Z</t>
         </is>
       </c>
     </row>
@@ -18626,7 +18626,7 @@
       </c>
       <c r="S213" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:25Z</t>
+          <t>2026-10-10T23:42:25Z</t>
         </is>
       </c>
     </row>
@@ -18715,7 +18715,7 @@
       </c>
       <c r="S214" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:25Z</t>
+          <t>2026-10-10T23:42:25Z</t>
         </is>
       </c>
     </row>
@@ -18804,7 +18804,7 @@
       </c>
       <c r="S215" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:25Z</t>
+          <t>2026-10-10T23:42:25Z</t>
         </is>
       </c>
     </row>
@@ -18889,7 +18889,7 @@
       </c>
       <c r="S216" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:25Z</t>
+          <t>2026-10-10T23:42:25Z</t>
         </is>
       </c>
     </row>
@@ -18978,7 +18978,7 @@
       </c>
       <c r="S217" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:25Z</t>
+          <t>2026-10-10T23:42:25Z</t>
         </is>
       </c>
     </row>
@@ -19067,7 +19067,7 @@
       </c>
       <c r="S218" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:25Z</t>
+          <t>2026-10-10T23:42:25Z</t>
         </is>
       </c>
     </row>
@@ -19152,7 +19152,7 @@
       </c>
       <c r="S219" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:25Z</t>
+          <t>2026-10-10T23:42:25Z</t>
         </is>
       </c>
     </row>
@@ -19241,7 +19241,7 @@
       </c>
       <c r="S220" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:25Z</t>
+          <t>2026-10-10T23:42:25Z</t>
         </is>
       </c>
     </row>
@@ -19330,7 +19330,7 @@
       </c>
       <c r="S221" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:25Z</t>
+          <t>2026-10-10T23:42:25Z</t>
         </is>
       </c>
     </row>
@@ -19415,7 +19415,7 @@
       </c>
       <c r="S222" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:25Z</t>
+          <t>2026-10-10T23:42:25Z</t>
         </is>
       </c>
     </row>
@@ -19504,7 +19504,7 @@
       </c>
       <c r="S223" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:25Z</t>
+          <t>2026-10-10T23:42:25Z</t>
         </is>
       </c>
     </row>
@@ -19593,7 +19593,7 @@
       </c>
       <c r="S224" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:25Z</t>
+          <t>2026-10-10T23:42:25Z</t>
         </is>
       </c>
     </row>
@@ -19678,7 +19678,7 @@
       </c>
       <c r="S225" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:25Z</t>
+          <t>2026-10-10T23:42:25Z</t>
         </is>
       </c>
     </row>
@@ -19767,7 +19767,7 @@
       </c>
       <c r="S226" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:25Z</t>
+          <t>2026-10-10T23:42:25Z</t>
         </is>
       </c>
     </row>
@@ -19856,7 +19856,7 @@
       </c>
       <c r="S227" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:25Z</t>
+          <t>2026-10-10T23:42:25Z</t>
         </is>
       </c>
     </row>
@@ -19941,7 +19941,7 @@
       </c>
       <c r="S228" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:25Z</t>
+          <t>2026-10-10T23:42:25Z</t>
         </is>
       </c>
     </row>
@@ -20030,7 +20030,7 @@
       </c>
       <c r="S229" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:25Z</t>
+          <t>2026-10-10T23:42:25Z</t>
         </is>
       </c>
     </row>
@@ -20119,7 +20119,7 @@
       </c>
       <c r="S230" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:25Z</t>
+          <t>2026-10-10T23:42:25Z</t>
         </is>
       </c>
     </row>
@@ -20204,7 +20204,7 @@
       </c>
       <c r="S231" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:25Z</t>
+          <t>2026-10-10T23:42:25Z</t>
         </is>
       </c>
     </row>
@@ -20293,7 +20293,7 @@
       </c>
       <c r="S232" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:25Z</t>
+          <t>2026-10-10T23:42:25Z</t>
         </is>
       </c>
     </row>
@@ -20382,7 +20382,7 @@
       </c>
       <c r="S233" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:25Z</t>
+          <t>2026-10-10T23:42:25Z</t>
         </is>
       </c>
     </row>
@@ -20467,7 +20467,7 @@
       </c>
       <c r="S234" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:25Z</t>
+          <t>2026-10-10T23:42:25Z</t>
         </is>
       </c>
     </row>
@@ -20556,7 +20556,7 @@
       </c>
       <c r="S235" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:25Z</t>
+          <t>2026-10-10T23:42:25Z</t>
         </is>
       </c>
     </row>
@@ -20645,7 +20645,7 @@
       </c>
       <c r="S236" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:25Z</t>
+          <t>2026-10-10T23:42:25Z</t>
         </is>
       </c>
     </row>
@@ -20730,7 +20730,7 @@
       </c>
       <c r="S237" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:25Z</t>
+          <t>2026-10-10T23:42:25Z</t>
         </is>
       </c>
     </row>
@@ -20819,7 +20819,7 @@
       </c>
       <c r="S238" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:25Z</t>
+          <t>2026-10-10T23:42:25Z</t>
         </is>
       </c>
     </row>
@@ -20908,7 +20908,7 @@
       </c>
       <c r="S239" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:25Z</t>
+          <t>2026-10-10T23:42:25Z</t>
         </is>
       </c>
     </row>
@@ -20997,7 +20997,7 @@
       </c>
       <c r="S240" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:25Z</t>
+          <t>2026-10-10T23:42:25Z</t>
         </is>
       </c>
     </row>
@@ -21086,7 +21086,7 @@
       </c>
       <c r="S241" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:25Z</t>
+          <t>2026-10-10T23:42:25Z</t>
         </is>
       </c>
     </row>
@@ -21175,7 +21175,7 @@
       </c>
       <c r="S242" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:25Z</t>
+          <t>2026-10-10T23:42:25Z</t>
         </is>
       </c>
     </row>
@@ -21264,7 +21264,7 @@
       </c>
       <c r="S243" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:25Z</t>
+          <t>2026-10-10T23:42:25Z</t>
         </is>
       </c>
     </row>
@@ -21353,7 +21353,7 @@
       </c>
       <c r="S244" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:25Z</t>
+          <t>2026-10-10T23:42:25Z</t>
         </is>
       </c>
     </row>
@@ -21442,7 +21442,7 @@
       </c>
       <c r="S245" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:25Z</t>
+          <t>2026-10-10T23:42:25Z</t>
         </is>
       </c>
     </row>
@@ -21531,7 +21531,7 @@
       </c>
       <c r="S246" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:25Z</t>
+          <t>2026-10-10T23:42:25Z</t>
         </is>
       </c>
     </row>
@@ -21620,7 +21620,7 @@
       </c>
       <c r="S247" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:25Z</t>
+          <t>2026-10-10T23:42:25Z</t>
         </is>
       </c>
     </row>
@@ -21709,7 +21709,7 @@
       </c>
       <c r="S248" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:25Z</t>
+          <t>2026-10-10T23:42:25Z</t>
         </is>
       </c>
     </row>
@@ -21798,7 +21798,7 @@
       </c>
       <c r="S249" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:25Z</t>
+          <t>2026-10-10T23:42:25Z</t>
         </is>
       </c>
     </row>
@@ -21887,7 +21887,7 @@
       </c>
       <c r="S250" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:25Z</t>
+          <t>2026-10-10T23:42:25Z</t>
         </is>
       </c>
     </row>
@@ -22019,7 +22019,7 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:25Z</t>
+          <t>2026-10-10T23:42:25Z</t>
         </is>
       </c>
     </row>
@@ -22099,7 +22099,7 @@
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>{"dataset_id": "bcv_pib_sector_institucional_anual", "title": "Producto interno bruto por sector institucional anual", "table": "Variaciones porcentuales", "source_file": "5_2_1_si_anual.xlsx", "base": "2007", "price_type": "Precios constantes", "measure": "Variación porcentual interanual", "frequency": "Anual", "period": "2025", "year": 2025, "quarter": null, "classification": "Sector institucional", "component": "Impuestos netos sobre los productos", "value": 10.600260421283764, "unit": "Porcentaje", "status": "Preliminar", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/cuentas_macroeconomicas/5_2_1_si_anual.xlsx", "fetched_at": "2026-10-10T00:11:25Z"}</t>
+          <t>{"dataset_id": "bcv_pib_sector_institucional_anual", "title": "Producto interno bruto por sector institucional anual", "table": "Variaciones porcentuales", "source_file": "5_2_1_si_anual.xlsx", "base": "2007", "price_type": "Precios constantes", "measure": "Variación porcentual interanual", "frequency": "Anual", "period": "2025", "year": 2025, "quarter": null, "classification": "Sector institucional", "component": "Impuestos netos sobre los productos", "value": 10.600260421283764, "unit": "Porcentaje", "status": "Preliminar", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/cuentas_macroeconomicas/5_2_1_si_anual.xlsx", "fetched_at": "2026-10-10T23:42:25Z"}</t>
         </is>
       </c>
     </row>

--- a/assets/data/bcv/excel/ove_bcv_pib_sector_institucional_anual.xlsx
+++ b/assets/data/bcv/excel/ove_bcv_pib_sector_institucional_anual.xlsx
@@ -736,7 +736,7 @@
       </c>
       <c r="S7" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T23:42:25Z</t>
+          <t>2026-10-11T23:49:14Z</t>
         </is>
       </c>
     </row>
@@ -821,7 +821,7 @@
       </c>
       <c r="S8" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T23:42:25Z</t>
+          <t>2026-10-11T23:49:14Z</t>
         </is>
       </c>
     </row>
@@ -906,7 +906,7 @@
       </c>
       <c r="S9" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T23:42:25Z</t>
+          <t>2026-10-11T23:49:14Z</t>
         </is>
       </c>
     </row>
@@ -991,7 +991,7 @@
       </c>
       <c r="S10" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T23:42:25Z</t>
+          <t>2026-10-11T23:49:14Z</t>
         </is>
       </c>
     </row>
@@ -1076,7 +1076,7 @@
       </c>
       <c r="S11" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T23:42:25Z</t>
+          <t>2026-10-11T23:49:14Z</t>
         </is>
       </c>
     </row>
@@ -1161,7 +1161,7 @@
       </c>
       <c r="S12" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T23:42:25Z</t>
+          <t>2026-10-11T23:49:14Z</t>
         </is>
       </c>
     </row>
@@ -1246,7 +1246,7 @@
       </c>
       <c r="S13" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T23:42:25Z</t>
+          <t>2026-10-11T23:49:14Z</t>
         </is>
       </c>
     </row>
@@ -1331,7 +1331,7 @@
       </c>
       <c r="S14" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T23:42:25Z</t>
+          <t>2026-10-11T23:49:14Z</t>
         </is>
       </c>
     </row>
@@ -1416,7 +1416,7 @@
       </c>
       <c r="S15" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T23:42:25Z</t>
+          <t>2026-10-11T23:49:14Z</t>
         </is>
       </c>
     </row>
@@ -1501,7 +1501,7 @@
       </c>
       <c r="S16" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T23:42:25Z</t>
+          <t>2026-10-11T23:49:14Z</t>
         </is>
       </c>
     </row>
@@ -1586,7 +1586,7 @@
       </c>
       <c r="S17" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T23:42:25Z</t>
+          <t>2026-10-11T23:49:14Z</t>
         </is>
       </c>
     </row>
@@ -1671,7 +1671,7 @@
       </c>
       <c r="S18" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T23:42:25Z</t>
+          <t>2026-10-11T23:49:14Z</t>
         </is>
       </c>
     </row>
@@ -1756,7 +1756,7 @@
       </c>
       <c r="S19" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T23:42:25Z</t>
+          <t>2026-10-11T23:49:14Z</t>
         </is>
       </c>
     </row>
@@ -1841,7 +1841,7 @@
       </c>
       <c r="S20" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T23:42:25Z</t>
+          <t>2026-10-11T23:49:14Z</t>
         </is>
       </c>
     </row>
@@ -1926,7 +1926,7 @@
       </c>
       <c r="S21" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T23:42:25Z</t>
+          <t>2026-10-11T23:49:14Z</t>
         </is>
       </c>
     </row>
@@ -2011,7 +2011,7 @@
       </c>
       <c r="S22" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T23:42:25Z</t>
+          <t>2026-10-11T23:49:14Z</t>
         </is>
       </c>
     </row>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="S23" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T23:42:25Z</t>
+          <t>2026-10-11T23:49:14Z</t>
         </is>
       </c>
     </row>
@@ -2181,7 +2181,7 @@
       </c>
       <c r="S24" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T23:42:25Z</t>
+          <t>2026-10-11T23:49:14Z</t>
         </is>
       </c>
     </row>
@@ -2266,7 +2266,7 @@
       </c>
       <c r="S25" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T23:42:25Z</t>
+          <t>2026-10-11T23:49:14Z</t>
         </is>
       </c>
     </row>
@@ -2351,7 +2351,7 @@
       </c>
       <c r="S26" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T23:42:25Z</t>
+          <t>2026-10-11T23:49:14Z</t>
         </is>
       </c>
     </row>
@@ -2436,7 +2436,7 @@
       </c>
       <c r="S27" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T23:42:25Z</t>
+          <t>2026-10-11T23:49:14Z</t>
         </is>
       </c>
     </row>
@@ -2525,7 +2525,7 @@
       </c>
       <c r="S28" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T23:42:25Z</t>
+          <t>2026-10-11T23:49:14Z</t>
         </is>
       </c>
     </row>
@@ -2614,7 +2614,7 @@
       </c>
       <c r="S29" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T23:42:25Z</t>
+          <t>2026-10-11T23:49:14Z</t>
         </is>
       </c>
     </row>
@@ -2699,7 +2699,7 @@
       </c>
       <c r="S30" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T23:42:25Z</t>
+          <t>2026-10-11T23:49:14Z</t>
         </is>
       </c>
     </row>
@@ -2788,7 +2788,7 @@
       </c>
       <c r="S31" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T23:42:25Z</t>
+          <t>2026-10-11T23:49:14Z</t>
         </is>
       </c>
     </row>
@@ -2877,7 +2877,7 @@
       </c>
       <c r="S32" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T23:42:25Z</t>
+          <t>2026-10-11T23:49:14Z</t>
         </is>
       </c>
     </row>
@@ -2962,7 +2962,7 @@
       </c>
       <c r="S33" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T23:42:25Z</t>
+          <t>2026-10-11T23:49:14Z</t>
         </is>
       </c>
     </row>
@@ -3051,7 +3051,7 @@
       </c>
       <c r="S34" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T23:42:25Z</t>
+          <t>2026-10-11T23:49:14Z</t>
         </is>
       </c>
     </row>
@@ -3140,7 +3140,7 @@
       </c>
       <c r="S35" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T23:42:25Z</t>
+          <t>2026-10-11T23:49:14Z</t>
         </is>
       </c>
     </row>
@@ -3225,7 +3225,7 @@
       </c>
       <c r="S36" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T23:42:25Z</t>
+          <t>2026-10-11T23:49:14Z</t>
         </is>
       </c>
     </row>
@@ -3314,7 +3314,7 @@
       </c>
       <c r="S37" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T23:42:25Z</t>
+          <t>2026-10-11T23:49:14Z</t>
         </is>
       </c>
     </row>
@@ -3403,7 +3403,7 @@
       </c>
       <c r="S38" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T23:42:25Z</t>
+          <t>2026-10-11T23:49:14Z</t>
         </is>
       </c>
     </row>
@@ -3488,7 +3488,7 @@
       </c>
       <c r="S39" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T23:42:25Z</t>
+          <t>2026-10-11T23:49:14Z</t>
         </is>
       </c>
     </row>
@@ -3577,7 +3577,7 @@
       </c>
       <c r="S40" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T23:42:25Z</t>
+          <t>2026-10-11T23:49:14Z</t>
         </is>
       </c>
     </row>
@@ -3666,7 +3666,7 @@
       </c>
       <c r="S41" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T23:42:25Z</t>
+          <t>2026-10-11T23:49:14Z</t>
         </is>
       </c>
     </row>
@@ -3751,7 +3751,7 @@
       </c>
       <c r="S42" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T23:42:25Z</t>
+          <t>2026-10-11T23:49:14Z</t>
         </is>
       </c>
     </row>
@@ -3840,7 +3840,7 @@
       </c>
       <c r="S43" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T23:42:25Z</t>
+          <t>2026-10-11T23:49:14Z</t>
         </is>
       </c>
     </row>
@@ -3929,7 +3929,7 @@
       </c>
       <c r="S44" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T23:42:25Z</t>
+          <t>2026-10-11T23:49:14Z</t>
         </is>
       </c>
     </row>
@@ -4014,7 +4014,7 @@
       </c>
       <c r="S45" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T23:42:25Z</t>
+          <t>2026-10-11T23:49:14Z</t>
         </is>
       </c>
     </row>
@@ -4103,7 +4103,7 @@
       </c>
       <c r="S46" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T23:42:25Z</t>
+          <t>2026-10-11T23:49:14Z</t>
         </is>
       </c>
     </row>
@@ -4192,7 +4192,7 @@
       </c>
       <c r="S47" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T23:42:25Z</t>
+          <t>2026-10-11T23:49:14Z</t>
         </is>
       </c>
     </row>
@@ -4277,7 +4277,7 @@
       </c>
       <c r="S48" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T23:42:25Z</t>
+          <t>2026-10-11T23:49:14Z</t>
         </is>
       </c>
     </row>
@@ -4366,7 +4366,7 @@
       </c>
       <c r="S49" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T23:42:25Z</t>
+          <t>2026-10-11T23:49:14Z</t>
         </is>
       </c>
     </row>
@@ -4455,7 +4455,7 @@
       </c>
       <c r="S50" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T23:42:25Z</t>
+          <t>2026-10-11T23:49:14Z</t>
         </is>
       </c>
     </row>
@@ -4540,7 +4540,7 @@
       </c>
       <c r="S51" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T23:42:25Z</t>
+          <t>2026-10-11T23:49:14Z</t>
         </is>
       </c>
     </row>
@@ -4629,7 +4629,7 @@
       </c>
       <c r="S52" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T23:42:25Z</t>
+          <t>2026-10-11T23:49:14Z</t>
         </is>
       </c>
     </row>
@@ -4718,7 +4718,7 @@
       </c>
       <c r="S53" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T23:42:25Z</t>
+          <t>2026-10-11T23:49:14Z</t>
         </is>
       </c>
     </row>
@@ -4803,7 +4803,7 @@
       </c>
       <c r="S54" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T23:42:25Z</t>
+          <t>2026-10-11T23:49:14Z</t>
         </is>
       </c>
     </row>
@@ -4892,7 +4892,7 @@
       </c>
       <c r="S55" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T23:42:25Z</t>
+          <t>2026-10-11T23:49:14Z</t>
         </is>
       </c>
     </row>
@@ -4981,7 +4981,7 @@
       </c>
       <c r="S56" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T23:42:25Z</t>
+          <t>2026-10-11T23:49:14Z</t>
         </is>
       </c>
     </row>
@@ -5070,7 +5070,7 @@
       </c>
       <c r="S57" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T23:42:25Z</t>
+          <t>2026-10-11T23:49:14Z</t>
         </is>
       </c>
     </row>
@@ -5159,7 +5159,7 @@
       </c>
       <c r="S58" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T23:42:25Z</t>
+          <t>2026-10-11T23:49:14Z</t>
         </is>
       </c>
     </row>
@@ -5248,7 +5248,7 @@
       </c>
       <c r="S59" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T23:42:25Z</t>
+          <t>2026-10-11T23:49:14Z</t>
         </is>
       </c>
     </row>
@@ -5337,7 +5337,7 @@
       </c>
       <c r="S60" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T23:42:25Z</t>
+          <t>2026-10-11T23:49:14Z</t>
         </is>
       </c>
     </row>
@@ -5426,7 +5426,7 @@
       </c>
       <c r="S61" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T23:42:25Z</t>
+          <t>2026-10-11T23:49:14Z</t>
         </is>
       </c>
     </row>
@@ -5515,7 +5515,7 @@
       </c>
       <c r="S62" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T23:42:25Z</t>
+          <t>2026-10-11T23:49:14Z</t>
         </is>
       </c>
     </row>
@@ -5604,7 +5604,7 @@
       </c>
       <c r="S63" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T23:42:25Z</t>
+          <t>2026-10-11T23:49:14Z</t>
         </is>
       </c>
     </row>
@@ -5693,7 +5693,7 @@
       </c>
       <c r="S64" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T23:42:25Z</t>
+          <t>2026-10-11T23:49:14Z</t>
         </is>
       </c>
     </row>
@@ -5782,7 +5782,7 @@
       </c>
       <c r="S65" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T23:42:25Z</t>
+          <t>2026-10-11T23:49:14Z</t>
         </is>
       </c>
     </row>
@@ -5871,7 +5871,7 @@
       </c>
       <c r="S66" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T23:42:25Z</t>
+          <t>2026-10-11T23:49:14Z</t>
         </is>
       </c>
     </row>
@@ -5960,7 +5960,7 @@
       </c>
       <c r="S67" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T23:42:25Z</t>
+          <t>2026-10-11T23:49:14Z</t>
         </is>
       </c>
     </row>
@@ -6045,7 +6045,7 @@
       </c>
       <c r="S68" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T23:42:25Z</t>
+          <t>2026-10-11T23:49:14Z</t>
         </is>
       </c>
     </row>
@@ -6130,7 +6130,7 @@
       </c>
       <c r="S69" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T23:42:25Z</t>
+          <t>2026-10-11T23:49:14Z</t>
         </is>
       </c>
     </row>
@@ -6215,7 +6215,7 @@
       </c>
       <c r="S70" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T23:42:25Z</t>
+          <t>2026-10-11T23:49:14Z</t>
         </is>
       </c>
     </row>
@@ -6300,7 +6300,7 @@
       </c>
       <c r="S71" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T23:42:25Z</t>
+          <t>2026-10-11T23:49:14Z</t>
         </is>
       </c>
     </row>
@@ -6385,7 +6385,7 @@
       </c>
       <c r="S72" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T23:42:25Z</t>
+          <t>2026-10-11T23:49:14Z</t>
         </is>
       </c>
     </row>
@@ -6470,7 +6470,7 @@
       </c>
       <c r="S73" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T23:42:25Z</t>
+          <t>2026-10-11T23:49:14Z</t>
         </is>
       </c>
     </row>
@@ -6555,7 +6555,7 @@
       </c>
       <c r="S74" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T23:42:25Z</t>
+          <t>2026-10-11T23:49:14Z</t>
         </is>
       </c>
     </row>
@@ -6640,7 +6640,7 @@
       </c>
       <c r="S75" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T23:42:25Z</t>
+          <t>2026-10-11T23:49:14Z</t>
         </is>
       </c>
     </row>
@@ -6725,7 +6725,7 @@
       </c>
       <c r="S76" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T23:42:25Z</t>
+          <t>2026-10-11T23:49:14Z</t>
         </is>
       </c>
     </row>
@@ -6810,7 +6810,7 @@
       </c>
       <c r="S77" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T23:42:25Z</t>
+          <t>2026-10-11T23:49:14Z</t>
         </is>
       </c>
     </row>
@@ -6895,7 +6895,7 @@
       </c>
       <c r="S78" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T23:42:25Z</t>
+          <t>2026-10-11T23:49:14Z</t>
         </is>
       </c>
     </row>
@@ -6980,7 +6980,7 @@
       </c>
       <c r="S79" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T23:42:25Z</t>
+          <t>2026-10-11T23:49:14Z</t>
         </is>
       </c>
     </row>
@@ -7065,7 +7065,7 @@
       </c>
       <c r="S80" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T23:42:25Z</t>
+          <t>2026-10-11T23:49:14Z</t>
         </is>
       </c>
     </row>
@@ -7150,7 +7150,7 @@
       </c>
       <c r="S81" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T23:42:25Z</t>
+          <t>2026-10-11T23:49:14Z</t>
         </is>
       </c>
     </row>
@@ -7235,7 +7235,7 @@
       </c>
       <c r="S82" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T23:42:25Z</t>
+          <t>2026-10-11T23:49:14Z</t>
         </is>
       </c>
     </row>
@@ -7320,7 +7320,7 @@
       </c>
       <c r="S83" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T23:42:25Z</t>
+          <t>2026-10-11T23:49:14Z</t>
         </is>
       </c>
     </row>
@@ -7405,7 +7405,7 @@
       </c>
       <c r="S84" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T23:42:25Z</t>
+          <t>2026-10-11T23:49:14Z</t>
         </is>
       </c>
     </row>
@@ -7490,7 +7490,7 @@
       </c>
       <c r="S85" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T23:42:25Z</t>
+          <t>2026-10-11T23:49:14Z</t>
         </is>
       </c>
     </row>
@@ -7575,7 +7575,7 @@
       </c>
       <c r="S86" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T23:42:25Z</t>
+          <t>2026-10-11T23:49:14Z</t>
         </is>
       </c>
     </row>
@@ -7660,7 +7660,7 @@
       </c>
       <c r="S87" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T23:42:25Z</t>
+          <t>2026-10-11T23:49:14Z</t>
         </is>
       </c>
     </row>
@@ -7745,7 +7745,7 @@
       </c>
       <c r="S88" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T23:42:25Z</t>
+          <t>2026-10-11T23:49:14Z</t>
         </is>
       </c>
     </row>
@@ -7834,7 +7834,7 @@
       </c>
       <c r="S89" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T23:42:25Z</t>
+          <t>2026-10-11T23:49:14Z</t>
         </is>
       </c>
     </row>
@@ -7923,7 +7923,7 @@
       </c>
       <c r="S90" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T23:42:25Z</t>
+          <t>2026-10-11T23:49:14Z</t>
         </is>
       </c>
     </row>
@@ -8008,7 +8008,7 @@
       </c>
       <c r="S91" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T23:42:25Z</t>
+          <t>2026-10-11T23:49:14Z</t>
         </is>
       </c>
     </row>
@@ -8097,7 +8097,7 @@
       </c>
       <c r="S92" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T23:42:25Z</t>
+          <t>2026-10-11T23:49:14Z</t>
         </is>
       </c>
     </row>
@@ -8186,7 +8186,7 @@
       </c>
       <c r="S93" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T23:42:25Z</t>
+          <t>2026-10-11T23:49:14Z</t>
         </is>
       </c>
     </row>
@@ -8271,7 +8271,7 @@
       </c>
       <c r="S94" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T23:42:25Z</t>
+          <t>2026-10-11T23:49:14Z</t>
         </is>
       </c>
     </row>
@@ -8360,7 +8360,7 @@
       </c>
       <c r="S95" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T23:42:25Z</t>
+          <t>2026-10-11T23:49:14Z</t>
         </is>
       </c>
     </row>
@@ -8449,7 +8449,7 @@
       </c>
       <c r="S96" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T23:42:25Z</t>
+          <t>2026-10-11T23:49:14Z</t>
         </is>
       </c>
     </row>
@@ -8534,7 +8534,7 @@
       </c>
       <c r="S97" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T23:42:25Z</t>
+          <t>2026-10-11T23:49:14Z</t>
         </is>
       </c>
     </row>
@@ -8623,7 +8623,7 @@
       </c>
       <c r="S98" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T23:42:25Z</t>
+          <t>2026-10-11T23:49:14Z</t>
         </is>
       </c>
     </row>
@@ -8712,7 +8712,7 @@
       </c>
       <c r="S99" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T23:42:25Z</t>
+          <t>2026-10-11T23:49:14Z</t>
         </is>
       </c>
     </row>
@@ -8797,7 +8797,7 @@
       </c>
       <c r="S100" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T23:42:25Z</t>
+          <t>2026-10-11T23:49:14Z</t>
         </is>
       </c>
     </row>
@@ -8886,7 +8886,7 @@
       </c>
       <c r="S101" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T23:42:25Z</t>
+          <t>2026-10-11T23:49:14Z</t>
         </is>
       </c>
     </row>
@@ -8975,7 +8975,7 @@
       </c>
       <c r="S102" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T23:42:25Z</t>
+          <t>2026-10-11T23:49:14Z</t>
         </is>
       </c>
     </row>
@@ -9060,7 +9060,7 @@
       </c>
       <c r="S103" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T23:42:25Z</t>
+          <t>2026-10-11T23:49:14Z</t>
         </is>
       </c>
     </row>
@@ -9149,7 +9149,7 @@
       </c>
       <c r="S104" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T23:42:25Z</t>
+          <t>2026-10-11T23:49:14Z</t>
         </is>
       </c>
     </row>
@@ -9238,7 +9238,7 @@
       </c>
       <c r="S105" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T23:42:25Z</t>
+          <t>2026-10-11T23:49:14Z</t>
         </is>
       </c>
     </row>
@@ -9323,7 +9323,7 @@
       </c>
       <c r="S106" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T23:42:25Z</t>
+          <t>2026-10-11T23:49:14Z</t>
         </is>
       </c>
     </row>
@@ -9412,7 +9412,7 @@
       </c>
       <c r="S107" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T23:42:25Z</t>
+          <t>2026-10-11T23:49:14Z</t>
         </is>
       </c>
     </row>
@@ -9501,7 +9501,7 @@
       </c>
       <c r="S108" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T23:42:25Z</t>
+          <t>2026-10-11T23:49:14Z</t>
         </is>
       </c>
     </row>
@@ -9586,7 +9586,7 @@
       </c>
       <c r="S109" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T23:42:25Z</t>
+          <t>2026-10-11T23:49:14Z</t>
         </is>
       </c>
     </row>
@@ -9675,7 +9675,7 @@
       </c>
       <c r="S110" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T23:42:25Z</t>
+          <t>2026-10-11T23:49:14Z</t>
         </is>
       </c>
     </row>
@@ -9764,7 +9764,7 @@
       </c>
       <c r="S111" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T23:42:25Z</t>
+          <t>2026-10-11T23:49:14Z</t>
         </is>
       </c>
     </row>
@@ -9849,7 +9849,7 @@
       </c>
       <c r="S112" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T23:42:25Z</t>
+          <t>2026-10-11T23:49:14Z</t>
         </is>
       </c>
     </row>
@@ -9938,7 +9938,7 @@
       </c>
       <c r="S113" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T23:42:25Z</t>
+          <t>2026-10-11T23:49:14Z</t>
         </is>
       </c>
     </row>
@@ -10027,7 +10027,7 @@
       </c>
       <c r="S114" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T23:42:25Z</t>
+          <t>2026-10-11T23:49:14Z</t>
         </is>
       </c>
     </row>
@@ -10112,7 +10112,7 @@
       </c>
       <c r="S115" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T23:42:25Z</t>
+          <t>2026-10-11T23:49:14Z</t>
         </is>
       </c>
     </row>
@@ -10201,7 +10201,7 @@
       </c>
       <c r="S116" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T23:42:25Z</t>
+          <t>2026-10-11T23:49:14Z</t>
         </is>
       </c>
     </row>
@@ -10290,7 +10290,7 @@
       </c>
       <c r="S117" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T23:42:25Z</t>
+          <t>2026-10-11T23:49:14Z</t>
         </is>
       </c>
     </row>
@@ -10379,7 +10379,7 @@
       </c>
       <c r="S118" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T23:42:25Z</t>
+          <t>2026-10-11T23:49:14Z</t>
         </is>
       </c>
     </row>
@@ -10468,7 +10468,7 @@
       </c>
       <c r="S119" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T23:42:25Z</t>
+          <t>2026-10-11T23:49:14Z</t>
         </is>
       </c>
     </row>
@@ -10557,7 +10557,7 @@
       </c>
       <c r="S120" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T23:42:25Z</t>
+          <t>2026-10-11T23:49:14Z</t>
         </is>
       </c>
     </row>
@@ -10646,7 +10646,7 @@
       </c>
       <c r="S121" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T23:42:25Z</t>
+          <t>2026-10-11T23:49:14Z</t>
         </is>
       </c>
     </row>
@@ -10735,7 +10735,7 @@
       </c>
       <c r="S122" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T23:42:25Z</t>
+          <t>2026-10-11T23:49:14Z</t>
         </is>
       </c>
     </row>
@@ -10824,7 +10824,7 @@
       </c>
       <c r="S123" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T23:42:25Z</t>
+          <t>2026-10-11T23:49:14Z</t>
         </is>
       </c>
     </row>
@@ -10913,7 +10913,7 @@
       </c>
       <c r="S124" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T23:42:25Z</t>
+          <t>2026-10-11T23:49:14Z</t>
         </is>
       </c>
     </row>
@@ -11002,7 +11002,7 @@
       </c>
       <c r="S125" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T23:42:25Z</t>
+          <t>2026-10-11T23:49:14Z</t>
         </is>
       </c>
     </row>
@@ -11091,7 +11091,7 @@
       </c>
       <c r="S126" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T23:42:25Z</t>
+          <t>2026-10-11T23:49:14Z</t>
         </is>
       </c>
     </row>
@@ -11180,7 +11180,7 @@
       </c>
       <c r="S127" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T23:42:25Z</t>
+          <t>2026-10-11T23:49:14Z</t>
         </is>
       </c>
     </row>
@@ -11269,7 +11269,7 @@
       </c>
       <c r="S128" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T23:42:25Z</t>
+          <t>2026-10-11T23:49:14Z</t>
         </is>
       </c>
     </row>
@@ -11354,7 +11354,7 @@
       </c>
       <c r="S129" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T23:42:25Z</t>
+          <t>2026-10-11T23:49:14Z</t>
         </is>
       </c>
     </row>
@@ -11439,7 +11439,7 @@
       </c>
       <c r="S130" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T23:42:25Z</t>
+          <t>2026-10-11T23:49:14Z</t>
         </is>
       </c>
     </row>
@@ -11524,7 +11524,7 @@
       </c>
       <c r="S131" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T23:42:25Z</t>
+          <t>2026-10-11T23:49:14Z</t>
         </is>
       </c>
     </row>
@@ -11609,7 +11609,7 @@
       </c>
       <c r="S132" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T23:42:25Z</t>
+          <t>2026-10-11T23:49:14Z</t>
         </is>
       </c>
     </row>
@@ -11694,7 +11694,7 @@
       </c>
       <c r="S133" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T23:42:25Z</t>
+          <t>2026-10-11T23:49:14Z</t>
         </is>
       </c>
     </row>
@@ -11779,7 +11779,7 @@
       </c>
       <c r="S134" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T23:42:25Z</t>
+          <t>2026-10-11T23:49:14Z</t>
         </is>
       </c>
     </row>
@@ -11864,7 +11864,7 @@
       </c>
       <c r="S135" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T23:42:25Z</t>
+          <t>2026-10-11T23:49:14Z</t>
         </is>
       </c>
     </row>
@@ -11949,7 +11949,7 @@
       </c>
       <c r="S136" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T23:42:25Z</t>
+          <t>2026-10-11T23:49:14Z</t>
         </is>
       </c>
     </row>
@@ -12034,7 +12034,7 @@
       </c>
       <c r="S137" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T23:42:25Z</t>
+          <t>2026-10-11T23:49:14Z</t>
         </is>
       </c>
     </row>
@@ -12119,7 +12119,7 @@
       </c>
       <c r="S138" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T23:42:25Z</t>
+          <t>2026-10-11T23:49:14Z</t>
         </is>
       </c>
     </row>
@@ -12204,7 +12204,7 @@
       </c>
       <c r="S139" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T23:42:25Z</t>
+          <t>2026-10-11T23:49:14Z</t>
         </is>
       </c>
     </row>
@@ -12289,7 +12289,7 @@
       </c>
       <c r="S140" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T23:42:25Z</t>
+          <t>2026-10-11T23:49:14Z</t>
         </is>
       </c>
     </row>
@@ -12374,7 +12374,7 @@
       </c>
       <c r="S141" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T23:42:25Z</t>
+          <t>2026-10-11T23:49:14Z</t>
         </is>
       </c>
     </row>
@@ -12459,7 +12459,7 @@
       </c>
       <c r="S142" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T23:42:25Z</t>
+          <t>2026-10-11T23:49:14Z</t>
         </is>
       </c>
     </row>
@@ -12544,7 +12544,7 @@
       </c>
       <c r="S143" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T23:42:25Z</t>
+          <t>2026-10-11T23:49:14Z</t>
         </is>
       </c>
     </row>
@@ -12629,7 +12629,7 @@
       </c>
       <c r="S144" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T23:42:25Z</t>
+          <t>2026-10-11T23:49:14Z</t>
         </is>
       </c>
     </row>
@@ -12714,7 +12714,7 @@
       </c>
       <c r="S145" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T23:42:25Z</t>
+          <t>2026-10-11T23:49:14Z</t>
         </is>
       </c>
     </row>
@@ -12799,7 +12799,7 @@
       </c>
       <c r="S146" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T23:42:25Z</t>
+          <t>2026-10-11T23:49:14Z</t>
         </is>
       </c>
     </row>
@@ -12884,7 +12884,7 @@
       </c>
       <c r="S147" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T23:42:25Z</t>
+          <t>2026-10-11T23:49:14Z</t>
         </is>
       </c>
     </row>
@@ -12969,7 +12969,7 @@
       </c>
       <c r="S148" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T23:42:25Z</t>
+          <t>2026-10-11T23:49:14Z</t>
         </is>
       </c>
     </row>
@@ -13054,7 +13054,7 @@
       </c>
       <c r="S149" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T23:42:25Z</t>
+          <t>2026-10-11T23:49:14Z</t>
         </is>
       </c>
     </row>
@@ -13143,7 +13143,7 @@
       </c>
       <c r="S150" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T23:42:25Z</t>
+          <t>2026-10-11T23:49:14Z</t>
         </is>
       </c>
     </row>
@@ -13232,7 +13232,7 @@
       </c>
       <c r="S151" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T23:42:25Z</t>
+          <t>2026-10-11T23:49:14Z</t>
         </is>
       </c>
     </row>
@@ -13317,7 +13317,7 @@
       </c>
       <c r="S152" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T23:42:25Z</t>
+          <t>2026-10-11T23:49:14Z</t>
         </is>
       </c>
     </row>
@@ -13406,7 +13406,7 @@
       </c>
       <c r="S153" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T23:42:25Z</t>
+          <t>2026-10-11T23:49:14Z</t>
         </is>
       </c>
     </row>
@@ -13495,7 +13495,7 @@
       </c>
       <c r="S154" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T23:42:25Z</t>
+          <t>2026-10-11T23:49:14Z</t>
         </is>
       </c>
     </row>
@@ -13580,7 +13580,7 @@
       </c>
       <c r="S155" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T23:42:25Z</t>
+          <t>2026-10-11T23:49:14Z</t>
         </is>
       </c>
     </row>
@@ -13669,7 +13669,7 @@
       </c>
       <c r="S156" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T23:42:25Z</t>
+          <t>2026-10-11T23:49:14Z</t>
         </is>
       </c>
     </row>
@@ -13758,7 +13758,7 @@
       </c>
       <c r="S157" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T23:42:25Z</t>
+          <t>2026-10-11T23:49:14Z</t>
         </is>
       </c>
     </row>
@@ -13843,7 +13843,7 @@
       </c>
       <c r="S158" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T23:42:25Z</t>
+          <t>2026-10-11T23:49:14Z</t>
         </is>
       </c>
     </row>
@@ -13932,7 +13932,7 @@
       </c>
       <c r="S159" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T23:42:25Z</t>
+          <t>2026-10-11T23:49:14Z</t>
         </is>
       </c>
     </row>
@@ -14021,7 +14021,7 @@
       </c>
       <c r="S160" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T23:42:25Z</t>
+          <t>2026-10-11T23:49:14Z</t>
         </is>
       </c>
     </row>
@@ -14106,7 +14106,7 @@
       </c>
       <c r="S161" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T23:42:25Z</t>
+          <t>2026-10-11T23:49:14Z</t>
         </is>
       </c>
     </row>
@@ -14195,7 +14195,7 @@
       </c>
       <c r="S162" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T23:42:25Z</t>
+          <t>2026-10-11T23:49:14Z</t>
         </is>
       </c>
     </row>
@@ -14284,7 +14284,7 @@
       </c>
       <c r="S163" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T23:42:25Z</t>
+          <t>2026-10-11T23:49:14Z</t>
         </is>
       </c>
     </row>
@@ -14369,7 +14369,7 @@
       </c>
       <c r="S164" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T23:42:25Z</t>
+          <t>2026-10-11T23:49:14Z</t>
         </is>
       </c>
     </row>
@@ -14458,7 +14458,7 @@
       </c>
       <c r="S165" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T23:42:25Z</t>
+          <t>2026-10-11T23:49:14Z</t>
         </is>
       </c>
     </row>
@@ -14547,7 +14547,7 @@
       </c>
       <c r="S166" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T23:42:25Z</t>
+          <t>2026-10-11T23:49:14Z</t>
         </is>
       </c>
     </row>
@@ -14632,7 +14632,7 @@
       </c>
       <c r="S167" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T23:42:25Z</t>
+          <t>2026-10-11T23:49:14Z</t>
         </is>
       </c>
     </row>
@@ -14721,7 +14721,7 @@
       </c>
       <c r="S168" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T23:42:25Z</t>
+          <t>2026-10-11T23:49:14Z</t>
         </is>
       </c>
     </row>
@@ -14810,7 +14810,7 @@
       </c>
       <c r="S169" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T23:42:25Z</t>
+          <t>2026-10-11T23:49:14Z</t>
         </is>
       </c>
     </row>
@@ -14895,7 +14895,7 @@
       </c>
       <c r="S170" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T23:42:25Z</t>
+          <t>2026-10-11T23:49:14Z</t>
         </is>
       </c>
     </row>
@@ -14984,7 +14984,7 @@
       </c>
       <c r="S171" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T23:42:25Z</t>
+          <t>2026-10-11T23:49:14Z</t>
         </is>
       </c>
     </row>
@@ -15073,7 +15073,7 @@
       </c>
       <c r="S172" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T23:42:25Z</t>
+          <t>2026-10-11T23:49:14Z</t>
         </is>
       </c>
     </row>
@@ -15158,7 +15158,7 @@
       </c>
       <c r="S173" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T23:42:25Z</t>
+          <t>2026-10-11T23:49:14Z</t>
         </is>
       </c>
     </row>
@@ -15247,7 +15247,7 @@
       </c>
       <c r="S174" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T23:42:25Z</t>
+          <t>2026-10-11T23:49:14Z</t>
         </is>
       </c>
     </row>
@@ -15336,7 +15336,7 @@
       </c>
       <c r="S175" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T23:42:25Z</t>
+          <t>2026-10-11T23:49:14Z</t>
         </is>
       </c>
     </row>
@@ -15421,7 +15421,7 @@
       </c>
       <c r="S176" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T23:42:25Z</t>
+          <t>2026-10-11T23:49:14Z</t>
         </is>
       </c>
     </row>
@@ -15510,7 +15510,7 @@
       </c>
       <c r="S177" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T23:42:25Z</t>
+          <t>2026-10-11T23:49:14Z</t>
         </is>
       </c>
     </row>
@@ -15599,7 +15599,7 @@
       </c>
       <c r="S178" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T23:42:25Z</t>
+          <t>2026-10-11T23:49:14Z</t>
         </is>
       </c>
     </row>
@@ -15688,7 +15688,7 @@
       </c>
       <c r="S179" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T23:42:25Z</t>
+          <t>2026-10-11T23:49:14Z</t>
         </is>
       </c>
     </row>
@@ -15777,7 +15777,7 @@
       </c>
       <c r="S180" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T23:42:25Z</t>
+          <t>2026-10-11T23:49:14Z</t>
         </is>
       </c>
     </row>
@@ -15866,7 +15866,7 @@
       </c>
       <c r="S181" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T23:42:25Z</t>
+          <t>2026-10-11T23:49:14Z</t>
         </is>
       </c>
     </row>
@@ -15955,7 +15955,7 @@
       </c>
       <c r="S182" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T23:42:25Z</t>
+          <t>2026-10-11T23:49:14Z</t>
         </is>
       </c>
     </row>
@@ -16044,7 +16044,7 @@
       </c>
       <c r="S183" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T23:42:25Z</t>
+          <t>2026-10-11T23:49:14Z</t>
         </is>
       </c>
     </row>
@@ -16133,7 +16133,7 @@
       </c>
       <c r="S184" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T23:42:25Z</t>
+          <t>2026-10-11T23:49:14Z</t>
         </is>
       </c>
     </row>
@@ -16222,7 +16222,7 @@
       </c>
       <c r="S185" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T23:42:25Z</t>
+          <t>2026-10-11T23:49:14Z</t>
         </is>
       </c>
     </row>
@@ -16311,7 +16311,7 @@
       </c>
       <c r="S186" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T23:42:25Z</t>
+          <t>2026-10-11T23:49:14Z</t>
         </is>
       </c>
     </row>
@@ -16400,7 +16400,7 @@
       </c>
       <c r="S187" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T23:42:25Z</t>
+          <t>2026-10-11T23:49:14Z</t>
         </is>
       </c>
     </row>
@@ -16489,7 +16489,7 @@
       </c>
       <c r="S188" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T23:42:25Z</t>
+          <t>2026-10-11T23:49:14Z</t>
         </is>
       </c>
     </row>
@@ -16578,7 +16578,7 @@
       </c>
       <c r="S189" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T23:42:25Z</t>
+          <t>2026-10-11T23:49:14Z</t>
         </is>
       </c>
     </row>
@@ -16663,7 +16663,7 @@
       </c>
       <c r="S190" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T23:42:25Z</t>
+          <t>2026-10-11T23:49:14Z</t>
         </is>
       </c>
     </row>
@@ -16748,7 +16748,7 @@
       </c>
       <c r="S191" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T23:42:25Z</t>
+          <t>2026-10-11T23:49:14Z</t>
         </is>
       </c>
     </row>
@@ -16833,7 +16833,7 @@
       </c>
       <c r="S192" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T23:42:25Z</t>
+          <t>2026-10-11T23:49:14Z</t>
         </is>
       </c>
     </row>
@@ -16918,7 +16918,7 @@
       </c>
       <c r="S193" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T23:42:25Z</t>
+          <t>2026-10-11T23:49:14Z</t>
         </is>
       </c>
     </row>
@@ -17003,7 +17003,7 @@
       </c>
       <c r="S194" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T23:42:25Z</t>
+          <t>2026-10-11T23:49:14Z</t>
         </is>
       </c>
     </row>
@@ -17088,7 +17088,7 @@
       </c>
       <c r="S195" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T23:42:25Z</t>
+          <t>2026-10-11T23:49:14Z</t>
         </is>
       </c>
     </row>
@@ -17173,7 +17173,7 @@
       </c>
       <c r="S196" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T23:42:25Z</t>
+          <t>2026-10-11T23:49:14Z</t>
         </is>
       </c>
     </row>
@@ -17258,7 +17258,7 @@
       </c>
       <c r="S197" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T23:42:25Z</t>
+          <t>2026-10-11T23:49:14Z</t>
         </is>
       </c>
     </row>
@@ -17343,7 +17343,7 @@
       </c>
       <c r="S198" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T23:42:25Z</t>
+          <t>2026-10-11T23:49:14Z</t>
         </is>
       </c>
     </row>
@@ -17428,7 +17428,7 @@
       </c>
       <c r="S199" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T23:42:25Z</t>
+          <t>2026-10-11T23:49:14Z</t>
         </is>
       </c>
     </row>
@@ -17513,7 +17513,7 @@
       </c>
       <c r="S200" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T23:42:25Z</t>
+          <t>2026-10-11T23:49:14Z</t>
         </is>
       </c>
     </row>
@@ -17598,7 +17598,7 @@
       </c>
       <c r="S201" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T23:42:25Z</t>
+          <t>2026-10-11T23:49:14Z</t>
         </is>
       </c>
     </row>
@@ -17683,7 +17683,7 @@
       </c>
       <c r="S202" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T23:42:25Z</t>
+          <t>2026-10-11T23:49:14Z</t>
         </is>
       </c>
     </row>
@@ -17768,7 +17768,7 @@
       </c>
       <c r="S203" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T23:42:25Z</t>
+          <t>2026-10-11T23:49:14Z</t>
         </is>
       </c>
     </row>
@@ -17853,7 +17853,7 @@
       </c>
       <c r="S204" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T23:42:25Z</t>
+          <t>2026-10-11T23:49:14Z</t>
         </is>
       </c>
     </row>
@@ -17938,7 +17938,7 @@
       </c>
       <c r="S205" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T23:42:25Z</t>
+          <t>2026-10-11T23:49:14Z</t>
         </is>
       </c>
     </row>
@@ -18023,7 +18023,7 @@
       </c>
       <c r="S206" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T23:42:25Z</t>
+          <t>2026-10-11T23:49:14Z</t>
         </is>
       </c>
     </row>
@@ -18108,7 +18108,7 @@
       </c>
       <c r="S207" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T23:42:25Z</t>
+          <t>2026-10-11T23:49:14Z</t>
         </is>
       </c>
     </row>
@@ -18193,7 +18193,7 @@
       </c>
       <c r="S208" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T23:42:25Z</t>
+          <t>2026-10-11T23:49:14Z</t>
         </is>
       </c>
     </row>
@@ -18278,7 +18278,7 @@
       </c>
       <c r="S209" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T23:42:25Z</t>
+          <t>2026-10-11T23:49:14Z</t>
         </is>
       </c>
     </row>
@@ -18363,7 +18363,7 @@
       </c>
       <c r="S210" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T23:42:25Z</t>
+          <t>2026-10-11T23:49:14Z</t>
         </is>
       </c>
     </row>
@@ -18452,7 +18452,7 @@
       </c>
       <c r="S211" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T23:42:25Z</t>
+          <t>2026-10-11T23:49:14Z</t>
         </is>
       </c>
     </row>
@@ -18541,7 +18541,7 @@
       </c>
       <c r="S212" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T23:42:25Z</t>
+          <t>2026-10-11T23:49:14Z</t>
         </is>
       </c>
     </row>
@@ -18626,7 +18626,7 @@
       </c>
       <c r="S213" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T23:42:25Z</t>
+          <t>2026-10-11T23:49:14Z</t>
         </is>
       </c>
     </row>
@@ -18715,7 +18715,7 @@
       </c>
       <c r="S214" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T23:42:25Z</t>
+          <t>2026-10-11T23:49:14Z</t>
         </is>
       </c>
     </row>
@@ -18804,7 +18804,7 @@
       </c>
       <c r="S215" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T23:42:25Z</t>
+          <t>2026-10-11T23:49:14Z</t>
         </is>
       </c>
     </row>
@@ -18889,7 +18889,7 @@
       </c>
       <c r="S216" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T23:42:25Z</t>
+          <t>2026-10-11T23:49:14Z</t>
         </is>
       </c>
     </row>
@@ -18978,7 +18978,7 @@
       </c>
       <c r="S217" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T23:42:25Z</t>
+          <t>2026-10-11T23:49:14Z</t>
         </is>
       </c>
     </row>
@@ -19067,7 +19067,7 @@
       </c>
       <c r="S218" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T23:42:25Z</t>
+          <t>2026-10-11T23:49:14Z</t>
         </is>
       </c>
     </row>
@@ -19152,7 +19152,7 @@
       </c>
       <c r="S219" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T23:42:25Z</t>
+          <t>2026-10-11T23:49:14Z</t>
         </is>
       </c>
     </row>
@@ -19241,7 +19241,7 @@
       </c>
       <c r="S220" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T23:42:25Z</t>
+          <t>2026-10-11T23:49:14Z</t>
         </is>
       </c>
     </row>
@@ -19330,7 +19330,7 @@
       </c>
       <c r="S221" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T23:42:25Z</t>
+          <t>2026-10-11T23:49:14Z</t>
         </is>
       </c>
     </row>
@@ -19415,7 +19415,7 @@
       </c>
       <c r="S222" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T23:42:25Z</t>
+          <t>2026-10-11T23:49:14Z</t>
         </is>
       </c>
     </row>
@@ -19504,7 +19504,7 @@
       </c>
       <c r="S223" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T23:42:25Z</t>
+          <t>2026-10-11T23:49:14Z</t>
         </is>
       </c>
     </row>
@@ -19593,7 +19593,7 @@
       </c>
       <c r="S224" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T23:42:25Z</t>
+          <t>2026-10-11T23:49:14Z</t>
         </is>
       </c>
     </row>
@@ -19678,7 +19678,7 @@
       </c>
       <c r="S225" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T23:42:25Z</t>
+          <t>2026-10-11T23:49:14Z</t>
         </is>
       </c>
     </row>
@@ -19767,7 +19767,7 @@
       </c>
       <c r="S226" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T23:42:25Z</t>
+          <t>2026-10-11T23:49:14Z</t>
         </is>
       </c>
     </row>
@@ -19856,7 +19856,7 @@
       </c>
       <c r="S227" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T23:42:25Z</t>
+          <t>2026-10-11T23:49:14Z</t>
         </is>
       </c>
     </row>
@@ -19941,7 +19941,7 @@
       </c>
       <c r="S228" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T23:42:25Z</t>
+          <t>2026-10-11T23:49:14Z</t>
         </is>
       </c>
     </row>
@@ -20030,7 +20030,7 @@
       </c>
       <c r="S229" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T23:42:25Z</t>
+          <t>2026-10-11T23:49:14Z</t>
         </is>
       </c>
     </row>
@@ -20119,7 +20119,7 @@
       </c>
       <c r="S230" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T23:42:25Z</t>
+          <t>2026-10-11T23:49:14Z</t>
         </is>
       </c>
     </row>
@@ -20204,7 +20204,7 @@
       </c>
       <c r="S231" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T23:42:25Z</t>
+          <t>2026-10-11T23:49:14Z</t>
         </is>
       </c>
     </row>
@@ -20293,7 +20293,7 @@
       </c>
       <c r="S232" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T23:42:25Z</t>
+          <t>2026-10-11T23:49:14Z</t>
         </is>
       </c>
     </row>
@@ -20382,7 +20382,7 @@
       </c>
       <c r="S233" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T23:42:25Z</t>
+          <t>2026-10-11T23:49:14Z</t>
         </is>
       </c>
     </row>
@@ -20467,7 +20467,7 @@
       </c>
       <c r="S234" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T23:42:25Z</t>
+          <t>2026-10-11T23:49:14Z</t>
         </is>
       </c>
     </row>
@@ -20556,7 +20556,7 @@
       </c>
       <c r="S235" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T23:42:25Z</t>
+          <t>2026-10-11T23:49:14Z</t>
         </is>
       </c>
     </row>
@@ -20645,7 +20645,7 @@
       </c>
       <c r="S236" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T23:42:25Z</t>
+          <t>2026-10-11T23:49:14Z</t>
         </is>
       </c>
     </row>
@@ -20730,7 +20730,7 @@
       </c>
       <c r="S237" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T23:42:25Z</t>
+          <t>2026-10-11T23:49:14Z</t>
         </is>
       </c>
     </row>
@@ -20819,7 +20819,7 @@
       </c>
       <c r="S238" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T23:42:25Z</t>
+          <t>2026-10-11T23:49:14Z</t>
         </is>
       </c>
     </row>
@@ -20908,7 +20908,7 @@
       </c>
       <c r="S239" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T23:42:25Z</t>
+          <t>2026-10-11T23:49:14Z</t>
         </is>
       </c>
     </row>
@@ -20997,7 +20997,7 @@
       </c>
       <c r="S240" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T23:42:25Z</t>
+          <t>2026-10-11T23:49:14Z</t>
         </is>
       </c>
     </row>
@@ -21086,7 +21086,7 @@
       </c>
       <c r="S241" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T23:42:25Z</t>
+          <t>2026-10-11T23:49:14Z</t>
         </is>
       </c>
     </row>
@@ -21175,7 +21175,7 @@
       </c>
       <c r="S242" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T23:42:25Z</t>
+          <t>2026-10-11T23:49:14Z</t>
         </is>
       </c>
     </row>
@@ -21264,7 +21264,7 @@
       </c>
       <c r="S243" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T23:42:25Z</t>
+          <t>2026-10-11T23:49:14Z</t>
         </is>
       </c>
     </row>
@@ -21353,7 +21353,7 @@
       </c>
       <c r="S244" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T23:42:25Z</t>
+          <t>2026-10-11T23:49:14Z</t>
         </is>
       </c>
     </row>
@@ -21442,7 +21442,7 @@
       </c>
       <c r="S245" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T23:42:25Z</t>
+          <t>2026-10-11T23:49:14Z</t>
         </is>
       </c>
     </row>
@@ -21531,7 +21531,7 @@
       </c>
       <c r="S246" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T23:42:25Z</t>
+          <t>2026-10-11T23:49:14Z</t>
         </is>
       </c>
     </row>
@@ -21620,7 +21620,7 @@
       </c>
       <c r="S247" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T23:42:25Z</t>
+          <t>2026-10-11T23:49:14Z</t>
         </is>
       </c>
     </row>
@@ -21709,7 +21709,7 @@
       </c>
       <c r="S248" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T23:42:25Z</t>
+          <t>2026-10-11T23:49:14Z</t>
         </is>
       </c>
     </row>
@@ -21798,7 +21798,7 @@
       </c>
       <c r="S249" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T23:42:25Z</t>
+          <t>2026-10-11T23:49:14Z</t>
         </is>
       </c>
     </row>
@@ -21887,7 +21887,7 @@
       </c>
       <c r="S250" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T23:42:25Z</t>
+          <t>2026-10-11T23:49:14Z</t>
         </is>
       </c>
     </row>
@@ -22019,7 +22019,7 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T23:42:25Z</t>
+          <t>2026-10-11T23:49:14Z</t>
         </is>
       </c>
     </row>
@@ -22099,7 +22099,7 @@
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>{"dataset_id": "bcv_pib_sector_institucional_anual", "title": "Producto interno bruto por sector institucional anual", "table": "Variaciones porcentuales", "source_file": "5_2_1_si_anual.xlsx", "base": "2007", "price_type": "Precios constantes", "measure": "Variación porcentual interanual", "frequency": "Anual", "period": "2025", "year": 2025, "quarter": null, "classification": "Sector institucional", "component": "Impuestos netos sobre los productos", "value": 10.600260421283764, "unit": "Porcentaje", "status": "Preliminar", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/cuentas_macroeconomicas/5_2_1_si_anual.xlsx", "fetched_at": "2026-10-10T23:42:25Z"}</t>
+          <t>{"dataset_id": "bcv_pib_sector_institucional_anual", "title": "Producto interno bruto por sector institucional anual", "table": "Variaciones porcentuales", "source_file": "5_2_1_si_anual.xlsx", "base": "2007", "price_type": "Precios constantes", "measure": "Variación porcentual interanual", "frequency": "Anual", "period": "2025", "year": 2025, "quarter": null, "classification": "Sector institucional", "component": "Impuestos netos sobre los productos", "value": 10.600260421283764, "unit": "Porcentaje", "status": "Preliminar", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/cuentas_macroeconomicas/5_2_1_si_anual.xlsx", "fetched_at": "2026-10-11T23:49:14Z"}</t>
         </is>
       </c>
     </row>

--- a/assets/data/bcv/excel/ove_bcv_pib_sector_institucional_anual.xlsx
+++ b/assets/data/bcv/excel/ove_bcv_pib_sector_institucional_anual.xlsx
@@ -736,7 +736,7 @@
       </c>
       <c r="S7" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11T23:49:14Z</t>
+          <t>2026-10-12T21:43:48Z</t>
         </is>
       </c>
     </row>
@@ -821,7 +821,7 @@
       </c>
       <c r="S8" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11T23:49:14Z</t>
+          <t>2026-10-12T21:43:48Z</t>
         </is>
       </c>
     </row>
@@ -906,7 +906,7 @@
       </c>
       <c r="S9" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11T23:49:14Z</t>
+          <t>2026-10-12T21:43:48Z</t>
         </is>
       </c>
     </row>
@@ -991,7 +991,7 @@
       </c>
       <c r="S10" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11T23:49:14Z</t>
+          <t>2026-10-12T21:43:48Z</t>
         </is>
       </c>
     </row>
@@ -1076,7 +1076,7 @@
       </c>
       <c r="S11" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11T23:49:14Z</t>
+          <t>2026-10-12T21:43:48Z</t>
         </is>
       </c>
     </row>
@@ -1161,7 +1161,7 @@
       </c>
       <c r="S12" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11T23:49:14Z</t>
+          <t>2026-10-12T21:43:48Z</t>
         </is>
       </c>
     </row>
@@ -1246,7 +1246,7 @@
       </c>
       <c r="S13" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11T23:49:14Z</t>
+          <t>2026-10-12T21:43:48Z</t>
         </is>
       </c>
     </row>
@@ -1331,7 +1331,7 @@
       </c>
       <c r="S14" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11T23:49:14Z</t>
+          <t>2026-10-12T21:43:48Z</t>
         </is>
       </c>
     </row>
@@ -1416,7 +1416,7 @@
       </c>
       <c r="S15" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11T23:49:14Z</t>
+          <t>2026-10-12T21:43:48Z</t>
         </is>
       </c>
     </row>
@@ -1501,7 +1501,7 @@
       </c>
       <c r="S16" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11T23:49:14Z</t>
+          <t>2026-10-12T21:43:48Z</t>
         </is>
       </c>
     </row>
@@ -1586,7 +1586,7 @@
       </c>
       <c r="S17" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11T23:49:14Z</t>
+          <t>2026-10-12T21:43:48Z</t>
         </is>
       </c>
     </row>
@@ -1671,7 +1671,7 @@
       </c>
       <c r="S18" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11T23:49:14Z</t>
+          <t>2026-10-12T21:43:48Z</t>
         </is>
       </c>
     </row>
@@ -1756,7 +1756,7 @@
       </c>
       <c r="S19" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11T23:49:14Z</t>
+          <t>2026-10-12T21:43:48Z</t>
         </is>
       </c>
     </row>
@@ -1841,7 +1841,7 @@
       </c>
       <c r="S20" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11T23:49:14Z</t>
+          <t>2026-10-12T21:43:48Z</t>
         </is>
       </c>
     </row>
@@ -1926,7 +1926,7 @@
       </c>
       <c r="S21" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11T23:49:14Z</t>
+          <t>2026-10-12T21:43:48Z</t>
         </is>
       </c>
     </row>
@@ -2011,7 +2011,7 @@
       </c>
       <c r="S22" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11T23:49:14Z</t>
+          <t>2026-10-12T21:43:48Z</t>
         </is>
       </c>
     </row>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="S23" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11T23:49:14Z</t>
+          <t>2026-10-12T21:43:48Z</t>
         </is>
       </c>
     </row>
@@ -2181,7 +2181,7 @@
       </c>
       <c r="S24" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11T23:49:14Z</t>
+          <t>2026-10-12T21:43:48Z</t>
         </is>
       </c>
     </row>
@@ -2266,7 +2266,7 @@
       </c>
       <c r="S25" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11T23:49:14Z</t>
+          <t>2026-10-12T21:43:48Z</t>
         </is>
       </c>
     </row>
@@ -2351,7 +2351,7 @@
       </c>
       <c r="S26" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11T23:49:14Z</t>
+          <t>2026-10-12T21:43:48Z</t>
         </is>
       </c>
     </row>
@@ -2436,7 +2436,7 @@
       </c>
       <c r="S27" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11T23:49:14Z</t>
+          <t>2026-10-12T21:43:48Z</t>
         </is>
       </c>
     </row>
@@ -2525,7 +2525,7 @@
       </c>
       <c r="S28" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11T23:49:14Z</t>
+          <t>2026-10-12T21:43:48Z</t>
         </is>
       </c>
     </row>
@@ -2614,7 +2614,7 @@
       </c>
       <c r="S29" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11T23:49:14Z</t>
+          <t>2026-10-12T21:43:48Z</t>
         </is>
       </c>
     </row>
@@ -2699,7 +2699,7 @@
       </c>
       <c r="S30" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11T23:49:14Z</t>
+          <t>2026-10-12T21:43:48Z</t>
         </is>
       </c>
     </row>
@@ -2788,7 +2788,7 @@
       </c>
       <c r="S31" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11T23:49:14Z</t>
+          <t>2026-10-12T21:43:48Z</t>
         </is>
       </c>
     </row>
@@ -2877,7 +2877,7 @@
       </c>
       <c r="S32" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11T23:49:14Z</t>
+          <t>2026-10-12T21:43:48Z</t>
         </is>
       </c>
     </row>
@@ -2962,7 +2962,7 @@
       </c>
       <c r="S33" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11T23:49:14Z</t>
+          <t>2026-10-12T21:43:48Z</t>
         </is>
       </c>
     </row>
@@ -3051,7 +3051,7 @@
       </c>
       <c r="S34" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11T23:49:14Z</t>
+          <t>2026-10-12T21:43:48Z</t>
         </is>
       </c>
     </row>
@@ -3140,7 +3140,7 @@
       </c>
       <c r="S35" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11T23:49:14Z</t>
+          <t>2026-10-12T21:43:48Z</t>
         </is>
       </c>
     </row>
@@ -3225,7 +3225,7 @@
       </c>
       <c r="S36" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11T23:49:14Z</t>
+          <t>2026-10-12T21:43:48Z</t>
         </is>
       </c>
     </row>
@@ -3314,7 +3314,7 @@
       </c>
       <c r="S37" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11T23:49:14Z</t>
+          <t>2026-10-12T21:43:48Z</t>
         </is>
       </c>
     </row>
@@ -3403,7 +3403,7 @@
       </c>
       <c r="S38" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11T23:49:14Z</t>
+          <t>2026-10-12T21:43:48Z</t>
         </is>
       </c>
     </row>
@@ -3488,7 +3488,7 @@
       </c>
       <c r="S39" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11T23:49:14Z</t>
+          <t>2026-10-12T21:43:48Z</t>
         </is>
       </c>
     </row>
@@ -3577,7 +3577,7 @@
       </c>
       <c r="S40" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11T23:49:14Z</t>
+          <t>2026-10-12T21:43:48Z</t>
         </is>
       </c>
     </row>
@@ -3666,7 +3666,7 @@
       </c>
       <c r="S41" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11T23:49:14Z</t>
+          <t>2026-10-12T21:43:48Z</t>
         </is>
       </c>
     </row>
@@ -3751,7 +3751,7 @@
       </c>
       <c r="S42" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11T23:49:14Z</t>
+          <t>2026-10-12T21:43:48Z</t>
         </is>
       </c>
     </row>
@@ -3840,7 +3840,7 @@
       </c>
       <c r="S43" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11T23:49:14Z</t>
+          <t>2026-10-12T21:43:48Z</t>
         </is>
       </c>
     </row>
@@ -3929,7 +3929,7 @@
       </c>
       <c r="S44" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11T23:49:14Z</t>
+          <t>2026-10-12T21:43:48Z</t>
         </is>
       </c>
     </row>
@@ -4014,7 +4014,7 @@
       </c>
       <c r="S45" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11T23:49:14Z</t>
+          <t>2026-10-12T21:43:48Z</t>
         </is>
       </c>
     </row>
@@ -4103,7 +4103,7 @@
       </c>
       <c r="S46" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11T23:49:14Z</t>
+          <t>2026-10-12T21:43:48Z</t>
         </is>
       </c>
     </row>
@@ -4192,7 +4192,7 @@
       </c>
       <c r="S47" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11T23:49:14Z</t>
+          <t>2026-10-12T21:43:48Z</t>
         </is>
       </c>
     </row>
@@ -4277,7 +4277,7 @@
       </c>
       <c r="S48" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11T23:49:14Z</t>
+          <t>2026-10-12T21:43:48Z</t>
         </is>
       </c>
     </row>
@@ -4366,7 +4366,7 @@
       </c>
       <c r="S49" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11T23:49:14Z</t>
+          <t>2026-10-12T21:43:48Z</t>
         </is>
       </c>
     </row>
@@ -4455,7 +4455,7 @@
       </c>
       <c r="S50" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11T23:49:14Z</t>
+          <t>2026-10-12T21:43:48Z</t>
         </is>
       </c>
     </row>
@@ -4540,7 +4540,7 @@
       </c>
       <c r="S51" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11T23:49:14Z</t>
+          <t>2026-10-12T21:43:48Z</t>
         </is>
       </c>
     </row>
@@ -4629,7 +4629,7 @@
       </c>
       <c r="S52" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11T23:49:14Z</t>
+          <t>2026-10-12T21:43:48Z</t>
         </is>
       </c>
     </row>
@@ -4718,7 +4718,7 @@
       </c>
       <c r="S53" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11T23:49:14Z</t>
+          <t>2026-10-12T21:43:48Z</t>
         </is>
       </c>
     </row>
@@ -4803,7 +4803,7 @@
       </c>
       <c r="S54" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11T23:49:14Z</t>
+          <t>2026-10-12T21:43:48Z</t>
         </is>
       </c>
     </row>
@@ -4892,7 +4892,7 @@
       </c>
       <c r="S55" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11T23:49:14Z</t>
+          <t>2026-10-12T21:43:48Z</t>
         </is>
       </c>
     </row>
@@ -4981,7 +4981,7 @@
       </c>
       <c r="S56" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11T23:49:14Z</t>
+          <t>2026-10-12T21:43:48Z</t>
         </is>
       </c>
     </row>
@@ -5070,7 +5070,7 @@
       </c>
       <c r="S57" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11T23:49:14Z</t>
+          <t>2026-10-12T21:43:48Z</t>
         </is>
       </c>
     </row>
@@ -5159,7 +5159,7 @@
       </c>
       <c r="S58" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11T23:49:14Z</t>
+          <t>2026-10-12T21:43:48Z</t>
         </is>
       </c>
     </row>
@@ -5248,7 +5248,7 @@
       </c>
       <c r="S59" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11T23:49:14Z</t>
+          <t>2026-10-12T21:43:48Z</t>
         </is>
       </c>
     </row>
@@ -5337,7 +5337,7 @@
       </c>
       <c r="S60" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11T23:49:14Z</t>
+          <t>2026-10-12T21:43:48Z</t>
         </is>
       </c>
     </row>
@@ -5426,7 +5426,7 @@
       </c>
       <c r="S61" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11T23:49:14Z</t>
+          <t>2026-10-12T21:43:48Z</t>
         </is>
       </c>
     </row>
@@ -5515,7 +5515,7 @@
       </c>
       <c r="S62" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11T23:49:14Z</t>
+          <t>2026-10-12T21:43:48Z</t>
         </is>
       </c>
     </row>
@@ -5604,7 +5604,7 @@
       </c>
       <c r="S63" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11T23:49:14Z</t>
+          <t>2026-10-12T21:43:48Z</t>
         </is>
       </c>
     </row>
@@ -5693,7 +5693,7 @@
       </c>
       <c r="S64" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11T23:49:14Z</t>
+          <t>2026-10-12T21:43:48Z</t>
         </is>
       </c>
     </row>
@@ -5782,7 +5782,7 @@
       </c>
       <c r="S65" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11T23:49:14Z</t>
+          <t>2026-10-12T21:43:48Z</t>
         </is>
       </c>
     </row>
@@ -5871,7 +5871,7 @@
       </c>
       <c r="S66" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11T23:49:14Z</t>
+          <t>2026-10-12T21:43:48Z</t>
         </is>
       </c>
     </row>
@@ -5960,7 +5960,7 @@
       </c>
       <c r="S67" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11T23:49:14Z</t>
+          <t>2026-10-12T21:43:48Z</t>
         </is>
       </c>
     </row>
@@ -6045,7 +6045,7 @@
       </c>
       <c r="S68" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11T23:49:14Z</t>
+          <t>2026-10-12T21:43:48Z</t>
         </is>
       </c>
     </row>
@@ -6130,7 +6130,7 @@
       </c>
       <c r="S69" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11T23:49:14Z</t>
+          <t>2026-10-12T21:43:48Z</t>
         </is>
       </c>
     </row>
@@ -6215,7 +6215,7 @@
       </c>
       <c r="S70" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11T23:49:14Z</t>
+          <t>2026-10-12T21:43:48Z</t>
         </is>
       </c>
     </row>
@@ -6300,7 +6300,7 @@
       </c>
       <c r="S71" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11T23:49:14Z</t>
+          <t>2026-10-12T21:43:48Z</t>
         </is>
       </c>
     </row>
@@ -6385,7 +6385,7 @@
       </c>
       <c r="S72" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11T23:49:14Z</t>
+          <t>2026-10-12T21:43:48Z</t>
         </is>
       </c>
     </row>
@@ -6470,7 +6470,7 @@
       </c>
       <c r="S73" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11T23:49:14Z</t>
+          <t>2026-10-12T21:43:48Z</t>
         </is>
       </c>
     </row>
@@ -6555,7 +6555,7 @@
       </c>
       <c r="S74" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11T23:49:14Z</t>
+          <t>2026-10-12T21:43:48Z</t>
         </is>
       </c>
     </row>
@@ -6640,7 +6640,7 @@
       </c>
       <c r="S75" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11T23:49:14Z</t>
+          <t>2026-10-12T21:43:48Z</t>
         </is>
       </c>
     </row>
@@ -6725,7 +6725,7 @@
       </c>
       <c r="S76" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11T23:49:14Z</t>
+          <t>2026-10-12T21:43:48Z</t>
         </is>
       </c>
     </row>
@@ -6810,7 +6810,7 @@
       </c>
       <c r="S77" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11T23:49:14Z</t>
+          <t>2026-10-12T21:43:48Z</t>
         </is>
       </c>
     </row>
@@ -6895,7 +6895,7 @@
       </c>
       <c r="S78" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11T23:49:14Z</t>
+          <t>2026-10-12T21:43:48Z</t>
         </is>
       </c>
     </row>
@@ -6980,7 +6980,7 @@
       </c>
       <c r="S79" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11T23:49:14Z</t>
+          <t>2026-10-12T21:43:48Z</t>
         </is>
       </c>
     </row>
@@ -7065,7 +7065,7 @@
       </c>
       <c r="S80" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11T23:49:14Z</t>
+          <t>2026-10-12T21:43:48Z</t>
         </is>
       </c>
     </row>
@@ -7150,7 +7150,7 @@
       </c>
       <c r="S81" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11T23:49:14Z</t>
+          <t>2026-10-12T21:43:48Z</t>
         </is>
       </c>
     </row>
@@ -7235,7 +7235,7 @@
       </c>
       <c r="S82" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11T23:49:14Z</t>
+          <t>2026-10-12T21:43:48Z</t>
         </is>
       </c>
     </row>
@@ -7320,7 +7320,7 @@
       </c>
       <c r="S83" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11T23:49:14Z</t>
+          <t>2026-10-12T21:43:48Z</t>
         </is>
       </c>
     </row>
@@ -7405,7 +7405,7 @@
       </c>
       <c r="S84" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11T23:49:14Z</t>
+          <t>2026-10-12T21:43:48Z</t>
         </is>
       </c>
     </row>
@@ -7490,7 +7490,7 @@
       </c>
       <c r="S85" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11T23:49:14Z</t>
+          <t>2026-10-12T21:43:48Z</t>
         </is>
       </c>
     </row>
@@ -7575,7 +7575,7 @@
       </c>
       <c r="S86" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11T23:49:14Z</t>
+          <t>2026-10-12T21:43:48Z</t>
         </is>
       </c>
     </row>
@@ -7660,7 +7660,7 @@
       </c>
       <c r="S87" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11T23:49:14Z</t>
+          <t>2026-10-12T21:43:48Z</t>
         </is>
       </c>
     </row>
@@ -7745,7 +7745,7 @@
       </c>
       <c r="S88" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11T23:49:14Z</t>
+          <t>2026-10-12T21:43:48Z</t>
         </is>
       </c>
     </row>
@@ -7834,7 +7834,7 @@
       </c>
       <c r="S89" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11T23:49:14Z</t>
+          <t>2026-10-12T21:43:48Z</t>
         </is>
       </c>
     </row>
@@ -7923,7 +7923,7 @@
       </c>
       <c r="S90" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11T23:49:14Z</t>
+          <t>2026-10-12T21:43:48Z</t>
         </is>
       </c>
     </row>
@@ -8008,7 +8008,7 @@
       </c>
       <c r="S91" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11T23:49:14Z</t>
+          <t>2026-10-12T21:43:48Z</t>
         </is>
       </c>
     </row>
@@ -8097,7 +8097,7 @@
       </c>
       <c r="S92" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11T23:49:14Z</t>
+          <t>2026-10-12T21:43:48Z</t>
         </is>
       </c>
     </row>
@@ -8186,7 +8186,7 @@
       </c>
       <c r="S93" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11T23:49:14Z</t>
+          <t>2026-10-12T21:43:48Z</t>
         </is>
       </c>
     </row>
@@ -8271,7 +8271,7 @@
       </c>
       <c r="S94" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11T23:49:14Z</t>
+          <t>2026-10-12T21:43:48Z</t>
         </is>
       </c>
     </row>
@@ -8360,7 +8360,7 @@
       </c>
       <c r="S95" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11T23:49:14Z</t>
+          <t>2026-10-12T21:43:48Z</t>
         </is>
       </c>
     </row>
@@ -8449,7 +8449,7 @@
       </c>
       <c r="S96" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11T23:49:14Z</t>
+          <t>2026-10-12T21:43:48Z</t>
         </is>
       </c>
     </row>
@@ -8534,7 +8534,7 @@
       </c>
       <c r="S97" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11T23:49:14Z</t>
+          <t>2026-10-12T21:43:48Z</t>
         </is>
       </c>
     </row>
@@ -8623,7 +8623,7 @@
       </c>
       <c r="S98" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11T23:49:14Z</t>
+          <t>2026-10-12T21:43:48Z</t>
         </is>
       </c>
     </row>
@@ -8712,7 +8712,7 @@
       </c>
       <c r="S99" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11T23:49:14Z</t>
+          <t>2026-10-12T21:43:48Z</t>
         </is>
       </c>
     </row>
@@ -8797,7 +8797,7 @@
       </c>
       <c r="S100" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11T23:49:14Z</t>
+          <t>2026-10-12T21:43:48Z</t>
         </is>
       </c>
     </row>
@@ -8886,7 +8886,7 @@
       </c>
       <c r="S101" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11T23:49:14Z</t>
+          <t>2026-10-12T21:43:48Z</t>
         </is>
       </c>
     </row>
@@ -8975,7 +8975,7 @@
       </c>
       <c r="S102" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11T23:49:14Z</t>
+          <t>2026-10-12T21:43:48Z</t>
         </is>
       </c>
     </row>
@@ -9060,7 +9060,7 @@
       </c>
       <c r="S103" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11T23:49:14Z</t>
+          <t>2026-10-12T21:43:48Z</t>
         </is>
       </c>
     </row>
@@ -9149,7 +9149,7 @@
       </c>
       <c r="S104" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11T23:49:14Z</t>
+          <t>2026-10-12T21:43:48Z</t>
         </is>
       </c>
     </row>
@@ -9238,7 +9238,7 @@
       </c>
       <c r="S105" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11T23:49:14Z</t>
+          <t>2026-10-12T21:43:48Z</t>
         </is>
       </c>
     </row>
@@ -9323,7 +9323,7 @@
       </c>
       <c r="S106" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11T23:49:14Z</t>
+          <t>2026-10-12T21:43:48Z</t>
         </is>
       </c>
     </row>
@@ -9412,7 +9412,7 @@
       </c>
       <c r="S107" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11T23:49:14Z</t>
+          <t>2026-10-12T21:43:48Z</t>
         </is>
       </c>
     </row>
@@ -9501,7 +9501,7 @@
       </c>
       <c r="S108" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11T23:49:14Z</t>
+          <t>2026-10-12T21:43:48Z</t>
         </is>
       </c>
     </row>
@@ -9586,7 +9586,7 @@
       </c>
       <c r="S109" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11T23:49:14Z</t>
+          <t>2026-10-12T21:43:48Z</t>
         </is>
       </c>
     </row>
@@ -9675,7 +9675,7 @@
       </c>
       <c r="S110" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11T23:49:14Z</t>
+          <t>2026-10-12T21:43:48Z</t>
         </is>
       </c>
     </row>
@@ -9764,7 +9764,7 @@
       </c>
       <c r="S111" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11T23:49:14Z</t>
+          <t>2026-10-12T21:43:48Z</t>
         </is>
       </c>
     </row>
@@ -9849,7 +9849,7 @@
       </c>
       <c r="S112" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11T23:49:14Z</t>
+          <t>2026-10-12T21:43:48Z</t>
         </is>
       </c>
     </row>
@@ -9938,7 +9938,7 @@
       </c>
       <c r="S113" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11T23:49:14Z</t>
+          <t>2026-10-12T21:43:48Z</t>
         </is>
       </c>
     </row>
@@ -10027,7 +10027,7 @@
       </c>
       <c r="S114" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11T23:49:14Z</t>
+          <t>2026-10-12T21:43:48Z</t>
         </is>
       </c>
     </row>
@@ -10112,7 +10112,7 @@
       </c>
       <c r="S115" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11T23:49:14Z</t>
+          <t>2026-10-12T21:43:48Z</t>
         </is>
       </c>
     </row>
@@ -10201,7 +10201,7 @@
       </c>
       <c r="S116" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11T23:49:14Z</t>
+          <t>2026-10-12T21:43:48Z</t>
         </is>
       </c>
     </row>
@@ -10290,7 +10290,7 @@
       </c>
       <c r="S117" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11T23:49:14Z</t>
+          <t>2026-10-12T21:43:48Z</t>
         </is>
       </c>
     </row>
@@ -10379,7 +10379,7 @@
       </c>
       <c r="S118" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11T23:49:14Z</t>
+          <t>2026-10-12T21:43:48Z</t>
         </is>
       </c>
     </row>
@@ -10468,7 +10468,7 @@
       </c>
       <c r="S119" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11T23:49:14Z</t>
+          <t>2026-10-12T21:43:48Z</t>
         </is>
       </c>
     </row>
@@ -10557,7 +10557,7 @@
       </c>
       <c r="S120" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11T23:49:14Z</t>
+          <t>2026-10-12T21:43:48Z</t>
         </is>
       </c>
     </row>
@@ -10646,7 +10646,7 @@
       </c>
       <c r="S121" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11T23:49:14Z</t>
+          <t>2026-10-12T21:43:48Z</t>
         </is>
       </c>
     </row>
@@ -10735,7 +10735,7 @@
       </c>
       <c r="S122" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11T23:49:14Z</t>
+          <t>2026-10-12T21:43:48Z</t>
         </is>
       </c>
     </row>
@@ -10824,7 +10824,7 @@
       </c>
       <c r="S123" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11T23:49:14Z</t>
+          <t>2026-10-12T21:43:48Z</t>
         </is>
       </c>
     </row>
@@ -10913,7 +10913,7 @@
       </c>
       <c r="S124" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11T23:49:14Z</t>
+          <t>2026-10-12T21:43:48Z</t>
         </is>
       </c>
     </row>
@@ -11002,7 +11002,7 @@
       </c>
       <c r="S125" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11T23:49:14Z</t>
+          <t>2026-10-12T21:43:48Z</t>
         </is>
       </c>
     </row>
@@ -11091,7 +11091,7 @@
       </c>
       <c r="S126" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11T23:49:14Z</t>
+          <t>2026-10-12T21:43:48Z</t>
         </is>
       </c>
     </row>
@@ -11180,7 +11180,7 @@
       </c>
       <c r="S127" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11T23:49:14Z</t>
+          <t>2026-10-12T21:43:48Z</t>
         </is>
       </c>
     </row>
@@ -11269,7 +11269,7 @@
       </c>
       <c r="S128" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11T23:49:14Z</t>
+          <t>2026-10-12T21:43:48Z</t>
         </is>
       </c>
     </row>
@@ -11354,7 +11354,7 @@
       </c>
       <c r="S129" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11T23:49:14Z</t>
+          <t>2026-10-12T21:43:48Z</t>
         </is>
       </c>
     </row>
@@ -11439,7 +11439,7 @@
       </c>
       <c r="S130" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11T23:49:14Z</t>
+          <t>2026-10-12T21:43:48Z</t>
         </is>
       </c>
     </row>
@@ -11524,7 +11524,7 @@
       </c>
       <c r="S131" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11T23:49:14Z</t>
+          <t>2026-10-12T21:43:48Z</t>
         </is>
       </c>
     </row>
@@ -11609,7 +11609,7 @@
       </c>
       <c r="S132" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11T23:49:14Z</t>
+          <t>2026-10-12T21:43:48Z</t>
         </is>
       </c>
     </row>
@@ -11694,7 +11694,7 @@
       </c>
       <c r="S133" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11T23:49:14Z</t>
+          <t>2026-10-12T21:43:48Z</t>
         </is>
       </c>
     </row>
@@ -11779,7 +11779,7 @@
       </c>
       <c r="S134" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11T23:49:14Z</t>
+          <t>2026-10-12T21:43:48Z</t>
         </is>
       </c>
     </row>
@@ -11864,7 +11864,7 @@
       </c>
       <c r="S135" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11T23:49:14Z</t>
+          <t>2026-10-12T21:43:48Z</t>
         </is>
       </c>
     </row>
@@ -11949,7 +11949,7 @@
       </c>
       <c r="S136" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11T23:49:14Z</t>
+          <t>2026-10-12T21:43:48Z</t>
         </is>
       </c>
     </row>
@@ -12034,7 +12034,7 @@
       </c>
       <c r="S137" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11T23:49:14Z</t>
+          <t>2026-10-12T21:43:48Z</t>
         </is>
       </c>
     </row>
@@ -12119,7 +12119,7 @@
       </c>
       <c r="S138" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11T23:49:14Z</t>
+          <t>2026-10-12T21:43:48Z</t>
         </is>
       </c>
     </row>
@@ -12204,7 +12204,7 @@
       </c>
       <c r="S139" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11T23:49:14Z</t>
+          <t>2026-10-12T21:43:48Z</t>
         </is>
       </c>
     </row>
@@ -12289,7 +12289,7 @@
       </c>
       <c r="S140" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11T23:49:14Z</t>
+          <t>2026-10-12T21:43:48Z</t>
         </is>
       </c>
     </row>
@@ -12374,7 +12374,7 @@
       </c>
       <c r="S141" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11T23:49:14Z</t>
+          <t>2026-10-12T21:43:48Z</t>
         </is>
       </c>
     </row>
@@ -12459,7 +12459,7 @@
       </c>
       <c r="S142" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11T23:49:14Z</t>
+          <t>2026-10-12T21:43:48Z</t>
         </is>
       </c>
     </row>
@@ -12544,7 +12544,7 @@
       </c>
       <c r="S143" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11T23:49:14Z</t>
+          <t>2026-10-12T21:43:48Z</t>
         </is>
       </c>
     </row>
@@ -12629,7 +12629,7 @@
       </c>
       <c r="S144" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11T23:49:14Z</t>
+          <t>2026-10-12T21:43:48Z</t>
         </is>
       </c>
     </row>
@@ -12714,7 +12714,7 @@
       </c>
       <c r="S145" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11T23:49:14Z</t>
+          <t>2026-10-12T21:43:48Z</t>
         </is>
       </c>
     </row>
@@ -12799,7 +12799,7 @@
       </c>
       <c r="S146" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11T23:49:14Z</t>
+          <t>2026-10-12T21:43:48Z</t>
         </is>
       </c>
     </row>
@@ -12884,7 +12884,7 @@
       </c>
       <c r="S147" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11T23:49:14Z</t>
+          <t>2026-10-12T21:43:48Z</t>
         </is>
       </c>
     </row>
@@ -12969,7 +12969,7 @@
       </c>
       <c r="S148" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11T23:49:14Z</t>
+          <t>2026-10-12T21:43:48Z</t>
         </is>
       </c>
     </row>
@@ -13054,7 +13054,7 @@
       </c>
       <c r="S149" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11T23:49:14Z</t>
+          <t>2026-10-12T21:43:48Z</t>
         </is>
       </c>
     </row>
@@ -13143,7 +13143,7 @@
       </c>
       <c r="S150" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11T23:49:14Z</t>
+          <t>2026-10-12T21:43:48Z</t>
         </is>
       </c>
     </row>
@@ -13232,7 +13232,7 @@
       </c>
       <c r="S151" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11T23:49:14Z</t>
+          <t>2026-10-12T21:43:48Z</t>
         </is>
       </c>
     </row>
@@ -13317,7 +13317,7 @@
       </c>
       <c r="S152" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11T23:49:14Z</t>
+          <t>2026-10-12T21:43:48Z</t>
         </is>
       </c>
     </row>
@@ -13406,7 +13406,7 @@
       </c>
       <c r="S153" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11T23:49:14Z</t>
+          <t>2026-10-12T21:43:48Z</t>
         </is>
       </c>
     </row>
@@ -13495,7 +13495,7 @@
       </c>
       <c r="S154" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11T23:49:14Z</t>
+          <t>2026-10-12T21:43:48Z</t>
         </is>
       </c>
     </row>
@@ -13580,7 +13580,7 @@
       </c>
       <c r="S155" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11T23:49:14Z</t>
+          <t>2026-10-12T21:43:48Z</t>
         </is>
       </c>
     </row>
@@ -13669,7 +13669,7 @@
       </c>
       <c r="S156" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11T23:49:14Z</t>
+          <t>2026-10-12T21:43:48Z</t>
         </is>
       </c>
     </row>
@@ -13758,7 +13758,7 @@
       </c>
       <c r="S157" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11T23:49:14Z</t>
+          <t>2026-10-12T21:43:48Z</t>
         </is>
       </c>
     </row>
@@ -13843,7 +13843,7 @@
       </c>
       <c r="S158" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11T23:49:14Z</t>
+          <t>2026-10-12T21:43:48Z</t>
         </is>
       </c>
     </row>
@@ -13932,7 +13932,7 @@
       </c>
       <c r="S159" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11T23:49:14Z</t>
+          <t>2026-10-12T21:43:48Z</t>
         </is>
       </c>
     </row>
@@ -14021,7 +14021,7 @@
       </c>
       <c r="S160" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11T23:49:14Z</t>
+          <t>2026-10-12T21:43:48Z</t>
         </is>
       </c>
     </row>
@@ -14106,7 +14106,7 @@
       </c>
       <c r="S161" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11T23:49:14Z</t>
+          <t>2026-10-12T21:43:48Z</t>
         </is>
       </c>
     </row>
@@ -14195,7 +14195,7 @@
       </c>
       <c r="S162" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11T23:49:14Z</t>
+          <t>2026-10-12T21:43:48Z</t>
         </is>
       </c>
     </row>
@@ -14284,7 +14284,7 @@
       </c>
       <c r="S163" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11T23:49:14Z</t>
+          <t>2026-10-12T21:43:48Z</t>
         </is>
       </c>
     </row>
@@ -14369,7 +14369,7 @@
       </c>
       <c r="S164" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11T23:49:14Z</t>
+          <t>2026-10-12T21:43:48Z</t>
         </is>
       </c>
     </row>
@@ -14458,7 +14458,7 @@
       </c>
       <c r="S165" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11T23:49:14Z</t>
+          <t>2026-10-12T21:43:48Z</t>
         </is>
       </c>
     </row>
@@ -14547,7 +14547,7 @@
       </c>
       <c r="S166" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11T23:49:14Z</t>
+          <t>2026-10-12T21:43:48Z</t>
         </is>
       </c>
     </row>
@@ -14632,7 +14632,7 @@
       </c>
       <c r="S167" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11T23:49:14Z</t>
+          <t>2026-10-12T21:43:48Z</t>
         </is>
       </c>
     </row>
@@ -14721,7 +14721,7 @@
       </c>
       <c r="S168" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11T23:49:14Z</t>
+          <t>2026-10-12T21:43:48Z</t>
         </is>
       </c>
     </row>
@@ -14810,7 +14810,7 @@
       </c>
       <c r="S169" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11T23:49:14Z</t>
+          <t>2026-10-12T21:43:48Z</t>
         </is>
       </c>
     </row>
@@ -14895,7 +14895,7 @@
       </c>
       <c r="S170" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11T23:49:14Z</t>
+          <t>2026-10-12T21:43:48Z</t>
         </is>
       </c>
     </row>
@@ -14984,7 +14984,7 @@
       </c>
       <c r="S171" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11T23:49:14Z</t>
+          <t>2026-10-12T21:43:48Z</t>
         </is>
       </c>
     </row>
@@ -15073,7 +15073,7 @@
       </c>
       <c r="S172" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11T23:49:14Z</t>
+          <t>2026-10-12T21:43:48Z</t>
         </is>
       </c>
     </row>
@@ -15158,7 +15158,7 @@
       </c>
       <c r="S173" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11T23:49:14Z</t>
+          <t>2026-10-12T21:43:48Z</t>
         </is>
       </c>
     </row>
@@ -15247,7 +15247,7 @@
       </c>
       <c r="S174" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11T23:49:14Z</t>
+          <t>2026-10-12T21:43:48Z</t>
         </is>
       </c>
     </row>
@@ -15336,7 +15336,7 @@
       </c>
       <c r="S175" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11T23:49:14Z</t>
+          <t>2026-10-12T21:43:48Z</t>
         </is>
       </c>
     </row>
@@ -15421,7 +15421,7 @@
       </c>
       <c r="S176" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11T23:49:14Z</t>
+          <t>2026-10-12T21:43:48Z</t>
         </is>
       </c>
     </row>
@@ -15510,7 +15510,7 @@
       </c>
       <c r="S177" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11T23:49:14Z</t>
+          <t>2026-10-12T21:43:48Z</t>
         </is>
       </c>
     </row>
@@ -15599,7 +15599,7 @@
       </c>
       <c r="S178" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11T23:49:14Z</t>
+          <t>2026-10-12T21:43:48Z</t>
         </is>
       </c>
     </row>
@@ -15688,7 +15688,7 @@
       </c>
       <c r="S179" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11T23:49:14Z</t>
+          <t>2026-10-12T21:43:48Z</t>
         </is>
       </c>
     </row>
@@ -15777,7 +15777,7 @@
       </c>
       <c r="S180" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11T23:49:14Z</t>
+          <t>2026-10-12T21:43:48Z</t>
         </is>
       </c>
     </row>
@@ -15866,7 +15866,7 @@
       </c>
       <c r="S181" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11T23:49:14Z</t>
+          <t>2026-10-12T21:43:48Z</t>
         </is>
       </c>
     </row>
@@ -15955,7 +15955,7 @@
       </c>
       <c r="S182" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11T23:49:14Z</t>
+          <t>2026-10-12T21:43:48Z</t>
         </is>
       </c>
     </row>
@@ -16044,7 +16044,7 @@
       </c>
       <c r="S183" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11T23:49:14Z</t>
+          <t>2026-10-12T21:43:48Z</t>
         </is>
       </c>
     </row>
@@ -16133,7 +16133,7 @@
       </c>
       <c r="S184" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11T23:49:14Z</t>
+          <t>2026-10-12T21:43:48Z</t>
         </is>
       </c>
     </row>
@@ -16222,7 +16222,7 @@
       </c>
       <c r="S185" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11T23:49:14Z</t>
+          <t>2026-10-12T21:43:48Z</t>
         </is>
       </c>
     </row>
@@ -16311,7 +16311,7 @@
       </c>
       <c r="S186" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11T23:49:14Z</t>
+          <t>2026-10-12T21:43:48Z</t>
         </is>
       </c>
     </row>
@@ -16400,7 +16400,7 @@
       </c>
       <c r="S187" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11T23:49:14Z</t>
+          <t>2026-10-12T21:43:48Z</t>
         </is>
       </c>
     </row>
@@ -16489,7 +16489,7 @@
       </c>
       <c r="S188" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11T23:49:14Z</t>
+          <t>2026-10-12T21:43:48Z</t>
         </is>
       </c>
     </row>
@@ -16578,7 +16578,7 @@
       </c>
       <c r="S189" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11T23:49:14Z</t>
+          <t>2026-10-12T21:43:48Z</t>
         </is>
       </c>
     </row>
@@ -16663,7 +16663,7 @@
       </c>
       <c r="S190" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11T23:49:14Z</t>
+          <t>2026-10-12T21:43:48Z</t>
         </is>
       </c>
     </row>
@@ -16748,7 +16748,7 @@
       </c>
       <c r="S191" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11T23:49:14Z</t>
+          <t>2026-10-12T21:43:48Z</t>
         </is>
       </c>
     </row>
@@ -16833,7 +16833,7 @@
       </c>
       <c r="S192" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11T23:49:14Z</t>
+          <t>2026-10-12T21:43:48Z</t>
         </is>
       </c>
     </row>
@@ -16918,7 +16918,7 @@
       </c>
       <c r="S193" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11T23:49:14Z</t>
+          <t>2026-10-12T21:43:48Z</t>
         </is>
       </c>
     </row>
@@ -17003,7 +17003,7 @@
       </c>
       <c r="S194" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11T23:49:14Z</t>
+          <t>2026-10-12T21:43:48Z</t>
         </is>
       </c>
     </row>
@@ -17088,7 +17088,7 @@
       </c>
       <c r="S195" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11T23:49:14Z</t>
+          <t>2026-10-12T21:43:48Z</t>
         </is>
       </c>
     </row>
@@ -17173,7 +17173,7 @@
       </c>
       <c r="S196" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11T23:49:14Z</t>
+          <t>2026-10-12T21:43:48Z</t>
         </is>
       </c>
     </row>
@@ -17258,7 +17258,7 @@
       </c>
       <c r="S197" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11T23:49:14Z</t>
+          <t>2026-10-12T21:43:48Z</t>
         </is>
       </c>
     </row>
@@ -17343,7 +17343,7 @@
       </c>
       <c r="S198" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11T23:49:14Z</t>
+          <t>2026-10-12T21:43:48Z</t>
         </is>
       </c>
     </row>
@@ -17428,7 +17428,7 @@
       </c>
       <c r="S199" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11T23:49:14Z</t>
+          <t>2026-10-12T21:43:48Z</t>
         </is>
       </c>
     </row>
@@ -17513,7 +17513,7 @@
       </c>
       <c r="S200" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11T23:49:14Z</t>
+          <t>2026-10-12T21:43:48Z</t>
         </is>
       </c>
     </row>
@@ -17598,7 +17598,7 @@
       </c>
       <c r="S201" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11T23:49:14Z</t>
+          <t>2026-10-12T21:43:48Z</t>
         </is>
       </c>
     </row>
@@ -17683,7 +17683,7 @@
       </c>
       <c r="S202" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11T23:49:14Z</t>
+          <t>2026-10-12T21:43:48Z</t>
         </is>
       </c>
     </row>
@@ -17768,7 +17768,7 @@
       </c>
       <c r="S203" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11T23:49:14Z</t>
+          <t>2026-10-12T21:43:48Z</t>
         </is>
       </c>
     </row>
@@ -17853,7 +17853,7 @@
       </c>
       <c r="S204" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11T23:49:14Z</t>
+          <t>2026-10-12T21:43:48Z</t>
         </is>
       </c>
     </row>
@@ -17938,7 +17938,7 @@
       </c>
       <c r="S205" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11T23:49:14Z</t>
+          <t>2026-10-12T21:43:48Z</t>
         </is>
       </c>
     </row>
@@ -18023,7 +18023,7 @@
       </c>
       <c r="S206" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11T23:49:14Z</t>
+          <t>2026-10-12T21:43:48Z</t>
         </is>
       </c>
     </row>
@@ -18108,7 +18108,7 @@
       </c>
       <c r="S207" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11T23:49:14Z</t>
+          <t>2026-10-12T21:43:48Z</t>
         </is>
       </c>
     </row>
@@ -18193,7 +18193,7 @@
       </c>
       <c r="S208" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11T23:49:14Z</t>
+          <t>2026-10-12T21:43:48Z</t>
         </is>
       </c>
     </row>
@@ -18278,7 +18278,7 @@
       </c>
       <c r="S209" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11T23:49:14Z</t>
+          <t>2026-10-12T21:43:48Z</t>
         </is>
       </c>
     </row>
@@ -18363,7 +18363,7 @@
       </c>
       <c r="S210" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11T23:49:14Z</t>
+          <t>2026-10-12T21:43:48Z</t>
         </is>
       </c>
     </row>
@@ -18452,7 +18452,7 @@
       </c>
       <c r="S211" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11T23:49:14Z</t>
+          <t>2026-10-12T21:43:48Z</t>
         </is>
       </c>
     </row>
@@ -18541,7 +18541,7 @@
       </c>
       <c r="S212" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11T23:49:14Z</t>
+          <t>2026-10-12T21:43:48Z</t>
         </is>
       </c>
     </row>
@@ -18626,7 +18626,7 @@
       </c>
       <c r="S213" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11T23:49:14Z</t>
+          <t>2026-10-12T21:43:48Z</t>
         </is>
       </c>
     </row>
@@ -18715,7 +18715,7 @@
       </c>
       <c r="S214" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11T23:49:14Z</t>
+          <t>2026-10-12T21:43:48Z</t>
         </is>
       </c>
     </row>
@@ -18804,7 +18804,7 @@
       </c>
       <c r="S215" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11T23:49:14Z</t>
+          <t>2026-10-12T21:43:48Z</t>
         </is>
       </c>
     </row>
@@ -18889,7 +18889,7 @@
       </c>
       <c r="S216" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11T23:49:14Z</t>
+          <t>2026-10-12T21:43:48Z</t>
         </is>
       </c>
     </row>
@@ -18978,7 +18978,7 @@
       </c>
       <c r="S217" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11T23:49:14Z</t>
+          <t>2026-10-12T21:43:48Z</t>
         </is>
       </c>
     </row>
@@ -19067,7 +19067,7 @@
       </c>
       <c r="S218" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11T23:49:14Z</t>
+          <t>2026-10-12T21:43:48Z</t>
         </is>
       </c>
     </row>
@@ -19152,7 +19152,7 @@
       </c>
       <c r="S219" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11T23:49:14Z</t>
+          <t>2026-10-12T21:43:48Z</t>
         </is>
       </c>
     </row>
@@ -19241,7 +19241,7 @@
       </c>
       <c r="S220" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11T23:49:14Z</t>
+          <t>2026-10-12T21:43:48Z</t>
         </is>
       </c>
     </row>
@@ -19330,7 +19330,7 @@
       </c>
       <c r="S221" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11T23:49:14Z</t>
+          <t>2026-10-12T21:43:48Z</t>
         </is>
       </c>
     </row>
@@ -19415,7 +19415,7 @@
       </c>
       <c r="S222" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11T23:49:14Z</t>
+          <t>2026-10-12T21:43:48Z</t>
         </is>
       </c>
     </row>
@@ -19504,7 +19504,7 @@
       </c>
       <c r="S223" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11T23:49:14Z</t>
+          <t>2026-10-12T21:43:48Z</t>
         </is>
       </c>
     </row>
@@ -19593,7 +19593,7 @@
       </c>
       <c r="S224" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11T23:49:14Z</t>
+          <t>2026-10-12T21:43:48Z</t>
         </is>
       </c>
     </row>
@@ -19678,7 +19678,7 @@
       </c>
       <c r="S225" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11T23:49:14Z</t>
+          <t>2026-10-12T21:43:48Z</t>
         </is>
       </c>
     </row>
@@ -19767,7 +19767,7 @@
       </c>
       <c r="S226" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11T23:49:14Z</t>
+          <t>2026-10-12T21:43:48Z</t>
         </is>
       </c>
     </row>
@@ -19856,7 +19856,7 @@
       </c>
       <c r="S227" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11T23:49:14Z</t>
+          <t>2026-10-12T21:43:48Z</t>
         </is>
       </c>
     </row>
@@ -19941,7 +19941,7 @@
       </c>
       <c r="S228" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11T23:49:14Z</t>
+          <t>2026-10-12T21:43:48Z</t>
         </is>
       </c>
     </row>
@@ -20030,7 +20030,7 @@
       </c>
       <c r="S229" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11T23:49:14Z</t>
+          <t>2026-10-12T21:43:48Z</t>
         </is>
       </c>
     </row>
@@ -20119,7 +20119,7 @@
       </c>
       <c r="S230" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11T23:49:14Z</t>
+          <t>2026-10-12T21:43:48Z</t>
         </is>
       </c>
     </row>
@@ -20204,7 +20204,7 @@
       </c>
       <c r="S231" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11T23:49:14Z</t>
+          <t>2026-10-12T21:43:48Z</t>
         </is>
       </c>
     </row>
@@ -20293,7 +20293,7 @@
       </c>
       <c r="S232" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11T23:49:14Z</t>
+          <t>2026-10-12T21:43:48Z</t>
         </is>
       </c>
     </row>
@@ -20382,7 +20382,7 @@
       </c>
       <c r="S233" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11T23:49:14Z</t>
+          <t>2026-10-12T21:43:48Z</t>
         </is>
       </c>
     </row>
@@ -20467,7 +20467,7 @@
       </c>
       <c r="S234" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11T23:49:14Z</t>
+          <t>2026-10-12T21:43:48Z</t>
         </is>
       </c>
     </row>
@@ -20556,7 +20556,7 @@
       </c>
       <c r="S235" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11T23:49:14Z</t>
+          <t>2026-10-12T21:43:48Z</t>
         </is>
       </c>
     </row>
@@ -20645,7 +20645,7 @@
       </c>
       <c r="S236" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11T23:49:14Z</t>
+          <t>2026-10-12T21:43:48Z</t>
         </is>
       </c>
     </row>
@@ -20730,7 +20730,7 @@
       </c>
       <c r="S237" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11T23:49:14Z</t>
+          <t>2026-10-12T21:43:48Z</t>
         </is>
       </c>
     </row>
@@ -20819,7 +20819,7 @@
       </c>
       <c r="S238" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11T23:49:14Z</t>
+          <t>2026-10-12T21:43:48Z</t>
         </is>
       </c>
     </row>
@@ -20908,7 +20908,7 @@
       </c>
       <c r="S239" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11T23:49:14Z</t>
+          <t>2026-10-12T21:43:48Z</t>
         </is>
       </c>
     </row>
@@ -20997,7 +20997,7 @@
       </c>
       <c r="S240" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11T23:49:14Z</t>
+          <t>2026-10-12T21:43:48Z</t>
         </is>
       </c>
     </row>
@@ -21086,7 +21086,7 @@
       </c>
       <c r="S241" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11T23:49:14Z</t>
+          <t>2026-10-12T21:43:48Z</t>
         </is>
       </c>
     </row>
@@ -21175,7 +21175,7 @@
       </c>
       <c r="S242" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11T23:49:14Z</t>
+          <t>2026-10-12T21:43:48Z</t>
         </is>
       </c>
     </row>
@@ -21264,7 +21264,7 @@
       </c>
       <c r="S243" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11T23:49:14Z</t>
+          <t>2026-10-12T21:43:48Z</t>
         </is>
       </c>
     </row>
@@ -21353,7 +21353,7 @@
       </c>
       <c r="S244" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11T23:49:14Z</t>
+          <t>2026-10-12T21:43:48Z</t>
         </is>
       </c>
     </row>
@@ -21442,7 +21442,7 @@
       </c>
       <c r="S245" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11T23:49:14Z</t>
+          <t>2026-10-12T21:43:48Z</t>
         </is>
       </c>
     </row>
@@ -21531,7 +21531,7 @@
       </c>
       <c r="S246" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11T23:49:14Z</t>
+          <t>2026-10-12T21:43:48Z</t>
         </is>
       </c>
     </row>
@@ -21620,7 +21620,7 @@
       </c>
       <c r="S247" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11T23:49:14Z</t>
+          <t>2026-10-12T21:43:48Z</t>
         </is>
       </c>
     </row>
@@ -21709,7 +21709,7 @@
       </c>
       <c r="S248" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11T23:49:14Z</t>
+          <t>2026-10-12T21:43:48Z</t>
         </is>
       </c>
     </row>
@@ -21798,7 +21798,7 @@
       </c>
       <c r="S249" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11T23:49:14Z</t>
+          <t>2026-10-12T21:43:48Z</t>
         </is>
       </c>
     </row>
@@ -21887,7 +21887,7 @@
       </c>
       <c r="S250" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11T23:49:14Z</t>
+          <t>2026-10-12T21:43:48Z</t>
         </is>
       </c>
     </row>
@@ -22019,7 +22019,7 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11T23:49:14Z</t>
+          <t>2026-10-12T21:43:48Z</t>
         </is>
       </c>
     </row>
@@ -22099,7 +22099,7 @@
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>{"dataset_id": "bcv_pib_sector_institucional_anual", "title": "Producto interno bruto por sector institucional anual", "table": "Variaciones porcentuales", "source_file": "5_2_1_si_anual.xlsx", "base": "2007", "price_type": "Precios constantes", "measure": "Variación porcentual interanual", "frequency": "Anual", "period": "2025", "year": 2025, "quarter": null, "classification": "Sector institucional", "component": "Impuestos netos sobre los productos", "value": 10.600260421283764, "unit": "Porcentaje", "status": "Preliminar", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/cuentas_macroeconomicas/5_2_1_si_anual.xlsx", "fetched_at": "2026-10-11T23:49:14Z"}</t>
+          <t>{"dataset_id": "bcv_pib_sector_institucional_anual", "title": "Producto interno bruto por sector institucional anual", "table": "Variaciones porcentuales", "source_file": "5_2_1_si_anual.xlsx", "base": "2007", "price_type": "Precios constantes", "measure": "Variación porcentual interanual", "frequency": "Anual", "period": "2025", "year": 2025, "quarter": null, "classification": "Sector institucional", "component": "Impuestos netos sobre los productos", "value": 10.600260421283764, "unit": "Porcentaje", "status": "Preliminar", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/cuentas_macroeconomicas/5_2_1_si_anual.xlsx", "fetched_at": "2026-10-12T21:43:48Z"}</t>
         </is>
       </c>
     </row>

--- a/assets/data/bcv/excel/ove_bcv_pib_sector_institucional_anual.xlsx
+++ b/assets/data/bcv/excel/ove_bcv_pib_sector_institucional_anual.xlsx
@@ -736,7 +736,7 @@
       </c>
       <c r="S7" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12T21:43:48Z</t>
+          <t>2026-10-13T02:10:28Z</t>
         </is>
       </c>
     </row>
@@ -821,7 +821,7 @@
       </c>
       <c r="S8" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12T21:43:48Z</t>
+          <t>2026-10-13T02:10:28Z</t>
         </is>
       </c>
     </row>
@@ -906,7 +906,7 @@
       </c>
       <c r="S9" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12T21:43:48Z</t>
+          <t>2026-10-13T02:10:28Z</t>
         </is>
       </c>
     </row>
@@ -991,7 +991,7 @@
       </c>
       <c r="S10" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12T21:43:48Z</t>
+          <t>2026-10-13T02:10:28Z</t>
         </is>
       </c>
     </row>
@@ -1076,7 +1076,7 @@
       </c>
       <c r="S11" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12T21:43:48Z</t>
+          <t>2026-10-13T02:10:28Z</t>
         </is>
       </c>
     </row>
@@ -1161,7 +1161,7 @@
       </c>
       <c r="S12" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12T21:43:48Z</t>
+          <t>2026-10-13T02:10:28Z</t>
         </is>
       </c>
     </row>
@@ -1246,7 +1246,7 @@
       </c>
       <c r="S13" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12T21:43:48Z</t>
+          <t>2026-10-13T02:10:28Z</t>
         </is>
       </c>
     </row>
@@ -1331,7 +1331,7 @@
       </c>
       <c r="S14" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12T21:43:48Z</t>
+          <t>2026-10-13T02:10:28Z</t>
         </is>
       </c>
     </row>
@@ -1416,7 +1416,7 @@
       </c>
       <c r="S15" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12T21:43:48Z</t>
+          <t>2026-10-13T02:10:28Z</t>
         </is>
       </c>
     </row>
@@ -1501,7 +1501,7 @@
       </c>
       <c r="S16" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12T21:43:48Z</t>
+          <t>2026-10-13T02:10:28Z</t>
         </is>
       </c>
     </row>
@@ -1586,7 +1586,7 @@
       </c>
       <c r="S17" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12T21:43:48Z</t>
+          <t>2026-10-13T02:10:28Z</t>
         </is>
       </c>
     </row>
@@ -1671,7 +1671,7 @@
       </c>
       <c r="S18" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12T21:43:48Z</t>
+          <t>2026-10-13T02:10:28Z</t>
         </is>
       </c>
     </row>
@@ -1756,7 +1756,7 @@
       </c>
       <c r="S19" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12T21:43:48Z</t>
+          <t>2026-10-13T02:10:28Z</t>
         </is>
       </c>
     </row>
@@ -1841,7 +1841,7 @@
       </c>
       <c r="S20" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12T21:43:48Z</t>
+          <t>2026-10-13T02:10:28Z</t>
         </is>
       </c>
     </row>
@@ -1926,7 +1926,7 @@
       </c>
       <c r="S21" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12T21:43:48Z</t>
+          <t>2026-10-13T02:10:28Z</t>
         </is>
       </c>
     </row>
@@ -2011,7 +2011,7 @@
       </c>
       <c r="S22" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12T21:43:48Z</t>
+          <t>2026-10-13T02:10:28Z</t>
         </is>
       </c>
     </row>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="S23" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12T21:43:48Z</t>
+          <t>2026-10-13T02:10:28Z</t>
         </is>
       </c>
     </row>
@@ -2181,7 +2181,7 @@
       </c>
       <c r="S24" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12T21:43:48Z</t>
+          <t>2026-10-13T02:10:28Z</t>
         </is>
       </c>
     </row>
@@ -2266,7 +2266,7 @@
       </c>
       <c r="S25" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12T21:43:48Z</t>
+          <t>2026-10-13T02:10:28Z</t>
         </is>
       </c>
     </row>
@@ -2351,7 +2351,7 @@
       </c>
       <c r="S26" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12T21:43:48Z</t>
+          <t>2026-10-13T02:10:28Z</t>
         </is>
       </c>
     </row>
@@ -2436,7 +2436,7 @@
       </c>
       <c r="S27" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12T21:43:48Z</t>
+          <t>2026-10-13T02:10:28Z</t>
         </is>
       </c>
     </row>
@@ -2525,7 +2525,7 @@
       </c>
       <c r="S28" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12T21:43:48Z</t>
+          <t>2026-10-13T02:10:28Z</t>
         </is>
       </c>
     </row>
@@ -2614,7 +2614,7 @@
       </c>
       <c r="S29" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12T21:43:48Z</t>
+          <t>2026-10-13T02:10:28Z</t>
         </is>
       </c>
     </row>
@@ -2699,7 +2699,7 @@
       </c>
       <c r="S30" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12T21:43:48Z</t>
+          <t>2026-10-13T02:10:28Z</t>
         </is>
       </c>
     </row>
@@ -2788,7 +2788,7 @@
       </c>
       <c r="S31" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12T21:43:48Z</t>
+          <t>2026-10-13T02:10:28Z</t>
         </is>
       </c>
     </row>
@@ -2877,7 +2877,7 @@
       </c>
       <c r="S32" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12T21:43:48Z</t>
+          <t>2026-10-13T02:10:28Z</t>
         </is>
       </c>
     </row>
@@ -2962,7 +2962,7 @@
       </c>
       <c r="S33" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12T21:43:48Z</t>
+          <t>2026-10-13T02:10:28Z</t>
         </is>
       </c>
     </row>
@@ -3051,7 +3051,7 @@
       </c>
       <c r="S34" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12T21:43:48Z</t>
+          <t>2026-10-13T02:10:28Z</t>
         </is>
       </c>
     </row>
@@ -3140,7 +3140,7 @@
       </c>
       <c r="S35" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12T21:43:48Z</t>
+          <t>2026-10-13T02:10:28Z</t>
         </is>
       </c>
     </row>
@@ -3225,7 +3225,7 @@
       </c>
       <c r="S36" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12T21:43:48Z</t>
+          <t>2026-10-13T02:10:28Z</t>
         </is>
       </c>
     </row>
@@ -3314,7 +3314,7 @@
       </c>
       <c r="S37" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12T21:43:48Z</t>
+          <t>2026-10-13T02:10:28Z</t>
         </is>
       </c>
     </row>
@@ -3403,7 +3403,7 @@
       </c>
       <c r="S38" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12T21:43:48Z</t>
+          <t>2026-10-13T02:10:28Z</t>
         </is>
       </c>
     </row>
@@ -3488,7 +3488,7 @@
       </c>
       <c r="S39" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12T21:43:48Z</t>
+          <t>2026-10-13T02:10:28Z</t>
         </is>
       </c>
     </row>
@@ -3577,7 +3577,7 @@
       </c>
       <c r="S40" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12T21:43:48Z</t>
+          <t>2026-10-13T02:10:28Z</t>
         </is>
       </c>
     </row>
@@ -3666,7 +3666,7 @@
       </c>
       <c r="S41" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12T21:43:48Z</t>
+          <t>2026-10-13T02:10:28Z</t>
         </is>
       </c>
     </row>
@@ -3751,7 +3751,7 @@
       </c>
       <c r="S42" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12T21:43:48Z</t>
+          <t>2026-10-13T02:10:28Z</t>
         </is>
       </c>
     </row>
@@ -3840,7 +3840,7 @@
       </c>
       <c r="S43" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12T21:43:48Z</t>
+          <t>2026-10-13T02:10:28Z</t>
         </is>
       </c>
     </row>
@@ -3929,7 +3929,7 @@
       </c>
       <c r="S44" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12T21:43:48Z</t>
+          <t>2026-10-13T02:10:28Z</t>
         </is>
       </c>
     </row>
@@ -4014,7 +4014,7 @@
       </c>
       <c r="S45" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12T21:43:48Z</t>
+          <t>2026-10-13T02:10:28Z</t>
         </is>
       </c>
     </row>
@@ -4103,7 +4103,7 @@
       </c>
       <c r="S46" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12T21:43:48Z</t>
+          <t>2026-10-13T02:10:28Z</t>
         </is>
       </c>
     </row>
@@ -4192,7 +4192,7 @@
       </c>
       <c r="S47" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12T21:43:48Z</t>
+          <t>2026-10-13T02:10:28Z</t>
         </is>
       </c>
     </row>
@@ -4277,7 +4277,7 @@
       </c>
       <c r="S48" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12T21:43:48Z</t>
+          <t>2026-10-13T02:10:28Z</t>
         </is>
       </c>
     </row>
@@ -4366,7 +4366,7 @@
       </c>
       <c r="S49" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12T21:43:48Z</t>
+          <t>2026-10-13T02:10:28Z</t>
         </is>
       </c>
     </row>
@@ -4455,7 +4455,7 @@
       </c>
       <c r="S50" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12T21:43:48Z</t>
+          <t>2026-10-13T02:10:28Z</t>
         </is>
       </c>
     </row>
@@ -4540,7 +4540,7 @@
       </c>
       <c r="S51" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12T21:43:48Z</t>
+          <t>2026-10-13T02:10:28Z</t>
         </is>
       </c>
     </row>
@@ -4629,7 +4629,7 @@
       </c>
       <c r="S52" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12T21:43:48Z</t>
+          <t>2026-10-13T02:10:28Z</t>
         </is>
       </c>
     </row>
@@ -4718,7 +4718,7 @@
       </c>
       <c r="S53" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12T21:43:48Z</t>
+          <t>2026-10-13T02:10:28Z</t>
         </is>
       </c>
     </row>
@@ -4803,7 +4803,7 @@
       </c>
       <c r="S54" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12T21:43:48Z</t>
+          <t>2026-10-13T02:10:28Z</t>
         </is>
       </c>
     </row>
@@ -4892,7 +4892,7 @@
       </c>
       <c r="S55" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12T21:43:48Z</t>
+          <t>2026-10-13T02:10:28Z</t>
         </is>
       </c>
     </row>
@@ -4981,7 +4981,7 @@
       </c>
       <c r="S56" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12T21:43:48Z</t>
+          <t>2026-10-13T02:10:28Z</t>
         </is>
       </c>
     </row>
@@ -5070,7 +5070,7 @@
       </c>
       <c r="S57" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12T21:43:48Z</t>
+          <t>2026-10-13T02:10:28Z</t>
         </is>
       </c>
     </row>
@@ -5159,7 +5159,7 @@
       </c>
       <c r="S58" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12T21:43:48Z</t>
+          <t>2026-10-13T02:10:28Z</t>
         </is>
       </c>
     </row>
@@ -5248,7 +5248,7 @@
       </c>
       <c r="S59" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12T21:43:48Z</t>
+          <t>2026-10-13T02:10:28Z</t>
         </is>
       </c>
     </row>
@@ -5337,7 +5337,7 @@
       </c>
       <c r="S60" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12T21:43:48Z</t>
+          <t>2026-10-13T02:10:28Z</t>
         </is>
       </c>
     </row>
@@ -5426,7 +5426,7 @@
       </c>
       <c r="S61" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12T21:43:48Z</t>
+          <t>2026-10-13T02:10:28Z</t>
         </is>
       </c>
     </row>
@@ -5515,7 +5515,7 @@
       </c>
       <c r="S62" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12T21:43:48Z</t>
+          <t>2026-10-13T02:10:28Z</t>
         </is>
       </c>
     </row>
@@ -5604,7 +5604,7 @@
       </c>
       <c r="S63" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12T21:43:48Z</t>
+          <t>2026-10-13T02:10:28Z</t>
         </is>
       </c>
     </row>
@@ -5693,7 +5693,7 @@
       </c>
       <c r="S64" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12T21:43:48Z</t>
+          <t>2026-10-13T02:10:28Z</t>
         </is>
       </c>
     </row>
@@ -5782,7 +5782,7 @@
       </c>
       <c r="S65" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12T21:43:48Z</t>
+          <t>2026-10-13T02:10:28Z</t>
         </is>
       </c>
     </row>
@@ -5871,7 +5871,7 @@
       </c>
       <c r="S66" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12T21:43:48Z</t>
+          <t>2026-10-13T02:10:28Z</t>
         </is>
       </c>
     </row>
@@ -5960,7 +5960,7 @@
       </c>
       <c r="S67" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12T21:43:48Z</t>
+          <t>2026-10-13T02:10:28Z</t>
         </is>
       </c>
     </row>
@@ -6045,7 +6045,7 @@
       </c>
       <c r="S68" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12T21:43:48Z</t>
+          <t>2026-10-13T02:10:28Z</t>
         </is>
       </c>
     </row>
@@ -6130,7 +6130,7 @@
       </c>
       <c r="S69" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12T21:43:48Z</t>
+          <t>2026-10-13T02:10:28Z</t>
         </is>
       </c>
     </row>
@@ -6215,7 +6215,7 @@
       </c>
       <c r="S70" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12T21:43:48Z</t>
+          <t>2026-10-13T02:10:28Z</t>
         </is>
       </c>
     </row>
@@ -6300,7 +6300,7 @@
       </c>
       <c r="S71" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12T21:43:48Z</t>
+          <t>2026-10-13T02:10:28Z</t>
         </is>
       </c>
     </row>
@@ -6385,7 +6385,7 @@
       </c>
       <c r="S72" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12T21:43:48Z</t>
+          <t>2026-10-13T02:10:28Z</t>
         </is>
       </c>
     </row>
@@ -6470,7 +6470,7 @@
       </c>
       <c r="S73" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12T21:43:48Z</t>
+          <t>2026-10-13T02:10:28Z</t>
         </is>
       </c>
     </row>
@@ -6555,7 +6555,7 @@
       </c>
       <c r="S74" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12T21:43:48Z</t>
+          <t>2026-10-13T02:10:28Z</t>
         </is>
       </c>
     </row>
@@ -6640,7 +6640,7 @@
       </c>
       <c r="S75" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12T21:43:48Z</t>
+          <t>2026-10-13T02:10:28Z</t>
         </is>
       </c>
     </row>
@@ -6725,7 +6725,7 @@
       </c>
       <c r="S76" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12T21:43:48Z</t>
+          <t>2026-10-13T02:10:28Z</t>
         </is>
       </c>
     </row>
@@ -6810,7 +6810,7 @@
       </c>
       <c r="S77" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12T21:43:48Z</t>
+          <t>2026-10-13T02:10:28Z</t>
         </is>
       </c>
     </row>
@@ -6895,7 +6895,7 @@
       </c>
       <c r="S78" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12T21:43:48Z</t>
+          <t>2026-10-13T02:10:28Z</t>
         </is>
       </c>
     </row>
@@ -6980,7 +6980,7 @@
       </c>
       <c r="S79" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12T21:43:48Z</t>
+          <t>2026-10-13T02:10:28Z</t>
         </is>
       </c>
     </row>
@@ -7065,7 +7065,7 @@
       </c>
       <c r="S80" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12T21:43:48Z</t>
+          <t>2026-10-13T02:10:28Z</t>
         </is>
       </c>
     </row>
@@ -7150,7 +7150,7 @@
       </c>
       <c r="S81" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12T21:43:48Z</t>
+          <t>2026-10-13T02:10:28Z</t>
         </is>
       </c>
     </row>
@@ -7235,7 +7235,7 @@
       </c>
       <c r="S82" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12T21:43:48Z</t>
+          <t>2026-10-13T02:10:28Z</t>
         </is>
       </c>
     </row>
@@ -7320,7 +7320,7 @@
       </c>
       <c r="S83" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12T21:43:48Z</t>
+          <t>2026-10-13T02:10:28Z</t>
         </is>
       </c>
     </row>
@@ -7405,7 +7405,7 @@
       </c>
       <c r="S84" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12T21:43:48Z</t>
+          <t>2026-10-13T02:10:28Z</t>
         </is>
       </c>
     </row>
@@ -7490,7 +7490,7 @@
       </c>
       <c r="S85" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12T21:43:48Z</t>
+          <t>2026-10-13T02:10:28Z</t>
         </is>
       </c>
     </row>
@@ -7575,7 +7575,7 @@
       </c>
       <c r="S86" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12T21:43:48Z</t>
+          <t>2026-10-13T02:10:28Z</t>
         </is>
       </c>
     </row>
@@ -7660,7 +7660,7 @@
       </c>
       <c r="S87" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12T21:43:48Z</t>
+          <t>2026-10-13T02:10:28Z</t>
         </is>
       </c>
     </row>
@@ -7745,7 +7745,7 @@
       </c>
       <c r="S88" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12T21:43:48Z</t>
+          <t>2026-10-13T02:10:28Z</t>
         </is>
       </c>
     </row>
@@ -7834,7 +7834,7 @@
       </c>
       <c r="S89" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12T21:43:48Z</t>
+          <t>2026-10-13T02:10:28Z</t>
         </is>
       </c>
     </row>
@@ -7923,7 +7923,7 @@
       </c>
       <c r="S90" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12T21:43:48Z</t>
+          <t>2026-10-13T02:10:28Z</t>
         </is>
       </c>
     </row>
@@ -8008,7 +8008,7 @@
       </c>
       <c r="S91" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12T21:43:48Z</t>
+          <t>2026-10-13T02:10:28Z</t>
         </is>
       </c>
     </row>
@@ -8097,7 +8097,7 @@
       </c>
       <c r="S92" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12T21:43:48Z</t>
+          <t>2026-10-13T02:10:28Z</t>
         </is>
       </c>
     </row>
@@ -8186,7 +8186,7 @@
       </c>
       <c r="S93" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12T21:43:48Z</t>
+          <t>2026-10-13T02:10:28Z</t>
         </is>
       </c>
     </row>
@@ -8271,7 +8271,7 @@
       </c>
       <c r="S94" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12T21:43:48Z</t>
+          <t>2026-10-13T02:10:28Z</t>
         </is>
       </c>
     </row>
@@ -8360,7 +8360,7 @@
       </c>
       <c r="S95" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12T21:43:48Z</t>
+          <t>2026-10-13T02:10:28Z</t>
         </is>
       </c>
     </row>
@@ -8449,7 +8449,7 @@
       </c>
       <c r="S96" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12T21:43:48Z</t>
+          <t>2026-10-13T02:10:28Z</t>
         </is>
       </c>
     </row>
@@ -8534,7 +8534,7 @@
       </c>
       <c r="S97" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12T21:43:48Z</t>
+          <t>2026-10-13T02:10:28Z</t>
         </is>
       </c>
     </row>
@@ -8623,7 +8623,7 @@
       </c>
       <c r="S98" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12T21:43:48Z</t>
+          <t>2026-10-13T02:10:28Z</t>
         </is>
       </c>
     </row>
@@ -8712,7 +8712,7 @@
       </c>
       <c r="S99" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12T21:43:48Z</t>
+          <t>2026-10-13T02:10:28Z</t>
         </is>
       </c>
     </row>
@@ -8797,7 +8797,7 @@
       </c>
       <c r="S100" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12T21:43:48Z</t>
+          <t>2026-10-13T02:10:28Z</t>
         </is>
       </c>
     </row>
@@ -8886,7 +8886,7 @@
       </c>
       <c r="S101" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12T21:43:48Z</t>
+          <t>2026-10-13T02:10:28Z</t>
         </is>
       </c>
     </row>
@@ -8975,7 +8975,7 @@
       </c>
       <c r="S102" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12T21:43:48Z</t>
+          <t>2026-10-13T02:10:28Z</t>
         </is>
       </c>
     </row>
@@ -9060,7 +9060,7 @@
       </c>
       <c r="S103" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12T21:43:48Z</t>
+          <t>2026-10-13T02:10:28Z</t>
         </is>
       </c>
     </row>
@@ -9149,7 +9149,7 @@
       </c>
       <c r="S104" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12T21:43:48Z</t>
+          <t>2026-10-13T02:10:28Z</t>
         </is>
       </c>
     </row>
@@ -9238,7 +9238,7 @@
       </c>
       <c r="S105" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12T21:43:48Z</t>
+          <t>2026-10-13T02:10:28Z</t>
         </is>
       </c>
     </row>
@@ -9323,7 +9323,7 @@
       </c>
       <c r="S106" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12T21:43:48Z</t>
+          <t>2026-10-13T02:10:28Z</t>
         </is>
       </c>
     </row>
@@ -9412,7 +9412,7 @@
       </c>
       <c r="S107" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12T21:43:48Z</t>
+          <t>2026-10-13T02:10:28Z</t>
         </is>
       </c>
     </row>
@@ -9501,7 +9501,7 @@
       </c>
       <c r="S108" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12T21:43:48Z</t>
+          <t>2026-10-13T02:10:28Z</t>
         </is>
       </c>
     </row>
@@ -9586,7 +9586,7 @@
       </c>
       <c r="S109" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12T21:43:48Z</t>
+          <t>2026-10-13T02:10:28Z</t>
         </is>
       </c>
     </row>
@@ -9675,7 +9675,7 @@
       </c>
       <c r="S110" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12T21:43:48Z</t>
+          <t>2026-10-13T02:10:28Z</t>
         </is>
       </c>
     </row>
@@ -9764,7 +9764,7 @@
       </c>
       <c r="S111" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12T21:43:48Z</t>
+          <t>2026-10-13T02:10:28Z</t>
         </is>
       </c>
     </row>
@@ -9849,7 +9849,7 @@
       </c>
       <c r="S112" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12T21:43:48Z</t>
+          <t>2026-10-13T02:10:28Z</t>
         </is>
       </c>
     </row>
@@ -9938,7 +9938,7 @@
       </c>
       <c r="S113" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12T21:43:48Z</t>
+          <t>2026-10-13T02:10:28Z</t>
         </is>
       </c>
     </row>
@@ -10027,7 +10027,7 @@
       </c>
       <c r="S114" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12T21:43:48Z</t>
+          <t>2026-10-13T02:10:28Z</t>
         </is>
       </c>
     </row>
@@ -10112,7 +10112,7 @@
       </c>
       <c r="S115" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12T21:43:48Z</t>
+          <t>2026-10-13T02:10:28Z</t>
         </is>
       </c>
     </row>
@@ -10201,7 +10201,7 @@
       </c>
       <c r="S116" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12T21:43:48Z</t>
+          <t>2026-10-13T02:10:28Z</t>
         </is>
       </c>
     </row>
@@ -10290,7 +10290,7 @@
       </c>
       <c r="S117" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12T21:43:48Z</t>
+          <t>2026-10-13T02:10:28Z</t>
         </is>
       </c>
     </row>
@@ -10379,7 +10379,7 @@
       </c>
       <c r="S118" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12T21:43:48Z</t>
+          <t>2026-10-13T02:10:28Z</t>
         </is>
       </c>
     </row>
@@ -10468,7 +10468,7 @@
       </c>
       <c r="S119" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12T21:43:48Z</t>
+          <t>2026-10-13T02:10:28Z</t>
         </is>
       </c>
     </row>
@@ -10557,7 +10557,7 @@
       </c>
       <c r="S120" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12T21:43:48Z</t>
+          <t>2026-10-13T02:10:28Z</t>
         </is>
       </c>
     </row>
@@ -10646,7 +10646,7 @@
       </c>
       <c r="S121" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12T21:43:48Z</t>
+          <t>2026-10-13T02:10:28Z</t>
         </is>
       </c>
     </row>
@@ -10735,7 +10735,7 @@
       </c>
       <c r="S122" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12T21:43:48Z</t>
+          <t>2026-10-13T02:10:28Z</t>
         </is>
       </c>
     </row>
@@ -10824,7 +10824,7 @@
       </c>
       <c r="S123" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12T21:43:48Z</t>
+          <t>2026-10-13T02:10:28Z</t>
         </is>
       </c>
     </row>
@@ -10913,7 +10913,7 @@
       </c>
       <c r="S124" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12T21:43:48Z</t>
+          <t>2026-10-13T02:10:28Z</t>
         </is>
       </c>
     </row>
@@ -11002,7 +11002,7 @@
       </c>
       <c r="S125" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12T21:43:48Z</t>
+          <t>2026-10-13T02:10:28Z</t>
         </is>
       </c>
     </row>
@@ -11091,7 +11091,7 @@
       </c>
       <c r="S126" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12T21:43:48Z</t>
+          <t>2026-10-13T02:10:28Z</t>
         </is>
       </c>
     </row>
@@ -11180,7 +11180,7 @@
       </c>
       <c r="S127" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12T21:43:48Z</t>
+          <t>2026-10-13T02:10:28Z</t>
         </is>
       </c>
     </row>
@@ -11269,7 +11269,7 @@
       </c>
       <c r="S128" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12T21:43:48Z</t>
+          <t>2026-10-13T02:10:28Z</t>
         </is>
       </c>
     </row>
@@ -11354,7 +11354,7 @@
       </c>
       <c r="S129" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12T21:43:48Z</t>
+          <t>2026-10-13T02:10:28Z</t>
         </is>
       </c>
     </row>
@@ -11439,7 +11439,7 @@
       </c>
       <c r="S130" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12T21:43:48Z</t>
+          <t>2026-10-13T02:10:28Z</t>
         </is>
       </c>
     </row>
@@ -11524,7 +11524,7 @@
       </c>
       <c r="S131" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12T21:43:48Z</t>
+          <t>2026-10-13T02:10:28Z</t>
         </is>
       </c>
     </row>
@@ -11609,7 +11609,7 @@
       </c>
       <c r="S132" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12T21:43:48Z</t>
+          <t>2026-10-13T02:10:28Z</t>
         </is>
       </c>
     </row>
@@ -11694,7 +11694,7 @@
       </c>
       <c r="S133" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12T21:43:48Z</t>
+          <t>2026-10-13T02:10:28Z</t>
         </is>
       </c>
     </row>
@@ -11779,7 +11779,7 @@
       </c>
       <c r="S134" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12T21:43:48Z</t>
+          <t>2026-10-13T02:10:28Z</t>
         </is>
       </c>
     </row>
@@ -11864,7 +11864,7 @@
       </c>
       <c r="S135" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12T21:43:48Z</t>
+          <t>2026-10-13T02:10:28Z</t>
         </is>
       </c>
     </row>
@@ -11949,7 +11949,7 @@
       </c>
       <c r="S136" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12T21:43:48Z</t>
+          <t>2026-10-13T02:10:28Z</t>
         </is>
       </c>
     </row>
@@ -12034,7 +12034,7 @@
       </c>
       <c r="S137" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12T21:43:48Z</t>
+          <t>2026-10-13T02:10:28Z</t>
         </is>
       </c>
     </row>
@@ -12119,7 +12119,7 @@
       </c>
       <c r="S138" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12T21:43:48Z</t>
+          <t>2026-10-13T02:10:28Z</t>
         </is>
       </c>
     </row>
@@ -12204,7 +12204,7 @@
       </c>
       <c r="S139" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12T21:43:48Z</t>
+          <t>2026-10-13T02:10:28Z</t>
         </is>
       </c>
     </row>
@@ -12289,7 +12289,7 @@
       </c>
       <c r="S140" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12T21:43:48Z</t>
+          <t>2026-10-13T02:10:28Z</t>
         </is>
       </c>
     </row>
@@ -12374,7 +12374,7 @@
       </c>
       <c r="S141" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12T21:43:48Z</t>
+          <t>2026-10-13T02:10:28Z</t>
         </is>
       </c>
     </row>
@@ -12459,7 +12459,7 @@
       </c>
       <c r="S142" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12T21:43:48Z</t>
+          <t>2026-10-13T02:10:28Z</t>
         </is>
       </c>
     </row>
@@ -12544,7 +12544,7 @@
       </c>
       <c r="S143" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12T21:43:48Z</t>
+          <t>2026-10-13T02:10:28Z</t>
         </is>
       </c>
     </row>
@@ -12629,7 +12629,7 @@
       </c>
       <c r="S144" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12T21:43:48Z</t>
+          <t>2026-10-13T02:10:28Z</t>
         </is>
       </c>
     </row>
@@ -12714,7 +12714,7 @@
       </c>
       <c r="S145" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12T21:43:48Z</t>
+          <t>2026-10-13T02:10:28Z</t>
         </is>
       </c>
     </row>
@@ -12799,7 +12799,7 @@
       </c>
       <c r="S146" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12T21:43:48Z</t>
+          <t>2026-10-13T02:10:28Z</t>
         </is>
       </c>
     </row>
@@ -12884,7 +12884,7 @@
       </c>
       <c r="S147" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12T21:43:48Z</t>
+          <t>2026-10-13T02:10:28Z</t>
         </is>
       </c>
     </row>
@@ -12969,7 +12969,7 @@
       </c>
       <c r="S148" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12T21:43:48Z</t>
+          <t>2026-10-13T02:10:28Z</t>
         </is>
       </c>
     </row>
@@ -13054,7 +13054,7 @@
       </c>
       <c r="S149" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12T21:43:48Z</t>
+          <t>2026-10-13T02:10:28Z</t>
         </is>
       </c>
     </row>
@@ -13143,7 +13143,7 @@
       </c>
       <c r="S150" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12T21:43:48Z</t>
+          <t>2026-10-13T02:10:28Z</t>
         </is>
       </c>
     </row>
@@ -13232,7 +13232,7 @@
       </c>
       <c r="S151" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12T21:43:48Z</t>
+          <t>2026-10-13T02:10:28Z</t>
         </is>
       </c>
     </row>
@@ -13317,7 +13317,7 @@
       </c>
       <c r="S152" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12T21:43:48Z</t>
+          <t>2026-10-13T02:10:28Z</t>
         </is>
       </c>
     </row>
@@ -13406,7 +13406,7 @@
       </c>
       <c r="S153" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12T21:43:48Z</t>
+          <t>2026-10-13T02:10:28Z</t>
         </is>
       </c>
     </row>
@@ -13495,7 +13495,7 @@
       </c>
       <c r="S154" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12T21:43:48Z</t>
+          <t>2026-10-13T02:10:28Z</t>
         </is>
       </c>
     </row>
@@ -13580,7 +13580,7 @@
       </c>
       <c r="S155" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12T21:43:48Z</t>
+          <t>2026-10-13T02:10:28Z</t>
         </is>
       </c>
     </row>
@@ -13669,7 +13669,7 @@
       </c>
       <c r="S156" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12T21:43:48Z</t>
+          <t>2026-10-13T02:10:28Z</t>
         </is>
       </c>
     </row>
@@ -13758,7 +13758,7 @@
       </c>
       <c r="S157" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12T21:43:48Z</t>
+          <t>2026-10-13T02:10:28Z</t>
         </is>
       </c>
     </row>
@@ -13843,7 +13843,7 @@
       </c>
       <c r="S158" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12T21:43:48Z</t>
+          <t>2026-10-13T02:10:28Z</t>
         </is>
       </c>
     </row>
@@ -13932,7 +13932,7 @@
       </c>
       <c r="S159" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12T21:43:48Z</t>
+          <t>2026-10-13T02:10:28Z</t>
         </is>
       </c>
     </row>
@@ -14021,7 +14021,7 @@
       </c>
       <c r="S160" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12T21:43:48Z</t>
+          <t>2026-10-13T02:10:28Z</t>
         </is>
       </c>
     </row>
@@ -14106,7 +14106,7 @@
       </c>
       <c r="S161" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12T21:43:48Z</t>
+          <t>2026-10-13T02:10:28Z</t>
         </is>
       </c>
     </row>
@@ -14195,7 +14195,7 @@
       </c>
       <c r="S162" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12T21:43:48Z</t>
+          <t>2026-10-13T02:10:28Z</t>
         </is>
       </c>
     </row>
@@ -14284,7 +14284,7 @@
       </c>
       <c r="S163" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12T21:43:48Z</t>
+          <t>2026-10-13T02:10:28Z</t>
         </is>
       </c>
     </row>
@@ -14369,7 +14369,7 @@
       </c>
       <c r="S164" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12T21:43:48Z</t>
+          <t>2026-10-13T02:10:28Z</t>
         </is>
       </c>
     </row>
@@ -14458,7 +14458,7 @@
       </c>
       <c r="S165" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12T21:43:48Z</t>
+          <t>2026-10-13T02:10:28Z</t>
         </is>
       </c>
     </row>
@@ -14547,7 +14547,7 @@
       </c>
       <c r="S166" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12T21:43:48Z</t>
+          <t>2026-10-13T02:10:28Z</t>
         </is>
       </c>
     </row>
@@ -14632,7 +14632,7 @@
       </c>
       <c r="S167" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12T21:43:48Z</t>
+          <t>2026-10-13T02:10:28Z</t>
         </is>
       </c>
     </row>
@@ -14721,7 +14721,7 @@
       </c>
       <c r="S168" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12T21:43:48Z</t>
+          <t>2026-10-13T02:10:28Z</t>
         </is>
       </c>
     </row>
@@ -14810,7 +14810,7 @@
       </c>
       <c r="S169" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12T21:43:48Z</t>
+          <t>2026-10-13T02:10:28Z</t>
         </is>
       </c>
     </row>
@@ -14895,7 +14895,7 @@
       </c>
       <c r="S170" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12T21:43:48Z</t>
+          <t>2026-10-13T02:10:28Z</t>
         </is>
       </c>
     </row>
@@ -14984,7 +14984,7 @@
       </c>
       <c r="S171" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12T21:43:48Z</t>
+          <t>2026-10-13T02:10:28Z</t>
         </is>
       </c>
     </row>
@@ -15073,7 +15073,7 @@
       </c>
       <c r="S172" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12T21:43:48Z</t>
+          <t>2026-10-13T02:10:28Z</t>
         </is>
       </c>
     </row>
@@ -15158,7 +15158,7 @@
       </c>
       <c r="S173" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12T21:43:48Z</t>
+          <t>2026-10-13T02:10:28Z</t>
         </is>
       </c>
     </row>
@@ -15247,7 +15247,7 @@
       </c>
       <c r="S174" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12T21:43:48Z</t>
+          <t>2026-10-13T02:10:28Z</t>
         </is>
       </c>
     </row>
@@ -15336,7 +15336,7 @@
       </c>
       <c r="S175" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12T21:43:48Z</t>
+          <t>2026-10-13T02:10:28Z</t>
         </is>
       </c>
     </row>
@@ -15421,7 +15421,7 @@
       </c>
       <c r="S176" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12T21:43:48Z</t>
+          <t>2026-10-13T02:10:28Z</t>
         </is>
       </c>
     </row>
@@ -15510,7 +15510,7 @@
       </c>
       <c r="S177" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12T21:43:48Z</t>
+          <t>2026-10-13T02:10:28Z</t>
         </is>
       </c>
     </row>
@@ -15599,7 +15599,7 @@
       </c>
       <c r="S178" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12T21:43:48Z</t>
+          <t>2026-10-13T02:10:28Z</t>
         </is>
       </c>
     </row>
@@ -15688,7 +15688,7 @@
       </c>
       <c r="S179" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12T21:43:48Z</t>
+          <t>2026-10-13T02:10:28Z</t>
         </is>
       </c>
     </row>
@@ -15777,7 +15777,7 @@
       </c>
       <c r="S180" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12T21:43:48Z</t>
+          <t>2026-10-13T02:10:28Z</t>
         </is>
       </c>
     </row>
@@ -15866,7 +15866,7 @@
       </c>
       <c r="S181" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12T21:43:48Z</t>
+          <t>2026-10-13T02:10:28Z</t>
         </is>
       </c>
     </row>
@@ -15955,7 +15955,7 @@
       </c>
       <c r="S182" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12T21:43:48Z</t>
+          <t>2026-10-13T02:10:28Z</t>
         </is>
       </c>
     </row>
@@ -16044,7 +16044,7 @@
       </c>
       <c r="S183" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12T21:43:48Z</t>
+          <t>2026-10-13T02:10:28Z</t>
         </is>
       </c>
     </row>
@@ -16133,7 +16133,7 @@
       </c>
       <c r="S184" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12T21:43:48Z</t>
+          <t>2026-10-13T02:10:28Z</t>
         </is>
       </c>
     </row>
@@ -16222,7 +16222,7 @@
       </c>
       <c r="S185" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12T21:43:48Z</t>
+          <t>2026-10-13T02:10:28Z</t>
         </is>
       </c>
     </row>
@@ -16311,7 +16311,7 @@
       </c>
       <c r="S186" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12T21:43:48Z</t>
+          <t>2026-10-13T02:10:28Z</t>
         </is>
       </c>
     </row>
@@ -16400,7 +16400,7 @@
       </c>
       <c r="S187" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12T21:43:48Z</t>
+          <t>2026-10-13T02:10:28Z</t>
         </is>
       </c>
     </row>
@@ -16489,7 +16489,7 @@
       </c>
       <c r="S188" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12T21:43:48Z</t>
+          <t>2026-10-13T02:10:28Z</t>
         </is>
       </c>
     </row>
@@ -16578,7 +16578,7 @@
       </c>
       <c r="S189" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12T21:43:48Z</t>
+          <t>2026-10-13T02:10:28Z</t>
         </is>
       </c>
     </row>
@@ -16663,7 +16663,7 @@
       </c>
       <c r="S190" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12T21:43:48Z</t>
+          <t>2026-10-13T02:10:28Z</t>
         </is>
       </c>
     </row>
@@ -16748,7 +16748,7 @@
       </c>
       <c r="S191" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12T21:43:48Z</t>
+          <t>2026-10-13T02:10:28Z</t>
         </is>
       </c>
     </row>
@@ -16833,7 +16833,7 @@
       </c>
       <c r="S192" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12T21:43:48Z</t>
+          <t>2026-10-13T02:10:28Z</t>
         </is>
       </c>
     </row>
@@ -16918,7 +16918,7 @@
       </c>
       <c r="S193" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12T21:43:48Z</t>
+          <t>2026-10-13T02:10:28Z</t>
         </is>
       </c>
     </row>
@@ -17003,7 +17003,7 @@
       </c>
       <c r="S194" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12T21:43:48Z</t>
+          <t>2026-10-13T02:10:28Z</t>
         </is>
       </c>
     </row>
@@ -17088,7 +17088,7 @@
       </c>
       <c r="S195" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12T21:43:48Z</t>
+          <t>2026-10-13T02:10:28Z</t>
         </is>
       </c>
     </row>
@@ -17173,7 +17173,7 @@
       </c>
       <c r="S196" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12T21:43:48Z</t>
+          <t>2026-10-13T02:10:28Z</t>
         </is>
       </c>
     </row>
@@ -17258,7 +17258,7 @@
       </c>
       <c r="S197" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12T21:43:48Z</t>
+          <t>2026-10-13T02:10:28Z</t>
         </is>
       </c>
     </row>
@@ -17343,7 +17343,7 @@
       </c>
       <c r="S198" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12T21:43:48Z</t>
+          <t>2026-10-13T02:10:28Z</t>
         </is>
       </c>
     </row>
@@ -17428,7 +17428,7 @@
       </c>
       <c r="S199" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12T21:43:48Z</t>
+          <t>2026-10-13T02:10:28Z</t>
         </is>
       </c>
     </row>
@@ -17513,7 +17513,7 @@
       </c>
       <c r="S200" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12T21:43:48Z</t>
+          <t>2026-10-13T02:10:28Z</t>
         </is>
       </c>
     </row>
@@ -17598,7 +17598,7 @@
       </c>
       <c r="S201" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12T21:43:48Z</t>
+          <t>2026-10-13T02:10:28Z</t>
         </is>
       </c>
     </row>
@@ -17683,7 +17683,7 @@
       </c>
       <c r="S202" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12T21:43:48Z</t>
+          <t>2026-10-13T02:10:28Z</t>
         </is>
       </c>
     </row>
@@ -17768,7 +17768,7 @@
       </c>
       <c r="S203" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12T21:43:48Z</t>
+          <t>2026-10-13T02:10:28Z</t>
         </is>
       </c>
     </row>
@@ -17853,7 +17853,7 @@
       </c>
       <c r="S204" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12T21:43:48Z</t>
+          <t>2026-10-13T02:10:28Z</t>
         </is>
       </c>
     </row>
@@ -17938,7 +17938,7 @@
       </c>
       <c r="S205" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12T21:43:48Z</t>
+          <t>2026-10-13T02:10:28Z</t>
         </is>
       </c>
     </row>
@@ -18023,7 +18023,7 @@
       </c>
       <c r="S206" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12T21:43:48Z</t>
+          <t>2026-10-13T02:10:28Z</t>
         </is>
       </c>
     </row>
@@ -18108,7 +18108,7 @@
       </c>
       <c r="S207" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12T21:43:48Z</t>
+          <t>2026-10-13T02:10:28Z</t>
         </is>
       </c>
     </row>
@@ -18193,7 +18193,7 @@
       </c>
       <c r="S208" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12T21:43:48Z</t>
+          <t>2026-10-13T02:10:28Z</t>
         </is>
       </c>
     </row>
@@ -18278,7 +18278,7 @@
       </c>
       <c r="S209" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12T21:43:48Z</t>
+          <t>2026-10-13T02:10:28Z</t>
         </is>
       </c>
     </row>
@@ -18363,7 +18363,7 @@
       </c>
       <c r="S210" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12T21:43:48Z</t>
+          <t>2026-10-13T02:10:28Z</t>
         </is>
       </c>
     </row>
@@ -18452,7 +18452,7 @@
       </c>
       <c r="S211" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12T21:43:48Z</t>
+          <t>2026-10-13T02:10:28Z</t>
         </is>
       </c>
     </row>
@@ -18541,7 +18541,7 @@
       </c>
       <c r="S212" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12T21:43:48Z</t>
+          <t>2026-10-13T02:10:28Z</t>
         </is>
       </c>
     </row>
@@ -18626,7 +18626,7 @@
       </c>
       <c r="S213" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12T21:43:48Z</t>
+          <t>2026-10-13T02:10:28Z</t>
         </is>
       </c>
     </row>
@@ -18715,7 +18715,7 @@
       </c>
       <c r="S214" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12T21:43:48Z</t>
+          <t>2026-10-13T02:10:28Z</t>
         </is>
       </c>
     </row>
@@ -18804,7 +18804,7 @@
       </c>
       <c r="S215" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12T21:43:48Z</t>
+          <t>2026-10-13T02:10:28Z</t>
         </is>
       </c>
     </row>
@@ -18889,7 +18889,7 @@
       </c>
       <c r="S216" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12T21:43:48Z</t>
+          <t>2026-10-13T02:10:28Z</t>
         </is>
       </c>
     </row>
@@ -18978,7 +18978,7 @@
       </c>
       <c r="S217" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12T21:43:48Z</t>
+          <t>2026-10-13T02:10:28Z</t>
         </is>
       </c>
     </row>
@@ -19067,7 +19067,7 @@
       </c>
       <c r="S218" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12T21:43:48Z</t>
+          <t>2026-10-13T02:10:28Z</t>
         </is>
       </c>
     </row>
@@ -19152,7 +19152,7 @@
       </c>
       <c r="S219" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12T21:43:48Z</t>
+          <t>2026-10-13T02:10:28Z</t>
         </is>
       </c>
     </row>
@@ -19241,7 +19241,7 @@
       </c>
       <c r="S220" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12T21:43:48Z</t>
+          <t>2026-10-13T02:10:28Z</t>
         </is>
       </c>
     </row>
@@ -19330,7 +19330,7 @@
       </c>
       <c r="S221" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12T21:43:48Z</t>
+          <t>2026-10-13T02:10:28Z</t>
         </is>
       </c>
     </row>
@@ -19415,7 +19415,7 @@
       </c>
       <c r="S222" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12T21:43:48Z</t>
+          <t>2026-10-13T02:10:28Z</t>
         </is>
       </c>
     </row>
@@ -19504,7 +19504,7 @@
       </c>
       <c r="S223" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12T21:43:48Z</t>
+          <t>2026-10-13T02:10:28Z</t>
         </is>
       </c>
     </row>
@@ -19593,7 +19593,7 @@
       </c>
       <c r="S224" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12T21:43:48Z</t>
+          <t>2026-10-13T02:10:28Z</t>
         </is>
       </c>
     </row>
@@ -19678,7 +19678,7 @@
       </c>
       <c r="S225" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12T21:43:48Z</t>
+          <t>2026-10-13T02:10:28Z</t>
         </is>
       </c>
     </row>
@@ -19767,7 +19767,7 @@
       </c>
       <c r="S226" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12T21:43:48Z</t>
+          <t>2026-10-13T02:10:28Z</t>
         </is>
       </c>
     </row>
@@ -19856,7 +19856,7 @@
       </c>
       <c r="S227" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12T21:43:48Z</t>
+          <t>2026-10-13T02:10:28Z</t>
         </is>
       </c>
     </row>
@@ -19941,7 +19941,7 @@
       </c>
       <c r="S228" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12T21:43:48Z</t>
+          <t>2026-10-13T02:10:28Z</t>
         </is>
       </c>
     </row>
@@ -20030,7 +20030,7 @@
       </c>
       <c r="S229" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12T21:43:48Z</t>
+          <t>2026-10-13T02:10:28Z</t>
         </is>
       </c>
     </row>
@@ -20119,7 +20119,7 @@
       </c>
       <c r="S230" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12T21:43:48Z</t>
+          <t>2026-10-13T02:10:28Z</t>
         </is>
       </c>
     </row>
@@ -20204,7 +20204,7 @@
       </c>
       <c r="S231" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12T21:43:48Z</t>
+          <t>2026-10-13T02:10:28Z</t>
         </is>
       </c>
     </row>
@@ -20293,7 +20293,7 @@
       </c>
       <c r="S232" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12T21:43:48Z</t>
+          <t>2026-10-13T02:10:28Z</t>
         </is>
       </c>
     </row>
@@ -20382,7 +20382,7 @@
       </c>
       <c r="S233" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12T21:43:48Z</t>
+          <t>2026-10-13T02:10:28Z</t>
         </is>
       </c>
     </row>
@@ -20467,7 +20467,7 @@
       </c>
       <c r="S234" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12T21:43:48Z</t>
+          <t>2026-10-13T02:10:28Z</t>
         </is>
       </c>
     </row>
@@ -20556,7 +20556,7 @@
       </c>
       <c r="S235" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12T21:43:48Z</t>
+          <t>2026-10-13T02:10:28Z</t>
         </is>
       </c>
     </row>
@@ -20645,7 +20645,7 @@
       </c>
       <c r="S236" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12T21:43:48Z</t>
+          <t>2026-10-13T02:10:28Z</t>
         </is>
       </c>
     </row>
@@ -20730,7 +20730,7 @@
       </c>
       <c r="S237" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12T21:43:48Z</t>
+          <t>2026-10-13T02:10:28Z</t>
         </is>
       </c>
     </row>
@@ -20819,7 +20819,7 @@
       </c>
       <c r="S238" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12T21:43:48Z</t>
+          <t>2026-10-13T02:10:28Z</t>
         </is>
       </c>
     </row>
@@ -20908,7 +20908,7 @@
       </c>
       <c r="S239" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12T21:43:48Z</t>
+          <t>2026-10-13T02:10:28Z</t>
         </is>
       </c>
     </row>
@@ -20997,7 +20997,7 @@
       </c>
       <c r="S240" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12T21:43:48Z</t>
+          <t>2026-10-13T02:10:28Z</t>
         </is>
       </c>
     </row>
@@ -21086,7 +21086,7 @@
       </c>
       <c r="S241" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12T21:43:48Z</t>
+          <t>2026-10-13T02:10:28Z</t>
         </is>
       </c>
     </row>
@@ -21175,7 +21175,7 @@
       </c>
       <c r="S242" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12T21:43:48Z</t>
+          <t>2026-10-13T02:10:28Z</t>
         </is>
       </c>
     </row>
@@ -21264,7 +21264,7 @@
       </c>
       <c r="S243" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12T21:43:48Z</t>
+          <t>2026-10-13T02:10:28Z</t>
         </is>
       </c>
     </row>
@@ -21353,7 +21353,7 @@
       </c>
       <c r="S244" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12T21:43:48Z</t>
+          <t>2026-10-13T02:10:28Z</t>
         </is>
       </c>
     </row>
@@ -21442,7 +21442,7 @@
       </c>
       <c r="S245" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12T21:43:48Z</t>
+          <t>2026-10-13T02:10:28Z</t>
         </is>
       </c>
     </row>
@@ -21531,7 +21531,7 @@
       </c>
       <c r="S246" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12T21:43:48Z</t>
+          <t>2026-10-13T02:10:28Z</t>
         </is>
       </c>
     </row>
@@ -21620,7 +21620,7 @@
       </c>
       <c r="S247" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12T21:43:48Z</t>
+          <t>2026-10-13T02:10:28Z</t>
         </is>
       </c>
     </row>
@@ -21709,7 +21709,7 @@
       </c>
       <c r="S248" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12T21:43:48Z</t>
+          <t>2026-10-13T02:10:28Z</t>
         </is>
       </c>
     </row>
@@ -21798,7 +21798,7 @@
       </c>
       <c r="S249" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12T21:43:48Z</t>
+          <t>2026-10-13T02:10:28Z</t>
         </is>
       </c>
     </row>
@@ -21887,7 +21887,7 @@
       </c>
       <c r="S250" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12T21:43:48Z</t>
+          <t>2026-10-13T02:10:28Z</t>
         </is>
       </c>
     </row>
@@ -22019,7 +22019,7 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12T21:43:48Z</t>
+          <t>2026-10-13T02:10:28Z</t>
         </is>
       </c>
     </row>
@@ -22099,7 +22099,7 @@
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>{"dataset_id": "bcv_pib_sector_institucional_anual", "title": "Producto interno bruto por sector institucional anual", "table": "Variaciones porcentuales", "source_file": "5_2_1_si_anual.xlsx", "base": "2007", "price_type": "Precios constantes", "measure": "Variación porcentual interanual", "frequency": "Anual", "period": "2025", "year": 2025, "quarter": null, "classification": "Sector institucional", "component": "Impuestos netos sobre los productos", "value": 10.600260421283764, "unit": "Porcentaje", "status": "Preliminar", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/cuentas_macroeconomicas/5_2_1_si_anual.xlsx", "fetched_at": "2026-10-12T21:43:48Z"}</t>
+          <t>{"dataset_id": "bcv_pib_sector_institucional_anual", "title": "Producto interno bruto por sector institucional anual", "table": "Variaciones porcentuales", "source_file": "5_2_1_si_anual.xlsx", "base": "2007", "price_type": "Precios constantes", "measure": "Variación porcentual interanual", "frequency": "Anual", "period": "2025", "year": 2025, "quarter": null, "classification": "Sector institucional", "component": "Impuestos netos sobre los productos", "value": 10.600260421283764, "unit": "Porcentaje", "status": "Preliminar", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/cuentas_macroeconomicas/5_2_1_si_anual.xlsx", "fetched_at": "2026-10-13T02:10:28Z"}</t>
         </is>
       </c>
     </row>

--- a/assets/data/bcv/excel/ove_bcv_pib_sector_institucional_anual.xlsx
+++ b/assets/data/bcv/excel/ove_bcv_pib_sector_institucional_anual.xlsx
@@ -736,7 +736,7 @@
       </c>
       <c r="S7" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T02:10:28Z</t>
+          <t>2026-10-13T23:48:08Z</t>
         </is>
       </c>
     </row>
@@ -821,7 +821,7 @@
       </c>
       <c r="S8" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T02:10:28Z</t>
+          <t>2026-10-13T23:48:08Z</t>
         </is>
       </c>
     </row>
@@ -906,7 +906,7 @@
       </c>
       <c r="S9" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T02:10:28Z</t>
+          <t>2026-10-13T23:48:08Z</t>
         </is>
       </c>
     </row>
@@ -991,7 +991,7 @@
       </c>
       <c r="S10" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T02:10:28Z</t>
+          <t>2026-10-13T23:48:08Z</t>
         </is>
       </c>
     </row>
@@ -1076,7 +1076,7 @@
       </c>
       <c r="S11" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T02:10:28Z</t>
+          <t>2026-10-13T23:48:08Z</t>
         </is>
       </c>
     </row>
@@ -1161,7 +1161,7 @@
       </c>
       <c r="S12" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T02:10:28Z</t>
+          <t>2026-10-13T23:48:08Z</t>
         </is>
       </c>
     </row>
@@ -1246,7 +1246,7 @@
       </c>
       <c r="S13" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T02:10:28Z</t>
+          <t>2026-10-13T23:48:08Z</t>
         </is>
       </c>
     </row>
@@ -1331,7 +1331,7 @@
       </c>
       <c r="S14" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T02:10:28Z</t>
+          <t>2026-10-13T23:48:08Z</t>
         </is>
       </c>
     </row>
@@ -1416,7 +1416,7 @@
       </c>
       <c r="S15" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T02:10:28Z</t>
+          <t>2026-10-13T23:48:08Z</t>
         </is>
       </c>
     </row>
@@ -1501,7 +1501,7 @@
       </c>
       <c r="S16" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T02:10:28Z</t>
+          <t>2026-10-13T23:48:08Z</t>
         </is>
       </c>
     </row>
@@ -1586,7 +1586,7 @@
       </c>
       <c r="S17" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T02:10:28Z</t>
+          <t>2026-10-13T23:48:08Z</t>
         </is>
       </c>
     </row>
@@ -1671,7 +1671,7 @@
       </c>
       <c r="S18" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T02:10:28Z</t>
+          <t>2026-10-13T23:48:08Z</t>
         </is>
       </c>
     </row>
@@ -1756,7 +1756,7 @@
       </c>
       <c r="S19" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T02:10:28Z</t>
+          <t>2026-10-13T23:48:08Z</t>
         </is>
       </c>
     </row>
@@ -1841,7 +1841,7 @@
       </c>
       <c r="S20" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T02:10:28Z</t>
+          <t>2026-10-13T23:48:08Z</t>
         </is>
       </c>
     </row>
@@ -1926,7 +1926,7 @@
       </c>
       <c r="S21" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T02:10:28Z</t>
+          <t>2026-10-13T23:48:08Z</t>
         </is>
       </c>
     </row>
@@ -2011,7 +2011,7 @@
       </c>
       <c r="S22" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T02:10:28Z</t>
+          <t>2026-10-13T23:48:08Z</t>
         </is>
       </c>
     </row>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="S23" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T02:10:28Z</t>
+          <t>2026-10-13T23:48:08Z</t>
         </is>
       </c>
     </row>
@@ -2181,7 +2181,7 @@
       </c>
       <c r="S24" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T02:10:28Z</t>
+          <t>2026-10-13T23:48:08Z</t>
         </is>
       </c>
     </row>
@@ -2266,7 +2266,7 @@
       </c>
       <c r="S25" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T02:10:28Z</t>
+          <t>2026-10-13T23:48:08Z</t>
         </is>
       </c>
     </row>
@@ -2351,7 +2351,7 @@
       </c>
       <c r="S26" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T02:10:28Z</t>
+          <t>2026-10-13T23:48:08Z</t>
         </is>
       </c>
     </row>
@@ -2436,7 +2436,7 @@
       </c>
       <c r="S27" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T02:10:28Z</t>
+          <t>2026-10-13T23:48:08Z</t>
         </is>
       </c>
     </row>
@@ -2525,7 +2525,7 @@
       </c>
       <c r="S28" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T02:10:28Z</t>
+          <t>2026-10-13T23:48:08Z</t>
         </is>
       </c>
     </row>
@@ -2614,7 +2614,7 @@
       </c>
       <c r="S29" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T02:10:28Z</t>
+          <t>2026-10-13T23:48:08Z</t>
         </is>
       </c>
     </row>
@@ -2699,7 +2699,7 @@
       </c>
       <c r="S30" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T02:10:28Z</t>
+          <t>2026-10-13T23:48:08Z</t>
         </is>
       </c>
     </row>
@@ -2788,7 +2788,7 @@
       </c>
       <c r="S31" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T02:10:28Z</t>
+          <t>2026-10-13T23:48:08Z</t>
         </is>
       </c>
     </row>
@@ -2877,7 +2877,7 @@
       </c>
       <c r="S32" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T02:10:28Z</t>
+          <t>2026-10-13T23:48:08Z</t>
         </is>
       </c>
     </row>
@@ -2962,7 +2962,7 @@
       </c>
       <c r="S33" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T02:10:28Z</t>
+          <t>2026-10-13T23:48:08Z</t>
         </is>
       </c>
     </row>
@@ -3051,7 +3051,7 @@
       </c>
       <c r="S34" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T02:10:28Z</t>
+          <t>2026-10-13T23:48:08Z</t>
         </is>
       </c>
     </row>
@@ -3140,7 +3140,7 @@
       </c>
       <c r="S35" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T02:10:28Z</t>
+          <t>2026-10-13T23:48:08Z</t>
         </is>
       </c>
     </row>
@@ -3225,7 +3225,7 @@
       </c>
       <c r="S36" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T02:10:28Z</t>
+          <t>2026-10-13T23:48:08Z</t>
         </is>
       </c>
     </row>
@@ -3314,7 +3314,7 @@
       </c>
       <c r="S37" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T02:10:28Z</t>
+          <t>2026-10-13T23:48:08Z</t>
         </is>
       </c>
     </row>
@@ -3403,7 +3403,7 @@
       </c>
       <c r="S38" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T02:10:28Z</t>
+          <t>2026-10-13T23:48:08Z</t>
         </is>
       </c>
     </row>
@@ -3488,7 +3488,7 @@
       </c>
       <c r="S39" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T02:10:28Z</t>
+          <t>2026-10-13T23:48:08Z</t>
         </is>
       </c>
     </row>
@@ -3577,7 +3577,7 @@
       </c>
       <c r="S40" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T02:10:28Z</t>
+          <t>2026-10-13T23:48:08Z</t>
         </is>
       </c>
     </row>
@@ -3666,7 +3666,7 @@
       </c>
       <c r="S41" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T02:10:28Z</t>
+          <t>2026-10-13T23:48:08Z</t>
         </is>
       </c>
     </row>
@@ -3751,7 +3751,7 @@
       </c>
       <c r="S42" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T02:10:28Z</t>
+          <t>2026-10-13T23:48:08Z</t>
         </is>
       </c>
     </row>
@@ -3840,7 +3840,7 @@
       </c>
       <c r="S43" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T02:10:28Z</t>
+          <t>2026-10-13T23:48:08Z</t>
         </is>
       </c>
     </row>
@@ -3929,7 +3929,7 @@
       </c>
       <c r="S44" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T02:10:28Z</t>
+          <t>2026-10-13T23:48:08Z</t>
         </is>
       </c>
     </row>
@@ -4014,7 +4014,7 @@
       </c>
       <c r="S45" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T02:10:28Z</t>
+          <t>2026-10-13T23:48:08Z</t>
         </is>
       </c>
     </row>
@@ -4103,7 +4103,7 @@
       </c>
       <c r="S46" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T02:10:28Z</t>
+          <t>2026-10-13T23:48:08Z</t>
         </is>
       </c>
     </row>
@@ -4192,7 +4192,7 @@
       </c>
       <c r="S47" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T02:10:28Z</t>
+          <t>2026-10-13T23:48:08Z</t>
         </is>
       </c>
     </row>
@@ -4277,7 +4277,7 @@
       </c>
       <c r="S48" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T02:10:28Z</t>
+          <t>2026-10-13T23:48:08Z</t>
         </is>
       </c>
     </row>
@@ -4366,7 +4366,7 @@
       </c>
       <c r="S49" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T02:10:28Z</t>
+          <t>2026-10-13T23:48:08Z</t>
         </is>
       </c>
     </row>
@@ -4455,7 +4455,7 @@
       </c>
       <c r="S50" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T02:10:28Z</t>
+          <t>2026-10-13T23:48:08Z</t>
         </is>
       </c>
     </row>
@@ -4540,7 +4540,7 @@
       </c>
       <c r="S51" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T02:10:28Z</t>
+          <t>2026-10-13T23:48:08Z</t>
         </is>
       </c>
     </row>
@@ -4629,7 +4629,7 @@
       </c>
       <c r="S52" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T02:10:28Z</t>
+          <t>2026-10-13T23:48:08Z</t>
         </is>
       </c>
     </row>
@@ -4718,7 +4718,7 @@
       </c>
       <c r="S53" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T02:10:28Z</t>
+          <t>2026-10-13T23:48:08Z</t>
         </is>
       </c>
     </row>
@@ -4803,7 +4803,7 @@
       </c>
       <c r="S54" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T02:10:28Z</t>
+          <t>2026-10-13T23:48:08Z</t>
         </is>
       </c>
     </row>
@@ -4892,7 +4892,7 @@
       </c>
       <c r="S55" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T02:10:28Z</t>
+          <t>2026-10-13T23:48:08Z</t>
         </is>
       </c>
     </row>
@@ -4981,7 +4981,7 @@
       </c>
       <c r="S56" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T02:10:28Z</t>
+          <t>2026-10-13T23:48:08Z</t>
         </is>
       </c>
     </row>
@@ -5070,7 +5070,7 @@
       </c>
       <c r="S57" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T02:10:28Z</t>
+          <t>2026-10-13T23:48:08Z</t>
         </is>
       </c>
     </row>
@@ -5159,7 +5159,7 @@
       </c>
       <c r="S58" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T02:10:28Z</t>
+          <t>2026-10-13T23:48:08Z</t>
         </is>
       </c>
     </row>
@@ -5248,7 +5248,7 @@
       </c>
       <c r="S59" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T02:10:28Z</t>
+          <t>2026-10-13T23:48:08Z</t>
         </is>
       </c>
     </row>
@@ -5337,7 +5337,7 @@
       </c>
       <c r="S60" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T02:10:28Z</t>
+          <t>2026-10-13T23:48:08Z</t>
         </is>
       </c>
     </row>
@@ -5426,7 +5426,7 @@
       </c>
       <c r="S61" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T02:10:28Z</t>
+          <t>2026-10-13T23:48:08Z</t>
         </is>
       </c>
     </row>
@@ -5515,7 +5515,7 @@
       </c>
       <c r="S62" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T02:10:28Z</t>
+          <t>2026-10-13T23:48:08Z</t>
         </is>
       </c>
     </row>
@@ -5604,7 +5604,7 @@
       </c>
       <c r="S63" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T02:10:28Z</t>
+          <t>2026-10-13T23:48:08Z</t>
         </is>
       </c>
     </row>
@@ -5693,7 +5693,7 @@
       </c>
       <c r="S64" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T02:10:28Z</t>
+          <t>2026-10-13T23:48:08Z</t>
         </is>
       </c>
     </row>
@@ -5782,7 +5782,7 @@
       </c>
       <c r="S65" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T02:10:28Z</t>
+          <t>2026-10-13T23:48:08Z</t>
         </is>
       </c>
     </row>
@@ -5871,7 +5871,7 @@
       </c>
       <c r="S66" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T02:10:28Z</t>
+          <t>2026-10-13T23:48:08Z</t>
         </is>
       </c>
     </row>
@@ -5960,7 +5960,7 @@
       </c>
       <c r="S67" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T02:10:28Z</t>
+          <t>2026-10-13T23:48:08Z</t>
         </is>
       </c>
     </row>
@@ -6045,7 +6045,7 @@
       </c>
       <c r="S68" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T02:10:28Z</t>
+          <t>2026-10-13T23:48:08Z</t>
         </is>
       </c>
     </row>
@@ -6130,7 +6130,7 @@
       </c>
       <c r="S69" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T02:10:28Z</t>
+          <t>2026-10-13T23:48:08Z</t>
         </is>
       </c>
     </row>
@@ -6215,7 +6215,7 @@
       </c>
       <c r="S70" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T02:10:28Z</t>
+          <t>2026-10-13T23:48:08Z</t>
         </is>
       </c>
     </row>
@@ -6300,7 +6300,7 @@
       </c>
       <c r="S71" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T02:10:28Z</t>
+          <t>2026-10-13T23:48:08Z</t>
         </is>
       </c>
     </row>
@@ -6385,7 +6385,7 @@
       </c>
       <c r="S72" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T02:10:28Z</t>
+          <t>2026-10-13T23:48:08Z</t>
         </is>
       </c>
     </row>
@@ -6470,7 +6470,7 @@
       </c>
       <c r="S73" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T02:10:28Z</t>
+          <t>2026-10-13T23:48:08Z</t>
         </is>
       </c>
     </row>
@@ -6555,7 +6555,7 @@
       </c>
       <c r="S74" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T02:10:28Z</t>
+          <t>2026-10-13T23:48:08Z</t>
         </is>
       </c>
     </row>
@@ -6640,7 +6640,7 @@
       </c>
       <c r="S75" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T02:10:28Z</t>
+          <t>2026-10-13T23:48:08Z</t>
         </is>
       </c>
     </row>
@@ -6725,7 +6725,7 @@
       </c>
       <c r="S76" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T02:10:28Z</t>
+          <t>2026-10-13T23:48:08Z</t>
         </is>
       </c>
     </row>
@@ -6810,7 +6810,7 @@
       </c>
       <c r="S77" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T02:10:28Z</t>
+          <t>2026-10-13T23:48:08Z</t>
         </is>
       </c>
     </row>
@@ -6895,7 +6895,7 @@
       </c>
       <c r="S78" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T02:10:28Z</t>
+          <t>2026-10-13T23:48:08Z</t>
         </is>
       </c>
     </row>
@@ -6980,7 +6980,7 @@
       </c>
       <c r="S79" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T02:10:28Z</t>
+          <t>2026-10-13T23:48:08Z</t>
         </is>
       </c>
     </row>
@@ -7065,7 +7065,7 @@
       </c>
       <c r="S80" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T02:10:28Z</t>
+          <t>2026-10-13T23:48:08Z</t>
         </is>
       </c>
     </row>
@@ -7150,7 +7150,7 @@
       </c>
       <c r="S81" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T02:10:28Z</t>
+          <t>2026-10-13T23:48:08Z</t>
         </is>
       </c>
     </row>
@@ -7235,7 +7235,7 @@
       </c>
       <c r="S82" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T02:10:28Z</t>
+          <t>2026-10-13T23:48:08Z</t>
         </is>
       </c>
     </row>
@@ -7320,7 +7320,7 @@
       </c>
       <c r="S83" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T02:10:28Z</t>
+          <t>2026-10-13T23:48:08Z</t>
         </is>
       </c>
     </row>
@@ -7405,7 +7405,7 @@
       </c>
       <c r="S84" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T02:10:28Z</t>
+          <t>2026-10-13T23:48:08Z</t>
         </is>
       </c>
     </row>
@@ -7490,7 +7490,7 @@
       </c>
       <c r="S85" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T02:10:28Z</t>
+          <t>2026-10-13T23:48:08Z</t>
         </is>
       </c>
     </row>
@@ -7575,7 +7575,7 @@
       </c>
       <c r="S86" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T02:10:28Z</t>
+          <t>2026-10-13T23:48:08Z</t>
         </is>
       </c>
     </row>
@@ -7660,7 +7660,7 @@
       </c>
       <c r="S87" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T02:10:28Z</t>
+          <t>2026-10-13T23:48:08Z</t>
         </is>
       </c>
     </row>
@@ -7745,7 +7745,7 @@
       </c>
       <c r="S88" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T02:10:28Z</t>
+          <t>2026-10-13T23:48:08Z</t>
         </is>
       </c>
     </row>
@@ -7834,7 +7834,7 @@
       </c>
       <c r="S89" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T02:10:28Z</t>
+          <t>2026-10-13T23:48:08Z</t>
         </is>
       </c>
     </row>
@@ -7923,7 +7923,7 @@
       </c>
       <c r="S90" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T02:10:28Z</t>
+          <t>2026-10-13T23:48:08Z</t>
         </is>
       </c>
     </row>
@@ -8008,7 +8008,7 @@
       </c>
       <c r="S91" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T02:10:28Z</t>
+          <t>2026-10-13T23:48:08Z</t>
         </is>
       </c>
     </row>
@@ -8097,7 +8097,7 @@
       </c>
       <c r="S92" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T02:10:28Z</t>
+          <t>2026-10-13T23:48:08Z</t>
         </is>
       </c>
     </row>
@@ -8186,7 +8186,7 @@
       </c>
       <c r="S93" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T02:10:28Z</t>
+          <t>2026-10-13T23:48:08Z</t>
         </is>
       </c>
     </row>
@@ -8271,7 +8271,7 @@
       </c>
       <c r="S94" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T02:10:28Z</t>
+          <t>2026-10-13T23:48:08Z</t>
         </is>
       </c>
     </row>
@@ -8360,7 +8360,7 @@
       </c>
       <c r="S95" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T02:10:28Z</t>
+          <t>2026-10-13T23:48:08Z</t>
         </is>
       </c>
     </row>
@@ -8449,7 +8449,7 @@
       </c>
       <c r="S96" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T02:10:28Z</t>
+          <t>2026-10-13T23:48:08Z</t>
         </is>
       </c>
     </row>
@@ -8534,7 +8534,7 @@
       </c>
       <c r="S97" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T02:10:28Z</t>
+          <t>2026-10-13T23:48:08Z</t>
         </is>
       </c>
     </row>
@@ -8623,7 +8623,7 @@
       </c>
       <c r="S98" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T02:10:28Z</t>
+          <t>2026-10-13T23:48:08Z</t>
         </is>
       </c>
     </row>
@@ -8712,7 +8712,7 @@
       </c>
       <c r="S99" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T02:10:28Z</t>
+          <t>2026-10-13T23:48:08Z</t>
         </is>
       </c>
     </row>
@@ -8797,7 +8797,7 @@
       </c>
       <c r="S100" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T02:10:28Z</t>
+          <t>2026-10-13T23:48:08Z</t>
         </is>
       </c>
     </row>
@@ -8886,7 +8886,7 @@
       </c>
       <c r="S101" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T02:10:28Z</t>
+          <t>2026-10-13T23:48:08Z</t>
         </is>
       </c>
     </row>
@@ -8975,7 +8975,7 @@
       </c>
       <c r="S102" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T02:10:28Z</t>
+          <t>2026-10-13T23:48:08Z</t>
         </is>
       </c>
     </row>
@@ -9060,7 +9060,7 @@
       </c>
       <c r="S103" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T02:10:28Z</t>
+          <t>2026-10-13T23:48:08Z</t>
         </is>
       </c>
     </row>
@@ -9149,7 +9149,7 @@
       </c>
       <c r="S104" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T02:10:28Z</t>
+          <t>2026-10-13T23:48:08Z</t>
         </is>
       </c>
     </row>
@@ -9238,7 +9238,7 @@
       </c>
       <c r="S105" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T02:10:28Z</t>
+          <t>2026-10-13T23:48:08Z</t>
         </is>
       </c>
     </row>
@@ -9323,7 +9323,7 @@
       </c>
       <c r="S106" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T02:10:28Z</t>
+          <t>2026-10-13T23:48:08Z</t>
         </is>
       </c>
     </row>
@@ -9412,7 +9412,7 @@
       </c>
       <c r="S107" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T02:10:28Z</t>
+          <t>2026-10-13T23:48:08Z</t>
         </is>
       </c>
     </row>
@@ -9501,7 +9501,7 @@
       </c>
       <c r="S108" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T02:10:28Z</t>
+          <t>2026-10-13T23:48:08Z</t>
         </is>
       </c>
     </row>
@@ -9586,7 +9586,7 @@
       </c>
       <c r="S109" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T02:10:28Z</t>
+          <t>2026-10-13T23:48:08Z</t>
         </is>
       </c>
     </row>
@@ -9675,7 +9675,7 @@
       </c>
       <c r="S110" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T02:10:28Z</t>
+          <t>2026-10-13T23:48:08Z</t>
         </is>
       </c>
     </row>
@@ -9764,7 +9764,7 @@
       </c>
       <c r="S111" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T02:10:28Z</t>
+          <t>2026-10-13T23:48:08Z</t>
         </is>
       </c>
     </row>
@@ -9849,7 +9849,7 @@
       </c>
       <c r="S112" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T02:10:28Z</t>
+          <t>2026-10-13T23:48:08Z</t>
         </is>
       </c>
     </row>
@@ -9938,7 +9938,7 @@
       </c>
       <c r="S113" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T02:10:28Z</t>
+          <t>2026-10-13T23:48:08Z</t>
         </is>
       </c>
     </row>
@@ -10027,7 +10027,7 @@
       </c>
       <c r="S114" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T02:10:28Z</t>
+          <t>2026-10-13T23:48:08Z</t>
         </is>
       </c>
     </row>
@@ -10112,7 +10112,7 @@
       </c>
       <c r="S115" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T02:10:28Z</t>
+          <t>2026-10-13T23:48:08Z</t>
         </is>
       </c>
     </row>
@@ -10201,7 +10201,7 @@
       </c>
       <c r="S116" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T02:10:28Z</t>
+          <t>2026-10-13T23:48:08Z</t>
         </is>
       </c>
     </row>
@@ -10290,7 +10290,7 @@
       </c>
       <c r="S117" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T02:10:28Z</t>
+          <t>2026-10-13T23:48:08Z</t>
         </is>
       </c>
     </row>
@@ -10379,7 +10379,7 @@
       </c>
       <c r="S118" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T02:10:28Z</t>
+          <t>2026-10-13T23:48:08Z</t>
         </is>
       </c>
     </row>
@@ -10468,7 +10468,7 @@
       </c>
       <c r="S119" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T02:10:28Z</t>
+          <t>2026-10-13T23:48:08Z</t>
         </is>
       </c>
     </row>
@@ -10557,7 +10557,7 @@
       </c>
       <c r="S120" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T02:10:28Z</t>
+          <t>2026-10-13T23:48:08Z</t>
         </is>
       </c>
     </row>
@@ -10646,7 +10646,7 @@
       </c>
       <c r="S121" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T02:10:28Z</t>
+          <t>2026-10-13T23:48:08Z</t>
         </is>
       </c>
     </row>
@@ -10735,7 +10735,7 @@
       </c>
       <c r="S122" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T02:10:28Z</t>
+          <t>2026-10-13T23:48:08Z</t>
         </is>
       </c>
     </row>
@@ -10824,7 +10824,7 @@
       </c>
       <c r="S123" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T02:10:28Z</t>
+          <t>2026-10-13T23:48:08Z</t>
         </is>
       </c>
     </row>
@@ -10913,7 +10913,7 @@
       </c>
       <c r="S124" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T02:10:28Z</t>
+          <t>2026-10-13T23:48:08Z</t>
         </is>
       </c>
     </row>
@@ -11002,7 +11002,7 @@
       </c>
       <c r="S125" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T02:10:28Z</t>
+          <t>2026-10-13T23:48:08Z</t>
         </is>
       </c>
     </row>
@@ -11091,7 +11091,7 @@
       </c>
       <c r="S126" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T02:10:28Z</t>
+          <t>2026-10-13T23:48:08Z</t>
         </is>
       </c>
     </row>
@@ -11180,7 +11180,7 @@
       </c>
       <c r="S127" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T02:10:28Z</t>
+          <t>2026-10-13T23:48:08Z</t>
         </is>
       </c>
     </row>
@@ -11269,7 +11269,7 @@
       </c>
       <c r="S128" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T02:10:28Z</t>
+          <t>2026-10-13T23:48:08Z</t>
         </is>
       </c>
     </row>
@@ -11354,7 +11354,7 @@
       </c>
       <c r="S129" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T02:10:28Z</t>
+          <t>2026-10-13T23:48:08Z</t>
         </is>
       </c>
     </row>
@@ -11439,7 +11439,7 @@
       </c>
       <c r="S130" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T02:10:28Z</t>
+          <t>2026-10-13T23:48:08Z</t>
         </is>
       </c>
     </row>
@@ -11524,7 +11524,7 @@
       </c>
       <c r="S131" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T02:10:28Z</t>
+          <t>2026-10-13T23:48:08Z</t>
         </is>
       </c>
     </row>
@@ -11609,7 +11609,7 @@
       </c>
       <c r="S132" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T02:10:28Z</t>
+          <t>2026-10-13T23:48:08Z</t>
         </is>
       </c>
     </row>
@@ -11694,7 +11694,7 @@
       </c>
       <c r="S133" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T02:10:28Z</t>
+          <t>2026-10-13T23:48:08Z</t>
         </is>
       </c>
     </row>
@@ -11779,7 +11779,7 @@
       </c>
       <c r="S134" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T02:10:28Z</t>
+          <t>2026-10-13T23:48:08Z</t>
         </is>
       </c>
     </row>
@@ -11864,7 +11864,7 @@
       </c>
       <c r="S135" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T02:10:28Z</t>
+          <t>2026-10-13T23:48:08Z</t>
         </is>
       </c>
     </row>
@@ -11949,7 +11949,7 @@
       </c>
       <c r="S136" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T02:10:28Z</t>
+          <t>2026-10-13T23:48:08Z</t>
         </is>
       </c>
     </row>
@@ -12034,7 +12034,7 @@
       </c>
       <c r="S137" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T02:10:28Z</t>
+          <t>2026-10-13T23:48:08Z</t>
         </is>
       </c>
     </row>
@@ -12119,7 +12119,7 @@
       </c>
       <c r="S138" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T02:10:28Z</t>
+          <t>2026-10-13T23:48:08Z</t>
         </is>
       </c>
     </row>
@@ -12204,7 +12204,7 @@
       </c>
       <c r="S139" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T02:10:28Z</t>
+          <t>2026-10-13T23:48:08Z</t>
         </is>
       </c>
     </row>
@@ -12289,7 +12289,7 @@
       </c>
       <c r="S140" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T02:10:28Z</t>
+          <t>2026-10-13T23:48:08Z</t>
         </is>
       </c>
     </row>
@@ -12374,7 +12374,7 @@
       </c>
       <c r="S141" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T02:10:28Z</t>
+          <t>2026-10-13T23:48:08Z</t>
         </is>
       </c>
     </row>
@@ -12459,7 +12459,7 @@
       </c>
       <c r="S142" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T02:10:28Z</t>
+          <t>2026-10-13T23:48:08Z</t>
         </is>
       </c>
     </row>
@@ -12544,7 +12544,7 @@
       </c>
       <c r="S143" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T02:10:28Z</t>
+          <t>2026-10-13T23:48:08Z</t>
         </is>
       </c>
     </row>
@@ -12629,7 +12629,7 @@
       </c>
       <c r="S144" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T02:10:28Z</t>
+          <t>2026-10-13T23:48:08Z</t>
         </is>
       </c>
     </row>
@@ -12714,7 +12714,7 @@
       </c>
       <c r="S145" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T02:10:28Z</t>
+          <t>2026-10-13T23:48:08Z</t>
         </is>
       </c>
     </row>
@@ -12799,7 +12799,7 @@
       </c>
       <c r="S146" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T02:10:28Z</t>
+          <t>2026-10-13T23:48:08Z</t>
         </is>
       </c>
     </row>
@@ -12884,7 +12884,7 @@
       </c>
       <c r="S147" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T02:10:28Z</t>
+          <t>2026-10-13T23:48:08Z</t>
         </is>
       </c>
     </row>
@@ -12969,7 +12969,7 @@
       </c>
       <c r="S148" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T02:10:28Z</t>
+          <t>2026-10-13T23:48:08Z</t>
         </is>
       </c>
     </row>
@@ -13054,7 +13054,7 @@
       </c>
       <c r="S149" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T02:10:28Z</t>
+          <t>2026-10-13T23:48:08Z</t>
         </is>
       </c>
     </row>
@@ -13143,7 +13143,7 @@
       </c>
       <c r="S150" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T02:10:28Z</t>
+          <t>2026-10-13T23:48:08Z</t>
         </is>
       </c>
     </row>
@@ -13232,7 +13232,7 @@
       </c>
       <c r="S151" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T02:10:28Z</t>
+          <t>2026-10-13T23:48:08Z</t>
         </is>
       </c>
     </row>
@@ -13317,7 +13317,7 @@
       </c>
       <c r="S152" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T02:10:28Z</t>
+          <t>2026-10-13T23:48:08Z</t>
         </is>
       </c>
     </row>
@@ -13406,7 +13406,7 @@
       </c>
       <c r="S153" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T02:10:28Z</t>
+          <t>2026-10-13T23:48:08Z</t>
         </is>
       </c>
     </row>
@@ -13495,7 +13495,7 @@
       </c>
       <c r="S154" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T02:10:28Z</t>
+          <t>2026-10-13T23:48:08Z</t>
         </is>
       </c>
     </row>
@@ -13580,7 +13580,7 @@
       </c>
       <c r="S155" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T02:10:28Z</t>
+          <t>2026-10-13T23:48:08Z</t>
         </is>
       </c>
     </row>
@@ -13669,7 +13669,7 @@
       </c>
       <c r="S156" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T02:10:28Z</t>
+          <t>2026-10-13T23:48:08Z</t>
         </is>
       </c>
     </row>
@@ -13758,7 +13758,7 @@
       </c>
       <c r="S157" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T02:10:28Z</t>
+          <t>2026-10-13T23:48:08Z</t>
         </is>
       </c>
     </row>
@@ -13843,7 +13843,7 @@
       </c>
       <c r="S158" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T02:10:28Z</t>
+          <t>2026-10-13T23:48:08Z</t>
         </is>
       </c>
     </row>
@@ -13932,7 +13932,7 @@
       </c>
       <c r="S159" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T02:10:28Z</t>
+          <t>2026-10-13T23:48:08Z</t>
         </is>
       </c>
     </row>
@@ -14021,7 +14021,7 @@
       </c>
       <c r="S160" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T02:10:28Z</t>
+          <t>2026-10-13T23:48:08Z</t>
         </is>
       </c>
     </row>
@@ -14106,7 +14106,7 @@
       </c>
       <c r="S161" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T02:10:28Z</t>
+          <t>2026-10-13T23:48:08Z</t>
         </is>
       </c>
     </row>
@@ -14195,7 +14195,7 @@
       </c>
       <c r="S162" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T02:10:28Z</t>
+          <t>2026-10-13T23:48:08Z</t>
         </is>
       </c>
     </row>
@@ -14284,7 +14284,7 @@
       </c>
       <c r="S163" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T02:10:28Z</t>
+          <t>2026-10-13T23:48:08Z</t>
         </is>
       </c>
     </row>
@@ -14369,7 +14369,7 @@
       </c>
       <c r="S164" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T02:10:28Z</t>
+          <t>2026-10-13T23:48:08Z</t>
         </is>
       </c>
     </row>
@@ -14458,7 +14458,7 @@
       </c>
       <c r="S165" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T02:10:28Z</t>
+          <t>2026-10-13T23:48:08Z</t>
         </is>
       </c>
     </row>
@@ -14547,7 +14547,7 @@
       </c>
       <c r="S166" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T02:10:28Z</t>
+          <t>2026-10-13T23:48:08Z</t>
         </is>
       </c>
     </row>
@@ -14632,7 +14632,7 @@
       </c>
       <c r="S167" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T02:10:28Z</t>
+          <t>2026-10-13T23:48:08Z</t>
         </is>
       </c>
     </row>
@@ -14721,7 +14721,7 @@
       </c>
       <c r="S168" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T02:10:28Z</t>
+          <t>2026-10-13T23:48:08Z</t>
         </is>
       </c>
     </row>
@@ -14810,7 +14810,7 @@
       </c>
       <c r="S169" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T02:10:28Z</t>
+          <t>2026-10-13T23:48:08Z</t>
         </is>
       </c>
     </row>
@@ -14895,7 +14895,7 @@
       </c>
       <c r="S170" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T02:10:28Z</t>
+          <t>2026-10-13T23:48:08Z</t>
         </is>
       </c>
     </row>
@@ -14984,7 +14984,7 @@
       </c>
       <c r="S171" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T02:10:28Z</t>
+          <t>2026-10-13T23:48:08Z</t>
         </is>
       </c>
     </row>
@@ -15073,7 +15073,7 @@
       </c>
       <c r="S172" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T02:10:28Z</t>
+          <t>2026-10-13T23:48:08Z</t>
         </is>
       </c>
     </row>
@@ -15158,7 +15158,7 @@
       </c>
       <c r="S173" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T02:10:28Z</t>
+          <t>2026-10-13T23:48:08Z</t>
         </is>
       </c>
     </row>
@@ -15247,7 +15247,7 @@
       </c>
       <c r="S174" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T02:10:28Z</t>
+          <t>2026-10-13T23:48:08Z</t>
         </is>
       </c>
     </row>
@@ -15336,7 +15336,7 @@
       </c>
       <c r="S175" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T02:10:28Z</t>
+          <t>2026-10-13T23:48:08Z</t>
         </is>
       </c>
     </row>
@@ -15421,7 +15421,7 @@
       </c>
       <c r="S176" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T02:10:28Z</t>
+          <t>2026-10-13T23:48:08Z</t>
         </is>
       </c>
     </row>
@@ -15510,7 +15510,7 @@
       </c>
       <c r="S177" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T02:10:28Z</t>
+          <t>2026-10-13T23:48:08Z</t>
         </is>
       </c>
     </row>
@@ -15599,7 +15599,7 @@
       </c>
       <c r="S178" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T02:10:28Z</t>
+          <t>2026-10-13T23:48:08Z</t>
         </is>
       </c>
     </row>
@@ -15688,7 +15688,7 @@
       </c>
       <c r="S179" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T02:10:28Z</t>
+          <t>2026-10-13T23:48:08Z</t>
         </is>
       </c>
     </row>
@@ -15777,7 +15777,7 @@
       </c>
       <c r="S180" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T02:10:28Z</t>
+          <t>2026-10-13T23:48:08Z</t>
         </is>
       </c>
     </row>
@@ -15866,7 +15866,7 @@
       </c>
       <c r="S181" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T02:10:28Z</t>
+          <t>2026-10-13T23:48:08Z</t>
         </is>
       </c>
     </row>
@@ -15955,7 +15955,7 @@
       </c>
       <c r="S182" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T02:10:28Z</t>
+          <t>2026-10-13T23:48:08Z</t>
         </is>
       </c>
     </row>
@@ -16044,7 +16044,7 @@
       </c>
       <c r="S183" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T02:10:28Z</t>
+          <t>2026-10-13T23:48:08Z</t>
         </is>
       </c>
     </row>
@@ -16133,7 +16133,7 @@
       </c>
       <c r="S184" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T02:10:28Z</t>
+          <t>2026-10-13T23:48:08Z</t>
         </is>
       </c>
     </row>
@@ -16222,7 +16222,7 @@
       </c>
       <c r="S185" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T02:10:28Z</t>
+          <t>2026-10-13T23:48:08Z</t>
         </is>
       </c>
     </row>
@@ -16311,7 +16311,7 @@
       </c>
       <c r="S186" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T02:10:28Z</t>
+          <t>2026-10-13T23:48:08Z</t>
         </is>
       </c>
     </row>
@@ -16400,7 +16400,7 @@
       </c>
       <c r="S187" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T02:10:28Z</t>
+          <t>2026-10-13T23:48:08Z</t>
         </is>
       </c>
     </row>
@@ -16489,7 +16489,7 @@
       </c>
       <c r="S188" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T02:10:28Z</t>
+          <t>2026-10-13T23:48:08Z</t>
         </is>
       </c>
     </row>
@@ -16578,7 +16578,7 @@
       </c>
       <c r="S189" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T02:10:28Z</t>
+          <t>2026-10-13T23:48:08Z</t>
         </is>
       </c>
     </row>
@@ -16663,7 +16663,7 @@
       </c>
       <c r="S190" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T02:10:28Z</t>
+          <t>2026-10-13T23:48:08Z</t>
         </is>
       </c>
     </row>
@@ -16748,7 +16748,7 @@
       </c>
       <c r="S191" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T02:10:28Z</t>
+          <t>2026-10-13T23:48:08Z</t>
         </is>
       </c>
     </row>
@@ -16833,7 +16833,7 @@
       </c>
       <c r="S192" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T02:10:28Z</t>
+          <t>2026-10-13T23:48:08Z</t>
         </is>
       </c>
     </row>
@@ -16918,7 +16918,7 @@
       </c>
       <c r="S193" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T02:10:28Z</t>
+          <t>2026-10-13T23:48:08Z</t>
         </is>
       </c>
     </row>
@@ -17003,7 +17003,7 @@
       </c>
       <c r="S194" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T02:10:28Z</t>
+          <t>2026-10-13T23:48:08Z</t>
         </is>
       </c>
     </row>
@@ -17088,7 +17088,7 @@
       </c>
       <c r="S195" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T02:10:28Z</t>
+          <t>2026-10-13T23:48:08Z</t>
         </is>
       </c>
     </row>
@@ -17173,7 +17173,7 @@
       </c>
       <c r="S196" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T02:10:28Z</t>
+          <t>2026-10-13T23:48:08Z</t>
         </is>
       </c>
     </row>
@@ -17258,7 +17258,7 @@
       </c>
       <c r="S197" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T02:10:28Z</t>
+          <t>2026-10-13T23:48:08Z</t>
         </is>
       </c>
     </row>
@@ -17343,7 +17343,7 @@
       </c>
       <c r="S198" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T02:10:28Z</t>
+          <t>2026-10-13T23:48:08Z</t>
         </is>
       </c>
     </row>
@@ -17428,7 +17428,7 @@
       </c>
       <c r="S199" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T02:10:28Z</t>
+          <t>2026-10-13T23:48:08Z</t>
         </is>
       </c>
     </row>
@@ -17513,7 +17513,7 @@
       </c>
       <c r="S200" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T02:10:28Z</t>
+          <t>2026-10-13T23:48:08Z</t>
         </is>
       </c>
     </row>
@@ -17598,7 +17598,7 @@
       </c>
       <c r="S201" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T02:10:28Z</t>
+          <t>2026-10-13T23:48:08Z</t>
         </is>
       </c>
     </row>
@@ -17683,7 +17683,7 @@
       </c>
       <c r="S202" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T02:10:28Z</t>
+          <t>2026-10-13T23:48:08Z</t>
         </is>
       </c>
     </row>
@@ -17768,7 +17768,7 @@
       </c>
       <c r="S203" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T02:10:28Z</t>
+          <t>2026-10-13T23:48:08Z</t>
         </is>
       </c>
     </row>
@@ -17853,7 +17853,7 @@
       </c>
       <c r="S204" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T02:10:28Z</t>
+          <t>2026-10-13T23:48:08Z</t>
         </is>
       </c>
     </row>
@@ -17938,7 +17938,7 @@
       </c>
       <c r="S205" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T02:10:28Z</t>
+          <t>2026-10-13T23:48:08Z</t>
         </is>
       </c>
     </row>
@@ -18023,7 +18023,7 @@
       </c>
       <c r="S206" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T02:10:28Z</t>
+          <t>2026-10-13T23:48:08Z</t>
         </is>
       </c>
     </row>
@@ -18108,7 +18108,7 @@
       </c>
       <c r="S207" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T02:10:28Z</t>
+          <t>2026-10-13T23:48:08Z</t>
         </is>
       </c>
     </row>
@@ -18193,7 +18193,7 @@
       </c>
       <c r="S208" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T02:10:28Z</t>
+          <t>2026-10-13T23:48:08Z</t>
         </is>
       </c>
     </row>
@@ -18278,7 +18278,7 @@
       </c>
       <c r="S209" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T02:10:28Z</t>
+          <t>2026-10-13T23:48:08Z</t>
         </is>
       </c>
     </row>
@@ -18363,7 +18363,7 @@
       </c>
       <c r="S210" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T02:10:28Z</t>
+          <t>2026-10-13T23:48:08Z</t>
         </is>
       </c>
     </row>
@@ -18452,7 +18452,7 @@
       </c>
       <c r="S211" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T02:10:28Z</t>
+          <t>2026-10-13T23:48:08Z</t>
         </is>
       </c>
     </row>
@@ -18541,7 +18541,7 @@
       </c>
       <c r="S212" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T02:10:28Z</t>
+          <t>2026-10-13T23:48:08Z</t>
         </is>
       </c>
     </row>
@@ -18626,7 +18626,7 @@
       </c>
       <c r="S213" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T02:10:28Z</t>
+          <t>2026-10-13T23:48:08Z</t>
         </is>
       </c>
     </row>
@@ -18715,7 +18715,7 @@
       </c>
       <c r="S214" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T02:10:28Z</t>
+          <t>2026-10-13T23:48:08Z</t>
         </is>
       </c>
     </row>
@@ -18804,7 +18804,7 @@
       </c>
       <c r="S215" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T02:10:28Z</t>
+          <t>2026-10-13T23:48:08Z</t>
         </is>
       </c>
     </row>
@@ -18889,7 +18889,7 @@
       </c>
       <c r="S216" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T02:10:28Z</t>
+          <t>2026-10-13T23:48:08Z</t>
         </is>
       </c>
     </row>
@@ -18978,7 +18978,7 @@
       </c>
       <c r="S217" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T02:10:28Z</t>
+          <t>2026-10-13T23:48:08Z</t>
         </is>
       </c>
     </row>
@@ -19067,7 +19067,7 @@
       </c>
       <c r="S218" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T02:10:28Z</t>
+          <t>2026-10-13T23:48:08Z</t>
         </is>
       </c>
     </row>
@@ -19152,7 +19152,7 @@
       </c>
       <c r="S219" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T02:10:28Z</t>
+          <t>2026-10-13T23:48:08Z</t>
         </is>
       </c>
     </row>
@@ -19241,7 +19241,7 @@
       </c>
       <c r="S220" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T02:10:28Z</t>
+          <t>2026-10-13T23:48:08Z</t>
         </is>
       </c>
     </row>
@@ -19330,7 +19330,7 @@
       </c>
       <c r="S221" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T02:10:28Z</t>
+          <t>2026-10-13T23:48:08Z</t>
         </is>
       </c>
     </row>
@@ -19415,7 +19415,7 @@
       </c>
       <c r="S222" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T02:10:28Z</t>
+          <t>2026-10-13T23:48:08Z</t>
         </is>
       </c>
     </row>
@@ -19504,7 +19504,7 @@
       </c>
       <c r="S223" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T02:10:28Z</t>
+          <t>2026-10-13T23:48:08Z</t>
         </is>
       </c>
     </row>
@@ -19593,7 +19593,7 @@
       </c>
       <c r="S224" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T02:10:28Z</t>
+          <t>2026-10-13T23:48:08Z</t>
         </is>
       </c>
     </row>
@@ -19678,7 +19678,7 @@
       </c>
       <c r="S225" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T02:10:28Z</t>
+          <t>2026-10-13T23:48:08Z</t>
         </is>
       </c>
     </row>
@@ -19767,7 +19767,7 @@
       </c>
       <c r="S226" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T02:10:28Z</t>
+          <t>2026-10-13T23:48:08Z</t>
         </is>
       </c>
     </row>
@@ -19856,7 +19856,7 @@
       </c>
       <c r="S227" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T02:10:28Z</t>
+          <t>2026-10-13T23:48:08Z</t>
         </is>
       </c>
     </row>
@@ -19941,7 +19941,7 @@
       </c>
       <c r="S228" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T02:10:28Z</t>
+          <t>2026-10-13T23:48:08Z</t>
         </is>
       </c>
     </row>
@@ -20030,7 +20030,7 @@
       </c>
       <c r="S229" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T02:10:28Z</t>
+          <t>2026-10-13T23:48:08Z</t>
         </is>
       </c>
     </row>
@@ -20119,7 +20119,7 @@
       </c>
       <c r="S230" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T02:10:28Z</t>
+          <t>2026-10-13T23:48:08Z</t>
         </is>
       </c>
     </row>
@@ -20204,7 +20204,7 @@
       </c>
       <c r="S231" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T02:10:28Z</t>
+          <t>2026-10-13T23:48:08Z</t>
         </is>
       </c>
     </row>
@@ -20293,7 +20293,7 @@
       </c>
       <c r="S232" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T02:10:28Z</t>
+          <t>2026-10-13T23:48:08Z</t>
         </is>
       </c>
     </row>
@@ -20382,7 +20382,7 @@
       </c>
       <c r="S233" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T02:10:28Z</t>
+          <t>2026-10-13T23:48:08Z</t>
         </is>
       </c>
     </row>
@@ -20467,7 +20467,7 @@
       </c>
       <c r="S234" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T02:10:28Z</t>
+          <t>2026-10-13T23:48:08Z</t>
         </is>
       </c>
     </row>
@@ -20556,7 +20556,7 @@
       </c>
       <c r="S235" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T02:10:28Z</t>
+          <t>2026-10-13T23:48:08Z</t>
         </is>
       </c>
     </row>
@@ -20645,7 +20645,7 @@
       </c>
       <c r="S236" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T02:10:28Z</t>
+          <t>2026-10-13T23:48:08Z</t>
         </is>
       </c>
     </row>
@@ -20730,7 +20730,7 @@
       </c>
       <c r="S237" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T02:10:28Z</t>
+          <t>2026-10-13T23:48:08Z</t>
         </is>
       </c>
     </row>
@@ -20819,7 +20819,7 @@
       </c>
       <c r="S238" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T02:10:28Z</t>
+          <t>2026-10-13T23:48:08Z</t>
         </is>
       </c>
     </row>
@@ -20908,7 +20908,7 @@
       </c>
       <c r="S239" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T02:10:28Z</t>
+          <t>2026-10-13T23:48:08Z</t>
         </is>
       </c>
     </row>
@@ -20997,7 +20997,7 @@
       </c>
       <c r="S240" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T02:10:28Z</t>
+          <t>2026-10-13T23:48:08Z</t>
         </is>
       </c>
     </row>
@@ -21086,7 +21086,7 @@
       </c>
       <c r="S241" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T02:10:28Z</t>
+          <t>2026-10-13T23:48:08Z</t>
         </is>
       </c>
     </row>
@@ -21175,7 +21175,7 @@
       </c>
       <c r="S242" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T02:10:28Z</t>
+          <t>2026-10-13T23:48:08Z</t>
         </is>
       </c>
     </row>
@@ -21264,7 +21264,7 @@
       </c>
       <c r="S243" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T02:10:28Z</t>
+          <t>2026-10-13T23:48:08Z</t>
         </is>
       </c>
     </row>
@@ -21353,7 +21353,7 @@
       </c>
       <c r="S244" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T02:10:28Z</t>
+          <t>2026-10-13T23:48:08Z</t>
         </is>
       </c>
     </row>
@@ -21442,7 +21442,7 @@
       </c>
       <c r="S245" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T02:10:28Z</t>
+          <t>2026-10-13T23:48:08Z</t>
         </is>
       </c>
     </row>
@@ -21531,7 +21531,7 @@
       </c>
       <c r="S246" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T02:10:28Z</t>
+          <t>2026-10-13T23:48:08Z</t>
         </is>
       </c>
     </row>
@@ -21620,7 +21620,7 @@
       </c>
       <c r="S247" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T02:10:28Z</t>
+          <t>2026-10-13T23:48:08Z</t>
         </is>
       </c>
     </row>
@@ -21709,7 +21709,7 @@
       </c>
       <c r="S248" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T02:10:28Z</t>
+          <t>2026-10-13T23:48:08Z</t>
         </is>
       </c>
     </row>
@@ -21798,7 +21798,7 @@
       </c>
       <c r="S249" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T02:10:28Z</t>
+          <t>2026-10-13T23:48:08Z</t>
         </is>
       </c>
     </row>
@@ -21887,7 +21887,7 @@
       </c>
       <c r="S250" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T02:10:28Z</t>
+          <t>2026-10-13T23:48:08Z</t>
         </is>
       </c>
     </row>
@@ -22019,7 +22019,7 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T02:10:28Z</t>
+          <t>2026-10-13T23:48:08Z</t>
         </is>
       </c>
     </row>
@@ -22099,7 +22099,7 @@
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>{"dataset_id": "bcv_pib_sector_institucional_anual", "title": "Producto interno bruto por sector institucional anual", "table": "Variaciones porcentuales", "source_file": "5_2_1_si_anual.xlsx", "base": "2007", "price_type": "Precios constantes", "measure": "Variación porcentual interanual", "frequency": "Anual", "period": "2025", "year": 2025, "quarter": null, "classification": "Sector institucional", "component": "Impuestos netos sobre los productos", "value": 10.600260421283764, "unit": "Porcentaje", "status": "Preliminar", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/cuentas_macroeconomicas/5_2_1_si_anual.xlsx", "fetched_at": "2026-10-13T02:10:28Z"}</t>
+          <t>{"dataset_id": "bcv_pib_sector_institucional_anual", "title": "Producto interno bruto por sector institucional anual", "table": "Variaciones porcentuales", "source_file": "5_2_1_si_anual.xlsx", "base": "2007", "price_type": "Precios constantes", "measure": "Variación porcentual interanual", "frequency": "Anual", "period": "2025", "year": 2025, "quarter": null, "classification": "Sector institucional", "component": "Impuestos netos sobre los productos", "value": 10.600260421283764, "unit": "Porcentaje", "status": "Preliminar", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/cuentas_macroeconomicas/5_2_1_si_anual.xlsx", "fetched_at": "2026-10-13T23:48:08Z"}</t>
         </is>
       </c>
     </row>

--- a/assets/data/bcv/excel/ove_bcv_pib_sector_institucional_anual.xlsx
+++ b/assets/data/bcv/excel/ove_bcv_pib_sector_institucional_anual.xlsx
@@ -736,7 +736,7 @@
       </c>
       <c r="S7" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T23:48:08Z</t>
+          <t>2026-10-14T23:20:56Z</t>
         </is>
       </c>
     </row>
@@ -821,7 +821,7 @@
       </c>
       <c r="S8" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T23:48:08Z</t>
+          <t>2026-10-14T23:20:56Z</t>
         </is>
       </c>
     </row>
@@ -906,7 +906,7 @@
       </c>
       <c r="S9" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T23:48:08Z</t>
+          <t>2026-10-14T23:20:56Z</t>
         </is>
       </c>
     </row>
@@ -991,7 +991,7 @@
       </c>
       <c r="S10" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T23:48:08Z</t>
+          <t>2026-10-14T23:20:56Z</t>
         </is>
       </c>
     </row>
@@ -1076,7 +1076,7 @@
       </c>
       <c r="S11" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T23:48:08Z</t>
+          <t>2026-10-14T23:20:56Z</t>
         </is>
       </c>
     </row>
@@ -1161,7 +1161,7 @@
       </c>
       <c r="S12" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T23:48:08Z</t>
+          <t>2026-10-14T23:20:56Z</t>
         </is>
       </c>
     </row>
@@ -1246,7 +1246,7 @@
       </c>
       <c r="S13" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T23:48:08Z</t>
+          <t>2026-10-14T23:20:56Z</t>
         </is>
       </c>
     </row>
@@ -1331,7 +1331,7 @@
       </c>
       <c r="S14" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T23:48:08Z</t>
+          <t>2026-10-14T23:20:56Z</t>
         </is>
       </c>
     </row>
@@ -1416,7 +1416,7 @@
       </c>
       <c r="S15" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T23:48:08Z</t>
+          <t>2026-10-14T23:20:56Z</t>
         </is>
       </c>
     </row>
@@ -1501,7 +1501,7 @@
       </c>
       <c r="S16" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T23:48:08Z</t>
+          <t>2026-10-14T23:20:56Z</t>
         </is>
       </c>
     </row>
@@ -1586,7 +1586,7 @@
       </c>
       <c r="S17" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T23:48:08Z</t>
+          <t>2026-10-14T23:20:56Z</t>
         </is>
       </c>
     </row>
@@ -1671,7 +1671,7 @@
       </c>
       <c r="S18" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T23:48:08Z</t>
+          <t>2026-10-14T23:20:56Z</t>
         </is>
       </c>
     </row>
@@ -1756,7 +1756,7 @@
       </c>
       <c r="S19" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T23:48:08Z</t>
+          <t>2026-10-14T23:20:56Z</t>
         </is>
       </c>
     </row>
@@ -1841,7 +1841,7 @@
       </c>
       <c r="S20" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T23:48:08Z</t>
+          <t>2026-10-14T23:20:56Z</t>
         </is>
       </c>
     </row>
@@ -1926,7 +1926,7 @@
       </c>
       <c r="S21" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T23:48:08Z</t>
+          <t>2026-10-14T23:20:56Z</t>
         </is>
       </c>
     </row>
@@ -2011,7 +2011,7 @@
       </c>
       <c r="S22" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T23:48:08Z</t>
+          <t>2026-10-14T23:20:56Z</t>
         </is>
       </c>
     </row>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="S23" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T23:48:08Z</t>
+          <t>2026-10-14T23:20:56Z</t>
         </is>
       </c>
     </row>
@@ -2181,7 +2181,7 @@
       </c>
       <c r="S24" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T23:48:08Z</t>
+          <t>2026-10-14T23:20:56Z</t>
         </is>
       </c>
     </row>
@@ -2266,7 +2266,7 @@
       </c>
       <c r="S25" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T23:48:08Z</t>
+          <t>2026-10-14T23:20:56Z</t>
         </is>
       </c>
     </row>
@@ -2351,7 +2351,7 @@
       </c>
       <c r="S26" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T23:48:08Z</t>
+          <t>2026-10-14T23:20:56Z</t>
         </is>
       </c>
     </row>
@@ -2436,7 +2436,7 @@
       </c>
       <c r="S27" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T23:48:08Z</t>
+          <t>2026-10-14T23:20:56Z</t>
         </is>
       </c>
     </row>
@@ -2525,7 +2525,7 @@
       </c>
       <c r="S28" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T23:48:08Z</t>
+          <t>2026-10-14T23:20:56Z</t>
         </is>
       </c>
     </row>
@@ -2614,7 +2614,7 @@
       </c>
       <c r="S29" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T23:48:08Z</t>
+          <t>2026-10-14T23:20:56Z</t>
         </is>
       </c>
     </row>
@@ -2699,7 +2699,7 @@
       </c>
       <c r="S30" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T23:48:08Z</t>
+          <t>2026-10-14T23:20:56Z</t>
         </is>
       </c>
     </row>
@@ -2788,7 +2788,7 @@
       </c>
       <c r="S31" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T23:48:08Z</t>
+          <t>2026-10-14T23:20:56Z</t>
         </is>
       </c>
     </row>
@@ -2877,7 +2877,7 @@
       </c>
       <c r="S32" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T23:48:08Z</t>
+          <t>2026-10-14T23:20:56Z</t>
         </is>
       </c>
     </row>
@@ -2962,7 +2962,7 @@
       </c>
       <c r="S33" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T23:48:08Z</t>
+          <t>2026-10-14T23:20:56Z</t>
         </is>
       </c>
     </row>
@@ -3051,7 +3051,7 @@
       </c>
       <c r="S34" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T23:48:08Z</t>
+          <t>2026-10-14T23:20:56Z</t>
         </is>
       </c>
     </row>
@@ -3140,7 +3140,7 @@
       </c>
       <c r="S35" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T23:48:08Z</t>
+          <t>2026-10-14T23:20:56Z</t>
         </is>
       </c>
     </row>
@@ -3225,7 +3225,7 @@
       </c>
       <c r="S36" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T23:48:08Z</t>
+          <t>2026-10-14T23:20:56Z</t>
         </is>
       </c>
     </row>
@@ -3314,7 +3314,7 @@
       </c>
       <c r="S37" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T23:48:08Z</t>
+          <t>2026-10-14T23:20:56Z</t>
         </is>
       </c>
     </row>
@@ -3403,7 +3403,7 @@
       </c>
       <c r="S38" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T23:48:08Z</t>
+          <t>2026-10-14T23:20:56Z</t>
         </is>
       </c>
     </row>
@@ -3488,7 +3488,7 @@
       </c>
       <c r="S39" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T23:48:08Z</t>
+          <t>2026-10-14T23:20:56Z</t>
         </is>
       </c>
     </row>
@@ -3577,7 +3577,7 @@
       </c>
       <c r="S40" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T23:48:08Z</t>
+          <t>2026-10-14T23:20:56Z</t>
         </is>
       </c>
     </row>
@@ -3666,7 +3666,7 @@
       </c>
       <c r="S41" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T23:48:08Z</t>
+          <t>2026-10-14T23:20:56Z</t>
         </is>
       </c>
     </row>
@@ -3751,7 +3751,7 @@
       </c>
       <c r="S42" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T23:48:08Z</t>
+          <t>2026-10-14T23:20:56Z</t>
         </is>
       </c>
     </row>
@@ -3840,7 +3840,7 @@
       </c>
       <c r="S43" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T23:48:08Z</t>
+          <t>2026-10-14T23:20:56Z</t>
         </is>
       </c>
     </row>
@@ -3929,7 +3929,7 @@
       </c>
       <c r="S44" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T23:48:08Z</t>
+          <t>2026-10-14T23:20:56Z</t>
         </is>
       </c>
     </row>
@@ -4014,7 +4014,7 @@
       </c>
       <c r="S45" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T23:48:08Z</t>
+          <t>2026-10-14T23:20:56Z</t>
         </is>
       </c>
     </row>
@@ -4103,7 +4103,7 @@
       </c>
       <c r="S46" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T23:48:08Z</t>
+          <t>2026-10-14T23:20:56Z</t>
         </is>
       </c>
     </row>
@@ -4192,7 +4192,7 @@
       </c>
       <c r="S47" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T23:48:08Z</t>
+          <t>2026-10-14T23:20:56Z</t>
         </is>
       </c>
     </row>
@@ -4277,7 +4277,7 @@
       </c>
       <c r="S48" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T23:48:08Z</t>
+          <t>2026-10-14T23:20:56Z</t>
         </is>
       </c>
     </row>
@@ -4366,7 +4366,7 @@
       </c>
       <c r="S49" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T23:48:08Z</t>
+          <t>2026-10-14T23:20:56Z</t>
         </is>
       </c>
     </row>
@@ -4455,7 +4455,7 @@
       </c>
       <c r="S50" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T23:48:08Z</t>
+          <t>2026-10-14T23:20:56Z</t>
         </is>
       </c>
     </row>
@@ -4540,7 +4540,7 @@
       </c>
       <c r="S51" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T23:48:08Z</t>
+          <t>2026-10-14T23:20:56Z</t>
         </is>
       </c>
     </row>
@@ -4629,7 +4629,7 @@
       </c>
       <c r="S52" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T23:48:08Z</t>
+          <t>2026-10-14T23:20:56Z</t>
         </is>
       </c>
     </row>
@@ -4718,7 +4718,7 @@
       </c>
       <c r="S53" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T23:48:08Z</t>
+          <t>2026-10-14T23:20:56Z</t>
         </is>
       </c>
     </row>
@@ -4803,7 +4803,7 @@
       </c>
       <c r="S54" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T23:48:08Z</t>
+          <t>2026-10-14T23:20:56Z</t>
         </is>
       </c>
     </row>
@@ -4892,7 +4892,7 @@
       </c>
       <c r="S55" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T23:48:08Z</t>
+          <t>2026-10-14T23:20:56Z</t>
         </is>
       </c>
     </row>
@@ -4981,7 +4981,7 @@
       </c>
       <c r="S56" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T23:48:08Z</t>
+          <t>2026-10-14T23:20:56Z</t>
         </is>
       </c>
     </row>
@@ -5070,7 +5070,7 @@
       </c>
       <c r="S57" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T23:48:08Z</t>
+          <t>2026-10-14T23:20:56Z</t>
         </is>
       </c>
     </row>
@@ -5159,7 +5159,7 @@
       </c>
       <c r="S58" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T23:48:08Z</t>
+          <t>2026-10-14T23:20:56Z</t>
         </is>
       </c>
     </row>
@@ -5248,7 +5248,7 @@
       </c>
       <c r="S59" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T23:48:08Z</t>
+          <t>2026-10-14T23:20:56Z</t>
         </is>
       </c>
     </row>
@@ -5337,7 +5337,7 @@
       </c>
       <c r="S60" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T23:48:08Z</t>
+          <t>2026-10-14T23:20:56Z</t>
         </is>
       </c>
     </row>
@@ -5426,7 +5426,7 @@
       </c>
       <c r="S61" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T23:48:08Z</t>
+          <t>2026-10-14T23:20:56Z</t>
         </is>
       </c>
     </row>
@@ -5515,7 +5515,7 @@
       </c>
       <c r="S62" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T23:48:08Z</t>
+          <t>2026-10-14T23:20:56Z</t>
         </is>
       </c>
     </row>
@@ -5604,7 +5604,7 @@
       </c>
       <c r="S63" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T23:48:08Z</t>
+          <t>2026-10-14T23:20:56Z</t>
         </is>
       </c>
     </row>
@@ -5693,7 +5693,7 @@
       </c>
       <c r="S64" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T23:48:08Z</t>
+          <t>2026-10-14T23:20:56Z</t>
         </is>
       </c>
     </row>
@@ -5782,7 +5782,7 @@
       </c>
       <c r="S65" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T23:48:08Z</t>
+          <t>2026-10-14T23:20:56Z</t>
         </is>
       </c>
     </row>
@@ -5871,7 +5871,7 @@
       </c>
       <c r="S66" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T23:48:08Z</t>
+          <t>2026-10-14T23:20:56Z</t>
         </is>
       </c>
     </row>
@@ -5960,7 +5960,7 @@
       </c>
       <c r="S67" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T23:48:08Z</t>
+          <t>2026-10-14T23:20:56Z</t>
         </is>
       </c>
     </row>
@@ -6045,7 +6045,7 @@
       </c>
       <c r="S68" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T23:48:08Z</t>
+          <t>2026-10-14T23:20:56Z</t>
         </is>
       </c>
     </row>
@@ -6130,7 +6130,7 @@
       </c>
       <c r="S69" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T23:48:08Z</t>
+          <t>2026-10-14T23:20:56Z</t>
         </is>
       </c>
     </row>
@@ -6215,7 +6215,7 @@
       </c>
       <c r="S70" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T23:48:08Z</t>
+          <t>2026-10-14T23:20:56Z</t>
         </is>
       </c>
     </row>
@@ -6300,7 +6300,7 @@
       </c>
       <c r="S71" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T23:48:08Z</t>
+          <t>2026-10-14T23:20:56Z</t>
         </is>
       </c>
     </row>
@@ -6385,7 +6385,7 @@
       </c>
       <c r="S72" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T23:48:08Z</t>
+          <t>2026-10-14T23:20:56Z</t>
         </is>
       </c>
     </row>
@@ -6470,7 +6470,7 @@
       </c>
       <c r="S73" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T23:48:08Z</t>
+          <t>2026-10-14T23:20:56Z</t>
         </is>
       </c>
     </row>
@@ -6555,7 +6555,7 @@
       </c>
       <c r="S74" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T23:48:08Z</t>
+          <t>2026-10-14T23:20:56Z</t>
         </is>
       </c>
     </row>
@@ -6640,7 +6640,7 @@
       </c>
       <c r="S75" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T23:48:08Z</t>
+          <t>2026-10-14T23:20:56Z</t>
         </is>
       </c>
     </row>
@@ -6725,7 +6725,7 @@
       </c>
       <c r="S76" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T23:48:08Z</t>
+          <t>2026-10-14T23:20:56Z</t>
         </is>
       </c>
     </row>
@@ -6810,7 +6810,7 @@
       </c>
       <c r="S77" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T23:48:08Z</t>
+          <t>2026-10-14T23:20:56Z</t>
         </is>
       </c>
     </row>
@@ -6895,7 +6895,7 @@
       </c>
       <c r="S78" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T23:48:08Z</t>
+          <t>2026-10-14T23:20:56Z</t>
         </is>
       </c>
     </row>
@@ -6980,7 +6980,7 @@
       </c>
       <c r="S79" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T23:48:08Z</t>
+          <t>2026-10-14T23:20:56Z</t>
         </is>
       </c>
     </row>
@@ -7065,7 +7065,7 @@
       </c>
       <c r="S80" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T23:48:08Z</t>
+          <t>2026-10-14T23:20:56Z</t>
         </is>
       </c>
     </row>
@@ -7150,7 +7150,7 @@
       </c>
       <c r="S81" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T23:48:08Z</t>
+          <t>2026-10-14T23:20:56Z</t>
         </is>
       </c>
     </row>
@@ -7235,7 +7235,7 @@
       </c>
       <c r="S82" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T23:48:08Z</t>
+          <t>2026-10-14T23:20:56Z</t>
         </is>
       </c>
     </row>
@@ -7320,7 +7320,7 @@
       </c>
       <c r="S83" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T23:48:08Z</t>
+          <t>2026-10-14T23:20:56Z</t>
         </is>
       </c>
     </row>
@@ -7405,7 +7405,7 @@
       </c>
       <c r="S84" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T23:48:08Z</t>
+          <t>2026-10-14T23:20:56Z</t>
         </is>
       </c>
     </row>
@@ -7490,7 +7490,7 @@
       </c>
       <c r="S85" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T23:48:08Z</t>
+          <t>2026-10-14T23:20:56Z</t>
         </is>
       </c>
     </row>
@@ -7575,7 +7575,7 @@
       </c>
       <c r="S86" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T23:48:08Z</t>
+          <t>2026-10-14T23:20:56Z</t>
         </is>
       </c>
     </row>
@@ -7660,7 +7660,7 @@
       </c>
       <c r="S87" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T23:48:08Z</t>
+          <t>2026-10-14T23:20:56Z</t>
         </is>
       </c>
     </row>
@@ -7745,7 +7745,7 @@
       </c>
       <c r="S88" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T23:48:08Z</t>
+          <t>2026-10-14T23:20:56Z</t>
         </is>
       </c>
     </row>
@@ -7834,7 +7834,7 @@
       </c>
       <c r="S89" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T23:48:08Z</t>
+          <t>2026-10-14T23:20:56Z</t>
         </is>
       </c>
     </row>
@@ -7923,7 +7923,7 @@
       </c>
       <c r="S90" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T23:48:08Z</t>
+          <t>2026-10-14T23:20:56Z</t>
         </is>
       </c>
     </row>
@@ -8008,7 +8008,7 @@
       </c>
       <c r="S91" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T23:48:08Z</t>
+          <t>2026-10-14T23:20:56Z</t>
         </is>
       </c>
     </row>
@@ -8097,7 +8097,7 @@
       </c>
       <c r="S92" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T23:48:08Z</t>
+          <t>2026-10-14T23:20:56Z</t>
         </is>
       </c>
     </row>
@@ -8186,7 +8186,7 @@
       </c>
       <c r="S93" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T23:48:08Z</t>
+          <t>2026-10-14T23:20:56Z</t>
         </is>
       </c>
     </row>
@@ -8271,7 +8271,7 @@
       </c>
       <c r="S94" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T23:48:08Z</t>
+          <t>2026-10-14T23:20:56Z</t>
         </is>
       </c>
     </row>
@@ -8360,7 +8360,7 @@
       </c>
       <c r="S95" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T23:48:08Z</t>
+          <t>2026-10-14T23:20:56Z</t>
         </is>
       </c>
     </row>
@@ -8449,7 +8449,7 @@
       </c>
       <c r="S96" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T23:48:08Z</t>
+          <t>2026-10-14T23:20:56Z</t>
         </is>
       </c>
     </row>
@@ -8534,7 +8534,7 @@
       </c>
       <c r="S97" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T23:48:08Z</t>
+          <t>2026-10-14T23:20:56Z</t>
         </is>
       </c>
     </row>
@@ -8623,7 +8623,7 @@
       </c>
       <c r="S98" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T23:48:08Z</t>
+          <t>2026-10-14T23:20:56Z</t>
         </is>
       </c>
     </row>
@@ -8712,7 +8712,7 @@
       </c>
       <c r="S99" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T23:48:08Z</t>
+          <t>2026-10-14T23:20:56Z</t>
         </is>
       </c>
     </row>
@@ -8797,7 +8797,7 @@
       </c>
       <c r="S100" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T23:48:08Z</t>
+          <t>2026-10-14T23:20:56Z</t>
         </is>
       </c>
     </row>
@@ -8886,7 +8886,7 @@
       </c>
       <c r="S101" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T23:48:08Z</t>
+          <t>2026-10-14T23:20:56Z</t>
         </is>
       </c>
     </row>
@@ -8975,7 +8975,7 @@
       </c>
       <c r="S102" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T23:48:08Z</t>
+          <t>2026-10-14T23:20:56Z</t>
         </is>
       </c>
     </row>
@@ -9060,7 +9060,7 @@
       </c>
       <c r="S103" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T23:48:08Z</t>
+          <t>2026-10-14T23:20:56Z</t>
         </is>
       </c>
     </row>
@@ -9149,7 +9149,7 @@
       </c>
       <c r="S104" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T23:48:08Z</t>
+          <t>2026-10-14T23:20:56Z</t>
         </is>
       </c>
     </row>
@@ -9238,7 +9238,7 @@
       </c>
       <c r="S105" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T23:48:08Z</t>
+          <t>2026-10-14T23:20:56Z</t>
         </is>
       </c>
     </row>
@@ -9323,7 +9323,7 @@
       </c>
       <c r="S106" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T23:48:08Z</t>
+          <t>2026-10-14T23:20:56Z</t>
         </is>
       </c>
     </row>
@@ -9412,7 +9412,7 @@
       </c>
       <c r="S107" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T23:48:08Z</t>
+          <t>2026-10-14T23:20:56Z</t>
         </is>
       </c>
     </row>
@@ -9501,7 +9501,7 @@
       </c>
       <c r="S108" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T23:48:08Z</t>
+          <t>2026-10-14T23:20:56Z</t>
         </is>
       </c>
     </row>
@@ -9586,7 +9586,7 @@
       </c>
       <c r="S109" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T23:48:08Z</t>
+          <t>2026-10-14T23:20:56Z</t>
         </is>
       </c>
     </row>
@@ -9675,7 +9675,7 @@
       </c>
       <c r="S110" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T23:48:08Z</t>
+          <t>2026-10-14T23:20:56Z</t>
         </is>
       </c>
     </row>
@@ -9764,7 +9764,7 @@
       </c>
       <c r="S111" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T23:48:08Z</t>
+          <t>2026-10-14T23:20:56Z</t>
         </is>
       </c>
     </row>
@@ -9849,7 +9849,7 @@
       </c>
       <c r="S112" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T23:48:08Z</t>
+          <t>2026-10-14T23:20:56Z</t>
         </is>
       </c>
     </row>
@@ -9938,7 +9938,7 @@
       </c>
       <c r="S113" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T23:48:08Z</t>
+          <t>2026-10-14T23:20:56Z</t>
         </is>
       </c>
     </row>
@@ -10027,7 +10027,7 @@
       </c>
       <c r="S114" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T23:48:08Z</t>
+          <t>2026-10-14T23:20:56Z</t>
         </is>
       </c>
     </row>
@@ -10112,7 +10112,7 @@
       </c>
       <c r="S115" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T23:48:08Z</t>
+          <t>2026-10-14T23:20:56Z</t>
         </is>
       </c>
     </row>
@@ -10201,7 +10201,7 @@
       </c>
       <c r="S116" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T23:48:08Z</t>
+          <t>2026-10-14T23:20:56Z</t>
         </is>
       </c>
     </row>
@@ -10290,7 +10290,7 @@
       </c>
       <c r="S117" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T23:48:08Z</t>
+          <t>2026-10-14T23:20:56Z</t>
         </is>
       </c>
     </row>
@@ -10379,7 +10379,7 @@
       </c>
       <c r="S118" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T23:48:08Z</t>
+          <t>2026-10-14T23:20:56Z</t>
         </is>
       </c>
     </row>
@@ -10468,7 +10468,7 @@
       </c>
       <c r="S119" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T23:48:08Z</t>
+          <t>2026-10-14T23:20:56Z</t>
         </is>
       </c>
     </row>
@@ -10557,7 +10557,7 @@
       </c>
       <c r="S120" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T23:48:08Z</t>
+          <t>2026-10-14T23:20:56Z</t>
         </is>
       </c>
     </row>
@@ -10646,7 +10646,7 @@
       </c>
       <c r="S121" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T23:48:08Z</t>
+          <t>2026-10-14T23:20:56Z</t>
         </is>
       </c>
     </row>
@@ -10735,7 +10735,7 @@
       </c>
       <c r="S122" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T23:48:08Z</t>
+          <t>2026-10-14T23:20:56Z</t>
         </is>
       </c>
     </row>
@@ -10824,7 +10824,7 @@
       </c>
       <c r="S123" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T23:48:08Z</t>
+          <t>2026-10-14T23:20:56Z</t>
         </is>
       </c>
     </row>
@@ -10913,7 +10913,7 @@
       </c>
       <c r="S124" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T23:48:08Z</t>
+          <t>2026-10-14T23:20:56Z</t>
         </is>
       </c>
     </row>
@@ -11002,7 +11002,7 @@
       </c>
       <c r="S125" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T23:48:08Z</t>
+          <t>2026-10-14T23:20:56Z</t>
         </is>
       </c>
     </row>
@@ -11091,7 +11091,7 @@
       </c>
       <c r="S126" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T23:48:08Z</t>
+          <t>2026-10-14T23:20:56Z</t>
         </is>
       </c>
     </row>
@@ -11180,7 +11180,7 @@
       </c>
       <c r="S127" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T23:48:08Z</t>
+          <t>2026-10-14T23:20:56Z</t>
         </is>
       </c>
     </row>
@@ -11269,7 +11269,7 @@
       </c>
       <c r="S128" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T23:48:08Z</t>
+          <t>2026-10-14T23:20:56Z</t>
         </is>
       </c>
     </row>
@@ -11354,7 +11354,7 @@
       </c>
       <c r="S129" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T23:48:08Z</t>
+          <t>2026-10-14T23:20:56Z</t>
         </is>
       </c>
     </row>
@@ -11439,7 +11439,7 @@
       </c>
       <c r="S130" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T23:48:08Z</t>
+          <t>2026-10-14T23:20:56Z</t>
         </is>
       </c>
     </row>
@@ -11524,7 +11524,7 @@
       </c>
       <c r="S131" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T23:48:08Z</t>
+          <t>2026-10-14T23:20:56Z</t>
         </is>
       </c>
     </row>
@@ -11609,7 +11609,7 @@
       </c>
       <c r="S132" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T23:48:08Z</t>
+          <t>2026-10-14T23:20:56Z</t>
         </is>
       </c>
     </row>
@@ -11694,7 +11694,7 @@
       </c>
       <c r="S133" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T23:48:08Z</t>
+          <t>2026-10-14T23:20:56Z</t>
         </is>
       </c>
     </row>
@@ -11779,7 +11779,7 @@
       </c>
       <c r="S134" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T23:48:08Z</t>
+          <t>2026-10-14T23:20:56Z</t>
         </is>
       </c>
     </row>
@@ -11864,7 +11864,7 @@
       </c>
       <c r="S135" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T23:48:08Z</t>
+          <t>2026-10-14T23:20:56Z</t>
         </is>
       </c>
     </row>
@@ -11949,7 +11949,7 @@
       </c>
       <c r="S136" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T23:48:08Z</t>
+          <t>2026-10-14T23:20:56Z</t>
         </is>
       </c>
     </row>
@@ -12034,7 +12034,7 @@
       </c>
       <c r="S137" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T23:48:08Z</t>
+          <t>2026-10-14T23:20:56Z</t>
         </is>
       </c>
     </row>
@@ -12119,7 +12119,7 @@
       </c>
       <c r="S138" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T23:48:08Z</t>
+          <t>2026-10-14T23:20:56Z</t>
         </is>
       </c>
     </row>
@@ -12204,7 +12204,7 @@
       </c>
       <c r="S139" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T23:48:08Z</t>
+          <t>2026-10-14T23:20:56Z</t>
         </is>
       </c>
     </row>
@@ -12289,7 +12289,7 @@
       </c>
       <c r="S140" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T23:48:08Z</t>
+          <t>2026-10-14T23:20:56Z</t>
         </is>
       </c>
     </row>
@@ -12374,7 +12374,7 @@
       </c>
       <c r="S141" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T23:48:08Z</t>
+          <t>2026-10-14T23:20:56Z</t>
         </is>
       </c>
     </row>
@@ -12459,7 +12459,7 @@
       </c>
       <c r="S142" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T23:48:08Z</t>
+          <t>2026-10-14T23:20:56Z</t>
         </is>
       </c>
     </row>
@@ -12544,7 +12544,7 @@
       </c>
       <c r="S143" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T23:48:08Z</t>
+          <t>2026-10-14T23:20:56Z</t>
         </is>
       </c>
     </row>
@@ -12629,7 +12629,7 @@
       </c>
       <c r="S144" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T23:48:08Z</t>
+          <t>2026-10-14T23:20:56Z</t>
         </is>
       </c>
     </row>
@@ -12714,7 +12714,7 @@
       </c>
       <c r="S145" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T23:48:08Z</t>
+          <t>2026-10-14T23:20:56Z</t>
         </is>
       </c>
     </row>
@@ -12799,7 +12799,7 @@
       </c>
       <c r="S146" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T23:48:08Z</t>
+          <t>2026-10-14T23:20:56Z</t>
         </is>
       </c>
     </row>
@@ -12884,7 +12884,7 @@
       </c>
       <c r="S147" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T23:48:08Z</t>
+          <t>2026-10-14T23:20:56Z</t>
         </is>
       </c>
     </row>
@@ -12969,7 +12969,7 @@
       </c>
       <c r="S148" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T23:48:08Z</t>
+          <t>2026-10-14T23:20:56Z</t>
         </is>
       </c>
     </row>
@@ -13054,7 +13054,7 @@
       </c>
       <c r="S149" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T23:48:08Z</t>
+          <t>2026-10-14T23:20:56Z</t>
         </is>
       </c>
     </row>
@@ -13143,7 +13143,7 @@
       </c>
       <c r="S150" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T23:48:08Z</t>
+          <t>2026-10-14T23:20:56Z</t>
         </is>
       </c>
     </row>
@@ -13232,7 +13232,7 @@
       </c>
       <c r="S151" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T23:48:08Z</t>
+          <t>2026-10-14T23:20:56Z</t>
         </is>
       </c>
     </row>
@@ -13317,7 +13317,7 @@
       </c>
       <c r="S152" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T23:48:08Z</t>
+          <t>2026-10-14T23:20:56Z</t>
         </is>
       </c>
     </row>
@@ -13406,7 +13406,7 @@
       </c>
       <c r="S153" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T23:48:08Z</t>
+          <t>2026-10-14T23:20:56Z</t>
         </is>
       </c>
     </row>
@@ -13495,7 +13495,7 @@
       </c>
       <c r="S154" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T23:48:08Z</t>
+          <t>2026-10-14T23:20:56Z</t>
         </is>
       </c>
     </row>
@@ -13580,7 +13580,7 @@
       </c>
       <c r="S155" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T23:48:08Z</t>
+          <t>2026-10-14T23:20:56Z</t>
         </is>
       </c>
     </row>
@@ -13669,7 +13669,7 @@
       </c>
       <c r="S156" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T23:48:08Z</t>
+          <t>2026-10-14T23:20:56Z</t>
         </is>
       </c>
     </row>
@@ -13758,7 +13758,7 @@
       </c>
       <c r="S157" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T23:48:08Z</t>
+          <t>2026-10-14T23:20:56Z</t>
         </is>
       </c>
     </row>
@@ -13843,7 +13843,7 @@
       </c>
       <c r="S158" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T23:48:08Z</t>
+          <t>2026-10-14T23:20:56Z</t>
         </is>
       </c>
     </row>
@@ -13932,7 +13932,7 @@
       </c>
       <c r="S159" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T23:48:08Z</t>
+          <t>2026-10-14T23:20:56Z</t>
         </is>
       </c>
     </row>
@@ -14021,7 +14021,7 @@
       </c>
       <c r="S160" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T23:48:08Z</t>
+          <t>2026-10-14T23:20:56Z</t>
         </is>
       </c>
     </row>
@@ -14106,7 +14106,7 @@
       </c>
       <c r="S161" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T23:48:08Z</t>
+          <t>2026-10-14T23:20:56Z</t>
         </is>
       </c>
     </row>
@@ -14195,7 +14195,7 @@
       </c>
       <c r="S162" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T23:48:08Z</t>
+          <t>2026-10-14T23:20:56Z</t>
         </is>
       </c>
     </row>
@@ -14284,7 +14284,7 @@
       </c>
       <c r="S163" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T23:48:08Z</t>
+          <t>2026-10-14T23:20:56Z</t>
         </is>
       </c>
     </row>
@@ -14369,7 +14369,7 @@
       </c>
       <c r="S164" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T23:48:08Z</t>
+          <t>2026-10-14T23:20:56Z</t>
         </is>
       </c>
     </row>
@@ -14458,7 +14458,7 @@
       </c>
       <c r="S165" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T23:48:08Z</t>
+          <t>2026-10-14T23:20:56Z</t>
         </is>
       </c>
     </row>
@@ -14547,7 +14547,7 @@
       </c>
       <c r="S166" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T23:48:08Z</t>
+          <t>2026-10-14T23:20:56Z</t>
         </is>
       </c>
     </row>
@@ -14632,7 +14632,7 @@
       </c>
       <c r="S167" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T23:48:08Z</t>
+          <t>2026-10-14T23:20:56Z</t>
         </is>
       </c>
     </row>
@@ -14721,7 +14721,7 @@
       </c>
       <c r="S168" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T23:48:08Z</t>
+          <t>2026-10-14T23:20:56Z</t>
         </is>
       </c>
     </row>
@@ -14810,7 +14810,7 @@
       </c>
       <c r="S169" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T23:48:08Z</t>
+          <t>2026-10-14T23:20:56Z</t>
         </is>
       </c>
     </row>
@@ -14895,7 +14895,7 @@
       </c>
       <c r="S170" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T23:48:08Z</t>
+          <t>2026-10-14T23:20:56Z</t>
         </is>
       </c>
     </row>
@@ -14984,7 +14984,7 @@
       </c>
       <c r="S171" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T23:48:08Z</t>
+          <t>2026-10-14T23:20:56Z</t>
         </is>
       </c>
     </row>
@@ -15073,7 +15073,7 @@
       </c>
       <c r="S172" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T23:48:08Z</t>
+          <t>2026-10-14T23:20:56Z</t>
         </is>
       </c>
     </row>
@@ -15158,7 +15158,7 @@
       </c>
       <c r="S173" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T23:48:08Z</t>
+          <t>2026-10-14T23:20:56Z</t>
         </is>
       </c>
     </row>
@@ -15247,7 +15247,7 @@
       </c>
       <c r="S174" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T23:48:08Z</t>
+          <t>2026-10-14T23:20:56Z</t>
         </is>
       </c>
     </row>
@@ -15336,7 +15336,7 @@
       </c>
       <c r="S175" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T23:48:08Z</t>
+          <t>2026-10-14T23:20:56Z</t>
         </is>
       </c>
     </row>
@@ -15421,7 +15421,7 @@
       </c>
       <c r="S176" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T23:48:08Z</t>
+          <t>2026-10-14T23:20:56Z</t>
         </is>
       </c>
     </row>
@@ -15510,7 +15510,7 @@
       </c>
       <c r="S177" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T23:48:08Z</t>
+          <t>2026-10-14T23:20:56Z</t>
         </is>
       </c>
     </row>
@@ -15599,7 +15599,7 @@
       </c>
       <c r="S178" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T23:48:08Z</t>
+          <t>2026-10-14T23:20:56Z</t>
         </is>
       </c>
     </row>
@@ -15688,7 +15688,7 @@
       </c>
       <c r="S179" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T23:48:08Z</t>
+          <t>2026-10-14T23:20:56Z</t>
         </is>
       </c>
     </row>
@@ -15777,7 +15777,7 @@
       </c>
       <c r="S180" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T23:48:08Z</t>
+          <t>2026-10-14T23:20:56Z</t>
         </is>
       </c>
     </row>
@@ -15866,7 +15866,7 @@
       </c>
       <c r="S181" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T23:48:08Z</t>
+          <t>2026-10-14T23:20:56Z</t>
         </is>
       </c>
     </row>
@@ -15955,7 +15955,7 @@
       </c>
       <c r="S182" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T23:48:08Z</t>
+          <t>2026-10-14T23:20:56Z</t>
         </is>
       </c>
     </row>
@@ -16044,7 +16044,7 @@
       </c>
       <c r="S183" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T23:48:08Z</t>
+          <t>2026-10-14T23:20:56Z</t>
         </is>
       </c>
     </row>
@@ -16133,7 +16133,7 @@
       </c>
       <c r="S184" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T23:48:08Z</t>
+          <t>2026-10-14T23:20:56Z</t>
         </is>
       </c>
     </row>
@@ -16222,7 +16222,7 @@
       </c>
       <c r="S185" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T23:48:08Z</t>
+          <t>2026-10-14T23:20:56Z</t>
         </is>
       </c>
     </row>
@@ -16311,7 +16311,7 @@
       </c>
       <c r="S186" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T23:48:08Z</t>
+          <t>2026-10-14T23:20:56Z</t>
         </is>
       </c>
     </row>
@@ -16400,7 +16400,7 @@
       </c>
       <c r="S187" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T23:48:08Z</t>
+          <t>2026-10-14T23:20:56Z</t>
         </is>
       </c>
     </row>
@@ -16489,7 +16489,7 @@
       </c>
       <c r="S188" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T23:48:08Z</t>
+          <t>2026-10-14T23:20:56Z</t>
         </is>
       </c>
     </row>
@@ -16578,7 +16578,7 @@
       </c>
       <c r="S189" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T23:48:08Z</t>
+          <t>2026-10-14T23:20:56Z</t>
         </is>
       </c>
     </row>
@@ -16663,7 +16663,7 @@
       </c>
       <c r="S190" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T23:48:08Z</t>
+          <t>2026-10-14T23:20:56Z</t>
         </is>
       </c>
     </row>
@@ -16748,7 +16748,7 @@
       </c>
       <c r="S191" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T23:48:08Z</t>
+          <t>2026-10-14T23:20:56Z</t>
         </is>
       </c>
     </row>
@@ -16833,7 +16833,7 @@
       </c>
       <c r="S192" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T23:48:08Z</t>
+          <t>2026-10-14T23:20:56Z</t>
         </is>
       </c>
     </row>
@@ -16918,7 +16918,7 @@
       </c>
       <c r="S193" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T23:48:08Z</t>
+          <t>2026-10-14T23:20:56Z</t>
         </is>
       </c>
     </row>
@@ -17003,7 +17003,7 @@
       </c>
       <c r="S194" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T23:48:08Z</t>
+          <t>2026-10-14T23:20:56Z</t>
         </is>
       </c>
     </row>
@@ -17088,7 +17088,7 @@
       </c>
       <c r="S195" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T23:48:08Z</t>
+          <t>2026-10-14T23:20:56Z</t>
         </is>
       </c>
     </row>
@@ -17173,7 +17173,7 @@
       </c>
       <c r="S196" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T23:48:08Z</t>
+          <t>2026-10-14T23:20:56Z</t>
         </is>
       </c>
     </row>
@@ -17258,7 +17258,7 @@
       </c>
       <c r="S197" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T23:48:08Z</t>
+          <t>2026-10-14T23:20:56Z</t>
         </is>
       </c>
     </row>
@@ -17343,7 +17343,7 @@
       </c>
       <c r="S198" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T23:48:08Z</t>
+          <t>2026-10-14T23:20:56Z</t>
         </is>
       </c>
     </row>
@@ -17428,7 +17428,7 @@
       </c>
       <c r="S199" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T23:48:08Z</t>
+          <t>2026-10-14T23:20:56Z</t>
         </is>
       </c>
     </row>
@@ -17513,7 +17513,7 @@
       </c>
       <c r="S200" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T23:48:08Z</t>
+          <t>2026-10-14T23:20:56Z</t>
         </is>
       </c>
     </row>
@@ -17598,7 +17598,7 @@
       </c>
       <c r="S201" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T23:48:08Z</t>
+          <t>2026-10-14T23:20:56Z</t>
         </is>
       </c>
     </row>
@@ -17683,7 +17683,7 @@
       </c>
       <c r="S202" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T23:48:08Z</t>
+          <t>2026-10-14T23:20:56Z</t>
         </is>
       </c>
     </row>
@@ -17768,7 +17768,7 @@
       </c>
       <c r="S203" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T23:48:08Z</t>
+          <t>2026-10-14T23:20:56Z</t>
         </is>
       </c>
     </row>
@@ -17853,7 +17853,7 @@
       </c>
       <c r="S204" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T23:48:08Z</t>
+          <t>2026-10-14T23:20:56Z</t>
         </is>
       </c>
     </row>
@@ -17938,7 +17938,7 @@
       </c>
       <c r="S205" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T23:48:08Z</t>
+          <t>2026-10-14T23:20:56Z</t>
         </is>
       </c>
     </row>
@@ -18023,7 +18023,7 @@
       </c>
       <c r="S206" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T23:48:08Z</t>
+          <t>2026-10-14T23:20:56Z</t>
         </is>
       </c>
     </row>
@@ -18108,7 +18108,7 @@
       </c>
       <c r="S207" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T23:48:08Z</t>
+          <t>2026-10-14T23:20:56Z</t>
         </is>
       </c>
     </row>
@@ -18193,7 +18193,7 @@
       </c>
       <c r="S208" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T23:48:08Z</t>
+          <t>2026-10-14T23:20:56Z</t>
         </is>
       </c>
     </row>
@@ -18278,7 +18278,7 @@
       </c>
       <c r="S209" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T23:48:08Z</t>
+          <t>2026-10-14T23:20:56Z</t>
         </is>
       </c>
     </row>
@@ -18363,7 +18363,7 @@
       </c>
       <c r="S210" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T23:48:08Z</t>
+          <t>2026-10-14T23:20:56Z</t>
         </is>
       </c>
     </row>
@@ -18452,7 +18452,7 @@
       </c>
       <c r="S211" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T23:48:08Z</t>
+          <t>2026-10-14T23:20:56Z</t>
         </is>
       </c>
     </row>
@@ -18541,7 +18541,7 @@
       </c>
       <c r="S212" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T23:48:08Z</t>
+          <t>2026-10-14T23:20:56Z</t>
         </is>
       </c>
     </row>
@@ -18626,7 +18626,7 @@
       </c>
       <c r="S213" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T23:48:08Z</t>
+          <t>2026-10-14T23:20:56Z</t>
         </is>
       </c>
     </row>
@@ -18715,7 +18715,7 @@
       </c>
       <c r="S214" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T23:48:08Z</t>
+          <t>2026-10-14T23:20:56Z</t>
         </is>
       </c>
     </row>
@@ -18804,7 +18804,7 @@
       </c>
       <c r="S215" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T23:48:08Z</t>
+          <t>2026-10-14T23:20:56Z</t>
         </is>
       </c>
     </row>
@@ -18889,7 +18889,7 @@
       </c>
       <c r="S216" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T23:48:08Z</t>
+          <t>2026-10-14T23:20:56Z</t>
         </is>
       </c>
     </row>
@@ -18978,7 +18978,7 @@
       </c>
       <c r="S217" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T23:48:08Z</t>
+          <t>2026-10-14T23:20:56Z</t>
         </is>
       </c>
     </row>
@@ -19067,7 +19067,7 @@
       </c>
       <c r="S218" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T23:48:08Z</t>
+          <t>2026-10-14T23:20:56Z</t>
         </is>
       </c>
     </row>
@@ -19152,7 +19152,7 @@
       </c>
       <c r="S219" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T23:48:08Z</t>
+          <t>2026-10-14T23:20:56Z</t>
         </is>
       </c>
     </row>
@@ -19241,7 +19241,7 @@
       </c>
       <c r="S220" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T23:48:08Z</t>
+          <t>2026-10-14T23:20:56Z</t>
         </is>
       </c>
     </row>
@@ -19330,7 +19330,7 @@
       </c>
       <c r="S221" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T23:48:08Z</t>
+          <t>2026-10-14T23:20:56Z</t>
         </is>
       </c>
     </row>
@@ -19415,7 +19415,7 @@
       </c>
       <c r="S222" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T23:48:08Z</t>
+          <t>2026-10-14T23:20:56Z</t>
         </is>
       </c>
     </row>
@@ -19504,7 +19504,7 @@
       </c>
       <c r="S223" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T23:48:08Z</t>
+          <t>2026-10-14T23:20:56Z</t>
         </is>
       </c>
     </row>
@@ -19593,7 +19593,7 @@
       </c>
       <c r="S224" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T23:48:08Z</t>
+          <t>2026-10-14T23:20:56Z</t>
         </is>
       </c>
     </row>
@@ -19678,7 +19678,7 @@
       </c>
       <c r="S225" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T23:48:08Z</t>
+          <t>2026-10-14T23:20:56Z</t>
         </is>
       </c>
     </row>
@@ -19767,7 +19767,7 @@
       </c>
       <c r="S226" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T23:48:08Z</t>
+          <t>2026-10-14T23:20:56Z</t>
         </is>
       </c>
     </row>
@@ -19856,7 +19856,7 @@
       </c>
       <c r="S227" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T23:48:08Z</t>
+          <t>2026-10-14T23:20:56Z</t>
         </is>
       </c>
     </row>
@@ -19941,7 +19941,7 @@
       </c>
       <c r="S228" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T23:48:08Z</t>
+          <t>2026-10-14T23:20:56Z</t>
         </is>
       </c>
     </row>
@@ -20030,7 +20030,7 @@
       </c>
       <c r="S229" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T23:48:08Z</t>
+          <t>2026-10-14T23:20:56Z</t>
         </is>
       </c>
     </row>
@@ -20119,7 +20119,7 @@
       </c>
       <c r="S230" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T23:48:08Z</t>
+          <t>2026-10-14T23:20:56Z</t>
         </is>
       </c>
     </row>
@@ -20204,7 +20204,7 @@
       </c>
       <c r="S231" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T23:48:08Z</t>
+          <t>2026-10-14T23:20:56Z</t>
         </is>
       </c>
     </row>
@@ -20293,7 +20293,7 @@
       </c>
       <c r="S232" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T23:48:08Z</t>
+          <t>2026-10-14T23:20:56Z</t>
         </is>
       </c>
     </row>
@@ -20382,7 +20382,7 @@
       </c>
       <c r="S233" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T23:48:08Z</t>
+          <t>2026-10-14T23:20:56Z</t>
         </is>
       </c>
     </row>
@@ -20467,7 +20467,7 @@
       </c>
       <c r="S234" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T23:48:08Z</t>
+          <t>2026-10-14T23:20:56Z</t>
         </is>
       </c>
     </row>
@@ -20556,7 +20556,7 @@
       </c>
       <c r="S235" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T23:48:08Z</t>
+          <t>2026-10-14T23:20:56Z</t>
         </is>
       </c>
     </row>
@@ -20645,7 +20645,7 @@
       </c>
       <c r="S236" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T23:48:08Z</t>
+          <t>2026-10-14T23:20:56Z</t>
         </is>
       </c>
     </row>
@@ -20730,7 +20730,7 @@
       </c>
       <c r="S237" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T23:48:08Z</t>
+          <t>2026-10-14T23:20:56Z</t>
         </is>
       </c>
     </row>
@@ -20819,7 +20819,7 @@
       </c>
       <c r="S238" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T23:48:08Z</t>
+          <t>2026-10-14T23:20:56Z</t>
         </is>
       </c>
     </row>
@@ -20908,7 +20908,7 @@
       </c>
       <c r="S239" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T23:48:08Z</t>
+          <t>2026-10-14T23:20:56Z</t>
         </is>
       </c>
     </row>
@@ -20997,7 +20997,7 @@
       </c>
       <c r="S240" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T23:48:08Z</t>
+          <t>2026-10-14T23:20:56Z</t>
         </is>
       </c>
     </row>
@@ -21086,7 +21086,7 @@
       </c>
       <c r="S241" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T23:48:08Z</t>
+          <t>2026-10-14T23:20:56Z</t>
         </is>
       </c>
     </row>
@@ -21175,7 +21175,7 @@
       </c>
       <c r="S242" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T23:48:08Z</t>
+          <t>2026-10-14T23:20:56Z</t>
         </is>
       </c>
     </row>
@@ -21264,7 +21264,7 @@
       </c>
       <c r="S243" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T23:48:08Z</t>
+          <t>2026-10-14T23:20:56Z</t>
         </is>
       </c>
     </row>
@@ -21353,7 +21353,7 @@
       </c>
       <c r="S244" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T23:48:08Z</t>
+          <t>2026-10-14T23:20:56Z</t>
         </is>
       </c>
     </row>
@@ -21442,7 +21442,7 @@
       </c>
       <c r="S245" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T23:48:08Z</t>
+          <t>2026-10-14T23:20:56Z</t>
         </is>
       </c>
     </row>
@@ -21531,7 +21531,7 @@
       </c>
       <c r="S246" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T23:48:08Z</t>
+          <t>2026-10-14T23:20:56Z</t>
         </is>
       </c>
     </row>
@@ -21620,7 +21620,7 @@
       </c>
       <c r="S247" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T23:48:08Z</t>
+          <t>2026-10-14T23:20:56Z</t>
         </is>
       </c>
     </row>
@@ -21709,7 +21709,7 @@
       </c>
       <c r="S248" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T23:48:08Z</t>
+          <t>2026-10-14T23:20:56Z</t>
         </is>
       </c>
     </row>
@@ -21798,7 +21798,7 @@
       </c>
       <c r="S249" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T23:48:08Z</t>
+          <t>2026-10-14T23:20:56Z</t>
         </is>
       </c>
     </row>
@@ -21887,7 +21887,7 @@
       </c>
       <c r="S250" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T23:48:08Z</t>
+          <t>2026-10-14T23:20:56Z</t>
         </is>
       </c>
     </row>
@@ -22019,7 +22019,7 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T23:48:08Z</t>
+          <t>2026-10-14T23:20:56Z</t>
         </is>
       </c>
     </row>
@@ -22099,7 +22099,7 @@
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>{"dataset_id": "bcv_pib_sector_institucional_anual", "title": "Producto interno bruto por sector institucional anual", "table": "Variaciones porcentuales", "source_file": "5_2_1_si_anual.xlsx", "base": "2007", "price_type": "Precios constantes", "measure": "Variación porcentual interanual", "frequency": "Anual", "period": "2025", "year": 2025, "quarter": null, "classification": "Sector institucional", "component": "Impuestos netos sobre los productos", "value": 10.600260421283764, "unit": "Porcentaje", "status": "Preliminar", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/cuentas_macroeconomicas/5_2_1_si_anual.xlsx", "fetched_at": "2026-10-13T23:48:08Z"}</t>
+          <t>{"dataset_id": "bcv_pib_sector_institucional_anual", "title": "Producto interno bruto por sector institucional anual", "table": "Variaciones porcentuales", "source_file": "5_2_1_si_anual.xlsx", "base": "2007", "price_type": "Precios constantes", "measure": "Variación porcentual interanual", "frequency": "Anual", "period": "2025", "year": 2025, "quarter": null, "classification": "Sector institucional", "component": "Impuestos netos sobre los productos", "value": 10.600260421283764, "unit": "Porcentaje", "status": "Preliminar", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/cuentas_macroeconomicas/5_2_1_si_anual.xlsx", "fetched_at": "2026-10-14T23:20:56Z"}</t>
         </is>
       </c>
     </row>

--- a/assets/data/bcv/excel/ove_bcv_pib_sector_institucional_anual.xlsx
+++ b/assets/data/bcv/excel/ove_bcv_pib_sector_institucional_anual.xlsx
@@ -736,7 +736,7 @@
       </c>
       <c r="S7" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14T23:20:56Z</t>
+          <t>2026-10-15T23:09:49Z</t>
         </is>
       </c>
     </row>
@@ -821,7 +821,7 @@
       </c>
       <c r="S8" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14T23:20:56Z</t>
+          <t>2026-10-15T23:09:49Z</t>
         </is>
       </c>
     </row>
@@ -906,7 +906,7 @@
       </c>
       <c r="S9" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14T23:20:56Z</t>
+          <t>2026-10-15T23:09:49Z</t>
         </is>
       </c>
     </row>
@@ -991,7 +991,7 @@
       </c>
       <c r="S10" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14T23:20:56Z</t>
+          <t>2026-10-15T23:09:49Z</t>
         </is>
       </c>
     </row>
@@ -1076,7 +1076,7 @@
       </c>
       <c r="S11" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14T23:20:56Z</t>
+          <t>2026-10-15T23:09:49Z</t>
         </is>
       </c>
     </row>
@@ -1161,7 +1161,7 @@
       </c>
       <c r="S12" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14T23:20:56Z</t>
+          <t>2026-10-15T23:09:49Z</t>
         </is>
       </c>
     </row>
@@ -1246,7 +1246,7 @@
       </c>
       <c r="S13" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14T23:20:56Z</t>
+          <t>2026-10-15T23:09:49Z</t>
         </is>
       </c>
     </row>
@@ -1331,7 +1331,7 @@
       </c>
       <c r="S14" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14T23:20:56Z</t>
+          <t>2026-10-15T23:09:49Z</t>
         </is>
       </c>
     </row>
@@ -1416,7 +1416,7 @@
       </c>
       <c r="S15" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14T23:20:56Z</t>
+          <t>2026-10-15T23:09:49Z</t>
         </is>
       </c>
     </row>
@@ -1501,7 +1501,7 @@
       </c>
       <c r="S16" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14T23:20:56Z</t>
+          <t>2026-10-15T23:09:49Z</t>
         </is>
       </c>
     </row>
@@ -1586,7 +1586,7 @@
       </c>
       <c r="S17" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14T23:20:56Z</t>
+          <t>2026-10-15T23:09:49Z</t>
         </is>
       </c>
     </row>
@@ -1671,7 +1671,7 @@
       </c>
       <c r="S18" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14T23:20:56Z</t>
+          <t>2026-10-15T23:09:49Z</t>
         </is>
       </c>
     </row>
@@ -1756,7 +1756,7 @@
       </c>
       <c r="S19" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14T23:20:56Z</t>
+          <t>2026-10-15T23:09:49Z</t>
         </is>
       </c>
     </row>
@@ -1841,7 +1841,7 @@
       </c>
       <c r="S20" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14T23:20:56Z</t>
+          <t>2026-10-15T23:09:49Z</t>
         </is>
       </c>
     </row>
@@ -1926,7 +1926,7 @@
       </c>
       <c r="S21" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14T23:20:56Z</t>
+          <t>2026-10-15T23:09:49Z</t>
         </is>
       </c>
     </row>
@@ -2011,7 +2011,7 @@
       </c>
       <c r="S22" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14T23:20:56Z</t>
+          <t>2026-10-15T23:09:49Z</t>
         </is>
       </c>
     </row>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="S23" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14T23:20:56Z</t>
+          <t>2026-10-15T23:09:49Z</t>
         </is>
       </c>
     </row>
@@ -2181,7 +2181,7 @@
       </c>
       <c r="S24" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14T23:20:56Z</t>
+          <t>2026-10-15T23:09:49Z</t>
         </is>
       </c>
     </row>
@@ -2266,7 +2266,7 @@
       </c>
       <c r="S25" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14T23:20:56Z</t>
+          <t>2026-10-15T23:09:49Z</t>
         </is>
       </c>
     </row>
@@ -2351,7 +2351,7 @@
       </c>
       <c r="S26" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14T23:20:56Z</t>
+          <t>2026-10-15T23:09:49Z</t>
         </is>
       </c>
     </row>
@@ -2436,7 +2436,7 @@
       </c>
       <c r="S27" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14T23:20:56Z</t>
+          <t>2026-10-15T23:09:49Z</t>
         </is>
       </c>
     </row>
@@ -2525,7 +2525,7 @@
       </c>
       <c r="S28" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14T23:20:56Z</t>
+          <t>2026-10-15T23:09:49Z</t>
         </is>
       </c>
     </row>
@@ -2614,7 +2614,7 @@
       </c>
       <c r="S29" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14T23:20:56Z</t>
+          <t>2026-10-15T23:09:49Z</t>
         </is>
       </c>
     </row>
@@ -2699,7 +2699,7 @@
       </c>
       <c r="S30" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14T23:20:56Z</t>
+          <t>2026-10-15T23:09:49Z</t>
         </is>
       </c>
     </row>
@@ -2788,7 +2788,7 @@
       </c>
       <c r="S31" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14T23:20:56Z</t>
+          <t>2026-10-15T23:09:49Z</t>
         </is>
       </c>
     </row>
@@ -2877,7 +2877,7 @@
       </c>
       <c r="S32" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14T23:20:56Z</t>
+          <t>2026-10-15T23:09:49Z</t>
         </is>
       </c>
     </row>
@@ -2962,7 +2962,7 @@
       </c>
       <c r="S33" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14T23:20:56Z</t>
+          <t>2026-10-15T23:09:49Z</t>
         </is>
       </c>
     </row>
@@ -3051,7 +3051,7 @@
       </c>
       <c r="S34" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14T23:20:56Z</t>
+          <t>2026-10-15T23:09:49Z</t>
         </is>
       </c>
     </row>
@@ -3140,7 +3140,7 @@
       </c>
       <c r="S35" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14T23:20:56Z</t>
+          <t>2026-10-15T23:09:49Z</t>
         </is>
       </c>
     </row>
@@ -3225,7 +3225,7 @@
       </c>
       <c r="S36" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14T23:20:56Z</t>
+          <t>2026-10-15T23:09:49Z</t>
         </is>
       </c>
     </row>
@@ -3314,7 +3314,7 @@
       </c>
       <c r="S37" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14T23:20:56Z</t>
+          <t>2026-10-15T23:09:49Z</t>
         </is>
       </c>
     </row>
@@ -3403,7 +3403,7 @@
       </c>
       <c r="S38" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14T23:20:56Z</t>
+          <t>2026-10-15T23:09:49Z</t>
         </is>
       </c>
     </row>
@@ -3488,7 +3488,7 @@
       </c>
       <c r="S39" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14T23:20:56Z</t>
+          <t>2026-10-15T23:09:49Z</t>
         </is>
       </c>
     </row>
@@ -3577,7 +3577,7 @@
       </c>
       <c r="S40" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14T23:20:56Z</t>
+          <t>2026-10-15T23:09:49Z</t>
         </is>
       </c>
     </row>
@@ -3666,7 +3666,7 @@
       </c>
       <c r="S41" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14T23:20:56Z</t>
+          <t>2026-10-15T23:09:49Z</t>
         </is>
       </c>
     </row>
@@ -3751,7 +3751,7 @@
       </c>
       <c r="S42" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14T23:20:56Z</t>
+          <t>2026-10-15T23:09:49Z</t>
         </is>
       </c>
     </row>
@@ -3840,7 +3840,7 @@
       </c>
       <c r="S43" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14T23:20:56Z</t>
+          <t>2026-10-15T23:09:49Z</t>
         </is>
       </c>
     </row>
@@ -3929,7 +3929,7 @@
       </c>
       <c r="S44" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14T23:20:56Z</t>
+          <t>2026-10-15T23:09:49Z</t>
         </is>
       </c>
     </row>
@@ -4014,7 +4014,7 @@
       </c>
       <c r="S45" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14T23:20:56Z</t>
+          <t>2026-10-15T23:09:49Z</t>
         </is>
       </c>
     </row>
@@ -4103,7 +4103,7 @@
       </c>
       <c r="S46" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14T23:20:56Z</t>
+          <t>2026-10-15T23:09:49Z</t>
         </is>
       </c>
     </row>
@@ -4192,7 +4192,7 @@
       </c>
       <c r="S47" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14T23:20:56Z</t>
+          <t>2026-10-15T23:09:49Z</t>
         </is>
       </c>
     </row>
@@ -4277,7 +4277,7 @@
       </c>
       <c r="S48" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14T23:20:56Z</t>
+          <t>2026-10-15T23:09:49Z</t>
         </is>
       </c>
     </row>
@@ -4366,7 +4366,7 @@
       </c>
       <c r="S49" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14T23:20:56Z</t>
+          <t>2026-10-15T23:09:49Z</t>
         </is>
       </c>
     </row>
@@ -4455,7 +4455,7 @@
       </c>
       <c r="S50" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14T23:20:56Z</t>
+          <t>2026-10-15T23:09:49Z</t>
         </is>
       </c>
     </row>
@@ -4540,7 +4540,7 @@
       </c>
       <c r="S51" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14T23:20:56Z</t>
+          <t>2026-10-15T23:09:49Z</t>
         </is>
       </c>
     </row>
@@ -4629,7 +4629,7 @@
       </c>
       <c r="S52" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14T23:20:56Z</t>
+          <t>2026-10-15T23:09:49Z</t>
         </is>
       </c>
     </row>
@@ -4718,7 +4718,7 @@
       </c>
       <c r="S53" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14T23:20:56Z</t>
+          <t>2026-10-15T23:09:49Z</t>
         </is>
       </c>
     </row>
@@ -4803,7 +4803,7 @@
       </c>
       <c r="S54" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14T23:20:56Z</t>
+          <t>2026-10-15T23:09:49Z</t>
         </is>
       </c>
     </row>
@@ -4892,7 +4892,7 @@
       </c>
       <c r="S55" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14T23:20:56Z</t>
+          <t>2026-10-15T23:09:49Z</t>
         </is>
       </c>
     </row>
@@ -4981,7 +4981,7 @@
       </c>
       <c r="S56" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14T23:20:56Z</t>
+          <t>2026-10-15T23:09:49Z</t>
         </is>
       </c>
     </row>
@@ -5070,7 +5070,7 @@
       </c>
       <c r="S57" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14T23:20:56Z</t>
+          <t>2026-10-15T23:09:49Z</t>
         </is>
       </c>
     </row>
@@ -5159,7 +5159,7 @@
       </c>
       <c r="S58" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14T23:20:56Z</t>
+          <t>2026-10-15T23:09:49Z</t>
         </is>
       </c>
     </row>
@@ -5248,7 +5248,7 @@
       </c>
       <c r="S59" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14T23:20:56Z</t>
+          <t>2026-10-15T23:09:49Z</t>
         </is>
       </c>
     </row>
@@ -5337,7 +5337,7 @@
       </c>
       <c r="S60" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14T23:20:56Z</t>
+          <t>2026-10-15T23:09:49Z</t>
         </is>
       </c>
     </row>
@@ -5426,7 +5426,7 @@
       </c>
       <c r="S61" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14T23:20:56Z</t>
+          <t>2026-10-15T23:09:49Z</t>
         </is>
       </c>
     </row>
@@ -5515,7 +5515,7 @@
       </c>
       <c r="S62" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14T23:20:56Z</t>
+          <t>2026-10-15T23:09:49Z</t>
         </is>
       </c>
     </row>
@@ -5604,7 +5604,7 @@
       </c>
       <c r="S63" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14T23:20:56Z</t>
+          <t>2026-10-15T23:09:49Z</t>
         </is>
       </c>
     </row>
@@ -5693,7 +5693,7 @@
       </c>
       <c r="S64" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14T23:20:56Z</t>
+          <t>2026-10-15T23:09:49Z</t>
         </is>
       </c>
     </row>
@@ -5782,7 +5782,7 @@
       </c>
       <c r="S65" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14T23:20:56Z</t>
+          <t>2026-10-15T23:09:49Z</t>
         </is>
       </c>
     </row>
@@ -5871,7 +5871,7 @@
       </c>
       <c r="S66" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14T23:20:56Z</t>
+          <t>2026-10-15T23:09:49Z</t>
         </is>
       </c>
     </row>
@@ -5960,7 +5960,7 @@
       </c>
       <c r="S67" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14T23:20:56Z</t>
+          <t>2026-10-15T23:09:49Z</t>
         </is>
       </c>
     </row>
@@ -6045,7 +6045,7 @@
       </c>
       <c r="S68" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14T23:20:56Z</t>
+          <t>2026-10-15T23:09:49Z</t>
         </is>
       </c>
     </row>
@@ -6130,7 +6130,7 @@
       </c>
       <c r="S69" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14T23:20:56Z</t>
+          <t>2026-10-15T23:09:49Z</t>
         </is>
       </c>
     </row>
@@ -6215,7 +6215,7 @@
       </c>
       <c r="S70" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14T23:20:56Z</t>
+          <t>2026-10-15T23:09:49Z</t>
         </is>
       </c>
     </row>
@@ -6300,7 +6300,7 @@
       </c>
       <c r="S71" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14T23:20:56Z</t>
+          <t>2026-10-15T23:09:49Z</t>
         </is>
       </c>
     </row>
@@ -6385,7 +6385,7 @@
       </c>
       <c r="S72" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14T23:20:56Z</t>
+          <t>2026-10-15T23:09:49Z</t>
         </is>
       </c>
     </row>
@@ -6470,7 +6470,7 @@
       </c>
       <c r="S73" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14T23:20:56Z</t>
+          <t>2026-10-15T23:09:49Z</t>
         </is>
       </c>
     </row>
@@ -6555,7 +6555,7 @@
       </c>
       <c r="S74" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14T23:20:56Z</t>
+          <t>2026-10-15T23:09:49Z</t>
         </is>
       </c>
     </row>
@@ -6640,7 +6640,7 @@
       </c>
       <c r="S75" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14T23:20:56Z</t>
+          <t>2026-10-15T23:09:49Z</t>
         </is>
       </c>
     </row>
@@ -6725,7 +6725,7 @@
       </c>
       <c r="S76" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14T23:20:56Z</t>
+          <t>2026-10-15T23:09:49Z</t>
         </is>
       </c>
     </row>
@@ -6810,7 +6810,7 @@
       </c>
       <c r="S77" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14T23:20:56Z</t>
+          <t>2026-10-15T23:09:49Z</t>
         </is>
       </c>
     </row>
@@ -6895,7 +6895,7 @@
       </c>
       <c r="S78" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14T23:20:56Z</t>
+          <t>2026-10-15T23:09:49Z</t>
         </is>
       </c>
     </row>
@@ -6980,7 +6980,7 @@
       </c>
       <c r="S79" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14T23:20:56Z</t>
+          <t>2026-10-15T23:09:49Z</t>
         </is>
       </c>
     </row>
@@ -7065,7 +7065,7 @@
       </c>
       <c r="S80" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14T23:20:56Z</t>
+          <t>2026-10-15T23:09:49Z</t>
         </is>
       </c>
     </row>
@@ -7150,7 +7150,7 @@
       </c>
       <c r="S81" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14T23:20:56Z</t>
+          <t>2026-10-15T23:09:49Z</t>
         </is>
       </c>
     </row>
@@ -7235,7 +7235,7 @@
       </c>
       <c r="S82" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14T23:20:56Z</t>
+          <t>2026-10-15T23:09:49Z</t>
         </is>
       </c>
     </row>
@@ -7320,7 +7320,7 @@
       </c>
       <c r="S83" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14T23:20:56Z</t>
+          <t>2026-10-15T23:09:49Z</t>
         </is>
       </c>
     </row>
@@ -7405,7 +7405,7 @@
       </c>
       <c r="S84" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14T23:20:56Z</t>
+          <t>2026-10-15T23:09:49Z</t>
         </is>
       </c>
     </row>
@@ -7490,7 +7490,7 @@
       </c>
       <c r="S85" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14T23:20:56Z</t>
+          <t>2026-10-15T23:09:49Z</t>
         </is>
       </c>
     </row>
@@ -7575,7 +7575,7 @@
       </c>
       <c r="S86" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14T23:20:56Z</t>
+          <t>2026-10-15T23:09:49Z</t>
         </is>
       </c>
     </row>
@@ -7660,7 +7660,7 @@
       </c>
       <c r="S87" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14T23:20:56Z</t>
+          <t>2026-10-15T23:09:49Z</t>
         </is>
       </c>
     </row>
@@ -7745,7 +7745,7 @@
       </c>
       <c r="S88" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14T23:20:56Z</t>
+          <t>2026-10-15T23:09:49Z</t>
         </is>
       </c>
     </row>
@@ -7834,7 +7834,7 @@
       </c>
       <c r="S89" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14T23:20:56Z</t>
+          <t>2026-10-15T23:09:49Z</t>
         </is>
       </c>
     </row>
@@ -7923,7 +7923,7 @@
       </c>
       <c r="S90" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14T23:20:56Z</t>
+          <t>2026-10-15T23:09:49Z</t>
         </is>
       </c>
     </row>
@@ -8008,7 +8008,7 @@
       </c>
       <c r="S91" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14T23:20:56Z</t>
+          <t>2026-10-15T23:09:49Z</t>
         </is>
       </c>
     </row>
@@ -8097,7 +8097,7 @@
       </c>
       <c r="S92" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14T23:20:56Z</t>
+          <t>2026-10-15T23:09:49Z</t>
         </is>
       </c>
     </row>
@@ -8186,7 +8186,7 @@
       </c>
       <c r="S93" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14T23:20:56Z</t>
+          <t>2026-10-15T23:09:49Z</t>
         </is>
       </c>
     </row>
@@ -8271,7 +8271,7 @@
       </c>
       <c r="S94" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14T23:20:56Z</t>
+          <t>2026-10-15T23:09:49Z</t>
         </is>
       </c>
     </row>
@@ -8360,7 +8360,7 @@
       </c>
       <c r="S95" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14T23:20:56Z</t>
+          <t>2026-10-15T23:09:49Z</t>
         </is>
       </c>
     </row>
@@ -8449,7 +8449,7 @@
       </c>
       <c r="S96" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14T23:20:56Z</t>
+          <t>2026-10-15T23:09:49Z</t>
         </is>
       </c>
     </row>
@@ -8534,7 +8534,7 @@
       </c>
       <c r="S97" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14T23:20:56Z</t>
+          <t>2026-10-15T23:09:49Z</t>
         </is>
       </c>
     </row>
@@ -8623,7 +8623,7 @@
       </c>
       <c r="S98" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14T23:20:56Z</t>
+          <t>2026-10-15T23:09:49Z</t>
         </is>
       </c>
     </row>
@@ -8712,7 +8712,7 @@
       </c>
       <c r="S99" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14T23:20:56Z</t>
+          <t>2026-10-15T23:09:49Z</t>
         </is>
       </c>
     </row>
@@ -8797,7 +8797,7 @@
       </c>
       <c r="S100" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14T23:20:56Z</t>
+          <t>2026-10-15T23:09:49Z</t>
         </is>
       </c>
     </row>
@@ -8886,7 +8886,7 @@
       </c>
       <c r="S101" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14T23:20:56Z</t>
+          <t>2026-10-15T23:09:49Z</t>
         </is>
       </c>
     </row>
@@ -8975,7 +8975,7 @@
       </c>
       <c r="S102" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14T23:20:56Z</t>
+          <t>2026-10-15T23:09:49Z</t>
         </is>
       </c>
     </row>
@@ -9060,7 +9060,7 @@
       </c>
       <c r="S103" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14T23:20:56Z</t>
+          <t>2026-10-15T23:09:49Z</t>
         </is>
       </c>
     </row>
@@ -9149,7 +9149,7 @@
       </c>
       <c r="S104" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14T23:20:56Z</t>
+          <t>2026-10-15T23:09:49Z</t>
         </is>
       </c>
     </row>
@@ -9238,7 +9238,7 @@
       </c>
       <c r="S105" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14T23:20:56Z</t>
+          <t>2026-10-15T23:09:49Z</t>
         </is>
       </c>
     </row>
@@ -9323,7 +9323,7 @@
       </c>
       <c r="S106" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14T23:20:56Z</t>
+          <t>2026-10-15T23:09:49Z</t>
         </is>
       </c>
     </row>
@@ -9412,7 +9412,7 @@
       </c>
       <c r="S107" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14T23:20:56Z</t>
+          <t>2026-10-15T23:09:49Z</t>
         </is>
       </c>
     </row>
@@ -9501,7 +9501,7 @@
       </c>
       <c r="S108" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14T23:20:56Z</t>
+          <t>2026-10-15T23:09:49Z</t>
         </is>
       </c>
     </row>
@@ -9586,7 +9586,7 @@
       </c>
       <c r="S109" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14T23:20:56Z</t>
+          <t>2026-10-15T23:09:49Z</t>
         </is>
       </c>
     </row>
@@ -9675,7 +9675,7 @@
       </c>
       <c r="S110" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14T23:20:56Z</t>
+          <t>2026-10-15T23:09:49Z</t>
         </is>
       </c>
     </row>
@@ -9764,7 +9764,7 @@
       </c>
       <c r="S111" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14T23:20:56Z</t>
+          <t>2026-10-15T23:09:49Z</t>
         </is>
       </c>
     </row>
@@ -9849,7 +9849,7 @@
       </c>
       <c r="S112" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14T23:20:56Z</t>
+          <t>2026-10-15T23:09:49Z</t>
         </is>
       </c>
     </row>
@@ -9938,7 +9938,7 @@
       </c>
       <c r="S113" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14T23:20:56Z</t>
+          <t>2026-10-15T23:09:49Z</t>
         </is>
       </c>
     </row>
@@ -10027,7 +10027,7 @@
       </c>
       <c r="S114" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14T23:20:56Z</t>
+          <t>2026-10-15T23:09:49Z</t>
         </is>
       </c>
     </row>
@@ -10112,7 +10112,7 @@
       </c>
       <c r="S115" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14T23:20:56Z</t>
+          <t>2026-10-15T23:09:49Z</t>
         </is>
       </c>
     </row>
@@ -10201,7 +10201,7 @@
       </c>
       <c r="S116" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14T23:20:56Z</t>
+          <t>2026-10-15T23:09:49Z</t>
         </is>
       </c>
     </row>
@@ -10290,7 +10290,7 @@
       </c>
       <c r="S117" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14T23:20:56Z</t>
+          <t>2026-10-15T23:09:49Z</t>
         </is>
       </c>
     </row>
@@ -10379,7 +10379,7 @@
       </c>
       <c r="S118" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14T23:20:56Z</t>
+          <t>2026-10-15T23:09:49Z</t>
         </is>
       </c>
     </row>
@@ -10468,7 +10468,7 @@
       </c>
       <c r="S119" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14T23:20:56Z</t>
+          <t>2026-10-15T23:09:49Z</t>
         </is>
       </c>
     </row>
@@ -10557,7 +10557,7 @@
       </c>
       <c r="S120" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14T23:20:56Z</t>
+          <t>2026-10-15T23:09:49Z</t>
         </is>
       </c>
     </row>
@@ -10646,7 +10646,7 @@
       </c>
       <c r="S121" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14T23:20:56Z</t>
+          <t>2026-10-15T23:09:49Z</t>
         </is>
       </c>
     </row>
@@ -10735,7 +10735,7 @@
       </c>
       <c r="S122" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14T23:20:56Z</t>
+          <t>2026-10-15T23:09:49Z</t>
         </is>
       </c>
     </row>
@@ -10824,7 +10824,7 @@
       </c>
       <c r="S123" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14T23:20:56Z</t>
+          <t>2026-10-15T23:09:49Z</t>
         </is>
       </c>
     </row>
@@ -10913,7 +10913,7 @@
       </c>
       <c r="S124" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14T23:20:56Z</t>
+          <t>2026-10-15T23:09:49Z</t>
         </is>
       </c>
     </row>
@@ -11002,7 +11002,7 @@
       </c>
       <c r="S125" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14T23:20:56Z</t>
+          <t>2026-10-15T23:09:49Z</t>
         </is>
       </c>
     </row>
@@ -11091,7 +11091,7 @@
       </c>
       <c r="S126" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14T23:20:56Z</t>
+          <t>2026-10-15T23:09:49Z</t>
         </is>
       </c>
     </row>
@@ -11180,7 +11180,7 @@
       </c>
       <c r="S127" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14T23:20:56Z</t>
+          <t>2026-10-15T23:09:49Z</t>
         </is>
       </c>
     </row>
@@ -11269,7 +11269,7 @@
       </c>
       <c r="S128" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14T23:20:56Z</t>
+          <t>2026-10-15T23:09:49Z</t>
         </is>
       </c>
     </row>
@@ -11354,7 +11354,7 @@
       </c>
       <c r="S129" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14T23:20:56Z</t>
+          <t>2026-10-15T23:09:49Z</t>
         </is>
       </c>
     </row>
@@ -11439,7 +11439,7 @@
       </c>
       <c r="S130" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14T23:20:56Z</t>
+          <t>2026-10-15T23:09:49Z</t>
         </is>
       </c>
     </row>
@@ -11524,7 +11524,7 @@
       </c>
       <c r="S131" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14T23:20:56Z</t>
+          <t>2026-10-15T23:09:49Z</t>
         </is>
       </c>
     </row>
@@ -11609,7 +11609,7 @@
       </c>
       <c r="S132" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14T23:20:56Z</t>
+          <t>2026-10-15T23:09:49Z</t>
         </is>
       </c>
     </row>
@@ -11694,7 +11694,7 @@
       </c>
       <c r="S133" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14T23:20:56Z</t>
+          <t>2026-10-15T23:09:49Z</t>
         </is>
       </c>
     </row>
@@ -11779,7 +11779,7 @@
       </c>
       <c r="S134" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14T23:20:56Z</t>
+          <t>2026-10-15T23:09:49Z</t>
         </is>
       </c>
     </row>
@@ -11864,7 +11864,7 @@
       </c>
       <c r="S135" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14T23:20:56Z</t>
+          <t>2026-10-15T23:09:49Z</t>
         </is>
       </c>
     </row>
@@ -11949,7 +11949,7 @@
       </c>
       <c r="S136" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14T23:20:56Z</t>
+          <t>2026-10-15T23:09:49Z</t>
         </is>
       </c>
     </row>
@@ -12034,7 +12034,7 @@
       </c>
       <c r="S137" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14T23:20:56Z</t>
+          <t>2026-10-15T23:09:49Z</t>
         </is>
       </c>
     </row>
@@ -12119,7 +12119,7 @@
       </c>
       <c r="S138" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14T23:20:56Z</t>
+          <t>2026-10-15T23:09:49Z</t>
         </is>
       </c>
     </row>
@@ -12204,7 +12204,7 @@
       </c>
       <c r="S139" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14T23:20:56Z</t>
+          <t>2026-10-15T23:09:49Z</t>
         </is>
       </c>
     </row>
@@ -12289,7 +12289,7 @@
       </c>
       <c r="S140" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14T23:20:56Z</t>
+          <t>2026-10-15T23:09:49Z</t>
         </is>
       </c>
     </row>
@@ -12374,7 +12374,7 @@
       </c>
       <c r="S141" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14T23:20:56Z</t>
+          <t>2026-10-15T23:09:49Z</t>
         </is>
       </c>
     </row>
@@ -12459,7 +12459,7 @@
       </c>
       <c r="S142" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14T23:20:56Z</t>
+          <t>2026-10-15T23:09:49Z</t>
         </is>
       </c>
     </row>
@@ -12544,7 +12544,7 @@
       </c>
       <c r="S143" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14T23:20:56Z</t>
+          <t>2026-10-15T23:09:49Z</t>
         </is>
       </c>
     </row>
@@ -12629,7 +12629,7 @@
       </c>
       <c r="S144" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14T23:20:56Z</t>
+          <t>2026-10-15T23:09:49Z</t>
         </is>
       </c>
     </row>
@@ -12714,7 +12714,7 @@
       </c>
       <c r="S145" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14T23:20:56Z</t>
+          <t>2026-10-15T23:09:49Z</t>
         </is>
       </c>
     </row>
@@ -12799,7 +12799,7 @@
       </c>
       <c r="S146" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14T23:20:56Z</t>
+          <t>2026-10-15T23:09:49Z</t>
         </is>
       </c>
     </row>
@@ -12884,7 +12884,7 @@
       </c>
       <c r="S147" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14T23:20:56Z</t>
+          <t>2026-10-15T23:09:49Z</t>
         </is>
       </c>
     </row>
@@ -12969,7 +12969,7 @@
       </c>
       <c r="S148" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14T23:20:56Z</t>
+          <t>2026-10-15T23:09:49Z</t>
         </is>
       </c>
     </row>
@@ -13054,7 +13054,7 @@
       </c>
       <c r="S149" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14T23:20:56Z</t>
+          <t>2026-10-15T23:09:49Z</t>
         </is>
       </c>
     </row>
@@ -13143,7 +13143,7 @@
       </c>
       <c r="S150" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14T23:20:56Z</t>
+          <t>2026-10-15T23:09:49Z</t>
         </is>
       </c>
     </row>
@@ -13232,7 +13232,7 @@
       </c>
       <c r="S151" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14T23:20:56Z</t>
+          <t>2026-10-15T23:09:49Z</t>
         </is>
       </c>
     </row>
@@ -13317,7 +13317,7 @@
       </c>
       <c r="S152" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14T23:20:56Z</t>
+          <t>2026-10-15T23:09:49Z</t>
         </is>
       </c>
     </row>
@@ -13406,7 +13406,7 @@
       </c>
       <c r="S153" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14T23:20:56Z</t>
+          <t>2026-10-15T23:09:49Z</t>
         </is>
       </c>
     </row>
@@ -13495,7 +13495,7 @@
       </c>
       <c r="S154" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14T23:20:56Z</t>
+          <t>2026-10-15T23:09:49Z</t>
         </is>
       </c>
     </row>
@@ -13580,7 +13580,7 @@
       </c>
       <c r="S155" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14T23:20:56Z</t>
+          <t>2026-10-15T23:09:49Z</t>
         </is>
       </c>
     </row>
@@ -13669,7 +13669,7 @@
       </c>
       <c r="S156" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14T23:20:56Z</t>
+          <t>2026-10-15T23:09:49Z</t>
         </is>
       </c>
     </row>
@@ -13758,7 +13758,7 @@
       </c>
       <c r="S157" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14T23:20:56Z</t>
+          <t>2026-10-15T23:09:49Z</t>
         </is>
       </c>
     </row>
@@ -13843,7 +13843,7 @@
       </c>
       <c r="S158" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14T23:20:56Z</t>
+          <t>2026-10-15T23:09:49Z</t>
         </is>
       </c>
     </row>
@@ -13932,7 +13932,7 @@
       </c>
       <c r="S159" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14T23:20:56Z</t>
+          <t>2026-10-15T23:09:49Z</t>
         </is>
       </c>
     </row>
@@ -14021,7 +14021,7 @@
       </c>
       <c r="S160" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14T23:20:56Z</t>
+          <t>2026-10-15T23:09:49Z</t>
         </is>
       </c>
     </row>
@@ -14106,7 +14106,7 @@
       </c>
       <c r="S161" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14T23:20:56Z</t>
+          <t>2026-10-15T23:09:49Z</t>
         </is>
       </c>
     </row>
@@ -14195,7 +14195,7 @@
       </c>
       <c r="S162" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14T23:20:56Z</t>
+          <t>2026-10-15T23:09:49Z</t>
         </is>
       </c>
     </row>
@@ -14284,7 +14284,7 @@
       </c>
       <c r="S163" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14T23:20:56Z</t>
+          <t>2026-10-15T23:09:49Z</t>
         </is>
       </c>
     </row>
@@ -14369,7 +14369,7 @@
       </c>
       <c r="S164" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14T23:20:56Z</t>
+          <t>2026-10-15T23:09:49Z</t>
         </is>
       </c>
     </row>
@@ -14458,7 +14458,7 @@
       </c>
       <c r="S165" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14T23:20:56Z</t>
+          <t>2026-10-15T23:09:49Z</t>
         </is>
       </c>
     </row>
@@ -14547,7 +14547,7 @@
       </c>
       <c r="S166" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14T23:20:56Z</t>
+          <t>2026-10-15T23:09:49Z</t>
         </is>
       </c>
     </row>
@@ -14632,7 +14632,7 @@
       </c>
       <c r="S167" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14T23:20:56Z</t>
+          <t>2026-10-15T23:09:49Z</t>
         </is>
       </c>
     </row>
@@ -14721,7 +14721,7 @@
       </c>
       <c r="S168" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14T23:20:56Z</t>
+          <t>2026-10-15T23:09:49Z</t>
         </is>
       </c>
     </row>
@@ -14810,7 +14810,7 @@
       </c>
       <c r="S169" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14T23:20:56Z</t>
+          <t>2026-10-15T23:09:49Z</t>
         </is>
       </c>
     </row>
@@ -14895,7 +14895,7 @@
       </c>
       <c r="S170" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14T23:20:56Z</t>
+          <t>2026-10-15T23:09:49Z</t>
         </is>
       </c>
     </row>
@@ -14984,7 +14984,7 @@
       </c>
       <c r="S171" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14T23:20:56Z</t>
+          <t>2026-10-15T23:09:49Z</t>
         </is>
       </c>
     </row>
@@ -15073,7 +15073,7 @@
       </c>
       <c r="S172" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14T23:20:56Z</t>
+          <t>2026-10-15T23:09:49Z</t>
         </is>
       </c>
     </row>
@@ -15158,7 +15158,7 @@
       </c>
       <c r="S173" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14T23:20:56Z</t>
+          <t>2026-10-15T23:09:49Z</t>
         </is>
       </c>
     </row>
@@ -15247,7 +15247,7 @@
       </c>
       <c r="S174" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14T23:20:56Z</t>
+          <t>2026-10-15T23:09:49Z</t>
         </is>
       </c>
     </row>
@@ -15336,7 +15336,7 @@
       </c>
       <c r="S175" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14T23:20:56Z</t>
+          <t>2026-10-15T23:09:49Z</t>
         </is>
       </c>
     </row>
@@ -15421,7 +15421,7 @@
       </c>
       <c r="S176" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14T23:20:56Z</t>
+          <t>2026-10-15T23:09:49Z</t>
         </is>
       </c>
     </row>
@@ -15510,7 +15510,7 @@
       </c>
       <c r="S177" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14T23:20:56Z</t>
+          <t>2026-10-15T23:09:49Z</t>
         </is>
       </c>
     </row>
@@ -15599,7 +15599,7 @@
       </c>
       <c r="S178" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14T23:20:56Z</t>
+          <t>2026-10-15T23:09:49Z</t>
         </is>
       </c>
     </row>
@@ -15688,7 +15688,7 @@
       </c>
       <c r="S179" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14T23:20:56Z</t>
+          <t>2026-10-15T23:09:49Z</t>
         </is>
       </c>
     </row>
@@ -15777,7 +15777,7 @@
       </c>
       <c r="S180" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14T23:20:56Z</t>
+          <t>2026-10-15T23:09:49Z</t>
         </is>
       </c>
     </row>
@@ -15866,7 +15866,7 @@
       </c>
       <c r="S181" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14T23:20:56Z</t>
+          <t>2026-10-15T23:09:49Z</t>
         </is>
       </c>
     </row>
@@ -15955,7 +15955,7 @@
       </c>
       <c r="S182" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14T23:20:56Z</t>
+          <t>2026-10-15T23:09:49Z</t>
         </is>
       </c>
     </row>
@@ -16044,7 +16044,7 @@
       </c>
       <c r="S183" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14T23:20:56Z</t>
+          <t>2026-10-15T23:09:49Z</t>
         </is>
       </c>
     </row>
@@ -16133,7 +16133,7 @@
       </c>
       <c r="S184" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14T23:20:56Z</t>
+          <t>2026-10-15T23:09:49Z</t>
         </is>
       </c>
     </row>
@@ -16222,7 +16222,7 @@
       </c>
       <c r="S185" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14T23:20:56Z</t>
+          <t>2026-10-15T23:09:49Z</t>
         </is>
       </c>
     </row>
@@ -16311,7 +16311,7 @@
       </c>
       <c r="S186" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14T23:20:56Z</t>
+          <t>2026-10-15T23:09:49Z</t>
         </is>
       </c>
     </row>
@@ -16400,7 +16400,7 @@
       </c>
       <c r="S187" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14T23:20:56Z</t>
+          <t>2026-10-15T23:09:49Z</t>
         </is>
       </c>
     </row>
@@ -16489,7 +16489,7 @@
       </c>
       <c r="S188" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14T23:20:56Z</t>
+          <t>2026-10-15T23:09:49Z</t>
         </is>
       </c>
     </row>
@@ -16578,7 +16578,7 @@
       </c>
       <c r="S189" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14T23:20:56Z</t>
+          <t>2026-10-15T23:09:49Z</t>
         </is>
       </c>
     </row>
@@ -16663,7 +16663,7 @@
       </c>
       <c r="S190" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14T23:20:56Z</t>
+          <t>2026-10-15T23:09:49Z</t>
         </is>
       </c>
     </row>
@@ -16748,7 +16748,7 @@
       </c>
       <c r="S191" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14T23:20:56Z</t>
+          <t>2026-10-15T23:09:49Z</t>
         </is>
       </c>
     </row>
@@ -16833,7 +16833,7 @@
       </c>
       <c r="S192" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14T23:20:56Z</t>
+          <t>2026-10-15T23:09:49Z</t>
         </is>
       </c>
     </row>
@@ -16918,7 +16918,7 @@
       </c>
       <c r="S193" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14T23:20:56Z</t>
+          <t>2026-10-15T23:09:49Z</t>
         </is>
       </c>
     </row>
@@ -17003,7 +17003,7 @@
       </c>
       <c r="S194" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14T23:20:56Z</t>
+          <t>2026-10-15T23:09:49Z</t>
         </is>
       </c>
     </row>
@@ -17088,7 +17088,7 @@
       </c>
       <c r="S195" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14T23:20:56Z</t>
+          <t>2026-10-15T23:09:49Z</t>
         </is>
       </c>
     </row>
@@ -17173,7 +17173,7 @@
       </c>
       <c r="S196" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14T23:20:56Z</t>
+          <t>2026-10-15T23:09:49Z</t>
         </is>
       </c>
     </row>
@@ -17258,7 +17258,7 @@
       </c>
       <c r="S197" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14T23:20:56Z</t>
+          <t>2026-10-15T23:09:49Z</t>
         </is>
       </c>
     </row>
@@ -17343,7 +17343,7 @@
       </c>
       <c r="S198" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14T23:20:56Z</t>
+          <t>2026-10-15T23:09:49Z</t>
         </is>
       </c>
     </row>
@@ -17428,7 +17428,7 @@
       </c>
       <c r="S199" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14T23:20:56Z</t>
+          <t>2026-10-15T23:09:49Z</t>
         </is>
       </c>
     </row>
@@ -17513,7 +17513,7 @@
       </c>
       <c r="S200" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14T23:20:56Z</t>
+          <t>2026-10-15T23:09:49Z</t>
         </is>
       </c>
     </row>
@@ -17598,7 +17598,7 @@
       </c>
       <c r="S201" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14T23:20:56Z</t>
+          <t>2026-10-15T23:09:49Z</t>
         </is>
       </c>
     </row>
@@ -17683,7 +17683,7 @@
       </c>
       <c r="S202" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14T23:20:56Z</t>
+          <t>2026-10-15T23:09:49Z</t>
         </is>
       </c>
     </row>
@@ -17768,7 +17768,7 @@
       </c>
       <c r="S203" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14T23:20:56Z</t>
+          <t>2026-10-15T23:09:49Z</t>
         </is>
       </c>
     </row>
@@ -17853,7 +17853,7 @@
       </c>
       <c r="S204" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14T23:20:56Z</t>
+          <t>2026-10-15T23:09:49Z</t>
         </is>
       </c>
     </row>
@@ -17938,7 +17938,7 @@
       </c>
       <c r="S205" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14T23:20:56Z</t>
+          <t>2026-10-15T23:09:49Z</t>
         </is>
       </c>
     </row>
@@ -18023,7 +18023,7 @@
       </c>
       <c r="S206" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14T23:20:56Z</t>
+          <t>2026-10-15T23:09:49Z</t>
         </is>
       </c>
     </row>
@@ -18108,7 +18108,7 @@
       </c>
       <c r="S207" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14T23:20:56Z</t>
+          <t>2026-10-15T23:09:49Z</t>
         </is>
       </c>
     </row>
@@ -18193,7 +18193,7 @@
       </c>
       <c r="S208" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14T23:20:56Z</t>
+          <t>2026-10-15T23:09:49Z</t>
         </is>
       </c>
     </row>
@@ -18278,7 +18278,7 @@
       </c>
       <c r="S209" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14T23:20:56Z</t>
+          <t>2026-10-15T23:09:49Z</t>
         </is>
       </c>
     </row>
@@ -18363,7 +18363,7 @@
       </c>
       <c r="S210" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14T23:20:56Z</t>
+          <t>2026-10-15T23:09:49Z</t>
         </is>
       </c>
     </row>
@@ -18452,7 +18452,7 @@
       </c>
       <c r="S211" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14T23:20:56Z</t>
+          <t>2026-10-15T23:09:49Z</t>
         </is>
       </c>
     </row>
@@ -18541,7 +18541,7 @@
       </c>
       <c r="S212" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14T23:20:56Z</t>
+          <t>2026-10-15T23:09:49Z</t>
         </is>
       </c>
     </row>
@@ -18626,7 +18626,7 @@
       </c>
       <c r="S213" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14T23:20:56Z</t>
+          <t>2026-10-15T23:09:49Z</t>
         </is>
       </c>
     </row>
@@ -18715,7 +18715,7 @@
       </c>
       <c r="S214" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14T23:20:56Z</t>
+          <t>2026-10-15T23:09:49Z</t>
         </is>
       </c>
     </row>
@@ -18804,7 +18804,7 @@
       </c>
       <c r="S215" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14T23:20:56Z</t>
+          <t>2026-10-15T23:09:49Z</t>
         </is>
       </c>
     </row>
@@ -18889,7 +18889,7 @@
       </c>
       <c r="S216" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14T23:20:56Z</t>
+          <t>2026-10-15T23:09:49Z</t>
         </is>
       </c>
     </row>
@@ -18978,7 +18978,7 @@
       </c>
       <c r="S217" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14T23:20:56Z</t>
+          <t>2026-10-15T23:09:49Z</t>
         </is>
       </c>
     </row>
@@ -19067,7 +19067,7 @@
       </c>
       <c r="S218" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14T23:20:56Z</t>
+          <t>2026-10-15T23:09:49Z</t>
         </is>
       </c>
     </row>
@@ -19152,7 +19152,7 @@
       </c>
       <c r="S219" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14T23:20:56Z</t>
+          <t>2026-10-15T23:09:49Z</t>
         </is>
       </c>
     </row>
@@ -19241,7 +19241,7 @@
       </c>
       <c r="S220" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14T23:20:56Z</t>
+          <t>2026-10-15T23:09:49Z</t>
         </is>
       </c>
     </row>
@@ -19330,7 +19330,7 @@
       </c>
       <c r="S221" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14T23:20:56Z</t>
+          <t>2026-10-15T23:09:49Z</t>
         </is>
       </c>
     </row>
@@ -19415,7 +19415,7 @@
       </c>
       <c r="S222" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14T23:20:56Z</t>
+          <t>2026-10-15T23:09:49Z</t>
         </is>
       </c>
     </row>
@@ -19504,7 +19504,7 @@
       </c>
       <c r="S223" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14T23:20:56Z</t>
+          <t>2026-10-15T23:09:49Z</t>
         </is>
       </c>
     </row>
@@ -19593,7 +19593,7 @@
       </c>
       <c r="S224" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14T23:20:56Z</t>
+          <t>2026-10-15T23:09:49Z</t>
         </is>
       </c>
     </row>
@@ -19678,7 +19678,7 @@
       </c>
       <c r="S225" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14T23:20:56Z</t>
+          <t>2026-10-15T23:09:49Z</t>
         </is>
       </c>
     </row>
@@ -19767,7 +19767,7 @@
       </c>
       <c r="S226" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14T23:20:56Z</t>
+          <t>2026-10-15T23:09:49Z</t>
         </is>
       </c>
     </row>
@@ -19856,7 +19856,7 @@
       </c>
       <c r="S227" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14T23:20:56Z</t>
+          <t>2026-10-15T23:09:49Z</t>
         </is>
       </c>
     </row>
@@ -19941,7 +19941,7 @@
       </c>
       <c r="S228" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14T23:20:56Z</t>
+          <t>2026-10-15T23:09:49Z</t>
         </is>
       </c>
     </row>
@@ -20030,7 +20030,7 @@
       </c>
       <c r="S229" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14T23:20:56Z</t>
+          <t>2026-10-15T23:09:49Z</t>
         </is>
       </c>
     </row>
@@ -20119,7 +20119,7 @@
       </c>
       <c r="S230" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14T23:20:56Z</t>
+          <t>2026-10-15T23:09:49Z</t>
         </is>
       </c>
     </row>
@@ -20204,7 +20204,7 @@
       </c>
       <c r="S231" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14T23:20:56Z</t>
+          <t>2026-10-15T23:09:49Z</t>
         </is>
       </c>
     </row>
@@ -20293,7 +20293,7 @@
       </c>
       <c r="S232" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14T23:20:56Z</t>
+          <t>2026-10-15T23:09:49Z</t>
         </is>
       </c>
     </row>
@@ -20382,7 +20382,7 @@
       </c>
       <c r="S233" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14T23:20:56Z</t>
+          <t>2026-10-15T23:09:49Z</t>
         </is>
       </c>
     </row>
@@ -20467,7 +20467,7 @@
       </c>
       <c r="S234" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14T23:20:56Z</t>
+          <t>2026-10-15T23:09:49Z</t>
         </is>
       </c>
     </row>
@@ -20556,7 +20556,7 @@
       </c>
       <c r="S235" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14T23:20:56Z</t>
+          <t>2026-10-15T23:09:49Z</t>
         </is>
       </c>
     </row>
@@ -20645,7 +20645,7 @@
       </c>
       <c r="S236" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14T23:20:56Z</t>
+          <t>2026-10-15T23:09:49Z</t>
         </is>
       </c>
     </row>
@@ -20730,7 +20730,7 @@
       </c>
       <c r="S237" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14T23:20:56Z</t>
+          <t>2026-10-15T23:09:49Z</t>
         </is>
       </c>
     </row>
@@ -20819,7 +20819,7 @@
       </c>
       <c r="S238" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14T23:20:56Z</t>
+          <t>2026-10-15T23:09:49Z</t>
         </is>
       </c>
     </row>
@@ -20908,7 +20908,7 @@
       </c>
       <c r="S239" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14T23:20:56Z</t>
+          <t>2026-10-15T23:09:49Z</t>
         </is>
       </c>
     </row>
@@ -20997,7 +20997,7 @@
       </c>
       <c r="S240" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14T23:20:56Z</t>
+          <t>2026-10-15T23:09:49Z</t>
         </is>
       </c>
     </row>
@@ -21086,7 +21086,7 @@
       </c>
       <c r="S241" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14T23:20:56Z</t>
+          <t>2026-10-15T23:09:49Z</t>
         </is>
       </c>
     </row>
@@ -21175,7 +21175,7 @@
       </c>
       <c r="S242" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14T23:20:56Z</t>
+          <t>2026-10-15T23:09:49Z</t>
         </is>
       </c>
     </row>
@@ -21264,7 +21264,7 @@
       </c>
       <c r="S243" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14T23:20:56Z</t>
+          <t>2026-10-15T23:09:49Z</t>
         </is>
       </c>
     </row>
@@ -21353,7 +21353,7 @@
       </c>
       <c r="S244" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14T23:20:56Z</t>
+          <t>2026-10-15T23:09:49Z</t>
         </is>
       </c>
     </row>
@@ -21442,7 +21442,7 @@
       </c>
       <c r="S245" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14T23:20:56Z</t>
+          <t>2026-10-15T23:09:49Z</t>
         </is>
       </c>
     </row>
@@ -21531,7 +21531,7 @@
       </c>
       <c r="S246" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14T23:20:56Z</t>
+          <t>2026-10-15T23:09:49Z</t>
         </is>
       </c>
     </row>
@@ -21620,7 +21620,7 @@
       </c>
       <c r="S247" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14T23:20:56Z</t>
+          <t>2026-10-15T23:09:49Z</t>
         </is>
       </c>
     </row>
@@ -21709,7 +21709,7 @@
       </c>
       <c r="S248" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14T23:20:56Z</t>
+          <t>2026-10-15T23:09:49Z</t>
         </is>
       </c>
     </row>
@@ -21798,7 +21798,7 @@
       </c>
       <c r="S249" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14T23:20:56Z</t>
+          <t>2026-10-15T23:09:49Z</t>
         </is>
       </c>
     </row>
@@ -21887,7 +21887,7 @@
       </c>
       <c r="S250" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14T23:20:56Z</t>
+          <t>2026-10-15T23:09:49Z</t>
         </is>
       </c>
     </row>
@@ -22019,7 +22019,7 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14T23:20:56Z</t>
+          <t>2026-10-15T23:09:49Z</t>
         </is>
       </c>
     </row>
@@ -22099,7 +22099,7 @@
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>{"dataset_id": "bcv_pib_sector_institucional_anual", "title": "Producto interno bruto por sector institucional anual", "table": "Variaciones porcentuales", "source_file": "5_2_1_si_anual.xlsx", "base": "2007", "price_type": "Precios constantes", "measure": "Variación porcentual interanual", "frequency": "Anual", "period": "2025", "year": 2025, "quarter": null, "classification": "Sector institucional", "component": "Impuestos netos sobre los productos", "value": 10.600260421283764, "unit": "Porcentaje", "status": "Preliminar", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/cuentas_macroeconomicas/5_2_1_si_anual.xlsx", "fetched_at": "2026-10-14T23:20:56Z"}</t>
+          <t>{"dataset_id": "bcv_pib_sector_institucional_anual", "title": "Producto interno bruto por sector institucional anual", "table": "Variaciones porcentuales", "source_file": "5_2_1_si_anual.xlsx", "base": "2007", "price_type": "Precios constantes", "measure": "Variación porcentual interanual", "frequency": "Anual", "period": "2025", "year": 2025, "quarter": null, "classification": "Sector institucional", "component": "Impuestos netos sobre los productos", "value": 10.600260421283764, "unit": "Porcentaje", "status": "Preliminar", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/cuentas_macroeconomicas/5_2_1_si_anual.xlsx", "fetched_at": "2026-10-15T23:09:49Z"}</t>
         </is>
       </c>
     </row>

--- a/assets/data/bcv/excel/ove_bcv_pib_sector_institucional_anual.xlsx
+++ b/assets/data/bcv/excel/ove_bcv_pib_sector_institucional_anual.xlsx
@@ -736,7 +736,7 @@
       </c>
       <c r="S7" s="4" t="inlineStr">
         <is>
-          <t>2026-10-15T23:09:49Z</t>
+          <t>2026-10-16T22:56:27Z</t>
         </is>
       </c>
     </row>
@@ -821,7 +821,7 @@
       </c>
       <c r="S8" s="4" t="inlineStr">
         <is>
-          <t>2026-10-15T23:09:49Z</t>
+          <t>2026-10-16T22:56:27Z</t>
         </is>
       </c>
     </row>
@@ -906,7 +906,7 @@
       </c>
       <c r="S9" s="4" t="inlineStr">
         <is>
-          <t>2026-10-15T23:09:49Z</t>
+          <t>2026-10-16T22:56:27Z</t>
         </is>
       </c>
     </row>
@@ -991,7 +991,7 @@
       </c>
       <c r="S10" s="4" t="inlineStr">
         <is>
-          <t>2026-10-15T23:09:49Z</t>
+          <t>2026-10-16T22:56:27Z</t>
         </is>
       </c>
     </row>
@@ -1076,7 +1076,7 @@
       </c>
       <c r="S11" s="4" t="inlineStr">
         <is>
-          <t>2026-10-15T23:09:49Z</t>
+          <t>2026-10-16T22:56:27Z</t>
         </is>
       </c>
     </row>
@@ -1161,7 +1161,7 @@
       </c>
       <c r="S12" s="4" t="inlineStr">
         <is>
-          <t>2026-10-15T23:09:49Z</t>
+          <t>2026-10-16T22:56:27Z</t>
         </is>
       </c>
     </row>
@@ -1246,7 +1246,7 @@
       </c>
       <c r="S13" s="4" t="inlineStr">
         <is>
-          <t>2026-10-15T23:09:49Z</t>
+          <t>2026-10-16T22:56:27Z</t>
         </is>
       </c>
     </row>
@@ -1331,7 +1331,7 @@
       </c>
       <c r="S14" s="4" t="inlineStr">
         <is>
-          <t>2026-10-15T23:09:49Z</t>
+          <t>2026-10-16T22:56:27Z</t>
         </is>
       </c>
     </row>
@@ -1416,7 +1416,7 @@
       </c>
       <c r="S15" s="4" t="inlineStr">
         <is>
-          <t>2026-10-15T23:09:49Z</t>
+          <t>2026-10-16T22:56:27Z</t>
         </is>
       </c>
     </row>
@@ -1501,7 +1501,7 @@
       </c>
       <c r="S16" s="4" t="inlineStr">
         <is>
-          <t>2026-10-15T23:09:49Z</t>
+          <t>2026-10-16T22:56:27Z</t>
         </is>
       </c>
     </row>
@@ -1586,7 +1586,7 @@
       </c>
       <c r="S17" s="4" t="inlineStr">
         <is>
-          <t>2026-10-15T23:09:49Z</t>
+          <t>2026-10-16T22:56:27Z</t>
         </is>
       </c>
     </row>
@@ -1671,7 +1671,7 @@
       </c>
       <c r="S18" s="4" t="inlineStr">
         <is>
-          <t>2026-10-15T23:09:49Z</t>
+          <t>2026-10-16T22:56:27Z</t>
         </is>
       </c>
     </row>
@@ -1756,7 +1756,7 @@
       </c>
       <c r="S19" s="4" t="inlineStr">
         <is>
-          <t>2026-10-15T23:09:49Z</t>
+          <t>2026-10-16T22:56:27Z</t>
         </is>
       </c>
     </row>
@@ -1841,7 +1841,7 @@
       </c>
       <c r="S20" s="4" t="inlineStr">
         <is>
-          <t>2026-10-15T23:09:49Z</t>
+          <t>2026-10-16T22:56:27Z</t>
         </is>
       </c>
     </row>
@@ -1926,7 +1926,7 @@
       </c>
       <c r="S21" s="4" t="inlineStr">
         <is>
-          <t>2026-10-15T23:09:49Z</t>
+          <t>2026-10-16T22:56:27Z</t>
         </is>
       </c>
     </row>
@@ -2011,7 +2011,7 @@
       </c>
       <c r="S22" s="4" t="inlineStr">
         <is>
-          <t>2026-10-15T23:09:49Z</t>
+          <t>2026-10-16T22:56:27Z</t>
         </is>
       </c>
     </row>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="S23" s="4" t="inlineStr">
         <is>
-          <t>2026-10-15T23:09:49Z</t>
+          <t>2026-10-16T22:56:27Z</t>
         </is>
       </c>
     </row>
@@ -2181,7 +2181,7 @@
       </c>
       <c r="S24" s="4" t="inlineStr">
         <is>
-          <t>2026-10-15T23:09:49Z</t>
+          <t>2026-10-16T22:56:27Z</t>
         </is>
       </c>
     </row>
@@ -2266,7 +2266,7 @@
       </c>
       <c r="S25" s="4" t="inlineStr">
         <is>
-          <t>2026-10-15T23:09:49Z</t>
+          <t>2026-10-16T22:56:27Z</t>
         </is>
       </c>
     </row>
@@ -2351,7 +2351,7 @@
       </c>
       <c r="S26" s="4" t="inlineStr">
         <is>
-          <t>2026-10-15T23:09:49Z</t>
+          <t>2026-10-16T22:56:27Z</t>
         </is>
       </c>
     </row>
@@ -2436,7 +2436,7 @@
       </c>
       <c r="S27" s="4" t="inlineStr">
         <is>
-          <t>2026-10-15T23:09:49Z</t>
+          <t>2026-10-16T22:56:27Z</t>
         </is>
       </c>
     </row>
@@ -2525,7 +2525,7 @@
       </c>
       <c r="S28" s="4" t="inlineStr">
         <is>
-          <t>2026-10-15T23:09:49Z</t>
+          <t>2026-10-16T22:56:27Z</t>
         </is>
       </c>
     </row>
@@ -2614,7 +2614,7 @@
       </c>
       <c r="S29" s="4" t="inlineStr">
         <is>
-          <t>2026-10-15T23:09:49Z</t>
+          <t>2026-10-16T22:56:27Z</t>
         </is>
       </c>
     </row>
@@ -2699,7 +2699,7 @@
       </c>
       <c r="S30" s="4" t="inlineStr">
         <is>
-          <t>2026-10-15T23:09:49Z</t>
+          <t>2026-10-16T22:56:27Z</t>
         </is>
       </c>
     </row>
@@ -2788,7 +2788,7 @@
       </c>
       <c r="S31" s="4" t="inlineStr">
         <is>
-          <t>2026-10-15T23:09:49Z</t>
+          <t>2026-10-16T22:56:27Z</t>
         </is>
       </c>
     </row>
@@ -2877,7 +2877,7 @@
       </c>
       <c r="S32" s="4" t="inlineStr">
         <is>
-          <t>2026-10-15T23:09:49Z</t>
+          <t>2026-10-16T22:56:27Z</t>
         </is>
       </c>
     </row>
@@ -2962,7 +2962,7 @@
       </c>
       <c r="S33" s="4" t="inlineStr">
         <is>
-          <t>2026-10-15T23:09:49Z</t>
+          <t>2026-10-16T22:56:27Z</t>
         </is>
       </c>
     </row>
@@ -3051,7 +3051,7 @@
       </c>
       <c r="S34" s="4" t="inlineStr">
         <is>
-          <t>2026-10-15T23:09:49Z</t>
+          <t>2026-10-16T22:56:27Z</t>
         </is>
       </c>
     </row>
@@ -3140,7 +3140,7 @@
       </c>
       <c r="S35" s="4" t="inlineStr">
         <is>
-          <t>2026-10-15T23:09:49Z</t>
+          <t>2026-10-16T22:56:27Z</t>
         </is>
       </c>
     </row>
@@ -3225,7 +3225,7 @@
       </c>
       <c r="S36" s="4" t="inlineStr">
         <is>
-          <t>2026-10-15T23:09:49Z</t>
+          <t>2026-10-16T22:56:27Z</t>
         </is>
       </c>
     </row>
@@ -3314,7 +3314,7 @@
       </c>
       <c r="S37" s="4" t="inlineStr">
         <is>
-          <t>2026-10-15T23:09:49Z</t>
+          <t>2026-10-16T22:56:27Z</t>
         </is>
       </c>
     </row>
@@ -3403,7 +3403,7 @@
       </c>
       <c r="S38" s="4" t="inlineStr">
         <is>
-          <t>2026-10-15T23:09:49Z</t>
+          <t>2026-10-16T22:56:27Z</t>
         </is>
       </c>
     </row>
@@ -3488,7 +3488,7 @@
       </c>
       <c r="S39" s="4" t="inlineStr">
         <is>
-          <t>2026-10-15T23:09:49Z</t>
+          <t>2026-10-16T22:56:27Z</t>
         </is>
       </c>
     </row>
@@ -3577,7 +3577,7 @@
       </c>
       <c r="S40" s="4" t="inlineStr">
         <is>
-          <t>2026-10-15T23:09:49Z</t>
+          <t>2026-10-16T22:56:27Z</t>
         </is>
       </c>
     </row>
@@ -3666,7 +3666,7 @@
       </c>
       <c r="S41" s="4" t="inlineStr">
         <is>
-          <t>2026-10-15T23:09:49Z</t>
+          <t>2026-10-16T22:56:27Z</t>
         </is>
       </c>
     </row>
@@ -3751,7 +3751,7 @@
       </c>
       <c r="S42" s="4" t="inlineStr">
         <is>
-          <t>2026-10-15T23:09:49Z</t>
+          <t>2026-10-16T22:56:27Z</t>
         </is>
       </c>
     </row>
@@ -3840,7 +3840,7 @@
       </c>
       <c r="S43" s="4" t="inlineStr">
         <is>
-          <t>2026-10-15T23:09:49Z</t>
+          <t>2026-10-16T22:56:27Z</t>
         </is>
       </c>
     </row>
@@ -3929,7 +3929,7 @@
       </c>
       <c r="S44" s="4" t="inlineStr">
         <is>
-          <t>2026-10-15T23:09:49Z</t>
+          <t>2026-10-16T22:56:27Z</t>
         </is>
       </c>
     </row>
@@ -4014,7 +4014,7 @@
       </c>
       <c r="S45" s="4" t="inlineStr">
         <is>
-          <t>2026-10-15T23:09:49Z</t>
+          <t>2026-10-16T22:56:27Z</t>
         </is>
       </c>
     </row>
@@ -4103,7 +4103,7 @@
       </c>
       <c r="S46" s="4" t="inlineStr">
         <is>
-          <t>2026-10-15T23:09:49Z</t>
+          <t>2026-10-16T22:56:27Z</t>
         </is>
       </c>
     </row>
@@ -4192,7 +4192,7 @@
       </c>
       <c r="S47" s="4" t="inlineStr">
         <is>
-          <t>2026-10-15T23:09:49Z</t>
+          <t>2026-10-16T22:56:27Z</t>
         </is>
       </c>
     </row>
@@ -4277,7 +4277,7 @@
       </c>
       <c r="S48" s="4" t="inlineStr">
         <is>
-          <t>2026-10-15T23:09:49Z</t>
+          <t>2026-10-16T22:56:27Z</t>
         </is>
       </c>
     </row>
@@ -4366,7 +4366,7 @@
       </c>
       <c r="S49" s="4" t="inlineStr">
         <is>
-          <t>2026-10-15T23:09:49Z</t>
+          <t>2026-10-16T22:56:27Z</t>
         </is>
       </c>
     </row>
@@ -4455,7 +4455,7 @@
       </c>
       <c r="S50" s="4" t="inlineStr">
         <is>
-          <t>2026-10-15T23:09:49Z</t>
+          <t>2026-10-16T22:56:27Z</t>
         </is>
       </c>
     </row>
@@ -4540,7 +4540,7 @@
       </c>
       <c r="S51" s="4" t="inlineStr">
         <is>
-          <t>2026-10-15T23:09:49Z</t>
+          <t>2026-10-16T22:56:27Z</t>
         </is>
       </c>
     </row>
@@ -4629,7 +4629,7 @@
       </c>
       <c r="S52" s="4" t="inlineStr">
         <is>
-          <t>2026-10-15T23:09:49Z</t>
+          <t>2026-10-16T22:56:27Z</t>
         </is>
       </c>
     </row>
@@ -4718,7 +4718,7 @@
       </c>
       <c r="S53" s="4" t="inlineStr">
         <is>
-          <t>2026-10-15T23:09:49Z</t>
+          <t>2026-10-16T22:56:27Z</t>
         </is>
       </c>
     </row>
@@ -4803,7 +4803,7 @@
       </c>
       <c r="S54" s="4" t="inlineStr">
         <is>
-          <t>2026-10-15T23:09:49Z</t>
+          <t>2026-10-16T22:56:27Z</t>
         </is>
       </c>
     </row>
@@ -4892,7 +4892,7 @@
       </c>
       <c r="S55" s="4" t="inlineStr">
         <is>
-          <t>2026-10-15T23:09:49Z</t>
+          <t>2026-10-16T22:56:27Z</t>
         </is>
       </c>
     </row>
@@ -4981,7 +4981,7 @@
       </c>
       <c r="S56" s="4" t="inlineStr">
         <is>
-          <t>2026-10-15T23:09:49Z</t>
+          <t>2026-10-16T22:56:27Z</t>
         </is>
       </c>
     </row>
@@ -5070,7 +5070,7 @@
       </c>
       <c r="S57" s="4" t="inlineStr">
         <is>
-          <t>2026-10-15T23:09:49Z</t>
+          <t>2026-10-16T22:56:27Z</t>
         </is>
       </c>
     </row>
@@ -5159,7 +5159,7 @@
       </c>
       <c r="S58" s="4" t="inlineStr">
         <is>
-          <t>2026-10-15T23:09:49Z</t>
+          <t>2026-10-16T22:56:27Z</t>
         </is>
       </c>
     </row>
@@ -5248,7 +5248,7 @@
       </c>
       <c r="S59" s="4" t="inlineStr">
         <is>
-          <t>2026-10-15T23:09:49Z</t>
+          <t>2026-10-16T22:56:27Z</t>
         </is>
       </c>
     </row>
@@ -5337,7 +5337,7 @@
       </c>
       <c r="S60" s="4" t="inlineStr">
         <is>
-          <t>2026-10-15T23:09:49Z</t>
+          <t>2026-10-16T22:56:27Z</t>
         </is>
       </c>
     </row>
@@ -5426,7 +5426,7 @@
       </c>
       <c r="S61" s="4" t="inlineStr">
         <is>
-          <t>2026-10-15T23:09:49Z</t>
+          <t>2026-10-16T22:56:27Z</t>
         </is>
       </c>
     </row>
@@ -5515,7 +5515,7 @@
       </c>
       <c r="S62" s="4" t="inlineStr">
         <is>
-          <t>2026-10-15T23:09:49Z</t>
+          <t>2026-10-16T22:56:27Z</t>
         </is>
       </c>
     </row>
@@ -5604,7 +5604,7 @@
       </c>
       <c r="S63" s="4" t="inlineStr">
         <is>
-          <t>2026-10-15T23:09:49Z</t>
+          <t>2026-10-16T22:56:27Z</t>
         </is>
       </c>
     </row>
@@ -5693,7 +5693,7 @@
       </c>
       <c r="S64" s="4" t="inlineStr">
         <is>
-          <t>2026-10-15T23:09:49Z</t>
+          <t>2026-10-16T22:56:27Z</t>
         </is>
       </c>
     </row>
@@ -5782,7 +5782,7 @@
       </c>
       <c r="S65" s="4" t="inlineStr">
         <is>
-          <t>2026-10-15T23:09:49Z</t>
+          <t>2026-10-16T22:56:27Z</t>
         </is>
       </c>
     </row>
@@ -5871,7 +5871,7 @@
       </c>
       <c r="S66" s="4" t="inlineStr">
         <is>
-          <t>2026-10-15T23:09:49Z</t>
+          <t>2026-10-16T22:56:27Z</t>
         </is>
       </c>
     </row>
@@ -5960,7 +5960,7 @@
       </c>
       <c r="S67" s="4" t="inlineStr">
         <is>
-          <t>2026-10-15T23:09:49Z</t>
+          <t>2026-10-16T22:56:27Z</t>
         </is>
       </c>
     </row>
@@ -6045,7 +6045,7 @@
       </c>
       <c r="S68" s="4" t="inlineStr">
         <is>
-          <t>2026-10-15T23:09:49Z</t>
+          <t>2026-10-16T22:56:27Z</t>
         </is>
       </c>
     </row>
@@ -6130,7 +6130,7 @@
       </c>
       <c r="S69" s="4" t="inlineStr">
         <is>
-          <t>2026-10-15T23:09:49Z</t>
+          <t>2026-10-16T22:56:27Z</t>
         </is>
       </c>
     </row>
@@ -6215,7 +6215,7 @@
       </c>
       <c r="S70" s="4" t="inlineStr">
         <is>
-          <t>2026-10-15T23:09:49Z</t>
+          <t>2026-10-16T22:56:27Z</t>
         </is>
       </c>
     </row>
@@ -6300,7 +6300,7 @@
       </c>
       <c r="S71" s="4" t="inlineStr">
         <is>
-          <t>2026-10-15T23:09:49Z</t>
+          <t>2026-10-16T22:56:27Z</t>
         </is>
       </c>
     </row>
@@ -6385,7 +6385,7 @@
       </c>
       <c r="S72" s="4" t="inlineStr">
         <is>
-          <t>2026-10-15T23:09:49Z</t>
+          <t>2026-10-16T22:56:27Z</t>
         </is>
       </c>
     </row>
@@ -6470,7 +6470,7 @@
       </c>
       <c r="S73" s="4" t="inlineStr">
         <is>
-          <t>2026-10-15T23:09:49Z</t>
+          <t>2026-10-16T22:56:27Z</t>
         </is>
       </c>
     </row>
@@ -6555,7 +6555,7 @@
       </c>
       <c r="S74" s="4" t="inlineStr">
         <is>
-          <t>2026-10-15T23:09:49Z</t>
+          <t>2026-10-16T22:56:27Z</t>
         </is>
       </c>
     </row>
@@ -6640,7 +6640,7 @@
       </c>
       <c r="S75" s="4" t="inlineStr">
         <is>
-          <t>2026-10-15T23:09:49Z</t>
+          <t>2026-10-16T22:56:27Z</t>
         </is>
       </c>
     </row>
@@ -6725,7 +6725,7 @@
       </c>
       <c r="S76" s="4" t="inlineStr">
         <is>
-          <t>2026-10-15T23:09:49Z</t>
+          <t>2026-10-16T22:56:27Z</t>
         </is>
       </c>
     </row>
@@ -6810,7 +6810,7 @@
       </c>
       <c r="S77" s="4" t="inlineStr">
         <is>
-          <t>2026-10-15T23:09:49Z</t>
+          <t>2026-10-16T22:56:27Z</t>
         </is>
       </c>
     </row>
@@ -6895,7 +6895,7 @@
       </c>
       <c r="S78" s="4" t="inlineStr">
         <is>
-          <t>2026-10-15T23:09:49Z</t>
+          <t>2026-10-16T22:56:27Z</t>
         </is>
       </c>
     </row>
@@ -6980,7 +6980,7 @@
       </c>
       <c r="S79" s="4" t="inlineStr">
         <is>
-          <t>2026-10-15T23:09:49Z</t>
+          <t>2026-10-16T22:56:27Z</t>
         </is>
       </c>
     </row>
@@ -7065,7 +7065,7 @@
       </c>
       <c r="S80" s="4" t="inlineStr">
         <is>
-          <t>2026-10-15T23:09:49Z</t>
+          <t>2026-10-16T22:56:27Z</t>
         </is>
       </c>
     </row>
@@ -7150,7 +7150,7 @@
       </c>
       <c r="S81" s="4" t="inlineStr">
         <is>
-          <t>2026-10-15T23:09:49Z</t>
+          <t>2026-10-16T22:56:27Z</t>
         </is>
       </c>
     </row>
@@ -7235,7 +7235,7 @@
       </c>
       <c r="S82" s="4" t="inlineStr">
         <is>
-          <t>2026-10-15T23:09:49Z</t>
+          <t>2026-10-16T22:56:27Z</t>
         </is>
       </c>
     </row>
@@ -7320,7 +7320,7 @@
       </c>
       <c r="S83" s="4" t="inlineStr">
         <is>
-          <t>2026-10-15T23:09:49Z</t>
+          <t>2026-10-16T22:56:27Z</t>
         </is>
       </c>
     </row>
@@ -7405,7 +7405,7 @@
       </c>
       <c r="S84" s="4" t="inlineStr">
         <is>
-          <t>2026-10-15T23:09:49Z</t>
+          <t>2026-10-16T22:56:27Z</t>
         </is>
       </c>
     </row>
@@ -7490,7 +7490,7 @@
       </c>
       <c r="S85" s="4" t="inlineStr">
         <is>
-          <t>2026-10-15T23:09:49Z</t>
+          <t>2026-10-16T22:56:27Z</t>
         </is>
       </c>
     </row>
@@ -7575,7 +7575,7 @@
       </c>
       <c r="S86" s="4" t="inlineStr">
         <is>
-          <t>2026-10-15T23:09:49Z</t>
+          <t>2026-10-16T22:56:27Z</t>
         </is>
       </c>
     </row>
@@ -7660,7 +7660,7 @@
       </c>
       <c r="S87" s="4" t="inlineStr">
         <is>
-          <t>2026-10-15T23:09:49Z</t>
+          <t>2026-10-16T22:56:27Z</t>
         </is>
       </c>
     </row>
@@ -7745,7 +7745,7 @@
       </c>
       <c r="S88" s="4" t="inlineStr">
         <is>
-          <t>2026-10-15T23:09:49Z</t>
+          <t>2026-10-16T22:56:27Z</t>
         </is>
       </c>
     </row>
@@ -7834,7 +7834,7 @@
       </c>
       <c r="S89" s="4" t="inlineStr">
         <is>
-          <t>2026-10-15T23:09:49Z</t>
+          <t>2026-10-16T22:56:27Z</t>
         </is>
       </c>
     </row>
@@ -7923,7 +7923,7 @@
       </c>
       <c r="S90" s="4" t="inlineStr">
         <is>
-          <t>2026-10-15T23:09:49Z</t>
+          <t>2026-10-16T22:56:27Z</t>
         </is>
       </c>
     </row>
@@ -8008,7 +8008,7 @@
       </c>
       <c r="S91" s="4" t="inlineStr">
         <is>
-          <t>2026-10-15T23:09:49Z</t>
+          <t>2026-10-16T22:56:27Z</t>
         </is>
       </c>
     </row>
@@ -8097,7 +8097,7 @@
       </c>
       <c r="S92" s="4" t="inlineStr">
         <is>
-          <t>2026-10-15T23:09:49Z</t>
+          <t>2026-10-16T22:56:27Z</t>
         </is>
       </c>
     </row>
@@ -8186,7 +8186,7 @@
       </c>
       <c r="S93" s="4" t="inlineStr">
         <is>
-          <t>2026-10-15T23:09:49Z</t>
+          <t>2026-10-16T22:56:27Z</t>
         </is>
       </c>
     </row>
@@ -8271,7 +8271,7 @@
       </c>
       <c r="S94" s="4" t="inlineStr">
         <is>
-          <t>2026-10-15T23:09:49Z</t>
+          <t>2026-10-16T22:56:27Z</t>
         </is>
       </c>
     </row>
@@ -8360,7 +8360,7 @@
       </c>
       <c r="S95" s="4" t="inlineStr">
         <is>
-          <t>2026-10-15T23:09:49Z</t>
+          <t>2026-10-16T22:56:27Z</t>
         </is>
       </c>
     </row>
@@ -8449,7 +8449,7 @@
       </c>
       <c r="S96" s="4" t="inlineStr">
         <is>
-          <t>2026-10-15T23:09:49Z</t>
+          <t>2026-10-16T22:56:27Z</t>
         </is>
       </c>
     </row>
@@ -8534,7 +8534,7 @@
       </c>
       <c r="S97" s="4" t="inlineStr">
         <is>
-          <t>2026-10-15T23:09:49Z</t>
+          <t>2026-10-16T22:56:27Z</t>
         </is>
       </c>
     </row>
@@ -8623,7 +8623,7 @@
       </c>
       <c r="S98" s="4" t="inlineStr">
         <is>
-          <t>2026-10-15T23:09:49Z</t>
+          <t>2026-10-16T22:56:27Z</t>
         </is>
       </c>
     </row>
@@ -8712,7 +8712,7 @@
       </c>
       <c r